--- a/Term_Examination_Schedule_S.Y._2026-2027_Optimized.xlsx
+++ b/Term_Examination_Schedule_S.Y._2026-2027_Optimized.xlsx
@@ -3475,7 +3475,7 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Grade  6</t>
+          <t>Grade 6</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
@@ -3531,7 +3531,7 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Grade  6</t>
+          <t>Grade 6</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
@@ -3587,7 +3587,7 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Grade  6</t>
+          <t>Grade 6</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
@@ -3643,7 +3643,7 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Grade  6</t>
+          <t>Grade 6</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
@@ -3699,7 +3699,7 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Grade  6</t>
+          <t>Grade 6</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
@@ -3755,7 +3755,7 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Grade  6</t>
+          <t>Grade 6</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
@@ -3811,7 +3811,7 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Grade  6</t>
+          <t>Grade 6</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
@@ -3867,7 +3867,7 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Grade  6</t>
+          <t>Grade 6</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
@@ -3923,7 +3923,7 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Grade  6</t>
+          <t>Grade 6</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
@@ -3979,7 +3979,7 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Grade  6</t>
+          <t>Grade 6</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
@@ -11763,7 +11763,7 @@
       </c>
       <c r="G203" t="inlineStr">
         <is>
-          <t>K2</t>
+          <t>Kinder 2</t>
         </is>
       </c>
       <c r="H203" t="inlineStr">
@@ -11787,7 +11787,7 @@
         </is>
       </c>
       <c r="L203" t="n">
-        <v>45</v>
+        <v>30</v>
       </c>
     </row>
     <row r="204">
@@ -11819,7 +11819,7 @@
       </c>
       <c r="G204" t="inlineStr">
         <is>
-          <t>K2</t>
+          <t>Kinder 2</t>
         </is>
       </c>
       <c r="H204" t="inlineStr">
@@ -11843,7 +11843,7 @@
         </is>
       </c>
       <c r="L204" t="n">
-        <v>45</v>
+        <v>30</v>
       </c>
     </row>
     <row r="205">
@@ -11875,7 +11875,7 @@
       </c>
       <c r="G205" t="inlineStr">
         <is>
-          <t>K2</t>
+          <t>Kinder 2</t>
         </is>
       </c>
       <c r="H205" t="inlineStr">
@@ -11899,7 +11899,7 @@
         </is>
       </c>
       <c r="L205" t="n">
-        <v>45</v>
+        <v>30</v>
       </c>
     </row>
     <row r="206">
@@ -11931,7 +11931,7 @@
       </c>
       <c r="G206" t="inlineStr">
         <is>
-          <t>K2</t>
+          <t>Kinder 2</t>
         </is>
       </c>
       <c r="H206" t="inlineStr">
@@ -11955,7 +11955,7 @@
         </is>
       </c>
       <c r="L206" t="n">
-        <v>45</v>
+        <v>30</v>
       </c>
     </row>
     <row r="207">
@@ -11987,7 +11987,7 @@
       </c>
       <c r="G207" t="inlineStr">
         <is>
-          <t>K1</t>
+          <t>Kinder 1</t>
         </is>
       </c>
       <c r="H207" t="inlineStr">
@@ -12011,7 +12011,7 @@
         </is>
       </c>
       <c r="L207" t="n">
-        <v>45</v>
+        <v>30</v>
       </c>
     </row>
     <row r="208">
@@ -12043,7 +12043,7 @@
       </c>
       <c r="G208" t="inlineStr">
         <is>
-          <t>K1</t>
+          <t>Kinder 1</t>
         </is>
       </c>
       <c r="H208" t="inlineStr">
@@ -12067,7 +12067,7 @@
         </is>
       </c>
       <c r="L208" t="n">
-        <v>45</v>
+        <v>30</v>
       </c>
     </row>
     <row r="209">
@@ -12099,7 +12099,7 @@
       </c>
       <c r="G209" t="inlineStr">
         <is>
-          <t>K1</t>
+          <t>Kinder 1</t>
         </is>
       </c>
       <c r="H209" t="inlineStr">
@@ -12123,7 +12123,7 @@
         </is>
       </c>
       <c r="L209" t="n">
-        <v>45</v>
+        <v>30</v>
       </c>
     </row>
     <row r="210">
@@ -12155,7 +12155,7 @@
       </c>
       <c r="G210" t="inlineStr">
         <is>
-          <t>K1</t>
+          <t>Kinder 1</t>
         </is>
       </c>
       <c r="H210" t="inlineStr">
@@ -12179,7 +12179,7 @@
         </is>
       </c>
       <c r="L210" t="n">
-        <v>45</v>
+        <v>30</v>
       </c>
     </row>
     <row r="211">
@@ -15291,7 +15291,7 @@
       </c>
       <c r="G266" t="inlineStr">
         <is>
-          <t>K2</t>
+          <t>Kinder 2</t>
         </is>
       </c>
       <c r="H266" t="inlineStr">
@@ -15315,7 +15315,7 @@
         </is>
       </c>
       <c r="L266" t="n">
-        <v>45</v>
+        <v>30</v>
       </c>
     </row>
     <row r="267">
@@ -15347,7 +15347,7 @@
       </c>
       <c r="G267" t="inlineStr">
         <is>
-          <t>K2</t>
+          <t>Kinder 2</t>
         </is>
       </c>
       <c r="H267" t="inlineStr">
@@ -15371,7 +15371,7 @@
         </is>
       </c>
       <c r="L267" t="n">
-        <v>45</v>
+        <v>30</v>
       </c>
     </row>
     <row r="268">
@@ -15403,7 +15403,7 @@
       </c>
       <c r="G268" t="inlineStr">
         <is>
-          <t>K2</t>
+          <t>Kinder 2</t>
         </is>
       </c>
       <c r="H268" t="inlineStr">
@@ -15427,7 +15427,7 @@
         </is>
       </c>
       <c r="L268" t="n">
-        <v>45</v>
+        <v>30</v>
       </c>
     </row>
     <row r="269">
@@ -15459,7 +15459,7 @@
       </c>
       <c r="G269" t="inlineStr">
         <is>
-          <t>K2</t>
+          <t>Kinder 2</t>
         </is>
       </c>
       <c r="H269" t="inlineStr">
@@ -15483,7 +15483,7 @@
         </is>
       </c>
       <c r="L269" t="n">
-        <v>45</v>
+        <v>30</v>
       </c>
     </row>
     <row r="270">

--- a/Term_Examination_Schedule_S.Y._2026-2027_Optimized.xlsx
+++ b/Term_Examination_Schedule_S.Y._2026-2027_Optimized.xlsx
@@ -7,7 +7,7 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Master Exam Schedule (Opt A)" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Exam Schedule (Option C)" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -488,11 +488,11 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>10:00 AM – 11:00 AM</t>
+          <t>07:30 AM – 08:30 AM</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -536,19 +536,19 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Saturday, September 6, 2026</t>
+          <t>Tuesday, September 2, 2026</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>08:45 AM – 09:45 AM</t>
+          <t>07:30 AM – 08:30 AM</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -600,11 +600,11 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>08:45 AM – 09:45 AM</t>
+          <t>07:30 AM – 08:30 AM</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -648,19 +648,19 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Sunday, September 7, 2026</t>
+          <t>Wednesday, September 3, 2026</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>07:30 AM – 08:30 AM</t>
+          <t>10:00 AM – 11:00 AM</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -712,11 +712,11 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>07:30 AM – 08:30 AM</t>
+          <t>10:00 AM – 11:00 AM</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -760,19 +760,19 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Tuesday, September 2, 2026</t>
+          <t>Wednesday, September 3, 2026</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>10:00 AM – 11:00 AM</t>
+          <t>08:45 AM – 09:45 AM</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -816,19 +816,19 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Saturday, September 6, 2026</t>
+          <t>Tuesday, September 2, 2026</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>10:00 AM – 11:00 AM</t>
+          <t>08:45 AM – 09:45 AM</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -872,19 +872,19 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Sunday, September 7, 2026</t>
+          <t>Wednesday, September 3, 2026</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>08:45 AM – 09:45 AM</t>
+          <t>10:00 AM – 11:00 AM</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -928,19 +928,19 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Wednesday, September 3, 2026</t>
+          <t>Saturday, September 6, 2026</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>07:30 AM – 08:30 AM</t>
+          <t>08:45 AM – 09:45 AM</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -984,11 +984,11 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Sunday, September 7, 2026</t>
+          <t>Saturday, September 6, 2026</t>
         </is>
       </c>
       <c r="C11" t="n">
@@ -1040,19 +1040,19 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
+        <v>2</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Wednesday, September 3, 2026</t>
+        </is>
+      </c>
+      <c r="C12" t="n">
         <v>3</v>
       </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>Saturday, September 6, 2026</t>
-        </is>
-      </c>
-      <c r="C12" t="n">
-        <v>1</v>
-      </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>07:30 AM – 08:30 AM</t>
+          <t>10:00 AM – 11:00 AM</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -1096,19 +1096,19 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Saturday, September 6, 2026</t>
+          <t>Wednesday, September 3, 2026</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>10:00 AM – 11:00 AM</t>
+          <t>08:45 AM – 09:45 AM</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -1152,19 +1152,19 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Tuesday, September 2, 2026</t>
+          <t>Wednesday, September 3, 2026</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>10:00 AM – 11:00 AM</t>
+          <t>07:30 AM – 08:30 AM</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -1208,19 +1208,19 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Wednesday, September 3, 2026</t>
+          <t>Tuesday, September 2, 2026</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>08:45 AM – 09:45 AM</t>
+          <t>10:00 AM – 11:00 AM</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -1376,19 +1376,19 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Wednesday, September 3, 2026</t>
+          <t>Saturday, September 6, 2026</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>07:30 AM – 08:30 AM</t>
+          <t>08:45 AM – 09:45 AM</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -1432,11 +1432,11 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Sunday, September 7, 2026</t>
+          <t>Saturday, September 6, 2026</t>
         </is>
       </c>
       <c r="C19" t="n">
@@ -1488,19 +1488,19 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Tuesday, September 2, 2026</t>
+          <t>Wednesday, September 3, 2026</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>08:45 AM – 09:45 AM</t>
+          <t>10:00 AM – 11:00 AM</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -1552,11 +1552,11 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>07:30 AM – 08:30 AM</t>
+          <t>10:00 AM – 11:00 AM</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -1600,19 +1600,19 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Sunday, September 7, 2026</t>
+          <t>Wednesday, September 3, 2026</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>10:00 AM – 11:00 AM</t>
+          <t>08:45 AM – 09:45 AM</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -1656,19 +1656,19 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Tuesday, September 2, 2026</t>
+          <t>Wednesday, September 3, 2026</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>10:00 AM – 11:00 AM</t>
+          <t>07:30 AM – 08:30 AM</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -1712,19 +1712,19 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Saturday, September 6, 2026</t>
+          <t>Tuesday, September 2, 2026</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>10:00 AM – 11:00 AM</t>
+          <t>08:45 AM – 09:45 AM</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -1768,19 +1768,19 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Wednesday, September 3, 2026</t>
+          <t>Tuesday, September 2, 2026</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>08:45 AM – 09:45 AM</t>
+          <t>07:30 AM – 08:30 AM</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -1824,19 +1824,19 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Sunday, September 7, 2026</t>
+          <t>Saturday, September 6, 2026</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>08:45 AM – 09:45 AM</t>
+          <t>10:00 AM – 11:00 AM</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -1880,19 +1880,19 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Sunday, September 7, 2026</t>
+          <t>Saturday, September 6, 2026</t>
         </is>
       </c>
       <c r="C27" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>10:00 AM – 11:00 AM</t>
+          <t>08:45 AM – 09:45 AM</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
@@ -1936,19 +1936,19 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Tuesday, September 2, 2026</t>
+          <t>Saturday, September 6, 2026</t>
         </is>
       </c>
       <c r="C28" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>10:00 AM – 11:00 AM</t>
+          <t>07:30 AM – 08:30 AM</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
@@ -1992,19 +1992,19 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Tuesday, September 2, 2026</t>
+          <t>Wednesday, September 3, 2026</t>
         </is>
       </c>
       <c r="C29" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>08:45 AM – 09:45 AM</t>
+          <t>10:00 AM – 11:00 AM</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
@@ -2048,19 +2048,19 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Sunday, September 7, 2026</t>
+          <t>Wednesday, September 3, 2026</t>
         </is>
       </c>
       <c r="C30" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>07:30 AM – 08:30 AM</t>
+          <t>08:45 AM – 09:45 AM</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
@@ -2104,11 +2104,11 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Saturday, September 6, 2026</t>
+          <t>Wednesday, September 3, 2026</t>
         </is>
       </c>
       <c r="C31" t="n">
@@ -2160,19 +2160,19 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
+        <v>1</v>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Tuesday, September 2, 2026</t>
+        </is>
+      </c>
+      <c r="C32" t="n">
         <v>3</v>
       </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>Saturday, September 6, 2026</t>
-        </is>
-      </c>
-      <c r="C32" t="n">
-        <v>2</v>
-      </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>08:45 AM – 09:45 AM</t>
+          <t>10:00 AM – 11:00 AM</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
@@ -2216,19 +2216,19 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Saturday, September 6, 2026</t>
+          <t>Tuesday, September 2, 2026</t>
         </is>
       </c>
       <c r="C33" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>10:00 AM – 11:00 AM</t>
+          <t>08:45 AM – 09:45 AM</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
@@ -2272,11 +2272,11 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Wednesday, September 3, 2026</t>
+          <t>Tuesday, September 2, 2026</t>
         </is>
       </c>
       <c r="C34" t="n">
@@ -2328,11 +2328,11 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Tuesday, September 2, 2026</t>
+          <t>Sunday, September 7, 2026</t>
         </is>
       </c>
       <c r="C35" t="n">
@@ -2384,11 +2384,11 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Sunday, September 7, 2026</t>
+          <t>Saturday, September 6, 2026</t>
         </is>
       </c>
       <c r="C36" t="n">
@@ -2448,11 +2448,11 @@
         </is>
       </c>
       <c r="C37" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>08:45 AM – 09:45 AM</t>
+          <t>10:00 AM – 11:00 AM</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
@@ -2552,19 +2552,19 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Tuesday, September 2, 2026</t>
+          <t>Saturday, September 6, 2026</t>
         </is>
       </c>
       <c r="C39" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>10:00 AM – 11:00 AM</t>
+          <t>07:30 AM – 08:30 AM</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
@@ -2608,19 +2608,19 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Sunday, September 7, 2026</t>
+          <t>Wednesday, September 3, 2026</t>
         </is>
       </c>
       <c r="C40" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>08:45 AM – 09:45 AM</t>
+          <t>07:30 AM – 08:30 AM</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
@@ -2720,19 +2720,19 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Sunday, September 7, 2026</t>
+          <t>Tuesday, September 2, 2026</t>
         </is>
       </c>
       <c r="C42" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>07:30 AM – 08:30 AM</t>
+          <t>10:00 AM – 11:00 AM</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
@@ -2784,11 +2784,11 @@
         </is>
       </c>
       <c r="C43" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>07:30 AM – 08:30 AM</t>
+          <t>08:45 AM – 09:45 AM</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
@@ -2832,19 +2832,19 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Saturday, September 6, 2026</t>
+          <t>Tuesday, September 2, 2026</t>
         </is>
       </c>
       <c r="C44" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>10:00 AM – 11:00 AM</t>
+          <t>07:30 AM – 08:30 AM</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
@@ -2888,19 +2888,19 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Wednesday, September 3, 2026</t>
+          <t>Sunday, September 7, 2026</t>
         </is>
       </c>
       <c r="C45" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>08:45 AM – 09:45 AM</t>
+          <t>07:30 AM – 08:30 AM</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
@@ -2944,19 +2944,19 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Sunday, September 7, 2026</t>
+          <t>Saturday, September 6, 2026</t>
         </is>
       </c>
       <c r="C46" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>08:45 AM – 09:45 AM</t>
+          <t>10:00 AM – 11:00 AM</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
@@ -3000,19 +3000,19 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
+        <v>2</v>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>Wednesday, September 3, 2026</t>
+        </is>
+      </c>
+      <c r="C47" t="n">
         <v>3</v>
       </c>
-      <c r="B47" t="inlineStr">
-        <is>
-          <t>Saturday, September 6, 2026</t>
-        </is>
-      </c>
-      <c r="C47" t="n">
-        <v>2</v>
-      </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>08:45 AM – 09:45 AM</t>
+          <t>10:00 AM – 11:00 AM</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
@@ -3056,19 +3056,19 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Sunday, September 7, 2026</t>
+          <t>Wednesday, September 3, 2026</t>
         </is>
       </c>
       <c r="C48" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>10:00 AM – 11:00 AM</t>
+          <t>08:45 AM – 09:45 AM</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
@@ -3120,11 +3120,11 @@
         </is>
       </c>
       <c r="C49" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>07:30 AM – 08:30 AM</t>
+          <t>08:45 AM – 09:45 AM</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
@@ -3176,11 +3176,11 @@
         </is>
       </c>
       <c r="C50" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>10:00 AM – 11:00 AM</t>
+          <t>07:30 AM – 08:30 AM</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
@@ -3224,11 +3224,11 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Tuesday, September 2, 2026</t>
+          <t>Wednesday, September 3, 2026</t>
         </is>
       </c>
       <c r="C51" t="n">
@@ -3392,19 +3392,19 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Wednesday, September 3, 2026</t>
+          <t>Tuesday, September 2, 2026</t>
         </is>
       </c>
       <c r="C54" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>10:00 AM – 11:00 AM</t>
+          <t>07:30 AM – 08:30 AM</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
@@ -3448,19 +3448,19 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Tuesday, September 2, 2026</t>
+          <t>Sunday, September 7, 2026</t>
         </is>
       </c>
       <c r="C55" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>08:45 AM – 09:45 AM</t>
+          <t>07:30 AM – 08:30 AM</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
@@ -3512,11 +3512,11 @@
         </is>
       </c>
       <c r="C56" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>08:45 AM – 09:45 AM</t>
+          <t>10:00 AM – 11:00 AM</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
@@ -3568,11 +3568,11 @@
         </is>
       </c>
       <c r="C57" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>07:30 AM – 08:30 AM</t>
+          <t>08:45 AM – 09:45 AM</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
@@ -3672,19 +3672,19 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Tuesday, September 2, 2026</t>
+          <t>Wednesday, September 3, 2026</t>
         </is>
       </c>
       <c r="C59" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>07:30 AM – 08:30 AM</t>
+          <t>08:45 AM – 09:45 AM</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
@@ -3728,19 +3728,19 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Sunday, September 7, 2026</t>
+          <t>Saturday, September 6, 2026</t>
         </is>
       </c>
       <c r="C60" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>08:45 AM – 09:45 AM</t>
+          <t>07:30 AM – 08:30 AM</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
@@ -3784,19 +3784,19 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Saturday, September 6, 2026</t>
+          <t>Wednesday, September 3, 2026</t>
         </is>
       </c>
       <c r="C61" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>10:00 AM – 11:00 AM</t>
+          <t>07:30 AM – 08:30 AM</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
@@ -3840,19 +3840,19 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Sunday, September 7, 2026</t>
+          <t>Tuesday, September 2, 2026</t>
         </is>
       </c>
       <c r="C62" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>07:30 AM – 08:30 AM</t>
+          <t>10:00 AM – 11:00 AM</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
@@ -3904,11 +3904,11 @@
         </is>
       </c>
       <c r="C63" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>10:00 AM – 11:00 AM</t>
+          <t>08:45 AM – 09:45 AM</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
@@ -3952,19 +3952,19 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Sunday, September 7, 2026</t>
+          <t>Tuesday, September 2, 2026</t>
         </is>
       </c>
       <c r="C64" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>10:00 AM – 11:00 AM</t>
+          <t>07:30 AM – 08:30 AM</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
@@ -4008,19 +4008,19 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Sunday, September 7, 2026</t>
+          <t>Tuesday, September 2, 2026</t>
         </is>
       </c>
       <c r="C65" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>03:10 PM – 03:40 PM</t>
+          <t>01:30 PM – 02:15 PM</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
@@ -4064,19 +4064,19 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Tuesday, September 2, 2026</t>
+          <t>Wednesday, September 3, 2026</t>
         </is>
       </c>
       <c r="C66" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>03:10 PM – 03:40 PM</t>
+          <t>01:30 PM – 02:15 PM</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
@@ -4120,19 +4120,19 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Saturday, September 6, 2026</t>
+          <t>Tuesday, September 2, 2026</t>
         </is>
       </c>
       <c r="C67" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>03:10 PM – 03:40 PM</t>
+          <t>02:20 PM – 03:05 PM</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
@@ -4176,19 +4176,19 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Wednesday, September 3, 2026</t>
+          <t>Tuesday, September 2, 2026</t>
         </is>
       </c>
       <c r="C68" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>02:20 PM – 03:05 PM</t>
+          <t>03:10 PM – 03:40 PM</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
@@ -4232,11 +4232,11 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Tuesday, September 2, 2026</t>
+          <t>Saturday, September 6, 2026</t>
         </is>
       </c>
       <c r="C69" t="n">
@@ -4288,19 +4288,19 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Sunday, September 7, 2026</t>
+          <t>Saturday, September 6, 2026</t>
         </is>
       </c>
       <c r="C70" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>01:45 PM – 02:45 PM</t>
+          <t>02:45 PM – 03:30 PM</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
@@ -4344,19 +4344,19 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Sunday, September 7, 2026</t>
+          <t>Saturday, September 6, 2026</t>
         </is>
       </c>
       <c r="C71" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>02:45 PM – 03:30 PM</t>
+          <t>12:30 PM – 01:30 PM</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
@@ -4400,19 +4400,19 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Sunday, September 7, 2026</t>
+          <t>Tuesday, September 2, 2026</t>
         </is>
       </c>
       <c r="C72" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>12:30 PM – 01:30 PM</t>
+          <t>02:45 PM – 03:30 PM</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
@@ -4456,19 +4456,19 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Saturday, September 6, 2026</t>
+          <t>Wednesday, September 3, 2026</t>
         </is>
       </c>
       <c r="C73" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>02:45 PM – 03:30 PM</t>
+          <t>12:30 PM – 01:30 PM</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
@@ -4512,19 +4512,19 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Tuesday, September 2, 2026</t>
+          <t>Wednesday, September 3, 2026</t>
         </is>
       </c>
       <c r="C74" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>01:45 PM – 02:45 PM</t>
+          <t>02:45 PM – 03:30 PM</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
@@ -4576,11 +4576,11 @@
         </is>
       </c>
       <c r="C75" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>12:30 PM – 01:30 PM</t>
+          <t>01:45 PM – 02:45 PM</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
@@ -4632,11 +4632,11 @@
         </is>
       </c>
       <c r="C76" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>12:30 PM – 01:30 PM</t>
+          <t>01:45 PM – 02:45 PM</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
@@ -4688,11 +4688,11 @@
         </is>
       </c>
       <c r="C77" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>02:45 PM – 03:30 PM</t>
+          <t>12:30 PM – 01:30 PM</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
@@ -4736,19 +4736,19 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Tuesday, September 2, 2026</t>
+          <t>Saturday, September 6, 2026</t>
         </is>
       </c>
       <c r="C78" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>02:45 PM – 03:30 PM</t>
+          <t>01:45 PM – 02:45 PM</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
@@ -4792,11 +4792,11 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Saturday, September 6, 2026</t>
+          <t>Tuesday, September 2, 2026</t>
         </is>
       </c>
       <c r="C79" t="n">
@@ -4848,11 +4848,11 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Wednesday, September 3, 2026</t>
+          <t>Saturday, September 6, 2026</t>
         </is>
       </c>
       <c r="C80" t="n">
@@ -4904,19 +4904,19 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Saturday, September 6, 2026</t>
+          <t>Wednesday, September 3, 2026</t>
         </is>
       </c>
       <c r="C81" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>01:45 PM – 02:45 PM</t>
+          <t>12:30 PM – 01:30 PM</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
@@ -4960,19 +4960,19 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Tuesday, September 2, 2026</t>
+          <t>Wednesday, September 3, 2026</t>
         </is>
       </c>
       <c r="C82" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>12:30 PM – 01:30 PM</t>
+          <t>02:45 PM – 03:30 PM</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
@@ -5016,11 +5016,11 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Tuesday, September 2, 2026</t>
+          <t>Wednesday, September 3, 2026</t>
         </is>
       </c>
       <c r="C83" t="n">
@@ -5072,11 +5072,11 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Wednesday, September 3, 2026</t>
+          <t>Tuesday, September 2, 2026</t>
         </is>
       </c>
       <c r="C84" t="n">
@@ -5128,11 +5128,11 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Sunday, September 7, 2026</t>
+          <t>Tuesday, September 2, 2026</t>
         </is>
       </c>
       <c r="C85" t="n">
@@ -5184,19 +5184,19 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Wednesday, September 3, 2026</t>
+          <t>Saturday, September 6, 2026</t>
         </is>
       </c>
       <c r="C86" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>01:45 PM – 02:45 PM</t>
+          <t>12:30 PM – 01:30 PM</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
@@ -5248,11 +5248,11 @@
         </is>
       </c>
       <c r="C87" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>02:45 PM – 03:30 PM</t>
+          <t>01:45 PM – 02:45 PM</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
@@ -5296,11 +5296,11 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Wednesday, September 3, 2026</t>
+          <t>Saturday, September 6, 2026</t>
         </is>
       </c>
       <c r="C88" t="n">
@@ -5352,19 +5352,19 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
+        <v>1</v>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>Tuesday, September 2, 2026</t>
+        </is>
+      </c>
+      <c r="C89" t="n">
         <v>3</v>
       </c>
-      <c r="B89" t="inlineStr">
-        <is>
-          <t>Saturday, September 6, 2026</t>
-        </is>
-      </c>
-      <c r="C89" t="n">
-        <v>2</v>
-      </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>01:45 PM – 02:45 PM</t>
+          <t>02:45 PM – 03:30 PM</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
@@ -5408,19 +5408,19 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Sunday, September 7, 2026</t>
+          <t>Wednesday, September 3, 2026</t>
         </is>
       </c>
       <c r="C90" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>01:45 PM – 02:45 PM</t>
+          <t>12:30 PM – 01:30 PM</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
@@ -5464,11 +5464,11 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Tuesday, September 2, 2026</t>
+          <t>Wednesday, September 3, 2026</t>
         </is>
       </c>
       <c r="C91" t="n">
@@ -5528,11 +5528,11 @@
         </is>
       </c>
       <c r="C92" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>12:30 PM – 01:30 PM</t>
+          <t>01:45 PM – 02:45 PM</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
@@ -5576,19 +5576,19 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Sunday, September 7, 2026</t>
+          <t>Tuesday, September 2, 2026</t>
         </is>
       </c>
       <c r="C93" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>12:30 PM – 01:30 PM</t>
+          <t>01:45 PM – 02:45 PM</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
@@ -5632,11 +5632,11 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Saturday, September 6, 2026</t>
+          <t>Tuesday, September 2, 2026</t>
         </is>
       </c>
       <c r="C94" t="n">
@@ -5688,19 +5688,19 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Tuesday, September 2, 2026</t>
+          <t>Wednesday, September 3, 2026</t>
         </is>
       </c>
       <c r="C95" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>01:45 PM – 02:45 PM</t>
+          <t>02:45 PM – 03:30 PM</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
@@ -5744,19 +5744,19 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Saturday, September 6, 2026</t>
+          <t>Sunday, September 7, 2026</t>
         </is>
       </c>
       <c r="C96" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>02:45 PM – 03:30 PM</t>
+          <t>01:45 PM – 02:45 PM</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
@@ -5800,11 +5800,11 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>Wednesday, September 3, 2026</t>
+          <t>Saturday, September 6, 2026</t>
         </is>
       </c>
       <c r="C97" t="n">
@@ -5968,19 +5968,19 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
+        <v>1</v>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>Tuesday, September 2, 2026</t>
+        </is>
+      </c>
+      <c r="C100" t="n">
         <v>3</v>
       </c>
-      <c r="B100" t="inlineStr">
-        <is>
-          <t>Saturday, September 6, 2026</t>
-        </is>
-      </c>
-      <c r="C100" t="n">
-        <v>2</v>
-      </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>01:45 PM – 02:45 PM</t>
+          <t>02:45 PM – 03:30 PM</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
@@ -6032,11 +6032,11 @@
         </is>
       </c>
       <c r="C101" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>12:30 PM – 01:30 PM</t>
+          <t>01:45 PM – 02:45 PM</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
@@ -6080,19 +6080,19 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>Sunday, September 7, 2026</t>
+          <t>Wednesday, September 3, 2026</t>
         </is>
       </c>
       <c r="C102" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>01:45 PM – 02:45 PM</t>
+          <t>12:30 PM – 01:30 PM</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
@@ -6136,19 +6136,19 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>Sunday, September 7, 2026</t>
+          <t>Tuesday, September 2, 2026</t>
         </is>
       </c>
       <c r="C103" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>02:45 PM – 03:30 PM</t>
+          <t>12:30 PM – 01:30 PM</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
@@ -6200,11 +6200,11 @@
         </is>
       </c>
       <c r="C104" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>02:45 PM – 03:30 PM</t>
+          <t>01:45 PM – 02:45 PM</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
@@ -6248,11 +6248,11 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>Wednesday, September 3, 2026</t>
+          <t>Sunday, September 7, 2026</t>
         </is>
       </c>
       <c r="C105" t="n">
@@ -6304,19 +6304,19 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>Sunday, September 7, 2026</t>
+          <t>Saturday, September 6, 2026</t>
         </is>
       </c>
       <c r="C106" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>01:45 PM – 02:45 PM</t>
+          <t>02:45 PM – 03:30 PM</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
@@ -6360,19 +6360,19 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>Sunday, September 7, 2026</t>
+          <t>Saturday, September 6, 2026</t>
         </is>
       </c>
       <c r="C107" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>02:45 PM – 03:30 PM</t>
+          <t>01:45 PM – 02:45 PM</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
@@ -6416,19 +6416,19 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>Saturday, September 6, 2026</t>
+          <t>Wednesday, September 3, 2026</t>
         </is>
       </c>
       <c r="C108" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>02:45 PM – 03:30 PM</t>
+          <t>01:45 PM – 02:45 PM</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
@@ -6472,19 +6472,19 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>Sunday, September 7, 2026</t>
+          <t>Wednesday, September 3, 2026</t>
         </is>
       </c>
       <c r="C109" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>12:30 PM – 01:30 PM</t>
+          <t>02:45 PM – 03:30 PM</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
@@ -6536,11 +6536,11 @@
         </is>
       </c>
       <c r="C110" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>12:30 PM – 01:30 PM</t>
+          <t>02:45 PM – 03:30 PM</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
@@ -6584,19 +6584,19 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>Tuesday, September 2, 2026</t>
+          <t>Sunday, September 7, 2026</t>
         </is>
       </c>
       <c r="C111" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>02:45 PM – 03:30 PM</t>
+          <t>12:30 PM – 01:30 PM</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
@@ -6648,11 +6648,11 @@
         </is>
       </c>
       <c r="C112" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>02:45 PM – 03:30 PM</t>
+          <t>12:30 PM – 01:30 PM</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
@@ -6696,19 +6696,19 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>Saturday, September 6, 2026</t>
+          <t>Tuesday, September 2, 2026</t>
         </is>
       </c>
       <c r="C113" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>12:30 PM – 01:30 PM</t>
+          <t>01:45 PM – 02:45 PM</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
@@ -6752,19 +6752,19 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>Saturday, September 6, 2026</t>
+          <t>Tuesday, September 2, 2026</t>
         </is>
       </c>
       <c r="C114" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>01:45 PM – 02:45 PM</t>
+          <t>12:30 PM – 01:30 PM</t>
         </is>
       </c>
       <c r="E114" t="inlineStr">
@@ -6808,19 +6808,19 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>Sunday, September 7, 2026</t>
+          <t>Wednesday, September 3, 2026</t>
         </is>
       </c>
       <c r="C115" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>12:30 PM – 01:30 PM</t>
+          <t>01:45 PM – 02:45 PM</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
@@ -6864,19 +6864,19 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>Wednesday, September 3, 2026</t>
+          <t>Saturday, September 6, 2026</t>
         </is>
       </c>
       <c r="C116" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>01:45 PM – 02:45 PM</t>
+          <t>02:45 PM – 03:30 PM</t>
         </is>
       </c>
       <c r="E116" t="inlineStr">
@@ -6928,11 +6928,11 @@
         </is>
       </c>
       <c r="C117" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>12:30 PM – 01:30 PM</t>
+          <t>01:45 PM – 02:45 PM</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
@@ -6976,19 +6976,19 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>Saturday, September 6, 2026</t>
+          <t>Sunday, September 7, 2026</t>
         </is>
       </c>
       <c r="C118" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>01:45 PM – 02:45 PM</t>
+          <t>12:30 PM – 01:30 PM</t>
         </is>
       </c>
       <c r="E118" t="inlineStr">
@@ -7032,19 +7032,19 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>Tuesday, September 2, 2026</t>
+          <t>Wednesday, September 3, 2026</t>
         </is>
       </c>
       <c r="C119" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>01:45 PM – 02:45 PM</t>
+          <t>02:45 PM – 03:30 PM</t>
         </is>
       </c>
       <c r="E119" t="inlineStr">
@@ -7088,11 +7088,11 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>Wednesday, September 3, 2026</t>
+          <t>Saturday, September 6, 2026</t>
         </is>
       </c>
       <c r="C120" t="n">
@@ -7144,11 +7144,11 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>Sunday, September 7, 2026</t>
+          <t>Tuesday, September 2, 2026</t>
         </is>
       </c>
       <c r="C121" t="n">
@@ -7200,19 +7200,19 @@
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>Saturday, September 6, 2026</t>
+          <t>Wednesday, September 3, 2026</t>
         </is>
       </c>
       <c r="C122" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>02:45 PM – 03:30 PM</t>
+          <t>12:30 PM – 01:30 PM</t>
         </is>
       </c>
       <c r="E122" t="inlineStr">
@@ -7256,11 +7256,11 @@
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>Sunday, September 7, 2026</t>
+          <t>Tuesday, September 2, 2026</t>
         </is>
       </c>
       <c r="C123" t="n">
@@ -7368,19 +7368,19 @@
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>Wednesday, September 3, 2026</t>
+          <t>Saturday, September 6, 2026</t>
         </is>
       </c>
       <c r="C125" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>01:45 PM – 02:45 PM</t>
+          <t>02:45 PM – 03:30 PM</t>
         </is>
       </c>
       <c r="E125" t="inlineStr">
@@ -7488,11 +7488,11 @@
         </is>
       </c>
       <c r="C127" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>12:30 PM – 01:30 PM</t>
+          <t>01:45 PM – 02:45 PM</t>
         </is>
       </c>
       <c r="E127" t="inlineStr">
@@ -7544,11 +7544,11 @@
         </is>
       </c>
       <c r="C128" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>01:45 PM – 02:45 PM</t>
+          <t>02:45 PM – 03:30 PM</t>
         </is>
       </c>
       <c r="E128" t="inlineStr">
@@ -7592,19 +7592,19 @@
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>Saturday, September 6, 2026</t>
+          <t>Wednesday, September 3, 2026</t>
         </is>
       </c>
       <c r="C129" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>01:45 PM – 02:45 PM</t>
+          <t>12:30 PM – 01:30 PM</t>
         </is>
       </c>
       <c r="E129" t="inlineStr">
@@ -7648,19 +7648,19 @@
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>Tuesday, September 2, 2026</t>
+          <t>Wednesday, September 3, 2026</t>
         </is>
       </c>
       <c r="C130" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>01:45 PM – 02:45 PM</t>
+          <t>02:45 PM – 03:30 PM</t>
         </is>
       </c>
       <c r="E130" t="inlineStr">
@@ -7704,11 +7704,11 @@
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>Sunday, September 7, 2026</t>
+          <t>Tuesday, September 2, 2026</t>
         </is>
       </c>
       <c r="C131" t="n">
@@ -7768,11 +7768,11 @@
         </is>
       </c>
       <c r="C132" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>12:30 PM – 01:30 PM</t>
+          <t>01:45 PM – 02:45 PM</t>
         </is>
       </c>
       <c r="E132" t="inlineStr">
@@ -7816,19 +7816,19 @@
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>Saturday, September 6, 2026</t>
+          <t>Tuesday, September 2, 2026</t>
         </is>
       </c>
       <c r="C133" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>02:45 PM – 03:30 PM</t>
+          <t>01:45 PM – 02:45 PM</t>
         </is>
       </c>
       <c r="E133" t="inlineStr">
@@ -7928,11 +7928,11 @@
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>Saturday, September 6, 2026</t>
+          <t>Tuesday, September 2, 2026</t>
         </is>
       </c>
       <c r="C135" t="n">
@@ -7984,19 +7984,19 @@
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>Sunday, September 7, 2026</t>
+          <t>Tuesday, September 2, 2026</t>
         </is>
       </c>
       <c r="C136" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>03:10 PM – 03:40 PM</t>
+          <t>02:20 PM – 03:05 PM</t>
         </is>
       </c>
       <c r="E136" t="inlineStr">
@@ -8040,19 +8040,19 @@
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>Tuesday, September 2, 2026</t>
+          <t>Wednesday, September 3, 2026</t>
         </is>
       </c>
       <c r="C137" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>03:10 PM – 03:40 PM</t>
+          <t>01:30 PM – 02:15 PM</t>
         </is>
       </c>
       <c r="E137" t="inlineStr">
@@ -8104,11 +8104,11 @@
         </is>
       </c>
       <c r="C138" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>02:20 PM – 03:05 PM</t>
+          <t>01:30 PM – 02:15 PM</t>
         </is>
       </c>
       <c r="E138" t="inlineStr">
@@ -8152,19 +8152,19 @@
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>Sunday, September 7, 2026</t>
+          <t>Saturday, September 6, 2026</t>
         </is>
       </c>
       <c r="C139" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>12:30 PM – 01:30 PM</t>
+          <t>01:45 PM – 02:45 PM</t>
         </is>
       </c>
       <c r="E139" t="inlineStr">
@@ -8216,11 +8216,11 @@
         </is>
       </c>
       <c r="C140" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>02:45 PM – 03:30 PM</t>
+          <t>12:30 PM – 01:30 PM</t>
         </is>
       </c>
       <c r="E140" t="inlineStr">
@@ -8264,19 +8264,19 @@
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>Tuesday, September 2, 2026</t>
+          <t>Wednesday, September 3, 2026</t>
         </is>
       </c>
       <c r="C141" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>01:45 PM – 02:45 PM</t>
+          <t>02:45 PM – 03:30 PM</t>
         </is>
       </c>
       <c r="E141" t="inlineStr">
@@ -8320,11 +8320,11 @@
     </row>
     <row r="142">
       <c r="A142" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>Saturday, September 6, 2026</t>
+          <t>Wednesday, September 3, 2026</t>
         </is>
       </c>
       <c r="C142" t="n">
@@ -8376,11 +8376,11 @@
     </row>
     <row r="143">
       <c r="A143" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>Tuesday, September 2, 2026</t>
+          <t>Wednesday, September 3, 2026</t>
         </is>
       </c>
       <c r="C143" t="n">
@@ -8432,11 +8432,11 @@
     </row>
     <row r="144">
       <c r="A144" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>Sunday, September 7, 2026</t>
+          <t>Tuesday, September 2, 2026</t>
         </is>
       </c>
       <c r="C144" t="n">
@@ -8496,11 +8496,11 @@
         </is>
       </c>
       <c r="C145" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>02:45 PM – 03:30 PM</t>
+          <t>12:30 PM – 01:30 PM</t>
         </is>
       </c>
       <c r="E145" t="inlineStr">
@@ -8544,11 +8544,11 @@
     </row>
     <row r="146">
       <c r="A146" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>Wednesday, September 3, 2026</t>
+          <t>Tuesday, September 2, 2026</t>
         </is>
       </c>
       <c r="C146" t="n">
@@ -8600,19 +8600,19 @@
     </row>
     <row r="147">
       <c r="A147" t="n">
+        <v>2</v>
+      </c>
+      <c r="B147" t="inlineStr">
+        <is>
+          <t>Wednesday, September 3, 2026</t>
+        </is>
+      </c>
+      <c r="C147" t="n">
         <v>3</v>
       </c>
-      <c r="B147" t="inlineStr">
-        <is>
-          <t>Saturday, September 6, 2026</t>
-        </is>
-      </c>
-      <c r="C147" t="n">
-        <v>1</v>
-      </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>12:30 PM – 01:30 PM</t>
+          <t>02:45 PM – 03:30 PM</t>
         </is>
       </c>
       <c r="E147" t="inlineStr">
@@ -8656,11 +8656,11 @@
     </row>
     <row r="148">
       <c r="A148" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>Sunday, September 7, 2026</t>
+          <t>Saturday, September 6, 2026</t>
         </is>
       </c>
       <c r="C148" t="n">
@@ -8776,11 +8776,11 @@
         </is>
       </c>
       <c r="C150" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>01:45 PM – 02:45 PM</t>
+          <t>12:30 PM – 01:30 PM</t>
         </is>
       </c>
       <c r="E150" t="inlineStr">
@@ -8832,11 +8832,11 @@
         </is>
       </c>
       <c r="C151" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>01:45 PM – 02:45 PM</t>
+          <t>12:30 PM – 01:30 PM</t>
         </is>
       </c>
       <c r="E151" t="inlineStr">
@@ -8888,11 +8888,11 @@
         </is>
       </c>
       <c r="C152" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>02:45 PM – 03:30 PM</t>
+          <t>01:45 PM – 02:45 PM</t>
         </is>
       </c>
       <c r="E152" t="inlineStr">
@@ -8936,11 +8936,11 @@
     </row>
     <row r="153">
       <c r="A153" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>Saturday, September 6, 2026</t>
+          <t>Tuesday, September 2, 2026</t>
         </is>
       </c>
       <c r="C153" t="n">
@@ -9048,19 +9048,19 @@
     </row>
     <row r="155">
       <c r="A155" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>Sunday, September 7, 2026</t>
+          <t>Wednesday, September 3, 2026</t>
         </is>
       </c>
       <c r="C155" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>01:45 PM – 02:45 PM</t>
+          <t>02:45 PM – 03:30 PM</t>
         </is>
       </c>
       <c r="E155" t="inlineStr">
@@ -9112,11 +9112,11 @@
         </is>
       </c>
       <c r="C156" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>12:30 PM – 01:30 PM</t>
+          <t>01:45 PM – 02:45 PM</t>
         </is>
       </c>
       <c r="E156" t="inlineStr">
@@ -9160,19 +9160,19 @@
     </row>
     <row r="157">
       <c r="A157" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>Tuesday, September 2, 2026</t>
+          <t>Saturday, September 6, 2026</t>
         </is>
       </c>
       <c r="C157" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>12:30 PM – 01:30 PM</t>
+          <t>01:45 PM – 02:45 PM</t>
         </is>
       </c>
       <c r="E157" t="inlineStr">
@@ -9216,19 +9216,19 @@
     </row>
     <row r="158">
       <c r="A158" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>Tuesday, September 2, 2026</t>
+          <t>Saturday, September 6, 2026</t>
         </is>
       </c>
       <c r="C158" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>01:45 PM – 02:45 PM</t>
+          <t>12:30 PM – 01:30 PM</t>
         </is>
       </c>
       <c r="E158" t="inlineStr">
@@ -9272,11 +9272,11 @@
     </row>
     <row r="159">
       <c r="A159" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>Tuesday, September 2, 2026</t>
+          <t>Saturday, September 6, 2026</t>
         </is>
       </c>
       <c r="C159" t="n">
@@ -9336,11 +9336,11 @@
         </is>
       </c>
       <c r="C160" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>02:45 PM – 03:30 PM</t>
+          <t>12:30 PM – 01:30 PM</t>
         </is>
       </c>
       <c r="E160" t="inlineStr">
@@ -9384,19 +9384,19 @@
     </row>
     <row r="161">
       <c r="A161" t="n">
+        <v>1</v>
+      </c>
+      <c r="B161" t="inlineStr">
+        <is>
+          <t>Tuesday, September 2, 2026</t>
+        </is>
+      </c>
+      <c r="C161" t="n">
         <v>3</v>
       </c>
-      <c r="B161" t="inlineStr">
-        <is>
-          <t>Saturday, September 6, 2026</t>
-        </is>
-      </c>
-      <c r="C161" t="n">
-        <v>1</v>
-      </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>12:30 PM – 01:30 PM</t>
+          <t>02:45 PM – 03:30 PM</t>
         </is>
       </c>
       <c r="E161" t="inlineStr">
@@ -9440,19 +9440,19 @@
     </row>
     <row r="162">
       <c r="A162" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>Sunday, September 7, 2026</t>
+          <t>Tuesday, September 2, 2026</t>
         </is>
       </c>
       <c r="C162" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>02:45 PM – 03:30 PM</t>
+          <t>01:45 PM – 02:45 PM</t>
         </is>
       </c>
       <c r="E162" t="inlineStr">
@@ -9496,19 +9496,19 @@
     </row>
     <row r="163">
       <c r="A163" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>Wednesday, September 3, 2026</t>
+          <t>Tuesday, September 2, 2026</t>
         </is>
       </c>
       <c r="C163" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>01:45 PM – 02:45 PM</t>
+          <t>12:30 PM – 01:30 PM</t>
         </is>
       </c>
       <c r="E163" t="inlineStr">
@@ -9552,19 +9552,19 @@
     </row>
     <row r="164">
       <c r="A164" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>Wednesday, September 3, 2026</t>
+          <t>Sunday, September 7, 2026</t>
         </is>
       </c>
       <c r="C164" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>02:45 PM – 03:30 PM</t>
+          <t>12:30 PM – 01:30 PM</t>
         </is>
       </c>
       <c r="E164" t="inlineStr">
@@ -9608,19 +9608,19 @@
     </row>
     <row r="165">
       <c r="A165" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>Sunday, September 7, 2026</t>
+          <t>Saturday, September 6, 2026</t>
         </is>
       </c>
       <c r="C165" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>12:30 PM – 01:30 PM</t>
+          <t>02:45 PM – 03:30 PM</t>
         </is>
       </c>
       <c r="E165" t="inlineStr">
@@ -9728,11 +9728,11 @@
         </is>
       </c>
       <c r="C167" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t>02:45 PM – 03:30 PM</t>
+          <t>12:30 PM – 01:30 PM</t>
         </is>
       </c>
       <c r="E167" t="inlineStr">
@@ -9776,19 +9776,19 @@
     </row>
     <row r="168">
       <c r="A168" t="n">
+        <v>2</v>
+      </c>
+      <c r="B168" t="inlineStr">
+        <is>
+          <t>Wednesday, September 3, 2026</t>
+        </is>
+      </c>
+      <c r="C168" t="n">
         <v>3</v>
       </c>
-      <c r="B168" t="inlineStr">
-        <is>
-          <t>Saturday, September 6, 2026</t>
-        </is>
-      </c>
-      <c r="C168" t="n">
-        <v>1</v>
-      </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t>12:30 PM – 01:30 PM</t>
+          <t>02:45 PM – 03:30 PM</t>
         </is>
       </c>
       <c r="E168" t="inlineStr">
@@ -9832,11 +9832,11 @@
     </row>
     <row r="169">
       <c r="A169" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>Saturday, September 6, 2026</t>
+          <t>Wednesday, September 3, 2026</t>
         </is>
       </c>
       <c r="C169" t="n">
@@ -9952,11 +9952,11 @@
         </is>
       </c>
       <c r="C171" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t>01:45 PM – 02:45 PM</t>
+          <t>12:30 PM – 01:30 PM</t>
         </is>
       </c>
       <c r="E171" t="inlineStr">
@@ -10000,19 +10000,19 @@
     </row>
     <row r="172">
       <c r="A172" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>Sunday, September 7, 2026</t>
+          <t>Tuesday, September 2, 2026</t>
         </is>
       </c>
       <c r="C172" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
-          <t>02:45 PM – 03:30 PM</t>
+          <t>01:45 PM – 02:45 PM</t>
         </is>
       </c>
       <c r="E172" t="inlineStr">
@@ -10064,11 +10064,11 @@
         </is>
       </c>
       <c r="C173" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t>01:45 PM – 02:45 PM</t>
+          <t>12:30 PM – 01:30 PM</t>
         </is>
       </c>
       <c r="E173" t="inlineStr">
@@ -10112,11 +10112,11 @@
     </row>
     <row r="174">
       <c r="A174" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>Tuesday, September 2, 2026</t>
+          <t>Saturday, September 6, 2026</t>
         </is>
       </c>
       <c r="C174" t="n">
@@ -10168,19 +10168,19 @@
     </row>
     <row r="175">
       <c r="A175" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>Sunday, September 7, 2026</t>
+          <t>Saturday, September 6, 2026</t>
         </is>
       </c>
       <c r="C175" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
-          <t>02:45 PM – 03:30 PM</t>
+          <t>12:30 PM – 01:30 PM</t>
         </is>
       </c>
       <c r="E175" t="inlineStr">
@@ -10224,11 +10224,11 @@
     </row>
     <row r="176">
       <c r="A176" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>Tuesday, September 2, 2026</t>
+          <t>Saturday, September 6, 2026</t>
         </is>
       </c>
       <c r="C176" t="n">
@@ -10288,11 +10288,11 @@
         </is>
       </c>
       <c r="C177" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
-          <t>12:30 PM – 01:30 PM</t>
+          <t>02:45 PM – 03:30 PM</t>
         </is>
       </c>
       <c r="E177" t="inlineStr">
@@ -10336,19 +10336,19 @@
     </row>
     <row r="178">
       <c r="A178" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>Sunday, September 7, 2026</t>
+          <t>Wednesday, September 3, 2026</t>
         </is>
       </c>
       <c r="C178" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
-          <t>12:30 PM – 01:30 PM</t>
+          <t>01:45 PM – 02:45 PM</t>
         </is>
       </c>
       <c r="E178" t="inlineStr">
@@ -10400,11 +10400,11 @@
         </is>
       </c>
       <c r="C179" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
-          <t>02:45 PM – 03:30 PM</t>
+          <t>12:30 PM – 01:30 PM</t>
         </is>
       </c>
       <c r="E179" t="inlineStr">
@@ -10448,19 +10448,19 @@
     </row>
     <row r="180">
       <c r="A180" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>Wednesday, September 3, 2026</t>
+          <t>Tuesday, September 2, 2026</t>
         </is>
       </c>
       <c r="C180" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
-          <t>01:45 PM – 02:45 PM</t>
+          <t>02:45 PM – 03:30 PM</t>
         </is>
       </c>
       <c r="E180" t="inlineStr">
@@ -10512,11 +10512,11 @@
         </is>
       </c>
       <c r="C181" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
-          <t>12:30 PM – 01:30 PM</t>
+          <t>01:45 PM – 02:45 PM</t>
         </is>
       </c>
       <c r="E181" t="inlineStr">
@@ -10560,11 +10560,11 @@
     </row>
     <row r="182">
       <c r="A182" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>Saturday, September 6, 2026</t>
+          <t>Tuesday, September 2, 2026</t>
         </is>
       </c>
       <c r="C182" t="n">
@@ -10624,11 +10624,11 @@
         </is>
       </c>
       <c r="C183" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
-          <t>02:45 PM – 03:30 PM</t>
+          <t>12:30 PM – 01:30 PM</t>
         </is>
       </c>
       <c r="E183" t="inlineStr">
@@ -10672,19 +10672,19 @@
     </row>
     <row r="184">
       <c r="A184" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>Tuesday, September 2, 2026</t>
+          <t>Wednesday, September 3, 2026</t>
         </is>
       </c>
       <c r="C184" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
-          <t>12:30 PM – 01:30 PM</t>
+          <t>01:45 PM – 02:45 PM</t>
         </is>
       </c>
       <c r="E184" t="inlineStr">
@@ -10728,11 +10728,11 @@
     </row>
     <row r="185">
       <c r="A185" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>Wednesday, September 3, 2026</t>
+          <t>Saturday, September 6, 2026</t>
         </is>
       </c>
       <c r="C185" t="n">
@@ -10840,11 +10840,11 @@
     </row>
     <row r="187">
       <c r="A187" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>Saturday, September 6, 2026</t>
+          <t>Wednesday, September 3, 2026</t>
         </is>
       </c>
       <c r="C187" t="n">
@@ -10896,19 +10896,19 @@
     </row>
     <row r="188">
       <c r="A188" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>Sunday, September 7, 2026</t>
+          <t>Saturday, September 6, 2026</t>
         </is>
       </c>
       <c r="C188" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D188" t="inlineStr">
         <is>
-          <t>01:45 PM – 02:45 PM</t>
+          <t>12:30 PM – 01:30 PM</t>
         </is>
       </c>
       <c r="E188" t="inlineStr">
@@ -10960,11 +10960,11 @@
         </is>
       </c>
       <c r="C189" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D189" t="inlineStr">
         <is>
-          <t>01:45 PM – 02:45 PM</t>
+          <t>02:45 PM – 03:30 PM</t>
         </is>
       </c>
       <c r="E189" t="inlineStr">
@@ -11016,11 +11016,11 @@
         </is>
       </c>
       <c r="C190" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D190" t="inlineStr">
         <is>
-          <t>01:45 PM – 02:45 PM</t>
+          <t>02:45 PM – 03:30 PM</t>
         </is>
       </c>
       <c r="E190" t="inlineStr">
@@ -11064,19 +11064,19 @@
     </row>
     <row r="191">
       <c r="A191" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>Saturday, September 6, 2026</t>
+          <t>Tuesday, September 2, 2026</t>
         </is>
       </c>
       <c r="C191" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D191" t="inlineStr">
         <is>
-          <t>02:45 PM – 03:30 PM</t>
+          <t>01:45 PM – 02:45 PM</t>
         </is>
       </c>
       <c r="E191" t="inlineStr">
@@ -11128,11 +11128,11 @@
         </is>
       </c>
       <c r="C192" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D192" t="inlineStr">
         <is>
-          <t>02:45 PM – 03:30 PM</t>
+          <t>12:30 PM – 01:30 PM</t>
         </is>
       </c>
       <c r="E192" t="inlineStr">
@@ -11176,19 +11176,19 @@
     </row>
     <row r="193">
       <c r="A193" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>Wednesday, September 3, 2026</t>
+          <t>Sunday, September 7, 2026</t>
         </is>
       </c>
       <c r="C193" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D193" t="inlineStr">
         <is>
-          <t>02:45 PM – 03:30 PM</t>
+          <t>12:30 PM – 01:30 PM</t>
         </is>
       </c>
       <c r="E193" t="inlineStr">
@@ -11232,19 +11232,19 @@
     </row>
     <row r="194">
       <c r="A194" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>Tuesday, September 2, 2026</t>
+          <t>Saturday, September 6, 2026</t>
         </is>
       </c>
       <c r="C194" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D194" t="inlineStr">
         <is>
-          <t>01:45 PM – 02:45 PM</t>
+          <t>02:45 PM – 03:30 PM</t>
         </is>
       </c>
       <c r="E194" t="inlineStr">
@@ -11288,19 +11288,19 @@
     </row>
     <row r="195">
       <c r="A195" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>Sunday, September 7, 2026</t>
+          <t>Saturday, September 6, 2026</t>
         </is>
       </c>
       <c r="C195" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D195" t="inlineStr">
         <is>
-          <t>12:30 PM – 01:30 PM</t>
+          <t>01:45 PM – 02:45 PM</t>
         </is>
       </c>
       <c r="E195" t="inlineStr">
@@ -11352,11 +11352,11 @@
         </is>
       </c>
       <c r="C196" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D196" t="inlineStr">
         <is>
-          <t>02:45 PM – 03:30 PM</t>
+          <t>12:30 PM – 01:30 PM</t>
         </is>
       </c>
       <c r="E196" t="inlineStr">
@@ -11408,11 +11408,11 @@
         </is>
       </c>
       <c r="C197" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D197" t="inlineStr">
         <is>
-          <t>12:30 PM – 01:30 PM</t>
+          <t>02:45 PM – 03:30 PM</t>
         </is>
       </c>
       <c r="E197" t="inlineStr">
@@ -11456,19 +11456,19 @@
     </row>
     <row r="198">
       <c r="A198" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>Tuesday, September 2, 2026</t>
+          <t>Wednesday, September 3, 2026</t>
         </is>
       </c>
       <c r="C198" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D198" t="inlineStr">
         <is>
-          <t>02:45 PM – 03:30 PM</t>
+          <t>01:45 PM – 02:45 PM</t>
         </is>
       </c>
       <c r="E198" t="inlineStr">
@@ -11512,19 +11512,19 @@
     </row>
     <row r="199">
       <c r="A199" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>Saturday, September 6, 2026</t>
+          <t>Wednesday, September 3, 2026</t>
         </is>
       </c>
       <c r="C199" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D199" t="inlineStr">
         <is>
-          <t>01:45 PM – 02:45 PM</t>
+          <t>12:30 PM – 01:30 PM</t>
         </is>
       </c>
       <c r="E199" t="inlineStr">
@@ -11568,19 +11568,19 @@
     </row>
     <row r="200">
       <c r="A200" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>Sunday, September 7, 2026</t>
+          <t>Tuesday, September 2, 2026</t>
         </is>
       </c>
       <c r="C200" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D200" t="inlineStr">
         <is>
-          <t>02:45 PM – 03:30 PM</t>
+          <t>01:45 PM – 02:45 PM</t>
         </is>
       </c>
       <c r="E200" t="inlineStr">
@@ -11632,11 +11632,11 @@
         </is>
       </c>
       <c r="C201" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D201" t="inlineStr">
         <is>
-          <t>12:30 PM – 01:30 PM</t>
+          <t>02:45 PM – 03:30 PM</t>
         </is>
       </c>
       <c r="E201" t="inlineStr">
@@ -11680,11 +11680,11 @@
     </row>
     <row r="202">
       <c r="A202" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>Saturday, September 6, 2026</t>
+          <t>Tuesday, September 2, 2026</t>
         </is>
       </c>
       <c r="C202" t="n">
@@ -11736,11 +11736,11 @@
     </row>
     <row r="203">
       <c r="A203" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>Wednesday, September 3, 2026</t>
+          <t>Saturday, September 6, 2026</t>
         </is>
       </c>
       <c r="C203" t="n">
@@ -11792,19 +11792,19 @@
     </row>
     <row r="204">
       <c r="A204" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="B204" t="inlineStr">
         <is>
-          <t>Sunday, September 7, 2026</t>
+          <t>Tuesday, September 2, 2026</t>
         </is>
       </c>
       <c r="C204" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D204" t="inlineStr">
         <is>
-          <t>03:30 PM – 04:30 PM</t>
+          <t>04:45 PM – 05:45 PM</t>
         </is>
       </c>
       <c r="E204" t="inlineStr">
@@ -11848,11 +11848,11 @@
     </row>
     <row r="205">
       <c r="A205" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B205" t="inlineStr">
         <is>
-          <t>Saturday, September 6, 2026</t>
+          <t>Wednesday, September 3, 2026</t>
         </is>
       </c>
       <c r="C205" t="n">
@@ -11912,11 +11912,11 @@
         </is>
       </c>
       <c r="C206" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D206" t="inlineStr">
         <is>
-          <t>04:45 PM – 05:45 PM</t>
+          <t>03:30 PM – 04:30 PM</t>
         </is>
       </c>
       <c r="E206" t="inlineStr">
@@ -11960,11 +11960,11 @@
     </row>
     <row r="207">
       <c r="A207" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B207" t="inlineStr">
         <is>
-          <t>Wednesday, September 3, 2026</t>
+          <t>Tuesday, September 2, 2026</t>
         </is>
       </c>
       <c r="C207" t="n">
@@ -12016,11 +12016,11 @@
     </row>
     <row r="208">
       <c r="A208" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="B208" t="inlineStr">
         <is>
-          <t>Tuesday, September 2, 2026</t>
+          <t>Sunday, September 7, 2026</t>
         </is>
       </c>
       <c r="C208" t="n">
@@ -12072,11 +12072,11 @@
     </row>
     <row r="209">
       <c r="A209" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="B209" t="inlineStr">
         <is>
-          <t>Sunday, September 7, 2026</t>
+          <t>Tuesday, September 2, 2026</t>
         </is>
       </c>
       <c r="C209" t="n">
@@ -12128,11 +12128,11 @@
     </row>
     <row r="210">
       <c r="A210" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="B210" t="inlineStr">
         <is>
-          <t>Saturday, September 6, 2026</t>
+          <t>Tuesday, September 2, 2026</t>
         </is>
       </c>
       <c r="C210" t="n">
@@ -12184,19 +12184,19 @@
     </row>
     <row r="211">
       <c r="A211" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="B211" t="inlineStr">
         <is>
-          <t>Tuesday, September 2, 2026</t>
+          <t>Saturday, September 6, 2026</t>
         </is>
       </c>
       <c r="C211" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D211" t="inlineStr">
         <is>
-          <t>04:45 PM – 05:45 PM</t>
+          <t>05:45 PM – 06:45 PM</t>
         </is>
       </c>
       <c r="E211" t="inlineStr">
@@ -12240,11 +12240,11 @@
     </row>
     <row r="212">
       <c r="A212" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B212" t="inlineStr">
         <is>
-          <t>Wednesday, September 3, 2026</t>
+          <t>Saturday, September 6, 2026</t>
         </is>
       </c>
       <c r="C212" t="n">
@@ -12296,19 +12296,19 @@
     </row>
     <row r="213">
       <c r="A213" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="B213" t="inlineStr">
         <is>
-          <t>Saturday, September 6, 2026</t>
+          <t>Tuesday, September 2, 2026</t>
         </is>
       </c>
       <c r="C213" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D213" t="inlineStr">
         <is>
-          <t>03:30 PM – 04:30 PM</t>
+          <t>04:45 PM – 05:45 PM</t>
         </is>
       </c>
       <c r="E213" t="inlineStr">
@@ -12352,19 +12352,19 @@
     </row>
     <row r="214">
       <c r="A214" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B214" t="inlineStr">
         <is>
-          <t>Tuesday, September 2, 2026</t>
+          <t>Wednesday, September 3, 2026</t>
         </is>
       </c>
       <c r="C214" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D214" t="inlineStr">
         <is>
-          <t>05:45 PM – 06:45 PM</t>
+          <t>03:30 PM – 04:30 PM</t>
         </is>
       </c>
       <c r="E214" t="inlineStr">
@@ -12472,11 +12472,11 @@
         </is>
       </c>
       <c r="C216" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D216" t="inlineStr">
         <is>
-          <t>03:30 PM – 04:30 PM</t>
+          <t>05:45 PM – 06:45 PM</t>
         </is>
       </c>
       <c r="E216" t="inlineStr">
@@ -12576,19 +12576,19 @@
     </row>
     <row r="218">
       <c r="A218" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="B218" t="inlineStr">
         <is>
-          <t>Sunday, September 7, 2026</t>
+          <t>Tuesday, September 2, 2026</t>
         </is>
       </c>
       <c r="C218" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D218" t="inlineStr">
         <is>
-          <t>04:45 PM – 05:45 PM</t>
+          <t>03:30 PM – 04:30 PM</t>
         </is>
       </c>
       <c r="E218" t="inlineStr">
@@ -12632,11 +12632,11 @@
     </row>
     <row r="219">
       <c r="A219" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B219" t="inlineStr">
         <is>
-          <t>Wednesday, September 3, 2026</t>
+          <t>Saturday, September 6, 2026</t>
         </is>
       </c>
       <c r="C219" t="n">
@@ -12688,19 +12688,19 @@
     </row>
     <row r="220">
       <c r="A220" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B220" t="inlineStr">
         <is>
-          <t>Tuesday, September 2, 2026</t>
+          <t>Wednesday, September 3, 2026</t>
         </is>
       </c>
       <c r="C220" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D220" t="inlineStr">
         <is>
-          <t>03:30 PM – 04:30 PM</t>
+          <t>04:45 PM – 05:45 PM</t>
         </is>
       </c>
       <c r="E220" t="inlineStr">
@@ -12744,19 +12744,19 @@
     </row>
     <row r="221">
       <c r="A221" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B221" t="inlineStr">
         <is>
-          <t>Wednesday, September 3, 2026</t>
+          <t>Saturday, September 6, 2026</t>
         </is>
       </c>
       <c r="C221" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D221" t="inlineStr">
         <is>
-          <t>05:45 PM – 06:45 PM</t>
+          <t>03:30 PM – 04:30 PM</t>
         </is>
       </c>
       <c r="E221" t="inlineStr">
@@ -12808,11 +12808,11 @@
         </is>
       </c>
       <c r="C222" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D222" t="inlineStr">
         <is>
-          <t>03:30 PM – 04:30 PM</t>
+          <t>05:45 PM – 06:45 PM</t>
         </is>
       </c>
       <c r="E222" t="inlineStr">
@@ -12856,11 +12856,11 @@
     </row>
     <row r="223">
       <c r="A223" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="B223" t="inlineStr">
         <is>
-          <t>Sunday, September 7, 2026</t>
+          <t>Wednesday, September 3, 2026</t>
         </is>
       </c>
       <c r="C223" t="n">
@@ -12912,11 +12912,11 @@
     </row>
     <row r="224">
       <c r="A224" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="B224" t="inlineStr">
         <is>
-          <t>Saturday, September 6, 2026</t>
+          <t>Tuesday, September 2, 2026</t>
         </is>
       </c>
       <c r="C224" t="n">
@@ -12968,19 +12968,19 @@
     </row>
     <row r="225">
       <c r="A225" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="B225" t="inlineStr">
         <is>
-          <t>Saturday, September 6, 2026</t>
+          <t>Tuesday, September 2, 2026</t>
         </is>
       </c>
       <c r="C225" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D225" t="inlineStr">
         <is>
-          <t>03:30 PM – 04:30 PM</t>
+          <t>04:45 PM – 05:45 PM</t>
         </is>
       </c>
       <c r="E225" t="inlineStr">
@@ -13024,19 +13024,19 @@
     </row>
     <row r="226">
       <c r="A226" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="B226" t="inlineStr">
         <is>
-          <t>Sunday, September 7, 2026</t>
+          <t>Tuesday, September 2, 2026</t>
         </is>
       </c>
       <c r="C226" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D226" t="inlineStr">
         <is>
-          <t>05:45 PM – 06:45 PM</t>
+          <t>03:30 PM – 04:30 PM</t>
         </is>
       </c>
       <c r="E226" t="inlineStr">
@@ -13192,19 +13192,19 @@
     </row>
     <row r="229">
       <c r="A229" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="B229" t="inlineStr">
         <is>
-          <t>Tuesday, September 2, 2026</t>
+          <t>Saturday, September 6, 2026</t>
         </is>
       </c>
       <c r="C229" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D229" t="inlineStr">
         <is>
-          <t>03:30 PM – 04:30 PM</t>
+          <t>04:45 PM – 05:45 PM</t>
         </is>
       </c>
       <c r="E229" t="inlineStr">
@@ -13304,19 +13304,19 @@
     </row>
     <row r="231">
       <c r="A231" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="B231" t="inlineStr">
         <is>
-          <t>Sunday, September 7, 2026</t>
+          <t>Tuesday, September 2, 2026</t>
         </is>
       </c>
       <c r="C231" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D231" t="inlineStr">
         <is>
-          <t>03:30 PM – 04:30 PM</t>
+          <t>05:45 PM – 06:45 PM</t>
         </is>
       </c>
       <c r="E231" t="inlineStr">
@@ -13368,11 +13368,11 @@
         </is>
       </c>
       <c r="C232" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D232" t="inlineStr">
         <is>
-          <t>04:45 PM – 05:45 PM</t>
+          <t>03:30 PM – 04:30 PM</t>
         </is>
       </c>
       <c r="E232" t="inlineStr">
@@ -13416,19 +13416,19 @@
     </row>
     <row r="233">
       <c r="A233" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="B233" t="inlineStr">
         <is>
-          <t>Sunday, September 7, 2026</t>
+          <t>Wednesday, September 3, 2026</t>
         </is>
       </c>
       <c r="C233" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D233" t="inlineStr">
         <is>
-          <t>05:45 PM – 06:45 PM</t>
+          <t>03:30 PM – 04:30 PM</t>
         </is>
       </c>
       <c r="E233" t="inlineStr">
@@ -13472,11 +13472,11 @@
     </row>
     <row r="234">
       <c r="A234" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="B234" t="inlineStr">
         <is>
-          <t>Sunday, September 7, 2026</t>
+          <t>Tuesday, September 2, 2026</t>
         </is>
       </c>
       <c r="C234" t="n">
@@ -13528,11 +13528,11 @@
     </row>
     <row r="235">
       <c r="A235" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B235" t="inlineStr">
         <is>
-          <t>Wednesday, September 3, 2026</t>
+          <t>Tuesday, September 2, 2026</t>
         </is>
       </c>
       <c r="C235" t="n">
@@ -13592,11 +13592,11 @@
         </is>
       </c>
       <c r="C236" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D236" t="inlineStr">
         <is>
-          <t>03:30 PM – 04:30 PM</t>
+          <t>05:45 PM – 06:45 PM</t>
         </is>
       </c>
       <c r="E236" t="inlineStr">
@@ -13640,19 +13640,19 @@
     </row>
     <row r="237">
       <c r="A237" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B237" t="inlineStr">
         <is>
-          <t>Wednesday, September 3, 2026</t>
+          <t>Saturday, September 6, 2026</t>
         </is>
       </c>
       <c r="C237" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D237" t="inlineStr">
         <is>
-          <t>03:30 PM – 04:30 PM</t>
+          <t>05:45 PM – 06:45 PM</t>
         </is>
       </c>
       <c r="E237" t="inlineStr">
@@ -13696,19 +13696,19 @@
     </row>
     <row r="238">
       <c r="A238" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B238" t="inlineStr">
         <is>
-          <t>Sunday, September 7, 2026</t>
+          <t>Saturday, September 6, 2026</t>
         </is>
       </c>
       <c r="C238" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D238" t="inlineStr">
         <is>
-          <t>04:45 PM – 05:45 PM</t>
+          <t>03:30 PM – 04:30 PM</t>
         </is>
       </c>
       <c r="E238" t="inlineStr">
@@ -13752,19 +13752,19 @@
     </row>
     <row r="239">
       <c r="A239" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="B239" t="inlineStr">
         <is>
-          <t>Tuesday, September 2, 2026</t>
+          <t>Saturday, September 6, 2026</t>
         </is>
       </c>
       <c r="C239" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D239" t="inlineStr">
         <is>
-          <t>05:45 PM – 06:45 PM</t>
+          <t>04:45 PM – 05:45 PM</t>
         </is>
       </c>
       <c r="E239" t="inlineStr">
@@ -13808,19 +13808,19 @@
     </row>
     <row r="240">
       <c r="A240" t="n">
+        <v>1</v>
+      </c>
+      <c r="B240" t="inlineStr">
+        <is>
+          <t>Tuesday, September 2, 2026</t>
+        </is>
+      </c>
+      <c r="C240" t="n">
         <v>3</v>
       </c>
-      <c r="B240" t="inlineStr">
-        <is>
-          <t>Saturday, September 6, 2026</t>
-        </is>
-      </c>
-      <c r="C240" t="n">
-        <v>1</v>
-      </c>
       <c r="D240" t="inlineStr">
         <is>
-          <t>03:30 PM – 04:30 PM</t>
+          <t>05:45 PM – 06:45 PM</t>
         </is>
       </c>
       <c r="E240" t="inlineStr">
@@ -13864,19 +13864,19 @@
     </row>
     <row r="241">
       <c r="A241" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B241" t="inlineStr">
         <is>
-          <t>Tuesday, September 2, 2026</t>
+          <t>Wednesday, September 3, 2026</t>
         </is>
       </c>
       <c r="C241" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D241" t="inlineStr">
         <is>
-          <t>03:30 PM – 04:30 PM</t>
+          <t>05:45 PM – 06:45 PM</t>
         </is>
       </c>
       <c r="E241" t="inlineStr">
@@ -13920,19 +13920,19 @@
     </row>
     <row r="242">
       <c r="A242" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B242" t="inlineStr">
         <is>
-          <t>Tuesday, September 2, 2026</t>
+          <t>Wednesday, September 3, 2026</t>
         </is>
       </c>
       <c r="C242" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D242" t="inlineStr">
         <is>
-          <t>04:45 PM – 05:45 PM</t>
+          <t>03:30 PM – 04:30 PM</t>
         </is>
       </c>
       <c r="E242" t="inlineStr">
@@ -13984,11 +13984,11 @@
         </is>
       </c>
       <c r="C243" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D243" t="inlineStr">
         <is>
-          <t>05:45 PM – 06:45 PM</t>
+          <t>04:45 PM – 05:45 PM</t>
         </is>
       </c>
       <c r="E243" t="inlineStr">
@@ -14032,19 +14032,19 @@
     </row>
     <row r="244">
       <c r="A244" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="B244" t="inlineStr">
         <is>
-          <t>Saturday, September 6, 2026</t>
+          <t>Tuesday, September 2, 2026</t>
         </is>
       </c>
       <c r="C244" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D244" t="inlineStr">
         <is>
-          <t>05:45 PM – 06:45 PM</t>
+          <t>03:30 PM – 04:30 PM</t>
         </is>
       </c>
       <c r="E244" t="inlineStr">
@@ -14088,19 +14088,19 @@
     </row>
     <row r="245">
       <c r="A245" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="B245" t="inlineStr">
         <is>
-          <t>Sunday, September 7, 2026</t>
+          <t>Tuesday, September 2, 2026</t>
         </is>
       </c>
       <c r="C245" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D245" t="inlineStr">
         <is>
-          <t>05:45 PM – 06:45 PM</t>
+          <t>04:45 PM – 05:45 PM</t>
         </is>
       </c>
       <c r="E245" t="inlineStr">
@@ -14144,11 +14144,11 @@
     </row>
     <row r="246">
       <c r="A246" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="B246" t="inlineStr">
         <is>
-          <t>Tuesday, September 2, 2026</t>
+          <t>Sunday, September 7, 2026</t>
         </is>
       </c>
       <c r="C246" t="n">
@@ -14200,19 +14200,19 @@
     </row>
     <row r="247">
       <c r="A247" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="B247" t="inlineStr">
         <is>
-          <t>Sunday, September 7, 2026</t>
+          <t>Wednesday, September 3, 2026</t>
         </is>
       </c>
       <c r="C247" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D247" t="inlineStr">
         <is>
-          <t>12:30 PM – 01:30 PM</t>
+          <t>01:45 PM – 02:45 PM</t>
         </is>
       </c>
       <c r="E247" t="inlineStr">
@@ -14312,19 +14312,19 @@
     </row>
     <row r="249">
       <c r="A249" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="B249" t="inlineStr">
         <is>
-          <t>Sunday, September 7, 2026</t>
+          <t>Wednesday, September 3, 2026</t>
         </is>
       </c>
       <c r="C249" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D249" t="inlineStr">
         <is>
-          <t>02:45 PM – 03:30 PM</t>
+          <t>12:30 PM – 01:30 PM</t>
         </is>
       </c>
       <c r="E249" t="inlineStr">
@@ -14368,11 +14368,11 @@
     </row>
     <row r="250">
       <c r="A250" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B250" t="inlineStr">
         <is>
-          <t>Wednesday, September 3, 2026</t>
+          <t>Saturday, September 6, 2026</t>
         </is>
       </c>
       <c r="C250" t="n">
@@ -14424,19 +14424,19 @@
     </row>
     <row r="251">
       <c r="A251" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="B251" t="inlineStr">
         <is>
-          <t>Tuesday, September 2, 2026</t>
+          <t>Saturday, September 6, 2026</t>
         </is>
       </c>
       <c r="C251" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D251" t="inlineStr">
         <is>
-          <t>01:45 PM – 02:45 PM</t>
+          <t>12:30 PM – 01:30 PM</t>
         </is>
       </c>
       <c r="E251" t="inlineStr">
@@ -14480,19 +14480,19 @@
     </row>
     <row r="252">
       <c r="A252" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="B252" t="inlineStr">
         <is>
-          <t>Sunday, September 7, 2026</t>
+          <t>Wednesday, September 3, 2026</t>
         </is>
       </c>
       <c r="C252" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D252" t="inlineStr">
         <is>
-          <t>01:45 PM – 02:45 PM</t>
+          <t>02:45 PM – 03:30 PM</t>
         </is>
       </c>
       <c r="E252" t="inlineStr">
@@ -14536,19 +14536,19 @@
     </row>
     <row r="253">
       <c r="A253" t="n">
+        <v>1</v>
+      </c>
+      <c r="B253" t="inlineStr">
+        <is>
+          <t>Tuesday, September 2, 2026</t>
+        </is>
+      </c>
+      <c r="C253" t="n">
         <v>3</v>
       </c>
-      <c r="B253" t="inlineStr">
-        <is>
-          <t>Saturday, September 6, 2026</t>
-        </is>
-      </c>
-      <c r="C253" t="n">
-        <v>2</v>
-      </c>
       <c r="D253" t="inlineStr">
         <is>
-          <t>01:45 PM – 02:45 PM</t>
+          <t>02:45 PM – 03:30 PM</t>
         </is>
       </c>
       <c r="E253" t="inlineStr">
@@ -14592,19 +14592,19 @@
     </row>
     <row r="254">
       <c r="A254" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B254" t="inlineStr">
         <is>
-          <t>Wednesday, September 3, 2026</t>
+          <t>Tuesday, September 2, 2026</t>
         </is>
       </c>
       <c r="C254" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D254" t="inlineStr">
         <is>
-          <t>02:45 PM – 03:30 PM</t>
+          <t>01:45 PM – 02:45 PM</t>
         </is>
       </c>
       <c r="E254" t="inlineStr">
@@ -14648,11 +14648,11 @@
     </row>
     <row r="255">
       <c r="A255" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="B255" t="inlineStr">
         <is>
-          <t>Saturday, September 6, 2026</t>
+          <t>Tuesday, September 2, 2026</t>
         </is>
       </c>
       <c r="C255" t="n">
@@ -14704,19 +14704,19 @@
     </row>
     <row r="256">
       <c r="A256" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="B256" t="inlineStr">
         <is>
-          <t>Wednesday, September 3, 2026</t>
+          <t>Sunday, September 7, 2026</t>
         </is>
       </c>
       <c r="C256" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D256" t="inlineStr">
         <is>
-          <t>05:45 PM – 06:45 PM</t>
+          <t>03:30 PM – 04:30 PM</t>
         </is>
       </c>
       <c r="E256" t="inlineStr">
@@ -14760,11 +14760,11 @@
     </row>
     <row r="257">
       <c r="A257" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B257" t="inlineStr">
         <is>
-          <t>Sunday, September 7, 2026</t>
+          <t>Saturday, September 6, 2026</t>
         </is>
       </c>
       <c r="C257" t="n">
@@ -14824,11 +14824,11 @@
         </is>
       </c>
       <c r="C258" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D258" t="inlineStr">
         <is>
-          <t>05:45 PM – 06:45 PM</t>
+          <t>03:30 PM – 04:30 PM</t>
         </is>
       </c>
       <c r="E258" t="inlineStr">
@@ -14928,11 +14928,11 @@
     </row>
     <row r="260">
       <c r="A260" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="B260" t="inlineStr">
         <is>
-          <t>Tuesday, September 2, 2026</t>
+          <t>Saturday, September 6, 2026</t>
         </is>
       </c>
       <c r="C260" t="n">
@@ -14992,11 +14992,11 @@
         </is>
       </c>
       <c r="C261" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D261" t="inlineStr">
         <is>
-          <t>03:30 PM – 04:30 PM</t>
+          <t>04:45 PM – 05:45 PM</t>
         </is>
       </c>
       <c r="E261" t="inlineStr">
@@ -15040,11 +15040,11 @@
     </row>
     <row r="262">
       <c r="A262" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="B262" t="inlineStr">
         <is>
-          <t>Tuesday, September 2, 2026</t>
+          <t>Sunday, September 7, 2026</t>
         </is>
       </c>
       <c r="C262" t="n">
@@ -15096,19 +15096,19 @@
     </row>
     <row r="263">
       <c r="A263" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="B263" t="inlineStr">
         <is>
-          <t>Sunday, September 7, 2026</t>
+          <t>Tuesday, September 2, 2026</t>
         </is>
       </c>
       <c r="C263" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D263" t="inlineStr">
         <is>
-          <t>03:30 PM – 04:30 PM</t>
+          <t>05:45 PM – 06:45 PM</t>
         </is>
       </c>
       <c r="E263" t="inlineStr">
@@ -15152,19 +15152,19 @@
     </row>
     <row r="264">
       <c r="A264" t="n">
+        <v>2</v>
+      </c>
+      <c r="B264" t="inlineStr">
+        <is>
+          <t>Wednesday, September 3, 2026</t>
+        </is>
+      </c>
+      <c r="C264" t="n">
         <v>3</v>
       </c>
-      <c r="B264" t="inlineStr">
-        <is>
-          <t>Saturday, September 6, 2026</t>
-        </is>
-      </c>
-      <c r="C264" t="n">
-        <v>2</v>
-      </c>
       <c r="D264" t="inlineStr">
         <is>
-          <t>04:45 PM – 05:45 PM</t>
+          <t>05:45 PM – 06:45 PM</t>
         </is>
       </c>
       <c r="E264" t="inlineStr">
@@ -15216,11 +15216,11 @@
         </is>
       </c>
       <c r="C265" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D265" t="inlineStr">
         <is>
-          <t>04:45 PM – 05:45 PM</t>
+          <t>03:30 PM – 04:30 PM</t>
         </is>
       </c>
       <c r="E265" t="inlineStr">
@@ -15264,19 +15264,19 @@
     </row>
     <row r="266">
       <c r="A266" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B266" t="inlineStr">
         <is>
-          <t>Tuesday, September 2, 2026</t>
+          <t>Wednesday, September 3, 2026</t>
         </is>
       </c>
       <c r="C266" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D266" t="inlineStr">
         <is>
-          <t>05:45 PM – 06:45 PM</t>
+          <t>04:45 PM – 05:45 PM</t>
         </is>
       </c>
       <c r="E266" t="inlineStr">
@@ -15320,11 +15320,11 @@
     </row>
     <row r="267">
       <c r="A267" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="B267" t="inlineStr">
         <is>
-          <t>Saturday, September 6, 2026</t>
+          <t>Tuesday, September 2, 2026</t>
         </is>
       </c>
       <c r="C267" t="n">
@@ -15384,11 +15384,11 @@
         </is>
       </c>
       <c r="C268" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D268" t="inlineStr">
         <is>
-          <t>04:45 PM – 05:45 PM</t>
+          <t>03:30 PM – 04:30 PM</t>
         </is>
       </c>
       <c r="E268" t="inlineStr">
@@ -15432,11 +15432,11 @@
     </row>
     <row r="269">
       <c r="A269" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="B269" t="inlineStr">
         <is>
-          <t>Sunday, September 7, 2026</t>
+          <t>Tuesday, September 2, 2026</t>
         </is>
       </c>
       <c r="C269" t="n">
@@ -15496,11 +15496,11 @@
         </is>
       </c>
       <c r="C270" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D270" t="inlineStr">
         <is>
-          <t>04:45 PM – 05:45 PM</t>
+          <t>03:30 PM – 04:30 PM</t>
         </is>
       </c>
       <c r="E270" t="inlineStr">
@@ -15544,19 +15544,19 @@
     </row>
     <row r="271">
       <c r="A271" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="B271" t="inlineStr">
         <is>
-          <t>Sunday, September 7, 2026</t>
+          <t>Tuesday, September 2, 2026</t>
         </is>
       </c>
       <c r="C271" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D271" t="inlineStr">
         <is>
-          <t>03:30 PM – 04:30 PM</t>
+          <t>05:45 PM – 06:45 PM</t>
         </is>
       </c>
       <c r="E271" t="inlineStr">
@@ -15608,11 +15608,11 @@
         </is>
       </c>
       <c r="C272" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D272" t="inlineStr">
         <is>
-          <t>03:30 PM – 04:30 PM</t>
+          <t>04:45 PM – 05:45 PM</t>
         </is>
       </c>
       <c r="E272" t="inlineStr">
@@ -15664,11 +15664,11 @@
         </is>
       </c>
       <c r="C273" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D273" t="inlineStr">
         <is>
-          <t>04:45 PM – 05:45 PM</t>
+          <t>05:45 PM – 06:45 PM</t>
         </is>
       </c>
       <c r="E273" t="inlineStr">
@@ -15712,19 +15712,19 @@
     </row>
     <row r="274">
       <c r="A274" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="B274" t="inlineStr">
         <is>
-          <t>Tuesday, September 2, 2026</t>
+          <t>Sunday, September 7, 2026</t>
         </is>
       </c>
       <c r="C274" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D274" t="inlineStr">
         <is>
-          <t>03:30 PM – 04:30 PM</t>
+          <t>04:45 PM – 05:45 PM</t>
         </is>
       </c>
       <c r="E274" t="inlineStr">
@@ -15768,19 +15768,19 @@
     </row>
     <row r="275">
       <c r="A275" t="n">
+        <v>4</v>
+      </c>
+      <c r="B275" t="inlineStr">
+        <is>
+          <t>Sunday, September 7, 2026</t>
+        </is>
+      </c>
+      <c r="C275" t="n">
         <v>3</v>
       </c>
-      <c r="B275" t="inlineStr">
-        <is>
-          <t>Saturday, September 6, 2026</t>
-        </is>
-      </c>
-      <c r="C275" t="n">
-        <v>2</v>
-      </c>
       <c r="D275" t="inlineStr">
         <is>
-          <t>04:45 PM – 05:45 PM</t>
+          <t>05:45 PM – 06:45 PM</t>
         </is>
       </c>
       <c r="E275" t="inlineStr">
@@ -15832,11 +15832,11 @@
         </is>
       </c>
       <c r="C276" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D276" t="inlineStr">
         <is>
-          <t>03:30 PM – 04:30 PM</t>
+          <t>05:45 PM – 06:45 PM</t>
         </is>
       </c>
       <c r="E276" t="inlineStr">
@@ -15936,19 +15936,19 @@
     </row>
     <row r="278">
       <c r="A278" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="B278" t="inlineStr">
         <is>
-          <t>Saturday, September 6, 2026</t>
+          <t>Tuesday, September 2, 2026</t>
         </is>
       </c>
       <c r="C278" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D278" t="inlineStr">
         <is>
-          <t>03:30 PM – 04:30 PM</t>
+          <t>04:45 PM – 05:45 PM</t>
         </is>
       </c>
       <c r="E278" t="inlineStr">
@@ -15992,19 +15992,19 @@
     </row>
     <row r="279">
       <c r="A279" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B279" t="inlineStr">
         <is>
-          <t>Tuesday, September 2, 2026</t>
+          <t>Wednesday, September 3, 2026</t>
         </is>
       </c>
       <c r="C279" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D279" t="inlineStr">
         <is>
-          <t>04:45 PM – 05:45 PM</t>
+          <t>03:30 PM – 04:30 PM</t>
         </is>
       </c>
       <c r="E279" t="inlineStr">
@@ -16048,11 +16048,11 @@
     </row>
     <row r="280">
       <c r="A280" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B280" t="inlineStr">
         <is>
-          <t>Wednesday, September 3, 2026</t>
+          <t>Tuesday, September 2, 2026</t>
         </is>
       </c>
       <c r="C280" t="n">
@@ -16112,11 +16112,11 @@
         </is>
       </c>
       <c r="C281" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D281" t="inlineStr">
         <is>
-          <t>05:45 PM – 06:45 PM</t>
+          <t>03:30 PM – 04:30 PM</t>
         </is>
       </c>
       <c r="E281" t="inlineStr">
@@ -16160,19 +16160,19 @@
     </row>
     <row r="282">
       <c r="A282" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B282" t="inlineStr">
         <is>
-          <t>Sunday, September 7, 2026</t>
+          <t>Saturday, September 6, 2026</t>
         </is>
       </c>
       <c r="C282" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D282" t="inlineStr">
         <is>
-          <t>05:45 PM – 06:45 PM</t>
+          <t>04:45 PM – 05:45 PM</t>
         </is>
       </c>
       <c r="E282" t="inlineStr">
@@ -16216,11 +16216,11 @@
     </row>
     <row r="283">
       <c r="A283" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B283" t="inlineStr">
         <is>
-          <t>Wednesday, September 3, 2026</t>
+          <t>Saturday, September 6, 2026</t>
         </is>
       </c>
       <c r="C283" t="n">
@@ -16272,11 +16272,11 @@
     </row>
     <row r="284">
       <c r="A284" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B284" t="inlineStr">
         <is>
-          <t>Saturday, September 6, 2026</t>
+          <t>Wednesday, September 3, 2026</t>
         </is>
       </c>
       <c r="C284" t="n">
@@ -16336,11 +16336,11 @@
         </is>
       </c>
       <c r="C285" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D285" t="inlineStr">
         <is>
-          <t>05:45 PM – 06:45 PM</t>
+          <t>03:30 PM – 04:30 PM</t>
         </is>
       </c>
       <c r="E285" t="inlineStr">
@@ -16440,19 +16440,19 @@
     </row>
     <row r="287">
       <c r="A287" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="B287" t="inlineStr">
         <is>
-          <t>Saturday, September 6, 2026</t>
+          <t>Tuesday, September 2, 2026</t>
         </is>
       </c>
       <c r="C287" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D287" t="inlineStr">
         <is>
-          <t>04:45 PM – 05:45 PM</t>
+          <t>03:30 PM – 04:30 PM</t>
         </is>
       </c>
       <c r="E287" t="inlineStr">
@@ -16496,19 +16496,19 @@
     </row>
     <row r="288">
       <c r="A288" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B288" t="inlineStr">
         <is>
-          <t>Saturday, September 6, 2026</t>
+          <t>Wednesday, September 3, 2026</t>
         </is>
       </c>
       <c r="C288" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D288" t="inlineStr">
         <is>
-          <t>03:30 PM – 04:30 PM</t>
+          <t>04:45 PM – 05:45 PM</t>
         </is>
       </c>
       <c r="E288" t="inlineStr">
@@ -16552,11 +16552,11 @@
     </row>
     <row r="289">
       <c r="A289" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="B289" t="inlineStr">
         <is>
-          <t>Sunday, September 7, 2026</t>
+          <t>Tuesday, September 2, 2026</t>
         </is>
       </c>
       <c r="C289" t="n">
@@ -16608,19 +16608,19 @@
     </row>
     <row r="290">
       <c r="A290" t="n">
+        <v>1</v>
+      </c>
+      <c r="B290" t="inlineStr">
+        <is>
+          <t>Tuesday, September 2, 2026</t>
+        </is>
+      </c>
+      <c r="C290" t="n">
         <v>3</v>
       </c>
-      <c r="B290" t="inlineStr">
-        <is>
-          <t>Saturday, September 6, 2026</t>
-        </is>
-      </c>
-      <c r="C290" t="n">
-        <v>2</v>
-      </c>
       <c r="D290" t="inlineStr">
         <is>
-          <t>04:45 PM – 05:45 PM</t>
+          <t>05:45 PM – 06:45 PM</t>
         </is>
       </c>
       <c r="E290" t="inlineStr">
@@ -16664,11 +16664,11 @@
     </row>
     <row r="291">
       <c r="A291" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="B291" t="inlineStr">
         <is>
-          <t>Wednesday, September 3, 2026</t>
+          <t>Sunday, September 7, 2026</t>
         </is>
       </c>
       <c r="C291" t="n">
@@ -16720,19 +16720,19 @@
     </row>
     <row r="292">
       <c r="A292" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B292" t="inlineStr">
         <is>
-          <t>Sunday, September 7, 2026</t>
+          <t>Saturday, September 6, 2026</t>
         </is>
       </c>
       <c r="C292" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D292" t="inlineStr">
         <is>
-          <t>03:30 PM – 04:30 PM</t>
+          <t>05:45 PM – 06:45 PM</t>
         </is>
       </c>
       <c r="E292" t="inlineStr">
@@ -16776,19 +16776,19 @@
     </row>
     <row r="293">
       <c r="A293" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B293" t="inlineStr">
         <is>
-          <t>Tuesday, September 2, 2026</t>
+          <t>Wednesday, September 3, 2026</t>
         </is>
       </c>
       <c r="C293" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D293" t="inlineStr">
         <is>
-          <t>04:45 PM – 05:45 PM</t>
+          <t>05:45 PM – 06:45 PM</t>
         </is>
       </c>
       <c r="E293" t="inlineStr">
@@ -16832,19 +16832,19 @@
     </row>
     <row r="294">
       <c r="A294" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="B294" t="inlineStr">
         <is>
-          <t>Tuesday, September 2, 2026</t>
+          <t>Saturday, September 6, 2026</t>
         </is>
       </c>
       <c r="C294" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D294" t="inlineStr">
         <is>
-          <t>03:30 PM – 04:30 PM</t>
+          <t>04:45 PM – 05:45 PM</t>
         </is>
       </c>
       <c r="E294" t="inlineStr">
@@ -16888,19 +16888,19 @@
     </row>
     <row r="295">
       <c r="A295" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B295" t="inlineStr">
         <is>
-          <t>Sunday, September 7, 2026</t>
+          <t>Saturday, September 6, 2026</t>
         </is>
       </c>
       <c r="C295" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D295" t="inlineStr">
         <is>
-          <t>04:45 PM – 05:45 PM</t>
+          <t>03:30 PM – 04:30 PM</t>
         </is>
       </c>
       <c r="E295" t="inlineStr">
@@ -16944,19 +16944,19 @@
     </row>
     <row r="296">
       <c r="A296" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B296" t="inlineStr">
         <is>
-          <t>Saturday, September 6, 2026</t>
+          <t>Wednesday, September 3, 2026</t>
         </is>
       </c>
       <c r="C296" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D296" t="inlineStr">
         <is>
-          <t>03:30 PM – 04:30 PM</t>
+          <t>04:45 PM – 05:45 PM</t>
         </is>
       </c>
       <c r="E296" t="inlineStr">
@@ -17008,11 +17008,11 @@
         </is>
       </c>
       <c r="C297" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D297" t="inlineStr">
         <is>
-          <t>05:45 PM – 06:45 PM</t>
+          <t>04:45 PM – 05:45 PM</t>
         </is>
       </c>
       <c r="E297" t="inlineStr">
@@ -17056,11 +17056,11 @@
     </row>
     <row r="298">
       <c r="A298" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B298" t="inlineStr">
         <is>
-          <t>Wednesday, September 3, 2026</t>
+          <t>Tuesday, September 2, 2026</t>
         </is>
       </c>
       <c r="C298" t="n">
@@ -17112,11 +17112,11 @@
     </row>
     <row r="299">
       <c r="A299" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B299" t="inlineStr">
         <is>
-          <t>Saturday, September 6, 2026</t>
+          <t>Sunday, September 7, 2026</t>
         </is>
       </c>
       <c r="C299" t="n">
@@ -17168,19 +17168,19 @@
     </row>
     <row r="300">
       <c r="A300" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="B300" t="inlineStr">
         <is>
-          <t>Tuesday, September 2, 2026</t>
+          <t>Saturday, September 6, 2026</t>
         </is>
       </c>
       <c r="C300" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D300" t="inlineStr">
         <is>
-          <t>05:45 PM – 06:45 PM</t>
+          <t>03:30 PM – 04:30 PM</t>
         </is>
       </c>
       <c r="E300" t="inlineStr">
@@ -17224,11 +17224,11 @@
     </row>
     <row r="301">
       <c r="A301" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B301" t="inlineStr">
         <is>
-          <t>Wednesday, September 3, 2026</t>
+          <t>Saturday, September 6, 2026</t>
         </is>
       </c>
       <c r="C301" t="n">
@@ -17280,19 +17280,19 @@
     </row>
     <row r="302">
       <c r="A302" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="B302" t="inlineStr">
         <is>
-          <t>Tuesday, September 2, 2026</t>
+          <t>Saturday, September 6, 2026</t>
         </is>
       </c>
       <c r="C302" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D302" t="inlineStr">
         <is>
-          <t>04:45 PM – 05:45 PM</t>
+          <t>05:45 PM – 06:45 PM</t>
         </is>
       </c>
       <c r="E302" t="inlineStr">
@@ -17336,11 +17336,11 @@
     </row>
     <row r="303">
       <c r="A303" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="B303" t="inlineStr">
         <is>
-          <t>Sunday, September 7, 2026</t>
+          <t>Wednesday, September 3, 2026</t>
         </is>
       </c>
       <c r="C303" t="n">
@@ -17392,11 +17392,11 @@
     </row>
     <row r="304">
       <c r="A304" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B304" t="inlineStr">
         <is>
-          <t>Saturday, September 6, 2026</t>
+          <t>Wednesday, September 3, 2026</t>
         </is>
       </c>
       <c r="C304" t="n">
@@ -17456,11 +17456,11 @@
         </is>
       </c>
       <c r="C305" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D305" t="inlineStr">
         <is>
-          <t>03:30 PM – 04:30 PM</t>
+          <t>04:45 PM – 05:45 PM</t>
         </is>
       </c>
       <c r="E305" t="inlineStr">
@@ -17504,19 +17504,19 @@
     </row>
     <row r="306">
       <c r="A306" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B306" t="inlineStr">
         <is>
-          <t>Wednesday, September 3, 2026</t>
+          <t>Tuesday, September 2, 2026</t>
         </is>
       </c>
       <c r="C306" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D306" t="inlineStr">
         <is>
-          <t>05:45 PM – 06:45 PM</t>
+          <t>04:45 PM – 05:45 PM</t>
         </is>
       </c>
       <c r="E306" t="inlineStr">
@@ -17568,11 +17568,11 @@
         </is>
       </c>
       <c r="C307" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D307" t="inlineStr">
         <is>
-          <t>03:30 PM – 04:30 PM</t>
+          <t>05:45 PM – 06:45 PM</t>
         </is>
       </c>
       <c r="E307" t="inlineStr">
@@ -17616,19 +17616,19 @@
     </row>
     <row r="308">
       <c r="A308" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="B308" t="inlineStr">
         <is>
-          <t>Sunday, September 7, 2026</t>
+          <t>Tuesday, September 2, 2026</t>
         </is>
       </c>
       <c r="C308" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D308" t="inlineStr">
         <is>
-          <t>05:45 PM – 06:45 PM</t>
+          <t>03:30 PM – 04:30 PM</t>
         </is>
       </c>
       <c r="E308" t="inlineStr">
@@ -17672,19 +17672,19 @@
     </row>
     <row r="309">
       <c r="A309" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B309" t="inlineStr">
         <is>
-          <t>Saturday, September 6, 2026</t>
+          <t>Sunday, September 7, 2026</t>
         </is>
       </c>
       <c r="C309" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D309" t="inlineStr">
         <is>
-          <t>04:45 PM – 05:45 PM</t>
+          <t>03:30 PM – 04:30 PM</t>
         </is>
       </c>
       <c r="E309" t="inlineStr">
@@ -17728,19 +17728,19 @@
     </row>
     <row r="310">
       <c r="A310" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B310" t="inlineStr">
         <is>
-          <t>Saturday, September 6, 2026</t>
+          <t>Sunday, September 7, 2026</t>
         </is>
       </c>
       <c r="C310" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D310" t="inlineStr">
         <is>
-          <t>03:30 PM – 04:30 PM</t>
+          <t>04:45 PM – 05:45 PM</t>
         </is>
       </c>
       <c r="E310" t="inlineStr">
@@ -17792,11 +17792,11 @@
         </is>
       </c>
       <c r="C311" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D311" t="inlineStr">
         <is>
-          <t>03:30 PM – 04:30 PM</t>
+          <t>05:45 PM – 06:45 PM</t>
         </is>
       </c>
       <c r="E311" t="inlineStr">
@@ -17840,19 +17840,19 @@
     </row>
     <row r="312">
       <c r="A312" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B312" t="inlineStr">
         <is>
-          <t>Sunday, September 7, 2026</t>
+          <t>Saturday, September 6, 2026</t>
         </is>
       </c>
       <c r="C312" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D312" t="inlineStr">
         <is>
-          <t>05:45 PM – 06:45 PM</t>
+          <t>03:30 PM – 04:30 PM</t>
         </is>
       </c>
       <c r="E312" t="inlineStr">
@@ -17896,19 +17896,19 @@
     </row>
     <row r="313">
       <c r="A313" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B313" t="inlineStr">
         <is>
-          <t>Tuesday, September 2, 2026</t>
+          <t>Wednesday, September 3, 2026</t>
         </is>
       </c>
       <c r="C313" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D313" t="inlineStr">
         <is>
-          <t>04:45 PM – 05:45 PM</t>
+          <t>05:45 PM – 06:45 PM</t>
         </is>
       </c>
       <c r="E313" t="inlineStr">
@@ -17952,19 +17952,19 @@
     </row>
     <row r="314">
       <c r="A314" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B314" t="inlineStr">
         <is>
-          <t>Wednesday, September 3, 2026</t>
+          <t>Tuesday, September 2, 2026</t>
         </is>
       </c>
       <c r="C314" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D314" t="inlineStr">
         <is>
-          <t>04:45 PM – 05:45 PM</t>
+          <t>05:45 PM – 06:45 PM</t>
         </is>
       </c>
       <c r="E314" t="inlineStr">
@@ -18008,19 +18008,19 @@
     </row>
     <row r="315">
       <c r="A315" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="B315" t="inlineStr">
         <is>
-          <t>Saturday, September 6, 2026</t>
+          <t>Tuesday, September 2, 2026</t>
         </is>
       </c>
       <c r="C315" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D315" t="inlineStr">
         <is>
-          <t>05:45 PM – 06:45 PM</t>
+          <t>03:30 PM – 04:30 PM</t>
         </is>
       </c>
       <c r="E315" t="inlineStr">
@@ -18064,11 +18064,11 @@
     </row>
     <row r="316">
       <c r="A316" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B316" t="inlineStr">
         <is>
-          <t>Tuesday, September 2, 2026</t>
+          <t>Wednesday, September 3, 2026</t>
         </is>
       </c>
       <c r="C316" t="n">
@@ -18120,19 +18120,19 @@
     </row>
     <row r="317">
       <c r="A317" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B317" t="inlineStr">
         <is>
-          <t>Wednesday, September 3, 2026</t>
+          <t>Saturday, September 6, 2026</t>
         </is>
       </c>
       <c r="C317" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D317" t="inlineStr">
         <is>
-          <t>03:30 PM – 04:30 PM</t>
+          <t>04:45 PM – 05:45 PM</t>
         </is>
       </c>
       <c r="E317" t="inlineStr">
@@ -18176,19 +18176,19 @@
     </row>
     <row r="318">
       <c r="A318" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B318" t="inlineStr">
         <is>
-          <t>Wednesday, September 3, 2026</t>
+          <t>Tuesday, September 2, 2026</t>
         </is>
       </c>
       <c r="C318" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D318" t="inlineStr">
         <is>
-          <t>05:45 PM – 06:45 PM</t>
+          <t>04:45 PM – 05:45 PM</t>
         </is>
       </c>
       <c r="E318" t="inlineStr">
@@ -18240,11 +18240,11 @@
         </is>
       </c>
       <c r="C319" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D319" t="inlineStr">
         <is>
-          <t>04:45 PM – 05:45 PM</t>
+          <t>05:45 PM – 06:45 PM</t>
         </is>
       </c>
       <c r="E319" t="inlineStr">
@@ -18288,19 +18288,19 @@
     </row>
     <row r="320">
       <c r="A320" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B320" t="inlineStr">
         <is>
-          <t>Wednesday, September 3, 2026</t>
+          <t>Saturday, September 6, 2026</t>
         </is>
       </c>
       <c r="C320" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D320" t="inlineStr">
         <is>
-          <t>04:45 PM – 05:45 PM</t>
+          <t>05:45 PM – 06:45 PM</t>
         </is>
       </c>
       <c r="E320" t="inlineStr">
@@ -18352,11 +18352,11 @@
         </is>
       </c>
       <c r="C321" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D321" t="inlineStr">
         <is>
-          <t>03:30 PM – 04:30 PM</t>
+          <t>04:45 PM – 05:45 PM</t>
         </is>
       </c>
       <c r="E321" t="inlineStr">
@@ -18400,19 +18400,19 @@
     </row>
     <row r="322">
       <c r="A322" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B322" t="inlineStr">
         <is>
-          <t>Wednesday, September 3, 2026</t>
+          <t>Saturday, September 6, 2026</t>
         </is>
       </c>
       <c r="C322" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D322" t="inlineStr">
         <is>
-          <t>05:45 PM – 06:45 PM</t>
+          <t>03:30 PM – 04:30 PM</t>
         </is>
       </c>
       <c r="E322" t="inlineStr">
@@ -18464,11 +18464,11 @@
         </is>
       </c>
       <c r="C323" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D323" t="inlineStr">
         <is>
-          <t>03:30 PM – 04:30 PM</t>
+          <t>04:45 PM – 05:45 PM</t>
         </is>
       </c>
       <c r="E323" t="inlineStr">
@@ -18520,11 +18520,11 @@
         </is>
       </c>
       <c r="C324" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D324" t="inlineStr">
         <is>
-          <t>05:45 PM – 06:45 PM</t>
+          <t>03:30 PM – 04:30 PM</t>
         </is>
       </c>
       <c r="E324" t="inlineStr">
@@ -18568,19 +18568,19 @@
     </row>
     <row r="325">
       <c r="A325" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B325" t="inlineStr">
         <is>
-          <t>Tuesday, September 2, 2026</t>
+          <t>Wednesday, September 3, 2026</t>
         </is>
       </c>
       <c r="C325" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D325" t="inlineStr">
         <is>
-          <t>04:45 PM – 05:45 PM</t>
+          <t>03:30 PM – 04:30 PM</t>
         </is>
       </c>
       <c r="E325" t="inlineStr">
@@ -18632,11 +18632,11 @@
         </is>
       </c>
       <c r="C326" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D326" t="inlineStr">
         <is>
-          <t>03:30 PM – 04:30 PM</t>
+          <t>05:45 PM – 06:45 PM</t>
         </is>
       </c>
       <c r="E326" t="inlineStr">
@@ -18680,19 +18680,19 @@
     </row>
     <row r="327">
       <c r="A327" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="B327" t="inlineStr">
         <is>
-          <t>Sunday, September 7, 2026</t>
+          <t>Tuesday, September 2, 2026</t>
         </is>
       </c>
       <c r="C327" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D327" t="inlineStr">
         <is>
-          <t>03:30 PM – 04:30 PM</t>
+          <t>04:45 PM – 05:45 PM</t>
         </is>
       </c>
       <c r="E327" t="inlineStr">
@@ -18744,11 +18744,11 @@
         </is>
       </c>
       <c r="C328" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D328" t="inlineStr">
         <is>
-          <t>05:45 PM – 06:45 PM</t>
+          <t>03:30 PM – 04:30 PM</t>
         </is>
       </c>
       <c r="E328" t="inlineStr">
@@ -18792,19 +18792,19 @@
     </row>
     <row r="329">
       <c r="A329" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B329" t="inlineStr">
         <is>
-          <t>Saturday, September 6, 2026</t>
+          <t>Sunday, September 7, 2026</t>
         </is>
       </c>
       <c r="C329" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D329" t="inlineStr">
         <is>
-          <t>05:45 PM – 06:45 PM</t>
+          <t>03:30 PM – 04:30 PM</t>
         </is>
       </c>
       <c r="E329" t="inlineStr">
@@ -18848,19 +18848,19 @@
     </row>
     <row r="330">
       <c r="A330" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="B330" t="inlineStr">
         <is>
-          <t>Tuesday, September 2, 2026</t>
+          <t>Saturday, September 6, 2026</t>
         </is>
       </c>
       <c r="C330" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D330" t="inlineStr">
         <is>
-          <t>04:45 PM – 05:45 PM</t>
+          <t>05:45 PM – 06:45 PM</t>
         </is>
       </c>
       <c r="E330" t="inlineStr">
@@ -18904,19 +18904,19 @@
     </row>
     <row r="331">
       <c r="A331" t="n">
+        <v>2</v>
+      </c>
+      <c r="B331" t="inlineStr">
+        <is>
+          <t>Wednesday, September 3, 2026</t>
+        </is>
+      </c>
+      <c r="C331" t="n">
         <v>3</v>
       </c>
-      <c r="B331" t="inlineStr">
-        <is>
-          <t>Saturday, September 6, 2026</t>
-        </is>
-      </c>
-      <c r="C331" t="n">
-        <v>1</v>
-      </c>
       <c r="D331" t="inlineStr">
         <is>
-          <t>03:30 PM – 04:30 PM</t>
+          <t>05:45 PM – 06:45 PM</t>
         </is>
       </c>
       <c r="E331" t="inlineStr">
@@ -18960,19 +18960,19 @@
     </row>
     <row r="332">
       <c r="A332" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="B332" t="inlineStr">
         <is>
-          <t>Wednesday, September 3, 2026</t>
+          <t>Sunday, September 7, 2026</t>
         </is>
       </c>
       <c r="C332" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D332" t="inlineStr">
         <is>
-          <t>03:30 PM – 04:30 PM</t>
+          <t>04:45 PM – 05:45 PM</t>
         </is>
       </c>
       <c r="E332" t="inlineStr">
@@ -19072,19 +19072,19 @@
     </row>
     <row r="334">
       <c r="A334" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="B334" t="inlineStr">
         <is>
-          <t>Sunday, September 7, 2026</t>
+          <t>Wednesday, September 3, 2026</t>
         </is>
       </c>
       <c r="C334" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D334" t="inlineStr">
         <is>
-          <t>05:45 PM – 06:45 PM</t>
+          <t>04:45 PM – 05:45 PM</t>
         </is>
       </c>
       <c r="E334" t="inlineStr">
@@ -19128,19 +19128,19 @@
     </row>
     <row r="335">
       <c r="A335" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B335" t="inlineStr">
         <is>
-          <t>Tuesday, September 2, 2026</t>
+          <t>Wednesday, September 3, 2026</t>
         </is>
       </c>
       <c r="C335" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D335" t="inlineStr">
         <is>
-          <t>05:45 PM – 06:45 PM</t>
+          <t>03:30 PM – 04:30 PM</t>
         </is>
       </c>
       <c r="E335" t="inlineStr">
@@ -19184,19 +19184,19 @@
     </row>
     <row r="336">
       <c r="A336" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B336" t="inlineStr">
         <is>
-          <t>Wednesday, September 3, 2026</t>
+          <t>Tuesday, September 2, 2026</t>
         </is>
       </c>
       <c r="C336" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D336" t="inlineStr">
         <is>
-          <t>04:45 PM – 05:45 PM</t>
+          <t>05:45 PM – 06:45 PM</t>
         </is>
       </c>
       <c r="E336" t="inlineStr">
@@ -19240,19 +19240,19 @@
     </row>
     <row r="337">
       <c r="A337" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="B337" t="inlineStr">
         <is>
-          <t>Sunday, September 7, 2026</t>
+          <t>Tuesday, September 2, 2026</t>
         </is>
       </c>
       <c r="C337" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D337" t="inlineStr">
         <is>
-          <t>03:30 PM – 04:30 PM</t>
+          <t>04:45 PM – 05:45 PM</t>
         </is>
       </c>
       <c r="E337" t="inlineStr">
@@ -19296,19 +19296,19 @@
     </row>
     <row r="338">
       <c r="A338" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B338" t="inlineStr">
         <is>
-          <t>Wednesday, September 3, 2026</t>
+          <t>Tuesday, September 2, 2026</t>
         </is>
       </c>
       <c r="C338" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D338" t="inlineStr">
         <is>
-          <t>05:45 PM – 06:45 PM</t>
+          <t>03:30 PM – 04:30 PM</t>
         </is>
       </c>
       <c r="E338" t="inlineStr">
@@ -19352,11 +19352,11 @@
     </row>
     <row r="339">
       <c r="A339" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="B339" t="inlineStr">
         <is>
-          <t>Tuesday, September 2, 2026</t>
+          <t>Sunday, September 7, 2026</t>
         </is>
       </c>
       <c r="C339" t="n">
@@ -19408,19 +19408,19 @@
     </row>
     <row r="340">
       <c r="A340" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B340" t="inlineStr">
         <is>
-          <t>Wednesday, September 3, 2026</t>
+          <t>Tuesday, September 2, 2026</t>
         </is>
       </c>
       <c r="C340" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D340" t="inlineStr">
         <is>
-          <t>05:45 PM – 06:45 PM</t>
+          <t>03:30 PM – 04:30 PM</t>
         </is>
       </c>
       <c r="E340" t="inlineStr">
@@ -19520,19 +19520,19 @@
     </row>
     <row r="342">
       <c r="A342" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="B342" t="inlineStr">
         <is>
-          <t>Sunday, September 7, 2026</t>
+          <t>Wednesday, September 3, 2026</t>
         </is>
       </c>
       <c r="C342" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D342" t="inlineStr">
         <is>
-          <t>05:45 PM – 06:45 PM</t>
+          <t>03:30 PM – 04:30 PM</t>
         </is>
       </c>
       <c r="E342" t="inlineStr">
@@ -19584,11 +19584,11 @@
         </is>
       </c>
       <c r="C343" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D343" t="inlineStr">
         <is>
-          <t>03:30 PM – 04:30 PM</t>
+          <t>05:45 PM – 06:45 PM</t>
         </is>
       </c>
       <c r="E343" t="inlineStr">
@@ -19632,11 +19632,11 @@
     </row>
     <row r="344">
       <c r="A344" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="B344" t="inlineStr">
         <is>
-          <t>Tuesday, September 2, 2026</t>
+          <t>Sunday, September 7, 2026</t>
         </is>
       </c>
       <c r="C344" t="n">
@@ -19688,11 +19688,11 @@
     </row>
     <row r="345">
       <c r="A345" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="B345" t="inlineStr">
         <is>
-          <t>Tuesday, September 2, 2026</t>
+          <t>Sunday, September 7, 2026</t>
         </is>
       </c>
       <c r="C345" t="n">
@@ -19744,11 +19744,11 @@
     </row>
     <row r="346">
       <c r="A346" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="B346" t="inlineStr">
         <is>
-          <t>Saturday, September 6, 2026</t>
+          <t>Tuesday, September 2, 2026</t>
         </is>
       </c>
       <c r="C346" t="n">
@@ -19800,19 +19800,19 @@
     </row>
     <row r="347">
       <c r="A347" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="B347" t="inlineStr">
         <is>
-          <t>Saturday, September 6, 2026</t>
+          <t>Tuesday, September 2, 2026</t>
         </is>
       </c>
       <c r="C347" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D347" t="inlineStr">
         <is>
-          <t>03:30 PM – 04:30 PM</t>
+          <t>04:45 PM – 05:45 PM</t>
         </is>
       </c>
       <c r="E347" t="inlineStr">
@@ -19856,11 +19856,11 @@
     </row>
     <row r="348">
       <c r="A348" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B348" t="inlineStr">
         <is>
-          <t>Sunday, September 7, 2026</t>
+          <t>Saturday, September 6, 2026</t>
         </is>
       </c>
       <c r="C348" t="n">
@@ -19920,11 +19920,11 @@
         </is>
       </c>
       <c r="C349" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D349" t="inlineStr">
         <is>
-          <t>05:45 PM – 06:45 PM</t>
+          <t>04:45 PM – 05:45 PM</t>
         </is>
       </c>
       <c r="E349" t="inlineStr">
@@ -19968,11 +19968,11 @@
     </row>
     <row r="350">
       <c r="A350" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B350" t="inlineStr">
         <is>
-          <t>Saturday, September 6, 2026</t>
+          <t>Wednesday, September 3, 2026</t>
         </is>
       </c>
       <c r="C350" t="n">
@@ -20024,19 +20024,19 @@
     </row>
     <row r="351">
       <c r="A351" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="B351" t="inlineStr">
         <is>
-          <t>Wednesday, September 3, 2026</t>
+          <t>Sunday, September 7, 2026</t>
         </is>
       </c>
       <c r="C351" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D351" t="inlineStr">
         <is>
-          <t>05:45 PM – 06:45 PM</t>
+          <t>03:30 PM – 04:30 PM</t>
         </is>
       </c>
       <c r="E351" t="inlineStr">
@@ -20080,19 +20080,19 @@
     </row>
     <row r="352">
       <c r="A352" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B352" t="inlineStr">
         <is>
-          <t>Wednesday, September 3, 2026</t>
+          <t>Saturday, September 6, 2026</t>
         </is>
       </c>
       <c r="C352" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D352" t="inlineStr">
         <is>
-          <t>03:30 PM – 04:30 PM</t>
+          <t>05:45 PM – 06:45 PM</t>
         </is>
       </c>
       <c r="E352" t="inlineStr">
@@ -20144,11 +20144,11 @@
         </is>
       </c>
       <c r="C353" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D353" t="inlineStr">
         <is>
-          <t>03:30 PM – 04:30 PM</t>
+          <t>04:45 PM – 05:45 PM</t>
         </is>
       </c>
       <c r="E353" t="inlineStr">
@@ -20192,19 +20192,19 @@
     </row>
     <row r="354">
       <c r="A354" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="B354" t="inlineStr">
         <is>
-          <t>Tuesday, September 2, 2026</t>
+          <t>Saturday, September 6, 2026</t>
         </is>
       </c>
       <c r="C354" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D354" t="inlineStr">
         <is>
-          <t>05:45 PM – 06:45 PM</t>
+          <t>03:30 PM – 04:30 PM</t>
         </is>
       </c>
       <c r="E354" t="inlineStr">
@@ -20248,19 +20248,19 @@
     </row>
     <row r="355">
       <c r="A355" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B355" t="inlineStr">
         <is>
-          <t>Tuesday, September 2, 2026</t>
+          <t>Wednesday, September 3, 2026</t>
         </is>
       </c>
       <c r="C355" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D355" t="inlineStr">
         <is>
-          <t>04:45 PM – 05:45 PM</t>
+          <t>03:30 PM – 04:30 PM</t>
         </is>
       </c>
       <c r="E355" t="inlineStr">
@@ -20304,11 +20304,11 @@
     </row>
     <row r="356">
       <c r="A356" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="B356" t="inlineStr">
         <is>
-          <t>Sunday, September 7, 2026</t>
+          <t>Tuesday, September 2, 2026</t>
         </is>
       </c>
       <c r="C356" t="n">
@@ -20360,19 +20360,19 @@
     </row>
     <row r="357">
       <c r="A357" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="B357" t="inlineStr">
         <is>
-          <t>Sunday, September 7, 2026</t>
+          <t>Wednesday, September 3, 2026</t>
         </is>
       </c>
       <c r="C357" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D357" t="inlineStr">
         <is>
-          <t>03:30 PM – 04:30 PM</t>
+          <t>04:45 PM – 05:45 PM</t>
         </is>
       </c>
       <c r="E357" t="inlineStr">
@@ -20416,19 +20416,19 @@
     </row>
     <row r="358">
       <c r="A358" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="B358" t="inlineStr">
         <is>
-          <t>Saturday, September 6, 2026</t>
+          <t>Tuesday, September 2, 2026</t>
         </is>
       </c>
       <c r="C358" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D358" t="inlineStr">
         <is>
-          <t>04:45 PM – 05:45 PM</t>
+          <t>03:30 PM – 04:30 PM</t>
         </is>
       </c>
       <c r="E358" t="inlineStr">
@@ -20472,11 +20472,11 @@
     </row>
     <row r="359">
       <c r="A359" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B359" t="inlineStr">
         <is>
-          <t>Saturday, September 6, 2026</t>
+          <t>Sunday, September 7, 2026</t>
         </is>
       </c>
       <c r="C359" t="n">
@@ -20528,19 +20528,19 @@
     </row>
     <row r="360">
       <c r="A360" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B360" t="inlineStr">
         <is>
-          <t>Wednesday, September 3, 2026</t>
+          <t>Saturday, September 6, 2026</t>
         </is>
       </c>
       <c r="C360" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D360" t="inlineStr">
         <is>
-          <t>04:45 PM – 05:45 PM</t>
+          <t>05:45 PM – 06:45 PM</t>
         </is>
       </c>
       <c r="E360" t="inlineStr">
@@ -20584,19 +20584,19 @@
     </row>
     <row r="361">
       <c r="A361" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B361" t="inlineStr">
         <is>
-          <t>Tuesday, September 2, 2026</t>
+          <t>Wednesday, September 3, 2026</t>
         </is>
       </c>
       <c r="C361" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D361" t="inlineStr">
         <is>
-          <t>04:45 PM – 05:45 PM</t>
+          <t>03:30 PM – 04:30 PM</t>
         </is>
       </c>
       <c r="E361" t="inlineStr">
@@ -20640,11 +20640,11 @@
     </row>
     <row r="362">
       <c r="A362" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B362" t="inlineStr">
         <is>
-          <t>Sunday, September 7, 2026</t>
+          <t>Saturday, September 6, 2026</t>
         </is>
       </c>
       <c r="C362" t="n">
@@ -20752,19 +20752,19 @@
     </row>
     <row r="364">
       <c r="A364" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B364" t="inlineStr">
         <is>
-          <t>Tuesday, September 2, 2026</t>
+          <t>Wednesday, September 3, 2026</t>
         </is>
       </c>
       <c r="C364" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D364" t="inlineStr">
         <is>
-          <t>05:45 PM – 06:45 PM</t>
+          <t>04:45 PM – 05:45 PM</t>
         </is>
       </c>
       <c r="E364" t="inlineStr">
@@ -20808,11 +20808,11 @@
     </row>
     <row r="365">
       <c r="A365" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B365" t="inlineStr">
         <is>
-          <t>Saturday, September 6, 2026</t>
+          <t>Sunday, September 7, 2026</t>
         </is>
       </c>
       <c r="C365" t="n">
@@ -20864,19 +20864,19 @@
     </row>
     <row r="366">
       <c r="A366" t="n">
+        <v>1</v>
+      </c>
+      <c r="B366" t="inlineStr">
+        <is>
+          <t>Tuesday, September 2, 2026</t>
+        </is>
+      </c>
+      <c r="C366" t="n">
         <v>3</v>
       </c>
-      <c r="B366" t="inlineStr">
-        <is>
-          <t>Saturday, September 6, 2026</t>
-        </is>
-      </c>
-      <c r="C366" t="n">
-        <v>2</v>
-      </c>
       <c r="D366" t="inlineStr">
         <is>
-          <t>04:45 PM – 05:45 PM</t>
+          <t>05:45 PM – 06:45 PM</t>
         </is>
       </c>
       <c r="E366" t="inlineStr">
@@ -20920,11 +20920,11 @@
     </row>
     <row r="367">
       <c r="A367" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="B367" t="inlineStr">
         <is>
-          <t>Sunday, September 7, 2026</t>
+          <t>Tuesday, September 2, 2026</t>
         </is>
       </c>
       <c r="C367" t="n">
@@ -20976,11 +20976,11 @@
     </row>
     <row r="368">
       <c r="A368" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B368" t="inlineStr">
         <is>
-          <t>Wednesday, September 3, 2026</t>
+          <t>Tuesday, September 2, 2026</t>
         </is>
       </c>
       <c r="C368" t="n">
@@ -21032,19 +21032,19 @@
     </row>
     <row r="369">
       <c r="A369" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B369" t="inlineStr">
         <is>
-          <t>Saturday, September 6, 2026</t>
+          <t>Sunday, September 7, 2026</t>
         </is>
       </c>
       <c r="C369" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D369" t="inlineStr">
         <is>
-          <t>07:30 AM – 08:30 AM</t>
+          <t>08:45 AM – 09:45 AM</t>
         </is>
       </c>
       <c r="E369" t="inlineStr">
@@ -21096,11 +21096,11 @@
         </is>
       </c>
       <c r="C370" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D370" t="inlineStr">
         <is>
-          <t>10:00 AM – 11:00 AM</t>
+          <t>07:30 AM – 08:30 AM</t>
         </is>
       </c>
       <c r="E370" t="inlineStr">
@@ -21200,11 +21200,11 @@
     </row>
     <row r="372">
       <c r="A372" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="B372" t="inlineStr">
         <is>
-          <t>Tuesday, September 2, 2026</t>
+          <t>Saturday, September 6, 2026</t>
         </is>
       </c>
       <c r="C372" t="n">
@@ -21264,11 +21264,11 @@
         </is>
       </c>
       <c r="C373" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D373" t="inlineStr">
         <is>
-          <t>08:45 AM – 09:45 AM</t>
+          <t>10:00 AM – 11:00 AM</t>
         </is>
       </c>
       <c r="E373" t="inlineStr">
@@ -21312,11 +21312,11 @@
     </row>
     <row r="374">
       <c r="A374" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="B374" t="inlineStr">
         <is>
-          <t>Sunday, September 7, 2026</t>
+          <t>Wednesday, September 3, 2026</t>
         </is>
       </c>
       <c r="C374" t="n">
@@ -21376,11 +21376,11 @@
         </is>
       </c>
       <c r="C375" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D375" t="inlineStr">
         <is>
-          <t>10:00 AM – 11:00 AM</t>
+          <t>07:30 AM – 08:30 AM</t>
         </is>
       </c>
       <c r="E375" t="inlineStr">
@@ -21424,11 +21424,11 @@
     </row>
     <row r="376">
       <c r="A376" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="B376" t="inlineStr">
         <is>
-          <t>Saturday, September 6, 2026</t>
+          <t>Tuesday, September 2, 2026</t>
         </is>
       </c>
       <c r="C376" t="n">
@@ -21480,19 +21480,19 @@
     </row>
     <row r="377">
       <c r="A377" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="B377" t="inlineStr">
         <is>
-          <t>Sunday, September 7, 2026</t>
+          <t>Tuesday, September 2, 2026</t>
         </is>
       </c>
       <c r="C377" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D377" t="inlineStr">
         <is>
-          <t>07:30 AM – 09:30 AM</t>
+          <t>10:00 AM – 12:00 PM</t>
         </is>
       </c>
       <c r="E377" t="inlineStr">
@@ -21544,11 +21544,11 @@
         </is>
       </c>
       <c r="C378" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D378" t="inlineStr">
         <is>
-          <t>10:00 AM – 11:00 AM</t>
+          <t>07:30 AM – 08:30 AM</t>
         </is>
       </c>
       <c r="E378" t="inlineStr">
@@ -21600,11 +21600,11 @@
         </is>
       </c>
       <c r="C379" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D379" t="inlineStr">
         <is>
-          <t>07:30 AM – 08:30 AM</t>
+          <t>08:45 AM – 09:45 AM</t>
         </is>
       </c>
       <c r="E379" t="inlineStr">
@@ -21648,19 +21648,19 @@
     </row>
     <row r="380">
       <c r="A380" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="B380" t="inlineStr">
         <is>
-          <t>Tuesday, September 2, 2026</t>
+          <t>Sunday, September 7, 2026</t>
         </is>
       </c>
       <c r="C380" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D380" t="inlineStr">
         <is>
-          <t>10:00 AM – 12:00 PM</t>
+          <t>07:30 AM – 09:30 AM</t>
         </is>
       </c>
       <c r="E380" t="inlineStr">
@@ -21704,19 +21704,19 @@
     </row>
     <row r="381">
       <c r="A381" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B381" t="inlineStr">
         <is>
-          <t>Wednesday, September 3, 2026</t>
+          <t>Saturday, September 6, 2026</t>
         </is>
       </c>
       <c r="C381" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D381" t="inlineStr">
         <is>
-          <t>08:45 AM – 09:45 AM</t>
+          <t>10:00 AM – 11:00 AM</t>
         </is>
       </c>
       <c r="E381" t="inlineStr">
@@ -21760,19 +21760,19 @@
     </row>
     <row r="382">
       <c r="A382" t="n">
+        <v>2</v>
+      </c>
+      <c r="B382" t="inlineStr">
+        <is>
+          <t>Wednesday, September 3, 2026</t>
+        </is>
+      </c>
+      <c r="C382" t="n">
         <v>3</v>
       </c>
-      <c r="B382" t="inlineStr">
-        <is>
-          <t>Saturday, September 6, 2026</t>
-        </is>
-      </c>
-      <c r="C382" t="n">
-        <v>2</v>
-      </c>
       <c r="D382" t="inlineStr">
         <is>
-          <t>08:45 AM – 09:45 AM</t>
+          <t>10:00 AM – 11:00 AM</t>
         </is>
       </c>
       <c r="E382" t="inlineStr">
@@ -21816,19 +21816,19 @@
     </row>
     <row r="383">
       <c r="A383" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B383" t="inlineStr">
         <is>
-          <t>Sunday, September 7, 2026</t>
+          <t>Saturday, September 6, 2026</t>
         </is>
       </c>
       <c r="C383" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D383" t="inlineStr">
         <is>
-          <t>10:00 AM – 11:00 AM</t>
+          <t>08:45 AM – 09:45 AM</t>
         </is>
       </c>
       <c r="E383" t="inlineStr">
@@ -21872,19 +21872,19 @@
     </row>
     <row r="384">
       <c r="A384" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B384" t="inlineStr">
         <is>
-          <t>Tuesday, September 2, 2026</t>
+          <t>Wednesday, September 3, 2026</t>
         </is>
       </c>
       <c r="C384" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D384" t="inlineStr">
         <is>
-          <t>07:30 AM – 08:30 AM</t>
+          <t>08:45 AM – 09:45 AM</t>
         </is>
       </c>
       <c r="E384" t="inlineStr">
@@ -21928,19 +21928,19 @@
     </row>
     <row r="385">
       <c r="A385" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B385" t="inlineStr">
         <is>
-          <t>Tuesday, September 2, 2026</t>
+          <t>Wednesday, September 3, 2026</t>
         </is>
       </c>
       <c r="C385" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D385" t="inlineStr">
         <is>
-          <t>08:45 AM – 09:45 AM</t>
+          <t>07:30 AM – 08:30 AM</t>
         </is>
       </c>
       <c r="E385" t="inlineStr">
@@ -21984,19 +21984,19 @@
     </row>
     <row r="386">
       <c r="A386" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B386" t="inlineStr">
         <is>
-          <t>Wednesday, September 3, 2026</t>
+          <t>Tuesday, September 2, 2026</t>
         </is>
       </c>
       <c r="C386" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D386" t="inlineStr">
         <is>
-          <t>07:30 AM – 08:30 AM</t>
+          <t>08:45 AM – 09:45 AM</t>
         </is>
       </c>
       <c r="E386" t="inlineStr">
@@ -22040,19 +22040,19 @@
     </row>
     <row r="387">
       <c r="A387" t="n">
+        <v>1</v>
+      </c>
+      <c r="B387" t="inlineStr">
+        <is>
+          <t>Tuesday, September 2, 2026</t>
+        </is>
+      </c>
+      <c r="C387" t="n">
         <v>3</v>
       </c>
-      <c r="B387" t="inlineStr">
-        <is>
-          <t>Saturday, September 6, 2026</t>
-        </is>
-      </c>
-      <c r="C387" t="n">
-        <v>1</v>
-      </c>
       <c r="D387" t="inlineStr">
         <is>
-          <t>07:30 AM – 08:30 AM</t>
+          <t>10:00 AM – 11:00 AM</t>
         </is>
       </c>
       <c r="E387" t="inlineStr">
@@ -22096,19 +22096,19 @@
     </row>
     <row r="388">
       <c r="A388" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B388" t="inlineStr">
         <is>
-          <t>Wednesday, September 3, 2026</t>
+          <t>Tuesday, September 2, 2026</t>
         </is>
       </c>
       <c r="C388" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D388" t="inlineStr">
         <is>
-          <t>10:00 AM – 11:00 AM</t>
+          <t>07:30 AM – 08:30 AM</t>
         </is>
       </c>
       <c r="E388" t="inlineStr">
@@ -22160,11 +22160,11 @@
         </is>
       </c>
       <c r="C389" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D389" t="inlineStr">
         <is>
-          <t>08:45 AM – 09:45 AM</t>
+          <t>10:00 AM – 11:00 AM</t>
         </is>
       </c>
       <c r="E389" t="inlineStr">
@@ -22216,11 +22216,11 @@
         </is>
       </c>
       <c r="C390" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D390" t="inlineStr">
         <is>
-          <t>07:30 AM – 09:30 AM</t>
+          <t>09:45 AM – 11:45 AM</t>
         </is>
       </c>
       <c r="E390" t="inlineStr">
@@ -22264,19 +22264,19 @@
     </row>
     <row r="391">
       <c r="A391" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B391" t="inlineStr">
         <is>
-          <t>Wednesday, September 3, 2026</t>
+          <t>Saturday, September 6, 2026</t>
         </is>
       </c>
       <c r="C391" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D391" t="inlineStr">
         <is>
-          <t>08:45 AM – 09:45 AM</t>
+          <t>07:30 AM – 08:30 AM</t>
         </is>
       </c>
       <c r="E391" t="inlineStr">
@@ -22320,11 +22320,11 @@
     </row>
     <row r="392">
       <c r="A392" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B392" t="inlineStr">
         <is>
-          <t>Saturday, September 6, 2026</t>
+          <t>Wednesday, September 3, 2026</t>
         </is>
       </c>
       <c r="C392" t="n">
@@ -22384,11 +22384,11 @@
         </is>
       </c>
       <c r="C393" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D393" t="inlineStr">
         <is>
-          <t>07:30 AM – 08:30 AM</t>
+          <t>08:45 AM – 09:45 AM</t>
         </is>
       </c>
       <c r="E393" t="inlineStr">
@@ -22432,19 +22432,19 @@
     </row>
     <row r="394">
       <c r="A394" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="B394" t="inlineStr">
         <is>
-          <t>Sunday, September 7, 2026</t>
+          <t>Wednesday, September 3, 2026</t>
         </is>
       </c>
       <c r="C394" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D394" t="inlineStr">
         <is>
-          <t>08:45 AM – 09:45 AM</t>
+          <t>07:30 AM – 08:30 AM</t>
         </is>
       </c>
       <c r="E394" t="inlineStr">
@@ -22488,19 +22488,19 @@
     </row>
     <row r="395">
       <c r="A395" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="B395" t="inlineStr">
         <is>
-          <t>Sunday, September 7, 2026</t>
+          <t>Tuesday, September 2, 2026</t>
         </is>
       </c>
       <c r="C395" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D395" t="inlineStr">
         <is>
-          <t>07:30 AM – 08:30 AM</t>
+          <t>10:00 AM – 11:00 AM</t>
         </is>
       </c>
       <c r="E395" t="inlineStr">
@@ -22544,19 +22544,19 @@
     </row>
     <row r="396">
       <c r="A396" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="B396" t="inlineStr">
         <is>
-          <t>Sunday, September 7, 2026</t>
+          <t>Tuesday, September 2, 2026</t>
         </is>
       </c>
       <c r="C396" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D396" t="inlineStr">
         <is>
-          <t>10:00 AM – 11:00 AM</t>
+          <t>08:45 AM – 09:45 AM</t>
         </is>
       </c>
       <c r="E396" t="inlineStr">
@@ -22608,11 +22608,11 @@
         </is>
       </c>
       <c r="C397" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D397" t="inlineStr">
         <is>
-          <t>08:45 AM – 09:45 AM</t>
+          <t>07:30 AM – 08:30 AM</t>
         </is>
       </c>
       <c r="E397" t="inlineStr">
@@ -22656,11 +22656,11 @@
     </row>
     <row r="398">
       <c r="A398" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="B398" t="inlineStr">
         <is>
-          <t>Tuesday, September 2, 2026</t>
+          <t>Saturday, September 6, 2026</t>
         </is>
       </c>
       <c r="C398" t="n">
@@ -22712,19 +22712,19 @@
     </row>
     <row r="399">
       <c r="A399" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B399" t="inlineStr">
         <is>
-          <t>Wednesday, September 3, 2026</t>
+          <t>Saturday, September 6, 2026</t>
         </is>
       </c>
       <c r="C399" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D399" t="inlineStr">
         <is>
-          <t>07:30 AM – 08:30 AM</t>
+          <t>08:45 AM – 09:45 AM</t>
         </is>
       </c>
       <c r="E399" t="inlineStr">
@@ -22768,11 +22768,11 @@
     </row>
     <row r="400">
       <c r="A400" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B400" t="inlineStr">
         <is>
-          <t>Sunday, September 7, 2026</t>
+          <t>Saturday, September 6, 2026</t>
         </is>
       </c>
       <c r="C400" t="n">
@@ -22824,11 +22824,11 @@
     </row>
     <row r="401">
       <c r="A401" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B401" t="inlineStr">
         <is>
-          <t>Saturday, September 6, 2026</t>
+          <t>Wednesday, September 3, 2026</t>
         </is>
       </c>
       <c r="C401" t="n">
@@ -22880,11 +22880,11 @@
     </row>
     <row r="402">
       <c r="A402" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B402" t="inlineStr">
         <is>
-          <t>Saturday, September 6, 2026</t>
+          <t>Wednesday, September 3, 2026</t>
         </is>
       </c>
       <c r="C402" t="n">
@@ -22944,11 +22944,11 @@
         </is>
       </c>
       <c r="C403" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D403" t="inlineStr">
         <is>
-          <t>10:00 AM – 11:00 AM</t>
+          <t>07:30 AM – 08:30 AM</t>
         </is>
       </c>
       <c r="E403" t="inlineStr">
@@ -22992,19 +22992,19 @@
     </row>
     <row r="404">
       <c r="A404" t="n">
+        <v>1</v>
+      </c>
+      <c r="B404" t="inlineStr">
+        <is>
+          <t>Tuesday, September 2, 2026</t>
+        </is>
+      </c>
+      <c r="C404" t="n">
         <v>3</v>
       </c>
-      <c r="B404" t="inlineStr">
-        <is>
-          <t>Saturday, September 6, 2026</t>
-        </is>
-      </c>
-      <c r="C404" t="n">
-        <v>1</v>
-      </c>
       <c r="D404" t="inlineStr">
         <is>
-          <t>07:30 AM – 08:30 AM</t>
+          <t>10:00 AM – 11:00 AM</t>
         </is>
       </c>
       <c r="E404" t="inlineStr">
@@ -23048,11 +23048,11 @@
     </row>
     <row r="405">
       <c r="A405" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="B405" t="inlineStr">
         <is>
-          <t>Sunday, September 7, 2026</t>
+          <t>Tuesday, September 2, 2026</t>
         </is>
       </c>
       <c r="C405" t="n">
@@ -23112,11 +23112,11 @@
         </is>
       </c>
       <c r="C406" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D406" t="inlineStr">
         <is>
-          <t>08:45 AM – 09:45 AM</t>
+          <t>07:30 AM – 08:30 AM</t>
         </is>
       </c>
       <c r="E406" t="inlineStr">
@@ -23160,19 +23160,19 @@
     </row>
     <row r="407">
       <c r="A407" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B407" t="inlineStr">
         <is>
-          <t>Sunday, September 7, 2026</t>
+          <t>Saturday, September 6, 2026</t>
         </is>
       </c>
       <c r="C407" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D407" t="inlineStr">
         <is>
-          <t>08:45 AM – 09:45 AM</t>
+          <t>10:00 AM – 11:00 AM</t>
         </is>
       </c>
       <c r="E407" t="inlineStr">
@@ -23216,19 +23216,19 @@
     </row>
     <row r="408">
       <c r="A408" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B408" t="inlineStr">
         <is>
-          <t>Sunday, September 7, 2026</t>
+          <t>Saturday, September 6, 2026</t>
         </is>
       </c>
       <c r="C408" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D408" t="inlineStr">
         <is>
-          <t>07:30 AM – 08:30 AM</t>
+          <t>08:45 AM – 09:45 AM</t>
         </is>
       </c>
       <c r="E408" t="inlineStr">
@@ -23272,19 +23272,19 @@
     </row>
     <row r="409">
       <c r="A409" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B409" t="inlineStr">
         <is>
-          <t>Wednesday, September 3, 2026</t>
+          <t>Saturday, September 6, 2026</t>
         </is>
       </c>
       <c r="C409" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D409" t="inlineStr">
         <is>
-          <t>09:45 AM – 11:45 AM</t>
+          <t>07:30 AM – 09:30 AM</t>
         </is>
       </c>
       <c r="E409" t="inlineStr">
@@ -23328,19 +23328,19 @@
     </row>
     <row r="410">
       <c r="A410" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B410" t="inlineStr">
         <is>
-          <t>Tuesday, September 2, 2026</t>
+          <t>Wednesday, September 3, 2026</t>
         </is>
       </c>
       <c r="C410" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D410" t="inlineStr">
         <is>
-          <t>09:45 AM – 11:45 AM</t>
+          <t>10:00 AM – 12:00 PM</t>
         </is>
       </c>
       <c r="E410" t="inlineStr">
@@ -23392,11 +23392,11 @@
         </is>
       </c>
       <c r="C411" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D411" t="inlineStr">
         <is>
-          <t>07:30 AM – 08:30 AM</t>
+          <t>08:45 AM – 09:45 AM</t>
         </is>
       </c>
       <c r="E411" t="inlineStr">
@@ -23440,19 +23440,19 @@
     </row>
     <row r="412">
       <c r="A412" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B412" t="inlineStr">
         <is>
-          <t>Tuesday, September 2, 2026</t>
+          <t>Wednesday, September 3, 2026</t>
         </is>
       </c>
       <c r="C412" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D412" t="inlineStr">
         <is>
-          <t>10:00 AM – 11:00 AM</t>
+          <t>07:30 AM – 08:30 AM</t>
         </is>
       </c>
       <c r="E412" t="inlineStr">
@@ -23496,11 +23496,11 @@
     </row>
     <row r="413">
       <c r="A413" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="B413" t="inlineStr">
         <is>
-          <t>Saturday, September 6, 2026</t>
+          <t>Tuesday, September 2, 2026</t>
         </is>
       </c>
       <c r="C413" t="n">
@@ -23552,19 +23552,19 @@
     </row>
     <row r="414">
       <c r="A414" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B414" t="inlineStr">
         <is>
-          <t>Wednesday, September 3, 2026</t>
+          <t>Tuesday, September 2, 2026</t>
         </is>
       </c>
       <c r="C414" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D414" t="inlineStr">
         <is>
-          <t>10:00 AM – 11:00 AM</t>
+          <t>07:30 AM – 08:30 AM</t>
         </is>
       </c>
       <c r="E414" t="inlineStr">
@@ -23608,11 +23608,11 @@
     </row>
     <row r="415">
       <c r="A415" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="B415" t="inlineStr">
         <is>
-          <t>Saturday, September 6, 2026</t>
+          <t>Tuesday, September 2, 2026</t>
         </is>
       </c>
       <c r="C415" t="n">
@@ -23720,19 +23720,19 @@
     </row>
     <row r="417">
       <c r="A417" t="n">
+        <v>2</v>
+      </c>
+      <c r="B417" t="inlineStr">
+        <is>
+          <t>Wednesday, September 3, 2026</t>
+        </is>
+      </c>
+      <c r="C417" t="n">
         <v>3</v>
       </c>
-      <c r="B417" t="inlineStr">
-        <is>
-          <t>Saturday, September 6, 2026</t>
-        </is>
-      </c>
-      <c r="C417" t="n">
-        <v>1</v>
-      </c>
       <c r="D417" t="inlineStr">
         <is>
-          <t>07:30 AM – 08:30 AM</t>
+          <t>10:00 AM – 11:00 AM</t>
         </is>
       </c>
       <c r="E417" t="inlineStr">
@@ -23776,19 +23776,19 @@
     </row>
     <row r="418">
       <c r="A418" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B418" t="inlineStr">
         <is>
-          <t>Tuesday, September 2, 2026</t>
+          <t>Wednesday, September 3, 2026</t>
         </is>
       </c>
       <c r="C418" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D418" t="inlineStr">
         <is>
-          <t>10:00 AM – 11:00 AM</t>
+          <t>08:45 AM – 09:45 AM</t>
         </is>
       </c>
       <c r="E418" t="inlineStr">
@@ -23888,19 +23888,19 @@
     </row>
     <row r="420">
       <c r="A420" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="B420" t="inlineStr">
         <is>
-          <t>Sunday, September 7, 2026</t>
+          <t>Tuesday, September 2, 2026</t>
         </is>
       </c>
       <c r="C420" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D420" t="inlineStr">
         <is>
-          <t>08:45 AM – 09:45 AM</t>
+          <t>10:00 AM – 11:00 AM</t>
         </is>
       </c>
       <c r="E420" t="inlineStr">
@@ -23944,19 +23944,19 @@
     </row>
     <row r="421">
       <c r="A421" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="B421" t="inlineStr">
         <is>
-          <t>Saturday, September 6, 2026</t>
+          <t>Tuesday, September 2, 2026</t>
         </is>
       </c>
       <c r="C421" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D421" t="inlineStr">
         <is>
-          <t>10:00 AM – 11:00 AM</t>
+          <t>08:45 AM – 09:45 AM</t>
         </is>
       </c>
       <c r="E421" t="inlineStr">
@@ -24000,19 +24000,19 @@
     </row>
     <row r="422">
       <c r="A422" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="B422" t="inlineStr">
         <is>
-          <t>Sunday, September 7, 2026</t>
+          <t>Tuesday, September 2, 2026</t>
         </is>
       </c>
       <c r="C422" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D422" t="inlineStr">
         <is>
-          <t>10:00 AM – 11:00 AM</t>
+          <t>07:30 AM – 08:30 AM</t>
         </is>
       </c>
       <c r="E422" t="inlineStr">
@@ -24056,11 +24056,11 @@
     </row>
     <row r="423">
       <c r="A423" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="B423" t="inlineStr">
         <is>
-          <t>Tuesday, September 2, 2026</t>
+          <t>Sunday, September 7, 2026</t>
         </is>
       </c>
       <c r="C423" t="n">
@@ -24120,11 +24120,11 @@
         </is>
       </c>
       <c r="C424" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D424" t="inlineStr">
         <is>
-          <t>01:45 PM – 02:45 PM</t>
+          <t>02:45 PM – 03:30 PM</t>
         </is>
       </c>
       <c r="E424" t="inlineStr">
@@ -24168,19 +24168,19 @@
     </row>
     <row r="425">
       <c r="A425" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="B425" t="inlineStr">
         <is>
-          <t>Sunday, September 7, 2026</t>
+          <t>Wednesday, September 3, 2026</t>
         </is>
       </c>
       <c r="C425" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D425" t="inlineStr">
         <is>
-          <t>01:45 PM – 02:45 PM</t>
+          <t>12:30 PM – 01:30 PM</t>
         </is>
       </c>
       <c r="E425" t="inlineStr">
@@ -24224,19 +24224,19 @@
     </row>
     <row r="426">
       <c r="A426" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B426" t="inlineStr">
         <is>
-          <t>Sunday, September 7, 2026</t>
+          <t>Saturday, September 6, 2026</t>
         </is>
       </c>
       <c r="C426" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D426" t="inlineStr">
         <is>
-          <t>12:30 PM – 01:30 PM</t>
+          <t>01:45 PM – 02:45 PM</t>
         </is>
       </c>
       <c r="E426" t="inlineStr">
@@ -24280,11 +24280,11 @@
     </row>
     <row r="427">
       <c r="A427" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B427" t="inlineStr">
         <is>
-          <t>Tuesday, September 2, 2026</t>
+          <t>Wednesday, September 3, 2026</t>
         </is>
       </c>
       <c r="C427" t="n">
@@ -24336,19 +24336,19 @@
     </row>
     <row r="428">
       <c r="A428" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B428" t="inlineStr">
         <is>
-          <t>Wednesday, September 3, 2026</t>
+          <t>Saturday, September 6, 2026</t>
         </is>
       </c>
       <c r="C428" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D428" t="inlineStr">
         <is>
-          <t>01:45 PM – 02:45 PM</t>
+          <t>12:30 PM – 01:30 PM</t>
         </is>
       </c>
       <c r="E428" t="inlineStr">
@@ -24392,19 +24392,19 @@
     </row>
     <row r="429">
       <c r="A429" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B429" t="inlineStr">
         <is>
-          <t>Wednesday, September 3, 2026</t>
+          <t>Tuesday, September 2, 2026</t>
         </is>
       </c>
       <c r="C429" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D429" t="inlineStr">
         <is>
-          <t>12:30 PM – 01:30 PM</t>
+          <t>02:45 PM – 03:30 PM</t>
         </is>
       </c>
       <c r="E429" t="inlineStr">
@@ -24448,11 +24448,11 @@
     </row>
     <row r="430">
       <c r="A430" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B430" t="inlineStr">
         <is>
-          <t>Tuesday, September 2, 2026</t>
+          <t>Wednesday, September 3, 2026</t>
         </is>
       </c>
       <c r="C430" t="n">
@@ -24504,19 +24504,19 @@
     </row>
     <row r="431">
       <c r="A431" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B431" t="inlineStr">
         <is>
-          <t>Wednesday, September 3, 2026</t>
+          <t>Tuesday, September 2, 2026</t>
         </is>
       </c>
       <c r="C431" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D431" t="inlineStr">
         <is>
-          <t>02:45 PM – 03:30 PM</t>
+          <t>01:45 PM – 02:45 PM</t>
         </is>
       </c>
       <c r="E431" t="inlineStr">
@@ -24560,19 +24560,19 @@
     </row>
     <row r="432">
       <c r="A432" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="B432" t="inlineStr">
         <is>
-          <t>Saturday, September 6, 2026</t>
+          <t>Tuesday, September 2, 2026</t>
         </is>
       </c>
       <c r="C432" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D432" t="inlineStr">
         <is>
-          <t>02:45 PM – 03:30 PM</t>
+          <t>12:30 PM – 01:30 PM</t>
         </is>
       </c>
       <c r="E432" t="inlineStr">
@@ -24616,11 +24616,11 @@
     </row>
     <row r="433">
       <c r="A433" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B433" t="inlineStr">
         <is>
-          <t>Saturday, September 6, 2026</t>
+          <t>Sunday, September 7, 2026</t>
         </is>
       </c>
       <c r="C433" t="n">
@@ -24672,19 +24672,19 @@
     </row>
     <row r="434">
       <c r="A434" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="B434" t="inlineStr">
         <is>
-          <t>Wednesday, September 3, 2026</t>
+          <t>Sunday, September 7, 2026</t>
         </is>
       </c>
       <c r="C434" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D434" t="inlineStr">
         <is>
-          <t>01:45 PM – 02:45 PM</t>
+          <t>12:30 PM – 01:30 PM</t>
         </is>
       </c>
       <c r="E434" t="inlineStr">
@@ -24736,11 +24736,11 @@
         </is>
       </c>
       <c r="C435" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D435" t="inlineStr">
         <is>
-          <t>02:45 PM – 03:30 PM</t>
+          <t>01:45 PM – 02:45 PM</t>
         </is>
       </c>
       <c r="E435" t="inlineStr">
@@ -24784,11 +24784,11 @@
     </row>
     <row r="436">
       <c r="A436" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="B436" t="inlineStr">
         <is>
-          <t>Tuesday, September 2, 2026</t>
+          <t>Saturday, September 6, 2026</t>
         </is>
       </c>
       <c r="C436" t="n">
@@ -24840,19 +24840,19 @@
     </row>
     <row r="437">
       <c r="A437" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="B437" t="inlineStr">
         <is>
-          <t>Sunday, September 7, 2026</t>
+          <t>Wednesday, September 3, 2026</t>
         </is>
       </c>
       <c r="C437" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D437" t="inlineStr">
         <is>
-          <t>01:45 PM – 02:45 PM</t>
+          <t>02:45 PM – 03:30 PM</t>
         </is>
       </c>
       <c r="E437" t="inlineStr">
@@ -24896,11 +24896,11 @@
     </row>
     <row r="438">
       <c r="A438" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B438" t="inlineStr">
         <is>
-          <t>Sunday, September 7, 2026</t>
+          <t>Saturday, September 6, 2026</t>
         </is>
       </c>
       <c r="C438" t="n">
@@ -24952,19 +24952,19 @@
     </row>
     <row r="439">
       <c r="A439" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B439" t="inlineStr">
         <is>
-          <t>Saturday, September 6, 2026</t>
+          <t>Wednesday, September 3, 2026</t>
         </is>
       </c>
       <c r="C439" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D439" t="inlineStr">
         <is>
-          <t>02:45 PM – 03:30 PM</t>
+          <t>12:30 PM – 01:30 PM</t>
         </is>
       </c>
       <c r="E439" t="inlineStr">
@@ -25016,11 +25016,11 @@
         </is>
       </c>
       <c r="C440" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D440" t="inlineStr">
         <is>
-          <t>01:45 PM – 02:45 PM</t>
+          <t>12:30 PM – 01:30 PM</t>
         </is>
       </c>
       <c r="E440" t="inlineStr">
@@ -25064,19 +25064,19 @@
     </row>
     <row r="441">
       <c r="A441" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B441" t="inlineStr">
         <is>
-          <t>Wednesday, September 3, 2026</t>
+          <t>Tuesday, September 2, 2026</t>
         </is>
       </c>
       <c r="C441" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D441" t="inlineStr">
         <is>
-          <t>12:30 PM – 01:30 PM</t>
+          <t>02:45 PM – 03:30 PM</t>
         </is>
       </c>
       <c r="E441" t="inlineStr">
@@ -25120,19 +25120,19 @@
     </row>
     <row r="442">
       <c r="A442" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="B442" t="inlineStr">
         <is>
-          <t>Saturday, September 6, 2026</t>
+          <t>Tuesday, September 2, 2026</t>
         </is>
       </c>
       <c r="C442" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D442" t="inlineStr">
         <is>
-          <t>12:30 PM – 01:30 PM</t>
+          <t>01:45 PM – 02:45 PM</t>
         </is>
       </c>
       <c r="E442" t="inlineStr">
@@ -25176,19 +25176,19 @@
     </row>
     <row r="443">
       <c r="A443" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="B443" t="inlineStr">
         <is>
-          <t>Tuesday, September 2, 2026</t>
+          <t>Sunday, September 7, 2026</t>
         </is>
       </c>
       <c r="C443" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D443" t="inlineStr">
         <is>
-          <t>02:45 PM – 03:30 PM</t>
+          <t>12:30 PM – 01:30 PM</t>
         </is>
       </c>
       <c r="E443" t="inlineStr">
@@ -25232,19 +25232,19 @@
     </row>
     <row r="444">
       <c r="A444" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="B444" t="inlineStr">
         <is>
-          <t>Tuesday, September 2, 2026</t>
+          <t>Saturday, September 6, 2026</t>
         </is>
       </c>
       <c r="C444" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D444" t="inlineStr">
         <is>
-          <t>12:30 PM – 01:30 PM</t>
+          <t>02:45 PM – 03:30 PM</t>
         </is>
       </c>
       <c r="E444" t="inlineStr">
@@ -25344,19 +25344,19 @@
     </row>
     <row r="446">
       <c r="A446" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B446" t="inlineStr">
         <is>
-          <t>Wednesday, September 3, 2026</t>
+          <t>Saturday, September 6, 2026</t>
         </is>
       </c>
       <c r="C446" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D446" t="inlineStr">
         <is>
-          <t>02:45 PM – 03:30 PM</t>
+          <t>12:30 PM – 01:30 PM</t>
         </is>
       </c>
       <c r="E446" t="inlineStr">
@@ -25400,19 +25400,19 @@
     </row>
     <row r="447">
       <c r="A447" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B447" t="inlineStr">
         <is>
-          <t>Saturday, September 6, 2026</t>
+          <t>Wednesday, September 3, 2026</t>
         </is>
       </c>
       <c r="C447" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D447" t="inlineStr">
         <is>
-          <t>02:45 PM – 03:30 PM</t>
+          <t>01:45 PM – 02:45 PM</t>
         </is>
       </c>
       <c r="E447" t="inlineStr">
@@ -25456,19 +25456,19 @@
     </row>
     <row r="448">
       <c r="A448" t="n">
+        <v>2</v>
+      </c>
+      <c r="B448" t="inlineStr">
+        <is>
+          <t>Wednesday, September 3, 2026</t>
+        </is>
+      </c>
+      <c r="C448" t="n">
         <v>3</v>
       </c>
-      <c r="B448" t="inlineStr">
-        <is>
-          <t>Saturday, September 6, 2026</t>
-        </is>
-      </c>
-      <c r="C448" t="n">
-        <v>1</v>
-      </c>
       <c r="D448" t="inlineStr">
         <is>
-          <t>12:30 PM – 01:30 PM</t>
+          <t>02:45 PM – 03:30 PM</t>
         </is>
       </c>
       <c r="E448" t="inlineStr">
@@ -25568,11 +25568,11 @@
     </row>
     <row r="450">
       <c r="A450" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="B450" t="inlineStr">
         <is>
-          <t>Sunday, September 7, 2026</t>
+          <t>Tuesday, September 2, 2026</t>
         </is>
       </c>
       <c r="C450" t="n">
@@ -25624,19 +25624,19 @@
     </row>
     <row r="451">
       <c r="A451" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="B451" t="inlineStr">
         <is>
-          <t>Sunday, September 7, 2026</t>
+          <t>Tuesday, September 2, 2026</t>
         </is>
       </c>
       <c r="C451" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D451" t="inlineStr">
         <is>
-          <t>12:30 PM – 01:30 PM</t>
+          <t>01:45 PM – 02:45 PM</t>
         </is>
       </c>
       <c r="E451" t="inlineStr">
@@ -25688,11 +25688,11 @@
         </is>
       </c>
       <c r="C452" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D452" t="inlineStr">
         <is>
-          <t>01:45 PM – 02:45 PM</t>
+          <t>12:30 PM – 01:30 PM</t>
         </is>
       </c>
       <c r="E452" t="inlineStr">
@@ -25736,11 +25736,11 @@
     </row>
     <row r="453">
       <c r="A453" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B453" t="inlineStr">
         <is>
-          <t>Saturday, September 6, 2026</t>
+          <t>Wednesday, September 3, 2026</t>
         </is>
       </c>
       <c r="C453" t="n">
@@ -25792,19 +25792,19 @@
     </row>
     <row r="454">
       <c r="A454" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B454" t="inlineStr">
         <is>
-          <t>Tuesday, September 2, 2026</t>
+          <t>Wednesday, September 3, 2026</t>
         </is>
       </c>
       <c r="C454" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D454" t="inlineStr">
         <is>
-          <t>02:45 PM – 03:30 PM</t>
+          <t>01:45 PM – 02:45 PM</t>
         </is>
       </c>
       <c r="E454" t="inlineStr">
@@ -25848,19 +25848,19 @@
     </row>
     <row r="455">
       <c r="A455" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B455" t="inlineStr">
         <is>
-          <t>Sunday, September 7, 2026</t>
+          <t>Saturday, September 6, 2026</t>
         </is>
       </c>
       <c r="C455" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D455" t="inlineStr">
         <is>
-          <t>12:30 PM – 01:30 PM</t>
+          <t>01:45 PM – 02:45 PM</t>
         </is>
       </c>
       <c r="E455" t="inlineStr">
@@ -25904,19 +25904,19 @@
     </row>
     <row r="456">
       <c r="A456" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="B456" t="inlineStr">
         <is>
-          <t>Tuesday, September 2, 2026</t>
+          <t>Saturday, September 6, 2026</t>
         </is>
       </c>
       <c r="C456" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D456" t="inlineStr">
         <is>
-          <t>12:30 PM – 01:30 PM</t>
+          <t>02:45 PM – 03:30 PM</t>
         </is>
       </c>
       <c r="E456" t="inlineStr">
@@ -25960,11 +25960,11 @@
     </row>
     <row r="457">
       <c r="A457" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B457" t="inlineStr">
         <is>
-          <t>Wednesday, September 3, 2026</t>
+          <t>Saturday, September 6, 2026</t>
         </is>
       </c>
       <c r="C457" t="n">
@@ -26016,19 +26016,19 @@
     </row>
     <row r="458">
       <c r="A458" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B458" t="inlineStr">
         <is>
-          <t>Saturday, September 6, 2026</t>
+          <t>Wednesday, September 3, 2026</t>
         </is>
       </c>
       <c r="C458" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D458" t="inlineStr">
         <is>
-          <t>01:45 PM – 02:45 PM</t>
+          <t>12:30 PM – 01:30 PM</t>
         </is>
       </c>
       <c r="E458" t="inlineStr">
@@ -26080,11 +26080,11 @@
         </is>
       </c>
       <c r="C459" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D459" t="inlineStr">
         <is>
-          <t>01:45 PM – 02:45 PM</t>
+          <t>02:45 PM – 03:30 PM</t>
         </is>
       </c>
       <c r="E459" t="inlineStr">
@@ -26128,19 +26128,19 @@
     </row>
     <row r="460">
       <c r="A460" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B460" t="inlineStr">
         <is>
-          <t>Wednesday, September 3, 2026</t>
+          <t>Tuesday, September 2, 2026</t>
         </is>
       </c>
       <c r="C460" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D460" t="inlineStr">
         <is>
-          <t>02:45 PM – 03:30 PM</t>
+          <t>12:30 PM – 01:30 PM</t>
         </is>
       </c>
       <c r="E460" t="inlineStr">
@@ -26184,19 +26184,19 @@
     </row>
     <row r="461">
       <c r="A461" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="B461" t="inlineStr">
         <is>
-          <t>Sunday, September 7, 2026</t>
+          <t>Tuesday, September 2, 2026</t>
         </is>
       </c>
       <c r="C461" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D461" t="inlineStr">
         <is>
-          <t>02:45 PM – 03:30 PM</t>
+          <t>01:45 PM – 02:45 PM</t>
         </is>
       </c>
       <c r="E461" t="inlineStr">
@@ -26248,11 +26248,11 @@
         </is>
       </c>
       <c r="C462" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D462" t="inlineStr">
         <is>
-          <t>01:45 PM – 02:45 PM</t>
+          <t>12:30 PM – 01:30 PM</t>
         </is>
       </c>
       <c r="E462" t="inlineStr">
@@ -26296,11 +26296,11 @@
     </row>
     <row r="463">
       <c r="A463" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B463" t="inlineStr">
         <is>
-          <t>Wednesday, September 3, 2026</t>
+          <t>Saturday, September 6, 2026</t>
         </is>
       </c>
       <c r="C463" t="n">
@@ -26352,11 +26352,11 @@
     </row>
     <row r="464">
       <c r="A464" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="B464" t="inlineStr">
         <is>
-          <t>Sunday, September 7, 2026</t>
+          <t>Tuesday, September 2, 2026</t>
         </is>
       </c>
       <c r="C464" t="n">
@@ -26408,19 +26408,19 @@
     </row>
     <row r="465">
       <c r="A465" t="n">
+        <v>2</v>
+      </c>
+      <c r="B465" t="inlineStr">
+        <is>
+          <t>Wednesday, September 3, 2026</t>
+        </is>
+      </c>
+      <c r="C465" t="n">
         <v>3</v>
       </c>
-      <c r="B465" t="inlineStr">
-        <is>
-          <t>Saturday, September 6, 2026</t>
-        </is>
-      </c>
-      <c r="C465" t="n">
-        <v>1</v>
-      </c>
       <c r="D465" t="inlineStr">
         <is>
-          <t>12:30 PM – 01:30 PM</t>
+          <t>02:45 PM – 03:30 PM</t>
         </is>
       </c>
       <c r="E465" t="inlineStr">
@@ -26464,19 +26464,19 @@
     </row>
     <row r="466">
       <c r="A466" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B466" t="inlineStr">
         <is>
-          <t>Sunday, September 7, 2026</t>
+          <t>Saturday, September 6, 2026</t>
         </is>
       </c>
       <c r="C466" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D466" t="inlineStr">
         <is>
-          <t>02:45 PM – 03:30 PM</t>
+          <t>12:30 PM – 01:30 PM</t>
         </is>
       </c>
       <c r="E466" t="inlineStr">
@@ -26576,11 +26576,11 @@
     </row>
     <row r="468">
       <c r="A468" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B468" t="inlineStr">
         <is>
-          <t>Wednesday, September 3, 2026</t>
+          <t>Tuesday, September 2, 2026</t>
         </is>
       </c>
       <c r="C468" t="n">
@@ -26632,19 +26632,19 @@
     </row>
     <row r="469">
       <c r="A469" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="B469" t="inlineStr">
         <is>
-          <t>Tuesday, September 2, 2026</t>
+          <t>Sunday, September 7, 2026</t>
         </is>
       </c>
       <c r="C469" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D469" t="inlineStr">
         <is>
-          <t>02:45 PM – 03:30 PM</t>
+          <t>01:45 PM – 02:45 PM</t>
         </is>
       </c>
       <c r="E469" t="inlineStr">
@@ -26688,11 +26688,11 @@
     </row>
     <row r="470">
       <c r="A470" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B470" t="inlineStr">
         <is>
-          <t>Saturday, September 6, 2026</t>
+          <t>Wednesday, September 3, 2026</t>
         </is>
       </c>
       <c r="C470" t="n">
@@ -26864,11 +26864,11 @@
         </is>
       </c>
       <c r="C473" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D473" t="inlineStr">
         <is>
-          <t>01:45 PM – 02:45 PM</t>
+          <t>02:45 PM – 03:30 PM</t>
         </is>
       </c>
       <c r="E473" t="inlineStr">
@@ -26912,11 +26912,11 @@
     </row>
     <row r="474">
       <c r="A474" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="B474" t="inlineStr">
         <is>
-          <t>Sunday, September 7, 2026</t>
+          <t>Wednesday, September 3, 2026</t>
         </is>
       </c>
       <c r="C474" t="n">
@@ -26968,19 +26968,19 @@
     </row>
     <row r="475">
       <c r="A475" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="B475" t="inlineStr">
         <is>
-          <t>Tuesday, September 2, 2026</t>
+          <t>Saturday, September 6, 2026</t>
         </is>
       </c>
       <c r="C475" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D475" t="inlineStr">
         <is>
-          <t>02:45 PM – 03:30 PM</t>
+          <t>12:30 PM – 01:30 PM</t>
         </is>
       </c>
       <c r="E475" t="inlineStr">
@@ -27024,11 +27024,11 @@
     </row>
     <row r="476">
       <c r="A476" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="B476" t="inlineStr">
         <is>
-          <t>Sunday, September 7, 2026</t>
+          <t>Tuesday, September 2, 2026</t>
         </is>
       </c>
       <c r="C476" t="n">
@@ -27080,19 +27080,19 @@
     </row>
     <row r="477">
       <c r="A477" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="B477" t="inlineStr">
         <is>
-          <t>Saturday, September 6, 2026</t>
+          <t>Tuesday, September 2, 2026</t>
         </is>
       </c>
       <c r="C477" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D477" t="inlineStr">
         <is>
-          <t>12:30 PM – 01:30 PM</t>
+          <t>01:45 PM – 02:45 PM</t>
         </is>
       </c>
       <c r="E477" t="inlineStr">
@@ -27192,19 +27192,19 @@
     </row>
     <row r="479">
       <c r="A479" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="B479" t="inlineStr">
         <is>
-          <t>Tuesday, September 2, 2026</t>
+          <t>Saturday, September 6, 2026</t>
         </is>
       </c>
       <c r="C479" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D479" t="inlineStr">
         <is>
-          <t>10:00 AM – 11:00 AM</t>
+          <t>07:30 AM – 08:30 AM</t>
         </is>
       </c>
       <c r="E479" t="inlineStr">
@@ -27256,11 +27256,11 @@
         </is>
       </c>
       <c r="C480" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D480" t="inlineStr">
         <is>
-          <t>08:45 AM – 09:45 AM</t>
+          <t>10:00 AM – 11:00 AM</t>
         </is>
       </c>
       <c r="E480" t="inlineStr">
@@ -27304,19 +27304,19 @@
     </row>
     <row r="481">
       <c r="A481" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B481" t="inlineStr">
         <is>
-          <t>Tuesday, September 2, 2026</t>
+          <t>Wednesday, September 3, 2026</t>
         </is>
       </c>
       <c r="C481" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D481" t="inlineStr">
         <is>
-          <t>07:30 AM – 08:30 AM</t>
+          <t>08:45 AM – 09:45 AM</t>
         </is>
       </c>
       <c r="E481" t="inlineStr">
@@ -27416,19 +27416,19 @@
     </row>
     <row r="483">
       <c r="A483" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="B483" t="inlineStr">
         <is>
-          <t>Sunday, September 7, 2026</t>
+          <t>Tuesday, September 2, 2026</t>
         </is>
       </c>
       <c r="C483" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D483" t="inlineStr">
         <is>
-          <t>08:45 AM – 09:45 AM</t>
+          <t>10:00 AM – 11:00 AM</t>
         </is>
       </c>
       <c r="E483" t="inlineStr">
@@ -27472,19 +27472,19 @@
     </row>
     <row r="484">
       <c r="A484" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="B484" t="inlineStr">
         <is>
-          <t>Saturday, September 6, 2026</t>
+          <t>Tuesday, September 2, 2026</t>
         </is>
       </c>
       <c r="C484" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D484" t="inlineStr">
         <is>
-          <t>07:30 AM – 08:30 AM</t>
+          <t>08:45 AM – 09:45 AM</t>
         </is>
       </c>
       <c r="E484" t="inlineStr">
@@ -27528,11 +27528,11 @@
     </row>
     <row r="485">
       <c r="A485" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="B485" t="inlineStr">
         <is>
-          <t>Sunday, September 7, 2026</t>
+          <t>Tuesday, September 2, 2026</t>
         </is>
       </c>
       <c r="C485" t="n">
@@ -27584,11 +27584,11 @@
     </row>
     <row r="486">
       <c r="A486" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="B486" t="inlineStr">
         <is>
-          <t>Wednesday, September 3, 2026</t>
+          <t>Sunday, September 7, 2026</t>
         </is>
       </c>
       <c r="C486" t="n">
@@ -27640,19 +27640,19 @@
     </row>
     <row r="487">
       <c r="A487" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="B487" t="inlineStr">
         <is>
-          <t>Tuesday, September 2, 2026</t>
+          <t>Saturday, September 6, 2026</t>
         </is>
       </c>
       <c r="C487" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D487" t="inlineStr">
         <is>
-          <t>03:30 PM – 04:30 PM</t>
+          <t>04:45 PM – 05:45 PM</t>
         </is>
       </c>
       <c r="E487" t="inlineStr">
@@ -27696,19 +27696,19 @@
     </row>
     <row r="488">
       <c r="A488" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B488" t="inlineStr">
         <is>
-          <t>Tuesday, September 2, 2026</t>
+          <t>Wednesday, September 3, 2026</t>
         </is>
       </c>
       <c r="C488" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D488" t="inlineStr">
         <is>
-          <t>05:45 PM – 06:45 PM</t>
+          <t>03:30 PM – 04:30 PM</t>
         </is>
       </c>
       <c r="E488" t="inlineStr">
@@ -27752,11 +27752,11 @@
     </row>
     <row r="489">
       <c r="A489" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B489" t="inlineStr">
         <is>
-          <t>Saturday, September 6, 2026</t>
+          <t>Sunday, September 7, 2026</t>
         </is>
       </c>
       <c r="C489" t="n">
@@ -27808,19 +27808,19 @@
     </row>
     <row r="490">
       <c r="A490" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="B490" t="inlineStr">
         <is>
-          <t>Tuesday, September 2, 2026</t>
+          <t>Saturday, September 6, 2026</t>
         </is>
       </c>
       <c r="C490" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D490" t="inlineStr">
         <is>
-          <t>04:45 PM – 05:45 PM</t>
+          <t>05:45 PM – 06:45 PM</t>
         </is>
       </c>
       <c r="E490" t="inlineStr">
@@ -27864,19 +27864,19 @@
     </row>
     <row r="491">
       <c r="A491" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="B491" t="inlineStr">
         <is>
-          <t>Sunday, September 7, 2026</t>
+          <t>Tuesday, September 2, 2026</t>
         </is>
       </c>
       <c r="C491" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D491" t="inlineStr">
         <is>
-          <t>03:30 PM – 04:30 PM</t>
+          <t>04:45 PM – 05:45 PM</t>
         </is>
       </c>
       <c r="E491" t="inlineStr">
@@ -27920,19 +27920,19 @@
     </row>
     <row r="492">
       <c r="A492" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B492" t="inlineStr">
         <is>
-          <t>Sunday, September 7, 2026</t>
+          <t>Saturday, September 6, 2026</t>
         </is>
       </c>
       <c r="C492" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D492" t="inlineStr">
         <is>
-          <t>04:45 PM – 05:45 PM</t>
+          <t>03:30 PM – 04:30 PM</t>
         </is>
       </c>
       <c r="E492" t="inlineStr">
@@ -27976,11 +27976,11 @@
     </row>
     <row r="493">
       <c r="A493" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="B493" t="inlineStr">
         <is>
-          <t>Sunday, September 7, 2026</t>
+          <t>Tuesday, September 2, 2026</t>
         </is>
       </c>
       <c r="C493" t="n">
@@ -28032,11 +28032,11 @@
     </row>
     <row r="494">
       <c r="A494" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B494" t="inlineStr">
         <is>
-          <t>Saturday, September 6, 2026</t>
+          <t>Wednesday, September 3, 2026</t>
         </is>
       </c>
       <c r="C494" t="n">
@@ -28088,11 +28088,11 @@
     </row>
     <row r="495">
       <c r="A495" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B495" t="inlineStr">
         <is>
-          <t>Wednesday, September 3, 2026</t>
+          <t>Tuesday, September 2, 2026</t>
         </is>
       </c>
       <c r="C495" t="n">
@@ -28144,11 +28144,11 @@
     </row>
     <row r="496">
       <c r="A496" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B496" t="inlineStr">
         <is>
-          <t>Saturday, September 6, 2026</t>
+          <t>Sunday, September 7, 2026</t>
         </is>
       </c>
       <c r="C496" t="n">
@@ -28200,19 +28200,19 @@
     </row>
     <row r="497">
       <c r="A497" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B497" t="inlineStr">
         <is>
-          <t>Wednesday, September 3, 2026</t>
+          <t>Tuesday, September 2, 2026</t>
         </is>
       </c>
       <c r="C497" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D497" t="inlineStr">
         <is>
-          <t>05:45 PM – 06:45 PM</t>
+          <t>04:45 PM – 05:45 PM</t>
         </is>
       </c>
       <c r="E497" t="inlineStr">
@@ -28256,19 +28256,19 @@
     </row>
     <row r="498">
       <c r="A498" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B498" t="inlineStr">
         <is>
-          <t>Wednesday, September 3, 2026</t>
+          <t>Saturday, September 6, 2026</t>
         </is>
       </c>
       <c r="C498" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D498" t="inlineStr">
         <is>
-          <t>04:45 PM – 05:45 PM</t>
+          <t>05:45 PM – 06:45 PM</t>
         </is>
       </c>
       <c r="E498" t="inlineStr">
@@ -28312,19 +28312,19 @@
     </row>
     <row r="499">
       <c r="A499" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B499" t="inlineStr">
         <is>
-          <t>Sunday, September 7, 2026</t>
+          <t>Saturday, September 6, 2026</t>
         </is>
       </c>
       <c r="C499" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D499" t="inlineStr">
         <is>
-          <t>03:30 PM – 04:30 PM</t>
+          <t>04:45 PM – 05:45 PM</t>
         </is>
       </c>
       <c r="E499" t="inlineStr">
@@ -28368,19 +28368,19 @@
     </row>
     <row r="500">
       <c r="A500" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B500" t="inlineStr">
         <is>
-          <t>Tuesday, September 2, 2026</t>
+          <t>Wednesday, September 3, 2026</t>
         </is>
       </c>
       <c r="C500" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D500" t="inlineStr">
         <is>
-          <t>03:30 PM – 04:30 PM</t>
+          <t>05:45 PM – 06:45 PM</t>
         </is>
       </c>
       <c r="E500" t="inlineStr">
@@ -28424,11 +28424,11 @@
     </row>
     <row r="501">
       <c r="A501" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B501" t="inlineStr">
         <is>
-          <t>Tuesday, September 2, 2026</t>
+          <t>Wednesday, September 3, 2026</t>
         </is>
       </c>
       <c r="C501" t="n">
@@ -28480,19 +28480,19 @@
     </row>
     <row r="502">
       <c r="A502" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B502" t="inlineStr">
         <is>
-          <t>Saturday, September 6, 2026</t>
+          <t>Wednesday, September 3, 2026</t>
         </is>
       </c>
       <c r="C502" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D502" t="inlineStr">
         <is>
-          <t>04:45 PM – 05:45 PM</t>
+          <t>03:30 PM – 04:30 PM</t>
         </is>
       </c>
       <c r="E502" t="inlineStr">
@@ -28536,11 +28536,11 @@
     </row>
     <row r="503">
       <c r="A503" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="B503" t="inlineStr">
         <is>
-          <t>Sunday, September 7, 2026</t>
+          <t>Tuesday, September 2, 2026</t>
         </is>
       </c>
       <c r="C503" t="n">
@@ -28592,19 +28592,19 @@
     </row>
     <row r="504">
       <c r="A504" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B504" t="inlineStr">
         <is>
-          <t>Sunday, September 7, 2026</t>
+          <t>Saturday, September 6, 2026</t>
         </is>
       </c>
       <c r="C504" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D504" t="inlineStr">
         <is>
-          <t>04:45 PM – 05:45 PM</t>
+          <t>03:30 PM – 04:30 PM</t>
         </is>
       </c>
       <c r="E504" t="inlineStr">
@@ -28656,11 +28656,11 @@
         </is>
       </c>
       <c r="C505" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D505" t="inlineStr">
         <is>
-          <t>05:45 PM – 06:45 PM</t>
+          <t>03:30 PM – 04:30 PM</t>
         </is>
       </c>
       <c r="E505" t="inlineStr">
@@ -28704,11 +28704,11 @@
     </row>
     <row r="506">
       <c r="A506" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="B506" t="inlineStr">
         <is>
-          <t>Tuesday, September 2, 2026</t>
+          <t>Sunday, September 7, 2026</t>
         </is>
       </c>
       <c r="C506" t="n">
@@ -28768,11 +28768,11 @@
         </is>
       </c>
       <c r="C507" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D507" t="inlineStr">
         <is>
-          <t>05:45 PM – 06:45 PM</t>
+          <t>03:30 PM – 04:30 PM</t>
         </is>
       </c>
       <c r="E507" t="inlineStr">
@@ -28816,19 +28816,19 @@
     </row>
     <row r="508">
       <c r="A508" t="n">
+        <v>2</v>
+      </c>
+      <c r="B508" t="inlineStr">
+        <is>
+          <t>Wednesday, September 3, 2026</t>
+        </is>
+      </c>
+      <c r="C508" t="n">
         <v>3</v>
       </c>
-      <c r="B508" t="inlineStr">
-        <is>
-          <t>Saturday, September 6, 2026</t>
-        </is>
-      </c>
-      <c r="C508" t="n">
-        <v>2</v>
-      </c>
       <c r="D508" t="inlineStr">
         <is>
-          <t>04:45 PM – 05:45 PM</t>
+          <t>05:45 PM – 06:45 PM</t>
         </is>
       </c>
       <c r="E508" t="inlineStr">
@@ -28872,11 +28872,11 @@
     </row>
     <row r="509">
       <c r="A509" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B509" t="inlineStr">
         <is>
-          <t>Sunday, September 7, 2026</t>
+          <t>Saturday, September 6, 2026</t>
         </is>
       </c>
       <c r="C509" t="n">
@@ -28928,11 +28928,11 @@
     </row>
     <row r="510">
       <c r="A510" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="B510" t="inlineStr">
         <is>
-          <t>Sunday, September 7, 2026</t>
+          <t>Wednesday, September 3, 2026</t>
         </is>
       </c>
       <c r="C510" t="n">
@@ -28984,19 +28984,19 @@
     </row>
     <row r="511">
       <c r="A511" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="B511" t="inlineStr">
         <is>
-          <t>Wednesday, September 3, 2026</t>
+          <t>Sunday, September 7, 2026</t>
         </is>
       </c>
       <c r="C511" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D511" t="inlineStr">
         <is>
-          <t>04:45 PM – 05:45 PM</t>
+          <t>05:45 PM – 06:45 PM</t>
         </is>
       </c>
       <c r="E511" t="inlineStr">
@@ -29040,19 +29040,19 @@
     </row>
     <row r="512">
       <c r="A512" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="B512" t="inlineStr">
         <is>
-          <t>Tuesday, September 2, 2026</t>
+          <t>Saturday, September 6, 2026</t>
         </is>
       </c>
       <c r="C512" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D512" t="inlineStr">
         <is>
-          <t>04:45 PM – 05:45 PM</t>
+          <t>03:30 PM – 04:30 PM</t>
         </is>
       </c>
       <c r="E512" t="inlineStr">
@@ -29096,19 +29096,19 @@
     </row>
     <row r="513">
       <c r="A513" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B513" t="inlineStr">
         <is>
-          <t>Wednesday, September 3, 2026</t>
+          <t>Tuesday, September 2, 2026</t>
         </is>
       </c>
       <c r="C513" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D513" t="inlineStr">
         <is>
-          <t>05:45 PM – 06:45 PM</t>
+          <t>04:45 PM – 05:45 PM</t>
         </is>
       </c>
       <c r="E513" t="inlineStr">
@@ -29208,19 +29208,19 @@
     </row>
     <row r="515">
       <c r="A515" t="n">
+        <v>1</v>
+      </c>
+      <c r="B515" t="inlineStr">
+        <is>
+          <t>Tuesday, September 2, 2026</t>
+        </is>
+      </c>
+      <c r="C515" t="n">
         <v>3</v>
       </c>
-      <c r="B515" t="inlineStr">
-        <is>
-          <t>Saturday, September 6, 2026</t>
-        </is>
-      </c>
-      <c r="C515" t="n">
-        <v>1</v>
-      </c>
       <c r="D515" t="inlineStr">
         <is>
-          <t>03:30 PM – 04:30 PM</t>
+          <t>05:45 PM – 06:45 PM</t>
         </is>
       </c>
       <c r="E515" t="inlineStr">
@@ -29264,19 +29264,19 @@
     </row>
     <row r="516">
       <c r="A516" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="B516" t="inlineStr">
         <is>
-          <t>Sunday, September 7, 2026</t>
+          <t>Wednesday, September 3, 2026</t>
         </is>
       </c>
       <c r="C516" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D516" t="inlineStr">
         <is>
-          <t>05:45 PM – 06:45 PM</t>
+          <t>04:45 PM – 05:45 PM</t>
         </is>
       </c>
       <c r="E516" t="inlineStr">
@@ -29376,11 +29376,11 @@
     </row>
     <row r="518">
       <c r="A518" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B518" t="inlineStr">
         <is>
-          <t>Wednesday, September 3, 2026</t>
+          <t>Tuesday, September 2, 2026</t>
         </is>
       </c>
       <c r="C518" t="n">
@@ -29432,11 +29432,11 @@
     </row>
     <row r="519">
       <c r="A519" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B519" t="inlineStr">
         <is>
-          <t>Saturday, September 6, 2026</t>
+          <t>Wednesday, September 3, 2026</t>
         </is>
       </c>
       <c r="C519" t="n">
@@ -29488,11 +29488,11 @@
     </row>
     <row r="520">
       <c r="A520" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B520" t="inlineStr">
         <is>
-          <t>Wednesday, September 3, 2026</t>
+          <t>Saturday, September 6, 2026</t>
         </is>
       </c>
       <c r="C520" t="n">
@@ -29544,19 +29544,19 @@
     </row>
     <row r="521">
       <c r="A521" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B521" t="inlineStr">
         <is>
-          <t>Tuesday, September 2, 2026</t>
+          <t>Wednesday, September 3, 2026</t>
         </is>
       </c>
       <c r="C521" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D521" t="inlineStr">
         <is>
-          <t>04:45 PM – 05:45 PM</t>
+          <t>03:30 PM – 04:30 PM</t>
         </is>
       </c>
       <c r="E521" t="inlineStr">
@@ -29600,19 +29600,19 @@
     </row>
     <row r="522">
       <c r="A522" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="B522" t="inlineStr">
         <is>
-          <t>Tuesday, September 2, 2026</t>
+          <t>Sunday, September 7, 2026</t>
         </is>
       </c>
       <c r="C522" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D522" t="inlineStr">
         <is>
-          <t>03:30 PM – 04:30 PM</t>
+          <t>05:45 PM – 06:45 PM</t>
         </is>
       </c>
       <c r="E522" t="inlineStr">
@@ -29656,11 +29656,11 @@
     </row>
     <row r="523">
       <c r="A523" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="B523" t="inlineStr">
         <is>
-          <t>Sunday, September 7, 2026</t>
+          <t>Tuesday, September 2, 2026</t>
         </is>
       </c>
       <c r="C523" t="n">
@@ -29712,11 +29712,11 @@
     </row>
     <row r="524">
       <c r="A524" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="B524" t="inlineStr">
         <is>
-          <t>Sunday, September 7, 2026</t>
+          <t>Tuesday, September 2, 2026</t>
         </is>
       </c>
       <c r="C524" t="n">
@@ -29768,19 +29768,19 @@
     </row>
     <row r="525">
       <c r="A525" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B525" t="inlineStr">
         <is>
-          <t>Saturday, September 6, 2026</t>
+          <t>Wednesday, September 3, 2026</t>
         </is>
       </c>
       <c r="C525" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D525" t="inlineStr">
         <is>
-          <t>05:45 PM – 06:45 PM</t>
+          <t>04:45 PM – 05:45 PM</t>
         </is>
       </c>
       <c r="E525" t="inlineStr">
@@ -29824,19 +29824,19 @@
     </row>
     <row r="526">
       <c r="A526" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="B526" t="inlineStr">
         <is>
-          <t>Tuesday, September 2, 2026</t>
+          <t>Saturday, September 6, 2026</t>
         </is>
       </c>
       <c r="C526" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D526" t="inlineStr">
         <is>
-          <t>03:30 PM – 04:30 PM</t>
+          <t>04:45 PM – 05:45 PM</t>
         </is>
       </c>
       <c r="E526" t="inlineStr">
@@ -29880,19 +29880,19 @@
     </row>
     <row r="527">
       <c r="A527" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B527" t="inlineStr">
         <is>
-          <t>Wednesday, September 3, 2026</t>
+          <t>Tuesday, September 2, 2026</t>
         </is>
       </c>
       <c r="C527" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D527" t="inlineStr">
         <is>
-          <t>03:30 PM – 04:30 PM</t>
+          <t>05:45 PM – 06:45 PM</t>
         </is>
       </c>
       <c r="E527" t="inlineStr">
@@ -29936,19 +29936,19 @@
     </row>
     <row r="528">
       <c r="A528" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B528" t="inlineStr">
         <is>
-          <t>Tuesday, September 2, 2026</t>
+          <t>Wednesday, September 3, 2026</t>
         </is>
       </c>
       <c r="C528" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D528" t="inlineStr">
         <is>
-          <t>04:45 PM – 05:45 PM</t>
+          <t>05:45 PM – 06:45 PM</t>
         </is>
       </c>
       <c r="E528" t="inlineStr">
@@ -29992,19 +29992,19 @@
     </row>
     <row r="529">
       <c r="A529" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="B529" t="inlineStr">
         <is>
-          <t>Saturday, September 6, 2026</t>
+          <t>Tuesday, September 2, 2026</t>
         </is>
       </c>
       <c r="C529" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D529" t="inlineStr">
         <is>
-          <t>04:45 PM – 05:45 PM</t>
+          <t>03:30 PM – 04:30 PM</t>
         </is>
       </c>
       <c r="E529" t="inlineStr">
@@ -30048,19 +30048,19 @@
     </row>
     <row r="530">
       <c r="A530" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="B530" t="inlineStr">
         <is>
-          <t>Sunday, September 7, 2026</t>
+          <t>Wednesday, September 3, 2026</t>
         </is>
       </c>
       <c r="C530" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D530" t="inlineStr">
         <is>
-          <t>04:45 PM – 05:45 PM</t>
+          <t>03:30 PM – 04:30 PM</t>
         </is>
       </c>
       <c r="E530" t="inlineStr">
@@ -30104,11 +30104,11 @@
     </row>
     <row r="531">
       <c r="A531" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B531" t="inlineStr">
         <is>
-          <t>Wednesday, September 3, 2026</t>
+          <t>Tuesday, September 2, 2026</t>
         </is>
       </c>
       <c r="C531" t="n">
@@ -30160,19 +30160,19 @@
     </row>
     <row r="532">
       <c r="A532" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="B532" t="inlineStr">
         <is>
-          <t>Wednesday, September 3, 2026</t>
+          <t>Sunday, September 7, 2026</t>
         </is>
       </c>
       <c r="C532" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D532" t="inlineStr">
         <is>
-          <t>05:45 PM – 06:45 PM</t>
+          <t>04:45 PM – 05:45 PM</t>
         </is>
       </c>
       <c r="E532" t="inlineStr">
@@ -30272,19 +30272,19 @@
     </row>
     <row r="534">
       <c r="A534" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B534" t="inlineStr">
         <is>
-          <t>Sunday, September 7, 2026</t>
+          <t>Saturday, September 6, 2026</t>
         </is>
       </c>
       <c r="C534" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D534" t="inlineStr">
         <is>
-          <t>04:45 PM – 05:45 PM</t>
+          <t>05:45 PM – 06:45 PM</t>
         </is>
       </c>
       <c r="E534" t="inlineStr">
@@ -30328,11 +30328,11 @@
     </row>
     <row r="535">
       <c r="A535" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B535" t="inlineStr">
         <is>
-          <t>Tuesday, September 2, 2026</t>
+          <t>Wednesday, September 3, 2026</t>
         </is>
       </c>
       <c r="C535" t="n">
@@ -30384,11 +30384,11 @@
     </row>
     <row r="536">
       <c r="A536" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="B536" t="inlineStr">
         <is>
-          <t>Sunday, September 7, 2026</t>
+          <t>Tuesday, September 2, 2026</t>
         </is>
       </c>
       <c r="C536" t="n">
@@ -30440,19 +30440,19 @@
     </row>
     <row r="537">
       <c r="A537" t="n">
+        <v>2</v>
+      </c>
+      <c r="B537" t="inlineStr">
+        <is>
+          <t>Wednesday, September 3, 2026</t>
+        </is>
+      </c>
+      <c r="C537" t="n">
         <v>3</v>
       </c>
-      <c r="B537" t="inlineStr">
-        <is>
-          <t>Saturday, September 6, 2026</t>
-        </is>
-      </c>
-      <c r="C537" t="n">
-        <v>1</v>
-      </c>
       <c r="D537" t="inlineStr">
         <is>
-          <t>03:30 PM – 04:30 PM</t>
+          <t>05:45 PM – 06:45 PM</t>
         </is>
       </c>
       <c r="E537" t="inlineStr">
@@ -30552,19 +30552,19 @@
     </row>
     <row r="539">
       <c r="A539" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="B539" t="inlineStr">
         <is>
-          <t>Wednesday, September 3, 2026</t>
+          <t>Sunday, September 7, 2026</t>
         </is>
       </c>
       <c r="C539" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D539" t="inlineStr">
         <is>
-          <t>05:45 PM – 06:45 PM</t>
+          <t>03:30 PM – 04:30 PM</t>
         </is>
       </c>
       <c r="E539" t="inlineStr">
@@ -30608,19 +30608,19 @@
     </row>
     <row r="540">
       <c r="A540" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B540" t="inlineStr">
         <is>
-          <t>Wednesday, September 3, 2026</t>
+          <t>Tuesday, September 2, 2026</t>
         </is>
       </c>
       <c r="C540" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D540" t="inlineStr">
         <is>
-          <t>03:30 PM – 04:30 PM</t>
+          <t>05:45 PM – 06:45 PM</t>
         </is>
       </c>
       <c r="E540" t="inlineStr">
@@ -30664,19 +30664,19 @@
     </row>
     <row r="541">
       <c r="A541" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="B541" t="inlineStr">
         <is>
-          <t>Saturday, September 6, 2026</t>
+          <t>Tuesday, September 2, 2026</t>
         </is>
       </c>
       <c r="C541" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D541" t="inlineStr">
         <is>
-          <t>05:45 PM – 06:45 PM</t>
+          <t>04:45 PM – 05:45 PM</t>
         </is>
       </c>
       <c r="E541" t="inlineStr">
@@ -30720,11 +30720,11 @@
     </row>
     <row r="542">
       <c r="A542" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="B542" t="inlineStr">
         <is>
-          <t>Tuesday, September 2, 2026</t>
+          <t>Sunday, September 7, 2026</t>
         </is>
       </c>
       <c r="C542" t="n">
@@ -30776,11 +30776,11 @@
     </row>
     <row r="543">
       <c r="A543" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B543" t="inlineStr">
         <is>
-          <t>Saturday, September 6, 2026</t>
+          <t>Wednesday, September 3, 2026</t>
         </is>
       </c>
       <c r="C543" t="n">
@@ -30840,11 +30840,11 @@
         </is>
       </c>
       <c r="C544" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D544" t="inlineStr">
         <is>
-          <t>03:30 PM – 04:30 PM</t>
+          <t>04:45 PM – 05:45 PM</t>
         </is>
       </c>
       <c r="E544" t="inlineStr">
@@ -30888,11 +30888,11 @@
     </row>
     <row r="545">
       <c r="A545" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="B545" t="inlineStr">
         <is>
-          <t>Tuesday, September 2, 2026</t>
+          <t>Sunday, September 7, 2026</t>
         </is>
       </c>
       <c r="C545" t="n">
@@ -30944,11 +30944,11 @@
     </row>
     <row r="546">
       <c r="A546" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B546" t="inlineStr">
         <is>
-          <t>Wednesday, September 3, 2026</t>
+          <t>Saturday, September 6, 2026</t>
         </is>
       </c>
       <c r="C546" t="n">
@@ -31008,11 +31008,11 @@
         </is>
       </c>
       <c r="C547" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D547" t="inlineStr">
         <is>
-          <t>04:45 PM – 05:45 PM</t>
+          <t>05:45 PM – 06:45 PM</t>
         </is>
       </c>
       <c r="E547" t="inlineStr">
@@ -31056,11 +31056,11 @@
     </row>
     <row r="548">
       <c r="A548" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="B548" t="inlineStr">
         <is>
-          <t>Sunday, September 7, 2026</t>
+          <t>Tuesday, September 2, 2026</t>
         </is>
       </c>
       <c r="C548" t="n">
@@ -31112,19 +31112,19 @@
     </row>
     <row r="549">
       <c r="A549" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="B549" t="inlineStr">
         <is>
-          <t>Saturday, September 6, 2026</t>
+          <t>Tuesday, September 2, 2026</t>
         </is>
       </c>
       <c r="C549" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D549" t="inlineStr">
         <is>
-          <t>05:45 PM – 06:45 PM</t>
+          <t>04:45 PM – 05:45 PM</t>
         </is>
       </c>
       <c r="E549" t="inlineStr">
@@ -31176,11 +31176,11 @@
         </is>
       </c>
       <c r="C550" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D550" t="inlineStr">
         <is>
-          <t>05:45 PM – 06:45 PM</t>
+          <t>03:30 PM – 04:30 PM</t>
         </is>
       </c>
       <c r="E550" t="inlineStr">

--- a/Term_Examination_Schedule_S.Y._2026-2027_Optimized.xlsx
+++ b/Term_Examination_Schedule_S.Y._2026-2027_Optimized.xlsx
@@ -480,11 +480,11 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Saturday, September 6, 2026</t>
+          <t>Wednesday, September 2, 2026</t>
         </is>
       </c>
       <c r="C2" t="n">
@@ -536,19 +536,19 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Tuesday, September 2, 2026</t>
+          <t>Thursday, September 3, 2026</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>07:30 AM – 08:30 AM</t>
+          <t>10:00 AM – 11:00 AM</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -596,7 +596,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Wednesday, September 3, 2026</t>
+          <t>Thursday, September 3, 2026</t>
         </is>
       </c>
       <c r="C4" t="n">
@@ -652,15 +652,15 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Wednesday, September 3, 2026</t>
+          <t>Thursday, September 3, 2026</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>10:00 AM – 11:00 AM</t>
+          <t>08:45 AM – 09:45 AM</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -708,7 +708,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Tuesday, September 2, 2026</t>
+          <t>Wednesday, September 2, 2026</t>
         </is>
       </c>
       <c r="C6" t="n">
@@ -764,15 +764,15 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Wednesday, September 3, 2026</t>
+          <t>Thursday, September 3, 2026</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>08:45 AM – 09:45 AM</t>
+          <t>10:00 AM – 11:00 AM</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -820,7 +820,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Tuesday, September 2, 2026</t>
+          <t>Wednesday, September 2, 2026</t>
         </is>
       </c>
       <c r="C8" t="n">
@@ -872,19 +872,19 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Wednesday, September 3, 2026</t>
+          <t>Wednesday, September 2, 2026</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>10:00 AM – 11:00 AM</t>
+          <t>07:30 AM – 08:30 AM</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -932,7 +932,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Saturday, September 6, 2026</t>
+          <t>Sunday, September 6, 2026</t>
         </is>
       </c>
       <c r="C10" t="n">
@@ -988,7 +988,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Saturday, September 6, 2026</t>
+          <t>Sunday, September 6, 2026</t>
         </is>
       </c>
       <c r="C11" t="n">
@@ -1044,7 +1044,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Wednesday, September 3, 2026</t>
+          <t>Thursday, September 3, 2026</t>
         </is>
       </c>
       <c r="C12" t="n">
@@ -1100,7 +1100,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Wednesday, September 3, 2026</t>
+          <t>Thursday, September 3, 2026</t>
         </is>
       </c>
       <c r="C13" t="n">
@@ -1156,7 +1156,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Wednesday, September 3, 2026</t>
+          <t>Thursday, September 3, 2026</t>
         </is>
       </c>
       <c r="C14" t="n">
@@ -1212,7 +1212,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Tuesday, September 2, 2026</t>
+          <t>Wednesday, September 2, 2026</t>
         </is>
       </c>
       <c r="C15" t="n">
@@ -1268,7 +1268,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Tuesday, September 2, 2026</t>
+          <t>Wednesday, September 2, 2026</t>
         </is>
       </c>
       <c r="C16" t="n">
@@ -1324,7 +1324,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Tuesday, September 2, 2026</t>
+          <t>Wednesday, September 2, 2026</t>
         </is>
       </c>
       <c r="C17" t="n">
@@ -1380,7 +1380,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Saturday, September 6, 2026</t>
+          <t>Sunday, September 6, 2026</t>
         </is>
       </c>
       <c r="C18" t="n">
@@ -1436,7 +1436,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Saturday, September 6, 2026</t>
+          <t>Sunday, September 6, 2026</t>
         </is>
       </c>
       <c r="C19" t="n">
@@ -1492,7 +1492,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Wednesday, September 3, 2026</t>
+          <t>Thursday, September 3, 2026</t>
         </is>
       </c>
       <c r="C20" t="n">
@@ -1548,7 +1548,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Tuesday, September 2, 2026</t>
+          <t>Wednesday, September 2, 2026</t>
         </is>
       </c>
       <c r="C21" t="n">
@@ -1604,7 +1604,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Wednesday, September 3, 2026</t>
+          <t>Thursday, September 3, 2026</t>
         </is>
       </c>
       <c r="C22" t="n">
@@ -1660,7 +1660,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Wednesday, September 3, 2026</t>
+          <t>Thursday, September 3, 2026</t>
         </is>
       </c>
       <c r="C23" t="n">
@@ -1716,15 +1716,15 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Tuesday, September 2, 2026</t>
+          <t>Wednesday, September 2, 2026</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>08:45 AM – 09:45 AM</t>
+          <t>07:30 AM – 08:30 AM</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -1772,15 +1772,15 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Tuesday, September 2, 2026</t>
+          <t>Wednesday, September 2, 2026</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>07:30 AM – 08:30 AM</t>
+          <t>08:45 AM – 09:45 AM</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -1828,7 +1828,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Saturday, September 6, 2026</t>
+          <t>Sunday, September 6, 2026</t>
         </is>
       </c>
       <c r="C26" t="n">
@@ -1884,7 +1884,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Saturday, September 6, 2026</t>
+          <t>Sunday, September 6, 2026</t>
         </is>
       </c>
       <c r="C27" t="n">
@@ -1940,7 +1940,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Saturday, September 6, 2026</t>
+          <t>Sunday, September 6, 2026</t>
         </is>
       </c>
       <c r="C28" t="n">
@@ -1996,7 +1996,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Wednesday, September 3, 2026</t>
+          <t>Thursday, September 3, 2026</t>
         </is>
       </c>
       <c r="C29" t="n">
@@ -2052,7 +2052,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Wednesday, September 3, 2026</t>
+          <t>Thursday, September 3, 2026</t>
         </is>
       </c>
       <c r="C30" t="n">
@@ -2108,7 +2108,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Wednesday, September 3, 2026</t>
+          <t>Thursday, September 3, 2026</t>
         </is>
       </c>
       <c r="C31" t="n">
@@ -2164,7 +2164,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Tuesday, September 2, 2026</t>
+          <t>Wednesday, September 2, 2026</t>
         </is>
       </c>
       <c r="C32" t="n">
@@ -2220,7 +2220,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Tuesday, September 2, 2026</t>
+          <t>Wednesday, September 2, 2026</t>
         </is>
       </c>
       <c r="C33" t="n">
@@ -2276,7 +2276,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Tuesday, September 2, 2026</t>
+          <t>Wednesday, September 2, 2026</t>
         </is>
       </c>
       <c r="C34" t="n">
@@ -2332,7 +2332,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Sunday, September 7, 2026</t>
+          <t>Monday, September 7, 2026</t>
         </is>
       </c>
       <c r="C35" t="n">
@@ -2388,7 +2388,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Saturday, September 6, 2026</t>
+          <t>Sunday, September 6, 2026</t>
         </is>
       </c>
       <c r="C36" t="n">
@@ -2444,7 +2444,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Wednesday, September 3, 2026</t>
+          <t>Thursday, September 3, 2026</t>
         </is>
       </c>
       <c r="C37" t="n">
@@ -2500,7 +2500,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Saturday, September 6, 2026</t>
+          <t>Sunday, September 6, 2026</t>
         </is>
       </c>
       <c r="C38" t="n">
@@ -2556,7 +2556,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Saturday, September 6, 2026</t>
+          <t>Sunday, September 6, 2026</t>
         </is>
       </c>
       <c r="C39" t="n">
@@ -2612,15 +2612,15 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Wednesday, September 3, 2026</t>
+          <t>Thursday, September 3, 2026</t>
         </is>
       </c>
       <c r="C40" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>07:30 AM – 08:30 AM</t>
+          <t>08:45 AM – 09:45 AM</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
@@ -2664,19 +2664,19 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Tuesday, September 2, 2026</t>
+          <t>Thursday, September 3, 2026</t>
         </is>
       </c>
       <c r="C41" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>08:45 AM – 09:45 AM</t>
+          <t>07:30 AM – 08:30 AM</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
@@ -2724,7 +2724,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Tuesday, September 2, 2026</t>
+          <t>Wednesday, September 2, 2026</t>
         </is>
       </c>
       <c r="C42" t="n">
@@ -2776,11 +2776,11 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Wednesday, September 3, 2026</t>
+          <t>Wednesday, September 2, 2026</t>
         </is>
       </c>
       <c r="C43" t="n">
@@ -2836,7 +2836,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Tuesday, September 2, 2026</t>
+          <t>Wednesday, September 2, 2026</t>
         </is>
       </c>
       <c r="C44" t="n">
@@ -2892,7 +2892,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Sunday, September 7, 2026</t>
+          <t>Monday, September 7, 2026</t>
         </is>
       </c>
       <c r="C45" t="n">
@@ -2948,7 +2948,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Saturday, September 6, 2026</t>
+          <t>Sunday, September 6, 2026</t>
         </is>
       </c>
       <c r="C46" t="n">
@@ -3004,7 +3004,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Wednesday, September 3, 2026</t>
+          <t>Thursday, September 3, 2026</t>
         </is>
       </c>
       <c r="C47" t="n">
@@ -3060,7 +3060,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Wednesday, September 3, 2026</t>
+          <t>Thursday, September 3, 2026</t>
         </is>
       </c>
       <c r="C48" t="n">
@@ -3116,7 +3116,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Saturday, September 6, 2026</t>
+          <t>Sunday, September 6, 2026</t>
         </is>
       </c>
       <c r="C49" t="n">
@@ -3172,7 +3172,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Saturday, September 6, 2026</t>
+          <t>Sunday, September 6, 2026</t>
         </is>
       </c>
       <c r="C50" t="n">
@@ -3228,7 +3228,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Wednesday, September 3, 2026</t>
+          <t>Thursday, September 3, 2026</t>
         </is>
       </c>
       <c r="C51" t="n">
@@ -3284,15 +3284,15 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Tuesday, September 2, 2026</t>
+          <t>Wednesday, September 2, 2026</t>
         </is>
       </c>
       <c r="C52" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>10:00 AM – 11:00 AM</t>
+          <t>08:45 AM – 09:45 AM</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
@@ -3340,15 +3340,15 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Tuesday, September 2, 2026</t>
+          <t>Wednesday, September 2, 2026</t>
         </is>
       </c>
       <c r="C53" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>08:45 AM – 09:45 AM</t>
+          <t>07:30 AM – 08:30 AM</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
@@ -3396,15 +3396,15 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Tuesday, September 2, 2026</t>
+          <t>Wednesday, September 2, 2026</t>
         </is>
       </c>
       <c r="C54" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>07:30 AM – 08:30 AM</t>
+          <t>10:00 AM – 11:00 AM</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
@@ -3452,7 +3452,7 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Sunday, September 7, 2026</t>
+          <t>Monday, September 7, 2026</t>
         </is>
       </c>
       <c r="C55" t="n">
@@ -3508,7 +3508,7 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Saturday, September 6, 2026</t>
+          <t>Sunday, September 6, 2026</t>
         </is>
       </c>
       <c r="C56" t="n">
@@ -3564,7 +3564,7 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Saturday, September 6, 2026</t>
+          <t>Sunday, September 6, 2026</t>
         </is>
       </c>
       <c r="C57" t="n">
@@ -3616,19 +3616,19 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Wednesday, September 3, 2026</t>
+          <t>Monday, September 7, 2026</t>
         </is>
       </c>
       <c r="C58" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>10:00 AM – 11:00 AM</t>
+          <t>08:45 AM – 09:45 AM</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
@@ -3676,7 +3676,7 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Wednesday, September 3, 2026</t>
+          <t>Thursday, September 3, 2026</t>
         </is>
       </c>
       <c r="C59" t="n">
@@ -3728,19 +3728,19 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
+        <v>2</v>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>Thursday, September 3, 2026</t>
+        </is>
+      </c>
+      <c r="C60" t="n">
         <v>3</v>
       </c>
-      <c r="B60" t="inlineStr">
-        <is>
-          <t>Saturday, September 6, 2026</t>
-        </is>
-      </c>
-      <c r="C60" t="n">
-        <v>1</v>
-      </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>07:30 AM – 08:30 AM</t>
+          <t>10:00 AM – 11:00 AM</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
@@ -3788,7 +3788,7 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Wednesday, September 3, 2026</t>
+          <t>Thursday, September 3, 2026</t>
         </is>
       </c>
       <c r="C61" t="n">
@@ -3844,7 +3844,7 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Tuesday, September 2, 2026</t>
+          <t>Wednesday, September 2, 2026</t>
         </is>
       </c>
       <c r="C62" t="n">
@@ -3900,7 +3900,7 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Tuesday, September 2, 2026</t>
+          <t>Wednesday, September 2, 2026</t>
         </is>
       </c>
       <c r="C63" t="n">
@@ -3956,7 +3956,7 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Tuesday, September 2, 2026</t>
+          <t>Wednesday, September 2, 2026</t>
         </is>
       </c>
       <c r="C64" t="n">
@@ -4012,7 +4012,7 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Tuesday, September 2, 2026</t>
+          <t>Wednesday, September 2, 2026</t>
         </is>
       </c>
       <c r="C65" t="n">
@@ -4068,7 +4068,7 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Wednesday, September 3, 2026</t>
+          <t>Thursday, September 3, 2026</t>
         </is>
       </c>
       <c r="C66" t="n">
@@ -4124,7 +4124,7 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Tuesday, September 2, 2026</t>
+          <t>Wednesday, September 2, 2026</t>
         </is>
       </c>
       <c r="C67" t="n">
@@ -4180,7 +4180,7 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Tuesday, September 2, 2026</t>
+          <t>Wednesday, September 2, 2026</t>
         </is>
       </c>
       <c r="C68" t="n">
@@ -4236,7 +4236,7 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Saturday, September 6, 2026</t>
+          <t>Sunday, September 6, 2026</t>
         </is>
       </c>
       <c r="C69" t="n">
@@ -4292,7 +4292,7 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Saturday, September 6, 2026</t>
+          <t>Sunday, September 6, 2026</t>
         </is>
       </c>
       <c r="C70" t="n">
@@ -4348,7 +4348,7 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Saturday, September 6, 2026</t>
+          <t>Sunday, September 6, 2026</t>
         </is>
       </c>
       <c r="C71" t="n">
@@ -4404,7 +4404,7 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Tuesday, September 2, 2026</t>
+          <t>Wednesday, September 2, 2026</t>
         </is>
       </c>
       <c r="C72" t="n">
@@ -4460,7 +4460,7 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Wednesday, September 3, 2026</t>
+          <t>Thursday, September 3, 2026</t>
         </is>
       </c>
       <c r="C73" t="n">
@@ -4516,7 +4516,7 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Wednesday, September 3, 2026</t>
+          <t>Thursday, September 3, 2026</t>
         </is>
       </c>
       <c r="C74" t="n">
@@ -4572,7 +4572,7 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Wednesday, September 3, 2026</t>
+          <t>Thursday, September 3, 2026</t>
         </is>
       </c>
       <c r="C75" t="n">
@@ -4628,7 +4628,7 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Tuesday, September 2, 2026</t>
+          <t>Wednesday, September 2, 2026</t>
         </is>
       </c>
       <c r="C76" t="n">
@@ -4684,7 +4684,7 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Tuesday, September 2, 2026</t>
+          <t>Wednesday, September 2, 2026</t>
         </is>
       </c>
       <c r="C77" t="n">
@@ -4740,7 +4740,7 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Saturday, September 6, 2026</t>
+          <t>Sunday, September 6, 2026</t>
         </is>
       </c>
       <c r="C78" t="n">
@@ -4792,11 +4792,11 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Tuesday, September 2, 2026</t>
+          <t>Sunday, September 6, 2026</t>
         </is>
       </c>
       <c r="C79" t="n">
@@ -4848,19 +4848,19 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Saturday, September 6, 2026</t>
+          <t>Thursday, September 3, 2026</t>
         </is>
       </c>
       <c r="C80" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>12:30 PM – 01:30 PM</t>
+          <t>01:45 PM – 02:45 PM</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
@@ -4908,7 +4908,7 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Wednesday, September 3, 2026</t>
+          <t>Thursday, September 3, 2026</t>
         </is>
       </c>
       <c r="C81" t="n">
@@ -4964,7 +4964,7 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Wednesday, September 3, 2026</t>
+          <t>Thursday, September 3, 2026</t>
         </is>
       </c>
       <c r="C82" t="n">
@@ -5016,19 +5016,19 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Wednesday, September 3, 2026</t>
+          <t>Wednesday, September 2, 2026</t>
         </is>
       </c>
       <c r="C83" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>01:45 PM – 02:45 PM</t>
+          <t>02:45 PM – 03:30 PM</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
@@ -5076,7 +5076,7 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Tuesday, September 2, 2026</t>
+          <t>Wednesday, September 2, 2026</t>
         </is>
       </c>
       <c r="C84" t="n">
@@ -5132,7 +5132,7 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Tuesday, September 2, 2026</t>
+          <t>Wednesday, September 2, 2026</t>
         </is>
       </c>
       <c r="C85" t="n">
@@ -5188,7 +5188,7 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Saturday, September 6, 2026</t>
+          <t>Sunday, September 6, 2026</t>
         </is>
       </c>
       <c r="C86" t="n">
@@ -5244,7 +5244,7 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Saturday, September 6, 2026</t>
+          <t>Sunday, September 6, 2026</t>
         </is>
       </c>
       <c r="C87" t="n">
@@ -5300,7 +5300,7 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Saturday, September 6, 2026</t>
+          <t>Sunday, September 6, 2026</t>
         </is>
       </c>
       <c r="C88" t="n">
@@ -5356,7 +5356,7 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Tuesday, September 2, 2026</t>
+          <t>Wednesday, September 2, 2026</t>
         </is>
       </c>
       <c r="C89" t="n">
@@ -5412,15 +5412,15 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Wednesday, September 3, 2026</t>
+          <t>Thursday, September 3, 2026</t>
         </is>
       </c>
       <c r="C90" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>12:30 PM – 01:30 PM</t>
+          <t>02:45 PM – 03:30 PM</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
@@ -5468,15 +5468,15 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Wednesday, September 3, 2026</t>
+          <t>Thursday, September 3, 2026</t>
         </is>
       </c>
       <c r="C91" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>02:45 PM – 03:30 PM</t>
+          <t>01:45 PM – 02:45 PM</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
@@ -5524,15 +5524,15 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Wednesday, September 3, 2026</t>
+          <t>Thursday, September 3, 2026</t>
         </is>
       </c>
       <c r="C92" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>01:45 PM – 02:45 PM</t>
+          <t>12:30 PM – 01:30 PM</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
@@ -5580,7 +5580,7 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Tuesday, September 2, 2026</t>
+          <t>Wednesday, September 2, 2026</t>
         </is>
       </c>
       <c r="C93" t="n">
@@ -5636,7 +5636,7 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Tuesday, September 2, 2026</t>
+          <t>Wednesday, September 2, 2026</t>
         </is>
       </c>
       <c r="C94" t="n">
@@ -5692,15 +5692,15 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Wednesday, September 3, 2026</t>
+          <t>Thursday, September 3, 2026</t>
         </is>
       </c>
       <c r="C95" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>02:45 PM – 03:30 PM</t>
+          <t>12:30 PM – 01:30 PM</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
@@ -5748,15 +5748,15 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Sunday, September 7, 2026</t>
+          <t>Monday, September 7, 2026</t>
         </is>
       </c>
       <c r="C96" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>01:45 PM – 02:45 PM</t>
+          <t>12:30 PM – 01:30 PM</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
@@ -5804,7 +5804,7 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>Saturday, September 6, 2026</t>
+          <t>Sunday, September 6, 2026</t>
         </is>
       </c>
       <c r="C97" t="n">
@@ -5860,15 +5860,15 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>Sunday, September 7, 2026</t>
+          <t>Monday, September 7, 2026</t>
         </is>
       </c>
       <c r="C98" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>12:30 PM – 01:30 PM</t>
+          <t>01:45 PM – 02:45 PM</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
@@ -5916,7 +5916,7 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>Wednesday, September 3, 2026</t>
+          <t>Thursday, September 3, 2026</t>
         </is>
       </c>
       <c r="C99" t="n">
@@ -5972,7 +5972,7 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>Tuesday, September 2, 2026</t>
+          <t>Wednesday, September 2, 2026</t>
         </is>
       </c>
       <c r="C100" t="n">
@@ -6028,7 +6028,7 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>Saturday, September 6, 2026</t>
+          <t>Sunday, September 6, 2026</t>
         </is>
       </c>
       <c r="C101" t="n">
@@ -6084,15 +6084,15 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>Wednesday, September 3, 2026</t>
+          <t>Thursday, September 3, 2026</t>
         </is>
       </c>
       <c r="C102" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>12:30 PM – 01:30 PM</t>
+          <t>02:45 PM – 03:30 PM</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
@@ -6140,7 +6140,7 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>Tuesday, September 2, 2026</t>
+          <t>Wednesday, September 2, 2026</t>
         </is>
       </c>
       <c r="C103" t="n">
@@ -6196,7 +6196,7 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>Tuesday, September 2, 2026</t>
+          <t>Wednesday, September 2, 2026</t>
         </is>
       </c>
       <c r="C104" t="n">
@@ -6252,15 +6252,15 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>Sunday, September 7, 2026</t>
+          <t>Monday, September 7, 2026</t>
         </is>
       </c>
       <c r="C105" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>01:45 PM – 02:45 PM</t>
+          <t>02:45 PM – 03:30 PM</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
@@ -6308,7 +6308,7 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>Saturday, September 6, 2026</t>
+          <t>Sunday, September 6, 2026</t>
         </is>
       </c>
       <c r="C106" t="n">
@@ -6364,7 +6364,7 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>Saturday, September 6, 2026</t>
+          <t>Sunday, September 6, 2026</t>
         </is>
       </c>
       <c r="C107" t="n">
@@ -6420,7 +6420,7 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>Wednesday, September 3, 2026</t>
+          <t>Thursday, September 3, 2026</t>
         </is>
       </c>
       <c r="C108" t="n">
@@ -6476,7 +6476,7 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>Wednesday, September 3, 2026</t>
+          <t>Thursday, September 3, 2026</t>
         </is>
       </c>
       <c r="C109" t="n">
@@ -6532,7 +6532,7 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>Tuesday, September 2, 2026</t>
+          <t>Wednesday, September 2, 2026</t>
         </is>
       </c>
       <c r="C110" t="n">
@@ -6584,11 +6584,11 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>Sunday, September 7, 2026</t>
+          <t>Sunday, September 6, 2026</t>
         </is>
       </c>
       <c r="C111" t="n">
@@ -6644,7 +6644,7 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>Wednesday, September 3, 2026</t>
+          <t>Thursday, September 3, 2026</t>
         </is>
       </c>
       <c r="C112" t="n">
@@ -6700,7 +6700,7 @@
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>Tuesday, September 2, 2026</t>
+          <t>Wednesday, September 2, 2026</t>
         </is>
       </c>
       <c r="C113" t="n">
@@ -6756,7 +6756,7 @@
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>Tuesday, September 2, 2026</t>
+          <t>Wednesday, September 2, 2026</t>
         </is>
       </c>
       <c r="C114" t="n">
@@ -6808,19 +6808,19 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>Wednesday, September 3, 2026</t>
+          <t>Wednesday, September 2, 2026</t>
         </is>
       </c>
       <c r="C115" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>01:45 PM – 02:45 PM</t>
+          <t>02:45 PM – 03:30 PM</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
@@ -6864,19 +6864,19 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>Saturday, September 6, 2026</t>
+          <t>Monday, September 7, 2026</t>
         </is>
       </c>
       <c r="C116" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>02:45 PM – 03:30 PM</t>
+          <t>01:45 PM – 02:45 PM</t>
         </is>
       </c>
       <c r="E116" t="inlineStr">
@@ -6924,15 +6924,15 @@
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>Saturday, September 6, 2026</t>
+          <t>Sunday, September 6, 2026</t>
         </is>
       </c>
       <c r="C117" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>01:45 PM – 02:45 PM</t>
+          <t>02:45 PM – 03:30 PM</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
@@ -6980,7 +6980,7 @@
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>Sunday, September 7, 2026</t>
+          <t>Monday, September 7, 2026</t>
         </is>
       </c>
       <c r="C118" t="n">
@@ -7032,19 +7032,19 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>Wednesday, September 3, 2026</t>
+          <t>Wednesday, September 2, 2026</t>
         </is>
       </c>
       <c r="C119" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>02:45 PM – 03:30 PM</t>
+          <t>12:30 PM – 01:30 PM</t>
         </is>
       </c>
       <c r="E119" t="inlineStr">
@@ -7092,7 +7092,7 @@
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>Saturday, September 6, 2026</t>
+          <t>Sunday, September 6, 2026</t>
         </is>
       </c>
       <c r="C120" t="n">
@@ -7144,19 +7144,19 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>Tuesday, September 2, 2026</t>
+          <t>Thursday, September 3, 2026</t>
         </is>
       </c>
       <c r="C121" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>02:45 PM – 03:30 PM</t>
+          <t>01:45 PM – 02:45 PM</t>
         </is>
       </c>
       <c r="E121" t="inlineStr">
@@ -7204,7 +7204,7 @@
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>Wednesday, September 3, 2026</t>
+          <t>Thursday, September 3, 2026</t>
         </is>
       </c>
       <c r="C122" t="n">
@@ -7260,7 +7260,7 @@
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>Tuesday, September 2, 2026</t>
+          <t>Wednesday, September 2, 2026</t>
         </is>
       </c>
       <c r="C123" t="n">
@@ -7312,19 +7312,19 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>Tuesday, September 2, 2026</t>
+          <t>Sunday, September 6, 2026</t>
         </is>
       </c>
       <c r="C124" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>12:30 PM – 01:30 PM</t>
+          <t>01:45 PM – 02:45 PM</t>
         </is>
       </c>
       <c r="E124" t="inlineStr">
@@ -7372,7 +7372,7 @@
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>Saturday, September 6, 2026</t>
+          <t>Sunday, September 6, 2026</t>
         </is>
       </c>
       <c r="C125" t="n">
@@ -7428,7 +7428,7 @@
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>Sunday, September 7, 2026</t>
+          <t>Monday, September 7, 2026</t>
         </is>
       </c>
       <c r="C126" t="n">
@@ -7484,7 +7484,7 @@
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>Saturday, September 6, 2026</t>
+          <t>Sunday, September 6, 2026</t>
         </is>
       </c>
       <c r="C127" t="n">
@@ -7536,19 +7536,19 @@
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>Sunday, September 7, 2026</t>
+          <t>Sunday, September 6, 2026</t>
         </is>
       </c>
       <c r="C128" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>02:45 PM – 03:30 PM</t>
+          <t>12:30 PM – 01:30 PM</t>
         </is>
       </c>
       <c r="E128" t="inlineStr">
@@ -7596,7 +7596,7 @@
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>Wednesday, September 3, 2026</t>
+          <t>Thursday, September 3, 2026</t>
         </is>
       </c>
       <c r="C129" t="n">
@@ -7652,7 +7652,7 @@
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>Wednesday, September 3, 2026</t>
+          <t>Thursday, September 3, 2026</t>
         </is>
       </c>
       <c r="C130" t="n">
@@ -7704,19 +7704,19 @@
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>Tuesday, September 2, 2026</t>
+          <t>Thursday, September 3, 2026</t>
         </is>
       </c>
       <c r="C131" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>02:45 PM – 03:30 PM</t>
+          <t>01:45 PM – 02:45 PM</t>
         </is>
       </c>
       <c r="E131" t="inlineStr">
@@ -7760,19 +7760,19 @@
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>Wednesday, September 3, 2026</t>
+          <t>Wednesday, September 2, 2026</t>
         </is>
       </c>
       <c r="C132" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>01:45 PM – 02:45 PM</t>
+          <t>02:45 PM – 03:30 PM</t>
         </is>
       </c>
       <c r="E132" t="inlineStr">
@@ -7820,7 +7820,7 @@
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>Tuesday, September 2, 2026</t>
+          <t>Wednesday, September 2, 2026</t>
         </is>
       </c>
       <c r="C133" t="n">
@@ -7876,7 +7876,7 @@
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>Tuesday, September 2, 2026</t>
+          <t>Wednesday, September 2, 2026</t>
         </is>
       </c>
       <c r="C134" t="n">
@@ -7932,7 +7932,7 @@
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>Tuesday, September 2, 2026</t>
+          <t>Wednesday, September 2, 2026</t>
         </is>
       </c>
       <c r="C135" t="n">
@@ -7988,7 +7988,7 @@
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>Tuesday, September 2, 2026</t>
+          <t>Wednesday, September 2, 2026</t>
         </is>
       </c>
       <c r="C136" t="n">
@@ -8044,7 +8044,7 @@
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>Wednesday, September 3, 2026</t>
+          <t>Thursday, September 3, 2026</t>
         </is>
       </c>
       <c r="C137" t="n">
@@ -8100,7 +8100,7 @@
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>Tuesday, September 2, 2026</t>
+          <t>Wednesday, September 2, 2026</t>
         </is>
       </c>
       <c r="C138" t="n">
@@ -8156,7 +8156,7 @@
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>Saturday, September 6, 2026</t>
+          <t>Sunday, September 6, 2026</t>
         </is>
       </c>
       <c r="C139" t="n">
@@ -8212,7 +8212,7 @@
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>Saturday, September 6, 2026</t>
+          <t>Sunday, September 6, 2026</t>
         </is>
       </c>
       <c r="C140" t="n">
@@ -8268,7 +8268,7 @@
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>Wednesday, September 3, 2026</t>
+          <t>Thursday, September 3, 2026</t>
         </is>
       </c>
       <c r="C141" t="n">
@@ -8324,7 +8324,7 @@
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>Wednesday, September 3, 2026</t>
+          <t>Thursday, September 3, 2026</t>
         </is>
       </c>
       <c r="C142" t="n">
@@ -8380,7 +8380,7 @@
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>Wednesday, September 3, 2026</t>
+          <t>Thursday, September 3, 2026</t>
         </is>
       </c>
       <c r="C143" t="n">
@@ -8436,7 +8436,7 @@
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>Tuesday, September 2, 2026</t>
+          <t>Wednesday, September 2, 2026</t>
         </is>
       </c>
       <c r="C144" t="n">
@@ -8492,7 +8492,7 @@
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>Tuesday, September 2, 2026</t>
+          <t>Wednesday, September 2, 2026</t>
         </is>
       </c>
       <c r="C145" t="n">
@@ -8548,7 +8548,7 @@
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>Tuesday, September 2, 2026</t>
+          <t>Wednesday, September 2, 2026</t>
         </is>
       </c>
       <c r="C146" t="n">
@@ -8604,7 +8604,7 @@
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>Wednesday, September 3, 2026</t>
+          <t>Thursday, September 3, 2026</t>
         </is>
       </c>
       <c r="C147" t="n">
@@ -8660,15 +8660,15 @@
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>Saturday, September 6, 2026</t>
+          <t>Sunday, September 6, 2026</t>
         </is>
       </c>
       <c r="C148" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>01:45 PM – 02:45 PM</t>
+          <t>02:45 PM – 03:30 PM</t>
         </is>
       </c>
       <c r="E148" t="inlineStr">
@@ -8716,7 +8716,7 @@
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>Tuesday, September 2, 2026</t>
+          <t>Wednesday, September 2, 2026</t>
         </is>
       </c>
       <c r="C149" t="n">
@@ -8772,7 +8772,7 @@
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>Saturday, September 6, 2026</t>
+          <t>Sunday, September 6, 2026</t>
         </is>
       </c>
       <c r="C150" t="n">
@@ -8824,11 +8824,11 @@
     </row>
     <row r="151">
       <c r="A151" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>Wednesday, September 3, 2026</t>
+          <t>Monday, September 7, 2026</t>
         </is>
       </c>
       <c r="C151" t="n">
@@ -8880,19 +8880,19 @@
     </row>
     <row r="152">
       <c r="A152" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>Wednesday, September 3, 2026</t>
+          <t>Wednesday, September 2, 2026</t>
         </is>
       </c>
       <c r="C152" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>01:45 PM – 02:45 PM</t>
+          <t>02:45 PM – 03:30 PM</t>
         </is>
       </c>
       <c r="E152" t="inlineStr">
@@ -8936,19 +8936,19 @@
     </row>
     <row r="153">
       <c r="A153" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>Tuesday, September 2, 2026</t>
+          <t>Thursday, September 3, 2026</t>
         </is>
       </c>
       <c r="C153" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>02:45 PM – 03:30 PM</t>
+          <t>12:30 PM – 01:30 PM</t>
         </is>
       </c>
       <c r="E153" t="inlineStr">
@@ -8996,7 +8996,7 @@
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>Tuesday, September 2, 2026</t>
+          <t>Wednesday, September 2, 2026</t>
         </is>
       </c>
       <c r="C154" t="n">
@@ -9052,7 +9052,7 @@
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>Wednesday, September 3, 2026</t>
+          <t>Thursday, September 3, 2026</t>
         </is>
       </c>
       <c r="C155" t="n">
@@ -9108,7 +9108,7 @@
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>Wednesday, September 3, 2026</t>
+          <t>Thursday, September 3, 2026</t>
         </is>
       </c>
       <c r="C156" t="n">
@@ -9164,7 +9164,7 @@
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>Saturday, September 6, 2026</t>
+          <t>Sunday, September 6, 2026</t>
         </is>
       </c>
       <c r="C157" t="n">
@@ -9220,7 +9220,7 @@
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>Saturday, September 6, 2026</t>
+          <t>Sunday, September 6, 2026</t>
         </is>
       </c>
       <c r="C158" t="n">
@@ -9276,7 +9276,7 @@
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>Saturday, September 6, 2026</t>
+          <t>Sunday, September 6, 2026</t>
         </is>
       </c>
       <c r="C159" t="n">
@@ -9332,7 +9332,7 @@
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>Wednesday, September 3, 2026</t>
+          <t>Thursday, September 3, 2026</t>
         </is>
       </c>
       <c r="C160" t="n">
@@ -9388,7 +9388,7 @@
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>Tuesday, September 2, 2026</t>
+          <t>Wednesday, September 2, 2026</t>
         </is>
       </c>
       <c r="C161" t="n">
@@ -9444,7 +9444,7 @@
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>Tuesday, September 2, 2026</t>
+          <t>Wednesday, September 2, 2026</t>
         </is>
       </c>
       <c r="C162" t="n">
@@ -9500,7 +9500,7 @@
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>Tuesday, September 2, 2026</t>
+          <t>Wednesday, September 2, 2026</t>
         </is>
       </c>
       <c r="C163" t="n">
@@ -9556,7 +9556,7 @@
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>Sunday, September 7, 2026</t>
+          <t>Monday, September 7, 2026</t>
         </is>
       </c>
       <c r="C164" t="n">
@@ -9612,7 +9612,7 @@
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>Saturday, September 6, 2026</t>
+          <t>Sunday, September 6, 2026</t>
         </is>
       </c>
       <c r="C165" t="n">
@@ -9668,15 +9668,15 @@
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>Wednesday, September 3, 2026</t>
+          <t>Thursday, September 3, 2026</t>
         </is>
       </c>
       <c r="C166" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>12:30 PM – 01:30 PM</t>
+          <t>01:45 PM – 02:45 PM</t>
         </is>
       </c>
       <c r="E166" t="inlineStr">
@@ -9724,7 +9724,7 @@
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>Saturday, September 6, 2026</t>
+          <t>Sunday, September 6, 2026</t>
         </is>
       </c>
       <c r="C167" t="n">
@@ -9780,7 +9780,7 @@
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>Wednesday, September 3, 2026</t>
+          <t>Thursday, September 3, 2026</t>
         </is>
       </c>
       <c r="C168" t="n">
@@ -9836,15 +9836,15 @@
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>Wednesday, September 3, 2026</t>
+          <t>Thursday, September 3, 2026</t>
         </is>
       </c>
       <c r="C169" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t>01:45 PM – 02:45 PM</t>
+          <t>12:30 PM – 01:30 PM</t>
         </is>
       </c>
       <c r="E169" t="inlineStr">
@@ -9892,7 +9892,7 @@
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>Tuesday, September 2, 2026</t>
+          <t>Wednesday, September 2, 2026</t>
         </is>
       </c>
       <c r="C170" t="n">
@@ -9948,7 +9948,7 @@
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>Tuesday, September 2, 2026</t>
+          <t>Wednesday, September 2, 2026</t>
         </is>
       </c>
       <c r="C171" t="n">
@@ -10004,7 +10004,7 @@
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>Tuesday, September 2, 2026</t>
+          <t>Wednesday, September 2, 2026</t>
         </is>
       </c>
       <c r="C172" t="n">
@@ -10060,7 +10060,7 @@
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>Sunday, September 7, 2026</t>
+          <t>Monday, September 7, 2026</t>
         </is>
       </c>
       <c r="C173" t="n">
@@ -10116,7 +10116,7 @@
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>Saturday, September 6, 2026</t>
+          <t>Sunday, September 6, 2026</t>
         </is>
       </c>
       <c r="C174" t="n">
@@ -10172,7 +10172,7 @@
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>Saturday, September 6, 2026</t>
+          <t>Sunday, September 6, 2026</t>
         </is>
       </c>
       <c r="C175" t="n">
@@ -10228,7 +10228,7 @@
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>Saturday, September 6, 2026</t>
+          <t>Sunday, September 6, 2026</t>
         </is>
       </c>
       <c r="C176" t="n">
@@ -10284,7 +10284,7 @@
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>Wednesday, September 3, 2026</t>
+          <t>Thursday, September 3, 2026</t>
         </is>
       </c>
       <c r="C177" t="n">
@@ -10340,7 +10340,7 @@
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>Wednesday, September 3, 2026</t>
+          <t>Thursday, September 3, 2026</t>
         </is>
       </c>
       <c r="C178" t="n">
@@ -10396,7 +10396,7 @@
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>Wednesday, September 3, 2026</t>
+          <t>Thursday, September 3, 2026</t>
         </is>
       </c>
       <c r="C179" t="n">
@@ -10452,7 +10452,7 @@
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>Tuesday, September 2, 2026</t>
+          <t>Wednesday, September 2, 2026</t>
         </is>
       </c>
       <c r="C180" t="n">
@@ -10508,7 +10508,7 @@
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>Tuesday, September 2, 2026</t>
+          <t>Wednesday, September 2, 2026</t>
         </is>
       </c>
       <c r="C181" t="n">
@@ -10564,7 +10564,7 @@
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>Tuesday, September 2, 2026</t>
+          <t>Wednesday, September 2, 2026</t>
         </is>
       </c>
       <c r="C182" t="n">
@@ -10620,7 +10620,7 @@
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>Sunday, September 7, 2026</t>
+          <t>Monday, September 7, 2026</t>
         </is>
       </c>
       <c r="C183" t="n">
@@ -10676,15 +10676,15 @@
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>Wednesday, September 3, 2026</t>
+          <t>Thursday, September 3, 2026</t>
         </is>
       </c>
       <c r="C184" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
-          <t>01:45 PM – 02:45 PM</t>
+          <t>02:45 PM – 03:30 PM</t>
         </is>
       </c>
       <c r="E184" t="inlineStr">
@@ -10732,7 +10732,7 @@
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>Saturday, September 6, 2026</t>
+          <t>Sunday, September 6, 2026</t>
         </is>
       </c>
       <c r="C185" t="n">
@@ -10788,15 +10788,15 @@
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>Saturday, September 6, 2026</t>
+          <t>Sunday, September 6, 2026</t>
         </is>
       </c>
       <c r="C186" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>
-          <t>01:45 PM – 02:45 PM</t>
+          <t>12:30 PM – 01:30 PM</t>
         </is>
       </c>
       <c r="E186" t="inlineStr">
@@ -10844,15 +10844,15 @@
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>Wednesday, September 3, 2026</t>
+          <t>Thursday, September 3, 2026</t>
         </is>
       </c>
       <c r="C187" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>
-          <t>12:30 PM – 01:30 PM</t>
+          <t>01:45 PM – 02:45 PM</t>
         </is>
       </c>
       <c r="E187" t="inlineStr">
@@ -10900,15 +10900,15 @@
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>Saturday, September 6, 2026</t>
+          <t>Sunday, September 6, 2026</t>
         </is>
       </c>
       <c r="C188" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D188" t="inlineStr">
         <is>
-          <t>12:30 PM – 01:30 PM</t>
+          <t>01:45 PM – 02:45 PM</t>
         </is>
       </c>
       <c r="E188" t="inlineStr">
@@ -10956,7 +10956,7 @@
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>Tuesday, September 2, 2026</t>
+          <t>Wednesday, September 2, 2026</t>
         </is>
       </c>
       <c r="C189" t="n">
@@ -11012,15 +11012,15 @@
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>Wednesday, September 3, 2026</t>
+          <t>Thursday, September 3, 2026</t>
         </is>
       </c>
       <c r="C190" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D190" t="inlineStr">
         <is>
-          <t>02:45 PM – 03:30 PM</t>
+          <t>12:30 PM – 01:30 PM</t>
         </is>
       </c>
       <c r="E190" t="inlineStr">
@@ -11068,7 +11068,7 @@
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>Tuesday, September 2, 2026</t>
+          <t>Wednesday, September 2, 2026</t>
         </is>
       </c>
       <c r="C191" t="n">
@@ -11124,7 +11124,7 @@
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>Tuesday, September 2, 2026</t>
+          <t>Wednesday, September 2, 2026</t>
         </is>
       </c>
       <c r="C192" t="n">
@@ -11180,7 +11180,7 @@
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>Sunday, September 7, 2026</t>
+          <t>Monday, September 7, 2026</t>
         </is>
       </c>
       <c r="C193" t="n">
@@ -11236,7 +11236,7 @@
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>Saturday, September 6, 2026</t>
+          <t>Sunday, September 6, 2026</t>
         </is>
       </c>
       <c r="C194" t="n">
@@ -11292,7 +11292,7 @@
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>Saturday, September 6, 2026</t>
+          <t>Sunday, September 6, 2026</t>
         </is>
       </c>
       <c r="C195" t="n">
@@ -11348,7 +11348,7 @@
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>Saturday, September 6, 2026</t>
+          <t>Sunday, September 6, 2026</t>
         </is>
       </c>
       <c r="C196" t="n">
@@ -11404,7 +11404,7 @@
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>Wednesday, September 3, 2026</t>
+          <t>Thursday, September 3, 2026</t>
         </is>
       </c>
       <c r="C197" t="n">
@@ -11460,7 +11460,7 @@
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>Wednesday, September 3, 2026</t>
+          <t>Thursday, September 3, 2026</t>
         </is>
       </c>
       <c r="C198" t="n">
@@ -11516,7 +11516,7 @@
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>Wednesday, September 3, 2026</t>
+          <t>Thursday, September 3, 2026</t>
         </is>
       </c>
       <c r="C199" t="n">
@@ -11572,7 +11572,7 @@
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>Tuesday, September 2, 2026</t>
+          <t>Wednesday, September 2, 2026</t>
         </is>
       </c>
       <c r="C200" t="n">
@@ -11628,7 +11628,7 @@
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>Tuesday, September 2, 2026</t>
+          <t>Wednesday, September 2, 2026</t>
         </is>
       </c>
       <c r="C201" t="n">
@@ -11684,7 +11684,7 @@
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>Tuesday, September 2, 2026</t>
+          <t>Wednesday, September 2, 2026</t>
         </is>
       </c>
       <c r="C202" t="n">
@@ -11740,7 +11740,7 @@
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>Saturday, September 6, 2026</t>
+          <t>Sunday, September 6, 2026</t>
         </is>
       </c>
       <c r="C203" t="n">
@@ -11796,15 +11796,15 @@
       </c>
       <c r="B204" t="inlineStr">
         <is>
-          <t>Tuesday, September 2, 2026</t>
+          <t>Wednesday, September 2, 2026</t>
         </is>
       </c>
       <c r="C204" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D204" t="inlineStr">
         <is>
-          <t>04:45 PM – 05:45 PM</t>
+          <t>03:30 PM – 04:30 PM</t>
         </is>
       </c>
       <c r="E204" t="inlineStr">
@@ -11852,7 +11852,7 @@
       </c>
       <c r="B205" t="inlineStr">
         <is>
-          <t>Wednesday, September 3, 2026</t>
+          <t>Thursday, September 3, 2026</t>
         </is>
       </c>
       <c r="C205" t="n">
@@ -11904,19 +11904,19 @@
     </row>
     <row r="206">
       <c r="A206" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B206" t="inlineStr">
         <is>
-          <t>Wednesday, September 3, 2026</t>
+          <t>Wednesday, September 2, 2026</t>
         </is>
       </c>
       <c r="C206" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D206" t="inlineStr">
         <is>
-          <t>03:30 PM – 04:30 PM</t>
+          <t>05:45 PM – 06:45 PM</t>
         </is>
       </c>
       <c r="E206" t="inlineStr">
@@ -11964,15 +11964,15 @@
       </c>
       <c r="B207" t="inlineStr">
         <is>
-          <t>Tuesday, September 2, 2026</t>
+          <t>Wednesday, September 2, 2026</t>
         </is>
       </c>
       <c r="C207" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D207" t="inlineStr">
         <is>
-          <t>04:45 PM – 05:45 PM</t>
+          <t>05:45 PM – 06:45 PM</t>
         </is>
       </c>
       <c r="E207" t="inlineStr">
@@ -12016,19 +12016,19 @@
     </row>
     <row r="208">
       <c r="A208" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="B208" t="inlineStr">
         <is>
-          <t>Sunday, September 7, 2026</t>
+          <t>Thursday, September 3, 2026</t>
         </is>
       </c>
       <c r="C208" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D208" t="inlineStr">
         <is>
-          <t>04:45 PM – 05:45 PM</t>
+          <t>05:45 PM – 06:45 PM</t>
         </is>
       </c>
       <c r="E208" t="inlineStr">
@@ -12072,19 +12072,19 @@
     </row>
     <row r="209">
       <c r="A209" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="B209" t="inlineStr">
         <is>
-          <t>Tuesday, September 2, 2026</t>
+          <t>Sunday, September 6, 2026</t>
         </is>
       </c>
       <c r="C209" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D209" t="inlineStr">
         <is>
-          <t>03:30 PM – 04:30 PM</t>
+          <t>05:45 PM – 06:45 PM</t>
         </is>
       </c>
       <c r="E209" t="inlineStr">
@@ -12132,15 +12132,15 @@
       </c>
       <c r="B210" t="inlineStr">
         <is>
-          <t>Tuesday, September 2, 2026</t>
+          <t>Wednesday, September 2, 2026</t>
         </is>
       </c>
       <c r="C210" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D210" t="inlineStr">
         <is>
-          <t>05:45 PM – 06:45 PM</t>
+          <t>04:45 PM – 05:45 PM</t>
         </is>
       </c>
       <c r="E210" t="inlineStr">
@@ -12188,15 +12188,15 @@
       </c>
       <c r="B211" t="inlineStr">
         <is>
-          <t>Saturday, September 6, 2026</t>
+          <t>Sunday, September 6, 2026</t>
         </is>
       </c>
       <c r="C211" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D211" t="inlineStr">
         <is>
-          <t>05:45 PM – 06:45 PM</t>
+          <t>04:45 PM – 05:45 PM</t>
         </is>
       </c>
       <c r="E211" t="inlineStr">
@@ -12240,19 +12240,19 @@
     </row>
     <row r="212">
       <c r="A212" t="n">
+        <v>2</v>
+      </c>
+      <c r="B212" t="inlineStr">
+        <is>
+          <t>Thursday, September 3, 2026</t>
+        </is>
+      </c>
+      <c r="C212" t="n">
         <v>3</v>
       </c>
-      <c r="B212" t="inlineStr">
-        <is>
-          <t>Saturday, September 6, 2026</t>
-        </is>
-      </c>
-      <c r="C212" t="n">
-        <v>1</v>
-      </c>
       <c r="D212" t="inlineStr">
         <is>
-          <t>03:30 PM – 04:30 PM</t>
+          <t>05:45 PM – 06:45 PM</t>
         </is>
       </c>
       <c r="E212" t="inlineStr">
@@ -12296,19 +12296,19 @@
     </row>
     <row r="213">
       <c r="A213" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B213" t="inlineStr">
         <is>
-          <t>Tuesday, September 2, 2026</t>
+          <t>Thursday, September 3, 2026</t>
         </is>
       </c>
       <c r="C213" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D213" t="inlineStr">
         <is>
-          <t>04:45 PM – 05:45 PM</t>
+          <t>03:30 PM – 04:30 PM</t>
         </is>
       </c>
       <c r="E213" t="inlineStr">
@@ -12356,15 +12356,15 @@
       </c>
       <c r="B214" t="inlineStr">
         <is>
-          <t>Wednesday, September 3, 2026</t>
+          <t>Thursday, September 3, 2026</t>
         </is>
       </c>
       <c r="C214" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D214" t="inlineStr">
         <is>
-          <t>03:30 PM – 04:30 PM</t>
+          <t>04:45 PM – 05:45 PM</t>
         </is>
       </c>
       <c r="E214" t="inlineStr">
@@ -12408,19 +12408,19 @@
     </row>
     <row r="215">
       <c r="A215" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B215" t="inlineStr">
         <is>
-          <t>Wednesday, September 3, 2026</t>
+          <t>Sunday, September 6, 2026</t>
         </is>
       </c>
       <c r="C215" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D215" t="inlineStr">
         <is>
-          <t>05:45 PM – 06:45 PM</t>
+          <t>03:30 PM – 04:30 PM</t>
         </is>
       </c>
       <c r="E215" t="inlineStr">
@@ -12468,15 +12468,15 @@
       </c>
       <c r="B216" t="inlineStr">
         <is>
-          <t>Tuesday, September 2, 2026</t>
+          <t>Wednesday, September 2, 2026</t>
         </is>
       </c>
       <c r="C216" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D216" t="inlineStr">
         <is>
-          <t>05:45 PM – 06:45 PM</t>
+          <t>04:45 PM – 05:45 PM</t>
         </is>
       </c>
       <c r="E216" t="inlineStr">
@@ -12520,19 +12520,19 @@
     </row>
     <row r="217">
       <c r="A217" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B217" t="inlineStr">
         <is>
-          <t>Wednesday, September 3, 2026</t>
+          <t>Wednesday, September 2, 2026</t>
         </is>
       </c>
       <c r="C217" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D217" t="inlineStr">
         <is>
-          <t>04:45 PM – 05:45 PM</t>
+          <t>05:45 PM – 06:45 PM</t>
         </is>
       </c>
       <c r="E217" t="inlineStr">
@@ -12580,7 +12580,7 @@
       </c>
       <c r="B218" t="inlineStr">
         <is>
-          <t>Tuesday, September 2, 2026</t>
+          <t>Wednesday, September 2, 2026</t>
         </is>
       </c>
       <c r="C218" t="n">
@@ -12636,7 +12636,7 @@
       </c>
       <c r="B219" t="inlineStr">
         <is>
-          <t>Saturday, September 6, 2026</t>
+          <t>Sunday, September 6, 2026</t>
         </is>
       </c>
       <c r="C219" t="n">
@@ -12688,19 +12688,19 @@
     </row>
     <row r="220">
       <c r="A220" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B220" t="inlineStr">
         <is>
-          <t>Wednesday, September 3, 2026</t>
+          <t>Sunday, September 6, 2026</t>
         </is>
       </c>
       <c r="C220" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D220" t="inlineStr">
         <is>
-          <t>04:45 PM – 05:45 PM</t>
+          <t>03:30 PM – 04:30 PM</t>
         </is>
       </c>
       <c r="E220" t="inlineStr">
@@ -12744,19 +12744,19 @@
     </row>
     <row r="221">
       <c r="A221" t="n">
+        <v>2</v>
+      </c>
+      <c r="B221" t="inlineStr">
+        <is>
+          <t>Thursday, September 3, 2026</t>
+        </is>
+      </c>
+      <c r="C221" t="n">
         <v>3</v>
       </c>
-      <c r="B221" t="inlineStr">
-        <is>
-          <t>Saturday, September 6, 2026</t>
-        </is>
-      </c>
-      <c r="C221" t="n">
-        <v>1</v>
-      </c>
       <c r="D221" t="inlineStr">
         <is>
-          <t>03:30 PM – 04:30 PM</t>
+          <t>05:45 PM – 06:45 PM</t>
         </is>
       </c>
       <c r="E221" t="inlineStr">
@@ -12800,19 +12800,19 @@
     </row>
     <row r="222">
       <c r="A222" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B222" t="inlineStr">
         <is>
-          <t>Wednesday, September 3, 2026</t>
+          <t>Wednesday, September 2, 2026</t>
         </is>
       </c>
       <c r="C222" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D222" t="inlineStr">
         <is>
-          <t>05:45 PM – 06:45 PM</t>
+          <t>03:30 PM – 04:30 PM</t>
         </is>
       </c>
       <c r="E222" t="inlineStr">
@@ -12860,15 +12860,15 @@
       </c>
       <c r="B223" t="inlineStr">
         <is>
-          <t>Wednesday, September 3, 2026</t>
+          <t>Thursday, September 3, 2026</t>
         </is>
       </c>
       <c r="C223" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D223" t="inlineStr">
         <is>
-          <t>03:30 PM – 04:30 PM</t>
+          <t>04:45 PM – 05:45 PM</t>
         </is>
       </c>
       <c r="E223" t="inlineStr">
@@ -12912,19 +12912,19 @@
     </row>
     <row r="224">
       <c r="A224" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B224" t="inlineStr">
         <is>
-          <t>Tuesday, September 2, 2026</t>
+          <t>Thursday, September 3, 2026</t>
         </is>
       </c>
       <c r="C224" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D224" t="inlineStr">
         <is>
-          <t>05:45 PM – 06:45 PM</t>
+          <t>03:30 PM – 04:30 PM</t>
         </is>
       </c>
       <c r="E224" t="inlineStr">
@@ -12972,7 +12972,7 @@
       </c>
       <c r="B225" t="inlineStr">
         <is>
-          <t>Tuesday, September 2, 2026</t>
+          <t>Wednesday, September 2, 2026</t>
         </is>
       </c>
       <c r="C225" t="n">
@@ -13028,15 +13028,15 @@
       </c>
       <c r="B226" t="inlineStr">
         <is>
-          <t>Tuesday, September 2, 2026</t>
+          <t>Wednesday, September 2, 2026</t>
         </is>
       </c>
       <c r="C226" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D226" t="inlineStr">
         <is>
-          <t>03:30 PM – 04:30 PM</t>
+          <t>05:45 PM – 06:45 PM</t>
         </is>
       </c>
       <c r="E226" t="inlineStr">
@@ -13084,15 +13084,15 @@
       </c>
       <c r="B227" t="inlineStr">
         <is>
-          <t>Wednesday, September 3, 2026</t>
+          <t>Thursday, September 3, 2026</t>
         </is>
       </c>
       <c r="C227" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D227" t="inlineStr">
         <is>
-          <t>05:45 PM – 06:45 PM</t>
+          <t>04:45 PM – 05:45 PM</t>
         </is>
       </c>
       <c r="E227" t="inlineStr">
@@ -13140,15 +13140,15 @@
       </c>
       <c r="B228" t="inlineStr">
         <is>
-          <t>Saturday, September 6, 2026</t>
+          <t>Sunday, September 6, 2026</t>
         </is>
       </c>
       <c r="C228" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D228" t="inlineStr">
         <is>
-          <t>05:45 PM – 06:45 PM</t>
+          <t>04:45 PM – 05:45 PM</t>
         </is>
       </c>
       <c r="E228" t="inlineStr">
@@ -13192,19 +13192,19 @@
     </row>
     <row r="229">
       <c r="A229" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B229" t="inlineStr">
         <is>
-          <t>Saturday, September 6, 2026</t>
+          <t>Monday, September 7, 2026</t>
         </is>
       </c>
       <c r="C229" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D229" t="inlineStr">
         <is>
-          <t>04:45 PM – 05:45 PM</t>
+          <t>03:30 PM – 04:30 PM</t>
         </is>
       </c>
       <c r="E229" t="inlineStr">
@@ -13252,15 +13252,15 @@
       </c>
       <c r="B230" t="inlineStr">
         <is>
-          <t>Wednesday, September 3, 2026</t>
+          <t>Thursday, September 3, 2026</t>
         </is>
       </c>
       <c r="C230" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D230" t="inlineStr">
         <is>
-          <t>04:45 PM – 05:45 PM</t>
+          <t>05:45 PM – 06:45 PM</t>
         </is>
       </c>
       <c r="E230" t="inlineStr">
@@ -13308,15 +13308,15 @@
       </c>
       <c r="B231" t="inlineStr">
         <is>
-          <t>Tuesday, September 2, 2026</t>
+          <t>Wednesday, September 2, 2026</t>
         </is>
       </c>
       <c r="C231" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D231" t="inlineStr">
         <is>
-          <t>05:45 PM – 06:45 PM</t>
+          <t>03:30 PM – 04:30 PM</t>
         </is>
       </c>
       <c r="E231" t="inlineStr">
@@ -13364,7 +13364,7 @@
       </c>
       <c r="B232" t="inlineStr">
         <is>
-          <t>Saturday, September 6, 2026</t>
+          <t>Sunday, September 6, 2026</t>
         </is>
       </c>
       <c r="C232" t="n">
@@ -13420,7 +13420,7 @@
       </c>
       <c r="B233" t="inlineStr">
         <is>
-          <t>Wednesday, September 3, 2026</t>
+          <t>Thursday, September 3, 2026</t>
         </is>
       </c>
       <c r="C233" t="n">
@@ -13476,15 +13476,15 @@
       </c>
       <c r="B234" t="inlineStr">
         <is>
-          <t>Tuesday, September 2, 2026</t>
+          <t>Wednesday, September 2, 2026</t>
         </is>
       </c>
       <c r="C234" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D234" t="inlineStr">
         <is>
-          <t>04:45 PM – 05:45 PM</t>
+          <t>05:45 PM – 06:45 PM</t>
         </is>
       </c>
       <c r="E234" t="inlineStr">
@@ -13532,15 +13532,15 @@
       </c>
       <c r="B235" t="inlineStr">
         <is>
-          <t>Tuesday, September 2, 2026</t>
+          <t>Wednesday, September 2, 2026</t>
         </is>
       </c>
       <c r="C235" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D235" t="inlineStr">
         <is>
-          <t>03:30 PM – 04:30 PM</t>
+          <t>04:45 PM – 05:45 PM</t>
         </is>
       </c>
       <c r="E235" t="inlineStr">
@@ -13584,19 +13584,19 @@
     </row>
     <row r="236">
       <c r="A236" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B236" t="inlineStr">
         <is>
-          <t>Sunday, September 7, 2026</t>
+          <t>Sunday, September 6, 2026</t>
         </is>
       </c>
       <c r="C236" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D236" t="inlineStr">
         <is>
-          <t>05:45 PM – 06:45 PM</t>
+          <t>04:45 PM – 05:45 PM</t>
         </is>
       </c>
       <c r="E236" t="inlineStr">
@@ -13640,19 +13640,19 @@
     </row>
     <row r="237">
       <c r="A237" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B237" t="inlineStr">
         <is>
-          <t>Saturday, September 6, 2026</t>
+          <t>Monday, September 7, 2026</t>
         </is>
       </c>
       <c r="C237" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D237" t="inlineStr">
         <is>
-          <t>05:45 PM – 06:45 PM</t>
+          <t>03:30 PM – 04:30 PM</t>
         </is>
       </c>
       <c r="E237" t="inlineStr">
@@ -13700,7 +13700,7 @@
       </c>
       <c r="B238" t="inlineStr">
         <is>
-          <t>Saturday, September 6, 2026</t>
+          <t>Sunday, September 6, 2026</t>
         </is>
       </c>
       <c r="C238" t="n">
@@ -13756,15 +13756,15 @@
       </c>
       <c r="B239" t="inlineStr">
         <is>
-          <t>Saturday, September 6, 2026</t>
+          <t>Sunday, September 6, 2026</t>
         </is>
       </c>
       <c r="C239" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D239" t="inlineStr">
         <is>
-          <t>04:45 PM – 05:45 PM</t>
+          <t>05:45 PM – 06:45 PM</t>
         </is>
       </c>
       <c r="E239" t="inlineStr">
@@ -13812,15 +13812,15 @@
       </c>
       <c r="B240" t="inlineStr">
         <is>
-          <t>Tuesday, September 2, 2026</t>
+          <t>Wednesday, September 2, 2026</t>
         </is>
       </c>
       <c r="C240" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D240" t="inlineStr">
         <is>
-          <t>05:45 PM – 06:45 PM</t>
+          <t>03:30 PM – 04:30 PM</t>
         </is>
       </c>
       <c r="E240" t="inlineStr">
@@ -13868,15 +13868,15 @@
       </c>
       <c r="B241" t="inlineStr">
         <is>
-          <t>Wednesday, September 3, 2026</t>
+          <t>Thursday, September 3, 2026</t>
         </is>
       </c>
       <c r="C241" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D241" t="inlineStr">
         <is>
-          <t>05:45 PM – 06:45 PM</t>
+          <t>03:30 PM – 04:30 PM</t>
         </is>
       </c>
       <c r="E241" t="inlineStr">
@@ -13924,15 +13924,15 @@
       </c>
       <c r="B242" t="inlineStr">
         <is>
-          <t>Wednesday, September 3, 2026</t>
+          <t>Thursday, September 3, 2026</t>
         </is>
       </c>
       <c r="C242" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D242" t="inlineStr">
         <is>
-          <t>03:30 PM – 04:30 PM</t>
+          <t>05:45 PM – 06:45 PM</t>
         </is>
       </c>
       <c r="E242" t="inlineStr">
@@ -13976,11 +13976,11 @@
     </row>
     <row r="243">
       <c r="A243" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="B243" t="inlineStr">
         <is>
-          <t>Wednesday, September 3, 2026</t>
+          <t>Monday, September 7, 2026</t>
         </is>
       </c>
       <c r="C243" t="n">
@@ -14032,19 +14032,19 @@
     </row>
     <row r="244">
       <c r="A244" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B244" t="inlineStr">
         <is>
-          <t>Tuesday, September 2, 2026</t>
+          <t>Thursday, September 3, 2026</t>
         </is>
       </c>
       <c r="C244" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D244" t="inlineStr">
         <is>
-          <t>03:30 PM – 04:30 PM</t>
+          <t>04:45 PM – 05:45 PM</t>
         </is>
       </c>
       <c r="E244" t="inlineStr">
@@ -14092,7 +14092,7 @@
       </c>
       <c r="B245" t="inlineStr">
         <is>
-          <t>Tuesday, September 2, 2026</t>
+          <t>Wednesday, September 2, 2026</t>
         </is>
       </c>
       <c r="C245" t="n">
@@ -14144,19 +14144,19 @@
     </row>
     <row r="246">
       <c r="A246" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B246" t="inlineStr">
         <is>
-          <t>Sunday, September 7, 2026</t>
+          <t>Sunday, September 6, 2026</t>
         </is>
       </c>
       <c r="C246" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D246" t="inlineStr">
         <is>
-          <t>12:30 PM – 01:30 PM</t>
+          <t>02:45 PM – 03:30 PM</t>
         </is>
       </c>
       <c r="E246" t="inlineStr">
@@ -14204,15 +14204,15 @@
       </c>
       <c r="B247" t="inlineStr">
         <is>
-          <t>Wednesday, September 3, 2026</t>
+          <t>Thursday, September 3, 2026</t>
         </is>
       </c>
       <c r="C247" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D247" t="inlineStr">
         <is>
-          <t>01:45 PM – 02:45 PM</t>
+          <t>02:45 PM – 03:30 PM</t>
         </is>
       </c>
       <c r="E247" t="inlineStr">
@@ -14256,19 +14256,19 @@
     </row>
     <row r="248">
       <c r="A248" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B248" t="inlineStr">
         <is>
-          <t>Saturday, September 6, 2026</t>
+          <t>Monday, September 7, 2026</t>
         </is>
       </c>
       <c r="C248" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D248" t="inlineStr">
         <is>
-          <t>02:45 PM – 03:30 PM</t>
+          <t>12:30 PM – 01:30 PM</t>
         </is>
       </c>
       <c r="E248" t="inlineStr">
@@ -14316,15 +14316,15 @@
       </c>
       <c r="B249" t="inlineStr">
         <is>
-          <t>Wednesday, September 3, 2026</t>
+          <t>Thursday, September 3, 2026</t>
         </is>
       </c>
       <c r="C249" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D249" t="inlineStr">
         <is>
-          <t>12:30 PM – 01:30 PM</t>
+          <t>01:45 PM – 02:45 PM</t>
         </is>
       </c>
       <c r="E249" t="inlineStr">
@@ -14372,7 +14372,7 @@
       </c>
       <c r="B250" t="inlineStr">
         <is>
-          <t>Saturday, September 6, 2026</t>
+          <t>Sunday, September 6, 2026</t>
         </is>
       </c>
       <c r="C250" t="n">
@@ -14428,7 +14428,7 @@
       </c>
       <c r="B251" t="inlineStr">
         <is>
-          <t>Saturday, September 6, 2026</t>
+          <t>Sunday, September 6, 2026</t>
         </is>
       </c>
       <c r="C251" t="n">
@@ -14484,15 +14484,15 @@
       </c>
       <c r="B252" t="inlineStr">
         <is>
-          <t>Wednesday, September 3, 2026</t>
+          <t>Thursday, September 3, 2026</t>
         </is>
       </c>
       <c r="C252" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D252" t="inlineStr">
         <is>
-          <t>02:45 PM – 03:30 PM</t>
+          <t>12:30 PM – 01:30 PM</t>
         </is>
       </c>
       <c r="E252" t="inlineStr">
@@ -14540,7 +14540,7 @@
       </c>
       <c r="B253" t="inlineStr">
         <is>
-          <t>Tuesday, September 2, 2026</t>
+          <t>Wednesday, September 2, 2026</t>
         </is>
       </c>
       <c r="C253" t="n">
@@ -14596,7 +14596,7 @@
       </c>
       <c r="B254" t="inlineStr">
         <is>
-          <t>Tuesday, September 2, 2026</t>
+          <t>Wednesday, September 2, 2026</t>
         </is>
       </c>
       <c r="C254" t="n">
@@ -14652,7 +14652,7 @@
       </c>
       <c r="B255" t="inlineStr">
         <is>
-          <t>Tuesday, September 2, 2026</t>
+          <t>Wednesday, September 2, 2026</t>
         </is>
       </c>
       <c r="C255" t="n">
@@ -14708,7 +14708,7 @@
       </c>
       <c r="B256" t="inlineStr">
         <is>
-          <t>Sunday, September 7, 2026</t>
+          <t>Monday, September 7, 2026</t>
         </is>
       </c>
       <c r="C256" t="n">
@@ -14764,7 +14764,7 @@
       </c>
       <c r="B257" t="inlineStr">
         <is>
-          <t>Saturday, September 6, 2026</t>
+          <t>Sunday, September 6, 2026</t>
         </is>
       </c>
       <c r="C257" t="n">
@@ -14820,7 +14820,7 @@
       </c>
       <c r="B258" t="inlineStr">
         <is>
-          <t>Saturday, September 6, 2026</t>
+          <t>Sunday, September 6, 2026</t>
         </is>
       </c>
       <c r="C258" t="n">
@@ -14876,7 +14876,7 @@
       </c>
       <c r="B259" t="inlineStr">
         <is>
-          <t>Tuesday, September 2, 2026</t>
+          <t>Wednesday, September 2, 2026</t>
         </is>
       </c>
       <c r="C259" t="n">
@@ -14932,7 +14932,7 @@
       </c>
       <c r="B260" t="inlineStr">
         <is>
-          <t>Saturday, September 6, 2026</t>
+          <t>Sunday, September 6, 2026</t>
         </is>
       </c>
       <c r="C260" t="n">
@@ -14988,7 +14988,7 @@
       </c>
       <c r="B261" t="inlineStr">
         <is>
-          <t>Wednesday, September 3, 2026</t>
+          <t>Thursday, September 3, 2026</t>
         </is>
       </c>
       <c r="C261" t="n">
@@ -15040,19 +15040,19 @@
     </row>
     <row r="262">
       <c r="A262" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="B262" t="inlineStr">
         <is>
-          <t>Sunday, September 7, 2026</t>
+          <t>Thursday, September 3, 2026</t>
         </is>
       </c>
       <c r="C262" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D262" t="inlineStr">
         <is>
-          <t>04:45 PM – 05:45 PM</t>
+          <t>03:30 PM – 04:30 PM</t>
         </is>
       </c>
       <c r="E262" t="inlineStr">
@@ -15100,15 +15100,15 @@
       </c>
       <c r="B263" t="inlineStr">
         <is>
-          <t>Tuesday, September 2, 2026</t>
+          <t>Wednesday, September 2, 2026</t>
         </is>
       </c>
       <c r="C263" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D263" t="inlineStr">
         <is>
-          <t>05:45 PM – 06:45 PM</t>
+          <t>04:45 PM – 05:45 PM</t>
         </is>
       </c>
       <c r="E263" t="inlineStr">
@@ -15156,7 +15156,7 @@
       </c>
       <c r="B264" t="inlineStr">
         <is>
-          <t>Wednesday, September 3, 2026</t>
+          <t>Thursday, September 3, 2026</t>
         </is>
       </c>
       <c r="C264" t="n">
@@ -15208,19 +15208,19 @@
     </row>
     <row r="265">
       <c r="A265" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B265" t="inlineStr">
         <is>
-          <t>Wednesday, September 3, 2026</t>
+          <t>Wednesday, September 2, 2026</t>
         </is>
       </c>
       <c r="C265" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D265" t="inlineStr">
         <is>
-          <t>03:30 PM – 04:30 PM</t>
+          <t>05:45 PM – 06:45 PM</t>
         </is>
       </c>
       <c r="E265" t="inlineStr">
@@ -15268,7 +15268,7 @@
       </c>
       <c r="B266" t="inlineStr">
         <is>
-          <t>Wednesday, September 3, 2026</t>
+          <t>Thursday, September 3, 2026</t>
         </is>
       </c>
       <c r="C266" t="n">
@@ -15324,7 +15324,7 @@
       </c>
       <c r="B267" t="inlineStr">
         <is>
-          <t>Tuesday, September 2, 2026</t>
+          <t>Wednesday, September 2, 2026</t>
         </is>
       </c>
       <c r="C267" t="n">
@@ -15376,19 +15376,19 @@
     </row>
     <row r="268">
       <c r="A268" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B268" t="inlineStr">
         <is>
-          <t>Wednesday, September 3, 2026</t>
+          <t>Wednesday, September 2, 2026</t>
         </is>
       </c>
       <c r="C268" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D268" t="inlineStr">
         <is>
-          <t>03:30 PM – 04:30 PM</t>
+          <t>05:45 PM – 06:45 PM</t>
         </is>
       </c>
       <c r="E268" t="inlineStr">
@@ -15436,7 +15436,7 @@
       </c>
       <c r="B269" t="inlineStr">
         <is>
-          <t>Tuesday, September 2, 2026</t>
+          <t>Wednesday, September 2, 2026</t>
         </is>
       </c>
       <c r="C269" t="n">
@@ -15492,7 +15492,7 @@
       </c>
       <c r="B270" t="inlineStr">
         <is>
-          <t>Wednesday, September 3, 2026</t>
+          <t>Thursday, September 3, 2026</t>
         </is>
       </c>
       <c r="C270" t="n">
@@ -15548,15 +15548,15 @@
       </c>
       <c r="B271" t="inlineStr">
         <is>
-          <t>Tuesday, September 2, 2026</t>
+          <t>Wednesday, September 2, 2026</t>
         </is>
       </c>
       <c r="C271" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D271" t="inlineStr">
         <is>
-          <t>05:45 PM – 06:45 PM</t>
+          <t>03:30 PM – 04:30 PM</t>
         </is>
       </c>
       <c r="E271" t="inlineStr">
@@ -15604,7 +15604,7 @@
       </c>
       <c r="B272" t="inlineStr">
         <is>
-          <t>Tuesday, September 2, 2026</t>
+          <t>Wednesday, September 2, 2026</t>
         </is>
       </c>
       <c r="C272" t="n">
@@ -15656,11 +15656,11 @@
     </row>
     <row r="273">
       <c r="A273" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="B273" t="inlineStr">
         <is>
-          <t>Sunday, September 7, 2026</t>
+          <t>Wednesday, September 2, 2026</t>
         </is>
       </c>
       <c r="C273" t="n">
@@ -15698,7 +15698,7 @@
       </c>
       <c r="J273" t="inlineStr">
         <is>
-          <t>tchr_faidh</t>
+          <t>ustadh_faidh</t>
         </is>
       </c>
       <c r="K273" t="inlineStr">
@@ -15716,15 +15716,15 @@
       </c>
       <c r="B274" t="inlineStr">
         <is>
-          <t>Sunday, September 7, 2026</t>
+          <t>Monday, September 7, 2026</t>
         </is>
       </c>
       <c r="C274" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D274" t="inlineStr">
         <is>
-          <t>04:45 PM – 05:45 PM</t>
+          <t>03:30 PM – 04:30 PM</t>
         </is>
       </c>
       <c r="E274" t="inlineStr">
@@ -15768,19 +15768,19 @@
     </row>
     <row r="275">
       <c r="A275" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B275" t="inlineStr">
         <is>
-          <t>Sunday, September 7, 2026</t>
+          <t>Sunday, September 6, 2026</t>
         </is>
       </c>
       <c r="C275" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D275" t="inlineStr">
         <is>
-          <t>05:45 PM – 06:45 PM</t>
+          <t>03:30 PM – 04:30 PM</t>
         </is>
       </c>
       <c r="E275" t="inlineStr">
@@ -15828,7 +15828,7 @@
       </c>
       <c r="B276" t="inlineStr">
         <is>
-          <t>Wednesday, September 3, 2026</t>
+          <t>Thursday, September 3, 2026</t>
         </is>
       </c>
       <c r="C276" t="n">
@@ -15880,19 +15880,19 @@
     </row>
     <row r="277">
       <c r="A277" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B277" t="inlineStr">
         <is>
-          <t>Wednesday, September 3, 2026</t>
+          <t>Wednesday, September 2, 2026</t>
         </is>
       </c>
       <c r="C277" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D277" t="inlineStr">
         <is>
-          <t>04:45 PM – 05:45 PM</t>
+          <t>05:45 PM – 06:45 PM</t>
         </is>
       </c>
       <c r="E277" t="inlineStr">
@@ -15936,19 +15936,19 @@
     </row>
     <row r="278">
       <c r="A278" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B278" t="inlineStr">
         <is>
-          <t>Tuesday, September 2, 2026</t>
+          <t>Thursday, September 3, 2026</t>
         </is>
       </c>
       <c r="C278" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D278" t="inlineStr">
         <is>
-          <t>04:45 PM – 05:45 PM</t>
+          <t>03:30 PM – 04:30 PM</t>
         </is>
       </c>
       <c r="E278" t="inlineStr">
@@ -15996,15 +15996,15 @@
       </c>
       <c r="B279" t="inlineStr">
         <is>
-          <t>Wednesday, September 3, 2026</t>
+          <t>Thursday, September 3, 2026</t>
         </is>
       </c>
       <c r="C279" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D279" t="inlineStr">
         <is>
-          <t>03:30 PM – 04:30 PM</t>
+          <t>04:45 PM – 05:45 PM</t>
         </is>
       </c>
       <c r="E279" t="inlineStr">
@@ -16052,15 +16052,15 @@
       </c>
       <c r="B280" t="inlineStr">
         <is>
-          <t>Tuesday, September 2, 2026</t>
+          <t>Wednesday, September 2, 2026</t>
         </is>
       </c>
       <c r="C280" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D280" t="inlineStr">
         <is>
-          <t>05:45 PM – 06:45 PM</t>
+          <t>04:45 PM – 05:45 PM</t>
         </is>
       </c>
       <c r="E280" t="inlineStr">
@@ -16108,7 +16108,7 @@
       </c>
       <c r="B281" t="inlineStr">
         <is>
-          <t>Tuesday, September 2, 2026</t>
+          <t>Wednesday, September 2, 2026</t>
         </is>
       </c>
       <c r="C281" t="n">
@@ -16164,7 +16164,7 @@
       </c>
       <c r="B282" t="inlineStr">
         <is>
-          <t>Saturday, September 6, 2026</t>
+          <t>Sunday, September 6, 2026</t>
         </is>
       </c>
       <c r="C282" t="n">
@@ -16216,19 +16216,19 @@
     </row>
     <row r="283">
       <c r="A283" t="n">
+        <v>2</v>
+      </c>
+      <c r="B283" t="inlineStr">
+        <is>
+          <t>Thursday, September 3, 2026</t>
+        </is>
+      </c>
+      <c r="C283" t="n">
         <v>3</v>
       </c>
-      <c r="B283" t="inlineStr">
-        <is>
-          <t>Saturday, September 6, 2026</t>
-        </is>
-      </c>
-      <c r="C283" t="n">
-        <v>1</v>
-      </c>
       <c r="D283" t="inlineStr">
         <is>
-          <t>03:30 PM – 04:30 PM</t>
+          <t>05:45 PM – 06:45 PM</t>
         </is>
       </c>
       <c r="E283" t="inlineStr">
@@ -16272,19 +16272,19 @@
     </row>
     <row r="284">
       <c r="A284" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B284" t="inlineStr">
         <is>
-          <t>Wednesday, September 3, 2026</t>
+          <t>Wednesday, September 2, 2026</t>
         </is>
       </c>
       <c r="C284" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D284" t="inlineStr">
         <is>
-          <t>05:45 PM – 06:45 PM</t>
+          <t>03:30 PM – 04:30 PM</t>
         </is>
       </c>
       <c r="E284" t="inlineStr">
@@ -16332,7 +16332,7 @@
       </c>
       <c r="B285" t="inlineStr">
         <is>
-          <t>Wednesday, September 3, 2026</t>
+          <t>Thursday, September 3, 2026</t>
         </is>
       </c>
       <c r="C285" t="n">
@@ -16384,11 +16384,11 @@
     </row>
     <row r="286">
       <c r="A286" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="B286" t="inlineStr">
         <is>
-          <t>Tuesday, September 2, 2026</t>
+          <t>Sunday, September 6, 2026</t>
         </is>
       </c>
       <c r="C286" t="n">
@@ -16440,19 +16440,19 @@
     </row>
     <row r="287">
       <c r="A287" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B287" t="inlineStr">
         <is>
-          <t>Tuesday, September 2, 2026</t>
+          <t>Thursday, September 3, 2026</t>
         </is>
       </c>
       <c r="C287" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D287" t="inlineStr">
         <is>
-          <t>03:30 PM – 04:30 PM</t>
+          <t>04:45 PM – 05:45 PM</t>
         </is>
       </c>
       <c r="E287" t="inlineStr">
@@ -16496,19 +16496,19 @@
     </row>
     <row r="288">
       <c r="A288" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B288" t="inlineStr">
         <is>
-          <t>Wednesday, September 3, 2026</t>
+          <t>Wednesday, September 2, 2026</t>
         </is>
       </c>
       <c r="C288" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D288" t="inlineStr">
         <is>
-          <t>04:45 PM – 05:45 PM</t>
+          <t>05:45 PM – 06:45 PM</t>
         </is>
       </c>
       <c r="E288" t="inlineStr">
@@ -16556,7 +16556,7 @@
       </c>
       <c r="B289" t="inlineStr">
         <is>
-          <t>Tuesday, September 2, 2026</t>
+          <t>Wednesday, September 2, 2026</t>
         </is>
       </c>
       <c r="C289" t="n">
@@ -16608,11 +16608,11 @@
     </row>
     <row r="290">
       <c r="A290" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B290" t="inlineStr">
         <is>
-          <t>Tuesday, September 2, 2026</t>
+          <t>Thursday, September 3, 2026</t>
         </is>
       </c>
       <c r="C290" t="n">
@@ -16668,15 +16668,15 @@
       </c>
       <c r="B291" t="inlineStr">
         <is>
-          <t>Sunday, September 7, 2026</t>
+          <t>Monday, September 7, 2026</t>
         </is>
       </c>
       <c r="C291" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D291" t="inlineStr">
         <is>
-          <t>04:45 PM – 05:45 PM</t>
+          <t>03:30 PM – 04:30 PM</t>
         </is>
       </c>
       <c r="E291" t="inlineStr">
@@ -16724,7 +16724,7 @@
       </c>
       <c r="B292" t="inlineStr">
         <is>
-          <t>Saturday, September 6, 2026</t>
+          <t>Sunday, September 6, 2026</t>
         </is>
       </c>
       <c r="C292" t="n">
@@ -16780,15 +16780,15 @@
       </c>
       <c r="B293" t="inlineStr">
         <is>
-          <t>Wednesday, September 3, 2026</t>
+          <t>Thursday, September 3, 2026</t>
         </is>
       </c>
       <c r="C293" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D293" t="inlineStr">
         <is>
-          <t>05:45 PM – 06:45 PM</t>
+          <t>04:45 PM – 05:45 PM</t>
         </is>
       </c>
       <c r="E293" t="inlineStr">
@@ -16836,7 +16836,7 @@
       </c>
       <c r="B294" t="inlineStr">
         <is>
-          <t>Saturday, September 6, 2026</t>
+          <t>Sunday, September 6, 2026</t>
         </is>
       </c>
       <c r="C294" t="n">
@@ -16892,7 +16892,7 @@
       </c>
       <c r="B295" t="inlineStr">
         <is>
-          <t>Saturday, September 6, 2026</t>
+          <t>Sunday, September 6, 2026</t>
         </is>
       </c>
       <c r="C295" t="n">
@@ -16944,19 +16944,19 @@
     </row>
     <row r="296">
       <c r="A296" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B296" t="inlineStr">
         <is>
-          <t>Wednesday, September 3, 2026</t>
+          <t>Wednesday, September 2, 2026</t>
         </is>
       </c>
       <c r="C296" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D296" t="inlineStr">
         <is>
-          <t>04:45 PM – 05:45 PM</t>
+          <t>03:30 PM – 04:30 PM</t>
         </is>
       </c>
       <c r="E296" t="inlineStr">
@@ -17004,15 +17004,15 @@
       </c>
       <c r="B297" t="inlineStr">
         <is>
-          <t>Tuesday, September 2, 2026</t>
+          <t>Wednesday, September 2, 2026</t>
         </is>
       </c>
       <c r="C297" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D297" t="inlineStr">
         <is>
-          <t>04:45 PM – 05:45 PM</t>
+          <t>05:45 PM – 06:45 PM</t>
         </is>
       </c>
       <c r="E297" t="inlineStr">
@@ -17060,15 +17060,15 @@
       </c>
       <c r="B298" t="inlineStr">
         <is>
-          <t>Tuesday, September 2, 2026</t>
+          <t>Wednesday, September 2, 2026</t>
         </is>
       </c>
       <c r="C298" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D298" t="inlineStr">
         <is>
-          <t>03:30 PM – 04:30 PM</t>
+          <t>04:45 PM – 05:45 PM</t>
         </is>
       </c>
       <c r="E298" t="inlineStr">
@@ -17116,7 +17116,7 @@
       </c>
       <c r="B299" t="inlineStr">
         <is>
-          <t>Sunday, September 7, 2026</t>
+          <t>Monday, September 7, 2026</t>
         </is>
       </c>
       <c r="C299" t="n">
@@ -17172,15 +17172,15 @@
       </c>
       <c r="B300" t="inlineStr">
         <is>
-          <t>Saturday, September 6, 2026</t>
+          <t>Sunday, September 6, 2026</t>
         </is>
       </c>
       <c r="C300" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D300" t="inlineStr">
         <is>
-          <t>03:30 PM – 04:30 PM</t>
+          <t>04:45 PM – 05:45 PM</t>
         </is>
       </c>
       <c r="E300" t="inlineStr">
@@ -17224,19 +17224,19 @@
     </row>
     <row r="301">
       <c r="A301" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B301" t="inlineStr">
         <is>
-          <t>Saturday, September 6, 2026</t>
+          <t>Thursday, September 3, 2026</t>
         </is>
       </c>
       <c r="C301" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D301" t="inlineStr">
         <is>
-          <t>04:45 PM – 05:45 PM</t>
+          <t>03:30 PM – 04:30 PM</t>
         </is>
       </c>
       <c r="E301" t="inlineStr">
@@ -17266,7 +17266,7 @@
       </c>
       <c r="J301" t="inlineStr">
         <is>
-          <t>tchr_faidh</t>
+          <t>ustadh_faidh</t>
         </is>
       </c>
       <c r="K301" t="inlineStr">
@@ -17284,15 +17284,15 @@
       </c>
       <c r="B302" t="inlineStr">
         <is>
-          <t>Saturday, September 6, 2026</t>
+          <t>Sunday, September 6, 2026</t>
         </is>
       </c>
       <c r="C302" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D302" t="inlineStr">
         <is>
-          <t>05:45 PM – 06:45 PM</t>
+          <t>03:30 PM – 04:30 PM</t>
         </is>
       </c>
       <c r="E302" t="inlineStr">
@@ -17322,7 +17322,7 @@
       </c>
       <c r="J302" t="inlineStr">
         <is>
-          <t>tchr_saliha</t>
+          <t>ustadha_saliha</t>
         </is>
       </c>
       <c r="K302" t="inlineStr">
@@ -17336,19 +17336,19 @@
     </row>
     <row r="303">
       <c r="A303" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="B303" t="inlineStr">
         <is>
-          <t>Wednesday, September 3, 2026</t>
+          <t>Monday, September 7, 2026</t>
         </is>
       </c>
       <c r="C303" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D303" t="inlineStr">
         <is>
-          <t>03:30 PM – 04:30 PM</t>
+          <t>04:45 PM – 05:45 PM</t>
         </is>
       </c>
       <c r="E303" t="inlineStr">
@@ -17392,11 +17392,11 @@
     </row>
     <row r="304">
       <c r="A304" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B304" t="inlineStr">
         <is>
-          <t>Wednesday, September 3, 2026</t>
+          <t>Wednesday, September 2, 2026</t>
         </is>
       </c>
       <c r="C304" t="n">
@@ -17452,15 +17452,15 @@
       </c>
       <c r="B305" t="inlineStr">
         <is>
-          <t>Wednesday, September 3, 2026</t>
+          <t>Thursday, September 3, 2026</t>
         </is>
       </c>
       <c r="C305" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D305" t="inlineStr">
         <is>
-          <t>04:45 PM – 05:45 PM</t>
+          <t>05:45 PM – 06:45 PM</t>
         </is>
       </c>
       <c r="E305" t="inlineStr">
@@ -17508,7 +17508,7 @@
       </c>
       <c r="B306" t="inlineStr">
         <is>
-          <t>Tuesday, September 2, 2026</t>
+          <t>Wednesday, September 2, 2026</t>
         </is>
       </c>
       <c r="C306" t="n">
@@ -17560,19 +17560,19 @@
     </row>
     <row r="307">
       <c r="A307" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B307" t="inlineStr">
         <is>
-          <t>Tuesday, September 2, 2026</t>
+          <t>Thursday, September 3, 2026</t>
         </is>
       </c>
       <c r="C307" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D307" t="inlineStr">
         <is>
-          <t>05:45 PM – 06:45 PM</t>
+          <t>04:45 PM – 05:45 PM</t>
         </is>
       </c>
       <c r="E307" t="inlineStr">
@@ -17620,7 +17620,7 @@
       </c>
       <c r="B308" t="inlineStr">
         <is>
-          <t>Tuesday, September 2, 2026</t>
+          <t>Wednesday, September 2, 2026</t>
         </is>
       </c>
       <c r="C308" t="n">
@@ -17676,15 +17676,15 @@
       </c>
       <c r="B309" t="inlineStr">
         <is>
-          <t>Sunday, September 7, 2026</t>
+          <t>Monday, September 7, 2026</t>
         </is>
       </c>
       <c r="C309" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D309" t="inlineStr">
         <is>
-          <t>03:30 PM – 04:30 PM</t>
+          <t>04:45 PM – 05:45 PM</t>
         </is>
       </c>
       <c r="E309" t="inlineStr">
@@ -17732,15 +17732,15 @@
       </c>
       <c r="B310" t="inlineStr">
         <is>
-          <t>Sunday, September 7, 2026</t>
+          <t>Monday, September 7, 2026</t>
         </is>
       </c>
       <c r="C310" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D310" t="inlineStr">
         <is>
-          <t>04:45 PM – 05:45 PM</t>
+          <t>03:30 PM – 04:30 PM</t>
         </is>
       </c>
       <c r="E310" t="inlineStr">
@@ -17784,11 +17784,11 @@
     </row>
     <row r="311">
       <c r="A311" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B311" t="inlineStr">
         <is>
-          <t>Sunday, September 7, 2026</t>
+          <t>Sunday, September 6, 2026</t>
         </is>
       </c>
       <c r="C311" t="n">
@@ -17844,7 +17844,7 @@
       </c>
       <c r="B312" t="inlineStr">
         <is>
-          <t>Saturday, September 6, 2026</t>
+          <t>Sunday, September 6, 2026</t>
         </is>
       </c>
       <c r="C312" t="n">
@@ -17896,19 +17896,19 @@
     </row>
     <row r="313">
       <c r="A313" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B313" t="inlineStr">
         <is>
-          <t>Wednesday, September 3, 2026</t>
+          <t>Sunday, September 6, 2026</t>
         </is>
       </c>
       <c r="C313" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D313" t="inlineStr">
         <is>
-          <t>05:45 PM – 06:45 PM</t>
+          <t>04:45 PM – 05:45 PM</t>
         </is>
       </c>
       <c r="E313" t="inlineStr">
@@ -17956,15 +17956,15 @@
       </c>
       <c r="B314" t="inlineStr">
         <is>
-          <t>Tuesday, September 2, 2026</t>
+          <t>Wednesday, September 2, 2026</t>
         </is>
       </c>
       <c r="C314" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D314" t="inlineStr">
         <is>
-          <t>05:45 PM – 06:45 PM</t>
+          <t>03:30 PM – 04:30 PM</t>
         </is>
       </c>
       <c r="E314" t="inlineStr">
@@ -18008,19 +18008,19 @@
     </row>
     <row r="315">
       <c r="A315" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B315" t="inlineStr">
         <is>
-          <t>Tuesday, September 2, 2026</t>
+          <t>Thursday, September 3, 2026</t>
         </is>
       </c>
       <c r="C315" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D315" t="inlineStr">
         <is>
-          <t>03:30 PM – 04:30 PM</t>
+          <t>05:45 PM – 06:45 PM</t>
         </is>
       </c>
       <c r="E315" t="inlineStr">
@@ -18068,7 +18068,7 @@
       </c>
       <c r="B316" t="inlineStr">
         <is>
-          <t>Wednesday, September 3, 2026</t>
+          <t>Thursday, September 3, 2026</t>
         </is>
       </c>
       <c r="C316" t="n">
@@ -18120,19 +18120,19 @@
     </row>
     <row r="317">
       <c r="A317" t="n">
+        <v>1</v>
+      </c>
+      <c r="B317" t="inlineStr">
+        <is>
+          <t>Wednesday, September 2, 2026</t>
+        </is>
+      </c>
+      <c r="C317" t="n">
         <v>3</v>
       </c>
-      <c r="B317" t="inlineStr">
-        <is>
-          <t>Saturday, September 6, 2026</t>
-        </is>
-      </c>
-      <c r="C317" t="n">
-        <v>2</v>
-      </c>
       <c r="D317" t="inlineStr">
         <is>
-          <t>04:45 PM – 05:45 PM</t>
+          <t>05:45 PM – 06:45 PM</t>
         </is>
       </c>
       <c r="E317" t="inlineStr">
@@ -18180,7 +18180,7 @@
       </c>
       <c r="B318" t="inlineStr">
         <is>
-          <t>Tuesday, September 2, 2026</t>
+          <t>Wednesday, September 2, 2026</t>
         </is>
       </c>
       <c r="C318" t="n">
@@ -18236,7 +18236,7 @@
       </c>
       <c r="B319" t="inlineStr">
         <is>
-          <t>Sunday, September 7, 2026</t>
+          <t>Monday, September 7, 2026</t>
         </is>
       </c>
       <c r="C319" t="n">
@@ -18292,7 +18292,7 @@
       </c>
       <c r="B320" t="inlineStr">
         <is>
-          <t>Saturday, September 6, 2026</t>
+          <t>Sunday, September 6, 2026</t>
         </is>
       </c>
       <c r="C320" t="n">
@@ -18348,7 +18348,7 @@
       </c>
       <c r="B321" t="inlineStr">
         <is>
-          <t>Saturday, September 6, 2026</t>
+          <t>Sunday, September 6, 2026</t>
         </is>
       </c>
       <c r="C321" t="n">
@@ -18404,7 +18404,7 @@
       </c>
       <c r="B322" t="inlineStr">
         <is>
-          <t>Saturday, September 6, 2026</t>
+          <t>Sunday, September 6, 2026</t>
         </is>
       </c>
       <c r="C322" t="n">
@@ -18460,15 +18460,15 @@
       </c>
       <c r="B323" t="inlineStr">
         <is>
-          <t>Wednesday, September 3, 2026</t>
+          <t>Thursday, September 3, 2026</t>
         </is>
       </c>
       <c r="C323" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D323" t="inlineStr">
         <is>
-          <t>04:45 PM – 05:45 PM</t>
+          <t>05:45 PM – 06:45 PM</t>
         </is>
       </c>
       <c r="E323" t="inlineStr">
@@ -18512,19 +18512,19 @@
     </row>
     <row r="324">
       <c r="A324" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="B324" t="inlineStr">
         <is>
-          <t>Sunday, September 7, 2026</t>
+          <t>Thursday, September 3, 2026</t>
         </is>
       </c>
       <c r="C324" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D324" t="inlineStr">
         <is>
-          <t>03:30 PM – 04:30 PM</t>
+          <t>04:45 PM – 05:45 PM</t>
         </is>
       </c>
       <c r="E324" t="inlineStr">
@@ -18572,7 +18572,7 @@
       </c>
       <c r="B325" t="inlineStr">
         <is>
-          <t>Wednesday, September 3, 2026</t>
+          <t>Thursday, September 3, 2026</t>
         </is>
       </c>
       <c r="C325" t="n">
@@ -18628,7 +18628,7 @@
       </c>
       <c r="B326" t="inlineStr">
         <is>
-          <t>Tuesday, September 2, 2026</t>
+          <t>Wednesday, September 2, 2026</t>
         </is>
       </c>
       <c r="C326" t="n">
@@ -18684,7 +18684,7 @@
       </c>
       <c r="B327" t="inlineStr">
         <is>
-          <t>Tuesday, September 2, 2026</t>
+          <t>Wednesday, September 2, 2026</t>
         </is>
       </c>
       <c r="C327" t="n">
@@ -18740,7 +18740,7 @@
       </c>
       <c r="B328" t="inlineStr">
         <is>
-          <t>Tuesday, September 2, 2026</t>
+          <t>Wednesday, September 2, 2026</t>
         </is>
       </c>
       <c r="C328" t="n">
@@ -18796,7 +18796,7 @@
       </c>
       <c r="B329" t="inlineStr">
         <is>
-          <t>Sunday, September 7, 2026</t>
+          <t>Monday, September 7, 2026</t>
         </is>
       </c>
       <c r="C329" t="n">
@@ -18852,7 +18852,7 @@
       </c>
       <c r="B330" t="inlineStr">
         <is>
-          <t>Saturday, September 6, 2026</t>
+          <t>Sunday, September 6, 2026</t>
         </is>
       </c>
       <c r="C330" t="n">
@@ -18904,19 +18904,19 @@
     </row>
     <row r="331">
       <c r="A331" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B331" t="inlineStr">
         <is>
-          <t>Wednesday, September 3, 2026</t>
+          <t>Wednesday, September 2, 2026</t>
         </is>
       </c>
       <c r="C331" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D331" t="inlineStr">
         <is>
-          <t>05:45 PM – 06:45 PM</t>
+          <t>03:30 PM – 04:30 PM</t>
         </is>
       </c>
       <c r="E331" t="inlineStr">
@@ -18960,11 +18960,11 @@
     </row>
     <row r="332">
       <c r="A332" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="B332" t="inlineStr">
         <is>
-          <t>Sunday, September 7, 2026</t>
+          <t>Wednesday, September 2, 2026</t>
         </is>
       </c>
       <c r="C332" t="n">
@@ -19002,7 +19002,7 @@
       </c>
       <c r="J332" t="inlineStr">
         <is>
-          <t>tchr_faidh</t>
+          <t>ustadh_faidh</t>
         </is>
       </c>
       <c r="K332" t="inlineStr">
@@ -19020,7 +19020,7 @@
       </c>
       <c r="B333" t="inlineStr">
         <is>
-          <t>Saturday, September 6, 2026</t>
+          <t>Sunday, September 6, 2026</t>
         </is>
       </c>
       <c r="C333" t="n">
@@ -19076,7 +19076,7 @@
       </c>
       <c r="B334" t="inlineStr">
         <is>
-          <t>Wednesday, September 3, 2026</t>
+          <t>Thursday, September 3, 2026</t>
         </is>
       </c>
       <c r="C334" t="n">
@@ -19114,12 +19114,12 @@
       </c>
       <c r="J334" t="inlineStr">
         <is>
-          <t>tchr_saimonah</t>
+          <t>tchr_saimona</t>
         </is>
       </c>
       <c r="K334" t="inlineStr">
         <is>
-          <t>Teacher Saimonah</t>
+          <t>Teacher Saimona</t>
         </is>
       </c>
       <c r="L334" t="n">
@@ -19128,11 +19128,11 @@
     </row>
     <row r="335">
       <c r="A335" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B335" t="inlineStr">
         <is>
-          <t>Wednesday, September 3, 2026</t>
+          <t>Sunday, September 6, 2026</t>
         </is>
       </c>
       <c r="C335" t="n">
@@ -19184,11 +19184,11 @@
     </row>
     <row r="336">
       <c r="A336" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B336" t="inlineStr">
         <is>
-          <t>Tuesday, September 2, 2026</t>
+          <t>Thursday, September 3, 2026</t>
         </is>
       </c>
       <c r="C336" t="n">
@@ -19240,19 +19240,19 @@
     </row>
     <row r="337">
       <c r="A337" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B337" t="inlineStr">
         <is>
-          <t>Tuesday, September 2, 2026</t>
+          <t>Thursday, September 3, 2026</t>
         </is>
       </c>
       <c r="C337" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D337" t="inlineStr">
         <is>
-          <t>04:45 PM – 05:45 PM</t>
+          <t>03:30 PM – 04:30 PM</t>
         </is>
       </c>
       <c r="E337" t="inlineStr">
@@ -19300,15 +19300,15 @@
       </c>
       <c r="B338" t="inlineStr">
         <is>
-          <t>Tuesday, September 2, 2026</t>
+          <t>Wednesday, September 2, 2026</t>
         </is>
       </c>
       <c r="C338" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D338" t="inlineStr">
         <is>
-          <t>03:30 PM – 04:30 PM</t>
+          <t>05:45 PM – 06:45 PM</t>
         </is>
       </c>
       <c r="E338" t="inlineStr">
@@ -19356,7 +19356,7 @@
       </c>
       <c r="B339" t="inlineStr">
         <is>
-          <t>Sunday, September 7, 2026</t>
+          <t>Monday, September 7, 2026</t>
         </is>
       </c>
       <c r="C339" t="n">
@@ -19408,11 +19408,11 @@
     </row>
     <row r="340">
       <c r="A340" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B340" t="inlineStr">
         <is>
-          <t>Tuesday, September 2, 2026</t>
+          <t>Thursday, September 3, 2026</t>
         </is>
       </c>
       <c r="C340" t="n">
@@ -19468,15 +19468,15 @@
       </c>
       <c r="B341" t="inlineStr">
         <is>
-          <t>Saturday, September 6, 2026</t>
+          <t>Sunday, September 6, 2026</t>
         </is>
       </c>
       <c r="C341" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D341" t="inlineStr">
         <is>
-          <t>04:45 PM – 05:45 PM</t>
+          <t>05:45 PM – 06:45 PM</t>
         </is>
       </c>
       <c r="E341" t="inlineStr">
@@ -19524,15 +19524,15 @@
       </c>
       <c r="B342" t="inlineStr">
         <is>
-          <t>Wednesday, September 3, 2026</t>
+          <t>Thursday, September 3, 2026</t>
         </is>
       </c>
       <c r="C342" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D342" t="inlineStr">
         <is>
-          <t>03:30 PM – 04:30 PM</t>
+          <t>05:45 PM – 06:45 PM</t>
         </is>
       </c>
       <c r="E342" t="inlineStr">
@@ -19576,19 +19576,19 @@
     </row>
     <row r="343">
       <c r="A343" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="B343" t="inlineStr">
         <is>
-          <t>Wednesday, September 3, 2026</t>
+          <t>Monday, September 7, 2026</t>
         </is>
       </c>
       <c r="C343" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D343" t="inlineStr">
         <is>
-          <t>05:45 PM – 06:45 PM</t>
+          <t>04:45 PM – 05:45 PM</t>
         </is>
       </c>
       <c r="E343" t="inlineStr">
@@ -19632,19 +19632,19 @@
     </row>
     <row r="344">
       <c r="A344" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B344" t="inlineStr">
         <is>
-          <t>Sunday, September 7, 2026</t>
+          <t>Sunday, September 6, 2026</t>
         </is>
       </c>
       <c r="C344" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D344" t="inlineStr">
         <is>
-          <t>05:45 PM – 06:45 PM</t>
+          <t>04:45 PM – 05:45 PM</t>
         </is>
       </c>
       <c r="E344" t="inlineStr">
@@ -19688,19 +19688,19 @@
     </row>
     <row r="345">
       <c r="A345" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B345" t="inlineStr">
         <is>
-          <t>Sunday, September 7, 2026</t>
+          <t>Sunday, September 6, 2026</t>
         </is>
       </c>
       <c r="C345" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D345" t="inlineStr">
         <is>
-          <t>04:45 PM – 05:45 PM</t>
+          <t>03:30 PM – 04:30 PM</t>
         </is>
       </c>
       <c r="E345" t="inlineStr">
@@ -19748,15 +19748,15 @@
       </c>
       <c r="B346" t="inlineStr">
         <is>
-          <t>Tuesday, September 2, 2026</t>
+          <t>Wednesday, September 2, 2026</t>
         </is>
       </c>
       <c r="C346" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D346" t="inlineStr">
         <is>
-          <t>05:45 PM – 06:45 PM</t>
+          <t>03:30 PM – 04:30 PM</t>
         </is>
       </c>
       <c r="E346" t="inlineStr">
@@ -19804,15 +19804,15 @@
       </c>
       <c r="B347" t="inlineStr">
         <is>
-          <t>Tuesday, September 2, 2026</t>
+          <t>Wednesday, September 2, 2026</t>
         </is>
       </c>
       <c r="C347" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D347" t="inlineStr">
         <is>
-          <t>04:45 PM – 05:45 PM</t>
+          <t>05:45 PM – 06:45 PM</t>
         </is>
       </c>
       <c r="E347" t="inlineStr">
@@ -19856,19 +19856,19 @@
     </row>
     <row r="348">
       <c r="A348" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="B348" t="inlineStr">
         <is>
-          <t>Saturday, September 6, 2026</t>
+          <t>Wednesday, September 2, 2026</t>
         </is>
       </c>
       <c r="C348" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D348" t="inlineStr">
         <is>
-          <t>03:30 PM – 04:30 PM</t>
+          <t>04:45 PM – 05:45 PM</t>
         </is>
       </c>
       <c r="E348" t="inlineStr">
@@ -19916,15 +19916,15 @@
       </c>
       <c r="B349" t="inlineStr">
         <is>
-          <t>Sunday, September 7, 2026</t>
+          <t>Monday, September 7, 2026</t>
         </is>
       </c>
       <c r="C349" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D349" t="inlineStr">
         <is>
-          <t>04:45 PM – 05:45 PM</t>
+          <t>03:30 PM – 04:30 PM</t>
         </is>
       </c>
       <c r="E349" t="inlineStr">
@@ -19972,15 +19972,15 @@
       </c>
       <c r="B350" t="inlineStr">
         <is>
-          <t>Wednesday, September 3, 2026</t>
+          <t>Thursday, September 3, 2026</t>
         </is>
       </c>
       <c r="C350" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D350" t="inlineStr">
         <is>
-          <t>05:45 PM – 06:45 PM</t>
+          <t>04:45 PM – 05:45 PM</t>
         </is>
       </c>
       <c r="E350" t="inlineStr">
@@ -20024,19 +20024,19 @@
     </row>
     <row r="351">
       <c r="A351" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B351" t="inlineStr">
         <is>
-          <t>Sunday, September 7, 2026</t>
+          <t>Sunday, September 6, 2026</t>
         </is>
       </c>
       <c r="C351" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D351" t="inlineStr">
         <is>
-          <t>03:30 PM – 04:30 PM</t>
+          <t>05:45 PM – 06:45 PM</t>
         </is>
       </c>
       <c r="E351" t="inlineStr">
@@ -20084,15 +20084,15 @@
       </c>
       <c r="B352" t="inlineStr">
         <is>
-          <t>Saturday, September 6, 2026</t>
+          <t>Sunday, September 6, 2026</t>
         </is>
       </c>
       <c r="C352" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D352" t="inlineStr">
         <is>
-          <t>05:45 PM – 06:45 PM</t>
+          <t>04:45 PM – 05:45 PM</t>
         </is>
       </c>
       <c r="E352" t="inlineStr">
@@ -20140,15 +20140,15 @@
       </c>
       <c r="B353" t="inlineStr">
         <is>
-          <t>Saturday, September 6, 2026</t>
+          <t>Sunday, September 6, 2026</t>
         </is>
       </c>
       <c r="C353" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D353" t="inlineStr">
         <is>
-          <t>04:45 PM – 05:45 PM</t>
+          <t>03:30 PM – 04:30 PM</t>
         </is>
       </c>
       <c r="E353" t="inlineStr">
@@ -20192,19 +20192,19 @@
     </row>
     <row r="354">
       <c r="A354" t="n">
+        <v>2</v>
+      </c>
+      <c r="B354" t="inlineStr">
+        <is>
+          <t>Thursday, September 3, 2026</t>
+        </is>
+      </c>
+      <c r="C354" t="n">
         <v>3</v>
       </c>
-      <c r="B354" t="inlineStr">
-        <is>
-          <t>Saturday, September 6, 2026</t>
-        </is>
-      </c>
-      <c r="C354" t="n">
-        <v>1</v>
-      </c>
       <c r="D354" t="inlineStr">
         <is>
-          <t>03:30 PM – 04:30 PM</t>
+          <t>05:45 PM – 06:45 PM</t>
         </is>
       </c>
       <c r="E354" t="inlineStr">
@@ -20252,7 +20252,7 @@
       </c>
       <c r="B355" t="inlineStr">
         <is>
-          <t>Wednesday, September 3, 2026</t>
+          <t>Thursday, September 3, 2026</t>
         </is>
       </c>
       <c r="C355" t="n">
@@ -20308,7 +20308,7 @@
       </c>
       <c r="B356" t="inlineStr">
         <is>
-          <t>Tuesday, September 2, 2026</t>
+          <t>Wednesday, September 2, 2026</t>
         </is>
       </c>
       <c r="C356" t="n">
@@ -20360,19 +20360,19 @@
     </row>
     <row r="357">
       <c r="A357" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B357" t="inlineStr">
         <is>
-          <t>Wednesday, September 3, 2026</t>
+          <t>Wednesday, September 2, 2026</t>
         </is>
       </c>
       <c r="C357" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D357" t="inlineStr">
         <is>
-          <t>04:45 PM – 05:45 PM</t>
+          <t>05:45 PM – 06:45 PM</t>
         </is>
       </c>
       <c r="E357" t="inlineStr">
@@ -20420,7 +20420,7 @@
       </c>
       <c r="B358" t="inlineStr">
         <is>
-          <t>Tuesday, September 2, 2026</t>
+          <t>Wednesday, September 2, 2026</t>
         </is>
       </c>
       <c r="C358" t="n">
@@ -20476,7 +20476,7 @@
       </c>
       <c r="B359" t="inlineStr">
         <is>
-          <t>Sunday, September 7, 2026</t>
+          <t>Monday, September 7, 2026</t>
         </is>
       </c>
       <c r="C359" t="n">
@@ -20532,7 +20532,7 @@
       </c>
       <c r="B360" t="inlineStr">
         <is>
-          <t>Saturday, September 6, 2026</t>
+          <t>Sunday, September 6, 2026</t>
         </is>
       </c>
       <c r="C360" t="n">
@@ -20588,15 +20588,15 @@
       </c>
       <c r="B361" t="inlineStr">
         <is>
-          <t>Wednesday, September 3, 2026</t>
+          <t>Thursday, September 3, 2026</t>
         </is>
       </c>
       <c r="C361" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D361" t="inlineStr">
         <is>
-          <t>03:30 PM – 04:30 PM</t>
+          <t>05:45 PM – 06:45 PM</t>
         </is>
       </c>
       <c r="E361" t="inlineStr">
@@ -20644,15 +20644,15 @@
       </c>
       <c r="B362" t="inlineStr">
         <is>
-          <t>Saturday, September 6, 2026</t>
+          <t>Sunday, September 6, 2026</t>
         </is>
       </c>
       <c r="C362" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D362" t="inlineStr">
         <is>
-          <t>03:30 PM – 04:30 PM</t>
+          <t>04:45 PM – 05:45 PM</t>
         </is>
       </c>
       <c r="E362" t="inlineStr">
@@ -20696,19 +20696,19 @@
     </row>
     <row r="363">
       <c r="A363" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B363" t="inlineStr">
         <is>
-          <t>Wednesday, September 3, 2026</t>
+          <t>Sunday, September 6, 2026</t>
         </is>
       </c>
       <c r="C363" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D363" t="inlineStr">
         <is>
-          <t>05:45 PM – 06:45 PM</t>
+          <t>03:30 PM – 04:30 PM</t>
         </is>
       </c>
       <c r="E363" t="inlineStr">
@@ -20756,7 +20756,7 @@
       </c>
       <c r="B364" t="inlineStr">
         <is>
-          <t>Wednesday, September 3, 2026</t>
+          <t>Thursday, September 3, 2026</t>
         </is>
       </c>
       <c r="C364" t="n">
@@ -20808,19 +20808,19 @@
     </row>
     <row r="365">
       <c r="A365" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="B365" t="inlineStr">
         <is>
-          <t>Sunday, September 7, 2026</t>
+          <t>Thursday, September 3, 2026</t>
         </is>
       </c>
       <c r="C365" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D365" t="inlineStr">
         <is>
-          <t>05:45 PM – 06:45 PM</t>
+          <t>03:30 PM – 04:30 PM</t>
         </is>
       </c>
       <c r="E365" t="inlineStr">
@@ -20868,7 +20868,7 @@
       </c>
       <c r="B366" t="inlineStr">
         <is>
-          <t>Tuesday, September 2, 2026</t>
+          <t>Wednesday, September 2, 2026</t>
         </is>
       </c>
       <c r="C366" t="n">
@@ -20924,7 +20924,7 @@
       </c>
       <c r="B367" t="inlineStr">
         <is>
-          <t>Tuesday, September 2, 2026</t>
+          <t>Wednesday, September 2, 2026</t>
         </is>
       </c>
       <c r="C367" t="n">
@@ -20980,7 +20980,7 @@
       </c>
       <c r="B368" t="inlineStr">
         <is>
-          <t>Tuesday, September 2, 2026</t>
+          <t>Wednesday, September 2, 2026</t>
         </is>
       </c>
       <c r="C368" t="n">
@@ -21036,15 +21036,15 @@
       </c>
       <c r="B369" t="inlineStr">
         <is>
-          <t>Sunday, September 7, 2026</t>
+          <t>Monday, September 7, 2026</t>
         </is>
       </c>
       <c r="C369" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D369" t="inlineStr">
         <is>
-          <t>08:45 AM – 09:45 AM</t>
+          <t>07:30 AM – 08:30 AM</t>
         </is>
       </c>
       <c r="E369" t="inlineStr">
@@ -21088,19 +21088,19 @@
     </row>
     <row r="370">
       <c r="A370" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B370" t="inlineStr">
         <is>
-          <t>Sunday, September 7, 2026</t>
+          <t>Sunday, September 6, 2026</t>
         </is>
       </c>
       <c r="C370" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D370" t="inlineStr">
         <is>
-          <t>07:30 AM – 08:30 AM</t>
+          <t>10:00 AM – 11:00 AM</t>
         </is>
       </c>
       <c r="E370" t="inlineStr">
@@ -21148,15 +21148,15 @@
       </c>
       <c r="B371" t="inlineStr">
         <is>
-          <t>Saturday, September 6, 2026</t>
+          <t>Sunday, September 6, 2026</t>
         </is>
       </c>
       <c r="C371" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D371" t="inlineStr">
         <is>
-          <t>10:00 AM – 11:00 AM</t>
+          <t>08:45 AM – 09:45 AM</t>
         </is>
       </c>
       <c r="E371" t="inlineStr">
@@ -21204,15 +21204,15 @@
       </c>
       <c r="B372" t="inlineStr">
         <is>
-          <t>Saturday, September 6, 2026</t>
+          <t>Sunday, September 6, 2026</t>
         </is>
       </c>
       <c r="C372" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D372" t="inlineStr">
         <is>
-          <t>08:45 AM – 09:45 AM</t>
+          <t>07:30 AM – 08:30 AM</t>
         </is>
       </c>
       <c r="E372" t="inlineStr">
@@ -21260,7 +21260,7 @@
       </c>
       <c r="B373" t="inlineStr">
         <is>
-          <t>Wednesday, September 3, 2026</t>
+          <t>Thursday, September 3, 2026</t>
         </is>
       </c>
       <c r="C373" t="n">
@@ -21316,7 +21316,7 @@
       </c>
       <c r="B374" t="inlineStr">
         <is>
-          <t>Wednesday, September 3, 2026</t>
+          <t>Thursday, September 3, 2026</t>
         </is>
       </c>
       <c r="C374" t="n">
@@ -21372,7 +21372,7 @@
       </c>
       <c r="B375" t="inlineStr">
         <is>
-          <t>Wednesday, September 3, 2026</t>
+          <t>Thursday, September 3, 2026</t>
         </is>
       </c>
       <c r="C375" t="n">
@@ -21428,7 +21428,7 @@
       </c>
       <c r="B376" t="inlineStr">
         <is>
-          <t>Tuesday, September 2, 2026</t>
+          <t>Wednesday, September 2, 2026</t>
         </is>
       </c>
       <c r="C376" t="n">
@@ -21484,7 +21484,7 @@
       </c>
       <c r="B377" t="inlineStr">
         <is>
-          <t>Tuesday, September 2, 2026</t>
+          <t>Wednesday, September 2, 2026</t>
         </is>
       </c>
       <c r="C377" t="n">
@@ -21540,7 +21540,7 @@
       </c>
       <c r="B378" t="inlineStr">
         <is>
-          <t>Tuesday, September 2, 2026</t>
+          <t>Wednesday, September 2, 2026</t>
         </is>
       </c>
       <c r="C378" t="n">
@@ -21596,15 +21596,15 @@
       </c>
       <c r="B379" t="inlineStr">
         <is>
-          <t>Sunday, September 7, 2026</t>
+          <t>Monday, September 7, 2026</t>
         </is>
       </c>
       <c r="C379" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D379" t="inlineStr">
         <is>
-          <t>08:45 AM – 09:45 AM</t>
+          <t>07:30 AM – 08:30 AM</t>
         </is>
       </c>
       <c r="E379" t="inlineStr">
@@ -21648,19 +21648,19 @@
     </row>
     <row r="380">
       <c r="A380" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B380" t="inlineStr">
         <is>
-          <t>Sunday, September 7, 2026</t>
+          <t>Sunday, September 6, 2026</t>
         </is>
       </c>
       <c r="C380" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D380" t="inlineStr">
         <is>
-          <t>07:30 AM – 09:30 AM</t>
+          <t>10:00 AM – 12:00 PM</t>
         </is>
       </c>
       <c r="E380" t="inlineStr">
@@ -21708,15 +21708,15 @@
       </c>
       <c r="B381" t="inlineStr">
         <is>
-          <t>Saturday, September 6, 2026</t>
+          <t>Sunday, September 6, 2026</t>
         </is>
       </c>
       <c r="C381" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D381" t="inlineStr">
         <is>
-          <t>10:00 AM – 11:00 AM</t>
+          <t>08:45 AM – 09:45 AM</t>
         </is>
       </c>
       <c r="E381" t="inlineStr">
@@ -21764,7 +21764,7 @@
       </c>
       <c r="B382" t="inlineStr">
         <is>
-          <t>Wednesday, September 3, 2026</t>
+          <t>Thursday, September 3, 2026</t>
         </is>
       </c>
       <c r="C382" t="n">
@@ -21820,15 +21820,15 @@
       </c>
       <c r="B383" t="inlineStr">
         <is>
-          <t>Saturday, September 6, 2026</t>
+          <t>Sunday, September 6, 2026</t>
         </is>
       </c>
       <c r="C383" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D383" t="inlineStr">
         <is>
-          <t>08:45 AM – 09:45 AM</t>
+          <t>07:30 AM – 08:30 AM</t>
         </is>
       </c>
       <c r="E383" t="inlineStr">
@@ -21876,7 +21876,7 @@
       </c>
       <c r="B384" t="inlineStr">
         <is>
-          <t>Wednesday, September 3, 2026</t>
+          <t>Thursday, September 3, 2026</t>
         </is>
       </c>
       <c r="C384" t="n">
@@ -21932,7 +21932,7 @@
       </c>
       <c r="B385" t="inlineStr">
         <is>
-          <t>Wednesday, September 3, 2026</t>
+          <t>Thursday, September 3, 2026</t>
         </is>
       </c>
       <c r="C385" t="n">
@@ -21988,7 +21988,7 @@
       </c>
       <c r="B386" t="inlineStr">
         <is>
-          <t>Tuesday, September 2, 2026</t>
+          <t>Wednesday, September 2, 2026</t>
         </is>
       </c>
       <c r="C386" t="n">
@@ -22044,7 +22044,7 @@
       </c>
       <c r="B387" t="inlineStr">
         <is>
-          <t>Tuesday, September 2, 2026</t>
+          <t>Wednesday, September 2, 2026</t>
         </is>
       </c>
       <c r="C387" t="n">
@@ -22100,7 +22100,7 @@
       </c>
       <c r="B388" t="inlineStr">
         <is>
-          <t>Tuesday, September 2, 2026</t>
+          <t>Wednesday, September 2, 2026</t>
         </is>
       </c>
       <c r="C388" t="n">
@@ -22156,7 +22156,7 @@
       </c>
       <c r="B389" t="inlineStr">
         <is>
-          <t>Saturday, September 6, 2026</t>
+          <t>Sunday, September 6, 2026</t>
         </is>
       </c>
       <c r="C389" t="n">
@@ -22212,7 +22212,7 @@
       </c>
       <c r="B390" t="inlineStr">
         <is>
-          <t>Saturday, September 6, 2026</t>
+          <t>Sunday, September 6, 2026</t>
         </is>
       </c>
       <c r="C390" t="n">
@@ -22268,7 +22268,7 @@
       </c>
       <c r="B391" t="inlineStr">
         <is>
-          <t>Saturday, September 6, 2026</t>
+          <t>Sunday, September 6, 2026</t>
         </is>
       </c>
       <c r="C391" t="n">
@@ -22324,7 +22324,7 @@
       </c>
       <c r="B392" t="inlineStr">
         <is>
-          <t>Wednesday, September 3, 2026</t>
+          <t>Thursday, September 3, 2026</t>
         </is>
       </c>
       <c r="C392" t="n">
@@ -22380,7 +22380,7 @@
       </c>
       <c r="B393" t="inlineStr">
         <is>
-          <t>Wednesday, September 3, 2026</t>
+          <t>Thursday, September 3, 2026</t>
         </is>
       </c>
       <c r="C393" t="n">
@@ -22436,7 +22436,7 @@
       </c>
       <c r="B394" t="inlineStr">
         <is>
-          <t>Wednesday, September 3, 2026</t>
+          <t>Thursday, September 3, 2026</t>
         </is>
       </c>
       <c r="C394" t="n">
@@ -22492,7 +22492,7 @@
       </c>
       <c r="B395" t="inlineStr">
         <is>
-          <t>Tuesday, September 2, 2026</t>
+          <t>Wednesday, September 2, 2026</t>
         </is>
       </c>
       <c r="C395" t="n">
@@ -22548,7 +22548,7 @@
       </c>
       <c r="B396" t="inlineStr">
         <is>
-          <t>Tuesday, September 2, 2026</t>
+          <t>Wednesday, September 2, 2026</t>
         </is>
       </c>
       <c r="C396" t="n">
@@ -22604,7 +22604,7 @@
       </c>
       <c r="B397" t="inlineStr">
         <is>
-          <t>Tuesday, September 2, 2026</t>
+          <t>Wednesday, September 2, 2026</t>
         </is>
       </c>
       <c r="C397" t="n">
@@ -22660,7 +22660,7 @@
       </c>
       <c r="B398" t="inlineStr">
         <is>
-          <t>Saturday, September 6, 2026</t>
+          <t>Sunday, September 6, 2026</t>
         </is>
       </c>
       <c r="C398" t="n">
@@ -22716,7 +22716,7 @@
       </c>
       <c r="B399" t="inlineStr">
         <is>
-          <t>Saturday, September 6, 2026</t>
+          <t>Sunday, September 6, 2026</t>
         </is>
       </c>
       <c r="C399" t="n">
@@ -22772,7 +22772,7 @@
       </c>
       <c r="B400" t="inlineStr">
         <is>
-          <t>Saturday, September 6, 2026</t>
+          <t>Sunday, September 6, 2026</t>
         </is>
       </c>
       <c r="C400" t="n">
@@ -22828,7 +22828,7 @@
       </c>
       <c r="B401" t="inlineStr">
         <is>
-          <t>Wednesday, September 3, 2026</t>
+          <t>Thursday, September 3, 2026</t>
         </is>
       </c>
       <c r="C401" t="n">
@@ -22884,7 +22884,7 @@
       </c>
       <c r="B402" t="inlineStr">
         <is>
-          <t>Wednesday, September 3, 2026</t>
+          <t>Thursday, September 3, 2026</t>
         </is>
       </c>
       <c r="C402" t="n">
@@ -22940,7 +22940,7 @@
       </c>
       <c r="B403" t="inlineStr">
         <is>
-          <t>Wednesday, September 3, 2026</t>
+          <t>Thursday, September 3, 2026</t>
         </is>
       </c>
       <c r="C403" t="n">
@@ -22996,7 +22996,7 @@
       </c>
       <c r="B404" t="inlineStr">
         <is>
-          <t>Tuesday, September 2, 2026</t>
+          <t>Wednesday, September 2, 2026</t>
         </is>
       </c>
       <c r="C404" t="n">
@@ -23052,7 +23052,7 @@
       </c>
       <c r="B405" t="inlineStr">
         <is>
-          <t>Tuesday, September 2, 2026</t>
+          <t>Wednesday, September 2, 2026</t>
         </is>
       </c>
       <c r="C405" t="n">
@@ -23108,7 +23108,7 @@
       </c>
       <c r="B406" t="inlineStr">
         <is>
-          <t>Tuesday, September 2, 2026</t>
+          <t>Wednesday, September 2, 2026</t>
         </is>
       </c>
       <c r="C406" t="n">
@@ -23164,7 +23164,7 @@
       </c>
       <c r="B407" t="inlineStr">
         <is>
-          <t>Saturday, September 6, 2026</t>
+          <t>Sunday, September 6, 2026</t>
         </is>
       </c>
       <c r="C407" t="n">
@@ -23220,7 +23220,7 @@
       </c>
       <c r="B408" t="inlineStr">
         <is>
-          <t>Saturday, September 6, 2026</t>
+          <t>Sunday, September 6, 2026</t>
         </is>
       </c>
       <c r="C408" t="n">
@@ -23276,7 +23276,7 @@
       </c>
       <c r="B409" t="inlineStr">
         <is>
-          <t>Saturday, September 6, 2026</t>
+          <t>Sunday, September 6, 2026</t>
         </is>
       </c>
       <c r="C409" t="n">
@@ -23332,7 +23332,7 @@
       </c>
       <c r="B410" t="inlineStr">
         <is>
-          <t>Wednesday, September 3, 2026</t>
+          <t>Thursday, September 3, 2026</t>
         </is>
       </c>
       <c r="C410" t="n">
@@ -23388,7 +23388,7 @@
       </c>
       <c r="B411" t="inlineStr">
         <is>
-          <t>Wednesday, September 3, 2026</t>
+          <t>Thursday, September 3, 2026</t>
         </is>
       </c>
       <c r="C411" t="n">
@@ -23444,7 +23444,7 @@
       </c>
       <c r="B412" t="inlineStr">
         <is>
-          <t>Wednesday, September 3, 2026</t>
+          <t>Thursday, September 3, 2026</t>
         </is>
       </c>
       <c r="C412" t="n">
@@ -23500,7 +23500,7 @@
       </c>
       <c r="B413" t="inlineStr">
         <is>
-          <t>Tuesday, September 2, 2026</t>
+          <t>Wednesday, September 2, 2026</t>
         </is>
       </c>
       <c r="C413" t="n">
@@ -23556,7 +23556,7 @@
       </c>
       <c r="B414" t="inlineStr">
         <is>
-          <t>Tuesday, September 2, 2026</t>
+          <t>Wednesday, September 2, 2026</t>
         </is>
       </c>
       <c r="C414" t="n">
@@ -23612,7 +23612,7 @@
       </c>
       <c r="B415" t="inlineStr">
         <is>
-          <t>Tuesday, September 2, 2026</t>
+          <t>Wednesday, September 2, 2026</t>
         </is>
       </c>
       <c r="C415" t="n">
@@ -23668,7 +23668,7 @@
       </c>
       <c r="B416" t="inlineStr">
         <is>
-          <t>Saturday, September 6, 2026</t>
+          <t>Sunday, September 6, 2026</t>
         </is>
       </c>
       <c r="C416" t="n">
@@ -23724,7 +23724,7 @@
       </c>
       <c r="B417" t="inlineStr">
         <is>
-          <t>Wednesday, September 3, 2026</t>
+          <t>Thursday, September 3, 2026</t>
         </is>
       </c>
       <c r="C417" t="n">
@@ -23780,7 +23780,7 @@
       </c>
       <c r="B418" t="inlineStr">
         <is>
-          <t>Wednesday, September 3, 2026</t>
+          <t>Thursday, September 3, 2026</t>
         </is>
       </c>
       <c r="C418" t="n">
@@ -23836,7 +23836,7 @@
       </c>
       <c r="B419" t="inlineStr">
         <is>
-          <t>Wednesday, September 3, 2026</t>
+          <t>Thursday, September 3, 2026</t>
         </is>
       </c>
       <c r="C419" t="n">
@@ -23892,7 +23892,7 @@
       </c>
       <c r="B420" t="inlineStr">
         <is>
-          <t>Tuesday, September 2, 2026</t>
+          <t>Wednesday, September 2, 2026</t>
         </is>
       </c>
       <c r="C420" t="n">
@@ -23948,7 +23948,7 @@
       </c>
       <c r="B421" t="inlineStr">
         <is>
-          <t>Tuesday, September 2, 2026</t>
+          <t>Wednesday, September 2, 2026</t>
         </is>
       </c>
       <c r="C421" t="n">
@@ -24004,7 +24004,7 @@
       </c>
       <c r="B422" t="inlineStr">
         <is>
-          <t>Tuesday, September 2, 2026</t>
+          <t>Wednesday, September 2, 2026</t>
         </is>
       </c>
       <c r="C422" t="n">
@@ -24060,7 +24060,7 @@
       </c>
       <c r="B423" t="inlineStr">
         <is>
-          <t>Sunday, September 7, 2026</t>
+          <t>Monday, September 7, 2026</t>
         </is>
       </c>
       <c r="C423" t="n">
@@ -24116,7 +24116,7 @@
       </c>
       <c r="B424" t="inlineStr">
         <is>
-          <t>Saturday, September 6, 2026</t>
+          <t>Sunday, September 6, 2026</t>
         </is>
       </c>
       <c r="C424" t="n">
@@ -24172,15 +24172,15 @@
       </c>
       <c r="B425" t="inlineStr">
         <is>
-          <t>Wednesday, September 3, 2026</t>
+          <t>Thursday, September 3, 2026</t>
         </is>
       </c>
       <c r="C425" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D425" t="inlineStr">
         <is>
-          <t>12:30 PM – 01:30 PM</t>
+          <t>02:45 PM – 03:30 PM</t>
         </is>
       </c>
       <c r="E425" t="inlineStr">
@@ -24228,7 +24228,7 @@
       </c>
       <c r="B426" t="inlineStr">
         <is>
-          <t>Saturday, September 6, 2026</t>
+          <t>Sunday, September 6, 2026</t>
         </is>
       </c>
       <c r="C426" t="n">
@@ -24280,19 +24280,19 @@
     </row>
     <row r="427">
       <c r="A427" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B427" t="inlineStr">
         <is>
-          <t>Wednesday, September 3, 2026</t>
+          <t>Sunday, September 6, 2026</t>
         </is>
       </c>
       <c r="C427" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D427" t="inlineStr">
         <is>
-          <t>02:45 PM – 03:30 PM</t>
+          <t>12:30 PM – 01:30 PM</t>
         </is>
       </c>
       <c r="E427" t="inlineStr">
@@ -24336,19 +24336,19 @@
     </row>
     <row r="428">
       <c r="A428" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B428" t="inlineStr">
         <is>
-          <t>Saturday, September 6, 2026</t>
+          <t>Thursday, September 3, 2026</t>
         </is>
       </c>
       <c r="C428" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D428" t="inlineStr">
         <is>
-          <t>12:30 PM – 01:30 PM</t>
+          <t>01:45 PM – 02:45 PM</t>
         </is>
       </c>
       <c r="E428" t="inlineStr">
@@ -24396,7 +24396,7 @@
       </c>
       <c r="B429" t="inlineStr">
         <is>
-          <t>Tuesday, September 2, 2026</t>
+          <t>Wednesday, September 2, 2026</t>
         </is>
       </c>
       <c r="C429" t="n">
@@ -24452,15 +24452,15 @@
       </c>
       <c r="B430" t="inlineStr">
         <is>
-          <t>Wednesday, September 3, 2026</t>
+          <t>Thursday, September 3, 2026</t>
         </is>
       </c>
       <c r="C430" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D430" t="inlineStr">
         <is>
-          <t>01:45 PM – 02:45 PM</t>
+          <t>12:30 PM – 01:30 PM</t>
         </is>
       </c>
       <c r="E430" t="inlineStr">
@@ -24508,7 +24508,7 @@
       </c>
       <c r="B431" t="inlineStr">
         <is>
-          <t>Tuesday, September 2, 2026</t>
+          <t>Wednesday, September 2, 2026</t>
         </is>
       </c>
       <c r="C431" t="n">
@@ -24516,7 +24516,7 @@
       </c>
       <c r="D431" t="inlineStr">
         <is>
-          <t>01:45 PM – 02:45 PM</t>
+          <t>01:30 PM – 03:30 PM</t>
         </is>
       </c>
       <c r="E431" t="inlineStr">
@@ -24564,7 +24564,7 @@
       </c>
       <c r="B432" t="inlineStr">
         <is>
-          <t>Tuesday, September 2, 2026</t>
+          <t>Wednesday, September 2, 2026</t>
         </is>
       </c>
       <c r="C432" t="n">
@@ -24620,7 +24620,7 @@
       </c>
       <c r="B433" t="inlineStr">
         <is>
-          <t>Sunday, September 7, 2026</t>
+          <t>Monday, September 7, 2026</t>
         </is>
       </c>
       <c r="C433" t="n">
@@ -24676,7 +24676,7 @@
       </c>
       <c r="B434" t="inlineStr">
         <is>
-          <t>Sunday, September 7, 2026</t>
+          <t>Monday, September 7, 2026</t>
         </is>
       </c>
       <c r="C434" t="n">
@@ -24732,15 +24732,15 @@
       </c>
       <c r="B435" t="inlineStr">
         <is>
-          <t>Wednesday, September 3, 2026</t>
+          <t>Thursday, September 3, 2026</t>
         </is>
       </c>
       <c r="C435" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D435" t="inlineStr">
         <is>
-          <t>01:45 PM – 02:45 PM</t>
+          <t>02:45 PM – 03:30 PM</t>
         </is>
       </c>
       <c r="E435" t="inlineStr">
@@ -24788,7 +24788,7 @@
       </c>
       <c r="B436" t="inlineStr">
         <is>
-          <t>Saturday, September 6, 2026</t>
+          <t>Sunday, September 6, 2026</t>
         </is>
       </c>
       <c r="C436" t="n">
@@ -24840,19 +24840,19 @@
     </row>
     <row r="437">
       <c r="A437" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B437" t="inlineStr">
         <is>
-          <t>Wednesday, September 3, 2026</t>
+          <t>Sunday, September 6, 2026</t>
         </is>
       </c>
       <c r="C437" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D437" t="inlineStr">
         <is>
-          <t>02:45 PM – 03:30 PM</t>
+          <t>12:30 PM – 02:30 PM</t>
         </is>
       </c>
       <c r="E437" t="inlineStr">
@@ -24900,15 +24900,15 @@
       </c>
       <c r="B438" t="inlineStr">
         <is>
-          <t>Saturday, September 6, 2026</t>
+          <t>Sunday, September 6, 2026</t>
         </is>
       </c>
       <c r="C438" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D438" t="inlineStr">
         <is>
-          <t>12:30 PM – 01:30 PM</t>
+          <t>01:45 PM – 02:45 PM</t>
         </is>
       </c>
       <c r="E438" t="inlineStr">
@@ -24956,15 +24956,15 @@
       </c>
       <c r="B439" t="inlineStr">
         <is>
-          <t>Wednesday, September 3, 2026</t>
+          <t>Thursday, September 3, 2026</t>
         </is>
       </c>
       <c r="C439" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D439" t="inlineStr">
         <is>
-          <t>12:30 PM – 01:30 PM</t>
+          <t>01:45 PM – 02:45 PM</t>
         </is>
       </c>
       <c r="E439" t="inlineStr">
@@ -25012,7 +25012,7 @@
       </c>
       <c r="B440" t="inlineStr">
         <is>
-          <t>Tuesday, September 2, 2026</t>
+          <t>Wednesday, September 2, 2026</t>
         </is>
       </c>
       <c r="C440" t="n">
@@ -25068,7 +25068,7 @@
       </c>
       <c r="B441" t="inlineStr">
         <is>
-          <t>Tuesday, September 2, 2026</t>
+          <t>Wednesday, September 2, 2026</t>
         </is>
       </c>
       <c r="C441" t="n">
@@ -25120,19 +25120,19 @@
     </row>
     <row r="442">
       <c r="A442" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B442" t="inlineStr">
         <is>
-          <t>Tuesday, September 2, 2026</t>
+          <t>Thursday, September 3, 2026</t>
         </is>
       </c>
       <c r="C442" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D442" t="inlineStr">
         <is>
-          <t>01:45 PM – 02:45 PM</t>
+          <t>12:30 PM – 01:30 PM</t>
         </is>
       </c>
       <c r="E442" t="inlineStr">
@@ -25180,7 +25180,7 @@
       </c>
       <c r="B443" t="inlineStr">
         <is>
-          <t>Sunday, September 7, 2026</t>
+          <t>Monday, September 7, 2026</t>
         </is>
       </c>
       <c r="C443" t="n">
@@ -25236,7 +25236,7 @@
       </c>
       <c r="B444" t="inlineStr">
         <is>
-          <t>Saturday, September 6, 2026</t>
+          <t>Sunday, September 6, 2026</t>
         </is>
       </c>
       <c r="C444" t="n">
@@ -25244,7 +25244,7 @@
       </c>
       <c r="D444" t="inlineStr">
         <is>
-          <t>02:45 PM – 03:30 PM</t>
+          <t>12:30 PM – 02:30 PM</t>
         </is>
       </c>
       <c r="E444" t="inlineStr">
@@ -25292,7 +25292,7 @@
       </c>
       <c r="B445" t="inlineStr">
         <is>
-          <t>Saturday, September 6, 2026</t>
+          <t>Sunday, September 6, 2026</t>
         </is>
       </c>
       <c r="C445" t="n">
@@ -25348,7 +25348,7 @@
       </c>
       <c r="B446" t="inlineStr">
         <is>
-          <t>Saturday, September 6, 2026</t>
+          <t>Sunday, September 6, 2026</t>
         </is>
       </c>
       <c r="C446" t="n">
@@ -25404,7 +25404,7 @@
       </c>
       <c r="B447" t="inlineStr">
         <is>
-          <t>Wednesday, September 3, 2026</t>
+          <t>Thursday, September 3, 2026</t>
         </is>
       </c>
       <c r="C447" t="n">
@@ -25460,7 +25460,7 @@
       </c>
       <c r="B448" t="inlineStr">
         <is>
-          <t>Wednesday, September 3, 2026</t>
+          <t>Thursday, September 3, 2026</t>
         </is>
       </c>
       <c r="C448" t="n">
@@ -25516,7 +25516,7 @@
       </c>
       <c r="B449" t="inlineStr">
         <is>
-          <t>Wednesday, September 3, 2026</t>
+          <t>Thursday, September 3, 2026</t>
         </is>
       </c>
       <c r="C449" t="n">
@@ -25572,7 +25572,7 @@
       </c>
       <c r="B450" t="inlineStr">
         <is>
-          <t>Tuesday, September 2, 2026</t>
+          <t>Wednesday, September 2, 2026</t>
         </is>
       </c>
       <c r="C450" t="n">
@@ -25628,7 +25628,7 @@
       </c>
       <c r="B451" t="inlineStr">
         <is>
-          <t>Tuesday, September 2, 2026</t>
+          <t>Wednesday, September 2, 2026</t>
         </is>
       </c>
       <c r="C451" t="n">
@@ -25684,7 +25684,7 @@
       </c>
       <c r="B452" t="inlineStr">
         <is>
-          <t>Tuesday, September 2, 2026</t>
+          <t>Wednesday, September 2, 2026</t>
         </is>
       </c>
       <c r="C452" t="n">
@@ -25740,7 +25740,7 @@
       </c>
       <c r="B453" t="inlineStr">
         <is>
-          <t>Wednesday, September 3, 2026</t>
+          <t>Thursday, September 3, 2026</t>
         </is>
       </c>
       <c r="C453" t="n">
@@ -25796,15 +25796,15 @@
       </c>
       <c r="B454" t="inlineStr">
         <is>
-          <t>Wednesday, September 3, 2026</t>
+          <t>Thursday, September 3, 2026</t>
         </is>
       </c>
       <c r="C454" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D454" t="inlineStr">
         <is>
-          <t>01:45 PM – 02:45 PM</t>
+          <t>12:30 PM – 01:30 PM</t>
         </is>
       </c>
       <c r="E454" t="inlineStr">
@@ -25852,15 +25852,15 @@
       </c>
       <c r="B455" t="inlineStr">
         <is>
-          <t>Saturday, September 6, 2026</t>
+          <t>Sunday, September 6, 2026</t>
         </is>
       </c>
       <c r="C455" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D455" t="inlineStr">
         <is>
-          <t>01:45 PM – 02:45 PM</t>
+          <t>12:30 PM – 02:30 PM</t>
         </is>
       </c>
       <c r="E455" t="inlineStr">
@@ -25904,19 +25904,19 @@
     </row>
     <row r="456">
       <c r="A456" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B456" t="inlineStr">
         <is>
-          <t>Saturday, September 6, 2026</t>
+          <t>Monday, September 7, 2026</t>
         </is>
       </c>
       <c r="C456" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D456" t="inlineStr">
         <is>
-          <t>02:45 PM – 03:30 PM</t>
+          <t>12:30 PM – 01:30 PM</t>
         </is>
       </c>
       <c r="E456" t="inlineStr">
@@ -25964,15 +25964,15 @@
       </c>
       <c r="B457" t="inlineStr">
         <is>
-          <t>Saturday, September 6, 2026</t>
+          <t>Sunday, September 6, 2026</t>
         </is>
       </c>
       <c r="C457" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D457" t="inlineStr">
         <is>
-          <t>12:30 PM – 01:30 PM</t>
+          <t>01:45 PM – 02:45 PM</t>
         </is>
       </c>
       <c r="E457" t="inlineStr">
@@ -26020,15 +26020,15 @@
       </c>
       <c r="B458" t="inlineStr">
         <is>
-          <t>Wednesday, September 3, 2026</t>
+          <t>Thursday, September 3, 2026</t>
         </is>
       </c>
       <c r="C458" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D458" t="inlineStr">
         <is>
-          <t>12:30 PM – 01:30 PM</t>
+          <t>01:45 PM – 02:45 PM</t>
         </is>
       </c>
       <c r="E458" t="inlineStr">
@@ -26072,19 +26072,19 @@
     </row>
     <row r="459">
       <c r="A459" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="B459" t="inlineStr">
         <is>
-          <t>Tuesday, September 2, 2026</t>
+          <t>Monday, September 7, 2026</t>
         </is>
       </c>
       <c r="C459" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D459" t="inlineStr">
         <is>
-          <t>02:45 PM – 03:30 PM</t>
+          <t>01:45 PM – 02:45 PM</t>
         </is>
       </c>
       <c r="E459" t="inlineStr">
@@ -26132,7 +26132,7 @@
       </c>
       <c r="B460" t="inlineStr">
         <is>
-          <t>Tuesday, September 2, 2026</t>
+          <t>Wednesday, September 2, 2026</t>
         </is>
       </c>
       <c r="C460" t="n">
@@ -26188,15 +26188,15 @@
       </c>
       <c r="B461" t="inlineStr">
         <is>
-          <t>Tuesday, September 2, 2026</t>
+          <t>Wednesday, September 2, 2026</t>
         </is>
       </c>
       <c r="C461" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D461" t="inlineStr">
         <is>
-          <t>01:45 PM – 02:45 PM</t>
+          <t>02:45 PM – 03:30 PM</t>
         </is>
       </c>
       <c r="E461" t="inlineStr">
@@ -26244,7 +26244,7 @@
       </c>
       <c r="B462" t="inlineStr">
         <is>
-          <t>Tuesday, September 2, 2026</t>
+          <t>Wednesday, September 2, 2026</t>
         </is>
       </c>
       <c r="C462" t="n">
@@ -26300,15 +26300,15 @@
       </c>
       <c r="B463" t="inlineStr">
         <is>
-          <t>Saturday, September 6, 2026</t>
+          <t>Sunday, September 6, 2026</t>
         </is>
       </c>
       <c r="C463" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D463" t="inlineStr">
         <is>
-          <t>01:45 PM – 02:45 PM</t>
+          <t>02:45 PM – 03:30 PM</t>
         </is>
       </c>
       <c r="E463" t="inlineStr">
@@ -26352,11 +26352,11 @@
     </row>
     <row r="464">
       <c r="A464" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B464" t="inlineStr">
         <is>
-          <t>Tuesday, September 2, 2026</t>
+          <t>Thursday, September 3, 2026</t>
         </is>
       </c>
       <c r="C464" t="n">
@@ -26412,7 +26412,7 @@
       </c>
       <c r="B465" t="inlineStr">
         <is>
-          <t>Wednesday, September 3, 2026</t>
+          <t>Thursday, September 3, 2026</t>
         </is>
       </c>
       <c r="C465" t="n">
@@ -26468,15 +26468,15 @@
       </c>
       <c r="B466" t="inlineStr">
         <is>
-          <t>Saturday, September 6, 2026</t>
+          <t>Sunday, September 6, 2026</t>
         </is>
       </c>
       <c r="C466" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D466" t="inlineStr">
         <is>
-          <t>12:30 PM – 01:30 PM</t>
+          <t>01:45 PM – 02:45 PM</t>
         </is>
       </c>
       <c r="E466" t="inlineStr">
@@ -26524,7 +26524,7 @@
       </c>
       <c r="B467" t="inlineStr">
         <is>
-          <t>Wednesday, September 3, 2026</t>
+          <t>Thursday, September 3, 2026</t>
         </is>
       </c>
       <c r="C467" t="n">
@@ -26576,19 +26576,19 @@
     </row>
     <row r="468">
       <c r="A468" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="B468" t="inlineStr">
         <is>
-          <t>Tuesday, September 2, 2026</t>
+          <t>Sunday, September 6, 2026</t>
         </is>
       </c>
       <c r="C468" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D468" t="inlineStr">
         <is>
-          <t>02:45 PM – 03:30 PM</t>
+          <t>12:30 PM – 01:30 PM</t>
         </is>
       </c>
       <c r="E468" t="inlineStr">
@@ -26632,19 +26632,19 @@
     </row>
     <row r="469">
       <c r="A469" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="B469" t="inlineStr">
         <is>
-          <t>Sunday, September 7, 2026</t>
+          <t>Wednesday, September 2, 2026</t>
         </is>
       </c>
       <c r="C469" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D469" t="inlineStr">
         <is>
-          <t>01:45 PM – 02:45 PM</t>
+          <t>12:30 PM – 02:30 PM</t>
         </is>
       </c>
       <c r="E469" t="inlineStr">
@@ -26688,11 +26688,11 @@
     </row>
     <row r="470">
       <c r="A470" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B470" t="inlineStr">
         <is>
-          <t>Wednesday, September 3, 2026</t>
+          <t>Wednesday, September 2, 2026</t>
         </is>
       </c>
       <c r="C470" t="n">
@@ -26744,11 +26744,11 @@
     </row>
     <row r="471">
       <c r="A471" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B471" t="inlineStr">
         <is>
-          <t>Wednesday, September 3, 2026</t>
+          <t>Wednesday, September 2, 2026</t>
         </is>
       </c>
       <c r="C471" t="n">
@@ -26804,7 +26804,7 @@
       </c>
       <c r="B472" t="inlineStr">
         <is>
-          <t>Saturday, September 6, 2026</t>
+          <t>Sunday, September 6, 2026</t>
         </is>
       </c>
       <c r="C472" t="n">
@@ -26860,7 +26860,7 @@
       </c>
       <c r="B473" t="inlineStr">
         <is>
-          <t>Wednesday, September 3, 2026</t>
+          <t>Thursday, September 3, 2026</t>
         </is>
       </c>
       <c r="C473" t="n">
@@ -26916,7 +26916,7 @@
       </c>
       <c r="B474" t="inlineStr">
         <is>
-          <t>Wednesday, September 3, 2026</t>
+          <t>Thursday, September 3, 2026</t>
         </is>
       </c>
       <c r="C474" t="n">
@@ -26924,7 +26924,7 @@
       </c>
       <c r="D474" t="inlineStr">
         <is>
-          <t>01:45 PM – 02:45 PM</t>
+          <t>01:30 PM – 03:30 PM</t>
         </is>
       </c>
       <c r="E474" t="inlineStr">
@@ -26972,7 +26972,7 @@
       </c>
       <c r="B475" t="inlineStr">
         <is>
-          <t>Saturday, September 6, 2026</t>
+          <t>Sunday, September 6, 2026</t>
         </is>
       </c>
       <c r="C475" t="n">
@@ -27024,19 +27024,19 @@
     </row>
     <row r="476">
       <c r="A476" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B476" t="inlineStr">
         <is>
-          <t>Tuesday, September 2, 2026</t>
+          <t>Thursday, September 3, 2026</t>
         </is>
       </c>
       <c r="C476" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D476" t="inlineStr">
         <is>
-          <t>02:45 PM – 03:30 PM</t>
+          <t>12:30 PM – 01:30 PM</t>
         </is>
       </c>
       <c r="E476" t="inlineStr">
@@ -27084,15 +27084,15 @@
       </c>
       <c r="B477" t="inlineStr">
         <is>
-          <t>Tuesday, September 2, 2026</t>
+          <t>Wednesday, September 2, 2026</t>
         </is>
       </c>
       <c r="C477" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D477" t="inlineStr">
         <is>
-          <t>01:45 PM – 02:45 PM</t>
+          <t>02:45 PM – 03:30 PM</t>
         </is>
       </c>
       <c r="E477" t="inlineStr">
@@ -27140,15 +27140,15 @@
       </c>
       <c r="B478" t="inlineStr">
         <is>
-          <t>Tuesday, September 2, 2026</t>
+          <t>Wednesday, September 2, 2026</t>
         </is>
       </c>
       <c r="C478" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D478" t="inlineStr">
         <is>
-          <t>12:30 PM – 01:30 PM</t>
+          <t>01:45 PM – 02:45 PM</t>
         </is>
       </c>
       <c r="E478" t="inlineStr">
@@ -27196,7 +27196,7 @@
       </c>
       <c r="B479" t="inlineStr">
         <is>
-          <t>Saturday, September 6, 2026</t>
+          <t>Sunday, September 6, 2026</t>
         </is>
       </c>
       <c r="C479" t="n">
@@ -27252,7 +27252,7 @@
       </c>
       <c r="B480" t="inlineStr">
         <is>
-          <t>Wednesday, September 3, 2026</t>
+          <t>Thursday, September 3, 2026</t>
         </is>
       </c>
       <c r="C480" t="n">
@@ -27308,7 +27308,7 @@
       </c>
       <c r="B481" t="inlineStr">
         <is>
-          <t>Wednesday, September 3, 2026</t>
+          <t>Thursday, September 3, 2026</t>
         </is>
       </c>
       <c r="C481" t="n">
@@ -27364,7 +27364,7 @@
       </c>
       <c r="B482" t="inlineStr">
         <is>
-          <t>Wednesday, September 3, 2026</t>
+          <t>Thursday, September 3, 2026</t>
         </is>
       </c>
       <c r="C482" t="n">
@@ -27420,7 +27420,7 @@
       </c>
       <c r="B483" t="inlineStr">
         <is>
-          <t>Tuesday, September 2, 2026</t>
+          <t>Wednesday, September 2, 2026</t>
         </is>
       </c>
       <c r="C483" t="n">
@@ -27476,7 +27476,7 @@
       </c>
       <c r="B484" t="inlineStr">
         <is>
-          <t>Tuesday, September 2, 2026</t>
+          <t>Wednesday, September 2, 2026</t>
         </is>
       </c>
       <c r="C484" t="n">
@@ -27532,7 +27532,7 @@
       </c>
       <c r="B485" t="inlineStr">
         <is>
-          <t>Tuesday, September 2, 2026</t>
+          <t>Wednesday, September 2, 2026</t>
         </is>
       </c>
       <c r="C485" t="n">
@@ -27588,7 +27588,7 @@
       </c>
       <c r="B486" t="inlineStr">
         <is>
-          <t>Sunday, September 7, 2026</t>
+          <t>Monday, September 7, 2026</t>
         </is>
       </c>
       <c r="C486" t="n">
@@ -27640,19 +27640,19 @@
     </row>
     <row r="487">
       <c r="A487" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B487" t="inlineStr">
         <is>
-          <t>Saturday, September 6, 2026</t>
+          <t>Monday, September 7, 2026</t>
         </is>
       </c>
       <c r="C487" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D487" t="inlineStr">
         <is>
-          <t>04:45 PM – 05:45 PM</t>
+          <t>03:30 PM – 04:30 PM</t>
         </is>
       </c>
       <c r="E487" t="inlineStr">
@@ -27700,7 +27700,7 @@
       </c>
       <c r="B488" t="inlineStr">
         <is>
-          <t>Wednesday, September 3, 2026</t>
+          <t>Thursday, September 3, 2026</t>
         </is>
       </c>
       <c r="C488" t="n">
@@ -27752,19 +27752,19 @@
     </row>
     <row r="489">
       <c r="A489" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B489" t="inlineStr">
         <is>
-          <t>Sunday, September 7, 2026</t>
+          <t>Sunday, September 6, 2026</t>
         </is>
       </c>
       <c r="C489" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D489" t="inlineStr">
         <is>
-          <t>03:30 PM – 04:30 PM</t>
+          <t>04:45 PM – 05:45 PM</t>
         </is>
       </c>
       <c r="E489" t="inlineStr">
@@ -27812,7 +27812,7 @@
       </c>
       <c r="B490" t="inlineStr">
         <is>
-          <t>Saturday, September 6, 2026</t>
+          <t>Sunday, September 6, 2026</t>
         </is>
       </c>
       <c r="C490" t="n">
@@ -27864,11 +27864,11 @@
     </row>
     <row r="491">
       <c r="A491" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B491" t="inlineStr">
         <is>
-          <t>Tuesday, September 2, 2026</t>
+          <t>Thursday, September 3, 2026</t>
         </is>
       </c>
       <c r="C491" t="n">
@@ -27924,7 +27924,7 @@
       </c>
       <c r="B492" t="inlineStr">
         <is>
-          <t>Saturday, September 6, 2026</t>
+          <t>Sunday, September 6, 2026</t>
         </is>
       </c>
       <c r="C492" t="n">
@@ -27976,11 +27976,11 @@
     </row>
     <row r="493">
       <c r="A493" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B493" t="inlineStr">
         <is>
-          <t>Tuesday, September 2, 2026</t>
+          <t>Thursday, September 3, 2026</t>
         </is>
       </c>
       <c r="C493" t="n">
@@ -28032,11 +28032,11 @@
     </row>
     <row r="494">
       <c r="A494" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B494" t="inlineStr">
         <is>
-          <t>Wednesday, September 3, 2026</t>
+          <t>Wednesday, September 2, 2026</t>
         </is>
       </c>
       <c r="C494" t="n">
@@ -28044,7 +28044,7 @@
       </c>
       <c r="D494" t="inlineStr">
         <is>
-          <t>05:45 PM – 06:45 PM</t>
+          <t>03:30 PM – 05:30 PM</t>
         </is>
       </c>
       <c r="E494" t="inlineStr">
@@ -28092,15 +28092,15 @@
       </c>
       <c r="B495" t="inlineStr">
         <is>
-          <t>Tuesday, September 2, 2026</t>
+          <t>Wednesday, September 2, 2026</t>
         </is>
       </c>
       <c r="C495" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D495" t="inlineStr">
         <is>
-          <t>03:30 PM – 04:30 PM</t>
+          <t>04:45 PM – 05:45 PM</t>
         </is>
       </c>
       <c r="E495" t="inlineStr">
@@ -28148,7 +28148,7 @@
       </c>
       <c r="B496" t="inlineStr">
         <is>
-          <t>Sunday, September 7, 2026</t>
+          <t>Monday, September 7, 2026</t>
         </is>
       </c>
       <c r="C496" t="n">
@@ -28200,19 +28200,19 @@
     </row>
     <row r="497">
       <c r="A497" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B497" t="inlineStr">
         <is>
-          <t>Tuesday, September 2, 2026</t>
+          <t>Thursday, September 3, 2026</t>
         </is>
       </c>
       <c r="C497" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D497" t="inlineStr">
         <is>
-          <t>04:45 PM – 05:45 PM</t>
+          <t>03:30 PM – 04:30 PM</t>
         </is>
       </c>
       <c r="E497" t="inlineStr">
@@ -28260,15 +28260,15 @@
       </c>
       <c r="B498" t="inlineStr">
         <is>
-          <t>Saturday, September 6, 2026</t>
+          <t>Sunday, September 6, 2026</t>
         </is>
       </c>
       <c r="C498" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D498" t="inlineStr">
         <is>
-          <t>05:45 PM – 06:45 PM</t>
+          <t>04:45 PM – 05:45 PM</t>
         </is>
       </c>
       <c r="E498" t="inlineStr">
@@ -28316,15 +28316,15 @@
       </c>
       <c r="B499" t="inlineStr">
         <is>
-          <t>Saturday, September 6, 2026</t>
+          <t>Sunday, September 6, 2026</t>
         </is>
       </c>
       <c r="C499" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D499" t="inlineStr">
         <is>
-          <t>04:45 PM – 05:45 PM</t>
+          <t>03:30 PM – 04:30 PM</t>
         </is>
       </c>
       <c r="E499" t="inlineStr">
@@ -28372,7 +28372,7 @@
       </c>
       <c r="B500" t="inlineStr">
         <is>
-          <t>Wednesday, September 3, 2026</t>
+          <t>Thursday, September 3, 2026</t>
         </is>
       </c>
       <c r="C500" t="n">
@@ -28428,7 +28428,7 @@
       </c>
       <c r="B501" t="inlineStr">
         <is>
-          <t>Wednesday, September 3, 2026</t>
+          <t>Thursday, September 3, 2026</t>
         </is>
       </c>
       <c r="C501" t="n">
@@ -28480,19 +28480,19 @@
     </row>
     <row r="502">
       <c r="A502" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="B502" t="inlineStr">
         <is>
-          <t>Wednesday, September 3, 2026</t>
+          <t>Monday, September 7, 2026</t>
         </is>
       </c>
       <c r="C502" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D502" t="inlineStr">
         <is>
-          <t>03:30 PM – 04:30 PM</t>
+          <t>03:30 PM – 05:30 PM</t>
         </is>
       </c>
       <c r="E502" t="inlineStr">
@@ -28540,15 +28540,15 @@
       </c>
       <c r="B503" t="inlineStr">
         <is>
-          <t>Tuesday, September 2, 2026</t>
+          <t>Wednesday, September 2, 2026</t>
         </is>
       </c>
       <c r="C503" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D503" t="inlineStr">
         <is>
-          <t>05:45 PM – 06:45 PM</t>
+          <t>04:45 PM – 05:45 PM</t>
         </is>
       </c>
       <c r="E503" t="inlineStr">
@@ -28592,19 +28592,19 @@
     </row>
     <row r="504">
       <c r="A504" t="n">
+        <v>1</v>
+      </c>
+      <c r="B504" t="inlineStr">
+        <is>
+          <t>Wednesday, September 2, 2026</t>
+        </is>
+      </c>
+      <c r="C504" t="n">
         <v>3</v>
       </c>
-      <c r="B504" t="inlineStr">
-        <is>
-          <t>Saturday, September 6, 2026</t>
-        </is>
-      </c>
-      <c r="C504" t="n">
-        <v>1</v>
-      </c>
       <c r="D504" t="inlineStr">
         <is>
-          <t>03:30 PM – 04:30 PM</t>
+          <t>05:45 PM – 06:45 PM</t>
         </is>
       </c>
       <c r="E504" t="inlineStr">
@@ -28652,7 +28652,7 @@
       </c>
       <c r="B505" t="inlineStr">
         <is>
-          <t>Tuesday, September 2, 2026</t>
+          <t>Wednesday, September 2, 2026</t>
         </is>
       </c>
       <c r="C505" t="n">
@@ -28708,7 +28708,7 @@
       </c>
       <c r="B506" t="inlineStr">
         <is>
-          <t>Sunday, September 7, 2026</t>
+          <t>Monday, September 7, 2026</t>
         </is>
       </c>
       <c r="C506" t="n">
@@ -28760,19 +28760,19 @@
     </row>
     <row r="507">
       <c r="A507" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B507" t="inlineStr">
         <is>
-          <t>Tuesday, September 2, 2026</t>
+          <t>Thursday, September 3, 2026</t>
         </is>
       </c>
       <c r="C507" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D507" t="inlineStr">
         <is>
-          <t>03:30 PM – 04:30 PM</t>
+          <t>05:45 PM – 06:45 PM</t>
         </is>
       </c>
       <c r="E507" t="inlineStr">
@@ -28820,15 +28820,15 @@
       </c>
       <c r="B508" t="inlineStr">
         <is>
-          <t>Wednesday, September 3, 2026</t>
+          <t>Thursday, September 3, 2026</t>
         </is>
       </c>
       <c r="C508" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D508" t="inlineStr">
         <is>
-          <t>05:45 PM – 06:45 PM</t>
+          <t>04:45 PM – 05:45 PM</t>
         </is>
       </c>
       <c r="E508" t="inlineStr">
@@ -28876,7 +28876,7 @@
       </c>
       <c r="B509" t="inlineStr">
         <is>
-          <t>Saturday, September 6, 2026</t>
+          <t>Sunday, September 6, 2026</t>
         </is>
       </c>
       <c r="C509" t="n">
@@ -28928,11 +28928,11 @@
     </row>
     <row r="510">
       <c r="A510" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B510" t="inlineStr">
         <is>
-          <t>Wednesday, September 3, 2026</t>
+          <t>Sunday, September 6, 2026</t>
         </is>
       </c>
       <c r="C510" t="n">
@@ -28984,19 +28984,19 @@
     </row>
     <row r="511">
       <c r="A511" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B511" t="inlineStr">
         <is>
-          <t>Sunday, September 7, 2026</t>
+          <t>Sunday, September 6, 2026</t>
         </is>
       </c>
       <c r="C511" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D511" t="inlineStr">
         <is>
-          <t>05:45 PM – 06:45 PM</t>
+          <t>03:30 PM – 04:30 PM</t>
         </is>
       </c>
       <c r="E511" t="inlineStr">
@@ -29040,11 +29040,11 @@
     </row>
     <row r="512">
       <c r="A512" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B512" t="inlineStr">
         <is>
-          <t>Saturday, September 6, 2026</t>
+          <t>Thursday, September 3, 2026</t>
         </is>
       </c>
       <c r="C512" t="n">
@@ -29052,7 +29052,7 @@
       </c>
       <c r="D512" t="inlineStr">
         <is>
-          <t>03:30 PM – 04:30 PM</t>
+          <t>03:30 PM – 05:30 PM</t>
         </is>
       </c>
       <c r="E512" t="inlineStr">
@@ -29100,15 +29100,15 @@
       </c>
       <c r="B513" t="inlineStr">
         <is>
-          <t>Tuesday, September 2, 2026</t>
+          <t>Wednesday, September 2, 2026</t>
         </is>
       </c>
       <c r="C513" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D513" t="inlineStr">
         <is>
-          <t>04:45 PM – 05:45 PM</t>
+          <t>05:45 PM – 06:45 PM</t>
         </is>
       </c>
       <c r="E513" t="inlineStr">
@@ -29152,19 +29152,19 @@
     </row>
     <row r="514">
       <c r="A514" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B514" t="inlineStr">
         <is>
-          <t>Wednesday, September 3, 2026</t>
+          <t>Wednesday, September 2, 2026</t>
         </is>
       </c>
       <c r="C514" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D514" t="inlineStr">
         <is>
-          <t>03:30 PM – 04:30 PM</t>
+          <t>04:45 PM – 05:45 PM</t>
         </is>
       </c>
       <c r="E514" t="inlineStr">
@@ -29212,15 +29212,15 @@
       </c>
       <c r="B515" t="inlineStr">
         <is>
-          <t>Tuesday, September 2, 2026</t>
+          <t>Wednesday, September 2, 2026</t>
         </is>
       </c>
       <c r="C515" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D515" t="inlineStr">
         <is>
-          <t>05:45 PM – 06:45 PM</t>
+          <t>03:30 PM – 04:30 PM</t>
         </is>
       </c>
       <c r="E515" t="inlineStr">
@@ -29268,7 +29268,7 @@
       </c>
       <c r="B516" t="inlineStr">
         <is>
-          <t>Wednesday, September 3, 2026</t>
+          <t>Thursday, September 3, 2026</t>
         </is>
       </c>
       <c r="C516" t="n">
@@ -29324,7 +29324,7 @@
       </c>
       <c r="B517" t="inlineStr">
         <is>
-          <t>Saturday, September 6, 2026</t>
+          <t>Sunday, September 6, 2026</t>
         </is>
       </c>
       <c r="C517" t="n">
@@ -29380,15 +29380,15 @@
       </c>
       <c r="B518" t="inlineStr">
         <is>
-          <t>Tuesday, September 2, 2026</t>
+          <t>Wednesday, September 2, 2026</t>
         </is>
       </c>
       <c r="C518" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D518" t="inlineStr">
         <is>
-          <t>05:45 PM – 06:45 PM</t>
+          <t>04:45 PM – 05:45 PM</t>
         </is>
       </c>
       <c r="E518" t="inlineStr">
@@ -29436,7 +29436,7 @@
       </c>
       <c r="B519" t="inlineStr">
         <is>
-          <t>Wednesday, September 3, 2026</t>
+          <t>Thursday, September 3, 2026</t>
         </is>
       </c>
       <c r="C519" t="n">
@@ -29488,19 +29488,19 @@
     </row>
     <row r="520">
       <c r="A520" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B520" t="inlineStr">
         <is>
-          <t>Saturday, September 6, 2026</t>
+          <t>Monday, September 7, 2026</t>
         </is>
       </c>
       <c r="C520" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D520" t="inlineStr">
         <is>
-          <t>03:30 PM – 04:30 PM</t>
+          <t>04:45 PM – 05:45 PM</t>
         </is>
       </c>
       <c r="E520" t="inlineStr">
@@ -29548,7 +29548,7 @@
       </c>
       <c r="B521" t="inlineStr">
         <is>
-          <t>Wednesday, September 3, 2026</t>
+          <t>Thursday, September 3, 2026</t>
         </is>
       </c>
       <c r="C521" t="n">
@@ -29556,7 +29556,7 @@
       </c>
       <c r="D521" t="inlineStr">
         <is>
-          <t>03:30 PM – 04:30 PM</t>
+          <t>03:30 PM – 05:30 PM</t>
         </is>
       </c>
       <c r="E521" t="inlineStr">
@@ -29600,19 +29600,19 @@
     </row>
     <row r="522">
       <c r="A522" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B522" t="inlineStr">
         <is>
-          <t>Sunday, September 7, 2026</t>
+          <t>Sunday, September 6, 2026</t>
         </is>
       </c>
       <c r="C522" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D522" t="inlineStr">
         <is>
-          <t>05:45 PM – 06:45 PM</t>
+          <t>03:30 PM – 04:30 PM</t>
         </is>
       </c>
       <c r="E522" t="inlineStr">
@@ -29660,15 +29660,15 @@
       </c>
       <c r="B523" t="inlineStr">
         <is>
-          <t>Tuesday, September 2, 2026</t>
+          <t>Wednesday, September 2, 2026</t>
         </is>
       </c>
       <c r="C523" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D523" t="inlineStr">
         <is>
-          <t>04:45 PM – 05:45 PM</t>
+          <t>05:45 PM – 06:45 PM</t>
         </is>
       </c>
       <c r="E523" t="inlineStr">
@@ -29716,7 +29716,7 @@
       </c>
       <c r="B524" t="inlineStr">
         <is>
-          <t>Tuesday, September 2, 2026</t>
+          <t>Wednesday, September 2, 2026</t>
         </is>
       </c>
       <c r="C524" t="n">
@@ -29768,11 +29768,11 @@
     </row>
     <row r="525">
       <c r="A525" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B525" t="inlineStr">
         <is>
-          <t>Wednesday, September 3, 2026</t>
+          <t>Wednesday, September 2, 2026</t>
         </is>
       </c>
       <c r="C525" t="n">
@@ -29828,15 +29828,15 @@
       </c>
       <c r="B526" t="inlineStr">
         <is>
-          <t>Saturday, September 6, 2026</t>
+          <t>Sunday, September 6, 2026</t>
         </is>
       </c>
       <c r="C526" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D526" t="inlineStr">
         <is>
-          <t>04:45 PM – 05:45 PM</t>
+          <t>03:30 PM – 04:30 PM</t>
         </is>
       </c>
       <c r="E526" t="inlineStr">
@@ -29884,15 +29884,15 @@
       </c>
       <c r="B527" t="inlineStr">
         <is>
-          <t>Tuesday, September 2, 2026</t>
+          <t>Wednesday, September 2, 2026</t>
         </is>
       </c>
       <c r="C527" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D527" t="inlineStr">
         <is>
-          <t>05:45 PM – 06:45 PM</t>
+          <t>03:30 PM – 04:30 PM</t>
         </is>
       </c>
       <c r="E527" t="inlineStr">
@@ -29940,7 +29940,7 @@
       </c>
       <c r="B528" t="inlineStr">
         <is>
-          <t>Wednesday, September 3, 2026</t>
+          <t>Thursday, September 3, 2026</t>
         </is>
       </c>
       <c r="C528" t="n">
@@ -29992,19 +29992,19 @@
     </row>
     <row r="529">
       <c r="A529" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="B529" t="inlineStr">
         <is>
-          <t>Tuesday, September 2, 2026</t>
+          <t>Monday, September 7, 2026</t>
         </is>
       </c>
       <c r="C529" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D529" t="inlineStr">
         <is>
-          <t>03:30 PM – 04:30 PM</t>
+          <t>04:45 PM – 05:45 PM</t>
         </is>
       </c>
       <c r="E529" t="inlineStr">
@@ -30052,15 +30052,15 @@
       </c>
       <c r="B530" t="inlineStr">
         <is>
-          <t>Wednesday, September 3, 2026</t>
+          <t>Thursday, September 3, 2026</t>
         </is>
       </c>
       <c r="C530" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D530" t="inlineStr">
         <is>
-          <t>03:30 PM – 04:30 PM</t>
+          <t>04:45 PM – 05:45 PM</t>
         </is>
       </c>
       <c r="E530" t="inlineStr">
@@ -30104,19 +30104,19 @@
     </row>
     <row r="531">
       <c r="A531" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="B531" t="inlineStr">
         <is>
-          <t>Tuesday, September 2, 2026</t>
+          <t>Monday, September 7, 2026</t>
         </is>
       </c>
       <c r="C531" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D531" t="inlineStr">
         <is>
-          <t>04:45 PM – 05:45 PM</t>
+          <t>05:45 PM – 06:45 PM</t>
         </is>
       </c>
       <c r="E531" t="inlineStr">
@@ -30160,19 +30160,19 @@
     </row>
     <row r="532">
       <c r="A532" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="B532" t="inlineStr">
         <is>
-          <t>Sunday, September 7, 2026</t>
+          <t>Wednesday, September 2, 2026</t>
         </is>
       </c>
       <c r="C532" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D532" t="inlineStr">
         <is>
-          <t>04:45 PM – 05:45 PM</t>
+          <t>03:30 PM – 05:30 PM</t>
         </is>
       </c>
       <c r="E532" t="inlineStr">
@@ -30216,19 +30216,19 @@
     </row>
     <row r="533">
       <c r="A533" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B533" t="inlineStr">
         <is>
-          <t>Sunday, September 7, 2026</t>
+          <t>Sunday, September 6, 2026</t>
         </is>
       </c>
       <c r="C533" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D533" t="inlineStr">
         <is>
-          <t>05:45 PM – 06:45 PM</t>
+          <t>04:45 PM – 05:45 PM</t>
         </is>
       </c>
       <c r="E533" t="inlineStr">
@@ -30276,7 +30276,7 @@
       </c>
       <c r="B534" t="inlineStr">
         <is>
-          <t>Saturday, September 6, 2026</t>
+          <t>Sunday, September 6, 2026</t>
         </is>
       </c>
       <c r="C534" t="n">
@@ -30284,7 +30284,7 @@
       </c>
       <c r="D534" t="inlineStr">
         <is>
-          <t>05:45 PM – 06:45 PM</t>
+          <t>03:30 PM – 05:30 PM</t>
         </is>
       </c>
       <c r="E534" t="inlineStr">
@@ -30328,19 +30328,19 @@
     </row>
     <row r="535">
       <c r="A535" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B535" t="inlineStr">
         <is>
-          <t>Wednesday, September 3, 2026</t>
+          <t>Wednesday, September 2, 2026</t>
         </is>
       </c>
       <c r="C535" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D535" t="inlineStr">
         <is>
-          <t>03:30 PM – 04:30 PM</t>
+          <t>04:45 PM – 05:45 PM</t>
         </is>
       </c>
       <c r="E535" t="inlineStr">
@@ -30384,19 +30384,19 @@
     </row>
     <row r="536">
       <c r="A536" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B536" t="inlineStr">
         <is>
-          <t>Tuesday, September 2, 2026</t>
+          <t>Thursday, September 3, 2026</t>
         </is>
       </c>
       <c r="C536" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D536" t="inlineStr">
         <is>
-          <t>03:30 PM – 04:30 PM</t>
+          <t>05:45 PM – 06:45 PM</t>
         </is>
       </c>
       <c r="E536" t="inlineStr">
@@ -30440,19 +30440,19 @@
     </row>
     <row r="537">
       <c r="A537" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B537" t="inlineStr">
         <is>
-          <t>Wednesday, September 3, 2026</t>
+          <t>Wednesday, September 2, 2026</t>
         </is>
       </c>
       <c r="C537" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D537" t="inlineStr">
         <is>
-          <t>05:45 PM – 06:45 PM</t>
+          <t>03:30 PM – 04:30 PM</t>
         </is>
       </c>
       <c r="E537" t="inlineStr">
@@ -30500,7 +30500,7 @@
       </c>
       <c r="B538" t="inlineStr">
         <is>
-          <t>Wednesday, September 3, 2026</t>
+          <t>Thursday, September 3, 2026</t>
         </is>
       </c>
       <c r="C538" t="n">
@@ -30552,11 +30552,11 @@
     </row>
     <row r="539">
       <c r="A539" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="B539" t="inlineStr">
         <is>
-          <t>Sunday, September 7, 2026</t>
+          <t>Thursday, September 3, 2026</t>
         </is>
       </c>
       <c r="C539" t="n">
@@ -30612,7 +30612,7 @@
       </c>
       <c r="B540" t="inlineStr">
         <is>
-          <t>Tuesday, September 2, 2026</t>
+          <t>Wednesday, September 2, 2026</t>
         </is>
       </c>
       <c r="C540" t="n">
@@ -30664,19 +30664,19 @@
     </row>
     <row r="541">
       <c r="A541" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="B541" t="inlineStr">
         <is>
-          <t>Tuesday, September 2, 2026</t>
+          <t>Monday, September 7, 2026</t>
         </is>
       </c>
       <c r="C541" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D541" t="inlineStr">
         <is>
-          <t>04:45 PM – 05:45 PM</t>
+          <t>05:45 PM – 06:45 PM</t>
         </is>
       </c>
       <c r="E541" t="inlineStr">
@@ -30724,15 +30724,15 @@
       </c>
       <c r="B542" t="inlineStr">
         <is>
-          <t>Sunday, September 7, 2026</t>
+          <t>Monday, September 7, 2026</t>
         </is>
       </c>
       <c r="C542" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D542" t="inlineStr">
         <is>
-          <t>05:45 PM – 06:45 PM</t>
+          <t>04:45 PM – 05:45 PM</t>
         </is>
       </c>
       <c r="E542" t="inlineStr">
@@ -30776,11 +30776,11 @@
     </row>
     <row r="543">
       <c r="A543" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B543" t="inlineStr">
         <is>
-          <t>Wednesday, September 3, 2026</t>
+          <t>Wednesday, September 2, 2026</t>
         </is>
       </c>
       <c r="C543" t="n">
@@ -30836,7 +30836,7 @@
       </c>
       <c r="B544" t="inlineStr">
         <is>
-          <t>Wednesday, September 3, 2026</t>
+          <t>Thursday, September 3, 2026</t>
         </is>
       </c>
       <c r="C544" t="n">
@@ -30888,19 +30888,19 @@
     </row>
     <row r="545">
       <c r="A545" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="B545" t="inlineStr">
         <is>
-          <t>Sunday, September 7, 2026</t>
+          <t>Thursday, September 3, 2026</t>
         </is>
       </c>
       <c r="C545" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D545" t="inlineStr">
         <is>
-          <t>04:45 PM – 05:45 PM</t>
+          <t>05:45 PM – 06:45 PM</t>
         </is>
       </c>
       <c r="E545" t="inlineStr">
@@ -30944,11 +30944,11 @@
     </row>
     <row r="546">
       <c r="A546" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="B546" t="inlineStr">
         <is>
-          <t>Saturday, September 6, 2026</t>
+          <t>Wednesday, September 2, 2026</t>
         </is>
       </c>
       <c r="C546" t="n">
@@ -31000,19 +31000,19 @@
     </row>
     <row r="547">
       <c r="A547" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="B547" t="inlineStr">
         <is>
-          <t>Wednesday, September 3, 2026</t>
+          <t>Monday, September 7, 2026</t>
         </is>
       </c>
       <c r="C547" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D547" t="inlineStr">
         <is>
-          <t>05:45 PM – 06:45 PM</t>
+          <t>04:45 PM – 05:45 PM</t>
         </is>
       </c>
       <c r="E547" t="inlineStr">
@@ -31056,11 +31056,11 @@
     </row>
     <row r="548">
       <c r="A548" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="B548" t="inlineStr">
         <is>
-          <t>Tuesday, September 2, 2026</t>
+          <t>Monday, September 7, 2026</t>
         </is>
       </c>
       <c r="C548" t="n">
@@ -31116,7 +31116,7 @@
       </c>
       <c r="B549" t="inlineStr">
         <is>
-          <t>Tuesday, September 2, 2026</t>
+          <t>Wednesday, September 2, 2026</t>
         </is>
       </c>
       <c r="C549" t="n">
@@ -31124,7 +31124,7 @@
       </c>
       <c r="D549" t="inlineStr">
         <is>
-          <t>04:45 PM – 05:45 PM</t>
+          <t>04:45 PM – 06:45 PM</t>
         </is>
       </c>
       <c r="E549" t="inlineStr">
@@ -31168,11 +31168,11 @@
     </row>
     <row r="550">
       <c r="A550" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B550" t="inlineStr">
         <is>
-          <t>Tuesday, September 2, 2026</t>
+          <t>Thursday, September 3, 2026</t>
         </is>
       </c>
       <c r="C550" t="n">

--- a/Term_Examination_Schedule_S.Y._2026-2027_Optimized.xlsx
+++ b/Term_Examination_Schedule_S.Y._2026-2027_Optimized.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L550"/>
+  <dimension ref="A1:L548"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -480,11 +480,11 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Wednesday, September 2, 2026</t>
+          <t>Sunday, September 6, 2026</t>
         </is>
       </c>
       <c r="C2" t="n">
@@ -704,11 +704,11 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Wednesday, September 2, 2026</t>
+          <t>Sunday, September 6, 2026</t>
         </is>
       </c>
       <c r="C6" t="n">
@@ -936,11 +936,11 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>09:00 AM – 10:00 AM</t>
+          <t>08:00 AM – 09:00 AM</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -984,19 +984,19 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Sunday, September 6, 2026</t>
+          <t>Thursday, September 3, 2026</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>08:00 AM – 09:00 AM</t>
+          <t>09:00 AM – 10:00 AM</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -1096,19 +1096,19 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Thursday, September 3, 2026</t>
+          <t>Monday, September 7, 2026</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>09:00 AM – 10:00 AM</t>
+          <t>08:00 AM – 09:00 AM</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -1824,19 +1824,19 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Sunday, September 6, 2026</t>
+          <t>Monday, September 7, 2026</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>10:25 AM – 11:25 AM</t>
+          <t>09:00 AM – 10:00 AM</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -1992,11 +1992,11 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Thursday, September 3, 2026</t>
+          <t>Sunday, September 6, 2026</t>
         </is>
       </c>
       <c r="C29" t="n">
@@ -2034,12 +2034,12 @@
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>unassigned</t>
+          <t>tchr_normylah</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>Filipino - Tchr. Normayla</t>
+          <t>Teacher Normylah</t>
         </is>
       </c>
       <c r="L29" t="n">
@@ -3042,12 +3042,12 @@
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>unassigned</t>
+          <t>tchr_obaydah</t>
         </is>
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>Qur'an - Ust. Ubaydah</t>
+          <t>Ustadh Obaydah</t>
         </is>
       </c>
       <c r="L47" t="n">
@@ -3168,11 +3168,11 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Monday, September 7, 2026</t>
+          <t>Sunday, September 6, 2026</t>
         </is>
       </c>
       <c r="C50" t="n">
@@ -3994,12 +3994,12 @@
       </c>
       <c r="J64" t="inlineStr">
         <is>
-          <t>unassigned</t>
+          <t>tchr_wendy</t>
         </is>
       </c>
       <c r="K64" t="inlineStr">
         <is>
-          <t>Science - Tchr. Wendelyn</t>
+          <t>Teacher Wendy</t>
         </is>
       </c>
       <c r="L64" t="n">
@@ -4016,11 +4016,11 @@
         </is>
       </c>
       <c r="C65" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>01:30 PM – 02:15 PM</t>
+          <t>02:20 PM – 03:05 PM</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
@@ -4128,11 +4128,11 @@
         </is>
       </c>
       <c r="C67" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>02:20 PM – 03:05 PM</t>
+          <t>01:30 PM – 02:15 PM</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
@@ -4296,11 +4296,11 @@
         </is>
       </c>
       <c r="C70" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>12:40 PM – 01:40 PM</t>
+          <t>01:50 PM – 02:50 PM</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
@@ -4464,11 +4464,11 @@
         </is>
       </c>
       <c r="C73" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>12:40 PM – 01:40 PM</t>
+          <t>03:10 PM – 04:10 PM</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
@@ -4520,11 +4520,11 @@
         </is>
       </c>
       <c r="C74" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>03:10 PM – 04:10 PM</t>
+          <t>12:40 PM – 01:40 PM</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
@@ -4568,11 +4568,11 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Thursday, September 3, 2026</t>
+          <t>Wednesday, September 2, 2026</t>
         </is>
       </c>
       <c r="C75" t="n">
@@ -4624,11 +4624,11 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Wednesday, September 2, 2026</t>
+          <t>Thursday, September 3, 2026</t>
         </is>
       </c>
       <c r="C76" t="n">
@@ -4736,19 +4736,19 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Sunday, September 6, 2026</t>
+          <t>Monday, September 7, 2026</t>
         </is>
       </c>
       <c r="C78" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>03:10 PM – 04:10 PM</t>
+          <t>01:50 PM – 02:50 PM</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
@@ -4792,11 +4792,11 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Sunday, September 6, 2026</t>
+          <t>Thursday, September 3, 2026</t>
         </is>
       </c>
       <c r="C79" t="n">
@@ -4848,19 +4848,19 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Wednesday, September 2, 2026</t>
+          <t>Sunday, September 6, 2026</t>
         </is>
       </c>
       <c r="C80" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>03:10 PM – 04:10 PM</t>
+          <t>12:40 PM – 01:40 PM</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
@@ -4904,11 +4904,11 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Thursday, September 3, 2026</t>
+          <t>Monday, September 7, 2026</t>
         </is>
       </c>
       <c r="C81" t="n">
@@ -5016,19 +5016,19 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Thursday, September 3, 2026</t>
+          <t>Wednesday, September 2, 2026</t>
         </is>
       </c>
       <c r="C83" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>01:50 PM – 02:50 PM</t>
+          <t>03:10 PM – 04:10 PM</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
@@ -5240,19 +5240,19 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
+        <v>1</v>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>Wednesday, September 2, 2026</t>
+        </is>
+      </c>
+      <c r="C87" t="n">
         <v>3</v>
       </c>
-      <c r="B87" t="inlineStr">
-        <is>
-          <t>Sunday, September 6, 2026</t>
-        </is>
-      </c>
-      <c r="C87" t="n">
-        <v>2</v>
-      </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>01:50 PM – 02:50 PM</t>
+          <t>03:10 PM – 04:10 PM</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
@@ -5304,11 +5304,11 @@
         </is>
       </c>
       <c r="C88" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>03:10 PM – 04:10 PM</t>
+          <t>01:50 PM – 02:50 PM</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
@@ -5360,11 +5360,11 @@
         </is>
       </c>
       <c r="C89" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>03:10 PM – 04:10 PM</t>
+          <t>01:50 PM – 02:50 PM</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
@@ -5408,11 +5408,11 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Thursday, September 3, 2026</t>
+          <t>Sunday, September 6, 2026</t>
         </is>
       </c>
       <c r="C90" t="n">
@@ -5472,11 +5472,11 @@
         </is>
       </c>
       <c r="C91" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>01:50 PM – 02:50 PM</t>
+          <t>03:10 PM – 04:10 PM</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
@@ -5576,11 +5576,11 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Wednesday, September 2, 2026</t>
+          <t>Thursday, September 3, 2026</t>
         </is>
       </c>
       <c r="C93" t="n">
@@ -5674,12 +5674,12 @@
       </c>
       <c r="J94" t="inlineStr">
         <is>
-          <t>unassigned</t>
+          <t>tchr_normylah</t>
         </is>
       </c>
       <c r="K94" t="inlineStr">
         <is>
-          <t>Filipino - Tchr. Normayla</t>
+          <t>Teacher Normylah</t>
         </is>
       </c>
       <c r="L94" t="n">
@@ -5688,11 +5688,11 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Thursday, September 3, 2026</t>
+          <t>Wednesday, September 2, 2026</t>
         </is>
       </c>
       <c r="C95" t="n">
@@ -5744,11 +5744,11 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Monday, September 7, 2026</t>
+          <t>Sunday, September 6, 2026</t>
         </is>
       </c>
       <c r="C96" t="n">
@@ -5800,19 +5800,19 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>Monday, September 7, 2026</t>
+          <t>Sunday, September 6, 2026</t>
         </is>
       </c>
       <c r="C97" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>12:40 PM – 01:40 PM</t>
+          <t>01:50 PM – 02:50 PM</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
@@ -5856,11 +5856,11 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>Sunday, September 6, 2026</t>
+          <t>Thursday, September 3, 2026</t>
         </is>
       </c>
       <c r="C98" t="n">
@@ -5920,11 +5920,11 @@
         </is>
       </c>
       <c r="C99" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>03:10 PM – 04:10 PM</t>
+          <t>01:50 PM – 02:50 PM</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
@@ -6024,19 +6024,19 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>Sunday, September 6, 2026</t>
+          <t>Monday, September 7, 2026</t>
         </is>
       </c>
       <c r="C101" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>01:50 PM – 02:50 PM</t>
+          <t>12:40 PM – 01:40 PM</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
@@ -6080,11 +6080,11 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>Thursday, September 3, 2026</t>
+          <t>Monday, September 7, 2026</t>
         </is>
       </c>
       <c r="C102" t="n">
@@ -6136,11 +6136,11 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>Wednesday, September 2, 2026</t>
+          <t>Thursday, September 3, 2026</t>
         </is>
       </c>
       <c r="C103" t="n">
@@ -6248,19 +6248,19 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>Monday, September 7, 2026</t>
+          <t>Sunday, September 6, 2026</t>
         </is>
       </c>
       <c r="C105" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>01:50 PM – 02:50 PM</t>
+          <t>03:10 PM – 04:10 PM</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
@@ -6304,11 +6304,11 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>Monday, September 7, 2026</t>
+          <t>Wednesday, September 2, 2026</t>
         </is>
       </c>
       <c r="C106" t="n">
@@ -6368,11 +6368,11 @@
         </is>
       </c>
       <c r="C107" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>03:10 PM – 04:10 PM</t>
+          <t>01:50 PM – 02:50 PM</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
@@ -6416,11 +6416,11 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>Thursday, September 3, 2026</t>
+          <t>Wednesday, September 2, 2026</t>
         </is>
       </c>
       <c r="C108" t="n">
@@ -6584,19 +6584,19 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
+        <v>4</v>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>Monday, September 7, 2026</t>
+        </is>
+      </c>
+      <c r="C111" t="n">
         <v>3</v>
       </c>
-      <c r="B111" t="inlineStr">
-        <is>
-          <t>Sunday, September 6, 2026</t>
-        </is>
-      </c>
-      <c r="C111" t="n">
-        <v>2</v>
-      </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>01:50 PM – 02:50 PM</t>
+          <t>03:10 PM – 04:10 PM</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
@@ -6696,11 +6696,11 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>Wednesday, September 2, 2026</t>
+          <t>Monday, September 7, 2026</t>
         </is>
       </c>
       <c r="C113" t="n">
@@ -6752,19 +6752,19 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>Wednesday, September 2, 2026</t>
+          <t>Thursday, September 3, 2026</t>
         </is>
       </c>
       <c r="C114" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>12:40 PM – 01:40 PM</t>
+          <t>01:50 PM – 02:50 PM</t>
         </is>
       </c>
       <c r="E114" t="inlineStr">
@@ -6928,11 +6928,11 @@
         </is>
       </c>
       <c r="C117" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>03:10 PM – 04:10 PM</t>
+          <t>01:50 PM – 02:50 PM</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
@@ -7152,11 +7152,11 @@
         </is>
       </c>
       <c r="C121" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>03:10 PM – 04:10 PM</t>
+          <t>12:40 PM – 01:40 PM</t>
         </is>
       </c>
       <c r="E121" t="inlineStr">
@@ -7264,11 +7264,11 @@
         </is>
       </c>
       <c r="C123" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>01:50 PM – 02:50 PM</t>
+          <t>03:10 PM – 04:10 PM</t>
         </is>
       </c>
       <c r="E123" t="inlineStr">
@@ -7320,11 +7320,11 @@
         </is>
       </c>
       <c r="C124" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>12:40 PM – 01:40 PM</t>
+          <t>01:50 PM – 02:50 PM</t>
         </is>
       </c>
       <c r="E124" t="inlineStr">
@@ -7368,19 +7368,19 @@
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>Sunday, September 6, 2026</t>
+          <t>Monday, September 7, 2026</t>
         </is>
       </c>
       <c r="C125" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>03:10 PM – 04:10 PM</t>
+          <t>01:50 PM – 02:50 PM</t>
         </is>
       </c>
       <c r="E125" t="inlineStr">
@@ -7522,12 +7522,12 @@
       </c>
       <c r="J127" t="inlineStr">
         <is>
-          <t>unassigned</t>
+          <t>tchr_katrina</t>
         </is>
       </c>
       <c r="K127" t="inlineStr">
         <is>
-          <t>Math - Tchr. Kat</t>
+          <t>Teacher Katrina</t>
         </is>
       </c>
       <c r="L127" t="n">
@@ -7544,11 +7544,11 @@
         </is>
       </c>
       <c r="C128" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>12:40 PM – 01:40 PM</t>
+          <t>03:10 PM – 04:10 PM</t>
         </is>
       </c>
       <c r="E128" t="inlineStr">
@@ -7704,19 +7704,19 @@
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>Thursday, September 3, 2026</t>
+          <t>Wednesday, September 2, 2026</t>
         </is>
       </c>
       <c r="C131" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>01:50 PM – 02:50 PM</t>
+          <t>03:10 PM – 04:10 PM</t>
         </is>
       </c>
       <c r="E131" t="inlineStr">
@@ -7760,19 +7760,19 @@
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>Wednesday, September 2, 2026</t>
+          <t>Thursday, September 3, 2026</t>
         </is>
       </c>
       <c r="C132" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>03:10 PM – 04:10 PM</t>
+          <t>01:50 PM – 02:50 PM</t>
         </is>
       </c>
       <c r="E132" t="inlineStr">
@@ -7928,19 +7928,19 @@
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>Wednesday, September 2, 2026</t>
+          <t>Thursday, September 3, 2026</t>
         </is>
       </c>
       <c r="C135" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>03:10 PM – 03:40 PM</t>
+          <t>02:20 PM – 03:05 PM</t>
         </is>
       </c>
       <c r="E135" t="inlineStr">
@@ -7992,11 +7992,11 @@
         </is>
       </c>
       <c r="C136" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>02:20 PM – 03:05 PM</t>
+          <t>03:10 PM – 03:40 PM</t>
         </is>
       </c>
       <c r="E136" t="inlineStr">
@@ -8600,11 +8600,11 @@
     </row>
     <row r="147">
       <c r="A147" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>Thursday, September 3, 2026</t>
+          <t>Wednesday, September 2, 2026</t>
         </is>
       </c>
       <c r="C147" t="n">
@@ -8664,11 +8664,11 @@
         </is>
       </c>
       <c r="C148" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>03:10 PM – 04:10 PM</t>
+          <t>12:40 PM – 01:40 PM</t>
         </is>
       </c>
       <c r="E148" t="inlineStr">
@@ -8712,11 +8712,11 @@
     </row>
     <row r="149">
       <c r="A149" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>Thursday, September 3, 2026</t>
+          <t>Wednesday, September 2, 2026</t>
         </is>
       </c>
       <c r="C149" t="n">
@@ -8776,11 +8776,11 @@
         </is>
       </c>
       <c r="C150" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>12:40 PM – 01:40 PM</t>
+          <t>01:50 PM – 02:50 PM</t>
         </is>
       </c>
       <c r="E150" t="inlineStr">
@@ -8824,11 +8824,11 @@
     </row>
     <row r="151">
       <c r="A151" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>Thursday, September 3, 2026</t>
+          <t>Monday, September 7, 2026</t>
         </is>
       </c>
       <c r="C151" t="n">
@@ -8880,19 +8880,19 @@
     </row>
     <row r="152">
       <c r="A152" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>Wednesday, September 2, 2026</t>
+          <t>Thursday, September 3, 2026</t>
         </is>
       </c>
       <c r="C152" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>03:10 PM – 04:10 PM</t>
+          <t>01:50 PM – 02:50 PM</t>
         </is>
       </c>
       <c r="E152" t="inlineStr">
@@ -8936,19 +8936,19 @@
     </row>
     <row r="153">
       <c r="A153" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>Wednesday, September 2, 2026</t>
+          <t>Thursday, September 3, 2026</t>
         </is>
       </c>
       <c r="C153" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>01:50 PM – 02:50 PM</t>
+          <t>12:40 PM – 01:40 PM</t>
         </is>
       </c>
       <c r="E153" t="inlineStr">
@@ -9112,11 +9112,11 @@
         </is>
       </c>
       <c r="C156" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>01:50 PM – 02:50 PM</t>
+          <t>12:40 PM – 01:40 PM</t>
         </is>
       </c>
       <c r="E156" t="inlineStr">
@@ -9160,11 +9160,11 @@
     </row>
     <row r="157">
       <c r="A157" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>Sunday, September 6, 2026</t>
+          <t>Thursday, September 3, 2026</t>
         </is>
       </c>
       <c r="C157" t="n">
@@ -9216,11 +9216,11 @@
     </row>
     <row r="158">
       <c r="A158" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>Sunday, September 6, 2026</t>
+          <t>Monday, September 7, 2026</t>
         </is>
       </c>
       <c r="C158" t="n">
@@ -9272,11 +9272,11 @@
     </row>
     <row r="159">
       <c r="A159" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>Sunday, September 6, 2026</t>
+          <t>Wednesday, September 2, 2026</t>
         </is>
       </c>
       <c r="C159" t="n">
@@ -9328,11 +9328,11 @@
     </row>
     <row r="160">
       <c r="A160" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>Thursday, September 3, 2026</t>
+          <t>Sunday, September 6, 2026</t>
         </is>
       </c>
       <c r="C160" t="n">
@@ -9392,11 +9392,11 @@
         </is>
       </c>
       <c r="C161" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>03:10 PM – 04:10 PM</t>
+          <t>01:50 PM – 02:50 PM</t>
         </is>
       </c>
       <c r="E161" t="inlineStr">
@@ -9440,19 +9440,19 @@
     </row>
     <row r="162">
       <c r="A162" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>Wednesday, September 2, 2026</t>
+          <t>Monday, September 7, 2026</t>
         </is>
       </c>
       <c r="C162" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>01:50 PM – 02:50 PM</t>
+          <t>03:10 PM – 04:10 PM</t>
         </is>
       </c>
       <c r="E162" t="inlineStr">
@@ -9608,19 +9608,19 @@
     </row>
     <row r="165">
       <c r="A165" t="n">
+        <v>1</v>
+      </c>
+      <c r="B165" t="inlineStr">
+        <is>
+          <t>Wednesday, September 2, 2026</t>
+        </is>
+      </c>
+      <c r="C165" t="n">
         <v>3</v>
       </c>
-      <c r="B165" t="inlineStr">
-        <is>
-          <t>Sunday, September 6, 2026</t>
-        </is>
-      </c>
-      <c r="C165" t="n">
-        <v>2</v>
-      </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>01:50 PM – 02:50 PM</t>
+          <t>03:10 PM – 04:10 PM</t>
         </is>
       </c>
       <c r="E165" t="inlineStr">
@@ -9776,19 +9776,19 @@
     </row>
     <row r="168">
       <c r="A168" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>Thursday, September 3, 2026</t>
+          <t>Sunday, September 6, 2026</t>
         </is>
       </c>
       <c r="C168" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t>03:10 PM – 04:10 PM</t>
+          <t>01:50 PM – 02:50 PM</t>
         </is>
       </c>
       <c r="E168" t="inlineStr">
@@ -9840,11 +9840,11 @@
         </is>
       </c>
       <c r="C169" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t>12:40 PM – 01:40 PM</t>
+          <t>03:10 PM – 04:10 PM</t>
         </is>
       </c>
       <c r="E169" t="inlineStr">
@@ -9896,11 +9896,11 @@
         </is>
       </c>
       <c r="C170" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t>03:10 PM – 04:10 PM</t>
+          <t>01:50 PM – 02:50 PM</t>
         </is>
       </c>
       <c r="E170" t="inlineStr">
@@ -10000,19 +10000,19 @@
     </row>
     <row r="172">
       <c r="A172" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>Wednesday, September 2, 2026</t>
+          <t>Thursday, September 3, 2026</t>
         </is>
       </c>
       <c r="C172" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
-          <t>01:50 PM – 02:50 PM</t>
+          <t>12:40 PM – 01:40 PM</t>
         </is>
       </c>
       <c r="E172" t="inlineStr">
@@ -10224,11 +10224,11 @@
     </row>
     <row r="176">
       <c r="A176" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>Sunday, September 6, 2026</t>
+          <t>Monday, September 7, 2026</t>
         </is>
       </c>
       <c r="C176" t="n">
@@ -10280,11 +10280,11 @@
     </row>
     <row r="177">
       <c r="A177" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>Thursday, September 3, 2026</t>
+          <t>Sunday, September 6, 2026</t>
         </is>
       </c>
       <c r="C177" t="n">
@@ -10344,11 +10344,11 @@
         </is>
       </c>
       <c r="C178" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
-          <t>03:10 PM – 04:10 PM</t>
+          <t>01:50 PM – 02:50 PM</t>
         </is>
       </c>
       <c r="E178" t="inlineStr">
@@ -10792,11 +10792,11 @@
         </is>
       </c>
       <c r="C186" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>
-          <t>01:50 PM – 02:50 PM</t>
+          <t>12:40 PM – 01:40 PM</t>
         </is>
       </c>
       <c r="E186" t="inlineStr">
@@ -10848,11 +10848,11 @@
         </is>
       </c>
       <c r="C187" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>
-          <t>12:40 PM – 01:40 PM</t>
+          <t>01:50 PM – 02:50 PM</t>
         </is>
       </c>
       <c r="E187" t="inlineStr">
@@ -11274,12 +11274,12 @@
       </c>
       <c r="J194" t="inlineStr">
         <is>
-          <t>unassigned</t>
+          <t>tchr_katrina</t>
         </is>
       </c>
       <c r="K194" t="inlineStr">
         <is>
-          <t>Math - Tchr. Kat</t>
+          <t>Teacher Katrina</t>
         </is>
       </c>
       <c r="L194" t="n">
@@ -11736,19 +11736,19 @@
     </row>
     <row r="203">
       <c r="A203" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>Wednesday, September 2, 2026</t>
+          <t>Sunday, September 6, 2026</t>
         </is>
       </c>
       <c r="C203" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D203" t="inlineStr">
         <is>
-          <t>03:10 PM – 04:10 PM</t>
+          <t>04:20 PM – 05:20 PM</t>
         </is>
       </c>
       <c r="E203" t="inlineStr">
@@ -11800,11 +11800,11 @@
         </is>
       </c>
       <c r="C204" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D204" t="inlineStr">
         <is>
-          <t>04:20 PM – 05:20 PM</t>
+          <t>03:10 PM – 04:10 PM</t>
         </is>
       </c>
       <c r="E204" t="inlineStr">
@@ -11856,11 +11856,11 @@
         </is>
       </c>
       <c r="C205" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D205" t="inlineStr">
         <is>
-          <t>05:30 PM – 06:30 PM</t>
+          <t>04:20 PM – 05:20 PM</t>
         </is>
       </c>
       <c r="E205" t="inlineStr">
@@ -11904,19 +11904,19 @@
     </row>
     <row r="206">
       <c r="A206" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B206" t="inlineStr">
         <is>
-          <t>Thursday, September 3, 2026</t>
+          <t>Wednesday, September 2, 2026</t>
         </is>
       </c>
       <c r="C206" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D206" t="inlineStr">
         <is>
-          <t>03:10 PM – 04:10 PM</t>
+          <t>04:20 PM – 05:20 PM</t>
         </is>
       </c>
       <c r="E206" t="inlineStr">
@@ -11960,11 +11960,11 @@
     </row>
     <row r="207">
       <c r="A207" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="B207" t="inlineStr">
         <is>
-          <t>Wednesday, September 2, 2026</t>
+          <t>Sunday, September 6, 2026</t>
         </is>
       </c>
       <c r="C207" t="n">
@@ -12016,19 +12016,19 @@
     </row>
     <row r="208">
       <c r="A208" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="B208" t="inlineStr">
         <is>
-          <t>Wednesday, September 2, 2026</t>
+          <t>Monday, September 7, 2026</t>
         </is>
       </c>
       <c r="C208" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D208" t="inlineStr">
         <is>
-          <t>04:20 PM – 05:20 PM</t>
+          <t>05:30 PM – 06:30 PM</t>
         </is>
       </c>
       <c r="E208" t="inlineStr">
@@ -12072,11 +12072,11 @@
     </row>
     <row r="209">
       <c r="A209" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B209" t="inlineStr">
         <is>
-          <t>Monday, September 7, 2026</t>
+          <t>Sunday, September 6, 2026</t>
         </is>
       </c>
       <c r="C209" t="n">
@@ -12184,19 +12184,19 @@
     </row>
     <row r="211">
       <c r="A211" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="B211" t="inlineStr">
         <is>
-          <t>Monday, September 7, 2026</t>
+          <t>Thursday, September 3, 2026</t>
         </is>
       </c>
       <c r="C211" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D211" t="inlineStr">
         <is>
-          <t>03:10 PM – 04:10 PM</t>
+          <t>05:30 PM – 06:30 PM</t>
         </is>
       </c>
       <c r="E211" t="inlineStr">
@@ -12304,11 +12304,11 @@
         </is>
       </c>
       <c r="C213" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D213" t="inlineStr">
         <is>
-          <t>04:20 PM – 05:20 PM</t>
+          <t>03:10 PM – 04:10 PM</t>
         </is>
       </c>
       <c r="E213" t="inlineStr">
@@ -12352,19 +12352,19 @@
     </row>
     <row r="214">
       <c r="A214" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B214" t="inlineStr">
         <is>
-          <t>Thursday, September 3, 2026</t>
+          <t>Wednesday, September 2, 2026</t>
         </is>
       </c>
       <c r="C214" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D214" t="inlineStr">
         <is>
-          <t>05:30 PM – 06:30 PM</t>
+          <t>04:20 PM – 05:20 PM</t>
         </is>
       </c>
       <c r="E214" t="inlineStr">
@@ -12408,19 +12408,19 @@
     </row>
     <row r="215">
       <c r="A215" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="B215" t="inlineStr">
         <is>
-          <t>Wednesday, September 2, 2026</t>
+          <t>Monday, September 7, 2026</t>
         </is>
       </c>
       <c r="C215" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D215" t="inlineStr">
         <is>
-          <t>04:20 PM – 05:20 PM</t>
+          <t>03:10 PM – 04:10 PM</t>
         </is>
       </c>
       <c r="E215" t="inlineStr">
@@ -12472,11 +12472,11 @@
         </is>
       </c>
       <c r="C216" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D216" t="inlineStr">
         <is>
-          <t>03:10 PM – 04:10 PM</t>
+          <t>05:30 PM – 06:30 PM</t>
         </is>
       </c>
       <c r="E216" t="inlineStr">
@@ -12528,11 +12528,11 @@
         </is>
       </c>
       <c r="C217" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D217" t="inlineStr">
         <is>
-          <t>03:10 PM – 04:10 PM</t>
+          <t>04:20 PM – 05:20 PM</t>
         </is>
       </c>
       <c r="E217" t="inlineStr">
@@ -12584,11 +12584,11 @@
         </is>
       </c>
       <c r="C218" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D218" t="inlineStr">
         <is>
-          <t>05:30 PM – 06:30 PM</t>
+          <t>03:10 PM – 04:10 PM</t>
         </is>
       </c>
       <c r="E218" t="inlineStr">
@@ -12632,11 +12632,11 @@
     </row>
     <row r="219">
       <c r="A219" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B219" t="inlineStr">
         <is>
-          <t>Sunday, September 6, 2026</t>
+          <t>Monday, September 7, 2026</t>
         </is>
       </c>
       <c r="C219" t="n">
@@ -12688,19 +12688,19 @@
     </row>
     <row r="220">
       <c r="A220" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B220" t="inlineStr">
         <is>
-          <t>Sunday, September 6, 2026</t>
+          <t>Thursday, September 3, 2026</t>
         </is>
       </c>
       <c r="C220" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D220" t="inlineStr">
         <is>
-          <t>03:10 PM – 04:10 PM</t>
+          <t>04:20 PM – 05:20 PM</t>
         </is>
       </c>
       <c r="E220" t="inlineStr">
@@ -12744,19 +12744,19 @@
     </row>
     <row r="221">
       <c r="A221" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B221" t="inlineStr">
         <is>
-          <t>Thursday, September 3, 2026</t>
+          <t>Sunday, September 6, 2026</t>
         </is>
       </c>
       <c r="C221" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D221" t="inlineStr">
         <is>
-          <t>04:20 PM – 05:20 PM</t>
+          <t>05:30 PM – 06:30 PM</t>
         </is>
       </c>
       <c r="E221" t="inlineStr">
@@ -12800,11 +12800,11 @@
     </row>
     <row r="222">
       <c r="A222" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B222" t="inlineStr">
         <is>
-          <t>Wednesday, September 2, 2026</t>
+          <t>Thursday, September 3, 2026</t>
         </is>
       </c>
       <c r="C222" t="n">
@@ -12856,11 +12856,11 @@
     </row>
     <row r="223">
       <c r="A223" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B223" t="inlineStr">
         <is>
-          <t>Thursday, September 3, 2026</t>
+          <t>Wednesday, September 2, 2026</t>
         </is>
       </c>
       <c r="C223" t="n">
@@ -12912,11 +12912,11 @@
     </row>
     <row r="224">
       <c r="A224" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B224" t="inlineStr">
         <is>
-          <t>Wednesday, September 2, 2026</t>
+          <t>Thursday, September 3, 2026</t>
         </is>
       </c>
       <c r="C224" t="n">
@@ -13024,11 +13024,11 @@
     </row>
     <row r="226">
       <c r="A226" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B226" t="inlineStr">
         <is>
-          <t>Thursday, September 3, 2026</t>
+          <t>Wednesday, September 2, 2026</t>
         </is>
       </c>
       <c r="C226" t="n">
@@ -13144,11 +13144,11 @@
         </is>
       </c>
       <c r="C228" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D228" t="inlineStr">
         <is>
-          <t>04:20 PM – 05:20 PM</t>
+          <t>03:10 PM – 04:10 PM</t>
         </is>
       </c>
       <c r="E228" t="inlineStr">
@@ -13192,19 +13192,19 @@
     </row>
     <row r="229">
       <c r="A229" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B229" t="inlineStr">
         <is>
-          <t>Monday, September 7, 2026</t>
+          <t>Sunday, September 6, 2026</t>
         </is>
       </c>
       <c r="C229" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D229" t="inlineStr">
         <is>
-          <t>03:10 PM – 04:10 PM</t>
+          <t>05:30 PM – 06:30 PM</t>
         </is>
       </c>
       <c r="E229" t="inlineStr">
@@ -13248,19 +13248,19 @@
     </row>
     <row r="230">
       <c r="A230" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B230" t="inlineStr">
         <is>
-          <t>Thursday, September 3, 2026</t>
+          <t>Wednesday, September 2, 2026</t>
         </is>
       </c>
       <c r="C230" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D230" t="inlineStr">
         <is>
-          <t>04:20 PM – 05:20 PM</t>
+          <t>05:30 PM – 06:30 PM</t>
         </is>
       </c>
       <c r="E230" t="inlineStr">
@@ -13368,11 +13368,11 @@
         </is>
       </c>
       <c r="C232" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D232" t="inlineStr">
         <is>
-          <t>03:10 PM – 04:10 PM</t>
+          <t>04:20 PM – 05:20 PM</t>
         </is>
       </c>
       <c r="E232" t="inlineStr">
@@ -13416,19 +13416,19 @@
     </row>
     <row r="233">
       <c r="A233" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B233" t="inlineStr">
         <is>
-          <t>Wednesday, September 2, 2026</t>
+          <t>Thursday, September 3, 2026</t>
         </is>
       </c>
       <c r="C233" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D233" t="inlineStr">
         <is>
-          <t>05:30 PM – 06:30 PM</t>
+          <t>04:20 PM – 05:20 PM</t>
         </is>
       </c>
       <c r="E233" t="inlineStr">
@@ -13696,19 +13696,19 @@
     </row>
     <row r="238">
       <c r="A238" t="n">
+        <v>2</v>
+      </c>
+      <c r="B238" t="inlineStr">
+        <is>
+          <t>Thursday, September 3, 2026</t>
+        </is>
+      </c>
+      <c r="C238" t="n">
         <v>3</v>
       </c>
-      <c r="B238" t="inlineStr">
-        <is>
-          <t>Sunday, September 6, 2026</t>
-        </is>
-      </c>
-      <c r="C238" t="n">
-        <v>1</v>
-      </c>
       <c r="D238" t="inlineStr">
         <is>
-          <t>03:10 PM – 04:10 PM</t>
+          <t>05:30 PM – 06:30 PM</t>
         </is>
       </c>
       <c r="E238" t="inlineStr">
@@ -13920,19 +13920,19 @@
     </row>
     <row r="242">
       <c r="A242" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B242" t="inlineStr">
         <is>
-          <t>Thursday, September 3, 2026</t>
+          <t>Wednesday, September 2, 2026</t>
         </is>
       </c>
       <c r="C242" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D242" t="inlineStr">
         <is>
-          <t>05:30 PM – 06:30 PM</t>
+          <t>04:20 PM – 05:20 PM</t>
         </is>
       </c>
       <c r="E242" t="inlineStr">
@@ -13976,19 +13976,19 @@
     </row>
     <row r="243">
       <c r="A243" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="B243" t="inlineStr">
         <is>
-          <t>Thursday, September 3, 2026</t>
+          <t>Monday, September 7, 2026</t>
         </is>
       </c>
       <c r="C243" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D243" t="inlineStr">
         <is>
-          <t>03:10 PM – 04:10 PM</t>
+          <t>05:30 PM – 06:30 PM</t>
         </is>
       </c>
       <c r="E243" t="inlineStr">
@@ -14088,19 +14088,19 @@
     </row>
     <row r="245">
       <c r="A245" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B245" t="inlineStr">
         <is>
-          <t>Wednesday, September 2, 2026</t>
+          <t>Thursday, September 3, 2026</t>
         </is>
       </c>
       <c r="C245" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D245" t="inlineStr">
         <is>
-          <t>04:20 PM – 05:20 PM</t>
+          <t>03:10 PM – 04:10 PM</t>
         </is>
       </c>
       <c r="E245" t="inlineStr">
@@ -14144,19 +14144,19 @@
     </row>
     <row r="246">
       <c r="A246" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B246" t="inlineStr">
         <is>
-          <t>Sunday, September 6, 2026</t>
+          <t>Monday, September 7, 2026</t>
         </is>
       </c>
       <c r="C246" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D246" t="inlineStr">
         <is>
-          <t>03:10 PM – 04:10 PM</t>
+          <t>12:40 PM – 01:40 PM</t>
         </is>
       </c>
       <c r="E246" t="inlineStr">
@@ -14200,19 +14200,19 @@
     </row>
     <row r="247">
       <c r="A247" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B247" t="inlineStr">
         <is>
-          <t>Thursday, September 3, 2026</t>
+          <t>Wednesday, September 2, 2026</t>
         </is>
       </c>
       <c r="C247" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D247" t="inlineStr">
         <is>
-          <t>03:10 PM – 04:10 PM</t>
+          <t>01:50 PM – 02:50 PM</t>
         </is>
       </c>
       <c r="E247" t="inlineStr">
@@ -14264,11 +14264,11 @@
         </is>
       </c>
       <c r="C248" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D248" t="inlineStr">
         <is>
-          <t>01:50 PM – 02:50 PM</t>
+          <t>03:10 PM – 04:10 PM</t>
         </is>
       </c>
       <c r="E248" t="inlineStr">
@@ -14312,11 +14312,11 @@
     </row>
     <row r="249">
       <c r="A249" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B249" t="inlineStr">
         <is>
-          <t>Wednesday, September 2, 2026</t>
+          <t>Thursday, September 3, 2026</t>
         </is>
       </c>
       <c r="C249" t="n">
@@ -14368,19 +14368,19 @@
     </row>
     <row r="250">
       <c r="A250" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B250" t="inlineStr">
         <is>
-          <t>Monday, September 7, 2026</t>
+          <t>Sunday, September 6, 2026</t>
         </is>
       </c>
       <c r="C250" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D250" t="inlineStr">
         <is>
-          <t>03:10 PM – 04:10 PM</t>
+          <t>01:50 PM – 02:50 PM</t>
         </is>
       </c>
       <c r="E250" t="inlineStr">
@@ -14424,11 +14424,11 @@
     </row>
     <row r="251">
       <c r="A251" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="B251" t="inlineStr">
         <is>
-          <t>Sunday, September 6, 2026</t>
+          <t>Wednesday, September 2, 2026</t>
         </is>
       </c>
       <c r="C251" t="n">
@@ -14488,11 +14488,11 @@
         </is>
       </c>
       <c r="C252" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D252" t="inlineStr">
         <is>
-          <t>01:50 PM – 02:50 PM</t>
+          <t>12:40 PM – 01:40 PM</t>
         </is>
       </c>
       <c r="E252" t="inlineStr">
@@ -14536,11 +14536,11 @@
     </row>
     <row r="253">
       <c r="A253" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B253" t="inlineStr">
         <is>
-          <t>Thursday, September 3, 2026</t>
+          <t>Sunday, September 6, 2026</t>
         </is>
       </c>
       <c r="C253" t="n">
@@ -14648,19 +14648,19 @@
     </row>
     <row r="255">
       <c r="A255" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B255" t="inlineStr">
         <is>
-          <t>Wednesday, September 2, 2026</t>
+          <t>Thursday, September 3, 2026</t>
         </is>
       </c>
       <c r="C255" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D255" t="inlineStr">
         <is>
-          <t>12:40 PM – 01:40 PM</t>
+          <t>03:10 PM – 04:10 PM</t>
         </is>
       </c>
       <c r="E255" t="inlineStr">
@@ -14704,19 +14704,19 @@
     </row>
     <row r="256">
       <c r="A256" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B256" t="inlineStr">
         <is>
-          <t>Sunday, September 6, 2026</t>
+          <t>Monday, September 7, 2026</t>
         </is>
       </c>
       <c r="C256" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D256" t="inlineStr">
         <is>
-          <t>04:20 PM – 05:20 PM</t>
+          <t>03:10 PM – 04:10 PM</t>
         </is>
       </c>
       <c r="E256" t="inlineStr">
@@ -14816,11 +14816,11 @@
     </row>
     <row r="258">
       <c r="A258" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B258" t="inlineStr">
         <is>
-          <t>Thursday, September 3, 2026</t>
+          <t>Sunday, September 6, 2026</t>
         </is>
       </c>
       <c r="C258" t="n">
@@ -14880,11 +14880,11 @@
         </is>
       </c>
       <c r="C259" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D259" t="inlineStr">
         <is>
-          <t>03:10 PM – 04:10 PM</t>
+          <t>04:20 PM – 05:20 PM</t>
         </is>
       </c>
       <c r="E259" t="inlineStr">
@@ -14928,19 +14928,19 @@
     </row>
     <row r="260">
       <c r="A260" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B260" t="inlineStr">
         <is>
-          <t>Monday, September 7, 2026</t>
+          <t>Sunday, September 6, 2026</t>
         </is>
       </c>
       <c r="C260" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D260" t="inlineStr">
         <is>
-          <t>05:30 PM – 06:30 PM</t>
+          <t>04:20 PM – 05:20 PM</t>
         </is>
       </c>
       <c r="E260" t="inlineStr">
@@ -14984,11 +14984,11 @@
     </row>
     <row r="261">
       <c r="A261" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B261" t="inlineStr">
         <is>
-          <t>Sunday, September 6, 2026</t>
+          <t>Thursday, September 3, 2026</t>
         </is>
       </c>
       <c r="C261" t="n">
@@ -15040,19 +15040,19 @@
     </row>
     <row r="262">
       <c r="A262" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B262" t="inlineStr">
         <is>
-          <t>Wednesday, September 2, 2026</t>
+          <t>Thursday, September 3, 2026</t>
         </is>
       </c>
       <c r="C262" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D262" t="inlineStr">
         <is>
-          <t>04:20 PM – 05:20 PM</t>
+          <t>03:10 PM – 04:10 PM</t>
         </is>
       </c>
       <c r="E262" t="inlineStr">
@@ -15082,12 +15082,12 @@
       </c>
       <c r="J262" t="inlineStr">
         <is>
-          <t>unassigned</t>
+          <t>tchr_katrina</t>
         </is>
       </c>
       <c r="K262" t="inlineStr">
         <is>
-          <t>Math - Tchr. Kat</t>
+          <t>Teacher Katrina</t>
         </is>
       </c>
       <c r="L262" t="n">
@@ -15104,11 +15104,11 @@
         </is>
       </c>
       <c r="C263" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D263" t="inlineStr">
         <is>
-          <t>03:10 PM – 04:10 PM</t>
+          <t>05:30 PM – 06:30 PM</t>
         </is>
       </c>
       <c r="E263" t="inlineStr">
@@ -15160,11 +15160,11 @@
         </is>
       </c>
       <c r="C264" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D264" t="inlineStr">
         <is>
-          <t>05:30 PM – 06:30 PM</t>
+          <t>03:10 PM – 04:10 PM</t>
         </is>
       </c>
       <c r="E264" t="inlineStr">
@@ -15208,11 +15208,11 @@
     </row>
     <row r="265">
       <c r="A265" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B265" t="inlineStr">
         <is>
-          <t>Thursday, September 3, 2026</t>
+          <t>Wednesday, September 2, 2026</t>
         </is>
       </c>
       <c r="C265" t="n">
@@ -15272,11 +15272,11 @@
         </is>
       </c>
       <c r="C266" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D266" t="inlineStr">
         <is>
-          <t>05:30 PM – 06:30 PM</t>
+          <t>04:20 PM – 05:20 PM</t>
         </is>
       </c>
       <c r="E266" t="inlineStr">
@@ -15320,19 +15320,19 @@
     </row>
     <row r="267">
       <c r="A267" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B267" t="inlineStr">
         <is>
-          <t>Wednesday, September 2, 2026</t>
+          <t>Thursday, September 3, 2026</t>
         </is>
       </c>
       <c r="C267" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D267" t="inlineStr">
         <is>
-          <t>04:20 PM – 05:20 PM</t>
+          <t>03:10 PM – 04:10 PM</t>
         </is>
       </c>
       <c r="E267" t="inlineStr">
@@ -15376,19 +15376,19 @@
     </row>
     <row r="268">
       <c r="A268" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B268" t="inlineStr">
         <is>
-          <t>Thursday, September 3, 2026</t>
+          <t>Wednesday, September 2, 2026</t>
         </is>
       </c>
       <c r="C268" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D268" t="inlineStr">
         <is>
-          <t>03:10 PM – 04:10 PM</t>
+          <t>04:20 PM – 05:20 PM</t>
         </is>
       </c>
       <c r="E268" t="inlineStr">
@@ -15440,11 +15440,11 @@
         </is>
       </c>
       <c r="C269" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D269" t="inlineStr">
         <is>
-          <t>03:10 PM – 04:10 PM</t>
+          <t>05:30 PM – 06:30 PM</t>
         </is>
       </c>
       <c r="E269" t="inlineStr">
@@ -15496,11 +15496,11 @@
         </is>
       </c>
       <c r="C270" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D270" t="inlineStr">
         <is>
-          <t>03:10 PM – 04:10 PM</t>
+          <t>04:20 PM – 05:20 PM</t>
         </is>
       </c>
       <c r="E270" t="inlineStr">
@@ -15544,19 +15544,19 @@
     </row>
     <row r="271">
       <c r="A271" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B271" t="inlineStr">
         <is>
-          <t>Wednesday, September 2, 2026</t>
+          <t>Thursday, September 3, 2026</t>
         </is>
       </c>
       <c r="C271" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D271" t="inlineStr">
         <is>
-          <t>05:30 PM – 06:30 PM</t>
+          <t>03:10 PM – 04:10 PM</t>
         </is>
       </c>
       <c r="E271" t="inlineStr">
@@ -15608,11 +15608,11 @@
         </is>
       </c>
       <c r="C272" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D272" t="inlineStr">
         <is>
-          <t>03:10 PM – 04:10 PM</t>
+          <t>04:20 PM – 05:20 PM</t>
         </is>
       </c>
       <c r="E272" t="inlineStr">
@@ -15664,11 +15664,11 @@
         </is>
       </c>
       <c r="C273" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D273" t="inlineStr">
         <is>
-          <t>04:20 PM – 05:20 PM</t>
+          <t>03:10 PM – 04:10 PM</t>
         </is>
       </c>
       <c r="E273" t="inlineStr">
@@ -15712,19 +15712,19 @@
     </row>
     <row r="274">
       <c r="A274" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B274" t="inlineStr">
         <is>
-          <t>Sunday, September 6, 2026</t>
+          <t>Monday, September 7, 2026</t>
         </is>
       </c>
       <c r="C274" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D274" t="inlineStr">
         <is>
-          <t>04:20 PM – 05:20 PM</t>
+          <t>03:10 PM – 04:10 PM</t>
         </is>
       </c>
       <c r="E274" t="inlineStr">
@@ -15824,19 +15824,19 @@
     </row>
     <row r="276">
       <c r="A276" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B276" t="inlineStr">
         <is>
-          <t>Wednesday, September 2, 2026</t>
+          <t>Thursday, September 3, 2026</t>
         </is>
       </c>
       <c r="C276" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D276" t="inlineStr">
         <is>
-          <t>04:20 PM – 05:20 PM</t>
+          <t>05:30 PM – 06:30 PM</t>
         </is>
       </c>
       <c r="E276" t="inlineStr">
@@ -15888,11 +15888,11 @@
         </is>
       </c>
       <c r="C277" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D277" t="inlineStr">
         <is>
-          <t>05:30 PM – 06:30 PM</t>
+          <t>04:20 PM – 05:20 PM</t>
         </is>
       </c>
       <c r="E277" t="inlineStr">
@@ -15944,11 +15944,11 @@
         </is>
       </c>
       <c r="C278" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D278" t="inlineStr">
         <is>
-          <t>04:20 PM – 05:20 PM</t>
+          <t>03:10 PM – 04:10 PM</t>
         </is>
       </c>
       <c r="E278" t="inlineStr">
@@ -15992,19 +15992,19 @@
     </row>
     <row r="279">
       <c r="A279" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B279" t="inlineStr">
         <is>
-          <t>Thursday, September 3, 2026</t>
+          <t>Wednesday, September 2, 2026</t>
         </is>
       </c>
       <c r="C279" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D279" t="inlineStr">
         <is>
-          <t>03:10 PM – 04:10 PM</t>
+          <t>04:20 PM – 05:20 PM</t>
         </is>
       </c>
       <c r="E279" t="inlineStr">
@@ -16056,11 +16056,11 @@
         </is>
       </c>
       <c r="C280" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D280" t="inlineStr">
         <is>
-          <t>03:10 PM – 04:10 PM</t>
+          <t>05:30 PM – 06:30 PM</t>
         </is>
       </c>
       <c r="E280" t="inlineStr">
@@ -16112,11 +16112,11 @@
         </is>
       </c>
       <c r="C281" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D281" t="inlineStr">
         <is>
-          <t>05:30 PM – 06:30 PM</t>
+          <t>03:10 PM – 04:10 PM</t>
         </is>
       </c>
       <c r="E281" t="inlineStr">
@@ -16160,11 +16160,11 @@
     </row>
     <row r="282">
       <c r="A282" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B282" t="inlineStr">
         <is>
-          <t>Sunday, September 6, 2026</t>
+          <t>Thursday, September 3, 2026</t>
         </is>
       </c>
       <c r="C282" t="n">
@@ -16224,11 +16224,11 @@
         </is>
       </c>
       <c r="C283" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D283" t="inlineStr">
         <is>
-          <t>03:10 PM – 04:10 PM</t>
+          <t>04:20 PM – 05:20 PM</t>
         </is>
       </c>
       <c r="E283" t="inlineStr">
@@ -16272,11 +16272,11 @@
     </row>
     <row r="284">
       <c r="A284" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B284" t="inlineStr">
         <is>
-          <t>Wednesday, September 2, 2026</t>
+          <t>Thursday, September 3, 2026</t>
         </is>
       </c>
       <c r="C284" t="n">
@@ -16336,11 +16336,11 @@
         </is>
       </c>
       <c r="C285" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D285" t="inlineStr">
         <is>
-          <t>04:20 PM – 05:20 PM</t>
+          <t>03:10 PM – 04:10 PM</t>
         </is>
       </c>
       <c r="E285" t="inlineStr">
@@ -16384,11 +16384,11 @@
     </row>
     <row r="286">
       <c r="A286" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B286" t="inlineStr">
         <is>
-          <t>Thursday, September 3, 2026</t>
+          <t>Sunday, September 6, 2026</t>
         </is>
       </c>
       <c r="C286" t="n">
@@ -16440,11 +16440,11 @@
     </row>
     <row r="287">
       <c r="A287" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B287" t="inlineStr">
         <is>
-          <t>Thursday, September 3, 2026</t>
+          <t>Wednesday, September 2, 2026</t>
         </is>
       </c>
       <c r="C287" t="n">
@@ -16504,11 +16504,11 @@
         </is>
       </c>
       <c r="C288" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D288" t="inlineStr">
         <is>
-          <t>03:10 PM – 04:10 PM</t>
+          <t>04:20 PM – 05:20 PM</t>
         </is>
       </c>
       <c r="E288" t="inlineStr">
@@ -16560,11 +16560,11 @@
         </is>
       </c>
       <c r="C289" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D289" t="inlineStr">
         <is>
-          <t>04:20 PM – 05:20 PM</t>
+          <t>03:10 PM – 04:10 PM</t>
         </is>
       </c>
       <c r="E289" t="inlineStr">
@@ -16664,19 +16664,19 @@
     </row>
     <row r="291">
       <c r="A291" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B291" t="inlineStr">
         <is>
-          <t>Monday, September 7, 2026</t>
+          <t>Sunday, September 6, 2026</t>
         </is>
       </c>
       <c r="C291" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D291" t="inlineStr">
         <is>
-          <t>03:10 PM – 04:10 PM</t>
+          <t>05:30 PM – 06:30 PM</t>
         </is>
       </c>
       <c r="E291" t="inlineStr">
@@ -16728,11 +16728,11 @@
         </is>
       </c>
       <c r="C292" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D292" t="inlineStr">
         <is>
-          <t>04:20 PM – 05:20 PM</t>
+          <t>03:10 PM – 04:10 PM</t>
         </is>
       </c>
       <c r="E292" t="inlineStr">
@@ -16840,11 +16840,11 @@
         </is>
       </c>
       <c r="C294" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D294" t="inlineStr">
         <is>
-          <t>03:10 PM – 04:10 PM</t>
+          <t>04:20 PM – 05:20 PM</t>
         </is>
       </c>
       <c r="E294" t="inlineStr">
@@ -17112,11 +17112,11 @@
     </row>
     <row r="299">
       <c r="A299" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B299" t="inlineStr">
         <is>
-          <t>Monday, September 7, 2026</t>
+          <t>Sunday, September 6, 2026</t>
         </is>
       </c>
       <c r="C299" t="n">
@@ -17336,11 +17336,11 @@
     </row>
     <row r="303">
       <c r="A303" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B303" t="inlineStr">
         <is>
-          <t>Sunday, September 6, 2026</t>
+          <t>Monday, September 7, 2026</t>
         </is>
       </c>
       <c r="C303" t="n">
@@ -17400,11 +17400,11 @@
         </is>
       </c>
       <c r="C304" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D304" t="inlineStr">
         <is>
-          <t>04:20 PM – 05:20 PM</t>
+          <t>03:10 PM – 04:10 PM</t>
         </is>
       </c>
       <c r="E304" t="inlineStr">
@@ -17456,11 +17456,11 @@
         </is>
       </c>
       <c r="C305" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D305" t="inlineStr">
         <is>
-          <t>04:20 PM – 05:20 PM</t>
+          <t>03:10 PM – 04:10 PM</t>
         </is>
       </c>
       <c r="E305" t="inlineStr">
@@ -17504,11 +17504,11 @@
     </row>
     <row r="306">
       <c r="A306" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="B306" t="inlineStr">
         <is>
-          <t>Monday, September 7, 2026</t>
+          <t>Thursday, September 3, 2026</t>
         </is>
       </c>
       <c r="C306" t="n">
@@ -17624,11 +17624,11 @@
         </is>
       </c>
       <c r="C308" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D308" t="inlineStr">
         <is>
-          <t>03:10 PM – 04:10 PM</t>
+          <t>04:20 PM – 05:20 PM</t>
         </is>
       </c>
       <c r="E308" t="inlineStr">
@@ -17736,11 +17736,11 @@
         </is>
       </c>
       <c r="C310" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D310" t="inlineStr">
         <is>
-          <t>05:30 PM – 06:30 PM</t>
+          <t>03:10 PM – 04:10 PM</t>
         </is>
       </c>
       <c r="E310" t="inlineStr">
@@ -17848,11 +17848,11 @@
         </is>
       </c>
       <c r="C312" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D312" t="inlineStr">
         <is>
-          <t>03:10 PM – 04:10 PM</t>
+          <t>05:30 PM – 06:30 PM</t>
         </is>
       </c>
       <c r="E312" t="inlineStr">
@@ -17896,11 +17896,11 @@
     </row>
     <row r="313">
       <c r="A313" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B313" t="inlineStr">
         <is>
-          <t>Thursday, September 3, 2026</t>
+          <t>Wednesday, September 2, 2026</t>
         </is>
       </c>
       <c r="C313" t="n">
@@ -18008,19 +18008,19 @@
     </row>
     <row r="315">
       <c r="A315" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B315" t="inlineStr">
         <is>
-          <t>Thursday, September 3, 2026</t>
+          <t>Wednesday, September 2, 2026</t>
         </is>
       </c>
       <c r="C315" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D315" t="inlineStr">
         <is>
-          <t>03:10 PM – 04:10 PM</t>
+          <t>04:20 PM – 05:20 PM</t>
         </is>
       </c>
       <c r="E315" t="inlineStr">
@@ -18064,11 +18064,11 @@
     </row>
     <row r="316">
       <c r="A316" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B316" t="inlineStr">
         <is>
-          <t>Wednesday, September 2, 2026</t>
+          <t>Thursday, September 3, 2026</t>
         </is>
       </c>
       <c r="C316" t="n">
@@ -18176,19 +18176,19 @@
     </row>
     <row r="318">
       <c r="A318" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B318" t="inlineStr">
         <is>
-          <t>Wednesday, September 2, 2026</t>
+          <t>Thursday, September 3, 2026</t>
         </is>
       </c>
       <c r="C318" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D318" t="inlineStr">
         <is>
-          <t>04:20 PM – 05:20 PM</t>
+          <t>03:10 PM – 04:10 PM</t>
         </is>
       </c>
       <c r="E318" t="inlineStr">
@@ -18232,19 +18232,19 @@
     </row>
     <row r="319">
       <c r="A319" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="B319" t="inlineStr">
         <is>
-          <t>Sunday, September 6, 2026</t>
+          <t>Wednesday, September 2, 2026</t>
         </is>
       </c>
       <c r="C319" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D319" t="inlineStr">
         <is>
-          <t>04:20 PM – 05:20 PM</t>
+          <t>03:10 PM – 04:10 PM</t>
         </is>
       </c>
       <c r="E319" t="inlineStr">
@@ -18288,19 +18288,19 @@
     </row>
     <row r="320">
       <c r="A320" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B320" t="inlineStr">
         <is>
-          <t>Monday, September 7, 2026</t>
+          <t>Sunday, September 6, 2026</t>
         </is>
       </c>
       <c r="C320" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D320" t="inlineStr">
         <is>
-          <t>03:10 PM – 04:10 PM</t>
+          <t>05:30 PM – 06:30 PM</t>
         </is>
       </c>
       <c r="E320" t="inlineStr">
@@ -18352,11 +18352,11 @@
         </is>
       </c>
       <c r="C321" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D321" t="inlineStr">
         <is>
-          <t>05:30 PM – 06:30 PM</t>
+          <t>04:20 PM – 05:20 PM</t>
         </is>
       </c>
       <c r="E321" t="inlineStr">
@@ -18400,19 +18400,19 @@
     </row>
     <row r="322">
       <c r="A322" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B322" t="inlineStr">
         <is>
-          <t>Sunday, September 6, 2026</t>
+          <t>Monday, September 7, 2026</t>
         </is>
       </c>
       <c r="C322" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D322" t="inlineStr">
         <is>
-          <t>05:30 PM – 06:30 PM</t>
+          <t>04:20 PM – 05:20 PM</t>
         </is>
       </c>
       <c r="E322" t="inlineStr">
@@ -18464,11 +18464,11 @@
         </is>
       </c>
       <c r="C323" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D323" t="inlineStr">
         <is>
-          <t>04:20 PM – 05:20 PM</t>
+          <t>05:30 PM – 06:30 PM</t>
         </is>
       </c>
       <c r="E323" t="inlineStr">
@@ -18624,19 +18624,19 @@
     </row>
     <row r="326">
       <c r="A326" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="B326" t="inlineStr">
         <is>
-          <t>Wednesday, September 2, 2026</t>
+          <t>Sunday, September 6, 2026</t>
         </is>
       </c>
       <c r="C326" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D326" t="inlineStr">
         <is>
-          <t>05:30 PM – 06:30 PM</t>
+          <t>04:20 PM – 05:20 PM</t>
         </is>
       </c>
       <c r="E326" t="inlineStr">
@@ -18688,11 +18688,11 @@
         </is>
       </c>
       <c r="C327" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D327" t="inlineStr">
         <is>
-          <t>04:20 PM – 05:20 PM</t>
+          <t>05:30 PM – 06:30 PM</t>
         </is>
       </c>
       <c r="E327" t="inlineStr">
@@ -18744,11 +18744,11 @@
         </is>
       </c>
       <c r="C328" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D328" t="inlineStr">
         <is>
-          <t>03:10 PM – 04:10 PM</t>
+          <t>04:20 PM – 05:20 PM</t>
         </is>
       </c>
       <c r="E328" t="inlineStr">
@@ -18792,11 +18792,11 @@
     </row>
     <row r="329">
       <c r="A329" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B329" t="inlineStr">
         <is>
-          <t>Sunday, September 6, 2026</t>
+          <t>Monday, September 7, 2026</t>
         </is>
       </c>
       <c r="C329" t="n">
@@ -18856,11 +18856,11 @@
         </is>
       </c>
       <c r="C330" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D330" t="inlineStr">
         <is>
-          <t>05:30 PM – 06:30 PM</t>
+          <t>04:20 PM – 05:20 PM</t>
         </is>
       </c>
       <c r="E330" t="inlineStr">
@@ -18912,11 +18912,11 @@
         </is>
       </c>
       <c r="C331" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D331" t="inlineStr">
         <is>
-          <t>05:30 PM – 06:30 PM</t>
+          <t>04:20 PM – 05:20 PM</t>
         </is>
       </c>
       <c r="E331" t="inlineStr">
@@ -18946,12 +18946,12 @@
       </c>
       <c r="J331" t="inlineStr">
         <is>
-          <t>unassigned</t>
+          <t>tchr_obaydah</t>
         </is>
       </c>
       <c r="K331" t="inlineStr">
         <is>
-          <t>Qur'an - Ust. Obayda</t>
+          <t>Ustadh Obaydah</t>
         </is>
       </c>
       <c r="L331" t="n">
@@ -18960,19 +18960,19 @@
     </row>
     <row r="332">
       <c r="A332" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B332" t="inlineStr">
         <is>
-          <t>Thursday, September 3, 2026</t>
+          <t>Wednesday, September 2, 2026</t>
         </is>
       </c>
       <c r="C332" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D332" t="inlineStr">
         <is>
-          <t>04:20 PM – 05:20 PM</t>
+          <t>05:30 PM – 06:30 PM</t>
         </is>
       </c>
       <c r="E332" t="inlineStr">
@@ -19072,19 +19072,19 @@
     </row>
     <row r="334">
       <c r="A334" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B334" t="inlineStr">
         <is>
-          <t>Monday, September 7, 2026</t>
+          <t>Sunday, September 6, 2026</t>
         </is>
       </c>
       <c r="C334" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D334" t="inlineStr">
         <is>
-          <t>03:10 PM – 04:10 PM</t>
+          <t>05:30 PM – 06:30 PM</t>
         </is>
       </c>
       <c r="E334" t="inlineStr">
@@ -19184,11 +19184,11 @@
     </row>
     <row r="336">
       <c r="A336" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B336" t="inlineStr">
         <is>
-          <t>Wednesday, September 2, 2026</t>
+          <t>Thursday, September 3, 2026</t>
         </is>
       </c>
       <c r="C336" t="n">
@@ -19360,11 +19360,11 @@
         </is>
       </c>
       <c r="C339" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D339" t="inlineStr">
         <is>
-          <t>04:20 PM – 05:20 PM</t>
+          <t>05:30 PM – 06:30 PM</t>
         </is>
       </c>
       <c r="E339" t="inlineStr">
@@ -19408,11 +19408,11 @@
     </row>
     <row r="340">
       <c r="A340" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B340" t="inlineStr">
         <is>
-          <t>Thursday, September 3, 2026</t>
+          <t>Wednesday, September 2, 2026</t>
         </is>
       </c>
       <c r="C340" t="n">
@@ -19464,19 +19464,19 @@
     </row>
     <row r="341">
       <c r="A341" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B341" t="inlineStr">
         <is>
-          <t>Sunday, September 6, 2026</t>
+          <t>Monday, September 7, 2026</t>
         </is>
       </c>
       <c r="C341" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D341" t="inlineStr">
         <is>
-          <t>03:10 PM – 04:10 PM</t>
+          <t>04:20 PM – 05:20 PM</t>
         </is>
       </c>
       <c r="E341" t="inlineStr">
@@ -19520,19 +19520,19 @@
     </row>
     <row r="342">
       <c r="A342" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B342" t="inlineStr">
         <is>
-          <t>Thursday, September 3, 2026</t>
+          <t>Wednesday, September 2, 2026</t>
         </is>
       </c>
       <c r="C342" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D342" t="inlineStr">
         <is>
-          <t>03:10 PM – 04:10 PM</t>
+          <t>04:20 PM – 05:20 PM</t>
         </is>
       </c>
       <c r="E342" t="inlineStr">
@@ -19576,19 +19576,19 @@
     </row>
     <row r="343">
       <c r="A343" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B343" t="inlineStr">
         <is>
-          <t>Sunday, September 6, 2026</t>
+          <t>Monday, September 7, 2026</t>
         </is>
       </c>
       <c r="C343" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D343" t="inlineStr">
         <is>
-          <t>05:30 PM – 06:30 PM</t>
+          <t>03:10 PM – 04:10 PM</t>
         </is>
       </c>
       <c r="E343" t="inlineStr">
@@ -19632,11 +19632,11 @@
     </row>
     <row r="344">
       <c r="A344" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B344" t="inlineStr">
         <is>
-          <t>Monday, September 7, 2026</t>
+          <t>Sunday, September 6, 2026</t>
         </is>
       </c>
       <c r="C344" t="n">
@@ -19688,19 +19688,19 @@
     </row>
     <row r="345">
       <c r="A345" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B345" t="inlineStr">
         <is>
-          <t>Wednesday, September 2, 2026</t>
+          <t>Thursday, September 3, 2026</t>
         </is>
       </c>
       <c r="C345" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D345" t="inlineStr">
         <is>
-          <t>05:30 PM – 06:30 PM</t>
+          <t>03:10 PM – 04:10 PM</t>
         </is>
       </c>
       <c r="E345" t="inlineStr">
@@ -19800,19 +19800,19 @@
     </row>
     <row r="347">
       <c r="A347" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B347" t="inlineStr">
         <is>
-          <t>Wednesday, September 2, 2026</t>
+          <t>Thursday, September 3, 2026</t>
         </is>
       </c>
       <c r="C347" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D347" t="inlineStr">
         <is>
-          <t>04:20 PM – 05:20 PM</t>
+          <t>05:30 PM – 06:30 PM</t>
         </is>
       </c>
       <c r="E347" t="inlineStr">
@@ -20248,19 +20248,19 @@
     </row>
     <row r="355">
       <c r="A355" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B355" t="inlineStr">
         <is>
-          <t>Thursday, September 3, 2026</t>
+          <t>Wednesday, September 2, 2026</t>
         </is>
       </c>
       <c r="C355" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D355" t="inlineStr">
         <is>
-          <t>03:10 PM – 04:10 PM</t>
+          <t>05:30 PM – 06:30 PM</t>
         </is>
       </c>
       <c r="E355" t="inlineStr">
@@ -20312,11 +20312,11 @@
         </is>
       </c>
       <c r="C356" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D356" t="inlineStr">
         <is>
-          <t>05:30 PM – 06:30 PM</t>
+          <t>04:20 PM – 05:20 PM</t>
         </is>
       </c>
       <c r="E356" t="inlineStr">
@@ -20360,19 +20360,19 @@
     </row>
     <row r="357">
       <c r="A357" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B357" t="inlineStr">
         <is>
-          <t>Wednesday, September 2, 2026</t>
+          <t>Thursday, September 3, 2026</t>
         </is>
       </c>
       <c r="C357" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D357" t="inlineStr">
         <is>
-          <t>04:20 PM – 05:20 PM</t>
+          <t>03:10 PM – 04:10 PM</t>
         </is>
       </c>
       <c r="E357" t="inlineStr">
@@ -20480,11 +20480,11 @@
         </is>
       </c>
       <c r="C359" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D359" t="inlineStr">
         <is>
-          <t>03:10 PM – 04:10 PM</t>
+          <t>04:20 PM – 05:20 PM</t>
         </is>
       </c>
       <c r="E359" t="inlineStr">
@@ -20592,11 +20592,11 @@
         </is>
       </c>
       <c r="C361" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D361" t="inlineStr">
         <is>
-          <t>03:10 PM – 04:10 PM</t>
+          <t>05:30 PM – 06:30 PM</t>
         </is>
       </c>
       <c r="E361" t="inlineStr">
@@ -20648,11 +20648,11 @@
         </is>
       </c>
       <c r="C362" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D362" t="inlineStr">
         <is>
-          <t>03:10 PM – 04:10 PM</t>
+          <t>05:30 PM – 06:30 PM</t>
         </is>
       </c>
       <c r="E362" t="inlineStr">
@@ -20696,19 +20696,19 @@
     </row>
     <row r="363">
       <c r="A363" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B363" t="inlineStr">
         <is>
-          <t>Thursday, September 3, 2026</t>
+          <t>Sunday, September 6, 2026</t>
         </is>
       </c>
       <c r="C363" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D363" t="inlineStr">
         <is>
-          <t>05:30 PM – 06:30 PM</t>
+          <t>03:10 PM – 04:10 PM</t>
         </is>
       </c>
       <c r="E363" t="inlineStr">
@@ -20808,19 +20808,19 @@
     </row>
     <row r="365">
       <c r="A365" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="B365" t="inlineStr">
         <is>
-          <t>Monday, September 7, 2026</t>
+          <t>Thursday, September 3, 2026</t>
         </is>
       </c>
       <c r="C365" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D365" t="inlineStr">
         <is>
-          <t>04:20 PM – 05:20 PM</t>
+          <t>03:10 PM – 04:10 PM</t>
         </is>
       </c>
       <c r="E365" t="inlineStr">
@@ -21040,11 +21040,11 @@
         </is>
       </c>
       <c r="C369" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D369" t="inlineStr">
         <is>
-          <t>09:00 AM – 10:00 AM</t>
+          <t>10:25 AM – 11:25 AM</t>
         </is>
       </c>
       <c r="E369" t="inlineStr">
@@ -21088,19 +21088,19 @@
     </row>
     <row r="370">
       <c r="A370" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B370" t="inlineStr">
         <is>
-          <t>Monday, September 7, 2026</t>
+          <t>Sunday, September 6, 2026</t>
         </is>
       </c>
       <c r="C370" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D370" t="inlineStr">
         <is>
-          <t>08:00 AM – 09:00 AM</t>
+          <t>09:00 AM – 10:00 AM</t>
         </is>
       </c>
       <c r="E370" t="inlineStr">
@@ -21144,19 +21144,19 @@
     </row>
     <row r="371">
       <c r="A371" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B371" t="inlineStr">
         <is>
-          <t>Sunday, September 6, 2026</t>
+          <t>Monday, September 7, 2026</t>
         </is>
       </c>
       <c r="C371" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D371" t="inlineStr">
         <is>
-          <t>10:25 AM – 11:25 AM</t>
+          <t>09:00 AM – 10:00 AM</t>
         </is>
       </c>
       <c r="E371" t="inlineStr">
@@ -21200,19 +21200,19 @@
     </row>
     <row r="372">
       <c r="A372" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B372" t="inlineStr">
         <is>
-          <t>Sunday, September 6, 2026</t>
+          <t>Monday, September 7, 2026</t>
         </is>
       </c>
       <c r="C372" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D372" t="inlineStr">
         <is>
-          <t>09:00 AM – 10:00 AM</t>
+          <t>08:00 AM – 09:00 AM</t>
         </is>
       </c>
       <c r="E372" t="inlineStr">
@@ -21592,11 +21592,11 @@
     </row>
     <row r="379">
       <c r="A379" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B379" t="inlineStr">
         <is>
-          <t>Monday, September 7, 2026</t>
+          <t>Sunday, September 6, 2026</t>
         </is>
       </c>
       <c r="C379" t="n">
@@ -21648,11 +21648,11 @@
     </row>
     <row r="380">
       <c r="A380" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B380" t="inlineStr">
         <is>
-          <t>Sunday, September 6, 2026</t>
+          <t>Monday, September 7, 2026</t>
         </is>
       </c>
       <c r="C380" t="n">
@@ -21704,19 +21704,19 @@
     </row>
     <row r="381">
       <c r="A381" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B381" t="inlineStr">
         <is>
-          <t>Monday, September 7, 2026</t>
+          <t>Sunday, September 6, 2026</t>
         </is>
       </c>
       <c r="C381" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D381" t="inlineStr">
         <is>
-          <t>08:00 AM – 09:00 AM</t>
+          <t>10:25 AM – 11:25 AM</t>
         </is>
       </c>
       <c r="E381" t="inlineStr">
@@ -21824,11 +21824,11 @@
         </is>
       </c>
       <c r="C383" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D383" t="inlineStr">
         <is>
-          <t>10:25 AM – 11:25 AM</t>
+          <t>08:00 AM – 09:00 AM</t>
         </is>
       </c>
       <c r="E383" t="inlineStr">
@@ -22328,11 +22328,11 @@
         </is>
       </c>
       <c r="C392" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D392" t="inlineStr">
         <is>
-          <t>10:25 AM – 11:25 AM</t>
+          <t>09:00 AM – 10:00 AM</t>
         </is>
       </c>
       <c r="E392" t="inlineStr">
@@ -22384,11 +22384,11 @@
         </is>
       </c>
       <c r="C393" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D393" t="inlineStr">
         <is>
-          <t>09:00 AM – 10:00 AM</t>
+          <t>08:00 AM – 09:00 AM</t>
         </is>
       </c>
       <c r="E393" t="inlineStr">
@@ -22440,11 +22440,11 @@
         </is>
       </c>
       <c r="C394" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D394" t="inlineStr">
         <is>
-          <t>08:00 AM – 09:00 AM</t>
+          <t>10:25 AM – 11:25 AM</t>
         </is>
       </c>
       <c r="E394" t="inlineStr">
@@ -22776,11 +22776,11 @@
         </is>
       </c>
       <c r="C400" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D400" t="inlineStr">
         <is>
-          <t>08:00 AM – 09:00 AM</t>
+          <t>09:00 AM – 10:00 AM</t>
         </is>
       </c>
       <c r="E400" t="inlineStr">
@@ -22832,11 +22832,11 @@
         </is>
       </c>
       <c r="C401" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D401" t="inlineStr">
         <is>
-          <t>10:25 AM – 11:25 AM</t>
+          <t>09:00 AM – 10:00 AM</t>
         </is>
       </c>
       <c r="E401" t="inlineStr">
@@ -22888,11 +22888,11 @@
         </is>
       </c>
       <c r="C402" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D402" t="inlineStr">
         <is>
-          <t>09:00 AM – 10:00 AM</t>
+          <t>08:00 AM – 09:00 AM</t>
         </is>
       </c>
       <c r="E402" t="inlineStr">
@@ -22944,11 +22944,11 @@
         </is>
       </c>
       <c r="C403" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D403" t="inlineStr">
         <is>
-          <t>08:00 AM – 09:00 AM</t>
+          <t>10:25 AM – 11:25 AM</t>
         </is>
       </c>
       <c r="E403" t="inlineStr">
@@ -23000,11 +23000,11 @@
         </is>
       </c>
       <c r="C404" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D404" t="inlineStr">
         <is>
-          <t>09:00 AM – 10:00 AM</t>
+          <t>08:00 AM – 09:00 AM</t>
         </is>
       </c>
       <c r="E404" t="inlineStr">
@@ -23224,11 +23224,11 @@
         </is>
       </c>
       <c r="C408" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D408" t="inlineStr">
         <is>
-          <t>10:25 AM – 11:25 AM</t>
+          <t>09:00 AM – 10:00 AM</t>
         </is>
       </c>
       <c r="E408" t="inlineStr">
@@ -23392,11 +23392,11 @@
         </is>
       </c>
       <c r="C411" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D411" t="inlineStr">
         <is>
-          <t>09:00 AM – 10:00 AM</t>
+          <t>08:00 AM – 09:00 AM</t>
         </is>
       </c>
       <c r="E411" t="inlineStr">
@@ -23448,11 +23448,11 @@
         </is>
       </c>
       <c r="C412" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D412" t="inlineStr">
         <is>
-          <t>08:00 AM – 09:00 AM</t>
+          <t>10:25 AM – 11:25 AM</t>
         </is>
       </c>
       <c r="E412" t="inlineStr">
@@ -23672,11 +23672,11 @@
         </is>
       </c>
       <c r="C416" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D416" t="inlineStr">
         <is>
-          <t>09:00 AM – 10:00 AM</t>
+          <t>08:00 AM – 09:00 AM</t>
         </is>
       </c>
       <c r="E416" t="inlineStr">
@@ -23728,11 +23728,11 @@
         </is>
       </c>
       <c r="C417" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D417" t="inlineStr">
         <is>
-          <t>10:25 AM – 11:25 AM</t>
+          <t>09:00 AM – 10:00 AM</t>
         </is>
       </c>
       <c r="E417" t="inlineStr">
@@ -23784,11 +23784,11 @@
         </is>
       </c>
       <c r="C418" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D418" t="inlineStr">
         <is>
-          <t>09:00 AM – 10:00 AM</t>
+          <t>08:00 AM – 09:00 AM</t>
         </is>
       </c>
       <c r="E418" t="inlineStr">
@@ -23832,19 +23832,19 @@
     </row>
     <row r="419">
       <c r="A419" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B419" t="inlineStr">
         <is>
-          <t>Thursday, September 3, 2026</t>
+          <t>Wednesday, September 2, 2026</t>
         </is>
       </c>
       <c r="C419" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D419" t="inlineStr">
         <is>
-          <t>08:00 AM – 09:00 AM</t>
+          <t>10:25 AM – 11:25 AM</t>
         </is>
       </c>
       <c r="E419" t="inlineStr">
@@ -23896,11 +23896,11 @@
         </is>
       </c>
       <c r="C420" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D420" t="inlineStr">
         <is>
-          <t>10:25 AM – 11:25 AM</t>
+          <t>09:00 AM – 10:00 AM</t>
         </is>
       </c>
       <c r="E420" t="inlineStr">
@@ -23952,11 +23952,11 @@
         </is>
       </c>
       <c r="C421" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D421" t="inlineStr">
         <is>
-          <t>09:00 AM – 10:00 AM</t>
+          <t>08:00 AM – 09:00 AM</t>
         </is>
       </c>
       <c r="E421" t="inlineStr">
@@ -23981,17 +23981,17 @@
       </c>
       <c r="I421" t="inlineStr">
         <is>
-          <t>Research Consultation</t>
+          <t>Qur'an</t>
         </is>
       </c>
       <c r="J421" t="inlineStr">
         <is>
-          <t>unassigned</t>
+          <t>tchr_dipatuan</t>
         </is>
       </c>
       <c r="K421" t="inlineStr">
         <is>
-          <t>Research Consultation</t>
+          <t>Alim Dipatuan</t>
         </is>
       </c>
       <c r="L421" t="n">
@@ -24000,54 +24000,54 @@
     </row>
     <row r="422">
       <c r="A422" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="B422" t="inlineStr">
         <is>
-          <t>Wednesday, September 2, 2026</t>
+          <t>Monday, September 7, 2026</t>
         </is>
       </c>
       <c r="C422" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D422" t="inlineStr">
         <is>
-          <t>08:00 AM – 09:00 AM</t>
+          <t>03:10 PM – 04:10 PM</t>
         </is>
       </c>
       <c r="E422" t="inlineStr">
         <is>
-          <t>GRADE 12 - SUHAYB AR-RUMI</t>
+          <t>GRADE 7 - USAMA IBN ZAYD (1ST SHIFT) GIRLS</t>
         </is>
       </c>
       <c r="F422" t="inlineStr">
         <is>
-          <t>Senior High School</t>
+          <t>Junior High School</t>
         </is>
       </c>
       <c r="G422" t="inlineStr">
         <is>
-          <t>Grade 12</t>
+          <t>Grade 7</t>
         </is>
       </c>
       <c r="H422" t="inlineStr">
         <is>
-          <t>F2F</t>
+          <t>ODL - 1ST SHIFT</t>
         </is>
       </c>
       <c r="I422" t="inlineStr">
         <is>
-          <t>Qur'an</t>
+          <t>GMRC / Values</t>
         </is>
       </c>
       <c r="J422" t="inlineStr">
         <is>
-          <t>tchr_dipatuan</t>
+          <t>tchr_silfah</t>
         </is>
       </c>
       <c r="K422" t="inlineStr">
         <is>
-          <t>Alim Dipatuan</t>
+          <t>Ustadha Silfah</t>
         </is>
       </c>
       <c r="L422" t="n">
@@ -24056,19 +24056,19 @@
     </row>
     <row r="423">
       <c r="A423" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B423" t="inlineStr">
         <is>
-          <t>Monday, September 7, 2026</t>
+          <t>Sunday, September 6, 2026</t>
         </is>
       </c>
       <c r="C423" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D423" t="inlineStr">
         <is>
-          <t>01:50 PM – 02:50 PM</t>
+          <t>03:10 PM – 04:10 PM</t>
         </is>
       </c>
       <c r="E423" t="inlineStr">
@@ -24093,17 +24093,17 @@
       </c>
       <c r="I423" t="inlineStr">
         <is>
-          <t>GMRC / Values</t>
+          <t>Science</t>
         </is>
       </c>
       <c r="J423" t="inlineStr">
         <is>
-          <t>tchr_silfah</t>
+          <t>tchr_aniah</t>
         </is>
       </c>
       <c r="K423" t="inlineStr">
         <is>
-          <t>Ustadha Silfah</t>
+          <t>Teacher Aniah</t>
         </is>
       </c>
       <c r="L423" t="n">
@@ -24112,19 +24112,19 @@
     </row>
     <row r="424">
       <c r="A424" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="B424" t="inlineStr">
         <is>
-          <t>Monday, September 7, 2026</t>
+          <t>Thursday, September 3, 2026</t>
         </is>
       </c>
       <c r="C424" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D424" t="inlineStr">
         <is>
-          <t>12:40 PM – 01:40 PM</t>
+          <t>01:50 PM – 02:50 PM</t>
         </is>
       </c>
       <c r="E424" t="inlineStr">
@@ -24149,17 +24149,17 @@
       </c>
       <c r="I424" t="inlineStr">
         <is>
-          <t>Science</t>
+          <t>Qur'an</t>
         </is>
       </c>
       <c r="J424" t="inlineStr">
         <is>
-          <t>tchr_aniah</t>
+          <t>tchr_jaisam</t>
         </is>
       </c>
       <c r="K424" t="inlineStr">
         <is>
-          <t>Teacher Aniah</t>
+          <t>Ustadh Jaisam</t>
         </is>
       </c>
       <c r="L424" t="n">
@@ -24205,17 +24205,17 @@
       </c>
       <c r="I425" t="inlineStr">
         <is>
-          <t>Qur'an</t>
+          <t>Araling Panlipunan (AP)</t>
         </is>
       </c>
       <c r="J425" t="inlineStr">
         <is>
-          <t>tchr_jaisam</t>
+          <t>tchr_franchette</t>
         </is>
       </c>
       <c r="K425" t="inlineStr">
         <is>
-          <t>Ustadh Jaisam</t>
+          <t>Teacher Franchette</t>
         </is>
       </c>
       <c r="L425" t="n">
@@ -24224,19 +24224,19 @@
     </row>
     <row r="426">
       <c r="A426" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="B426" t="inlineStr">
         <is>
-          <t>Sunday, September 6, 2026</t>
+          <t>Wednesday, September 2, 2026</t>
         </is>
       </c>
       <c r="C426" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D426" t="inlineStr">
         <is>
-          <t>03:10 PM – 04:10 PM</t>
+          <t>01:50 PM – 02:50 PM</t>
         </is>
       </c>
       <c r="E426" t="inlineStr">
@@ -24261,17 +24261,17 @@
       </c>
       <c r="I426" t="inlineStr">
         <is>
-          <t>Araling Panlipunan (AP)</t>
+          <t>English</t>
         </is>
       </c>
       <c r="J426" t="inlineStr">
         <is>
-          <t>tchr_franchette</t>
+          <t>tchr_jairah</t>
         </is>
       </c>
       <c r="K426" t="inlineStr">
         <is>
-          <t>Teacher Franchette</t>
+          <t>Teacher Jairah</t>
         </is>
       </c>
       <c r="L426" t="n">
@@ -24288,11 +24288,11 @@
         </is>
       </c>
       <c r="C427" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D427" t="inlineStr">
         <is>
-          <t>01:50 PM – 02:50 PM</t>
+          <t>12:40 PM – 01:40 PM</t>
         </is>
       </c>
       <c r="E427" t="inlineStr">
@@ -24317,17 +24317,17 @@
       </c>
       <c r="I427" t="inlineStr">
         <is>
-          <t>English</t>
+          <t>Technology and Livelihood Education</t>
         </is>
       </c>
       <c r="J427" t="inlineStr">
         <is>
-          <t>tchr_jairah</t>
+          <t>tchr_halnaisa</t>
         </is>
       </c>
       <c r="K427" t="inlineStr">
         <is>
-          <t>Teacher Jairah</t>
+          <t>Teacher Halnaisa</t>
         </is>
       </c>
       <c r="L427" t="n">
@@ -24336,19 +24336,19 @@
     </row>
     <row r="428">
       <c r="A428" t="n">
+        <v>1</v>
+      </c>
+      <c r="B428" t="inlineStr">
+        <is>
+          <t>Wednesday, September 2, 2026</t>
+        </is>
+      </c>
+      <c r="C428" t="n">
         <v>3</v>
       </c>
-      <c r="B428" t="inlineStr">
-        <is>
-          <t>Sunday, September 6, 2026</t>
-        </is>
-      </c>
-      <c r="C428" t="n">
-        <v>1</v>
-      </c>
       <c r="D428" t="inlineStr">
         <is>
-          <t>12:40 PM – 01:40 PM</t>
+          <t>03:10 PM – 04:10 PM</t>
         </is>
       </c>
       <c r="E428" t="inlineStr">
@@ -24373,17 +24373,17 @@
       </c>
       <c r="I428" t="inlineStr">
         <is>
-          <t>Technology and Livelihood Education</t>
+          <t>Arabic Language</t>
         </is>
       </c>
       <c r="J428" t="inlineStr">
         <is>
-          <t>tchr_halnaisa</t>
+          <t>tchr_ali</t>
         </is>
       </c>
       <c r="K428" t="inlineStr">
         <is>
-          <t>Teacher Halnaisa</t>
+          <t>Ustadz Ali</t>
         </is>
       </c>
       <c r="L428" t="n">
@@ -24400,11 +24400,11 @@
         </is>
       </c>
       <c r="C429" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D429" t="inlineStr">
         <is>
-          <t>01:50 PM – 02:50 PM</t>
+          <t>12:40 PM – 01:40 PM</t>
         </is>
       </c>
       <c r="E429" t="inlineStr">
@@ -24429,17 +24429,17 @@
       </c>
       <c r="I429" t="inlineStr">
         <is>
-          <t>Arabic Language</t>
+          <t>SHAF</t>
         </is>
       </c>
       <c r="J429" t="inlineStr">
         <is>
-          <t>tchr_ali</t>
+          <t>tchr_samsuddin</t>
         </is>
       </c>
       <c r="K429" t="inlineStr">
         <is>
-          <t>Ustadz Ali</t>
+          <t>Alim Samsuddin</t>
         </is>
       </c>
       <c r="L429" t="n">
@@ -24448,11 +24448,11 @@
     </row>
     <row r="430">
       <c r="A430" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="B430" t="inlineStr">
         <is>
-          <t>Thursday, September 3, 2026</t>
+          <t>Monday, September 7, 2026</t>
         </is>
       </c>
       <c r="C430" t="n">
@@ -24460,7 +24460,7 @@
       </c>
       <c r="D430" t="inlineStr">
         <is>
-          <t>12:40 PM – 01:40 PM</t>
+          <t>12:40 PM – 02:50 PM</t>
         </is>
       </c>
       <c r="E430" t="inlineStr">
@@ -24485,21 +24485,21 @@
       </c>
       <c r="I430" t="inlineStr">
         <is>
-          <t>SHAF</t>
+          <t>Mathematics</t>
         </is>
       </c>
       <c r="J430" t="inlineStr">
         <is>
-          <t>tchr_samsuddin</t>
+          <t>tchr_ethel</t>
         </is>
       </c>
       <c r="K430" t="inlineStr">
         <is>
-          <t>Alim Samsuddin</t>
+          <t>Teacher Ethel</t>
         </is>
       </c>
       <c r="L430" t="n">
-        <v>60</v>
+        <v>120</v>
       </c>
     </row>
     <row r="431">
@@ -24512,11 +24512,11 @@
         </is>
       </c>
       <c r="C431" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D431" t="inlineStr">
         <is>
-          <t>12:40 PM – 02:50 PM</t>
+          <t>12:40 PM – 01:40 PM</t>
         </is>
       </c>
       <c r="E431" t="inlineStr">
@@ -24541,30 +24541,30 @@
       </c>
       <c r="I431" t="inlineStr">
         <is>
-          <t>Mathematics</t>
+          <t>Filipino</t>
         </is>
       </c>
       <c r="J431" t="inlineStr">
         <is>
-          <t>tchr_ethel</t>
+          <t>tchr_sophia</t>
         </is>
       </c>
       <c r="K431" t="inlineStr">
         <is>
-          <t>Teacher Ethel</t>
+          <t>Teacher Sophia</t>
         </is>
       </c>
       <c r="L431" t="n">
-        <v>120</v>
+        <v>60</v>
       </c>
     </row>
     <row r="432">
       <c r="A432" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="B432" t="inlineStr">
         <is>
-          <t>Wednesday, September 2, 2026</t>
+          <t>Monday, September 7, 2026</t>
         </is>
       </c>
       <c r="C432" t="n">
@@ -24577,7 +24577,7 @@
       </c>
       <c r="E432" t="inlineStr">
         <is>
-          <t>GRADE 7 - USAMA IBN ZAYD (1ST SHIFT) GIRLS</t>
+          <t>GRADE 7 - ABU SUFYAN IBN AL-HARITH (1ST SHIFT) BOYS</t>
         </is>
       </c>
       <c r="F432" t="inlineStr">
@@ -24597,17 +24597,17 @@
       </c>
       <c r="I432" t="inlineStr">
         <is>
-          <t>Filipino</t>
+          <t>Technology and Livelihood Education</t>
         </is>
       </c>
       <c r="J432" t="inlineStr">
         <is>
-          <t>tchr_sophia</t>
+          <t>tchr_halnaisa</t>
         </is>
       </c>
       <c r="K432" t="inlineStr">
         <is>
-          <t>Teacher Sophia</t>
+          <t>Teacher Halnaisa</t>
         </is>
       </c>
       <c r="L432" t="n">
@@ -24653,17 +24653,17 @@
       </c>
       <c r="I433" t="inlineStr">
         <is>
-          <t>Technology and Livelihood Education</t>
+          <t>English</t>
         </is>
       </c>
       <c r="J433" t="inlineStr">
         <is>
-          <t>tchr_halnaisa</t>
+          <t>tchr_jairah</t>
         </is>
       </c>
       <c r="K433" t="inlineStr">
         <is>
-          <t>Teacher Halnaisa</t>
+          <t>Teacher Jairah</t>
         </is>
       </c>
       <c r="L433" t="n">
@@ -24672,19 +24672,19 @@
     </row>
     <row r="434">
       <c r="A434" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="B434" t="inlineStr">
         <is>
-          <t>Monday, September 7, 2026</t>
+          <t>Thursday, September 3, 2026</t>
         </is>
       </c>
       <c r="C434" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D434" t="inlineStr">
         <is>
-          <t>12:40 PM – 01:40 PM</t>
+          <t>03:10 PM – 04:10 PM</t>
         </is>
       </c>
       <c r="E434" t="inlineStr">
@@ -24709,17 +24709,17 @@
       </c>
       <c r="I434" t="inlineStr">
         <is>
-          <t>English</t>
+          <t>Qur'an</t>
         </is>
       </c>
       <c r="J434" t="inlineStr">
         <is>
-          <t>tchr_jairah</t>
+          <t>tchr_jaisam</t>
         </is>
       </c>
       <c r="K434" t="inlineStr">
         <is>
-          <t>Teacher Jairah</t>
+          <t>Ustadh Jaisam</t>
         </is>
       </c>
       <c r="L434" t="n">
@@ -24728,11 +24728,11 @@
     </row>
     <row r="435">
       <c r="A435" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B435" t="inlineStr">
         <is>
-          <t>Thursday, September 3, 2026</t>
+          <t>Sunday, September 6, 2026</t>
         </is>
       </c>
       <c r="C435" t="n">
@@ -24765,17 +24765,17 @@
       </c>
       <c r="I435" t="inlineStr">
         <is>
-          <t>Qur'an</t>
+          <t>Science</t>
         </is>
       </c>
       <c r="J435" t="inlineStr">
         <is>
-          <t>tchr_jaisam</t>
+          <t>tchr_shirehan</t>
         </is>
       </c>
       <c r="K435" t="inlineStr">
         <is>
-          <t>Ustadh Jaisam</t>
+          <t>Teacher Shirehan</t>
         </is>
       </c>
       <c r="L435" t="n">
@@ -24792,11 +24792,11 @@
         </is>
       </c>
       <c r="C436" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D436" t="inlineStr">
         <is>
-          <t>03:10 PM – 04:10 PM</t>
+          <t>12:40 PM – 02:50 PM</t>
         </is>
       </c>
       <c r="E436" t="inlineStr">
@@ -24821,38 +24821,38 @@
       </c>
       <c r="I436" t="inlineStr">
         <is>
-          <t>Science</t>
+          <t>Mathematics</t>
         </is>
       </c>
       <c r="J436" t="inlineStr">
         <is>
-          <t>tchr_shirehan</t>
+          <t>tchr_ethel</t>
         </is>
       </c>
       <c r="K436" t="inlineStr">
         <is>
-          <t>Teacher Shirehan</t>
+          <t>Teacher Ethel</t>
         </is>
       </c>
       <c r="L436" t="n">
-        <v>60</v>
+        <v>120</v>
       </c>
     </row>
     <row r="437">
       <c r="A437" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B437" t="inlineStr">
         <is>
-          <t>Sunday, September 6, 2026</t>
+          <t>Thursday, September 3, 2026</t>
         </is>
       </c>
       <c r="C437" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D437" t="inlineStr">
         <is>
-          <t>12:40 PM – 02:50 PM</t>
+          <t>01:50 PM – 02:50 PM</t>
         </is>
       </c>
       <c r="E437" t="inlineStr">
@@ -24877,21 +24877,21 @@
       </c>
       <c r="I437" t="inlineStr">
         <is>
-          <t>Mathematics</t>
+          <t>GMRC / Values</t>
         </is>
       </c>
       <c r="J437" t="inlineStr">
         <is>
-          <t>tchr_ethel</t>
+          <t>tchr_silfah</t>
         </is>
       </c>
       <c r="K437" t="inlineStr">
         <is>
-          <t>Teacher Ethel</t>
+          <t>Ustadha Silfah</t>
         </is>
       </c>
       <c r="L437" t="n">
-        <v>120</v>
+        <v>60</v>
       </c>
     </row>
     <row r="438">
@@ -24904,11 +24904,11 @@
         </is>
       </c>
       <c r="C438" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D438" t="inlineStr">
         <is>
-          <t>01:50 PM – 02:50 PM</t>
+          <t>12:40 PM – 01:40 PM</t>
         </is>
       </c>
       <c r="E438" t="inlineStr">
@@ -24933,17 +24933,17 @@
       </c>
       <c r="I438" t="inlineStr">
         <is>
-          <t>GMRC / Values</t>
+          <t>Araling Panlipunan (AP)</t>
         </is>
       </c>
       <c r="J438" t="inlineStr">
         <is>
-          <t>tchr_silfah</t>
+          <t>tchr_franchette</t>
         </is>
       </c>
       <c r="K438" t="inlineStr">
         <is>
-          <t>Ustadha Silfah</t>
+          <t>Teacher Franchette</t>
         </is>
       </c>
       <c r="L438" t="n">
@@ -24952,11 +24952,11 @@
     </row>
     <row r="439">
       <c r="A439" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B439" t="inlineStr">
         <is>
-          <t>Thursday, September 3, 2026</t>
+          <t>Wednesday, September 2, 2026</t>
         </is>
       </c>
       <c r="C439" t="n">
@@ -24989,17 +24989,17 @@
       </c>
       <c r="I439" t="inlineStr">
         <is>
-          <t>Araling Panlipunan (AP)</t>
+          <t>Filipino</t>
         </is>
       </c>
       <c r="J439" t="inlineStr">
         <is>
-          <t>tchr_franchette</t>
+          <t>tchr_sophia</t>
         </is>
       </c>
       <c r="K439" t="inlineStr">
         <is>
-          <t>Teacher Franchette</t>
+          <t>Teacher Sophia</t>
         </is>
       </c>
       <c r="L439" t="n">
@@ -25016,11 +25016,11 @@
         </is>
       </c>
       <c r="C440" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D440" t="inlineStr">
         <is>
-          <t>12:40 PM – 01:40 PM</t>
+          <t>03:10 PM – 04:10 PM</t>
         </is>
       </c>
       <c r="E440" t="inlineStr">
@@ -25045,17 +25045,17 @@
       </c>
       <c r="I440" t="inlineStr">
         <is>
-          <t>Filipino</t>
+          <t>Arabic Language</t>
         </is>
       </c>
       <c r="J440" t="inlineStr">
         <is>
-          <t>tchr_sophia</t>
+          <t>tchr_ali</t>
         </is>
       </c>
       <c r="K440" t="inlineStr">
         <is>
-          <t>Teacher Sophia</t>
+          <t>Ustadz Ali</t>
         </is>
       </c>
       <c r="L440" t="n">
@@ -25072,11 +25072,11 @@
         </is>
       </c>
       <c r="C441" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D441" t="inlineStr">
         <is>
-          <t>03:10 PM – 04:10 PM</t>
+          <t>01:50 PM – 02:50 PM</t>
         </is>
       </c>
       <c r="E441" t="inlineStr">
@@ -25101,17 +25101,17 @@
       </c>
       <c r="I441" t="inlineStr">
         <is>
-          <t>Arabic Language</t>
+          <t>SHAF</t>
         </is>
       </c>
       <c r="J441" t="inlineStr">
         <is>
-          <t>tchr_ali</t>
+          <t>tchr_samsuddin</t>
         </is>
       </c>
       <c r="K441" t="inlineStr">
         <is>
-          <t>Ustadz Ali</t>
+          <t>Alim Samsuddin</t>
         </is>
       </c>
       <c r="L441" t="n">
@@ -25120,11 +25120,11 @@
     </row>
     <row r="442">
       <c r="A442" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="B442" t="inlineStr">
         <is>
-          <t>Wednesday, September 2, 2026</t>
+          <t>Sunday, September 6, 2026</t>
         </is>
       </c>
       <c r="C442" t="n">
@@ -25137,7 +25137,7 @@
       </c>
       <c r="E442" t="inlineStr">
         <is>
-          <t>GRADE 7 - ABU SUFYAN IBN AL-HARITH (1ST SHIFT) BOYS</t>
+          <t>GRADE 8 - SA'AD IBN MUA'DH (1ST SHIFT) - GIRLS</t>
         </is>
       </c>
       <c r="F442" t="inlineStr">
@@ -25147,7 +25147,7 @@
       </c>
       <c r="G442" t="inlineStr">
         <is>
-          <t>Grade 7</t>
+          <t>Grade 8</t>
         </is>
       </c>
       <c r="H442" t="inlineStr">
@@ -25157,17 +25157,17 @@
       </c>
       <c r="I442" t="inlineStr">
         <is>
-          <t>SHAF</t>
+          <t>Science</t>
         </is>
       </c>
       <c r="J442" t="inlineStr">
         <is>
-          <t>tchr_samsuddin</t>
+          <t>tchr_radzmia</t>
         </is>
       </c>
       <c r="K442" t="inlineStr">
         <is>
-          <t>Alim Samsuddin</t>
+          <t>Teacher Radzmia</t>
         </is>
       </c>
       <c r="L442" t="n">
@@ -25176,19 +25176,19 @@
     </row>
     <row r="443">
       <c r="A443" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B443" t="inlineStr">
         <is>
-          <t>Sunday, September 6, 2026</t>
+          <t>Monday, September 7, 2026</t>
         </is>
       </c>
       <c r="C443" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D443" t="inlineStr">
         <is>
-          <t>03:10 PM – 04:10 PM</t>
+          <t>12:40 PM – 02:50 PM</t>
         </is>
       </c>
       <c r="E443" t="inlineStr">
@@ -25213,38 +25213,38 @@
       </c>
       <c r="I443" t="inlineStr">
         <is>
-          <t>Science</t>
+          <t>Mathematics</t>
         </is>
       </c>
       <c r="J443" t="inlineStr">
         <is>
-          <t>tchr_radzmia</t>
+          <t>tchr_hannah</t>
         </is>
       </c>
       <c r="K443" t="inlineStr">
         <is>
-          <t>Teacher Radzmia</t>
+          <t>Teacher Hannah</t>
         </is>
       </c>
       <c r="L443" t="n">
-        <v>60</v>
+        <v>120</v>
       </c>
     </row>
     <row r="444">
       <c r="A444" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="B444" t="inlineStr">
         <is>
-          <t>Monday, September 7, 2026</t>
+          <t>Thursday, September 3, 2026</t>
         </is>
       </c>
       <c r="C444" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D444" t="inlineStr">
         <is>
-          <t>12:40 PM – 02:50 PM</t>
+          <t>03:10 PM – 04:10 PM</t>
         </is>
       </c>
       <c r="E444" t="inlineStr">
@@ -25269,38 +25269,38 @@
       </c>
       <c r="I444" t="inlineStr">
         <is>
-          <t>Mathematics</t>
+          <t>GMRC / Values</t>
         </is>
       </c>
       <c r="J444" t="inlineStr">
         <is>
-          <t>tchr_hannah</t>
+          <t>tchr_wardah</t>
         </is>
       </c>
       <c r="K444" t="inlineStr">
         <is>
-          <t>Teacher Hannah</t>
+          <t>Teacher Wardah</t>
         </is>
       </c>
       <c r="L444" t="n">
-        <v>120</v>
+        <v>60</v>
       </c>
     </row>
     <row r="445">
       <c r="A445" t="n">
+        <v>4</v>
+      </c>
+      <c r="B445" t="inlineStr">
+        <is>
+          <t>Monday, September 7, 2026</t>
+        </is>
+      </c>
+      <c r="C445" t="n">
         <v>3</v>
       </c>
-      <c r="B445" t="inlineStr">
-        <is>
-          <t>Sunday, September 6, 2026</t>
-        </is>
-      </c>
-      <c r="C445" t="n">
-        <v>2</v>
-      </c>
       <c r="D445" t="inlineStr">
         <is>
-          <t>01:50 PM – 02:50 PM</t>
+          <t>03:10 PM – 04:10 PM</t>
         </is>
       </c>
       <c r="E445" t="inlineStr">
@@ -25325,17 +25325,17 @@
       </c>
       <c r="I445" t="inlineStr">
         <is>
-          <t>GMRC / Values</t>
+          <t>Araling Panlipunan (AP)</t>
         </is>
       </c>
       <c r="J445" t="inlineStr">
         <is>
-          <t>tchr_wardah</t>
+          <t>tchr_franchette</t>
         </is>
       </c>
       <c r="K445" t="inlineStr">
         <is>
-          <t>Teacher Wardah</t>
+          <t>Teacher Franchette</t>
         </is>
       </c>
       <c r="L445" t="n">
@@ -25352,11 +25352,11 @@
         </is>
       </c>
       <c r="C446" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D446" t="inlineStr">
         <is>
-          <t>12:40 PM – 01:40 PM</t>
+          <t>03:10 PM – 04:10 PM</t>
         </is>
       </c>
       <c r="E446" t="inlineStr">
@@ -25381,17 +25381,17 @@
       </c>
       <c r="I446" t="inlineStr">
         <is>
-          <t>Araling Panlipunan (AP)</t>
+          <t>English</t>
         </is>
       </c>
       <c r="J446" t="inlineStr">
         <is>
-          <t>tchr_franchette</t>
+          <t>tchr_jairah</t>
         </is>
       </c>
       <c r="K446" t="inlineStr">
         <is>
-          <t>Teacher Franchette</t>
+          <t>Teacher Jairah</t>
         </is>
       </c>
       <c r="L446" t="n">
@@ -25408,11 +25408,11 @@
         </is>
       </c>
       <c r="C447" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D447" t="inlineStr">
         <is>
-          <t>03:10 PM – 04:10 PM</t>
+          <t>01:50 PM – 02:50 PM</t>
         </is>
       </c>
       <c r="E447" t="inlineStr">
@@ -25437,17 +25437,17 @@
       </c>
       <c r="I447" t="inlineStr">
         <is>
-          <t>English</t>
+          <t>Filipino</t>
         </is>
       </c>
       <c r="J447" t="inlineStr">
         <is>
-          <t>tchr_jairah</t>
+          <t>tchr_sophia</t>
         </is>
       </c>
       <c r="K447" t="inlineStr">
         <is>
-          <t>Teacher Jairah</t>
+          <t>Teacher Sophia</t>
         </is>
       </c>
       <c r="L447" t="n">
@@ -25464,11 +25464,11 @@
         </is>
       </c>
       <c r="C448" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D448" t="inlineStr">
         <is>
-          <t>01:50 PM – 02:50 PM</t>
+          <t>12:40 PM – 01:40 PM</t>
         </is>
       </c>
       <c r="E448" t="inlineStr">
@@ -25493,17 +25493,17 @@
       </c>
       <c r="I448" t="inlineStr">
         <is>
-          <t>Filipino</t>
+          <t>Technology and Livelihood Education</t>
         </is>
       </c>
       <c r="J448" t="inlineStr">
         <is>
-          <t>tchr_sophia</t>
+          <t>tchr_halnaisa</t>
         </is>
       </c>
       <c r="K448" t="inlineStr">
         <is>
-          <t>Teacher Sophia</t>
+          <t>Teacher Halnaisa</t>
         </is>
       </c>
       <c r="L448" t="n">
@@ -25512,19 +25512,19 @@
     </row>
     <row r="449">
       <c r="A449" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B449" t="inlineStr">
         <is>
-          <t>Thursday, September 3, 2026</t>
+          <t>Wednesday, September 2, 2026</t>
         </is>
       </c>
       <c r="C449" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D449" t="inlineStr">
         <is>
-          <t>12:40 PM – 01:40 PM</t>
+          <t>03:10 PM – 04:10 PM</t>
         </is>
       </c>
       <c r="E449" t="inlineStr">
@@ -25549,17 +25549,17 @@
       </c>
       <c r="I449" t="inlineStr">
         <is>
-          <t>Technology and Livelihood Education</t>
+          <t>SHAF</t>
         </is>
       </c>
       <c r="J449" t="inlineStr">
         <is>
-          <t>tchr_halnaisa</t>
+          <t>tchr_samsuddin</t>
         </is>
       </c>
       <c r="K449" t="inlineStr">
         <is>
-          <t>Teacher Halnaisa</t>
+          <t>Alim Samsuddin</t>
         </is>
       </c>
       <c r="L449" t="n">
@@ -25576,11 +25576,11 @@
         </is>
       </c>
       <c r="C450" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D450" t="inlineStr">
         <is>
-          <t>03:10 PM – 04:10 PM</t>
+          <t>01:50 PM – 02:50 PM</t>
         </is>
       </c>
       <c r="E450" t="inlineStr">
@@ -25605,17 +25605,17 @@
       </c>
       <c r="I450" t="inlineStr">
         <is>
-          <t>SHAF</t>
+          <t>Qur'an</t>
         </is>
       </c>
       <c r="J450" t="inlineStr">
         <is>
-          <t>tchr_samsuddin</t>
+          <t>tchr_jaisam</t>
         </is>
       </c>
       <c r="K450" t="inlineStr">
         <is>
-          <t>Alim Samsuddin</t>
+          <t>Ustadh Jaisam</t>
         </is>
       </c>
       <c r="L450" t="n">
@@ -25632,11 +25632,11 @@
         </is>
       </c>
       <c r="C451" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D451" t="inlineStr">
         <is>
-          <t>01:50 PM – 02:50 PM</t>
+          <t>12:40 PM – 01:40 PM</t>
         </is>
       </c>
       <c r="E451" t="inlineStr">
@@ -25661,17 +25661,17 @@
       </c>
       <c r="I451" t="inlineStr">
         <is>
-          <t>Qur'an</t>
+          <t>Arabic Language</t>
         </is>
       </c>
       <c r="J451" t="inlineStr">
         <is>
-          <t>tchr_jaisam</t>
+          <t>tchr_ali</t>
         </is>
       </c>
       <c r="K451" t="inlineStr">
         <is>
-          <t>Ustadh Jaisam</t>
+          <t>Ustadz Ali</t>
         </is>
       </c>
       <c r="L451" t="n">
@@ -25680,24 +25680,24 @@
     </row>
     <row r="452">
       <c r="A452" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B452" t="inlineStr">
         <is>
-          <t>Wednesday, September 2, 2026</t>
+          <t>Thursday, September 3, 2026</t>
         </is>
       </c>
       <c r="C452" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D452" t="inlineStr">
         <is>
-          <t>12:40 PM – 01:40 PM</t>
+          <t>03:10 PM – 04:10 PM</t>
         </is>
       </c>
       <c r="E452" t="inlineStr">
         <is>
-          <t>GRADE 8 - SA'AD IBN MUA'DH (1ST SHIFT) - GIRLS</t>
+          <t>GRADE 9 - ABU HURAYRAH (1ST SHIFT) GIRLS</t>
         </is>
       </c>
       <c r="F452" t="inlineStr">
@@ -25707,7 +25707,7 @@
       </c>
       <c r="G452" t="inlineStr">
         <is>
-          <t>Grade 8</t>
+          <t>Grade 9</t>
         </is>
       </c>
       <c r="H452" t="inlineStr">
@@ -25717,17 +25717,17 @@
       </c>
       <c r="I452" t="inlineStr">
         <is>
-          <t>Arabic Language</t>
+          <t>SHAF</t>
         </is>
       </c>
       <c r="J452" t="inlineStr">
         <is>
-          <t>tchr_ali</t>
+          <t>tchr_samsuddin</t>
         </is>
       </c>
       <c r="K452" t="inlineStr">
         <is>
-          <t>Ustadz Ali</t>
+          <t>Alim Samsuddin</t>
         </is>
       </c>
       <c r="L452" t="n">
@@ -25744,11 +25744,11 @@
         </is>
       </c>
       <c r="C453" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D453" t="inlineStr">
         <is>
-          <t>03:10 PM – 04:10 PM</t>
+          <t>12:40 PM – 01:40 PM</t>
         </is>
       </c>
       <c r="E453" t="inlineStr">
@@ -25773,17 +25773,17 @@
       </c>
       <c r="I453" t="inlineStr">
         <is>
-          <t>SHAF</t>
+          <t>Qur'an</t>
         </is>
       </c>
       <c r="J453" t="inlineStr">
         <is>
-          <t>tchr_samsuddin</t>
+          <t>tchr_abdulwahab</t>
         </is>
       </c>
       <c r="K453" t="inlineStr">
         <is>
-          <t>Alim Samsuddin</t>
+          <t>Alim Abdulwahab</t>
         </is>
       </c>
       <c r="L453" t="n">
@@ -25792,11 +25792,11 @@
     </row>
     <row r="454">
       <c r="A454" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="B454" t="inlineStr">
         <is>
-          <t>Thursday, September 3, 2026</t>
+          <t>Monday, September 7, 2026</t>
         </is>
       </c>
       <c r="C454" t="n">
@@ -25804,7 +25804,7 @@
       </c>
       <c r="D454" t="inlineStr">
         <is>
-          <t>12:40 PM – 01:40 PM</t>
+          <t>12:40 PM – 02:50 PM</t>
         </is>
       </c>
       <c r="E454" t="inlineStr">
@@ -25829,38 +25829,38 @@
       </c>
       <c r="I454" t="inlineStr">
         <is>
-          <t>Qur'an</t>
+          <t>Mathematics</t>
         </is>
       </c>
       <c r="J454" t="inlineStr">
         <is>
-          <t>tchr_abdulwahab</t>
+          <t>tchr_jhelyn</t>
         </is>
       </c>
       <c r="K454" t="inlineStr">
         <is>
-          <t>Alim Abdulwahab</t>
+          <t>Teacher Jhelyn</t>
         </is>
       </c>
       <c r="L454" t="n">
-        <v>60</v>
+        <v>120</v>
       </c>
     </row>
     <row r="455">
       <c r="A455" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B455" t="inlineStr">
         <is>
-          <t>Monday, September 7, 2026</t>
+          <t>Sunday, September 6, 2026</t>
         </is>
       </c>
       <c r="C455" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D455" t="inlineStr">
         <is>
-          <t>12:40 PM – 02:50 PM</t>
+          <t>03:10 PM – 04:10 PM</t>
         </is>
       </c>
       <c r="E455" t="inlineStr">
@@ -25885,21 +25885,21 @@
       </c>
       <c r="I455" t="inlineStr">
         <is>
-          <t>Mathematics</t>
+          <t>Technology and Livelihood Education</t>
         </is>
       </c>
       <c r="J455" t="inlineStr">
         <is>
-          <t>tchr_jhelyn</t>
+          <t>tchr_angeleni</t>
         </is>
       </c>
       <c r="K455" t="inlineStr">
         <is>
-          <t>Teacher Jhelyn</t>
+          <t>Teacher Angeleni</t>
         </is>
       </c>
       <c r="L455" t="n">
-        <v>120</v>
+        <v>60</v>
       </c>
     </row>
     <row r="456">
@@ -25912,11 +25912,11 @@
         </is>
       </c>
       <c r="C456" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D456" t="inlineStr">
         <is>
-          <t>03:10 PM – 04:10 PM</t>
+          <t>12:40 PM – 01:40 PM</t>
         </is>
       </c>
       <c r="E456" t="inlineStr">
@@ -25941,17 +25941,17 @@
       </c>
       <c r="I456" t="inlineStr">
         <is>
-          <t>Technology and Livelihood Education</t>
+          <t>Science</t>
         </is>
       </c>
       <c r="J456" t="inlineStr">
         <is>
-          <t>tchr_angeleni</t>
+          <t>tchr_sophia</t>
         </is>
       </c>
       <c r="K456" t="inlineStr">
         <is>
-          <t>Teacher Angeleni</t>
+          <t>Teacher Sophia</t>
         </is>
       </c>
       <c r="L456" t="n">
@@ -25960,19 +25960,19 @@
     </row>
     <row r="457">
       <c r="A457" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B457" t="inlineStr">
         <is>
-          <t>Sunday, September 6, 2026</t>
+          <t>Thursday, September 3, 2026</t>
         </is>
       </c>
       <c r="C457" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D457" t="inlineStr">
         <is>
-          <t>12:40 PM – 01:40 PM</t>
+          <t>01:50 PM – 02:50 PM</t>
         </is>
       </c>
       <c r="E457" t="inlineStr">
@@ -25997,17 +25997,17 @@
       </c>
       <c r="I457" t="inlineStr">
         <is>
-          <t>Science</t>
+          <t>Arabic Language</t>
         </is>
       </c>
       <c r="J457" t="inlineStr">
         <is>
-          <t>tchr_sophia</t>
+          <t>tchr_raslina</t>
         </is>
       </c>
       <c r="K457" t="inlineStr">
         <is>
-          <t>Teacher Sophia</t>
+          <t>Ustadh Raslina</t>
         </is>
       </c>
       <c r="L457" t="n">
@@ -26016,19 +26016,19 @@
     </row>
     <row r="458">
       <c r="A458" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B458" t="inlineStr">
         <is>
-          <t>Thursday, September 3, 2026</t>
+          <t>Wednesday, September 2, 2026</t>
         </is>
       </c>
       <c r="C458" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D458" t="inlineStr">
         <is>
-          <t>01:50 PM – 02:50 PM</t>
+          <t>03:10 PM – 04:10 PM</t>
         </is>
       </c>
       <c r="E458" t="inlineStr">
@@ -26053,17 +26053,17 @@
       </c>
       <c r="I458" t="inlineStr">
         <is>
-          <t>Arabic Language</t>
+          <t>English</t>
         </is>
       </c>
       <c r="J458" t="inlineStr">
         <is>
-          <t>tchr_raslina</t>
+          <t>tchr_norhaima</t>
         </is>
       </c>
       <c r="K458" t="inlineStr">
         <is>
-          <t>Ustadh Raslina</t>
+          <t>Teacher Norhaima</t>
         </is>
       </c>
       <c r="L458" t="n">
@@ -26080,11 +26080,11 @@
         </is>
       </c>
       <c r="C459" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D459" t="inlineStr">
         <is>
-          <t>03:10 PM – 04:10 PM</t>
+          <t>12:40 PM – 01:40 PM</t>
         </is>
       </c>
       <c r="E459" t="inlineStr">
@@ -26109,17 +26109,17 @@
       </c>
       <c r="I459" t="inlineStr">
         <is>
-          <t>English</t>
+          <t>Araling Panlipunan (AP)</t>
         </is>
       </c>
       <c r="J459" t="inlineStr">
         <is>
-          <t>tchr_norhaima</t>
+          <t>tchr_mohaymen</t>
         </is>
       </c>
       <c r="K459" t="inlineStr">
         <is>
-          <t>Teacher Norhaima</t>
+          <t>Sir Mohaymen</t>
         </is>
       </c>
       <c r="L459" t="n">
@@ -26136,11 +26136,11 @@
         </is>
       </c>
       <c r="C460" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D460" t="inlineStr">
         <is>
-          <t>12:40 PM – 01:40 PM</t>
+          <t>01:50 PM – 02:50 PM</t>
         </is>
       </c>
       <c r="E460" t="inlineStr">
@@ -26165,17 +26165,17 @@
       </c>
       <c r="I460" t="inlineStr">
         <is>
-          <t>Araling Panlipunan (AP)</t>
+          <t>Filipino</t>
         </is>
       </c>
       <c r="J460" t="inlineStr">
         <is>
-          <t>tchr_mohaymen</t>
+          <t>tchr_nadzra</t>
         </is>
       </c>
       <c r="K460" t="inlineStr">
         <is>
-          <t>Sir Mohaymen</t>
+          <t>Teacher Nadzra</t>
         </is>
       </c>
       <c r="L460" t="n">
@@ -26201,7 +26201,7 @@
       </c>
       <c r="E461" t="inlineStr">
         <is>
-          <t>GRADE 9 - ABU HURAYRAH (1ST SHIFT) GIRLS</t>
+          <t>GRADE 10 - UTBAH IBN GHAZWAN (1ST SHIFT) GIRLS</t>
         </is>
       </c>
       <c r="F461" t="inlineStr">
@@ -26211,7 +26211,7 @@
       </c>
       <c r="G461" t="inlineStr">
         <is>
-          <t>Grade 9</t>
+          <t>Grade 10</t>
         </is>
       </c>
       <c r="H461" t="inlineStr">
@@ -26221,17 +26221,17 @@
       </c>
       <c r="I461" t="inlineStr">
         <is>
-          <t>Filipino</t>
+          <t>Qur'an</t>
         </is>
       </c>
       <c r="J461" t="inlineStr">
         <is>
-          <t>tchr_nadzra</t>
+          <t>tchr_abdulwahab</t>
         </is>
       </c>
       <c r="K461" t="inlineStr">
         <is>
-          <t>Teacher Nadzra</t>
+          <t>Alim Abdulwahab</t>
         </is>
       </c>
       <c r="L461" t="n">
@@ -26240,19 +26240,19 @@
     </row>
     <row r="462">
       <c r="A462" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="B462" t="inlineStr">
         <is>
-          <t>Thursday, September 3, 2026</t>
+          <t>Monday, September 7, 2026</t>
         </is>
       </c>
       <c r="C462" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D462" t="inlineStr">
         <is>
-          <t>03:10 PM – 04:10 PM</t>
+          <t>12:40 PM – 01:40 PM</t>
         </is>
       </c>
       <c r="E462" t="inlineStr">
@@ -26277,17 +26277,17 @@
       </c>
       <c r="I462" t="inlineStr">
         <is>
-          <t>Qur'an</t>
+          <t>Technology and Livelihood Education</t>
         </is>
       </c>
       <c r="J462" t="inlineStr">
         <is>
-          <t>tchr_abdulwahab</t>
+          <t>tchr_angeleni</t>
         </is>
       </c>
       <c r="K462" t="inlineStr">
         <is>
-          <t>Alim Abdulwahab</t>
+          <t>Teacher Angeleni</t>
         </is>
       </c>
       <c r="L462" t="n">
@@ -26296,11 +26296,11 @@
     </row>
     <row r="463">
       <c r="A463" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="B463" t="inlineStr">
         <is>
-          <t>Monday, September 7, 2026</t>
+          <t>Wednesday, September 2, 2026</t>
         </is>
       </c>
       <c r="C463" t="n">
@@ -26333,17 +26333,17 @@
       </c>
       <c r="I463" t="inlineStr">
         <is>
-          <t>Technology and Livelihood Education</t>
+          <t>Arabic Language</t>
         </is>
       </c>
       <c r="J463" t="inlineStr">
         <is>
-          <t>tchr_angeleni</t>
+          <t>tchr_mamonas</t>
         </is>
       </c>
       <c r="K463" t="inlineStr">
         <is>
-          <t>Teacher Angeleni</t>
+          <t>Alim Mamonas</t>
         </is>
       </c>
       <c r="L463" t="n">
@@ -26360,11 +26360,11 @@
         </is>
       </c>
       <c r="C464" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D464" t="inlineStr">
         <is>
-          <t>01:50 PM – 02:50 PM</t>
+          <t>03:10 PM – 04:10 PM</t>
         </is>
       </c>
       <c r="E464" t="inlineStr">
@@ -26389,17 +26389,17 @@
       </c>
       <c r="I464" t="inlineStr">
         <is>
-          <t>Arabic Language</t>
+          <t>SHAF</t>
         </is>
       </c>
       <c r="J464" t="inlineStr">
         <is>
-          <t>tchr_mamonas</t>
+          <t>tchr_bustamante</t>
         </is>
       </c>
       <c r="K464" t="inlineStr">
         <is>
-          <t>Alim Mamonas</t>
+          <t>Alim Bustamante</t>
         </is>
       </c>
       <c r="L464" t="n">
@@ -26408,11 +26408,11 @@
     </row>
     <row r="465">
       <c r="A465" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="B465" t="inlineStr">
         <is>
-          <t>Wednesday, September 2, 2026</t>
+          <t>Sunday, September 6, 2026</t>
         </is>
       </c>
       <c r="C465" t="n">
@@ -26445,17 +26445,17 @@
       </c>
       <c r="I465" t="inlineStr">
         <is>
-          <t>SHAF</t>
+          <t>Araling Panlipunan (AP)</t>
         </is>
       </c>
       <c r="J465" t="inlineStr">
         <is>
-          <t>tchr_bustamante</t>
+          <t>tchr_mohaymen</t>
         </is>
       </c>
       <c r="K465" t="inlineStr">
         <is>
-          <t>Alim Bustamante</t>
+          <t>Sir Mohaymen</t>
         </is>
       </c>
       <c r="L465" t="n">
@@ -26464,19 +26464,19 @@
     </row>
     <row r="466">
       <c r="A466" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="B466" t="inlineStr">
         <is>
-          <t>Wednesday, September 2, 2026</t>
+          <t>Sunday, September 6, 2026</t>
         </is>
       </c>
       <c r="C466" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D466" t="inlineStr">
         <is>
-          <t>01:50 PM – 02:50 PM</t>
+          <t>12:40 PM – 01:40 PM</t>
         </is>
       </c>
       <c r="E466" t="inlineStr">
@@ -26501,17 +26501,17 @@
       </c>
       <c r="I466" t="inlineStr">
         <is>
-          <t>Araling Panlipunan (AP)</t>
+          <t>English</t>
         </is>
       </c>
       <c r="J466" t="inlineStr">
         <is>
-          <t>tchr_mohaymen</t>
+          <t>tchr_norhaima</t>
         </is>
       </c>
       <c r="K466" t="inlineStr">
         <is>
-          <t>Sir Mohaymen</t>
+          <t>Teacher Norhaima</t>
         </is>
       </c>
       <c r="L466" t="n">
@@ -26528,11 +26528,11 @@
         </is>
       </c>
       <c r="C467" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D467" t="inlineStr">
         <is>
-          <t>12:40 PM – 01:40 PM</t>
+          <t>01:50 PM – 02:50 PM</t>
         </is>
       </c>
       <c r="E467" t="inlineStr">
@@ -26557,17 +26557,17 @@
       </c>
       <c r="I467" t="inlineStr">
         <is>
-          <t>English</t>
+          <t>Science</t>
         </is>
       </c>
       <c r="J467" t="inlineStr">
         <is>
-          <t>tchr_norhaima</t>
+          <t>tchr_sophia</t>
         </is>
       </c>
       <c r="K467" t="inlineStr">
         <is>
-          <t>Teacher Norhaima</t>
+          <t>Teacher Sophia</t>
         </is>
       </c>
       <c r="L467" t="n">
@@ -26588,7 +26588,7 @@
       </c>
       <c r="D468" t="inlineStr">
         <is>
-          <t>12:40 PM – 01:40 PM</t>
+          <t>12:40 PM – 02:50 PM</t>
         </is>
       </c>
       <c r="E468" t="inlineStr">
@@ -26613,38 +26613,38 @@
       </c>
       <c r="I468" t="inlineStr">
         <is>
-          <t>Science</t>
+          <t>Mathematics</t>
         </is>
       </c>
       <c r="J468" t="inlineStr">
         <is>
-          <t>tchr_sophia</t>
+          <t>tchr_jhelyn</t>
         </is>
       </c>
       <c r="K468" t="inlineStr">
         <is>
-          <t>Teacher Sophia</t>
+          <t>Teacher Jhelyn</t>
         </is>
       </c>
       <c r="L468" t="n">
-        <v>60</v>
+        <v>120</v>
       </c>
     </row>
     <row r="469">
       <c r="A469" t="n">
+        <v>1</v>
+      </c>
+      <c r="B469" t="inlineStr">
+        <is>
+          <t>Wednesday, September 2, 2026</t>
+        </is>
+      </c>
+      <c r="C469" t="n">
         <v>3</v>
       </c>
-      <c r="B469" t="inlineStr">
-        <is>
-          <t>Sunday, September 6, 2026</t>
-        </is>
-      </c>
-      <c r="C469" t="n">
-        <v>2</v>
-      </c>
       <c r="D469" t="inlineStr">
         <is>
-          <t>12:40 PM – 02:50 PM</t>
+          <t>03:10 PM – 04:10 PM</t>
         </is>
       </c>
       <c r="E469" t="inlineStr">
@@ -26669,53 +26669,53 @@
       </c>
       <c r="I469" t="inlineStr">
         <is>
-          <t>Mathematics</t>
+          <t>Filipino</t>
         </is>
       </c>
       <c r="J469" t="inlineStr">
         <is>
-          <t>tchr_jhelyn</t>
+          <t>tchr_nadzra</t>
         </is>
       </c>
       <c r="K469" t="inlineStr">
         <is>
-          <t>Teacher Jhelyn</t>
+          <t>Teacher Nadzra</t>
         </is>
       </c>
       <c r="L469" t="n">
-        <v>120</v>
+        <v>60</v>
       </c>
     </row>
     <row r="470">
       <c r="A470" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B470" t="inlineStr">
         <is>
-          <t>Wednesday, September 2, 2026</t>
+          <t>Thursday, September 3, 2026</t>
         </is>
       </c>
       <c r="C470" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D470" t="inlineStr">
         <is>
-          <t>12:40 PM – 01:40 PM</t>
+          <t>03:10 PM – 04:10 PM</t>
         </is>
       </c>
       <c r="E470" t="inlineStr">
         <is>
-          <t>GRADE 10 - UTBAH IBN GHAZWAN (1ST SHIFT) GIRLS</t>
+          <t>GRADE 11 (1ST SHIFT GIRLS)</t>
         </is>
       </c>
       <c r="F470" t="inlineStr">
         <is>
-          <t>Junior High School</t>
+          <t>Senior High School</t>
         </is>
       </c>
       <c r="G470" t="inlineStr">
         <is>
-          <t>Grade 10</t>
+          <t>Grade 11</t>
         </is>
       </c>
       <c r="H470" t="inlineStr">
@@ -26725,17 +26725,17 @@
       </c>
       <c r="I470" t="inlineStr">
         <is>
-          <t>Filipino</t>
+          <t>Arabic Language</t>
         </is>
       </c>
       <c r="J470" t="inlineStr">
         <is>
-          <t>tchr_nadzra</t>
+          <t>tchr_mamonas</t>
         </is>
       </c>
       <c r="K470" t="inlineStr">
         <is>
-          <t>Teacher Nadzra</t>
+          <t>Alim Mamonas</t>
         </is>
       </c>
       <c r="L470" t="n">
@@ -26744,11 +26744,11 @@
     </row>
     <row r="471">
       <c r="A471" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B471" t="inlineStr">
         <is>
-          <t>Thursday, September 3, 2026</t>
+          <t>Sunday, September 6, 2026</t>
         </is>
       </c>
       <c r="C471" t="n">
@@ -26781,17 +26781,17 @@
       </c>
       <c r="I471" t="inlineStr">
         <is>
-          <t>Arabic Language</t>
+          <t>Science</t>
         </is>
       </c>
       <c r="J471" t="inlineStr">
         <is>
-          <t>tchr_mamonas</t>
+          <t>tchr_rowena</t>
         </is>
       </c>
       <c r="K471" t="inlineStr">
         <is>
-          <t>Alim Mamonas</t>
+          <t>Teacher Rowena</t>
         </is>
       </c>
       <c r="L471" t="n">
@@ -26800,19 +26800,19 @@
     </row>
     <row r="472">
       <c r="A472" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B472" t="inlineStr">
         <is>
-          <t>Sunday, September 6, 2026</t>
+          <t>Thursday, September 3, 2026</t>
         </is>
       </c>
       <c r="C472" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D472" t="inlineStr">
         <is>
-          <t>03:10 PM – 04:10 PM</t>
+          <t>01:50 PM – 02:50 PM</t>
         </is>
       </c>
       <c r="E472" t="inlineStr">
@@ -26837,17 +26837,17 @@
       </c>
       <c r="I472" t="inlineStr">
         <is>
-          <t>Science</t>
+          <t>Qur'an</t>
         </is>
       </c>
       <c r="J472" t="inlineStr">
         <is>
-          <t>tchr_rowena</t>
+          <t>tchr_abdulwahab</t>
         </is>
       </c>
       <c r="K472" t="inlineStr">
         <is>
-          <t>Teacher Rowena</t>
+          <t>Alim Abdulwahab</t>
         </is>
       </c>
       <c r="L472" t="n">
@@ -26856,11 +26856,11 @@
     </row>
     <row r="473">
       <c r="A473" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="B473" t="inlineStr">
         <is>
-          <t>Thursday, September 3, 2026</t>
+          <t>Monday, September 7, 2026</t>
         </is>
       </c>
       <c r="C473" t="n">
@@ -26868,7 +26868,7 @@
       </c>
       <c r="D473" t="inlineStr">
         <is>
-          <t>01:50 PM – 02:50 PM</t>
+          <t>12:40 PM – 02:50 PM</t>
         </is>
       </c>
       <c r="E473" t="inlineStr">
@@ -26893,30 +26893,30 @@
       </c>
       <c r="I473" t="inlineStr">
         <is>
-          <t>Qur'an</t>
+          <t>Mathematics</t>
         </is>
       </c>
       <c r="J473" t="inlineStr">
         <is>
-          <t>tchr_abdulwahab</t>
+          <t>tchr_jhelyn</t>
         </is>
       </c>
       <c r="K473" t="inlineStr">
         <is>
-          <t>Alim Abdulwahab</t>
+          <t>Teacher Jhelyn</t>
         </is>
       </c>
       <c r="L473" t="n">
-        <v>60</v>
+        <v>120</v>
       </c>
     </row>
     <row r="474">
       <c r="A474" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B474" t="inlineStr">
         <is>
-          <t>Sunday, September 6, 2026</t>
+          <t>Thursday, September 3, 2026</t>
         </is>
       </c>
       <c r="C474" t="n">
@@ -26924,7 +26924,7 @@
       </c>
       <c r="D474" t="inlineStr">
         <is>
-          <t>12:40 PM – 02:50 PM</t>
+          <t>12:40 PM – 01:40 PM</t>
         </is>
       </c>
       <c r="E474" t="inlineStr">
@@ -26949,38 +26949,38 @@
       </c>
       <c r="I474" t="inlineStr">
         <is>
-          <t>Mathematics</t>
+          <t>Ec</t>
         </is>
       </c>
       <c r="J474" t="inlineStr">
         <is>
-          <t>tchr_jhelyn</t>
+          <t>tchr_nadzra</t>
         </is>
       </c>
       <c r="K474" t="inlineStr">
         <is>
-          <t>Teacher Jhelyn</t>
+          <t>Teacher Nadzra</t>
         </is>
       </c>
       <c r="L474" t="n">
-        <v>120</v>
+        <v>60</v>
       </c>
     </row>
     <row r="475">
       <c r="A475" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B475" t="inlineStr">
         <is>
-          <t>Thursday, September 3, 2026</t>
+          <t>Wednesday, September 2, 2026</t>
         </is>
       </c>
       <c r="C475" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D475" t="inlineStr">
         <is>
-          <t>12:40 PM – 01:40 PM</t>
+          <t>03:10 PM – 04:10 PM</t>
         </is>
       </c>
       <c r="E475" t="inlineStr">
@@ -27005,17 +27005,17 @@
       </c>
       <c r="I475" t="inlineStr">
         <is>
-          <t>Ec</t>
+          <t>Pagbasa at Pagsusuri ng Iba't Ibang Teksto</t>
         </is>
       </c>
       <c r="J475" t="inlineStr">
         <is>
-          <t>tchr_nadzra</t>
+          <t>tchr_shirehan</t>
         </is>
       </c>
       <c r="K475" t="inlineStr">
         <is>
-          <t>Teacher Nadzra</t>
+          <t>Teacher Shirehan</t>
         </is>
       </c>
       <c r="L475" t="n">
@@ -27032,11 +27032,11 @@
         </is>
       </c>
       <c r="C476" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D476" t="inlineStr">
         <is>
-          <t>03:10 PM – 04:10 PM</t>
+          <t>01:50 PM – 02:50 PM</t>
         </is>
       </c>
       <c r="E476" t="inlineStr">
@@ -27061,17 +27061,17 @@
       </c>
       <c r="I476" t="inlineStr">
         <is>
-          <t>Pagbasa at Pagsusuri ng Iba't Ibang Teksto</t>
+          <t>Life and Career Skills</t>
         </is>
       </c>
       <c r="J476" t="inlineStr">
         <is>
-          <t>tchr_shirehan</t>
+          <t>tchr_norhaima</t>
         </is>
       </c>
       <c r="K476" t="inlineStr">
         <is>
-          <t>Teacher Shirehan</t>
+          <t>Teacher Norhaima</t>
         </is>
       </c>
       <c r="L476" t="n">
@@ -27088,11 +27088,11 @@
         </is>
       </c>
       <c r="C477" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D477" t="inlineStr">
         <is>
-          <t>01:50 PM – 02:50 PM</t>
+          <t>12:40 PM – 01:40 PM</t>
         </is>
       </c>
       <c r="E477" t="inlineStr">
@@ -27117,17 +27117,17 @@
       </c>
       <c r="I477" t="inlineStr">
         <is>
-          <t>Life and Career Skills</t>
+          <t>SHAF</t>
         </is>
       </c>
       <c r="J477" t="inlineStr">
         <is>
-          <t>tchr_norhaima</t>
+          <t>tchr_samsuddin</t>
         </is>
       </c>
       <c r="K477" t="inlineStr">
         <is>
-          <t>Teacher Norhaima</t>
+          <t>Alim Samsuddin</t>
         </is>
       </c>
       <c r="L477" t="n">
@@ -27136,24 +27136,24 @@
     </row>
     <row r="478">
       <c r="A478" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B478" t="inlineStr">
         <is>
-          <t>Wednesday, September 2, 2026</t>
+          <t>Thursday, September 3, 2026</t>
         </is>
       </c>
       <c r="C478" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D478" t="inlineStr">
         <is>
-          <t>12:40 PM – 01:40 PM</t>
+          <t>10:25 AM – 11:25 AM</t>
         </is>
       </c>
       <c r="E478" t="inlineStr">
         <is>
-          <t>GRADE 11 (1ST SHIFT GIRLS)</t>
+          <t>GRADE 12 - ABU MUSA AL-ASHARI</t>
         </is>
       </c>
       <c r="F478" t="inlineStr">
@@ -27163,27 +27163,27 @@
       </c>
       <c r="G478" t="inlineStr">
         <is>
-          <t>Grade 11</t>
+          <t>Grade 12</t>
         </is>
       </c>
       <c r="H478" t="inlineStr">
         <is>
-          <t>ODL - 1ST SHIFT</t>
+          <t>F2F</t>
         </is>
       </c>
       <c r="I478" t="inlineStr">
         <is>
-          <t>SHAF</t>
+          <t>Science</t>
         </is>
       </c>
       <c r="J478" t="inlineStr">
         <is>
-          <t>tchr_samsuddin</t>
+          <t>tchr_aniah</t>
         </is>
       </c>
       <c r="K478" t="inlineStr">
         <is>
-          <t>Alim Samsuddin</t>
+          <t>Teacher Aniah</t>
         </is>
       </c>
       <c r="L478" t="n">
@@ -27192,19 +27192,19 @@
     </row>
     <row r="479">
       <c r="A479" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B479" t="inlineStr">
         <is>
-          <t>Sunday, September 6, 2026</t>
+          <t>Thursday, September 3, 2026</t>
         </is>
       </c>
       <c r="C479" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D479" t="inlineStr">
         <is>
-          <t>08:00 AM – 09:00 AM</t>
+          <t>09:00 AM – 10:00 AM</t>
         </is>
       </c>
       <c r="E479" t="inlineStr">
@@ -27229,17 +27229,17 @@
       </c>
       <c r="I479" t="inlineStr">
         <is>
-          <t>Science</t>
+          <t>SHAF</t>
         </is>
       </c>
       <c r="J479" t="inlineStr">
         <is>
-          <t>tchr_aniah</t>
+          <t>tchr_samsuddin</t>
         </is>
       </c>
       <c r="K479" t="inlineStr">
         <is>
-          <t>Teacher Aniah</t>
+          <t>Alim Samsuddin</t>
         </is>
       </c>
       <c r="L479" t="n">
@@ -27256,11 +27256,11 @@
         </is>
       </c>
       <c r="C480" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D480" t="inlineStr">
         <is>
-          <t>10:25 AM – 11:25 AM</t>
+          <t>08:00 AM – 09:00 AM</t>
         </is>
       </c>
       <c r="E480" t="inlineStr">
@@ -27285,17 +27285,17 @@
       </c>
       <c r="I480" t="inlineStr">
         <is>
-          <t>SHAF</t>
+          <t>Arabic Language</t>
         </is>
       </c>
       <c r="J480" t="inlineStr">
         <is>
-          <t>tchr_samsuddin</t>
+          <t>tchr_mamonas</t>
         </is>
       </c>
       <c r="K480" t="inlineStr">
         <is>
-          <t>Alim Samsuddin</t>
+          <t>Alim Mamonas</t>
         </is>
       </c>
       <c r="L480" t="n">
@@ -27304,19 +27304,19 @@
     </row>
     <row r="481">
       <c r="A481" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B481" t="inlineStr">
         <is>
-          <t>Thursday, September 3, 2026</t>
+          <t>Wednesday, September 2, 2026</t>
         </is>
       </c>
       <c r="C481" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D481" t="inlineStr">
         <is>
-          <t>09:00 AM – 10:00 AM</t>
+          <t>10:25 AM – 11:25 AM</t>
         </is>
       </c>
       <c r="E481" t="inlineStr">
@@ -27341,17 +27341,17 @@
       </c>
       <c r="I481" t="inlineStr">
         <is>
-          <t>Arabic Language</t>
+          <t>Qur'an</t>
         </is>
       </c>
       <c r="J481" t="inlineStr">
         <is>
-          <t>tchr_mamonas</t>
+          <t>tchr_dipatuan</t>
         </is>
       </c>
       <c r="K481" t="inlineStr">
         <is>
-          <t>Alim Mamonas</t>
+          <t>Alim Dipatuan</t>
         </is>
       </c>
       <c r="L481" t="n">
@@ -27360,19 +27360,19 @@
     </row>
     <row r="482">
       <c r="A482" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B482" t="inlineStr">
         <is>
-          <t>Thursday, September 3, 2026</t>
+          <t>Wednesday, September 2, 2026</t>
         </is>
       </c>
       <c r="C482" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D482" t="inlineStr">
         <is>
-          <t>08:00 AM – 09:00 AM</t>
+          <t>09:00 AM – 10:00 AM</t>
         </is>
       </c>
       <c r="E482" t="inlineStr">
@@ -27397,17 +27397,17 @@
       </c>
       <c r="I482" t="inlineStr">
         <is>
-          <t>Qur'an</t>
+          <t>21st Century Literature</t>
         </is>
       </c>
       <c r="J482" t="inlineStr">
         <is>
-          <t>tchr_dipatuan</t>
+          <t>tchr_nof</t>
         </is>
       </c>
       <c r="K482" t="inlineStr">
         <is>
-          <t>Alim Dipatuan</t>
+          <t>Teacher Nof</t>
         </is>
       </c>
       <c r="L482" t="n">
@@ -27424,11 +27424,11 @@
         </is>
       </c>
       <c r="C483" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D483" t="inlineStr">
         <is>
-          <t>10:25 AM – 11:25 AM</t>
+          <t>08:00 AM – 09:00 AM</t>
         </is>
       </c>
       <c r="E483" t="inlineStr">
@@ -27453,17 +27453,17 @@
       </c>
       <c r="I483" t="inlineStr">
         <is>
-          <t>21st Century Literature</t>
+          <t>Practical Research 2</t>
         </is>
       </c>
       <c r="J483" t="inlineStr">
         <is>
-          <t>tchr_nof</t>
+          <t>tchr_aniah</t>
         </is>
       </c>
       <c r="K483" t="inlineStr">
         <is>
-          <t>Teacher Nof</t>
+          <t>Teacher Aniah</t>
         </is>
       </c>
       <c r="L483" t="n">
@@ -27472,54 +27472,54 @@
     </row>
     <row r="484">
       <c r="A484" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="B484" t="inlineStr">
         <is>
-          <t>Wednesday, September 2, 2026</t>
+          <t>Sunday, September 6, 2026</t>
         </is>
       </c>
       <c r="C484" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D484" t="inlineStr">
         <is>
-          <t>09:00 AM – 10:00 AM</t>
+          <t>05:30 PM – 06:30 PM</t>
         </is>
       </c>
       <c r="E484" t="inlineStr">
         <is>
-          <t>GRADE 12 - ABU MUSA AL-ASHARI</t>
+          <t>GRADE 7 - ANAS IBN MALIK (2ND SHIFT) - MIX</t>
         </is>
       </c>
       <c r="F484" t="inlineStr">
         <is>
-          <t>Senior High School</t>
+          <t>Junior High School</t>
         </is>
       </c>
       <c r="G484" t="inlineStr">
         <is>
-          <t>Grade 12</t>
+          <t>Grade 7</t>
         </is>
       </c>
       <c r="H484" t="inlineStr">
         <is>
-          <t>F2F</t>
+          <t>ODL - 2ND SHIFT</t>
         </is>
       </c>
       <c r="I484" t="inlineStr">
         <is>
-          <t>Practical Research 2</t>
+          <t>English</t>
         </is>
       </c>
       <c r="J484" t="inlineStr">
         <is>
-          <t>tchr_aniah</t>
+          <t>tchr_jairah</t>
         </is>
       </c>
       <c r="K484" t="inlineStr">
         <is>
-          <t>Teacher Aniah</t>
+          <t>Teacher Jairah</t>
         </is>
       </c>
       <c r="L484" t="n">
@@ -27528,54 +27528,54 @@
     </row>
     <row r="485">
       <c r="A485" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B485" t="inlineStr">
         <is>
-          <t>Wednesday, September 2, 2026</t>
+          <t>Thursday, September 3, 2026</t>
         </is>
       </c>
       <c r="C485" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D485" t="inlineStr">
         <is>
-          <t>08:00 AM – 09:00 AM</t>
+          <t>04:20 PM – 05:20 PM</t>
         </is>
       </c>
       <c r="E485" t="inlineStr">
         <is>
-          <t>GRADE 12 - ABU MUSA AL-ASHARI</t>
+          <t>GRADE 7 - ANAS IBN MALIK (2ND SHIFT) - MIX</t>
         </is>
       </c>
       <c r="F485" t="inlineStr">
         <is>
-          <t>Senior High School</t>
+          <t>Junior High School</t>
         </is>
       </c>
       <c r="G485" t="inlineStr">
         <is>
-          <t>Grade 12</t>
+          <t>Grade 7</t>
         </is>
       </c>
       <c r="H485" t="inlineStr">
         <is>
-          <t>F2F</t>
+          <t>ODL - 2ND SHIFT</t>
         </is>
       </c>
       <c r="I485" t="inlineStr">
         <is>
-          <t>Research Consulatation</t>
+          <t>Science</t>
         </is>
       </c>
       <c r="J485" t="inlineStr">
         <is>
-          <t>unassigned</t>
+          <t>tchr_shirehan</t>
         </is>
       </c>
       <c r="K485" t="inlineStr">
         <is>
-          <t>Research Consulatation</t>
+          <t>Teacher Shirehan</t>
         </is>
       </c>
       <c r="L485" t="n">
@@ -27584,19 +27584,19 @@
     </row>
     <row r="486">
       <c r="A486" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="B486" t="inlineStr">
         <is>
-          <t>Monday, September 7, 2026</t>
+          <t>Wednesday, September 2, 2026</t>
         </is>
       </c>
       <c r="C486" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D486" t="inlineStr">
         <is>
-          <t>04:20 PM – 05:20 PM</t>
+          <t>03:10 PM – 04:10 PM</t>
         </is>
       </c>
       <c r="E486" t="inlineStr">
@@ -27621,17 +27621,17 @@
       </c>
       <c r="I486" t="inlineStr">
         <is>
-          <t>English</t>
+          <t>Qur'an</t>
         </is>
       </c>
       <c r="J486" t="inlineStr">
         <is>
-          <t>tchr_jairah</t>
+          <t>tchr_jaisam</t>
         </is>
       </c>
       <c r="K486" t="inlineStr">
         <is>
-          <t>Teacher Jairah</t>
+          <t>Ustadh Jaisam</t>
         </is>
       </c>
       <c r="L486" t="n">
@@ -27648,11 +27648,11 @@
         </is>
       </c>
       <c r="C487" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D487" t="inlineStr">
         <is>
-          <t>03:10 PM – 04:10 PM</t>
+          <t>05:30 PM – 06:30 PM</t>
         </is>
       </c>
       <c r="E487" t="inlineStr">
@@ -27677,17 +27677,17 @@
       </c>
       <c r="I487" t="inlineStr">
         <is>
-          <t>Science</t>
+          <t>GMRC / Values</t>
         </is>
       </c>
       <c r="J487" t="inlineStr">
         <is>
-          <t>tchr_shirehan</t>
+          <t>tchr_silfah</t>
         </is>
       </c>
       <c r="K487" t="inlineStr">
         <is>
-          <t>Teacher Shirehan</t>
+          <t>Ustadha Silfah</t>
         </is>
       </c>
       <c r="L487" t="n">
@@ -27696,19 +27696,19 @@
     </row>
     <row r="488">
       <c r="A488" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="B488" t="inlineStr">
         <is>
-          <t>Wednesday, September 2, 2026</t>
+          <t>Sunday, September 6, 2026</t>
         </is>
       </c>
       <c r="C488" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D488" t="inlineStr">
         <is>
-          <t>05:30 PM – 06:30 PM</t>
+          <t>03:10 PM – 04:10 PM</t>
         </is>
       </c>
       <c r="E488" t="inlineStr">
@@ -27733,17 +27733,17 @@
       </c>
       <c r="I488" t="inlineStr">
         <is>
-          <t>Qur'an</t>
+          <t>Filipino</t>
         </is>
       </c>
       <c r="J488" t="inlineStr">
         <is>
-          <t>tchr_jaisam</t>
+          <t>tchr_sophia</t>
         </is>
       </c>
       <c r="K488" t="inlineStr">
         <is>
-          <t>Ustadh Jaisam</t>
+          <t>Teacher Sophia</t>
         </is>
       </c>
       <c r="L488" t="n">
@@ -27752,11 +27752,11 @@
     </row>
     <row r="489">
       <c r="A489" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B489" t="inlineStr">
         <is>
-          <t>Sunday, September 6, 2026</t>
+          <t>Thursday, September 3, 2026</t>
         </is>
       </c>
       <c r="C489" t="n">
@@ -27789,17 +27789,17 @@
       </c>
       <c r="I489" t="inlineStr">
         <is>
-          <t>GMRC / Values</t>
+          <t>SHAF</t>
         </is>
       </c>
       <c r="J489" t="inlineStr">
         <is>
-          <t>tchr_silfah</t>
+          <t>tchr_samsuddin</t>
         </is>
       </c>
       <c r="K489" t="inlineStr">
         <is>
-          <t>Ustadha Silfah</t>
+          <t>Alim Samsuddin</t>
         </is>
       </c>
       <c r="L489" t="n">
@@ -27808,11 +27808,11 @@
     </row>
     <row r="490">
       <c r="A490" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="B490" t="inlineStr">
         <is>
-          <t>Sunday, September 6, 2026</t>
+          <t>Wednesday, September 2, 2026</t>
         </is>
       </c>
       <c r="C490" t="n">
@@ -27845,17 +27845,17 @@
       </c>
       <c r="I490" t="inlineStr">
         <is>
-          <t>Filipino</t>
+          <t>Technology and Livelihood Education</t>
         </is>
       </c>
       <c r="J490" t="inlineStr">
         <is>
-          <t>tchr_sophia</t>
+          <t>tchr_halnaisa</t>
         </is>
       </c>
       <c r="K490" t="inlineStr">
         <is>
-          <t>Teacher Sophia</t>
+          <t>Teacher Halnaisa</t>
         </is>
       </c>
       <c r="L490" t="n">
@@ -27872,11 +27872,11 @@
         </is>
       </c>
       <c r="C491" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D491" t="inlineStr">
         <is>
-          <t>05:30 PM – 06:30 PM</t>
+          <t>03:10 PM – 04:10 PM</t>
         </is>
       </c>
       <c r="E491" t="inlineStr">
@@ -27901,17 +27901,17 @@
       </c>
       <c r="I491" t="inlineStr">
         <is>
-          <t>SHAF</t>
+          <t>Araling Panlipunan (AP)</t>
         </is>
       </c>
       <c r="J491" t="inlineStr">
         <is>
-          <t>tchr_samsuddin</t>
+          <t>tchr_franchette</t>
         </is>
       </c>
       <c r="K491" t="inlineStr">
         <is>
-          <t>Alim Samsuddin</t>
+          <t>Teacher Franchette</t>
         </is>
       </c>
       <c r="L491" t="n">
@@ -27920,11 +27920,11 @@
     </row>
     <row r="492">
       <c r="A492" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B492" t="inlineStr">
         <is>
-          <t>Sunday, September 6, 2026</t>
+          <t>Monday, September 7, 2026</t>
         </is>
       </c>
       <c r="C492" t="n">
@@ -27932,7 +27932,7 @@
       </c>
       <c r="D492" t="inlineStr">
         <is>
-          <t>03:10 PM – 04:10 PM</t>
+          <t>03:10 PM – 05:20 PM</t>
         </is>
       </c>
       <c r="E492" t="inlineStr">
@@ -27957,21 +27957,21 @@
       </c>
       <c r="I492" t="inlineStr">
         <is>
-          <t>Technology and Livelihood Education</t>
+          <t>Mathematics</t>
         </is>
       </c>
       <c r="J492" t="inlineStr">
         <is>
-          <t>tchr_halnaisa</t>
+          <t>tchr_ethel</t>
         </is>
       </c>
       <c r="K492" t="inlineStr">
         <is>
-          <t>Teacher Halnaisa</t>
+          <t>Teacher Ethel</t>
         </is>
       </c>
       <c r="L492" t="n">
-        <v>60</v>
+        <v>120</v>
       </c>
     </row>
     <row r="493">
@@ -27984,11 +27984,11 @@
         </is>
       </c>
       <c r="C493" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D493" t="inlineStr">
         <is>
-          <t>04:20 PM – 05:20 PM</t>
+          <t>05:30 PM – 06:30 PM</t>
         </is>
       </c>
       <c r="E493" t="inlineStr">
@@ -28013,17 +28013,17 @@
       </c>
       <c r="I493" t="inlineStr">
         <is>
-          <t>Araling Panlipunan (AP)</t>
+          <t>Arabic Language</t>
         </is>
       </c>
       <c r="J493" t="inlineStr">
         <is>
-          <t>tchr_franchette</t>
+          <t>tchr_ali</t>
         </is>
       </c>
       <c r="K493" t="inlineStr">
         <is>
-          <t>Teacher Franchette</t>
+          <t>Ustadz Ali</t>
         </is>
       </c>
       <c r="L493" t="n">
@@ -28032,24 +28032,24 @@
     </row>
     <row r="494">
       <c r="A494" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B494" t="inlineStr">
         <is>
-          <t>Thursday, September 3, 2026</t>
+          <t>Sunday, September 6, 2026</t>
         </is>
       </c>
       <c r="C494" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D494" t="inlineStr">
         <is>
-          <t>03:10 PM – 05:20 PM</t>
+          <t>05:30 PM – 06:30 PM</t>
         </is>
       </c>
       <c r="E494" t="inlineStr">
         <is>
-          <t>GRADE 7 - ANAS IBN MALIK (2ND SHIFT) - MIX</t>
+          <t>GRADE 8 - MU'ADH IBN JABAL (2ND SHIFT) - BOYS</t>
         </is>
       </c>
       <c r="F494" t="inlineStr">
@@ -28059,7 +28059,7 @@
       </c>
       <c r="G494" t="inlineStr">
         <is>
-          <t>Grade 7</t>
+          <t>Grade 8</t>
         </is>
       </c>
       <c r="H494" t="inlineStr">
@@ -28069,43 +28069,43 @@
       </c>
       <c r="I494" t="inlineStr">
         <is>
-          <t>Mathematics</t>
+          <t>Science</t>
         </is>
       </c>
       <c r="J494" t="inlineStr">
         <is>
-          <t>tchr_ethel</t>
+          <t>tchr_radzmia</t>
         </is>
       </c>
       <c r="K494" t="inlineStr">
         <is>
-          <t>Teacher Ethel</t>
+          <t>Teacher Radzmia</t>
         </is>
       </c>
       <c r="L494" t="n">
-        <v>120</v>
+        <v>60</v>
       </c>
     </row>
     <row r="495">
       <c r="A495" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B495" t="inlineStr">
         <is>
-          <t>Wednesday, September 2, 2026</t>
+          <t>Thursday, September 3, 2026</t>
         </is>
       </c>
       <c r="C495" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D495" t="inlineStr">
         <is>
-          <t>03:10 PM – 04:10 PM</t>
+          <t>05:30 PM – 06:30 PM</t>
         </is>
       </c>
       <c r="E495" t="inlineStr">
         <is>
-          <t>GRADE 7 - ANAS IBN MALIK (2ND SHIFT) - MIX</t>
+          <t>GRADE 8 - MU'ADH IBN JABAL (2ND SHIFT) - BOYS</t>
         </is>
       </c>
       <c r="F495" t="inlineStr">
@@ -28115,7 +28115,7 @@
       </c>
       <c r="G495" t="inlineStr">
         <is>
-          <t>Grade 7</t>
+          <t>Grade 8</t>
         </is>
       </c>
       <c r="H495" t="inlineStr">
@@ -28152,11 +28152,11 @@
         </is>
       </c>
       <c r="C496" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D496" t="inlineStr">
         <is>
-          <t>05:30 PM – 06:30 PM</t>
+          <t>04:20 PM – 05:20 PM</t>
         </is>
       </c>
       <c r="E496" t="inlineStr">
@@ -28181,17 +28181,17 @@
       </c>
       <c r="I496" t="inlineStr">
         <is>
-          <t>Science</t>
+          <t>Araling Panlipunan (AP)</t>
         </is>
       </c>
       <c r="J496" t="inlineStr">
         <is>
-          <t>tchr_radzmia</t>
+          <t>tchr_franchette</t>
         </is>
       </c>
       <c r="K496" t="inlineStr">
         <is>
-          <t>Teacher Radzmia</t>
+          <t>Teacher Franchette</t>
         </is>
       </c>
       <c r="L496" t="n">
@@ -28200,19 +28200,19 @@
     </row>
     <row r="497">
       <c r="A497" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="B497" t="inlineStr">
         <is>
-          <t>Wednesday, September 2, 2026</t>
+          <t>Sunday, September 6, 2026</t>
         </is>
       </c>
       <c r="C497" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D497" t="inlineStr">
         <is>
-          <t>04:20 PM – 05:20 PM</t>
+          <t>03:10 PM – 04:10 PM</t>
         </is>
       </c>
       <c r="E497" t="inlineStr">
@@ -28237,17 +28237,17 @@
       </c>
       <c r="I497" t="inlineStr">
         <is>
-          <t>Arabic Language</t>
+          <t>GMRC / Values</t>
         </is>
       </c>
       <c r="J497" t="inlineStr">
         <is>
-          <t>tchr_ali</t>
+          <t>tchr_wardah</t>
         </is>
       </c>
       <c r="K497" t="inlineStr">
         <is>
-          <t>Ustadz Ali</t>
+          <t>Teacher Wardah</t>
         </is>
       </c>
       <c r="L497" t="n">
@@ -28256,11 +28256,11 @@
     </row>
     <row r="498">
       <c r="A498" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="B498" t="inlineStr">
         <is>
-          <t>Sunday, September 6, 2026</t>
+          <t>Wednesday, September 2, 2026</t>
         </is>
       </c>
       <c r="C498" t="n">
@@ -28293,17 +28293,17 @@
       </c>
       <c r="I498" t="inlineStr">
         <is>
-          <t>Araling Panlipunan (AP)</t>
+          <t>SHAF</t>
         </is>
       </c>
       <c r="J498" t="inlineStr">
         <is>
-          <t>tchr_franchette</t>
+          <t>tchr_samsuddin</t>
         </is>
       </c>
       <c r="K498" t="inlineStr">
         <is>
-          <t>Teacher Franchette</t>
+          <t>Alim Samsuddin</t>
         </is>
       </c>
       <c r="L498" t="n">
@@ -28312,19 +28312,19 @@
     </row>
     <row r="499">
       <c r="A499" t="n">
+        <v>4</v>
+      </c>
+      <c r="B499" t="inlineStr">
+        <is>
+          <t>Monday, September 7, 2026</t>
+        </is>
+      </c>
+      <c r="C499" t="n">
         <v>3</v>
       </c>
-      <c r="B499" t="inlineStr">
-        <is>
-          <t>Sunday, September 6, 2026</t>
-        </is>
-      </c>
-      <c r="C499" t="n">
-        <v>2</v>
-      </c>
       <c r="D499" t="inlineStr">
         <is>
-          <t>04:20 PM – 05:20 PM</t>
+          <t>05:30 PM – 06:30 PM</t>
         </is>
       </c>
       <c r="E499" t="inlineStr">
@@ -28349,17 +28349,17 @@
       </c>
       <c r="I499" t="inlineStr">
         <is>
-          <t>GMRC / Values</t>
+          <t>English</t>
         </is>
       </c>
       <c r="J499" t="inlineStr">
         <is>
-          <t>tchr_wardah</t>
+          <t>tchr_jairah</t>
         </is>
       </c>
       <c r="K499" t="inlineStr">
         <is>
-          <t>Teacher Wardah</t>
+          <t>Teacher Jairah</t>
         </is>
       </c>
       <c r="L499" t="n">
@@ -28380,7 +28380,7 @@
       </c>
       <c r="D500" t="inlineStr">
         <is>
-          <t>03:10 PM – 04:10 PM</t>
+          <t>03:10 PM – 05:20 PM</t>
         </is>
       </c>
       <c r="E500" t="inlineStr">
@@ -28405,38 +28405,38 @@
       </c>
       <c r="I500" t="inlineStr">
         <is>
-          <t>SHAF</t>
+          <t>Mathematics</t>
         </is>
       </c>
       <c r="J500" t="inlineStr">
         <is>
-          <t>tchr_samsuddin</t>
+          <t>tchr_hannah</t>
         </is>
       </c>
       <c r="K500" t="inlineStr">
         <is>
-          <t>Alim Samsuddin</t>
+          <t>Teacher Hannah</t>
         </is>
       </c>
       <c r="L500" t="n">
-        <v>60</v>
+        <v>120</v>
       </c>
     </row>
     <row r="501">
       <c r="A501" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="B501" t="inlineStr">
         <is>
-          <t>Monday, September 7, 2026</t>
+          <t>Wednesday, September 2, 2026</t>
         </is>
       </c>
       <c r="C501" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D501" t="inlineStr">
         <is>
-          <t>03:10 PM – 04:10 PM</t>
+          <t>04:20 PM – 05:20 PM</t>
         </is>
       </c>
       <c r="E501" t="inlineStr">
@@ -28461,17 +28461,17 @@
       </c>
       <c r="I501" t="inlineStr">
         <is>
-          <t>English</t>
+          <t>Qur'an</t>
         </is>
       </c>
       <c r="J501" t="inlineStr">
         <is>
-          <t>tchr_jairah</t>
+          <t>tchr_jaisam</t>
         </is>
       </c>
       <c r="K501" t="inlineStr">
         <is>
-          <t>Teacher Jairah</t>
+          <t>Ustadh Jaisam</t>
         </is>
       </c>
       <c r="L501" t="n">
@@ -28480,19 +28480,19 @@
     </row>
     <row r="502">
       <c r="A502" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="B502" t="inlineStr">
         <is>
-          <t>Monday, September 7, 2026</t>
+          <t>Wednesday, September 2, 2026</t>
         </is>
       </c>
       <c r="C502" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D502" t="inlineStr">
         <is>
-          <t>03:10 PM – 05:20 PM</t>
+          <t>05:30 PM – 06:30 PM</t>
         </is>
       </c>
       <c r="E502" t="inlineStr">
@@ -28517,30 +28517,30 @@
       </c>
       <c r="I502" t="inlineStr">
         <is>
-          <t>Mathematics</t>
+          <t>Filipino</t>
         </is>
       </c>
       <c r="J502" t="inlineStr">
         <is>
-          <t>tchr_hannah</t>
+          <t>tchr_sophia</t>
         </is>
       </c>
       <c r="K502" t="inlineStr">
         <is>
-          <t>Teacher Hannah</t>
+          <t>Teacher Sophia</t>
         </is>
       </c>
       <c r="L502" t="n">
-        <v>120</v>
+        <v>60</v>
       </c>
     </row>
     <row r="503">
       <c r="A503" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="B503" t="inlineStr">
         <is>
-          <t>Wednesday, September 2, 2026</t>
+          <t>Monday, September 7, 2026</t>
         </is>
       </c>
       <c r="C503" t="n">
@@ -28573,17 +28573,17 @@
       </c>
       <c r="I503" t="inlineStr">
         <is>
-          <t>Qur'an</t>
+          <t>Technology and Livelihood Education</t>
         </is>
       </c>
       <c r="J503" t="inlineStr">
         <is>
-          <t>tchr_jaisam</t>
+          <t>tchr_halnaisa</t>
         </is>
       </c>
       <c r="K503" t="inlineStr">
         <is>
-          <t>Ustadh Jaisam</t>
+          <t>Teacher Halnaisa</t>
         </is>
       </c>
       <c r="L503" t="n">
@@ -28592,11 +28592,11 @@
     </row>
     <row r="504">
       <c r="A504" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="B504" t="inlineStr">
         <is>
-          <t>Wednesday, September 2, 2026</t>
+          <t>Sunday, September 6, 2026</t>
         </is>
       </c>
       <c r="C504" t="n">
@@ -28609,7 +28609,7 @@
       </c>
       <c r="E504" t="inlineStr">
         <is>
-          <t>GRADE 8 - MU'ADH IBN JABAL (2ND SHIFT) - BOYS</t>
+          <t>GRADE 8 - NUAYM IBN MAS'UD (2ND SHIFT) MIX</t>
         </is>
       </c>
       <c r="F504" t="inlineStr">
@@ -28629,17 +28629,17 @@
       </c>
       <c r="I504" t="inlineStr">
         <is>
-          <t>Filipino</t>
+          <t>Araling Panlipunan (AP)</t>
         </is>
       </c>
       <c r="J504" t="inlineStr">
         <is>
-          <t>tchr_sophia</t>
+          <t>tchr_franchette</t>
         </is>
       </c>
       <c r="K504" t="inlineStr">
         <is>
-          <t>Teacher Sophia</t>
+          <t>Teacher Franchette</t>
         </is>
       </c>
       <c r="L504" t="n">
@@ -28648,24 +28648,24 @@
     </row>
     <row r="505">
       <c r="A505" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B505" t="inlineStr">
         <is>
-          <t>Thursday, September 3, 2026</t>
+          <t>Wednesday, September 2, 2026</t>
         </is>
       </c>
       <c r="C505" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D505" t="inlineStr">
         <is>
-          <t>04:20 PM – 05:20 PM</t>
+          <t>03:10 PM – 04:10 PM</t>
         </is>
       </c>
       <c r="E505" t="inlineStr">
         <is>
-          <t>GRADE 8 - MU'ADH IBN JABAL (2ND SHIFT) - BOYS</t>
+          <t>GRADE 8 - NUAYM IBN MAS'UD (2ND SHIFT) MIX</t>
         </is>
       </c>
       <c r="F505" t="inlineStr">
@@ -28685,17 +28685,17 @@
       </c>
       <c r="I505" t="inlineStr">
         <is>
-          <t>Technology and Livelihood Education</t>
+          <t>SHAF</t>
         </is>
       </c>
       <c r="J505" t="inlineStr">
         <is>
-          <t>tchr_halnaisa</t>
+          <t>tchr_samsuddin</t>
         </is>
       </c>
       <c r="K505" t="inlineStr">
         <is>
-          <t>Teacher Halnaisa</t>
+          <t>Alim Samsuddin</t>
         </is>
       </c>
       <c r="L505" t="n">
@@ -28704,19 +28704,19 @@
     </row>
     <row r="506">
       <c r="A506" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="B506" t="inlineStr">
         <is>
-          <t>Monday, September 7, 2026</t>
+          <t>Wednesday, September 2, 2026</t>
         </is>
       </c>
       <c r="C506" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D506" t="inlineStr">
         <is>
-          <t>04:20 PM – 05:20 PM</t>
+          <t>05:30 PM – 06:30 PM</t>
         </is>
       </c>
       <c r="E506" t="inlineStr">
@@ -28741,17 +28741,17 @@
       </c>
       <c r="I506" t="inlineStr">
         <is>
-          <t>Araling Panlipunan (AP)</t>
+          <t>Qur'an</t>
         </is>
       </c>
       <c r="J506" t="inlineStr">
         <is>
-          <t>tchr_franchette</t>
+          <t>tchr_jaisam</t>
         </is>
       </c>
       <c r="K506" t="inlineStr">
         <is>
-          <t>Teacher Franchette</t>
+          <t>Ustadh Jaisam</t>
         </is>
       </c>
       <c r="L506" t="n">
@@ -28760,19 +28760,19 @@
     </row>
     <row r="507">
       <c r="A507" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B507" t="inlineStr">
         <is>
-          <t>Wednesday, September 2, 2026</t>
+          <t>Thursday, September 3, 2026</t>
         </is>
       </c>
       <c r="C507" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D507" t="inlineStr">
         <is>
-          <t>03:10 PM – 04:10 PM</t>
+          <t>04:20 PM – 05:20 PM</t>
         </is>
       </c>
       <c r="E507" t="inlineStr">
@@ -28797,17 +28797,17 @@
       </c>
       <c r="I507" t="inlineStr">
         <is>
-          <t>SHAF</t>
+          <t>Technology and Livelihood Education</t>
         </is>
       </c>
       <c r="J507" t="inlineStr">
         <is>
-          <t>tchr_samsuddin</t>
+          <t>tchr_halnaisa</t>
         </is>
       </c>
       <c r="K507" t="inlineStr">
         <is>
-          <t>Alim Samsuddin</t>
+          <t>Teacher Halnaisa</t>
         </is>
       </c>
       <c r="L507" t="n">
@@ -28816,19 +28816,19 @@
     </row>
     <row r="508">
       <c r="A508" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B508" t="inlineStr">
         <is>
-          <t>Thursday, September 3, 2026</t>
+          <t>Sunday, September 6, 2026</t>
         </is>
       </c>
       <c r="C508" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D508" t="inlineStr">
         <is>
-          <t>05:30 PM – 06:30 PM</t>
+          <t>04:20 PM – 05:20 PM</t>
         </is>
       </c>
       <c r="E508" t="inlineStr">
@@ -28853,17 +28853,17 @@
       </c>
       <c r="I508" t="inlineStr">
         <is>
-          <t>Qur'an</t>
+          <t>Filipino</t>
         </is>
       </c>
       <c r="J508" t="inlineStr">
         <is>
-          <t>tchr_jaisam</t>
+          <t>tchr_sophia</t>
         </is>
       </c>
       <c r="K508" t="inlineStr">
         <is>
-          <t>Ustadh Jaisam</t>
+          <t>Teacher Sophia</t>
         </is>
       </c>
       <c r="L508" t="n">
@@ -28872,19 +28872,19 @@
     </row>
     <row r="509">
       <c r="A509" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="B509" t="inlineStr">
         <is>
-          <t>Sunday, September 6, 2026</t>
+          <t>Wednesday, September 2, 2026</t>
         </is>
       </c>
       <c r="C509" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D509" t="inlineStr">
         <is>
-          <t>05:30 PM – 06:30 PM</t>
+          <t>04:20 PM – 05:20 PM</t>
         </is>
       </c>
       <c r="E509" t="inlineStr">
@@ -28909,17 +28909,17 @@
       </c>
       <c r="I509" t="inlineStr">
         <is>
-          <t>Technology and Livelihood Education</t>
+          <t>Science</t>
         </is>
       </c>
       <c r="J509" t="inlineStr">
         <is>
-          <t>tchr_halnaisa</t>
+          <t>tchr_radzmia</t>
         </is>
       </c>
       <c r="K509" t="inlineStr">
         <is>
-          <t>Teacher Halnaisa</t>
+          <t>Teacher Radzmia</t>
         </is>
       </c>
       <c r="L509" t="n">
@@ -28936,11 +28936,11 @@
         </is>
       </c>
       <c r="C510" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D510" t="inlineStr">
         <is>
-          <t>05:30 PM – 06:30 PM</t>
+          <t>03:10 PM – 05:20 PM</t>
         </is>
       </c>
       <c r="E510" t="inlineStr">
@@ -28965,30 +28965,30 @@
       </c>
       <c r="I510" t="inlineStr">
         <is>
-          <t>Filipino</t>
+          <t>Mathematics</t>
         </is>
       </c>
       <c r="J510" t="inlineStr">
         <is>
-          <t>tchr_sophia</t>
+          <t>tchr_hannah</t>
         </is>
       </c>
       <c r="K510" t="inlineStr">
         <is>
-          <t>Teacher Sophia</t>
+          <t>Teacher Hannah</t>
         </is>
       </c>
       <c r="L510" t="n">
-        <v>60</v>
+        <v>120</v>
       </c>
     </row>
     <row r="511">
       <c r="A511" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B511" t="inlineStr">
         <is>
-          <t>Wednesday, September 2, 2026</t>
+          <t>Thursday, September 3, 2026</t>
         </is>
       </c>
       <c r="C511" t="n">
@@ -29021,17 +29021,17 @@
       </c>
       <c r="I511" t="inlineStr">
         <is>
-          <t>Science</t>
+          <t>Arabic Language</t>
         </is>
       </c>
       <c r="J511" t="inlineStr">
         <is>
-          <t>tchr_radzmia</t>
+          <t>tchr_ali</t>
         </is>
       </c>
       <c r="K511" t="inlineStr">
         <is>
-          <t>Teacher Radzmia</t>
+          <t>Ustadz Ali</t>
         </is>
       </c>
       <c r="L511" t="n">
@@ -29040,11 +29040,11 @@
     </row>
     <row r="512">
       <c r="A512" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B512" t="inlineStr">
         <is>
-          <t>Sunday, September 6, 2026</t>
+          <t>Thursday, September 3, 2026</t>
         </is>
       </c>
       <c r="C512" t="n">
@@ -29052,7 +29052,7 @@
       </c>
       <c r="D512" t="inlineStr">
         <is>
-          <t>03:10 PM – 05:20 PM</t>
+          <t>03:10 PM – 04:10 PM</t>
         </is>
       </c>
       <c r="E512" t="inlineStr">
@@ -29077,38 +29077,38 @@
       </c>
       <c r="I512" t="inlineStr">
         <is>
-          <t>Mathematics</t>
+          <t>English</t>
         </is>
       </c>
       <c r="J512" t="inlineStr">
         <is>
-          <t>tchr_hannah</t>
+          <t>tchr_jairah</t>
         </is>
       </c>
       <c r="K512" t="inlineStr">
         <is>
-          <t>Teacher Hannah</t>
+          <t>Teacher Jairah</t>
         </is>
       </c>
       <c r="L512" t="n">
-        <v>120</v>
+        <v>60</v>
       </c>
     </row>
     <row r="513">
       <c r="A513" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="B513" t="inlineStr">
         <is>
-          <t>Wednesday, September 2, 2026</t>
+          <t>Sunday, September 6, 2026</t>
         </is>
       </c>
       <c r="C513" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D513" t="inlineStr">
         <is>
-          <t>04:20 PM – 05:20 PM</t>
+          <t>03:10 PM – 04:10 PM</t>
         </is>
       </c>
       <c r="E513" t="inlineStr">
@@ -29133,17 +29133,17 @@
       </c>
       <c r="I513" t="inlineStr">
         <is>
-          <t>Arabic Language</t>
+          <t>GMRC / Values</t>
         </is>
       </c>
       <c r="J513" t="inlineStr">
         <is>
-          <t>tchr_ali</t>
+          <t>tchr_wardah</t>
         </is>
       </c>
       <c r="K513" t="inlineStr">
         <is>
-          <t>Ustadz Ali</t>
+          <t>Teacher Wardah</t>
         </is>
       </c>
       <c r="L513" t="n">
@@ -29169,7 +29169,7 @@
       </c>
       <c r="E514" t="inlineStr">
         <is>
-          <t>GRADE 8 - NUAYM IBN MAS'UD (2ND SHIFT) MIX</t>
+          <t>GRADE 9 - ABU DHARR AL GHIFARRI (2ND SHIFT) BOYS</t>
         </is>
       </c>
       <c r="F514" t="inlineStr">
@@ -29179,7 +29179,7 @@
       </c>
       <c r="G514" t="inlineStr">
         <is>
-          <t>Grade 8</t>
+          <t>Grade 9</t>
         </is>
       </c>
       <c r="H514" t="inlineStr">
@@ -29189,17 +29189,17 @@
       </c>
       <c r="I514" t="inlineStr">
         <is>
-          <t>English</t>
+          <t>Arabic Language</t>
         </is>
       </c>
       <c r="J514" t="inlineStr">
         <is>
-          <t>tchr_jairah</t>
+          <t>tchr_ali</t>
         </is>
       </c>
       <c r="K514" t="inlineStr">
         <is>
-          <t>Teacher Jairah</t>
+          <t>Ustadz Ali</t>
         </is>
       </c>
       <c r="L514" t="n">
@@ -29208,24 +29208,24 @@
     </row>
     <row r="515">
       <c r="A515" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="B515" t="inlineStr">
         <is>
-          <t>Thursday, September 3, 2026</t>
+          <t>Monday, September 7, 2026</t>
         </is>
       </c>
       <c r="C515" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D515" t="inlineStr">
         <is>
-          <t>04:20 PM – 05:20 PM</t>
+          <t>05:30 PM – 06:30 PM</t>
         </is>
       </c>
       <c r="E515" t="inlineStr">
         <is>
-          <t>GRADE 8 - NUAYM IBN MAS'UD (2ND SHIFT) MIX</t>
+          <t>GRADE 9 - ABU DHARR AL GHIFARRI (2ND SHIFT) BOYS</t>
         </is>
       </c>
       <c r="F515" t="inlineStr">
@@ -29235,7 +29235,7 @@
       </c>
       <c r="G515" t="inlineStr">
         <is>
-          <t>Grade 8</t>
+          <t>Grade 9</t>
         </is>
       </c>
       <c r="H515" t="inlineStr">
@@ -29245,17 +29245,17 @@
       </c>
       <c r="I515" t="inlineStr">
         <is>
-          <t>GMRC / Values</t>
+          <t>Science</t>
         </is>
       </c>
       <c r="J515" t="inlineStr">
         <is>
-          <t>tchr_wardah</t>
+          <t>tchr_rowena</t>
         </is>
       </c>
       <c r="K515" t="inlineStr">
         <is>
-          <t>Teacher Wardah</t>
+          <t>Teacher Rowena</t>
         </is>
       </c>
       <c r="L515" t="n">
@@ -29272,11 +29272,11 @@
         </is>
       </c>
       <c r="C516" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D516" t="inlineStr">
         <is>
-          <t>03:10 PM – 04:10 PM</t>
+          <t>04:20 PM – 05:20 PM</t>
         </is>
       </c>
       <c r="E516" t="inlineStr">
@@ -29301,17 +29301,17 @@
       </c>
       <c r="I516" t="inlineStr">
         <is>
-          <t>Arabic Language</t>
+          <t>SHAF</t>
         </is>
       </c>
       <c r="J516" t="inlineStr">
         <is>
-          <t>tchr_ali</t>
+          <t>tchr_samsuddin</t>
         </is>
       </c>
       <c r="K516" t="inlineStr">
         <is>
-          <t>Ustadz Ali</t>
+          <t>Alim Samsuddin</t>
         </is>
       </c>
       <c r="L516" t="n">
@@ -29320,11 +29320,11 @@
     </row>
     <row r="517">
       <c r="A517" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="B517" t="inlineStr">
         <is>
-          <t>Sunday, September 6, 2026</t>
+          <t>Wednesday, September 2, 2026</t>
         </is>
       </c>
       <c r="C517" t="n">
@@ -29357,17 +29357,17 @@
       </c>
       <c r="I517" t="inlineStr">
         <is>
-          <t>Science</t>
+          <t>Qur'an</t>
         </is>
       </c>
       <c r="J517" t="inlineStr">
         <is>
-          <t>tchr_rowena</t>
+          <t>tchr_abdulwahab</t>
         </is>
       </c>
       <c r="K517" t="inlineStr">
         <is>
-          <t>Teacher Rowena</t>
+          <t>Alim Abdulwahab</t>
         </is>
       </c>
       <c r="L517" t="n">
@@ -29376,11 +29376,11 @@
     </row>
     <row r="518">
       <c r="A518" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B518" t="inlineStr">
         <is>
-          <t>Thursday, September 3, 2026</t>
+          <t>Wednesday, September 2, 2026</t>
         </is>
       </c>
       <c r="C518" t="n">
@@ -29413,17 +29413,17 @@
       </c>
       <c r="I518" t="inlineStr">
         <is>
-          <t>SHAF</t>
+          <t>English</t>
         </is>
       </c>
       <c r="J518" t="inlineStr">
         <is>
-          <t>tchr_samsuddin</t>
+          <t>tchr_norhaima</t>
         </is>
       </c>
       <c r="K518" t="inlineStr">
         <is>
-          <t>Alim Samsuddin</t>
+          <t>Teacher Norhaima</t>
         </is>
       </c>
       <c r="L518" t="n">
@@ -29432,19 +29432,19 @@
     </row>
     <row r="519">
       <c r="A519" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B519" t="inlineStr">
         <is>
-          <t>Thursday, September 3, 2026</t>
+          <t>Sunday, September 6, 2026</t>
         </is>
       </c>
       <c r="C519" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D519" t="inlineStr">
         <is>
-          <t>05:30 PM – 06:30 PM</t>
+          <t>03:10 PM – 05:20 PM</t>
         </is>
       </c>
       <c r="E519" t="inlineStr">
@@ -29469,38 +29469,38 @@
       </c>
       <c r="I519" t="inlineStr">
         <is>
-          <t>Qur'an</t>
+          <t>Mathematics</t>
         </is>
       </c>
       <c r="J519" t="inlineStr">
         <is>
-          <t>tchr_abdulwahab</t>
+          <t>tchr_jhelyn</t>
         </is>
       </c>
       <c r="K519" t="inlineStr">
         <is>
-          <t>Alim Abdulwahab</t>
+          <t>Teacher Jhelyn</t>
         </is>
       </c>
       <c r="L519" t="n">
-        <v>60</v>
+        <v>120</v>
       </c>
     </row>
     <row r="520">
       <c r="A520" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B520" t="inlineStr">
         <is>
-          <t>Sunday, September 6, 2026</t>
+          <t>Monday, September 7, 2026</t>
         </is>
       </c>
       <c r="C520" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D520" t="inlineStr">
         <is>
-          <t>04:20 PM – 05:20 PM</t>
+          <t>03:10 PM – 04:10 PM</t>
         </is>
       </c>
       <c r="E520" t="inlineStr">
@@ -29525,17 +29525,17 @@
       </c>
       <c r="I520" t="inlineStr">
         <is>
-          <t>English</t>
+          <t>Araling Panlipunan (AP)</t>
         </is>
       </c>
       <c r="J520" t="inlineStr">
         <is>
-          <t>tchr_norhaima</t>
+          <t>tchr_nof</t>
         </is>
       </c>
       <c r="K520" t="inlineStr">
         <is>
-          <t>Teacher Norhaima</t>
+          <t>Teacher Nof</t>
         </is>
       </c>
       <c r="L520" t="n">
@@ -29544,19 +29544,19 @@
     </row>
     <row r="521">
       <c r="A521" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="B521" t="inlineStr">
         <is>
-          <t>Monday, September 7, 2026</t>
+          <t>Thursday, September 3, 2026</t>
         </is>
       </c>
       <c r="C521" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D521" t="inlineStr">
         <is>
-          <t>03:10 PM – 05:20 PM</t>
+          <t>05:30 PM – 06:30 PM</t>
         </is>
       </c>
       <c r="E521" t="inlineStr">
@@ -29581,38 +29581,38 @@
       </c>
       <c r="I521" t="inlineStr">
         <is>
-          <t>Mathematics</t>
+          <t>Technology and Livelihood Education</t>
         </is>
       </c>
       <c r="J521" t="inlineStr">
         <is>
-          <t>tchr_jhelyn</t>
+          <t>tchr_angeleni</t>
         </is>
       </c>
       <c r="K521" t="inlineStr">
         <is>
-          <t>Teacher Jhelyn</t>
+          <t>Teacher Angeleni</t>
         </is>
       </c>
       <c r="L521" t="n">
-        <v>120</v>
+        <v>60</v>
       </c>
     </row>
     <row r="522">
       <c r="A522" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="B522" t="inlineStr">
         <is>
-          <t>Wednesday, September 2, 2026</t>
+          <t>Sunday, September 6, 2026</t>
         </is>
       </c>
       <c r="C522" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D522" t="inlineStr">
         <is>
-          <t>05:30 PM – 06:30 PM</t>
+          <t>03:10 PM – 04:10 PM</t>
         </is>
       </c>
       <c r="E522" t="inlineStr">
@@ -29637,17 +29637,17 @@
       </c>
       <c r="I522" t="inlineStr">
         <is>
-          <t>Araling Panlipunan (AP)</t>
+          <t>Filipino</t>
         </is>
       </c>
       <c r="J522" t="inlineStr">
         <is>
-          <t>tchr_nof</t>
+          <t>tchr_nadzra</t>
         </is>
       </c>
       <c r="K522" t="inlineStr">
         <is>
-          <t>Teacher Nof</t>
+          <t>Teacher Nadzra</t>
         </is>
       </c>
       <c r="L522" t="n">
@@ -29656,11 +29656,11 @@
     </row>
     <row r="523">
       <c r="A523" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B523" t="inlineStr">
         <is>
-          <t>Wednesday, September 2, 2026</t>
+          <t>Thursday, September 3, 2026</t>
         </is>
       </c>
       <c r="C523" t="n">
@@ -29673,7 +29673,7 @@
       </c>
       <c r="E523" t="inlineStr">
         <is>
-          <t>GRADE 9 - ABU DHARR AL GHIFARRI (2ND SHIFT) BOYS</t>
+          <t>GRADE 9 - ABU JANDAL IBN SUHAYL (2ND SHIFT) GIRLS</t>
         </is>
       </c>
       <c r="F523" t="inlineStr">
@@ -29693,17 +29693,17 @@
       </c>
       <c r="I523" t="inlineStr">
         <is>
-          <t>Technology and Livelihood Education</t>
+          <t>SHAF</t>
         </is>
       </c>
       <c r="J523" t="inlineStr">
         <is>
-          <t>tchr_angeleni</t>
+          <t>tchr_samsuddin</t>
         </is>
       </c>
       <c r="K523" t="inlineStr">
         <is>
-          <t>Teacher Angeleni</t>
+          <t>Alim Samsuddin</t>
         </is>
       </c>
       <c r="L523" t="n">
@@ -29712,24 +29712,24 @@
     </row>
     <row r="524">
       <c r="A524" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="B524" t="inlineStr">
         <is>
-          <t>Monday, September 7, 2026</t>
+          <t>Wednesday, September 2, 2026</t>
         </is>
       </c>
       <c r="C524" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D524" t="inlineStr">
         <is>
-          <t>03:10 PM – 04:10 PM</t>
+          <t>05:30 PM – 06:30 PM</t>
         </is>
       </c>
       <c r="E524" t="inlineStr">
         <is>
-          <t>GRADE 9 - ABU DHARR AL GHIFARRI (2ND SHIFT) BOYS</t>
+          <t>GRADE 9 - ABU JANDAL IBN SUHAYL (2ND SHIFT) GIRLS</t>
         </is>
       </c>
       <c r="F524" t="inlineStr">
@@ -29776,11 +29776,11 @@
         </is>
       </c>
       <c r="C525" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D525" t="inlineStr">
         <is>
-          <t>05:30 PM – 06:30 PM</t>
+          <t>04:20 PM – 05:20 PM</t>
         </is>
       </c>
       <c r="E525" t="inlineStr">
@@ -29805,17 +29805,17 @@
       </c>
       <c r="I525" t="inlineStr">
         <is>
-          <t>SHAF</t>
+          <t>Qur'an</t>
         </is>
       </c>
       <c r="J525" t="inlineStr">
         <is>
-          <t>tchr_samsuddin</t>
+          <t>tchr_abdulwahab</t>
         </is>
       </c>
       <c r="K525" t="inlineStr">
         <is>
-          <t>Alim Samsuddin</t>
+          <t>Alim Abdulwahab</t>
         </is>
       </c>
       <c r="L525" t="n">
@@ -29824,19 +29824,19 @@
     </row>
     <row r="526">
       <c r="A526" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B526" t="inlineStr">
         <is>
-          <t>Sunday, September 6, 2026</t>
+          <t>Monday, September 7, 2026</t>
         </is>
       </c>
       <c r="C526" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D526" t="inlineStr">
         <is>
-          <t>05:30 PM – 06:30 PM</t>
+          <t>03:10 PM – 04:10 PM</t>
         </is>
       </c>
       <c r="E526" t="inlineStr">
@@ -29861,17 +29861,17 @@
       </c>
       <c r="I526" t="inlineStr">
         <is>
-          <t>Filipino</t>
+          <t>Araling Panlipunan (AP)</t>
         </is>
       </c>
       <c r="J526" t="inlineStr">
         <is>
-          <t>tchr_nadzra</t>
+          <t>tchr_mohaymen</t>
         </is>
       </c>
       <c r="K526" t="inlineStr">
         <is>
-          <t>Teacher Nadzra</t>
+          <t>Sir Mohaymen</t>
         </is>
       </c>
       <c r="L526" t="n">
@@ -29880,19 +29880,19 @@
     </row>
     <row r="527">
       <c r="A527" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="B527" t="inlineStr">
         <is>
-          <t>Wednesday, September 2, 2026</t>
+          <t>Sunday, September 6, 2026</t>
         </is>
       </c>
       <c r="C527" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D527" t="inlineStr">
         <is>
-          <t>04:20 PM – 05:20 PM</t>
+          <t>03:10 PM – 04:10 PM</t>
         </is>
       </c>
       <c r="E527" t="inlineStr">
@@ -29917,17 +29917,17 @@
       </c>
       <c r="I527" t="inlineStr">
         <is>
-          <t>Qur'an</t>
+          <t>Science</t>
         </is>
       </c>
       <c r="J527" t="inlineStr">
         <is>
-          <t>tchr_abdulwahab</t>
+          <t>tchr_rowena</t>
         </is>
       </c>
       <c r="K527" t="inlineStr">
         <is>
-          <t>Alim Abdulwahab</t>
+          <t>Teacher Rowena</t>
         </is>
       </c>
       <c r="L527" t="n">
@@ -29936,19 +29936,19 @@
     </row>
     <row r="528">
       <c r="A528" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="B528" t="inlineStr">
         <is>
-          <t>Monday, September 7, 2026</t>
+          <t>Thursday, September 3, 2026</t>
         </is>
       </c>
       <c r="C528" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D528" t="inlineStr">
         <is>
-          <t>04:20 PM – 05:20 PM</t>
+          <t>03:10 PM – 04:10 PM</t>
         </is>
       </c>
       <c r="E528" t="inlineStr">
@@ -29973,17 +29973,17 @@
       </c>
       <c r="I528" t="inlineStr">
         <is>
-          <t>Araling Panlipunan (AP)</t>
+          <t>Arabic Language</t>
         </is>
       </c>
       <c r="J528" t="inlineStr">
         <is>
-          <t>tchr_mohaymen</t>
+          <t>tchr_ali</t>
         </is>
       </c>
       <c r="K528" t="inlineStr">
         <is>
-          <t>Sir Mohaymen</t>
+          <t>Ustadz Ali</t>
         </is>
       </c>
       <c r="L528" t="n">
@@ -29992,11 +29992,11 @@
     </row>
     <row r="529">
       <c r="A529" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B529" t="inlineStr">
         <is>
-          <t>Sunday, September 6, 2026</t>
+          <t>Monday, September 7, 2026</t>
         </is>
       </c>
       <c r="C529" t="n">
@@ -30029,17 +30029,17 @@
       </c>
       <c r="I529" t="inlineStr">
         <is>
-          <t>Science</t>
+          <t>Technology and Livelihood Education</t>
         </is>
       </c>
       <c r="J529" t="inlineStr">
         <is>
-          <t>tchr_rowena</t>
+          <t>tchr_angeleni</t>
         </is>
       </c>
       <c r="K529" t="inlineStr">
         <is>
-          <t>Teacher Rowena</t>
+          <t>Teacher Angeleni</t>
         </is>
       </c>
       <c r="L529" t="n">
@@ -30048,19 +30048,19 @@
     </row>
     <row r="530">
       <c r="A530" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B530" t="inlineStr">
         <is>
-          <t>Thursday, September 3, 2026</t>
+          <t>Sunday, September 6, 2026</t>
         </is>
       </c>
       <c r="C530" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D530" t="inlineStr">
         <is>
-          <t>05:30 PM – 06:30 PM</t>
+          <t>03:10 PM – 05:20 PM</t>
         </is>
       </c>
       <c r="E530" t="inlineStr">
@@ -30085,30 +30085,30 @@
       </c>
       <c r="I530" t="inlineStr">
         <is>
-          <t>Arabic Language</t>
+          <t>Mathematics</t>
         </is>
       </c>
       <c r="J530" t="inlineStr">
         <is>
-          <t>tchr_ali</t>
+          <t>tchr_jhelyn</t>
         </is>
       </c>
       <c r="K530" t="inlineStr">
         <is>
-          <t>Ustadz Ali</t>
+          <t>Teacher Jhelyn</t>
         </is>
       </c>
       <c r="L530" t="n">
-        <v>60</v>
+        <v>120</v>
       </c>
     </row>
     <row r="531">
       <c r="A531" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="B531" t="inlineStr">
         <is>
-          <t>Monday, September 7, 2026</t>
+          <t>Wednesday, September 2, 2026</t>
         </is>
       </c>
       <c r="C531" t="n">
@@ -30141,17 +30141,17 @@
       </c>
       <c r="I531" t="inlineStr">
         <is>
-          <t>Technology and Livelihood Education</t>
+          <t>English</t>
         </is>
       </c>
       <c r="J531" t="inlineStr">
         <is>
-          <t>tchr_angeleni</t>
+          <t>tchr_norhaima</t>
         </is>
       </c>
       <c r="K531" t="inlineStr">
         <is>
-          <t>Teacher Angeleni</t>
+          <t>Teacher Norhaima</t>
         </is>
       </c>
       <c r="L531" t="n">
@@ -30160,11 +30160,11 @@
     </row>
     <row r="532">
       <c r="A532" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="B532" t="inlineStr">
         <is>
-          <t>Thursday, September 3, 2026</t>
+          <t>Monday, September 7, 2026</t>
         </is>
       </c>
       <c r="C532" t="n">
@@ -30177,7 +30177,7 @@
       </c>
       <c r="E532" t="inlineStr">
         <is>
-          <t>GRADE 9 - ABU JANDAL IBN SUHAYL (2ND SHIFT) GIRLS</t>
+          <t>GRADE 10 - ABU AYYUB AL-ANSARI (2ND SHIFT) BOYS</t>
         </is>
       </c>
       <c r="F532" t="inlineStr">
@@ -30187,7 +30187,7 @@
       </c>
       <c r="G532" t="inlineStr">
         <is>
-          <t>Grade 9</t>
+          <t>Grade 10</t>
         </is>
       </c>
       <c r="H532" t="inlineStr">
@@ -30216,24 +30216,24 @@
     </row>
     <row r="533">
       <c r="A533" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B533" t="inlineStr">
         <is>
-          <t>Wednesday, September 2, 2026</t>
+          <t>Thursday, September 3, 2026</t>
         </is>
       </c>
       <c r="C533" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D533" t="inlineStr">
         <is>
-          <t>03:10 PM – 04:10 PM</t>
+          <t>05:30 PM – 06:30 PM</t>
         </is>
       </c>
       <c r="E533" t="inlineStr">
         <is>
-          <t>GRADE 9 - ABU JANDAL IBN SUHAYL (2ND SHIFT) GIRLS</t>
+          <t>GRADE 10 - ABU AYYUB AL-ANSARI (2ND SHIFT) BOYS</t>
         </is>
       </c>
       <c r="F533" t="inlineStr">
@@ -30243,7 +30243,7 @@
       </c>
       <c r="G533" t="inlineStr">
         <is>
-          <t>Grade 9</t>
+          <t>Grade 10</t>
         </is>
       </c>
       <c r="H533" t="inlineStr">
@@ -30253,17 +30253,17 @@
       </c>
       <c r="I533" t="inlineStr">
         <is>
-          <t>English</t>
+          <t>Qur'an</t>
         </is>
       </c>
       <c r="J533" t="inlineStr">
         <is>
-          <t>tchr_norhaima</t>
+          <t>tchr_abdulwahab</t>
         </is>
       </c>
       <c r="K533" t="inlineStr">
         <is>
-          <t>Teacher Norhaima</t>
+          <t>Alim Abdulwahab</t>
         </is>
       </c>
       <c r="L533" t="n">
@@ -30272,19 +30272,19 @@
     </row>
     <row r="534">
       <c r="A534" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="B534" t="inlineStr">
         <is>
-          <t>Monday, September 7, 2026</t>
+          <t>Wednesday, September 2, 2026</t>
         </is>
       </c>
       <c r="C534" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D534" t="inlineStr">
         <is>
-          <t>03:10 PM – 05:20 PM</t>
+          <t>04:20 PM – 05:20 PM</t>
         </is>
       </c>
       <c r="E534" t="inlineStr">
@@ -30309,38 +30309,38 @@
       </c>
       <c r="I534" t="inlineStr">
         <is>
-          <t>Mathematics</t>
+          <t>SHAF</t>
         </is>
       </c>
       <c r="J534" t="inlineStr">
         <is>
-          <t>tchr_jhelyn</t>
+          <t>tchr_bustamante</t>
         </is>
       </c>
       <c r="K534" t="inlineStr">
         <is>
-          <t>Teacher Jhelyn</t>
+          <t>Alim Bustamante</t>
         </is>
       </c>
       <c r="L534" t="n">
-        <v>120</v>
+        <v>60</v>
       </c>
     </row>
     <row r="535">
       <c r="A535" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B535" t="inlineStr">
         <is>
-          <t>Thursday, September 3, 2026</t>
+          <t>Wednesday, September 2, 2026</t>
         </is>
       </c>
       <c r="C535" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D535" t="inlineStr">
         <is>
-          <t>04:20 PM – 05:20 PM</t>
+          <t>03:10 PM – 04:10 PM</t>
         </is>
       </c>
       <c r="E535" t="inlineStr">
@@ -30365,17 +30365,17 @@
       </c>
       <c r="I535" t="inlineStr">
         <is>
-          <t>Qur'an</t>
+          <t>Arabic Language</t>
         </is>
       </c>
       <c r="J535" t="inlineStr">
         <is>
-          <t>tchr_abdulwahab</t>
+          <t>tchr_mamonas</t>
         </is>
       </c>
       <c r="K535" t="inlineStr">
         <is>
-          <t>Alim Abdulwahab</t>
+          <t>Alim Mamonas</t>
         </is>
       </c>
       <c r="L535" t="n">
@@ -30384,11 +30384,11 @@
     </row>
     <row r="536">
       <c r="A536" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B536" t="inlineStr">
         <is>
-          <t>Thursday, September 3, 2026</t>
+          <t>Sunday, September 6, 2026</t>
         </is>
       </c>
       <c r="C536" t="n">
@@ -30421,17 +30421,17 @@
       </c>
       <c r="I536" t="inlineStr">
         <is>
-          <t>SHAF</t>
+          <t>Araling Panlipunan (AP)</t>
         </is>
       </c>
       <c r="J536" t="inlineStr">
         <is>
-          <t>tchr_bustamante</t>
+          <t>tchr_mohaymen</t>
         </is>
       </c>
       <c r="K536" t="inlineStr">
         <is>
-          <t>Alim Bustamante</t>
+          <t>Sir Mohaymen</t>
         </is>
       </c>
       <c r="L536" t="n">
@@ -30440,11 +30440,11 @@
     </row>
     <row r="537">
       <c r="A537" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B537" t="inlineStr">
         <is>
-          <t>Thursday, September 3, 2026</t>
+          <t>Wednesday, September 2, 2026</t>
         </is>
       </c>
       <c r="C537" t="n">
@@ -30477,17 +30477,17 @@
       </c>
       <c r="I537" t="inlineStr">
         <is>
-          <t>Arabic Language</t>
+          <t>English</t>
         </is>
       </c>
       <c r="J537" t="inlineStr">
         <is>
-          <t>tchr_mamonas</t>
+          <t>tchr_norhaima</t>
         </is>
       </c>
       <c r="K537" t="inlineStr">
         <is>
-          <t>Alim Mamonas</t>
+          <t>Teacher Norhaima</t>
         </is>
       </c>
       <c r="L537" t="n">
@@ -30496,11 +30496,11 @@
     </row>
     <row r="538">
       <c r="A538" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B538" t="inlineStr">
         <is>
-          <t>Wednesday, September 2, 2026</t>
+          <t>Thursday, September 3, 2026</t>
         </is>
       </c>
       <c r="C538" t="n">
@@ -30533,17 +30533,17 @@
       </c>
       <c r="I538" t="inlineStr">
         <is>
-          <t>Araling Panlipunan (AP)</t>
+          <t>Filipino</t>
         </is>
       </c>
       <c r="J538" t="inlineStr">
         <is>
-          <t>tchr_mohaymen</t>
+          <t>tchr_nadzra</t>
         </is>
       </c>
       <c r="K538" t="inlineStr">
         <is>
-          <t>Sir Mohaymen</t>
+          <t>Teacher Nadzra</t>
         </is>
       </c>
       <c r="L538" t="n">
@@ -30552,19 +30552,19 @@
     </row>
     <row r="539">
       <c r="A539" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="B539" t="inlineStr">
         <is>
-          <t>Wednesday, September 2, 2026</t>
+          <t>Monday, September 7, 2026</t>
         </is>
       </c>
       <c r="C539" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D539" t="inlineStr">
         <is>
-          <t>04:20 PM – 05:20 PM</t>
+          <t>05:30 PM – 06:30 PM</t>
         </is>
       </c>
       <c r="E539" t="inlineStr">
@@ -30589,17 +30589,17 @@
       </c>
       <c r="I539" t="inlineStr">
         <is>
-          <t>English</t>
+          <t>Science</t>
         </is>
       </c>
       <c r="J539" t="inlineStr">
         <is>
-          <t>tchr_norhaima</t>
+          <t>tchr_sophia</t>
         </is>
       </c>
       <c r="K539" t="inlineStr">
         <is>
-          <t>Teacher Norhaima</t>
+          <t>Teacher Sophia</t>
         </is>
       </c>
       <c r="L539" t="n">
@@ -30608,19 +30608,19 @@
     </row>
     <row r="540">
       <c r="A540" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="B540" t="inlineStr">
         <is>
-          <t>Wednesday, September 2, 2026</t>
+          <t>Sunday, September 6, 2026</t>
         </is>
       </c>
       <c r="C540" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D540" t="inlineStr">
         <is>
-          <t>05:30 PM – 06:30 PM</t>
+          <t>04:20 PM – 05:20 PM</t>
         </is>
       </c>
       <c r="E540" t="inlineStr">
@@ -30645,17 +30645,17 @@
       </c>
       <c r="I540" t="inlineStr">
         <is>
-          <t>Filipino</t>
+          <t>Technology and Livelihood Education</t>
         </is>
       </c>
       <c r="J540" t="inlineStr">
         <is>
-          <t>tchr_nadzra</t>
+          <t>tchr_angeleni</t>
         </is>
       </c>
       <c r="K540" t="inlineStr">
         <is>
-          <t>Teacher Nadzra</t>
+          <t>Teacher Angeleni</t>
         </is>
       </c>
       <c r="L540" t="n">
@@ -30664,34 +30664,34 @@
     </row>
     <row r="541">
       <c r="A541" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B541" t="inlineStr">
         <is>
-          <t>Sunday, September 6, 2026</t>
+          <t>Thursday, September 3, 2026</t>
         </is>
       </c>
       <c r="C541" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D541" t="inlineStr">
         <is>
-          <t>05:30 PM – 06:30 PM</t>
+          <t>03:10 PM – 04:10 PM</t>
         </is>
       </c>
       <c r="E541" t="inlineStr">
         <is>
-          <t>GRADE 10 - ABU AYYUB AL-ANSARI (2ND SHIFT) BOYS</t>
+          <t>GRADE 11 (2ND SHIFT BOYS)</t>
         </is>
       </c>
       <c r="F541" t="inlineStr">
         <is>
-          <t>Junior High School</t>
+          <t>Senior High School</t>
         </is>
       </c>
       <c r="G541" t="inlineStr">
         <is>
-          <t>Grade 10</t>
+          <t>Grade 11</t>
         </is>
       </c>
       <c r="H541" t="inlineStr">
@@ -30701,17 +30701,17 @@
       </c>
       <c r="I541" t="inlineStr">
         <is>
-          <t>Science</t>
+          <t>SHAF</t>
         </is>
       </c>
       <c r="J541" t="inlineStr">
         <is>
-          <t>tchr_sophia</t>
+          <t>tchr_samsuddin</t>
         </is>
       </c>
       <c r="K541" t="inlineStr">
         <is>
-          <t>Teacher Sophia</t>
+          <t>Alim Samsuddin</t>
         </is>
       </c>
       <c r="L541" t="n">
@@ -30720,11 +30720,11 @@
     </row>
     <row r="542">
       <c r="A542" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="B542" t="inlineStr">
         <is>
-          <t>Monday, September 7, 2026</t>
+          <t>Wednesday, September 2, 2026</t>
         </is>
       </c>
       <c r="C542" t="n">
@@ -30737,17 +30737,17 @@
       </c>
       <c r="E542" t="inlineStr">
         <is>
-          <t>GRADE 10 - ABU AYYUB AL-ANSARI (2ND SHIFT) BOYS</t>
+          <t>GRADE 11 (2ND SHIFT BOYS)</t>
         </is>
       </c>
       <c r="F542" t="inlineStr">
         <is>
-          <t>Junior High School</t>
+          <t>Senior High School</t>
         </is>
       </c>
       <c r="G542" t="inlineStr">
         <is>
-          <t>Grade 10</t>
+          <t>Grade 11</t>
         </is>
       </c>
       <c r="H542" t="inlineStr">
@@ -30757,17 +30757,17 @@
       </c>
       <c r="I542" t="inlineStr">
         <is>
-          <t>Technology and Livelihood Education</t>
+          <t>Arabic Language</t>
         </is>
       </c>
       <c r="J542" t="inlineStr">
         <is>
-          <t>tchr_angeleni</t>
+          <t>tchr_mamonas</t>
         </is>
       </c>
       <c r="K542" t="inlineStr">
         <is>
-          <t>Teacher Angeleni</t>
+          <t>Alim Mamonas</t>
         </is>
       </c>
       <c r="L542" t="n">
@@ -30776,19 +30776,19 @@
     </row>
     <row r="543">
       <c r="A543" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="B543" t="inlineStr">
         <is>
-          <t>Wednesday, September 2, 2026</t>
+          <t>Sunday, September 6, 2026</t>
         </is>
       </c>
       <c r="C543" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D543" t="inlineStr">
         <is>
-          <t>04:20 PM – 05:20 PM</t>
+          <t>05:30 PM – 06:30 PM</t>
         </is>
       </c>
       <c r="E543" t="inlineStr">
@@ -30813,17 +30813,17 @@
       </c>
       <c r="I543" t="inlineStr">
         <is>
-          <t>SHAF</t>
+          <t>Life and Career Skills</t>
         </is>
       </c>
       <c r="J543" t="inlineStr">
         <is>
-          <t>tchr_samsuddin</t>
+          <t>tchr_norhaima</t>
         </is>
       </c>
       <c r="K543" t="inlineStr">
         <is>
-          <t>Alim Samsuddin</t>
+          <t>Teacher Norhaima</t>
         </is>
       </c>
       <c r="L543" t="n">
@@ -30832,19 +30832,19 @@
     </row>
     <row r="544">
       <c r="A544" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B544" t="inlineStr">
         <is>
-          <t>Wednesday, September 2, 2026</t>
+          <t>Thursday, September 3, 2026</t>
         </is>
       </c>
       <c r="C544" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D544" t="inlineStr">
         <is>
-          <t>03:10 PM – 04:10 PM</t>
+          <t>05:30 PM – 06:30 PM</t>
         </is>
       </c>
       <c r="E544" t="inlineStr">
@@ -30869,17 +30869,17 @@
       </c>
       <c r="I544" t="inlineStr">
         <is>
-          <t>Arabic Language</t>
+          <t>Science</t>
         </is>
       </c>
       <c r="J544" t="inlineStr">
         <is>
-          <t>tchr_mamonas</t>
+          <t>tchr_radzmia</t>
         </is>
       </c>
       <c r="K544" t="inlineStr">
         <is>
-          <t>Alim Mamonas</t>
+          <t>Teacher Radzmia</t>
         </is>
       </c>
       <c r="L544" t="n">
@@ -30888,19 +30888,19 @@
     </row>
     <row r="545">
       <c r="A545" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="B545" t="inlineStr">
         <is>
-          <t>Sunday, September 6, 2026</t>
+          <t>Wednesday, September 2, 2026</t>
         </is>
       </c>
       <c r="C545" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D545" t="inlineStr">
         <is>
-          <t>03:10 PM – 04:10 PM</t>
+          <t>04:20 PM – 05:20 PM</t>
         </is>
       </c>
       <c r="E545" t="inlineStr">
@@ -30925,17 +30925,17 @@
       </c>
       <c r="I545" t="inlineStr">
         <is>
-          <t>Life and Career Skills</t>
+          <t>Ec</t>
         </is>
       </c>
       <c r="J545" t="inlineStr">
         <is>
-          <t>tchr_norhaima</t>
+          <t>tchr_nadzra</t>
         </is>
       </c>
       <c r="K545" t="inlineStr">
         <is>
-          <t>Teacher Norhaima</t>
+          <t>Teacher Nadzra</t>
         </is>
       </c>
       <c r="L545" t="n">
@@ -30944,19 +30944,19 @@
     </row>
     <row r="546">
       <c r="A546" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B546" t="inlineStr">
         <is>
-          <t>Thursday, September 3, 2026</t>
+          <t>Sunday, September 6, 2026</t>
         </is>
       </c>
       <c r="C546" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D546" t="inlineStr">
         <is>
-          <t>05:30 PM – 06:30 PM</t>
+          <t>04:20 PM – 05:20 PM</t>
         </is>
       </c>
       <c r="E546" t="inlineStr">
@@ -30981,17 +30981,17 @@
       </c>
       <c r="I546" t="inlineStr">
         <is>
-          <t>Science</t>
+          <t>Pagbasa at Pagsusuri ng Iba't Ibang Teksto</t>
         </is>
       </c>
       <c r="J546" t="inlineStr">
         <is>
-          <t>tchr_radzmia</t>
+          <t>tchr_shirehan</t>
         </is>
       </c>
       <c r="K546" t="inlineStr">
         <is>
-          <t>Teacher Radzmia</t>
+          <t>Teacher Shirehan</t>
         </is>
       </c>
       <c r="L546" t="n">
@@ -31000,11 +31000,11 @@
     </row>
     <row r="547">
       <c r="A547" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="B547" t="inlineStr">
         <is>
-          <t>Thursday, September 3, 2026</t>
+          <t>Monday, September 7, 2026</t>
         </is>
       </c>
       <c r="C547" t="n">
@@ -31012,7 +31012,7 @@
       </c>
       <c r="D547" t="inlineStr">
         <is>
-          <t>04:20 PM – 05:20 PM</t>
+          <t>03:10 PM – 05:20 PM</t>
         </is>
       </c>
       <c r="E547" t="inlineStr">
@@ -31037,21 +31037,21 @@
       </c>
       <c r="I547" t="inlineStr">
         <is>
-          <t>Ec</t>
+          <t>Mathematics</t>
         </is>
       </c>
       <c r="J547" t="inlineStr">
         <is>
-          <t>tchr_nadzra</t>
+          <t>tchr_jhelyn</t>
         </is>
       </c>
       <c r="K547" t="inlineStr">
         <is>
-          <t>Teacher Nadzra</t>
+          <t>Teacher Jhelyn</t>
         </is>
       </c>
       <c r="L547" t="n">
-        <v>60</v>
+        <v>120</v>
       </c>
     </row>
     <row r="548">
@@ -31064,11 +31064,11 @@
         </is>
       </c>
       <c r="C548" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D548" t="inlineStr">
         <is>
-          <t>03:10 PM – 04:10 PM</t>
+          <t>04:20 PM – 05:20 PM</t>
         </is>
       </c>
       <c r="E548" t="inlineStr">
@@ -31093,132 +31093,20 @@
       </c>
       <c r="I548" t="inlineStr">
         <is>
-          <t>Pagbasa at Pagsusuri ng Iba't Ibang Teksto</t>
+          <t>Qur'an</t>
         </is>
       </c>
       <c r="J548" t="inlineStr">
         <is>
-          <t>tchr_shirehan</t>
+          <t>tchr_abdulwahab</t>
         </is>
       </c>
       <c r="K548" t="inlineStr">
         <is>
-          <t>Teacher Shirehan</t>
+          <t>Alim Abdulwahab</t>
         </is>
       </c>
       <c r="L548" t="n">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="549">
-      <c r="A549" t="n">
-        <v>3</v>
-      </c>
-      <c r="B549" t="inlineStr">
-        <is>
-          <t>Sunday, September 6, 2026</t>
-        </is>
-      </c>
-      <c r="C549" t="n">
-        <v>2</v>
-      </c>
-      <c r="D549" t="inlineStr">
-        <is>
-          <t>03:10 PM – 05:20 PM</t>
-        </is>
-      </c>
-      <c r="E549" t="inlineStr">
-        <is>
-          <t>GRADE 11 (2ND SHIFT BOYS)</t>
-        </is>
-      </c>
-      <c r="F549" t="inlineStr">
-        <is>
-          <t>Senior High School</t>
-        </is>
-      </c>
-      <c r="G549" t="inlineStr">
-        <is>
-          <t>Grade 11</t>
-        </is>
-      </c>
-      <c r="H549" t="inlineStr">
-        <is>
-          <t>ODL - 2ND SHIFT</t>
-        </is>
-      </c>
-      <c r="I549" t="inlineStr">
-        <is>
-          <t>Mathematics</t>
-        </is>
-      </c>
-      <c r="J549" t="inlineStr">
-        <is>
-          <t>tchr_jhelyn</t>
-        </is>
-      </c>
-      <c r="K549" t="inlineStr">
-        <is>
-          <t>Teacher Jhelyn</t>
-        </is>
-      </c>
-      <c r="L549" t="n">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="550">
-      <c r="A550" t="n">
-        <v>1</v>
-      </c>
-      <c r="B550" t="inlineStr">
-        <is>
-          <t>Wednesday, September 2, 2026</t>
-        </is>
-      </c>
-      <c r="C550" t="n">
-        <v>3</v>
-      </c>
-      <c r="D550" t="inlineStr">
-        <is>
-          <t>05:30 PM – 06:30 PM</t>
-        </is>
-      </c>
-      <c r="E550" t="inlineStr">
-        <is>
-          <t>GRADE 11 (2ND SHIFT BOYS)</t>
-        </is>
-      </c>
-      <c r="F550" t="inlineStr">
-        <is>
-          <t>Senior High School</t>
-        </is>
-      </c>
-      <c r="G550" t="inlineStr">
-        <is>
-          <t>Grade 11</t>
-        </is>
-      </c>
-      <c r="H550" t="inlineStr">
-        <is>
-          <t>ODL - 2ND SHIFT</t>
-        </is>
-      </c>
-      <c r="I550" t="inlineStr">
-        <is>
-          <t>Qur'an</t>
-        </is>
-      </c>
-      <c r="J550" t="inlineStr">
-        <is>
-          <t>tchr_abdulwahab</t>
-        </is>
-      </c>
-      <c r="K550" t="inlineStr">
-        <is>
-          <t>Alim Abdulwahab</t>
-        </is>
-      </c>
-      <c r="L550" t="n">
         <v>60</v>
       </c>
     </row>

--- a/Term_Examination_Schedule_S.Y._2026-2027_Optimized.xlsx
+++ b/Term_Examination_Schedule_S.Y._2026-2027_Optimized.xlsx
@@ -480,19 +480,19 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Sunday, September 6, 2026</t>
+          <t>Wednesday, September 2, 2026</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>09:00 AM – 10:00 AM</t>
+          <t>10:25 AM – 11:25 AM</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -592,19 +592,19 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Thursday, September 3, 2026</t>
+          <t>Sunday, September 6, 2026</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>08:00 AM – 09:00 AM</t>
+          <t>09:00 AM – 10:00 AM</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -648,19 +648,19 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Wednesday, September 2, 2026</t>
+          <t>Monday, September 7, 2026</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>08:00 AM – 09:00 AM</t>
+          <t>10:25 AM – 11:25 AM</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -704,11 +704,11 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Sunday, September 6, 2026</t>
+          <t>Thursday, September 3, 2026</t>
         </is>
       </c>
       <c r="C6" t="n">
@@ -760,19 +760,19 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Thursday, September 3, 2026</t>
+          <t>Sunday, September 6, 2026</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>08:00 AM – 09:00 AM</t>
+          <t>10:25 AM – 11:25 AM</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -824,11 +824,11 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>09:00 AM – 10:00 AM</t>
+          <t>08:00 AM – 09:00 AM</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -872,19 +872,19 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Wednesday, September 2, 2026</t>
+          <t>Monday, September 7, 2026</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>08:00 AM – 09:00 AM</t>
+          <t>10:25 AM – 11:25 AM</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -928,19 +928,19 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Sunday, September 6, 2026</t>
+          <t>Wednesday, September 2, 2026</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>08:00 AM – 09:00 AM</t>
+          <t>10:25 AM – 11:25 AM</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -984,19 +984,19 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Thursday, September 3, 2026</t>
+          <t>Sunday, September 6, 2026</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>09:00 AM – 10:00 AM</t>
+          <t>10:25 AM – 11:25 AM</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -1048,11 +1048,11 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>10:25 AM – 11:25 AM</t>
+          <t>09:00 AM – 10:00 AM</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -1104,11 +1104,11 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>08:00 AM – 09:00 AM</t>
+          <t>09:00 AM – 10:00 AM</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -1152,19 +1152,19 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Thursday, September 3, 2026</t>
+          <t>Monday, September 7, 2026</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>08:00 AM – 09:00 AM</t>
+          <t>10:25 AM – 11:25 AM</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -1216,11 +1216,11 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>10:25 AM – 11:25 AM</t>
+          <t>09:00 AM – 10:00 AM</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -1264,11 +1264,11 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Wednesday, September 2, 2026</t>
+          <t>Sunday, September 6, 2026</t>
         </is>
       </c>
       <c r="C16" t="n">
@@ -1320,19 +1320,19 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Wednesday, September 2, 2026</t>
+          <t>Thursday, September 3, 2026</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>08:00 AM – 09:00 AM</t>
+          <t>10:25 AM – 11:25 AM</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -1432,19 +1432,19 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Sunday, September 6, 2026</t>
+          <t>Thursday, September 3, 2026</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>08:00 AM – 09:00 AM</t>
+          <t>10:25 AM – 11:25 AM</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -1488,19 +1488,19 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Thursday, September 3, 2026</t>
+          <t>Wednesday, September 2, 2026</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>10:25 AM – 11:25 AM</t>
+          <t>09:00 AM – 10:00 AM</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -1544,11 +1544,11 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Wednesday, September 2, 2026</t>
+          <t>Sunday, September 6, 2026</t>
         </is>
       </c>
       <c r="C21" t="n">
@@ -1608,11 +1608,11 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>09:00 AM – 10:00 AM</t>
+          <t>08:00 AM – 09:00 AM</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -1656,19 +1656,19 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Thursday, September 3, 2026</t>
+          <t>Wednesday, September 2, 2026</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>08:00 AM – 09:00 AM</t>
+          <t>10:25 AM – 11:25 AM</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -1712,19 +1712,19 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Wednesday, September 2, 2026</t>
+          <t>Monday, September 7, 2026</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>09:00 AM – 10:00 AM</t>
+          <t>10:25 AM – 11:25 AM</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -1768,19 +1768,19 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Wednesday, September 2, 2026</t>
+          <t>Monday, September 7, 2026</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>08:00 AM – 09:00 AM</t>
+          <t>09:00 AM – 10:00 AM</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -1824,11 +1824,11 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Monday, September 7, 2026</t>
+          <t>Wednesday, September 2, 2026</t>
         </is>
       </c>
       <c r="C26" t="n">
@@ -1944,11 +1944,11 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>08:00 AM – 09:00 AM</t>
+          <t>10:25 AM – 11:25 AM</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
@@ -1992,11 +1992,11 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Sunday, September 6, 2026</t>
+          <t>Thursday, September 3, 2026</t>
         </is>
       </c>
       <c r="C29" t="n">
@@ -2056,11 +2056,11 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>09:00 AM – 10:00 AM</t>
+          <t>08:00 AM – 09:00 AM</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
@@ -2104,19 +2104,19 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Thursday, September 3, 2026</t>
+          <t>Wednesday, September 2, 2026</t>
         </is>
       </c>
       <c r="C31" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>08:00 AM – 09:00 AM</t>
+          <t>10:25 AM – 11:25 AM</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
@@ -2160,19 +2160,19 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Wednesday, September 2, 2026</t>
+          <t>Monday, September 7, 2026</t>
         </is>
       </c>
       <c r="C32" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>10:25 AM – 11:25 AM</t>
+          <t>09:00 AM – 10:00 AM</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
@@ -2216,11 +2216,11 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Wednesday, September 2, 2026</t>
+          <t>Thursday, September 3, 2026</t>
         </is>
       </c>
       <c r="C33" t="n">
@@ -2272,19 +2272,19 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Wednesday, September 2, 2026</t>
+          <t>Monday, September 7, 2026</t>
         </is>
       </c>
       <c r="C34" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>08:00 AM – 09:00 AM</t>
+          <t>10:25 AM – 11:25 AM</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
@@ -2328,19 +2328,19 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Monday, September 7, 2026</t>
+          <t>Sunday, September 6, 2026</t>
         </is>
       </c>
       <c r="C35" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>08:00 AM – 09:00 AM</t>
+          <t>09:00 AM – 10:00 AM</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
@@ -2392,11 +2392,11 @@
         </is>
       </c>
       <c r="C36" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>10:25 AM – 11:25 AM</t>
+          <t>08:00 AM – 09:00 AM</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
@@ -2440,19 +2440,19 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Thursday, September 3, 2026</t>
+          <t>Monday, September 7, 2026</t>
         </is>
       </c>
       <c r="C37" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>10:25 AM – 11:25 AM</t>
+          <t>08:00 AM – 09:00 AM</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
@@ -2496,19 +2496,19 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Sunday, September 6, 2026</t>
+          <t>Thursday, September 3, 2026</t>
         </is>
       </c>
       <c r="C38" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>09:00 AM – 10:00 AM</t>
+          <t>10:25 AM – 11:25 AM</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
@@ -2552,11 +2552,11 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Sunday, September 6, 2026</t>
+          <t>Thursday, September 3, 2026</t>
         </is>
       </c>
       <c r="C39" t="n">
@@ -2608,19 +2608,19 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Thursday, September 3, 2026</t>
+          <t>Monday, September 7, 2026</t>
         </is>
       </c>
       <c r="C40" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>09:00 AM – 10:00 AM</t>
+          <t>10:25 AM – 11:25 AM</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
@@ -2664,11 +2664,11 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Thursday, September 3, 2026</t>
+          <t>Wednesday, September 2, 2026</t>
         </is>
       </c>
       <c r="C41" t="n">
@@ -2720,11 +2720,11 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Wednesday, September 2, 2026</t>
+          <t>Sunday, September 6, 2026</t>
         </is>
       </c>
       <c r="C42" t="n">
@@ -2784,11 +2784,11 @@
         </is>
       </c>
       <c r="C43" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>09:00 AM – 10:00 AM</t>
+          <t>10:25 AM – 11:25 AM</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
@@ -2832,19 +2832,19 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Wednesday, September 2, 2026</t>
+          <t>Thursday, September 3, 2026</t>
         </is>
       </c>
       <c r="C44" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>08:00 AM – 09:00 AM</t>
+          <t>09:00 AM – 10:00 AM</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
@@ -2896,11 +2896,11 @@
         </is>
       </c>
       <c r="C45" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>08:00 AM – 09:00 AM</t>
+          <t>10:25 AM – 11:25 AM</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
@@ -2944,19 +2944,19 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Sunday, September 6, 2026</t>
+          <t>Thursday, September 3, 2026</t>
         </is>
       </c>
       <c r="C46" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>10:25 AM – 11:25 AM</t>
+          <t>09:00 AM – 10:00 AM</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
@@ -3000,19 +3000,19 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Thursday, September 3, 2026</t>
+          <t>Wednesday, September 2, 2026</t>
         </is>
       </c>
       <c r="C47" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>10:25 AM – 11:25 AM</t>
+          <t>09:00 AM – 10:00 AM</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
@@ -3064,11 +3064,11 @@
         </is>
       </c>
       <c r="C48" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>09:00 AM – 10:00 AM</t>
+          <t>08:00 AM – 09:00 AM</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
@@ -3120,11 +3120,11 @@
         </is>
       </c>
       <c r="C49" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>08:00 AM – 09:00 AM</t>
+          <t>10:25 AM – 11:25 AM</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
@@ -3168,19 +3168,19 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Sunday, September 6, 2026</t>
+          <t>Thursday, September 3, 2026</t>
         </is>
       </c>
       <c r="C50" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>09:00 AM – 10:00 AM</t>
+          <t>10:25 AM – 11:25 AM</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
@@ -3224,19 +3224,19 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Thursday, September 3, 2026</t>
+          <t>Wednesday, September 2, 2026</t>
         </is>
       </c>
       <c r="C51" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>08:00 AM – 09:00 AM</t>
+          <t>10:25 AM – 11:25 AM</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
@@ -3280,19 +3280,19 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Wednesday, September 2, 2026</t>
+          <t>Monday, September 7, 2026</t>
         </is>
       </c>
       <c r="C52" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>10:25 AM – 11:25 AM</t>
+          <t>09:00 AM – 10:00 AM</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
@@ -3336,11 +3336,11 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Wednesday, September 2, 2026</t>
+          <t>Sunday, September 6, 2026</t>
         </is>
       </c>
       <c r="C53" t="n">
@@ -3392,11 +3392,11 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Wednesday, September 2, 2026</t>
+          <t>Sunday, September 6, 2026</t>
         </is>
       </c>
       <c r="C54" t="n">
@@ -3448,11 +3448,11 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Monday, September 7, 2026</t>
+          <t>Thursday, September 3, 2026</t>
         </is>
       </c>
       <c r="C55" t="n">
@@ -3504,19 +3504,19 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Sunday, September 6, 2026</t>
+          <t>Wednesday, September 2, 2026</t>
         </is>
       </c>
       <c r="C56" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>10:25 AM – 11:25 AM</t>
+          <t>08:00 AM – 09:00 AM</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
@@ -3560,11 +3560,11 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Sunday, September 6, 2026</t>
+          <t>Thursday, September 3, 2026</t>
         </is>
       </c>
       <c r="C57" t="n">
@@ -3616,19 +3616,19 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Sunday, September 6, 2026</t>
+          <t>Wednesday, September 2, 2026</t>
         </is>
       </c>
       <c r="C58" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>08:00 AM – 09:00 AM</t>
+          <t>09:00 AM – 10:00 AM</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
@@ -3672,19 +3672,19 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Thursday, September 3, 2026</t>
+          <t>Sunday, September 6, 2026</t>
         </is>
       </c>
       <c r="C59" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>09:00 AM – 10:00 AM</t>
+          <t>10:25 AM – 11:25 AM</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
@@ -3784,19 +3784,19 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Thursday, September 3, 2026</t>
+          <t>Monday, September 7, 2026</t>
         </is>
       </c>
       <c r="C61" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>08:00 AM – 09:00 AM</t>
+          <t>10:25 AM – 11:25 AM</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
@@ -3840,19 +3840,19 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
+        <v>4</v>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>Monday, September 7, 2026</t>
+        </is>
+      </c>
+      <c r="C62" t="n">
         <v>1</v>
       </c>
-      <c r="B62" t="inlineStr">
-        <is>
-          <t>Wednesday, September 2, 2026</t>
-        </is>
-      </c>
-      <c r="C62" t="n">
-        <v>3</v>
-      </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>10:25 AM – 11:25 AM</t>
+          <t>08:00 AM – 09:00 AM</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
@@ -3896,11 +3896,11 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Wednesday, September 2, 2026</t>
+          <t>Sunday, September 6, 2026</t>
         </is>
       </c>
       <c r="C63" t="n">
@@ -3960,11 +3960,11 @@
         </is>
       </c>
       <c r="C64" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>08:00 AM – 09:00 AM</t>
+          <t>10:25 AM – 11:25 AM</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
@@ -4008,11 +4008,11 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Wednesday, September 2, 2026</t>
+          <t>Thursday, September 3, 2026</t>
         </is>
       </c>
       <c r="C65" t="n">
@@ -4064,19 +4064,19 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Thursday, September 3, 2026</t>
+          <t>Monday, September 7, 2026</t>
         </is>
       </c>
       <c r="C66" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>01:30 PM – 02:15 PM</t>
+          <t>03:10 PM – 03:40 PM</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
@@ -4120,19 +4120,19 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Wednesday, September 2, 2026</t>
+          <t>Sunday, September 6, 2026</t>
         </is>
       </c>
       <c r="C67" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>01:30 PM – 02:15 PM</t>
+          <t>02:20 PM – 03:05 PM</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
@@ -4184,11 +4184,11 @@
         </is>
       </c>
       <c r="C68" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>03:10 PM – 03:40 PM</t>
+          <t>02:20 PM – 03:05 PM</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
@@ -4240,11 +4240,11 @@
         </is>
       </c>
       <c r="C69" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>01:30 PM – 02:15 PM</t>
+          <t>03:10 PM – 03:40 PM</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
@@ -4296,11 +4296,11 @@
         </is>
       </c>
       <c r="C70" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>01:50 PM – 02:50 PM</t>
+          <t>03:10 PM – 04:10 PM</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
@@ -4352,11 +4352,11 @@
         </is>
       </c>
       <c r="C71" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>12:40 PM – 01:40 PM</t>
+          <t>03:10 PM – 04:10 PM</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
@@ -4400,19 +4400,19 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
+        <v>2</v>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>Thursday, September 3, 2026</t>
+        </is>
+      </c>
+      <c r="C72" t="n">
         <v>1</v>
       </c>
-      <c r="B72" t="inlineStr">
-        <is>
-          <t>Wednesday, September 2, 2026</t>
-        </is>
-      </c>
-      <c r="C72" t="n">
-        <v>3</v>
-      </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>03:10 PM – 04:10 PM</t>
+          <t>12:40 PM – 01:40 PM</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
@@ -4512,11 +4512,11 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Thursday, September 3, 2026</t>
+          <t>Monday, September 7, 2026</t>
         </is>
       </c>
       <c r="C74" t="n">
@@ -4568,19 +4568,19 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
+        <v>3</v>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>Sunday, September 6, 2026</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
         <v>1</v>
       </c>
-      <c r="B75" t="inlineStr">
-        <is>
-          <t>Wednesday, September 2, 2026</t>
-        </is>
-      </c>
-      <c r="C75" t="n">
-        <v>2</v>
-      </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>01:50 PM – 02:50 PM</t>
+          <t>12:40 PM – 01:40 PM</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
@@ -4624,11 +4624,11 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Thursday, September 3, 2026</t>
+          <t>Wednesday, September 2, 2026</t>
         </is>
       </c>
       <c r="C76" t="n">
@@ -4688,11 +4688,11 @@
         </is>
       </c>
       <c r="C77" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>12:40 PM – 01:40 PM</t>
+          <t>03:10 PM – 04:10 PM</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
@@ -4736,11 +4736,11 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Monday, September 7, 2026</t>
+          <t>Sunday, September 6, 2026</t>
         </is>
       </c>
       <c r="C78" t="n">
@@ -4792,19 +4792,19 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Thursday, September 3, 2026</t>
+          <t>Wednesday, September 2, 2026</t>
         </is>
       </c>
       <c r="C79" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>12:40 PM – 01:40 PM</t>
+          <t>03:10 PM – 04:10 PM</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
@@ -4904,19 +4904,19 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Monday, September 7, 2026</t>
+          <t>Thursday, September 3, 2026</t>
         </is>
       </c>
       <c r="C81" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>12:40 PM – 01:40 PM</t>
+          <t>03:10 PM – 04:10 PM</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
@@ -4960,19 +4960,19 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Thursday, September 3, 2026</t>
+          <t>Monday, September 7, 2026</t>
         </is>
       </c>
       <c r="C82" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>03:10 PM – 04:10 PM</t>
+          <t>12:40 PM – 01:40 PM</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
@@ -5024,11 +5024,11 @@
         </is>
       </c>
       <c r="C83" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>03:10 PM – 04:10 PM</t>
+          <t>12:40 PM – 01:40 PM</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
@@ -5072,19 +5072,19 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Wednesday, September 2, 2026</t>
+          <t>Monday, September 7, 2026</t>
         </is>
       </c>
       <c r="C84" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>01:50 PM – 02:50 PM</t>
+          <t>03:10 PM – 04:10 PM</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
@@ -5128,11 +5128,11 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Wednesday, September 2, 2026</t>
+          <t>Thursday, September 3, 2026</t>
         </is>
       </c>
       <c r="C85" t="n">
@@ -5184,19 +5184,19 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Sunday, September 6, 2026</t>
+          <t>Thursday, September 3, 2026</t>
         </is>
       </c>
       <c r="C86" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>12:40 PM – 01:40 PM</t>
+          <t>03:10 PM – 04:10 PM</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
@@ -5240,19 +5240,19 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Wednesday, September 2, 2026</t>
+          <t>Thursday, September 3, 2026</t>
         </is>
       </c>
       <c r="C87" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>03:10 PM – 04:10 PM</t>
+          <t>01:50 PM – 02:50 PM</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
@@ -5296,19 +5296,19 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Sunday, September 6, 2026</t>
+          <t>Monday, September 7, 2026</t>
         </is>
       </c>
       <c r="C88" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>01:50 PM – 02:50 PM</t>
+          <t>03:10 PM – 04:10 PM</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
@@ -5408,19 +5408,19 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Sunday, September 6, 2026</t>
+          <t>Monday, September 7, 2026</t>
         </is>
       </c>
       <c r="C90" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>03:10 PM – 04:10 PM</t>
+          <t>12:40 PM – 01:40 PM</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
@@ -5464,19 +5464,19 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Thursday, September 3, 2026</t>
+          <t>Wednesday, September 2, 2026</t>
         </is>
       </c>
       <c r="C91" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>03:10 PM – 04:10 PM</t>
+          <t>12:40 PM – 01:40 PM</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
@@ -5520,11 +5520,11 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Thursday, September 3, 2026</t>
+          <t>Sunday, September 6, 2026</t>
         </is>
       </c>
       <c r="C92" t="n">
@@ -5576,19 +5576,19 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Thursday, September 3, 2026</t>
+          <t>Sunday, September 6, 2026</t>
         </is>
       </c>
       <c r="C93" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>01:50 PM – 02:50 PM</t>
+          <t>03:10 PM – 04:10 PM</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
@@ -5640,11 +5640,11 @@
         </is>
       </c>
       <c r="C94" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>12:40 PM – 01:40 PM</t>
+          <t>03:10 PM – 04:10 PM</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
@@ -5688,11 +5688,11 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Wednesday, September 2, 2026</t>
+          <t>Monday, September 7, 2026</t>
         </is>
       </c>
       <c r="C95" t="n">
@@ -5800,11 +5800,11 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>Sunday, September 6, 2026</t>
+          <t>Monday, September 7, 2026</t>
         </is>
       </c>
       <c r="C97" t="n">
@@ -5864,11 +5864,11 @@
         </is>
       </c>
       <c r="C98" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>03:10 PM – 04:10 PM</t>
+          <t>01:50 PM – 02:50 PM</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
@@ -5920,11 +5920,11 @@
         </is>
       </c>
       <c r="C99" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>01:50 PM – 02:50 PM</t>
+          <t>12:40 PM – 01:40 PM</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
@@ -5968,11 +5968,11 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>Wednesday, September 2, 2026</t>
+          <t>Monday, September 7, 2026</t>
         </is>
       </c>
       <c r="C100" t="n">
@@ -6024,11 +6024,11 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>Monday, September 7, 2026</t>
+          <t>Wednesday, September 2, 2026</t>
         </is>
       </c>
       <c r="C101" t="n">
@@ -6080,19 +6080,19 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>Monday, September 7, 2026</t>
+          <t>Thursday, September 3, 2026</t>
         </is>
       </c>
       <c r="C102" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>01:50 PM – 02:50 PM</t>
+          <t>03:10 PM – 04:10 PM</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
@@ -6136,19 +6136,19 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>Thursday, September 3, 2026</t>
+          <t>Wednesday, September 2, 2026</t>
         </is>
       </c>
       <c r="C103" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>12:40 PM – 01:40 PM</t>
+          <t>01:50 PM – 02:50 PM</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
@@ -6192,11 +6192,11 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>Wednesday, September 2, 2026</t>
+          <t>Sunday, September 6, 2026</t>
         </is>
       </c>
       <c r="C104" t="n">
@@ -6248,11 +6248,11 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>Sunday, September 6, 2026</t>
+          <t>Wednesday, September 2, 2026</t>
         </is>
       </c>
       <c r="C105" t="n">
@@ -6360,11 +6360,11 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>Sunday, September 6, 2026</t>
+          <t>Monday, September 7, 2026</t>
         </is>
       </c>
       <c r="C107" t="n">
@@ -6480,11 +6480,11 @@
         </is>
       </c>
       <c r="C109" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>03:10 PM – 04:10 PM</t>
+          <t>12:40 PM – 01:40 PM</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
@@ -6528,11 +6528,11 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>Wednesday, September 2, 2026</t>
+          <t>Sunday, September 6, 2026</t>
         </is>
       </c>
       <c r="C110" t="n">
@@ -6640,11 +6640,11 @@
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>Thursday, September 3, 2026</t>
+          <t>Sunday, September 6, 2026</t>
         </is>
       </c>
       <c r="C112" t="n">
@@ -6696,19 +6696,19 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>Monday, September 7, 2026</t>
+          <t>Thursday, September 3, 2026</t>
         </is>
       </c>
       <c r="C113" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>01:50 PM – 02:50 PM</t>
+          <t>03:10 PM – 04:10 PM</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
@@ -6752,11 +6752,11 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>Thursday, September 3, 2026</t>
+          <t>Sunday, September 6, 2026</t>
         </is>
       </c>
       <c r="C114" t="n">
@@ -6808,19 +6808,19 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>Thursday, September 3, 2026</t>
+          <t>Wednesday, September 2, 2026</t>
         </is>
       </c>
       <c r="C115" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>03:10 PM – 04:10 PM</t>
+          <t>01:50 PM – 02:50 PM</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
@@ -6864,19 +6864,19 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>Monday, September 7, 2026</t>
+          <t>Sunday, September 6, 2026</t>
         </is>
       </c>
       <c r="C116" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>01:50 PM – 02:50 PM</t>
+          <t>03:10 PM – 04:10 PM</t>
         </is>
       </c>
       <c r="E116" t="inlineStr">
@@ -6920,11 +6920,11 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>Sunday, September 6, 2026</t>
+          <t>Monday, September 7, 2026</t>
         </is>
       </c>
       <c r="C117" t="n">
@@ -6976,19 +6976,19 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>Monday, September 7, 2026</t>
+          <t>Thursday, September 3, 2026</t>
         </is>
       </c>
       <c r="C118" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>12:40 PM – 01:40 PM</t>
+          <t>03:10 PM – 04:10 PM</t>
         </is>
       </c>
       <c r="E118" t="inlineStr">
@@ -7144,19 +7144,19 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>Wednesday, September 2, 2026</t>
+          <t>Monday, September 7, 2026</t>
         </is>
       </c>
       <c r="C121" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>12:40 PM – 01:40 PM</t>
+          <t>03:10 PM – 04:10 PM</t>
         </is>
       </c>
       <c r="E121" t="inlineStr">
@@ -7200,11 +7200,11 @@
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>Thursday, September 3, 2026</t>
+          <t>Sunday, September 6, 2026</t>
         </is>
       </c>
       <c r="C122" t="n">
@@ -7256,19 +7256,19 @@
     </row>
     <row r="123">
       <c r="A123" t="n">
+        <v>4</v>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>Monday, September 7, 2026</t>
+        </is>
+      </c>
+      <c r="C123" t="n">
         <v>1</v>
       </c>
-      <c r="B123" t="inlineStr">
-        <is>
-          <t>Wednesday, September 2, 2026</t>
-        </is>
-      </c>
-      <c r="C123" t="n">
-        <v>3</v>
-      </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>03:10 PM – 04:10 PM</t>
+          <t>12:40 PM – 01:40 PM</t>
         </is>
       </c>
       <c r="E123" t="inlineStr">
@@ -7320,11 +7320,11 @@
         </is>
       </c>
       <c r="C124" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>01:50 PM – 02:50 PM</t>
+          <t>12:40 PM – 01:40 PM</t>
         </is>
       </c>
       <c r="E124" t="inlineStr">
@@ -7368,11 +7368,11 @@
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>Monday, September 7, 2026</t>
+          <t>Sunday, September 6, 2026</t>
         </is>
       </c>
       <c r="C125" t="n">
@@ -7424,19 +7424,19 @@
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>Monday, September 7, 2026</t>
+          <t>Wednesday, September 2, 2026</t>
         </is>
       </c>
       <c r="C126" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>12:40 PM – 01:40 PM</t>
+          <t>01:50 PM – 02:50 PM</t>
         </is>
       </c>
       <c r="E126" t="inlineStr">
@@ -7480,19 +7480,19 @@
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>Sunday, September 6, 2026</t>
+          <t>Monday, September 7, 2026</t>
         </is>
       </c>
       <c r="C127" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>01:50 PM – 02:50 PM</t>
+          <t>03:10 PM – 04:10 PM</t>
         </is>
       </c>
       <c r="E127" t="inlineStr">
@@ -7536,19 +7536,19 @@
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>Sunday, September 6, 2026</t>
+          <t>Thursday, September 3, 2026</t>
         </is>
       </c>
       <c r="C128" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>03:10 PM – 04:10 PM</t>
+          <t>12:40 PM – 01:40 PM</t>
         </is>
       </c>
       <c r="E128" t="inlineStr">
@@ -7592,11 +7592,11 @@
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>Thursday, September 3, 2026</t>
+          <t>Monday, September 7, 2026</t>
         </is>
       </c>
       <c r="C129" t="n">
@@ -7648,11 +7648,11 @@
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>Thursday, September 3, 2026</t>
+          <t>Wednesday, September 2, 2026</t>
         </is>
       </c>
       <c r="C130" t="n">
@@ -7712,11 +7712,11 @@
         </is>
       </c>
       <c r="C131" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>03:10 PM – 04:10 PM</t>
+          <t>12:40 PM – 01:40 PM</t>
         </is>
       </c>
       <c r="E131" t="inlineStr">
@@ -7816,19 +7816,19 @@
     </row>
     <row r="133">
       <c r="A133" t="n">
+        <v>3</v>
+      </c>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>Sunday, September 6, 2026</t>
+        </is>
+      </c>
+      <c r="C133" t="n">
         <v>1</v>
       </c>
-      <c r="B133" t="inlineStr">
-        <is>
-          <t>Wednesday, September 2, 2026</t>
-        </is>
-      </c>
-      <c r="C133" t="n">
-        <v>2</v>
-      </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>01:50 PM – 02:50 PM</t>
+          <t>12:40 PM – 01:40 PM</t>
         </is>
       </c>
       <c r="E133" t="inlineStr">
@@ -7872,19 +7872,19 @@
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>Wednesday, September 2, 2026</t>
+          <t>Thursday, September 3, 2026</t>
         </is>
       </c>
       <c r="C134" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>12:40 PM – 01:40 PM</t>
+          <t>03:10 PM – 04:10 PM</t>
         </is>
       </c>
       <c r="E134" t="inlineStr">
@@ -7928,19 +7928,19 @@
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>Thursday, September 3, 2026</t>
+          <t>Sunday, September 6, 2026</t>
         </is>
       </c>
       <c r="C135" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>02:20 PM – 03:05 PM</t>
+          <t>03:10 PM – 03:40 PM</t>
         </is>
       </c>
       <c r="E135" t="inlineStr">
@@ -7984,19 +7984,19 @@
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>Wednesday, September 2, 2026</t>
+          <t>Thursday, September 3, 2026</t>
         </is>
       </c>
       <c r="C136" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>03:10 PM – 03:40 PM</t>
+          <t>02:20 PM – 03:05 PM</t>
         </is>
       </c>
       <c r="E136" t="inlineStr">
@@ -8040,19 +8040,19 @@
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>Thursday, September 3, 2026</t>
+          <t>Wednesday, September 2, 2026</t>
         </is>
       </c>
       <c r="C137" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>01:30 PM – 02:15 PM</t>
+          <t>03:10 PM – 03:40 PM</t>
         </is>
       </c>
       <c r="E137" t="inlineStr">
@@ -8096,11 +8096,11 @@
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>Wednesday, September 2, 2026</t>
+          <t>Monday, September 7, 2026</t>
         </is>
       </c>
       <c r="C138" t="n">
@@ -8152,19 +8152,19 @@
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>Sunday, September 6, 2026</t>
+          <t>Monday, September 7, 2026</t>
         </is>
       </c>
       <c r="C139" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>01:50 PM – 02:50 PM</t>
+          <t>03:10 PM – 04:10 PM</t>
         </is>
       </c>
       <c r="E139" t="inlineStr">
@@ -8208,11 +8208,11 @@
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>Sunday, September 6, 2026</t>
+          <t>Monday, September 7, 2026</t>
         </is>
       </c>
       <c r="C140" t="n">
@@ -8272,11 +8272,11 @@
         </is>
       </c>
       <c r="C141" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>03:10 PM – 04:10 PM</t>
+          <t>01:50 PM – 02:50 PM</t>
         </is>
       </c>
       <c r="E141" t="inlineStr">
@@ -8320,19 +8320,19 @@
     </row>
     <row r="142">
       <c r="A142" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>Thursday, September 3, 2026</t>
+          <t>Wednesday, September 2, 2026</t>
         </is>
       </c>
       <c r="C142" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>01:50 PM – 02:50 PM</t>
+          <t>03:10 PM – 04:10 PM</t>
         </is>
       </c>
       <c r="E142" t="inlineStr">
@@ -8384,11 +8384,11 @@
         </is>
       </c>
       <c r="C143" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>12:40 PM – 01:40 PM</t>
+          <t>03:10 PM – 04:10 PM</t>
         </is>
       </c>
       <c r="E143" t="inlineStr">
@@ -8432,11 +8432,11 @@
     </row>
     <row r="144">
       <c r="A144" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>Wednesday, September 2, 2026</t>
+          <t>Sunday, September 6, 2026</t>
         </is>
       </c>
       <c r="C144" t="n">
@@ -8496,11 +8496,11 @@
         </is>
       </c>
       <c r="C145" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>12:40 PM – 01:40 PM</t>
+          <t>01:50 PM – 02:50 PM</t>
         </is>
       </c>
       <c r="E145" t="inlineStr">
@@ -8544,19 +8544,19 @@
     </row>
     <row r="146">
       <c r="A146" t="n">
+        <v>3</v>
+      </c>
+      <c r="B146" t="inlineStr">
+        <is>
+          <t>Sunday, September 6, 2026</t>
+        </is>
+      </c>
+      <c r="C146" t="n">
         <v>1</v>
       </c>
-      <c r="B146" t="inlineStr">
-        <is>
-          <t>Wednesday, September 2, 2026</t>
-        </is>
-      </c>
-      <c r="C146" t="n">
-        <v>2</v>
-      </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>01:50 PM – 02:50 PM</t>
+          <t>12:40 PM – 01:40 PM</t>
         </is>
       </c>
       <c r="E146" t="inlineStr">
@@ -8600,19 +8600,19 @@
     </row>
     <row r="147">
       <c r="A147" t="n">
+        <v>2</v>
+      </c>
+      <c r="B147" t="inlineStr">
+        <is>
+          <t>Thursday, September 3, 2026</t>
+        </is>
+      </c>
+      <c r="C147" t="n">
         <v>1</v>
       </c>
-      <c r="B147" t="inlineStr">
-        <is>
-          <t>Wednesday, September 2, 2026</t>
-        </is>
-      </c>
-      <c r="C147" t="n">
-        <v>3</v>
-      </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>03:10 PM – 04:10 PM</t>
+          <t>12:40 PM – 01:40 PM</t>
         </is>
       </c>
       <c r="E147" t="inlineStr">
@@ -8656,19 +8656,19 @@
     </row>
     <row r="148">
       <c r="A148" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>Sunday, September 6, 2026</t>
+          <t>Monday, September 7, 2026</t>
         </is>
       </c>
       <c r="C148" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>12:40 PM – 01:40 PM</t>
+          <t>01:50 PM – 02:50 PM</t>
         </is>
       </c>
       <c r="E148" t="inlineStr">
@@ -8712,19 +8712,19 @@
     </row>
     <row r="149">
       <c r="A149" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>Wednesday, September 2, 2026</t>
+          <t>Monday, September 7, 2026</t>
         </is>
       </c>
       <c r="C149" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>01:50 PM – 02:50 PM</t>
+          <t>03:10 PM – 04:10 PM</t>
         </is>
       </c>
       <c r="E149" t="inlineStr">
@@ -8824,19 +8824,19 @@
     </row>
     <row r="151">
       <c r="A151" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>Monday, September 7, 2026</t>
+          <t>Sunday, September 6, 2026</t>
         </is>
       </c>
       <c r="C151" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>12:40 PM – 01:40 PM</t>
+          <t>03:10 PM – 04:10 PM</t>
         </is>
       </c>
       <c r="E151" t="inlineStr">
@@ -8880,19 +8880,19 @@
     </row>
     <row r="152">
       <c r="A152" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>Thursday, September 3, 2026</t>
+          <t>Wednesday, September 2, 2026</t>
         </is>
       </c>
       <c r="C152" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>01:50 PM – 02:50 PM</t>
+          <t>12:40 PM – 01:40 PM</t>
         </is>
       </c>
       <c r="E152" t="inlineStr">
@@ -8936,19 +8936,19 @@
     </row>
     <row r="153">
       <c r="A153" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>Thursday, September 3, 2026</t>
+          <t>Wednesday, September 2, 2026</t>
         </is>
       </c>
       <c r="C153" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>12:40 PM – 01:40 PM</t>
+          <t>03:10 PM – 04:10 PM</t>
         </is>
       </c>
       <c r="E153" t="inlineStr">
@@ -8992,19 +8992,19 @@
     </row>
     <row r="154">
       <c r="A154" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>Wednesday, September 2, 2026</t>
+          <t>Thursday, September 3, 2026</t>
         </is>
       </c>
       <c r="C154" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>12:40 PM – 01:40 PM</t>
+          <t>01:50 PM – 02:50 PM</t>
         </is>
       </c>
       <c r="E154" t="inlineStr">
@@ -9048,19 +9048,19 @@
     </row>
     <row r="155">
       <c r="A155" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>Thursday, September 3, 2026</t>
+          <t>Monday, September 7, 2026</t>
         </is>
       </c>
       <c r="C155" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>03:10 PM – 04:10 PM</t>
+          <t>01:50 PM – 02:50 PM</t>
         </is>
       </c>
       <c r="E155" t="inlineStr">
@@ -9112,11 +9112,11 @@
         </is>
       </c>
       <c r="C156" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>12:40 PM – 01:40 PM</t>
+          <t>03:10 PM – 04:10 PM</t>
         </is>
       </c>
       <c r="E156" t="inlineStr">
@@ -9160,19 +9160,19 @@
     </row>
     <row r="157">
       <c r="A157" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>Thursday, September 3, 2026</t>
+          <t>Sunday, September 6, 2026</t>
         </is>
       </c>
       <c r="C157" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>01:50 PM – 02:50 PM</t>
+          <t>03:10 PM – 04:10 PM</t>
         </is>
       </c>
       <c r="E157" t="inlineStr">
@@ -9224,11 +9224,11 @@
         </is>
       </c>
       <c r="C158" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>12:40 PM – 01:40 PM</t>
+          <t>03:10 PM – 04:10 PM</t>
         </is>
       </c>
       <c r="E158" t="inlineStr">
@@ -9272,19 +9272,19 @@
     </row>
     <row r="159">
       <c r="A159" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>Wednesday, September 2, 2026</t>
+          <t>Sunday, September 6, 2026</t>
         </is>
       </c>
       <c r="C159" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>03:10 PM – 04:10 PM</t>
+          <t>01:50 PM – 02:50 PM</t>
         </is>
       </c>
       <c r="E159" t="inlineStr">
@@ -9328,11 +9328,11 @@
     </row>
     <row r="160">
       <c r="A160" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>Sunday, September 6, 2026</t>
+          <t>Wednesday, September 2, 2026</t>
         </is>
       </c>
       <c r="C160" t="n">
@@ -9448,11 +9448,11 @@
         </is>
       </c>
       <c r="C162" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>03:10 PM – 04:10 PM</t>
+          <t>12:40 PM – 01:40 PM</t>
         </is>
       </c>
       <c r="E162" t="inlineStr">
@@ -9496,19 +9496,19 @@
     </row>
     <row r="163">
       <c r="A163" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>Wednesday, September 2, 2026</t>
+          <t>Thursday, September 3, 2026</t>
         </is>
       </c>
       <c r="C163" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>12:40 PM – 01:40 PM</t>
+          <t>01:50 PM – 02:50 PM</t>
         </is>
       </c>
       <c r="E163" t="inlineStr">
@@ -9552,19 +9552,19 @@
     </row>
     <row r="164">
       <c r="A164" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>Sunday, September 6, 2026</t>
+          <t>Wednesday, September 2, 2026</t>
         </is>
       </c>
       <c r="C164" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>03:10 PM – 04:10 PM</t>
+          <t>01:50 PM – 02:50 PM</t>
         </is>
       </c>
       <c r="E164" t="inlineStr">
@@ -9608,19 +9608,19 @@
     </row>
     <row r="165">
       <c r="A165" t="n">
+        <v>4</v>
+      </c>
+      <c r="B165" t="inlineStr">
+        <is>
+          <t>Monday, September 7, 2026</t>
+        </is>
+      </c>
+      <c r="C165" t="n">
         <v>1</v>
       </c>
-      <c r="B165" t="inlineStr">
-        <is>
-          <t>Wednesday, September 2, 2026</t>
-        </is>
-      </c>
-      <c r="C165" t="n">
-        <v>3</v>
-      </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>03:10 PM – 04:10 PM</t>
+          <t>12:40 PM – 01:40 PM</t>
         </is>
       </c>
       <c r="E165" t="inlineStr">
@@ -9672,11 +9672,11 @@
         </is>
       </c>
       <c r="C166" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>01:50 PM – 02:50 PM</t>
+          <t>03:10 PM – 04:10 PM</t>
         </is>
       </c>
       <c r="E166" t="inlineStr">
@@ -9728,11 +9728,11 @@
         </is>
       </c>
       <c r="C167" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t>12:40 PM – 01:40 PM</t>
+          <t>01:50 PM – 02:50 PM</t>
         </is>
       </c>
       <c r="E167" t="inlineStr">
@@ -9776,11 +9776,11 @@
     </row>
     <row r="168">
       <c r="A168" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>Sunday, September 6, 2026</t>
+          <t>Thursday, September 3, 2026</t>
         </is>
       </c>
       <c r="C168" t="n">
@@ -9832,19 +9832,19 @@
     </row>
     <row r="169">
       <c r="A169" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>Thursday, September 3, 2026</t>
+          <t>Monday, September 7, 2026</t>
         </is>
       </c>
       <c r="C169" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t>03:10 PM – 04:10 PM</t>
+          <t>01:50 PM – 02:50 PM</t>
         </is>
       </c>
       <c r="E169" t="inlineStr">
@@ -9888,19 +9888,19 @@
     </row>
     <row r="170">
       <c r="A170" t="n">
+        <v>3</v>
+      </c>
+      <c r="B170" t="inlineStr">
+        <is>
+          <t>Sunday, September 6, 2026</t>
+        </is>
+      </c>
+      <c r="C170" t="n">
         <v>1</v>
       </c>
-      <c r="B170" t="inlineStr">
-        <is>
-          <t>Wednesday, September 2, 2026</t>
-        </is>
-      </c>
-      <c r="C170" t="n">
-        <v>2</v>
-      </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t>01:50 PM – 02:50 PM</t>
+          <t>12:40 PM – 01:40 PM</t>
         </is>
       </c>
       <c r="E170" t="inlineStr">
@@ -9944,19 +9944,19 @@
     </row>
     <row r="171">
       <c r="A171" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>Wednesday, September 2, 2026</t>
+          <t>Monday, September 7, 2026</t>
         </is>
       </c>
       <c r="C171" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t>12:40 PM – 01:40 PM</t>
+          <t>03:10 PM – 04:10 PM</t>
         </is>
       </c>
       <c r="E171" t="inlineStr">
@@ -10000,11 +10000,11 @@
     </row>
     <row r="172">
       <c r="A172" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>Thursday, September 3, 2026</t>
+          <t>Wednesday, September 2, 2026</t>
         </is>
       </c>
       <c r="C172" t="n">
@@ -10056,19 +10056,19 @@
     </row>
     <row r="173">
       <c r="A173" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>Monday, September 7, 2026</t>
+          <t>Sunday, September 6, 2026</t>
         </is>
       </c>
       <c r="C173" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t>12:40 PM – 01:40 PM</t>
+          <t>03:10 PM – 04:10 PM</t>
         </is>
       </c>
       <c r="E173" t="inlineStr">
@@ -10112,11 +10112,11 @@
     </row>
     <row r="174">
       <c r="A174" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>Sunday, September 6, 2026</t>
+          <t>Monday, September 7, 2026</t>
         </is>
       </c>
       <c r="C174" t="n">
@@ -10168,19 +10168,19 @@
     </row>
     <row r="175">
       <c r="A175" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>Sunday, September 6, 2026</t>
+          <t>Monday, September 7, 2026</t>
         </is>
       </c>
       <c r="C175" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
-          <t>12:40 PM – 01:40 PM</t>
+          <t>01:50 PM – 02:50 PM</t>
         </is>
       </c>
       <c r="E175" t="inlineStr">
@@ -10224,11 +10224,11 @@
     </row>
     <row r="176">
       <c r="A176" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>Monday, September 7, 2026</t>
+          <t>Sunday, September 6, 2026</t>
         </is>
       </c>
       <c r="C176" t="n">
@@ -10280,19 +10280,19 @@
     </row>
     <row r="177">
       <c r="A177" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>Sunday, September 6, 2026</t>
+          <t>Wednesday, September 2, 2026</t>
         </is>
       </c>
       <c r="C177" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
-          <t>01:50 PM – 02:50 PM</t>
+          <t>12:40 PM – 01:40 PM</t>
         </is>
       </c>
       <c r="E177" t="inlineStr">
@@ -10344,11 +10344,11 @@
         </is>
       </c>
       <c r="C178" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
-          <t>01:50 PM – 02:50 PM</t>
+          <t>03:10 PM – 04:10 PM</t>
         </is>
       </c>
       <c r="E178" t="inlineStr">
@@ -10400,11 +10400,11 @@
         </is>
       </c>
       <c r="C179" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
-          <t>12:40 PM – 01:40 PM</t>
+          <t>01:50 PM – 02:50 PM</t>
         </is>
       </c>
       <c r="E179" t="inlineStr">
@@ -10504,19 +10504,19 @@
     </row>
     <row r="181">
       <c r="A181" t="n">
+        <v>3</v>
+      </c>
+      <c r="B181" t="inlineStr">
+        <is>
+          <t>Sunday, September 6, 2026</t>
+        </is>
+      </c>
+      <c r="C181" t="n">
         <v>1</v>
       </c>
-      <c r="B181" t="inlineStr">
-        <is>
-          <t>Wednesday, September 2, 2026</t>
-        </is>
-      </c>
-      <c r="C181" t="n">
-        <v>2</v>
-      </c>
       <c r="D181" t="inlineStr">
         <is>
-          <t>01:50 PM – 02:50 PM</t>
+          <t>12:40 PM – 01:40 PM</t>
         </is>
       </c>
       <c r="E181" t="inlineStr">
@@ -10568,11 +10568,11 @@
         </is>
       </c>
       <c r="C182" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
-          <t>12:40 PM – 01:40 PM</t>
+          <t>01:50 PM – 02:50 PM</t>
         </is>
       </c>
       <c r="E182" t="inlineStr">
@@ -10616,19 +10616,19 @@
     </row>
     <row r="183">
       <c r="A183" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>Monday, September 7, 2026</t>
+          <t>Wednesday, September 2, 2026</t>
         </is>
       </c>
       <c r="C183" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
-          <t>12:40 PM – 01:40 PM</t>
+          <t>01:50 PM – 02:50 PM</t>
         </is>
       </c>
       <c r="E183" t="inlineStr">
@@ -10672,19 +10672,19 @@
     </row>
     <row r="184">
       <c r="A184" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>Thursday, September 3, 2026</t>
+          <t>Monday, September 7, 2026</t>
         </is>
       </c>
       <c r="C184" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
-          <t>03:10 PM – 04:10 PM</t>
+          <t>01:50 PM – 02:50 PM</t>
         </is>
       </c>
       <c r="E184" t="inlineStr">
@@ -10728,11 +10728,11 @@
     </row>
     <row r="185">
       <c r="A185" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>Sunday, September 6, 2026</t>
+          <t>Thursday, September 3, 2026</t>
         </is>
       </c>
       <c r="C185" t="n">
@@ -10792,11 +10792,11 @@
         </is>
       </c>
       <c r="C186" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>
-          <t>12:40 PM – 01:40 PM</t>
+          <t>01:50 PM – 02:50 PM</t>
         </is>
       </c>
       <c r="E186" t="inlineStr">
@@ -10840,11 +10840,11 @@
     </row>
     <row r="187">
       <c r="A187" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>Sunday, September 6, 2026</t>
+          <t>Thursday, September 3, 2026</t>
         </is>
       </c>
       <c r="C187" t="n">
@@ -10896,19 +10896,19 @@
     </row>
     <row r="188">
       <c r="A188" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>Thursday, September 3, 2026</t>
+          <t>Monday, September 7, 2026</t>
         </is>
       </c>
       <c r="C188" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D188" t="inlineStr">
         <is>
-          <t>01:50 PM – 02:50 PM</t>
+          <t>12:40 PM – 01:40 PM</t>
         </is>
       </c>
       <c r="E188" t="inlineStr">
@@ -10952,19 +10952,19 @@
     </row>
     <row r="189">
       <c r="A189" t="n">
+        <v>3</v>
+      </c>
+      <c r="B189" t="inlineStr">
+        <is>
+          <t>Sunday, September 6, 2026</t>
+        </is>
+      </c>
+      <c r="C189" t="n">
         <v>1</v>
       </c>
-      <c r="B189" t="inlineStr">
-        <is>
-          <t>Wednesday, September 2, 2026</t>
-        </is>
-      </c>
-      <c r="C189" t="n">
-        <v>3</v>
-      </c>
       <c r="D189" t="inlineStr">
         <is>
-          <t>03:10 PM – 04:10 PM</t>
+          <t>12:40 PM – 01:40 PM</t>
         </is>
       </c>
       <c r="E189" t="inlineStr">
@@ -11008,19 +11008,19 @@
     </row>
     <row r="190">
       <c r="A190" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>Thursday, September 3, 2026</t>
+          <t>Sunday, September 6, 2026</t>
         </is>
       </c>
       <c r="C190" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D190" t="inlineStr">
         <is>
-          <t>12:40 PM – 01:40 PM</t>
+          <t>03:10 PM – 04:10 PM</t>
         </is>
       </c>
       <c r="E190" t="inlineStr">
@@ -11072,11 +11072,11 @@
         </is>
       </c>
       <c r="C191" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D191" t="inlineStr">
         <is>
-          <t>01:50 PM – 02:50 PM</t>
+          <t>12:40 PM – 01:40 PM</t>
         </is>
       </c>
       <c r="E191" t="inlineStr">
@@ -11120,19 +11120,19 @@
     </row>
     <row r="192">
       <c r="A192" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>Wednesday, September 2, 2026</t>
+          <t>Monday, September 7, 2026</t>
         </is>
       </c>
       <c r="C192" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D192" t="inlineStr">
         <is>
-          <t>12:40 PM – 01:40 PM</t>
+          <t>03:10 PM – 04:10 PM</t>
         </is>
       </c>
       <c r="E192" t="inlineStr">
@@ -11232,11 +11232,11 @@
     </row>
     <row r="194">
       <c r="A194" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>Sunday, September 6, 2026</t>
+          <t>Thursday, September 3, 2026</t>
         </is>
       </c>
       <c r="C194" t="n">
@@ -11288,19 +11288,19 @@
     </row>
     <row r="195">
       <c r="A195" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>Sunday, September 6, 2026</t>
+          <t>Monday, September 7, 2026</t>
         </is>
       </c>
       <c r="C195" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D195" t="inlineStr">
         <is>
-          <t>01:50 PM – 02:50 PM</t>
+          <t>03:10 PM – 04:10 PM</t>
         </is>
       </c>
       <c r="E195" t="inlineStr">
@@ -11344,11 +11344,11 @@
     </row>
     <row r="196">
       <c r="A196" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>Sunday, September 6, 2026</t>
+          <t>Thursday, September 3, 2026</t>
         </is>
       </c>
       <c r="C196" t="n">
@@ -11400,11 +11400,11 @@
     </row>
     <row r="197">
       <c r="A197" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>Thursday, September 3, 2026</t>
+          <t>Sunday, September 6, 2026</t>
         </is>
       </c>
       <c r="C197" t="n">
@@ -11456,11 +11456,11 @@
     </row>
     <row r="198">
       <c r="A198" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>Thursday, September 3, 2026</t>
+          <t>Wednesday, September 2, 2026</t>
         </is>
       </c>
       <c r="C198" t="n">
@@ -11512,19 +11512,19 @@
     </row>
     <row r="199">
       <c r="A199" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>Thursday, September 3, 2026</t>
+          <t>Monday, September 7, 2026</t>
         </is>
       </c>
       <c r="C199" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D199" t="inlineStr">
         <is>
-          <t>12:40 PM – 01:40 PM</t>
+          <t>01:50 PM – 02:50 PM</t>
         </is>
       </c>
       <c r="E199" t="inlineStr">
@@ -11568,19 +11568,19 @@
     </row>
     <row r="200">
       <c r="A200" t="n">
+        <v>3</v>
+      </c>
+      <c r="B200" t="inlineStr">
+        <is>
+          <t>Sunday, September 6, 2026</t>
+        </is>
+      </c>
+      <c r="C200" t="n">
         <v>1</v>
       </c>
-      <c r="B200" t="inlineStr">
-        <is>
-          <t>Wednesday, September 2, 2026</t>
-        </is>
-      </c>
-      <c r="C200" t="n">
-        <v>2</v>
-      </c>
       <c r="D200" t="inlineStr">
         <is>
-          <t>01:50 PM – 02:50 PM</t>
+          <t>12:40 PM – 01:40 PM</t>
         </is>
       </c>
       <c r="E200" t="inlineStr">
@@ -11680,19 +11680,19 @@
     </row>
     <row r="202">
       <c r="A202" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>Wednesday, September 2, 2026</t>
+          <t>Sunday, September 6, 2026</t>
         </is>
       </c>
       <c r="C202" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D202" t="inlineStr">
         <is>
-          <t>12:40 PM – 01:40 PM</t>
+          <t>01:50 PM – 02:50 PM</t>
         </is>
       </c>
       <c r="E202" t="inlineStr">
@@ -11744,11 +11744,11 @@
         </is>
       </c>
       <c r="C203" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D203" t="inlineStr">
         <is>
-          <t>04:20 PM – 05:20 PM</t>
+          <t>05:30 PM – 06:30 PM</t>
         </is>
       </c>
       <c r="E203" t="inlineStr">
@@ -11792,19 +11792,19 @@
     </row>
     <row r="204">
       <c r="A204" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B204" t="inlineStr">
         <is>
-          <t>Wednesday, September 2, 2026</t>
+          <t>Thursday, September 3, 2026</t>
         </is>
       </c>
       <c r="C204" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D204" t="inlineStr">
         <is>
-          <t>03:10 PM – 04:10 PM</t>
+          <t>04:20 PM – 05:20 PM</t>
         </is>
       </c>
       <c r="E204" t="inlineStr">
@@ -11848,19 +11848,19 @@
     </row>
     <row r="205">
       <c r="A205" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="B205" t="inlineStr">
         <is>
-          <t>Thursday, September 3, 2026</t>
+          <t>Monday, September 7, 2026</t>
         </is>
       </c>
       <c r="C205" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D205" t="inlineStr">
         <is>
-          <t>04:20 PM – 05:20 PM</t>
+          <t>03:10 PM – 04:10 PM</t>
         </is>
       </c>
       <c r="E205" t="inlineStr">
@@ -11912,11 +11912,11 @@
         </is>
       </c>
       <c r="C206" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D206" t="inlineStr">
         <is>
-          <t>04:20 PM – 05:20 PM</t>
+          <t>03:10 PM – 04:10 PM</t>
         </is>
       </c>
       <c r="E206" t="inlineStr">
@@ -12016,11 +12016,11 @@
     </row>
     <row r="208">
       <c r="A208" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="B208" t="inlineStr">
         <is>
-          <t>Monday, September 7, 2026</t>
+          <t>Thursday, September 3, 2026</t>
         </is>
       </c>
       <c r="C208" t="n">
@@ -12072,19 +12072,19 @@
     </row>
     <row r="209">
       <c r="A209" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="B209" t="inlineStr">
         <is>
-          <t>Sunday, September 6, 2026</t>
+          <t>Wednesday, September 2, 2026</t>
         </is>
       </c>
       <c r="C209" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D209" t="inlineStr">
         <is>
-          <t>03:10 PM – 04:10 PM</t>
+          <t>05:30 PM – 06:30 PM</t>
         </is>
       </c>
       <c r="E209" t="inlineStr">
@@ -12128,19 +12128,19 @@
     </row>
     <row r="210">
       <c r="A210" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="B210" t="inlineStr">
         <is>
-          <t>Wednesday, September 2, 2026</t>
+          <t>Monday, September 7, 2026</t>
         </is>
       </c>
       <c r="C210" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D210" t="inlineStr">
         <is>
-          <t>03:10 PM – 04:10 PM</t>
+          <t>05:30 PM – 06:30 PM</t>
         </is>
       </c>
       <c r="E210" t="inlineStr">
@@ -12184,11 +12184,11 @@
     </row>
     <row r="211">
       <c r="A211" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B211" t="inlineStr">
         <is>
-          <t>Thursday, September 3, 2026</t>
+          <t>Wednesday, September 2, 2026</t>
         </is>
       </c>
       <c r="C211" t="n">
@@ -12240,11 +12240,11 @@
     </row>
     <row r="212">
       <c r="A212" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B212" t="inlineStr">
         <is>
-          <t>Sunday, September 6, 2026</t>
+          <t>Monday, September 7, 2026</t>
         </is>
       </c>
       <c r="C212" t="n">
@@ -12304,11 +12304,11 @@
         </is>
       </c>
       <c r="C213" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D213" t="inlineStr">
         <is>
-          <t>03:10 PM – 04:10 PM</t>
+          <t>04:20 PM – 05:20 PM</t>
         </is>
       </c>
       <c r="E213" t="inlineStr">
@@ -12352,19 +12352,19 @@
     </row>
     <row r="214">
       <c r="A214" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="B214" t="inlineStr">
         <is>
-          <t>Wednesday, September 2, 2026</t>
+          <t>Sunday, September 6, 2026</t>
         </is>
       </c>
       <c r="C214" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D214" t="inlineStr">
         <is>
-          <t>04:20 PM – 05:20 PM</t>
+          <t>05:30 PM – 06:30 PM</t>
         </is>
       </c>
       <c r="E214" t="inlineStr">
@@ -12408,11 +12408,11 @@
     </row>
     <row r="215">
       <c r="A215" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="B215" t="inlineStr">
         <is>
-          <t>Monday, September 7, 2026</t>
+          <t>Thursday, September 3, 2026</t>
         </is>
       </c>
       <c r="C215" t="n">
@@ -12464,19 +12464,19 @@
     </row>
     <row r="216">
       <c r="A216" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="B216" t="inlineStr">
         <is>
-          <t>Wednesday, September 2, 2026</t>
+          <t>Sunday, September 6, 2026</t>
         </is>
       </c>
       <c r="C216" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D216" t="inlineStr">
         <is>
-          <t>05:30 PM – 06:30 PM</t>
+          <t>04:20 PM – 05:20 PM</t>
         </is>
       </c>
       <c r="E216" t="inlineStr">
@@ -12520,11 +12520,11 @@
     </row>
     <row r="217">
       <c r="A217" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B217" t="inlineStr">
         <is>
-          <t>Thursday, September 3, 2026</t>
+          <t>Wednesday, September 2, 2026</t>
         </is>
       </c>
       <c r="C217" t="n">
@@ -12576,19 +12576,19 @@
     </row>
     <row r="218">
       <c r="A218" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="B218" t="inlineStr">
         <is>
-          <t>Wednesday, September 2, 2026</t>
+          <t>Monday, September 7, 2026</t>
         </is>
       </c>
       <c r="C218" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D218" t="inlineStr">
         <is>
-          <t>03:10 PM – 04:10 PM</t>
+          <t>04:20 PM – 05:20 PM</t>
         </is>
       </c>
       <c r="E218" t="inlineStr">
@@ -12632,19 +12632,19 @@
     </row>
     <row r="219">
       <c r="A219" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B219" t="inlineStr">
         <is>
-          <t>Monday, September 7, 2026</t>
+          <t>Sunday, September 6, 2026</t>
         </is>
       </c>
       <c r="C219" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D219" t="inlineStr">
         <is>
-          <t>04:20 PM – 05:20 PM</t>
+          <t>03:10 PM – 04:10 PM</t>
         </is>
       </c>
       <c r="E219" t="inlineStr">
@@ -12744,11 +12744,11 @@
     </row>
     <row r="221">
       <c r="A221" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="B221" t="inlineStr">
         <is>
-          <t>Sunday, September 6, 2026</t>
+          <t>Wednesday, September 2, 2026</t>
         </is>
       </c>
       <c r="C221" t="n">
@@ -12808,11 +12808,11 @@
         </is>
       </c>
       <c r="C222" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D222" t="inlineStr">
         <is>
-          <t>05:30 PM – 06:30 PM</t>
+          <t>03:10 PM – 04:10 PM</t>
         </is>
       </c>
       <c r="E222" t="inlineStr">
@@ -12856,19 +12856,19 @@
     </row>
     <row r="223">
       <c r="A223" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="B223" t="inlineStr">
         <is>
-          <t>Wednesday, September 2, 2026</t>
+          <t>Sunday, September 6, 2026</t>
         </is>
       </c>
       <c r="C223" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D223" t="inlineStr">
         <is>
-          <t>03:10 PM – 04:10 PM</t>
+          <t>05:30 PM – 06:30 PM</t>
         </is>
       </c>
       <c r="E223" t="inlineStr">
@@ -12912,19 +12912,19 @@
     </row>
     <row r="224">
       <c r="A224" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="B224" t="inlineStr">
         <is>
-          <t>Thursday, September 3, 2026</t>
+          <t>Monday, September 7, 2026</t>
         </is>
       </c>
       <c r="C224" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D224" t="inlineStr">
         <is>
-          <t>03:10 PM – 04:10 PM</t>
+          <t>04:20 PM – 05:20 PM</t>
         </is>
       </c>
       <c r="E224" t="inlineStr">
@@ -12976,11 +12976,11 @@
         </is>
       </c>
       <c r="C225" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D225" t="inlineStr">
         <is>
-          <t>04:20 PM – 05:20 PM</t>
+          <t>03:10 PM – 04:10 PM</t>
         </is>
       </c>
       <c r="E225" t="inlineStr">
@@ -13024,11 +13024,11 @@
     </row>
     <row r="226">
       <c r="A226" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="B226" t="inlineStr">
         <is>
-          <t>Wednesday, September 2, 2026</t>
+          <t>Monday, September 7, 2026</t>
         </is>
       </c>
       <c r="C226" t="n">
@@ -13080,19 +13080,19 @@
     </row>
     <row r="227">
       <c r="A227" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B227" t="inlineStr">
         <is>
-          <t>Thursday, September 3, 2026</t>
+          <t>Sunday, September 6, 2026</t>
         </is>
       </c>
       <c r="C227" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D227" t="inlineStr">
         <is>
-          <t>05:30 PM – 06:30 PM</t>
+          <t>04:20 PM – 05:20 PM</t>
         </is>
       </c>
       <c r="E227" t="inlineStr">
@@ -13136,11 +13136,11 @@
     </row>
     <row r="228">
       <c r="A228" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B228" t="inlineStr">
         <is>
-          <t>Sunday, September 6, 2026</t>
+          <t>Thursday, September 3, 2026</t>
         </is>
       </c>
       <c r="C228" t="n">
@@ -13192,19 +13192,19 @@
     </row>
     <row r="229">
       <c r="A229" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B229" t="inlineStr">
         <is>
-          <t>Sunday, September 6, 2026</t>
+          <t>Monday, September 7, 2026</t>
         </is>
       </c>
       <c r="C229" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D229" t="inlineStr">
         <is>
-          <t>05:30 PM – 06:30 PM</t>
+          <t>03:10 PM – 04:10 PM</t>
         </is>
       </c>
       <c r="E229" t="inlineStr">
@@ -13248,11 +13248,11 @@
     </row>
     <row r="230">
       <c r="A230" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B230" t="inlineStr">
         <is>
-          <t>Wednesday, September 2, 2026</t>
+          <t>Thursday, September 3, 2026</t>
         </is>
       </c>
       <c r="C230" t="n">
@@ -13304,19 +13304,19 @@
     </row>
     <row r="231">
       <c r="A231" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="B231" t="inlineStr">
         <is>
-          <t>Thursday, September 3, 2026</t>
+          <t>Monday, September 7, 2026</t>
         </is>
       </c>
       <c r="C231" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D231" t="inlineStr">
         <is>
-          <t>03:10 PM – 04:10 PM</t>
+          <t>04:20 PM – 05:20 PM</t>
         </is>
       </c>
       <c r="E231" t="inlineStr">
@@ -13360,19 +13360,19 @@
     </row>
     <row r="232">
       <c r="A232" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B232" t="inlineStr">
         <is>
-          <t>Sunday, September 6, 2026</t>
+          <t>Monday, September 7, 2026</t>
         </is>
       </c>
       <c r="C232" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D232" t="inlineStr">
         <is>
-          <t>04:20 PM – 05:20 PM</t>
+          <t>05:30 PM – 06:30 PM</t>
         </is>
       </c>
       <c r="E232" t="inlineStr">
@@ -13416,11 +13416,11 @@
     </row>
     <row r="233">
       <c r="A233" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B233" t="inlineStr">
         <is>
-          <t>Thursday, September 3, 2026</t>
+          <t>Wednesday, September 2, 2026</t>
         </is>
       </c>
       <c r="C233" t="n">
@@ -13480,11 +13480,11 @@
         </is>
       </c>
       <c r="C234" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D234" t="inlineStr">
         <is>
-          <t>04:20 PM – 05:20 PM</t>
+          <t>05:30 PM – 06:30 PM</t>
         </is>
       </c>
       <c r="E234" t="inlineStr">
@@ -13528,19 +13528,19 @@
     </row>
     <row r="235">
       <c r="A235" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="B235" t="inlineStr">
         <is>
-          <t>Wednesday, September 2, 2026</t>
+          <t>Sunday, September 6, 2026</t>
         </is>
       </c>
       <c r="C235" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D235" t="inlineStr">
         <is>
-          <t>03:10 PM – 04:10 PM</t>
+          <t>05:30 PM – 06:30 PM</t>
         </is>
       </c>
       <c r="E235" t="inlineStr">
@@ -13584,19 +13584,19 @@
     </row>
     <row r="236">
       <c r="A236" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B236" t="inlineStr">
         <is>
-          <t>Monday, September 7, 2026</t>
+          <t>Sunday, September 6, 2026</t>
         </is>
       </c>
       <c r="C236" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D236" t="inlineStr">
         <is>
-          <t>03:10 PM – 04:10 PM</t>
+          <t>04:20 PM – 05:20 PM</t>
         </is>
       </c>
       <c r="E236" t="inlineStr">
@@ -13640,19 +13640,19 @@
     </row>
     <row r="237">
       <c r="A237" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B237" t="inlineStr">
         <is>
-          <t>Sunday, September 6, 2026</t>
+          <t>Thursday, September 3, 2026</t>
         </is>
       </c>
       <c r="C237" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D237" t="inlineStr">
         <is>
-          <t>05:30 PM – 06:30 PM</t>
+          <t>04:20 PM – 05:20 PM</t>
         </is>
       </c>
       <c r="E237" t="inlineStr">
@@ -13704,11 +13704,11 @@
         </is>
       </c>
       <c r="C238" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D238" t="inlineStr">
         <is>
-          <t>05:30 PM – 06:30 PM</t>
+          <t>03:10 PM – 04:10 PM</t>
         </is>
       </c>
       <c r="E238" t="inlineStr">
@@ -13752,19 +13752,19 @@
     </row>
     <row r="239">
       <c r="A239" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B239" t="inlineStr">
         <is>
-          <t>Sunday, September 6, 2026</t>
+          <t>Thursday, September 3, 2026</t>
         </is>
       </c>
       <c r="C239" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D239" t="inlineStr">
         <is>
-          <t>04:20 PM – 05:20 PM</t>
+          <t>05:30 PM – 06:30 PM</t>
         </is>
       </c>
       <c r="E239" t="inlineStr">
@@ -13808,19 +13808,19 @@
     </row>
     <row r="240">
       <c r="A240" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B240" t="inlineStr">
         <is>
-          <t>Thursday, September 3, 2026</t>
+          <t>Wednesday, September 2, 2026</t>
         </is>
       </c>
       <c r="C240" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D240" t="inlineStr">
         <is>
-          <t>04:20 PM – 05:20 PM</t>
+          <t>05:30 PM – 06:30 PM</t>
         </is>
       </c>
       <c r="E240" t="inlineStr">
@@ -13920,19 +13920,19 @@
     </row>
     <row r="242">
       <c r="A242" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="B242" t="inlineStr">
         <is>
-          <t>Wednesday, September 2, 2026</t>
+          <t>Sunday, September 6, 2026</t>
         </is>
       </c>
       <c r="C242" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D242" t="inlineStr">
         <is>
-          <t>04:20 PM – 05:20 PM</t>
+          <t>05:30 PM – 06:30 PM</t>
         </is>
       </c>
       <c r="E242" t="inlineStr">
@@ -13984,11 +13984,11 @@
         </is>
       </c>
       <c r="C243" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D243" t="inlineStr">
         <is>
-          <t>05:30 PM – 06:30 PM</t>
+          <t>04:20 PM – 05:20 PM</t>
         </is>
       </c>
       <c r="E243" t="inlineStr">
@@ -14040,11 +14040,11 @@
         </is>
       </c>
       <c r="C244" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D244" t="inlineStr">
         <is>
-          <t>05:30 PM – 06:30 PM</t>
+          <t>04:20 PM – 05:20 PM</t>
         </is>
       </c>
       <c r="E244" t="inlineStr">
@@ -14088,19 +14088,19 @@
     </row>
     <row r="245">
       <c r="A245" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="B245" t="inlineStr">
         <is>
-          <t>Thursday, September 3, 2026</t>
+          <t>Monday, September 7, 2026</t>
         </is>
       </c>
       <c r="C245" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D245" t="inlineStr">
         <is>
-          <t>03:10 PM – 04:10 PM</t>
+          <t>05:30 PM – 06:30 PM</t>
         </is>
       </c>
       <c r="E245" t="inlineStr">
@@ -14144,19 +14144,19 @@
     </row>
     <row r="246">
       <c r="A246" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="B246" t="inlineStr">
         <is>
-          <t>Monday, September 7, 2026</t>
+          <t>Thursday, September 3, 2026</t>
         </is>
       </c>
       <c r="C246" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D246" t="inlineStr">
         <is>
-          <t>12:40 PM – 01:40 PM</t>
+          <t>03:10 PM – 04:10 PM</t>
         </is>
       </c>
       <c r="E246" t="inlineStr">
@@ -14200,11 +14200,11 @@
     </row>
     <row r="247">
       <c r="A247" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="B247" t="inlineStr">
         <is>
-          <t>Wednesday, September 2, 2026</t>
+          <t>Monday, September 7, 2026</t>
         </is>
       </c>
       <c r="C247" t="n">
@@ -14312,11 +14312,11 @@
     </row>
     <row r="249">
       <c r="A249" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B249" t="inlineStr">
         <is>
-          <t>Thursday, September 3, 2026</t>
+          <t>Wednesday, September 2, 2026</t>
         </is>
       </c>
       <c r="C249" t="n">
@@ -14368,11 +14368,11 @@
     </row>
     <row r="250">
       <c r="A250" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B250" t="inlineStr">
         <is>
-          <t>Sunday, September 6, 2026</t>
+          <t>Thursday, September 3, 2026</t>
         </is>
       </c>
       <c r="C250" t="n">
@@ -14432,11 +14432,11 @@
         </is>
       </c>
       <c r="C251" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D251" t="inlineStr">
         <is>
-          <t>12:40 PM – 01:40 PM</t>
+          <t>03:10 PM – 04:10 PM</t>
         </is>
       </c>
       <c r="E251" t="inlineStr">
@@ -14480,11 +14480,11 @@
     </row>
     <row r="252">
       <c r="A252" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="B252" t="inlineStr">
         <is>
-          <t>Thursday, September 3, 2026</t>
+          <t>Monday, September 7, 2026</t>
         </is>
       </c>
       <c r="C252" t="n">
@@ -14536,11 +14536,11 @@
     </row>
     <row r="253">
       <c r="A253" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="B253" t="inlineStr">
         <is>
-          <t>Sunday, September 6, 2026</t>
+          <t>Wednesday, September 2, 2026</t>
         </is>
       </c>
       <c r="C253" t="n">
@@ -14592,19 +14592,19 @@
     </row>
     <row r="254">
       <c r="A254" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="B254" t="inlineStr">
         <is>
-          <t>Wednesday, September 2, 2026</t>
+          <t>Sunday, September 6, 2026</t>
         </is>
       </c>
       <c r="C254" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D254" t="inlineStr">
         <is>
-          <t>03:10 PM – 04:10 PM</t>
+          <t>01:50 PM – 02:50 PM</t>
         </is>
       </c>
       <c r="E254" t="inlineStr">
@@ -14656,11 +14656,11 @@
         </is>
       </c>
       <c r="C255" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D255" t="inlineStr">
         <is>
-          <t>03:10 PM – 04:10 PM</t>
+          <t>12:40 PM – 01:40 PM</t>
         </is>
       </c>
       <c r="E255" t="inlineStr">
@@ -14704,19 +14704,19 @@
     </row>
     <row r="256">
       <c r="A256" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="B256" t="inlineStr">
         <is>
-          <t>Monday, September 7, 2026</t>
+          <t>Wednesday, September 2, 2026</t>
         </is>
       </c>
       <c r="C256" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D256" t="inlineStr">
         <is>
-          <t>03:10 PM – 04:10 PM</t>
+          <t>05:30 PM – 06:30 PM</t>
         </is>
       </c>
       <c r="E256" t="inlineStr">
@@ -14768,11 +14768,11 @@
         </is>
       </c>
       <c r="C257" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D257" t="inlineStr">
         <is>
-          <t>03:10 PM – 04:10 PM</t>
+          <t>05:30 PM – 06:30 PM</t>
         </is>
       </c>
       <c r="E257" t="inlineStr">
@@ -14816,11 +14816,11 @@
     </row>
     <row r="258">
       <c r="A258" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B258" t="inlineStr">
         <is>
-          <t>Sunday, September 6, 2026</t>
+          <t>Thursday, September 3, 2026</t>
         </is>
       </c>
       <c r="C258" t="n">
@@ -14872,11 +14872,11 @@
     </row>
     <row r="259">
       <c r="A259" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="B259" t="inlineStr">
         <is>
-          <t>Thursday, September 3, 2026</t>
+          <t>Monday, September 7, 2026</t>
         </is>
       </c>
       <c r="C259" t="n">
@@ -14928,19 +14928,19 @@
     </row>
     <row r="260">
       <c r="A260" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B260" t="inlineStr">
         <is>
-          <t>Sunday, September 6, 2026</t>
+          <t>Thursday, September 3, 2026</t>
         </is>
       </c>
       <c r="C260" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D260" t="inlineStr">
         <is>
-          <t>04:20 PM – 05:20 PM</t>
+          <t>03:10 PM – 04:10 PM</t>
         </is>
       </c>
       <c r="E260" t="inlineStr">
@@ -14984,19 +14984,19 @@
     </row>
     <row r="261">
       <c r="A261" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B261" t="inlineStr">
         <is>
-          <t>Thursday, September 3, 2026</t>
+          <t>Sunday, September 6, 2026</t>
         </is>
       </c>
       <c r="C261" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D261" t="inlineStr">
         <is>
-          <t>05:30 PM – 06:30 PM</t>
+          <t>03:10 PM – 04:10 PM</t>
         </is>
       </c>
       <c r="E261" t="inlineStr">
@@ -15040,19 +15040,19 @@
     </row>
     <row r="262">
       <c r="A262" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B262" t="inlineStr">
         <is>
-          <t>Thursday, September 3, 2026</t>
+          <t>Sunday, September 6, 2026</t>
         </is>
       </c>
       <c r="C262" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D262" t="inlineStr">
         <is>
-          <t>03:10 PM – 04:10 PM</t>
+          <t>04:20 PM – 05:20 PM</t>
         </is>
       </c>
       <c r="E262" t="inlineStr">
@@ -15104,11 +15104,11 @@
         </is>
       </c>
       <c r="C263" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D263" t="inlineStr">
         <is>
-          <t>05:30 PM – 06:30 PM</t>
+          <t>04:20 PM – 05:20 PM</t>
         </is>
       </c>
       <c r="E263" t="inlineStr">
@@ -15152,19 +15152,19 @@
     </row>
     <row r="264">
       <c r="A264" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="B264" t="inlineStr">
         <is>
-          <t>Wednesday, September 2, 2026</t>
+          <t>Monday, September 7, 2026</t>
         </is>
       </c>
       <c r="C264" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D264" t="inlineStr">
         <is>
-          <t>03:10 PM – 04:10 PM</t>
+          <t>05:30 PM – 06:30 PM</t>
         </is>
       </c>
       <c r="E264" t="inlineStr">
@@ -15216,11 +15216,11 @@
         </is>
       </c>
       <c r="C265" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D265" t="inlineStr">
         <is>
-          <t>04:20 PM – 05:20 PM</t>
+          <t>03:10 PM – 04:10 PM</t>
         </is>
       </c>
       <c r="E265" t="inlineStr">
@@ -15264,19 +15264,19 @@
     </row>
     <row r="266">
       <c r="A266" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B266" t="inlineStr">
         <is>
-          <t>Thursday, September 3, 2026</t>
+          <t>Sunday, September 6, 2026</t>
         </is>
       </c>
       <c r="C266" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D266" t="inlineStr">
         <is>
-          <t>04:20 PM – 05:20 PM</t>
+          <t>05:30 PM – 06:30 PM</t>
         </is>
       </c>
       <c r="E266" t="inlineStr">
@@ -15328,11 +15328,11 @@
         </is>
       </c>
       <c r="C267" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D267" t="inlineStr">
         <is>
-          <t>03:10 PM – 04:10 PM</t>
+          <t>05:30 PM – 06:30 PM</t>
         </is>
       </c>
       <c r="E267" t="inlineStr">
@@ -15384,11 +15384,11 @@
         </is>
       </c>
       <c r="C268" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D268" t="inlineStr">
         <is>
-          <t>04:20 PM – 05:20 PM</t>
+          <t>03:10 PM – 04:10 PM</t>
         </is>
       </c>
       <c r="E268" t="inlineStr">
@@ -15432,11 +15432,11 @@
     </row>
     <row r="269">
       <c r="A269" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="B269" t="inlineStr">
         <is>
-          <t>Wednesday, September 2, 2026</t>
+          <t>Monday, September 7, 2026</t>
         </is>
       </c>
       <c r="C269" t="n">
@@ -15488,19 +15488,19 @@
     </row>
     <row r="270">
       <c r="A270" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B270" t="inlineStr">
         <is>
-          <t>Thursday, September 3, 2026</t>
+          <t>Sunday, September 6, 2026</t>
         </is>
       </c>
       <c r="C270" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D270" t="inlineStr">
         <is>
-          <t>04:20 PM – 05:20 PM</t>
+          <t>05:30 PM – 06:30 PM</t>
         </is>
       </c>
       <c r="E270" t="inlineStr">
@@ -15544,19 +15544,19 @@
     </row>
     <row r="271">
       <c r="A271" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B271" t="inlineStr">
         <is>
-          <t>Thursday, September 3, 2026</t>
+          <t>Wednesday, September 2, 2026</t>
         </is>
       </c>
       <c r="C271" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D271" t="inlineStr">
         <is>
-          <t>03:10 PM – 04:10 PM</t>
+          <t>05:30 PM – 06:30 PM</t>
         </is>
       </c>
       <c r="E271" t="inlineStr">
@@ -15600,19 +15600,19 @@
     </row>
     <row r="272">
       <c r="A272" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B272" t="inlineStr">
         <is>
-          <t>Wednesday, September 2, 2026</t>
+          <t>Thursday, September 3, 2026</t>
         </is>
       </c>
       <c r="C272" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D272" t="inlineStr">
         <is>
-          <t>04:20 PM – 05:20 PM</t>
+          <t>05:30 PM – 06:30 PM</t>
         </is>
       </c>
       <c r="E272" t="inlineStr">
@@ -15656,19 +15656,19 @@
     </row>
     <row r="273">
       <c r="A273" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="B273" t="inlineStr">
         <is>
-          <t>Wednesday, September 2, 2026</t>
+          <t>Monday, September 7, 2026</t>
         </is>
       </c>
       <c r="C273" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D273" t="inlineStr">
         <is>
-          <t>03:10 PM – 04:10 PM</t>
+          <t>05:30 PM – 06:30 PM</t>
         </is>
       </c>
       <c r="E273" t="inlineStr">
@@ -15712,19 +15712,19 @@
     </row>
     <row r="274">
       <c r="A274" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="B274" t="inlineStr">
         <is>
-          <t>Monday, September 7, 2026</t>
+          <t>Wednesday, September 2, 2026</t>
         </is>
       </c>
       <c r="C274" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D274" t="inlineStr">
         <is>
-          <t>03:10 PM – 04:10 PM</t>
+          <t>04:20 PM – 05:20 PM</t>
         </is>
       </c>
       <c r="E274" t="inlineStr">
@@ -15768,11 +15768,11 @@
     </row>
     <row r="275">
       <c r="A275" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B275" t="inlineStr">
         <is>
-          <t>Sunday, September 6, 2026</t>
+          <t>Thursday, September 3, 2026</t>
         </is>
       </c>
       <c r="C275" t="n">
@@ -15824,11 +15824,11 @@
     </row>
     <row r="276">
       <c r="A276" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B276" t="inlineStr">
         <is>
-          <t>Thursday, September 3, 2026</t>
+          <t>Sunday, September 6, 2026</t>
         </is>
       </c>
       <c r="C276" t="n">
@@ -15880,11 +15880,11 @@
     </row>
     <row r="277">
       <c r="A277" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B277" t="inlineStr">
         <is>
-          <t>Thursday, September 3, 2026</t>
+          <t>Sunday, September 6, 2026</t>
         </is>
       </c>
       <c r="C277" t="n">
@@ -15944,11 +15944,11 @@
         </is>
       </c>
       <c r="C278" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D278" t="inlineStr">
         <is>
-          <t>03:10 PM – 04:10 PM</t>
+          <t>04:20 PM – 05:20 PM</t>
         </is>
       </c>
       <c r="E278" t="inlineStr">
@@ -16000,11 +16000,11 @@
         </is>
       </c>
       <c r="C279" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D279" t="inlineStr">
         <is>
-          <t>04:20 PM – 05:20 PM</t>
+          <t>05:30 PM – 06:30 PM</t>
         </is>
       </c>
       <c r="E279" t="inlineStr">
@@ -16048,19 +16048,19 @@
     </row>
     <row r="280">
       <c r="A280" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="B280" t="inlineStr">
         <is>
-          <t>Wednesday, September 2, 2026</t>
+          <t>Monday, September 7, 2026</t>
         </is>
       </c>
       <c r="C280" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D280" t="inlineStr">
         <is>
-          <t>05:30 PM – 06:30 PM</t>
+          <t>04:20 PM – 05:20 PM</t>
         </is>
       </c>
       <c r="E280" t="inlineStr">
@@ -16104,19 +16104,19 @@
     </row>
     <row r="281">
       <c r="A281" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="B281" t="inlineStr">
         <is>
-          <t>Wednesday, September 2, 2026</t>
+          <t>Monday, September 7, 2026</t>
         </is>
       </c>
       <c r="C281" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D281" t="inlineStr">
         <is>
-          <t>03:10 PM – 04:10 PM</t>
+          <t>05:30 PM – 06:30 PM</t>
         </is>
       </c>
       <c r="E281" t="inlineStr">
@@ -16160,11 +16160,11 @@
     </row>
     <row r="282">
       <c r="A282" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="B282" t="inlineStr">
         <is>
-          <t>Thursday, September 3, 2026</t>
+          <t>Monday, September 7, 2026</t>
         </is>
       </c>
       <c r="C282" t="n">
@@ -16216,19 +16216,19 @@
     </row>
     <row r="283">
       <c r="A283" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B283" t="inlineStr">
         <is>
-          <t>Sunday, September 6, 2026</t>
+          <t>Monday, September 7, 2026</t>
         </is>
       </c>
       <c r="C283" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D283" t="inlineStr">
         <is>
-          <t>04:20 PM – 05:20 PM</t>
+          <t>05:30 PM – 06:30 PM</t>
         </is>
       </c>
       <c r="E283" t="inlineStr">
@@ -16272,19 +16272,19 @@
     </row>
     <row r="284">
       <c r="A284" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B284" t="inlineStr">
         <is>
-          <t>Thursday, September 3, 2026</t>
+          <t>Wednesday, September 2, 2026</t>
         </is>
       </c>
       <c r="C284" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D284" t="inlineStr">
         <is>
-          <t>05:30 PM – 06:30 PM</t>
+          <t>04:20 PM – 05:20 PM</t>
         </is>
       </c>
       <c r="E284" t="inlineStr">
@@ -16328,19 +16328,19 @@
     </row>
     <row r="285">
       <c r="A285" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B285" t="inlineStr">
         <is>
-          <t>Thursday, September 3, 2026</t>
+          <t>Sunday, September 6, 2026</t>
         </is>
       </c>
       <c r="C285" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D285" t="inlineStr">
         <is>
-          <t>03:10 PM – 04:10 PM</t>
+          <t>05:30 PM – 06:30 PM</t>
         </is>
       </c>
       <c r="E285" t="inlineStr">
@@ -16384,19 +16384,19 @@
     </row>
     <row r="286">
       <c r="A286" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="B286" t="inlineStr">
         <is>
-          <t>Sunday, September 6, 2026</t>
+          <t>Wednesday, September 2, 2026</t>
         </is>
       </c>
       <c r="C286" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D286" t="inlineStr">
         <is>
-          <t>03:10 PM – 04:10 PM</t>
+          <t>05:30 PM – 06:30 PM</t>
         </is>
       </c>
       <c r="E286" t="inlineStr">
@@ -16440,19 +16440,19 @@
     </row>
     <row r="287">
       <c r="A287" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B287" t="inlineStr">
         <is>
-          <t>Wednesday, September 2, 2026</t>
+          <t>Thursday, September 3, 2026</t>
         </is>
       </c>
       <c r="C287" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D287" t="inlineStr">
         <is>
-          <t>05:30 PM – 06:30 PM</t>
+          <t>04:20 PM – 05:20 PM</t>
         </is>
       </c>
       <c r="E287" t="inlineStr">
@@ -16496,11 +16496,11 @@
     </row>
     <row r="288">
       <c r="A288" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="B288" t="inlineStr">
         <is>
-          <t>Wednesday, September 2, 2026</t>
+          <t>Sunday, September 6, 2026</t>
         </is>
       </c>
       <c r="C288" t="n">
@@ -16552,11 +16552,11 @@
     </row>
     <row r="289">
       <c r="A289" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B289" t="inlineStr">
         <is>
-          <t>Wednesday, September 2, 2026</t>
+          <t>Thursday, September 3, 2026</t>
         </is>
       </c>
       <c r="C289" t="n">
@@ -16608,19 +16608,19 @@
     </row>
     <row r="290">
       <c r="A290" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="B290" t="inlineStr">
         <is>
-          <t>Thursday, September 3, 2026</t>
+          <t>Monday, September 7, 2026</t>
         </is>
       </c>
       <c r="C290" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D290" t="inlineStr">
         <is>
-          <t>04:20 PM – 05:20 PM</t>
+          <t>05:30 PM – 06:30 PM</t>
         </is>
       </c>
       <c r="E290" t="inlineStr">
@@ -16672,11 +16672,11 @@
         </is>
       </c>
       <c r="C291" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D291" t="inlineStr">
         <is>
-          <t>05:30 PM – 06:30 PM</t>
+          <t>03:10 PM – 04:10 PM</t>
         </is>
       </c>
       <c r="E291" t="inlineStr">
@@ -16720,19 +16720,19 @@
     </row>
     <row r="292">
       <c r="A292" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B292" t="inlineStr">
         <is>
-          <t>Sunday, September 6, 2026</t>
+          <t>Monday, September 7, 2026</t>
         </is>
       </c>
       <c r="C292" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D292" t="inlineStr">
         <is>
-          <t>03:10 PM – 04:10 PM</t>
+          <t>04:20 PM – 05:20 PM</t>
         </is>
       </c>
       <c r="E292" t="inlineStr">
@@ -16776,11 +16776,11 @@
     </row>
     <row r="293">
       <c r="A293" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B293" t="inlineStr">
         <is>
-          <t>Thursday, September 3, 2026</t>
+          <t>Wednesday, September 2, 2026</t>
         </is>
       </c>
       <c r="C293" t="n">
@@ -16832,11 +16832,11 @@
     </row>
     <row r="294">
       <c r="A294" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B294" t="inlineStr">
         <is>
-          <t>Sunday, September 6, 2026</t>
+          <t>Thursday, September 3, 2026</t>
         </is>
       </c>
       <c r="C294" t="n">
@@ -16888,19 +16888,19 @@
     </row>
     <row r="295">
       <c r="A295" t="n">
+        <v>4</v>
+      </c>
+      <c r="B295" t="inlineStr">
+        <is>
+          <t>Monday, September 7, 2026</t>
+        </is>
+      </c>
+      <c r="C295" t="n">
         <v>1</v>
       </c>
-      <c r="B295" t="inlineStr">
-        <is>
-          <t>Wednesday, September 2, 2026</t>
-        </is>
-      </c>
-      <c r="C295" t="n">
-        <v>3</v>
-      </c>
       <c r="D295" t="inlineStr">
         <is>
-          <t>05:30 PM – 06:30 PM</t>
+          <t>03:10 PM – 04:10 PM</t>
         </is>
       </c>
       <c r="E295" t="inlineStr">
@@ -16952,11 +16952,11 @@
         </is>
       </c>
       <c r="C296" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D296" t="inlineStr">
         <is>
-          <t>03:10 PM – 04:10 PM</t>
+          <t>05:30 PM – 06:30 PM</t>
         </is>
       </c>
       <c r="E296" t="inlineStr">
@@ -17000,19 +17000,19 @@
     </row>
     <row r="297">
       <c r="A297" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="B297" t="inlineStr">
         <is>
-          <t>Wednesday, September 2, 2026</t>
+          <t>Sunday, September 6, 2026</t>
         </is>
       </c>
       <c r="C297" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D297" t="inlineStr">
         <is>
-          <t>04:20 PM – 05:20 PM</t>
+          <t>05:30 PM – 06:30 PM</t>
         </is>
       </c>
       <c r="E297" t="inlineStr">
@@ -17112,11 +17112,11 @@
     </row>
     <row r="299">
       <c r="A299" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B299" t="inlineStr">
         <is>
-          <t>Sunday, September 6, 2026</t>
+          <t>Thursday, September 3, 2026</t>
         </is>
       </c>
       <c r="C299" t="n">
@@ -17176,11 +17176,11 @@
         </is>
       </c>
       <c r="C300" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D300" t="inlineStr">
         <is>
-          <t>05:30 PM – 06:30 PM</t>
+          <t>03:10 PM – 04:10 PM</t>
         </is>
       </c>
       <c r="E300" t="inlineStr">
@@ -17224,19 +17224,19 @@
     </row>
     <row r="301">
       <c r="A301" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B301" t="inlineStr">
         <is>
-          <t>Thursday, September 3, 2026</t>
+          <t>Wednesday, September 2, 2026</t>
         </is>
       </c>
       <c r="C301" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D301" t="inlineStr">
         <is>
-          <t>05:30 PM – 06:30 PM</t>
+          <t>04:20 PM – 05:20 PM</t>
         </is>
       </c>
       <c r="E301" t="inlineStr">
@@ -17288,11 +17288,11 @@
         </is>
       </c>
       <c r="C302" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D302" t="inlineStr">
         <is>
-          <t>04:20 PM – 05:20 PM</t>
+          <t>05:30 PM – 06:30 PM</t>
         </is>
       </c>
       <c r="E302" t="inlineStr">
@@ -17336,19 +17336,19 @@
     </row>
     <row r="303">
       <c r="A303" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="B303" t="inlineStr">
         <is>
-          <t>Monday, September 7, 2026</t>
+          <t>Thursday, September 3, 2026</t>
         </is>
       </c>
       <c r="C303" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D303" t="inlineStr">
         <is>
-          <t>03:10 PM – 04:10 PM</t>
+          <t>05:30 PM – 06:30 PM</t>
         </is>
       </c>
       <c r="E303" t="inlineStr">
@@ -17448,11 +17448,11 @@
     </row>
     <row r="305">
       <c r="A305" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="B305" t="inlineStr">
         <is>
-          <t>Thursday, September 3, 2026</t>
+          <t>Monday, September 7, 2026</t>
         </is>
       </c>
       <c r="C305" t="n">
@@ -17504,11 +17504,11 @@
     </row>
     <row r="306">
       <c r="A306" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="B306" t="inlineStr">
         <is>
-          <t>Thursday, September 3, 2026</t>
+          <t>Monday, September 7, 2026</t>
         </is>
       </c>
       <c r="C306" t="n">
@@ -17616,19 +17616,19 @@
     </row>
     <row r="308">
       <c r="A308" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="B308" t="inlineStr">
         <is>
-          <t>Wednesday, September 2, 2026</t>
+          <t>Monday, September 7, 2026</t>
         </is>
       </c>
       <c r="C308" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D308" t="inlineStr">
         <is>
-          <t>04:20 PM – 05:20 PM</t>
+          <t>05:30 PM – 06:30 PM</t>
         </is>
       </c>
       <c r="E308" t="inlineStr">
@@ -17680,11 +17680,11 @@
         </is>
       </c>
       <c r="C309" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D309" t="inlineStr">
         <is>
-          <t>03:10 PM – 04:10 PM</t>
+          <t>04:20 PM – 05:20 PM</t>
         </is>
       </c>
       <c r="E309" t="inlineStr">
@@ -17736,11 +17736,11 @@
         </is>
       </c>
       <c r="C310" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D310" t="inlineStr">
         <is>
-          <t>03:10 PM – 04:10 PM</t>
+          <t>05:30 PM – 06:30 PM</t>
         </is>
       </c>
       <c r="E310" t="inlineStr">
@@ -17784,19 +17784,19 @@
     </row>
     <row r="311">
       <c r="A311" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="B311" t="inlineStr">
         <is>
-          <t>Sunday, September 6, 2026</t>
+          <t>Wednesday, September 2, 2026</t>
         </is>
       </c>
       <c r="C311" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D311" t="inlineStr">
         <is>
-          <t>04:20 PM – 05:20 PM</t>
+          <t>05:30 PM – 06:30 PM</t>
         </is>
       </c>
       <c r="E311" t="inlineStr">
@@ -17840,11 +17840,11 @@
     </row>
     <row r="312">
       <c r="A312" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B312" t="inlineStr">
         <is>
-          <t>Sunday, September 6, 2026</t>
+          <t>Monday, September 7, 2026</t>
         </is>
       </c>
       <c r="C312" t="n">
@@ -17896,19 +17896,19 @@
     </row>
     <row r="313">
       <c r="A313" t="n">
+        <v>4</v>
+      </c>
+      <c r="B313" t="inlineStr">
+        <is>
+          <t>Monday, September 7, 2026</t>
+        </is>
+      </c>
+      <c r="C313" t="n">
         <v>1</v>
       </c>
-      <c r="B313" t="inlineStr">
-        <is>
-          <t>Wednesday, September 2, 2026</t>
-        </is>
-      </c>
-      <c r="C313" t="n">
-        <v>3</v>
-      </c>
       <c r="D313" t="inlineStr">
         <is>
-          <t>05:30 PM – 06:30 PM</t>
+          <t>03:10 PM – 04:10 PM</t>
         </is>
       </c>
       <c r="E313" t="inlineStr">
@@ -17952,11 +17952,11 @@
     </row>
     <row r="314">
       <c r="A314" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B314" t="inlineStr">
         <is>
-          <t>Thursday, September 3, 2026</t>
+          <t>Wednesday, September 2, 2026</t>
         </is>
       </c>
       <c r="C314" t="n">
@@ -18008,19 +18008,19 @@
     </row>
     <row r="315">
       <c r="A315" t="n">
+        <v>2</v>
+      </c>
+      <c r="B315" t="inlineStr">
+        <is>
+          <t>Thursday, September 3, 2026</t>
+        </is>
+      </c>
+      <c r="C315" t="n">
         <v>1</v>
       </c>
-      <c r="B315" t="inlineStr">
-        <is>
-          <t>Wednesday, September 2, 2026</t>
-        </is>
-      </c>
-      <c r="C315" t="n">
-        <v>2</v>
-      </c>
       <c r="D315" t="inlineStr">
         <is>
-          <t>04:20 PM – 05:20 PM</t>
+          <t>03:10 PM – 04:10 PM</t>
         </is>
       </c>
       <c r="E315" t="inlineStr">
@@ -18064,19 +18064,19 @@
     </row>
     <row r="316">
       <c r="A316" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B316" t="inlineStr">
         <is>
-          <t>Thursday, September 3, 2026</t>
+          <t>Sunday, September 6, 2026</t>
         </is>
       </c>
       <c r="C316" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D316" t="inlineStr">
         <is>
-          <t>05:30 PM – 06:30 PM</t>
+          <t>04:20 PM – 05:20 PM</t>
         </is>
       </c>
       <c r="E316" t="inlineStr">
@@ -18184,11 +18184,11 @@
         </is>
       </c>
       <c r="C318" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D318" t="inlineStr">
         <is>
-          <t>03:10 PM – 04:10 PM</t>
+          <t>05:30 PM – 06:30 PM</t>
         </is>
       </c>
       <c r="E318" t="inlineStr">
@@ -18232,19 +18232,19 @@
     </row>
     <row r="319">
       <c r="A319" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="B319" t="inlineStr">
         <is>
-          <t>Wednesday, September 2, 2026</t>
+          <t>Monday, September 7, 2026</t>
         </is>
       </c>
       <c r="C319" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D319" t="inlineStr">
         <is>
-          <t>03:10 PM – 04:10 PM</t>
+          <t>05:30 PM – 06:30 PM</t>
         </is>
       </c>
       <c r="E319" t="inlineStr">
@@ -18288,19 +18288,19 @@
     </row>
     <row r="320">
       <c r="A320" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B320" t="inlineStr">
         <is>
-          <t>Sunday, September 6, 2026</t>
+          <t>Monday, September 7, 2026</t>
         </is>
       </c>
       <c r="C320" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D320" t="inlineStr">
         <is>
-          <t>05:30 PM – 06:30 PM</t>
+          <t>04:20 PM – 05:20 PM</t>
         </is>
       </c>
       <c r="E320" t="inlineStr">
@@ -18344,11 +18344,11 @@
     </row>
     <row r="321">
       <c r="A321" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B321" t="inlineStr">
         <is>
-          <t>Thursday, September 3, 2026</t>
+          <t>Sunday, September 6, 2026</t>
         </is>
       </c>
       <c r="C321" t="n">
@@ -18400,19 +18400,19 @@
     </row>
     <row r="322">
       <c r="A322" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="B322" t="inlineStr">
         <is>
-          <t>Monday, September 7, 2026</t>
+          <t>Thursday, September 3, 2026</t>
         </is>
       </c>
       <c r="C322" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D322" t="inlineStr">
         <is>
-          <t>04:20 PM – 05:20 PM</t>
+          <t>05:30 PM – 06:30 PM</t>
         </is>
       </c>
       <c r="E322" t="inlineStr">
@@ -18456,19 +18456,19 @@
     </row>
     <row r="323">
       <c r="A323" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="B323" t="inlineStr">
         <is>
-          <t>Thursday, September 3, 2026</t>
+          <t>Monday, September 7, 2026</t>
         </is>
       </c>
       <c r="C323" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D323" t="inlineStr">
         <is>
-          <t>05:30 PM – 06:30 PM</t>
+          <t>03:10 PM – 04:10 PM</t>
         </is>
       </c>
       <c r="E323" t="inlineStr">
@@ -18512,19 +18512,19 @@
     </row>
     <row r="324">
       <c r="A324" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="B324" t="inlineStr">
         <is>
-          <t>Sunday, September 6, 2026</t>
+          <t>Wednesday, September 2, 2026</t>
         </is>
       </c>
       <c r="C324" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D324" t="inlineStr">
         <is>
-          <t>03:10 PM – 04:10 PM</t>
+          <t>04:20 PM – 05:20 PM</t>
         </is>
       </c>
       <c r="E324" t="inlineStr">
@@ -18568,11 +18568,11 @@
     </row>
     <row r="325">
       <c r="A325" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B325" t="inlineStr">
         <is>
-          <t>Thursday, September 3, 2026</t>
+          <t>Sunday, September 6, 2026</t>
         </is>
       </c>
       <c r="C325" t="n">
@@ -18624,19 +18624,19 @@
     </row>
     <row r="326">
       <c r="A326" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="B326" t="inlineStr">
         <is>
-          <t>Sunday, September 6, 2026</t>
+          <t>Wednesday, September 2, 2026</t>
         </is>
       </c>
       <c r="C326" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D326" t="inlineStr">
         <is>
-          <t>04:20 PM – 05:20 PM</t>
+          <t>05:30 PM – 06:30 PM</t>
         </is>
       </c>
       <c r="E326" t="inlineStr">
@@ -18680,19 +18680,19 @@
     </row>
     <row r="327">
       <c r="A327" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B327" t="inlineStr">
         <is>
-          <t>Wednesday, September 2, 2026</t>
+          <t>Thursday, September 3, 2026</t>
         </is>
       </c>
       <c r="C327" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D327" t="inlineStr">
         <is>
-          <t>05:30 PM – 06:30 PM</t>
+          <t>04:20 PM – 05:20 PM</t>
         </is>
       </c>
       <c r="E327" t="inlineStr">
@@ -18744,11 +18744,11 @@
         </is>
       </c>
       <c r="C328" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D328" t="inlineStr">
         <is>
-          <t>04:20 PM – 05:20 PM</t>
+          <t>03:10 PM – 04:10 PM</t>
         </is>
       </c>
       <c r="E328" t="inlineStr">
@@ -18848,19 +18848,19 @@
     </row>
     <row r="330">
       <c r="A330" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B330" t="inlineStr">
         <is>
-          <t>Sunday, September 6, 2026</t>
+          <t>Monday, September 7, 2026</t>
         </is>
       </c>
       <c r="C330" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D330" t="inlineStr">
         <is>
-          <t>04:20 PM – 05:20 PM</t>
+          <t>05:30 PM – 06:30 PM</t>
         </is>
       </c>
       <c r="E330" t="inlineStr">
@@ -18904,19 +18904,19 @@
     </row>
     <row r="331">
       <c r="A331" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B331" t="inlineStr">
         <is>
-          <t>Thursday, September 3, 2026</t>
+          <t>Sunday, September 6, 2026</t>
         </is>
       </c>
       <c r="C331" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D331" t="inlineStr">
         <is>
-          <t>04:20 PM – 05:20 PM</t>
+          <t>05:30 PM – 06:30 PM</t>
         </is>
       </c>
       <c r="E331" t="inlineStr">
@@ -18960,19 +18960,19 @@
     </row>
     <row r="332">
       <c r="A332" t="n">
+        <v>3</v>
+      </c>
+      <c r="B332" t="inlineStr">
+        <is>
+          <t>Sunday, September 6, 2026</t>
+        </is>
+      </c>
+      <c r="C332" t="n">
         <v>1</v>
       </c>
-      <c r="B332" t="inlineStr">
-        <is>
-          <t>Wednesday, September 2, 2026</t>
-        </is>
-      </c>
-      <c r="C332" t="n">
-        <v>3</v>
-      </c>
       <c r="D332" t="inlineStr">
         <is>
-          <t>05:30 PM – 06:30 PM</t>
+          <t>03:10 PM – 04:10 PM</t>
         </is>
       </c>
       <c r="E332" t="inlineStr">
@@ -19016,19 +19016,19 @@
     </row>
     <row r="333">
       <c r="A333" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B333" t="inlineStr">
         <is>
-          <t>Sunday, September 6, 2026</t>
+          <t>Thursday, September 3, 2026</t>
         </is>
       </c>
       <c r="C333" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D333" t="inlineStr">
         <is>
-          <t>03:10 PM – 04:10 PM</t>
+          <t>04:20 PM – 05:20 PM</t>
         </is>
       </c>
       <c r="E333" t="inlineStr">
@@ -19072,11 +19072,11 @@
     </row>
     <row r="334">
       <c r="A334" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="B334" t="inlineStr">
         <is>
-          <t>Sunday, September 6, 2026</t>
+          <t>Wednesday, September 2, 2026</t>
         </is>
       </c>
       <c r="C334" t="n">
@@ -19136,11 +19136,11 @@
         </is>
       </c>
       <c r="C335" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D335" t="inlineStr">
         <is>
-          <t>03:10 PM – 04:10 PM</t>
+          <t>05:30 PM – 06:30 PM</t>
         </is>
       </c>
       <c r="E335" t="inlineStr">
@@ -19192,11 +19192,11 @@
         </is>
       </c>
       <c r="C336" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D336" t="inlineStr">
         <is>
-          <t>05:30 PM – 06:30 PM</t>
+          <t>03:10 PM – 04:10 PM</t>
         </is>
       </c>
       <c r="E336" t="inlineStr">
@@ -19248,11 +19248,11 @@
         </is>
       </c>
       <c r="C337" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D337" t="inlineStr">
         <is>
-          <t>04:20 PM – 05:20 PM</t>
+          <t>03:10 PM – 04:10 PM</t>
         </is>
       </c>
       <c r="E337" t="inlineStr">
@@ -19304,11 +19304,11 @@
         </is>
       </c>
       <c r="C338" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D338" t="inlineStr">
         <is>
-          <t>03:10 PM – 04:10 PM</t>
+          <t>04:20 PM – 05:20 PM</t>
         </is>
       </c>
       <c r="E338" t="inlineStr">
@@ -19352,19 +19352,19 @@
     </row>
     <row r="339">
       <c r="A339" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B339" t="inlineStr">
         <is>
-          <t>Sunday, September 6, 2026</t>
+          <t>Monday, September 7, 2026</t>
         </is>
       </c>
       <c r="C339" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D339" t="inlineStr">
         <is>
-          <t>05:30 PM – 06:30 PM</t>
+          <t>03:10 PM – 04:10 PM</t>
         </is>
       </c>
       <c r="E339" t="inlineStr">
@@ -19408,11 +19408,11 @@
     </row>
     <row r="340">
       <c r="A340" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="B340" t="inlineStr">
         <is>
-          <t>Wednesday, September 2, 2026</t>
+          <t>Sunday, September 6, 2026</t>
         </is>
       </c>
       <c r="C340" t="n">
@@ -19464,19 +19464,19 @@
     </row>
     <row r="341">
       <c r="A341" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="B341" t="inlineStr">
         <is>
-          <t>Monday, September 7, 2026</t>
+          <t>Wednesday, September 2, 2026</t>
         </is>
       </c>
       <c r="C341" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D341" t="inlineStr">
         <is>
-          <t>04:20 PM – 05:20 PM</t>
+          <t>03:10 PM – 04:10 PM</t>
         </is>
       </c>
       <c r="E341" t="inlineStr">
@@ -19520,11 +19520,11 @@
     </row>
     <row r="342">
       <c r="A342" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B342" t="inlineStr">
         <is>
-          <t>Wednesday, September 2, 2026</t>
+          <t>Thursday, September 3, 2026</t>
         </is>
       </c>
       <c r="C342" t="n">
@@ -19576,19 +19576,19 @@
     </row>
     <row r="343">
       <c r="A343" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="B343" t="inlineStr">
         <is>
-          <t>Monday, September 7, 2026</t>
+          <t>Wednesday, September 2, 2026</t>
         </is>
       </c>
       <c r="C343" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D343" t="inlineStr">
         <is>
-          <t>03:10 PM – 04:10 PM</t>
+          <t>05:30 PM – 06:30 PM</t>
         </is>
       </c>
       <c r="E343" t="inlineStr">
@@ -19632,19 +19632,19 @@
     </row>
     <row r="344">
       <c r="A344" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B344" t="inlineStr">
         <is>
-          <t>Sunday, September 6, 2026</t>
+          <t>Thursday, September 3, 2026</t>
         </is>
       </c>
       <c r="C344" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D344" t="inlineStr">
         <is>
-          <t>04:20 PM – 05:20 PM</t>
+          <t>05:30 PM – 06:30 PM</t>
         </is>
       </c>
       <c r="E344" t="inlineStr">
@@ -19688,19 +19688,19 @@
     </row>
     <row r="345">
       <c r="A345" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="B345" t="inlineStr">
         <is>
-          <t>Thursday, September 3, 2026</t>
+          <t>Monday, September 7, 2026</t>
         </is>
       </c>
       <c r="C345" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D345" t="inlineStr">
         <is>
-          <t>03:10 PM – 04:10 PM</t>
+          <t>05:30 PM – 06:30 PM</t>
         </is>
       </c>
       <c r="E345" t="inlineStr">
@@ -19744,11 +19744,11 @@
     </row>
     <row r="346">
       <c r="A346" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B346" t="inlineStr">
         <is>
-          <t>Thursday, September 3, 2026</t>
+          <t>Sunday, September 6, 2026</t>
         </is>
       </c>
       <c r="C346" t="n">
@@ -19800,19 +19800,19 @@
     </row>
     <row r="347">
       <c r="A347" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="B347" t="inlineStr">
         <is>
-          <t>Thursday, September 3, 2026</t>
+          <t>Monday, September 7, 2026</t>
         </is>
       </c>
       <c r="C347" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D347" t="inlineStr">
         <is>
-          <t>05:30 PM – 06:30 PM</t>
+          <t>04:20 PM – 05:20 PM</t>
         </is>
       </c>
       <c r="E347" t="inlineStr">
@@ -19856,11 +19856,11 @@
     </row>
     <row r="348">
       <c r="A348" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="B348" t="inlineStr">
         <is>
-          <t>Wednesday, September 2, 2026</t>
+          <t>Sunday, September 6, 2026</t>
         </is>
       </c>
       <c r="C348" t="n">
@@ -19968,19 +19968,19 @@
     </row>
     <row r="350">
       <c r="A350" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B350" t="inlineStr">
         <is>
-          <t>Thursday, September 3, 2026</t>
+          <t>Sunday, September 6, 2026</t>
         </is>
       </c>
       <c r="C350" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D350" t="inlineStr">
         <is>
-          <t>05:30 PM – 06:30 PM</t>
+          <t>04:20 PM – 05:20 PM</t>
         </is>
       </c>
       <c r="E350" t="inlineStr">
@@ -20024,19 +20024,19 @@
     </row>
     <row r="351">
       <c r="A351" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="B351" t="inlineStr">
         <is>
-          <t>Sunday, September 6, 2026</t>
+          <t>Wednesday, September 2, 2026</t>
         </is>
       </c>
       <c r="C351" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D351" t="inlineStr">
         <is>
-          <t>05:30 PM – 06:30 PM</t>
+          <t>03:10 PM – 04:10 PM</t>
         </is>
       </c>
       <c r="E351" t="inlineStr">
@@ -20080,11 +20080,11 @@
     </row>
     <row r="352">
       <c r="A352" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B352" t="inlineStr">
         <is>
-          <t>Sunday, September 6, 2026</t>
+          <t>Thursday, September 3, 2026</t>
         </is>
       </c>
       <c r="C352" t="n">
@@ -20136,19 +20136,19 @@
     </row>
     <row r="353">
       <c r="A353" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B353" t="inlineStr">
         <is>
-          <t>Sunday, September 6, 2026</t>
+          <t>Thursday, September 3, 2026</t>
         </is>
       </c>
       <c r="C353" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D353" t="inlineStr">
         <is>
-          <t>03:10 PM – 04:10 PM</t>
+          <t>05:30 PM – 06:30 PM</t>
         </is>
       </c>
       <c r="E353" t="inlineStr">
@@ -20192,11 +20192,11 @@
     </row>
     <row r="354">
       <c r="A354" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B354" t="inlineStr">
         <is>
-          <t>Thursday, September 3, 2026</t>
+          <t>Wednesday, September 2, 2026</t>
         </is>
       </c>
       <c r="C354" t="n">
@@ -20248,19 +20248,19 @@
     </row>
     <row r="355">
       <c r="A355" t="n">
+        <v>2</v>
+      </c>
+      <c r="B355" t="inlineStr">
+        <is>
+          <t>Thursday, September 3, 2026</t>
+        </is>
+      </c>
+      <c r="C355" t="n">
         <v>1</v>
       </c>
-      <c r="B355" t="inlineStr">
-        <is>
-          <t>Wednesday, September 2, 2026</t>
-        </is>
-      </c>
-      <c r="C355" t="n">
-        <v>3</v>
-      </c>
       <c r="D355" t="inlineStr">
         <is>
-          <t>05:30 PM – 06:30 PM</t>
+          <t>03:10 PM – 04:10 PM</t>
         </is>
       </c>
       <c r="E355" t="inlineStr">
@@ -20304,11 +20304,11 @@
     </row>
     <row r="356">
       <c r="A356" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="B356" t="inlineStr">
         <is>
-          <t>Wednesday, September 2, 2026</t>
+          <t>Monday, September 7, 2026</t>
         </is>
       </c>
       <c r="C356" t="n">
@@ -20360,19 +20360,19 @@
     </row>
     <row r="357">
       <c r="A357" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="B357" t="inlineStr">
         <is>
-          <t>Thursday, September 3, 2026</t>
+          <t>Monday, September 7, 2026</t>
         </is>
       </c>
       <c r="C357" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D357" t="inlineStr">
         <is>
-          <t>03:10 PM – 04:10 PM</t>
+          <t>05:30 PM – 06:30 PM</t>
         </is>
       </c>
       <c r="E357" t="inlineStr">
@@ -20416,19 +20416,19 @@
     </row>
     <row r="358">
       <c r="A358" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="B358" t="inlineStr">
         <is>
-          <t>Wednesday, September 2, 2026</t>
+          <t>Sunday, September 6, 2026</t>
         </is>
       </c>
       <c r="C358" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D358" t="inlineStr">
         <is>
-          <t>03:10 PM – 04:10 PM</t>
+          <t>05:30 PM – 06:30 PM</t>
         </is>
       </c>
       <c r="E358" t="inlineStr">
@@ -20480,11 +20480,11 @@
         </is>
       </c>
       <c r="C359" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D359" t="inlineStr">
         <is>
-          <t>04:20 PM – 05:20 PM</t>
+          <t>03:10 PM – 04:10 PM</t>
         </is>
       </c>
       <c r="E359" t="inlineStr">
@@ -20528,11 +20528,11 @@
     </row>
     <row r="360">
       <c r="A360" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B360" t="inlineStr">
         <is>
-          <t>Sunday, September 6, 2026</t>
+          <t>Thursday, September 3, 2026</t>
         </is>
       </c>
       <c r="C360" t="n">
@@ -20584,19 +20584,19 @@
     </row>
     <row r="361">
       <c r="A361" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="B361" t="inlineStr">
         <is>
-          <t>Thursday, September 3, 2026</t>
+          <t>Monday, September 7, 2026</t>
         </is>
       </c>
       <c r="C361" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D361" t="inlineStr">
         <is>
-          <t>05:30 PM – 06:30 PM</t>
+          <t>04:20 PM – 05:20 PM</t>
         </is>
       </c>
       <c r="E361" t="inlineStr">
@@ -20648,11 +20648,11 @@
         </is>
       </c>
       <c r="C362" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D362" t="inlineStr">
         <is>
-          <t>05:30 PM – 06:30 PM</t>
+          <t>03:10 PM – 04:10 PM</t>
         </is>
       </c>
       <c r="E362" t="inlineStr">
@@ -20696,11 +20696,11 @@
     </row>
     <row r="363">
       <c r="A363" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B363" t="inlineStr">
         <is>
-          <t>Sunday, September 6, 2026</t>
+          <t>Thursday, September 3, 2026</t>
         </is>
       </c>
       <c r="C363" t="n">
@@ -20752,11 +20752,11 @@
     </row>
     <row r="364">
       <c r="A364" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B364" t="inlineStr">
         <is>
-          <t>Thursday, September 3, 2026</t>
+          <t>Sunday, September 6, 2026</t>
         </is>
       </c>
       <c r="C364" t="n">
@@ -20808,19 +20808,19 @@
     </row>
     <row r="365">
       <c r="A365" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B365" t="inlineStr">
         <is>
-          <t>Thursday, September 3, 2026</t>
+          <t>Sunday, September 6, 2026</t>
         </is>
       </c>
       <c r="C365" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D365" t="inlineStr">
         <is>
-          <t>03:10 PM – 04:10 PM</t>
+          <t>05:30 PM – 06:30 PM</t>
         </is>
       </c>
       <c r="E365" t="inlineStr">
@@ -20864,11 +20864,11 @@
     </row>
     <row r="366">
       <c r="A366" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B366" t="inlineStr">
         <is>
-          <t>Wednesday, September 2, 2026</t>
+          <t>Thursday, September 3, 2026</t>
         </is>
       </c>
       <c r="C366" t="n">
@@ -20928,11 +20928,11 @@
         </is>
       </c>
       <c r="C367" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D367" t="inlineStr">
         <is>
-          <t>04:20 PM – 05:20 PM</t>
+          <t>05:30 PM – 06:30 PM</t>
         </is>
       </c>
       <c r="E367" t="inlineStr">
@@ -21032,19 +21032,19 @@
     </row>
     <row r="369">
       <c r="A369" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B369" t="inlineStr">
         <is>
-          <t>Monday, September 7, 2026</t>
+          <t>Sunday, September 6, 2026</t>
         </is>
       </c>
       <c r="C369" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D369" t="inlineStr">
         <is>
-          <t>10:25 AM – 11:25 AM</t>
+          <t>09:00 AM – 10:00 AM</t>
         </is>
       </c>
       <c r="E369" t="inlineStr">
@@ -21088,19 +21088,19 @@
     </row>
     <row r="370">
       <c r="A370" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B370" t="inlineStr">
         <is>
-          <t>Sunday, September 6, 2026</t>
+          <t>Thursday, September 3, 2026</t>
         </is>
       </c>
       <c r="C370" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D370" t="inlineStr">
         <is>
-          <t>09:00 AM – 10:00 AM</t>
+          <t>10:25 AM – 11:25 AM</t>
         </is>
       </c>
       <c r="E370" t="inlineStr">
@@ -21152,11 +21152,11 @@
         </is>
       </c>
       <c r="C371" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D371" t="inlineStr">
         <is>
-          <t>09:00 AM – 10:00 AM</t>
+          <t>08:00 AM – 09:00 AM</t>
         </is>
       </c>
       <c r="E371" t="inlineStr">
@@ -21200,19 +21200,19 @@
     </row>
     <row r="372">
       <c r="A372" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="B372" t="inlineStr">
         <is>
-          <t>Monday, September 7, 2026</t>
+          <t>Wednesday, September 2, 2026</t>
         </is>
       </c>
       <c r="C372" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D372" t="inlineStr">
         <is>
-          <t>08:00 AM – 09:00 AM</t>
+          <t>10:25 AM – 11:25 AM</t>
         </is>
       </c>
       <c r="E372" t="inlineStr">
@@ -21264,11 +21264,11 @@
         </is>
       </c>
       <c r="C373" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D373" t="inlineStr">
         <is>
-          <t>08:00 AM – 09:00 AM</t>
+          <t>10:25 AM – 11:25 AM</t>
         </is>
       </c>
       <c r="E373" t="inlineStr">
@@ -21312,11 +21312,11 @@
     </row>
     <row r="374">
       <c r="A374" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="B374" t="inlineStr">
         <is>
-          <t>Thursday, September 3, 2026</t>
+          <t>Monday, September 7, 2026</t>
         </is>
       </c>
       <c r="C374" t="n">
@@ -21368,19 +21368,19 @@
     </row>
     <row r="375">
       <c r="A375" t="n">
+        <v>3</v>
+      </c>
+      <c r="B375" t="inlineStr">
+        <is>
+          <t>Sunday, September 6, 2026</t>
+        </is>
+      </c>
+      <c r="C375" t="n">
         <v>1</v>
       </c>
-      <c r="B375" t="inlineStr">
-        <is>
-          <t>Wednesday, September 2, 2026</t>
-        </is>
-      </c>
-      <c r="C375" t="n">
-        <v>3</v>
-      </c>
       <c r="D375" t="inlineStr">
         <is>
-          <t>10:25 AM – 11:25 AM</t>
+          <t>08:00 AM – 09:00 AM</t>
         </is>
       </c>
       <c r="E375" t="inlineStr">
@@ -21424,11 +21424,11 @@
     </row>
     <row r="376">
       <c r="A376" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B376" t="inlineStr">
         <is>
-          <t>Wednesday, September 2, 2026</t>
+          <t>Thursday, September 3, 2026</t>
         </is>
       </c>
       <c r="C376" t="n">
@@ -21480,11 +21480,11 @@
     </row>
     <row r="377">
       <c r="A377" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B377" t="inlineStr">
         <is>
-          <t>Thursday, September 3, 2026</t>
+          <t>Wednesday, September 2, 2026</t>
         </is>
       </c>
       <c r="C377" t="n">
@@ -21536,11 +21536,11 @@
     </row>
     <row r="378">
       <c r="A378" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B378" t="inlineStr">
         <is>
-          <t>Wednesday, September 2, 2026</t>
+          <t>Thursday, September 3, 2026</t>
         </is>
       </c>
       <c r="C378" t="n">
@@ -21600,11 +21600,11 @@
         </is>
       </c>
       <c r="C379" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D379" t="inlineStr">
         <is>
-          <t>09:00 AM – 10:00 AM</t>
+          <t>08:00 AM – 09:00 AM</t>
         </is>
       </c>
       <c r="E379" t="inlineStr">
@@ -21648,15 +21648,15 @@
     </row>
     <row r="380">
       <c r="A380" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="B380" t="inlineStr">
         <is>
-          <t>Monday, September 7, 2026</t>
+          <t>Wednesday, September 2, 2026</t>
         </is>
       </c>
       <c r="C380" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D380" t="inlineStr">
         <is>
@@ -21704,11 +21704,11 @@
     </row>
     <row r="381">
       <c r="A381" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B381" t="inlineStr">
         <is>
-          <t>Sunday, September 6, 2026</t>
+          <t>Monday, September 7, 2026</t>
         </is>
       </c>
       <c r="C381" t="n">
@@ -21760,11 +21760,11 @@
     </row>
     <row r="382">
       <c r="A382" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B382" t="inlineStr">
         <is>
-          <t>Thursday, September 3, 2026</t>
+          <t>Sunday, September 6, 2026</t>
         </is>
       </c>
       <c r="C382" t="n">
@@ -21816,11 +21816,11 @@
     </row>
     <row r="383">
       <c r="A383" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B383" t="inlineStr">
         <is>
-          <t>Sunday, September 6, 2026</t>
+          <t>Monday, September 7, 2026</t>
         </is>
       </c>
       <c r="C383" t="n">
@@ -21872,11 +21872,11 @@
     </row>
     <row r="384">
       <c r="A384" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B384" t="inlineStr">
         <is>
-          <t>Thursday, September 3, 2026</t>
+          <t>Sunday, September 6, 2026</t>
         </is>
       </c>
       <c r="C384" t="n">
@@ -21928,19 +21928,19 @@
     </row>
     <row r="385">
       <c r="A385" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="B385" t="inlineStr">
         <is>
-          <t>Thursday, September 3, 2026</t>
+          <t>Monday, September 7, 2026</t>
         </is>
       </c>
       <c r="C385" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D385" t="inlineStr">
         <is>
-          <t>08:00 AM – 09:00 AM</t>
+          <t>09:00 AM – 10:00 AM</t>
         </is>
       </c>
       <c r="E385" t="inlineStr">
@@ -21984,19 +21984,19 @@
     </row>
     <row r="386">
       <c r="A386" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B386" t="inlineStr">
         <is>
-          <t>Wednesday, September 2, 2026</t>
+          <t>Thursday, September 3, 2026</t>
         </is>
       </c>
       <c r="C386" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D386" t="inlineStr">
         <is>
-          <t>09:00 AM – 10:00 AM</t>
+          <t>10:25 AM – 11:25 AM</t>
         </is>
       </c>
       <c r="E386" t="inlineStr">
@@ -22040,19 +22040,19 @@
     </row>
     <row r="387">
       <c r="A387" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B387" t="inlineStr">
         <is>
-          <t>Wednesday, September 2, 2026</t>
+          <t>Thursday, September 3, 2026</t>
         </is>
       </c>
       <c r="C387" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D387" t="inlineStr">
         <is>
-          <t>10:25 AM – 11:25 AM</t>
+          <t>09:00 AM – 10:00 AM</t>
         </is>
       </c>
       <c r="E387" t="inlineStr">
@@ -22152,19 +22152,19 @@
     </row>
     <row r="389">
       <c r="A389" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="B389" t="inlineStr">
         <is>
-          <t>Monday, September 7, 2026</t>
+          <t>Thursday, September 3, 2026</t>
         </is>
       </c>
       <c r="C389" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D389" t="inlineStr">
         <is>
-          <t>08:00 AM – 09:00 AM</t>
+          <t>09:00 AM – 10:00 AM</t>
         </is>
       </c>
       <c r="E389" t="inlineStr">
@@ -22208,15 +22208,15 @@
     </row>
     <row r="390">
       <c r="A390" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="B390" t="inlineStr">
         <is>
-          <t>Sunday, September 6, 2026</t>
+          <t>Wednesday, September 2, 2026</t>
         </is>
       </c>
       <c r="C390" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D390" t="inlineStr">
         <is>
@@ -22264,19 +22264,19 @@
     </row>
     <row r="391">
       <c r="A391" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B391" t="inlineStr">
         <is>
-          <t>Sunday, September 6, 2026</t>
+          <t>Monday, September 7, 2026</t>
         </is>
       </c>
       <c r="C391" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D391" t="inlineStr">
         <is>
-          <t>08:00 AM – 09:00 AM</t>
+          <t>10:25 AM – 11:25 AM</t>
         </is>
       </c>
       <c r="E391" t="inlineStr">
@@ -22320,19 +22320,19 @@
     </row>
     <row r="392">
       <c r="A392" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="B392" t="inlineStr">
         <is>
-          <t>Thursday, September 3, 2026</t>
+          <t>Monday, September 7, 2026</t>
         </is>
       </c>
       <c r="C392" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D392" t="inlineStr">
         <is>
-          <t>09:00 AM – 10:00 AM</t>
+          <t>08:00 AM – 09:00 AM</t>
         </is>
       </c>
       <c r="E392" t="inlineStr">
@@ -22384,11 +22384,11 @@
         </is>
       </c>
       <c r="C393" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D393" t="inlineStr">
         <is>
-          <t>08:00 AM – 09:00 AM</t>
+          <t>10:25 AM – 11:25 AM</t>
         </is>
       </c>
       <c r="E393" t="inlineStr">
@@ -22432,11 +22432,11 @@
     </row>
     <row r="394">
       <c r="A394" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B394" t="inlineStr">
         <is>
-          <t>Thursday, September 3, 2026</t>
+          <t>Sunday, September 6, 2026</t>
         </is>
       </c>
       <c r="C394" t="n">
@@ -22488,19 +22488,19 @@
     </row>
     <row r="395">
       <c r="A395" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="B395" t="inlineStr">
         <is>
-          <t>Wednesday, September 2, 2026</t>
+          <t>Monday, September 7, 2026</t>
         </is>
       </c>
       <c r="C395" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D395" t="inlineStr">
         <is>
-          <t>10:25 AM – 11:25 AM</t>
+          <t>09:00 AM – 10:00 AM</t>
         </is>
       </c>
       <c r="E395" t="inlineStr">
@@ -22544,11 +22544,11 @@
     </row>
     <row r="396">
       <c r="A396" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="B396" t="inlineStr">
         <is>
-          <t>Wednesday, September 2, 2026</t>
+          <t>Sunday, September 6, 2026</t>
         </is>
       </c>
       <c r="C396" t="n">
@@ -22608,11 +22608,11 @@
         </is>
       </c>
       <c r="C397" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D397" t="inlineStr">
         <is>
-          <t>08:00 AM – 09:00 AM</t>
+          <t>10:25 AM – 11:25 AM</t>
         </is>
       </c>
       <c r="E397" t="inlineStr">
@@ -22656,11 +22656,11 @@
     </row>
     <row r="398">
       <c r="A398" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B398" t="inlineStr">
         <is>
-          <t>Sunday, September 6, 2026</t>
+          <t>Thursday, September 3, 2026</t>
         </is>
       </c>
       <c r="C398" t="n">
@@ -22712,11 +22712,11 @@
     </row>
     <row r="399">
       <c r="A399" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="B399" t="inlineStr">
         <is>
-          <t>Monday, September 7, 2026</t>
+          <t>Thursday, September 3, 2026</t>
         </is>
       </c>
       <c r="C399" t="n">
@@ -22824,11 +22824,11 @@
     </row>
     <row r="401">
       <c r="A401" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B401" t="inlineStr">
         <is>
-          <t>Thursday, September 3, 2026</t>
+          <t>Wednesday, September 2, 2026</t>
         </is>
       </c>
       <c r="C401" t="n">
@@ -22880,19 +22880,19 @@
     </row>
     <row r="402">
       <c r="A402" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B402" t="inlineStr">
         <is>
-          <t>Sunday, September 6, 2026</t>
+          <t>Thursday, September 3, 2026</t>
         </is>
       </c>
       <c r="C402" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D402" t="inlineStr">
         <is>
-          <t>08:00 AM – 09:00 AM</t>
+          <t>09:00 AM – 10:00 AM</t>
         </is>
       </c>
       <c r="E402" t="inlineStr">
@@ -22936,19 +22936,19 @@
     </row>
     <row r="403">
       <c r="A403" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="B403" t="inlineStr">
         <is>
-          <t>Thursday, September 3, 2026</t>
+          <t>Monday, September 7, 2026</t>
         </is>
       </c>
       <c r="C403" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D403" t="inlineStr">
         <is>
-          <t>10:25 AM – 11:25 AM</t>
+          <t>08:00 AM – 09:00 AM</t>
         </is>
       </c>
       <c r="E403" t="inlineStr">
@@ -22992,19 +22992,19 @@
     </row>
     <row r="404">
       <c r="A404" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B404" t="inlineStr">
         <is>
-          <t>Thursday, September 3, 2026</t>
+          <t>Wednesday, September 2, 2026</t>
         </is>
       </c>
       <c r="C404" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D404" t="inlineStr">
         <is>
-          <t>08:00 AM – 09:00 AM</t>
+          <t>10:25 AM – 11:25 AM</t>
         </is>
       </c>
       <c r="E404" t="inlineStr">
@@ -23048,11 +23048,11 @@
     </row>
     <row r="405">
       <c r="A405" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="B405" t="inlineStr">
         <is>
-          <t>Wednesday, September 2, 2026</t>
+          <t>Monday, September 7, 2026</t>
         </is>
       </c>
       <c r="C405" t="n">
@@ -23104,19 +23104,19 @@
     </row>
     <row r="406">
       <c r="A406" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="B406" t="inlineStr">
         <is>
-          <t>Wednesday, September 2, 2026</t>
+          <t>Sunday, September 6, 2026</t>
         </is>
       </c>
       <c r="C406" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D406" t="inlineStr">
         <is>
-          <t>08:00 AM – 09:00 AM</t>
+          <t>10:25 AM – 11:25 AM</t>
         </is>
       </c>
       <c r="E406" t="inlineStr">
@@ -23160,11 +23160,11 @@
     </row>
     <row r="407">
       <c r="A407" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="B407" t="inlineStr">
         <is>
-          <t>Sunday, September 6, 2026</t>
+          <t>Wednesday, September 2, 2026</t>
         </is>
       </c>
       <c r="C407" t="n">
@@ -23216,19 +23216,19 @@
     </row>
     <row r="408">
       <c r="A408" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="B408" t="inlineStr">
         <is>
-          <t>Thursday, September 3, 2026</t>
+          <t>Monday, September 7, 2026</t>
         </is>
       </c>
       <c r="C408" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D408" t="inlineStr">
         <is>
-          <t>09:00 AM – 10:00 AM</t>
+          <t>08:00 AM – 09:00 AM</t>
         </is>
       </c>
       <c r="E408" t="inlineStr">
@@ -23272,15 +23272,15 @@
     </row>
     <row r="409">
       <c r="A409" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B409" t="inlineStr">
         <is>
-          <t>Monday, September 7, 2026</t>
+          <t>Sunday, September 6, 2026</t>
         </is>
       </c>
       <c r="C409" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D409" t="inlineStr">
         <is>
@@ -23328,15 +23328,15 @@
     </row>
     <row r="410">
       <c r="A410" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B410" t="inlineStr">
         <is>
-          <t>Sunday, September 6, 2026</t>
+          <t>Monday, September 7, 2026</t>
         </is>
       </c>
       <c r="C410" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D410" t="inlineStr">
         <is>
@@ -23384,19 +23384,19 @@
     </row>
     <row r="411">
       <c r="A411" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B411" t="inlineStr">
         <is>
-          <t>Thursday, September 3, 2026</t>
+          <t>Wednesday, September 2, 2026</t>
         </is>
       </c>
       <c r="C411" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D411" t="inlineStr">
         <is>
-          <t>08:00 AM – 09:00 AM</t>
+          <t>09:00 AM – 10:00 AM</t>
         </is>
       </c>
       <c r="E411" t="inlineStr">
@@ -23448,11 +23448,11 @@
         </is>
       </c>
       <c r="C412" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D412" t="inlineStr">
         <is>
-          <t>10:25 AM – 11:25 AM</t>
+          <t>08:00 AM – 09:00 AM</t>
         </is>
       </c>
       <c r="E412" t="inlineStr">
@@ -23496,19 +23496,19 @@
     </row>
     <row r="413">
       <c r="A413" t="n">
+        <v>3</v>
+      </c>
+      <c r="B413" t="inlineStr">
+        <is>
+          <t>Sunday, September 6, 2026</t>
+        </is>
+      </c>
+      <c r="C413" t="n">
         <v>1</v>
       </c>
-      <c r="B413" t="inlineStr">
-        <is>
-          <t>Wednesday, September 2, 2026</t>
-        </is>
-      </c>
-      <c r="C413" t="n">
-        <v>3</v>
-      </c>
       <c r="D413" t="inlineStr">
         <is>
-          <t>10:25 AM – 11:25 AM</t>
+          <t>08:00 AM – 09:00 AM</t>
         </is>
       </c>
       <c r="E413" t="inlineStr">
@@ -23608,11 +23608,11 @@
     </row>
     <row r="415">
       <c r="A415" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B415" t="inlineStr">
         <is>
-          <t>Wednesday, September 2, 2026</t>
+          <t>Thursday, September 3, 2026</t>
         </is>
       </c>
       <c r="C415" t="n">
@@ -23672,11 +23672,11 @@
         </is>
       </c>
       <c r="C416" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D416" t="inlineStr">
         <is>
-          <t>08:00 AM – 09:00 AM</t>
+          <t>10:25 AM – 11:25 AM</t>
         </is>
       </c>
       <c r="E416" t="inlineStr">
@@ -23720,19 +23720,19 @@
     </row>
     <row r="417">
       <c r="A417" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B417" t="inlineStr">
         <is>
-          <t>Thursday, September 3, 2026</t>
+          <t>Wednesday, September 2, 2026</t>
         </is>
       </c>
       <c r="C417" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D417" t="inlineStr">
         <is>
-          <t>09:00 AM – 10:00 AM</t>
+          <t>08:00 AM – 09:00 AM</t>
         </is>
       </c>
       <c r="E417" t="inlineStr">
@@ -23776,19 +23776,19 @@
     </row>
     <row r="418">
       <c r="A418" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B418" t="inlineStr">
         <is>
-          <t>Thursday, September 3, 2026</t>
+          <t>Sunday, September 6, 2026</t>
         </is>
       </c>
       <c r="C418" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D418" t="inlineStr">
         <is>
-          <t>08:00 AM – 09:00 AM</t>
+          <t>09:00 AM – 10:00 AM</t>
         </is>
       </c>
       <c r="E418" t="inlineStr">
@@ -23832,11 +23832,11 @@
     </row>
     <row r="419">
       <c r="A419" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B419" t="inlineStr">
         <is>
-          <t>Wednesday, September 2, 2026</t>
+          <t>Thursday, September 3, 2026</t>
         </is>
       </c>
       <c r="C419" t="n">
@@ -23888,19 +23888,19 @@
     </row>
     <row r="420">
       <c r="A420" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="B420" t="inlineStr">
         <is>
-          <t>Wednesday, September 2, 2026</t>
+          <t>Monday, September 7, 2026</t>
         </is>
       </c>
       <c r="C420" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D420" t="inlineStr">
         <is>
-          <t>09:00 AM – 10:00 AM</t>
+          <t>10:25 AM – 11:25 AM</t>
         </is>
       </c>
       <c r="E420" t="inlineStr">
@@ -23952,11 +23952,11 @@
         </is>
       </c>
       <c r="C421" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D421" t="inlineStr">
         <is>
-          <t>08:00 AM – 09:00 AM</t>
+          <t>09:00 AM – 10:00 AM</t>
         </is>
       </c>
       <c r="E421" t="inlineStr">
@@ -24000,19 +24000,19 @@
     </row>
     <row r="422">
       <c r="A422" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B422" t="inlineStr">
         <is>
-          <t>Monday, September 7, 2026</t>
+          <t>Sunday, September 6, 2026</t>
         </is>
       </c>
       <c r="C422" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D422" t="inlineStr">
         <is>
-          <t>03:10 PM – 04:10 PM</t>
+          <t>12:40 PM – 01:40 PM</t>
         </is>
       </c>
       <c r="E422" t="inlineStr">
@@ -24056,11 +24056,11 @@
     </row>
     <row r="423">
       <c r="A423" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B423" t="inlineStr">
         <is>
-          <t>Sunday, September 6, 2026</t>
+          <t>Monday, September 7, 2026</t>
         </is>
       </c>
       <c r="C423" t="n">
@@ -24168,11 +24168,11 @@
     </row>
     <row r="425">
       <c r="A425" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B425" t="inlineStr">
         <is>
-          <t>Thursday, September 3, 2026</t>
+          <t>Wednesday, September 2, 2026</t>
         </is>
       </c>
       <c r="C425" t="n">
@@ -24232,11 +24232,11 @@
         </is>
       </c>
       <c r="C426" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D426" t="inlineStr">
         <is>
-          <t>01:50 PM – 02:50 PM</t>
+          <t>12:40 PM – 01:40 PM</t>
         </is>
       </c>
       <c r="E426" t="inlineStr">
@@ -24280,19 +24280,19 @@
     </row>
     <row r="427">
       <c r="A427" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B427" t="inlineStr">
         <is>
-          <t>Sunday, September 6, 2026</t>
+          <t>Thursday, September 3, 2026</t>
         </is>
       </c>
       <c r="C427" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D427" t="inlineStr">
         <is>
-          <t>12:40 PM – 01:40 PM</t>
+          <t>03:10 PM – 04:10 PM</t>
         </is>
       </c>
       <c r="E427" t="inlineStr">
@@ -24336,19 +24336,19 @@
     </row>
     <row r="428">
       <c r="A428" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="B428" t="inlineStr">
         <is>
-          <t>Wednesday, September 2, 2026</t>
+          <t>Sunday, September 6, 2026</t>
         </is>
       </c>
       <c r="C428" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D428" t="inlineStr">
         <is>
-          <t>03:10 PM – 04:10 PM</t>
+          <t>01:50 PM – 02:50 PM</t>
         </is>
       </c>
       <c r="E428" t="inlineStr">
@@ -24504,19 +24504,19 @@
     </row>
     <row r="431">
       <c r="A431" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="B431" t="inlineStr">
         <is>
-          <t>Wednesday, September 2, 2026</t>
+          <t>Sunday, September 6, 2026</t>
         </is>
       </c>
       <c r="C431" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D431" t="inlineStr">
         <is>
-          <t>12:40 PM – 01:40 PM</t>
+          <t>03:10 PM – 04:10 PM</t>
         </is>
       </c>
       <c r="E431" t="inlineStr">
@@ -24568,11 +24568,11 @@
         </is>
       </c>
       <c r="C432" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D432" t="inlineStr">
         <is>
-          <t>12:40 PM – 01:40 PM</t>
+          <t>01:50 PM – 02:50 PM</t>
         </is>
       </c>
       <c r="E432" t="inlineStr">
@@ -24616,19 +24616,19 @@
     </row>
     <row r="433">
       <c r="A433" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="B433" t="inlineStr">
         <is>
-          <t>Monday, September 7, 2026</t>
+          <t>Thursday, September 3, 2026</t>
         </is>
       </c>
       <c r="C433" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D433" t="inlineStr">
         <is>
-          <t>01:50 PM – 02:50 PM</t>
+          <t>03:10 PM – 04:10 PM</t>
         </is>
       </c>
       <c r="E433" t="inlineStr">
@@ -24680,11 +24680,11 @@
         </is>
       </c>
       <c r="C434" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D434" t="inlineStr">
         <is>
-          <t>03:10 PM – 04:10 PM</t>
+          <t>01:50 PM – 02:50 PM</t>
         </is>
       </c>
       <c r="E434" t="inlineStr">
@@ -24728,11 +24728,11 @@
     </row>
     <row r="435">
       <c r="A435" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="B435" t="inlineStr">
         <is>
-          <t>Sunday, September 6, 2026</t>
+          <t>Wednesday, September 2, 2026</t>
         </is>
       </c>
       <c r="C435" t="n">
@@ -24792,7 +24792,7 @@
         </is>
       </c>
       <c r="C436" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D436" t="inlineStr">
         <is>
@@ -24840,19 +24840,19 @@
     </row>
     <row r="437">
       <c r="A437" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B437" t="inlineStr">
         <is>
-          <t>Thursday, September 3, 2026</t>
+          <t>Sunday, September 6, 2026</t>
         </is>
       </c>
       <c r="C437" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D437" t="inlineStr">
         <is>
-          <t>01:50 PM – 02:50 PM</t>
+          <t>12:40 PM – 01:40 PM</t>
         </is>
       </c>
       <c r="E437" t="inlineStr">
@@ -24896,19 +24896,19 @@
     </row>
     <row r="438">
       <c r="A438" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B438" t="inlineStr">
         <is>
-          <t>Thursday, September 3, 2026</t>
+          <t>Wednesday, September 2, 2026</t>
         </is>
       </c>
       <c r="C438" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D438" t="inlineStr">
         <is>
-          <t>12:40 PM – 01:40 PM</t>
+          <t>01:50 PM – 02:50 PM</t>
         </is>
       </c>
       <c r="E438" t="inlineStr">
@@ -25008,19 +25008,19 @@
     </row>
     <row r="440">
       <c r="A440" t="n">
+        <v>4</v>
+      </c>
+      <c r="B440" t="inlineStr">
+        <is>
+          <t>Monday, September 7, 2026</t>
+        </is>
+      </c>
+      <c r="C440" t="n">
         <v>1</v>
       </c>
-      <c r="B440" t="inlineStr">
-        <is>
-          <t>Wednesday, September 2, 2026</t>
-        </is>
-      </c>
-      <c r="C440" t="n">
-        <v>3</v>
-      </c>
       <c r="D440" t="inlineStr">
         <is>
-          <t>03:10 PM – 04:10 PM</t>
+          <t>12:40 PM – 01:40 PM</t>
         </is>
       </c>
       <c r="E440" t="inlineStr">
@@ -25064,19 +25064,19 @@
     </row>
     <row r="441">
       <c r="A441" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="B441" t="inlineStr">
         <is>
-          <t>Wednesday, September 2, 2026</t>
+          <t>Monday, September 7, 2026</t>
         </is>
       </c>
       <c r="C441" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D441" t="inlineStr">
         <is>
-          <t>01:50 PM – 02:50 PM</t>
+          <t>03:10 PM – 04:10 PM</t>
         </is>
       </c>
       <c r="E441" t="inlineStr">
@@ -25120,19 +25120,19 @@
     </row>
     <row r="442">
       <c r="A442" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B442" t="inlineStr">
         <is>
-          <t>Sunday, September 6, 2026</t>
+          <t>Thursday, September 3, 2026</t>
         </is>
       </c>
       <c r="C442" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D442" t="inlineStr">
         <is>
-          <t>01:50 PM – 02:50 PM</t>
+          <t>12:40 PM – 01:40 PM</t>
         </is>
       </c>
       <c r="E442" t="inlineStr">
@@ -25184,7 +25184,7 @@
         </is>
       </c>
       <c r="C443" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D443" t="inlineStr">
         <is>
@@ -25232,19 +25232,19 @@
     </row>
     <row r="444">
       <c r="A444" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="B444" t="inlineStr">
         <is>
-          <t>Thursday, September 3, 2026</t>
+          <t>Monday, September 7, 2026</t>
         </is>
       </c>
       <c r="C444" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D444" t="inlineStr">
         <is>
-          <t>03:10 PM – 04:10 PM</t>
+          <t>12:40 PM – 01:40 PM</t>
         </is>
       </c>
       <c r="E444" t="inlineStr">
@@ -25288,19 +25288,19 @@
     </row>
     <row r="445">
       <c r="A445" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="B445" t="inlineStr">
         <is>
-          <t>Monday, September 7, 2026</t>
+          <t>Thursday, September 3, 2026</t>
         </is>
       </c>
       <c r="C445" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D445" t="inlineStr">
         <is>
-          <t>03:10 PM – 04:10 PM</t>
+          <t>01:50 PM – 02:50 PM</t>
         </is>
       </c>
       <c r="E445" t="inlineStr">
@@ -25352,11 +25352,11 @@
         </is>
       </c>
       <c r="C446" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D446" t="inlineStr">
         <is>
-          <t>03:10 PM – 04:10 PM</t>
+          <t>12:40 PM – 01:40 PM</t>
         </is>
       </c>
       <c r="E446" t="inlineStr">
@@ -25408,11 +25408,11 @@
         </is>
       </c>
       <c r="C447" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D447" t="inlineStr">
         <is>
-          <t>01:50 PM – 02:50 PM</t>
+          <t>03:10 PM – 04:10 PM</t>
         </is>
       </c>
       <c r="E447" t="inlineStr">
@@ -25456,19 +25456,19 @@
     </row>
     <row r="448">
       <c r="A448" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B448" t="inlineStr">
         <is>
-          <t>Thursday, September 3, 2026</t>
+          <t>Sunday, September 6, 2026</t>
         </is>
       </c>
       <c r="C448" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D448" t="inlineStr">
         <is>
-          <t>12:40 PM – 01:40 PM</t>
+          <t>01:50 PM – 02:50 PM</t>
         </is>
       </c>
       <c r="E448" t="inlineStr">
@@ -25680,19 +25680,19 @@
     </row>
     <row r="452">
       <c r="A452" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="B452" t="inlineStr">
         <is>
-          <t>Thursday, September 3, 2026</t>
+          <t>Monday, September 7, 2026</t>
         </is>
       </c>
       <c r="C452" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D452" t="inlineStr">
         <is>
-          <t>03:10 PM – 04:10 PM</t>
+          <t>01:50 PM – 02:50 PM</t>
         </is>
       </c>
       <c r="E452" t="inlineStr">
@@ -25736,19 +25736,19 @@
     </row>
     <row r="453">
       <c r="A453" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B453" t="inlineStr">
         <is>
-          <t>Thursday, September 3, 2026</t>
+          <t>Wednesday, September 2, 2026</t>
         </is>
       </c>
       <c r="C453" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D453" t="inlineStr">
         <is>
-          <t>12:40 PM – 01:40 PM</t>
+          <t>03:10 PM – 04:10 PM</t>
         </is>
       </c>
       <c r="E453" t="inlineStr">
@@ -25792,15 +25792,15 @@
     </row>
     <row r="454">
       <c r="A454" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B454" t="inlineStr">
         <is>
-          <t>Monday, September 7, 2026</t>
+          <t>Sunday, September 6, 2026</t>
         </is>
       </c>
       <c r="C454" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D454" t="inlineStr">
         <is>
@@ -25848,11 +25848,11 @@
     </row>
     <row r="455">
       <c r="A455" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B455" t="inlineStr">
         <is>
-          <t>Sunday, September 6, 2026</t>
+          <t>Thursday, September 3, 2026</t>
         </is>
       </c>
       <c r="C455" t="n">
@@ -25904,19 +25904,19 @@
     </row>
     <row r="456">
       <c r="A456" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B456" t="inlineStr">
         <is>
-          <t>Sunday, September 6, 2026</t>
+          <t>Thursday, September 3, 2026</t>
         </is>
       </c>
       <c r="C456" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D456" t="inlineStr">
         <is>
-          <t>12:40 PM – 01:40 PM</t>
+          <t>01:50 PM – 02:50 PM</t>
         </is>
       </c>
       <c r="E456" t="inlineStr">
@@ -25968,11 +25968,11 @@
         </is>
       </c>
       <c r="C457" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D457" t="inlineStr">
         <is>
-          <t>01:50 PM – 02:50 PM</t>
+          <t>12:40 PM – 01:40 PM</t>
         </is>
       </c>
       <c r="E457" t="inlineStr">
@@ -26016,19 +26016,19 @@
     </row>
     <row r="458">
       <c r="A458" t="n">
+        <v>4</v>
+      </c>
+      <c r="B458" t="inlineStr">
+        <is>
+          <t>Monday, September 7, 2026</t>
+        </is>
+      </c>
+      <c r="C458" t="n">
         <v>1</v>
       </c>
-      <c r="B458" t="inlineStr">
-        <is>
-          <t>Wednesday, September 2, 2026</t>
-        </is>
-      </c>
-      <c r="C458" t="n">
-        <v>3</v>
-      </c>
       <c r="D458" t="inlineStr">
         <is>
-          <t>03:10 PM – 04:10 PM</t>
+          <t>12:40 PM – 01:40 PM</t>
         </is>
       </c>
       <c r="E458" t="inlineStr">
@@ -26128,19 +26128,19 @@
     </row>
     <row r="460">
       <c r="A460" t="n">
+        <v>3</v>
+      </c>
+      <c r="B460" t="inlineStr">
+        <is>
+          <t>Sunday, September 6, 2026</t>
+        </is>
+      </c>
+      <c r="C460" t="n">
         <v>1</v>
       </c>
-      <c r="B460" t="inlineStr">
-        <is>
-          <t>Wednesday, September 2, 2026</t>
-        </is>
-      </c>
-      <c r="C460" t="n">
-        <v>2</v>
-      </c>
       <c r="D460" t="inlineStr">
         <is>
-          <t>01:50 PM – 02:50 PM</t>
+          <t>12:40 PM – 01:40 PM</t>
         </is>
       </c>
       <c r="E460" t="inlineStr">
@@ -26184,19 +26184,19 @@
     </row>
     <row r="461">
       <c r="A461" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="B461" t="inlineStr">
         <is>
-          <t>Wednesday, September 2, 2026</t>
+          <t>Sunday, September 6, 2026</t>
         </is>
       </c>
       <c r="C461" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D461" t="inlineStr">
         <is>
-          <t>01:50 PM – 02:50 PM</t>
+          <t>03:10 PM – 04:10 PM</t>
         </is>
       </c>
       <c r="E461" t="inlineStr">
@@ -26248,11 +26248,11 @@
         </is>
       </c>
       <c r="C462" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D462" t="inlineStr">
         <is>
-          <t>12:40 PM – 01:40 PM</t>
+          <t>03:10 PM – 04:10 PM</t>
         </is>
       </c>
       <c r="E462" t="inlineStr">
@@ -26296,19 +26296,19 @@
     </row>
     <row r="463">
       <c r="A463" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B463" t="inlineStr">
         <is>
-          <t>Wednesday, September 2, 2026</t>
+          <t>Thursday, September 3, 2026</t>
         </is>
       </c>
       <c r="C463" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D463" t="inlineStr">
         <is>
-          <t>12:40 PM – 01:40 PM</t>
+          <t>03:10 PM – 04:10 PM</t>
         </is>
       </c>
       <c r="E463" t="inlineStr">
@@ -26360,11 +26360,11 @@
         </is>
       </c>
       <c r="C464" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D464" t="inlineStr">
         <is>
-          <t>03:10 PM – 04:10 PM</t>
+          <t>01:50 PM – 02:50 PM</t>
         </is>
       </c>
       <c r="E464" t="inlineStr">
@@ -26416,11 +26416,11 @@
         </is>
       </c>
       <c r="C465" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D465" t="inlineStr">
         <is>
-          <t>03:10 PM – 04:10 PM</t>
+          <t>12:40 PM – 01:40 PM</t>
         </is>
       </c>
       <c r="E465" t="inlineStr">
@@ -26464,19 +26464,19 @@
     </row>
     <row r="466">
       <c r="A466" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B466" t="inlineStr">
         <is>
-          <t>Sunday, September 6, 2026</t>
+          <t>Monday, September 7, 2026</t>
         </is>
       </c>
       <c r="C466" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D466" t="inlineStr">
         <is>
-          <t>12:40 PM – 01:40 PM</t>
+          <t>01:50 PM – 02:50 PM</t>
         </is>
       </c>
       <c r="E466" t="inlineStr">
@@ -26520,19 +26520,19 @@
     </row>
     <row r="467">
       <c r="A467" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B467" t="inlineStr">
         <is>
-          <t>Sunday, September 6, 2026</t>
+          <t>Thursday, September 3, 2026</t>
         </is>
       </c>
       <c r="C467" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D467" t="inlineStr">
         <is>
-          <t>01:50 PM – 02:50 PM</t>
+          <t>12:40 PM – 01:40 PM</t>
         </is>
       </c>
       <c r="E467" t="inlineStr">
@@ -26576,11 +26576,11 @@
     </row>
     <row r="468">
       <c r="A468" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B468" t="inlineStr">
         <is>
-          <t>Thursday, September 3, 2026</t>
+          <t>Wednesday, September 2, 2026</t>
         </is>
       </c>
       <c r="C468" t="n">
@@ -26688,19 +26688,19 @@
     </row>
     <row r="470">
       <c r="A470" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="B470" t="inlineStr">
         <is>
-          <t>Thursday, September 3, 2026</t>
+          <t>Monday, September 7, 2026</t>
         </is>
       </c>
       <c r="C470" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D470" t="inlineStr">
         <is>
-          <t>03:10 PM – 04:10 PM</t>
+          <t>12:40 PM – 01:40 PM</t>
         </is>
       </c>
       <c r="E470" t="inlineStr">
@@ -26800,11 +26800,11 @@
     </row>
     <row r="472">
       <c r="A472" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B472" t="inlineStr">
         <is>
-          <t>Thursday, September 3, 2026</t>
+          <t>Wednesday, September 2, 2026</t>
         </is>
       </c>
       <c r="C472" t="n">
@@ -26856,11 +26856,11 @@
     </row>
     <row r="473">
       <c r="A473" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="B473" t="inlineStr">
         <is>
-          <t>Monday, September 7, 2026</t>
+          <t>Thursday, September 3, 2026</t>
         </is>
       </c>
       <c r="C473" t="n">
@@ -26968,11 +26968,11 @@
     </row>
     <row r="475">
       <c r="A475" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="B475" t="inlineStr">
         <is>
-          <t>Wednesday, September 2, 2026</t>
+          <t>Monday, September 7, 2026</t>
         </is>
       </c>
       <c r="C475" t="n">
@@ -27024,11 +27024,11 @@
     </row>
     <row r="476">
       <c r="A476" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="B476" t="inlineStr">
         <is>
-          <t>Wednesday, September 2, 2026</t>
+          <t>Sunday, September 6, 2026</t>
         </is>
       </c>
       <c r="C476" t="n">
@@ -27192,19 +27192,19 @@
     </row>
     <row r="479">
       <c r="A479" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B479" t="inlineStr">
         <is>
-          <t>Thursday, September 3, 2026</t>
+          <t>Wednesday, September 2, 2026</t>
         </is>
       </c>
       <c r="C479" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D479" t="inlineStr">
         <is>
-          <t>09:00 AM – 10:00 AM</t>
+          <t>10:25 AM – 11:25 AM</t>
         </is>
       </c>
       <c r="E479" t="inlineStr">
@@ -27248,19 +27248,19 @@
     </row>
     <row r="480">
       <c r="A480" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="B480" t="inlineStr">
         <is>
-          <t>Thursday, September 3, 2026</t>
+          <t>Monday, September 7, 2026</t>
         </is>
       </c>
       <c r="C480" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D480" t="inlineStr">
         <is>
-          <t>08:00 AM – 09:00 AM</t>
+          <t>10:25 AM – 11:25 AM</t>
         </is>
       </c>
       <c r="E480" t="inlineStr">
@@ -27304,19 +27304,19 @@
     </row>
     <row r="481">
       <c r="A481" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="B481" t="inlineStr">
         <is>
-          <t>Wednesday, September 2, 2026</t>
+          <t>Monday, September 7, 2026</t>
         </is>
       </c>
       <c r="C481" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D481" t="inlineStr">
         <is>
-          <t>10:25 AM – 11:25 AM</t>
+          <t>09:00 AM – 10:00 AM</t>
         </is>
       </c>
       <c r="E481" t="inlineStr">
@@ -27360,19 +27360,19 @@
     </row>
     <row r="482">
       <c r="A482" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="B482" t="inlineStr">
         <is>
-          <t>Wednesday, September 2, 2026</t>
+          <t>Sunday, September 6, 2026</t>
         </is>
       </c>
       <c r="C482" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D482" t="inlineStr">
         <is>
-          <t>09:00 AM – 10:00 AM</t>
+          <t>10:25 AM – 11:25 AM</t>
         </is>
       </c>
       <c r="E482" t="inlineStr">
@@ -27424,11 +27424,11 @@
         </is>
       </c>
       <c r="C483" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D483" t="inlineStr">
         <is>
-          <t>08:00 AM – 09:00 AM</t>
+          <t>09:00 AM – 10:00 AM</t>
         </is>
       </c>
       <c r="E483" t="inlineStr">
@@ -27472,19 +27472,19 @@
     </row>
     <row r="484">
       <c r="A484" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B484" t="inlineStr">
         <is>
-          <t>Sunday, September 6, 2026</t>
+          <t>Monday, September 7, 2026</t>
         </is>
       </c>
       <c r="C484" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D484" t="inlineStr">
         <is>
-          <t>05:30 PM – 06:30 PM</t>
+          <t>03:10 PM – 04:10 PM</t>
         </is>
       </c>
       <c r="E484" t="inlineStr">
@@ -27528,19 +27528,19 @@
     </row>
     <row r="485">
       <c r="A485" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B485" t="inlineStr">
         <is>
-          <t>Thursday, September 3, 2026</t>
+          <t>Sunday, September 6, 2026</t>
         </is>
       </c>
       <c r="C485" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D485" t="inlineStr">
         <is>
-          <t>04:20 PM – 05:20 PM</t>
+          <t>05:30 PM – 06:30 PM</t>
         </is>
       </c>
       <c r="E485" t="inlineStr">
@@ -27584,19 +27584,19 @@
     </row>
     <row r="486">
       <c r="A486" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B486" t="inlineStr">
         <is>
-          <t>Wednesday, September 2, 2026</t>
+          <t>Thursday, September 3, 2026</t>
         </is>
       </c>
       <c r="C486" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D486" t="inlineStr">
         <is>
-          <t>03:10 PM – 04:10 PM</t>
+          <t>04:20 PM – 05:20 PM</t>
         </is>
       </c>
       <c r="E486" t="inlineStr">
@@ -27648,11 +27648,11 @@
         </is>
       </c>
       <c r="C487" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D487" t="inlineStr">
         <is>
-          <t>05:30 PM – 06:30 PM</t>
+          <t>04:20 PM – 05:20 PM</t>
         </is>
       </c>
       <c r="E487" t="inlineStr">
@@ -27704,11 +27704,11 @@
         </is>
       </c>
       <c r="C488" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D488" t="inlineStr">
         <is>
-          <t>03:10 PM – 04:10 PM</t>
+          <t>04:20 PM – 05:20 PM</t>
         </is>
       </c>
       <c r="E488" t="inlineStr">
@@ -27808,19 +27808,19 @@
     </row>
     <row r="490">
       <c r="A490" t="n">
+        <v>3</v>
+      </c>
+      <c r="B490" t="inlineStr">
+        <is>
+          <t>Sunday, September 6, 2026</t>
+        </is>
+      </c>
+      <c r="C490" t="n">
         <v>1</v>
       </c>
-      <c r="B490" t="inlineStr">
-        <is>
-          <t>Wednesday, September 2, 2026</t>
-        </is>
-      </c>
-      <c r="C490" t="n">
-        <v>2</v>
-      </c>
       <c r="D490" t="inlineStr">
         <is>
-          <t>04:20 PM – 05:20 PM</t>
+          <t>03:10 PM – 04:10 PM</t>
         </is>
       </c>
       <c r="E490" t="inlineStr">
@@ -27864,19 +27864,19 @@
     </row>
     <row r="491">
       <c r="A491" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="B491" t="inlineStr">
         <is>
-          <t>Thursday, September 3, 2026</t>
+          <t>Monday, September 7, 2026</t>
         </is>
       </c>
       <c r="C491" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D491" t="inlineStr">
         <is>
-          <t>03:10 PM – 04:10 PM</t>
+          <t>05:30 PM – 06:30 PM</t>
         </is>
       </c>
       <c r="E491" t="inlineStr">
@@ -27920,15 +27920,15 @@
     </row>
     <row r="492">
       <c r="A492" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="B492" t="inlineStr">
         <is>
-          <t>Monday, September 7, 2026</t>
+          <t>Wednesday, September 2, 2026</t>
         </is>
       </c>
       <c r="C492" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D492" t="inlineStr">
         <is>
@@ -27984,11 +27984,11 @@
         </is>
       </c>
       <c r="C493" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D493" t="inlineStr">
         <is>
-          <t>05:30 PM – 06:30 PM</t>
+          <t>03:10 PM – 04:10 PM</t>
         </is>
       </c>
       <c r="E493" t="inlineStr">
@@ -28096,11 +28096,11 @@
         </is>
       </c>
       <c r="C495" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D495" t="inlineStr">
         <is>
-          <t>05:30 PM – 06:30 PM</t>
+          <t>04:20 PM – 05:20 PM</t>
         </is>
       </c>
       <c r="E495" t="inlineStr">
@@ -28144,19 +28144,19 @@
     </row>
     <row r="496">
       <c r="A496" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B496" t="inlineStr">
         <is>
-          <t>Sunday, September 6, 2026</t>
+          <t>Monday, September 7, 2026</t>
         </is>
       </c>
       <c r="C496" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D496" t="inlineStr">
         <is>
-          <t>04:20 PM – 05:20 PM</t>
+          <t>03:10 PM – 04:10 PM</t>
         </is>
       </c>
       <c r="E496" t="inlineStr">
@@ -28200,11 +28200,11 @@
     </row>
     <row r="497">
       <c r="A497" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B497" t="inlineStr">
         <is>
-          <t>Sunday, September 6, 2026</t>
+          <t>Thursday, September 3, 2026</t>
         </is>
       </c>
       <c r="C497" t="n">
@@ -28312,11 +28312,11 @@
     </row>
     <row r="499">
       <c r="A499" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="B499" t="inlineStr">
         <is>
-          <t>Monday, September 7, 2026</t>
+          <t>Thursday, September 3, 2026</t>
         </is>
       </c>
       <c r="C499" t="n">
@@ -28368,11 +28368,11 @@
     </row>
     <row r="500">
       <c r="A500" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B500" t="inlineStr">
         <is>
-          <t>Thursday, September 3, 2026</t>
+          <t>Sunday, September 6, 2026</t>
         </is>
       </c>
       <c r="C500" t="n">
@@ -28480,19 +28480,19 @@
     </row>
     <row r="502">
       <c r="A502" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="B502" t="inlineStr">
         <is>
-          <t>Wednesday, September 2, 2026</t>
+          <t>Monday, September 7, 2026</t>
         </is>
       </c>
       <c r="C502" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D502" t="inlineStr">
         <is>
-          <t>05:30 PM – 06:30 PM</t>
+          <t>04:20 PM – 05:20 PM</t>
         </is>
       </c>
       <c r="E502" t="inlineStr">
@@ -28536,19 +28536,19 @@
     </row>
     <row r="503">
       <c r="A503" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="B503" t="inlineStr">
         <is>
-          <t>Monday, September 7, 2026</t>
+          <t>Wednesday, September 2, 2026</t>
         </is>
       </c>
       <c r="C503" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D503" t="inlineStr">
         <is>
-          <t>03:10 PM – 04:10 PM</t>
+          <t>05:30 PM – 06:30 PM</t>
         </is>
       </c>
       <c r="E503" t="inlineStr">
@@ -28648,19 +28648,19 @@
     </row>
     <row r="505">
       <c r="A505" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="B505" t="inlineStr">
         <is>
-          <t>Wednesday, September 2, 2026</t>
+          <t>Monday, September 7, 2026</t>
         </is>
       </c>
       <c r="C505" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D505" t="inlineStr">
         <is>
-          <t>03:10 PM – 04:10 PM</t>
+          <t>05:30 PM – 06:30 PM</t>
         </is>
       </c>
       <c r="E505" t="inlineStr">
@@ -28704,19 +28704,19 @@
     </row>
     <row r="506">
       <c r="A506" t="n">
+        <v>3</v>
+      </c>
+      <c r="B506" t="inlineStr">
+        <is>
+          <t>Sunday, September 6, 2026</t>
+        </is>
+      </c>
+      <c r="C506" t="n">
         <v>1</v>
       </c>
-      <c r="B506" t="inlineStr">
-        <is>
-          <t>Wednesday, September 2, 2026</t>
-        </is>
-      </c>
-      <c r="C506" t="n">
-        <v>3</v>
-      </c>
       <c r="D506" t="inlineStr">
         <is>
-          <t>05:30 PM – 06:30 PM</t>
+          <t>03:10 PM – 04:10 PM</t>
         </is>
       </c>
       <c r="E506" t="inlineStr">
@@ -28760,11 +28760,11 @@
     </row>
     <row r="507">
       <c r="A507" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B507" t="inlineStr">
         <is>
-          <t>Thursday, September 3, 2026</t>
+          <t>Sunday, September 6, 2026</t>
         </is>
       </c>
       <c r="C507" t="n">
@@ -28816,19 +28816,19 @@
     </row>
     <row r="508">
       <c r="A508" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="B508" t="inlineStr">
         <is>
-          <t>Sunday, September 6, 2026</t>
+          <t>Wednesday, September 2, 2026</t>
         </is>
       </c>
       <c r="C508" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D508" t="inlineStr">
         <is>
-          <t>04:20 PM – 05:20 PM</t>
+          <t>05:30 PM – 06:30 PM</t>
         </is>
       </c>
       <c r="E508" t="inlineStr">
@@ -28928,15 +28928,15 @@
     </row>
     <row r="510">
       <c r="A510" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="B510" t="inlineStr">
         <is>
-          <t>Monday, September 7, 2026</t>
+          <t>Thursday, September 3, 2026</t>
         </is>
       </c>
       <c r="C510" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D510" t="inlineStr">
         <is>
@@ -28992,11 +28992,11 @@
         </is>
       </c>
       <c r="C511" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D511" t="inlineStr">
         <is>
-          <t>05:30 PM – 06:30 PM</t>
+          <t>03:10 PM – 04:10 PM</t>
         </is>
       </c>
       <c r="E511" t="inlineStr">
@@ -29040,19 +29040,19 @@
     </row>
     <row r="512">
       <c r="A512" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="B512" t="inlineStr">
         <is>
-          <t>Thursday, September 3, 2026</t>
+          <t>Monday, September 7, 2026</t>
         </is>
       </c>
       <c r="C512" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D512" t="inlineStr">
         <is>
-          <t>03:10 PM – 04:10 PM</t>
+          <t>04:20 PM – 05:20 PM</t>
         </is>
       </c>
       <c r="E512" t="inlineStr">
@@ -29096,11 +29096,11 @@
     </row>
     <row r="513">
       <c r="A513" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="B513" t="inlineStr">
         <is>
-          <t>Sunday, September 6, 2026</t>
+          <t>Wednesday, September 2, 2026</t>
         </is>
       </c>
       <c r="C513" t="n">
@@ -29160,11 +29160,11 @@
         </is>
       </c>
       <c r="C514" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D514" t="inlineStr">
         <is>
-          <t>03:10 PM – 04:10 PM</t>
+          <t>05:30 PM – 06:30 PM</t>
         </is>
       </c>
       <c r="E514" t="inlineStr">
@@ -29216,11 +29216,11 @@
         </is>
       </c>
       <c r="C515" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D515" t="inlineStr">
         <is>
-          <t>05:30 PM – 06:30 PM</t>
+          <t>04:20 PM – 05:20 PM</t>
         </is>
       </c>
       <c r="E515" t="inlineStr">
@@ -29264,11 +29264,11 @@
     </row>
     <row r="516">
       <c r="A516" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B516" t="inlineStr">
         <is>
-          <t>Thursday, September 3, 2026</t>
+          <t>Wednesday, September 2, 2026</t>
         </is>
       </c>
       <c r="C516" t="n">
@@ -29320,11 +29320,11 @@
     </row>
     <row r="517">
       <c r="A517" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="B517" t="inlineStr">
         <is>
-          <t>Wednesday, September 2, 2026</t>
+          <t>Monday, September 7, 2026</t>
         </is>
       </c>
       <c r="C517" t="n">
@@ -29376,19 +29376,19 @@
     </row>
     <row r="518">
       <c r="A518" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="B518" t="inlineStr">
         <is>
-          <t>Wednesday, September 2, 2026</t>
+          <t>Sunday, September 6, 2026</t>
         </is>
       </c>
       <c r="C518" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D518" t="inlineStr">
         <is>
-          <t>04:20 PM – 05:20 PM</t>
+          <t>05:30 PM – 06:30 PM</t>
         </is>
       </c>
       <c r="E518" t="inlineStr">
@@ -29440,7 +29440,7 @@
         </is>
       </c>
       <c r="C519" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D519" t="inlineStr">
         <is>
@@ -29488,19 +29488,19 @@
     </row>
     <row r="520">
       <c r="A520" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="B520" t="inlineStr">
         <is>
-          <t>Monday, September 7, 2026</t>
+          <t>Wednesday, September 2, 2026</t>
         </is>
       </c>
       <c r="C520" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D520" t="inlineStr">
         <is>
-          <t>03:10 PM – 04:10 PM</t>
+          <t>05:30 PM – 06:30 PM</t>
         </is>
       </c>
       <c r="E520" t="inlineStr">
@@ -29552,11 +29552,11 @@
         </is>
       </c>
       <c r="C521" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D521" t="inlineStr">
         <is>
-          <t>05:30 PM – 06:30 PM</t>
+          <t>04:20 PM – 05:20 PM</t>
         </is>
       </c>
       <c r="E521" t="inlineStr">
@@ -29600,11 +29600,11 @@
     </row>
     <row r="522">
       <c r="A522" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="B522" t="inlineStr">
         <is>
-          <t>Sunday, September 6, 2026</t>
+          <t>Wednesday, September 2, 2026</t>
         </is>
       </c>
       <c r="C522" t="n">
@@ -29656,19 +29656,19 @@
     </row>
     <row r="523">
       <c r="A523" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B523" t="inlineStr">
         <is>
-          <t>Thursday, September 3, 2026</t>
+          <t>Sunday, September 6, 2026</t>
         </is>
       </c>
       <c r="C523" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D523" t="inlineStr">
         <is>
-          <t>04:20 PM – 05:20 PM</t>
+          <t>05:30 PM – 06:30 PM</t>
         </is>
       </c>
       <c r="E523" t="inlineStr">
@@ -29720,11 +29720,11 @@
         </is>
       </c>
       <c r="C524" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D524" t="inlineStr">
         <is>
-          <t>05:30 PM – 06:30 PM</t>
+          <t>04:20 PM – 05:20 PM</t>
         </is>
       </c>
       <c r="E524" t="inlineStr">
@@ -29768,19 +29768,19 @@
     </row>
     <row r="525">
       <c r="A525" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="B525" t="inlineStr">
         <is>
-          <t>Wednesday, September 2, 2026</t>
+          <t>Monday, September 7, 2026</t>
         </is>
       </c>
       <c r="C525" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D525" t="inlineStr">
         <is>
-          <t>04:20 PM – 05:20 PM</t>
+          <t>05:30 PM – 06:30 PM</t>
         </is>
       </c>
       <c r="E525" t="inlineStr">
@@ -29824,19 +29824,19 @@
     </row>
     <row r="526">
       <c r="A526" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B526" t="inlineStr">
         <is>
-          <t>Monday, September 7, 2026</t>
+          <t>Sunday, September 6, 2026</t>
         </is>
       </c>
       <c r="C526" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D526" t="inlineStr">
         <is>
-          <t>03:10 PM – 04:10 PM</t>
+          <t>04:20 PM – 05:20 PM</t>
         </is>
       </c>
       <c r="E526" t="inlineStr">
@@ -29880,19 +29880,19 @@
     </row>
     <row r="527">
       <c r="A527" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="B527" t="inlineStr">
         <is>
-          <t>Sunday, September 6, 2026</t>
+          <t>Wednesday, September 2, 2026</t>
         </is>
       </c>
       <c r="C527" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D527" t="inlineStr">
         <is>
-          <t>03:10 PM – 04:10 PM</t>
+          <t>05:30 PM – 06:30 PM</t>
         </is>
       </c>
       <c r="E527" t="inlineStr">
@@ -29936,19 +29936,19 @@
     </row>
     <row r="528">
       <c r="A528" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="B528" t="inlineStr">
         <is>
-          <t>Thursday, September 3, 2026</t>
+          <t>Monday, September 7, 2026</t>
         </is>
       </c>
       <c r="C528" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D528" t="inlineStr">
         <is>
-          <t>03:10 PM – 04:10 PM</t>
+          <t>04:20 PM – 05:20 PM</t>
         </is>
       </c>
       <c r="E528" t="inlineStr">
@@ -29992,19 +29992,19 @@
     </row>
     <row r="529">
       <c r="A529" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B529" t="inlineStr">
         <is>
-          <t>Monday, September 7, 2026</t>
+          <t>Sunday, September 6, 2026</t>
         </is>
       </c>
       <c r="C529" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D529" t="inlineStr">
         <is>
-          <t>04:20 PM – 05:20 PM</t>
+          <t>03:10 PM – 04:10 PM</t>
         </is>
       </c>
       <c r="E529" t="inlineStr">
@@ -30048,15 +30048,15 @@
     </row>
     <row r="530">
       <c r="A530" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B530" t="inlineStr">
         <is>
-          <t>Sunday, September 6, 2026</t>
+          <t>Thursday, September 3, 2026</t>
         </is>
       </c>
       <c r="C530" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D530" t="inlineStr">
         <is>
@@ -30104,19 +30104,19 @@
     </row>
     <row r="531">
       <c r="A531" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B531" t="inlineStr">
         <is>
-          <t>Wednesday, September 2, 2026</t>
+          <t>Thursday, September 3, 2026</t>
         </is>
       </c>
       <c r="C531" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D531" t="inlineStr">
         <is>
-          <t>03:10 PM – 04:10 PM</t>
+          <t>05:30 PM – 06:30 PM</t>
         </is>
       </c>
       <c r="E531" t="inlineStr">
@@ -30168,7 +30168,7 @@
         </is>
       </c>
       <c r="C532" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D532" t="inlineStr">
         <is>
@@ -30272,19 +30272,19 @@
     </row>
     <row r="534">
       <c r="A534" t="n">
+        <v>3</v>
+      </c>
+      <c r="B534" t="inlineStr">
+        <is>
+          <t>Sunday, September 6, 2026</t>
+        </is>
+      </c>
+      <c r="C534" t="n">
         <v>1</v>
       </c>
-      <c r="B534" t="inlineStr">
-        <is>
-          <t>Wednesday, September 2, 2026</t>
-        </is>
-      </c>
-      <c r="C534" t="n">
-        <v>2</v>
-      </c>
       <c r="D534" t="inlineStr">
         <is>
-          <t>04:20 PM – 05:20 PM</t>
+          <t>03:10 PM – 04:10 PM</t>
         </is>
       </c>
       <c r="E534" t="inlineStr">
@@ -30336,11 +30336,11 @@
         </is>
       </c>
       <c r="C535" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D535" t="inlineStr">
         <is>
-          <t>03:10 PM – 04:10 PM</t>
+          <t>05:30 PM – 06:30 PM</t>
         </is>
       </c>
       <c r="E535" t="inlineStr">
@@ -30384,11 +30384,11 @@
     </row>
     <row r="536">
       <c r="A536" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B536" t="inlineStr">
         <is>
-          <t>Sunday, September 6, 2026</t>
+          <t>Monday, September 7, 2026</t>
         </is>
       </c>
       <c r="C536" t="n">
@@ -30440,19 +30440,19 @@
     </row>
     <row r="537">
       <c r="A537" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B537" t="inlineStr">
         <is>
-          <t>Wednesday, September 2, 2026</t>
+          <t>Thursday, September 3, 2026</t>
         </is>
       </c>
       <c r="C537" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D537" t="inlineStr">
         <is>
-          <t>05:30 PM – 06:30 PM</t>
+          <t>04:20 PM – 05:20 PM</t>
         </is>
       </c>
       <c r="E537" t="inlineStr">
@@ -30496,19 +30496,19 @@
     </row>
     <row r="538">
       <c r="A538" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B538" t="inlineStr">
         <is>
-          <t>Thursday, September 3, 2026</t>
+          <t>Sunday, September 6, 2026</t>
         </is>
       </c>
       <c r="C538" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D538" t="inlineStr">
         <is>
-          <t>03:10 PM – 04:10 PM</t>
+          <t>04:20 PM – 05:20 PM</t>
         </is>
       </c>
       <c r="E538" t="inlineStr">
@@ -30552,19 +30552,19 @@
     </row>
     <row r="539">
       <c r="A539" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="B539" t="inlineStr">
         <is>
-          <t>Monday, September 7, 2026</t>
+          <t>Wednesday, September 2, 2026</t>
         </is>
       </c>
       <c r="C539" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D539" t="inlineStr">
         <is>
-          <t>05:30 PM – 06:30 PM</t>
+          <t>04:20 PM – 05:20 PM</t>
         </is>
       </c>
       <c r="E539" t="inlineStr">
@@ -30608,19 +30608,19 @@
     </row>
     <row r="540">
       <c r="A540" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="B540" t="inlineStr">
         <is>
-          <t>Sunday, September 6, 2026</t>
+          <t>Wednesday, September 2, 2026</t>
         </is>
       </c>
       <c r="C540" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D540" t="inlineStr">
         <is>
-          <t>04:20 PM – 05:20 PM</t>
+          <t>03:10 PM – 04:10 PM</t>
         </is>
       </c>
       <c r="E540" t="inlineStr">
@@ -30664,11 +30664,11 @@
     </row>
     <row r="541">
       <c r="A541" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B541" t="inlineStr">
         <is>
-          <t>Thursday, September 3, 2026</t>
+          <t>Sunday, September 6, 2026</t>
         </is>
       </c>
       <c r="C541" t="n">
@@ -30720,11 +30720,11 @@
     </row>
     <row r="542">
       <c r="A542" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="B542" t="inlineStr">
         <is>
-          <t>Wednesday, September 2, 2026</t>
+          <t>Sunday, September 6, 2026</t>
         </is>
       </c>
       <c r="C542" t="n">
@@ -30776,11 +30776,11 @@
     </row>
     <row r="543">
       <c r="A543" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="B543" t="inlineStr">
         <is>
-          <t>Sunday, September 6, 2026</t>
+          <t>Wednesday, September 2, 2026</t>
         </is>
       </c>
       <c r="C543" t="n">
@@ -30832,11 +30832,11 @@
     </row>
     <row r="544">
       <c r="A544" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="B544" t="inlineStr">
         <is>
-          <t>Thursday, September 3, 2026</t>
+          <t>Monday, September 7, 2026</t>
         </is>
       </c>
       <c r="C544" t="n">
@@ -30888,11 +30888,11 @@
     </row>
     <row r="545">
       <c r="A545" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="B545" t="inlineStr">
         <is>
-          <t>Wednesday, September 2, 2026</t>
+          <t>Monday, September 7, 2026</t>
         </is>
       </c>
       <c r="C545" t="n">
@@ -30944,19 +30944,19 @@
     </row>
     <row r="546">
       <c r="A546" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B546" t="inlineStr">
         <is>
-          <t>Sunday, September 6, 2026</t>
+          <t>Thursday, September 3, 2026</t>
         </is>
       </c>
       <c r="C546" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D546" t="inlineStr">
         <is>
-          <t>04:20 PM – 05:20 PM</t>
+          <t>05:30 PM – 06:30 PM</t>
         </is>
       </c>
       <c r="E546" t="inlineStr">
@@ -31000,15 +31000,15 @@
     </row>
     <row r="547">
       <c r="A547" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="B547" t="inlineStr">
         <is>
-          <t>Monday, September 7, 2026</t>
+          <t>Wednesday, September 2, 2026</t>
         </is>
       </c>
       <c r="C547" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D547" t="inlineStr">
         <is>

--- a/Term_Examination_Schedule_S.Y._2026-2027_Optimized.xlsx
+++ b/Term_Examination_Schedule_S.Y._2026-2027_Optimized.xlsx
@@ -592,19 +592,19 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Sunday, September 6, 2026</t>
+          <t>Monday, September 7, 2026</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>09:00 AM – 10:00 AM</t>
+          <t>10:25 AM – 11:25 AM</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -648,11 +648,11 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Monday, September 7, 2026</t>
+          <t>Sunday, September 6, 2026</t>
         </is>
       </c>
       <c r="C5" t="n">
@@ -704,11 +704,11 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Thursday, September 3, 2026</t>
+          <t>Sunday, September 6, 2026</t>
         </is>
       </c>
       <c r="C6" t="n">
@@ -760,11 +760,11 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Sunday, September 6, 2026</t>
+          <t>Thursday, September 3, 2026</t>
         </is>
       </c>
       <c r="C7" t="n">
@@ -816,19 +816,19 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Wednesday, September 2, 2026</t>
+          <t>Monday, September 7, 2026</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>08:00 AM – 09:00 AM</t>
+          <t>09:00 AM – 10:00 AM</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -872,11 +872,11 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Monday, September 7, 2026</t>
+          <t>Wednesday, September 2, 2026</t>
         </is>
       </c>
       <c r="C9" t="n">
@@ -928,19 +928,19 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Wednesday, September 2, 2026</t>
+          <t>Thursday, September 3, 2026</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>10:25 AM – 11:25 AM</t>
+          <t>09:00 AM – 10:00 AM</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -992,11 +992,11 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>10:25 AM – 11:25 AM</t>
+          <t>09:00 AM – 10:00 AM</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -1048,11 +1048,11 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>09:00 AM – 10:00 AM</t>
+          <t>10:25 AM – 11:25 AM</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -1104,11 +1104,11 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>09:00 AM – 10:00 AM</t>
+          <t>08:00 AM – 09:00 AM</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -1152,19 +1152,19 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Monday, September 7, 2026</t>
+          <t>Wednesday, September 2, 2026</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>10:25 AM – 11:25 AM</t>
+          <t>08:00 AM – 09:00 AM</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -1208,19 +1208,19 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Wednesday, September 2, 2026</t>
+          <t>Sunday, September 6, 2026</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>09:00 AM – 10:00 AM</t>
+          <t>10:25 AM – 11:25 AM</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -1264,11 +1264,11 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Sunday, September 6, 2026</t>
+          <t>Monday, September 7, 2026</t>
         </is>
       </c>
       <c r="C16" t="n">
@@ -1320,19 +1320,19 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Thursday, September 3, 2026</t>
+          <t>Wednesday, September 2, 2026</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>10:25 AM – 11:25 AM</t>
+          <t>09:00 AM – 10:00 AM</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -1376,11 +1376,11 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Sunday, September 6, 2026</t>
+          <t>Monday, September 7, 2026</t>
         </is>
       </c>
       <c r="C18" t="n">
@@ -1432,19 +1432,19 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Thursday, September 3, 2026</t>
+          <t>Sunday, September 6, 2026</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>10:25 AM – 11:25 AM</t>
+          <t>08:00 AM – 09:00 AM</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -1488,19 +1488,19 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Wednesday, September 2, 2026</t>
+          <t>Thursday, September 3, 2026</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>09:00 AM – 10:00 AM</t>
+          <t>10:25 AM – 11:25 AM</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -1600,19 +1600,19 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Thursday, September 3, 2026</t>
+          <t>Wednesday, September 2, 2026</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>08:00 AM – 09:00 AM</t>
+          <t>10:25 AM – 11:25 AM</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -1656,11 +1656,11 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Wednesday, September 2, 2026</t>
+          <t>Monday, September 7, 2026</t>
         </is>
       </c>
       <c r="C23" t="n">
@@ -1712,19 +1712,19 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Monday, September 7, 2026</t>
+          <t>Thursday, September 3, 2026</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>10:25 AM – 11:25 AM</t>
+          <t>09:00 AM – 10:00 AM</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -1768,19 +1768,19 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Monday, September 7, 2026</t>
+          <t>Wednesday, September 2, 2026</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>09:00 AM – 10:00 AM</t>
+          <t>08:00 AM – 09:00 AM</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -1832,11 +1832,11 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>09:00 AM – 10:00 AM</t>
+          <t>10:25 AM – 11:25 AM</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -1880,19 +1880,19 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Sunday, September 6, 2026</t>
+          <t>Monday, September 7, 2026</t>
         </is>
       </c>
       <c r="C27" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>09:00 AM – 10:00 AM</t>
+          <t>10:25 AM – 11:25 AM</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
@@ -1936,11 +1936,11 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Sunday, September 6, 2026</t>
+          <t>Thursday, September 3, 2026</t>
         </is>
       </c>
       <c r="C28" t="n">
@@ -1992,19 +1992,19 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Thursday, September 3, 2026</t>
+          <t>Sunday, September 6, 2026</t>
         </is>
       </c>
       <c r="C29" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>10:25 AM – 11:25 AM</t>
+          <t>08:00 AM – 09:00 AM</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
@@ -2104,11 +2104,11 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Wednesday, September 2, 2026</t>
+          <t>Sunday, September 6, 2026</t>
         </is>
       </c>
       <c r="C31" t="n">
@@ -2160,19 +2160,19 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Monday, September 7, 2026</t>
+          <t>Wednesday, September 2, 2026</t>
         </is>
       </c>
       <c r="C32" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>09:00 AM – 10:00 AM</t>
+          <t>08:00 AM – 09:00 AM</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
@@ -2216,19 +2216,19 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Thursday, September 3, 2026</t>
+          <t>Monday, September 7, 2026</t>
         </is>
       </c>
       <c r="C33" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>09:00 AM – 10:00 AM</t>
+          <t>08:00 AM – 09:00 AM</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
@@ -2272,19 +2272,19 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Monday, September 7, 2026</t>
+          <t>Sunday, September 6, 2026</t>
         </is>
       </c>
       <c r="C34" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>10:25 AM – 11:25 AM</t>
+          <t>09:00 AM – 10:00 AM</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
@@ -2328,19 +2328,19 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Sunday, September 6, 2026</t>
+          <t>Monday, September 7, 2026</t>
         </is>
       </c>
       <c r="C35" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>09:00 AM – 10:00 AM</t>
+          <t>10:25 AM – 11:25 AM</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
@@ -2392,11 +2392,11 @@
         </is>
       </c>
       <c r="C36" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>08:00 AM – 09:00 AM</t>
+          <t>09:00 AM – 10:00 AM</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
@@ -2440,19 +2440,19 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Monday, September 7, 2026</t>
+          <t>Sunday, September 6, 2026</t>
         </is>
       </c>
       <c r="C37" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>08:00 AM – 09:00 AM</t>
+          <t>10:25 AM – 11:25 AM</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
@@ -2504,11 +2504,11 @@
         </is>
       </c>
       <c r="C38" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>10:25 AM – 11:25 AM</t>
+          <t>09:00 AM – 10:00 AM</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
@@ -2552,19 +2552,19 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Thursday, September 3, 2026</t>
+          <t>Wednesday, September 2, 2026</t>
         </is>
       </c>
       <c r="C39" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>08:00 AM – 09:00 AM</t>
+          <t>10:25 AM – 11:25 AM</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
@@ -2608,11 +2608,11 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Monday, September 7, 2026</t>
+          <t>Thursday, September 3, 2026</t>
         </is>
       </c>
       <c r="C40" t="n">
@@ -2664,11 +2664,11 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Wednesday, September 2, 2026</t>
+          <t>Monday, September 7, 2026</t>
         </is>
       </c>
       <c r="C41" t="n">
@@ -2728,11 +2728,11 @@
         </is>
       </c>
       <c r="C42" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>10:25 AM – 11:25 AM</t>
+          <t>08:00 AM – 09:00 AM</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
@@ -2776,19 +2776,19 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Wednesday, September 2, 2026</t>
+          <t>Monday, September 7, 2026</t>
         </is>
       </c>
       <c r="C43" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>10:25 AM – 11:25 AM</t>
+          <t>09:00 AM – 10:00 AM</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
@@ -2832,11 +2832,11 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Thursday, September 3, 2026</t>
+          <t>Wednesday, September 2, 2026</t>
         </is>
       </c>
       <c r="C44" t="n">
@@ -2888,11 +2888,11 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Monday, September 7, 2026</t>
+          <t>Thursday, September 3, 2026</t>
         </is>
       </c>
       <c r="C45" t="n">
@@ -3008,11 +3008,11 @@
         </is>
       </c>
       <c r="C47" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>09:00 AM – 10:00 AM</t>
+          <t>08:00 AM – 09:00 AM</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
@@ -3056,19 +3056,19 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Thursday, September 3, 2026</t>
+          <t>Wednesday, September 2, 2026</t>
         </is>
       </c>
       <c r="C48" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>08:00 AM – 09:00 AM</t>
+          <t>09:00 AM – 10:00 AM</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
@@ -3112,19 +3112,19 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Sunday, September 6, 2026</t>
+          <t>Monday, September 7, 2026</t>
         </is>
       </c>
       <c r="C49" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>10:25 AM – 11:25 AM</t>
+          <t>08:00 AM – 09:00 AM</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
@@ -3168,11 +3168,11 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Thursday, September 3, 2026</t>
+          <t>Sunday, September 6, 2026</t>
         </is>
       </c>
       <c r="C50" t="n">
@@ -3224,19 +3224,19 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Wednesday, September 2, 2026</t>
+          <t>Monday, September 7, 2026</t>
         </is>
       </c>
       <c r="C51" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>10:25 AM – 11:25 AM</t>
+          <t>09:00 AM – 10:00 AM</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
@@ -3280,19 +3280,19 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Monday, September 7, 2026</t>
+          <t>Thursday, September 3, 2026</t>
         </is>
       </c>
       <c r="C52" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>09:00 AM – 10:00 AM</t>
+          <t>08:00 AM – 09:00 AM</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
@@ -3336,19 +3336,19 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Sunday, September 6, 2026</t>
+          <t>Monday, September 7, 2026</t>
         </is>
       </c>
       <c r="C53" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>09:00 AM – 10:00 AM</t>
+          <t>10:25 AM – 11:25 AM</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
@@ -3400,11 +3400,11 @@
         </is>
       </c>
       <c r="C54" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>08:00 AM – 09:00 AM</t>
+          <t>09:00 AM – 10:00 AM</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
@@ -3448,19 +3448,19 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Thursday, September 3, 2026</t>
+          <t>Sunday, September 6, 2026</t>
         </is>
       </c>
       <c r="C55" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>08:00 AM – 09:00 AM</t>
+          <t>09:00 AM – 10:00 AM</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
@@ -3504,11 +3504,11 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Wednesday, September 2, 2026</t>
+          <t>Sunday, September 6, 2026</t>
         </is>
       </c>
       <c r="C56" t="n">
@@ -3568,11 +3568,11 @@
         </is>
       </c>
       <c r="C57" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>09:00 AM – 10:00 AM</t>
+          <t>10:25 AM – 11:25 AM</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
@@ -3616,11 +3616,11 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Wednesday, September 2, 2026</t>
+          <t>Monday, September 7, 2026</t>
         </is>
       </c>
       <c r="C58" t="n">
@@ -3672,19 +3672,19 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Sunday, September 6, 2026</t>
+          <t>Thursday, September 3, 2026</t>
         </is>
       </c>
       <c r="C59" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>10:25 AM – 11:25 AM</t>
+          <t>08:00 AM – 09:00 AM</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
@@ -3728,11 +3728,11 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Thursday, September 3, 2026</t>
+          <t>Sunday, September 6, 2026</t>
         </is>
       </c>
       <c r="C60" t="n">
@@ -3784,11 +3784,11 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Monday, September 7, 2026</t>
+          <t>Wednesday, September 2, 2026</t>
         </is>
       </c>
       <c r="C61" t="n">
@@ -3840,19 +3840,19 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Monday, September 7, 2026</t>
+          <t>Thursday, September 3, 2026</t>
         </is>
       </c>
       <c r="C62" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>08:00 AM – 09:00 AM</t>
+          <t>09:00 AM – 10:00 AM</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
@@ -3896,19 +3896,19 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Sunday, September 6, 2026</t>
+          <t>Monday, September 7, 2026</t>
         </is>
       </c>
       <c r="C63" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>09:00 AM – 10:00 AM</t>
+          <t>10:25 AM – 11:25 AM</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
@@ -3960,11 +3960,11 @@
         </is>
       </c>
       <c r="C64" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>10:25 AM – 11:25 AM</t>
+          <t>08:00 AM – 09:00 AM</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
@@ -4008,19 +4008,19 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Thursday, September 3, 2026</t>
+          <t>Sunday, September 6, 2026</t>
         </is>
       </c>
       <c r="C65" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>02:20 PM – 03:05 PM</t>
+          <t>01:30 PM – 02:15 PM</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
@@ -4120,11 +4120,11 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Sunday, September 6, 2026</t>
+          <t>Wednesday, September 2, 2026</t>
         </is>
       </c>
       <c r="C67" t="n">
@@ -4176,11 +4176,11 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Wednesday, September 2, 2026</t>
+          <t>Thursday, September 3, 2026</t>
         </is>
       </c>
       <c r="C68" t="n">
@@ -4240,11 +4240,11 @@
         </is>
       </c>
       <c r="C69" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>03:10 PM – 03:40 PM</t>
+          <t>02:20 PM – 03:05 PM</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
@@ -4288,19 +4288,19 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Monday, September 7, 2026</t>
+          <t>Wednesday, September 2, 2026</t>
         </is>
       </c>
       <c r="C70" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>03:10 PM – 04:10 PM</t>
+          <t>12:40 PM – 01:40 PM</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
@@ -4344,19 +4344,19 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Sunday, September 6, 2026</t>
+          <t>Thursday, September 3, 2026</t>
         </is>
       </c>
       <c r="C71" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>03:10 PM – 04:10 PM</t>
+          <t>01:50 PM – 02:50 PM</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
@@ -4400,19 +4400,19 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Thursday, September 3, 2026</t>
+          <t>Sunday, September 6, 2026</t>
         </is>
       </c>
       <c r="C72" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>12:40 PM – 01:40 PM</t>
+          <t>01:50 PM – 02:50 PM</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
@@ -4456,11 +4456,11 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Thursday, September 3, 2026</t>
+          <t>Sunday, September 6, 2026</t>
         </is>
       </c>
       <c r="C73" t="n">
@@ -4520,11 +4520,11 @@
         </is>
       </c>
       <c r="C74" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>12:40 PM – 01:40 PM</t>
+          <t>01:50 PM – 02:50 PM</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
@@ -4568,19 +4568,19 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Sunday, September 6, 2026</t>
+          <t>Wednesday, September 2, 2026</t>
         </is>
       </c>
       <c r="C75" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>12:40 PM – 01:40 PM</t>
+          <t>03:10 PM – 04:10 PM</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
@@ -4624,19 +4624,19 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
+        <v>4</v>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>Monday, September 7, 2026</t>
+        </is>
+      </c>
+      <c r="C76" t="n">
         <v>1</v>
       </c>
-      <c r="B76" t="inlineStr">
-        <is>
-          <t>Wednesday, September 2, 2026</t>
-        </is>
-      </c>
-      <c r="C76" t="n">
-        <v>2</v>
-      </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>01:50 PM – 02:50 PM</t>
+          <t>12:40 PM – 01:40 PM</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
@@ -4680,19 +4680,19 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
+        <v>2</v>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>Thursday, September 3, 2026</t>
+        </is>
+      </c>
+      <c r="C77" t="n">
         <v>1</v>
       </c>
-      <c r="B77" t="inlineStr">
-        <is>
-          <t>Wednesday, September 2, 2026</t>
-        </is>
-      </c>
-      <c r="C77" t="n">
-        <v>3</v>
-      </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>03:10 PM – 04:10 PM</t>
+          <t>12:40 PM – 01:40 PM</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
@@ -4792,19 +4792,19 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
+        <v>2</v>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>Thursday, September 3, 2026</t>
+        </is>
+      </c>
+      <c r="C79" t="n">
         <v>1</v>
       </c>
-      <c r="B79" t="inlineStr">
-        <is>
-          <t>Wednesday, September 2, 2026</t>
-        </is>
-      </c>
-      <c r="C79" t="n">
-        <v>3</v>
-      </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>03:10 PM – 04:10 PM</t>
+          <t>12:40 PM – 01:40 PM</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
@@ -4848,19 +4848,19 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Sunday, September 6, 2026</t>
+          <t>Thursday, September 3, 2026</t>
         </is>
       </c>
       <c r="C80" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>12:40 PM – 01:40 PM</t>
+          <t>01:50 PM – 02:50 PM</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
@@ -4904,19 +4904,19 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Thursday, September 3, 2026</t>
+          <t>Monday, September 7, 2026</t>
         </is>
       </c>
       <c r="C81" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>03:10 PM – 04:10 PM</t>
+          <t>12:40 PM – 01:40 PM</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
@@ -4968,11 +4968,11 @@
         </is>
       </c>
       <c r="C82" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>12:40 PM – 01:40 PM</t>
+          <t>01:50 PM – 02:50 PM</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
@@ -5024,11 +5024,11 @@
         </is>
       </c>
       <c r="C83" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>12:40 PM – 01:40 PM</t>
+          <t>01:50 PM – 02:50 PM</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
@@ -5072,19 +5072,19 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Monday, September 7, 2026</t>
+          <t>Wednesday, September 2, 2026</t>
         </is>
       </c>
       <c r="C84" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>03:10 PM – 04:10 PM</t>
+          <t>12:40 PM – 01:40 PM</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
@@ -5128,11 +5128,11 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Thursday, September 3, 2026</t>
+          <t>Sunday, September 6, 2026</t>
         </is>
       </c>
       <c r="C85" t="n">
@@ -5184,19 +5184,19 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Thursday, September 3, 2026</t>
+          <t>Sunday, September 6, 2026</t>
         </is>
       </c>
       <c r="C86" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>03:10 PM – 04:10 PM</t>
+          <t>12:40 PM – 01:40 PM</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
@@ -5240,11 +5240,11 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Thursday, September 3, 2026</t>
+          <t>Monday, September 7, 2026</t>
         </is>
       </c>
       <c r="C87" t="n">
@@ -5296,19 +5296,19 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Monday, September 7, 2026</t>
+          <t>Thursday, September 3, 2026</t>
         </is>
       </c>
       <c r="C88" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>03:10 PM – 04:10 PM</t>
+          <t>12:40 PM – 01:40 PM</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
@@ -5352,19 +5352,19 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
+        <v>4</v>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>Monday, September 7, 2026</t>
+        </is>
+      </c>
+      <c r="C89" t="n">
         <v>1</v>
       </c>
-      <c r="B89" t="inlineStr">
-        <is>
-          <t>Wednesday, September 2, 2026</t>
-        </is>
-      </c>
-      <c r="C89" t="n">
-        <v>2</v>
-      </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>01:50 PM – 02:50 PM</t>
+          <t>12:40 PM – 01:40 PM</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
@@ -5408,19 +5408,19 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Monday, September 7, 2026</t>
+          <t>Sunday, September 6, 2026</t>
         </is>
       </c>
       <c r="C90" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>12:40 PM – 01:40 PM</t>
+          <t>01:50 PM – 02:50 PM</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
@@ -5520,19 +5520,19 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Sunday, September 6, 2026</t>
+          <t>Thursday, September 3, 2026</t>
         </is>
       </c>
       <c r="C92" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>12:40 PM – 01:40 PM</t>
+          <t>01:50 PM – 02:50 PM</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
@@ -5576,11 +5576,11 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Sunday, September 6, 2026</t>
+          <t>Thursday, September 3, 2026</t>
         </is>
       </c>
       <c r="C93" t="n">
@@ -5696,11 +5696,11 @@
         </is>
       </c>
       <c r="C95" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>12:40 PM – 01:40 PM</t>
+          <t>03:10 PM – 04:10 PM</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
@@ -5744,19 +5744,19 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Sunday, September 6, 2026</t>
+          <t>Thursday, September 3, 2026</t>
         </is>
       </c>
       <c r="C96" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>03:10 PM – 04:10 PM</t>
+          <t>12:40 PM – 01:40 PM</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
@@ -5800,19 +5800,19 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>Monday, September 7, 2026</t>
+          <t>Sunday, September 6, 2026</t>
         </is>
       </c>
       <c r="C97" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>01:50 PM – 02:50 PM</t>
+          <t>03:10 PM – 04:10 PM</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
@@ -5856,11 +5856,11 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>Thursday, September 3, 2026</t>
+          <t>Wednesday, September 2, 2026</t>
         </is>
       </c>
       <c r="C98" t="n">
@@ -5920,11 +5920,11 @@
         </is>
       </c>
       <c r="C99" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>12:40 PM – 01:40 PM</t>
+          <t>01:50 PM – 02:50 PM</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
@@ -5968,19 +5968,19 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>Monday, September 7, 2026</t>
+          <t>Wednesday, September 2, 2026</t>
         </is>
       </c>
       <c r="C100" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>03:10 PM – 04:10 PM</t>
+          <t>12:40 PM – 01:40 PM</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
@@ -6024,19 +6024,19 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>Wednesday, September 2, 2026</t>
+          <t>Sunday, September 6, 2026</t>
         </is>
       </c>
       <c r="C101" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>12:40 PM – 01:40 PM</t>
+          <t>01:50 PM – 02:50 PM</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
@@ -6080,19 +6080,19 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>Thursday, September 3, 2026</t>
+          <t>Monday, September 7, 2026</t>
         </is>
       </c>
       <c r="C102" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>03:10 PM – 04:10 PM</t>
+          <t>01:50 PM – 02:50 PM</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
@@ -6136,19 +6136,19 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
+        <v>4</v>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>Monday, September 7, 2026</t>
+        </is>
+      </c>
+      <c r="C103" t="n">
         <v>1</v>
       </c>
-      <c r="B103" t="inlineStr">
-        <is>
-          <t>Wednesday, September 2, 2026</t>
-        </is>
-      </c>
-      <c r="C103" t="n">
-        <v>2</v>
-      </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>01:50 PM – 02:50 PM</t>
+          <t>12:40 PM – 01:40 PM</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
@@ -6200,11 +6200,11 @@
         </is>
       </c>
       <c r="C104" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>01:50 PM – 02:50 PM</t>
+          <t>12:40 PM – 01:40 PM</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
@@ -6248,11 +6248,11 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>Wednesday, September 2, 2026</t>
+          <t>Sunday, September 6, 2026</t>
         </is>
       </c>
       <c r="C105" t="n">
@@ -6304,19 +6304,19 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>Wednesday, September 2, 2026</t>
+          <t>Thursday, September 3, 2026</t>
         </is>
       </c>
       <c r="C106" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>12:40 PM – 01:40 PM</t>
+          <t>03:10 PM – 04:10 PM</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
@@ -6368,11 +6368,11 @@
         </is>
       </c>
       <c r="C107" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>01:50 PM – 02:50 PM</t>
+          <t>03:10 PM – 04:10 PM</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
@@ -6416,11 +6416,11 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>Wednesday, September 2, 2026</t>
+          <t>Monday, September 7, 2026</t>
         </is>
       </c>
       <c r="C108" t="n">
@@ -6472,11 +6472,11 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>Thursday, September 3, 2026</t>
+          <t>Monday, September 7, 2026</t>
         </is>
       </c>
       <c r="C109" t="n">
@@ -6528,19 +6528,19 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>Sunday, September 6, 2026</t>
+          <t>Wednesday, September 2, 2026</t>
         </is>
       </c>
       <c r="C110" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>03:10 PM – 04:10 PM</t>
+          <t>01:50 PM – 02:50 PM</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
@@ -6584,11 +6584,11 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>Monday, September 7, 2026</t>
+          <t>Wednesday, September 2, 2026</t>
         </is>
       </c>
       <c r="C111" t="n">
@@ -6648,11 +6648,11 @@
         </is>
       </c>
       <c r="C112" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>12:40 PM – 01:40 PM</t>
+          <t>01:50 PM – 02:50 PM</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
@@ -6696,19 +6696,19 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>Thursday, September 3, 2026</t>
+          <t>Wednesday, September 2, 2026</t>
         </is>
       </c>
       <c r="C113" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>03:10 PM – 04:10 PM</t>
+          <t>12:40 PM – 01:40 PM</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
@@ -6752,19 +6752,19 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>Sunday, September 6, 2026</t>
+          <t>Thursday, September 3, 2026</t>
         </is>
       </c>
       <c r="C114" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>01:50 PM – 02:50 PM</t>
+          <t>12:40 PM – 01:40 PM</t>
         </is>
       </c>
       <c r="E114" t="inlineStr">
@@ -6808,19 +6808,19 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>Wednesday, September 2, 2026</t>
+          <t>Monday, September 7, 2026</t>
         </is>
       </c>
       <c r="C115" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>01:50 PM – 02:50 PM</t>
+          <t>03:10 PM – 04:10 PM</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
@@ -6864,19 +6864,19 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>Sunday, September 6, 2026</t>
+          <t>Thursday, September 3, 2026</t>
         </is>
       </c>
       <c r="C116" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>03:10 PM – 04:10 PM</t>
+          <t>12:40 PM – 01:40 PM</t>
         </is>
       </c>
       <c r="E116" t="inlineStr">
@@ -6920,11 +6920,11 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>Monday, September 7, 2026</t>
+          <t>Sunday, September 6, 2026</t>
         </is>
       </c>
       <c r="C117" t="n">
@@ -6976,19 +6976,19 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>Thursday, September 3, 2026</t>
+          <t>Wednesday, September 2, 2026</t>
         </is>
       </c>
       <c r="C118" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>03:10 PM – 04:10 PM</t>
+          <t>01:50 PM – 02:50 PM</t>
         </is>
       </c>
       <c r="E118" t="inlineStr">
@@ -7040,11 +7040,11 @@
         </is>
       </c>
       <c r="C119" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>12:40 PM – 01:40 PM</t>
+          <t>03:10 PM – 04:10 PM</t>
         </is>
       </c>
       <c r="E119" t="inlineStr">
@@ -7088,11 +7088,11 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>Sunday, September 6, 2026</t>
+          <t>Wednesday, September 2, 2026</t>
         </is>
       </c>
       <c r="C120" t="n">
@@ -7144,11 +7144,11 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>Monday, September 7, 2026</t>
+          <t>Wednesday, September 2, 2026</t>
         </is>
       </c>
       <c r="C121" t="n">
@@ -7208,11 +7208,11 @@
         </is>
       </c>
       <c r="C122" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>01:50 PM – 02:50 PM</t>
+          <t>03:10 PM – 04:10 PM</t>
         </is>
       </c>
       <c r="E122" t="inlineStr">
@@ -7312,19 +7312,19 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>Wednesday, September 2, 2026</t>
+          <t>Monday, September 7, 2026</t>
         </is>
       </c>
       <c r="C124" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>12:40 PM – 01:40 PM</t>
+          <t>01:50 PM – 02:50 PM</t>
         </is>
       </c>
       <c r="E124" t="inlineStr">
@@ -7368,11 +7368,11 @@
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>Sunday, September 6, 2026</t>
+          <t>Monday, September 7, 2026</t>
         </is>
       </c>
       <c r="C125" t="n">
@@ -7480,11 +7480,11 @@
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>Monday, September 7, 2026</t>
+          <t>Sunday, September 6, 2026</t>
         </is>
       </c>
       <c r="C127" t="n">
@@ -7536,11 +7536,11 @@
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>Thursday, September 3, 2026</t>
+          <t>Sunday, September 6, 2026</t>
         </is>
       </c>
       <c r="C128" t="n">
@@ -7592,19 +7592,19 @@
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>Monday, September 7, 2026</t>
+          <t>Thursday, September 3, 2026</t>
         </is>
       </c>
       <c r="C129" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>12:40 PM – 01:40 PM</t>
+          <t>01:50 PM – 02:50 PM</t>
         </is>
       </c>
       <c r="E129" t="inlineStr">
@@ -7648,11 +7648,11 @@
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>Wednesday, September 2, 2026</t>
+          <t>Monday, September 7, 2026</t>
         </is>
       </c>
       <c r="C130" t="n">
@@ -7704,11 +7704,11 @@
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>Wednesday, September 2, 2026</t>
+          <t>Thursday, September 3, 2026</t>
         </is>
       </c>
       <c r="C131" t="n">
@@ -7768,11 +7768,11 @@
         </is>
       </c>
       <c r="C132" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>01:50 PM – 02:50 PM</t>
+          <t>03:10 PM – 04:10 PM</t>
         </is>
       </c>
       <c r="E132" t="inlineStr">
@@ -7816,11 +7816,11 @@
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>Sunday, September 6, 2026</t>
+          <t>Wednesday, September 2, 2026</t>
         </is>
       </c>
       <c r="C133" t="n">
@@ -7872,19 +7872,19 @@
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>Thursday, September 3, 2026</t>
+          <t>Sunday, September 6, 2026</t>
         </is>
       </c>
       <c r="C134" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>03:10 PM – 04:10 PM</t>
+          <t>01:50 PM – 02:50 PM</t>
         </is>
       </c>
       <c r="E134" t="inlineStr">
@@ -7928,11 +7928,11 @@
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>Sunday, September 6, 2026</t>
+          <t>Thursday, September 3, 2026</t>
         </is>
       </c>
       <c r="C135" t="n">
@@ -7984,11 +7984,11 @@
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>Thursday, September 3, 2026</t>
+          <t>Sunday, September 6, 2026</t>
         </is>
       </c>
       <c r="C136" t="n">
@@ -8040,11 +8040,11 @@
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>Wednesday, September 2, 2026</t>
+          <t>Monday, September 7, 2026</t>
         </is>
       </c>
       <c r="C137" t="n">
@@ -8096,19 +8096,19 @@
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>Monday, September 7, 2026</t>
+          <t>Wednesday, September 2, 2026</t>
         </is>
       </c>
       <c r="C138" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>01:30 PM – 02:15 PM</t>
+          <t>02:20 PM – 03:05 PM</t>
         </is>
       </c>
       <c r="E138" t="inlineStr">
@@ -8160,11 +8160,11 @@
         </is>
       </c>
       <c r="C139" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>03:10 PM – 04:10 PM</t>
+          <t>01:50 PM – 02:50 PM</t>
         </is>
       </c>
       <c r="E139" t="inlineStr">
@@ -8208,19 +8208,19 @@
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>Monday, September 7, 2026</t>
+          <t>Thursday, September 3, 2026</t>
         </is>
       </c>
       <c r="C140" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>12:40 PM – 01:40 PM</t>
+          <t>01:50 PM – 02:50 PM</t>
         </is>
       </c>
       <c r="E140" t="inlineStr">
@@ -8264,11 +8264,11 @@
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>Thursday, September 3, 2026</t>
+          <t>Wednesday, September 2, 2026</t>
         </is>
       </c>
       <c r="C141" t="n">
@@ -8320,19 +8320,19 @@
     </row>
     <row r="142">
       <c r="A142" t="n">
+        <v>3</v>
+      </c>
+      <c r="B142" t="inlineStr">
+        <is>
+          <t>Sunday, September 6, 2026</t>
+        </is>
+      </c>
+      <c r="C142" t="n">
         <v>1</v>
       </c>
-      <c r="B142" t="inlineStr">
-        <is>
-          <t>Wednesday, September 2, 2026</t>
-        </is>
-      </c>
-      <c r="C142" t="n">
-        <v>3</v>
-      </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>03:10 PM – 04:10 PM</t>
+          <t>12:40 PM – 01:40 PM</t>
         </is>
       </c>
       <c r="E142" t="inlineStr">
@@ -8376,19 +8376,19 @@
     </row>
     <row r="143">
       <c r="A143" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>Thursday, September 3, 2026</t>
+          <t>Sunday, September 6, 2026</t>
         </is>
       </c>
       <c r="C143" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>03:10 PM – 04:10 PM</t>
+          <t>01:50 PM – 02:50 PM</t>
         </is>
       </c>
       <c r="E143" t="inlineStr">
@@ -8432,19 +8432,19 @@
     </row>
     <row r="144">
       <c r="A144" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>Sunday, September 6, 2026</t>
+          <t>Thursday, September 3, 2026</t>
         </is>
       </c>
       <c r="C144" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>03:10 PM – 04:10 PM</t>
+          <t>12:40 PM – 01:40 PM</t>
         </is>
       </c>
       <c r="E144" t="inlineStr">
@@ -8488,19 +8488,19 @@
     </row>
     <row r="145">
       <c r="A145" t="n">
+        <v>4</v>
+      </c>
+      <c r="B145" t="inlineStr">
+        <is>
+          <t>Monday, September 7, 2026</t>
+        </is>
+      </c>
+      <c r="C145" t="n">
         <v>1</v>
       </c>
-      <c r="B145" t="inlineStr">
-        <is>
-          <t>Wednesday, September 2, 2026</t>
-        </is>
-      </c>
-      <c r="C145" t="n">
-        <v>2</v>
-      </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>01:50 PM – 02:50 PM</t>
+          <t>12:40 PM – 01:40 PM</t>
         </is>
       </c>
       <c r="E145" t="inlineStr">
@@ -8544,11 +8544,11 @@
     </row>
     <row r="146">
       <c r="A146" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>Sunday, September 6, 2026</t>
+          <t>Wednesday, September 2, 2026</t>
         </is>
       </c>
       <c r="C146" t="n">
@@ -8600,19 +8600,19 @@
     </row>
     <row r="147">
       <c r="A147" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>Thursday, September 3, 2026</t>
+          <t>Monday, September 7, 2026</t>
         </is>
       </c>
       <c r="C147" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>12:40 PM – 01:40 PM</t>
+          <t>01:50 PM – 02:50 PM</t>
         </is>
       </c>
       <c r="E147" t="inlineStr">
@@ -8656,19 +8656,19 @@
     </row>
     <row r="148">
       <c r="A148" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>Monday, September 7, 2026</t>
+          <t>Sunday, September 6, 2026</t>
         </is>
       </c>
       <c r="C148" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>01:50 PM – 02:50 PM</t>
+          <t>03:10 PM – 04:10 PM</t>
         </is>
       </c>
       <c r="E148" t="inlineStr">
@@ -8712,19 +8712,19 @@
     </row>
     <row r="149">
       <c r="A149" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>Monday, September 7, 2026</t>
+          <t>Thursday, September 3, 2026</t>
         </is>
       </c>
       <c r="C149" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>03:10 PM – 04:10 PM</t>
+          <t>12:40 PM – 01:40 PM</t>
         </is>
       </c>
       <c r="E149" t="inlineStr">
@@ -8768,19 +8768,19 @@
     </row>
     <row r="150">
       <c r="A150" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>Sunday, September 6, 2026</t>
+          <t>Wednesday, September 2, 2026</t>
         </is>
       </c>
       <c r="C150" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>01:50 PM – 02:50 PM</t>
+          <t>03:10 PM – 04:10 PM</t>
         </is>
       </c>
       <c r="E150" t="inlineStr">
@@ -8824,19 +8824,19 @@
     </row>
     <row r="151">
       <c r="A151" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>Sunday, September 6, 2026</t>
+          <t>Thursday, September 3, 2026</t>
         </is>
       </c>
       <c r="C151" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>03:10 PM – 04:10 PM</t>
+          <t>01:50 PM – 02:50 PM</t>
         </is>
       </c>
       <c r="E151" t="inlineStr">
@@ -8880,11 +8880,11 @@
     </row>
     <row r="152">
       <c r="A152" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>Wednesday, September 2, 2026</t>
+          <t>Sunday, September 6, 2026</t>
         </is>
       </c>
       <c r="C152" t="n">
@@ -8936,11 +8936,11 @@
     </row>
     <row r="153">
       <c r="A153" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>Wednesday, September 2, 2026</t>
+          <t>Monday, September 7, 2026</t>
         </is>
       </c>
       <c r="C153" t="n">
@@ -8992,11 +8992,11 @@
     </row>
     <row r="154">
       <c r="A154" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>Thursday, September 3, 2026</t>
+          <t>Wednesday, September 2, 2026</t>
         </is>
       </c>
       <c r="C154" t="n">
@@ -9048,19 +9048,19 @@
     </row>
     <row r="155">
       <c r="A155" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>Monday, September 7, 2026</t>
+          <t>Wednesday, September 2, 2026</t>
         </is>
       </c>
       <c r="C155" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>01:50 PM – 02:50 PM</t>
+          <t>12:40 PM – 01:40 PM</t>
         </is>
       </c>
       <c r="E155" t="inlineStr">
@@ -9104,19 +9104,19 @@
     </row>
     <row r="156">
       <c r="A156" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>Thursday, September 3, 2026</t>
+          <t>Sunday, September 6, 2026</t>
         </is>
       </c>
       <c r="C156" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>03:10 PM – 04:10 PM</t>
+          <t>12:40 PM – 01:40 PM</t>
         </is>
       </c>
       <c r="E156" t="inlineStr">
@@ -9160,11 +9160,11 @@
     </row>
     <row r="157">
       <c r="A157" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>Sunday, September 6, 2026</t>
+          <t>Wednesday, September 2, 2026</t>
         </is>
       </c>
       <c r="C157" t="n">
@@ -9216,11 +9216,11 @@
     </row>
     <row r="158">
       <c r="A158" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>Monday, September 7, 2026</t>
+          <t>Thursday, September 3, 2026</t>
         </is>
       </c>
       <c r="C158" t="n">
@@ -9272,11 +9272,11 @@
     </row>
     <row r="159">
       <c r="A159" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>Sunday, September 6, 2026</t>
+          <t>Thursday, September 3, 2026</t>
         </is>
       </c>
       <c r="C159" t="n">
@@ -9328,11 +9328,11 @@
     </row>
     <row r="160">
       <c r="A160" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>Wednesday, September 2, 2026</t>
+          <t>Thursday, September 3, 2026</t>
         </is>
       </c>
       <c r="C160" t="n">
@@ -9384,19 +9384,19 @@
     </row>
     <row r="161">
       <c r="A161" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>Wednesday, September 2, 2026</t>
+          <t>Monday, September 7, 2026</t>
         </is>
       </c>
       <c r="C161" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>01:50 PM – 02:50 PM</t>
+          <t>03:10 PM – 04:10 PM</t>
         </is>
       </c>
       <c r="E161" t="inlineStr">
@@ -9440,19 +9440,19 @@
     </row>
     <row r="162">
       <c r="A162" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>Monday, September 7, 2026</t>
+          <t>Sunday, September 6, 2026</t>
         </is>
       </c>
       <c r="C162" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>12:40 PM – 01:40 PM</t>
+          <t>03:10 PM – 04:10 PM</t>
         </is>
       </c>
       <c r="E162" t="inlineStr">
@@ -9496,11 +9496,11 @@
     </row>
     <row r="163">
       <c r="A163" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>Thursday, September 3, 2026</t>
+          <t>Monday, September 7, 2026</t>
         </is>
       </c>
       <c r="C163" t="n">
@@ -9560,11 +9560,11 @@
         </is>
       </c>
       <c r="C164" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>01:50 PM – 02:50 PM</t>
+          <t>03:10 PM – 04:10 PM</t>
         </is>
       </c>
       <c r="E164" t="inlineStr">
@@ -9672,11 +9672,11 @@
         </is>
       </c>
       <c r="C166" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>03:10 PM – 04:10 PM</t>
+          <t>12:40 PM – 01:40 PM</t>
         </is>
       </c>
       <c r="E166" t="inlineStr">
@@ -9720,11 +9720,11 @@
     </row>
     <row r="167">
       <c r="A167" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>Sunday, September 6, 2026</t>
+          <t>Monday, September 7, 2026</t>
         </is>
       </c>
       <c r="C167" t="n">
@@ -9776,11 +9776,11 @@
     </row>
     <row r="168">
       <c r="A168" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>Thursday, September 3, 2026</t>
+          <t>Sunday, September 6, 2026</t>
         </is>
       </c>
       <c r="C168" t="n">
@@ -9832,11 +9832,11 @@
     </row>
     <row r="169">
       <c r="A169" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>Monday, September 7, 2026</t>
+          <t>Thursday, September 3, 2026</t>
         </is>
       </c>
       <c r="C169" t="n">
@@ -9896,11 +9896,11 @@
         </is>
       </c>
       <c r="C170" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t>12:40 PM – 01:40 PM</t>
+          <t>03:10 PM – 04:10 PM</t>
         </is>
       </c>
       <c r="E170" t="inlineStr">
@@ -9944,19 +9944,19 @@
     </row>
     <row r="171">
       <c r="A171" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>Monday, September 7, 2026</t>
+          <t>Wednesday, September 2, 2026</t>
         </is>
       </c>
       <c r="C171" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t>03:10 PM – 04:10 PM</t>
+          <t>01:50 PM – 02:50 PM</t>
         </is>
       </c>
       <c r="E171" t="inlineStr">
@@ -10056,19 +10056,19 @@
     </row>
     <row r="173">
       <c r="A173" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>Sunday, September 6, 2026</t>
+          <t>Wednesday, September 2, 2026</t>
         </is>
       </c>
       <c r="C173" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t>03:10 PM – 04:10 PM</t>
+          <t>01:50 PM – 02:50 PM</t>
         </is>
       </c>
       <c r="E173" t="inlineStr">
@@ -10112,11 +10112,11 @@
     </row>
     <row r="174">
       <c r="A174" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>Monday, September 7, 2026</t>
+          <t>Thursday, September 3, 2026</t>
         </is>
       </c>
       <c r="C174" t="n">
@@ -10168,11 +10168,11 @@
     </row>
     <row r="175">
       <c r="A175" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>Monday, September 7, 2026</t>
+          <t>Sunday, September 6, 2026</t>
         </is>
       </c>
       <c r="C175" t="n">
@@ -10224,11 +10224,11 @@
     </row>
     <row r="176">
       <c r="A176" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>Sunday, September 6, 2026</t>
+          <t>Monday, September 7, 2026</t>
         </is>
       </c>
       <c r="C176" t="n">
@@ -10336,11 +10336,11 @@
     </row>
     <row r="178">
       <c r="A178" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>Thursday, September 3, 2026</t>
+          <t>Sunday, September 6, 2026</t>
         </is>
       </c>
       <c r="C178" t="n">
@@ -10448,19 +10448,19 @@
     </row>
     <row r="180">
       <c r="A180" t="n">
+        <v>4</v>
+      </c>
+      <c r="B180" t="inlineStr">
+        <is>
+          <t>Monday, September 7, 2026</t>
+        </is>
+      </c>
+      <c r="C180" t="n">
         <v>1</v>
       </c>
-      <c r="B180" t="inlineStr">
-        <is>
-          <t>Wednesday, September 2, 2026</t>
-        </is>
-      </c>
-      <c r="C180" t="n">
-        <v>3</v>
-      </c>
       <c r="D180" t="inlineStr">
         <is>
-          <t>03:10 PM – 04:10 PM</t>
+          <t>12:40 PM – 01:40 PM</t>
         </is>
       </c>
       <c r="E180" t="inlineStr">
@@ -10504,11 +10504,11 @@
     </row>
     <row r="181">
       <c r="A181" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>Sunday, September 6, 2026</t>
+          <t>Thursday, September 3, 2026</t>
         </is>
       </c>
       <c r="C181" t="n">
@@ -10568,11 +10568,11 @@
         </is>
       </c>
       <c r="C182" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
-          <t>01:50 PM – 02:50 PM</t>
+          <t>03:10 PM – 04:10 PM</t>
         </is>
       </c>
       <c r="E182" t="inlineStr">
@@ -10616,19 +10616,19 @@
     </row>
     <row r="183">
       <c r="A183" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>Wednesday, September 2, 2026</t>
+          <t>Sunday, September 6, 2026</t>
         </is>
       </c>
       <c r="C183" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
-          <t>01:50 PM – 02:50 PM</t>
+          <t>03:10 PM – 04:10 PM</t>
         </is>
       </c>
       <c r="E183" t="inlineStr">
@@ -10672,19 +10672,19 @@
     </row>
     <row r="184">
       <c r="A184" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>Monday, September 7, 2026</t>
+          <t>Thursday, September 3, 2026</t>
         </is>
       </c>
       <c r="C184" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
-          <t>01:50 PM – 02:50 PM</t>
+          <t>03:10 PM – 04:10 PM</t>
         </is>
       </c>
       <c r="E184" t="inlineStr">
@@ -10728,19 +10728,19 @@
     </row>
     <row r="185">
       <c r="A185" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>Thursday, September 3, 2026</t>
+          <t>Wednesday, September 2, 2026</t>
         </is>
       </c>
       <c r="C185" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
-          <t>03:10 PM – 04:10 PM</t>
+          <t>01:50 PM – 02:50 PM</t>
         </is>
       </c>
       <c r="E185" t="inlineStr">
@@ -10840,19 +10840,19 @@
     </row>
     <row r="187">
       <c r="A187" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>Thursday, September 3, 2026</t>
+          <t>Monday, September 7, 2026</t>
         </is>
       </c>
       <c r="C187" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>
-          <t>01:50 PM – 02:50 PM</t>
+          <t>03:10 PM – 04:10 PM</t>
         </is>
       </c>
       <c r="E187" t="inlineStr">
@@ -10896,19 +10896,19 @@
     </row>
     <row r="188">
       <c r="A188" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>Monday, September 7, 2026</t>
+          <t>Thursday, September 3, 2026</t>
         </is>
       </c>
       <c r="C188" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D188" t="inlineStr">
         <is>
-          <t>12:40 PM – 01:40 PM</t>
+          <t>01:50 PM – 02:50 PM</t>
         </is>
       </c>
       <c r="E188" t="inlineStr">
@@ -11008,19 +11008,19 @@
     </row>
     <row r="190">
       <c r="A190" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>Sunday, September 6, 2026</t>
+          <t>Wednesday, September 2, 2026</t>
         </is>
       </c>
       <c r="C190" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D190" t="inlineStr">
         <is>
-          <t>03:10 PM – 04:10 PM</t>
+          <t>12:40 PM – 01:40 PM</t>
         </is>
       </c>
       <c r="E190" t="inlineStr">
@@ -11064,11 +11064,11 @@
     </row>
     <row r="191">
       <c r="A191" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>Wednesday, September 2, 2026</t>
+          <t>Thursday, September 3, 2026</t>
         </is>
       </c>
       <c r="C191" t="n">
@@ -11128,11 +11128,11 @@
         </is>
       </c>
       <c r="C192" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D192" t="inlineStr">
         <is>
-          <t>03:10 PM – 04:10 PM</t>
+          <t>12:40 PM – 01:40 PM</t>
         </is>
       </c>
       <c r="E192" t="inlineStr">
@@ -11176,19 +11176,19 @@
     </row>
     <row r="193">
       <c r="A193" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>Monday, September 7, 2026</t>
+          <t>Thursday, September 3, 2026</t>
         </is>
       </c>
       <c r="C193" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D193" t="inlineStr">
         <is>
-          <t>12:40 PM – 01:40 PM</t>
+          <t>01:50 PM – 02:50 PM</t>
         </is>
       </c>
       <c r="E193" t="inlineStr">
@@ -11232,11 +11232,11 @@
     </row>
     <row r="194">
       <c r="A194" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>Thursday, September 3, 2026</t>
+          <t>Sunday, September 6, 2026</t>
         </is>
       </c>
       <c r="C194" t="n">
@@ -11296,11 +11296,11 @@
         </is>
       </c>
       <c r="C195" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D195" t="inlineStr">
         <is>
-          <t>03:10 PM – 04:10 PM</t>
+          <t>01:50 PM – 02:50 PM</t>
         </is>
       </c>
       <c r="E195" t="inlineStr">
@@ -11352,11 +11352,11 @@
         </is>
       </c>
       <c r="C196" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D196" t="inlineStr">
         <is>
-          <t>12:40 PM – 01:40 PM</t>
+          <t>03:10 PM – 04:10 PM</t>
         </is>
       </c>
       <c r="E196" t="inlineStr">
@@ -11400,19 +11400,19 @@
     </row>
     <row r="197">
       <c r="A197" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>Sunday, September 6, 2026</t>
+          <t>Wednesday, September 2, 2026</t>
         </is>
       </c>
       <c r="C197" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D197" t="inlineStr">
         <is>
-          <t>03:10 PM – 04:10 PM</t>
+          <t>12:40 PM – 01:40 PM</t>
         </is>
       </c>
       <c r="E197" t="inlineStr">
@@ -11456,19 +11456,19 @@
     </row>
     <row r="198">
       <c r="A198" t="n">
+        <v>4</v>
+      </c>
+      <c r="B198" t="inlineStr">
+        <is>
+          <t>Monday, September 7, 2026</t>
+        </is>
+      </c>
+      <c r="C198" t="n">
         <v>1</v>
       </c>
-      <c r="B198" t="inlineStr">
-        <is>
-          <t>Wednesday, September 2, 2026</t>
-        </is>
-      </c>
-      <c r="C198" t="n">
-        <v>2</v>
-      </c>
       <c r="D198" t="inlineStr">
         <is>
-          <t>01:50 PM – 02:50 PM</t>
+          <t>12:40 PM – 01:40 PM</t>
         </is>
       </c>
       <c r="E198" t="inlineStr">
@@ -11512,19 +11512,19 @@
     </row>
     <row r="199">
       <c r="A199" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>Monday, September 7, 2026</t>
+          <t>Thursday, September 3, 2026</t>
         </is>
       </c>
       <c r="C199" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D199" t="inlineStr">
         <is>
-          <t>01:50 PM – 02:50 PM</t>
+          <t>12:40 PM – 01:40 PM</t>
         </is>
       </c>
       <c r="E199" t="inlineStr">
@@ -11632,11 +11632,11 @@
         </is>
       </c>
       <c r="C201" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D201" t="inlineStr">
         <is>
-          <t>03:10 PM – 04:10 PM</t>
+          <t>01:50 PM – 02:50 PM</t>
         </is>
       </c>
       <c r="E201" t="inlineStr">
@@ -11736,19 +11736,19 @@
     </row>
     <row r="203">
       <c r="A203" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>Sunday, September 6, 2026</t>
+          <t>Thursday, September 3, 2026</t>
         </is>
       </c>
       <c r="C203" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D203" t="inlineStr">
         <is>
-          <t>05:30 PM – 06:30 PM</t>
+          <t>04:20 PM – 05:20 PM</t>
         </is>
       </c>
       <c r="E203" t="inlineStr">
@@ -11792,11 +11792,11 @@
     </row>
     <row r="204">
       <c r="A204" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B204" t="inlineStr">
         <is>
-          <t>Thursday, September 3, 2026</t>
+          <t>Wednesday, September 2, 2026</t>
         </is>
       </c>
       <c r="C204" t="n">
@@ -11848,19 +11848,19 @@
     </row>
     <row r="205">
       <c r="A205" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B205" t="inlineStr">
         <is>
-          <t>Monday, September 7, 2026</t>
+          <t>Sunday, September 6, 2026</t>
         </is>
       </c>
       <c r="C205" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D205" t="inlineStr">
         <is>
-          <t>03:10 PM – 04:10 PM</t>
+          <t>05:30 PM – 06:30 PM</t>
         </is>
       </c>
       <c r="E205" t="inlineStr">
@@ -11904,19 +11904,19 @@
     </row>
     <row r="206">
       <c r="A206" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="B206" t="inlineStr">
         <is>
-          <t>Wednesday, September 2, 2026</t>
+          <t>Monday, September 7, 2026</t>
         </is>
       </c>
       <c r="C206" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D206" t="inlineStr">
         <is>
-          <t>03:10 PM – 04:10 PM</t>
+          <t>04:20 PM – 05:20 PM</t>
         </is>
       </c>
       <c r="E206" t="inlineStr">
@@ -11960,11 +11960,11 @@
     </row>
     <row r="207">
       <c r="A207" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B207" t="inlineStr">
         <is>
-          <t>Sunday, September 6, 2026</t>
+          <t>Thursday, September 3, 2026</t>
         </is>
       </c>
       <c r="C207" t="n">
@@ -12016,11 +12016,11 @@
     </row>
     <row r="208">
       <c r="A208" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="B208" t="inlineStr">
         <is>
-          <t>Thursday, September 3, 2026</t>
+          <t>Monday, September 7, 2026</t>
         </is>
       </c>
       <c r="C208" t="n">
@@ -12080,11 +12080,11 @@
         </is>
       </c>
       <c r="C209" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D209" t="inlineStr">
         <is>
-          <t>05:30 PM – 06:30 PM</t>
+          <t>04:20 PM – 05:20 PM</t>
         </is>
       </c>
       <c r="E209" t="inlineStr">
@@ -12128,11 +12128,11 @@
     </row>
     <row r="210">
       <c r="A210" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B210" t="inlineStr">
         <is>
-          <t>Monday, September 7, 2026</t>
+          <t>Sunday, September 6, 2026</t>
         </is>
       </c>
       <c r="C210" t="n">
@@ -12184,11 +12184,11 @@
     </row>
     <row r="211">
       <c r="A211" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B211" t="inlineStr">
         <is>
-          <t>Wednesday, September 2, 2026</t>
+          <t>Thursday, September 3, 2026</t>
         </is>
       </c>
       <c r="C211" t="n">
@@ -12240,19 +12240,19 @@
     </row>
     <row r="212">
       <c r="A212" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="B212" t="inlineStr">
         <is>
-          <t>Monday, September 7, 2026</t>
+          <t>Thursday, September 3, 2026</t>
         </is>
       </c>
       <c r="C212" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D212" t="inlineStr">
         <is>
-          <t>05:30 PM – 06:30 PM</t>
+          <t>04:20 PM – 05:20 PM</t>
         </is>
       </c>
       <c r="E212" t="inlineStr">
@@ -12296,11 +12296,11 @@
     </row>
     <row r="213">
       <c r="A213" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B213" t="inlineStr">
         <is>
-          <t>Thursday, September 3, 2026</t>
+          <t>Sunday, September 6, 2026</t>
         </is>
       </c>
       <c r="C213" t="n">
@@ -12352,19 +12352,19 @@
     </row>
     <row r="214">
       <c r="A214" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B214" t="inlineStr">
         <is>
-          <t>Sunday, September 6, 2026</t>
+          <t>Monday, September 7, 2026</t>
         </is>
       </c>
       <c r="C214" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D214" t="inlineStr">
         <is>
-          <t>05:30 PM – 06:30 PM</t>
+          <t>03:10 PM – 04:10 PM</t>
         </is>
       </c>
       <c r="E214" t="inlineStr">
@@ -12408,19 +12408,19 @@
     </row>
     <row r="215">
       <c r="A215" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B215" t="inlineStr">
         <is>
-          <t>Thursday, September 3, 2026</t>
+          <t>Sunday, September 6, 2026</t>
         </is>
       </c>
       <c r="C215" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D215" t="inlineStr">
         <is>
-          <t>03:10 PM – 04:10 PM</t>
+          <t>05:30 PM – 06:30 PM</t>
         </is>
       </c>
       <c r="E215" t="inlineStr">
@@ -12464,19 +12464,19 @@
     </row>
     <row r="216">
       <c r="A216" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="B216" t="inlineStr">
         <is>
-          <t>Sunday, September 6, 2026</t>
+          <t>Wednesday, September 2, 2026</t>
         </is>
       </c>
       <c r="C216" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D216" t="inlineStr">
         <is>
-          <t>04:20 PM – 05:20 PM</t>
+          <t>05:30 PM – 06:30 PM</t>
         </is>
       </c>
       <c r="E216" t="inlineStr">
@@ -12520,19 +12520,19 @@
     </row>
     <row r="217">
       <c r="A217" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="B217" t="inlineStr">
         <is>
-          <t>Wednesday, September 2, 2026</t>
+          <t>Monday, September 7, 2026</t>
         </is>
       </c>
       <c r="C217" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D217" t="inlineStr">
         <is>
-          <t>04:20 PM – 05:20 PM</t>
+          <t>05:30 PM – 06:30 PM</t>
         </is>
       </c>
       <c r="E217" t="inlineStr">
@@ -12576,11 +12576,11 @@
     </row>
     <row r="218">
       <c r="A218" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="B218" t="inlineStr">
         <is>
-          <t>Monday, September 7, 2026</t>
+          <t>Wednesday, September 2, 2026</t>
         </is>
       </c>
       <c r="C218" t="n">
@@ -12632,19 +12632,19 @@
     </row>
     <row r="219">
       <c r="A219" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="B219" t="inlineStr">
         <is>
-          <t>Sunday, September 6, 2026</t>
+          <t>Wednesday, September 2, 2026</t>
         </is>
       </c>
       <c r="C219" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D219" t="inlineStr">
         <is>
-          <t>03:10 PM – 04:10 PM</t>
+          <t>05:30 PM – 06:30 PM</t>
         </is>
       </c>
       <c r="E219" t="inlineStr">
@@ -12688,19 +12688,19 @@
     </row>
     <row r="220">
       <c r="A220" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="B220" t="inlineStr">
         <is>
-          <t>Thursday, September 3, 2026</t>
+          <t>Monday, September 7, 2026</t>
         </is>
       </c>
       <c r="C220" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D220" t="inlineStr">
         <is>
-          <t>04:20 PM – 05:20 PM</t>
+          <t>05:30 PM – 06:30 PM</t>
         </is>
       </c>
       <c r="E220" t="inlineStr">
@@ -12752,11 +12752,11 @@
         </is>
       </c>
       <c r="C221" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D221" t="inlineStr">
         <is>
-          <t>05:30 PM – 06:30 PM</t>
+          <t>04:20 PM – 05:20 PM</t>
         </is>
       </c>
       <c r="E221" t="inlineStr">
@@ -12808,11 +12808,11 @@
         </is>
       </c>
       <c r="C222" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D222" t="inlineStr">
         <is>
-          <t>03:10 PM – 04:10 PM</t>
+          <t>05:30 PM – 06:30 PM</t>
         </is>
       </c>
       <c r="E222" t="inlineStr">
@@ -12856,19 +12856,19 @@
     </row>
     <row r="223">
       <c r="A223" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B223" t="inlineStr">
         <is>
-          <t>Sunday, September 6, 2026</t>
+          <t>Thursday, September 3, 2026</t>
         </is>
       </c>
       <c r="C223" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D223" t="inlineStr">
         <is>
-          <t>05:30 PM – 06:30 PM</t>
+          <t>04:20 PM – 05:20 PM</t>
         </is>
       </c>
       <c r="E223" t="inlineStr">
@@ -12968,19 +12968,19 @@
     </row>
     <row r="225">
       <c r="A225" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="B225" t="inlineStr">
         <is>
-          <t>Wednesday, September 2, 2026</t>
+          <t>Sunday, September 6, 2026</t>
         </is>
       </c>
       <c r="C225" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D225" t="inlineStr">
         <is>
-          <t>03:10 PM – 04:10 PM</t>
+          <t>05:30 PM – 06:30 PM</t>
         </is>
       </c>
       <c r="E225" t="inlineStr">
@@ -13024,19 +13024,19 @@
     </row>
     <row r="226">
       <c r="A226" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B226" t="inlineStr">
         <is>
-          <t>Monday, September 7, 2026</t>
+          <t>Sunday, September 6, 2026</t>
         </is>
       </c>
       <c r="C226" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D226" t="inlineStr">
         <is>
-          <t>05:30 PM – 06:30 PM</t>
+          <t>04:20 PM – 05:20 PM</t>
         </is>
       </c>
       <c r="E226" t="inlineStr">
@@ -13080,19 +13080,19 @@
     </row>
     <row r="227">
       <c r="A227" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B227" t="inlineStr">
         <is>
-          <t>Sunday, September 6, 2026</t>
+          <t>Thursday, September 3, 2026</t>
         </is>
       </c>
       <c r="C227" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D227" t="inlineStr">
         <is>
-          <t>04:20 PM – 05:20 PM</t>
+          <t>05:30 PM – 06:30 PM</t>
         </is>
       </c>
       <c r="E227" t="inlineStr">
@@ -13136,19 +13136,19 @@
     </row>
     <row r="228">
       <c r="A228" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B228" t="inlineStr">
         <is>
-          <t>Thursday, September 3, 2026</t>
+          <t>Sunday, September 6, 2026</t>
         </is>
       </c>
       <c r="C228" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D228" t="inlineStr">
         <is>
-          <t>03:10 PM – 04:10 PM</t>
+          <t>05:30 PM – 06:30 PM</t>
         </is>
       </c>
       <c r="E228" t="inlineStr">
@@ -13200,11 +13200,11 @@
         </is>
       </c>
       <c r="C229" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D229" t="inlineStr">
         <is>
-          <t>03:10 PM – 04:10 PM</t>
+          <t>04:20 PM – 05:20 PM</t>
         </is>
       </c>
       <c r="E229" t="inlineStr">
@@ -13248,19 +13248,19 @@
     </row>
     <row r="230">
       <c r="A230" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B230" t="inlineStr">
         <is>
-          <t>Thursday, September 3, 2026</t>
+          <t>Sunday, September 6, 2026</t>
         </is>
       </c>
       <c r="C230" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D230" t="inlineStr">
         <is>
-          <t>05:30 PM – 06:30 PM</t>
+          <t>03:10 PM – 04:10 PM</t>
         </is>
       </c>
       <c r="E230" t="inlineStr">
@@ -13312,11 +13312,11 @@
         </is>
       </c>
       <c r="C231" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D231" t="inlineStr">
         <is>
-          <t>04:20 PM – 05:20 PM</t>
+          <t>03:10 PM – 04:10 PM</t>
         </is>
       </c>
       <c r="E231" t="inlineStr">
@@ -13528,19 +13528,19 @@
     </row>
     <row r="235">
       <c r="A235" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B235" t="inlineStr">
         <is>
-          <t>Sunday, September 6, 2026</t>
+          <t>Thursday, September 3, 2026</t>
         </is>
       </c>
       <c r="C235" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D235" t="inlineStr">
         <is>
-          <t>05:30 PM – 06:30 PM</t>
+          <t>03:10 PM – 04:10 PM</t>
         </is>
       </c>
       <c r="E235" t="inlineStr">
@@ -13592,11 +13592,11 @@
         </is>
       </c>
       <c r="C236" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D236" t="inlineStr">
         <is>
-          <t>04:20 PM – 05:20 PM</t>
+          <t>05:30 PM – 06:30 PM</t>
         </is>
       </c>
       <c r="E236" t="inlineStr">
@@ -13640,11 +13640,11 @@
     </row>
     <row r="237">
       <c r="A237" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B237" t="inlineStr">
         <is>
-          <t>Thursday, September 3, 2026</t>
+          <t>Wednesday, September 2, 2026</t>
         </is>
       </c>
       <c r="C237" t="n">
@@ -13696,19 +13696,19 @@
     </row>
     <row r="238">
       <c r="A238" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="B238" t="inlineStr">
         <is>
-          <t>Thursday, September 3, 2026</t>
+          <t>Monday, September 7, 2026</t>
         </is>
       </c>
       <c r="C238" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D238" t="inlineStr">
         <is>
-          <t>03:10 PM – 04:10 PM</t>
+          <t>05:30 PM – 06:30 PM</t>
         </is>
       </c>
       <c r="E238" t="inlineStr">
@@ -13752,11 +13752,11 @@
     </row>
     <row r="239">
       <c r="A239" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B239" t="inlineStr">
         <is>
-          <t>Thursday, September 3, 2026</t>
+          <t>Wednesday, September 2, 2026</t>
         </is>
       </c>
       <c r="C239" t="n">
@@ -13808,19 +13808,19 @@
     </row>
     <row r="240">
       <c r="A240" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="B240" t="inlineStr">
         <is>
-          <t>Wednesday, September 2, 2026</t>
+          <t>Sunday, September 6, 2026</t>
         </is>
       </c>
       <c r="C240" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D240" t="inlineStr">
         <is>
-          <t>05:30 PM – 06:30 PM</t>
+          <t>04:20 PM – 05:20 PM</t>
         </is>
       </c>
       <c r="E240" t="inlineStr">
@@ -13864,19 +13864,19 @@
     </row>
     <row r="241">
       <c r="A241" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="B241" t="inlineStr">
         <is>
-          <t>Wednesday, September 2, 2026</t>
+          <t>Monday, September 7, 2026</t>
         </is>
       </c>
       <c r="C241" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D241" t="inlineStr">
         <is>
-          <t>03:10 PM – 04:10 PM</t>
+          <t>04:20 PM – 05:20 PM</t>
         </is>
       </c>
       <c r="E241" t="inlineStr">
@@ -13920,19 +13920,19 @@
     </row>
     <row r="242">
       <c r="A242" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="B242" t="inlineStr">
         <is>
-          <t>Sunday, September 6, 2026</t>
+          <t>Wednesday, September 2, 2026</t>
         </is>
       </c>
       <c r="C242" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D242" t="inlineStr">
         <is>
-          <t>05:30 PM – 06:30 PM</t>
+          <t>03:10 PM – 04:10 PM</t>
         </is>
       </c>
       <c r="E242" t="inlineStr">
@@ -13976,19 +13976,19 @@
     </row>
     <row r="243">
       <c r="A243" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="B243" t="inlineStr">
         <is>
-          <t>Monday, September 7, 2026</t>
+          <t>Thursday, September 3, 2026</t>
         </is>
       </c>
       <c r="C243" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D243" t="inlineStr">
         <is>
-          <t>04:20 PM – 05:20 PM</t>
+          <t>05:30 PM – 06:30 PM</t>
         </is>
       </c>
       <c r="E243" t="inlineStr">
@@ -14032,19 +14032,19 @@
     </row>
     <row r="244">
       <c r="A244" t="n">
+        <v>4</v>
+      </c>
+      <c r="B244" t="inlineStr">
+        <is>
+          <t>Monday, September 7, 2026</t>
+        </is>
+      </c>
+      <c r="C244" t="n">
         <v>1</v>
       </c>
-      <c r="B244" t="inlineStr">
-        <is>
-          <t>Wednesday, September 2, 2026</t>
-        </is>
-      </c>
-      <c r="C244" t="n">
-        <v>2</v>
-      </c>
       <c r="D244" t="inlineStr">
         <is>
-          <t>04:20 PM – 05:20 PM</t>
+          <t>03:10 PM – 04:10 PM</t>
         </is>
       </c>
       <c r="E244" t="inlineStr">
@@ -14088,19 +14088,19 @@
     </row>
     <row r="245">
       <c r="A245" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="B245" t="inlineStr">
         <is>
-          <t>Monday, September 7, 2026</t>
+          <t>Thursday, September 3, 2026</t>
         </is>
       </c>
       <c r="C245" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D245" t="inlineStr">
         <is>
-          <t>05:30 PM – 06:30 PM</t>
+          <t>04:20 PM – 05:20 PM</t>
         </is>
       </c>
       <c r="E245" t="inlineStr">
@@ -14144,19 +14144,19 @@
     </row>
     <row r="246">
       <c r="A246" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B246" t="inlineStr">
         <is>
-          <t>Thursday, September 3, 2026</t>
+          <t>Wednesday, September 2, 2026</t>
         </is>
       </c>
       <c r="C246" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D246" t="inlineStr">
         <is>
-          <t>03:10 PM – 04:10 PM</t>
+          <t>01:50 PM – 02:50 PM</t>
         </is>
       </c>
       <c r="E246" t="inlineStr">
@@ -14200,11 +14200,11 @@
     </row>
     <row r="247">
       <c r="A247" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B247" t="inlineStr">
         <is>
-          <t>Monday, September 7, 2026</t>
+          <t>Sunday, September 6, 2026</t>
         </is>
       </c>
       <c r="C247" t="n">
@@ -14256,11 +14256,11 @@
     </row>
     <row r="248">
       <c r="A248" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B248" t="inlineStr">
         <is>
-          <t>Sunday, September 6, 2026</t>
+          <t>Thursday, September 3, 2026</t>
         </is>
       </c>
       <c r="C248" t="n">
@@ -14312,11 +14312,11 @@
     </row>
     <row r="249">
       <c r="A249" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="B249" t="inlineStr">
         <is>
-          <t>Wednesday, September 2, 2026</t>
+          <t>Monday, September 7, 2026</t>
         </is>
       </c>
       <c r="C249" t="n">
@@ -14376,11 +14376,11 @@
         </is>
       </c>
       <c r="C250" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D250" t="inlineStr">
         <is>
-          <t>01:50 PM – 02:50 PM</t>
+          <t>12:40 PM – 01:40 PM</t>
         </is>
       </c>
       <c r="E250" t="inlineStr">
@@ -14432,11 +14432,11 @@
         </is>
       </c>
       <c r="C251" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D251" t="inlineStr">
         <is>
-          <t>03:10 PM – 04:10 PM</t>
+          <t>12:40 PM – 01:40 PM</t>
         </is>
       </c>
       <c r="E251" t="inlineStr">
@@ -14536,19 +14536,19 @@
     </row>
     <row r="253">
       <c r="A253" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="B253" t="inlineStr">
         <is>
-          <t>Wednesday, September 2, 2026</t>
+          <t>Sunday, September 6, 2026</t>
         </is>
       </c>
       <c r="C253" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D253" t="inlineStr">
         <is>
-          <t>12:40 PM – 01:40 PM</t>
+          <t>03:10 PM – 04:10 PM</t>
         </is>
       </c>
       <c r="E253" t="inlineStr">
@@ -14592,11 +14592,11 @@
     </row>
     <row r="254">
       <c r="A254" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B254" t="inlineStr">
         <is>
-          <t>Sunday, September 6, 2026</t>
+          <t>Thursday, September 3, 2026</t>
         </is>
       </c>
       <c r="C254" t="n">
@@ -14648,11 +14648,11 @@
     </row>
     <row r="255">
       <c r="A255" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B255" t="inlineStr">
         <is>
-          <t>Thursday, September 3, 2026</t>
+          <t>Sunday, September 6, 2026</t>
         </is>
       </c>
       <c r="C255" t="n">
@@ -14704,19 +14704,19 @@
     </row>
     <row r="256">
       <c r="A256" t="n">
+        <v>4</v>
+      </c>
+      <c r="B256" t="inlineStr">
+        <is>
+          <t>Monday, September 7, 2026</t>
+        </is>
+      </c>
+      <c r="C256" t="n">
         <v>1</v>
       </c>
-      <c r="B256" t="inlineStr">
-        <is>
-          <t>Wednesday, September 2, 2026</t>
-        </is>
-      </c>
-      <c r="C256" t="n">
-        <v>3</v>
-      </c>
       <c r="D256" t="inlineStr">
         <is>
-          <t>05:30 PM – 06:30 PM</t>
+          <t>03:10 PM – 04:10 PM</t>
         </is>
       </c>
       <c r="E256" t="inlineStr">
@@ -14760,11 +14760,11 @@
     </row>
     <row r="257">
       <c r="A257" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B257" t="inlineStr">
         <is>
-          <t>Sunday, September 6, 2026</t>
+          <t>Thursday, September 3, 2026</t>
         </is>
       </c>
       <c r="C257" t="n">
@@ -14816,19 +14816,19 @@
     </row>
     <row r="258">
       <c r="A258" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="B258" t="inlineStr">
         <is>
-          <t>Thursday, September 3, 2026</t>
+          <t>Monday, September 7, 2026</t>
         </is>
       </c>
       <c r="C258" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D258" t="inlineStr">
         <is>
-          <t>05:30 PM – 06:30 PM</t>
+          <t>04:20 PM – 05:20 PM</t>
         </is>
       </c>
       <c r="E258" t="inlineStr">
@@ -14872,11 +14872,11 @@
     </row>
     <row r="259">
       <c r="A259" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B259" t="inlineStr">
         <is>
-          <t>Monday, September 7, 2026</t>
+          <t>Sunday, September 6, 2026</t>
         </is>
       </c>
       <c r="C259" t="n">
@@ -14984,19 +14984,19 @@
     </row>
     <row r="261">
       <c r="A261" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B261" t="inlineStr">
         <is>
-          <t>Sunday, September 6, 2026</t>
+          <t>Monday, September 7, 2026</t>
         </is>
       </c>
       <c r="C261" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D261" t="inlineStr">
         <is>
-          <t>03:10 PM – 04:10 PM</t>
+          <t>05:30 PM – 06:30 PM</t>
         </is>
       </c>
       <c r="E261" t="inlineStr">
@@ -15040,19 +15040,19 @@
     </row>
     <row r="262">
       <c r="A262" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="B262" t="inlineStr">
         <is>
-          <t>Sunday, September 6, 2026</t>
+          <t>Wednesday, September 2, 2026</t>
         </is>
       </c>
       <c r="C262" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D262" t="inlineStr">
         <is>
-          <t>04:20 PM – 05:20 PM</t>
+          <t>05:30 PM – 06:30 PM</t>
         </is>
       </c>
       <c r="E262" t="inlineStr">
@@ -15096,11 +15096,11 @@
     </row>
     <row r="263">
       <c r="A263" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B263" t="inlineStr">
         <is>
-          <t>Wednesday, September 2, 2026</t>
+          <t>Thursday, September 3, 2026</t>
         </is>
       </c>
       <c r="C263" t="n">
@@ -15152,11 +15152,11 @@
     </row>
     <row r="264">
       <c r="A264" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B264" t="inlineStr">
         <is>
-          <t>Monday, September 7, 2026</t>
+          <t>Sunday, September 6, 2026</t>
         </is>
       </c>
       <c r="C264" t="n">
@@ -15320,11 +15320,11 @@
     </row>
     <row r="267">
       <c r="A267" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B267" t="inlineStr">
         <is>
-          <t>Thursday, September 3, 2026</t>
+          <t>Wednesday, September 2, 2026</t>
         </is>
       </c>
       <c r="C267" t="n">
@@ -15376,19 +15376,19 @@
     </row>
     <row r="268">
       <c r="A268" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B268" t="inlineStr">
         <is>
-          <t>Wednesday, September 2, 2026</t>
+          <t>Thursday, September 3, 2026</t>
         </is>
       </c>
       <c r="C268" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D268" t="inlineStr">
         <is>
-          <t>03:10 PM – 04:10 PM</t>
+          <t>04:20 PM – 05:20 PM</t>
         </is>
       </c>
       <c r="E268" t="inlineStr">
@@ -15544,11 +15544,11 @@
     </row>
     <row r="271">
       <c r="A271" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B271" t="inlineStr">
         <is>
-          <t>Wednesday, September 2, 2026</t>
+          <t>Thursday, September 3, 2026</t>
         </is>
       </c>
       <c r="C271" t="n">
@@ -15600,11 +15600,11 @@
     </row>
     <row r="272">
       <c r="A272" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="B272" t="inlineStr">
         <is>
-          <t>Thursday, September 3, 2026</t>
+          <t>Monday, September 7, 2026</t>
         </is>
       </c>
       <c r="C272" t="n">
@@ -15656,11 +15656,11 @@
     </row>
     <row r="273">
       <c r="A273" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="B273" t="inlineStr">
         <is>
-          <t>Monday, September 7, 2026</t>
+          <t>Wednesday, September 2, 2026</t>
         </is>
       </c>
       <c r="C273" t="n">
@@ -15698,7 +15698,7 @@
       </c>
       <c r="J273" t="inlineStr">
         <is>
-          <t>ustadh_faidh</t>
+          <t>tchr_faidh</t>
         </is>
       </c>
       <c r="K273" t="inlineStr">
@@ -15712,19 +15712,19 @@
     </row>
     <row r="274">
       <c r="A274" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B274" t="inlineStr">
         <is>
-          <t>Wednesday, September 2, 2026</t>
+          <t>Thursday, September 3, 2026</t>
         </is>
       </c>
       <c r="C274" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D274" t="inlineStr">
         <is>
-          <t>04:20 PM – 05:20 PM</t>
+          <t>05:30 PM – 06:30 PM</t>
         </is>
       </c>
       <c r="E274" t="inlineStr">
@@ -15768,19 +15768,19 @@
     </row>
     <row r="275">
       <c r="A275" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B275" t="inlineStr">
         <is>
-          <t>Thursday, September 3, 2026</t>
+          <t>Wednesday, September 2, 2026</t>
         </is>
       </c>
       <c r="C275" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D275" t="inlineStr">
         <is>
-          <t>03:10 PM – 04:10 PM</t>
+          <t>04:20 PM – 05:20 PM</t>
         </is>
       </c>
       <c r="E275" t="inlineStr">
@@ -15824,11 +15824,11 @@
     </row>
     <row r="276">
       <c r="A276" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B276" t="inlineStr">
         <is>
-          <t>Sunday, September 6, 2026</t>
+          <t>Monday, September 7, 2026</t>
         </is>
       </c>
       <c r="C276" t="n">
@@ -15880,11 +15880,11 @@
     </row>
     <row r="277">
       <c r="A277" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B277" t="inlineStr">
         <is>
-          <t>Sunday, September 6, 2026</t>
+          <t>Thursday, September 3, 2026</t>
         </is>
       </c>
       <c r="C277" t="n">
@@ -15936,19 +15936,19 @@
     </row>
     <row r="278">
       <c r="A278" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B278" t="inlineStr">
         <is>
-          <t>Thursday, September 3, 2026</t>
+          <t>Sunday, September 6, 2026</t>
         </is>
       </c>
       <c r="C278" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D278" t="inlineStr">
         <is>
-          <t>04:20 PM – 05:20 PM</t>
+          <t>03:10 PM – 04:10 PM</t>
         </is>
       </c>
       <c r="E278" t="inlineStr">
@@ -15992,19 +15992,19 @@
     </row>
     <row r="279">
       <c r="A279" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="B279" t="inlineStr">
         <is>
-          <t>Wednesday, September 2, 2026</t>
+          <t>Monday, September 7, 2026</t>
         </is>
       </c>
       <c r="C279" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D279" t="inlineStr">
         <is>
-          <t>05:30 PM – 06:30 PM</t>
+          <t>04:20 PM – 05:20 PM</t>
         </is>
       </c>
       <c r="E279" t="inlineStr">
@@ -16048,19 +16048,19 @@
     </row>
     <row r="280">
       <c r="A280" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="B280" t="inlineStr">
         <is>
-          <t>Monday, September 7, 2026</t>
+          <t>Wednesday, September 2, 2026</t>
         </is>
       </c>
       <c r="C280" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D280" t="inlineStr">
         <is>
-          <t>04:20 PM – 05:20 PM</t>
+          <t>05:30 PM – 06:30 PM</t>
         </is>
       </c>
       <c r="E280" t="inlineStr">
@@ -16104,19 +16104,19 @@
     </row>
     <row r="281">
       <c r="A281" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B281" t="inlineStr">
         <is>
-          <t>Monday, September 7, 2026</t>
+          <t>Sunday, September 6, 2026</t>
         </is>
       </c>
       <c r="C281" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D281" t="inlineStr">
         <is>
-          <t>05:30 PM – 06:30 PM</t>
+          <t>04:20 PM – 05:20 PM</t>
         </is>
       </c>
       <c r="E281" t="inlineStr">
@@ -16168,11 +16168,11 @@
         </is>
       </c>
       <c r="C282" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D282" t="inlineStr">
         <is>
-          <t>04:20 PM – 05:20 PM</t>
+          <t>05:30 PM – 06:30 PM</t>
         </is>
       </c>
       <c r="E282" t="inlineStr">
@@ -16216,19 +16216,19 @@
     </row>
     <row r="283">
       <c r="A283" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B283" t="inlineStr">
         <is>
-          <t>Monday, September 7, 2026</t>
+          <t>Sunday, September 6, 2026</t>
         </is>
       </c>
       <c r="C283" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D283" t="inlineStr">
         <is>
-          <t>05:30 PM – 06:30 PM</t>
+          <t>03:10 PM – 04:10 PM</t>
         </is>
       </c>
       <c r="E283" t="inlineStr">
@@ -16272,19 +16272,19 @@
     </row>
     <row r="284">
       <c r="A284" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B284" t="inlineStr">
         <is>
-          <t>Wednesday, September 2, 2026</t>
+          <t>Thursday, September 3, 2026</t>
         </is>
       </c>
       <c r="C284" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D284" t="inlineStr">
         <is>
-          <t>04:20 PM – 05:20 PM</t>
+          <t>05:30 PM – 06:30 PM</t>
         </is>
       </c>
       <c r="E284" t="inlineStr">
@@ -16328,11 +16328,11 @@
     </row>
     <row r="285">
       <c r="A285" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="B285" t="inlineStr">
         <is>
-          <t>Sunday, September 6, 2026</t>
+          <t>Wednesday, September 2, 2026</t>
         </is>
       </c>
       <c r="C285" t="n">
@@ -16384,11 +16384,11 @@
     </row>
     <row r="286">
       <c r="A286" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="B286" t="inlineStr">
         <is>
-          <t>Wednesday, September 2, 2026</t>
+          <t>Sunday, September 6, 2026</t>
         </is>
       </c>
       <c r="C286" t="n">
@@ -16496,11 +16496,11 @@
     </row>
     <row r="288">
       <c r="A288" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B288" t="inlineStr">
         <is>
-          <t>Sunday, September 6, 2026</t>
+          <t>Monday, September 7, 2026</t>
         </is>
       </c>
       <c r="C288" t="n">
@@ -16552,11 +16552,11 @@
     </row>
     <row r="289">
       <c r="A289" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B289" t="inlineStr">
         <is>
-          <t>Thursday, September 3, 2026</t>
+          <t>Wednesday, September 2, 2026</t>
         </is>
       </c>
       <c r="C289" t="n">
@@ -16608,11 +16608,11 @@
     </row>
     <row r="290">
       <c r="A290" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="B290" t="inlineStr">
         <is>
-          <t>Monday, September 7, 2026</t>
+          <t>Wednesday, September 2, 2026</t>
         </is>
       </c>
       <c r="C290" t="n">
@@ -16664,11 +16664,11 @@
     </row>
     <row r="291">
       <c r="A291" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="B291" t="inlineStr">
         <is>
-          <t>Sunday, September 6, 2026</t>
+          <t>Wednesday, September 2, 2026</t>
         </is>
       </c>
       <c r="C291" t="n">
@@ -16720,19 +16720,19 @@
     </row>
     <row r="292">
       <c r="A292" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B292" t="inlineStr">
         <is>
-          <t>Monday, September 7, 2026</t>
+          <t>Sunday, September 6, 2026</t>
         </is>
       </c>
       <c r="C292" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D292" t="inlineStr">
         <is>
-          <t>04:20 PM – 05:20 PM</t>
+          <t>05:30 PM – 06:30 PM</t>
         </is>
       </c>
       <c r="E292" t="inlineStr">
@@ -16776,19 +16776,19 @@
     </row>
     <row r="293">
       <c r="A293" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="B293" t="inlineStr">
         <is>
-          <t>Wednesday, September 2, 2026</t>
+          <t>Sunday, September 6, 2026</t>
         </is>
       </c>
       <c r="C293" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D293" t="inlineStr">
         <is>
-          <t>05:30 PM – 06:30 PM</t>
+          <t>04:20 PM – 05:20 PM</t>
         </is>
       </c>
       <c r="E293" t="inlineStr">
@@ -16832,19 +16832,19 @@
     </row>
     <row r="294">
       <c r="A294" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="B294" t="inlineStr">
         <is>
-          <t>Thursday, September 3, 2026</t>
+          <t>Monday, September 7, 2026</t>
         </is>
       </c>
       <c r="C294" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D294" t="inlineStr">
         <is>
-          <t>04:20 PM – 05:20 PM</t>
+          <t>03:10 PM – 04:10 PM</t>
         </is>
       </c>
       <c r="E294" t="inlineStr">
@@ -16888,19 +16888,19 @@
     </row>
     <row r="295">
       <c r="A295" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="B295" t="inlineStr">
         <is>
-          <t>Monday, September 7, 2026</t>
+          <t>Thursday, September 3, 2026</t>
         </is>
       </c>
       <c r="C295" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D295" t="inlineStr">
         <is>
-          <t>03:10 PM – 04:10 PM</t>
+          <t>04:20 PM – 05:20 PM</t>
         </is>
       </c>
       <c r="E295" t="inlineStr">
@@ -17000,19 +17000,19 @@
     </row>
     <row r="297">
       <c r="A297" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B297" t="inlineStr">
         <is>
-          <t>Sunday, September 6, 2026</t>
+          <t>Monday, September 7, 2026</t>
         </is>
       </c>
       <c r="C297" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D297" t="inlineStr">
         <is>
-          <t>05:30 PM – 06:30 PM</t>
+          <t>04:20 PM – 05:20 PM</t>
         </is>
       </c>
       <c r="E297" t="inlineStr">
@@ -17064,11 +17064,11 @@
         </is>
       </c>
       <c r="C298" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D298" t="inlineStr">
         <is>
-          <t>03:10 PM – 04:10 PM</t>
+          <t>04:20 PM – 05:20 PM</t>
         </is>
       </c>
       <c r="E298" t="inlineStr">
@@ -17120,11 +17120,11 @@
         </is>
       </c>
       <c r="C299" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D299" t="inlineStr">
         <is>
-          <t>03:10 PM – 04:10 PM</t>
+          <t>05:30 PM – 06:30 PM</t>
         </is>
       </c>
       <c r="E299" t="inlineStr">
@@ -17168,19 +17168,19 @@
     </row>
     <row r="300">
       <c r="A300" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="B300" t="inlineStr">
         <is>
-          <t>Sunday, September 6, 2026</t>
+          <t>Wednesday, September 2, 2026</t>
         </is>
       </c>
       <c r="C300" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D300" t="inlineStr">
         <is>
-          <t>03:10 PM – 04:10 PM</t>
+          <t>05:30 PM – 06:30 PM</t>
         </is>
       </c>
       <c r="E300" t="inlineStr">
@@ -17224,19 +17224,19 @@
     </row>
     <row r="301">
       <c r="A301" t="n">
+        <v>2</v>
+      </c>
+      <c r="B301" t="inlineStr">
+        <is>
+          <t>Thursday, September 3, 2026</t>
+        </is>
+      </c>
+      <c r="C301" t="n">
         <v>1</v>
       </c>
-      <c r="B301" t="inlineStr">
-        <is>
-          <t>Wednesday, September 2, 2026</t>
-        </is>
-      </c>
-      <c r="C301" t="n">
-        <v>2</v>
-      </c>
       <c r="D301" t="inlineStr">
         <is>
-          <t>04:20 PM – 05:20 PM</t>
+          <t>03:10 PM – 04:10 PM</t>
         </is>
       </c>
       <c r="E301" t="inlineStr">
@@ -17266,7 +17266,7 @@
       </c>
       <c r="J301" t="inlineStr">
         <is>
-          <t>ustadh_faidh</t>
+          <t>tchr_faidh</t>
         </is>
       </c>
       <c r="K301" t="inlineStr">
@@ -17280,19 +17280,19 @@
     </row>
     <row r="302">
       <c r="A302" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="B302" t="inlineStr">
         <is>
-          <t>Sunday, September 6, 2026</t>
+          <t>Wednesday, September 2, 2026</t>
         </is>
       </c>
       <c r="C302" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D302" t="inlineStr">
         <is>
-          <t>05:30 PM – 06:30 PM</t>
+          <t>03:10 PM – 04:10 PM</t>
         </is>
       </c>
       <c r="E302" t="inlineStr">
@@ -17322,7 +17322,7 @@
       </c>
       <c r="J302" t="inlineStr">
         <is>
-          <t>ustadha_saliha</t>
+          <t>tchr_saliha</t>
         </is>
       </c>
       <c r="K302" t="inlineStr">
@@ -17336,11 +17336,11 @@
     </row>
     <row r="303">
       <c r="A303" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B303" t="inlineStr">
         <is>
-          <t>Thursday, September 3, 2026</t>
+          <t>Sunday, September 6, 2026</t>
         </is>
       </c>
       <c r="C303" t="n">
@@ -17400,11 +17400,11 @@
         </is>
       </c>
       <c r="C304" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D304" t="inlineStr">
         <is>
-          <t>03:10 PM – 04:10 PM</t>
+          <t>04:20 PM – 05:20 PM</t>
         </is>
       </c>
       <c r="E304" t="inlineStr">
@@ -17448,11 +17448,11 @@
     </row>
     <row r="305">
       <c r="A305" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B305" t="inlineStr">
         <is>
-          <t>Monday, September 7, 2026</t>
+          <t>Sunday, September 6, 2026</t>
         </is>
       </c>
       <c r="C305" t="n">
@@ -17560,19 +17560,19 @@
     </row>
     <row r="307">
       <c r="A307" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="B307" t="inlineStr">
         <is>
-          <t>Wednesday, September 2, 2026</t>
+          <t>Sunday, September 6, 2026</t>
         </is>
       </c>
       <c r="C307" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D307" t="inlineStr">
         <is>
-          <t>05:30 PM – 06:30 PM</t>
+          <t>04:20 PM – 05:20 PM</t>
         </is>
       </c>
       <c r="E307" t="inlineStr">
@@ -17672,19 +17672,19 @@
     </row>
     <row r="309">
       <c r="A309" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="B309" t="inlineStr">
         <is>
-          <t>Monday, September 7, 2026</t>
+          <t>Thursday, September 3, 2026</t>
         </is>
       </c>
       <c r="C309" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D309" t="inlineStr">
         <is>
-          <t>04:20 PM – 05:20 PM</t>
+          <t>05:30 PM – 06:30 PM</t>
         </is>
       </c>
       <c r="E309" t="inlineStr">
@@ -17784,19 +17784,19 @@
     </row>
     <row r="311">
       <c r="A311" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="B311" t="inlineStr">
         <is>
-          <t>Wednesday, September 2, 2026</t>
+          <t>Monday, September 7, 2026</t>
         </is>
       </c>
       <c r="C311" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D311" t="inlineStr">
         <is>
-          <t>05:30 PM – 06:30 PM</t>
+          <t>04:20 PM – 05:20 PM</t>
         </is>
       </c>
       <c r="E311" t="inlineStr">
@@ -17896,11 +17896,11 @@
     </row>
     <row r="313">
       <c r="A313" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="B313" t="inlineStr">
         <is>
-          <t>Monday, September 7, 2026</t>
+          <t>Wednesday, September 2, 2026</t>
         </is>
       </c>
       <c r="C313" t="n">
@@ -17952,11 +17952,11 @@
     </row>
     <row r="314">
       <c r="A314" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B314" t="inlineStr">
         <is>
-          <t>Wednesday, September 2, 2026</t>
+          <t>Thursday, September 3, 2026</t>
         </is>
       </c>
       <c r="C314" t="n">
@@ -18008,19 +18008,19 @@
     </row>
     <row r="315">
       <c r="A315" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B315" t="inlineStr">
         <is>
-          <t>Thursday, September 3, 2026</t>
+          <t>Sunday, September 6, 2026</t>
         </is>
       </c>
       <c r="C315" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D315" t="inlineStr">
         <is>
-          <t>03:10 PM – 04:10 PM</t>
+          <t>04:20 PM – 05:20 PM</t>
         </is>
       </c>
       <c r="E315" t="inlineStr">
@@ -18064,19 +18064,19 @@
     </row>
     <row r="316">
       <c r="A316" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B316" t="inlineStr">
         <is>
-          <t>Sunday, September 6, 2026</t>
+          <t>Thursday, September 3, 2026</t>
         </is>
       </c>
       <c r="C316" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D316" t="inlineStr">
         <is>
-          <t>04:20 PM – 05:20 PM</t>
+          <t>03:10 PM – 04:10 PM</t>
         </is>
       </c>
       <c r="E316" t="inlineStr">
@@ -18120,11 +18120,11 @@
     </row>
     <row r="317">
       <c r="A317" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="B317" t="inlineStr">
         <is>
-          <t>Wednesday, September 2, 2026</t>
+          <t>Sunday, September 6, 2026</t>
         </is>
       </c>
       <c r="C317" t="n">
@@ -18176,19 +18176,19 @@
     </row>
     <row r="318">
       <c r="A318" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B318" t="inlineStr">
         <is>
-          <t>Thursday, September 3, 2026</t>
+          <t>Wednesday, September 2, 2026</t>
         </is>
       </c>
       <c r="C318" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D318" t="inlineStr">
         <is>
-          <t>05:30 PM – 06:30 PM</t>
+          <t>04:20 PM – 05:20 PM</t>
         </is>
       </c>
       <c r="E318" t="inlineStr">
@@ -18232,19 +18232,19 @@
     </row>
     <row r="319">
       <c r="A319" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="B319" t="inlineStr">
         <is>
-          <t>Monday, September 7, 2026</t>
+          <t>Thursday, September 3, 2026</t>
         </is>
       </c>
       <c r="C319" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D319" t="inlineStr">
         <is>
-          <t>05:30 PM – 06:30 PM</t>
+          <t>03:10 PM – 04:10 PM</t>
         </is>
       </c>
       <c r="E319" t="inlineStr">
@@ -18288,11 +18288,11 @@
     </row>
     <row r="320">
       <c r="A320" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="B320" t="inlineStr">
         <is>
-          <t>Monday, September 7, 2026</t>
+          <t>Wednesday, September 2, 2026</t>
         </is>
       </c>
       <c r="C320" t="n">
@@ -18344,11 +18344,11 @@
     </row>
     <row r="321">
       <c r="A321" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B321" t="inlineStr">
         <is>
-          <t>Sunday, September 6, 2026</t>
+          <t>Monday, September 7, 2026</t>
         </is>
       </c>
       <c r="C321" t="n">
@@ -18408,11 +18408,11 @@
         </is>
       </c>
       <c r="C322" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D322" t="inlineStr">
         <is>
-          <t>05:30 PM – 06:30 PM</t>
+          <t>04:20 PM – 05:20 PM</t>
         </is>
       </c>
       <c r="E322" t="inlineStr">
@@ -18456,19 +18456,19 @@
     </row>
     <row r="323">
       <c r="A323" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B323" t="inlineStr">
         <is>
-          <t>Monday, September 7, 2026</t>
+          <t>Sunday, September 6, 2026</t>
         </is>
       </c>
       <c r="C323" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D323" t="inlineStr">
         <is>
-          <t>03:10 PM – 04:10 PM</t>
+          <t>05:30 PM – 06:30 PM</t>
         </is>
       </c>
       <c r="E323" t="inlineStr">
@@ -18512,19 +18512,19 @@
     </row>
     <row r="324">
       <c r="A324" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="B324" t="inlineStr">
         <is>
-          <t>Wednesday, September 2, 2026</t>
+          <t>Monday, September 7, 2026</t>
         </is>
       </c>
       <c r="C324" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D324" t="inlineStr">
         <is>
-          <t>04:20 PM – 05:20 PM</t>
+          <t>05:30 PM – 06:30 PM</t>
         </is>
       </c>
       <c r="E324" t="inlineStr">
@@ -18568,11 +18568,11 @@
     </row>
     <row r="325">
       <c r="A325" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B325" t="inlineStr">
         <is>
-          <t>Sunday, September 6, 2026</t>
+          <t>Monday, September 7, 2026</t>
         </is>
       </c>
       <c r="C325" t="n">
@@ -18632,11 +18632,11 @@
         </is>
       </c>
       <c r="C326" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D326" t="inlineStr">
         <is>
-          <t>05:30 PM – 06:30 PM</t>
+          <t>03:10 PM – 04:10 PM</t>
         </is>
       </c>
       <c r="E326" t="inlineStr">
@@ -18680,11 +18680,11 @@
     </row>
     <row r="327">
       <c r="A327" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B327" t="inlineStr">
         <is>
-          <t>Thursday, September 3, 2026</t>
+          <t>Sunday, September 6, 2026</t>
         </is>
       </c>
       <c r="C327" t="n">
@@ -18744,11 +18744,11 @@
         </is>
       </c>
       <c r="C328" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D328" t="inlineStr">
         <is>
-          <t>03:10 PM – 04:10 PM</t>
+          <t>05:30 PM – 06:30 PM</t>
         </is>
       </c>
       <c r="E328" t="inlineStr">
@@ -18792,19 +18792,19 @@
     </row>
     <row r="329">
       <c r="A329" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="B329" t="inlineStr">
         <is>
-          <t>Monday, September 7, 2026</t>
+          <t>Wednesday, September 2, 2026</t>
         </is>
       </c>
       <c r="C329" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D329" t="inlineStr">
         <is>
-          <t>04:20 PM – 05:20 PM</t>
+          <t>05:30 PM – 06:30 PM</t>
         </is>
       </c>
       <c r="E329" t="inlineStr">
@@ -18960,19 +18960,19 @@
     </row>
     <row r="332">
       <c r="A332" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B332" t="inlineStr">
         <is>
-          <t>Sunday, September 6, 2026</t>
+          <t>Monday, September 7, 2026</t>
         </is>
       </c>
       <c r="C332" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D332" t="inlineStr">
         <is>
-          <t>03:10 PM – 04:10 PM</t>
+          <t>04:20 PM – 05:20 PM</t>
         </is>
       </c>
       <c r="E332" t="inlineStr">
@@ -19002,7 +19002,7 @@
       </c>
       <c r="J332" t="inlineStr">
         <is>
-          <t>ustadh_faidh</t>
+          <t>tchr_faidh</t>
         </is>
       </c>
       <c r="K332" t="inlineStr">
@@ -19016,11 +19016,11 @@
     </row>
     <row r="333">
       <c r="A333" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B333" t="inlineStr">
         <is>
-          <t>Thursday, September 3, 2026</t>
+          <t>Wednesday, September 2, 2026</t>
         </is>
       </c>
       <c r="C333" t="n">
@@ -19072,11 +19072,11 @@
     </row>
     <row r="334">
       <c r="A334" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B334" t="inlineStr">
         <is>
-          <t>Wednesday, September 2, 2026</t>
+          <t>Thursday, September 3, 2026</t>
         </is>
       </c>
       <c r="C334" t="n">
@@ -19114,12 +19114,12 @@
       </c>
       <c r="J334" t="inlineStr">
         <is>
-          <t>tchr_saimona</t>
+          <t>tchr_saimonah</t>
         </is>
       </c>
       <c r="K334" t="inlineStr">
         <is>
-          <t>Teacher Saimona</t>
+          <t>Teacher Saimonah</t>
         </is>
       </c>
       <c r="L334" t="n">
@@ -19136,11 +19136,11 @@
         </is>
       </c>
       <c r="C335" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D335" t="inlineStr">
         <is>
-          <t>05:30 PM – 06:30 PM</t>
+          <t>03:10 PM – 04:10 PM</t>
         </is>
       </c>
       <c r="E335" t="inlineStr">
@@ -19184,11 +19184,11 @@
     </row>
     <row r="336">
       <c r="A336" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B336" t="inlineStr">
         <is>
-          <t>Thursday, September 3, 2026</t>
+          <t>Wednesday, September 2, 2026</t>
         </is>
       </c>
       <c r="C336" t="n">
@@ -19240,19 +19240,19 @@
     </row>
     <row r="337">
       <c r="A337" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="B337" t="inlineStr">
         <is>
-          <t>Wednesday, September 2, 2026</t>
+          <t>Sunday, September 6, 2026</t>
         </is>
       </c>
       <c r="C337" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D337" t="inlineStr">
         <is>
-          <t>03:10 PM – 04:10 PM</t>
+          <t>04:20 PM – 05:20 PM</t>
         </is>
       </c>
       <c r="E337" t="inlineStr">
@@ -19296,11 +19296,11 @@
     </row>
     <row r="338">
       <c r="A338" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B338" t="inlineStr">
         <is>
-          <t>Wednesday, September 2, 2026</t>
+          <t>Thursday, September 3, 2026</t>
         </is>
       </c>
       <c r="C338" t="n">
@@ -19352,19 +19352,19 @@
     </row>
     <row r="339">
       <c r="A339" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B339" t="inlineStr">
         <is>
-          <t>Monday, September 7, 2026</t>
+          <t>Sunday, September 6, 2026</t>
         </is>
       </c>
       <c r="C339" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D339" t="inlineStr">
         <is>
-          <t>03:10 PM – 04:10 PM</t>
+          <t>04:20 PM – 05:20 PM</t>
         </is>
       </c>
       <c r="E339" t="inlineStr">
@@ -19416,11 +19416,11 @@
         </is>
       </c>
       <c r="C340" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D340" t="inlineStr">
         <is>
-          <t>05:30 PM – 06:30 PM</t>
+          <t>03:10 PM – 04:10 PM</t>
         </is>
       </c>
       <c r="E340" t="inlineStr">
@@ -19464,11 +19464,11 @@
     </row>
     <row r="341">
       <c r="A341" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B341" t="inlineStr">
         <is>
-          <t>Wednesday, September 2, 2026</t>
+          <t>Thursday, September 3, 2026</t>
         </is>
       </c>
       <c r="C341" t="n">
@@ -19520,11 +19520,11 @@
     </row>
     <row r="342">
       <c r="A342" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="B342" t="inlineStr">
         <is>
-          <t>Thursday, September 3, 2026</t>
+          <t>Monday, September 7, 2026</t>
         </is>
       </c>
       <c r="C342" t="n">
@@ -19576,11 +19576,11 @@
     </row>
     <row r="343">
       <c r="A343" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="B343" t="inlineStr">
         <is>
-          <t>Wednesday, September 2, 2026</t>
+          <t>Monday, September 7, 2026</t>
         </is>
       </c>
       <c r="C343" t="n">
@@ -19688,11 +19688,11 @@
     </row>
     <row r="345">
       <c r="A345" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="B345" t="inlineStr">
         <is>
-          <t>Monday, September 7, 2026</t>
+          <t>Wednesday, September 2, 2026</t>
         </is>
       </c>
       <c r="C345" t="n">
@@ -19744,19 +19744,19 @@
     </row>
     <row r="346">
       <c r="A346" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B346" t="inlineStr">
         <is>
-          <t>Sunday, September 6, 2026</t>
+          <t>Monday, September 7, 2026</t>
         </is>
       </c>
       <c r="C346" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D346" t="inlineStr">
         <is>
-          <t>04:20 PM – 05:20 PM</t>
+          <t>03:10 PM – 04:10 PM</t>
         </is>
       </c>
       <c r="E346" t="inlineStr">
@@ -19800,11 +19800,11 @@
     </row>
     <row r="347">
       <c r="A347" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="B347" t="inlineStr">
         <is>
-          <t>Monday, September 7, 2026</t>
+          <t>Wednesday, September 2, 2026</t>
         </is>
       </c>
       <c r="C347" t="n">
@@ -19856,11 +19856,11 @@
     </row>
     <row r="348">
       <c r="A348" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="B348" t="inlineStr">
         <is>
-          <t>Sunday, September 6, 2026</t>
+          <t>Wednesday, September 2, 2026</t>
         </is>
       </c>
       <c r="C348" t="n">
@@ -19912,19 +19912,19 @@
     </row>
     <row r="349">
       <c r="A349" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="B349" t="inlineStr">
         <is>
-          <t>Monday, September 7, 2026</t>
+          <t>Wednesday, September 2, 2026</t>
         </is>
       </c>
       <c r="C349" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D349" t="inlineStr">
         <is>
-          <t>03:10 PM – 04:10 PM</t>
+          <t>05:30 PM – 06:30 PM</t>
         </is>
       </c>
       <c r="E349" t="inlineStr">
@@ -19968,19 +19968,19 @@
     </row>
     <row r="350">
       <c r="A350" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B350" t="inlineStr">
         <is>
-          <t>Sunday, September 6, 2026</t>
+          <t>Thursday, September 3, 2026</t>
         </is>
       </c>
       <c r="C350" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D350" t="inlineStr">
         <is>
-          <t>04:20 PM – 05:20 PM</t>
+          <t>03:10 PM – 04:10 PM</t>
         </is>
       </c>
       <c r="E350" t="inlineStr">
@@ -20024,19 +20024,19 @@
     </row>
     <row r="351">
       <c r="A351" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="B351" t="inlineStr">
         <is>
-          <t>Wednesday, September 2, 2026</t>
+          <t>Sunday, September 6, 2026</t>
         </is>
       </c>
       <c r="C351" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D351" t="inlineStr">
         <is>
-          <t>03:10 PM – 04:10 PM</t>
+          <t>04:20 PM – 05:20 PM</t>
         </is>
       </c>
       <c r="E351" t="inlineStr">
@@ -20088,11 +20088,11 @@
         </is>
       </c>
       <c r="C352" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D352" t="inlineStr">
         <is>
-          <t>04:20 PM – 05:20 PM</t>
+          <t>05:30 PM – 06:30 PM</t>
         </is>
       </c>
       <c r="E352" t="inlineStr">
@@ -20136,11 +20136,11 @@
     </row>
     <row r="353">
       <c r="A353" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="B353" t="inlineStr">
         <is>
-          <t>Thursday, September 3, 2026</t>
+          <t>Monday, September 7, 2026</t>
         </is>
       </c>
       <c r="C353" t="n">
@@ -20192,19 +20192,19 @@
     </row>
     <row r="354">
       <c r="A354" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="B354" t="inlineStr">
         <is>
-          <t>Wednesday, September 2, 2026</t>
+          <t>Sunday, September 6, 2026</t>
         </is>
       </c>
       <c r="C354" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D354" t="inlineStr">
         <is>
-          <t>04:20 PM – 05:20 PM</t>
+          <t>05:30 PM – 06:30 PM</t>
         </is>
       </c>
       <c r="E354" t="inlineStr">
@@ -20248,11 +20248,11 @@
     </row>
     <row r="355">
       <c r="A355" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="B355" t="inlineStr">
         <is>
-          <t>Thursday, September 3, 2026</t>
+          <t>Monday, September 7, 2026</t>
         </is>
       </c>
       <c r="C355" t="n">
@@ -20304,11 +20304,11 @@
     </row>
     <row r="356">
       <c r="A356" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="B356" t="inlineStr">
         <is>
-          <t>Monday, September 7, 2026</t>
+          <t>Wednesday, September 2, 2026</t>
         </is>
       </c>
       <c r="C356" t="n">
@@ -20360,19 +20360,19 @@
     </row>
     <row r="357">
       <c r="A357" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="B357" t="inlineStr">
         <is>
-          <t>Monday, September 7, 2026</t>
+          <t>Thursday, September 3, 2026</t>
         </is>
       </c>
       <c r="C357" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D357" t="inlineStr">
         <is>
-          <t>05:30 PM – 06:30 PM</t>
+          <t>04:20 PM – 05:20 PM</t>
         </is>
       </c>
       <c r="E357" t="inlineStr">
@@ -20416,19 +20416,19 @@
     </row>
     <row r="358">
       <c r="A358" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B358" t="inlineStr">
         <is>
-          <t>Sunday, September 6, 2026</t>
+          <t>Monday, September 7, 2026</t>
         </is>
       </c>
       <c r="C358" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D358" t="inlineStr">
         <is>
-          <t>05:30 PM – 06:30 PM</t>
+          <t>04:20 PM – 05:20 PM</t>
         </is>
       </c>
       <c r="E358" t="inlineStr">
@@ -20472,11 +20472,11 @@
     </row>
     <row r="359">
       <c r="A359" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B359" t="inlineStr">
         <is>
-          <t>Monday, September 7, 2026</t>
+          <t>Sunday, September 6, 2026</t>
         </is>
       </c>
       <c r="C359" t="n">
@@ -20528,19 +20528,19 @@
     </row>
     <row r="360">
       <c r="A360" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B360" t="inlineStr">
         <is>
-          <t>Thursday, September 3, 2026</t>
+          <t>Sunday, September 6, 2026</t>
         </is>
       </c>
       <c r="C360" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D360" t="inlineStr">
         <is>
-          <t>04:20 PM – 05:20 PM</t>
+          <t>05:30 PM – 06:30 PM</t>
         </is>
       </c>
       <c r="E360" t="inlineStr">
@@ -20584,11 +20584,11 @@
     </row>
     <row r="361">
       <c r="A361" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B361" t="inlineStr">
         <is>
-          <t>Monday, September 7, 2026</t>
+          <t>Sunday, September 6, 2026</t>
         </is>
       </c>
       <c r="C361" t="n">
@@ -20640,11 +20640,11 @@
     </row>
     <row r="362">
       <c r="A362" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B362" t="inlineStr">
         <is>
-          <t>Sunday, September 6, 2026</t>
+          <t>Monday, September 7, 2026</t>
         </is>
       </c>
       <c r="C362" t="n">
@@ -20696,19 +20696,19 @@
     </row>
     <row r="363">
       <c r="A363" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="B363" t="inlineStr">
         <is>
-          <t>Thursday, September 3, 2026</t>
+          <t>Monday, September 7, 2026</t>
         </is>
       </c>
       <c r="C363" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D363" t="inlineStr">
         <is>
-          <t>03:10 PM – 04:10 PM</t>
+          <t>04:20 PM – 05:20 PM</t>
         </is>
       </c>
       <c r="E363" t="inlineStr">
@@ -20752,11 +20752,11 @@
     </row>
     <row r="364">
       <c r="A364" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B364" t="inlineStr">
         <is>
-          <t>Sunday, September 6, 2026</t>
+          <t>Thursday, September 3, 2026</t>
         </is>
       </c>
       <c r="C364" t="n">
@@ -20808,11 +20808,11 @@
     </row>
     <row r="365">
       <c r="A365" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B365" t="inlineStr">
         <is>
-          <t>Sunday, September 6, 2026</t>
+          <t>Thursday, September 3, 2026</t>
         </is>
       </c>
       <c r="C365" t="n">
@@ -20864,11 +20864,11 @@
     </row>
     <row r="366">
       <c r="A366" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B366" t="inlineStr">
         <is>
-          <t>Thursday, September 3, 2026</t>
+          <t>Wednesday, September 2, 2026</t>
         </is>
       </c>
       <c r="C366" t="n">
@@ -20928,11 +20928,11 @@
         </is>
       </c>
       <c r="C367" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D367" t="inlineStr">
         <is>
-          <t>05:30 PM – 06:30 PM</t>
+          <t>04:20 PM – 05:20 PM</t>
         </is>
       </c>
       <c r="E367" t="inlineStr">
@@ -21032,19 +21032,19 @@
     </row>
     <row r="369">
       <c r="A369" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="B369" t="inlineStr">
         <is>
-          <t>Sunday, September 6, 2026</t>
+          <t>Wednesday, September 2, 2026</t>
         </is>
       </c>
       <c r="C369" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D369" t="inlineStr">
         <is>
-          <t>09:00 AM – 10:00 AM</t>
+          <t>08:00 AM – 09:00 AM</t>
         </is>
       </c>
       <c r="E369" t="inlineStr">
@@ -21088,11 +21088,11 @@
     </row>
     <row r="370">
       <c r="A370" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="B370" t="inlineStr">
         <is>
-          <t>Thursday, September 3, 2026</t>
+          <t>Monday, September 7, 2026</t>
         </is>
       </c>
       <c r="C370" t="n">
@@ -21144,11 +21144,11 @@
     </row>
     <row r="371">
       <c r="A371" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B371" t="inlineStr">
         <is>
-          <t>Monday, September 7, 2026</t>
+          <t>Sunday, September 6, 2026</t>
         </is>
       </c>
       <c r="C371" t="n">
@@ -21200,19 +21200,19 @@
     </row>
     <row r="372">
       <c r="A372" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="B372" t="inlineStr">
         <is>
-          <t>Wednesday, September 2, 2026</t>
+          <t>Sunday, September 6, 2026</t>
         </is>
       </c>
       <c r="C372" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D372" t="inlineStr">
         <is>
-          <t>10:25 AM – 11:25 AM</t>
+          <t>09:00 AM – 10:00 AM</t>
         </is>
       </c>
       <c r="E372" t="inlineStr">
@@ -21256,19 +21256,19 @@
     </row>
     <row r="373">
       <c r="A373" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="B373" t="inlineStr">
         <is>
-          <t>Sunday, September 6, 2026</t>
+          <t>Wednesday, September 2, 2026</t>
         </is>
       </c>
       <c r="C373" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D373" t="inlineStr">
         <is>
-          <t>10:25 AM – 11:25 AM</t>
+          <t>09:00 AM – 10:00 AM</t>
         </is>
       </c>
       <c r="E373" t="inlineStr">
@@ -21320,11 +21320,11 @@
         </is>
       </c>
       <c r="C374" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D374" t="inlineStr">
         <is>
-          <t>10:25 AM – 11:25 AM</t>
+          <t>09:00 AM – 10:00 AM</t>
         </is>
       </c>
       <c r="E374" t="inlineStr">
@@ -21368,11 +21368,11 @@
     </row>
     <row r="375">
       <c r="A375" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B375" t="inlineStr">
         <is>
-          <t>Sunday, September 6, 2026</t>
+          <t>Monday, September 7, 2026</t>
         </is>
       </c>
       <c r="C375" t="n">
@@ -21424,19 +21424,19 @@
     </row>
     <row r="376">
       <c r="A376" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B376" t="inlineStr">
         <is>
-          <t>Thursday, September 3, 2026</t>
+          <t>Wednesday, September 2, 2026</t>
         </is>
       </c>
       <c r="C376" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D376" t="inlineStr">
         <is>
-          <t>09:00 AM – 10:00 AM</t>
+          <t>10:25 AM – 11:25 AM</t>
         </is>
       </c>
       <c r="E376" t="inlineStr">
@@ -21480,11 +21480,11 @@
     </row>
     <row r="377">
       <c r="A377" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B377" t="inlineStr">
         <is>
-          <t>Wednesday, September 2, 2026</t>
+          <t>Thursday, September 3, 2026</t>
         </is>
       </c>
       <c r="C377" t="n">
@@ -21544,11 +21544,11 @@
         </is>
       </c>
       <c r="C378" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D378" t="inlineStr">
         <is>
-          <t>08:00 AM – 09:00 AM</t>
+          <t>10:25 AM – 11:25 AM</t>
         </is>
       </c>
       <c r="E378" t="inlineStr">
@@ -21600,11 +21600,11 @@
         </is>
       </c>
       <c r="C379" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D379" t="inlineStr">
         <is>
-          <t>08:00 AM – 09:00 AM</t>
+          <t>09:00 AM – 10:00 AM</t>
         </is>
       </c>
       <c r="E379" t="inlineStr">
@@ -21648,15 +21648,15 @@
     </row>
     <row r="380">
       <c r="A380" t="n">
+        <v>4</v>
+      </c>
+      <c r="B380" t="inlineStr">
+        <is>
+          <t>Monday, September 7, 2026</t>
+        </is>
+      </c>
+      <c r="C380" t="n">
         <v>1</v>
-      </c>
-      <c r="B380" t="inlineStr">
-        <is>
-          <t>Wednesday, September 2, 2026</t>
-        </is>
-      </c>
-      <c r="C380" t="n">
-        <v>2</v>
       </c>
       <c r="D380" t="inlineStr">
         <is>
@@ -21704,11 +21704,11 @@
     </row>
     <row r="381">
       <c r="A381" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="B381" t="inlineStr">
         <is>
-          <t>Monday, September 7, 2026</t>
+          <t>Wednesday, September 2, 2026</t>
         </is>
       </c>
       <c r="C381" t="n">
@@ -21760,19 +21760,19 @@
     </row>
     <row r="382">
       <c r="A382" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B382" t="inlineStr">
         <is>
-          <t>Sunday, September 6, 2026</t>
+          <t>Thursday, September 3, 2026</t>
         </is>
       </c>
       <c r="C382" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D382" t="inlineStr">
         <is>
-          <t>10:25 AM – 11:25 AM</t>
+          <t>08:00 AM – 09:00 AM</t>
         </is>
       </c>
       <c r="E382" t="inlineStr">
@@ -21824,11 +21824,11 @@
         </is>
       </c>
       <c r="C383" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D383" t="inlineStr">
         <is>
-          <t>08:00 AM – 09:00 AM</t>
+          <t>10:25 AM – 11:25 AM</t>
         </is>
       </c>
       <c r="E383" t="inlineStr">
@@ -21872,11 +21872,11 @@
     </row>
     <row r="384">
       <c r="A384" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="B384" t="inlineStr">
         <is>
-          <t>Sunday, September 6, 2026</t>
+          <t>Wednesday, September 2, 2026</t>
         </is>
       </c>
       <c r="C384" t="n">
@@ -21928,19 +21928,19 @@
     </row>
     <row r="385">
       <c r="A385" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B385" t="inlineStr">
         <is>
-          <t>Monday, September 7, 2026</t>
+          <t>Sunday, September 6, 2026</t>
         </is>
       </c>
       <c r="C385" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D385" t="inlineStr">
         <is>
-          <t>09:00 AM – 10:00 AM</t>
+          <t>10:25 AM – 11:25 AM</t>
         </is>
       </c>
       <c r="E385" t="inlineStr">
@@ -22152,11 +22152,11 @@
     </row>
     <row r="389">
       <c r="A389" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="B389" t="inlineStr">
         <is>
-          <t>Thursday, September 3, 2026</t>
+          <t>Monday, September 7, 2026</t>
         </is>
       </c>
       <c r="C389" t="n">
@@ -22208,11 +22208,11 @@
     </row>
     <row r="390">
       <c r="A390" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="B390" t="inlineStr">
         <is>
-          <t>Wednesday, September 2, 2026</t>
+          <t>Sunday, September 6, 2026</t>
         </is>
       </c>
       <c r="C390" t="n">
@@ -22264,11 +22264,11 @@
     </row>
     <row r="391">
       <c r="A391" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="B391" t="inlineStr">
         <is>
-          <t>Monday, September 7, 2026</t>
+          <t>Thursday, September 3, 2026</t>
         </is>
       </c>
       <c r="C391" t="n">
@@ -22328,11 +22328,11 @@
         </is>
       </c>
       <c r="C392" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D392" t="inlineStr">
         <is>
-          <t>08:00 AM – 09:00 AM</t>
+          <t>10:25 AM – 11:25 AM</t>
         </is>
       </c>
       <c r="E392" t="inlineStr">
@@ -22376,11 +22376,11 @@
     </row>
     <row r="393">
       <c r="A393" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B393" t="inlineStr">
         <is>
-          <t>Thursday, September 3, 2026</t>
+          <t>Sunday, September 6, 2026</t>
         </is>
       </c>
       <c r="C393" t="n">
@@ -22432,19 +22432,19 @@
     </row>
     <row r="394">
       <c r="A394" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B394" t="inlineStr">
         <is>
-          <t>Sunday, September 6, 2026</t>
+          <t>Thursday, September 3, 2026</t>
         </is>
       </c>
       <c r="C394" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D394" t="inlineStr">
         <is>
-          <t>10:25 AM – 11:25 AM</t>
+          <t>08:00 AM – 09:00 AM</t>
         </is>
       </c>
       <c r="E394" t="inlineStr">
@@ -22488,11 +22488,11 @@
     </row>
     <row r="395">
       <c r="A395" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="B395" t="inlineStr">
         <is>
-          <t>Monday, September 7, 2026</t>
+          <t>Thursday, September 3, 2026</t>
         </is>
       </c>
       <c r="C395" t="n">
@@ -22544,19 +22544,19 @@
     </row>
     <row r="396">
       <c r="A396" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="B396" t="inlineStr">
         <is>
-          <t>Sunday, September 6, 2026</t>
+          <t>Wednesday, September 2, 2026</t>
         </is>
       </c>
       <c r="C396" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D396" t="inlineStr">
         <is>
-          <t>09:00 AM – 10:00 AM</t>
+          <t>10:25 AM – 11:25 AM</t>
         </is>
       </c>
       <c r="E396" t="inlineStr">
@@ -22608,11 +22608,11 @@
         </is>
       </c>
       <c r="C397" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D397" t="inlineStr">
         <is>
-          <t>10:25 AM – 11:25 AM</t>
+          <t>09:00 AM – 10:00 AM</t>
         </is>
       </c>
       <c r="E397" t="inlineStr">
@@ -22656,19 +22656,19 @@
     </row>
     <row r="398">
       <c r="A398" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="B398" t="inlineStr">
         <is>
-          <t>Thursday, September 3, 2026</t>
+          <t>Monday, September 7, 2026</t>
         </is>
       </c>
       <c r="C398" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D398" t="inlineStr">
         <is>
-          <t>10:25 AM – 11:25 AM</t>
+          <t>08:00 AM – 09:00 AM</t>
         </is>
       </c>
       <c r="E398" t="inlineStr">
@@ -22712,19 +22712,19 @@
     </row>
     <row r="399">
       <c r="A399" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B399" t="inlineStr">
         <is>
-          <t>Thursday, September 3, 2026</t>
+          <t>Wednesday, September 2, 2026</t>
         </is>
       </c>
       <c r="C399" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D399" t="inlineStr">
         <is>
-          <t>08:00 AM – 09:00 AM</t>
+          <t>10:25 AM – 11:25 AM</t>
         </is>
       </c>
       <c r="E399" t="inlineStr">
@@ -22768,19 +22768,19 @@
     </row>
     <row r="400">
       <c r="A400" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B400" t="inlineStr">
         <is>
-          <t>Sunday, September 6, 2026</t>
+          <t>Monday, September 7, 2026</t>
         </is>
       </c>
       <c r="C400" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D400" t="inlineStr">
         <is>
-          <t>09:00 AM – 10:00 AM</t>
+          <t>10:25 AM – 11:25 AM</t>
         </is>
       </c>
       <c r="E400" t="inlineStr">
@@ -22824,19 +22824,19 @@
     </row>
     <row r="401">
       <c r="A401" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B401" t="inlineStr">
         <is>
-          <t>Wednesday, September 2, 2026</t>
+          <t>Thursday, September 3, 2026</t>
         </is>
       </c>
       <c r="C401" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D401" t="inlineStr">
         <is>
-          <t>09:00 AM – 10:00 AM</t>
+          <t>10:25 AM – 11:25 AM</t>
         </is>
       </c>
       <c r="E401" t="inlineStr">
@@ -22880,19 +22880,19 @@
     </row>
     <row r="402">
       <c r="A402" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B402" t="inlineStr">
         <is>
-          <t>Thursday, September 3, 2026</t>
+          <t>Sunday, September 6, 2026</t>
         </is>
       </c>
       <c r="C402" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D402" t="inlineStr">
         <is>
-          <t>09:00 AM – 10:00 AM</t>
+          <t>08:00 AM – 09:00 AM</t>
         </is>
       </c>
       <c r="E402" t="inlineStr">
@@ -22936,19 +22936,19 @@
     </row>
     <row r="403">
       <c r="A403" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B403" t="inlineStr">
         <is>
-          <t>Monday, September 7, 2026</t>
+          <t>Sunday, September 6, 2026</t>
         </is>
       </c>
       <c r="C403" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D403" t="inlineStr">
         <is>
-          <t>08:00 AM – 09:00 AM</t>
+          <t>09:00 AM – 10:00 AM</t>
         </is>
       </c>
       <c r="E403" t="inlineStr">
@@ -22992,11 +22992,11 @@
     </row>
     <row r="404">
       <c r="A404" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="B404" t="inlineStr">
         <is>
-          <t>Wednesday, September 2, 2026</t>
+          <t>Sunday, September 6, 2026</t>
         </is>
       </c>
       <c r="C404" t="n">
@@ -23048,15 +23048,15 @@
     </row>
     <row r="405">
       <c r="A405" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="B405" t="inlineStr">
         <is>
-          <t>Monday, September 7, 2026</t>
+          <t>Thursday, September 3, 2026</t>
         </is>
       </c>
       <c r="C405" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D405" t="inlineStr">
         <is>
@@ -23104,19 +23104,19 @@
     </row>
     <row r="406">
       <c r="A406" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="B406" t="inlineStr">
         <is>
-          <t>Sunday, September 6, 2026</t>
+          <t>Wednesday, September 2, 2026</t>
         </is>
       </c>
       <c r="C406" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D406" t="inlineStr">
         <is>
-          <t>10:25 AM – 11:25 AM</t>
+          <t>09:00 AM – 10:00 AM</t>
         </is>
       </c>
       <c r="E406" t="inlineStr">
@@ -23160,19 +23160,19 @@
     </row>
     <row r="407">
       <c r="A407" t="n">
+        <v>2</v>
+      </c>
+      <c r="B407" t="inlineStr">
+        <is>
+          <t>Thursday, September 3, 2026</t>
+        </is>
+      </c>
+      <c r="C407" t="n">
         <v>1</v>
       </c>
-      <c r="B407" t="inlineStr">
-        <is>
-          <t>Wednesday, September 2, 2026</t>
-        </is>
-      </c>
-      <c r="C407" t="n">
-        <v>3</v>
-      </c>
       <c r="D407" t="inlineStr">
         <is>
-          <t>10:25 AM – 11:25 AM</t>
+          <t>08:00 AM – 09:00 AM</t>
         </is>
       </c>
       <c r="E407" t="inlineStr">
@@ -23216,19 +23216,19 @@
     </row>
     <row r="408">
       <c r="A408" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B408" t="inlineStr">
         <is>
-          <t>Monday, September 7, 2026</t>
+          <t>Sunday, September 6, 2026</t>
         </is>
       </c>
       <c r="C408" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D408" t="inlineStr">
         <is>
-          <t>08:00 AM – 09:00 AM</t>
+          <t>09:00 AM – 10:00 AM</t>
         </is>
       </c>
       <c r="E408" t="inlineStr">
@@ -23272,15 +23272,15 @@
     </row>
     <row r="409">
       <c r="A409" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B409" t="inlineStr">
         <is>
-          <t>Sunday, September 6, 2026</t>
+          <t>Monday, September 7, 2026</t>
         </is>
       </c>
       <c r="C409" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D409" t="inlineStr">
         <is>
@@ -23328,15 +23328,15 @@
     </row>
     <row r="410">
       <c r="A410" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="B410" t="inlineStr">
         <is>
-          <t>Monday, September 7, 2026</t>
+          <t>Wednesday, September 2, 2026</t>
         </is>
       </c>
       <c r="C410" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D410" t="inlineStr">
         <is>
@@ -23384,19 +23384,19 @@
     </row>
     <row r="411">
       <c r="A411" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B411" t="inlineStr">
         <is>
-          <t>Wednesday, September 2, 2026</t>
+          <t>Thursday, September 3, 2026</t>
         </is>
       </c>
       <c r="C411" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D411" t="inlineStr">
         <is>
-          <t>09:00 AM – 10:00 AM</t>
+          <t>10:25 AM – 11:25 AM</t>
         </is>
       </c>
       <c r="E411" t="inlineStr">
@@ -23440,19 +23440,19 @@
     </row>
     <row r="412">
       <c r="A412" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B412" t="inlineStr">
         <is>
-          <t>Thursday, September 3, 2026</t>
+          <t>Wednesday, September 2, 2026</t>
         </is>
       </c>
       <c r="C412" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D412" t="inlineStr">
         <is>
-          <t>08:00 AM – 09:00 AM</t>
+          <t>10:25 AM – 11:25 AM</t>
         </is>
       </c>
       <c r="E412" t="inlineStr">
@@ -23552,19 +23552,19 @@
     </row>
     <row r="414">
       <c r="A414" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="B414" t="inlineStr">
         <is>
-          <t>Wednesday, September 2, 2026</t>
+          <t>Monday, September 7, 2026</t>
         </is>
       </c>
       <c r="C414" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D414" t="inlineStr">
         <is>
-          <t>08:00 AM – 09:00 AM</t>
+          <t>10:25 AM – 11:25 AM</t>
         </is>
       </c>
       <c r="E414" t="inlineStr">
@@ -23664,11 +23664,11 @@
     </row>
     <row r="416">
       <c r="A416" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B416" t="inlineStr">
         <is>
-          <t>Sunday, September 6, 2026</t>
+          <t>Thursday, September 3, 2026</t>
         </is>
       </c>
       <c r="C416" t="n">
@@ -23720,19 +23720,19 @@
     </row>
     <row r="417">
       <c r="A417" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="B417" t="inlineStr">
         <is>
-          <t>Wednesday, September 2, 2026</t>
+          <t>Sunday, September 6, 2026</t>
         </is>
       </c>
       <c r="C417" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D417" t="inlineStr">
         <is>
-          <t>08:00 AM – 09:00 AM</t>
+          <t>10:25 AM – 11:25 AM</t>
         </is>
       </c>
       <c r="E417" t="inlineStr">
@@ -23776,19 +23776,19 @@
     </row>
     <row r="418">
       <c r="A418" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B418" t="inlineStr">
         <is>
-          <t>Sunday, September 6, 2026</t>
+          <t>Monday, September 7, 2026</t>
         </is>
       </c>
       <c r="C418" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D418" t="inlineStr">
         <is>
-          <t>09:00 AM – 10:00 AM</t>
+          <t>10:25 AM – 11:25 AM</t>
         </is>
       </c>
       <c r="E418" t="inlineStr">
@@ -23832,19 +23832,19 @@
     </row>
     <row r="419">
       <c r="A419" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B419" t="inlineStr">
         <is>
-          <t>Thursday, September 3, 2026</t>
+          <t>Wednesday, September 2, 2026</t>
         </is>
       </c>
       <c r="C419" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D419" t="inlineStr">
         <is>
-          <t>10:25 AM – 11:25 AM</t>
+          <t>09:00 AM – 10:00 AM</t>
         </is>
       </c>
       <c r="E419" t="inlineStr">
@@ -23888,19 +23888,19 @@
     </row>
     <row r="420">
       <c r="A420" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="B420" t="inlineStr">
         <is>
-          <t>Monday, September 7, 2026</t>
+          <t>Thursday, September 3, 2026</t>
         </is>
       </c>
       <c r="C420" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D420" t="inlineStr">
         <is>
-          <t>10:25 AM – 11:25 AM</t>
+          <t>09:00 AM – 10:00 AM</t>
         </is>
       </c>
       <c r="E420" t="inlineStr">
@@ -23952,11 +23952,11 @@
         </is>
       </c>
       <c r="C421" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D421" t="inlineStr">
         <is>
-          <t>09:00 AM – 10:00 AM</t>
+          <t>10:25 AM – 11:25 AM</t>
         </is>
       </c>
       <c r="E421" t="inlineStr">
@@ -24000,19 +24000,19 @@
     </row>
     <row r="422">
       <c r="A422" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B422" t="inlineStr">
         <is>
-          <t>Sunday, September 6, 2026</t>
+          <t>Monday, September 7, 2026</t>
         </is>
       </c>
       <c r="C422" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D422" t="inlineStr">
         <is>
-          <t>12:40 PM – 01:40 PM</t>
+          <t>01:50 PM – 02:50 PM</t>
         </is>
       </c>
       <c r="E422" t="inlineStr">
@@ -24056,11 +24056,11 @@
     </row>
     <row r="423">
       <c r="A423" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="B423" t="inlineStr">
         <is>
-          <t>Monday, September 7, 2026</t>
+          <t>Wednesday, September 2, 2026</t>
         </is>
       </c>
       <c r="C423" t="n">
@@ -24112,19 +24112,19 @@
     </row>
     <row r="424">
       <c r="A424" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="B424" t="inlineStr">
         <is>
-          <t>Thursday, September 3, 2026</t>
+          <t>Monday, September 7, 2026</t>
         </is>
       </c>
       <c r="C424" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D424" t="inlineStr">
         <is>
-          <t>01:50 PM – 02:50 PM</t>
+          <t>12:40 PM – 01:40 PM</t>
         </is>
       </c>
       <c r="E424" t="inlineStr">
@@ -24168,11 +24168,11 @@
     </row>
     <row r="425">
       <c r="A425" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="B425" t="inlineStr">
         <is>
-          <t>Wednesday, September 2, 2026</t>
+          <t>Monday, September 7, 2026</t>
         </is>
       </c>
       <c r="C425" t="n">
@@ -24224,11 +24224,11 @@
     </row>
     <row r="426">
       <c r="A426" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="B426" t="inlineStr">
         <is>
-          <t>Wednesday, September 2, 2026</t>
+          <t>Sunday, September 6, 2026</t>
         </is>
       </c>
       <c r="C426" t="n">
@@ -24280,19 +24280,19 @@
     </row>
     <row r="427">
       <c r="A427" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B427" t="inlineStr">
         <is>
-          <t>Thursday, September 3, 2026</t>
+          <t>Sunday, September 6, 2026</t>
         </is>
       </c>
       <c r="C427" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D427" t="inlineStr">
         <is>
-          <t>03:10 PM – 04:10 PM</t>
+          <t>01:50 PM – 02:50 PM</t>
         </is>
       </c>
       <c r="E427" t="inlineStr">
@@ -24336,19 +24336,19 @@
     </row>
     <row r="428">
       <c r="A428" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B428" t="inlineStr">
         <is>
-          <t>Sunday, September 6, 2026</t>
+          <t>Thursday, September 3, 2026</t>
         </is>
       </c>
       <c r="C428" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D428" t="inlineStr">
         <is>
-          <t>01:50 PM – 02:50 PM</t>
+          <t>03:10 PM – 04:10 PM</t>
         </is>
       </c>
       <c r="E428" t="inlineStr">
@@ -24392,19 +24392,19 @@
     </row>
     <row r="429">
       <c r="A429" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B429" t="inlineStr">
         <is>
-          <t>Thursday, September 3, 2026</t>
+          <t>Wednesday, September 2, 2026</t>
         </is>
       </c>
       <c r="C429" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D429" t="inlineStr">
         <is>
-          <t>12:40 PM – 01:40 PM</t>
+          <t>01:50 PM – 02:50 PM</t>
         </is>
       </c>
       <c r="E429" t="inlineStr">
@@ -24448,11 +24448,11 @@
     </row>
     <row r="430">
       <c r="A430" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="B430" t="inlineStr">
         <is>
-          <t>Monday, September 7, 2026</t>
+          <t>Thursday, September 3, 2026</t>
         </is>
       </c>
       <c r="C430" t="n">
@@ -24504,19 +24504,19 @@
     </row>
     <row r="431">
       <c r="A431" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="B431" t="inlineStr">
         <is>
-          <t>Sunday, September 6, 2026</t>
+          <t>Wednesday, September 2, 2026</t>
         </is>
       </c>
       <c r="C431" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D431" t="inlineStr">
         <is>
-          <t>03:10 PM – 04:10 PM</t>
+          <t>12:40 PM – 01:40 PM</t>
         </is>
       </c>
       <c r="E431" t="inlineStr">
@@ -24560,19 +24560,19 @@
     </row>
     <row r="432">
       <c r="A432" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="B432" t="inlineStr">
         <is>
-          <t>Monday, September 7, 2026</t>
+          <t>Wednesday, September 2, 2026</t>
         </is>
       </c>
       <c r="C432" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D432" t="inlineStr">
         <is>
-          <t>01:50 PM – 02:50 PM</t>
+          <t>12:40 PM – 01:40 PM</t>
         </is>
       </c>
       <c r="E432" t="inlineStr">
@@ -24616,11 +24616,11 @@
     </row>
     <row r="433">
       <c r="A433" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="B433" t="inlineStr">
         <is>
-          <t>Thursday, September 3, 2026</t>
+          <t>Monday, September 7, 2026</t>
         </is>
       </c>
       <c r="C433" t="n">
@@ -24672,19 +24672,19 @@
     </row>
     <row r="434">
       <c r="A434" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B434" t="inlineStr">
         <is>
-          <t>Thursday, September 3, 2026</t>
+          <t>Sunday, September 6, 2026</t>
         </is>
       </c>
       <c r="C434" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D434" t="inlineStr">
         <is>
-          <t>01:50 PM – 02:50 PM</t>
+          <t>03:10 PM – 04:10 PM</t>
         </is>
       </c>
       <c r="E434" t="inlineStr">
@@ -24728,19 +24728,19 @@
     </row>
     <row r="435">
       <c r="A435" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="B435" t="inlineStr">
         <is>
-          <t>Wednesday, September 2, 2026</t>
+          <t>Monday, September 7, 2026</t>
         </is>
       </c>
       <c r="C435" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D435" t="inlineStr">
         <is>
-          <t>03:10 PM – 04:10 PM</t>
+          <t>01:50 PM – 02:50 PM</t>
         </is>
       </c>
       <c r="E435" t="inlineStr">
@@ -24792,7 +24792,7 @@
         </is>
       </c>
       <c r="C436" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D436" t="inlineStr">
         <is>
@@ -24840,19 +24840,19 @@
     </row>
     <row r="437">
       <c r="A437" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B437" t="inlineStr">
         <is>
-          <t>Sunday, September 6, 2026</t>
+          <t>Thursday, September 3, 2026</t>
         </is>
       </c>
       <c r="C437" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D437" t="inlineStr">
         <is>
-          <t>12:40 PM – 01:40 PM</t>
+          <t>01:50 PM – 02:50 PM</t>
         </is>
       </c>
       <c r="E437" t="inlineStr">
@@ -24896,19 +24896,19 @@
     </row>
     <row r="438">
       <c r="A438" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B438" t="inlineStr">
         <is>
-          <t>Wednesday, September 2, 2026</t>
+          <t>Thursday, September 3, 2026</t>
         </is>
       </c>
       <c r="C438" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D438" t="inlineStr">
         <is>
-          <t>01:50 PM – 02:50 PM</t>
+          <t>03:10 PM – 04:10 PM</t>
         </is>
       </c>
       <c r="E438" t="inlineStr">
@@ -24952,11 +24952,11 @@
     </row>
     <row r="439">
       <c r="A439" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B439" t="inlineStr">
         <is>
-          <t>Wednesday, September 2, 2026</t>
+          <t>Thursday, September 3, 2026</t>
         </is>
       </c>
       <c r="C439" t="n">
@@ -25008,19 +25008,19 @@
     </row>
     <row r="440">
       <c r="A440" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="B440" t="inlineStr">
         <is>
-          <t>Monday, September 7, 2026</t>
+          <t>Wednesday, September 2, 2026</t>
         </is>
       </c>
       <c r="C440" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D440" t="inlineStr">
         <is>
-          <t>12:40 PM – 01:40 PM</t>
+          <t>03:10 PM – 04:10 PM</t>
         </is>
       </c>
       <c r="E440" t="inlineStr">
@@ -25064,19 +25064,19 @@
     </row>
     <row r="441">
       <c r="A441" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="B441" t="inlineStr">
         <is>
-          <t>Monday, September 7, 2026</t>
+          <t>Wednesday, September 2, 2026</t>
         </is>
       </c>
       <c r="C441" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D441" t="inlineStr">
         <is>
-          <t>03:10 PM – 04:10 PM</t>
+          <t>01:50 PM – 02:50 PM</t>
         </is>
       </c>
       <c r="E441" t="inlineStr">
@@ -25120,19 +25120,19 @@
     </row>
     <row r="442">
       <c r="A442" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B442" t="inlineStr">
         <is>
-          <t>Thursday, September 3, 2026</t>
+          <t>Sunday, September 6, 2026</t>
         </is>
       </c>
       <c r="C442" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D442" t="inlineStr">
         <is>
-          <t>12:40 PM – 01:40 PM</t>
+          <t>03:10 PM – 04:10 PM</t>
         </is>
       </c>
       <c r="E442" t="inlineStr">
@@ -25176,15 +25176,15 @@
     </row>
     <row r="443">
       <c r="A443" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="B443" t="inlineStr">
         <is>
-          <t>Monday, September 7, 2026</t>
+          <t>Thursday, September 3, 2026</t>
         </is>
       </c>
       <c r="C443" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D443" t="inlineStr">
         <is>
@@ -25232,19 +25232,19 @@
     </row>
     <row r="444">
       <c r="A444" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B444" t="inlineStr">
         <is>
-          <t>Monday, September 7, 2026</t>
+          <t>Sunday, September 6, 2026</t>
         </is>
       </c>
       <c r="C444" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D444" t="inlineStr">
         <is>
-          <t>12:40 PM – 01:40 PM</t>
+          <t>01:50 PM – 02:50 PM</t>
         </is>
       </c>
       <c r="E444" t="inlineStr">
@@ -25288,19 +25288,19 @@
     </row>
     <row r="445">
       <c r="A445" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B445" t="inlineStr">
         <is>
-          <t>Thursday, September 3, 2026</t>
+          <t>Sunday, September 6, 2026</t>
         </is>
       </c>
       <c r="C445" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D445" t="inlineStr">
         <is>
-          <t>01:50 PM – 02:50 PM</t>
+          <t>12:40 PM – 01:40 PM</t>
         </is>
       </c>
       <c r="E445" t="inlineStr">
@@ -25344,19 +25344,19 @@
     </row>
     <row r="446">
       <c r="A446" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B446" t="inlineStr">
         <is>
-          <t>Sunday, September 6, 2026</t>
+          <t>Thursday, September 3, 2026</t>
         </is>
       </c>
       <c r="C446" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D446" t="inlineStr">
         <is>
-          <t>12:40 PM – 01:40 PM</t>
+          <t>03:10 PM – 04:10 PM</t>
         </is>
       </c>
       <c r="E446" t="inlineStr">
@@ -25400,19 +25400,19 @@
     </row>
     <row r="447">
       <c r="A447" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="B447" t="inlineStr">
         <is>
-          <t>Thursday, September 3, 2026</t>
+          <t>Monday, September 7, 2026</t>
         </is>
       </c>
       <c r="C447" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D447" t="inlineStr">
         <is>
-          <t>03:10 PM – 04:10 PM</t>
+          <t>12:40 PM – 01:40 PM</t>
         </is>
       </c>
       <c r="E447" t="inlineStr">
@@ -25456,19 +25456,19 @@
     </row>
     <row r="448">
       <c r="A448" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B448" t="inlineStr">
         <is>
-          <t>Sunday, September 6, 2026</t>
+          <t>Monday, September 7, 2026</t>
         </is>
       </c>
       <c r="C448" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D448" t="inlineStr">
         <is>
-          <t>01:50 PM – 02:50 PM</t>
+          <t>03:10 PM – 04:10 PM</t>
         </is>
       </c>
       <c r="E448" t="inlineStr">
@@ -25520,11 +25520,11 @@
         </is>
       </c>
       <c r="C449" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D449" t="inlineStr">
         <is>
-          <t>03:10 PM – 04:10 PM</t>
+          <t>12:40 PM – 01:40 PM</t>
         </is>
       </c>
       <c r="E449" t="inlineStr">
@@ -25568,11 +25568,11 @@
     </row>
     <row r="450">
       <c r="A450" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="B450" t="inlineStr">
         <is>
-          <t>Wednesday, September 2, 2026</t>
+          <t>Monday, September 7, 2026</t>
         </is>
       </c>
       <c r="C450" t="n">
@@ -25632,11 +25632,11 @@
         </is>
       </c>
       <c r="C451" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D451" t="inlineStr">
         <is>
-          <t>12:40 PM – 01:40 PM</t>
+          <t>01:50 PM – 02:50 PM</t>
         </is>
       </c>
       <c r="E451" t="inlineStr">
@@ -25680,19 +25680,19 @@
     </row>
     <row r="452">
       <c r="A452" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B452" t="inlineStr">
         <is>
-          <t>Monday, September 7, 2026</t>
+          <t>Sunday, September 6, 2026</t>
         </is>
       </c>
       <c r="C452" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D452" t="inlineStr">
         <is>
-          <t>01:50 PM – 02:50 PM</t>
+          <t>03:10 PM – 04:10 PM</t>
         </is>
       </c>
       <c r="E452" t="inlineStr">
@@ -25736,11 +25736,11 @@
     </row>
     <row r="453">
       <c r="A453" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="B453" t="inlineStr">
         <is>
-          <t>Wednesday, September 2, 2026</t>
+          <t>Monday, September 7, 2026</t>
         </is>
       </c>
       <c r="C453" t="n">
@@ -25792,15 +25792,15 @@
     </row>
     <row r="454">
       <c r="A454" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B454" t="inlineStr">
         <is>
-          <t>Sunday, September 6, 2026</t>
+          <t>Monday, September 7, 2026</t>
         </is>
       </c>
       <c r="C454" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D454" t="inlineStr">
         <is>
@@ -25960,19 +25960,19 @@
     </row>
     <row r="457">
       <c r="A457" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B457" t="inlineStr">
         <is>
-          <t>Thursday, September 3, 2026</t>
+          <t>Wednesday, September 2, 2026</t>
         </is>
       </c>
       <c r="C457" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D457" t="inlineStr">
         <is>
-          <t>12:40 PM – 01:40 PM</t>
+          <t>03:10 PM – 04:10 PM</t>
         </is>
       </c>
       <c r="E457" t="inlineStr">
@@ -26016,11 +26016,11 @@
     </row>
     <row r="458">
       <c r="A458" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="B458" t="inlineStr">
         <is>
-          <t>Monday, September 7, 2026</t>
+          <t>Thursday, September 3, 2026</t>
         </is>
       </c>
       <c r="C458" t="n">
@@ -26136,11 +26136,11 @@
         </is>
       </c>
       <c r="C460" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D460" t="inlineStr">
         <is>
-          <t>12:40 PM – 01:40 PM</t>
+          <t>01:50 PM – 02:50 PM</t>
         </is>
       </c>
       <c r="E460" t="inlineStr">
@@ -26184,11 +26184,11 @@
     </row>
     <row r="461">
       <c r="A461" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="B461" t="inlineStr">
         <is>
-          <t>Sunday, September 6, 2026</t>
+          <t>Wednesday, September 2, 2026</t>
         </is>
       </c>
       <c r="C461" t="n">
@@ -26248,11 +26248,11 @@
         </is>
       </c>
       <c r="C462" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D462" t="inlineStr">
         <is>
-          <t>03:10 PM – 04:10 PM</t>
+          <t>01:50 PM – 02:50 PM</t>
         </is>
       </c>
       <c r="E462" t="inlineStr">
@@ -26296,11 +26296,11 @@
     </row>
     <row r="463">
       <c r="A463" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="B463" t="inlineStr">
         <is>
-          <t>Thursday, September 3, 2026</t>
+          <t>Monday, September 7, 2026</t>
         </is>
       </c>
       <c r="C463" t="n">
@@ -26360,11 +26360,11 @@
         </is>
       </c>
       <c r="C464" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D464" t="inlineStr">
         <is>
-          <t>01:50 PM – 02:50 PM</t>
+          <t>03:10 PM – 04:10 PM</t>
         </is>
       </c>
       <c r="E464" t="inlineStr">
@@ -26408,19 +26408,19 @@
     </row>
     <row r="465">
       <c r="A465" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="B465" t="inlineStr">
         <is>
-          <t>Sunday, September 6, 2026</t>
+          <t>Wednesday, September 2, 2026</t>
         </is>
       </c>
       <c r="C465" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D465" t="inlineStr">
         <is>
-          <t>12:40 PM – 01:40 PM</t>
+          <t>01:50 PM – 02:50 PM</t>
         </is>
       </c>
       <c r="E465" t="inlineStr">
@@ -26472,11 +26472,11 @@
         </is>
       </c>
       <c r="C466" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D466" t="inlineStr">
         <is>
-          <t>01:50 PM – 02:50 PM</t>
+          <t>12:40 PM – 01:40 PM</t>
         </is>
       </c>
       <c r="E466" t="inlineStr">
@@ -26520,19 +26520,19 @@
     </row>
     <row r="467">
       <c r="A467" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B467" t="inlineStr">
         <is>
-          <t>Thursday, September 3, 2026</t>
+          <t>Sunday, September 6, 2026</t>
         </is>
       </c>
       <c r="C467" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D467" t="inlineStr">
         <is>
-          <t>12:40 PM – 01:40 PM</t>
+          <t>03:10 PM – 04:10 PM</t>
         </is>
       </c>
       <c r="E467" t="inlineStr">
@@ -26576,11 +26576,11 @@
     </row>
     <row r="468">
       <c r="A468" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B468" t="inlineStr">
         <is>
-          <t>Wednesday, September 2, 2026</t>
+          <t>Thursday, September 3, 2026</t>
         </is>
       </c>
       <c r="C468" t="n">
@@ -26632,19 +26632,19 @@
     </row>
     <row r="469">
       <c r="A469" t="n">
+        <v>3</v>
+      </c>
+      <c r="B469" t="inlineStr">
+        <is>
+          <t>Sunday, September 6, 2026</t>
+        </is>
+      </c>
+      <c r="C469" t="n">
         <v>1</v>
       </c>
-      <c r="B469" t="inlineStr">
-        <is>
-          <t>Wednesday, September 2, 2026</t>
-        </is>
-      </c>
-      <c r="C469" t="n">
-        <v>3</v>
-      </c>
       <c r="D469" t="inlineStr">
         <is>
-          <t>03:10 PM – 04:10 PM</t>
+          <t>12:40 PM – 01:40 PM</t>
         </is>
       </c>
       <c r="E469" t="inlineStr">
@@ -26696,11 +26696,11 @@
         </is>
       </c>
       <c r="C470" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D470" t="inlineStr">
         <is>
-          <t>12:40 PM – 01:40 PM</t>
+          <t>01:50 PM – 02:50 PM</t>
         </is>
       </c>
       <c r="E470" t="inlineStr">
@@ -26744,19 +26744,19 @@
     </row>
     <row r="471">
       <c r="A471" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B471" t="inlineStr">
         <is>
-          <t>Sunday, September 6, 2026</t>
+          <t>Monday, September 7, 2026</t>
         </is>
       </c>
       <c r="C471" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D471" t="inlineStr">
         <is>
-          <t>03:10 PM – 04:10 PM</t>
+          <t>12:40 PM – 01:40 PM</t>
         </is>
       </c>
       <c r="E471" t="inlineStr">
@@ -26856,15 +26856,15 @@
     </row>
     <row r="473">
       <c r="A473" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B473" t="inlineStr">
         <is>
-          <t>Thursday, September 3, 2026</t>
+          <t>Sunday, September 6, 2026</t>
         </is>
       </c>
       <c r="C473" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D473" t="inlineStr">
         <is>
@@ -26920,11 +26920,11 @@
         </is>
       </c>
       <c r="C474" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D474" t="inlineStr">
         <is>
-          <t>12:40 PM – 01:40 PM</t>
+          <t>01:50 PM – 02:50 PM</t>
         </is>
       </c>
       <c r="E474" t="inlineStr">
@@ -26968,11 +26968,11 @@
     </row>
     <row r="475">
       <c r="A475" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="B475" t="inlineStr">
         <is>
-          <t>Monday, September 7, 2026</t>
+          <t>Wednesday, September 2, 2026</t>
         </is>
       </c>
       <c r="C475" t="n">
@@ -27032,11 +27032,11 @@
         </is>
       </c>
       <c r="C476" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D476" t="inlineStr">
         <is>
-          <t>01:50 PM – 02:50 PM</t>
+          <t>03:10 PM – 04:10 PM</t>
         </is>
       </c>
       <c r="E476" t="inlineStr">
@@ -27080,19 +27080,19 @@
     </row>
     <row r="477">
       <c r="A477" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B477" t="inlineStr">
         <is>
-          <t>Wednesday, September 2, 2026</t>
+          <t>Thursday, September 3, 2026</t>
         </is>
       </c>
       <c r="C477" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D477" t="inlineStr">
         <is>
-          <t>12:40 PM – 01:40 PM</t>
+          <t>03:10 PM – 04:10 PM</t>
         </is>
       </c>
       <c r="E477" t="inlineStr">
@@ -27136,19 +27136,19 @@
     </row>
     <row r="478">
       <c r="A478" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B478" t="inlineStr">
         <is>
-          <t>Thursday, September 3, 2026</t>
+          <t>Sunday, September 6, 2026</t>
         </is>
       </c>
       <c r="C478" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D478" t="inlineStr">
         <is>
-          <t>10:25 AM – 11:25 AM</t>
+          <t>09:00 AM – 10:00 AM</t>
         </is>
       </c>
       <c r="E478" t="inlineStr">
@@ -27200,11 +27200,11 @@
         </is>
       </c>
       <c r="C479" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D479" t="inlineStr">
         <is>
-          <t>10:25 AM – 11:25 AM</t>
+          <t>09:00 AM – 10:00 AM</t>
         </is>
       </c>
       <c r="E479" t="inlineStr">
@@ -27248,11 +27248,11 @@
     </row>
     <row r="480">
       <c r="A480" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="B480" t="inlineStr">
         <is>
-          <t>Monday, September 7, 2026</t>
+          <t>Thursday, September 3, 2026</t>
         </is>
       </c>
       <c r="C480" t="n">
@@ -27304,19 +27304,19 @@
     </row>
     <row r="481">
       <c r="A481" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B481" t="inlineStr">
         <is>
-          <t>Monday, September 7, 2026</t>
+          <t>Sunday, September 6, 2026</t>
         </is>
       </c>
       <c r="C481" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D481" t="inlineStr">
         <is>
-          <t>09:00 AM – 10:00 AM</t>
+          <t>08:00 AM – 09:00 AM</t>
         </is>
       </c>
       <c r="E481" t="inlineStr">
@@ -27360,11 +27360,11 @@
     </row>
     <row r="482">
       <c r="A482" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B482" t="inlineStr">
         <is>
-          <t>Sunday, September 6, 2026</t>
+          <t>Monday, September 7, 2026</t>
         </is>
       </c>
       <c r="C482" t="n">
@@ -27416,11 +27416,11 @@
     </row>
     <row r="483">
       <c r="A483" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="B483" t="inlineStr">
         <is>
-          <t>Wednesday, September 2, 2026</t>
+          <t>Monday, September 7, 2026</t>
         </is>
       </c>
       <c r="C483" t="n">
@@ -27472,19 +27472,19 @@
     </row>
     <row r="484">
       <c r="A484" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="B484" t="inlineStr">
         <is>
-          <t>Monday, September 7, 2026</t>
+          <t>Thursday, September 3, 2026</t>
         </is>
       </c>
       <c r="C484" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D484" t="inlineStr">
         <is>
-          <t>03:10 PM – 04:10 PM</t>
+          <t>05:30 PM – 06:30 PM</t>
         </is>
       </c>
       <c r="E484" t="inlineStr">
@@ -27528,19 +27528,19 @@
     </row>
     <row r="485">
       <c r="A485" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B485" t="inlineStr">
         <is>
-          <t>Sunday, September 6, 2026</t>
+          <t>Monday, September 7, 2026</t>
         </is>
       </c>
       <c r="C485" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D485" t="inlineStr">
         <is>
-          <t>05:30 PM – 06:30 PM</t>
+          <t>03:10 PM – 04:10 PM</t>
         </is>
       </c>
       <c r="E485" t="inlineStr">
@@ -27584,19 +27584,19 @@
     </row>
     <row r="486">
       <c r="A486" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="B486" t="inlineStr">
         <is>
-          <t>Thursday, September 3, 2026</t>
+          <t>Monday, September 7, 2026</t>
         </is>
       </c>
       <c r="C486" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D486" t="inlineStr">
         <is>
-          <t>04:20 PM – 05:20 PM</t>
+          <t>05:30 PM – 06:30 PM</t>
         </is>
       </c>
       <c r="E486" t="inlineStr">
@@ -27640,19 +27640,19 @@
     </row>
     <row r="487">
       <c r="A487" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="B487" t="inlineStr">
         <is>
-          <t>Monday, September 7, 2026</t>
+          <t>Wednesday, September 2, 2026</t>
         </is>
       </c>
       <c r="C487" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D487" t="inlineStr">
         <is>
-          <t>04:20 PM – 05:20 PM</t>
+          <t>05:30 PM – 06:30 PM</t>
         </is>
       </c>
       <c r="E487" t="inlineStr">
@@ -27704,11 +27704,11 @@
         </is>
       </c>
       <c r="C488" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D488" t="inlineStr">
         <is>
-          <t>04:20 PM – 05:20 PM</t>
+          <t>05:30 PM – 06:30 PM</t>
         </is>
       </c>
       <c r="E488" t="inlineStr">
@@ -27752,19 +27752,19 @@
     </row>
     <row r="489">
       <c r="A489" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B489" t="inlineStr">
         <is>
-          <t>Thursday, September 3, 2026</t>
+          <t>Sunday, September 6, 2026</t>
         </is>
       </c>
       <c r="C489" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D489" t="inlineStr">
         <is>
-          <t>05:30 PM – 06:30 PM</t>
+          <t>04:20 PM – 05:20 PM</t>
         </is>
       </c>
       <c r="E489" t="inlineStr">
@@ -27864,19 +27864,19 @@
     </row>
     <row r="491">
       <c r="A491" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="B491" t="inlineStr">
         <is>
-          <t>Monday, September 7, 2026</t>
+          <t>Wednesday, September 2, 2026</t>
         </is>
       </c>
       <c r="C491" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D491" t="inlineStr">
         <is>
-          <t>05:30 PM – 06:30 PM</t>
+          <t>04:20 PM – 05:20 PM</t>
         </is>
       </c>
       <c r="E491" t="inlineStr">
@@ -27920,15 +27920,15 @@
     </row>
     <row r="492">
       <c r="A492" t="n">
+        <v>2</v>
+      </c>
+      <c r="B492" t="inlineStr">
+        <is>
+          <t>Thursday, September 3, 2026</t>
+        </is>
+      </c>
+      <c r="C492" t="n">
         <v>1</v>
-      </c>
-      <c r="B492" t="inlineStr">
-        <is>
-          <t>Wednesday, September 2, 2026</t>
-        </is>
-      </c>
-      <c r="C492" t="n">
-        <v>2</v>
       </c>
       <c r="D492" t="inlineStr">
         <is>
@@ -27976,19 +27976,19 @@
     </row>
     <row r="493">
       <c r="A493" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="B493" t="inlineStr">
         <is>
-          <t>Wednesday, September 2, 2026</t>
+          <t>Monday, September 7, 2026</t>
         </is>
       </c>
       <c r="C493" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D493" t="inlineStr">
         <is>
-          <t>03:10 PM – 04:10 PM</t>
+          <t>04:20 PM – 05:20 PM</t>
         </is>
       </c>
       <c r="E493" t="inlineStr">
@@ -28032,19 +28032,19 @@
     </row>
     <row r="494">
       <c r="A494" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B494" t="inlineStr">
         <is>
-          <t>Sunday, September 6, 2026</t>
+          <t>Monday, September 7, 2026</t>
         </is>
       </c>
       <c r="C494" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D494" t="inlineStr">
         <is>
-          <t>05:30 PM – 06:30 PM</t>
+          <t>04:20 PM – 05:20 PM</t>
         </is>
       </c>
       <c r="E494" t="inlineStr">
@@ -28088,19 +28088,19 @@
     </row>
     <row r="495">
       <c r="A495" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="B495" t="inlineStr">
         <is>
-          <t>Thursday, September 3, 2026</t>
+          <t>Monday, September 7, 2026</t>
         </is>
       </c>
       <c r="C495" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D495" t="inlineStr">
         <is>
-          <t>04:20 PM – 05:20 PM</t>
+          <t>05:30 PM – 06:30 PM</t>
         </is>
       </c>
       <c r="E495" t="inlineStr">
@@ -28144,19 +28144,19 @@
     </row>
     <row r="496">
       <c r="A496" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="B496" t="inlineStr">
         <is>
-          <t>Monday, September 7, 2026</t>
+          <t>Thursday, September 3, 2026</t>
         </is>
       </c>
       <c r="C496" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D496" t="inlineStr">
         <is>
-          <t>03:10 PM – 04:10 PM</t>
+          <t>05:30 PM – 06:30 PM</t>
         </is>
       </c>
       <c r="E496" t="inlineStr">
@@ -28200,19 +28200,19 @@
     </row>
     <row r="497">
       <c r="A497" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B497" t="inlineStr">
         <is>
-          <t>Thursday, September 3, 2026</t>
+          <t>Wednesday, September 2, 2026</t>
         </is>
       </c>
       <c r="C497" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D497" t="inlineStr">
         <is>
-          <t>03:10 PM – 04:10 PM</t>
+          <t>04:20 PM – 05:20 PM</t>
         </is>
       </c>
       <c r="E497" t="inlineStr">
@@ -28256,19 +28256,19 @@
     </row>
     <row r="498">
       <c r="A498" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="B498" t="inlineStr">
         <is>
-          <t>Wednesday, September 2, 2026</t>
+          <t>Sunday, September 6, 2026</t>
         </is>
       </c>
       <c r="C498" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D498" t="inlineStr">
         <is>
-          <t>03:10 PM – 04:10 PM</t>
+          <t>05:30 PM – 06:30 PM</t>
         </is>
       </c>
       <c r="E498" t="inlineStr">
@@ -28312,11 +28312,11 @@
     </row>
     <row r="499">
       <c r="A499" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B499" t="inlineStr">
         <is>
-          <t>Thursday, September 3, 2026</t>
+          <t>Wednesday, September 2, 2026</t>
         </is>
       </c>
       <c r="C499" t="n">
@@ -28432,11 +28432,11 @@
         </is>
       </c>
       <c r="C501" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D501" t="inlineStr">
         <is>
-          <t>04:20 PM – 05:20 PM</t>
+          <t>03:10 PM – 04:10 PM</t>
         </is>
       </c>
       <c r="E501" t="inlineStr">
@@ -28488,11 +28488,11 @@
         </is>
       </c>
       <c r="C502" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D502" t="inlineStr">
         <is>
-          <t>04:20 PM – 05:20 PM</t>
+          <t>03:10 PM – 04:10 PM</t>
         </is>
       </c>
       <c r="E502" t="inlineStr">
@@ -28536,19 +28536,19 @@
     </row>
     <row r="503">
       <c r="A503" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B503" t="inlineStr">
         <is>
-          <t>Wednesday, September 2, 2026</t>
+          <t>Thursday, September 3, 2026</t>
         </is>
       </c>
       <c r="C503" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D503" t="inlineStr">
         <is>
-          <t>05:30 PM – 06:30 PM</t>
+          <t>04:20 PM – 05:20 PM</t>
         </is>
       </c>
       <c r="E503" t="inlineStr">
@@ -28600,11 +28600,11 @@
         </is>
       </c>
       <c r="C504" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D504" t="inlineStr">
         <is>
-          <t>05:30 PM – 06:30 PM</t>
+          <t>03:10 PM – 04:10 PM</t>
         </is>
       </c>
       <c r="E504" t="inlineStr">
@@ -28648,11 +28648,11 @@
     </row>
     <row r="505">
       <c r="A505" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="B505" t="inlineStr">
         <is>
-          <t>Monday, September 7, 2026</t>
+          <t>Thursday, September 3, 2026</t>
         </is>
       </c>
       <c r="C505" t="n">
@@ -28704,19 +28704,19 @@
     </row>
     <row r="506">
       <c r="A506" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="B506" t="inlineStr">
         <is>
-          <t>Sunday, September 6, 2026</t>
+          <t>Wednesday, September 2, 2026</t>
         </is>
       </c>
       <c r="C506" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D506" t="inlineStr">
         <is>
-          <t>03:10 PM – 04:10 PM</t>
+          <t>04:20 PM – 05:20 PM</t>
         </is>
       </c>
       <c r="E506" t="inlineStr">
@@ -28760,11 +28760,11 @@
     </row>
     <row r="507">
       <c r="A507" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B507" t="inlineStr">
         <is>
-          <t>Sunday, September 6, 2026</t>
+          <t>Thursday, September 3, 2026</t>
         </is>
       </c>
       <c r="C507" t="n">
@@ -28816,19 +28816,19 @@
     </row>
     <row r="508">
       <c r="A508" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="B508" t="inlineStr">
         <is>
-          <t>Wednesday, September 2, 2026</t>
+          <t>Sunday, September 6, 2026</t>
         </is>
       </c>
       <c r="C508" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D508" t="inlineStr">
         <is>
-          <t>05:30 PM – 06:30 PM</t>
+          <t>04:20 PM – 05:20 PM</t>
         </is>
       </c>
       <c r="E508" t="inlineStr">
@@ -28880,11 +28880,11 @@
         </is>
       </c>
       <c r="C509" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D509" t="inlineStr">
         <is>
-          <t>04:20 PM – 05:20 PM</t>
+          <t>03:10 PM – 04:10 PM</t>
         </is>
       </c>
       <c r="E509" t="inlineStr">
@@ -28928,15 +28928,15 @@
     </row>
     <row r="510">
       <c r="A510" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="B510" t="inlineStr">
         <is>
-          <t>Thursday, September 3, 2026</t>
+          <t>Monday, September 7, 2026</t>
         </is>
       </c>
       <c r="C510" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D510" t="inlineStr">
         <is>
@@ -28984,19 +28984,19 @@
     </row>
     <row r="511">
       <c r="A511" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B511" t="inlineStr">
         <is>
-          <t>Thursday, September 3, 2026</t>
+          <t>Wednesday, September 2, 2026</t>
         </is>
       </c>
       <c r="C511" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D511" t="inlineStr">
         <is>
-          <t>03:10 PM – 04:10 PM</t>
+          <t>05:30 PM – 06:30 PM</t>
         </is>
       </c>
       <c r="E511" t="inlineStr">
@@ -29048,11 +29048,11 @@
         </is>
       </c>
       <c r="C512" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D512" t="inlineStr">
         <is>
-          <t>04:20 PM – 05:20 PM</t>
+          <t>05:30 PM – 06:30 PM</t>
         </is>
       </c>
       <c r="E512" t="inlineStr">
@@ -29096,11 +29096,11 @@
     </row>
     <row r="513">
       <c r="A513" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B513" t="inlineStr">
         <is>
-          <t>Wednesday, September 2, 2026</t>
+          <t>Thursday, September 3, 2026</t>
         </is>
       </c>
       <c r="C513" t="n">
@@ -29152,19 +29152,19 @@
     </row>
     <row r="514">
       <c r="A514" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B514" t="inlineStr">
         <is>
-          <t>Thursday, September 3, 2026</t>
+          <t>Wednesday, September 2, 2026</t>
         </is>
       </c>
       <c r="C514" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D514" t="inlineStr">
         <is>
-          <t>05:30 PM – 06:30 PM</t>
+          <t>04:20 PM – 05:20 PM</t>
         </is>
       </c>
       <c r="E514" t="inlineStr">
@@ -29208,19 +29208,19 @@
     </row>
     <row r="515">
       <c r="A515" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B515" t="inlineStr">
         <is>
-          <t>Monday, September 7, 2026</t>
+          <t>Sunday, September 6, 2026</t>
         </is>
       </c>
       <c r="C515" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D515" t="inlineStr">
         <is>
-          <t>04:20 PM – 05:20 PM</t>
+          <t>05:30 PM – 06:30 PM</t>
         </is>
       </c>
       <c r="E515" t="inlineStr">
@@ -29264,19 +29264,19 @@
     </row>
     <row r="516">
       <c r="A516" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="B516" t="inlineStr">
         <is>
-          <t>Wednesday, September 2, 2026</t>
+          <t>Monday, September 7, 2026</t>
         </is>
       </c>
       <c r="C516" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D516" t="inlineStr">
         <is>
-          <t>04:20 PM – 05:20 PM</t>
+          <t>05:30 PM – 06:30 PM</t>
         </is>
       </c>
       <c r="E516" t="inlineStr">
@@ -29320,19 +29320,19 @@
     </row>
     <row r="517">
       <c r="A517" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B517" t="inlineStr">
         <is>
-          <t>Monday, September 7, 2026</t>
+          <t>Sunday, September 6, 2026</t>
         </is>
       </c>
       <c r="C517" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D517" t="inlineStr">
         <is>
-          <t>05:30 PM – 06:30 PM</t>
+          <t>03:10 PM – 04:10 PM</t>
         </is>
       </c>
       <c r="E517" t="inlineStr">
@@ -29376,19 +29376,19 @@
     </row>
     <row r="518">
       <c r="A518" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B518" t="inlineStr">
         <is>
-          <t>Sunday, September 6, 2026</t>
+          <t>Thursday, September 3, 2026</t>
         </is>
       </c>
       <c r="C518" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D518" t="inlineStr">
         <is>
-          <t>05:30 PM – 06:30 PM</t>
+          <t>03:10 PM – 04:10 PM</t>
         </is>
       </c>
       <c r="E518" t="inlineStr">
@@ -29432,11 +29432,11 @@
     </row>
     <row r="519">
       <c r="A519" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B519" t="inlineStr">
         <is>
-          <t>Sunday, September 6, 2026</t>
+          <t>Monday, September 7, 2026</t>
         </is>
       </c>
       <c r="C519" t="n">
@@ -29488,19 +29488,19 @@
     </row>
     <row r="520">
       <c r="A520" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B520" t="inlineStr">
         <is>
-          <t>Wednesday, September 2, 2026</t>
+          <t>Thursday, September 3, 2026</t>
         </is>
       </c>
       <c r="C520" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D520" t="inlineStr">
         <is>
-          <t>05:30 PM – 06:30 PM</t>
+          <t>04:20 PM – 05:20 PM</t>
         </is>
       </c>
       <c r="E520" t="inlineStr">
@@ -29544,19 +29544,19 @@
     </row>
     <row r="521">
       <c r="A521" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B521" t="inlineStr">
         <is>
-          <t>Thursday, September 3, 2026</t>
+          <t>Wednesday, September 2, 2026</t>
         </is>
       </c>
       <c r="C521" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D521" t="inlineStr">
         <is>
-          <t>04:20 PM – 05:20 PM</t>
+          <t>05:30 PM – 06:30 PM</t>
         </is>
       </c>
       <c r="E521" t="inlineStr">
@@ -29600,19 +29600,19 @@
     </row>
     <row r="522">
       <c r="A522" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="B522" t="inlineStr">
         <is>
-          <t>Wednesday, September 2, 2026</t>
+          <t>Sunday, September 6, 2026</t>
         </is>
       </c>
       <c r="C522" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D522" t="inlineStr">
         <is>
-          <t>03:10 PM – 04:10 PM</t>
+          <t>04:20 PM – 05:20 PM</t>
         </is>
       </c>
       <c r="E522" t="inlineStr">
@@ -29656,19 +29656,19 @@
     </row>
     <row r="523">
       <c r="A523" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B523" t="inlineStr">
         <is>
-          <t>Sunday, September 6, 2026</t>
+          <t>Monday, September 7, 2026</t>
         </is>
       </c>
       <c r="C523" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D523" t="inlineStr">
         <is>
-          <t>05:30 PM – 06:30 PM</t>
+          <t>03:10 PM – 04:10 PM</t>
         </is>
       </c>
       <c r="E523" t="inlineStr">
@@ -29712,19 +29712,19 @@
     </row>
     <row r="524">
       <c r="A524" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="B524" t="inlineStr">
         <is>
-          <t>Wednesday, September 2, 2026</t>
+          <t>Monday, September 7, 2026</t>
         </is>
       </c>
       <c r="C524" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D524" t="inlineStr">
         <is>
-          <t>04:20 PM – 05:20 PM</t>
+          <t>05:30 PM – 06:30 PM</t>
         </is>
       </c>
       <c r="E524" t="inlineStr">
@@ -29768,19 +29768,19 @@
     </row>
     <row r="525">
       <c r="A525" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="B525" t="inlineStr">
         <is>
-          <t>Monday, September 7, 2026</t>
+          <t>Thursday, September 3, 2026</t>
         </is>
       </c>
       <c r="C525" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D525" t="inlineStr">
         <is>
-          <t>05:30 PM – 06:30 PM</t>
+          <t>03:10 PM – 04:10 PM</t>
         </is>
       </c>
       <c r="E525" t="inlineStr">
@@ -29824,11 +29824,11 @@
     </row>
     <row r="526">
       <c r="A526" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B526" t="inlineStr">
         <is>
-          <t>Sunday, September 6, 2026</t>
+          <t>Monday, September 7, 2026</t>
         </is>
       </c>
       <c r="C526" t="n">
@@ -29880,19 +29880,19 @@
     </row>
     <row r="527">
       <c r="A527" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B527" t="inlineStr">
         <is>
-          <t>Wednesday, September 2, 2026</t>
+          <t>Thursday, September 3, 2026</t>
         </is>
       </c>
       <c r="C527" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D527" t="inlineStr">
         <is>
-          <t>05:30 PM – 06:30 PM</t>
+          <t>04:20 PM – 05:20 PM</t>
         </is>
       </c>
       <c r="E527" t="inlineStr">
@@ -29936,11 +29936,11 @@
     </row>
     <row r="528">
       <c r="A528" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="B528" t="inlineStr">
         <is>
-          <t>Monday, September 7, 2026</t>
+          <t>Wednesday, September 2, 2026</t>
         </is>
       </c>
       <c r="C528" t="n">
@@ -30000,11 +30000,11 @@
         </is>
       </c>
       <c r="C529" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D529" t="inlineStr">
         <is>
-          <t>03:10 PM – 04:10 PM</t>
+          <t>05:30 PM – 06:30 PM</t>
         </is>
       </c>
       <c r="E529" t="inlineStr">
@@ -30048,11 +30048,11 @@
     </row>
     <row r="530">
       <c r="A530" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B530" t="inlineStr">
         <is>
-          <t>Thursday, September 3, 2026</t>
+          <t>Sunday, September 6, 2026</t>
         </is>
       </c>
       <c r="C530" t="n">
@@ -30104,11 +30104,11 @@
     </row>
     <row r="531">
       <c r="A531" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B531" t="inlineStr">
         <is>
-          <t>Thursday, September 3, 2026</t>
+          <t>Wednesday, September 2, 2026</t>
         </is>
       </c>
       <c r="C531" t="n">
@@ -30160,15 +30160,15 @@
     </row>
     <row r="532">
       <c r="A532" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="B532" t="inlineStr">
         <is>
-          <t>Monday, September 7, 2026</t>
+          <t>Thursday, September 3, 2026</t>
         </is>
       </c>
       <c r="C532" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D532" t="inlineStr">
         <is>
@@ -30216,11 +30216,11 @@
     </row>
     <row r="533">
       <c r="A533" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="B533" t="inlineStr">
         <is>
-          <t>Thursday, September 3, 2026</t>
+          <t>Monday, September 7, 2026</t>
         </is>
       </c>
       <c r="C533" t="n">
@@ -30272,11 +30272,11 @@
     </row>
     <row r="534">
       <c r="A534" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B534" t="inlineStr">
         <is>
-          <t>Sunday, September 6, 2026</t>
+          <t>Monday, September 7, 2026</t>
         </is>
       </c>
       <c r="C534" t="n">
@@ -30328,11 +30328,11 @@
     </row>
     <row r="535">
       <c r="A535" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="B535" t="inlineStr">
         <is>
-          <t>Wednesday, September 2, 2026</t>
+          <t>Sunday, September 6, 2026</t>
         </is>
       </c>
       <c r="C535" t="n">
@@ -30384,19 +30384,19 @@
     </row>
     <row r="536">
       <c r="A536" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B536" t="inlineStr">
         <is>
-          <t>Monday, September 7, 2026</t>
+          <t>Sunday, September 6, 2026</t>
         </is>
       </c>
       <c r="C536" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D536" t="inlineStr">
         <is>
-          <t>03:10 PM – 04:10 PM</t>
+          <t>04:20 PM – 05:20 PM</t>
         </is>
       </c>
       <c r="E536" t="inlineStr">
@@ -30440,11 +30440,11 @@
     </row>
     <row r="537">
       <c r="A537" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B537" t="inlineStr">
         <is>
-          <t>Thursday, September 3, 2026</t>
+          <t>Wednesday, September 2, 2026</t>
         </is>
       </c>
       <c r="C537" t="n">
@@ -30496,19 +30496,19 @@
     </row>
     <row r="538">
       <c r="A538" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="B538" t="inlineStr">
         <is>
-          <t>Sunday, September 6, 2026</t>
+          <t>Wednesday, September 2, 2026</t>
         </is>
       </c>
       <c r="C538" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D538" t="inlineStr">
         <is>
-          <t>04:20 PM – 05:20 PM</t>
+          <t>03:10 PM – 04:10 PM</t>
         </is>
       </c>
       <c r="E538" t="inlineStr">
@@ -30552,19 +30552,19 @@
     </row>
     <row r="539">
       <c r="A539" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B539" t="inlineStr">
         <is>
-          <t>Wednesday, September 2, 2026</t>
+          <t>Thursday, September 3, 2026</t>
         </is>
       </c>
       <c r="C539" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D539" t="inlineStr">
         <is>
-          <t>04:20 PM – 05:20 PM</t>
+          <t>05:30 PM – 06:30 PM</t>
         </is>
       </c>
       <c r="E539" t="inlineStr">
@@ -30608,11 +30608,11 @@
     </row>
     <row r="540">
       <c r="A540" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="B540" t="inlineStr">
         <is>
-          <t>Wednesday, September 2, 2026</t>
+          <t>Sunday, September 6, 2026</t>
         </is>
       </c>
       <c r="C540" t="n">
@@ -30664,19 +30664,19 @@
     </row>
     <row r="541">
       <c r="A541" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B541" t="inlineStr">
         <is>
-          <t>Sunday, September 6, 2026</t>
+          <t>Monday, September 7, 2026</t>
         </is>
       </c>
       <c r="C541" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D541" t="inlineStr">
         <is>
-          <t>03:10 PM – 04:10 PM</t>
+          <t>04:20 PM – 05:20 PM</t>
         </is>
       </c>
       <c r="E541" t="inlineStr">
@@ -30720,11 +30720,11 @@
     </row>
     <row r="542">
       <c r="A542" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B542" t="inlineStr">
         <is>
-          <t>Sunday, September 6, 2026</t>
+          <t>Monday, September 7, 2026</t>
         </is>
       </c>
       <c r="C542" t="n">
@@ -30776,11 +30776,11 @@
     </row>
     <row r="543">
       <c r="A543" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="B543" t="inlineStr">
         <is>
-          <t>Wednesday, September 2, 2026</t>
+          <t>Sunday, September 6, 2026</t>
         </is>
       </c>
       <c r="C543" t="n">
@@ -30832,11 +30832,11 @@
     </row>
     <row r="544">
       <c r="A544" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="B544" t="inlineStr">
         <is>
-          <t>Monday, September 7, 2026</t>
+          <t>Thursday, September 3, 2026</t>
         </is>
       </c>
       <c r="C544" t="n">
@@ -30888,19 +30888,19 @@
     </row>
     <row r="545">
       <c r="A545" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="B545" t="inlineStr">
         <is>
-          <t>Monday, September 7, 2026</t>
+          <t>Wednesday, September 2, 2026</t>
         </is>
       </c>
       <c r="C545" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D545" t="inlineStr">
         <is>
-          <t>04:20 PM – 05:20 PM</t>
+          <t>05:30 PM – 06:30 PM</t>
         </is>
       </c>
       <c r="E545" t="inlineStr">
@@ -30952,11 +30952,11 @@
         </is>
       </c>
       <c r="C546" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D546" t="inlineStr">
         <is>
-          <t>05:30 PM – 06:30 PM</t>
+          <t>03:10 PM – 04:10 PM</t>
         </is>
       </c>
       <c r="E546" t="inlineStr">
@@ -31056,11 +31056,11 @@
     </row>
     <row r="548">
       <c r="A548" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B548" t="inlineStr">
         <is>
-          <t>Thursday, September 3, 2026</t>
+          <t>Sunday, September 6, 2026</t>
         </is>
       </c>
       <c r="C548" t="n">

--- a/Term_Examination_Schedule_S.Y._2026-2027_Optimized.xlsx
+++ b/Term_Examination_Schedule_S.Y._2026-2027_Optimized.xlsx
@@ -28054,22 +28054,22 @@
       </c>
       <c r="J419" t="inlineStr">
         <is>
-          <t>subj_mapeh</t>
+          <t>subj_filipino</t>
         </is>
       </c>
       <c r="K419" t="inlineStr">
         <is>
-          <t>MAPEH</t>
+          <t>Filipino</t>
         </is>
       </c>
       <c r="L419" t="inlineStr">
         <is>
-          <t>tchr_franchette</t>
+          <t>tchr_sophia</t>
         </is>
       </c>
       <c r="M419" t="inlineStr">
         <is>
-          <t>Teacher Franchette</t>
+          <t>Teacher Sophia</t>
         </is>
       </c>
       <c r="N419" t="n">
@@ -37558,22 +37558,22 @@
       </c>
       <c r="J563" t="inlineStr">
         <is>
-          <t>subj_filipino</t>
+          <t>subj_mapeh</t>
         </is>
       </c>
       <c r="K563" t="inlineStr">
         <is>
-          <t>Filipino</t>
+          <t>MAPEH</t>
         </is>
       </c>
       <c r="L563" t="inlineStr">
         <is>
-          <t>tchr_sophia</t>
+          <t>tchr_franchette</t>
         </is>
       </c>
       <c r="M563" t="inlineStr">
         <is>
-          <t>Teacher Sophia</t>
+          <t>Teacher Franchette</t>
         </is>
       </c>
       <c r="N563" t="n">

--- a/Term_Examination_Schedule_S.Y._2026-2027_Optimized.xlsx
+++ b/Term_Examination_Schedule_S.Y._2026-2027_Optimized.xlsx
@@ -2857,7 +2857,7 @@
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>Ustadh Hainur</t>
+          <t>Ustadha Hainur</t>
         </is>
       </c>
       <c r="N37" t="n">
@@ -7609,7 +7609,7 @@
       </c>
       <c r="M109" t="inlineStr">
         <is>
-          <t>Ustadh Hainur</t>
+          <t>Ustadha Hainur</t>
         </is>
       </c>
       <c r="N109" t="n">
@@ -7675,7 +7675,7 @@
       </c>
       <c r="M110" t="inlineStr">
         <is>
-          <t>Ustadh Hainur</t>
+          <t>Ustadha Hainur</t>
         </is>
       </c>
       <c r="N110" t="n">
@@ -8929,7 +8929,7 @@
       </c>
       <c r="M129" t="inlineStr">
         <is>
-          <t>Ustadh Hainur</t>
+          <t>Ustadha Hainur</t>
         </is>
       </c>
       <c r="N129" t="n">
@@ -9061,7 +9061,7 @@
       </c>
       <c r="M131" t="inlineStr">
         <is>
-          <t>Ustadh Hainur</t>
+          <t>Ustadha Hainur</t>
         </is>
       </c>
       <c r="N131" t="n">
@@ -9127,7 +9127,7 @@
       </c>
       <c r="M132" t="inlineStr">
         <is>
-          <t>Ustadh Hainur</t>
+          <t>Ustadha Hainur</t>
         </is>
       </c>
       <c r="N132" t="n">
@@ -12361,7 +12361,7 @@
       </c>
       <c r="M181" t="inlineStr">
         <is>
-          <t>Ustadh Hainur</t>
+          <t>Ustadha Hainur</t>
         </is>
       </c>
       <c r="N181" t="n">
@@ -13945,7 +13945,7 @@
       </c>
       <c r="M205" t="inlineStr">
         <is>
-          <t>Ustadh Hainur</t>
+          <t>Ustadha Hainur</t>
         </is>
       </c>
       <c r="N205" t="n">
@@ -13971,12 +13971,12 @@
       </c>
       <c r="E206" t="inlineStr">
         <is>
-          <t>sec_grade_2_talha_ibn_ubaydullah_1st_shift</t>
+          <t>sec_grade_3_habib_ibn_zayd_al_ansari_1st_shift_girls</t>
         </is>
       </c>
       <c r="F206" t="inlineStr">
         <is>
-          <t>GRADE 2 - TALHA IBN UBAYDULLAH (1ST SHIFT)</t>
+          <t>Grade 3 - HABIB IBN ZAYD AL-ANSARI (1ST SHIFT) - GIRLS</t>
         </is>
       </c>
       <c r="G206" t="inlineStr">
@@ -13986,7 +13986,7 @@
       </c>
       <c r="H206" t="inlineStr">
         <is>
-          <t>Grade 2</t>
+          <t>Grade 3</t>
         </is>
       </c>
       <c r="I206" t="inlineStr">
@@ -13996,22 +13996,22 @@
       </c>
       <c r="J206" t="inlineStr">
         <is>
-          <t>subj_arabic</t>
+          <t>subj_qur_an</t>
         </is>
       </c>
       <c r="K206" t="inlineStr">
         <is>
-          <t>Arabic</t>
+          <t>Qur'an</t>
         </is>
       </c>
       <c r="L206" t="inlineStr">
         <is>
-          <t>tchr_hainur</t>
+          <t>tchr_obaydah</t>
         </is>
       </c>
       <c r="M206" t="inlineStr">
         <is>
-          <t>Ustadh Hainur</t>
+          <t>Ustadh Obaydah</t>
         </is>
       </c>
       <c r="N206" t="n">
@@ -14037,12 +14037,12 @@
       </c>
       <c r="E207" t="inlineStr">
         <is>
-          <t>sec_grade_3_habib_ibn_zayd_al_ansari_1st_shift_girls</t>
+          <t>sec_grade_3_salman_al_farsi_1st_shift_mix</t>
         </is>
       </c>
       <c r="F207" t="inlineStr">
         <is>
-          <t>Grade 3 - HABIB IBN ZAYD AL-ANSARI (1ST SHIFT) - GIRLS</t>
+          <t>GRADE 3 - SALMAN AL FARSI (1ST SHIFT) MIX</t>
         </is>
       </c>
       <c r="G207" t="inlineStr">
@@ -14062,22 +14062,22 @@
       </c>
       <c r="J207" t="inlineStr">
         <is>
-          <t>subj_qur_an</t>
+          <t>subj_gmrc</t>
         </is>
       </c>
       <c r="K207" t="inlineStr">
         <is>
-          <t>Qur'an</t>
+          <t>GMRC</t>
         </is>
       </c>
       <c r="L207" t="inlineStr">
         <is>
-          <t>tchr_obaydah</t>
+          <t>tchr_zuhora</t>
         </is>
       </c>
       <c r="M207" t="inlineStr">
         <is>
-          <t>Ustadh Obaydah</t>
+          <t>Teacher Zuhora</t>
         </is>
       </c>
       <c r="N207" t="n">
@@ -14103,12 +14103,12 @@
       </c>
       <c r="E208" t="inlineStr">
         <is>
-          <t>sec_grade_3_salman_al_farsi_1st_shift_mix</t>
+          <t>sec_grade_3_ammar_ibn_yasir_1st_shift_boys</t>
         </is>
       </c>
       <c r="F208" t="inlineStr">
         <is>
-          <t>GRADE 3 - SALMAN AL FARSI (1ST SHIFT) MIX</t>
+          <t>GRADE 3 -AMMAR IBN YASIR (1ST SHIFT) - BOYS</t>
         </is>
       </c>
       <c r="G208" t="inlineStr">
@@ -14128,22 +14128,22 @@
       </c>
       <c r="J208" t="inlineStr">
         <is>
-          <t>subj_gmrc</t>
+          <t>subj_makabansa</t>
         </is>
       </c>
       <c r="K208" t="inlineStr">
         <is>
-          <t>GMRC</t>
+          <t>Makabansa</t>
         </is>
       </c>
       <c r="L208" t="inlineStr">
         <is>
-          <t>tchr_zuhora</t>
+          <t>tchr_zara</t>
         </is>
       </c>
       <c r="M208" t="inlineStr">
         <is>
-          <t>Teacher Zuhora</t>
+          <t>Teacher Zara</t>
         </is>
       </c>
       <c r="N208" t="n">
@@ -14169,12 +14169,12 @@
       </c>
       <c r="E209" t="inlineStr">
         <is>
-          <t>sec_grade_3_ammar_ibn_yasir_1st_shift_boys</t>
+          <t>sec_grade_4_abdur_rahman_ibn_awf_1st_shift</t>
         </is>
       </c>
       <c r="F209" t="inlineStr">
         <is>
-          <t>GRADE 3 -AMMAR IBN YASIR (1ST SHIFT) - BOYS</t>
+          <t>GRADE 4 - ABDUR RAHMAN IBN AWF (1ST SHIFT)</t>
         </is>
       </c>
       <c r="G209" t="inlineStr">
@@ -14184,7 +14184,7 @@
       </c>
       <c r="H209" t="inlineStr">
         <is>
-          <t>Grade 3</t>
+          <t>Grade 4</t>
         </is>
       </c>
       <c r="I209" t="inlineStr">
@@ -14194,22 +14194,22 @@
       </c>
       <c r="J209" t="inlineStr">
         <is>
-          <t>subj_makabansa</t>
+          <t>subj_science</t>
         </is>
       </c>
       <c r="K209" t="inlineStr">
         <is>
-          <t>Makabansa</t>
+          <t>Science</t>
         </is>
       </c>
       <c r="L209" t="inlineStr">
         <is>
-          <t>tchr_zara</t>
+          <t>tchr_anna</t>
         </is>
       </c>
       <c r="M209" t="inlineStr">
         <is>
-          <t>Teacher Zara</t>
+          <t>Teacher Anna</t>
         </is>
       </c>
       <c r="N209" t="n">
@@ -14235,12 +14235,12 @@
       </c>
       <c r="E210" t="inlineStr">
         <is>
-          <t>sec_grade_4_abdur_rahman_ibn_awf_1st_shift</t>
+          <t>sec_grade_4_hakim_ibn_hazm_1st_shift</t>
         </is>
       </c>
       <c r="F210" t="inlineStr">
         <is>
-          <t>GRADE 4 - ABDUR RAHMAN IBN AWF (1ST SHIFT)</t>
+          <t>GRADE 4 - HAKIM IBN HAZM(1ST SHIFT)</t>
         </is>
       </c>
       <c r="G210" t="inlineStr">
@@ -14260,22 +14260,22 @@
       </c>
       <c r="J210" t="inlineStr">
         <is>
-          <t>subj_science</t>
+          <t>subj_tle</t>
         </is>
       </c>
       <c r="K210" t="inlineStr">
         <is>
-          <t>Science</t>
+          <t>TLE</t>
         </is>
       </c>
       <c r="L210" t="inlineStr">
         <is>
-          <t>tchr_anna</t>
+          <t>tchr_monisa</t>
         </is>
       </c>
       <c r="M210" t="inlineStr">
         <is>
-          <t>Teacher Anna</t>
+          <t>Teacher Monisa</t>
         </is>
       </c>
       <c r="N210" t="n">
@@ -14301,12 +14301,12 @@
       </c>
       <c r="E211" t="inlineStr">
         <is>
-          <t>sec_grade_4_hakim_ibn_hazm_1st_shift</t>
+          <t>sec_grade_4_usayd_ibn_hudhayr_1st_shift_mix</t>
         </is>
       </c>
       <c r="F211" t="inlineStr">
         <is>
-          <t>GRADE 4 - HAKIM IBN HAZM(1ST SHIFT)</t>
+          <t>GRADE 4 - USAYD IBN HUDHAYR (1ST SHIFT) - MIX</t>
         </is>
       </c>
       <c r="G211" t="inlineStr">
@@ -14326,22 +14326,22 @@
       </c>
       <c r="J211" t="inlineStr">
         <is>
-          <t>subj_tle</t>
+          <t>subj_science</t>
         </is>
       </c>
       <c r="K211" t="inlineStr">
         <is>
-          <t>TLE</t>
+          <t>Science</t>
         </is>
       </c>
       <c r="L211" t="inlineStr">
         <is>
-          <t>tchr_monisa</t>
+          <t>tchr_saimonah</t>
         </is>
       </c>
       <c r="M211" t="inlineStr">
         <is>
-          <t>Teacher Monisa</t>
+          <t>Teacher Saimonah</t>
         </is>
       </c>
       <c r="N211" t="n">
@@ -14367,12 +14367,12 @@
       </c>
       <c r="E212" t="inlineStr">
         <is>
-          <t>sec_grade_4_usayd_ibn_hudhayr_1st_shift_mix</t>
+          <t>sec_grade_5_ayyash_ibn_abi_rabi_ah_1st_shift</t>
         </is>
       </c>
       <c r="F212" t="inlineStr">
         <is>
-          <t>GRADE 4 - USAYD IBN HUDHAYR (1ST SHIFT) - MIX</t>
+          <t>GRADE 5 - AYYASH IBN ABI RABI'AH(1ST SHIFT)</t>
         </is>
       </c>
       <c r="G212" t="inlineStr">
@@ -14382,7 +14382,7 @@
       </c>
       <c r="H212" t="inlineStr">
         <is>
-          <t>Grade 4</t>
+          <t>Grade 5</t>
         </is>
       </c>
       <c r="I212" t="inlineStr">
@@ -14392,22 +14392,22 @@
       </c>
       <c r="J212" t="inlineStr">
         <is>
-          <t>subj_science</t>
+          <t>subj_fil5</t>
         </is>
       </c>
       <c r="K212" t="inlineStr">
         <is>
-          <t>Science</t>
+          <t>Fil5</t>
         </is>
       </c>
       <c r="L212" t="inlineStr">
         <is>
-          <t>tchr_saimonah</t>
+          <t>tchr_jenny</t>
         </is>
       </c>
       <c r="M212" t="inlineStr">
         <is>
-          <t>Teacher Saimonah</t>
+          <t>Teacher Jenny</t>
         </is>
       </c>
       <c r="N212" t="n">
@@ -14433,12 +14433,12 @@
       </c>
       <c r="E213" t="inlineStr">
         <is>
-          <t>sec_grade_5_ayyash_ibn_abi_rabi_ah_1st_shift</t>
+          <t>sec_grade_5_hamza_ibn_abdul_1st_shift</t>
         </is>
       </c>
       <c r="F213" t="inlineStr">
         <is>
-          <t>GRADE 5 - AYYASH IBN ABI RABI'AH(1ST SHIFT)</t>
+          <t>GRADE 5 - HAMZA IBN ABDUL (1ST SHIFT)</t>
         </is>
       </c>
       <c r="G213" t="inlineStr">
@@ -14458,22 +14458,22 @@
       </c>
       <c r="J213" t="inlineStr">
         <is>
-          <t>subj_fil5</t>
+          <t>subj_math</t>
         </is>
       </c>
       <c r="K213" t="inlineStr">
         <is>
-          <t>Fil5</t>
+          <t>Math</t>
         </is>
       </c>
       <c r="L213" t="inlineStr">
         <is>
-          <t>tchr_jenny</t>
+          <t>tchr_fhairudz</t>
         </is>
       </c>
       <c r="M213" t="inlineStr">
         <is>
-          <t>Teacher Jenny</t>
+          <t>Teacher Fhairudz</t>
         </is>
       </c>
       <c r="N213" t="n">
@@ -14499,12 +14499,12 @@
       </c>
       <c r="E214" t="inlineStr">
         <is>
-          <t>sec_grade_5_hamza_ibn_abdul_1st_shift</t>
+          <t>sec_grade_5_muhammad_ibn_maslamah_1st_shift</t>
         </is>
       </c>
       <c r="F214" t="inlineStr">
         <is>
-          <t>GRADE 5 - HAMZA IBN ABDUL (1ST SHIFT)</t>
+          <t>GRADE 5 - MUHAMMAD IBN MASLAMAH (1ST SHIFT)</t>
         </is>
       </c>
       <c r="G214" t="inlineStr">
@@ -14524,22 +14524,22 @@
       </c>
       <c r="J214" t="inlineStr">
         <is>
-          <t>subj_math</t>
+          <t>subj_arabic</t>
         </is>
       </c>
       <c r="K214" t="inlineStr">
         <is>
-          <t>Math</t>
+          <t>Arabic</t>
         </is>
       </c>
       <c r="L214" t="inlineStr">
         <is>
-          <t>tchr_fhairudz</t>
+          <t>tchr_abdul_karim</t>
         </is>
       </c>
       <c r="M214" t="inlineStr">
         <is>
-          <t>Teacher Fhairudz</t>
+          <t>Alim Abdul Karim</t>
         </is>
       </c>
       <c r="N214" t="n">
@@ -14565,12 +14565,12 @@
       </c>
       <c r="E215" t="inlineStr">
         <is>
-          <t>sec_grade_5_muhammad_ibn_maslamah_1st_shift</t>
+          <t>sec_grade_6_abbas_ibn_abd_al_muttalib_1st_shift</t>
         </is>
       </c>
       <c r="F215" t="inlineStr">
         <is>
-          <t>GRADE 5 - MUHAMMAD IBN MASLAMAH (1ST SHIFT)</t>
+          <t>GRADE 6 - ABBAS IBN ABD AL-MUTTALIB (1ST SHIFT)</t>
         </is>
       </c>
       <c r="G215" t="inlineStr">
@@ -14580,7 +14580,7 @@
       </c>
       <c r="H215" t="inlineStr">
         <is>
-          <t>Grade 5</t>
+          <t>Grade 6</t>
         </is>
       </c>
       <c r="I215" t="inlineStr">
@@ -14600,12 +14600,12 @@
       </c>
       <c r="L215" t="inlineStr">
         <is>
-          <t>tchr_abdul_karim</t>
+          <t>tchr_ali</t>
         </is>
       </c>
       <c r="M215" t="inlineStr">
         <is>
-          <t>Alim Abdul Karim</t>
+          <t>Ustadh Ali</t>
         </is>
       </c>
       <c r="N215" t="n">
@@ -14626,17 +14626,17 @@
       </c>
       <c r="D216" t="inlineStr">
         <is>
-          <t>01:50 PM – 02:50 PM</t>
+          <t>01:50 PM – 04:10 PM</t>
         </is>
       </c>
       <c r="E216" t="inlineStr">
         <is>
-          <t>sec_grade_6_abbas_ibn_abd_al_muttalib_1st_shift</t>
+          <t>sec_grade_6_abdullah_ibn_salaam_1st_shift</t>
         </is>
       </c>
       <c r="F216" t="inlineStr">
         <is>
-          <t>GRADE 6 - ABBAS IBN ABD AL-MUTTALIB (1ST SHIFT)</t>
+          <t>GRADE 6 - ABDULLAH IBN SALAAM (1ST SHIFT)</t>
         </is>
       </c>
       <c r="G216" t="inlineStr">
@@ -14656,26 +14656,26 @@
       </c>
       <c r="J216" t="inlineStr">
         <is>
-          <t>subj_arabic</t>
+          <t>subj_math</t>
         </is>
       </c>
       <c r="K216" t="inlineStr">
         <is>
-          <t>Arabic</t>
+          <t>Math</t>
         </is>
       </c>
       <c r="L216" t="inlineStr">
         <is>
-          <t>tchr_ali</t>
+          <t>tchr_katrina</t>
         </is>
       </c>
       <c r="M216" t="inlineStr">
         <is>
-          <t>Ustadh Ali</t>
+          <t>Teacher Katrina</t>
         </is>
       </c>
       <c r="N216" t="n">
-        <v>60</v>
+        <v>120</v>
       </c>
     </row>
     <row r="217">
@@ -14692,27 +14692,27 @@
       </c>
       <c r="D217" t="inlineStr">
         <is>
-          <t>01:50 PM – 04:10 PM</t>
+          <t>01:50 PM – 02:50 PM</t>
         </is>
       </c>
       <c r="E217" t="inlineStr">
         <is>
-          <t>sec_grade_6_abdullah_ibn_salaam_1st_shift</t>
+          <t>sec_grade_7_abu_sufyan_ibn_al_harith_1st_shift_boys</t>
         </is>
       </c>
       <c r="F217" t="inlineStr">
         <is>
-          <t>GRADE 6 - ABDULLAH IBN SALAAM (1ST SHIFT)</t>
+          <t>GRADE 7 - ABU SUFYAN IBN AL-HARITH (1ST SHIFT) BOYS</t>
         </is>
       </c>
       <c r="G217" t="inlineStr">
         <is>
-          <t>Elementary</t>
+          <t>Junior High School</t>
         </is>
       </c>
       <c r="H217" t="inlineStr">
         <is>
-          <t>Grade 6</t>
+          <t>Grade 7</t>
         </is>
       </c>
       <c r="I217" t="inlineStr">
@@ -14722,26 +14722,26 @@
       </c>
       <c r="J217" t="inlineStr">
         <is>
-          <t>subj_math</t>
+          <t>subj_tle</t>
         </is>
       </c>
       <c r="K217" t="inlineStr">
         <is>
-          <t>Math</t>
+          <t>TLE</t>
         </is>
       </c>
       <c r="L217" t="inlineStr">
         <is>
-          <t>tchr_katrina</t>
+          <t>tchr_halnaisa</t>
         </is>
       </c>
       <c r="M217" t="inlineStr">
         <is>
-          <t>Teacher Katrina</t>
+          <t>Teacher Halnaisa</t>
         </is>
       </c>
       <c r="N217" t="n">
-        <v>120</v>
+        <v>60</v>
       </c>
     </row>
     <row r="218">
@@ -14763,12 +14763,12 @@
       </c>
       <c r="E218" t="inlineStr">
         <is>
-          <t>sec_grade_7_abu_sufyan_ibn_al_harith_1st_shift_boys</t>
+          <t>sec_grade_7_usama_ibn_zayd_1st_shift_girls</t>
         </is>
       </c>
       <c r="F218" t="inlineStr">
         <is>
-          <t>GRADE 7 - ABU SUFYAN IBN AL-HARITH (1ST SHIFT) BOYS</t>
+          <t>GRADE 7 - USAMA IBN ZAYD (1ST SHIFT) GIRLS</t>
         </is>
       </c>
       <c r="G218" t="inlineStr">
@@ -14788,22 +14788,22 @@
       </c>
       <c r="J218" t="inlineStr">
         <is>
-          <t>subj_tle</t>
+          <t>subj_shaf</t>
         </is>
       </c>
       <c r="K218" t="inlineStr">
         <is>
-          <t>TLE</t>
+          <t>SHAF</t>
         </is>
       </c>
       <c r="L218" t="inlineStr">
         <is>
-          <t>tchr_halnaisa</t>
+          <t>tchr_samsuddin</t>
         </is>
       </c>
       <c r="M218" t="inlineStr">
         <is>
-          <t>Teacher Halnaisa</t>
+          <t>Alim Samsuddin</t>
         </is>
       </c>
       <c r="N218" t="n">
@@ -14829,12 +14829,12 @@
       </c>
       <c r="E219" t="inlineStr">
         <is>
-          <t>sec_grade_7_usama_ibn_zayd_1st_shift_girls</t>
+          <t>sec_grade_8_sa_ad_ibn_mua_dh_1st_shift_girls</t>
         </is>
       </c>
       <c r="F219" t="inlineStr">
         <is>
-          <t>GRADE 7 - USAMA IBN ZAYD (1ST SHIFT) GIRLS</t>
+          <t>GRADE 8 - SA'AD IBN MUA'DH (1ST SHIFT) - GIRLS</t>
         </is>
       </c>
       <c r="G219" t="inlineStr">
@@ -14844,7 +14844,7 @@
       </c>
       <c r="H219" t="inlineStr">
         <is>
-          <t>Grade 7</t>
+          <t>Grade 8</t>
         </is>
       </c>
       <c r="I219" t="inlineStr">
@@ -14854,22 +14854,22 @@
       </c>
       <c r="J219" t="inlineStr">
         <is>
-          <t>subj_shaf</t>
+          <t>subj_mapeh</t>
         </is>
       </c>
       <c r="K219" t="inlineStr">
         <is>
-          <t>SHAF</t>
+          <t>MAPEH</t>
         </is>
       </c>
       <c r="L219" t="inlineStr">
         <is>
-          <t>tchr_samsuddin</t>
+          <t>tchr_franchette</t>
         </is>
       </c>
       <c r="M219" t="inlineStr">
         <is>
-          <t>Alim Samsuddin</t>
+          <t>Teacher Franchette</t>
         </is>
       </c>
       <c r="N219" t="n">
@@ -14890,17 +14890,17 @@
       </c>
       <c r="D220" t="inlineStr">
         <is>
-          <t>01:50 PM – 02:50 PM</t>
+          <t>01:50 PM – 04:10 PM</t>
         </is>
       </c>
       <c r="E220" t="inlineStr">
         <is>
-          <t>sec_grade_8_sa_ad_ibn_mua_dh_1st_shift_girls</t>
+          <t>sec_grade_9_abu_hurayrah_1st_shift_girls</t>
         </is>
       </c>
       <c r="F220" t="inlineStr">
         <is>
-          <t>GRADE 8 - SA'AD IBN MUA'DH (1ST SHIFT) - GIRLS</t>
+          <t>GRADE 9 - ABU HURAYRAH (1ST SHIFT) GIRLS</t>
         </is>
       </c>
       <c r="G220" t="inlineStr">
@@ -14910,7 +14910,7 @@
       </c>
       <c r="H220" t="inlineStr">
         <is>
-          <t>Grade 8</t>
+          <t>Grade 9</t>
         </is>
       </c>
       <c r="I220" t="inlineStr">
@@ -14920,26 +14920,26 @@
       </c>
       <c r="J220" t="inlineStr">
         <is>
-          <t>subj_mapeh</t>
+          <t>subj_math</t>
         </is>
       </c>
       <c r="K220" t="inlineStr">
         <is>
-          <t>MAPEH</t>
+          <t>Math</t>
         </is>
       </c>
       <c r="L220" t="inlineStr">
         <is>
-          <t>tchr_franchette</t>
+          <t>tchr_jhelyn</t>
         </is>
       </c>
       <c r="M220" t="inlineStr">
         <is>
-          <t>Teacher Franchette</t>
+          <t>Teacher Jhelyn</t>
         </is>
       </c>
       <c r="N220" t="n">
-        <v>60</v>
+        <v>120</v>
       </c>
     </row>
     <row r="221">
@@ -14952,31 +14952,31 @@
         </is>
       </c>
       <c r="C221" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D221" t="inlineStr">
         <is>
-          <t>01:50 PM – 04:10 PM</t>
+          <t>03:10 PM – 04:10 PM</t>
         </is>
       </c>
       <c r="E221" t="inlineStr">
         <is>
-          <t>sec_grade_9_abu_hurayrah_1st_shift_girls</t>
+          <t>sec_grade_1_hudhayfah_ibn_al_yam_1st_shift</t>
         </is>
       </c>
       <c r="F221" t="inlineStr">
         <is>
-          <t>GRADE 9 - ABU HURAYRAH (1ST SHIFT) GIRLS</t>
+          <t>GRADE 1 - HUDHAYFAH IBN AL-YAM (1ST SHIFT)</t>
         </is>
       </c>
       <c r="G221" t="inlineStr">
         <is>
-          <t>Junior High School</t>
+          <t>Elementary</t>
         </is>
       </c>
       <c r="H221" t="inlineStr">
         <is>
-          <t>Grade 9</t>
+          <t>Grade 1</t>
         </is>
       </c>
       <c r="I221" t="inlineStr">
@@ -14996,16 +14996,16 @@
       </c>
       <c r="L221" t="inlineStr">
         <is>
-          <t>tchr_jhelyn</t>
+          <t>tchr_joanna</t>
         </is>
       </c>
       <c r="M221" t="inlineStr">
         <is>
-          <t>Teacher Jhelyn</t>
+          <t>Teacher Joanna</t>
         </is>
       </c>
       <c r="N221" t="n">
-        <v>120</v>
+        <v>60</v>
       </c>
     </row>
     <row r="222">
@@ -15018,7 +15018,7 @@
         </is>
       </c>
       <c r="C222" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D222" t="inlineStr">
         <is>
@@ -15027,12 +15027,12 @@
       </c>
       <c r="E222" t="inlineStr">
         <is>
-          <t>sec_grade_1_hudhayfah_ibn_al_yam_1st_shift</t>
+          <t>sec_grade_1_sa_ad_ibn_abi_waqqaas_2nd_shift</t>
         </is>
       </c>
       <c r="F222" t="inlineStr">
         <is>
-          <t>GRADE 1 - HUDHAYFAH IBN AL-YAM (1ST SHIFT)</t>
+          <t>GRADE 1 - SA'AD IBN ABI WAQQAAS (2ND SHIFT)</t>
         </is>
       </c>
       <c r="G222" t="inlineStr">
@@ -15047,27 +15047,27 @@
       </c>
       <c r="I222" t="inlineStr">
         <is>
-          <t>ODL - 1ST SHIFT</t>
+          <t>ODL - 2ND SHIFT</t>
         </is>
       </c>
       <c r="J222" t="inlineStr">
         <is>
-          <t>subj_math</t>
+          <t>subj_arabic</t>
         </is>
       </c>
       <c r="K222" t="inlineStr">
         <is>
-          <t>Math</t>
+          <t>Arabic</t>
         </is>
       </c>
       <c r="L222" t="inlineStr">
         <is>
-          <t>tchr_joanna</t>
+          <t>tchr_hainur</t>
         </is>
       </c>
       <c r="M222" t="inlineStr">
         <is>
-          <t>Teacher Joanna</t>
+          <t>Ustadha Hainur</t>
         </is>
       </c>
       <c r="N222" t="n">
@@ -15093,12 +15093,12 @@
       </c>
       <c r="E223" t="inlineStr">
         <is>
-          <t>sec_grade_1_sa_ad_ibn_abi_waqqaas_2nd_shift</t>
+          <t>sec_grade_1_suhayb_ar_rumi_2nd_shift</t>
         </is>
       </c>
       <c r="F223" t="inlineStr">
         <is>
-          <t>GRADE 1 - SA'AD IBN ABI WAQQAAS (2ND SHIFT)</t>
+          <t>GRADE 1 - SUHAYB AR-RUMI (2ND SHIFT)</t>
         </is>
       </c>
       <c r="G223" t="inlineStr">
@@ -15118,22 +15118,22 @@
       </c>
       <c r="J223" t="inlineStr">
         <is>
-          <t>subj_arabic</t>
+          <t>subj_language</t>
         </is>
       </c>
       <c r="K223" t="inlineStr">
         <is>
-          <t>Arabic</t>
+          <t>Language</t>
         </is>
       </c>
       <c r="L223" t="inlineStr">
         <is>
-          <t>tchr_hainur</t>
+          <t>tchr_sahdia</t>
         </is>
       </c>
       <c r="M223" t="inlineStr">
         <is>
-          <t>Ustadh Hainur</t>
+          <t>Teacher Sahdia</t>
         </is>
       </c>
       <c r="N223" t="n">
@@ -15159,22 +15159,22 @@
       </c>
       <c r="E224" t="inlineStr">
         <is>
-          <t>sec_grade_1_suhayb_ar_rumi_2nd_shift</t>
+          <t>sec_grade_10_abu_ayyub_al_ansari_2nd_shift_boys</t>
         </is>
       </c>
       <c r="F224" t="inlineStr">
         <is>
-          <t>GRADE 1 - SUHAYB AR-RUMI (2ND SHIFT)</t>
+          <t>GRADE 10 - ABU AYYUB AL-ANSARI (2ND SHIFT) BOYS</t>
         </is>
       </c>
       <c r="G224" t="inlineStr">
         <is>
-          <t>Elementary</t>
+          <t>Junior High School</t>
         </is>
       </c>
       <c r="H224" t="inlineStr">
         <is>
-          <t>Grade 1</t>
+          <t>Grade 10</t>
         </is>
       </c>
       <c r="I224" t="inlineStr">
@@ -15184,22 +15184,22 @@
       </c>
       <c r="J224" t="inlineStr">
         <is>
-          <t>subj_language</t>
+          <t>subj_qur_an</t>
         </is>
       </c>
       <c r="K224" t="inlineStr">
         <is>
-          <t>Language</t>
+          <t>Qur'an</t>
         </is>
       </c>
       <c r="L224" t="inlineStr">
         <is>
-          <t>tchr_sahdia</t>
+          <t>tchr_abdulwahab</t>
         </is>
       </c>
       <c r="M224" t="inlineStr">
         <is>
-          <t>Teacher Sahdia</t>
+          <t>Alim Abdulwahab</t>
         </is>
       </c>
       <c r="N224" t="n">
@@ -15216,7 +15216,7 @@
         </is>
       </c>
       <c r="C225" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D225" t="inlineStr">
         <is>
@@ -15225,12 +15225,12 @@
       </c>
       <c r="E225" t="inlineStr">
         <is>
-          <t>sec_grade_10_abu_ayyub_al_ansari_2nd_shift_boys</t>
+          <t>sec_grade_10_utbah_ibn_ghazwan_1st_shift_girls</t>
         </is>
       </c>
       <c r="F225" t="inlineStr">
         <is>
-          <t>GRADE 10 - ABU AYYUB AL-ANSARI (2ND SHIFT) BOYS</t>
+          <t>GRADE 10 - UTBAH IBN GHAZWAN (1ST SHIFT) GIRLS</t>
         </is>
       </c>
       <c r="G225" t="inlineStr">
@@ -15245,27 +15245,27 @@
       </c>
       <c r="I225" t="inlineStr">
         <is>
-          <t>ODL - 2ND SHIFT</t>
+          <t>ODL - 1ST SHIFT</t>
         </is>
       </c>
       <c r="J225" t="inlineStr">
         <is>
-          <t>subj_qur_an</t>
+          <t>subj_english</t>
         </is>
       </c>
       <c r="K225" t="inlineStr">
         <is>
-          <t>Qur'an</t>
+          <t>English</t>
         </is>
       </c>
       <c r="L225" t="inlineStr">
         <is>
-          <t>tchr_abdulwahab</t>
+          <t>tchr_norhaima</t>
         </is>
       </c>
       <c r="M225" t="inlineStr">
         <is>
-          <t>Alim Abdulwahab</t>
+          <t>Teacher Norhaima</t>
         </is>
       </c>
       <c r="N225" t="n">
@@ -15282,7 +15282,7 @@
         </is>
       </c>
       <c r="C226" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D226" t="inlineStr">
         <is>
@@ -15291,47 +15291,47 @@
       </c>
       <c r="E226" t="inlineStr">
         <is>
-          <t>sec_grade_10_utbah_ibn_ghazwan_1st_shift_girls</t>
+          <t>sec_grade_11_2nd_shift_boys</t>
         </is>
       </c>
       <c r="F226" t="inlineStr">
         <is>
-          <t>GRADE 10 - UTBAH IBN GHAZWAN (1ST SHIFT) GIRLS</t>
+          <t>GRADE 11 (2ND SHIFT BOYS)</t>
         </is>
       </c>
       <c r="G226" t="inlineStr">
         <is>
-          <t>Junior High School</t>
+          <t>Senior High School</t>
         </is>
       </c>
       <c r="H226" t="inlineStr">
         <is>
-          <t>Grade 10</t>
+          <t>Grade 11</t>
         </is>
       </c>
       <c r="I226" t="inlineStr">
         <is>
-          <t>ODL - 1ST SHIFT</t>
+          <t>ODL - 2ND SHIFT</t>
         </is>
       </c>
       <c r="J226" t="inlineStr">
         <is>
-          <t>subj_english</t>
+          <t>subj_mabisang_komunikasyon</t>
         </is>
       </c>
       <c r="K226" t="inlineStr">
         <is>
-          <t>English</t>
+          <t>Mabisang Komunikasyon</t>
         </is>
       </c>
       <c r="L226" t="inlineStr">
         <is>
-          <t>tchr_norhaima</t>
+          <t>tchr_nadzra</t>
         </is>
       </c>
       <c r="M226" t="inlineStr">
         <is>
-          <t>Teacher Norhaima</t>
+          <t>Teacher Nadzra</t>
         </is>
       </c>
       <c r="N226" t="n">
@@ -15357,22 +15357,22 @@
       </c>
       <c r="E227" t="inlineStr">
         <is>
-          <t>sec_grade_11_2nd_shift_boys</t>
+          <t>sec_grade_2_saeed_ibn_zayd_2nd_shift</t>
         </is>
       </c>
       <c r="F227" t="inlineStr">
         <is>
-          <t>GRADE 11 (2ND SHIFT BOYS)</t>
+          <t>GRADE 2 - SAEED IBN ZAYD (2ND SHIFT)</t>
         </is>
       </c>
       <c r="G227" t="inlineStr">
         <is>
-          <t>Senior High School</t>
+          <t>Elementary</t>
         </is>
       </c>
       <c r="H227" t="inlineStr">
         <is>
-          <t>Grade 11</t>
+          <t>Grade 2</t>
         </is>
       </c>
       <c r="I227" t="inlineStr">
@@ -15382,22 +15382,22 @@
       </c>
       <c r="J227" t="inlineStr">
         <is>
-          <t>subj_mabisang_komunikasyon</t>
+          <t>subj_filipino</t>
         </is>
       </c>
       <c r="K227" t="inlineStr">
         <is>
-          <t>Mabisang Komunikasyon</t>
+          <t>Filipino</t>
         </is>
       </c>
       <c r="L227" t="inlineStr">
         <is>
-          <t>tchr_nadzra</t>
+          <t>tchr_zuhora</t>
         </is>
       </c>
       <c r="M227" t="inlineStr">
         <is>
-          <t>Teacher Nadzra</t>
+          <t>Teacher Zuhora</t>
         </is>
       </c>
       <c r="N227" t="n">
@@ -15423,12 +15423,12 @@
       </c>
       <c r="E228" t="inlineStr">
         <is>
-          <t>sec_grade_2_saeed_ibn_zayd_2nd_shift</t>
+          <t>sec_grade_3_as_ad_ibn_zurarah_2nd_shift_mix</t>
         </is>
       </c>
       <c r="F228" t="inlineStr">
         <is>
-          <t>GRADE 2 - SAEED IBN ZAYD (2ND SHIFT)</t>
+          <t>GRADE 3 - AS'AD IBN ZURARAH (2ND SHIFT) MIX</t>
         </is>
       </c>
       <c r="G228" t="inlineStr">
@@ -15438,7 +15438,7 @@
       </c>
       <c r="H228" t="inlineStr">
         <is>
-          <t>Grade 2</t>
+          <t>Grade 3</t>
         </is>
       </c>
       <c r="I228" t="inlineStr">
@@ -15448,22 +15448,22 @@
       </c>
       <c r="J228" t="inlineStr">
         <is>
-          <t>subj_filipino</t>
+          <t>subj_gmrc</t>
         </is>
       </c>
       <c r="K228" t="inlineStr">
         <is>
-          <t>Filipino</t>
+          <t>GMRC</t>
         </is>
       </c>
       <c r="L228" t="inlineStr">
         <is>
-          <t>tchr_zuhora</t>
+          <t>tchr_saliha</t>
         </is>
       </c>
       <c r="M228" t="inlineStr">
         <is>
-          <t>Teacher Zuhora</t>
+          <t>Ustadha Saliha</t>
         </is>
       </c>
       <c r="N228" t="n">
@@ -15480,7 +15480,7 @@
         </is>
       </c>
       <c r="C229" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D229" t="inlineStr">
         <is>
@@ -15489,12 +15489,12 @@
       </c>
       <c r="E229" t="inlineStr">
         <is>
-          <t>sec_grade_3_as_ad_ibn_zurarah_2nd_shift_mix</t>
+          <t>sec_grade_3_habib_ibn_zayd_al_ansari_1st_shift_girls</t>
         </is>
       </c>
       <c r="F229" t="inlineStr">
         <is>
-          <t>GRADE 3 - AS'AD IBN ZURARAH (2ND SHIFT) MIX</t>
+          <t>Grade 3 - HABIB IBN ZAYD AL-ANSARI (1ST SHIFT) - GIRLS</t>
         </is>
       </c>
       <c r="G229" t="inlineStr">
@@ -15509,7 +15509,7 @@
       </c>
       <c r="I229" t="inlineStr">
         <is>
-          <t>ODL - 2ND SHIFT</t>
+          <t>ODL - 1ST SHIFT</t>
         </is>
       </c>
       <c r="J229" t="inlineStr">
@@ -15524,12 +15524,12 @@
       </c>
       <c r="L229" t="inlineStr">
         <is>
-          <t>tchr_saliha</t>
+          <t>tchr_silfah</t>
         </is>
       </c>
       <c r="M229" t="inlineStr">
         <is>
-          <t>Ustadha Saliha</t>
+          <t>Ustadh Silfah</t>
         </is>
       </c>
       <c r="N229" t="n">
@@ -15555,12 +15555,12 @@
       </c>
       <c r="E230" t="inlineStr">
         <is>
-          <t>sec_grade_3_habib_ibn_zayd_al_ansari_1st_shift_girls</t>
+          <t>sec_grade_3_salman_al_farsi_1st_shift_mix</t>
         </is>
       </c>
       <c r="F230" t="inlineStr">
         <is>
-          <t>Grade 3 - HABIB IBN ZAYD AL-ANSARI (1ST SHIFT) - GIRLS</t>
+          <t>GRADE 3 - SALMAN AL FARSI (1ST SHIFT) MIX</t>
         </is>
       </c>
       <c r="G230" t="inlineStr">
@@ -15580,22 +15580,22 @@
       </c>
       <c r="J230" t="inlineStr">
         <is>
-          <t>subj_gmrc</t>
+          <t>subj_fil3</t>
         </is>
       </c>
       <c r="K230" t="inlineStr">
         <is>
-          <t>GMRC</t>
+          <t>Fil3</t>
         </is>
       </c>
       <c r="L230" t="inlineStr">
         <is>
-          <t>tchr_silfah</t>
+          <t>tchr_jenny</t>
         </is>
       </c>
       <c r="M230" t="inlineStr">
         <is>
-          <t>Ustadh Silfah</t>
+          <t>Teacher Jenny</t>
         </is>
       </c>
       <c r="N230" t="n">
@@ -15612,7 +15612,7 @@
         </is>
       </c>
       <c r="C231" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D231" t="inlineStr">
         <is>
@@ -15621,12 +15621,12 @@
       </c>
       <c r="E231" t="inlineStr">
         <is>
-          <t>sec_grade_3_salman_al_farsi_1st_shift_mix</t>
+          <t>sec_grade_3_thabit_ibn_qays_2nd_shift_boys</t>
         </is>
       </c>
       <c r="F231" t="inlineStr">
         <is>
-          <t>GRADE 3 - SALMAN AL FARSI (1ST SHIFT) MIX</t>
+          <t>GRADE 3 - THABIT IBN QAYS (2ND SHIFT) - BOYS</t>
         </is>
       </c>
       <c r="G231" t="inlineStr">
@@ -15641,27 +15641,27 @@
       </c>
       <c r="I231" t="inlineStr">
         <is>
-          <t>ODL - 1ST SHIFT</t>
+          <t>ODL - 2ND SHIFT</t>
         </is>
       </c>
       <c r="J231" t="inlineStr">
         <is>
-          <t>subj_fil3</t>
+          <t>subj_math</t>
         </is>
       </c>
       <c r="K231" t="inlineStr">
         <is>
-          <t>Fil3</t>
+          <t>Math</t>
         </is>
       </c>
       <c r="L231" t="inlineStr">
         <is>
-          <t>tchr_jenny</t>
+          <t>tchr_jerlyn</t>
         </is>
       </c>
       <c r="M231" t="inlineStr">
         <is>
-          <t>Teacher Jenny</t>
+          <t>Teacher Jerlyn</t>
         </is>
       </c>
       <c r="N231" t="n">
@@ -15687,12 +15687,12 @@
       </c>
       <c r="E232" t="inlineStr">
         <is>
-          <t>sec_grade_3_thabit_ibn_qays_2nd_shift_boys</t>
+          <t>sec_grade_3_zayd_ibn_haritha_2nd_shift_girls</t>
         </is>
       </c>
       <c r="F232" t="inlineStr">
         <is>
-          <t>GRADE 3 - THABIT IBN QAYS (2ND SHIFT) - BOYS</t>
+          <t>GRADE 3 - ZAYD IBN HARITHA (2ND SHIFT) - GIRLS</t>
         </is>
       </c>
       <c r="G232" t="inlineStr">
@@ -15712,22 +15712,22 @@
       </c>
       <c r="J232" t="inlineStr">
         <is>
-          <t>subj_math</t>
+          <t>subj_english</t>
         </is>
       </c>
       <c r="K232" t="inlineStr">
         <is>
-          <t>Math</t>
+          <t>English</t>
         </is>
       </c>
       <c r="L232" t="inlineStr">
         <is>
-          <t>tchr_jerlyn</t>
+          <t>tchr_marham</t>
         </is>
       </c>
       <c r="M232" t="inlineStr">
         <is>
-          <t>Teacher Jerlyn</t>
+          <t>Teacher Marham</t>
         </is>
       </c>
       <c r="N232" t="n">
@@ -15744,7 +15744,7 @@
         </is>
       </c>
       <c r="C233" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D233" t="inlineStr">
         <is>
@@ -15753,12 +15753,12 @@
       </c>
       <c r="E233" t="inlineStr">
         <is>
-          <t>sec_grade_3_zayd_ibn_haritha_2nd_shift_girls</t>
+          <t>sec_grade_3_ammar_ibn_yasir_1st_shift_boys</t>
         </is>
       </c>
       <c r="F233" t="inlineStr">
         <is>
-          <t>GRADE 3 - ZAYD IBN HARITHA (2ND SHIFT) - GIRLS</t>
+          <t>GRADE 3 -AMMAR IBN YASIR (1ST SHIFT) - BOYS</t>
         </is>
       </c>
       <c r="G233" t="inlineStr">
@@ -15773,27 +15773,27 @@
       </c>
       <c r="I233" t="inlineStr">
         <is>
-          <t>ODL - 2ND SHIFT</t>
+          <t>ODL - 1ST SHIFT</t>
         </is>
       </c>
       <c r="J233" t="inlineStr">
         <is>
-          <t>subj_english</t>
+          <t>subj_shaf</t>
         </is>
       </c>
       <c r="K233" t="inlineStr">
         <is>
-          <t>English</t>
+          <t>SHAF</t>
         </is>
       </c>
       <c r="L233" t="inlineStr">
         <is>
-          <t>tchr_marham</t>
+          <t>tchr_ersahad</t>
         </is>
       </c>
       <c r="M233" t="inlineStr">
         <is>
-          <t>Teacher Marham</t>
+          <t>Ustadh Ersahad</t>
         </is>
       </c>
       <c r="N233" t="n">
@@ -15819,12 +15819,12 @@
       </c>
       <c r="E234" t="inlineStr">
         <is>
-          <t>sec_grade_3_ammar_ibn_yasir_1st_shift_boys</t>
+          <t>sec_grade_4_abdur_rahman_ibn_awf_1st_shift</t>
         </is>
       </c>
       <c r="F234" t="inlineStr">
         <is>
-          <t>GRADE 3 -AMMAR IBN YASIR (1ST SHIFT) - BOYS</t>
+          <t>GRADE 4 - ABDUR RAHMAN IBN AWF (1ST SHIFT)</t>
         </is>
       </c>
       <c r="G234" t="inlineStr">
@@ -15834,7 +15834,7 @@
       </c>
       <c r="H234" t="inlineStr">
         <is>
-          <t>Grade 3</t>
+          <t>Grade 4</t>
         </is>
       </c>
       <c r="I234" t="inlineStr">
@@ -15844,22 +15844,22 @@
       </c>
       <c r="J234" t="inlineStr">
         <is>
-          <t>subj_shaf</t>
+          <t>subj_math</t>
         </is>
       </c>
       <c r="K234" t="inlineStr">
         <is>
-          <t>SHAF</t>
+          <t>Math</t>
         </is>
       </c>
       <c r="L234" t="inlineStr">
         <is>
-          <t>tchr_ersahad</t>
+          <t>tchr_arvin</t>
         </is>
       </c>
       <c r="M234" t="inlineStr">
         <is>
-          <t>Ustadh Ersahad</t>
+          <t>Teacher Arvin</t>
         </is>
       </c>
       <c r="N234" t="n">
@@ -15876,7 +15876,7 @@
         </is>
       </c>
       <c r="C235" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D235" t="inlineStr">
         <is>
@@ -15885,12 +15885,12 @@
       </c>
       <c r="E235" t="inlineStr">
         <is>
-          <t>sec_grade_4_abdur_rahman_ibn_awf_1st_shift</t>
+          <t>sec_grade_4_az_zubair_ibn_al_awwaam_2nd_shift</t>
         </is>
       </c>
       <c r="F235" t="inlineStr">
         <is>
-          <t>GRADE 4 - ABDUR RAHMAN IBN AWF (1ST SHIFT)</t>
+          <t>GRADE 4 - AZ ZUBAIR IBN AL AWWAAM (2ND SHIFT)</t>
         </is>
       </c>
       <c r="G235" t="inlineStr">
@@ -15905,27 +15905,27 @@
       </c>
       <c r="I235" t="inlineStr">
         <is>
-          <t>ODL - 1ST SHIFT</t>
+          <t>ODL - 2ND SHIFT</t>
         </is>
       </c>
       <c r="J235" t="inlineStr">
         <is>
-          <t>subj_math</t>
+          <t>subj_filipino</t>
         </is>
       </c>
       <c r="K235" t="inlineStr">
         <is>
-          <t>Math</t>
+          <t>Filipino</t>
         </is>
       </c>
       <c r="L235" t="inlineStr">
         <is>
-          <t>tchr_arvin</t>
+          <t>tchr_norhydie</t>
         </is>
       </c>
       <c r="M235" t="inlineStr">
         <is>
-          <t>Teacher Arvin</t>
+          <t>Teacher Norhydie</t>
         </is>
       </c>
       <c r="N235" t="n">
@@ -15942,7 +15942,7 @@
         </is>
       </c>
       <c r="C236" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D236" t="inlineStr">
         <is>
@@ -15951,12 +15951,12 @@
       </c>
       <c r="E236" t="inlineStr">
         <is>
-          <t>sec_grade_4_az_zubair_ibn_al_awwaam_2nd_shift</t>
+          <t>sec_grade_4_hakim_ibn_hazm_1st_shift</t>
         </is>
       </c>
       <c r="F236" t="inlineStr">
         <is>
-          <t>GRADE 4 - AZ ZUBAIR IBN AL AWWAAM (2ND SHIFT)</t>
+          <t>GRADE 4 - HAKIM IBN HAZM(1ST SHIFT)</t>
         </is>
       </c>
       <c r="G236" t="inlineStr">
@@ -15971,27 +15971,27 @@
       </c>
       <c r="I236" t="inlineStr">
         <is>
-          <t>ODL - 2ND SHIFT</t>
+          <t>ODL - 1ST SHIFT</t>
         </is>
       </c>
       <c r="J236" t="inlineStr">
         <is>
-          <t>subj_filipino</t>
+          <t>subj_math</t>
         </is>
       </c>
       <c r="K236" t="inlineStr">
         <is>
-          <t>Filipino</t>
+          <t>Math</t>
         </is>
       </c>
       <c r="L236" t="inlineStr">
         <is>
-          <t>tchr_norhydie</t>
+          <t>tchr_arvin</t>
         </is>
       </c>
       <c r="M236" t="inlineStr">
         <is>
-          <t>Teacher Norhydie</t>
+          <t>Teacher Arvin</t>
         </is>
       </c>
       <c r="N236" t="n">
@@ -16008,7 +16008,7 @@
         </is>
       </c>
       <c r="C237" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D237" t="inlineStr">
         <is>
@@ -16017,12 +16017,12 @@
       </c>
       <c r="E237" t="inlineStr">
         <is>
-          <t>sec_grade_4_hakim_ibn_hazm_1st_shift</t>
+          <t>sec_grade_4_ikrimah_ibn_abi_jahl_2nd_shift</t>
         </is>
       </c>
       <c r="F237" t="inlineStr">
         <is>
-          <t>GRADE 4 - HAKIM IBN HAZM(1ST SHIFT)</t>
+          <t>GRADE 4 - IKRIMAH IBN ABI JAHL (2ND SHIFT)</t>
         </is>
       </c>
       <c r="G237" t="inlineStr">
@@ -16037,27 +16037,27 @@
       </c>
       <c r="I237" t="inlineStr">
         <is>
-          <t>ODL - 1ST SHIFT</t>
+          <t>ODL - 2ND SHIFT</t>
         </is>
       </c>
       <c r="J237" t="inlineStr">
         <is>
-          <t>subj_math</t>
+          <t>subj_tle</t>
         </is>
       </c>
       <c r="K237" t="inlineStr">
         <is>
-          <t>Math</t>
+          <t>TLE</t>
         </is>
       </c>
       <c r="L237" t="inlineStr">
         <is>
-          <t>tchr_arvin</t>
+          <t>tchr_monisa</t>
         </is>
       </c>
       <c r="M237" t="inlineStr">
         <is>
-          <t>Teacher Arvin</t>
+          <t>Teacher Monisa</t>
         </is>
       </c>
       <c r="N237" t="n">
@@ -16083,12 +16083,12 @@
       </c>
       <c r="E238" t="inlineStr">
         <is>
-          <t>sec_grade_4_ikrimah_ibn_abi_jahl_2nd_shift</t>
+          <t>sec_grade_4_hassan_ibn_thabit_2nd_shift_mix</t>
         </is>
       </c>
       <c r="F238" t="inlineStr">
         <is>
-          <t>GRADE 4 - IKRIMAH IBN ABI JAHL (2ND SHIFT)</t>
+          <t>GRADE 4 -HASSAN IBN THABIT (2ND SHIFT) - MIX</t>
         </is>
       </c>
       <c r="G238" t="inlineStr">
@@ -16108,22 +16108,22 @@
       </c>
       <c r="J238" t="inlineStr">
         <is>
-          <t>subj_tle</t>
+          <t>subj_math</t>
         </is>
       </c>
       <c r="K238" t="inlineStr">
         <is>
-          <t>TLE</t>
+          <t>Math</t>
         </is>
       </c>
       <c r="L238" t="inlineStr">
         <is>
-          <t>tchr_monisa</t>
+          <t>tchr_saimonah</t>
         </is>
       </c>
       <c r="M238" t="inlineStr">
         <is>
-          <t>Teacher Monisa</t>
+          <t>Teacher Saimonah</t>
         </is>
       </c>
       <c r="N238" t="n">
@@ -16140,7 +16140,7 @@
         </is>
       </c>
       <c r="C239" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D239" t="inlineStr">
         <is>
@@ -16149,12 +16149,12 @@
       </c>
       <c r="E239" t="inlineStr">
         <is>
-          <t>sec_grade_4_hassan_ibn_thabit_2nd_shift_mix</t>
+          <t>sec_grade_5_ayyash_ibn_abi_rabi_ah_1st_shift</t>
         </is>
       </c>
       <c r="F239" t="inlineStr">
         <is>
-          <t>GRADE 4 -HASSAN IBN THABIT (2ND SHIFT) - MIX</t>
+          <t>GRADE 5 - AYYASH IBN ABI RABI'AH(1ST SHIFT)</t>
         </is>
       </c>
       <c r="G239" t="inlineStr">
@@ -16164,32 +16164,32 @@
       </c>
       <c r="H239" t="inlineStr">
         <is>
-          <t>Grade 4</t>
+          <t>Grade 5</t>
         </is>
       </c>
       <c r="I239" t="inlineStr">
         <is>
-          <t>ODL - 2ND SHIFT</t>
+          <t>ODL - 1ST SHIFT</t>
         </is>
       </c>
       <c r="J239" t="inlineStr">
         <is>
-          <t>subj_math</t>
+          <t>subj_shaf</t>
         </is>
       </c>
       <c r="K239" t="inlineStr">
         <is>
-          <t>Math</t>
+          <t>SHAF</t>
         </is>
       </c>
       <c r="L239" t="inlineStr">
         <is>
-          <t>tchr_saimonah</t>
+          <t>tchr_faidh</t>
         </is>
       </c>
       <c r="M239" t="inlineStr">
         <is>
-          <t>Teacher Saimonah</t>
+          <t>Ustadh Faidh</t>
         </is>
       </c>
       <c r="N239" t="n">
@@ -16215,12 +16215,12 @@
       </c>
       <c r="E240" t="inlineStr">
         <is>
-          <t>sec_grade_5_ayyash_ibn_abi_rabi_ah_1st_shift</t>
+          <t>sec_grade_5_hamza_ibn_abdul_1st_shift</t>
         </is>
       </c>
       <c r="F240" t="inlineStr">
         <is>
-          <t>GRADE 5 - AYYASH IBN ABI RABI'AH(1ST SHIFT)</t>
+          <t>GRADE 5 - HAMZA IBN ABDUL (1ST SHIFT)</t>
         </is>
       </c>
       <c r="G240" t="inlineStr">
@@ -16240,22 +16240,22 @@
       </c>
       <c r="J240" t="inlineStr">
         <is>
-          <t>subj_shaf</t>
+          <t>subj_gmrc</t>
         </is>
       </c>
       <c r="K240" t="inlineStr">
         <is>
-          <t>SHAF</t>
+          <t>GMRC</t>
         </is>
       </c>
       <c r="L240" t="inlineStr">
         <is>
-          <t>tchr_faidh</t>
+          <t>tchr_jairah</t>
         </is>
       </c>
       <c r="M240" t="inlineStr">
         <is>
-          <t>Ustadh Faidh</t>
+          <t>Teacher Jairah</t>
         </is>
       </c>
       <c r="N240" t="n">
@@ -16281,12 +16281,12 @@
       </c>
       <c r="E241" t="inlineStr">
         <is>
-          <t>sec_grade_5_hamza_ibn_abdul_1st_shift</t>
+          <t>sec_grade_5_muhammad_ibn_maslamah_1st_shift</t>
         </is>
       </c>
       <c r="F241" t="inlineStr">
         <is>
-          <t>GRADE 5 - HAMZA IBN ABDUL (1ST SHIFT)</t>
+          <t>GRADE 5 - MUHAMMAD IBN MASLAMAH (1ST SHIFT)</t>
         </is>
       </c>
       <c r="G241" t="inlineStr">
@@ -16306,22 +16306,22 @@
       </c>
       <c r="J241" t="inlineStr">
         <is>
-          <t>subj_gmrc</t>
+          <t>subj_araling_panlipunan</t>
         </is>
       </c>
       <c r="K241" t="inlineStr">
         <is>
-          <t>GMRC</t>
+          <t>Araling Panlipunan</t>
         </is>
       </c>
       <c r="L241" t="inlineStr">
         <is>
-          <t>tchr_jairah</t>
+          <t>tchr_keychell</t>
         </is>
       </c>
       <c r="M241" t="inlineStr">
         <is>
-          <t>Teacher Jairah</t>
+          <t>Teacher Keychell</t>
         </is>
       </c>
       <c r="N241" t="n">
@@ -16338,7 +16338,7 @@
         </is>
       </c>
       <c r="C242" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D242" t="inlineStr">
         <is>
@@ -16347,12 +16347,12 @@
       </c>
       <c r="E242" t="inlineStr">
         <is>
-          <t>sec_grade_5_muhammad_ibn_maslamah_1st_shift</t>
+          <t>sec_grade_5_mus_ab_ibn_abdul_mutalib_2nd_shift</t>
         </is>
       </c>
       <c r="F242" t="inlineStr">
         <is>
-          <t>GRADE 5 - MUHAMMAD IBN MASLAMAH (1ST SHIFT)</t>
+          <t>GRADE 5 - MUS'AB IBN ABDUL MUTALIB (2ND SHIFT)</t>
         </is>
       </c>
       <c r="G242" t="inlineStr">
@@ -16367,27 +16367,27 @@
       </c>
       <c r="I242" t="inlineStr">
         <is>
-          <t>ODL - 1ST SHIFT</t>
+          <t>ODL - 2ND SHIFT</t>
         </is>
       </c>
       <c r="J242" t="inlineStr">
         <is>
-          <t>subj_araling_panlipunan</t>
+          <t>subj_qur_an</t>
         </is>
       </c>
       <c r="K242" t="inlineStr">
         <is>
-          <t>Araling Panlipunan</t>
+          <t>Qur'an</t>
         </is>
       </c>
       <c r="L242" t="inlineStr">
         <is>
-          <t>tchr_keychell</t>
+          <t>tchr_jaisam</t>
         </is>
       </c>
       <c r="M242" t="inlineStr">
         <is>
-          <t>Teacher Keychell</t>
+          <t>Ustadh Jaisam</t>
         </is>
       </c>
       <c r="N242" t="n">
@@ -16404,7 +16404,7 @@
         </is>
       </c>
       <c r="C243" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D243" t="inlineStr">
         <is>
@@ -16413,12 +16413,12 @@
       </c>
       <c r="E243" t="inlineStr">
         <is>
-          <t>sec_grade_5_mus_ab_ibn_abdul_mutalib_2nd_shift</t>
+          <t>sec_grade_6_abbas_ibn_abd_al_muttalib_1st_shift</t>
         </is>
       </c>
       <c r="F243" t="inlineStr">
         <is>
-          <t>GRADE 5 - MUS'AB IBN ABDUL MUTALIB (2ND SHIFT)</t>
+          <t>GRADE 6 - ABBAS IBN ABD AL-MUTTALIB (1ST SHIFT)</t>
         </is>
       </c>
       <c r="G243" t="inlineStr">
@@ -16428,32 +16428,32 @@
       </c>
       <c r="H243" t="inlineStr">
         <is>
-          <t>Grade 5</t>
+          <t>Grade 6</t>
         </is>
       </c>
       <c r="I243" t="inlineStr">
         <is>
-          <t>ODL - 2ND SHIFT</t>
+          <t>ODL - 1ST SHIFT</t>
         </is>
       </c>
       <c r="J243" t="inlineStr">
         <is>
-          <t>subj_qur_an</t>
+          <t>subj_english</t>
         </is>
       </c>
       <c r="K243" t="inlineStr">
         <is>
-          <t>Qur'an</t>
+          <t>English</t>
         </is>
       </c>
       <c r="L243" t="inlineStr">
         <is>
-          <t>tchr_jaisam</t>
+          <t>tchr_jessa</t>
         </is>
       </c>
       <c r="M243" t="inlineStr">
         <is>
-          <t>Ustadh Jaisam</t>
+          <t>Teacher Jessa</t>
         </is>
       </c>
       <c r="N243" t="n">
@@ -16470,7 +16470,7 @@
         </is>
       </c>
       <c r="C244" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D244" t="inlineStr">
         <is>
@@ -16479,12 +16479,12 @@
       </c>
       <c r="E244" t="inlineStr">
         <is>
-          <t>sec_grade_6_abbas_ibn_abd_al_muttalib_1st_shift</t>
+          <t>sec_grade_6_dihya_ibn_khalifah_2nd_shift_girls</t>
         </is>
       </c>
       <c r="F244" t="inlineStr">
         <is>
-          <t>GRADE 6 - ABBAS IBN ABD AL-MUTTALIB (1ST SHIFT)</t>
+          <t>GRADE 6 - DIHYA IBN KHALIFAH (2ND SHIFT) GIRLS</t>
         </is>
       </c>
       <c r="G244" t="inlineStr">
@@ -16499,27 +16499,27 @@
       </c>
       <c r="I244" t="inlineStr">
         <is>
-          <t>ODL - 1ST SHIFT</t>
+          <t>ODL - 2ND SHIFT</t>
         </is>
       </c>
       <c r="J244" t="inlineStr">
         <is>
-          <t>subj_english</t>
+          <t>subj_qur_an</t>
         </is>
       </c>
       <c r="K244" t="inlineStr">
         <is>
-          <t>English</t>
+          <t>Qur'an</t>
         </is>
       </c>
       <c r="L244" t="inlineStr">
         <is>
-          <t>tchr_jessa</t>
+          <t>tchr_obaydah</t>
         </is>
       </c>
       <c r="M244" t="inlineStr">
         <is>
-          <t>Teacher Jessa</t>
+          <t>Ustadh Obaydah</t>
         </is>
       </c>
       <c r="N244" t="n">
@@ -16545,12 +16545,12 @@
       </c>
       <c r="E245" t="inlineStr">
         <is>
-          <t>sec_grade_6_dihya_ibn_khalifah_2nd_shift_girls</t>
+          <t>sec_grade_6_khaleed_ibn_waleed_2nd_shift</t>
         </is>
       </c>
       <c r="F245" t="inlineStr">
         <is>
-          <t>GRADE 6 - DIHYA IBN KHALIFAH (2ND SHIFT) GIRLS</t>
+          <t>GRADE 6 - KHALEED IBN WALEED (2ND SHIFT)</t>
         </is>
       </c>
       <c r="G245" t="inlineStr">
@@ -16570,22 +16570,22 @@
       </c>
       <c r="J245" t="inlineStr">
         <is>
-          <t>subj_qur_an</t>
+          <t>subj_arabic</t>
         </is>
       </c>
       <c r="K245" t="inlineStr">
         <is>
-          <t>Qur'an</t>
+          <t>Arabic</t>
         </is>
       </c>
       <c r="L245" t="inlineStr">
         <is>
-          <t>tchr_obaydah</t>
+          <t>tchr_ali</t>
         </is>
       </c>
       <c r="M245" t="inlineStr">
         <is>
-          <t>Ustadh Obaydah</t>
+          <t>Ustadh Ali</t>
         </is>
       </c>
       <c r="N245" t="n">
@@ -16602,7 +16602,7 @@
         </is>
       </c>
       <c r="C246" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D246" t="inlineStr">
         <is>
@@ -16611,47 +16611,47 @@
       </c>
       <c r="E246" t="inlineStr">
         <is>
-          <t>sec_grade_6_khaleed_ibn_waleed_2nd_shift</t>
+          <t>sec_grade_7_abu_sufyan_ibn_al_harith_1st_shift_boys</t>
         </is>
       </c>
       <c r="F246" t="inlineStr">
         <is>
-          <t>GRADE 6 - KHALEED IBN WALEED (2ND SHIFT)</t>
+          <t>GRADE 7 - ABU SUFYAN IBN AL-HARITH (1ST SHIFT) BOYS</t>
         </is>
       </c>
       <c r="G246" t="inlineStr">
         <is>
-          <t>Elementary</t>
+          <t>Junior High School</t>
         </is>
       </c>
       <c r="H246" t="inlineStr">
         <is>
-          <t>Grade 6</t>
+          <t>Grade 7</t>
         </is>
       </c>
       <c r="I246" t="inlineStr">
         <is>
-          <t>ODL - 2ND SHIFT</t>
+          <t>ODL - 1ST SHIFT</t>
         </is>
       </c>
       <c r="J246" t="inlineStr">
         <is>
-          <t>subj_arabic</t>
+          <t>subj_social_studies</t>
         </is>
       </c>
       <c r="K246" t="inlineStr">
         <is>
-          <t>Arabic</t>
+          <t>Social Studies</t>
         </is>
       </c>
       <c r="L246" t="inlineStr">
         <is>
-          <t>tchr_ali</t>
+          <t>tchr_shirehan</t>
         </is>
       </c>
       <c r="M246" t="inlineStr">
         <is>
-          <t>Ustadh Ali</t>
+          <t>Teacher Shirehan</t>
         </is>
       </c>
       <c r="N246" t="n">
@@ -16668,7 +16668,7 @@
         </is>
       </c>
       <c r="C247" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D247" t="inlineStr">
         <is>
@@ -16677,12 +16677,12 @@
       </c>
       <c r="E247" t="inlineStr">
         <is>
-          <t>sec_grade_7_abu_sufyan_ibn_al_harith_1st_shift_boys</t>
+          <t>sec_grade_7_anas_ibn_malik_2nd_shift_mix</t>
         </is>
       </c>
       <c r="F247" t="inlineStr">
         <is>
-          <t>GRADE 7 - ABU SUFYAN IBN AL-HARITH (1ST SHIFT) BOYS</t>
+          <t>GRADE 7 - ANAS IBN MALIK (2ND SHIFT) - MIX</t>
         </is>
       </c>
       <c r="G247" t="inlineStr">
@@ -16697,27 +16697,27 @@
       </c>
       <c r="I247" t="inlineStr">
         <is>
-          <t>ODL - 1ST SHIFT</t>
+          <t>ODL - 2ND SHIFT</t>
         </is>
       </c>
       <c r="J247" t="inlineStr">
         <is>
-          <t>subj_social_studies</t>
+          <t>subj_mapeh</t>
         </is>
       </c>
       <c r="K247" t="inlineStr">
         <is>
-          <t>Social Studies</t>
+          <t>MAPEH</t>
         </is>
       </c>
       <c r="L247" t="inlineStr">
         <is>
-          <t>tchr_shirehan</t>
+          <t>tchr_franchette</t>
         </is>
       </c>
       <c r="M247" t="inlineStr">
         <is>
-          <t>Teacher Shirehan</t>
+          <t>Teacher Franchette</t>
         </is>
       </c>
       <c r="N247" t="n">
@@ -16734,7 +16734,7 @@
         </is>
       </c>
       <c r="C248" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D248" t="inlineStr">
         <is>
@@ -16743,12 +16743,12 @@
       </c>
       <c r="E248" t="inlineStr">
         <is>
-          <t>sec_grade_7_anas_ibn_malik_2nd_shift_mix</t>
+          <t>sec_grade_7_usama_ibn_zayd_1st_shift_girls</t>
         </is>
       </c>
       <c r="F248" t="inlineStr">
         <is>
-          <t>GRADE 7 - ANAS IBN MALIK (2ND SHIFT) - MIX</t>
+          <t>GRADE 7 - USAMA IBN ZAYD (1ST SHIFT) GIRLS</t>
         </is>
       </c>
       <c r="G248" t="inlineStr">
@@ -16763,27 +16763,27 @@
       </c>
       <c r="I248" t="inlineStr">
         <is>
-          <t>ODL - 2ND SHIFT</t>
+          <t>ODL - 1ST SHIFT</t>
         </is>
       </c>
       <c r="J248" t="inlineStr">
         <is>
-          <t>subj_mapeh</t>
+          <t>subj_social_studies</t>
         </is>
       </c>
       <c r="K248" t="inlineStr">
         <is>
-          <t>MAPEH</t>
+          <t>Social Studies</t>
         </is>
       </c>
       <c r="L248" t="inlineStr">
         <is>
-          <t>tchr_franchette</t>
+          <t>tchr_shirehan</t>
         </is>
       </c>
       <c r="M248" t="inlineStr">
         <is>
-          <t>Teacher Franchette</t>
+          <t>Teacher Shirehan</t>
         </is>
       </c>
       <c r="N248" t="n">
@@ -16800,7 +16800,7 @@
         </is>
       </c>
       <c r="C249" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D249" t="inlineStr">
         <is>
@@ -16809,12 +16809,12 @@
       </c>
       <c r="E249" t="inlineStr">
         <is>
-          <t>sec_grade_7_usama_ibn_zayd_1st_shift_girls</t>
+          <t>sec_grade_8_mu_adh_ibn_jabal_2nd_shift_boys</t>
         </is>
       </c>
       <c r="F249" t="inlineStr">
         <is>
-          <t>GRADE 7 - USAMA IBN ZAYD (1ST SHIFT) GIRLS</t>
+          <t>GRADE 8 - MU'ADH IBN JABAL (2ND SHIFT) - BOYS</t>
         </is>
       </c>
       <c r="G249" t="inlineStr">
@@ -16824,32 +16824,32 @@
       </c>
       <c r="H249" t="inlineStr">
         <is>
-          <t>Grade 7</t>
+          <t>Grade 8</t>
         </is>
       </c>
       <c r="I249" t="inlineStr">
         <is>
-          <t>ODL - 1ST SHIFT</t>
+          <t>ODL - 2ND SHIFT</t>
         </is>
       </c>
       <c r="J249" t="inlineStr">
         <is>
-          <t>subj_social_studies</t>
+          <t>subj_science</t>
         </is>
       </c>
       <c r="K249" t="inlineStr">
         <is>
-          <t>Social Studies</t>
+          <t>Science</t>
         </is>
       </c>
       <c r="L249" t="inlineStr">
         <is>
-          <t>tchr_shirehan</t>
+          <t>tchr_radzmia</t>
         </is>
       </c>
       <c r="M249" t="inlineStr">
         <is>
-          <t>Teacher Shirehan</t>
+          <t>Teacher Radzmia</t>
         </is>
       </c>
       <c r="N249" t="n">
@@ -16875,12 +16875,12 @@
       </c>
       <c r="E250" t="inlineStr">
         <is>
-          <t>sec_grade_8_mu_adh_ibn_jabal_2nd_shift_boys</t>
+          <t>sec_grade_8_nuaym_ibn_mas_ud_2nd_shift_mix</t>
         </is>
       </c>
       <c r="F250" t="inlineStr">
         <is>
-          <t>GRADE 8 - MU'ADH IBN JABAL (2ND SHIFT) - BOYS</t>
+          <t>GRADE 8 - NUAYM IBN MAS'UD (2ND SHIFT) MIX</t>
         </is>
       </c>
       <c r="G250" t="inlineStr">
@@ -16900,22 +16900,22 @@
       </c>
       <c r="J250" t="inlineStr">
         <is>
-          <t>subj_science</t>
+          <t>subj_tle</t>
         </is>
       </c>
       <c r="K250" t="inlineStr">
         <is>
-          <t>Science</t>
+          <t>TLE</t>
         </is>
       </c>
       <c r="L250" t="inlineStr">
         <is>
-          <t>tchr_radzmia</t>
+          <t>tchr_halnaisa</t>
         </is>
       </c>
       <c r="M250" t="inlineStr">
         <is>
-          <t>Teacher Radzmia</t>
+          <t>Teacher Halnaisa</t>
         </is>
       </c>
       <c r="N250" t="n">
@@ -16932,7 +16932,7 @@
         </is>
       </c>
       <c r="C251" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D251" t="inlineStr">
         <is>
@@ -16941,12 +16941,12 @@
       </c>
       <c r="E251" t="inlineStr">
         <is>
-          <t>sec_grade_8_nuaym_ibn_mas_ud_2nd_shift_mix</t>
+          <t>sec_grade_8_sa_ad_ibn_mua_dh_1st_shift_girls</t>
         </is>
       </c>
       <c r="F251" t="inlineStr">
         <is>
-          <t>GRADE 8 - NUAYM IBN MAS'UD (2ND SHIFT) MIX</t>
+          <t>GRADE 8 - SA'AD IBN MUA'DH (1ST SHIFT) - GIRLS</t>
         </is>
       </c>
       <c r="G251" t="inlineStr">
@@ -16961,27 +16961,27 @@
       </c>
       <c r="I251" t="inlineStr">
         <is>
-          <t>ODL - 2ND SHIFT</t>
+          <t>ODL - 1ST SHIFT</t>
         </is>
       </c>
       <c r="J251" t="inlineStr">
         <is>
-          <t>subj_tle</t>
+          <t>subj_shaf</t>
         </is>
       </c>
       <c r="K251" t="inlineStr">
         <is>
-          <t>TLE</t>
+          <t>SHAF</t>
         </is>
       </c>
       <c r="L251" t="inlineStr">
         <is>
-          <t>tchr_halnaisa</t>
+          <t>tchr_samsuddin</t>
         </is>
       </c>
       <c r="M251" t="inlineStr">
         <is>
-          <t>Teacher Halnaisa</t>
+          <t>Alim Samsuddin</t>
         </is>
       </c>
       <c r="N251" t="n">
@@ -16998,7 +16998,7 @@
         </is>
       </c>
       <c r="C252" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D252" t="inlineStr">
         <is>
@@ -17007,12 +17007,12 @@
       </c>
       <c r="E252" t="inlineStr">
         <is>
-          <t>sec_grade_8_sa_ad_ibn_mua_dh_1st_shift_girls</t>
+          <t>sec_grade_9_abu_dharr_al_ghifarri_2nd_shift_boys</t>
         </is>
       </c>
       <c r="F252" t="inlineStr">
         <is>
-          <t>GRADE 8 - SA'AD IBN MUA'DH (1ST SHIFT) - GIRLS</t>
+          <t>GRADE 9 - ABU DHARR AL GHIFARRI (2ND SHIFT) BOYS</t>
         </is>
       </c>
       <c r="G252" t="inlineStr">
@@ -17022,32 +17022,32 @@
       </c>
       <c r="H252" t="inlineStr">
         <is>
-          <t>Grade 8</t>
+          <t>Grade 9</t>
         </is>
       </c>
       <c r="I252" t="inlineStr">
         <is>
-          <t>ODL - 1ST SHIFT</t>
+          <t>ODL - 2ND SHIFT</t>
         </is>
       </c>
       <c r="J252" t="inlineStr">
         <is>
-          <t>subj_shaf</t>
+          <t>subj_social_studies</t>
         </is>
       </c>
       <c r="K252" t="inlineStr">
         <is>
-          <t>SHAF</t>
+          <t>Social Science</t>
         </is>
       </c>
       <c r="L252" t="inlineStr">
         <is>
-          <t>tchr_samsuddin</t>
+          <t>tchr_sophia</t>
         </is>
       </c>
       <c r="M252" t="inlineStr">
         <is>
-          <t>Alim Samsuddin</t>
+          <t>Teacher Sophia</t>
         </is>
       </c>
       <c r="N252" t="n">
@@ -17073,12 +17073,12 @@
       </c>
       <c r="E253" t="inlineStr">
         <is>
-          <t>sec_grade_9_abu_dharr_al_ghifarri_2nd_shift_boys</t>
+          <t>sec_grade_9_abu_jandal_ibn_suhayl_2nd_shift_girls</t>
         </is>
       </c>
       <c r="F253" t="inlineStr">
         <is>
-          <t>GRADE 9 - ABU DHARR AL GHIFARRI (2ND SHIFT) BOYS</t>
+          <t>GRADE 9 - ABU JANDAL IBN SUHAYL (2ND SHIFT) GIRLS</t>
         </is>
       </c>
       <c r="G253" t="inlineStr">
@@ -17098,22 +17098,22 @@
       </c>
       <c r="J253" t="inlineStr">
         <is>
-          <t>subj_social_studies</t>
+          <t>subj_tle</t>
         </is>
       </c>
       <c r="K253" t="inlineStr">
         <is>
-          <t>Social Science</t>
+          <t>TLE</t>
         </is>
       </c>
       <c r="L253" t="inlineStr">
         <is>
-          <t>tchr_sophia</t>
+          <t>tchr_angeleni</t>
         </is>
       </c>
       <c r="M253" t="inlineStr">
         <is>
-          <t>Teacher Sophia</t>
+          <t>Teacher Angeleni</t>
         </is>
       </c>
       <c r="N253" t="n">
@@ -17130,21 +17130,21 @@
         </is>
       </c>
       <c r="C254" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D254" t="inlineStr">
         <is>
-          <t>03:10 PM – 04:10 PM</t>
+          <t>04:20 PM – 05:20 PM</t>
         </is>
       </c>
       <c r="E254" t="inlineStr">
         <is>
-          <t>sec_grade_9_abu_jandal_ibn_suhayl_2nd_shift_girls</t>
+          <t>sec_grade_10_abu_ayyub_al_ansari_2nd_shift_boys</t>
         </is>
       </c>
       <c r="F254" t="inlineStr">
         <is>
-          <t>GRADE 9 - ABU JANDAL IBN SUHAYL (2ND SHIFT) GIRLS</t>
+          <t>GRADE 10 - ABU AYYUB AL-ANSARI (2ND SHIFT) BOYS</t>
         </is>
       </c>
       <c r="G254" t="inlineStr">
@@ -17154,7 +17154,7 @@
       </c>
       <c r="H254" t="inlineStr">
         <is>
-          <t>Grade 9</t>
+          <t>Grade 10</t>
         </is>
       </c>
       <c r="I254" t="inlineStr">
@@ -17164,22 +17164,22 @@
       </c>
       <c r="J254" t="inlineStr">
         <is>
-          <t>subj_tle</t>
+          <t>subj_filipino</t>
         </is>
       </c>
       <c r="K254" t="inlineStr">
         <is>
-          <t>TLE</t>
+          <t>Filipino</t>
         </is>
       </c>
       <c r="L254" t="inlineStr">
         <is>
-          <t>tchr_angeleni</t>
+          <t>tchr_nadzra</t>
         </is>
       </c>
       <c r="M254" t="inlineStr">
         <is>
-          <t>Teacher Angeleni</t>
+          <t>Teacher Nadzra</t>
         </is>
       </c>
       <c r="N254" t="n">
@@ -17196,7 +17196,7 @@
         </is>
       </c>
       <c r="C255" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D255" t="inlineStr">
         <is>
@@ -17205,47 +17205,47 @@
       </c>
       <c r="E255" t="inlineStr">
         <is>
-          <t>sec_grade_10_abu_ayyub_al_ansari_2nd_shift_boys</t>
+          <t>sec_grade_11_1st_shift_girls</t>
         </is>
       </c>
       <c r="F255" t="inlineStr">
         <is>
-          <t>GRADE 10 - ABU AYYUB AL-ANSARI (2ND SHIFT) BOYS</t>
+          <t>GRADE 11 (1ST SHIFT GIRLS)</t>
         </is>
       </c>
       <c r="G255" t="inlineStr">
         <is>
-          <t>Junior High School</t>
+          <t>Senior High School</t>
         </is>
       </c>
       <c r="H255" t="inlineStr">
         <is>
-          <t>Grade 10</t>
+          <t>Grade 11</t>
         </is>
       </c>
       <c r="I255" t="inlineStr">
         <is>
-          <t>ODL - 2ND SHIFT</t>
+          <t>ODL - 1ST SHIFT</t>
         </is>
       </c>
       <c r="J255" t="inlineStr">
         <is>
-          <t>subj_filipino</t>
+          <t>subj_gen_bio_1</t>
         </is>
       </c>
       <c r="K255" t="inlineStr">
         <is>
-          <t>Filipino</t>
+          <t>Gen Bio 1</t>
         </is>
       </c>
       <c r="L255" t="inlineStr">
         <is>
-          <t>tchr_nadzra</t>
+          <t>tchr_rowena</t>
         </is>
       </c>
       <c r="M255" t="inlineStr">
         <is>
-          <t>Teacher Nadzra</t>
+          <t>Teacher Rowena</t>
         </is>
       </c>
       <c r="N255" t="n">
@@ -17262,21 +17262,21 @@
         </is>
       </c>
       <c r="C256" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D256" t="inlineStr">
         <is>
-          <t>04:20 PM – 05:20 PM</t>
+          <t>04:20 PM – 06:30 PM</t>
         </is>
       </c>
       <c r="E256" t="inlineStr">
         <is>
-          <t>sec_grade_11_1st_shift_girls</t>
+          <t>sec_grade_11_2nd_shift_boys</t>
         </is>
       </c>
       <c r="F256" t="inlineStr">
         <is>
-          <t>GRADE 11 (1ST SHIFT GIRLS)</t>
+          <t>GRADE 11 (2ND SHIFT BOYS)</t>
         </is>
       </c>
       <c r="G256" t="inlineStr">
@@ -17291,31 +17291,31 @@
       </c>
       <c r="I256" t="inlineStr">
         <is>
-          <t>ODL - 1ST SHIFT</t>
+          <t>ODL - 2ND SHIFT</t>
         </is>
       </c>
       <c r="J256" t="inlineStr">
         <is>
-          <t>subj_gen_bio_1</t>
+          <t>subj_gen_math</t>
         </is>
       </c>
       <c r="K256" t="inlineStr">
         <is>
-          <t>Gen Bio 1</t>
+          <t>Gen Math</t>
         </is>
       </c>
       <c r="L256" t="inlineStr">
         <is>
-          <t>tchr_rowena</t>
+          <t>tchr_jhelyn</t>
         </is>
       </c>
       <c r="M256" t="inlineStr">
         <is>
-          <t>Teacher Rowena</t>
+          <t>Teacher Jhelyn</t>
         </is>
       </c>
       <c r="N256" t="n">
-        <v>60</v>
+        <v>120</v>
       </c>
     </row>
     <row r="257">
@@ -17328,21 +17328,21 @@
         </is>
       </c>
       <c r="C257" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D257" t="inlineStr">
         <is>
-          <t>04:20 PM – 06:30 PM</t>
+          <t>04:20 PM – 05:20 PM</t>
         </is>
       </c>
       <c r="E257" t="inlineStr">
         <is>
-          <t>sec_grade_11_2nd_shift_boys</t>
+          <t>sec_grade_12_abu_musa_al_ashari</t>
         </is>
       </c>
       <c r="F257" t="inlineStr">
         <is>
-          <t>GRADE 11 (2ND SHIFT BOYS)</t>
+          <t>GRADE 12 - ABU MUSA AL-ASHARI</t>
         </is>
       </c>
       <c r="G257" t="inlineStr">
@@ -17352,36 +17352,36 @@
       </c>
       <c r="H257" t="inlineStr">
         <is>
-          <t>Grade 11</t>
+          <t>Grade 12</t>
         </is>
       </c>
       <c r="I257" t="inlineStr">
         <is>
-          <t>ODL - 2ND SHIFT</t>
+          <t>ODL - 1ST SHIFT</t>
         </is>
       </c>
       <c r="J257" t="inlineStr">
         <is>
-          <t>subj_gen_math</t>
+          <t>subj_mil</t>
         </is>
       </c>
       <c r="K257" t="inlineStr">
         <is>
-          <t>Gen Math</t>
+          <t>MIL</t>
         </is>
       </c>
       <c r="L257" t="inlineStr">
         <is>
-          <t>tchr_jhelyn</t>
+          <t>tchr_ethel</t>
         </is>
       </c>
       <c r="M257" t="inlineStr">
         <is>
-          <t>Teacher Jhelyn</t>
+          <t>Teacher Ethel</t>
         </is>
       </c>
       <c r="N257" t="n">
-        <v>120</v>
+        <v>60</v>
       </c>
     </row>
     <row r="258">
@@ -17394,7 +17394,7 @@
         </is>
       </c>
       <c r="C258" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D258" t="inlineStr">
         <is>
@@ -17403,47 +17403,47 @@
       </c>
       <c r="E258" t="inlineStr">
         <is>
-          <t>sec_grade_12_abu_musa_al_ashari</t>
+          <t>sec_grade_2_aasim_ibn_thabit_2nd_shift</t>
         </is>
       </c>
       <c r="F258" t="inlineStr">
         <is>
-          <t>GRADE 12 - ABU MUSA AL-ASHARI</t>
+          <t>GRADE 2 - AASIM IBN THABIT (2ND SHIFT)</t>
         </is>
       </c>
       <c r="G258" t="inlineStr">
         <is>
-          <t>Senior High School</t>
+          <t>Elementary</t>
         </is>
       </c>
       <c r="H258" t="inlineStr">
         <is>
-          <t>Grade 12</t>
+          <t>Grade 2</t>
         </is>
       </c>
       <c r="I258" t="inlineStr">
         <is>
-          <t>ODL - 1ST SHIFT</t>
+          <t>ODL - 2ND SHIFT</t>
         </is>
       </c>
       <c r="J258" t="inlineStr">
         <is>
-          <t>subj_mil</t>
+          <t>subj_makabansa</t>
         </is>
       </c>
       <c r="K258" t="inlineStr">
         <is>
-          <t>MIL</t>
+          <t>Makabansa</t>
         </is>
       </c>
       <c r="L258" t="inlineStr">
         <is>
-          <t>tchr_ethel</t>
+          <t>tchr_monisa</t>
         </is>
       </c>
       <c r="M258" t="inlineStr">
         <is>
-          <t>Teacher Ethel</t>
+          <t>Teacher Monisa</t>
         </is>
       </c>
       <c r="N258" t="n">
@@ -17469,12 +17469,12 @@
       </c>
       <c r="E259" t="inlineStr">
         <is>
-          <t>sec_grade_2_aasim_ibn_thabit_2nd_shift</t>
+          <t>sec_grade_3_as_ad_ibn_zurarah_2nd_shift_mix</t>
         </is>
       </c>
       <c r="F259" t="inlineStr">
         <is>
-          <t>GRADE 2 - AASIM IBN THABIT (2ND SHIFT)</t>
+          <t>GRADE 3 - AS'AD IBN ZURARAH (2ND SHIFT) MIX</t>
         </is>
       </c>
       <c r="G259" t="inlineStr">
@@ -17484,7 +17484,7 @@
       </c>
       <c r="H259" t="inlineStr">
         <is>
-          <t>Grade 2</t>
+          <t>Grade 3</t>
         </is>
       </c>
       <c r="I259" t="inlineStr">
@@ -17494,22 +17494,22 @@
       </c>
       <c r="J259" t="inlineStr">
         <is>
-          <t>subj_makabansa</t>
+          <t>subj_filipino</t>
         </is>
       </c>
       <c r="K259" t="inlineStr">
         <is>
-          <t>Makabansa</t>
+          <t>Filipino</t>
         </is>
       </c>
       <c r="L259" t="inlineStr">
         <is>
-          <t>tchr_monisa</t>
+          <t>tchr_jenny</t>
         </is>
       </c>
       <c r="M259" t="inlineStr">
         <is>
-          <t>Teacher Monisa</t>
+          <t>Teacher Jenny</t>
         </is>
       </c>
       <c r="N259" t="n">
@@ -17535,12 +17535,12 @@
       </c>
       <c r="E260" t="inlineStr">
         <is>
-          <t>sec_grade_3_as_ad_ibn_zurarah_2nd_shift_mix</t>
+          <t>sec_grade_3_thabit_ibn_qays_2nd_shift_boys</t>
         </is>
       </c>
       <c r="F260" t="inlineStr">
         <is>
-          <t>GRADE 3 - AS'AD IBN ZURARAH (2ND SHIFT) MIX</t>
+          <t>GRADE 3 - THABIT IBN QAYS (2ND SHIFT) - BOYS</t>
         </is>
       </c>
       <c r="G260" t="inlineStr">
@@ -17560,22 +17560,22 @@
       </c>
       <c r="J260" t="inlineStr">
         <is>
-          <t>subj_filipino</t>
+          <t>subj_arabic</t>
         </is>
       </c>
       <c r="K260" t="inlineStr">
         <is>
-          <t>Filipino</t>
+          <t>Arabic</t>
         </is>
       </c>
       <c r="L260" t="inlineStr">
         <is>
-          <t>tchr_jenny</t>
+          <t>tchr_silfah</t>
         </is>
       </c>
       <c r="M260" t="inlineStr">
         <is>
-          <t>Teacher Jenny</t>
+          <t>Ustadh Silfah</t>
         </is>
       </c>
       <c r="N260" t="n">
@@ -17601,12 +17601,12 @@
       </c>
       <c r="E261" t="inlineStr">
         <is>
-          <t>sec_grade_3_thabit_ibn_qays_2nd_shift_boys</t>
+          <t>sec_grade_3_zayd_ibn_haritha_2nd_shift_girls</t>
         </is>
       </c>
       <c r="F261" t="inlineStr">
         <is>
-          <t>GRADE 3 - THABIT IBN QAYS (2ND SHIFT) - BOYS</t>
+          <t>GRADE 3 - ZAYD IBN HARITHA (2ND SHIFT) - GIRLS</t>
         </is>
       </c>
       <c r="G261" t="inlineStr">
@@ -17667,12 +17667,12 @@
       </c>
       <c r="E262" t="inlineStr">
         <is>
-          <t>sec_grade_3_zayd_ibn_haritha_2nd_shift_girls</t>
+          <t>sec_grade_4_az_zubair_ibn_al_awwaam_2nd_shift</t>
         </is>
       </c>
       <c r="F262" t="inlineStr">
         <is>
-          <t>GRADE 3 - ZAYD IBN HARITHA (2ND SHIFT) - GIRLS</t>
+          <t>GRADE 4 - AZ ZUBAIR IBN AL AWWAAM (2ND SHIFT)</t>
         </is>
       </c>
       <c r="G262" t="inlineStr">
@@ -17682,7 +17682,7 @@
       </c>
       <c r="H262" t="inlineStr">
         <is>
-          <t>Grade 3</t>
+          <t>Grade 4</t>
         </is>
       </c>
       <c r="I262" t="inlineStr">
@@ -17692,22 +17692,22 @@
       </c>
       <c r="J262" t="inlineStr">
         <is>
-          <t>subj_arabic</t>
+          <t>subj_gmrc</t>
         </is>
       </c>
       <c r="K262" t="inlineStr">
         <is>
-          <t>Arabic</t>
+          <t>GMRC</t>
         </is>
       </c>
       <c r="L262" t="inlineStr">
         <is>
-          <t>tchr_silfah</t>
+          <t>tchr_sahdia</t>
         </is>
       </c>
       <c r="M262" t="inlineStr">
         <is>
-          <t>Ustadh Silfah</t>
+          <t>Teacher Sahdia</t>
         </is>
       </c>
       <c r="N262" t="n">
@@ -17733,12 +17733,12 @@
       </c>
       <c r="E263" t="inlineStr">
         <is>
-          <t>sec_grade_4_az_zubair_ibn_al_awwaam_2nd_shift</t>
+          <t>sec_grade_4_ikrimah_ibn_abi_jahl_2nd_shift</t>
         </is>
       </c>
       <c r="F263" t="inlineStr">
         <is>
-          <t>GRADE 4 - AZ ZUBAIR IBN AL AWWAAM (2ND SHIFT)</t>
+          <t>GRADE 4 - IKRIMAH IBN ABI JAHL (2ND SHIFT)</t>
         </is>
       </c>
       <c r="G263" t="inlineStr">
@@ -17758,22 +17758,22 @@
       </c>
       <c r="J263" t="inlineStr">
         <is>
-          <t>subj_gmrc</t>
+          <t>subj_qur_an</t>
         </is>
       </c>
       <c r="K263" t="inlineStr">
         <is>
-          <t>GMRC</t>
+          <t>Qur'an</t>
         </is>
       </c>
       <c r="L263" t="inlineStr">
         <is>
-          <t>tchr_sahdia</t>
+          <t>tchr_obaydah</t>
         </is>
       </c>
       <c r="M263" t="inlineStr">
         <is>
-          <t>Teacher Sahdia</t>
+          <t>Ustadh Obaydah</t>
         </is>
       </c>
       <c r="N263" t="n">
@@ -17799,12 +17799,12 @@
       </c>
       <c r="E264" t="inlineStr">
         <is>
-          <t>sec_grade_4_ikrimah_ibn_abi_jahl_2nd_shift</t>
+          <t>sec_grade_4_hassan_ibn_thabit_2nd_shift_mix</t>
         </is>
       </c>
       <c r="F264" t="inlineStr">
         <is>
-          <t>GRADE 4 - IKRIMAH IBN ABI JAHL (2ND SHIFT)</t>
+          <t>GRADE 4 -HASSAN IBN THABIT (2ND SHIFT) - MIX</t>
         </is>
       </c>
       <c r="G264" t="inlineStr">
@@ -17824,22 +17824,22 @@
       </c>
       <c r="J264" t="inlineStr">
         <is>
-          <t>subj_qur_an</t>
+          <t>subj_filipino</t>
         </is>
       </c>
       <c r="K264" t="inlineStr">
         <is>
-          <t>Qur'an</t>
+          <t>Filipino</t>
         </is>
       </c>
       <c r="L264" t="inlineStr">
         <is>
-          <t>tchr_obaydah</t>
+          <t>tchr_zuhora</t>
         </is>
       </c>
       <c r="M264" t="inlineStr">
         <is>
-          <t>Ustadh Obaydah</t>
+          <t>Teacher Zuhora</t>
         </is>
       </c>
       <c r="N264" t="n">
@@ -17865,12 +17865,12 @@
       </c>
       <c r="E265" t="inlineStr">
         <is>
-          <t>sec_grade_4_hassan_ibn_thabit_2nd_shift_mix</t>
+          <t>sec_grade_5_al_harith_bin_awf_2nd_shift</t>
         </is>
       </c>
       <c r="F265" t="inlineStr">
         <is>
-          <t>GRADE 4 -HASSAN IBN THABIT (2ND SHIFT) - MIX</t>
+          <t>GRADE 5 - AL HARITH BIN AWF (2ND SHIFT)</t>
         </is>
       </c>
       <c r="G265" t="inlineStr">
@@ -17880,7 +17880,7 @@
       </c>
       <c r="H265" t="inlineStr">
         <is>
-          <t>Grade 4</t>
+          <t>Grade 5</t>
         </is>
       </c>
       <c r="I265" t="inlineStr">
@@ -17890,22 +17890,22 @@
       </c>
       <c r="J265" t="inlineStr">
         <is>
-          <t>subj_filipino</t>
+          <t>subj_arabic</t>
         </is>
       </c>
       <c r="K265" t="inlineStr">
         <is>
-          <t>Filipino</t>
+          <t>Arabic</t>
         </is>
       </c>
       <c r="L265" t="inlineStr">
         <is>
-          <t>tchr_zuhora</t>
+          <t>tchr_ersahad</t>
         </is>
       </c>
       <c r="M265" t="inlineStr">
         <is>
-          <t>Teacher Zuhora</t>
+          <t>Ustadh Ersahad</t>
         </is>
       </c>
       <c r="N265" t="n">
@@ -17931,12 +17931,12 @@
       </c>
       <c r="E266" t="inlineStr">
         <is>
-          <t>sec_grade_5_al_harith_bin_awf_2nd_shift</t>
+          <t>sec_grade_5_ja_far_ibn_abi_talib_2nd_shift_mix</t>
         </is>
       </c>
       <c r="F266" t="inlineStr">
         <is>
-          <t>GRADE 5 - AL HARITH BIN AWF (2ND SHIFT)</t>
+          <t>GRADE 5 - JA'FAR IBN ABI TALIB (2ND SHIFT) - MIX</t>
         </is>
       </c>
       <c r="G266" t="inlineStr">
@@ -17956,22 +17956,22 @@
       </c>
       <c r="J266" t="inlineStr">
         <is>
-          <t>subj_arabic</t>
+          <t>subj_araling_panlipunan</t>
         </is>
       </c>
       <c r="K266" t="inlineStr">
         <is>
-          <t>Arabic</t>
+          <t>Araling Panlipunan</t>
         </is>
       </c>
       <c r="L266" t="inlineStr">
         <is>
-          <t>tchr_ersahad</t>
+          <t>tchr_saimonah</t>
         </is>
       </c>
       <c r="M266" t="inlineStr">
         <is>
-          <t>Ustadh Ersahad</t>
+          <t>Teacher Saimonah</t>
         </is>
       </c>
       <c r="N266" t="n">
@@ -17997,12 +17997,12 @@
       </c>
       <c r="E267" t="inlineStr">
         <is>
-          <t>sec_grade_5_ja_far_ibn_abi_talib_2nd_shift_mix</t>
+          <t>sec_grade_5_mus_ab_ibn_abdul_mutalib_2nd_shift</t>
         </is>
       </c>
       <c r="F267" t="inlineStr">
         <is>
-          <t>GRADE 5 - JA'FAR IBN ABI TALIB (2ND SHIFT) - MIX</t>
+          <t>GRADE 5 - MUS'AB IBN ABDUL MUTALIB (2ND SHIFT)</t>
         </is>
       </c>
       <c r="G267" t="inlineStr">
@@ -18022,22 +18022,22 @@
       </c>
       <c r="J267" t="inlineStr">
         <is>
-          <t>subj_araling_panlipunan</t>
+          <t>subj_mapeh</t>
         </is>
       </c>
       <c r="K267" t="inlineStr">
         <is>
-          <t>Araling Panlipunan</t>
+          <t>MAPEH</t>
         </is>
       </c>
       <c r="L267" t="inlineStr">
         <is>
-          <t>tchr_saimonah</t>
+          <t>tchr_norhydie</t>
         </is>
       </c>
       <c r="M267" t="inlineStr">
         <is>
-          <t>Teacher Saimonah</t>
+          <t>Teacher Norhydie</t>
         </is>
       </c>
       <c r="N267" t="n">
@@ -18063,12 +18063,12 @@
       </c>
       <c r="E268" t="inlineStr">
         <is>
-          <t>sec_grade_5_mus_ab_ibn_abdul_mutalib_2nd_shift</t>
+          <t>sec_grade_6_dihya_ibn_khalifah_2nd_shift_girls</t>
         </is>
       </c>
       <c r="F268" t="inlineStr">
         <is>
-          <t>GRADE 5 - MUS'AB IBN ABDUL MUTALIB (2ND SHIFT)</t>
+          <t>GRADE 6 - DIHYA IBN KHALIFAH (2ND SHIFT) GIRLS</t>
         </is>
       </c>
       <c r="G268" t="inlineStr">
@@ -18078,7 +18078,7 @@
       </c>
       <c r="H268" t="inlineStr">
         <is>
-          <t>Grade 5</t>
+          <t>Grade 6</t>
         </is>
       </c>
       <c r="I268" t="inlineStr">
@@ -18088,22 +18088,22 @@
       </c>
       <c r="J268" t="inlineStr">
         <is>
-          <t>subj_mapeh</t>
+          <t>subj_tle</t>
         </is>
       </c>
       <c r="K268" t="inlineStr">
         <is>
-          <t>MAPEH</t>
+          <t>TLE</t>
         </is>
       </c>
       <c r="L268" t="inlineStr">
         <is>
-          <t>tchr_norhydie</t>
+          <t>tchr_arvin</t>
         </is>
       </c>
       <c r="M268" t="inlineStr">
         <is>
-          <t>Teacher Norhydie</t>
+          <t>Teacher Arvin</t>
         </is>
       </c>
       <c r="N268" t="n">
@@ -18129,12 +18129,12 @@
       </c>
       <c r="E269" t="inlineStr">
         <is>
-          <t>sec_grade_6_dihya_ibn_khalifah_2nd_shift_girls</t>
+          <t>sec_grade_6_khaleed_ibn_waleed_2nd_shift</t>
         </is>
       </c>
       <c r="F269" t="inlineStr">
         <is>
-          <t>GRADE 6 - DIHYA IBN KHALIFAH (2ND SHIFT) GIRLS</t>
+          <t>GRADE 6 - KHALEED IBN WALEED (2ND SHIFT)</t>
         </is>
       </c>
       <c r="G269" t="inlineStr">
@@ -18154,22 +18154,22 @@
       </c>
       <c r="J269" t="inlineStr">
         <is>
-          <t>subj_tle</t>
+          <t>subj_fil</t>
         </is>
       </c>
       <c r="K269" t="inlineStr">
         <is>
-          <t>TLE</t>
+          <t>Fil</t>
         </is>
       </c>
       <c r="L269" t="inlineStr">
         <is>
-          <t>tchr_arvin</t>
+          <t>tchr_normylah</t>
         </is>
       </c>
       <c r="M269" t="inlineStr">
         <is>
-          <t>Teacher Arvin</t>
+          <t>Teacher Normylah</t>
         </is>
       </c>
       <c r="N269" t="n">
@@ -18195,22 +18195,22 @@
       </c>
       <c r="E270" t="inlineStr">
         <is>
-          <t>sec_grade_6_khaleed_ibn_waleed_2nd_shift</t>
+          <t>sec_grade_7_anas_ibn_malik_2nd_shift_mix</t>
         </is>
       </c>
       <c r="F270" t="inlineStr">
         <is>
-          <t>GRADE 6 - KHALEED IBN WALEED (2ND SHIFT)</t>
+          <t>GRADE 7 - ANAS IBN MALIK (2ND SHIFT) - MIX</t>
         </is>
       </c>
       <c r="G270" t="inlineStr">
         <is>
-          <t>Elementary</t>
+          <t>Junior High School</t>
         </is>
       </c>
       <c r="H270" t="inlineStr">
         <is>
-          <t>Grade 6</t>
+          <t>Grade 7</t>
         </is>
       </c>
       <c r="I270" t="inlineStr">
@@ -18220,22 +18220,22 @@
       </c>
       <c r="J270" t="inlineStr">
         <is>
-          <t>subj_fil</t>
+          <t>subj_shaf</t>
         </is>
       </c>
       <c r="K270" t="inlineStr">
         <is>
-          <t>Fil</t>
+          <t>SHAF</t>
         </is>
       </c>
       <c r="L270" t="inlineStr">
         <is>
-          <t>tchr_normylah</t>
+          <t>tchr_samsuddin</t>
         </is>
       </c>
       <c r="M270" t="inlineStr">
         <is>
-          <t>Teacher Normylah</t>
+          <t>Alim Samsuddin</t>
         </is>
       </c>
       <c r="N270" t="n">
@@ -18261,12 +18261,12 @@
       </c>
       <c r="E271" t="inlineStr">
         <is>
-          <t>sec_grade_7_anas_ibn_malik_2nd_shift_mix</t>
+          <t>sec_grade_8_mu_adh_ibn_jabal_2nd_shift_boys</t>
         </is>
       </c>
       <c r="F271" t="inlineStr">
         <is>
-          <t>GRADE 7 - ANAS IBN MALIK (2ND SHIFT) - MIX</t>
+          <t>GRADE 8 - MU'ADH IBN JABAL (2ND SHIFT) - BOYS</t>
         </is>
       </c>
       <c r="G271" t="inlineStr">
@@ -18276,7 +18276,7 @@
       </c>
       <c r="H271" t="inlineStr">
         <is>
-          <t>Grade 7</t>
+          <t>Grade 8</t>
         </is>
       </c>
       <c r="I271" t="inlineStr">
@@ -18286,22 +18286,22 @@
       </c>
       <c r="J271" t="inlineStr">
         <is>
-          <t>subj_shaf</t>
+          <t>subj_arabic</t>
         </is>
       </c>
       <c r="K271" t="inlineStr">
         <is>
-          <t>SHAF</t>
+          <t>Arabic</t>
         </is>
       </c>
       <c r="L271" t="inlineStr">
         <is>
-          <t>tchr_samsuddin</t>
+          <t>tchr_ali</t>
         </is>
       </c>
       <c r="M271" t="inlineStr">
         <is>
-          <t>Alim Samsuddin</t>
+          <t>Ustadh Ali</t>
         </is>
       </c>
       <c r="N271" t="n">
@@ -18327,12 +18327,12 @@
       </c>
       <c r="E272" t="inlineStr">
         <is>
-          <t>sec_grade_8_mu_adh_ibn_jabal_2nd_shift_boys</t>
+          <t>sec_grade_8_nuaym_ibn_mas_ud_2nd_shift_mix</t>
         </is>
       </c>
       <c r="F272" t="inlineStr">
         <is>
-          <t>GRADE 8 - MU'ADH IBN JABAL (2ND SHIFT) - BOYS</t>
+          <t>GRADE 8 - NUAYM IBN MAS'UD (2ND SHIFT) MIX</t>
         </is>
       </c>
       <c r="G272" t="inlineStr">
@@ -18393,12 +18393,12 @@
       </c>
       <c r="E273" t="inlineStr">
         <is>
-          <t>sec_grade_8_nuaym_ibn_mas_ud_2nd_shift_mix</t>
+          <t>sec_grade_9_abu_dharr_al_ghifarri_2nd_shift_boys</t>
         </is>
       </c>
       <c r="F273" t="inlineStr">
         <is>
-          <t>GRADE 8 - NUAYM IBN MAS'UD (2ND SHIFT) MIX</t>
+          <t>GRADE 9 - ABU DHARR AL GHIFARRI (2ND SHIFT) BOYS</t>
         </is>
       </c>
       <c r="G273" t="inlineStr">
@@ -18408,7 +18408,7 @@
       </c>
       <c r="H273" t="inlineStr">
         <is>
-          <t>Grade 8</t>
+          <t>Grade 9</t>
         </is>
       </c>
       <c r="I273" t="inlineStr">
@@ -18418,22 +18418,22 @@
       </c>
       <c r="J273" t="inlineStr">
         <is>
-          <t>subj_arabic</t>
+          <t>subj_english</t>
         </is>
       </c>
       <c r="K273" t="inlineStr">
         <is>
-          <t>Arabic</t>
+          <t>English</t>
         </is>
       </c>
       <c r="L273" t="inlineStr">
         <is>
-          <t>tchr_ali</t>
+          <t>tchr_norhaima</t>
         </is>
       </c>
       <c r="M273" t="inlineStr">
         <is>
-          <t>Ustadh Ali</t>
+          <t>Teacher Norhaima</t>
         </is>
       </c>
       <c r="N273" t="n">
@@ -18459,12 +18459,12 @@
       </c>
       <c r="E274" t="inlineStr">
         <is>
-          <t>sec_grade_9_abu_dharr_al_ghifarri_2nd_shift_boys</t>
+          <t>sec_grade_9_abu_jandal_ibn_suhayl_2nd_shift_girls</t>
         </is>
       </c>
       <c r="F274" t="inlineStr">
         <is>
-          <t>GRADE 9 - ABU DHARR AL GHIFARRI (2ND SHIFT) BOYS</t>
+          <t>GRADE 9 - ABU JANDAL IBN SUHAYL (2ND SHIFT) GIRLS</t>
         </is>
       </c>
       <c r="G274" t="inlineStr">
@@ -18484,22 +18484,22 @@
       </c>
       <c r="J274" t="inlineStr">
         <is>
-          <t>subj_english</t>
+          <t>subj_social_studies</t>
         </is>
       </c>
       <c r="K274" t="inlineStr">
         <is>
-          <t>English</t>
+          <t>Social Science</t>
         </is>
       </c>
       <c r="L274" t="inlineStr">
         <is>
-          <t>tchr_norhaima</t>
+          <t>tchr_sophia</t>
         </is>
       </c>
       <c r="M274" t="inlineStr">
         <is>
-          <t>Teacher Norhaima</t>
+          <t>Teacher Sophia</t>
         </is>
       </c>
       <c r="N274" t="n">
@@ -18525,22 +18525,22 @@
       </c>
       <c r="E275" t="inlineStr">
         <is>
-          <t>sec_grade_9_abu_jandal_ibn_suhayl_2nd_shift_girls</t>
+          <t>sec_k1_husain_ibn_ali_2nd_shift</t>
         </is>
       </c>
       <c r="F275" t="inlineStr">
         <is>
-          <t>GRADE 9 - ABU JANDAL IBN SUHAYL (2ND SHIFT) GIRLS</t>
+          <t>K1 - HUSAIN IBN ALI (2ND SHIFT)</t>
         </is>
       </c>
       <c r="G275" t="inlineStr">
         <is>
-          <t>Junior High School</t>
+          <t>Elementary</t>
         </is>
       </c>
       <c r="H275" t="inlineStr">
         <is>
-          <t>Grade 9</t>
+          <t>Kinder 1</t>
         </is>
       </c>
       <c r="I275" t="inlineStr">
@@ -18550,22 +18550,22 @@
       </c>
       <c r="J275" t="inlineStr">
         <is>
-          <t>subj_social_studies</t>
+          <t>subj_hadith</t>
         </is>
       </c>
       <c r="K275" t="inlineStr">
         <is>
-          <t>Social Science</t>
+          <t>Hadith</t>
         </is>
       </c>
       <c r="L275" t="inlineStr">
         <is>
-          <t>tchr_sophia</t>
+          <t>tchr_hainur</t>
         </is>
       </c>
       <c r="M275" t="inlineStr">
         <is>
-          <t>Teacher Sophia</t>
+          <t>Ustadha Hainur</t>
         </is>
       </c>
       <c r="N275" t="n">
@@ -18591,12 +18591,12 @@
       </c>
       <c r="E276" t="inlineStr">
         <is>
-          <t>sec_k1_husain_ibn_ali_2nd_shift</t>
+          <t>sec_k2_abdullah_ibn_mas_ud_2nd_shift</t>
         </is>
       </c>
       <c r="F276" t="inlineStr">
         <is>
-          <t>K1 - HUSAIN IBN ALI (2ND SHIFT)</t>
+          <t>K2 - ABDULLAH IBN MAS'UD (2ND SHIFT)</t>
         </is>
       </c>
       <c r="G276" t="inlineStr">
@@ -18606,7 +18606,7 @@
       </c>
       <c r="H276" t="inlineStr">
         <is>
-          <t>Kinder 1</t>
+          <t>Kinder 2</t>
         </is>
       </c>
       <c r="I276" t="inlineStr">
@@ -18616,22 +18616,22 @@
       </c>
       <c r="J276" t="inlineStr">
         <is>
-          <t>subj_hadith</t>
+          <t>subj_oral_written_exam</t>
         </is>
       </c>
       <c r="K276" t="inlineStr">
         <is>
-          <t>Hadith</t>
+          <t>Oral &amp; Written Exam</t>
         </is>
       </c>
       <c r="L276" t="inlineStr">
         <is>
-          <t>tchr_hainur</t>
+          <t>tchr_ayah</t>
         </is>
       </c>
       <c r="M276" t="inlineStr">
         <is>
-          <t>Ustadh Hainur</t>
+          <t>Teacher Ayah</t>
         </is>
       </c>
       <c r="N276" t="n">
@@ -18657,12 +18657,12 @@
       </c>
       <c r="E277" t="inlineStr">
         <is>
-          <t>sec_k2_abdullah_ibn_mas_ud_2nd_shift</t>
+          <t>sec_kinder_2_khabaab_ibn_arat_2nd_shift</t>
         </is>
       </c>
       <c r="F277" t="inlineStr">
         <is>
-          <t>K2 - ABDULLAH IBN MAS'UD (2ND SHIFT)</t>
+          <t>Kinder 2 KHABAAB IBN ARAT (2ND SHIFT)</t>
         </is>
       </c>
       <c r="G277" t="inlineStr">
@@ -18682,22 +18682,22 @@
       </c>
       <c r="J277" t="inlineStr">
         <is>
-          <t>subj_oral_written_exam</t>
+          <t>subj_hadith</t>
         </is>
       </c>
       <c r="K277" t="inlineStr">
         <is>
-          <t>Oral &amp; Written Exam</t>
+          <t>Hadith</t>
         </is>
       </c>
       <c r="L277" t="inlineStr">
         <is>
-          <t>tchr_ayah</t>
+          <t>tchr_faidh</t>
         </is>
       </c>
       <c r="M277" t="inlineStr">
         <is>
-          <t>Teacher Ayah</t>
+          <t>Ustadh Faidh</t>
         </is>
       </c>
       <c r="N277" t="n">
@@ -18714,21 +18714,21 @@
         </is>
       </c>
       <c r="C278" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D278" t="inlineStr">
         <is>
-          <t>04:20 PM – 05:20 PM</t>
+          <t>05:30 PM – 06:30 PM</t>
         </is>
       </c>
       <c r="E278" t="inlineStr">
         <is>
-          <t>sec_kinder_2_khabaab_ibn_arat_2nd_shift</t>
+          <t>sec_grade_1_sa_ad_ibn_abi_waqqaas_2nd_shift</t>
         </is>
       </c>
       <c r="F278" t="inlineStr">
         <is>
-          <t>Kinder 2 KHABAAB IBN ARAT (2ND SHIFT)</t>
+          <t>GRADE 1 - SA'AD IBN ABI WAQQAAS (2ND SHIFT)</t>
         </is>
       </c>
       <c r="G278" t="inlineStr">
@@ -18738,7 +18738,7 @@
       </c>
       <c r="H278" t="inlineStr">
         <is>
-          <t>Kinder 2</t>
+          <t>Grade 1</t>
         </is>
       </c>
       <c r="I278" t="inlineStr">
@@ -18748,22 +18748,22 @@
       </c>
       <c r="J278" t="inlineStr">
         <is>
-          <t>subj_hadith</t>
+          <t>subj_math</t>
         </is>
       </c>
       <c r="K278" t="inlineStr">
         <is>
-          <t>Hadith</t>
+          <t>Math</t>
         </is>
       </c>
       <c r="L278" t="inlineStr">
         <is>
-          <t>tchr_faidh</t>
+          <t>tchr_joanna</t>
         </is>
       </c>
       <c r="M278" t="inlineStr">
         <is>
-          <t>Ustadh Faidh</t>
+          <t>Teacher Joanna</t>
         </is>
       </c>
       <c r="N278" t="n">
@@ -18789,12 +18789,12 @@
       </c>
       <c r="E279" t="inlineStr">
         <is>
-          <t>sec_grade_1_sa_ad_ibn_abi_waqqaas_2nd_shift</t>
+          <t>sec_grade_1_suhayb_ar_rumi_2nd_shift</t>
         </is>
       </c>
       <c r="F279" t="inlineStr">
         <is>
-          <t>GRADE 1 - SA'AD IBN ABI WAQQAAS (2ND SHIFT)</t>
+          <t>GRADE 1 - SUHAYB AR-RUMI (2ND SHIFT)</t>
         </is>
       </c>
       <c r="G279" t="inlineStr">
@@ -18814,22 +18814,22 @@
       </c>
       <c r="J279" t="inlineStr">
         <is>
-          <t>subj_math</t>
+          <t>subj_reading_literacy</t>
         </is>
       </c>
       <c r="K279" t="inlineStr">
         <is>
-          <t>Math</t>
+          <t>Reading &amp; Literacy</t>
         </is>
       </c>
       <c r="L279" t="inlineStr">
         <is>
-          <t>tchr_joanna</t>
+          <t>tchr_katrina</t>
         </is>
       </c>
       <c r="M279" t="inlineStr">
         <is>
-          <t>Teacher Joanna</t>
+          <t>Teacher Katrina</t>
         </is>
       </c>
       <c r="N279" t="n">
@@ -18855,22 +18855,22 @@
       </c>
       <c r="E280" t="inlineStr">
         <is>
-          <t>sec_grade_1_suhayb_ar_rumi_2nd_shift</t>
+          <t>sec_grade_10_abu_ayyub_al_ansari_2nd_shift_boys</t>
         </is>
       </c>
       <c r="F280" t="inlineStr">
         <is>
-          <t>GRADE 1 - SUHAYB AR-RUMI (2ND SHIFT)</t>
+          <t>GRADE 10 - ABU AYYUB AL-ANSARI (2ND SHIFT) BOYS</t>
         </is>
       </c>
       <c r="G280" t="inlineStr">
         <is>
-          <t>Elementary</t>
+          <t>Junior High School</t>
         </is>
       </c>
       <c r="H280" t="inlineStr">
         <is>
-          <t>Grade 1</t>
+          <t>Grade 10</t>
         </is>
       </c>
       <c r="I280" t="inlineStr">
@@ -18880,22 +18880,22 @@
       </c>
       <c r="J280" t="inlineStr">
         <is>
-          <t>subj_reading_literacy</t>
+          <t>subj_shaf</t>
         </is>
       </c>
       <c r="K280" t="inlineStr">
         <is>
-          <t>Reading &amp; Literacy</t>
+          <t>SHAF</t>
         </is>
       </c>
       <c r="L280" t="inlineStr">
         <is>
-          <t>tchr_katrina</t>
+          <t>tchr_bustamante</t>
         </is>
       </c>
       <c r="M280" t="inlineStr">
         <is>
-          <t>Teacher Katrina</t>
+          <t>Alim Bustamante</t>
         </is>
       </c>
       <c r="N280" t="n">
@@ -18921,22 +18921,22 @@
       </c>
       <c r="E281" t="inlineStr">
         <is>
-          <t>sec_grade_10_abu_ayyub_al_ansari_2nd_shift_boys</t>
+          <t>sec_grade_2_aasim_ibn_thabit_2nd_shift</t>
         </is>
       </c>
       <c r="F281" t="inlineStr">
         <is>
-          <t>GRADE 10 - ABU AYYUB AL-ANSARI (2ND SHIFT) BOYS</t>
+          <t>GRADE 2 - AASIM IBN THABIT (2ND SHIFT)</t>
         </is>
       </c>
       <c r="G281" t="inlineStr">
         <is>
-          <t>Junior High School</t>
+          <t>Elementary</t>
         </is>
       </c>
       <c r="H281" t="inlineStr">
         <is>
-          <t>Grade 10</t>
+          <t>Grade 2</t>
         </is>
       </c>
       <c r="I281" t="inlineStr">
@@ -18946,22 +18946,22 @@
       </c>
       <c r="J281" t="inlineStr">
         <is>
-          <t>subj_shaf</t>
+          <t>subj_arabic</t>
         </is>
       </c>
       <c r="K281" t="inlineStr">
         <is>
-          <t>SHAF</t>
+          <t>Arabic</t>
         </is>
       </c>
       <c r="L281" t="inlineStr">
         <is>
-          <t>tchr_bustamante</t>
+          <t>tchr_hainur</t>
         </is>
       </c>
       <c r="M281" t="inlineStr">
         <is>
-          <t>Alim Bustamante</t>
+          <t>Ustadha Hainur</t>
         </is>
       </c>
       <c r="N281" t="n">
@@ -18987,12 +18987,12 @@
       </c>
       <c r="E282" t="inlineStr">
         <is>
-          <t>sec_grade_2_aasim_ibn_thabit_2nd_shift</t>
+          <t>sec_grade_2_saeed_ibn_zayd_2nd_shift</t>
         </is>
       </c>
       <c r="F282" t="inlineStr">
         <is>
-          <t>GRADE 2 - AASIM IBN THABIT (2ND SHIFT)</t>
+          <t>GRADE 2 - SAEED IBN ZAYD (2ND SHIFT)</t>
         </is>
       </c>
       <c r="G282" t="inlineStr">
@@ -19012,22 +19012,22 @@
       </c>
       <c r="J282" t="inlineStr">
         <is>
-          <t>subj_arabic</t>
+          <t>subj_makabansa</t>
         </is>
       </c>
       <c r="K282" t="inlineStr">
         <is>
-          <t>Arabic</t>
+          <t>Makabansa</t>
         </is>
       </c>
       <c r="L282" t="inlineStr">
         <is>
-          <t>tchr_hainur</t>
+          <t>tchr_monisa</t>
         </is>
       </c>
       <c r="M282" t="inlineStr">
         <is>
-          <t>Ustadh Hainur</t>
+          <t>Teacher Monisa</t>
         </is>
       </c>
       <c r="N282" t="n">
@@ -19053,12 +19053,12 @@
       </c>
       <c r="E283" t="inlineStr">
         <is>
-          <t>sec_grade_2_saeed_ibn_zayd_2nd_shift</t>
+          <t>sec_grade_3_as_ad_ibn_zurarah_2nd_shift_mix</t>
         </is>
       </c>
       <c r="F283" t="inlineStr">
         <is>
-          <t>GRADE 2 - SAEED IBN ZAYD (2ND SHIFT)</t>
+          <t>GRADE 3 - AS'AD IBN ZURARAH (2ND SHIFT) MIX</t>
         </is>
       </c>
       <c r="G283" t="inlineStr">
@@ -19068,7 +19068,7 @@
       </c>
       <c r="H283" t="inlineStr">
         <is>
-          <t>Grade 2</t>
+          <t>Grade 3</t>
         </is>
       </c>
       <c r="I283" t="inlineStr">
@@ -19078,22 +19078,22 @@
       </c>
       <c r="J283" t="inlineStr">
         <is>
-          <t>subj_makabansa</t>
+          <t>subj_science</t>
         </is>
       </c>
       <c r="K283" t="inlineStr">
         <is>
-          <t>Makabansa</t>
+          <t>Science</t>
         </is>
       </c>
       <c r="L283" t="inlineStr">
         <is>
-          <t>tchr_monisa</t>
+          <t>tchr_saimonah</t>
         </is>
       </c>
       <c r="M283" t="inlineStr">
         <is>
-          <t>Teacher Monisa</t>
+          <t>Teacher Saimonah</t>
         </is>
       </c>
       <c r="N283" t="n">
@@ -19119,12 +19119,12 @@
       </c>
       <c r="E284" t="inlineStr">
         <is>
-          <t>sec_grade_3_as_ad_ibn_zurarah_2nd_shift_mix</t>
+          <t>sec_grade_3_thabit_ibn_qays_2nd_shift_boys</t>
         </is>
       </c>
       <c r="F284" t="inlineStr">
         <is>
-          <t>GRADE 3 - AS'AD IBN ZURARAH (2ND SHIFT) MIX</t>
+          <t>GRADE 3 - THABIT IBN QAYS (2ND SHIFT) - BOYS</t>
         </is>
       </c>
       <c r="G284" t="inlineStr">
@@ -19144,22 +19144,22 @@
       </c>
       <c r="J284" t="inlineStr">
         <is>
-          <t>subj_science</t>
+          <t>subj_english</t>
         </is>
       </c>
       <c r="K284" t="inlineStr">
         <is>
-          <t>Science</t>
+          <t>English</t>
         </is>
       </c>
       <c r="L284" t="inlineStr">
         <is>
-          <t>tchr_saimonah</t>
+          <t>tchr_marham</t>
         </is>
       </c>
       <c r="M284" t="inlineStr">
         <is>
-          <t>Teacher Saimonah</t>
+          <t>Teacher Marham</t>
         </is>
       </c>
       <c r="N284" t="n">
@@ -19185,12 +19185,12 @@
       </c>
       <c r="E285" t="inlineStr">
         <is>
-          <t>sec_grade_3_thabit_ibn_qays_2nd_shift_boys</t>
+          <t>sec_grade_3_zayd_ibn_haritha_2nd_shift_girls</t>
         </is>
       </c>
       <c r="F285" t="inlineStr">
         <is>
-          <t>GRADE 3 - THABIT IBN QAYS (2ND SHIFT) - BOYS</t>
+          <t>GRADE 3 - ZAYD IBN HARITHA (2ND SHIFT) - GIRLS</t>
         </is>
       </c>
       <c r="G285" t="inlineStr">
@@ -19210,22 +19210,22 @@
       </c>
       <c r="J285" t="inlineStr">
         <is>
-          <t>subj_english</t>
+          <t>subj_math</t>
         </is>
       </c>
       <c r="K285" t="inlineStr">
         <is>
-          <t>English</t>
+          <t>Math</t>
         </is>
       </c>
       <c r="L285" t="inlineStr">
         <is>
-          <t>tchr_marham</t>
+          <t>tchr_jerlyn</t>
         </is>
       </c>
       <c r="M285" t="inlineStr">
         <is>
-          <t>Teacher Marham</t>
+          <t>Teacher Jerlyn</t>
         </is>
       </c>
       <c r="N285" t="n">
@@ -19251,12 +19251,12 @@
       </c>
       <c r="E286" t="inlineStr">
         <is>
-          <t>sec_grade_3_zayd_ibn_haritha_2nd_shift_girls</t>
+          <t>sec_grade_4_az_zubair_ibn_al_awwaam_2nd_shift</t>
         </is>
       </c>
       <c r="F286" t="inlineStr">
         <is>
-          <t>GRADE 3 - ZAYD IBN HARITHA (2ND SHIFT) - GIRLS</t>
+          <t>GRADE 4 - AZ ZUBAIR IBN AL AWWAAM (2ND SHIFT)</t>
         </is>
       </c>
       <c r="G286" t="inlineStr">
@@ -19266,7 +19266,7 @@
       </c>
       <c r="H286" t="inlineStr">
         <is>
-          <t>Grade 3</t>
+          <t>Grade 4</t>
         </is>
       </c>
       <c r="I286" t="inlineStr">
@@ -19276,22 +19276,22 @@
       </c>
       <c r="J286" t="inlineStr">
         <is>
-          <t>subj_math</t>
+          <t>subj_mapeh</t>
         </is>
       </c>
       <c r="K286" t="inlineStr">
         <is>
-          <t>Math</t>
+          <t>MAPEH</t>
         </is>
       </c>
       <c r="L286" t="inlineStr">
         <is>
-          <t>tchr_jerlyn</t>
+          <t>tchr_halnaisa</t>
         </is>
       </c>
       <c r="M286" t="inlineStr">
         <is>
-          <t>Teacher Jerlyn</t>
+          <t>Teacher Halnaisa</t>
         </is>
       </c>
       <c r="N286" t="n">
@@ -19317,12 +19317,12 @@
       </c>
       <c r="E287" t="inlineStr">
         <is>
-          <t>sec_grade_4_az_zubair_ibn_al_awwaam_2nd_shift</t>
+          <t>sec_grade_4_ikrimah_ibn_abi_jahl_2nd_shift</t>
         </is>
       </c>
       <c r="F287" t="inlineStr">
         <is>
-          <t>GRADE 4 - AZ ZUBAIR IBN AL AWWAAM (2ND SHIFT)</t>
+          <t>GRADE 4 - IKRIMAH IBN ABI JAHL (2ND SHIFT)</t>
         </is>
       </c>
       <c r="G287" t="inlineStr">
@@ -19342,22 +19342,22 @@
       </c>
       <c r="J287" t="inlineStr">
         <is>
-          <t>subj_mapeh</t>
+          <t>subj_gmrc</t>
         </is>
       </c>
       <c r="K287" t="inlineStr">
         <is>
-          <t>MAPEH</t>
+          <t>GMRC</t>
         </is>
       </c>
       <c r="L287" t="inlineStr">
         <is>
-          <t>tchr_halnaisa</t>
+          <t>tchr_sahdia</t>
         </is>
       </c>
       <c r="M287" t="inlineStr">
         <is>
-          <t>Teacher Halnaisa</t>
+          <t>Teacher Sahdia</t>
         </is>
       </c>
       <c r="N287" t="n">
@@ -19383,12 +19383,12 @@
       </c>
       <c r="E288" t="inlineStr">
         <is>
-          <t>sec_grade_4_ikrimah_ibn_abi_jahl_2nd_shift</t>
+          <t>sec_grade_5_al_harith_bin_awf_2nd_shift</t>
         </is>
       </c>
       <c r="F288" t="inlineStr">
         <is>
-          <t>GRADE 4 - IKRIMAH IBN ABI JAHL (2ND SHIFT)</t>
+          <t>GRADE 5 - AL HARITH BIN AWF (2ND SHIFT)</t>
         </is>
       </c>
       <c r="G288" t="inlineStr">
@@ -19398,7 +19398,7 @@
       </c>
       <c r="H288" t="inlineStr">
         <is>
-          <t>Grade 4</t>
+          <t>Grade 5</t>
         </is>
       </c>
       <c r="I288" t="inlineStr">
@@ -19408,22 +19408,22 @@
       </c>
       <c r="J288" t="inlineStr">
         <is>
-          <t>subj_gmrc</t>
+          <t>subj_science</t>
         </is>
       </c>
       <c r="K288" t="inlineStr">
         <is>
-          <t>GMRC</t>
+          <t>Science</t>
         </is>
       </c>
       <c r="L288" t="inlineStr">
         <is>
-          <t>tchr_sahdia</t>
+          <t>tchr_anna</t>
         </is>
       </c>
       <c r="M288" t="inlineStr">
         <is>
-          <t>Teacher Sahdia</t>
+          <t>Teacher Anna</t>
         </is>
       </c>
       <c r="N288" t="n">
@@ -19449,12 +19449,12 @@
       </c>
       <c r="E289" t="inlineStr">
         <is>
-          <t>sec_grade_5_al_harith_bin_awf_2nd_shift</t>
+          <t>sec_grade_5_ja_far_ibn_abi_talib_2nd_shift_mix</t>
         </is>
       </c>
       <c r="F289" t="inlineStr">
         <is>
-          <t>GRADE 5 - AL HARITH BIN AWF (2ND SHIFT)</t>
+          <t>GRADE 5 - JA'FAR IBN ABI TALIB (2ND SHIFT) - MIX</t>
         </is>
       </c>
       <c r="G289" t="inlineStr">
@@ -19474,22 +19474,22 @@
       </c>
       <c r="J289" t="inlineStr">
         <is>
-          <t>subj_science</t>
+          <t>subj_tle</t>
         </is>
       </c>
       <c r="K289" t="inlineStr">
         <is>
-          <t>Science</t>
+          <t>TLE</t>
         </is>
       </c>
       <c r="L289" t="inlineStr">
         <is>
-          <t>tchr_anna</t>
+          <t>tchr_jenny</t>
         </is>
       </c>
       <c r="M289" t="inlineStr">
         <is>
-          <t>Teacher Anna</t>
+          <t>Teacher Jenny</t>
         </is>
       </c>
       <c r="N289" t="n">
@@ -19515,12 +19515,12 @@
       </c>
       <c r="E290" t="inlineStr">
         <is>
-          <t>sec_grade_5_ja_far_ibn_abi_talib_2nd_shift_mix</t>
+          <t>sec_grade_5_mus_ab_ibn_abdul_mutalib_2nd_shift</t>
         </is>
       </c>
       <c r="F290" t="inlineStr">
         <is>
-          <t>GRADE 5 - JA'FAR IBN ABI TALIB (2ND SHIFT) - MIX</t>
+          <t>GRADE 5 - MUS'AB IBN ABDUL MUTALIB (2ND SHIFT)</t>
         </is>
       </c>
       <c r="G290" t="inlineStr">
@@ -19540,22 +19540,22 @@
       </c>
       <c r="J290" t="inlineStr">
         <is>
-          <t>subj_tle</t>
+          <t>subj_english</t>
         </is>
       </c>
       <c r="K290" t="inlineStr">
         <is>
-          <t>TLE</t>
+          <t>English</t>
         </is>
       </c>
       <c r="L290" t="inlineStr">
         <is>
-          <t>tchr_jenny</t>
+          <t>tchr_jessa</t>
         </is>
       </c>
       <c r="M290" t="inlineStr">
         <is>
-          <t>Teacher Jenny</t>
+          <t>Teacher Jessa</t>
         </is>
       </c>
       <c r="N290" t="n">
@@ -19581,12 +19581,12 @@
       </c>
       <c r="E291" t="inlineStr">
         <is>
-          <t>sec_grade_5_mus_ab_ibn_abdul_mutalib_2nd_shift</t>
+          <t>sec_grade_6_dihya_ibn_khalifah_2nd_shift_girls</t>
         </is>
       </c>
       <c r="F291" t="inlineStr">
         <is>
-          <t>GRADE 5 - MUS'AB IBN ABDUL MUTALIB (2ND SHIFT)</t>
+          <t>GRADE 6 - DIHYA IBN KHALIFAH (2ND SHIFT) GIRLS</t>
         </is>
       </c>
       <c r="G291" t="inlineStr">
@@ -19596,7 +19596,7 @@
       </c>
       <c r="H291" t="inlineStr">
         <is>
-          <t>Grade 5</t>
+          <t>Grade 6</t>
         </is>
       </c>
       <c r="I291" t="inlineStr">
@@ -19606,22 +19606,22 @@
       </c>
       <c r="J291" t="inlineStr">
         <is>
-          <t>subj_english</t>
+          <t>subj_filipino</t>
         </is>
       </c>
       <c r="K291" t="inlineStr">
         <is>
-          <t>English</t>
+          <t>Filipino</t>
         </is>
       </c>
       <c r="L291" t="inlineStr">
         <is>
-          <t>tchr_jessa</t>
+          <t>tchr_normylah</t>
         </is>
       </c>
       <c r="M291" t="inlineStr">
         <is>
-          <t>Teacher Jessa</t>
+          <t>Teacher Normylah</t>
         </is>
       </c>
       <c r="N291" t="n">
@@ -19647,12 +19647,12 @@
       </c>
       <c r="E292" t="inlineStr">
         <is>
-          <t>sec_grade_6_dihya_ibn_khalifah_2nd_shift_girls</t>
+          <t>sec_grade_6_khaleed_ibn_waleed_2nd_shift</t>
         </is>
       </c>
       <c r="F292" t="inlineStr">
         <is>
-          <t>GRADE 6 - DIHYA IBN KHALIFAH (2ND SHIFT) GIRLS</t>
+          <t>GRADE 6 - KHALEED IBN WALEED (2ND SHIFT)</t>
         </is>
       </c>
       <c r="G292" t="inlineStr">
@@ -19672,22 +19672,22 @@
       </c>
       <c r="J292" t="inlineStr">
         <is>
-          <t>subj_filipino</t>
+          <t>subj_shaf</t>
         </is>
       </c>
       <c r="K292" t="inlineStr">
         <is>
-          <t>Filipino</t>
+          <t>SHAF</t>
         </is>
       </c>
       <c r="L292" t="inlineStr">
         <is>
-          <t>tchr_normylah</t>
+          <t>tchr_abdiraheem</t>
         </is>
       </c>
       <c r="M292" t="inlineStr">
         <is>
-          <t>Teacher Normylah</t>
+          <t>Ustadh Abdiraheem</t>
         </is>
       </c>
       <c r="N292" t="n">
@@ -19713,22 +19713,22 @@
       </c>
       <c r="E293" t="inlineStr">
         <is>
-          <t>sec_grade_6_khaleed_ibn_waleed_2nd_shift</t>
+          <t>sec_grade_7_anas_ibn_malik_2nd_shift_mix</t>
         </is>
       </c>
       <c r="F293" t="inlineStr">
         <is>
-          <t>GRADE 6 - KHALEED IBN WALEED (2ND SHIFT)</t>
+          <t>GRADE 7 - ANAS IBN MALIK (2ND SHIFT) - MIX</t>
         </is>
       </c>
       <c r="G293" t="inlineStr">
         <is>
-          <t>Elementary</t>
+          <t>Junior High School</t>
         </is>
       </c>
       <c r="H293" t="inlineStr">
         <is>
-          <t>Grade 6</t>
+          <t>Grade 7</t>
         </is>
       </c>
       <c r="I293" t="inlineStr">
@@ -19738,22 +19738,22 @@
       </c>
       <c r="J293" t="inlineStr">
         <is>
-          <t>subj_shaf</t>
+          <t>subj_arabic</t>
         </is>
       </c>
       <c r="K293" t="inlineStr">
         <is>
-          <t>SHAF</t>
+          <t>Arabic</t>
         </is>
       </c>
       <c r="L293" t="inlineStr">
         <is>
-          <t>tchr_abdiraheem</t>
+          <t>tchr_ali</t>
         </is>
       </c>
       <c r="M293" t="inlineStr">
         <is>
-          <t>Ustadh Abdiraheem</t>
+          <t>Ustadh Ali</t>
         </is>
       </c>
       <c r="N293" t="n">
@@ -19779,12 +19779,12 @@
       </c>
       <c r="E294" t="inlineStr">
         <is>
-          <t>sec_grade_7_anas_ibn_malik_2nd_shift_mix</t>
+          <t>sec_grade_8_mu_adh_ibn_jabal_2nd_shift_boys</t>
         </is>
       </c>
       <c r="F294" t="inlineStr">
         <is>
-          <t>GRADE 7 - ANAS IBN MALIK (2ND SHIFT) - MIX</t>
+          <t>GRADE 8 - MU'ADH IBN JABAL (2ND SHIFT) - BOYS</t>
         </is>
       </c>
       <c r="G294" t="inlineStr">
@@ -19794,7 +19794,7 @@
       </c>
       <c r="H294" t="inlineStr">
         <is>
-          <t>Grade 7</t>
+          <t>Grade 8</t>
         </is>
       </c>
       <c r="I294" t="inlineStr">
@@ -19804,22 +19804,22 @@
       </c>
       <c r="J294" t="inlineStr">
         <is>
-          <t>subj_arabic</t>
+          <t>subj_shaf</t>
         </is>
       </c>
       <c r="K294" t="inlineStr">
         <is>
-          <t>Arabic</t>
+          <t>SHAF</t>
         </is>
       </c>
       <c r="L294" t="inlineStr">
         <is>
-          <t>tchr_ali</t>
+          <t>tchr_samsuddin</t>
         </is>
       </c>
       <c r="M294" t="inlineStr">
         <is>
-          <t>Ustadh Ali</t>
+          <t>Alim Samsuddin</t>
         </is>
       </c>
       <c r="N294" t="n">
@@ -19845,12 +19845,12 @@
       </c>
       <c r="E295" t="inlineStr">
         <is>
-          <t>sec_grade_8_mu_adh_ibn_jabal_2nd_shift_boys</t>
+          <t>sec_grade_8_nuaym_ibn_mas_ud_2nd_shift_mix</t>
         </is>
       </c>
       <c r="F295" t="inlineStr">
         <is>
-          <t>GRADE 8 - MU'ADH IBN JABAL (2ND SHIFT) - BOYS</t>
+          <t>GRADE 8 - NUAYM IBN MAS'UD (2ND SHIFT) MIX</t>
         </is>
       </c>
       <c r="G295" t="inlineStr">
@@ -19911,12 +19911,12 @@
       </c>
       <c r="E296" t="inlineStr">
         <is>
-          <t>sec_grade_8_nuaym_ibn_mas_ud_2nd_shift_mix</t>
+          <t>sec_grade_9_abu_dharr_al_ghifarri_2nd_shift_boys</t>
         </is>
       </c>
       <c r="F296" t="inlineStr">
         <is>
-          <t>GRADE 8 - NUAYM IBN MAS'UD (2ND SHIFT) MIX</t>
+          <t>GRADE 9 - ABU DHARR AL GHIFARRI (2ND SHIFT) BOYS</t>
         </is>
       </c>
       <c r="G296" t="inlineStr">
@@ -19926,7 +19926,7 @@
       </c>
       <c r="H296" t="inlineStr">
         <is>
-          <t>Grade 8</t>
+          <t>Grade 9</t>
         </is>
       </c>
       <c r="I296" t="inlineStr">
@@ -19936,22 +19936,22 @@
       </c>
       <c r="J296" t="inlineStr">
         <is>
-          <t>subj_shaf</t>
+          <t>subj_science</t>
         </is>
       </c>
       <c r="K296" t="inlineStr">
         <is>
-          <t>SHAF</t>
+          <t>Science</t>
         </is>
       </c>
       <c r="L296" t="inlineStr">
         <is>
-          <t>tchr_samsuddin</t>
+          <t>tchr_rowena</t>
         </is>
       </c>
       <c r="M296" t="inlineStr">
         <is>
-          <t>Alim Samsuddin</t>
+          <t>Teacher Rowena</t>
         </is>
       </c>
       <c r="N296" t="n">
@@ -19977,12 +19977,12 @@
       </c>
       <c r="E297" t="inlineStr">
         <is>
-          <t>sec_grade_9_abu_dharr_al_ghifarri_2nd_shift_boys</t>
+          <t>sec_grade_9_abu_jandal_ibn_suhayl_2nd_shift_girls</t>
         </is>
       </c>
       <c r="F297" t="inlineStr">
         <is>
-          <t>GRADE 9 - ABU DHARR AL GHIFARRI (2ND SHIFT) BOYS</t>
+          <t>GRADE 9 - ABU JANDAL IBN SUHAYL (2ND SHIFT) GIRLS</t>
         </is>
       </c>
       <c r="G297" t="inlineStr">
@@ -20002,22 +20002,22 @@
       </c>
       <c r="J297" t="inlineStr">
         <is>
-          <t>subj_science</t>
+          <t>subj_filipino</t>
         </is>
       </c>
       <c r="K297" t="inlineStr">
         <is>
-          <t>Science</t>
+          <t>Filipino</t>
         </is>
       </c>
       <c r="L297" t="inlineStr">
         <is>
-          <t>tchr_rowena</t>
+          <t>tchr_nadzra</t>
         </is>
       </c>
       <c r="M297" t="inlineStr">
         <is>
-          <t>Teacher Rowena</t>
+          <t>Teacher Nadzra</t>
         </is>
       </c>
       <c r="N297" t="n">
@@ -20026,64 +20026,64 @@
     </row>
     <row r="298">
       <c r="A298" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B298" t="inlineStr">
         <is>
-          <t>Thursday, September 3, 2026</t>
+          <t>Sunday, September 6, 2026</t>
         </is>
       </c>
       <c r="C298" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D298" t="inlineStr">
         <is>
-          <t>05:30 PM – 06:30 PM</t>
+          <t>08:00 AM – 09:00 AM</t>
         </is>
       </c>
       <c r="E298" t="inlineStr">
         <is>
-          <t>sec_grade_9_abu_jandal_ibn_suhayl_2nd_shift_girls</t>
+          <t>sec_grade_1_face_to_face</t>
         </is>
       </c>
       <c r="F298" t="inlineStr">
         <is>
-          <t>GRADE 9 - ABU JANDAL IBN SUHAYL (2ND SHIFT) GIRLS</t>
+          <t>GRADE 1 (FACE TO FACE)</t>
         </is>
       </c>
       <c r="G298" t="inlineStr">
         <is>
-          <t>Junior High School</t>
+          <t>Elementary</t>
         </is>
       </c>
       <c r="H298" t="inlineStr">
         <is>
-          <t>Grade 9</t>
+          <t>Grade 1</t>
         </is>
       </c>
       <c r="I298" t="inlineStr">
         <is>
-          <t>ODL - 2ND SHIFT</t>
+          <t>F2F</t>
         </is>
       </c>
       <c r="J298" t="inlineStr">
         <is>
-          <t>subj_filipino</t>
+          <t>subj_shaf</t>
         </is>
       </c>
       <c r="K298" t="inlineStr">
         <is>
-          <t>Filipino</t>
+          <t>SHAF</t>
         </is>
       </c>
       <c r="L298" t="inlineStr">
         <is>
-          <t>tchr_nadzra</t>
+          <t>tchr_abdiraheem</t>
         </is>
       </c>
       <c r="M298" t="inlineStr">
         <is>
-          <t>Teacher Nadzra</t>
+          <t>Ustadh Abdiraheem</t>
         </is>
       </c>
       <c r="N298" t="n">
@@ -20104,27 +20104,27 @@
       </c>
       <c r="D299" t="inlineStr">
         <is>
-          <t>08:00 AM – 09:00 AM</t>
+          <t>08:00 AM – 10:00 AM</t>
         </is>
       </c>
       <c r="E299" t="inlineStr">
         <is>
-          <t>sec_grade_1_face_to_face</t>
+          <t>sec_grade_12_suhayb_ar_rumi</t>
         </is>
       </c>
       <c r="F299" t="inlineStr">
         <is>
-          <t>GRADE 1 (FACE TO FACE)</t>
+          <t>GRADE 12 - SUHAYB AR-RUMI</t>
         </is>
       </c>
       <c r="G299" t="inlineStr">
         <is>
-          <t>Elementary</t>
+          <t>Senior High School</t>
         </is>
       </c>
       <c r="H299" t="inlineStr">
         <is>
-          <t>Grade 1</t>
+          <t>Grade 12</t>
         </is>
       </c>
       <c r="I299" t="inlineStr">
@@ -20134,26 +20134,26 @@
       </c>
       <c r="J299" t="inlineStr">
         <is>
-          <t>subj_shaf</t>
+          <t>subj_gen_physics_1</t>
         </is>
       </c>
       <c r="K299" t="inlineStr">
         <is>
-          <t>SHAF</t>
+          <t>General Physics 1</t>
         </is>
       </c>
       <c r="L299" t="inlineStr">
         <is>
-          <t>tchr_abdiraheem</t>
+          <t>tchr_aniah</t>
         </is>
       </c>
       <c r="M299" t="inlineStr">
         <is>
-          <t>Ustadh Abdiraheem</t>
+          <t>Teacher Aniah</t>
         </is>
       </c>
       <c r="N299" t="n">
-        <v>60</v>
+        <v>120</v>
       </c>
     </row>
     <row r="300">
@@ -20170,27 +20170,27 @@
       </c>
       <c r="D300" t="inlineStr">
         <is>
-          <t>08:00 AM – 10:00 AM</t>
+          <t>08:00 AM – 09:00 AM</t>
         </is>
       </c>
       <c r="E300" t="inlineStr">
         <is>
-          <t>sec_grade_12_suhayb_ar_rumi</t>
+          <t>sec_grade_3_face_to_face</t>
         </is>
       </c>
       <c r="F300" t="inlineStr">
         <is>
-          <t>GRADE 12 - SUHAYB AR-RUMI</t>
+          <t>GRADE 3 (FACE TO FACE)</t>
         </is>
       </c>
       <c r="G300" t="inlineStr">
         <is>
-          <t>Senior High School</t>
+          <t>Elementary</t>
         </is>
       </c>
       <c r="H300" t="inlineStr">
         <is>
-          <t>Grade 12</t>
+          <t>Grade 3</t>
         </is>
       </c>
       <c r="I300" t="inlineStr">
@@ -20200,26 +20200,26 @@
       </c>
       <c r="J300" t="inlineStr">
         <is>
-          <t>subj_gen_physics_1</t>
+          <t>subj_qur_an</t>
         </is>
       </c>
       <c r="K300" t="inlineStr">
         <is>
-          <t>General Physics 1</t>
+          <t>Qur'an</t>
         </is>
       </c>
       <c r="L300" t="inlineStr">
         <is>
-          <t>tchr_aniah</t>
+          <t>tchr_obaydah</t>
         </is>
       </c>
       <c r="M300" t="inlineStr">
         <is>
-          <t>Teacher Aniah</t>
+          <t>Ustadh Obaydah</t>
         </is>
       </c>
       <c r="N300" t="n">
-        <v>120</v>
+        <v>60</v>
       </c>
     </row>
     <row r="301">
@@ -20241,12 +20241,12 @@
       </c>
       <c r="E301" t="inlineStr">
         <is>
-          <t>sec_grade_3_face_to_face</t>
+          <t>sec_grade_5_face_to_face</t>
         </is>
       </c>
       <c r="F301" t="inlineStr">
         <is>
-          <t>GRADE 3 (FACE TO FACE)</t>
+          <t>GRADE 5 (FACE TO FACE)</t>
         </is>
       </c>
       <c r="G301" t="inlineStr">
@@ -20256,7 +20256,7 @@
       </c>
       <c r="H301" t="inlineStr">
         <is>
-          <t>Grade 3</t>
+          <t>Grade 5</t>
         </is>
       </c>
       <c r="I301" t="inlineStr">
@@ -20266,22 +20266,22 @@
       </c>
       <c r="J301" t="inlineStr">
         <is>
-          <t>subj_qur_an</t>
+          <t>subj_tle</t>
         </is>
       </c>
       <c r="K301" t="inlineStr">
         <is>
-          <t>Qur'an</t>
+          <t>TLE</t>
         </is>
       </c>
       <c r="L301" t="inlineStr">
         <is>
-          <t>tchr_obaydah</t>
+          <t>tchr_halnaisa</t>
         </is>
       </c>
       <c r="M301" t="inlineStr">
         <is>
-          <t>Ustadh Obaydah</t>
+          <t>Teacher Halnaisa</t>
         </is>
       </c>
       <c r="N301" t="n">
@@ -20307,22 +20307,22 @@
       </c>
       <c r="E302" t="inlineStr">
         <is>
-          <t>sec_grade_5_face_to_face</t>
+          <t>sec_grade_7_8_boys_face_to_face</t>
         </is>
       </c>
       <c r="F302" t="inlineStr">
         <is>
-          <t>GRADE 5 (FACE TO FACE)</t>
+          <t>GRADE 7 &amp; 8 BOYS (FACE TO FACE)</t>
         </is>
       </c>
       <c r="G302" t="inlineStr">
         <is>
-          <t>Elementary</t>
+          <t>Junior High School</t>
         </is>
       </c>
       <c r="H302" t="inlineStr">
         <is>
-          <t>Grade 5</t>
+          <t>Grade 7 &amp; 8</t>
         </is>
       </c>
       <c r="I302" t="inlineStr">
@@ -20332,22 +20332,22 @@
       </c>
       <c r="J302" t="inlineStr">
         <is>
-          <t>subj_tle</t>
+          <t>subj_mapeh</t>
         </is>
       </c>
       <c r="K302" t="inlineStr">
         <is>
-          <t>TLE</t>
+          <t>MAPEH</t>
         </is>
       </c>
       <c r="L302" t="inlineStr">
         <is>
-          <t>tchr_halnaisa</t>
+          <t>tchr_franchette</t>
         </is>
       </c>
       <c r="M302" t="inlineStr">
         <is>
-          <t>Teacher Halnaisa</t>
+          <t>Teacher Franchette</t>
         </is>
       </c>
       <c r="N302" t="n">
@@ -20373,12 +20373,12 @@
       </c>
       <c r="E303" t="inlineStr">
         <is>
-          <t>sec_grade_7_8_boys_face_to_face</t>
+          <t>sec_grade_7_8_girls_face_to_face</t>
         </is>
       </c>
       <c r="F303" t="inlineStr">
         <is>
-          <t>GRADE 7 &amp; 8 BOYS (FACE TO FACE)</t>
+          <t>GRADE 7 &amp; 8 GIRLS (FACE TO FACE)</t>
         </is>
       </c>
       <c r="G303" t="inlineStr">
@@ -20398,22 +20398,22 @@
       </c>
       <c r="J303" t="inlineStr">
         <is>
-          <t>subj_mapeh</t>
+          <t>subj_english</t>
         </is>
       </c>
       <c r="K303" t="inlineStr">
         <is>
-          <t>MAPEH</t>
+          <t>English</t>
         </is>
       </c>
       <c r="L303" t="inlineStr">
         <is>
-          <t>tchr_franchette</t>
+          <t>tchr_jairah</t>
         </is>
       </c>
       <c r="M303" t="inlineStr">
         <is>
-          <t>Teacher Franchette</t>
+          <t>Teacher Jairah</t>
         </is>
       </c>
       <c r="N303" t="n">
@@ -20439,12 +20439,12 @@
       </c>
       <c r="E304" t="inlineStr">
         <is>
-          <t>sec_grade_7_8_girls_face_to_face</t>
+          <t>sec_grade_9_10_boys_face_to_face</t>
         </is>
       </c>
       <c r="F304" t="inlineStr">
         <is>
-          <t>GRADE 7 &amp; 8 GIRLS (FACE TO FACE)</t>
+          <t>GRADE 9 &amp; 10 BOYS (FACE TO FACE)</t>
         </is>
       </c>
       <c r="G304" t="inlineStr">
@@ -20454,7 +20454,7 @@
       </c>
       <c r="H304" t="inlineStr">
         <is>
-          <t>Grade 7 &amp; 8</t>
+          <t>Grade 9 &amp; 10</t>
         </is>
       </c>
       <c r="I304" t="inlineStr">
@@ -20464,22 +20464,22 @@
       </c>
       <c r="J304" t="inlineStr">
         <is>
-          <t>subj_english</t>
+          <t>subj_tle</t>
         </is>
       </c>
       <c r="K304" t="inlineStr">
         <is>
-          <t>English</t>
+          <t>TLE</t>
         </is>
       </c>
       <c r="L304" t="inlineStr">
         <is>
-          <t>tchr_jairah</t>
+          <t>tchr_angeleni</t>
         </is>
       </c>
       <c r="M304" t="inlineStr">
         <is>
-          <t>Teacher Jairah</t>
+          <t>Teacher Angeleni</t>
         </is>
       </c>
       <c r="N304" t="n">
@@ -20505,12 +20505,12 @@
       </c>
       <c r="E305" t="inlineStr">
         <is>
-          <t>sec_grade_9_10_boys_face_to_face</t>
+          <t>sec_grade_9_10_girls_face_to_face</t>
         </is>
       </c>
       <c r="F305" t="inlineStr">
         <is>
-          <t>GRADE 9 &amp; 10 BOYS (FACE TO FACE)</t>
+          <t>GRADE 9 &amp; 10 GIRLS (FACE TO FACE)</t>
         </is>
       </c>
       <c r="G305" t="inlineStr">
@@ -20530,22 +20530,22 @@
       </c>
       <c r="J305" t="inlineStr">
         <is>
-          <t>subj_tle</t>
+          <t>subj_filipino</t>
         </is>
       </c>
       <c r="K305" t="inlineStr">
         <is>
-          <t>TLE</t>
+          <t>Filipino</t>
         </is>
       </c>
       <c r="L305" t="inlineStr">
         <is>
-          <t>tchr_angeleni</t>
+          <t>tchr_nadzra</t>
         </is>
       </c>
       <c r="M305" t="inlineStr">
         <is>
-          <t>Teacher Angeleni</t>
+          <t>Teacher Nadzra</t>
         </is>
       </c>
       <c r="N305" t="n">
@@ -20571,22 +20571,22 @@
       </c>
       <c r="E306" t="inlineStr">
         <is>
-          <t>sec_grade_9_10_girls_face_to_face</t>
+          <t>sec_kinder_2_class_schedule_f2f</t>
         </is>
       </c>
       <c r="F306" t="inlineStr">
         <is>
-          <t>GRADE 9 &amp; 10 GIRLS (FACE TO FACE)</t>
+          <t>KINDER 2 CLASS SCHEDULE (F2F)</t>
         </is>
       </c>
       <c r="G306" t="inlineStr">
         <is>
-          <t>Junior High School</t>
+          <t>Elementary</t>
         </is>
       </c>
       <c r="H306" t="inlineStr">
         <is>
-          <t>Grade 9 &amp; 10</t>
+          <t>Kinder 2</t>
         </is>
       </c>
       <c r="I306" t="inlineStr">
@@ -20596,22 +20596,22 @@
       </c>
       <c r="J306" t="inlineStr">
         <is>
-          <t>subj_filipino</t>
+          <t>subj_hadith</t>
         </is>
       </c>
       <c r="K306" t="inlineStr">
         <is>
-          <t>Filipino</t>
+          <t>Hadith</t>
         </is>
       </c>
       <c r="L306" t="inlineStr">
         <is>
-          <t>tchr_nadzra</t>
+          <t>tchr_saliha</t>
         </is>
       </c>
       <c r="M306" t="inlineStr">
         <is>
-          <t>Teacher Nadzra</t>
+          <t>Ustadha Saliha</t>
         </is>
       </c>
       <c r="N306" t="n">
@@ -20628,21 +20628,21 @@
         </is>
       </c>
       <c r="C307" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D307" t="inlineStr">
         <is>
-          <t>08:00 AM – 09:00 AM</t>
+          <t>09:00 AM – 10:00 AM</t>
         </is>
       </c>
       <c r="E307" t="inlineStr">
         <is>
-          <t>sec_kinder_2_class_schedule_f2f</t>
+          <t>sec_grade_6_face_to_face</t>
         </is>
       </c>
       <c r="F307" t="inlineStr">
         <is>
-          <t>KINDER 2 CLASS SCHEDULE (F2F)</t>
+          <t>GRADE  6  FACE TO FACE</t>
         </is>
       </c>
       <c r="G307" t="inlineStr">
@@ -20652,7 +20652,7 @@
       </c>
       <c r="H307" t="inlineStr">
         <is>
-          <t>Kinder 2</t>
+          <t>Grade 6</t>
         </is>
       </c>
       <c r="I307" t="inlineStr">
@@ -20662,22 +20662,22 @@
       </c>
       <c r="J307" t="inlineStr">
         <is>
-          <t>subj_hadith</t>
+          <t>subj_filipino</t>
         </is>
       </c>
       <c r="K307" t="inlineStr">
         <is>
-          <t>Hadith</t>
+          <t>Filipino</t>
         </is>
       </c>
       <c r="L307" t="inlineStr">
         <is>
-          <t>tchr_saliha</t>
+          <t>tchr_normylah</t>
         </is>
       </c>
       <c r="M307" t="inlineStr">
         <is>
-          <t>Ustadha Saliha</t>
+          <t>Teacher Normylah</t>
         </is>
       </c>
       <c r="N307" t="n">
@@ -20703,22 +20703,22 @@
       </c>
       <c r="E308" t="inlineStr">
         <is>
-          <t>sec_grade_6_face_to_face</t>
+          <t>sec_grade_11_face_to_face</t>
         </is>
       </c>
       <c r="F308" t="inlineStr">
         <is>
-          <t>GRADE  6  FACE TO FACE</t>
+          <t>GRADE 11 (FACE TO FACE)</t>
         </is>
       </c>
       <c r="G308" t="inlineStr">
         <is>
-          <t>Elementary</t>
+          <t>Senior High School</t>
         </is>
       </c>
       <c r="H308" t="inlineStr">
         <is>
-          <t>Grade 6</t>
+          <t>Grade 11</t>
         </is>
       </c>
       <c r="I308" t="inlineStr">
@@ -20728,22 +20728,22 @@
       </c>
       <c r="J308" t="inlineStr">
         <is>
-          <t>subj_filipino</t>
+          <t>subj_mabisang_komunikasyon</t>
         </is>
       </c>
       <c r="K308" t="inlineStr">
         <is>
-          <t>Filipino</t>
+          <t>Mabisang Komunikasyon</t>
         </is>
       </c>
       <c r="L308" t="inlineStr">
         <is>
-          <t>tchr_normylah</t>
+          <t>tchr_nadzra</t>
         </is>
       </c>
       <c r="M308" t="inlineStr">
         <is>
-          <t>Teacher Normylah</t>
+          <t>Teacher Nadzra</t>
         </is>
       </c>
       <c r="N308" t="n">
@@ -20769,22 +20769,22 @@
       </c>
       <c r="E309" t="inlineStr">
         <is>
-          <t>sec_grade_11_face_to_face</t>
+          <t>sec_grade_4_face_to_face</t>
         </is>
       </c>
       <c r="F309" t="inlineStr">
         <is>
-          <t>GRADE 11 (FACE TO FACE)</t>
+          <t>GRADE 4 (FACE TO FACE)</t>
         </is>
       </c>
       <c r="G309" t="inlineStr">
         <is>
-          <t>Senior High School</t>
+          <t>Elementary</t>
         </is>
       </c>
       <c r="H309" t="inlineStr">
         <is>
-          <t>Grade 11</t>
+          <t>Grade 4</t>
         </is>
       </c>
       <c r="I309" t="inlineStr">
@@ -20794,22 +20794,22 @@
       </c>
       <c r="J309" t="inlineStr">
         <is>
-          <t>subj_mabisang_komunikasyon</t>
+          <t>subj_science</t>
         </is>
       </c>
       <c r="K309" t="inlineStr">
         <is>
-          <t>Mabisang Komunikasyon</t>
+          <t>Science</t>
         </is>
       </c>
       <c r="L309" t="inlineStr">
         <is>
-          <t>tchr_nadzra</t>
+          <t>tchr_junaisah</t>
         </is>
       </c>
       <c r="M309" t="inlineStr">
         <is>
-          <t>Teacher Nadzra</t>
+          <t>Teacher Junaisah</t>
         </is>
       </c>
       <c r="N309" t="n">
@@ -20835,12 +20835,12 @@
       </c>
       <c r="E310" t="inlineStr">
         <is>
-          <t>sec_grade_4_face_to_face</t>
+          <t>sec_grade_5_face_to_face</t>
         </is>
       </c>
       <c r="F310" t="inlineStr">
         <is>
-          <t>GRADE 4 (FACE TO FACE)</t>
+          <t>GRADE 5 (FACE TO FACE)</t>
         </is>
       </c>
       <c r="G310" t="inlineStr">
@@ -20850,7 +20850,7 @@
       </c>
       <c r="H310" t="inlineStr">
         <is>
-          <t>Grade 4</t>
+          <t>Grade 5</t>
         </is>
       </c>
       <c r="I310" t="inlineStr">
@@ -20860,22 +20860,22 @@
       </c>
       <c r="J310" t="inlineStr">
         <is>
-          <t>subj_science</t>
+          <t>subj_shaf</t>
         </is>
       </c>
       <c r="K310" t="inlineStr">
         <is>
-          <t>Science</t>
+          <t>SHAF</t>
         </is>
       </c>
       <c r="L310" t="inlineStr">
         <is>
-          <t>tchr_junaisah</t>
+          <t>tchr_ersahad</t>
         </is>
       </c>
       <c r="M310" t="inlineStr">
         <is>
-          <t>Teacher Junaisah</t>
+          <t>Ustadh Ersahad</t>
         </is>
       </c>
       <c r="N310" t="n">
@@ -20901,22 +20901,22 @@
       </c>
       <c r="E311" t="inlineStr">
         <is>
-          <t>sec_grade_5_face_to_face</t>
+          <t>sec_grade_7_8_boys_face_to_face</t>
         </is>
       </c>
       <c r="F311" t="inlineStr">
         <is>
-          <t>GRADE 5 (FACE TO FACE)</t>
+          <t>GRADE 7 &amp; 8 BOYS (FACE TO FACE)</t>
         </is>
       </c>
       <c r="G311" t="inlineStr">
         <is>
-          <t>Elementary</t>
+          <t>Junior High School</t>
         </is>
       </c>
       <c r="H311" t="inlineStr">
         <is>
-          <t>Grade 5</t>
+          <t>Grade 7 &amp; 8</t>
         </is>
       </c>
       <c r="I311" t="inlineStr">
@@ -20926,22 +20926,22 @@
       </c>
       <c r="J311" t="inlineStr">
         <is>
-          <t>subj_shaf</t>
+          <t>subj_social_studies</t>
         </is>
       </c>
       <c r="K311" t="inlineStr">
         <is>
-          <t>SHAF</t>
+          <t>Social Studies</t>
         </is>
       </c>
       <c r="L311" t="inlineStr">
         <is>
-          <t>tchr_ersahad</t>
+          <t>tchr_shirehan</t>
         </is>
       </c>
       <c r="M311" t="inlineStr">
         <is>
-          <t>Ustadh Ersahad</t>
+          <t>Teacher Shirehan</t>
         </is>
       </c>
       <c r="N311" t="n">
@@ -20967,12 +20967,12 @@
       </c>
       <c r="E312" t="inlineStr">
         <is>
-          <t>sec_grade_7_8_boys_face_to_face</t>
+          <t>sec_grade_7_8_girls_face_to_face</t>
         </is>
       </c>
       <c r="F312" t="inlineStr">
         <is>
-          <t>GRADE 7 &amp; 8 BOYS (FACE TO FACE)</t>
+          <t>GRADE 7 &amp; 8 GIRLS (FACE TO FACE)</t>
         </is>
       </c>
       <c r="G312" t="inlineStr">
@@ -20992,22 +20992,22 @@
       </c>
       <c r="J312" t="inlineStr">
         <is>
-          <t>subj_social_studies</t>
+          <t>subj_science</t>
         </is>
       </c>
       <c r="K312" t="inlineStr">
         <is>
-          <t>Social Studies</t>
+          <t>Science</t>
         </is>
       </c>
       <c r="L312" t="inlineStr">
         <is>
-          <t>tchr_shirehan</t>
+          <t>tchr_radzmia</t>
         </is>
       </c>
       <c r="M312" t="inlineStr">
         <is>
-          <t>Teacher Shirehan</t>
+          <t>Teacher Radzmia</t>
         </is>
       </c>
       <c r="N312" t="n">
@@ -21033,12 +21033,12 @@
       </c>
       <c r="E313" t="inlineStr">
         <is>
-          <t>sec_grade_7_8_girls_face_to_face</t>
+          <t>sec_grade_9_10_boys_face_to_face</t>
         </is>
       </c>
       <c r="F313" t="inlineStr">
         <is>
-          <t>GRADE 7 &amp; 8 GIRLS (FACE TO FACE)</t>
+          <t>GRADE 9 &amp; 10 BOYS (FACE TO FACE)</t>
         </is>
       </c>
       <c r="G313" t="inlineStr">
@@ -21048,7 +21048,7 @@
       </c>
       <c r="H313" t="inlineStr">
         <is>
-          <t>Grade 7 &amp; 8</t>
+          <t>Grade 9 &amp; 10</t>
         </is>
       </c>
       <c r="I313" t="inlineStr">
@@ -21058,22 +21058,22 @@
       </c>
       <c r="J313" t="inlineStr">
         <is>
-          <t>subj_science</t>
+          <t>subj_values_ed</t>
         </is>
       </c>
       <c r="K313" t="inlineStr">
         <is>
-          <t>Science</t>
+          <t>Values Ed</t>
         </is>
       </c>
       <c r="L313" t="inlineStr">
         <is>
-          <t>tchr_radzmia</t>
+          <t>tchr_nof</t>
         </is>
       </c>
       <c r="M313" t="inlineStr">
         <is>
-          <t>Teacher Radzmia</t>
+          <t>Teacher Nof</t>
         </is>
       </c>
       <c r="N313" t="n">
@@ -21099,12 +21099,12 @@
       </c>
       <c r="E314" t="inlineStr">
         <is>
-          <t>sec_grade_9_10_boys_face_to_face</t>
+          <t>sec_grade_9_10_girls_face_to_face</t>
         </is>
       </c>
       <c r="F314" t="inlineStr">
         <is>
-          <t>GRADE 9 &amp; 10 BOYS (FACE TO FACE)</t>
+          <t>GRADE 9 &amp; 10 GIRLS (FACE TO FACE)</t>
         </is>
       </c>
       <c r="G314" t="inlineStr">
@@ -21124,22 +21124,22 @@
       </c>
       <c r="J314" t="inlineStr">
         <is>
-          <t>subj_values_ed</t>
+          <t>subj_qur_an</t>
         </is>
       </c>
       <c r="K314" t="inlineStr">
         <is>
-          <t>Values Ed</t>
+          <t>Qur'an</t>
         </is>
       </c>
       <c r="L314" t="inlineStr">
         <is>
-          <t>tchr_nof</t>
+          <t>tchr_abdulwahab</t>
         </is>
       </c>
       <c r="M314" t="inlineStr">
         <is>
-          <t>Teacher Nof</t>
+          <t>Alim Abdulwahab</t>
         </is>
       </c>
       <c r="N314" t="n">
@@ -21165,22 +21165,22 @@
       </c>
       <c r="E315" t="inlineStr">
         <is>
-          <t>sec_grade_9_10_girls_face_to_face</t>
+          <t>sec_kinder_2_class_schedule_f2f</t>
         </is>
       </c>
       <c r="F315" t="inlineStr">
         <is>
-          <t>GRADE 9 &amp; 10 GIRLS (FACE TO FACE)</t>
+          <t>KINDER 2 CLASS SCHEDULE (F2F)</t>
         </is>
       </c>
       <c r="G315" t="inlineStr">
         <is>
-          <t>Junior High School</t>
+          <t>Elementary</t>
         </is>
       </c>
       <c r="H315" t="inlineStr">
         <is>
-          <t>Grade 9 &amp; 10</t>
+          <t>Kinder 2</t>
         </is>
       </c>
       <c r="I315" t="inlineStr">
@@ -21200,12 +21200,12 @@
       </c>
       <c r="L315" t="inlineStr">
         <is>
-          <t>tchr_abdulwahab</t>
+          <t>tchr_jaisam</t>
         </is>
       </c>
       <c r="M315" t="inlineStr">
         <is>
-          <t>Alim Abdulwahab</t>
+          <t>Ustadh Jaisam</t>
         </is>
       </c>
       <c r="N315" t="n">
@@ -21222,21 +21222,21 @@
         </is>
       </c>
       <c r="C316" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D316" t="inlineStr">
         <is>
-          <t>09:00 AM – 10:00 AM</t>
+          <t>10:25 AM – 11:25 AM</t>
         </is>
       </c>
       <c r="E316" t="inlineStr">
         <is>
-          <t>sec_kinder_2_class_schedule_f2f</t>
+          <t>sec_grade_6_face_to_face</t>
         </is>
       </c>
       <c r="F316" t="inlineStr">
         <is>
-          <t>KINDER 2 CLASS SCHEDULE (F2F)</t>
+          <t>GRADE  6  FACE TO FACE</t>
         </is>
       </c>
       <c r="G316" t="inlineStr">
@@ -21246,7 +21246,7 @@
       </c>
       <c r="H316" t="inlineStr">
         <is>
-          <t>Kinder 2</t>
+          <t>Grade 6</t>
         </is>
       </c>
       <c r="I316" t="inlineStr">
@@ -21256,22 +21256,22 @@
       </c>
       <c r="J316" t="inlineStr">
         <is>
-          <t>subj_qur_an</t>
+          <t>subj_tle</t>
         </is>
       </c>
       <c r="K316" t="inlineStr">
         <is>
-          <t>Qur'an</t>
+          <t>TLE</t>
         </is>
       </c>
       <c r="L316" t="inlineStr">
         <is>
-          <t>tchr_jaisam</t>
+          <t>tchr_arvin</t>
         </is>
       </c>
       <c r="M316" t="inlineStr">
         <is>
-          <t>Ustadh Jaisam</t>
+          <t>Teacher Arvin</t>
         </is>
       </c>
       <c r="N316" t="n">
@@ -21297,12 +21297,12 @@
       </c>
       <c r="E317" t="inlineStr">
         <is>
-          <t>sec_grade_6_face_to_face</t>
+          <t>sec_grade_1_face_to_face</t>
         </is>
       </c>
       <c r="F317" t="inlineStr">
         <is>
-          <t>GRADE  6  FACE TO FACE</t>
+          <t>GRADE 1 (FACE TO FACE)</t>
         </is>
       </c>
       <c r="G317" t="inlineStr">
@@ -21312,7 +21312,7 @@
       </c>
       <c r="H317" t="inlineStr">
         <is>
-          <t>Grade 6</t>
+          <t>Grade 1</t>
         </is>
       </c>
       <c r="I317" t="inlineStr">
@@ -21322,22 +21322,22 @@
       </c>
       <c r="J317" t="inlineStr">
         <is>
-          <t>subj_tle</t>
+          <t>subj_qur_an</t>
         </is>
       </c>
       <c r="K317" t="inlineStr">
         <is>
-          <t>TLE</t>
+          <t>Qur'an</t>
         </is>
       </c>
       <c r="L317" t="inlineStr">
         <is>
-          <t>tchr_arvin</t>
+          <t>tchr_obaydah</t>
         </is>
       </c>
       <c r="M317" t="inlineStr">
         <is>
-          <t>Teacher Arvin</t>
+          <t>Ustadh Obaydah</t>
         </is>
       </c>
       <c r="N317" t="n">
@@ -21363,22 +21363,22 @@
       </c>
       <c r="E318" t="inlineStr">
         <is>
-          <t>sec_grade_1_face_to_face</t>
+          <t>sec_grade_11_face_to_face</t>
         </is>
       </c>
       <c r="F318" t="inlineStr">
         <is>
-          <t>GRADE 1 (FACE TO FACE)</t>
+          <t>GRADE 11 (FACE TO FACE)</t>
         </is>
       </c>
       <c r="G318" t="inlineStr">
         <is>
-          <t>Elementary</t>
+          <t>Senior High School</t>
         </is>
       </c>
       <c r="H318" t="inlineStr">
         <is>
-          <t>Grade 1</t>
+          <t>Grade 11</t>
         </is>
       </c>
       <c r="I318" t="inlineStr">
@@ -21388,22 +21388,22 @@
       </c>
       <c r="J318" t="inlineStr">
         <is>
-          <t>subj_qur_an</t>
+          <t>subj_pskp</t>
         </is>
       </c>
       <c r="K318" t="inlineStr">
         <is>
-          <t>Qur'an</t>
+          <t>PSKP</t>
         </is>
       </c>
       <c r="L318" t="inlineStr">
         <is>
-          <t>tchr_obaydah</t>
+          <t>tchr_shirehan</t>
         </is>
       </c>
       <c r="M318" t="inlineStr">
         <is>
-          <t>Ustadh Obaydah</t>
+          <t>Teacher Shirehan</t>
         </is>
       </c>
       <c r="N318" t="n">
@@ -21429,22 +21429,22 @@
       </c>
       <c r="E319" t="inlineStr">
         <is>
-          <t>sec_grade_11_face_to_face</t>
+          <t>sec_grade_2_face_to_face</t>
         </is>
       </c>
       <c r="F319" t="inlineStr">
         <is>
-          <t>GRADE 11 (FACE TO FACE)</t>
+          <t>GRADE 2 (FACE TO FACE)</t>
         </is>
       </c>
       <c r="G319" t="inlineStr">
         <is>
-          <t>Senior High School</t>
+          <t>Elementary</t>
         </is>
       </c>
       <c r="H319" t="inlineStr">
         <is>
-          <t>Grade 11</t>
+          <t>Grade 2</t>
         </is>
       </c>
       <c r="I319" t="inlineStr">
@@ -21454,22 +21454,22 @@
       </c>
       <c r="J319" t="inlineStr">
         <is>
-          <t>subj_pskp</t>
+          <t>subj_english</t>
         </is>
       </c>
       <c r="K319" t="inlineStr">
         <is>
-          <t>PSKP</t>
+          <t>English</t>
         </is>
       </c>
       <c r="L319" t="inlineStr">
         <is>
-          <t>tchr_shirehan</t>
+          <t>tchr_marham</t>
         </is>
       </c>
       <c r="M319" t="inlineStr">
         <is>
-          <t>Teacher Shirehan</t>
+          <t>Teacher Marham</t>
         </is>
       </c>
       <c r="N319" t="n">
@@ -21495,12 +21495,12 @@
       </c>
       <c r="E320" t="inlineStr">
         <is>
-          <t>sec_grade_2_face_to_face</t>
+          <t>sec_grade_4_face_to_face</t>
         </is>
       </c>
       <c r="F320" t="inlineStr">
         <is>
-          <t>GRADE 2 (FACE TO FACE)</t>
+          <t>GRADE 4 (FACE TO FACE)</t>
         </is>
       </c>
       <c r="G320" t="inlineStr">
@@ -21510,7 +21510,7 @@
       </c>
       <c r="H320" t="inlineStr">
         <is>
-          <t>Grade 2</t>
+          <t>Grade 4</t>
         </is>
       </c>
       <c r="I320" t="inlineStr">
@@ -21520,22 +21520,22 @@
       </c>
       <c r="J320" t="inlineStr">
         <is>
-          <t>subj_english</t>
+          <t>subj_araling_panlipunan</t>
         </is>
       </c>
       <c r="K320" t="inlineStr">
         <is>
-          <t>English</t>
+          <t>Araling Panlipunan</t>
         </is>
       </c>
       <c r="L320" t="inlineStr">
         <is>
-          <t>tchr_marham</t>
+          <t>tchr_monisa</t>
         </is>
       </c>
       <c r="M320" t="inlineStr">
         <is>
-          <t>Teacher Marham</t>
+          <t>Teacher Monisa</t>
         </is>
       </c>
       <c r="N320" t="n">
@@ -21561,12 +21561,12 @@
       </c>
       <c r="E321" t="inlineStr">
         <is>
-          <t>sec_grade_4_face_to_face</t>
+          <t>sec_grade_5_face_to_face</t>
         </is>
       </c>
       <c r="F321" t="inlineStr">
         <is>
-          <t>GRADE 4 (FACE TO FACE)</t>
+          <t>GRADE 5 (FACE TO FACE)</t>
         </is>
       </c>
       <c r="G321" t="inlineStr">
@@ -21576,7 +21576,7 @@
       </c>
       <c r="H321" t="inlineStr">
         <is>
-          <t>Grade 4</t>
+          <t>Grade 5</t>
         </is>
       </c>
       <c r="I321" t="inlineStr">
@@ -21586,22 +21586,22 @@
       </c>
       <c r="J321" t="inlineStr">
         <is>
-          <t>subj_araling_panlipunan</t>
+          <t>subj_arabic</t>
         </is>
       </c>
       <c r="K321" t="inlineStr">
         <is>
-          <t>Araling Panlipunan</t>
+          <t>Arabic</t>
         </is>
       </c>
       <c r="L321" t="inlineStr">
         <is>
-          <t>tchr_monisa</t>
+          <t>tchr_ersahad</t>
         </is>
       </c>
       <c r="M321" t="inlineStr">
         <is>
-          <t>Teacher Monisa</t>
+          <t>Ustadh Ersahad</t>
         </is>
       </c>
       <c r="N321" t="n">
@@ -21627,22 +21627,22 @@
       </c>
       <c r="E322" t="inlineStr">
         <is>
-          <t>sec_grade_5_face_to_face</t>
+          <t>sec_grade_7_8_boys_face_to_face</t>
         </is>
       </c>
       <c r="F322" t="inlineStr">
         <is>
-          <t>GRADE 5 (FACE TO FACE)</t>
+          <t>GRADE 7 &amp; 8 BOYS (FACE TO FACE)</t>
         </is>
       </c>
       <c r="G322" t="inlineStr">
         <is>
-          <t>Elementary</t>
+          <t>Junior High School</t>
         </is>
       </c>
       <c r="H322" t="inlineStr">
         <is>
-          <t>Grade 5</t>
+          <t>Grade 7 &amp; 8</t>
         </is>
       </c>
       <c r="I322" t="inlineStr">
@@ -21662,12 +21662,12 @@
       </c>
       <c r="L322" t="inlineStr">
         <is>
-          <t>tchr_ersahad</t>
+          <t>tchr_ali</t>
         </is>
       </c>
       <c r="M322" t="inlineStr">
         <is>
-          <t>Ustadh Ersahad</t>
+          <t>Ustadh Ali</t>
         </is>
       </c>
       <c r="N322" t="n">
@@ -21693,12 +21693,12 @@
       </c>
       <c r="E323" t="inlineStr">
         <is>
-          <t>sec_grade_7_8_boys_face_to_face</t>
+          <t>sec_grade_7_8_girls_face_to_face</t>
         </is>
       </c>
       <c r="F323" t="inlineStr">
         <is>
-          <t>GRADE 7 &amp; 8 BOYS (FACE TO FACE)</t>
+          <t>GRADE 7 &amp; 8 GIRLS (FACE TO FACE)</t>
         </is>
       </c>
       <c r="G323" t="inlineStr">
@@ -21718,22 +21718,22 @@
       </c>
       <c r="J323" t="inlineStr">
         <is>
-          <t>subj_arabic</t>
+          <t>subj_qur_an</t>
         </is>
       </c>
       <c r="K323" t="inlineStr">
         <is>
-          <t>Arabic</t>
+          <t>Qur'an</t>
         </is>
       </c>
       <c r="L323" t="inlineStr">
         <is>
-          <t>tchr_ali</t>
+          <t>tchr_jaisam</t>
         </is>
       </c>
       <c r="M323" t="inlineStr">
         <is>
-          <t>Ustadh Ali</t>
+          <t>Ustadh Jaisam</t>
         </is>
       </c>
       <c r="N323" t="n">
@@ -21759,12 +21759,12 @@
       </c>
       <c r="E324" t="inlineStr">
         <is>
-          <t>sec_grade_7_8_girls_face_to_face</t>
+          <t>sec_grade_9_10_boys_face_to_face</t>
         </is>
       </c>
       <c r="F324" t="inlineStr">
         <is>
-          <t>GRADE 7 &amp; 8 GIRLS (FACE TO FACE)</t>
+          <t>GRADE 9 &amp; 10 BOYS (FACE TO FACE)</t>
         </is>
       </c>
       <c r="G324" t="inlineStr">
@@ -21774,7 +21774,7 @@
       </c>
       <c r="H324" t="inlineStr">
         <is>
-          <t>Grade 7 &amp; 8</t>
+          <t>Grade 9 &amp; 10</t>
         </is>
       </c>
       <c r="I324" t="inlineStr">
@@ -21784,22 +21784,22 @@
       </c>
       <c r="J324" t="inlineStr">
         <is>
-          <t>subj_qur_an</t>
+          <t>subj_shaf</t>
         </is>
       </c>
       <c r="K324" t="inlineStr">
         <is>
-          <t>Qur'an</t>
+          <t>SHAF</t>
         </is>
       </c>
       <c r="L324" t="inlineStr">
         <is>
-          <t>tchr_jaisam</t>
+          <t>tchr_samsuddin</t>
         </is>
       </c>
       <c r="M324" t="inlineStr">
         <is>
-          <t>Ustadh Jaisam</t>
+          <t>Alim Samsuddin</t>
         </is>
       </c>
       <c r="N324" t="n">
@@ -21825,12 +21825,12 @@
       </c>
       <c r="E325" t="inlineStr">
         <is>
-          <t>sec_grade_9_10_boys_face_to_face</t>
+          <t>sec_grade_9_10_girls_face_to_face</t>
         </is>
       </c>
       <c r="F325" t="inlineStr">
         <is>
-          <t>GRADE 9 &amp; 10 BOYS (FACE TO FACE)</t>
+          <t>GRADE 9 &amp; 10 GIRLS (FACE TO FACE)</t>
         </is>
       </c>
       <c r="G325" t="inlineStr">
@@ -21850,22 +21850,22 @@
       </c>
       <c r="J325" t="inlineStr">
         <is>
-          <t>subj_shaf</t>
+          <t>subj_english</t>
         </is>
       </c>
       <c r="K325" t="inlineStr">
         <is>
-          <t>SHAF</t>
+          <t>English</t>
         </is>
       </c>
       <c r="L325" t="inlineStr">
         <is>
-          <t>tchr_samsuddin</t>
+          <t>tchr_norhaima</t>
         </is>
       </c>
       <c r="M325" t="inlineStr">
         <is>
-          <t>Alim Samsuddin</t>
+          <t>Teacher Norhaima</t>
         </is>
       </c>
       <c r="N325" t="n">
@@ -21891,22 +21891,22 @@
       </c>
       <c r="E326" t="inlineStr">
         <is>
-          <t>sec_grade_9_10_girls_face_to_face</t>
+          <t>sec_kinder_1_class_schedule_f2f</t>
         </is>
       </c>
       <c r="F326" t="inlineStr">
         <is>
-          <t>GRADE 9 &amp; 10 GIRLS (FACE TO FACE)</t>
+          <t>KINDER 1 CLASS SCHEDULE (F2F)</t>
         </is>
       </c>
       <c r="G326" t="inlineStr">
         <is>
-          <t>Junior High School</t>
+          <t>Elementary</t>
         </is>
       </c>
       <c r="H326" t="inlineStr">
         <is>
-          <t>Grade 9 &amp; 10</t>
+          <t>Kinder 1</t>
         </is>
       </c>
       <c r="I326" t="inlineStr">
@@ -21916,22 +21916,22 @@
       </c>
       <c r="J326" t="inlineStr">
         <is>
-          <t>subj_english</t>
+          <t>subj_arabic</t>
         </is>
       </c>
       <c r="K326" t="inlineStr">
         <is>
-          <t>English</t>
+          <t>Arabic</t>
         </is>
       </c>
       <c r="L326" t="inlineStr">
         <is>
-          <t>tchr_norhaima</t>
+          <t>tchr_saliha</t>
         </is>
       </c>
       <c r="M326" t="inlineStr">
         <is>
-          <t>Teacher Norhaima</t>
+          <t>Ustadha Saliha</t>
         </is>
       </c>
       <c r="N326" t="n">
@@ -21948,21 +21948,21 @@
         </is>
       </c>
       <c r="C327" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D327" t="inlineStr">
         <is>
-          <t>10:25 AM – 11:25 AM</t>
+          <t>12:40 PM – 01:40 PM</t>
         </is>
       </c>
       <c r="E327" t="inlineStr">
         <is>
-          <t>sec_kinder_1_class_schedule_f2f</t>
+          <t>sec_grade_1_ali_ibn_abi_talib_1st_shift</t>
         </is>
       </c>
       <c r="F327" t="inlineStr">
         <is>
-          <t>KINDER 1 CLASS SCHEDULE (F2F)</t>
+          <t>GRADE 1 - ALI IBN ABI TALIB(1ST SHIFT)</t>
         </is>
       </c>
       <c r="G327" t="inlineStr">
@@ -21972,12 +21972,12 @@
       </c>
       <c r="H327" t="inlineStr">
         <is>
-          <t>Kinder 1</t>
+          <t>Grade 1</t>
         </is>
       </c>
       <c r="I327" t="inlineStr">
         <is>
-          <t>F2F</t>
+          <t>ODL - 1ST SHIFT</t>
         </is>
       </c>
       <c r="J327" t="inlineStr">
@@ -21992,12 +21992,12 @@
       </c>
       <c r="L327" t="inlineStr">
         <is>
-          <t>tchr_saliha</t>
+          <t>tchr_hainur</t>
         </is>
       </c>
       <c r="M327" t="inlineStr">
         <is>
-          <t>Ustadha Saliha</t>
+          <t>Ustadha Hainur</t>
         </is>
       </c>
       <c r="N327" t="n">
@@ -22018,27 +22018,27 @@
       </c>
       <c r="D328" t="inlineStr">
         <is>
-          <t>12:40 PM – 01:40 PM</t>
+          <t>12:40 PM – 02:50 PM</t>
         </is>
       </c>
       <c r="E328" t="inlineStr">
         <is>
-          <t>sec_grade_1_ali_ibn_abi_talib_1st_shift</t>
+          <t>sec_grade_10_utbah_ibn_ghazwan_1st_shift_girls</t>
         </is>
       </c>
       <c r="F328" t="inlineStr">
         <is>
-          <t>GRADE 1 - ALI IBN ABI TALIB(1ST SHIFT)</t>
+          <t>GRADE 10 - UTBAH IBN GHAZWAN (1ST SHIFT) GIRLS</t>
         </is>
       </c>
       <c r="G328" t="inlineStr">
         <is>
-          <t>Elementary</t>
+          <t>Junior High School</t>
         </is>
       </c>
       <c r="H328" t="inlineStr">
         <is>
-          <t>Grade 1</t>
+          <t>Grade 10</t>
         </is>
       </c>
       <c r="I328" t="inlineStr">
@@ -22048,26 +22048,26 @@
       </c>
       <c r="J328" t="inlineStr">
         <is>
-          <t>subj_arabic</t>
+          <t>subj_math</t>
         </is>
       </c>
       <c r="K328" t="inlineStr">
         <is>
-          <t>Arabic</t>
+          <t>Math</t>
         </is>
       </c>
       <c r="L328" t="inlineStr">
         <is>
-          <t>tchr_hainur</t>
+          <t>tchr_jhelyn</t>
         </is>
       </c>
       <c r="M328" t="inlineStr">
         <is>
-          <t>Ustadh Hainur</t>
+          <t>Teacher Jhelyn</t>
         </is>
       </c>
       <c r="N328" t="n">
-        <v>60</v>
+        <v>120</v>
       </c>
     </row>
     <row r="329">
@@ -22084,27 +22084,27 @@
       </c>
       <c r="D329" t="inlineStr">
         <is>
-          <t>12:40 PM – 02:50 PM</t>
+          <t>12:40 PM – 01:40 PM</t>
         </is>
       </c>
       <c r="E329" t="inlineStr">
         <is>
-          <t>sec_grade_10_utbah_ibn_ghazwan_1st_shift_girls</t>
+          <t>sec_grade_12_abu_musa_al_ashari</t>
         </is>
       </c>
       <c r="F329" t="inlineStr">
         <is>
-          <t>GRADE 10 - UTBAH IBN GHAZWAN (1ST SHIFT) GIRLS</t>
+          <t>GRADE 12 - ABU MUSA AL-ASHARI</t>
         </is>
       </c>
       <c r="G329" t="inlineStr">
         <is>
-          <t>Junior High School</t>
+          <t>Senior High School</t>
         </is>
       </c>
       <c r="H329" t="inlineStr">
         <is>
-          <t>Grade 10</t>
+          <t>Grade 12</t>
         </is>
       </c>
       <c r="I329" t="inlineStr">
@@ -22114,26 +22114,26 @@
       </c>
       <c r="J329" t="inlineStr">
         <is>
-          <t>subj_math</t>
+          <t>subj_shaf</t>
         </is>
       </c>
       <c r="K329" t="inlineStr">
         <is>
-          <t>Math</t>
+          <t>SHAF</t>
         </is>
       </c>
       <c r="L329" t="inlineStr">
         <is>
-          <t>tchr_jhelyn</t>
+          <t>tchr_samsuddin</t>
         </is>
       </c>
       <c r="M329" t="inlineStr">
         <is>
-          <t>Teacher Jhelyn</t>
+          <t>Alim Samsuddin</t>
         </is>
       </c>
       <c r="N329" t="n">
-        <v>120</v>
+        <v>60</v>
       </c>
     </row>
     <row r="330">
@@ -22155,22 +22155,22 @@
       </c>
       <c r="E330" t="inlineStr">
         <is>
-          <t>sec_grade_12_abu_musa_al_ashari</t>
+          <t>sec_grade_2_amr_ibn_al_jamuh_1st_shift</t>
         </is>
       </c>
       <c r="F330" t="inlineStr">
         <is>
-          <t>GRADE 12 - ABU MUSA AL-ASHARI</t>
+          <t>GRADE 2 - AMR IBN AL-JAMUH (1ST SHIFT)</t>
         </is>
       </c>
       <c r="G330" t="inlineStr">
         <is>
-          <t>Senior High School</t>
+          <t>Elementary</t>
         </is>
       </c>
       <c r="H330" t="inlineStr">
         <is>
-          <t>Grade 12</t>
+          <t>Grade 2</t>
         </is>
       </c>
       <c r="I330" t="inlineStr">
@@ -22180,22 +22180,22 @@
       </c>
       <c r="J330" t="inlineStr">
         <is>
-          <t>subj_shaf</t>
+          <t>subj_math</t>
         </is>
       </c>
       <c r="K330" t="inlineStr">
         <is>
-          <t>SHAF</t>
+          <t>Math</t>
         </is>
       </c>
       <c r="L330" t="inlineStr">
         <is>
-          <t>tchr_samsuddin</t>
+          <t>tchr_sitti_kauzar</t>
         </is>
       </c>
       <c r="M330" t="inlineStr">
         <is>
-          <t>Alim Samsuddin</t>
+          <t>Teacher Sitti Kauzar</t>
         </is>
       </c>
       <c r="N330" t="n">
@@ -22221,12 +22221,12 @@
       </c>
       <c r="E331" t="inlineStr">
         <is>
-          <t>sec_grade_2_amr_ibn_al_jamuh_1st_shift</t>
+          <t>sec_grade_2_talha_ibn_ubaydullah_1st_shift</t>
         </is>
       </c>
       <c r="F331" t="inlineStr">
         <is>
-          <t>GRADE 2 - AMR IBN AL-JAMUH (1ST SHIFT)</t>
+          <t>GRADE 2 - TALHA IBN UBAYDULLAH (1ST SHIFT)</t>
         </is>
       </c>
       <c r="G331" t="inlineStr">
@@ -22246,22 +22246,22 @@
       </c>
       <c r="J331" t="inlineStr">
         <is>
-          <t>subj_math</t>
+          <t>subj_gmrc</t>
         </is>
       </c>
       <c r="K331" t="inlineStr">
         <is>
-          <t>Math</t>
+          <t>GMRC</t>
         </is>
       </c>
       <c r="L331" t="inlineStr">
         <is>
-          <t>tchr_sitti_kauzar</t>
+          <t>tchr_saliha</t>
         </is>
       </c>
       <c r="M331" t="inlineStr">
         <is>
-          <t>Teacher Sitti Kauzar</t>
+          <t>Ustadha Saliha</t>
         </is>
       </c>
       <c r="N331" t="n">
@@ -22287,12 +22287,12 @@
       </c>
       <c r="E332" t="inlineStr">
         <is>
-          <t>sec_grade_2_talha_ibn_ubaydullah_1st_shift</t>
+          <t>sec_grade_3_habib_ibn_zayd_al_ansari_1st_shift_girls</t>
         </is>
       </c>
       <c r="F332" t="inlineStr">
         <is>
-          <t>GRADE 2 - TALHA IBN UBAYDULLAH (1ST SHIFT)</t>
+          <t>Grade 3 - HABIB IBN ZAYD AL-ANSARI (1ST SHIFT) - GIRLS</t>
         </is>
       </c>
       <c r="G332" t="inlineStr">
@@ -22302,7 +22302,7 @@
       </c>
       <c r="H332" t="inlineStr">
         <is>
-          <t>Grade 2</t>
+          <t>Grade 3</t>
         </is>
       </c>
       <c r="I332" t="inlineStr">
@@ -22312,22 +22312,22 @@
       </c>
       <c r="J332" t="inlineStr">
         <is>
-          <t>subj_gmrc</t>
+          <t>subj_shaf</t>
         </is>
       </c>
       <c r="K332" t="inlineStr">
         <is>
-          <t>GMRC</t>
+          <t>SHAF</t>
         </is>
       </c>
       <c r="L332" t="inlineStr">
         <is>
-          <t>tchr_saliha</t>
+          <t>tchr_abdul_karim</t>
         </is>
       </c>
       <c r="M332" t="inlineStr">
         <is>
-          <t>Ustadha Saliha</t>
+          <t>Alim Abdul Karim</t>
         </is>
       </c>
       <c r="N332" t="n">
@@ -22353,12 +22353,12 @@
       </c>
       <c r="E333" t="inlineStr">
         <is>
-          <t>sec_grade_3_habib_ibn_zayd_al_ansari_1st_shift_girls</t>
+          <t>sec_grade_3_salman_al_farsi_1st_shift_mix</t>
         </is>
       </c>
       <c r="F333" t="inlineStr">
         <is>
-          <t>Grade 3 - HABIB IBN ZAYD AL-ANSARI (1ST SHIFT) - GIRLS</t>
+          <t>GRADE 3 - SALMAN AL FARSI (1ST SHIFT) MIX</t>
         </is>
       </c>
       <c r="G333" t="inlineStr">
@@ -22378,22 +22378,22 @@
       </c>
       <c r="J333" t="inlineStr">
         <is>
-          <t>subj_shaf</t>
+          <t>subj_math</t>
         </is>
       </c>
       <c r="K333" t="inlineStr">
         <is>
-          <t>SHAF</t>
+          <t>Math</t>
         </is>
       </c>
       <c r="L333" t="inlineStr">
         <is>
-          <t>tchr_abdul_karim</t>
+          <t>tchr_jerlyn</t>
         </is>
       </c>
       <c r="M333" t="inlineStr">
         <is>
-          <t>Alim Abdul Karim</t>
+          <t>Teacher Jerlyn</t>
         </is>
       </c>
       <c r="N333" t="n">
@@ -22419,12 +22419,12 @@
       </c>
       <c r="E334" t="inlineStr">
         <is>
-          <t>sec_grade_3_salman_al_farsi_1st_shift_mix</t>
+          <t>sec_grade_3_ammar_ibn_yasir_1st_shift_boys</t>
         </is>
       </c>
       <c r="F334" t="inlineStr">
         <is>
-          <t>GRADE 3 - SALMAN AL FARSI (1ST SHIFT) MIX</t>
+          <t>GRADE 3 -AMMAR IBN YASIR (1ST SHIFT) - BOYS</t>
         </is>
       </c>
       <c r="G334" t="inlineStr">
@@ -22444,22 +22444,22 @@
       </c>
       <c r="J334" t="inlineStr">
         <is>
-          <t>subj_math</t>
+          <t>subj_filipino</t>
         </is>
       </c>
       <c r="K334" t="inlineStr">
         <is>
-          <t>Math</t>
+          <t>Filipino</t>
         </is>
       </c>
       <c r="L334" t="inlineStr">
         <is>
-          <t>tchr_jerlyn</t>
+          <t>tchr_normylah</t>
         </is>
       </c>
       <c r="M334" t="inlineStr">
         <is>
-          <t>Teacher Jerlyn</t>
+          <t>Teacher Normylah</t>
         </is>
       </c>
       <c r="N334" t="n">
@@ -22485,12 +22485,12 @@
       </c>
       <c r="E335" t="inlineStr">
         <is>
-          <t>sec_grade_3_ammar_ibn_yasir_1st_shift_boys</t>
+          <t>sec_grade_4_abdur_rahman_ibn_awf_1st_shift</t>
         </is>
       </c>
       <c r="F335" t="inlineStr">
         <is>
-          <t>GRADE 3 -AMMAR IBN YASIR (1ST SHIFT) - BOYS</t>
+          <t>GRADE 4 - ABDUR RAHMAN IBN AWF (1ST SHIFT)</t>
         </is>
       </c>
       <c r="G335" t="inlineStr">
@@ -22500,7 +22500,7 @@
       </c>
       <c r="H335" t="inlineStr">
         <is>
-          <t>Grade 3</t>
+          <t>Grade 4</t>
         </is>
       </c>
       <c r="I335" t="inlineStr">
@@ -22510,22 +22510,22 @@
       </c>
       <c r="J335" t="inlineStr">
         <is>
-          <t>subj_filipino</t>
+          <t>subj_araling_panlipunan</t>
         </is>
       </c>
       <c r="K335" t="inlineStr">
         <is>
-          <t>Filipino</t>
+          <t>Araling Panlipunan</t>
         </is>
       </c>
       <c r="L335" t="inlineStr">
         <is>
-          <t>tchr_normylah</t>
+          <t>tchr_monisa</t>
         </is>
       </c>
       <c r="M335" t="inlineStr">
         <is>
-          <t>Teacher Normylah</t>
+          <t>Teacher Monisa</t>
         </is>
       </c>
       <c r="N335" t="n">
@@ -22551,12 +22551,12 @@
       </c>
       <c r="E336" t="inlineStr">
         <is>
-          <t>sec_grade_4_abdur_rahman_ibn_awf_1st_shift</t>
+          <t>sec_grade_4_hakim_ibn_hazm_1st_shift</t>
         </is>
       </c>
       <c r="F336" t="inlineStr">
         <is>
-          <t>GRADE 4 - ABDUR RAHMAN IBN AWF (1ST SHIFT)</t>
+          <t>GRADE 4 - HAKIM IBN HAZM(1ST SHIFT)</t>
         </is>
       </c>
       <c r="G336" t="inlineStr">
@@ -22576,22 +22576,22 @@
       </c>
       <c r="J336" t="inlineStr">
         <is>
-          <t>subj_araling_panlipunan</t>
+          <t>subj_english</t>
         </is>
       </c>
       <c r="K336" t="inlineStr">
         <is>
-          <t>Araling Panlipunan</t>
+          <t>English</t>
         </is>
       </c>
       <c r="L336" t="inlineStr">
         <is>
-          <t>tchr_monisa</t>
+          <t>tchr_arvin</t>
         </is>
       </c>
       <c r="M336" t="inlineStr">
         <is>
-          <t>Teacher Monisa</t>
+          <t>Teacher Arvin</t>
         </is>
       </c>
       <c r="N336" t="n">
@@ -22617,12 +22617,12 @@
       </c>
       <c r="E337" t="inlineStr">
         <is>
-          <t>sec_grade_4_hakim_ibn_hazm_1st_shift</t>
+          <t>sec_grade_4_usayd_ibn_hudhayr_1st_shift_mix</t>
         </is>
       </c>
       <c r="F337" t="inlineStr">
         <is>
-          <t>GRADE 4 - HAKIM IBN HAZM(1ST SHIFT)</t>
+          <t>GRADE 4 - USAYD IBN HUDHAYR (1ST SHIFT) - MIX</t>
         </is>
       </c>
       <c r="G337" t="inlineStr">
@@ -22642,22 +22642,22 @@
       </c>
       <c r="J337" t="inlineStr">
         <is>
-          <t>subj_english</t>
+          <t>subj_gmrc</t>
         </is>
       </c>
       <c r="K337" t="inlineStr">
         <is>
-          <t>English</t>
+          <t>GMRC</t>
         </is>
       </c>
       <c r="L337" t="inlineStr">
         <is>
-          <t>tchr_arvin</t>
+          <t>tchr_sahdia</t>
         </is>
       </c>
       <c r="M337" t="inlineStr">
         <is>
-          <t>Teacher Arvin</t>
+          <t>Teacher Sahdia</t>
         </is>
       </c>
       <c r="N337" t="n">
@@ -22683,12 +22683,12 @@
       </c>
       <c r="E338" t="inlineStr">
         <is>
-          <t>sec_grade_4_usayd_ibn_hudhayr_1st_shift_mix</t>
+          <t>sec_grade_5_ayyash_ibn_abi_rabi_ah_1st_shift</t>
         </is>
       </c>
       <c r="F338" t="inlineStr">
         <is>
-          <t>GRADE 4 - USAYD IBN HUDHAYR (1ST SHIFT) - MIX</t>
+          <t>GRADE 5 - AYYASH IBN ABI RABI'AH(1ST SHIFT)</t>
         </is>
       </c>
       <c r="G338" t="inlineStr">
@@ -22698,7 +22698,7 @@
       </c>
       <c r="H338" t="inlineStr">
         <is>
-          <t>Grade 4</t>
+          <t>Grade 5</t>
         </is>
       </c>
       <c r="I338" t="inlineStr">
@@ -22708,22 +22708,22 @@
       </c>
       <c r="J338" t="inlineStr">
         <is>
-          <t>subj_gmrc</t>
+          <t>subj_araling_panlipunan</t>
         </is>
       </c>
       <c r="K338" t="inlineStr">
         <is>
-          <t>GMRC</t>
+          <t>Araling Panlipunan</t>
         </is>
       </c>
       <c r="L338" t="inlineStr">
         <is>
-          <t>tchr_sahdia</t>
+          <t>tchr_saimonah</t>
         </is>
       </c>
       <c r="M338" t="inlineStr">
         <is>
-          <t>Teacher Sahdia</t>
+          <t>Teacher Saimonah</t>
         </is>
       </c>
       <c r="N338" t="n">
@@ -22749,12 +22749,12 @@
       </c>
       <c r="E339" t="inlineStr">
         <is>
-          <t>sec_grade_5_ayyash_ibn_abi_rabi_ah_1st_shift</t>
+          <t>sec_grade_5_hamza_ibn_abdul_1st_shift</t>
         </is>
       </c>
       <c r="F339" t="inlineStr">
         <is>
-          <t>GRADE 5 - AYYASH IBN ABI RABI'AH(1ST SHIFT)</t>
+          <t>GRADE 5 - HAMZA IBN ABDUL (1ST SHIFT)</t>
         </is>
       </c>
       <c r="G339" t="inlineStr">
@@ -22774,22 +22774,22 @@
       </c>
       <c r="J339" t="inlineStr">
         <is>
-          <t>subj_araling_panlipunan</t>
+          <t>subj_tle</t>
         </is>
       </c>
       <c r="K339" t="inlineStr">
         <is>
-          <t>Araling Panlipunan</t>
+          <t>TLE</t>
         </is>
       </c>
       <c r="L339" t="inlineStr">
         <is>
-          <t>tchr_saimonah</t>
+          <t>tchr_anna</t>
         </is>
       </c>
       <c r="M339" t="inlineStr">
         <is>
-          <t>Teacher Saimonah</t>
+          <t>Teacher Anna</t>
         </is>
       </c>
       <c r="N339" t="n">
@@ -22815,12 +22815,12 @@
       </c>
       <c r="E340" t="inlineStr">
         <is>
-          <t>sec_grade_5_hamza_ibn_abdul_1st_shift</t>
+          <t>sec_grade_5_muhammad_ibn_maslamah_1st_shift</t>
         </is>
       </c>
       <c r="F340" t="inlineStr">
         <is>
-          <t>GRADE 5 - HAMZA IBN ABDUL (1ST SHIFT)</t>
+          <t>GRADE 5 - MUHAMMAD IBN MASLAMAH (1ST SHIFT)</t>
         </is>
       </c>
       <c r="G340" t="inlineStr">
@@ -22840,22 +22840,22 @@
       </c>
       <c r="J340" t="inlineStr">
         <is>
-          <t>subj_tle</t>
+          <t>subj_filipino</t>
         </is>
       </c>
       <c r="K340" t="inlineStr">
         <is>
-          <t>TLE</t>
+          <t>Filipino</t>
         </is>
       </c>
       <c r="L340" t="inlineStr">
         <is>
-          <t>tchr_anna</t>
+          <t>tchr_joanna</t>
         </is>
       </c>
       <c r="M340" t="inlineStr">
         <is>
-          <t>Teacher Anna</t>
+          <t>Teacher Joanna</t>
         </is>
       </c>
       <c r="N340" t="n">
@@ -22881,12 +22881,12 @@
       </c>
       <c r="E341" t="inlineStr">
         <is>
-          <t>sec_grade_5_muhammad_ibn_maslamah_1st_shift</t>
+          <t>sec_grade_6_abbas_ibn_abd_al_muttalib_1st_shift</t>
         </is>
       </c>
       <c r="F341" t="inlineStr">
         <is>
-          <t>GRADE 5 - MUHAMMAD IBN MASLAMAH (1ST SHIFT)</t>
+          <t>GRADE 6 - ABBAS IBN ABD AL-MUTTALIB (1ST SHIFT)</t>
         </is>
       </c>
       <c r="G341" t="inlineStr">
@@ -22896,7 +22896,7 @@
       </c>
       <c r="H341" t="inlineStr">
         <is>
-          <t>Grade 5</t>
+          <t>Grade 6</t>
         </is>
       </c>
       <c r="I341" t="inlineStr">
@@ -22906,22 +22906,22 @@
       </c>
       <c r="J341" t="inlineStr">
         <is>
-          <t>subj_filipino</t>
+          <t>subj_shaf</t>
         </is>
       </c>
       <c r="K341" t="inlineStr">
         <is>
-          <t>Filipino</t>
+          <t>SHAF</t>
         </is>
       </c>
       <c r="L341" t="inlineStr">
         <is>
-          <t>tchr_joanna</t>
+          <t>tchr_abdiraheem</t>
         </is>
       </c>
       <c r="M341" t="inlineStr">
         <is>
-          <t>Teacher Joanna</t>
+          <t>Ustadh Abdiraheem</t>
         </is>
       </c>
       <c r="N341" t="n">
@@ -22947,12 +22947,12 @@
       </c>
       <c r="E342" t="inlineStr">
         <is>
-          <t>sec_grade_6_abbas_ibn_abd_al_muttalib_1st_shift</t>
+          <t>sec_grade_6_abdullah_ibn_salaam_1st_shift</t>
         </is>
       </c>
       <c r="F342" t="inlineStr">
         <is>
-          <t>GRADE 6 - ABBAS IBN ABD AL-MUTTALIB (1ST SHIFT)</t>
+          <t>GRADE 6 - ABDULLAH IBN SALAAM (1ST SHIFT)</t>
         </is>
       </c>
       <c r="G342" t="inlineStr">
@@ -22972,22 +22972,22 @@
       </c>
       <c r="J342" t="inlineStr">
         <is>
-          <t>subj_shaf</t>
+          <t>subj_english</t>
         </is>
       </c>
       <c r="K342" t="inlineStr">
         <is>
-          <t>SHAF</t>
+          <t>English</t>
         </is>
       </c>
       <c r="L342" t="inlineStr">
         <is>
-          <t>tchr_abdiraheem</t>
+          <t>tchr_jessa</t>
         </is>
       </c>
       <c r="M342" t="inlineStr">
         <is>
-          <t>Ustadh Abdiraheem</t>
+          <t>Teacher Jessa</t>
         </is>
       </c>
       <c r="N342" t="n">
@@ -23013,22 +23013,22 @@
       </c>
       <c r="E343" t="inlineStr">
         <is>
-          <t>sec_grade_6_abdullah_ibn_salaam_1st_shift</t>
+          <t>sec_grade_7_abu_sufyan_ibn_al_harith_1st_shift_boys</t>
         </is>
       </c>
       <c r="F343" t="inlineStr">
         <is>
-          <t>GRADE 6 - ABDULLAH IBN SALAAM (1ST SHIFT)</t>
+          <t>GRADE 7 - ABU SUFYAN IBN AL-HARITH (1ST SHIFT) BOYS</t>
         </is>
       </c>
       <c r="G343" t="inlineStr">
         <is>
-          <t>Elementary</t>
+          <t>Junior High School</t>
         </is>
       </c>
       <c r="H343" t="inlineStr">
         <is>
-          <t>Grade 6</t>
+          <t>Grade 7</t>
         </is>
       </c>
       <c r="I343" t="inlineStr">
@@ -23038,22 +23038,22 @@
       </c>
       <c r="J343" t="inlineStr">
         <is>
-          <t>subj_english</t>
+          <t>subj_arabic</t>
         </is>
       </c>
       <c r="K343" t="inlineStr">
         <is>
-          <t>English</t>
+          <t>Arabic</t>
         </is>
       </c>
       <c r="L343" t="inlineStr">
         <is>
-          <t>tchr_jessa</t>
+          <t>tchr_ali</t>
         </is>
       </c>
       <c r="M343" t="inlineStr">
         <is>
-          <t>Teacher Jessa</t>
+          <t>Ustadh Ali</t>
         </is>
       </c>
       <c r="N343" t="n">
@@ -23074,17 +23074,17 @@
       </c>
       <c r="D344" t="inlineStr">
         <is>
-          <t>12:40 PM – 01:40 PM</t>
+          <t>12:40 PM – 02:50 PM</t>
         </is>
       </c>
       <c r="E344" t="inlineStr">
         <is>
-          <t>sec_grade_7_abu_sufyan_ibn_al_harith_1st_shift_boys</t>
+          <t>sec_grade_7_usama_ibn_zayd_1st_shift_girls</t>
         </is>
       </c>
       <c r="F344" t="inlineStr">
         <is>
-          <t>GRADE 7 - ABU SUFYAN IBN AL-HARITH (1ST SHIFT) BOYS</t>
+          <t>GRADE 7 - USAMA IBN ZAYD (1ST SHIFT) GIRLS</t>
         </is>
       </c>
       <c r="G344" t="inlineStr">
@@ -23104,26 +23104,26 @@
       </c>
       <c r="J344" t="inlineStr">
         <is>
-          <t>subj_arabic</t>
+          <t>subj_math</t>
         </is>
       </c>
       <c r="K344" t="inlineStr">
         <is>
-          <t>Arabic</t>
+          <t>Math</t>
         </is>
       </c>
       <c r="L344" t="inlineStr">
         <is>
-          <t>tchr_ali</t>
+          <t>tchr_ethel</t>
         </is>
       </c>
       <c r="M344" t="inlineStr">
         <is>
-          <t>Ustadh Ali</t>
+          <t>Teacher Ethel</t>
         </is>
       </c>
       <c r="N344" t="n">
-        <v>60</v>
+        <v>120</v>
       </c>
     </row>
     <row r="345">
@@ -23140,17 +23140,17 @@
       </c>
       <c r="D345" t="inlineStr">
         <is>
-          <t>12:40 PM – 02:50 PM</t>
+          <t>12:40 PM – 01:40 PM</t>
         </is>
       </c>
       <c r="E345" t="inlineStr">
         <is>
-          <t>sec_grade_7_usama_ibn_zayd_1st_shift_girls</t>
+          <t>sec_grade_8_sa_ad_ibn_mua_dh_1st_shift_girls</t>
         </is>
       </c>
       <c r="F345" t="inlineStr">
         <is>
-          <t>GRADE 7 - USAMA IBN ZAYD (1ST SHIFT) GIRLS</t>
+          <t>GRADE 8 - SA'AD IBN MUA'DH (1ST SHIFT) - GIRLS</t>
         </is>
       </c>
       <c r="G345" t="inlineStr">
@@ -23160,7 +23160,7 @@
       </c>
       <c r="H345" t="inlineStr">
         <is>
-          <t>Grade 7</t>
+          <t>Grade 8</t>
         </is>
       </c>
       <c r="I345" t="inlineStr">
@@ -23170,26 +23170,26 @@
       </c>
       <c r="J345" t="inlineStr">
         <is>
-          <t>subj_math</t>
+          <t>subj_filipino</t>
         </is>
       </c>
       <c r="K345" t="inlineStr">
         <is>
-          <t>Math</t>
+          <t>Filipino</t>
         </is>
       </c>
       <c r="L345" t="inlineStr">
         <is>
-          <t>tchr_ethel</t>
+          <t>tchr_sophia</t>
         </is>
       </c>
       <c r="M345" t="inlineStr">
         <is>
-          <t>Teacher Ethel</t>
+          <t>Teacher Sophia</t>
         </is>
       </c>
       <c r="N345" t="n">
-        <v>120</v>
+        <v>60</v>
       </c>
     </row>
     <row r="346">
@@ -23211,12 +23211,12 @@
       </c>
       <c r="E346" t="inlineStr">
         <is>
-          <t>sec_grade_8_sa_ad_ibn_mua_dh_1st_shift_girls</t>
+          <t>sec_grade_9_abu_hurayrah_1st_shift_girls</t>
         </is>
       </c>
       <c r="F346" t="inlineStr">
         <is>
-          <t>GRADE 8 - SA'AD IBN MUA'DH (1ST SHIFT) - GIRLS</t>
+          <t>GRADE 9 - ABU HURAYRAH (1ST SHIFT) GIRLS</t>
         </is>
       </c>
       <c r="G346" t="inlineStr">
@@ -23226,7 +23226,7 @@
       </c>
       <c r="H346" t="inlineStr">
         <is>
-          <t>Grade 8</t>
+          <t>Grade 9</t>
         </is>
       </c>
       <c r="I346" t="inlineStr">
@@ -23236,22 +23236,22 @@
       </c>
       <c r="J346" t="inlineStr">
         <is>
-          <t>subj_filipino</t>
+          <t>subj_arabic</t>
         </is>
       </c>
       <c r="K346" t="inlineStr">
         <is>
-          <t>Filipino</t>
+          <t>Arabic</t>
         </is>
       </c>
       <c r="L346" t="inlineStr">
         <is>
-          <t>tchr_sophia</t>
+          <t>tchr_raslina</t>
         </is>
       </c>
       <c r="M346" t="inlineStr">
         <is>
-          <t>Teacher Sophia</t>
+          <t>Ustadh Raslina</t>
         </is>
       </c>
       <c r="N346" t="n">
@@ -23272,27 +23272,27 @@
       </c>
       <c r="D347" t="inlineStr">
         <is>
-          <t>12:40 PM – 01:40 PM</t>
+          <t>01:30 PM – 02:30 PM</t>
         </is>
       </c>
       <c r="E347" t="inlineStr">
         <is>
-          <t>sec_grade_9_abu_hurayrah_1st_shift_girls</t>
+          <t>sec_kinder_2_abu_bakr_as_sideeq_1st_shift</t>
         </is>
       </c>
       <c r="F347" t="inlineStr">
         <is>
-          <t>GRADE 9 - ABU HURAYRAH (1ST SHIFT) GIRLS</t>
+          <t>Kinder 2 ABU BAKR AS-SIDEEQ (1ST SHIFT)</t>
         </is>
       </c>
       <c r="G347" t="inlineStr">
         <is>
-          <t>Junior High School</t>
+          <t>Elementary</t>
         </is>
       </c>
       <c r="H347" t="inlineStr">
         <is>
-          <t>Grade 9</t>
+          <t>Kinder 2</t>
         </is>
       </c>
       <c r="I347" t="inlineStr">
@@ -23312,12 +23312,12 @@
       </c>
       <c r="L347" t="inlineStr">
         <is>
-          <t>tchr_raslina</t>
+          <t>tchr_silfah</t>
         </is>
       </c>
       <c r="M347" t="inlineStr">
         <is>
-          <t>Ustadh Raslina</t>
+          <t>Ustadh Silfah</t>
         </is>
       </c>
       <c r="N347" t="n">
@@ -23343,12 +23343,12 @@
       </c>
       <c r="E348" t="inlineStr">
         <is>
-          <t>sec_kinder_2_abu_bakr_as_sideeq_1st_shift</t>
+          <t>sec_kinder_2_uthman_ibn_affan_1st_shift</t>
         </is>
       </c>
       <c r="F348" t="inlineStr">
         <is>
-          <t>Kinder 2 ABU BAKR AS-SIDEEQ (1ST SHIFT)</t>
+          <t>Kinder 2 UTHMAN IBN AFFAN (1ST SHIFT)</t>
         </is>
       </c>
       <c r="G348" t="inlineStr">
@@ -23368,22 +23368,22 @@
       </c>
       <c r="J348" t="inlineStr">
         <is>
-          <t>subj_arabic</t>
+          <t>subj_oral_written_exam</t>
         </is>
       </c>
       <c r="K348" t="inlineStr">
         <is>
-          <t>Arabic</t>
+          <t>Oral &amp; Written Exam</t>
         </is>
       </c>
       <c r="L348" t="inlineStr">
         <is>
-          <t>tchr_silfah</t>
+          <t>tchr_ayah</t>
         </is>
       </c>
       <c r="M348" t="inlineStr">
         <is>
-          <t>Ustadh Silfah</t>
+          <t>Teacher Ayah</t>
         </is>
       </c>
       <c r="N348" t="n">
@@ -23400,21 +23400,21 @@
         </is>
       </c>
       <c r="C349" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D349" t="inlineStr">
         <is>
-          <t>01:30 PM – 02:30 PM</t>
+          <t>01:50 PM – 02:50 PM</t>
         </is>
       </c>
       <c r="E349" t="inlineStr">
         <is>
-          <t>sec_kinder_2_uthman_ibn_affan_1st_shift</t>
+          <t>sec_grade_1_hudhayfah_ibn_al_yam_1st_shift</t>
         </is>
       </c>
       <c r="F349" t="inlineStr">
         <is>
-          <t>Kinder 2 UTHMAN IBN AFFAN (1ST SHIFT)</t>
+          <t>GRADE 1 - HUDHAYFAH IBN AL-YAM (1ST SHIFT)</t>
         </is>
       </c>
       <c r="G349" t="inlineStr">
@@ -23424,7 +23424,7 @@
       </c>
       <c r="H349" t="inlineStr">
         <is>
-          <t>Kinder 2</t>
+          <t>Grade 1</t>
         </is>
       </c>
       <c r="I349" t="inlineStr">
@@ -23434,22 +23434,22 @@
       </c>
       <c r="J349" t="inlineStr">
         <is>
-          <t>subj_oral_written_exam</t>
+          <t>subj_language</t>
         </is>
       </c>
       <c r="K349" t="inlineStr">
         <is>
-          <t>Oral &amp; Written Exam</t>
+          <t>Language</t>
         </is>
       </c>
       <c r="L349" t="inlineStr">
         <is>
-          <t>tchr_ayah</t>
+          <t>tchr_sahdia</t>
         </is>
       </c>
       <c r="M349" t="inlineStr">
         <is>
-          <t>Teacher Ayah</t>
+          <t>Teacher Sahdia</t>
         </is>
       </c>
       <c r="N349" t="n">
@@ -23475,22 +23475,22 @@
       </c>
       <c r="E350" t="inlineStr">
         <is>
-          <t>sec_grade_1_hudhayfah_ibn_al_yam_1st_shift</t>
+          <t>sec_grade_11_1st_shift_girls</t>
         </is>
       </c>
       <c r="F350" t="inlineStr">
         <is>
-          <t>GRADE 1 - HUDHAYFAH IBN AL-YAM (1ST SHIFT)</t>
+          <t>GRADE 11 (1ST SHIFT GIRLS)</t>
         </is>
       </c>
       <c r="G350" t="inlineStr">
         <is>
-          <t>Elementary</t>
+          <t>Senior High School</t>
         </is>
       </c>
       <c r="H350" t="inlineStr">
         <is>
-          <t>Grade 1</t>
+          <t>Grade 11</t>
         </is>
       </c>
       <c r="I350" t="inlineStr">
@@ -23500,22 +23500,22 @@
       </c>
       <c r="J350" t="inlineStr">
         <is>
-          <t>subj_language</t>
+          <t>subj_gen_science</t>
         </is>
       </c>
       <c r="K350" t="inlineStr">
         <is>
-          <t>Language</t>
+          <t>Gen Science</t>
         </is>
       </c>
       <c r="L350" t="inlineStr">
         <is>
-          <t>tchr_sahdia</t>
+          <t>tchr_rowena</t>
         </is>
       </c>
       <c r="M350" t="inlineStr">
         <is>
-          <t>Teacher Sahdia</t>
+          <t>Teacher Rowena</t>
         </is>
       </c>
       <c r="N350" t="n">
@@ -23541,12 +23541,12 @@
       </c>
       <c r="E351" t="inlineStr">
         <is>
-          <t>sec_grade_11_1st_shift_girls</t>
+          <t>sec_grade_12_abu_musa_al_ashari</t>
         </is>
       </c>
       <c r="F351" t="inlineStr">
         <is>
-          <t>GRADE 11 (1ST SHIFT GIRLS)</t>
+          <t>GRADE 12 - ABU MUSA AL-ASHARI</t>
         </is>
       </c>
       <c r="G351" t="inlineStr">
@@ -23556,7 +23556,7 @@
       </c>
       <c r="H351" t="inlineStr">
         <is>
-          <t>Grade 11</t>
+          <t>Grade 12</t>
         </is>
       </c>
       <c r="I351" t="inlineStr">
@@ -23566,22 +23566,22 @@
       </c>
       <c r="J351" t="inlineStr">
         <is>
-          <t>subj_gen_science</t>
+          <t>subj_arabic</t>
         </is>
       </c>
       <c r="K351" t="inlineStr">
         <is>
-          <t>Gen Science</t>
+          <t>Arabic</t>
         </is>
       </c>
       <c r="L351" t="inlineStr">
         <is>
-          <t>tchr_rowena</t>
+          <t>tchr_mamonas</t>
         </is>
       </c>
       <c r="M351" t="inlineStr">
         <is>
-          <t>Teacher Rowena</t>
+          <t>Alim Mamonas</t>
         </is>
       </c>
       <c r="N351" t="n">
@@ -23607,22 +23607,22 @@
       </c>
       <c r="E352" t="inlineStr">
         <is>
-          <t>sec_grade_12_abu_musa_al_ashari</t>
+          <t>sec_grade_2_amr_ibn_al_jamuh_1st_shift</t>
         </is>
       </c>
       <c r="F352" t="inlineStr">
         <is>
-          <t>GRADE 12 - ABU MUSA AL-ASHARI</t>
+          <t>GRADE 2 - AMR IBN AL-JAMUH (1ST SHIFT)</t>
         </is>
       </c>
       <c r="G352" t="inlineStr">
         <is>
-          <t>Senior High School</t>
+          <t>Elementary</t>
         </is>
       </c>
       <c r="H352" t="inlineStr">
         <is>
-          <t>Grade 12</t>
+          <t>Grade 2</t>
         </is>
       </c>
       <c r="I352" t="inlineStr">
@@ -23632,22 +23632,22 @@
       </c>
       <c r="J352" t="inlineStr">
         <is>
-          <t>subj_arabic</t>
+          <t>subj_makabansa</t>
         </is>
       </c>
       <c r="K352" t="inlineStr">
         <is>
-          <t>Arabic</t>
+          <t>Makabansa</t>
         </is>
       </c>
       <c r="L352" t="inlineStr">
         <is>
-          <t>tchr_mamonas</t>
+          <t>tchr_monisa</t>
         </is>
       </c>
       <c r="M352" t="inlineStr">
         <is>
-          <t>Alim Mamonas</t>
+          <t>Teacher Monisa</t>
         </is>
       </c>
       <c r="N352" t="n">
@@ -23673,12 +23673,12 @@
       </c>
       <c r="E353" t="inlineStr">
         <is>
-          <t>sec_grade_2_amr_ibn_al_jamuh_1st_shift</t>
+          <t>sec_grade_2_talha_ibn_ubaydullah_1st_shift</t>
         </is>
       </c>
       <c r="F353" t="inlineStr">
         <is>
-          <t>GRADE 2 - AMR IBN AL-JAMUH (1ST SHIFT)</t>
+          <t>GRADE 2 - TALHA IBN UBAYDULLAH (1ST SHIFT)</t>
         </is>
       </c>
       <c r="G353" t="inlineStr">
@@ -23698,22 +23698,22 @@
       </c>
       <c r="J353" t="inlineStr">
         <is>
-          <t>subj_makabansa</t>
+          <t>subj_arabic</t>
         </is>
       </c>
       <c r="K353" t="inlineStr">
         <is>
-          <t>Makabansa</t>
+          <t>Arabic</t>
         </is>
       </c>
       <c r="L353" t="inlineStr">
         <is>
-          <t>tchr_monisa</t>
+          <t>tchr_hainur</t>
         </is>
       </c>
       <c r="M353" t="inlineStr">
         <is>
-          <t>Teacher Monisa</t>
+          <t>Ustadha Hainur</t>
         </is>
       </c>
       <c r="N353" t="n">
@@ -26683,7 +26683,7 @@
       </c>
       <c r="M398" t="inlineStr">
         <is>
-          <t>Ustadh Hainur</t>
+          <t>Ustadha Hainur</t>
         </is>
       </c>
       <c r="N398" t="n">
@@ -26749,7 +26749,7 @@
       </c>
       <c r="M399" t="inlineStr">
         <is>
-          <t>Ustadh Hainur</t>
+          <t>Ustadha Hainur</t>
         </is>
       </c>
       <c r="N399" t="n">
@@ -26881,7 +26881,7 @@
       </c>
       <c r="M401" t="inlineStr">
         <is>
-          <t>Ustadh Hainur</t>
+          <t>Ustadha Hainur</t>
         </is>
       </c>
       <c r="N401" t="n">
@@ -28663,7 +28663,7 @@
       </c>
       <c r="M428" t="inlineStr">
         <is>
-          <t>Ustadh Hainur</t>
+          <t>Ustadha Hainur</t>
         </is>
       </c>
       <c r="N428" t="n">
@@ -31699,7 +31699,7 @@
       </c>
       <c r="M474" t="inlineStr">
         <is>
-          <t>Ustadh Hainur</t>
+          <t>Ustadha Hainur</t>
         </is>
       </c>
       <c r="N474" t="n">
@@ -34075,7 +34075,7 @@
       </c>
       <c r="M510" t="inlineStr">
         <is>
-          <t>Ustadh Hainur</t>
+          <t>Ustadha Hainur</t>
         </is>
       </c>
       <c r="N510" t="n">
@@ -36385,7 +36385,7 @@
       </c>
       <c r="M545" t="inlineStr">
         <is>
-          <t>Ustadh Hainur</t>
+          <t>Ustadha Hainur</t>
         </is>
       </c>
       <c r="N545" t="n">
@@ -38695,7 +38695,7 @@
       </c>
       <c r="M580" t="inlineStr">
         <is>
-          <t>Ustadh Hainur</t>
+          <t>Ustadha Hainur</t>
         </is>
       </c>
       <c r="N580" t="n">

--- a/Term_Examination_Schedule_S.Y._2026-2027_Optimized.xlsx
+++ b/Term_Examination_Schedule_S.Y._2026-2027_Optimized.xlsx
@@ -2685,12 +2685,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>sec_grade_5_ayyash_ibn_abi_rabi_ah_1st_shift</t>
+          <t>sec_grade_5_hamza_ibn_abdul_1st_shift</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>GRADE 5 - AYYASH IBN ABI RABI'AH(1ST SHIFT)</t>
+          <t>GRADE 5 - HAMZA IBN ABDUL (1ST SHIFT)</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
@@ -2710,22 +2710,22 @@
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>subj_gmrc</t>
+          <t>subj_qur_an</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>GMRC</t>
+          <t>Qur'an</t>
         </is>
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>tchr_saliha</t>
+          <t>tchr_jaisam</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>Ustadha Saliha</t>
+          <t>Ustadh Jaisam</t>
         </is>
       </c>
       <c r="N35" t="n">
@@ -2751,12 +2751,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>sec_grade_5_hamza_ibn_abdul_1st_shift</t>
+          <t>sec_grade_6_abbas_ibn_abd_al_muttalib_1st_shift</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>GRADE 5 - HAMZA IBN ABDUL (1ST SHIFT)</t>
+          <t>GRADE 6 - ABBAS IBN ABD AL-MUTTALIB (1ST SHIFT)</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
@@ -2766,7 +2766,7 @@
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>Grade 5</t>
+          <t>Grade 6</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
@@ -2776,22 +2776,22 @@
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>subj_qur_an</t>
+          <t>subj_gmrc</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>Qur'an</t>
+          <t>GMRC</t>
         </is>
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>tchr_jaisam</t>
+          <t>tchr_silfah</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>Ustadh Jaisam</t>
+          <t>Ustadh Silfah</t>
         </is>
       </c>
       <c r="N36" t="n">
@@ -2808,21 +2808,21 @@
         </is>
       </c>
       <c r="C37" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>11:30 AM – 12:30 PM</t>
+          <t>12:40 PM – 01:40 PM</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>sec_grade_6_abbas_ibn_abd_al_muttalib_1st_shift</t>
+          <t>sec_grade_1_ali_ibn_abi_talib_1st_shift</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>GRADE 6 - ABBAS IBN ABD AL-MUTTALIB (1ST SHIFT)</t>
+          <t>GRADE 1 - ALI IBN ABI TALIB(1ST SHIFT)</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
@@ -2832,7 +2832,7 @@
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>Grade 6</t>
+          <t>Grade 1</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
@@ -2842,22 +2842,22 @@
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>subj_gmrc</t>
+          <t>subj_makabansa</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>GMRC</t>
+          <t>Makabansa</t>
         </is>
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>tchr_silfah</t>
+          <t>tchr_norhydie</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>Ustadh Silfah</t>
+          <t>Teacher Norhydie</t>
         </is>
       </c>
       <c r="N37" t="n">
@@ -2883,12 +2883,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>sec_grade_1_ali_ibn_abi_talib_1st_shift</t>
+          <t>sec_grade_1_hudhayfah_ibn_al_yam_1st_shift</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>GRADE 1 - ALI IBN ABI TALIB(1ST SHIFT)</t>
+          <t>GRADE 1 - HUDHAYFAH IBN AL-YAM (1ST SHIFT)</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
@@ -2908,22 +2908,22 @@
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>subj_makabansa</t>
+          <t>subj_arabic</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>Makabansa</t>
+          <t>Arabic</t>
         </is>
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>tchr_norhydie</t>
+          <t>tchr_hainur</t>
         </is>
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>Teacher Norhydie</t>
+          <t>Ustadha Hainur</t>
         </is>
       </c>
       <c r="N38" t="n">
@@ -2949,22 +2949,22 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>sec_grade_1_hudhayfah_ibn_al_yam_1st_shift</t>
+          <t>sec_grade_10_utbah_ibn_ghazwan_1st_shift_girls</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>GRADE 1 - HUDHAYFAH IBN AL-YAM (1ST SHIFT)</t>
+          <t>GRADE 10 - UTBAH IBN GHAZWAN (1ST SHIFT) GIRLS</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Elementary</t>
+          <t>Junior High School</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>Grade 1</t>
+          <t>Grade 10</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
@@ -2974,22 +2974,22 @@
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>subj_arabic</t>
+          <t>subj_social_studies</t>
         </is>
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>Arabic</t>
+          <t>Social Science</t>
         </is>
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>tchr_hainur</t>
+          <t>tchr_sophia</t>
         </is>
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>Ustadha Hainur</t>
+          <t>Teacher Sophia</t>
         </is>
       </c>
       <c r="N39" t="n">
@@ -3006,7 +3006,7 @@
         </is>
       </c>
       <c r="C40" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -3015,22 +3015,22 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>sec_grade_10_utbah_ibn_ghazwan_1st_shift_girls</t>
+          <t>sec_grade_11_1st_shift_girls</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>GRADE 10 - UTBAH IBN GHAZWAN (1ST SHIFT) GIRLS</t>
+          <t>GRADE 11 (1ST SHIFT GIRLS)</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Junior High School</t>
+          <t>Senior High School</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>Grade 10</t>
+          <t>Grade 11</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
@@ -3040,22 +3040,22 @@
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>subj_social_studies</t>
+          <t>subj_qur_an</t>
         </is>
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>Social Science</t>
+          <t>Qur'an</t>
         </is>
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>tchr_sophia</t>
+          <t>tchr_abdulwahab</t>
         </is>
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>Teacher Sophia</t>
+          <t>Alim Abdulwahab</t>
         </is>
       </c>
       <c r="N40" t="n">
@@ -3081,12 +3081,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>sec_grade_11_1st_shift_girls</t>
+          <t>sec_grade_12_abu_musa_al_ashari</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>GRADE 11 (1ST SHIFT GIRLS)</t>
+          <t>GRADE 12 - ABU MUSA AL-ASHARI</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
@@ -3096,7 +3096,7 @@
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>Grade 11</t>
+          <t>Grade 12</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
@@ -3106,22 +3106,22 @@
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>subj_qur_an</t>
+          <t>subj_pe_12</t>
         </is>
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>Qur'an</t>
+          <t>PE 12</t>
         </is>
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>tchr_abdulwahab</t>
+          <t>tchr_mohaymen</t>
         </is>
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>Alim Abdulwahab</t>
+          <t>Sir Mohaymen</t>
         </is>
       </c>
       <c r="N41" t="n">
@@ -3138,7 +3138,7 @@
         </is>
       </c>
       <c r="C42" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -3147,22 +3147,22 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>sec_grade_12_abu_musa_al_ashari</t>
+          <t>sec_grade_2_amr_ibn_al_jamuh_1st_shift</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>GRADE 12 - ABU MUSA AL-ASHARI</t>
+          <t>GRADE 2 - AMR IBN AL-JAMUH (1ST SHIFT)</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Senior High School</t>
+          <t>Elementary</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>Grade 12</t>
+          <t>Grade 2</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
@@ -3172,22 +3172,22 @@
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>subj_pe_12</t>
+          <t>subj_shaf</t>
         </is>
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>PE 12</t>
+          <t>SHAF</t>
         </is>
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>tchr_mohaymen</t>
+          <t>tchr_abdul_karim</t>
         </is>
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>Sir Mohaymen</t>
+          <t>Alim Abdul Karim</t>
         </is>
       </c>
       <c r="N42" t="n">
@@ -3213,12 +3213,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>sec_grade_2_amr_ibn_al_jamuh_1st_shift</t>
+          <t>sec_grade_2_talha_ibn_ubaydullah_1st_shift</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>GRADE 2 - AMR IBN AL-JAMUH (1ST SHIFT)</t>
+          <t>GRADE 2 - TALHA IBN UBAYDULLAH (1ST SHIFT)</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
@@ -3238,22 +3238,22 @@
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>subj_shaf</t>
+          <t>subj_filipino</t>
         </is>
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>SHAF</t>
+          <t>Filipino</t>
         </is>
       </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>tchr_abdul_karim</t>
+          <t>tchr_sitti_kauzar</t>
         </is>
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>Alim Abdul Karim</t>
+          <t>Teacher Sitti Kauzar</t>
         </is>
       </c>
       <c r="N43" t="n">
@@ -3279,12 +3279,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>sec_grade_2_talha_ibn_ubaydullah_1st_shift</t>
+          <t>sec_grade_3_ammar_ibn_yasir_1st_shift_boys</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>GRADE 2 - TALHA IBN UBAYDULLAH (1ST SHIFT)</t>
+          <t>GRADE 3 -AMMAR IBN YASIR (1ST SHIFT) - BOYS</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
@@ -3294,7 +3294,7 @@
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>Grade 2</t>
+          <t>Grade 3</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
@@ -3304,22 +3304,22 @@
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>subj_filipino</t>
+          <t>subj_qur_an</t>
         </is>
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>Filipino</t>
+          <t>Qur'an</t>
         </is>
       </c>
       <c r="L44" t="inlineStr">
         <is>
-          <t>tchr_sitti_kauzar</t>
+          <t>tchr_obaydah</t>
         </is>
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>Teacher Sitti Kauzar</t>
+          <t>Ustadh Obaydah</t>
         </is>
       </c>
       <c r="N44" t="n">
@@ -3345,12 +3345,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>sec_grade_3_ammar_ibn_yasir_1st_shift_boys</t>
+          <t>sec_grade_4_abdur_rahman_ibn_awf_1st_shift</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>GRADE 3 -AMMAR IBN YASIR (1ST SHIFT) - BOYS</t>
+          <t>GRADE 4 - ABDUR RAHMAN IBN AWF (1ST SHIFT)</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
@@ -3360,7 +3360,7 @@
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>Grade 3</t>
+          <t>Grade 4</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
@@ -3370,22 +3370,22 @@
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>subj_qur_an</t>
+          <t>subj_tle</t>
         </is>
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>Qur'an</t>
+          <t>TLE</t>
         </is>
       </c>
       <c r="L45" t="inlineStr">
         <is>
-          <t>tchr_obaydah</t>
+          <t>tchr_monisa</t>
         </is>
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>Ustadh Obaydah</t>
+          <t>Teacher Monisa</t>
         </is>
       </c>
       <c r="N45" t="n">
@@ -3411,12 +3411,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>sec_grade_4_abdur_rahman_ibn_awf_1st_shift</t>
+          <t>sec_grade_4_hakim_ibn_hazm_1st_shift</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>GRADE 4 - ABDUR RAHMAN IBN AWF (1ST SHIFT)</t>
+          <t>GRADE 4 - HAKIM IBN HAZM(1ST SHIFT)</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
@@ -3436,22 +3436,22 @@
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>subj_tle</t>
+          <t>subj_science</t>
         </is>
       </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t>TLE</t>
+          <t>Science</t>
         </is>
       </c>
       <c r="L46" t="inlineStr">
         <is>
-          <t>tchr_monisa</t>
+          <t>tchr_anna</t>
         </is>
       </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t>Teacher Monisa</t>
+          <t>Teacher Anna</t>
         </is>
       </c>
       <c r="N46" t="n">
@@ -3477,12 +3477,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>sec_grade_4_hakim_ibn_hazm_1st_shift</t>
+          <t>sec_grade_4_usayd_ibn_hudhayr_1st_shift_mix</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>GRADE 4 - HAKIM IBN HAZM(1ST SHIFT)</t>
+          <t>GRADE 4 - USAYD IBN HUDHAYR (1ST SHIFT) - MIX</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
@@ -3502,22 +3502,22 @@
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>subj_science</t>
+          <t>subj_shaf</t>
         </is>
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>Science</t>
+          <t>SHAF</t>
         </is>
       </c>
       <c r="L47" t="inlineStr">
         <is>
-          <t>tchr_anna</t>
+          <t>tchr_abdiraheem</t>
         </is>
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t>Teacher Anna</t>
+          <t>Ustadh Abdiraheem</t>
         </is>
       </c>
       <c r="N47" t="n">
@@ -3543,12 +3543,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>sec_grade_4_usayd_ibn_hudhayr_1st_shift_mix</t>
+          <t>sec_grade_5_ayyash_ibn_abi_rabi_ah_1st_shift</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>GRADE 4 - USAYD IBN HUDHAYR (1ST SHIFT) - MIX</t>
+          <t>GRADE 5 - AYYASH IBN ABI RABI'AH(1ST SHIFT)</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
@@ -3558,7 +3558,7 @@
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>Grade 4</t>
+          <t>Grade 5</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
@@ -3568,22 +3568,22 @@
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>subj_shaf</t>
+          <t>subj_gmrc</t>
         </is>
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>SHAF</t>
+          <t>GMRC</t>
         </is>
       </c>
       <c r="L48" t="inlineStr">
         <is>
-          <t>tchr_abdiraheem</t>
+          <t>tchr_saliha</t>
         </is>
       </c>
       <c r="M48" t="inlineStr">
         <is>
-          <t>Ustadh Abdiraheem</t>
+          <t>Ustadha Saliha</t>
         </is>
       </c>
       <c r="N48" t="n">
@@ -4062,21 +4062,21 @@
         </is>
       </c>
       <c r="C56" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>01:30 PM – 02:30 PM</t>
+          <t>01:50 PM – 02:50 PM</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>sec_kinder_2_uthman_ibn_affan_1st_shift</t>
+          <t>sec_grade_1_hudhayfah_ibn_al_yam_1st_shift</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Kinder 2 UTHMAN IBN AFFAN (1ST SHIFT)</t>
+          <t>GRADE 1 - HUDHAYFAH IBN AL-YAM (1ST SHIFT)</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
@@ -4086,7 +4086,7 @@
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>Kinder 2</t>
+          <t>Grade 1</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
@@ -4096,22 +4096,22 @@
       </c>
       <c r="J56" t="inlineStr">
         <is>
-          <t>subj_hadith</t>
+          <t>subj_makabansa</t>
         </is>
       </c>
       <c r="K56" t="inlineStr">
         <is>
-          <t>Hadith</t>
+          <t>Makabansa</t>
         </is>
       </c>
       <c r="L56" t="inlineStr">
         <is>
-          <t>tchr_saliha</t>
+          <t>tchr_norhydie</t>
         </is>
       </c>
       <c r="M56" t="inlineStr">
         <is>
-          <t>Ustadha Saliha</t>
+          <t>Teacher Norhydie</t>
         </is>
       </c>
       <c r="N56" t="n">
@@ -4137,22 +4137,22 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>sec_grade_1_hudhayfah_ibn_al_yam_1st_shift</t>
+          <t>sec_grade_10_utbah_ibn_ghazwan_1st_shift_girls</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>GRADE 1 - HUDHAYFAH IBN AL-YAM (1ST SHIFT)</t>
+          <t>GRADE 10 - UTBAH IBN GHAZWAN (1ST SHIFT) GIRLS</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Elementary</t>
+          <t>Junior High School</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>Grade 1</t>
+          <t>Grade 10</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
@@ -4162,22 +4162,22 @@
       </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t>subj_makabansa</t>
+          <t>subj_qur_an</t>
         </is>
       </c>
       <c r="K57" t="inlineStr">
         <is>
-          <t>Makabansa</t>
+          <t>Qur'an</t>
         </is>
       </c>
       <c r="L57" t="inlineStr">
         <is>
-          <t>tchr_norhydie</t>
+          <t>tchr_abdulwahab</t>
         </is>
       </c>
       <c r="M57" t="inlineStr">
         <is>
-          <t>Teacher Norhydie</t>
+          <t>Alim Abdulwahab</t>
         </is>
       </c>
       <c r="N57" t="n">
@@ -4194,7 +4194,7 @@
         </is>
       </c>
       <c r="C58" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -4203,22 +4203,22 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>sec_grade_10_utbah_ibn_ghazwan_1st_shift_girls</t>
+          <t>sec_grade_11_1st_shift_girls</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>GRADE 10 - UTBAH IBN GHAZWAN (1ST SHIFT) GIRLS</t>
+          <t>GRADE 11 (1ST SHIFT GIRLS)</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Junior High School</t>
+          <t>Senior High School</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>Grade 10</t>
+          <t>Grade 11</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
@@ -4228,22 +4228,22 @@
       </c>
       <c r="J58" t="inlineStr">
         <is>
-          <t>subj_qur_an</t>
+          <t>subj_arabic</t>
         </is>
       </c>
       <c r="K58" t="inlineStr">
         <is>
-          <t>Qur'an</t>
+          <t>Arabic</t>
         </is>
       </c>
       <c r="L58" t="inlineStr">
         <is>
-          <t>tchr_abdulwahab</t>
+          <t>tchr_mamonas</t>
         </is>
       </c>
       <c r="M58" t="inlineStr">
         <is>
-          <t>Alim Abdulwahab</t>
+          <t>Alim Mamonas</t>
         </is>
       </c>
       <c r="N58" t="n">
@@ -4269,12 +4269,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>sec_grade_11_1st_shift_girls</t>
+          <t>sec_grade_12_abu_musa_al_ashari</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>GRADE 11 (1ST SHIFT GIRLS)</t>
+          <t>GRADE 12 - ABU MUSA AL-ASHARI</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
@@ -4284,7 +4284,7 @@
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>Grade 11</t>
+          <t>Grade 12</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
@@ -4294,22 +4294,22 @@
       </c>
       <c r="J59" t="inlineStr">
         <is>
-          <t>subj_arabic</t>
+          <t>subj_gen_bio_1</t>
         </is>
       </c>
       <c r="K59" t="inlineStr">
         <is>
-          <t>Arabic</t>
+          <t>Gen Bio 1</t>
         </is>
       </c>
       <c r="L59" t="inlineStr">
         <is>
-          <t>tchr_mamonas</t>
+          <t>tchr_radzmia</t>
         </is>
       </c>
       <c r="M59" t="inlineStr">
         <is>
-          <t>Alim Mamonas</t>
+          <t>Teacher Radzmia</t>
         </is>
       </c>
       <c r="N59" t="n">
@@ -4326,7 +4326,7 @@
         </is>
       </c>
       <c r="C60" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -4335,22 +4335,22 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>sec_grade_12_abu_musa_al_ashari</t>
+          <t>sec_grade_2_amr_ibn_al_jamuh_1st_shift</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>GRADE 12 - ABU MUSA AL-ASHARI</t>
+          <t>GRADE 2 - AMR IBN AL-JAMUH (1ST SHIFT)</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Senior High School</t>
+          <t>Elementary</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>Grade 12</t>
+          <t>Grade 2</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
@@ -4360,22 +4360,22 @@
       </c>
       <c r="J60" t="inlineStr">
         <is>
-          <t>subj_gen_bio_1</t>
+          <t>subj_filipino</t>
         </is>
       </c>
       <c r="K60" t="inlineStr">
         <is>
-          <t>Gen Bio 1</t>
+          <t>Filipino</t>
         </is>
       </c>
       <c r="L60" t="inlineStr">
         <is>
-          <t>tchr_radzmia</t>
+          <t>tchr_sitti_kauzar</t>
         </is>
       </c>
       <c r="M60" t="inlineStr">
         <is>
-          <t>Teacher Radzmia</t>
+          <t>Teacher Sitti Kauzar</t>
         </is>
       </c>
       <c r="N60" t="n">
@@ -4401,12 +4401,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>sec_grade_2_amr_ibn_al_jamuh_1st_shift</t>
+          <t>sec_grade_2_talha_ibn_ubaydullah_1st_shift</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>GRADE 2 - AMR IBN AL-JAMUH (1ST SHIFT)</t>
+          <t>GRADE 2 - TALHA IBN UBAYDULLAH (1ST SHIFT)</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
@@ -4426,22 +4426,22 @@
       </c>
       <c r="J61" t="inlineStr">
         <is>
-          <t>subj_filipino</t>
+          <t>subj_makabansa</t>
         </is>
       </c>
       <c r="K61" t="inlineStr">
         <is>
-          <t>Filipino</t>
+          <t>Makabansa</t>
         </is>
       </c>
       <c r="L61" t="inlineStr">
         <is>
-          <t>tchr_sitti_kauzar</t>
+          <t>tchr_zuhora</t>
         </is>
       </c>
       <c r="M61" t="inlineStr">
         <is>
-          <t>Teacher Sitti Kauzar</t>
+          <t>Teacher Zuhora</t>
         </is>
       </c>
       <c r="N61" t="n">
@@ -4458,7 +4458,7 @@
         </is>
       </c>
       <c r="C62" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -4467,12 +4467,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>sec_grade_2_talha_ibn_ubaydullah_1st_shift</t>
+          <t>sec_grade_3_as_ad_ibn_zurarah_2nd_shift_mix</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>GRADE 2 - TALHA IBN UBAYDULLAH (1ST SHIFT)</t>
+          <t>GRADE 3 - AS'AD IBN ZURARAH (2ND SHIFT) MIX</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
@@ -4482,32 +4482,32 @@
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>Grade 2</t>
+          <t>Grade 3</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>ODL - 1ST SHIFT</t>
+          <t>ODL - 2ND SHIFT</t>
         </is>
       </c>
       <c r="J62" t="inlineStr">
         <is>
-          <t>subj_makabansa</t>
+          <t>subj_gmrc</t>
         </is>
       </c>
       <c r="K62" t="inlineStr">
         <is>
-          <t>Makabansa</t>
+          <t>GMRC</t>
         </is>
       </c>
       <c r="L62" t="inlineStr">
         <is>
-          <t>tchr_zuhora</t>
+          <t>tchr_saliha</t>
         </is>
       </c>
       <c r="M62" t="inlineStr">
         <is>
-          <t>Teacher Zuhora</t>
+          <t>Ustadha Saliha</t>
         </is>
       </c>
       <c r="N62" t="n">
@@ -15216,21 +15216,21 @@
         </is>
       </c>
       <c r="C225" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D225" t="inlineStr">
         <is>
-          <t>03:10 PM – 04:10 PM</t>
+          <t>02:40 PM – 03:40 PM</t>
         </is>
       </c>
       <c r="E225" t="inlineStr">
         <is>
-          <t>sec_grade_1_hudhayfah_ibn_al_yam_1st_shift</t>
+          <t>sec_kinder_2_uthman_ibn_affan_1st_shift</t>
         </is>
       </c>
       <c r="F225" t="inlineStr">
         <is>
-          <t>GRADE 1 - HUDHAYFAH IBN AL-YAM (1ST SHIFT)</t>
+          <t>Kinder 2 UTHMAN IBN AFFAN (1ST SHIFT)</t>
         </is>
       </c>
       <c r="G225" t="inlineStr">
@@ -15240,7 +15240,7 @@
       </c>
       <c r="H225" t="inlineStr">
         <is>
-          <t>Grade 1</t>
+          <t>Kinder 2</t>
         </is>
       </c>
       <c r="I225" t="inlineStr">
@@ -15250,22 +15250,22 @@
       </c>
       <c r="J225" t="inlineStr">
         <is>
-          <t>subj_math</t>
+          <t>subj_hadith</t>
         </is>
       </c>
       <c r="K225" t="inlineStr">
         <is>
-          <t>Math</t>
+          <t>Hadith</t>
         </is>
       </c>
       <c r="L225" t="inlineStr">
         <is>
-          <t>tchr_joanna</t>
+          <t>tchr_saliha</t>
         </is>
       </c>
       <c r="M225" t="inlineStr">
         <is>
-          <t>Teacher Joanna</t>
+          <t>Ustadha Saliha</t>
         </is>
       </c>
       <c r="N225" t="n">
@@ -15282,7 +15282,7 @@
         </is>
       </c>
       <c r="C226" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D226" t="inlineStr">
         <is>
@@ -15291,12 +15291,12 @@
       </c>
       <c r="E226" t="inlineStr">
         <is>
-          <t>sec_grade_1_sa_ad_ibn_abi_waqqaas_2nd_shift</t>
+          <t>sec_grade_1_hudhayfah_ibn_al_yam_1st_shift</t>
         </is>
       </c>
       <c r="F226" t="inlineStr">
         <is>
-          <t>GRADE 1 - SA'AD IBN ABI WAQQAAS (2ND SHIFT)</t>
+          <t>GRADE 1 - HUDHAYFAH IBN AL-YAM (1ST SHIFT)</t>
         </is>
       </c>
       <c r="G226" t="inlineStr">
@@ -15311,27 +15311,27 @@
       </c>
       <c r="I226" t="inlineStr">
         <is>
-          <t>ODL - 2ND SHIFT</t>
+          <t>ODL - 1ST SHIFT</t>
         </is>
       </c>
       <c r="J226" t="inlineStr">
         <is>
-          <t>subj_arabic</t>
+          <t>subj_math</t>
         </is>
       </c>
       <c r="K226" t="inlineStr">
         <is>
-          <t>Arabic</t>
+          <t>Math</t>
         </is>
       </c>
       <c r="L226" t="inlineStr">
         <is>
-          <t>tchr_hainur</t>
+          <t>tchr_joanna</t>
         </is>
       </c>
       <c r="M226" t="inlineStr">
         <is>
-          <t>Ustadha Hainur</t>
+          <t>Teacher Joanna</t>
         </is>
       </c>
       <c r="N226" t="n">
@@ -15357,12 +15357,12 @@
       </c>
       <c r="E227" t="inlineStr">
         <is>
-          <t>sec_grade_1_suhayb_ar_rumi_2nd_shift</t>
+          <t>sec_grade_1_sa_ad_ibn_abi_waqqaas_2nd_shift</t>
         </is>
       </c>
       <c r="F227" t="inlineStr">
         <is>
-          <t>GRADE 1 - SUHAYB AR-RUMI (2ND SHIFT)</t>
+          <t>GRADE 1 - SA'AD IBN ABI WAQQAAS (2ND SHIFT)</t>
         </is>
       </c>
       <c r="G227" t="inlineStr">
@@ -15382,22 +15382,22 @@
       </c>
       <c r="J227" t="inlineStr">
         <is>
-          <t>subj_language</t>
+          <t>subj_arabic</t>
         </is>
       </c>
       <c r="K227" t="inlineStr">
         <is>
-          <t>Language</t>
+          <t>Arabic</t>
         </is>
       </c>
       <c r="L227" t="inlineStr">
         <is>
-          <t>tchr_sahdia</t>
+          <t>tchr_hainur</t>
         </is>
       </c>
       <c r="M227" t="inlineStr">
         <is>
-          <t>Teacher Sahdia</t>
+          <t>Ustadha Hainur</t>
         </is>
       </c>
       <c r="N227" t="n">
@@ -15423,22 +15423,22 @@
       </c>
       <c r="E228" t="inlineStr">
         <is>
-          <t>sec_grade_10_abu_ayyub_al_ansari_2nd_shift_boys</t>
+          <t>sec_grade_1_suhayb_ar_rumi_2nd_shift</t>
         </is>
       </c>
       <c r="F228" t="inlineStr">
         <is>
-          <t>GRADE 10 - ABU AYYUB AL-ANSARI (2ND SHIFT) BOYS</t>
+          <t>GRADE 1 - SUHAYB AR-RUMI (2ND SHIFT)</t>
         </is>
       </c>
       <c r="G228" t="inlineStr">
         <is>
-          <t>Junior High School</t>
+          <t>Elementary</t>
         </is>
       </c>
       <c r="H228" t="inlineStr">
         <is>
-          <t>Grade 10</t>
+          <t>Grade 1</t>
         </is>
       </c>
       <c r="I228" t="inlineStr">
@@ -15448,22 +15448,22 @@
       </c>
       <c r="J228" t="inlineStr">
         <is>
-          <t>subj_qur_an</t>
+          <t>subj_language</t>
         </is>
       </c>
       <c r="K228" t="inlineStr">
         <is>
-          <t>Qur'an</t>
+          <t>Language</t>
         </is>
       </c>
       <c r="L228" t="inlineStr">
         <is>
-          <t>tchr_abdulwahab</t>
+          <t>tchr_sahdia</t>
         </is>
       </c>
       <c r="M228" t="inlineStr">
         <is>
-          <t>Alim Abdulwahab</t>
+          <t>Teacher Sahdia</t>
         </is>
       </c>
       <c r="N228" t="n">
@@ -15480,7 +15480,7 @@
         </is>
       </c>
       <c r="C229" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D229" t="inlineStr">
         <is>
@@ -15489,12 +15489,12 @@
       </c>
       <c r="E229" t="inlineStr">
         <is>
-          <t>sec_grade_10_utbah_ibn_ghazwan_1st_shift_girls</t>
+          <t>sec_grade_10_abu_ayyub_al_ansari_2nd_shift_boys</t>
         </is>
       </c>
       <c r="F229" t="inlineStr">
         <is>
-          <t>GRADE 10 - UTBAH IBN GHAZWAN (1ST SHIFT) GIRLS</t>
+          <t>GRADE 10 - ABU AYYUB AL-ANSARI (2ND SHIFT) BOYS</t>
         </is>
       </c>
       <c r="G229" t="inlineStr">
@@ -15509,27 +15509,27 @@
       </c>
       <c r="I229" t="inlineStr">
         <is>
-          <t>ODL - 1ST SHIFT</t>
+          <t>ODL - 2ND SHIFT</t>
         </is>
       </c>
       <c r="J229" t="inlineStr">
         <is>
-          <t>subj_english</t>
+          <t>subj_qur_an</t>
         </is>
       </c>
       <c r="K229" t="inlineStr">
         <is>
-          <t>English</t>
+          <t>Qur'an</t>
         </is>
       </c>
       <c r="L229" t="inlineStr">
         <is>
-          <t>tchr_norhaima</t>
+          <t>tchr_abdulwahab</t>
         </is>
       </c>
       <c r="M229" t="inlineStr">
         <is>
-          <t>Teacher Norhaima</t>
+          <t>Alim Abdulwahab</t>
         </is>
       </c>
       <c r="N229" t="n">
@@ -15546,7 +15546,7 @@
         </is>
       </c>
       <c r="C230" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D230" t="inlineStr">
         <is>
@@ -15555,47 +15555,47 @@
       </c>
       <c r="E230" t="inlineStr">
         <is>
-          <t>sec_grade_11_2nd_shift_boys</t>
+          <t>sec_grade_10_utbah_ibn_ghazwan_1st_shift_girls</t>
         </is>
       </c>
       <c r="F230" t="inlineStr">
         <is>
-          <t>GRADE 11 (2ND SHIFT BOYS)</t>
+          <t>GRADE 10 - UTBAH IBN GHAZWAN (1ST SHIFT) GIRLS</t>
         </is>
       </c>
       <c r="G230" t="inlineStr">
         <is>
-          <t>Senior High School</t>
+          <t>Junior High School</t>
         </is>
       </c>
       <c r="H230" t="inlineStr">
         <is>
-          <t>Grade 11</t>
+          <t>Grade 10</t>
         </is>
       </c>
       <c r="I230" t="inlineStr">
         <is>
-          <t>ODL - 2ND SHIFT</t>
+          <t>ODL - 1ST SHIFT</t>
         </is>
       </c>
       <c r="J230" t="inlineStr">
         <is>
-          <t>subj_mabisang_komunikasyon</t>
+          <t>subj_english</t>
         </is>
       </c>
       <c r="K230" t="inlineStr">
         <is>
-          <t>Mabisang Komunikasyon</t>
+          <t>English</t>
         </is>
       </c>
       <c r="L230" t="inlineStr">
         <is>
-          <t>tchr_nadzra</t>
+          <t>tchr_norhaima</t>
         </is>
       </c>
       <c r="M230" t="inlineStr">
         <is>
-          <t>Teacher Nadzra</t>
+          <t>Teacher Norhaima</t>
         </is>
       </c>
       <c r="N230" t="n">
@@ -15621,22 +15621,22 @@
       </c>
       <c r="E231" t="inlineStr">
         <is>
-          <t>sec_grade_2_saeed_ibn_zayd_2nd_shift</t>
+          <t>sec_grade_11_2nd_shift_boys</t>
         </is>
       </c>
       <c r="F231" t="inlineStr">
         <is>
-          <t>GRADE 2 - SAEED IBN ZAYD (2ND SHIFT)</t>
+          <t>GRADE 11 (2ND SHIFT BOYS)</t>
         </is>
       </c>
       <c r="G231" t="inlineStr">
         <is>
-          <t>Elementary</t>
+          <t>Senior High School</t>
         </is>
       </c>
       <c r="H231" t="inlineStr">
         <is>
-          <t>Grade 2</t>
+          <t>Grade 11</t>
         </is>
       </c>
       <c r="I231" t="inlineStr">
@@ -15646,22 +15646,22 @@
       </c>
       <c r="J231" t="inlineStr">
         <is>
-          <t>subj_filipino</t>
+          <t>subj_mabisang_komunikasyon</t>
         </is>
       </c>
       <c r="K231" t="inlineStr">
         <is>
-          <t>Filipino</t>
+          <t>Mabisang Komunikasyon</t>
         </is>
       </c>
       <c r="L231" t="inlineStr">
         <is>
-          <t>tchr_zuhora</t>
+          <t>tchr_nadzra</t>
         </is>
       </c>
       <c r="M231" t="inlineStr">
         <is>
-          <t>Teacher Zuhora</t>
+          <t>Teacher Nadzra</t>
         </is>
       </c>
       <c r="N231" t="n">
@@ -15687,12 +15687,12 @@
       </c>
       <c r="E232" t="inlineStr">
         <is>
-          <t>sec_grade_3_as_ad_ibn_zurarah_2nd_shift_mix</t>
+          <t>sec_grade_2_saeed_ibn_zayd_2nd_shift</t>
         </is>
       </c>
       <c r="F232" t="inlineStr">
         <is>
-          <t>GRADE 3 - AS'AD IBN ZURARAH (2ND SHIFT) MIX</t>
+          <t>GRADE 2 - SAEED IBN ZAYD (2ND SHIFT)</t>
         </is>
       </c>
       <c r="G232" t="inlineStr">
@@ -15702,7 +15702,7 @@
       </c>
       <c r="H232" t="inlineStr">
         <is>
-          <t>Grade 3</t>
+          <t>Grade 2</t>
         </is>
       </c>
       <c r="I232" t="inlineStr">
@@ -15712,22 +15712,22 @@
       </c>
       <c r="J232" t="inlineStr">
         <is>
-          <t>subj_gmrc</t>
+          <t>subj_filipino</t>
         </is>
       </c>
       <c r="K232" t="inlineStr">
         <is>
-          <t>GMRC</t>
+          <t>Filipino</t>
         </is>
       </c>
       <c r="L232" t="inlineStr">
         <is>
-          <t>tchr_saliha</t>
+          <t>tchr_zuhora</t>
         </is>
       </c>
       <c r="M232" t="inlineStr">
         <is>
-          <t>Ustadha Saliha</t>
+          <t>Teacher Zuhora</t>
         </is>
       </c>
       <c r="N232" t="n">

--- a/Term_Examination_Schedule_S.Y._2026-2027_Optimized.xlsx
+++ b/Term_Examination_Schedule_S.Y._2026-2027_Optimized.xlsx
@@ -12123,12 +12123,12 @@
       </c>
       <c r="E178" t="inlineStr">
         <is>
-          <t>sec_grade_3_face_to_face</t>
+          <t>sec_grade_4_face_to_face</t>
         </is>
       </c>
       <c r="F178" t="inlineStr">
         <is>
-          <t>GRADE 3 (FACE TO FACE)</t>
+          <t>GRADE 4 (FACE TO FACE)</t>
         </is>
       </c>
       <c r="G178" t="inlineStr">
@@ -12138,7 +12138,7 @@
       </c>
       <c r="H178" t="inlineStr">
         <is>
-          <t>Grade 3</t>
+          <t>Grade 4</t>
         </is>
       </c>
       <c r="I178" t="inlineStr">
@@ -12148,22 +12148,22 @@
       </c>
       <c r="J178" t="inlineStr">
         <is>
-          <t>subj_gmrc</t>
+          <t>subj_filipino</t>
         </is>
       </c>
       <c r="K178" t="inlineStr">
         <is>
-          <t>GMRC</t>
+          <t>Filipino</t>
         </is>
       </c>
       <c r="L178" t="inlineStr">
         <is>
-          <t>tchr_saliha</t>
+          <t>tchr_norhydie</t>
         </is>
       </c>
       <c r="M178" t="inlineStr">
         <is>
-          <t>Ustadha Saliha</t>
+          <t>Teacher Norhydie</t>
         </is>
       </c>
       <c r="N178" t="n">
@@ -12189,12 +12189,12 @@
       </c>
       <c r="E179" t="inlineStr">
         <is>
-          <t>sec_grade_4_face_to_face</t>
+          <t>sec_grade_5_face_to_face</t>
         </is>
       </c>
       <c r="F179" t="inlineStr">
         <is>
-          <t>GRADE 4 (FACE TO FACE)</t>
+          <t>GRADE 5 (FACE TO FACE)</t>
         </is>
       </c>
       <c r="G179" t="inlineStr">
@@ -12204,7 +12204,7 @@
       </c>
       <c r="H179" t="inlineStr">
         <is>
-          <t>Grade 4</t>
+          <t>Grade 5</t>
         </is>
       </c>
       <c r="I179" t="inlineStr">
@@ -12214,22 +12214,22 @@
       </c>
       <c r="J179" t="inlineStr">
         <is>
-          <t>subj_filipino</t>
+          <t>subj_qur_an</t>
         </is>
       </c>
       <c r="K179" t="inlineStr">
         <is>
-          <t>Filipino</t>
+          <t>Qur'an</t>
         </is>
       </c>
       <c r="L179" t="inlineStr">
         <is>
-          <t>tchr_norhydie</t>
+          <t>tchr_obaydah</t>
         </is>
       </c>
       <c r="M179" t="inlineStr">
         <is>
-          <t>Teacher Norhydie</t>
+          <t>Ustadh Obaydah</t>
         </is>
       </c>
       <c r="N179" t="n">
@@ -12255,22 +12255,22 @@
       </c>
       <c r="E180" t="inlineStr">
         <is>
-          <t>sec_grade_5_face_to_face</t>
+          <t>sec_grade_7_8_boys_face_to_face</t>
         </is>
       </c>
       <c r="F180" t="inlineStr">
         <is>
-          <t>GRADE 5 (FACE TO FACE)</t>
+          <t>GRADE 7 &amp; 8 BOYS (FACE TO FACE)</t>
         </is>
       </c>
       <c r="G180" t="inlineStr">
         <is>
-          <t>Elementary</t>
+          <t>Junior High School</t>
         </is>
       </c>
       <c r="H180" t="inlineStr">
         <is>
-          <t>Grade 5</t>
+          <t>Grade 7 &amp; 8</t>
         </is>
       </c>
       <c r="I180" t="inlineStr">
@@ -12280,22 +12280,22 @@
       </c>
       <c r="J180" t="inlineStr">
         <is>
-          <t>subj_qur_an</t>
+          <t>subj_english</t>
         </is>
       </c>
       <c r="K180" t="inlineStr">
         <is>
-          <t>Qur'an</t>
+          <t>English</t>
         </is>
       </c>
       <c r="L180" t="inlineStr">
         <is>
-          <t>tchr_obaydah</t>
+          <t>tchr_jairah</t>
         </is>
       </c>
       <c r="M180" t="inlineStr">
         <is>
-          <t>Ustadh Obaydah</t>
+          <t>Teacher Jairah</t>
         </is>
       </c>
       <c r="N180" t="n">
@@ -12321,12 +12321,12 @@
       </c>
       <c r="E181" t="inlineStr">
         <is>
-          <t>sec_grade_7_8_boys_face_to_face</t>
+          <t>sec_grade_7_8_girls_face_to_face</t>
         </is>
       </c>
       <c r="F181" t="inlineStr">
         <is>
-          <t>GRADE 7 &amp; 8 BOYS (FACE TO FACE)</t>
+          <t>GRADE 7 &amp; 8 GIRLS (FACE TO FACE)</t>
         </is>
       </c>
       <c r="G181" t="inlineStr">
@@ -12346,22 +12346,22 @@
       </c>
       <c r="J181" t="inlineStr">
         <is>
-          <t>subj_english</t>
+          <t>subj_shaf</t>
         </is>
       </c>
       <c r="K181" t="inlineStr">
         <is>
-          <t>English</t>
+          <t>SHAF</t>
         </is>
       </c>
       <c r="L181" t="inlineStr">
         <is>
-          <t>tchr_jairah</t>
+          <t>tchr_samsuddin</t>
         </is>
       </c>
       <c r="M181" t="inlineStr">
         <is>
-          <t>Teacher Jairah</t>
+          <t>Alim Samsuddin</t>
         </is>
       </c>
       <c r="N181" t="n">
@@ -12387,12 +12387,12 @@
       </c>
       <c r="E182" t="inlineStr">
         <is>
-          <t>sec_grade_7_8_girls_face_to_face</t>
+          <t>sec_grade_9_10_boys_face_to_face</t>
         </is>
       </c>
       <c r="F182" t="inlineStr">
         <is>
-          <t>GRADE 7 &amp; 8 GIRLS (FACE TO FACE)</t>
+          <t>GRADE 9 &amp; 10 BOYS (FACE TO FACE)</t>
         </is>
       </c>
       <c r="G182" t="inlineStr">
@@ -12402,7 +12402,7 @@
       </c>
       <c r="H182" t="inlineStr">
         <is>
-          <t>Grade 7 &amp; 8</t>
+          <t>Grade 9 &amp; 10</t>
         </is>
       </c>
       <c r="I182" t="inlineStr">
@@ -12412,22 +12412,22 @@
       </c>
       <c r="J182" t="inlineStr">
         <is>
-          <t>subj_shaf</t>
+          <t>subj_social_studies</t>
         </is>
       </c>
       <c r="K182" t="inlineStr">
         <is>
-          <t>SHAF</t>
+          <t>Social Science</t>
         </is>
       </c>
       <c r="L182" t="inlineStr">
         <is>
-          <t>tchr_samsuddin</t>
+          <t>tchr_sophia</t>
         </is>
       </c>
       <c r="M182" t="inlineStr">
         <is>
-          <t>Alim Samsuddin</t>
+          <t>Teacher Sophia</t>
         </is>
       </c>
       <c r="N182" t="n">
@@ -12453,12 +12453,12 @@
       </c>
       <c r="E183" t="inlineStr">
         <is>
-          <t>sec_grade_9_10_boys_face_to_face</t>
+          <t>sec_grade_9_10_girls_face_to_face</t>
         </is>
       </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t>GRADE 9 &amp; 10 BOYS (FACE TO FACE)</t>
+          <t>GRADE 9 &amp; 10 GIRLS (FACE TO FACE)</t>
         </is>
       </c>
       <c r="G183" t="inlineStr">
@@ -12478,22 +12478,22 @@
       </c>
       <c r="J183" t="inlineStr">
         <is>
-          <t>subj_social_studies</t>
+          <t>subj_values_ed</t>
         </is>
       </c>
       <c r="K183" t="inlineStr">
         <is>
-          <t>Social Science</t>
+          <t>Values Ed</t>
         </is>
       </c>
       <c r="L183" t="inlineStr">
         <is>
-          <t>tchr_sophia</t>
+          <t>tchr_nof</t>
         </is>
       </c>
       <c r="M183" t="inlineStr">
         <is>
-          <t>Teacher Sophia</t>
+          <t>Teacher Nof</t>
         </is>
       </c>
       <c r="N183" t="n">
@@ -12510,56 +12510,56 @@
         </is>
       </c>
       <c r="C184" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
-          <t>10:25 AM – 11:25 AM</t>
+          <t>11:30 AM – 12:30 PM</t>
         </is>
       </c>
       <c r="E184" t="inlineStr">
         <is>
-          <t>sec_grade_9_10_girls_face_to_face</t>
+          <t>sec_grade_2_amr_ibn_al_jamuh_1st_shift</t>
         </is>
       </c>
       <c r="F184" t="inlineStr">
         <is>
-          <t>GRADE 9 &amp; 10 GIRLS (FACE TO FACE)</t>
+          <t>GRADE 2 - AMR IBN AL-JAMUH (1ST SHIFT)</t>
         </is>
       </c>
       <c r="G184" t="inlineStr">
         <is>
-          <t>Junior High School</t>
+          <t>Elementary</t>
         </is>
       </c>
       <c r="H184" t="inlineStr">
         <is>
-          <t>Grade 9 &amp; 10</t>
+          <t>Grade 2</t>
         </is>
       </c>
       <c r="I184" t="inlineStr">
         <is>
-          <t>F2F</t>
+          <t>ODL - 1ST SHIFT</t>
         </is>
       </c>
       <c r="J184" t="inlineStr">
         <is>
-          <t>subj_values_ed</t>
+          <t>subj_arabic</t>
         </is>
       </c>
       <c r="K184" t="inlineStr">
         <is>
-          <t>Values Ed</t>
+          <t>Arabic</t>
         </is>
       </c>
       <c r="L184" t="inlineStr">
         <is>
-          <t>tchr_nof</t>
+          <t>tchr_hainur</t>
         </is>
       </c>
       <c r="M184" t="inlineStr">
         <is>
-          <t>Teacher Nof</t>
+          <t>Ustadha Hainur</t>
         </is>
       </c>
       <c r="N184" t="n">
@@ -12585,12 +12585,12 @@
       </c>
       <c r="E185" t="inlineStr">
         <is>
-          <t>sec_grade_2_amr_ibn_al_jamuh_1st_shift</t>
+          <t>sec_grade_3_habib_ibn_zayd_al_ansari_1st_shift_girls</t>
         </is>
       </c>
       <c r="F185" t="inlineStr">
         <is>
-          <t>GRADE 2 - AMR IBN AL-JAMUH (1ST SHIFT)</t>
+          <t>Grade 3 - HABIB IBN ZAYD AL-ANSARI (1ST SHIFT) - GIRLS</t>
         </is>
       </c>
       <c r="G185" t="inlineStr">
@@ -12600,7 +12600,7 @@
       </c>
       <c r="H185" t="inlineStr">
         <is>
-          <t>Grade 2</t>
+          <t>Grade 3</t>
         </is>
       </c>
       <c r="I185" t="inlineStr">
@@ -12610,22 +12610,22 @@
       </c>
       <c r="J185" t="inlineStr">
         <is>
-          <t>subj_arabic</t>
+          <t>subj_gmrc</t>
         </is>
       </c>
       <c r="K185" t="inlineStr">
         <is>
-          <t>Arabic</t>
+          <t>GMRC</t>
         </is>
       </c>
       <c r="L185" t="inlineStr">
         <is>
-          <t>tchr_hainur</t>
+          <t>tchr_silfah</t>
         </is>
       </c>
       <c r="M185" t="inlineStr">
         <is>
-          <t>Ustadha Hainur</t>
+          <t>Ustadh Silfah</t>
         </is>
       </c>
       <c r="N185" t="n">
@@ -12651,12 +12651,12 @@
       </c>
       <c r="E186" t="inlineStr">
         <is>
-          <t>sec_grade_3_habib_ibn_zayd_al_ansari_1st_shift_girls</t>
+          <t>sec_grade_4_abdur_rahman_ibn_awf_1st_shift</t>
         </is>
       </c>
       <c r="F186" t="inlineStr">
         <is>
-          <t>Grade 3 - HABIB IBN ZAYD AL-ANSARI (1ST SHIFT) - GIRLS</t>
+          <t>GRADE 4 - ABDUR RAHMAN IBN AWF (1ST SHIFT)</t>
         </is>
       </c>
       <c r="G186" t="inlineStr">
@@ -12666,7 +12666,7 @@
       </c>
       <c r="H186" t="inlineStr">
         <is>
-          <t>Grade 3</t>
+          <t>Grade 4</t>
         </is>
       </c>
       <c r="I186" t="inlineStr">
@@ -12676,22 +12676,22 @@
       </c>
       <c r="J186" t="inlineStr">
         <is>
-          <t>subj_gmrc</t>
+          <t>subj_math</t>
         </is>
       </c>
       <c r="K186" t="inlineStr">
         <is>
-          <t>GMRC</t>
+          <t>Math</t>
         </is>
       </c>
       <c r="L186" t="inlineStr">
         <is>
-          <t>tchr_silfah</t>
+          <t>tchr_arvin</t>
         </is>
       </c>
       <c r="M186" t="inlineStr">
         <is>
-          <t>Ustadh Silfah</t>
+          <t>Teacher Arvin</t>
         </is>
       </c>
       <c r="N186" t="n">
@@ -12717,22 +12717,22 @@
       </c>
       <c r="E187" t="inlineStr">
         <is>
-          <t>sec_grade_4_abdur_rahman_ibn_awf_1st_shift</t>
+          <t>sec_grade_7_usama_ibn_zayd_1st_shift_girls</t>
         </is>
       </c>
       <c r="F187" t="inlineStr">
         <is>
-          <t>GRADE 4 - ABDUR RAHMAN IBN AWF (1ST SHIFT)</t>
+          <t>GRADE 7 - USAMA IBN ZAYD (1ST SHIFT) GIRLS</t>
         </is>
       </c>
       <c r="G187" t="inlineStr">
         <is>
-          <t>Elementary</t>
+          <t>Junior High School</t>
         </is>
       </c>
       <c r="H187" t="inlineStr">
         <is>
-          <t>Grade 4</t>
+          <t>Grade 7</t>
         </is>
       </c>
       <c r="I187" t="inlineStr">
@@ -12742,22 +12742,22 @@
       </c>
       <c r="J187" t="inlineStr">
         <is>
-          <t>subj_math</t>
+          <t>subj_social_studies</t>
         </is>
       </c>
       <c r="K187" t="inlineStr">
         <is>
-          <t>Math</t>
+          <t>Social Studies</t>
         </is>
       </c>
       <c r="L187" t="inlineStr">
         <is>
-          <t>tchr_arvin</t>
+          <t>tchr_shirehan</t>
         </is>
       </c>
       <c r="M187" t="inlineStr">
         <is>
-          <t>Teacher Arvin</t>
+          <t>Teacher Shirehan</t>
         </is>
       </c>
       <c r="N187" t="n">
@@ -12774,31 +12774,31 @@
         </is>
       </c>
       <c r="C188" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D188" t="inlineStr">
         <is>
-          <t>11:30 AM – 12:30 PM</t>
+          <t>12:40 PM – 01:40 PM</t>
         </is>
       </c>
       <c r="E188" t="inlineStr">
         <is>
-          <t>sec_grade_7_usama_ibn_zayd_1st_shift_girls</t>
+          <t>sec_grade_1_ali_ibn_abi_talib_1st_shift</t>
         </is>
       </c>
       <c r="F188" t="inlineStr">
         <is>
-          <t>GRADE 7 - USAMA IBN ZAYD (1ST SHIFT) GIRLS</t>
+          <t>GRADE 1 - ALI IBN ABI TALIB(1ST SHIFT)</t>
         </is>
       </c>
       <c r="G188" t="inlineStr">
         <is>
-          <t>Junior High School</t>
+          <t>Elementary</t>
         </is>
       </c>
       <c r="H188" t="inlineStr">
         <is>
-          <t>Grade 7</t>
+          <t>Grade 1</t>
         </is>
       </c>
       <c r="I188" t="inlineStr">
@@ -12808,22 +12808,22 @@
       </c>
       <c r="J188" t="inlineStr">
         <is>
-          <t>subj_social_studies</t>
+          <t>subj_qur_an</t>
         </is>
       </c>
       <c r="K188" t="inlineStr">
         <is>
-          <t>Social Studies</t>
+          <t>Qur'an</t>
         </is>
       </c>
       <c r="L188" t="inlineStr">
         <is>
-          <t>tchr_shirehan</t>
+          <t>tchr_hainur</t>
         </is>
       </c>
       <c r="M188" t="inlineStr">
         <is>
-          <t>Teacher Shirehan</t>
+          <t>Ustadha Hainur</t>
         </is>
       </c>
       <c r="N188" t="n">
@@ -12849,12 +12849,12 @@
       </c>
       <c r="E189" t="inlineStr">
         <is>
-          <t>sec_grade_1_ali_ibn_abi_talib_1st_shift</t>
+          <t>sec_grade_1_hudhayfah_ibn_al_yam_1st_shift</t>
         </is>
       </c>
       <c r="F189" t="inlineStr">
         <is>
-          <t>GRADE 1 - ALI IBN ABI TALIB(1ST SHIFT)</t>
+          <t>GRADE 1 - HUDHAYFAH IBN AL-YAM (1ST SHIFT)</t>
         </is>
       </c>
       <c r="G189" t="inlineStr">
@@ -12874,22 +12874,22 @@
       </c>
       <c r="J189" t="inlineStr">
         <is>
-          <t>subj_qur_an</t>
+          <t>subj_reading_literacy</t>
         </is>
       </c>
       <c r="K189" t="inlineStr">
         <is>
-          <t>Qur'an</t>
+          <t>Reading &amp; Literacy</t>
         </is>
       </c>
       <c r="L189" t="inlineStr">
         <is>
-          <t>tchr_hainur</t>
+          <t>tchr_katrina</t>
         </is>
       </c>
       <c r="M189" t="inlineStr">
         <is>
-          <t>Ustadha Hainur</t>
+          <t>Teacher Katrina</t>
         </is>
       </c>
       <c r="N189" t="n">
@@ -12915,22 +12915,22 @@
       </c>
       <c r="E190" t="inlineStr">
         <is>
-          <t>sec_grade_1_hudhayfah_ibn_al_yam_1st_shift</t>
+          <t>sec_grade_10_utbah_ibn_ghazwan_1st_shift_girls</t>
         </is>
       </c>
       <c r="F190" t="inlineStr">
         <is>
-          <t>GRADE 1 - HUDHAYFAH IBN AL-YAM (1ST SHIFT)</t>
+          <t>GRADE 10 - UTBAH IBN GHAZWAN (1ST SHIFT) GIRLS</t>
         </is>
       </c>
       <c r="G190" t="inlineStr">
         <is>
-          <t>Elementary</t>
+          <t>Junior High School</t>
         </is>
       </c>
       <c r="H190" t="inlineStr">
         <is>
-          <t>Grade 1</t>
+          <t>Grade 10</t>
         </is>
       </c>
       <c r="I190" t="inlineStr">
@@ -12940,22 +12940,22 @@
       </c>
       <c r="J190" t="inlineStr">
         <is>
-          <t>subj_reading_literacy</t>
+          <t>subj_science</t>
         </is>
       </c>
       <c r="K190" t="inlineStr">
         <is>
-          <t>Reading &amp; Literacy</t>
+          <t>Science</t>
         </is>
       </c>
       <c r="L190" t="inlineStr">
         <is>
-          <t>tchr_katrina</t>
+          <t>tchr_rowena</t>
         </is>
       </c>
       <c r="M190" t="inlineStr">
         <is>
-          <t>Teacher Katrina</t>
+          <t>Teacher Rowena</t>
         </is>
       </c>
       <c r="N190" t="n">
@@ -12972,7 +12972,7 @@
         </is>
       </c>
       <c r="C191" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D191" t="inlineStr">
         <is>
@@ -12981,22 +12981,22 @@
       </c>
       <c r="E191" t="inlineStr">
         <is>
-          <t>sec_grade_10_utbah_ibn_ghazwan_1st_shift_girls</t>
+          <t>sec_grade_11_1st_shift_girls</t>
         </is>
       </c>
       <c r="F191" t="inlineStr">
         <is>
-          <t>GRADE 10 - UTBAH IBN GHAZWAN (1ST SHIFT) GIRLS</t>
+          <t>GRADE 11 (1ST SHIFT GIRLS)</t>
         </is>
       </c>
       <c r="G191" t="inlineStr">
         <is>
-          <t>Junior High School</t>
+          <t>Senior High School</t>
         </is>
       </c>
       <c r="H191" t="inlineStr">
         <is>
-          <t>Grade 10</t>
+          <t>Grade 11</t>
         </is>
       </c>
       <c r="I191" t="inlineStr">
@@ -13006,22 +13006,22 @@
       </c>
       <c r="J191" t="inlineStr">
         <is>
-          <t>subj_science</t>
+          <t>subj_pskp</t>
         </is>
       </c>
       <c r="K191" t="inlineStr">
         <is>
-          <t>Science</t>
+          <t>PSKP</t>
         </is>
       </c>
       <c r="L191" t="inlineStr">
         <is>
-          <t>tchr_rowena</t>
+          <t>tchr_shirehan</t>
         </is>
       </c>
       <c r="M191" t="inlineStr">
         <is>
-          <t>Teacher Rowena</t>
+          <t>Teacher Shirehan</t>
         </is>
       </c>
       <c r="N191" t="n">
@@ -13042,17 +13042,17 @@
       </c>
       <c r="D192" t="inlineStr">
         <is>
-          <t>12:40 PM – 01:40 PM</t>
+          <t>12:40 PM – 02:50 PM</t>
         </is>
       </c>
       <c r="E192" t="inlineStr">
         <is>
-          <t>sec_grade_11_1st_shift_girls</t>
+          <t>sec_grade_12_abu_musa_al_ashari</t>
         </is>
       </c>
       <c r="F192" t="inlineStr">
         <is>
-          <t>GRADE 11 (1ST SHIFT GIRLS)</t>
+          <t>GRADE 12 - ABU MUSA AL-ASHARI</t>
         </is>
       </c>
       <c r="G192" t="inlineStr">
@@ -13062,7 +13062,7 @@
       </c>
       <c r="H192" t="inlineStr">
         <is>
-          <t>Grade 11</t>
+          <t>Grade 12</t>
         </is>
       </c>
       <c r="I192" t="inlineStr">
@@ -13072,26 +13072,26 @@
       </c>
       <c r="J192" t="inlineStr">
         <is>
-          <t>subj_pskp</t>
+          <t>subj_gen_physics_1</t>
         </is>
       </c>
       <c r="K192" t="inlineStr">
         <is>
-          <t>PSKP</t>
+          <t>General Physics 1</t>
         </is>
       </c>
       <c r="L192" t="inlineStr">
         <is>
-          <t>tchr_shirehan</t>
+          <t>tchr_aniah</t>
         </is>
       </c>
       <c r="M192" t="inlineStr">
         <is>
-          <t>Teacher Shirehan</t>
+          <t>Teacher Aniah</t>
         </is>
       </c>
       <c r="N192" t="n">
-        <v>60</v>
+        <v>120</v>
       </c>
     </row>
     <row r="193">
@@ -13104,31 +13104,31 @@
         </is>
       </c>
       <c r="C193" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D193" t="inlineStr">
         <is>
-          <t>12:40 PM – 02:50 PM</t>
+          <t>12:40 PM – 01:40 PM</t>
         </is>
       </c>
       <c r="E193" t="inlineStr">
         <is>
-          <t>sec_grade_12_abu_musa_al_ashari</t>
+          <t>sec_grade_2_talha_ibn_ubaydullah_1st_shift</t>
         </is>
       </c>
       <c r="F193" t="inlineStr">
         <is>
-          <t>GRADE 12 - ABU MUSA AL-ASHARI</t>
+          <t>GRADE 2 - TALHA IBN UBAYDULLAH (1ST SHIFT)</t>
         </is>
       </c>
       <c r="G193" t="inlineStr">
         <is>
-          <t>Senior High School</t>
+          <t>Elementary</t>
         </is>
       </c>
       <c r="H193" t="inlineStr">
         <is>
-          <t>Grade 12</t>
+          <t>Grade 2</t>
         </is>
       </c>
       <c r="I193" t="inlineStr">
@@ -13138,26 +13138,26 @@
       </c>
       <c r="J193" t="inlineStr">
         <is>
-          <t>subj_gen_physics_1</t>
+          <t>subj_shaf</t>
         </is>
       </c>
       <c r="K193" t="inlineStr">
         <is>
-          <t>General Physics 1</t>
+          <t>SHAF</t>
         </is>
       </c>
       <c r="L193" t="inlineStr">
         <is>
-          <t>tchr_aniah</t>
+          <t>tchr_abdul_karim</t>
         </is>
       </c>
       <c r="M193" t="inlineStr">
         <is>
-          <t>Teacher Aniah</t>
+          <t>Alim Abdul Karim</t>
         </is>
       </c>
       <c r="N193" t="n">
-        <v>120</v>
+        <v>60</v>
       </c>
     </row>
     <row r="194">
@@ -13179,12 +13179,12 @@
       </c>
       <c r="E194" t="inlineStr">
         <is>
-          <t>sec_grade_2_talha_ibn_ubaydullah_1st_shift</t>
+          <t>sec_grade_3_salman_al_farsi_1st_shift_mix</t>
         </is>
       </c>
       <c r="F194" t="inlineStr">
         <is>
-          <t>GRADE 2 - TALHA IBN UBAYDULLAH (1ST SHIFT)</t>
+          <t>GRADE 3 - SALMAN AL FARSI (1ST SHIFT) MIX</t>
         </is>
       </c>
       <c r="G194" t="inlineStr">
@@ -13194,7 +13194,7 @@
       </c>
       <c r="H194" t="inlineStr">
         <is>
-          <t>Grade 2</t>
+          <t>Grade 3</t>
         </is>
       </c>
       <c r="I194" t="inlineStr">
@@ -13204,22 +13204,22 @@
       </c>
       <c r="J194" t="inlineStr">
         <is>
-          <t>subj_shaf</t>
+          <t>subj_arabic</t>
         </is>
       </c>
       <c r="K194" t="inlineStr">
         <is>
-          <t>SHAF</t>
+          <t>Arabic</t>
         </is>
       </c>
       <c r="L194" t="inlineStr">
         <is>
-          <t>tchr_abdul_karim</t>
+          <t>tchr_faidh</t>
         </is>
       </c>
       <c r="M194" t="inlineStr">
         <is>
-          <t>Alim Abdul Karim</t>
+          <t>Ustadh Faidh</t>
         </is>
       </c>
       <c r="N194" t="n">
@@ -13245,12 +13245,12 @@
       </c>
       <c r="E195" t="inlineStr">
         <is>
-          <t>sec_grade_3_salman_al_farsi_1st_shift_mix</t>
+          <t>sec_grade_3_ammar_ibn_yasir_1st_shift_boys</t>
         </is>
       </c>
       <c r="F195" t="inlineStr">
         <is>
-          <t>GRADE 3 - SALMAN AL FARSI (1ST SHIFT) MIX</t>
+          <t>GRADE 3 -AMMAR IBN YASIR (1ST SHIFT) - BOYS</t>
         </is>
       </c>
       <c r="G195" t="inlineStr">
@@ -13270,22 +13270,22 @@
       </c>
       <c r="J195" t="inlineStr">
         <is>
-          <t>subj_arabic</t>
+          <t>subj_math</t>
         </is>
       </c>
       <c r="K195" t="inlineStr">
         <is>
-          <t>Arabic</t>
+          <t>Math</t>
         </is>
       </c>
       <c r="L195" t="inlineStr">
         <is>
-          <t>tchr_faidh</t>
+          <t>tchr_jerlyn</t>
         </is>
       </c>
       <c r="M195" t="inlineStr">
         <is>
-          <t>Ustadh Faidh</t>
+          <t>Teacher Jerlyn</t>
         </is>
       </c>
       <c r="N195" t="n">
@@ -13311,12 +13311,12 @@
       </c>
       <c r="E196" t="inlineStr">
         <is>
-          <t>sec_grade_3_ammar_ibn_yasir_1st_shift_boys</t>
+          <t>sec_grade_4_abdur_rahman_ibn_awf_1st_shift</t>
         </is>
       </c>
       <c r="F196" t="inlineStr">
         <is>
-          <t>GRADE 3 -AMMAR IBN YASIR (1ST SHIFT) - BOYS</t>
+          <t>GRADE 4 - ABDUR RAHMAN IBN AWF (1ST SHIFT)</t>
         </is>
       </c>
       <c r="G196" t="inlineStr">
@@ -13326,7 +13326,7 @@
       </c>
       <c r="H196" t="inlineStr">
         <is>
-          <t>Grade 3</t>
+          <t>Grade 4</t>
         </is>
       </c>
       <c r="I196" t="inlineStr">
@@ -13336,22 +13336,22 @@
       </c>
       <c r="J196" t="inlineStr">
         <is>
-          <t>subj_math</t>
+          <t>subj_shaf</t>
         </is>
       </c>
       <c r="K196" t="inlineStr">
         <is>
-          <t>Math</t>
+          <t>SHAF</t>
         </is>
       </c>
       <c r="L196" t="inlineStr">
         <is>
-          <t>tchr_jerlyn</t>
+          <t>tchr_abdiraheem</t>
         </is>
       </c>
       <c r="M196" t="inlineStr">
         <is>
-          <t>Teacher Jerlyn</t>
+          <t>Ustadh Abdiraheem</t>
         </is>
       </c>
       <c r="N196" t="n">
@@ -13377,12 +13377,12 @@
       </c>
       <c r="E197" t="inlineStr">
         <is>
-          <t>sec_grade_4_abdur_rahman_ibn_awf_1st_shift</t>
+          <t>sec_grade_4_hakim_ibn_hazm_1st_shift</t>
         </is>
       </c>
       <c r="F197" t="inlineStr">
         <is>
-          <t>GRADE 4 - ABDUR RAHMAN IBN AWF (1ST SHIFT)</t>
+          <t>GRADE 4 - HAKIM IBN HAZM(1ST SHIFT)</t>
         </is>
       </c>
       <c r="G197" t="inlineStr">
@@ -13402,22 +13402,22 @@
       </c>
       <c r="J197" t="inlineStr">
         <is>
-          <t>subj_shaf</t>
+          <t>subj_fil</t>
         </is>
       </c>
       <c r="K197" t="inlineStr">
         <is>
-          <t>SHAF</t>
+          <t>FIL</t>
         </is>
       </c>
       <c r="L197" t="inlineStr">
         <is>
-          <t>tchr_abdiraheem</t>
+          <t>tchr_monisa</t>
         </is>
       </c>
       <c r="M197" t="inlineStr">
         <is>
-          <t>Ustadh Abdiraheem</t>
+          <t>Teacher Monisa</t>
         </is>
       </c>
       <c r="N197" t="n">
@@ -13443,12 +13443,12 @@
       </c>
       <c r="E198" t="inlineStr">
         <is>
-          <t>sec_grade_4_hakim_ibn_hazm_1st_shift</t>
+          <t>sec_grade_4_usayd_ibn_hudhayr_1st_shift_mix</t>
         </is>
       </c>
       <c r="F198" t="inlineStr">
         <is>
-          <t>GRADE 4 - HAKIM IBN HAZM(1ST SHIFT)</t>
+          <t>GRADE 4 - USAYD IBN HUDHAYR (1ST SHIFT) - MIX</t>
         </is>
       </c>
       <c r="G198" t="inlineStr">
@@ -13468,22 +13468,22 @@
       </c>
       <c r="J198" t="inlineStr">
         <is>
-          <t>subj_fil</t>
+          <t>subj_arabic</t>
         </is>
       </c>
       <c r="K198" t="inlineStr">
         <is>
-          <t>FIL</t>
+          <t>Arabic</t>
         </is>
       </c>
       <c r="L198" t="inlineStr">
         <is>
-          <t>tchr_monisa</t>
+          <t>tchr_ali</t>
         </is>
       </c>
       <c r="M198" t="inlineStr">
         <is>
-          <t>Teacher Monisa</t>
+          <t>Ustadh Ali</t>
         </is>
       </c>
       <c r="N198" t="n">
@@ -13509,12 +13509,12 @@
       </c>
       <c r="E199" t="inlineStr">
         <is>
-          <t>sec_grade_4_usayd_ibn_hudhayr_1st_shift_mix</t>
+          <t>sec_grade_5_ayyash_ibn_abi_rabi_ah_1st_shift</t>
         </is>
       </c>
       <c r="F199" t="inlineStr">
         <is>
-          <t>GRADE 4 - USAYD IBN HUDHAYR (1ST SHIFT) - MIX</t>
+          <t>GRADE 5 - AYYASH IBN ABI RABI'AH(1ST SHIFT)</t>
         </is>
       </c>
       <c r="G199" t="inlineStr">
@@ -13524,7 +13524,7 @@
       </c>
       <c r="H199" t="inlineStr">
         <is>
-          <t>Grade 4</t>
+          <t>Grade 5</t>
         </is>
       </c>
       <c r="I199" t="inlineStr">
@@ -13534,22 +13534,22 @@
       </c>
       <c r="J199" t="inlineStr">
         <is>
-          <t>subj_arabic</t>
+          <t>subj_english</t>
         </is>
       </c>
       <c r="K199" t="inlineStr">
         <is>
-          <t>Arabic</t>
+          <t>English</t>
         </is>
       </c>
       <c r="L199" t="inlineStr">
         <is>
-          <t>tchr_ali</t>
+          <t>tchr_jessa</t>
         </is>
       </c>
       <c r="M199" t="inlineStr">
         <is>
-          <t>Ustadh Ali</t>
+          <t>Teacher Jessa</t>
         </is>
       </c>
       <c r="N199" t="n">
@@ -13575,12 +13575,12 @@
       </c>
       <c r="E200" t="inlineStr">
         <is>
-          <t>sec_grade_5_ayyash_ibn_abi_rabi_ah_1st_shift</t>
+          <t>sec_grade_5_hamza_ibn_abdul_1st_shift</t>
         </is>
       </c>
       <c r="F200" t="inlineStr">
         <is>
-          <t>GRADE 5 - AYYASH IBN ABI RABI'AH(1ST SHIFT)</t>
+          <t>GRADE 5 - HAMZA IBN ABDUL (1ST SHIFT)</t>
         </is>
       </c>
       <c r="G200" t="inlineStr">
@@ -13600,22 +13600,22 @@
       </c>
       <c r="J200" t="inlineStr">
         <is>
-          <t>subj_english</t>
+          <t>subj_mapeh</t>
         </is>
       </c>
       <c r="K200" t="inlineStr">
         <is>
-          <t>English</t>
+          <t>MAPEH</t>
         </is>
       </c>
       <c r="L200" t="inlineStr">
         <is>
-          <t>tchr_jessa</t>
+          <t>tchr_keychell</t>
         </is>
       </c>
       <c r="M200" t="inlineStr">
         <is>
-          <t>Teacher Jessa</t>
+          <t>Teacher Keychell</t>
         </is>
       </c>
       <c r="N200" t="n">
@@ -13641,12 +13641,12 @@
       </c>
       <c r="E201" t="inlineStr">
         <is>
-          <t>sec_grade_5_hamza_ibn_abdul_1st_shift</t>
+          <t>sec_grade_5_muhammad_ibn_maslamah_1st_shift</t>
         </is>
       </c>
       <c r="F201" t="inlineStr">
         <is>
-          <t>GRADE 5 - HAMZA IBN ABDUL (1ST SHIFT)</t>
+          <t>GRADE 5 - MUHAMMAD IBN MASLAMAH (1ST SHIFT)</t>
         </is>
       </c>
       <c r="G201" t="inlineStr">
@@ -13666,22 +13666,22 @@
       </c>
       <c r="J201" t="inlineStr">
         <is>
-          <t>subj_mapeh</t>
+          <t>subj_math</t>
         </is>
       </c>
       <c r="K201" t="inlineStr">
         <is>
-          <t>MAPEH</t>
+          <t>Math</t>
         </is>
       </c>
       <c r="L201" t="inlineStr">
         <is>
-          <t>tchr_keychell</t>
+          <t>tchr_fhairudz</t>
         </is>
       </c>
       <c r="M201" t="inlineStr">
         <is>
-          <t>Teacher Keychell</t>
+          <t>Teacher Fhairudz</t>
         </is>
       </c>
       <c r="N201" t="n">
@@ -13707,12 +13707,12 @@
       </c>
       <c r="E202" t="inlineStr">
         <is>
-          <t>sec_grade_5_muhammad_ibn_maslamah_1st_shift</t>
+          <t>sec_grade_6_abbas_ibn_abd_al_muttalib_1st_shift</t>
         </is>
       </c>
       <c r="F202" t="inlineStr">
         <is>
-          <t>GRADE 5 - MUHAMMAD IBN MASLAMAH (1ST SHIFT)</t>
+          <t>GRADE 6 - ABBAS IBN ABD AL-MUTTALIB (1ST SHIFT)</t>
         </is>
       </c>
       <c r="G202" t="inlineStr">
@@ -13722,7 +13722,7 @@
       </c>
       <c r="H202" t="inlineStr">
         <is>
-          <t>Grade 5</t>
+          <t>Grade 6</t>
         </is>
       </c>
       <c r="I202" t="inlineStr">
@@ -13732,22 +13732,22 @@
       </c>
       <c r="J202" t="inlineStr">
         <is>
-          <t>subj_math</t>
+          <t>subj_qur_an</t>
         </is>
       </c>
       <c r="K202" t="inlineStr">
         <is>
-          <t>Math</t>
+          <t>Qur'an</t>
         </is>
       </c>
       <c r="L202" t="inlineStr">
         <is>
-          <t>tchr_fhairudz</t>
+          <t>tchr_jaisam</t>
         </is>
       </c>
       <c r="M202" t="inlineStr">
         <is>
-          <t>Teacher Fhairudz</t>
+          <t>Ustadh Jaisam</t>
         </is>
       </c>
       <c r="N202" t="n">
@@ -13773,12 +13773,12 @@
       </c>
       <c r="E203" t="inlineStr">
         <is>
-          <t>sec_grade_6_abbas_ibn_abd_al_muttalib_1st_shift</t>
+          <t>sec_grade_6_abdullah_ibn_salaam_1st_shift</t>
         </is>
       </c>
       <c r="F203" t="inlineStr">
         <is>
-          <t>GRADE 6 - ABBAS IBN ABD AL-MUTTALIB (1ST SHIFT)</t>
+          <t>GRADE 6 - ABDULLAH IBN SALAAM (1ST SHIFT)</t>
         </is>
       </c>
       <c r="G203" t="inlineStr">
@@ -13798,22 +13798,22 @@
       </c>
       <c r="J203" t="inlineStr">
         <is>
-          <t>subj_qur_an</t>
+          <t>subj_gmrc</t>
         </is>
       </c>
       <c r="K203" t="inlineStr">
         <is>
-          <t>Qur'an</t>
+          <t>GMRC</t>
         </is>
       </c>
       <c r="L203" t="inlineStr">
         <is>
-          <t>tchr_jaisam</t>
+          <t>tchr_silfah</t>
         </is>
       </c>
       <c r="M203" t="inlineStr">
         <is>
-          <t>Ustadh Jaisam</t>
+          <t>Ustadh Silfah</t>
         </is>
       </c>
       <c r="N203" t="n">
@@ -13839,22 +13839,22 @@
       </c>
       <c r="E204" t="inlineStr">
         <is>
-          <t>sec_grade_6_abdullah_ibn_salaam_1st_shift</t>
+          <t>sec_grade_7_abu_sufyan_ibn_al_harith_1st_shift_boys</t>
         </is>
       </c>
       <c r="F204" t="inlineStr">
         <is>
-          <t>GRADE 6 - ABDULLAH IBN SALAAM (1ST SHIFT)</t>
+          <t>GRADE 7 - ABU SUFYAN IBN AL-HARITH (1ST SHIFT) BOYS</t>
         </is>
       </c>
       <c r="G204" t="inlineStr">
         <is>
-          <t>Elementary</t>
+          <t>Junior High School</t>
         </is>
       </c>
       <c r="H204" t="inlineStr">
         <is>
-          <t>Grade 6</t>
+          <t>Grade 7</t>
         </is>
       </c>
       <c r="I204" t="inlineStr">
@@ -13864,22 +13864,22 @@
       </c>
       <c r="J204" t="inlineStr">
         <is>
-          <t>subj_gmrc</t>
+          <t>subj_english</t>
         </is>
       </c>
       <c r="K204" t="inlineStr">
         <is>
-          <t>GMRC</t>
+          <t>English</t>
         </is>
       </c>
       <c r="L204" t="inlineStr">
         <is>
-          <t>tchr_silfah</t>
+          <t>tchr_jairah</t>
         </is>
       </c>
       <c r="M204" t="inlineStr">
         <is>
-          <t>Ustadh Silfah</t>
+          <t>Teacher Jairah</t>
         </is>
       </c>
       <c r="N204" t="n">
@@ -13905,12 +13905,12 @@
       </c>
       <c r="E205" t="inlineStr">
         <is>
-          <t>sec_grade_7_abu_sufyan_ibn_al_harith_1st_shift_boys</t>
+          <t>sec_grade_7_usama_ibn_zayd_1st_shift_girls</t>
         </is>
       </c>
       <c r="F205" t="inlineStr">
         <is>
-          <t>GRADE 7 - ABU SUFYAN IBN AL-HARITH (1ST SHIFT) BOYS</t>
+          <t>GRADE 7 - USAMA IBN ZAYD (1ST SHIFT) GIRLS</t>
         </is>
       </c>
       <c r="G205" t="inlineStr">
@@ -13930,22 +13930,22 @@
       </c>
       <c r="J205" t="inlineStr">
         <is>
-          <t>subj_english</t>
+          <t>subj_mapeh</t>
         </is>
       </c>
       <c r="K205" t="inlineStr">
         <is>
-          <t>English</t>
+          <t>MAPEH</t>
         </is>
       </c>
       <c r="L205" t="inlineStr">
         <is>
-          <t>tchr_jairah</t>
+          <t>tchr_franchette</t>
         </is>
       </c>
       <c r="M205" t="inlineStr">
         <is>
-          <t>Teacher Jairah</t>
+          <t>Teacher Franchette</t>
         </is>
       </c>
       <c r="N205" t="n">
@@ -13971,12 +13971,12 @@
       </c>
       <c r="E206" t="inlineStr">
         <is>
-          <t>sec_grade_7_usama_ibn_zayd_1st_shift_girls</t>
+          <t>sec_grade_8_sa_ad_ibn_mua_dh_1st_shift_girls</t>
         </is>
       </c>
       <c r="F206" t="inlineStr">
         <is>
-          <t>GRADE 7 - USAMA IBN ZAYD (1ST SHIFT) GIRLS</t>
+          <t>GRADE 8 - SA'AD IBN MUA'DH (1ST SHIFT) - GIRLS</t>
         </is>
       </c>
       <c r="G206" t="inlineStr">
@@ -13986,7 +13986,7 @@
       </c>
       <c r="H206" t="inlineStr">
         <is>
-          <t>Grade 7</t>
+          <t>Grade 8</t>
         </is>
       </c>
       <c r="I206" t="inlineStr">
@@ -13996,22 +13996,22 @@
       </c>
       <c r="J206" t="inlineStr">
         <is>
-          <t>subj_mapeh</t>
+          <t>subj_values_ed</t>
         </is>
       </c>
       <c r="K206" t="inlineStr">
         <is>
-          <t>MAPEH</t>
+          <t>Values Ed</t>
         </is>
       </c>
       <c r="L206" t="inlineStr">
         <is>
-          <t>tchr_franchette</t>
+          <t>tchr_wardah</t>
         </is>
       </c>
       <c r="M206" t="inlineStr">
         <is>
-          <t>Teacher Franchette</t>
+          <t>Teacher Wardah</t>
         </is>
       </c>
       <c r="N206" t="n">
@@ -14037,12 +14037,12 @@
       </c>
       <c r="E207" t="inlineStr">
         <is>
-          <t>sec_grade_8_sa_ad_ibn_mua_dh_1st_shift_girls</t>
+          <t>sec_grade_9_abu_hurayrah_1st_shift_girls</t>
         </is>
       </c>
       <c r="F207" t="inlineStr">
         <is>
-          <t>GRADE 8 - SA'AD IBN MUA'DH (1ST SHIFT) - GIRLS</t>
+          <t>GRADE 9 - ABU HURAYRAH (1ST SHIFT) GIRLS</t>
         </is>
       </c>
       <c r="G207" t="inlineStr">
@@ -14052,7 +14052,7 @@
       </c>
       <c r="H207" t="inlineStr">
         <is>
-          <t>Grade 8</t>
+          <t>Grade 9</t>
         </is>
       </c>
       <c r="I207" t="inlineStr">
@@ -14062,22 +14062,22 @@
       </c>
       <c r="J207" t="inlineStr">
         <is>
-          <t>subj_values_ed</t>
+          <t>subj_filipino</t>
         </is>
       </c>
       <c r="K207" t="inlineStr">
         <is>
-          <t>Values Ed</t>
+          <t>Filipino</t>
         </is>
       </c>
       <c r="L207" t="inlineStr">
         <is>
-          <t>tchr_wardah</t>
+          <t>tchr_nadzra</t>
         </is>
       </c>
       <c r="M207" t="inlineStr">
         <is>
-          <t>Teacher Wardah</t>
+          <t>Teacher Nadzra</t>
         </is>
       </c>
       <c r="N207" t="n">
@@ -14094,31 +14094,31 @@
         </is>
       </c>
       <c r="C208" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D208" t="inlineStr">
         <is>
-          <t>12:40 PM – 01:40 PM</t>
+          <t>01:30 PM – 02:30 PM</t>
         </is>
       </c>
       <c r="E208" t="inlineStr">
         <is>
-          <t>sec_grade_9_abu_hurayrah_1st_shift_girls</t>
+          <t>sec_kinder_2_abu_bakr_as_sideeq_1st_shift</t>
         </is>
       </c>
       <c r="F208" t="inlineStr">
         <is>
-          <t>GRADE 9 - ABU HURAYRAH (1ST SHIFT) GIRLS</t>
+          <t>Kinder 2 ABU BAKR AS-SIDEEQ (1ST SHIFT)</t>
         </is>
       </c>
       <c r="G208" t="inlineStr">
         <is>
-          <t>Junior High School</t>
+          <t>Elementary</t>
         </is>
       </c>
       <c r="H208" t="inlineStr">
         <is>
-          <t>Grade 9</t>
+          <t>Kinder 2</t>
         </is>
       </c>
       <c r="I208" t="inlineStr">
@@ -14128,22 +14128,22 @@
       </c>
       <c r="J208" t="inlineStr">
         <is>
-          <t>subj_filipino</t>
+          <t>subj_hadith</t>
         </is>
       </c>
       <c r="K208" t="inlineStr">
         <is>
-          <t>Filipino</t>
+          <t>Hadith</t>
         </is>
       </c>
       <c r="L208" t="inlineStr">
         <is>
-          <t>tchr_nadzra</t>
+          <t>tchr_saliha</t>
         </is>
       </c>
       <c r="M208" t="inlineStr">
         <is>
-          <t>Teacher Nadzra</t>
+          <t>Ustadha Saliha</t>
         </is>
       </c>
       <c r="N208" t="n">
@@ -14160,21 +14160,21 @@
         </is>
       </c>
       <c r="C209" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D209" t="inlineStr">
         <is>
-          <t>01:30 PM – 02:30 PM</t>
+          <t>01:50 PM – 02:50 PM</t>
         </is>
       </c>
       <c r="E209" t="inlineStr">
         <is>
-          <t>sec_kinder_2_abu_bakr_as_sideeq_1st_shift</t>
+          <t>sec_grade_1_ali_ibn_abi_talib_1st_shift</t>
         </is>
       </c>
       <c r="F209" t="inlineStr">
         <is>
-          <t>Kinder 2 ABU BAKR AS-SIDEEQ (1ST SHIFT)</t>
+          <t>GRADE 1 - ALI IBN ABI TALIB(1ST SHIFT)</t>
         </is>
       </c>
       <c r="G209" t="inlineStr">
@@ -14184,7 +14184,7 @@
       </c>
       <c r="H209" t="inlineStr">
         <is>
-          <t>Kinder 2</t>
+          <t>Grade 1</t>
         </is>
       </c>
       <c r="I209" t="inlineStr">
@@ -14194,22 +14194,22 @@
       </c>
       <c r="J209" t="inlineStr">
         <is>
-          <t>subj_hadith</t>
+          <t>subj_math</t>
         </is>
       </c>
       <c r="K209" t="inlineStr">
         <is>
-          <t>Hadith</t>
+          <t>Math</t>
         </is>
       </c>
       <c r="L209" t="inlineStr">
         <is>
-          <t>tchr_saliha</t>
+          <t>tchr_joanna</t>
         </is>
       </c>
       <c r="M209" t="inlineStr">
         <is>
-          <t>Ustadha Saliha</t>
+          <t>Teacher Joanna</t>
         </is>
       </c>
       <c r="N209" t="n">
@@ -14235,22 +14235,22 @@
       </c>
       <c r="E210" t="inlineStr">
         <is>
-          <t>sec_grade_1_ali_ibn_abi_talib_1st_shift</t>
+          <t>sec_grade_10_utbah_ibn_ghazwan_1st_shift_girls</t>
         </is>
       </c>
       <c r="F210" t="inlineStr">
         <is>
-          <t>GRADE 1 - ALI IBN ABI TALIB(1ST SHIFT)</t>
+          <t>GRADE 10 - UTBAH IBN GHAZWAN (1ST SHIFT) GIRLS</t>
         </is>
       </c>
       <c r="G210" t="inlineStr">
         <is>
-          <t>Elementary</t>
+          <t>Junior High School</t>
         </is>
       </c>
       <c r="H210" t="inlineStr">
         <is>
-          <t>Grade 1</t>
+          <t>Grade 10</t>
         </is>
       </c>
       <c r="I210" t="inlineStr">
@@ -14260,22 +14260,22 @@
       </c>
       <c r="J210" t="inlineStr">
         <is>
-          <t>subj_math</t>
+          <t>subj_values_ed</t>
         </is>
       </c>
       <c r="K210" t="inlineStr">
         <is>
-          <t>Math</t>
+          <t>Values Ed</t>
         </is>
       </c>
       <c r="L210" t="inlineStr">
         <is>
-          <t>tchr_joanna</t>
+          <t>tchr_nof</t>
         </is>
       </c>
       <c r="M210" t="inlineStr">
         <is>
-          <t>Teacher Joanna</t>
+          <t>Teacher Nof</t>
         </is>
       </c>
       <c r="N210" t="n">
@@ -14292,7 +14292,7 @@
         </is>
       </c>
       <c r="C211" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D211" t="inlineStr">
         <is>
@@ -14301,22 +14301,22 @@
       </c>
       <c r="E211" t="inlineStr">
         <is>
-          <t>sec_grade_10_utbah_ibn_ghazwan_1st_shift_girls</t>
+          <t>sec_grade_11_1st_shift_girls</t>
         </is>
       </c>
       <c r="F211" t="inlineStr">
         <is>
-          <t>GRADE 10 - UTBAH IBN GHAZWAN (1ST SHIFT) GIRLS</t>
+          <t>GRADE 11 (1ST SHIFT GIRLS)</t>
         </is>
       </c>
       <c r="G211" t="inlineStr">
         <is>
-          <t>Junior High School</t>
+          <t>Senior High School</t>
         </is>
       </c>
       <c r="H211" t="inlineStr">
         <is>
-          <t>Grade 10</t>
+          <t>Grade 11</t>
         </is>
       </c>
       <c r="I211" t="inlineStr">
@@ -14326,22 +14326,22 @@
       </c>
       <c r="J211" t="inlineStr">
         <is>
-          <t>subj_values_ed</t>
+          <t>subj_ec</t>
         </is>
       </c>
       <c r="K211" t="inlineStr">
         <is>
-          <t>Values Ed</t>
+          <t>EC</t>
         </is>
       </c>
       <c r="L211" t="inlineStr">
         <is>
-          <t>tchr_nof</t>
+          <t>tchr_nadzra</t>
         </is>
       </c>
       <c r="M211" t="inlineStr">
         <is>
-          <t>Teacher Nof</t>
+          <t>Teacher Nadzra</t>
         </is>
       </c>
       <c r="N211" t="n">
@@ -14358,7 +14358,7 @@
         </is>
       </c>
       <c r="C212" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D212" t="inlineStr">
         <is>
@@ -14367,22 +14367,22 @@
       </c>
       <c r="E212" t="inlineStr">
         <is>
-          <t>sec_grade_11_1st_shift_girls</t>
+          <t>sec_grade_3_habib_ibn_zayd_al_ansari_1st_shift_girls</t>
         </is>
       </c>
       <c r="F212" t="inlineStr">
         <is>
-          <t>GRADE 11 (1ST SHIFT GIRLS)</t>
+          <t>Grade 3 - HABIB IBN ZAYD AL-ANSARI (1ST SHIFT) - GIRLS</t>
         </is>
       </c>
       <c r="G212" t="inlineStr">
         <is>
-          <t>Senior High School</t>
+          <t>Elementary</t>
         </is>
       </c>
       <c r="H212" t="inlineStr">
         <is>
-          <t>Grade 11</t>
+          <t>Grade 3</t>
         </is>
       </c>
       <c r="I212" t="inlineStr">
@@ -14392,22 +14392,22 @@
       </c>
       <c r="J212" t="inlineStr">
         <is>
-          <t>subj_ec</t>
+          <t>subj_qur_an</t>
         </is>
       </c>
       <c r="K212" t="inlineStr">
         <is>
-          <t>EC</t>
+          <t>Qur'an</t>
         </is>
       </c>
       <c r="L212" t="inlineStr">
         <is>
-          <t>tchr_nadzra</t>
+          <t>tchr_obaydah</t>
         </is>
       </c>
       <c r="M212" t="inlineStr">
         <is>
-          <t>Teacher Nadzra</t>
+          <t>Ustadh Obaydah</t>
         </is>
       </c>
       <c r="N212" t="n">
@@ -14433,12 +14433,12 @@
       </c>
       <c r="E213" t="inlineStr">
         <is>
-          <t>sec_grade_3_habib_ibn_zayd_al_ansari_1st_shift_girls</t>
+          <t>sec_grade_3_salman_al_farsi_1st_shift_mix</t>
         </is>
       </c>
       <c r="F213" t="inlineStr">
         <is>
-          <t>Grade 3 - HABIB IBN ZAYD AL-ANSARI (1ST SHIFT) - GIRLS</t>
+          <t>GRADE 3 - SALMAN AL FARSI (1ST SHIFT) MIX</t>
         </is>
       </c>
       <c r="G213" t="inlineStr">
@@ -14458,22 +14458,22 @@
       </c>
       <c r="J213" t="inlineStr">
         <is>
-          <t>subj_qur_an</t>
+          <t>subj_gmrc</t>
         </is>
       </c>
       <c r="K213" t="inlineStr">
         <is>
-          <t>Qur'an</t>
+          <t>GMRC</t>
         </is>
       </c>
       <c r="L213" t="inlineStr">
         <is>
-          <t>tchr_obaydah</t>
+          <t>tchr_zuhora</t>
         </is>
       </c>
       <c r="M213" t="inlineStr">
         <is>
-          <t>Ustadh Obaydah</t>
+          <t>Teacher Zuhora</t>
         </is>
       </c>
       <c r="N213" t="n">
@@ -14490,7 +14490,7 @@
         </is>
       </c>
       <c r="C214" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D214" t="inlineStr">
         <is>
@@ -14499,12 +14499,12 @@
       </c>
       <c r="E214" t="inlineStr">
         <is>
-          <t>sec_grade_3_salman_al_farsi_1st_shift_mix</t>
+          <t>sec_grade_3_zayd_ibn_haritha_2nd_shift_girls</t>
         </is>
       </c>
       <c r="F214" t="inlineStr">
         <is>
-          <t>GRADE 3 - SALMAN AL FARSI (1ST SHIFT) MIX</t>
+          <t>GRADE 3 - ZAYD IBN HARITHA (2ND SHIFT) - GIRLS</t>
         </is>
       </c>
       <c r="G214" t="inlineStr">
@@ -14519,27 +14519,27 @@
       </c>
       <c r="I214" t="inlineStr">
         <is>
-          <t>ODL - 1ST SHIFT</t>
+          <t>ODL - 2ND SHIFT</t>
         </is>
       </c>
       <c r="J214" t="inlineStr">
         <is>
-          <t>subj_gmrc</t>
+          <t>subj_arabic</t>
         </is>
       </c>
       <c r="K214" t="inlineStr">
         <is>
-          <t>GMRC</t>
+          <t>Arabic</t>
         </is>
       </c>
       <c r="L214" t="inlineStr">
         <is>
-          <t>tchr_zuhora</t>
+          <t>tchr_silfah</t>
         </is>
       </c>
       <c r="M214" t="inlineStr">
         <is>
-          <t>Teacher Zuhora</t>
+          <t>Ustadh Silfah</t>
         </is>
       </c>
       <c r="N214" t="n">
@@ -14556,7 +14556,7 @@
         </is>
       </c>
       <c r="C215" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D215" t="inlineStr">
         <is>
@@ -14565,12 +14565,12 @@
       </c>
       <c r="E215" t="inlineStr">
         <is>
-          <t>sec_grade_3_zayd_ibn_haritha_2nd_shift_girls</t>
+          <t>sec_grade_3_ammar_ibn_yasir_1st_shift_boys</t>
         </is>
       </c>
       <c r="F215" t="inlineStr">
         <is>
-          <t>GRADE 3 - ZAYD IBN HARITHA (2ND SHIFT) - GIRLS</t>
+          <t>GRADE 3 -AMMAR IBN YASIR (1ST SHIFT) - BOYS</t>
         </is>
       </c>
       <c r="G215" t="inlineStr">
@@ -14585,27 +14585,27 @@
       </c>
       <c r="I215" t="inlineStr">
         <is>
-          <t>ODL - 2ND SHIFT</t>
+          <t>ODL - 1ST SHIFT</t>
         </is>
       </c>
       <c r="J215" t="inlineStr">
         <is>
-          <t>subj_arabic</t>
+          <t>subj_makabansa</t>
         </is>
       </c>
       <c r="K215" t="inlineStr">
         <is>
-          <t>Arabic</t>
+          <t>Makabansa</t>
         </is>
       </c>
       <c r="L215" t="inlineStr">
         <is>
-          <t>tchr_silfah</t>
+          <t>tchr_zara</t>
         </is>
       </c>
       <c r="M215" t="inlineStr">
         <is>
-          <t>Ustadh Silfah</t>
+          <t>Teacher Zara</t>
         </is>
       </c>
       <c r="N215" t="n">
@@ -14631,12 +14631,12 @@
       </c>
       <c r="E216" t="inlineStr">
         <is>
-          <t>sec_grade_3_ammar_ibn_yasir_1st_shift_boys</t>
+          <t>sec_grade_4_abdur_rahman_ibn_awf_1st_shift</t>
         </is>
       </c>
       <c r="F216" t="inlineStr">
         <is>
-          <t>GRADE 3 -AMMAR IBN YASIR (1ST SHIFT) - BOYS</t>
+          <t>GRADE 4 - ABDUR RAHMAN IBN AWF (1ST SHIFT)</t>
         </is>
       </c>
       <c r="G216" t="inlineStr">
@@ -14646,7 +14646,7 @@
       </c>
       <c r="H216" t="inlineStr">
         <is>
-          <t>Grade 3</t>
+          <t>Grade 4</t>
         </is>
       </c>
       <c r="I216" t="inlineStr">
@@ -14656,22 +14656,22 @@
       </c>
       <c r="J216" t="inlineStr">
         <is>
-          <t>subj_makabansa</t>
+          <t>subj_science</t>
         </is>
       </c>
       <c r="K216" t="inlineStr">
         <is>
-          <t>Makabansa</t>
+          <t>Science</t>
         </is>
       </c>
       <c r="L216" t="inlineStr">
         <is>
-          <t>tchr_zara</t>
+          <t>tchr_anna</t>
         </is>
       </c>
       <c r="M216" t="inlineStr">
         <is>
-          <t>Teacher Zara</t>
+          <t>Teacher Anna</t>
         </is>
       </c>
       <c r="N216" t="n">
@@ -14697,12 +14697,12 @@
       </c>
       <c r="E217" t="inlineStr">
         <is>
-          <t>sec_grade_4_abdur_rahman_ibn_awf_1st_shift</t>
+          <t>sec_grade_4_hakim_ibn_hazm_1st_shift</t>
         </is>
       </c>
       <c r="F217" t="inlineStr">
         <is>
-          <t>GRADE 4 - ABDUR RAHMAN IBN AWF (1ST SHIFT)</t>
+          <t>GRADE 4 - HAKIM IBN HAZM(1ST SHIFT)</t>
         </is>
       </c>
       <c r="G217" t="inlineStr">
@@ -14722,22 +14722,22 @@
       </c>
       <c r="J217" t="inlineStr">
         <is>
-          <t>subj_science</t>
+          <t>subj_tle</t>
         </is>
       </c>
       <c r="K217" t="inlineStr">
         <is>
-          <t>Science</t>
+          <t>TLE</t>
         </is>
       </c>
       <c r="L217" t="inlineStr">
         <is>
-          <t>tchr_anna</t>
+          <t>tchr_monisa</t>
         </is>
       </c>
       <c r="M217" t="inlineStr">
         <is>
-          <t>Teacher Anna</t>
+          <t>Teacher Monisa</t>
         </is>
       </c>
       <c r="N217" t="n">
@@ -14763,12 +14763,12 @@
       </c>
       <c r="E218" t="inlineStr">
         <is>
-          <t>sec_grade_4_hakim_ibn_hazm_1st_shift</t>
+          <t>sec_grade_4_usayd_ibn_hudhayr_1st_shift_mix</t>
         </is>
       </c>
       <c r="F218" t="inlineStr">
         <is>
-          <t>GRADE 4 - HAKIM IBN HAZM(1ST SHIFT)</t>
+          <t>GRADE 4 - USAYD IBN HUDHAYR (1ST SHIFT) - MIX</t>
         </is>
       </c>
       <c r="G218" t="inlineStr">
@@ -14788,22 +14788,22 @@
       </c>
       <c r="J218" t="inlineStr">
         <is>
-          <t>subj_tle</t>
+          <t>subj_science</t>
         </is>
       </c>
       <c r="K218" t="inlineStr">
         <is>
-          <t>TLE</t>
+          <t>Science</t>
         </is>
       </c>
       <c r="L218" t="inlineStr">
         <is>
-          <t>tchr_monisa</t>
+          <t>tchr_saimonah</t>
         </is>
       </c>
       <c r="M218" t="inlineStr">
         <is>
-          <t>Teacher Monisa</t>
+          <t>Teacher Saimonah</t>
         </is>
       </c>
       <c r="N218" t="n">
@@ -14829,12 +14829,12 @@
       </c>
       <c r="E219" t="inlineStr">
         <is>
-          <t>sec_grade_4_usayd_ibn_hudhayr_1st_shift_mix</t>
+          <t>sec_grade_5_ayyash_ibn_abi_rabi_ah_1st_shift</t>
         </is>
       </c>
       <c r="F219" t="inlineStr">
         <is>
-          <t>GRADE 4 - USAYD IBN HUDHAYR (1ST SHIFT) - MIX</t>
+          <t>GRADE 5 - AYYASH IBN ABI RABI'AH(1ST SHIFT)</t>
         </is>
       </c>
       <c r="G219" t="inlineStr">
@@ -14844,7 +14844,7 @@
       </c>
       <c r="H219" t="inlineStr">
         <is>
-          <t>Grade 4</t>
+          <t>Grade 5</t>
         </is>
       </c>
       <c r="I219" t="inlineStr">
@@ -14854,22 +14854,22 @@
       </c>
       <c r="J219" t="inlineStr">
         <is>
-          <t>subj_science</t>
+          <t>subj_fil5</t>
         </is>
       </c>
       <c r="K219" t="inlineStr">
         <is>
-          <t>Science</t>
+          <t>Fil5</t>
         </is>
       </c>
       <c r="L219" t="inlineStr">
         <is>
-          <t>tchr_saimonah</t>
+          <t>tchr_jenny</t>
         </is>
       </c>
       <c r="M219" t="inlineStr">
         <is>
-          <t>Teacher Saimonah</t>
+          <t>Teacher Jenny</t>
         </is>
       </c>
       <c r="N219" t="n">
@@ -14895,12 +14895,12 @@
       </c>
       <c r="E220" t="inlineStr">
         <is>
-          <t>sec_grade_5_ayyash_ibn_abi_rabi_ah_1st_shift</t>
+          <t>sec_grade_5_hamza_ibn_abdul_1st_shift</t>
         </is>
       </c>
       <c r="F220" t="inlineStr">
         <is>
-          <t>GRADE 5 - AYYASH IBN ABI RABI'AH(1ST SHIFT)</t>
+          <t>GRADE 5 - HAMZA IBN ABDUL (1ST SHIFT)</t>
         </is>
       </c>
       <c r="G220" t="inlineStr">
@@ -14920,22 +14920,22 @@
       </c>
       <c r="J220" t="inlineStr">
         <is>
-          <t>subj_fil5</t>
+          <t>subj_math</t>
         </is>
       </c>
       <c r="K220" t="inlineStr">
         <is>
-          <t>Fil5</t>
+          <t>Math</t>
         </is>
       </c>
       <c r="L220" t="inlineStr">
         <is>
-          <t>tchr_jenny</t>
+          <t>tchr_fhairudz</t>
         </is>
       </c>
       <c r="M220" t="inlineStr">
         <is>
-          <t>Teacher Jenny</t>
+          <t>Teacher Fhairudz</t>
         </is>
       </c>
       <c r="N220" t="n">
@@ -14961,12 +14961,12 @@
       </c>
       <c r="E221" t="inlineStr">
         <is>
-          <t>sec_grade_5_hamza_ibn_abdul_1st_shift</t>
+          <t>sec_grade_5_muhammad_ibn_maslamah_1st_shift</t>
         </is>
       </c>
       <c r="F221" t="inlineStr">
         <is>
-          <t>GRADE 5 - HAMZA IBN ABDUL (1ST SHIFT)</t>
+          <t>GRADE 5 - MUHAMMAD IBN MASLAMAH (1ST SHIFT)</t>
         </is>
       </c>
       <c r="G221" t="inlineStr">
@@ -14986,22 +14986,22 @@
       </c>
       <c r="J221" t="inlineStr">
         <is>
-          <t>subj_math</t>
+          <t>subj_arabic</t>
         </is>
       </c>
       <c r="K221" t="inlineStr">
         <is>
-          <t>Math</t>
+          <t>Arabic</t>
         </is>
       </c>
       <c r="L221" t="inlineStr">
         <is>
-          <t>tchr_fhairudz</t>
+          <t>tchr_abdul_karim</t>
         </is>
       </c>
       <c r="M221" t="inlineStr">
         <is>
-          <t>Teacher Fhairudz</t>
+          <t>Alim Abdul Karim</t>
         </is>
       </c>
       <c r="N221" t="n">
@@ -15027,12 +15027,12 @@
       </c>
       <c r="E222" t="inlineStr">
         <is>
-          <t>sec_grade_5_muhammad_ibn_maslamah_1st_shift</t>
+          <t>sec_grade_6_abbas_ibn_abd_al_muttalib_1st_shift</t>
         </is>
       </c>
       <c r="F222" t="inlineStr">
         <is>
-          <t>GRADE 5 - MUHAMMAD IBN MASLAMAH (1ST SHIFT)</t>
+          <t>GRADE 6 - ABBAS IBN ABD AL-MUTTALIB (1ST SHIFT)</t>
         </is>
       </c>
       <c r="G222" t="inlineStr">
@@ -15042,7 +15042,7 @@
       </c>
       <c r="H222" t="inlineStr">
         <is>
-          <t>Grade 5</t>
+          <t>Grade 6</t>
         </is>
       </c>
       <c r="I222" t="inlineStr">
@@ -15062,12 +15062,12 @@
       </c>
       <c r="L222" t="inlineStr">
         <is>
-          <t>tchr_abdul_karim</t>
+          <t>tchr_ali</t>
         </is>
       </c>
       <c r="M222" t="inlineStr">
         <is>
-          <t>Alim Abdul Karim</t>
+          <t>Ustadh Ali</t>
         </is>
       </c>
       <c r="N222" t="n">
@@ -15088,17 +15088,17 @@
       </c>
       <c r="D223" t="inlineStr">
         <is>
-          <t>01:50 PM – 02:50 PM</t>
+          <t>01:50 PM – 04:10 PM</t>
         </is>
       </c>
       <c r="E223" t="inlineStr">
         <is>
-          <t>sec_grade_6_abbas_ibn_abd_al_muttalib_1st_shift</t>
+          <t>sec_grade_6_abdullah_ibn_salaam_1st_shift</t>
         </is>
       </c>
       <c r="F223" t="inlineStr">
         <is>
-          <t>GRADE 6 - ABBAS IBN ABD AL-MUTTALIB (1ST SHIFT)</t>
+          <t>GRADE 6 - ABDULLAH IBN SALAAM (1ST SHIFT)</t>
         </is>
       </c>
       <c r="G223" t="inlineStr">
@@ -15118,26 +15118,26 @@
       </c>
       <c r="J223" t="inlineStr">
         <is>
-          <t>subj_arabic</t>
+          <t>subj_math</t>
         </is>
       </c>
       <c r="K223" t="inlineStr">
         <is>
-          <t>Arabic</t>
+          <t>Math</t>
         </is>
       </c>
       <c r="L223" t="inlineStr">
         <is>
-          <t>tchr_ali</t>
+          <t>tchr_katrina</t>
         </is>
       </c>
       <c r="M223" t="inlineStr">
         <is>
-          <t>Ustadh Ali</t>
+          <t>Teacher Katrina</t>
         </is>
       </c>
       <c r="N223" t="n">
-        <v>60</v>
+        <v>120</v>
       </c>
     </row>
     <row r="224">
@@ -15154,27 +15154,27 @@
       </c>
       <c r="D224" t="inlineStr">
         <is>
-          <t>01:50 PM – 04:10 PM</t>
+          <t>01:50 PM – 02:50 PM</t>
         </is>
       </c>
       <c r="E224" t="inlineStr">
         <is>
-          <t>sec_grade_6_abdullah_ibn_salaam_1st_shift</t>
+          <t>sec_grade_7_abu_sufyan_ibn_al_harith_1st_shift_boys</t>
         </is>
       </c>
       <c r="F224" t="inlineStr">
         <is>
-          <t>GRADE 6 - ABDULLAH IBN SALAAM (1ST SHIFT)</t>
+          <t>GRADE 7 - ABU SUFYAN IBN AL-HARITH (1ST SHIFT) BOYS</t>
         </is>
       </c>
       <c r="G224" t="inlineStr">
         <is>
-          <t>Elementary</t>
+          <t>Junior High School</t>
         </is>
       </c>
       <c r="H224" t="inlineStr">
         <is>
-          <t>Grade 6</t>
+          <t>Grade 7</t>
         </is>
       </c>
       <c r="I224" t="inlineStr">
@@ -15184,26 +15184,26 @@
       </c>
       <c r="J224" t="inlineStr">
         <is>
-          <t>subj_math</t>
+          <t>subj_tle</t>
         </is>
       </c>
       <c r="K224" t="inlineStr">
         <is>
-          <t>Math</t>
+          <t>TLE</t>
         </is>
       </c>
       <c r="L224" t="inlineStr">
         <is>
-          <t>tchr_katrina</t>
+          <t>tchr_halnaisa</t>
         </is>
       </c>
       <c r="M224" t="inlineStr">
         <is>
-          <t>Teacher Katrina</t>
+          <t>Teacher Halnaisa</t>
         </is>
       </c>
       <c r="N224" t="n">
-        <v>120</v>
+        <v>60</v>
       </c>
     </row>
     <row r="225">
@@ -15225,12 +15225,12 @@
       </c>
       <c r="E225" t="inlineStr">
         <is>
-          <t>sec_grade_7_abu_sufyan_ibn_al_harith_1st_shift_boys</t>
+          <t>sec_grade_7_usama_ibn_zayd_1st_shift_girls</t>
         </is>
       </c>
       <c r="F225" t="inlineStr">
         <is>
-          <t>GRADE 7 - ABU SUFYAN IBN AL-HARITH (1ST SHIFT) BOYS</t>
+          <t>GRADE 7 - USAMA IBN ZAYD (1ST SHIFT) GIRLS</t>
         </is>
       </c>
       <c r="G225" t="inlineStr">
@@ -15250,22 +15250,22 @@
       </c>
       <c r="J225" t="inlineStr">
         <is>
-          <t>subj_tle</t>
+          <t>subj_shaf</t>
         </is>
       </c>
       <c r="K225" t="inlineStr">
         <is>
-          <t>TLE</t>
+          <t>SHAF</t>
         </is>
       </c>
       <c r="L225" t="inlineStr">
         <is>
-          <t>tchr_halnaisa</t>
+          <t>tchr_samsuddin</t>
         </is>
       </c>
       <c r="M225" t="inlineStr">
         <is>
-          <t>Teacher Halnaisa</t>
+          <t>Alim Samsuddin</t>
         </is>
       </c>
       <c r="N225" t="n">
@@ -15291,12 +15291,12 @@
       </c>
       <c r="E226" t="inlineStr">
         <is>
-          <t>sec_grade_7_usama_ibn_zayd_1st_shift_girls</t>
+          <t>sec_grade_8_sa_ad_ibn_mua_dh_1st_shift_girls</t>
         </is>
       </c>
       <c r="F226" t="inlineStr">
         <is>
-          <t>GRADE 7 - USAMA IBN ZAYD (1ST SHIFT) GIRLS</t>
+          <t>GRADE 8 - SA'AD IBN MUA'DH (1ST SHIFT) - GIRLS</t>
         </is>
       </c>
       <c r="G226" t="inlineStr">
@@ -15306,7 +15306,7 @@
       </c>
       <c r="H226" t="inlineStr">
         <is>
-          <t>Grade 7</t>
+          <t>Grade 8</t>
         </is>
       </c>
       <c r="I226" t="inlineStr">
@@ -15316,22 +15316,22 @@
       </c>
       <c r="J226" t="inlineStr">
         <is>
-          <t>subj_shaf</t>
+          <t>subj_mapeh</t>
         </is>
       </c>
       <c r="K226" t="inlineStr">
         <is>
-          <t>SHAF</t>
+          <t>MAPEH</t>
         </is>
       </c>
       <c r="L226" t="inlineStr">
         <is>
-          <t>tchr_samsuddin</t>
+          <t>tchr_franchette</t>
         </is>
       </c>
       <c r="M226" t="inlineStr">
         <is>
-          <t>Alim Samsuddin</t>
+          <t>Teacher Franchette</t>
         </is>
       </c>
       <c r="N226" t="n">
@@ -15352,17 +15352,17 @@
       </c>
       <c r="D227" t="inlineStr">
         <is>
-          <t>01:50 PM – 02:50 PM</t>
+          <t>01:50 PM – 04:10 PM</t>
         </is>
       </c>
       <c r="E227" t="inlineStr">
         <is>
-          <t>sec_grade_8_sa_ad_ibn_mua_dh_1st_shift_girls</t>
+          <t>sec_grade_9_abu_hurayrah_1st_shift_girls</t>
         </is>
       </c>
       <c r="F227" t="inlineStr">
         <is>
-          <t>GRADE 8 - SA'AD IBN MUA'DH (1ST SHIFT) - GIRLS</t>
+          <t>GRADE 9 - ABU HURAYRAH (1ST SHIFT) GIRLS</t>
         </is>
       </c>
       <c r="G227" t="inlineStr">
@@ -15372,7 +15372,7 @@
       </c>
       <c r="H227" t="inlineStr">
         <is>
-          <t>Grade 8</t>
+          <t>Grade 9</t>
         </is>
       </c>
       <c r="I227" t="inlineStr">
@@ -15382,26 +15382,26 @@
       </c>
       <c r="J227" t="inlineStr">
         <is>
-          <t>subj_mapeh</t>
+          <t>subj_math</t>
         </is>
       </c>
       <c r="K227" t="inlineStr">
         <is>
-          <t>MAPEH</t>
+          <t>Math</t>
         </is>
       </c>
       <c r="L227" t="inlineStr">
         <is>
-          <t>tchr_franchette</t>
+          <t>tchr_jhelyn</t>
         </is>
       </c>
       <c r="M227" t="inlineStr">
         <is>
-          <t>Teacher Franchette</t>
+          <t>Teacher Jhelyn</t>
         </is>
       </c>
       <c r="N227" t="n">
-        <v>60</v>
+        <v>120</v>
       </c>
     </row>
     <row r="228">
@@ -15414,60 +15414,60 @@
         </is>
       </c>
       <c r="C228" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D228" t="inlineStr">
         <is>
-          <t>01:50 PM – 04:10 PM</t>
+          <t>01:50 PM – 02:50 PM</t>
         </is>
       </c>
       <c r="E228" t="inlineStr">
         <is>
-          <t>sec_grade_9_abu_hurayrah_1st_shift_girls</t>
+          <t>sec_k2_umar_ibn_al_khattab_2nd_shift</t>
         </is>
       </c>
       <c r="F228" t="inlineStr">
         <is>
-          <t>GRADE 9 - ABU HURAYRAH (1ST SHIFT) GIRLS</t>
+          <t>K2 - UMAR IBN AL-KHATTAB (2ND SHIFT)</t>
         </is>
       </c>
       <c r="G228" t="inlineStr">
         <is>
-          <t>Junior High School</t>
+          <t>Elementary</t>
         </is>
       </c>
       <c r="H228" t="inlineStr">
         <is>
-          <t>Grade 9</t>
+          <t>Kinder 2</t>
         </is>
       </c>
       <c r="I228" t="inlineStr">
         <is>
-          <t>ODL - 1ST SHIFT</t>
+          <t>ODL - 2ND SHIFT</t>
         </is>
       </c>
       <c r="J228" t="inlineStr">
         <is>
-          <t>subj_math</t>
+          <t>subj_hadith</t>
         </is>
       </c>
       <c r="K228" t="inlineStr">
         <is>
-          <t>Math</t>
+          <t>Hadith</t>
         </is>
       </c>
       <c r="L228" t="inlineStr">
         <is>
-          <t>tchr_jhelyn</t>
+          <t>tchr_hainur</t>
         </is>
       </c>
       <c r="M228" t="inlineStr">
         <is>
-          <t>Teacher Jhelyn</t>
+          <t>Ustadha Hainur</t>
         </is>
       </c>
       <c r="N228" t="n">
-        <v>120</v>
+        <v>60</v>
       </c>
     </row>
     <row r="229">
@@ -15480,21 +15480,21 @@
         </is>
       </c>
       <c r="C229" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D229" t="inlineStr">
         <is>
-          <t>01:50 PM – 02:50 PM</t>
+          <t>02:40 PM – 03:40 PM</t>
         </is>
       </c>
       <c r="E229" t="inlineStr">
         <is>
-          <t>sec_k2_umar_ibn_al_khattab_2nd_shift</t>
+          <t>sec_kinder_2_uthman_ibn_affan_1st_shift</t>
         </is>
       </c>
       <c r="F229" t="inlineStr">
         <is>
-          <t>K2 - UMAR IBN AL-KHATTAB (2ND SHIFT)</t>
+          <t>Kinder 2 UTHMAN IBN AFFAN (1ST SHIFT)</t>
         </is>
       </c>
       <c r="G229" t="inlineStr">
@@ -15509,7 +15509,7 @@
       </c>
       <c r="I229" t="inlineStr">
         <is>
-          <t>ODL - 2ND SHIFT</t>
+          <t>ODL - 1ST SHIFT</t>
         </is>
       </c>
       <c r="J229" t="inlineStr">
@@ -15524,12 +15524,12 @@
       </c>
       <c r="L229" t="inlineStr">
         <is>
-          <t>tchr_hainur</t>
+          <t>tchr_saliha</t>
         </is>
       </c>
       <c r="M229" t="inlineStr">
         <is>
-          <t>Ustadha Hainur</t>
+          <t>Ustadha Saliha</t>
         </is>
       </c>
       <c r="N229" t="n">
@@ -15546,21 +15546,21 @@
         </is>
       </c>
       <c r="C230" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D230" t="inlineStr">
         <is>
-          <t>02:40 PM – 03:40 PM</t>
+          <t>03:10 PM – 04:10 PM</t>
         </is>
       </c>
       <c r="E230" t="inlineStr">
         <is>
-          <t>sec_kinder_2_uthman_ibn_affan_1st_shift</t>
+          <t>sec_grade_1_hudhayfah_ibn_al_yam_1st_shift</t>
         </is>
       </c>
       <c r="F230" t="inlineStr">
         <is>
-          <t>Kinder 2 UTHMAN IBN AFFAN (1ST SHIFT)</t>
+          <t>GRADE 1 - HUDHAYFAH IBN AL-YAM (1ST SHIFT)</t>
         </is>
       </c>
       <c r="G230" t="inlineStr">
@@ -15570,7 +15570,7 @@
       </c>
       <c r="H230" t="inlineStr">
         <is>
-          <t>Kinder 2</t>
+          <t>Grade 1</t>
         </is>
       </c>
       <c r="I230" t="inlineStr">
@@ -15580,22 +15580,22 @@
       </c>
       <c r="J230" t="inlineStr">
         <is>
-          <t>subj_hadith</t>
+          <t>subj_math</t>
         </is>
       </c>
       <c r="K230" t="inlineStr">
         <is>
-          <t>Hadith</t>
+          <t>Math</t>
         </is>
       </c>
       <c r="L230" t="inlineStr">
         <is>
-          <t>tchr_saliha</t>
+          <t>tchr_joanna</t>
         </is>
       </c>
       <c r="M230" t="inlineStr">
         <is>
-          <t>Ustadha Saliha</t>
+          <t>Teacher Joanna</t>
         </is>
       </c>
       <c r="N230" t="n">
@@ -15612,7 +15612,7 @@
         </is>
       </c>
       <c r="C231" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D231" t="inlineStr">
         <is>
@@ -15621,12 +15621,12 @@
       </c>
       <c r="E231" t="inlineStr">
         <is>
-          <t>sec_grade_1_hudhayfah_ibn_al_yam_1st_shift</t>
+          <t>sec_grade_1_sa_ad_ibn_abi_waqqaas_2nd_shift</t>
         </is>
       </c>
       <c r="F231" t="inlineStr">
         <is>
-          <t>GRADE 1 - HUDHAYFAH IBN AL-YAM (1ST SHIFT)</t>
+          <t>GRADE 1 - SA'AD IBN ABI WAQQAAS (2ND SHIFT)</t>
         </is>
       </c>
       <c r="G231" t="inlineStr">
@@ -15641,27 +15641,27 @@
       </c>
       <c r="I231" t="inlineStr">
         <is>
-          <t>ODL - 1ST SHIFT</t>
+          <t>ODL - 2ND SHIFT</t>
         </is>
       </c>
       <c r="J231" t="inlineStr">
         <is>
-          <t>subj_math</t>
+          <t>subj_arabic</t>
         </is>
       </c>
       <c r="K231" t="inlineStr">
         <is>
-          <t>Math</t>
+          <t>Arabic</t>
         </is>
       </c>
       <c r="L231" t="inlineStr">
         <is>
-          <t>tchr_joanna</t>
+          <t>tchr_hainur</t>
         </is>
       </c>
       <c r="M231" t="inlineStr">
         <is>
-          <t>Teacher Joanna</t>
+          <t>Ustadha Hainur</t>
         </is>
       </c>
       <c r="N231" t="n">
@@ -15687,12 +15687,12 @@
       </c>
       <c r="E232" t="inlineStr">
         <is>
-          <t>sec_grade_1_sa_ad_ibn_abi_waqqaas_2nd_shift</t>
+          <t>sec_grade_1_suhayb_ar_rumi_2nd_shift</t>
         </is>
       </c>
       <c r="F232" t="inlineStr">
         <is>
-          <t>GRADE 1 - SA'AD IBN ABI WAQQAAS (2ND SHIFT)</t>
+          <t>GRADE 1 - SUHAYB AR-RUMI (2ND SHIFT)</t>
         </is>
       </c>
       <c r="G232" t="inlineStr">
@@ -15712,22 +15712,22 @@
       </c>
       <c r="J232" t="inlineStr">
         <is>
-          <t>subj_arabic</t>
+          <t>subj_language</t>
         </is>
       </c>
       <c r="K232" t="inlineStr">
         <is>
-          <t>Arabic</t>
+          <t>Language</t>
         </is>
       </c>
       <c r="L232" t="inlineStr">
         <is>
-          <t>tchr_hainur</t>
+          <t>tchr_sahdia</t>
         </is>
       </c>
       <c r="M232" t="inlineStr">
         <is>
-          <t>Ustadha Hainur</t>
+          <t>Teacher Sahdia</t>
         </is>
       </c>
       <c r="N232" t="n">
@@ -15753,22 +15753,22 @@
       </c>
       <c r="E233" t="inlineStr">
         <is>
-          <t>sec_grade_1_suhayb_ar_rumi_2nd_shift</t>
+          <t>sec_grade_10_abu_ayyub_al_ansari_2nd_shift_boys</t>
         </is>
       </c>
       <c r="F233" t="inlineStr">
         <is>
-          <t>GRADE 1 - SUHAYB AR-RUMI (2ND SHIFT)</t>
+          <t>GRADE 10 - ABU AYYUB AL-ANSARI (2ND SHIFT) BOYS</t>
         </is>
       </c>
       <c r="G233" t="inlineStr">
         <is>
-          <t>Elementary</t>
+          <t>Junior High School</t>
         </is>
       </c>
       <c r="H233" t="inlineStr">
         <is>
-          <t>Grade 1</t>
+          <t>Grade 10</t>
         </is>
       </c>
       <c r="I233" t="inlineStr">
@@ -15778,22 +15778,22 @@
       </c>
       <c r="J233" t="inlineStr">
         <is>
-          <t>subj_language</t>
+          <t>subj_qur_an</t>
         </is>
       </c>
       <c r="K233" t="inlineStr">
         <is>
-          <t>Language</t>
+          <t>Qur'an</t>
         </is>
       </c>
       <c r="L233" t="inlineStr">
         <is>
-          <t>tchr_sahdia</t>
+          <t>tchr_abdulwahab</t>
         </is>
       </c>
       <c r="M233" t="inlineStr">
         <is>
-          <t>Teacher Sahdia</t>
+          <t>Alim Abdulwahab</t>
         </is>
       </c>
       <c r="N233" t="n">
@@ -15810,7 +15810,7 @@
         </is>
       </c>
       <c r="C234" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D234" t="inlineStr">
         <is>
@@ -15819,12 +15819,12 @@
       </c>
       <c r="E234" t="inlineStr">
         <is>
-          <t>sec_grade_10_abu_ayyub_al_ansari_2nd_shift_boys</t>
+          <t>sec_grade_10_utbah_ibn_ghazwan_1st_shift_girls</t>
         </is>
       </c>
       <c r="F234" t="inlineStr">
         <is>
-          <t>GRADE 10 - ABU AYYUB AL-ANSARI (2ND SHIFT) BOYS</t>
+          <t>GRADE 10 - UTBAH IBN GHAZWAN (1ST SHIFT) GIRLS</t>
         </is>
       </c>
       <c r="G234" t="inlineStr">
@@ -15839,27 +15839,27 @@
       </c>
       <c r="I234" t="inlineStr">
         <is>
-          <t>ODL - 2ND SHIFT</t>
+          <t>ODL - 1ST SHIFT</t>
         </is>
       </c>
       <c r="J234" t="inlineStr">
         <is>
-          <t>subj_qur_an</t>
+          <t>subj_english</t>
         </is>
       </c>
       <c r="K234" t="inlineStr">
         <is>
-          <t>Qur'an</t>
+          <t>English</t>
         </is>
       </c>
       <c r="L234" t="inlineStr">
         <is>
-          <t>tchr_abdulwahab</t>
+          <t>tchr_norhaima</t>
         </is>
       </c>
       <c r="M234" t="inlineStr">
         <is>
-          <t>Alim Abdulwahab</t>
+          <t>Teacher Norhaima</t>
         </is>
       </c>
       <c r="N234" t="n">
@@ -15876,7 +15876,7 @@
         </is>
       </c>
       <c r="C235" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D235" t="inlineStr">
         <is>
@@ -15885,47 +15885,47 @@
       </c>
       <c r="E235" t="inlineStr">
         <is>
-          <t>sec_grade_10_utbah_ibn_ghazwan_1st_shift_girls</t>
+          <t>sec_grade_11_2nd_shift_boys</t>
         </is>
       </c>
       <c r="F235" t="inlineStr">
         <is>
-          <t>GRADE 10 - UTBAH IBN GHAZWAN (1ST SHIFT) GIRLS</t>
+          <t>GRADE 11 (2ND SHIFT BOYS)</t>
         </is>
       </c>
       <c r="G235" t="inlineStr">
         <is>
-          <t>Junior High School</t>
+          <t>Senior High School</t>
         </is>
       </c>
       <c r="H235" t="inlineStr">
         <is>
-          <t>Grade 10</t>
+          <t>Grade 11</t>
         </is>
       </c>
       <c r="I235" t="inlineStr">
         <is>
-          <t>ODL - 1ST SHIFT</t>
+          <t>ODL - 2ND SHIFT</t>
         </is>
       </c>
       <c r="J235" t="inlineStr">
         <is>
-          <t>subj_english</t>
+          <t>subj_mabisang_komunikasyon</t>
         </is>
       </c>
       <c r="K235" t="inlineStr">
         <is>
-          <t>English</t>
+          <t>Mabisang Komunikasyon</t>
         </is>
       </c>
       <c r="L235" t="inlineStr">
         <is>
-          <t>tchr_norhaima</t>
+          <t>tchr_nadzra</t>
         </is>
       </c>
       <c r="M235" t="inlineStr">
         <is>
-          <t>Teacher Norhaima</t>
+          <t>Teacher Nadzra</t>
         </is>
       </c>
       <c r="N235" t="n">
@@ -15951,22 +15951,22 @@
       </c>
       <c r="E236" t="inlineStr">
         <is>
-          <t>sec_grade_11_2nd_shift_boys</t>
+          <t>sec_grade_2_saeed_ibn_zayd_2nd_shift</t>
         </is>
       </c>
       <c r="F236" t="inlineStr">
         <is>
-          <t>GRADE 11 (2ND SHIFT BOYS)</t>
+          <t>GRADE 2 - SAEED IBN ZAYD (2ND SHIFT)</t>
         </is>
       </c>
       <c r="G236" t="inlineStr">
         <is>
-          <t>Senior High School</t>
+          <t>Elementary</t>
         </is>
       </c>
       <c r="H236" t="inlineStr">
         <is>
-          <t>Grade 11</t>
+          <t>Grade 2</t>
         </is>
       </c>
       <c r="I236" t="inlineStr">
@@ -15976,22 +15976,22 @@
       </c>
       <c r="J236" t="inlineStr">
         <is>
-          <t>subj_mabisang_komunikasyon</t>
+          <t>subj_filipino</t>
         </is>
       </c>
       <c r="K236" t="inlineStr">
         <is>
-          <t>Mabisang Komunikasyon</t>
+          <t>Filipino</t>
         </is>
       </c>
       <c r="L236" t="inlineStr">
         <is>
-          <t>tchr_nadzra</t>
+          <t>tchr_zuhora</t>
         </is>
       </c>
       <c r="M236" t="inlineStr">
         <is>
-          <t>Teacher Nadzra</t>
+          <t>Teacher Zuhora</t>
         </is>
       </c>
       <c r="N236" t="n">
@@ -16008,7 +16008,7 @@
         </is>
       </c>
       <c r="C237" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D237" t="inlineStr">
         <is>
@@ -16017,12 +16017,12 @@
       </c>
       <c r="E237" t="inlineStr">
         <is>
-          <t>sec_grade_2_saeed_ibn_zayd_2nd_shift</t>
+          <t>sec_grade_3_salman_al_farsi_1st_shift_mix</t>
         </is>
       </c>
       <c r="F237" t="inlineStr">
         <is>
-          <t>GRADE 2 - SAEED IBN ZAYD (2ND SHIFT)</t>
+          <t>GRADE 3 - SALMAN AL FARSI (1ST SHIFT) MIX</t>
         </is>
       </c>
       <c r="G237" t="inlineStr">
@@ -16032,32 +16032,32 @@
       </c>
       <c r="H237" t="inlineStr">
         <is>
-          <t>Grade 2</t>
+          <t>Grade 3</t>
         </is>
       </c>
       <c r="I237" t="inlineStr">
         <is>
-          <t>ODL - 2ND SHIFT</t>
+          <t>ODL - 1ST SHIFT</t>
         </is>
       </c>
       <c r="J237" t="inlineStr">
         <is>
-          <t>subj_filipino</t>
+          <t>subj_fil3</t>
         </is>
       </c>
       <c r="K237" t="inlineStr">
         <is>
-          <t>Filipino</t>
+          <t>Fil3</t>
         </is>
       </c>
       <c r="L237" t="inlineStr">
         <is>
-          <t>tchr_zuhora</t>
+          <t>tchr_jenny</t>
         </is>
       </c>
       <c r="M237" t="inlineStr">
         <is>
-          <t>Teacher Zuhora</t>
+          <t>Teacher Jenny</t>
         </is>
       </c>
       <c r="N237" t="n">
@@ -16074,7 +16074,7 @@
         </is>
       </c>
       <c r="C238" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D238" t="inlineStr">
         <is>
@@ -16083,12 +16083,12 @@
       </c>
       <c r="E238" t="inlineStr">
         <is>
-          <t>sec_grade_3_salman_al_farsi_1st_shift_mix</t>
+          <t>sec_grade_3_thabit_ibn_qays_2nd_shift_boys</t>
         </is>
       </c>
       <c r="F238" t="inlineStr">
         <is>
-          <t>GRADE 3 - SALMAN AL FARSI (1ST SHIFT) MIX</t>
+          <t>GRADE 3 - THABIT IBN QAYS (2ND SHIFT) - BOYS</t>
         </is>
       </c>
       <c r="G238" t="inlineStr">
@@ -16103,27 +16103,27 @@
       </c>
       <c r="I238" t="inlineStr">
         <is>
-          <t>ODL - 1ST SHIFT</t>
+          <t>ODL - 2ND SHIFT</t>
         </is>
       </c>
       <c r="J238" t="inlineStr">
         <is>
-          <t>subj_fil3</t>
+          <t>subj_math</t>
         </is>
       </c>
       <c r="K238" t="inlineStr">
         <is>
-          <t>Fil3</t>
+          <t>Math</t>
         </is>
       </c>
       <c r="L238" t="inlineStr">
         <is>
-          <t>tchr_jenny</t>
+          <t>tchr_jerlyn</t>
         </is>
       </c>
       <c r="M238" t="inlineStr">
         <is>
-          <t>Teacher Jenny</t>
+          <t>Teacher Jerlyn</t>
         </is>
       </c>
       <c r="N238" t="n">
@@ -16149,12 +16149,12 @@
       </c>
       <c r="E239" t="inlineStr">
         <is>
-          <t>sec_grade_3_thabit_ibn_qays_2nd_shift_boys</t>
+          <t>sec_grade_3_zayd_ibn_haritha_2nd_shift_girls</t>
         </is>
       </c>
       <c r="F239" t="inlineStr">
         <is>
-          <t>GRADE 3 - THABIT IBN QAYS (2ND SHIFT) - BOYS</t>
+          <t>GRADE 3 - ZAYD IBN HARITHA (2ND SHIFT) - GIRLS</t>
         </is>
       </c>
       <c r="G239" t="inlineStr">
@@ -16174,22 +16174,22 @@
       </c>
       <c r="J239" t="inlineStr">
         <is>
-          <t>subj_math</t>
+          <t>subj_english</t>
         </is>
       </c>
       <c r="K239" t="inlineStr">
         <is>
-          <t>Math</t>
+          <t>English</t>
         </is>
       </c>
       <c r="L239" t="inlineStr">
         <is>
-          <t>tchr_jerlyn</t>
+          <t>tchr_marham</t>
         </is>
       </c>
       <c r="M239" t="inlineStr">
         <is>
-          <t>Teacher Jerlyn</t>
+          <t>Teacher Marham</t>
         </is>
       </c>
       <c r="N239" t="n">
@@ -16206,7 +16206,7 @@
         </is>
       </c>
       <c r="C240" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D240" t="inlineStr">
         <is>
@@ -16215,12 +16215,12 @@
       </c>
       <c r="E240" t="inlineStr">
         <is>
-          <t>sec_grade_3_zayd_ibn_haritha_2nd_shift_girls</t>
+          <t>sec_grade_3_ammar_ibn_yasir_1st_shift_boys</t>
         </is>
       </c>
       <c r="F240" t="inlineStr">
         <is>
-          <t>GRADE 3 - ZAYD IBN HARITHA (2ND SHIFT) - GIRLS</t>
+          <t>GRADE 3 -AMMAR IBN YASIR (1ST SHIFT) - BOYS</t>
         </is>
       </c>
       <c r="G240" t="inlineStr">
@@ -16235,27 +16235,27 @@
       </c>
       <c r="I240" t="inlineStr">
         <is>
-          <t>ODL - 2ND SHIFT</t>
+          <t>ODL - 1ST SHIFT</t>
         </is>
       </c>
       <c r="J240" t="inlineStr">
         <is>
-          <t>subj_english</t>
+          <t>subj_shaf</t>
         </is>
       </c>
       <c r="K240" t="inlineStr">
         <is>
-          <t>English</t>
+          <t>SHAF</t>
         </is>
       </c>
       <c r="L240" t="inlineStr">
         <is>
-          <t>tchr_marham</t>
+          <t>tchr_ersahad</t>
         </is>
       </c>
       <c r="M240" t="inlineStr">
         <is>
-          <t>Teacher Marham</t>
+          <t>Ustadh Ersahad</t>
         </is>
       </c>
       <c r="N240" t="n">
@@ -16272,7 +16272,7 @@
         </is>
       </c>
       <c r="C241" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D241" t="inlineStr">
         <is>
@@ -16281,12 +16281,12 @@
       </c>
       <c r="E241" t="inlineStr">
         <is>
-          <t>sec_grade_3_ammar_ibn_yasir_1st_shift_boys</t>
+          <t>sec_grade_4_az_zubair_ibn_al_awwaam_2nd_shift</t>
         </is>
       </c>
       <c r="F241" t="inlineStr">
         <is>
-          <t>GRADE 3 -AMMAR IBN YASIR (1ST SHIFT) - BOYS</t>
+          <t>GRADE 4 - AZ ZUBAIR IBN AL AWWAAM (2ND SHIFT)</t>
         </is>
       </c>
       <c r="G241" t="inlineStr">
@@ -16296,32 +16296,32 @@
       </c>
       <c r="H241" t="inlineStr">
         <is>
-          <t>Grade 3</t>
+          <t>Grade 4</t>
         </is>
       </c>
       <c r="I241" t="inlineStr">
         <is>
-          <t>ODL - 1ST SHIFT</t>
+          <t>ODL - 2ND SHIFT</t>
         </is>
       </c>
       <c r="J241" t="inlineStr">
         <is>
-          <t>subj_shaf</t>
+          <t>subj_filipino</t>
         </is>
       </c>
       <c r="K241" t="inlineStr">
         <is>
-          <t>SHAF</t>
+          <t>Filipino</t>
         </is>
       </c>
       <c r="L241" t="inlineStr">
         <is>
-          <t>tchr_ersahad</t>
+          <t>tchr_norhydie</t>
         </is>
       </c>
       <c r="M241" t="inlineStr">
         <is>
-          <t>Ustadh Ersahad</t>
+          <t>Teacher Norhydie</t>
         </is>
       </c>
       <c r="N241" t="n">
@@ -16338,7 +16338,7 @@
         </is>
       </c>
       <c r="C242" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D242" t="inlineStr">
         <is>
@@ -16347,12 +16347,12 @@
       </c>
       <c r="E242" t="inlineStr">
         <is>
-          <t>sec_grade_4_az_zubair_ibn_al_awwaam_2nd_shift</t>
+          <t>sec_grade_4_hakim_ibn_hazm_1st_shift</t>
         </is>
       </c>
       <c r="F242" t="inlineStr">
         <is>
-          <t>GRADE 4 - AZ ZUBAIR IBN AL AWWAAM (2ND SHIFT)</t>
+          <t>GRADE 4 - HAKIM IBN HAZM(1ST SHIFT)</t>
         </is>
       </c>
       <c r="G242" t="inlineStr">
@@ -16367,27 +16367,27 @@
       </c>
       <c r="I242" t="inlineStr">
         <is>
-          <t>ODL - 2ND SHIFT</t>
+          <t>ODL - 1ST SHIFT</t>
         </is>
       </c>
       <c r="J242" t="inlineStr">
         <is>
-          <t>subj_filipino</t>
+          <t>subj_math</t>
         </is>
       </c>
       <c r="K242" t="inlineStr">
         <is>
-          <t>Filipino</t>
+          <t>Math</t>
         </is>
       </c>
       <c r="L242" t="inlineStr">
         <is>
-          <t>tchr_norhydie</t>
+          <t>tchr_arvin</t>
         </is>
       </c>
       <c r="M242" t="inlineStr">
         <is>
-          <t>Teacher Norhydie</t>
+          <t>Teacher Arvin</t>
         </is>
       </c>
       <c r="N242" t="n">
@@ -16404,7 +16404,7 @@
         </is>
       </c>
       <c r="C243" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D243" t="inlineStr">
         <is>
@@ -16413,12 +16413,12 @@
       </c>
       <c r="E243" t="inlineStr">
         <is>
-          <t>sec_grade_4_hakim_ibn_hazm_1st_shift</t>
+          <t>sec_grade_4_ikrimah_ibn_abi_jahl_2nd_shift</t>
         </is>
       </c>
       <c r="F243" t="inlineStr">
         <is>
-          <t>GRADE 4 - HAKIM IBN HAZM(1ST SHIFT)</t>
+          <t>GRADE 4 - IKRIMAH IBN ABI JAHL (2ND SHIFT)</t>
         </is>
       </c>
       <c r="G243" t="inlineStr">
@@ -16433,27 +16433,27 @@
       </c>
       <c r="I243" t="inlineStr">
         <is>
-          <t>ODL - 1ST SHIFT</t>
+          <t>ODL - 2ND SHIFT</t>
         </is>
       </c>
       <c r="J243" t="inlineStr">
         <is>
-          <t>subj_math</t>
+          <t>subj_tle</t>
         </is>
       </c>
       <c r="K243" t="inlineStr">
         <is>
-          <t>Math</t>
+          <t>TLE</t>
         </is>
       </c>
       <c r="L243" t="inlineStr">
         <is>
-          <t>tchr_arvin</t>
+          <t>tchr_monisa</t>
         </is>
       </c>
       <c r="M243" t="inlineStr">
         <is>
-          <t>Teacher Arvin</t>
+          <t>Teacher Monisa</t>
         </is>
       </c>
       <c r="N243" t="n">
@@ -16479,12 +16479,12 @@
       </c>
       <c r="E244" t="inlineStr">
         <is>
-          <t>sec_grade_4_ikrimah_ibn_abi_jahl_2nd_shift</t>
+          <t>sec_grade_4_hassan_ibn_thabit_2nd_shift_mix</t>
         </is>
       </c>
       <c r="F244" t="inlineStr">
         <is>
-          <t>GRADE 4 - IKRIMAH IBN ABI JAHL (2ND SHIFT)</t>
+          <t>GRADE 4 -HASSAN IBN THABIT (2ND SHIFT) - MIX</t>
         </is>
       </c>
       <c r="G244" t="inlineStr">
@@ -16504,22 +16504,22 @@
       </c>
       <c r="J244" t="inlineStr">
         <is>
-          <t>subj_tle</t>
+          <t>subj_math</t>
         </is>
       </c>
       <c r="K244" t="inlineStr">
         <is>
-          <t>TLE</t>
+          <t>Math</t>
         </is>
       </c>
       <c r="L244" t="inlineStr">
         <is>
-          <t>tchr_monisa</t>
+          <t>tchr_saimonah</t>
         </is>
       </c>
       <c r="M244" t="inlineStr">
         <is>
-          <t>Teacher Monisa</t>
+          <t>Teacher Saimonah</t>
         </is>
       </c>
       <c r="N244" t="n">
@@ -16536,7 +16536,7 @@
         </is>
       </c>
       <c r="C245" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D245" t="inlineStr">
         <is>
@@ -16545,12 +16545,12 @@
       </c>
       <c r="E245" t="inlineStr">
         <is>
-          <t>sec_grade_4_hassan_ibn_thabit_2nd_shift_mix</t>
+          <t>sec_grade_5_ayyash_ibn_abi_rabi_ah_1st_shift</t>
         </is>
       </c>
       <c r="F245" t="inlineStr">
         <is>
-          <t>GRADE 4 -HASSAN IBN THABIT (2ND SHIFT) - MIX</t>
+          <t>GRADE 5 - AYYASH IBN ABI RABI'AH(1ST SHIFT)</t>
         </is>
       </c>
       <c r="G245" t="inlineStr">
@@ -16560,32 +16560,32 @@
       </c>
       <c r="H245" t="inlineStr">
         <is>
-          <t>Grade 4</t>
+          <t>Grade 5</t>
         </is>
       </c>
       <c r="I245" t="inlineStr">
         <is>
-          <t>ODL - 2ND SHIFT</t>
+          <t>ODL - 1ST SHIFT</t>
         </is>
       </c>
       <c r="J245" t="inlineStr">
         <is>
-          <t>subj_math</t>
+          <t>subj_shaf</t>
         </is>
       </c>
       <c r="K245" t="inlineStr">
         <is>
-          <t>Math</t>
+          <t>SHAF</t>
         </is>
       </c>
       <c r="L245" t="inlineStr">
         <is>
-          <t>tchr_saimonah</t>
+          <t>tchr_faidh</t>
         </is>
       </c>
       <c r="M245" t="inlineStr">
         <is>
-          <t>Teacher Saimonah</t>
+          <t>Ustadh Faidh</t>
         </is>
       </c>
       <c r="N245" t="n">
@@ -16611,12 +16611,12 @@
       </c>
       <c r="E246" t="inlineStr">
         <is>
-          <t>sec_grade_5_ayyash_ibn_abi_rabi_ah_1st_shift</t>
+          <t>sec_grade_5_hamza_ibn_abdul_1st_shift</t>
         </is>
       </c>
       <c r="F246" t="inlineStr">
         <is>
-          <t>GRADE 5 - AYYASH IBN ABI RABI'AH(1ST SHIFT)</t>
+          <t>GRADE 5 - HAMZA IBN ABDUL (1ST SHIFT)</t>
         </is>
       </c>
       <c r="G246" t="inlineStr">
@@ -16636,22 +16636,22 @@
       </c>
       <c r="J246" t="inlineStr">
         <is>
-          <t>subj_shaf</t>
+          <t>subj_gmrc</t>
         </is>
       </c>
       <c r="K246" t="inlineStr">
         <is>
-          <t>SHAF</t>
+          <t>GMRC</t>
         </is>
       </c>
       <c r="L246" t="inlineStr">
         <is>
-          <t>tchr_faidh</t>
+          <t>tchr_jairah</t>
         </is>
       </c>
       <c r="M246" t="inlineStr">
         <is>
-          <t>Ustadh Faidh</t>
+          <t>Teacher Jairah</t>
         </is>
       </c>
       <c r="N246" t="n">
@@ -16677,12 +16677,12 @@
       </c>
       <c r="E247" t="inlineStr">
         <is>
-          <t>sec_grade_5_hamza_ibn_abdul_1st_shift</t>
+          <t>sec_grade_5_muhammad_ibn_maslamah_1st_shift</t>
         </is>
       </c>
       <c r="F247" t="inlineStr">
         <is>
-          <t>GRADE 5 - HAMZA IBN ABDUL (1ST SHIFT)</t>
+          <t>GRADE 5 - MUHAMMAD IBN MASLAMAH (1ST SHIFT)</t>
         </is>
       </c>
       <c r="G247" t="inlineStr">
@@ -16702,22 +16702,22 @@
       </c>
       <c r="J247" t="inlineStr">
         <is>
-          <t>subj_gmrc</t>
+          <t>subj_araling_panlipunan</t>
         </is>
       </c>
       <c r="K247" t="inlineStr">
         <is>
-          <t>GMRC</t>
+          <t>Araling Panlipunan</t>
         </is>
       </c>
       <c r="L247" t="inlineStr">
         <is>
-          <t>tchr_jairah</t>
+          <t>tchr_keychell</t>
         </is>
       </c>
       <c r="M247" t="inlineStr">
         <is>
-          <t>Teacher Jairah</t>
+          <t>Teacher Keychell</t>
         </is>
       </c>
       <c r="N247" t="n">
@@ -16734,7 +16734,7 @@
         </is>
       </c>
       <c r="C248" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D248" t="inlineStr">
         <is>
@@ -16743,12 +16743,12 @@
       </c>
       <c r="E248" t="inlineStr">
         <is>
-          <t>sec_grade_5_muhammad_ibn_maslamah_1st_shift</t>
+          <t>sec_grade_5_mus_ab_ibn_abdul_mutalib_2nd_shift</t>
         </is>
       </c>
       <c r="F248" t="inlineStr">
         <is>
-          <t>GRADE 5 - MUHAMMAD IBN MASLAMAH (1ST SHIFT)</t>
+          <t>GRADE 5 - MUS'AB IBN ABDUL MUTALIB (2ND SHIFT)</t>
         </is>
       </c>
       <c r="G248" t="inlineStr">
@@ -16763,27 +16763,27 @@
       </c>
       <c r="I248" t="inlineStr">
         <is>
-          <t>ODL - 1ST SHIFT</t>
+          <t>ODL - 2ND SHIFT</t>
         </is>
       </c>
       <c r="J248" t="inlineStr">
         <is>
-          <t>subj_araling_panlipunan</t>
+          <t>subj_qur_an</t>
         </is>
       </c>
       <c r="K248" t="inlineStr">
         <is>
-          <t>Araling Panlipunan</t>
+          <t>Qur'an</t>
         </is>
       </c>
       <c r="L248" t="inlineStr">
         <is>
-          <t>tchr_keychell</t>
+          <t>tchr_jaisam</t>
         </is>
       </c>
       <c r="M248" t="inlineStr">
         <is>
-          <t>Teacher Keychell</t>
+          <t>Ustadh Jaisam</t>
         </is>
       </c>
       <c r="N248" t="n">
@@ -16800,7 +16800,7 @@
         </is>
       </c>
       <c r="C249" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D249" t="inlineStr">
         <is>
@@ -16809,12 +16809,12 @@
       </c>
       <c r="E249" t="inlineStr">
         <is>
-          <t>sec_grade_5_mus_ab_ibn_abdul_mutalib_2nd_shift</t>
+          <t>sec_grade_6_abbas_ibn_abd_al_muttalib_1st_shift</t>
         </is>
       </c>
       <c r="F249" t="inlineStr">
         <is>
-          <t>GRADE 5 - MUS'AB IBN ABDUL MUTALIB (2ND SHIFT)</t>
+          <t>GRADE 6 - ABBAS IBN ABD AL-MUTTALIB (1ST SHIFT)</t>
         </is>
       </c>
       <c r="G249" t="inlineStr">
@@ -16824,32 +16824,32 @@
       </c>
       <c r="H249" t="inlineStr">
         <is>
-          <t>Grade 5</t>
+          <t>Grade 6</t>
         </is>
       </c>
       <c r="I249" t="inlineStr">
         <is>
-          <t>ODL - 2ND SHIFT</t>
+          <t>ODL - 1ST SHIFT</t>
         </is>
       </c>
       <c r="J249" t="inlineStr">
         <is>
-          <t>subj_qur_an</t>
+          <t>subj_english</t>
         </is>
       </c>
       <c r="K249" t="inlineStr">
         <is>
-          <t>Qur'an</t>
+          <t>English</t>
         </is>
       </c>
       <c r="L249" t="inlineStr">
         <is>
-          <t>tchr_jaisam</t>
+          <t>tchr_jessa</t>
         </is>
       </c>
       <c r="M249" t="inlineStr">
         <is>
-          <t>Ustadh Jaisam</t>
+          <t>Teacher Jessa</t>
         </is>
       </c>
       <c r="N249" t="n">
@@ -16866,7 +16866,7 @@
         </is>
       </c>
       <c r="C250" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D250" t="inlineStr">
         <is>
@@ -16875,12 +16875,12 @@
       </c>
       <c r="E250" t="inlineStr">
         <is>
-          <t>sec_grade_6_abbas_ibn_abd_al_muttalib_1st_shift</t>
+          <t>sec_grade_6_dihya_ibn_khalifah_2nd_shift_girls</t>
         </is>
       </c>
       <c r="F250" t="inlineStr">
         <is>
-          <t>GRADE 6 - ABBAS IBN ABD AL-MUTTALIB (1ST SHIFT)</t>
+          <t>GRADE 6 - DIHYA IBN KHALIFAH (2ND SHIFT) GIRLS</t>
         </is>
       </c>
       <c r="G250" t="inlineStr">
@@ -16895,27 +16895,27 @@
       </c>
       <c r="I250" t="inlineStr">
         <is>
-          <t>ODL - 1ST SHIFT</t>
+          <t>ODL - 2ND SHIFT</t>
         </is>
       </c>
       <c r="J250" t="inlineStr">
         <is>
-          <t>subj_english</t>
+          <t>subj_qur_an</t>
         </is>
       </c>
       <c r="K250" t="inlineStr">
         <is>
-          <t>English</t>
+          <t>Qur'an</t>
         </is>
       </c>
       <c r="L250" t="inlineStr">
         <is>
-          <t>tchr_jessa</t>
+          <t>tchr_obaydah</t>
         </is>
       </c>
       <c r="M250" t="inlineStr">
         <is>
-          <t>Teacher Jessa</t>
+          <t>Ustadh Obaydah</t>
         </is>
       </c>
       <c r="N250" t="n">
@@ -16941,12 +16941,12 @@
       </c>
       <c r="E251" t="inlineStr">
         <is>
-          <t>sec_grade_6_dihya_ibn_khalifah_2nd_shift_girls</t>
+          <t>sec_grade_6_khaleed_ibn_waleed_2nd_shift</t>
         </is>
       </c>
       <c r="F251" t="inlineStr">
         <is>
-          <t>GRADE 6 - DIHYA IBN KHALIFAH (2ND SHIFT) GIRLS</t>
+          <t>GRADE 6 - KHALEED IBN WALEED (2ND SHIFT)</t>
         </is>
       </c>
       <c r="G251" t="inlineStr">
@@ -16966,22 +16966,22 @@
       </c>
       <c r="J251" t="inlineStr">
         <is>
-          <t>subj_qur_an</t>
+          <t>subj_arabic</t>
         </is>
       </c>
       <c r="K251" t="inlineStr">
         <is>
-          <t>Qur'an</t>
+          <t>Arabic</t>
         </is>
       </c>
       <c r="L251" t="inlineStr">
         <is>
-          <t>tchr_obaydah</t>
+          <t>tchr_ali</t>
         </is>
       </c>
       <c r="M251" t="inlineStr">
         <is>
-          <t>Ustadh Obaydah</t>
+          <t>Ustadh Ali</t>
         </is>
       </c>
       <c r="N251" t="n">
@@ -16998,7 +16998,7 @@
         </is>
       </c>
       <c r="C252" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D252" t="inlineStr">
         <is>
@@ -17007,47 +17007,47 @@
       </c>
       <c r="E252" t="inlineStr">
         <is>
-          <t>sec_grade_6_khaleed_ibn_waleed_2nd_shift</t>
+          <t>sec_grade_7_abu_sufyan_ibn_al_harith_1st_shift_boys</t>
         </is>
       </c>
       <c r="F252" t="inlineStr">
         <is>
-          <t>GRADE 6 - KHALEED IBN WALEED (2ND SHIFT)</t>
+          <t>GRADE 7 - ABU SUFYAN IBN AL-HARITH (1ST SHIFT) BOYS</t>
         </is>
       </c>
       <c r="G252" t="inlineStr">
         <is>
-          <t>Elementary</t>
+          <t>Junior High School</t>
         </is>
       </c>
       <c r="H252" t="inlineStr">
         <is>
-          <t>Grade 6</t>
+          <t>Grade 7</t>
         </is>
       </c>
       <c r="I252" t="inlineStr">
         <is>
-          <t>ODL - 2ND SHIFT</t>
+          <t>ODL - 1ST SHIFT</t>
         </is>
       </c>
       <c r="J252" t="inlineStr">
         <is>
-          <t>subj_arabic</t>
+          <t>subj_social_studies</t>
         </is>
       </c>
       <c r="K252" t="inlineStr">
         <is>
-          <t>Arabic</t>
+          <t>Social Studies</t>
         </is>
       </c>
       <c r="L252" t="inlineStr">
         <is>
-          <t>tchr_ali</t>
+          <t>tchr_shirehan</t>
         </is>
       </c>
       <c r="M252" t="inlineStr">
         <is>
-          <t>Ustadh Ali</t>
+          <t>Teacher Shirehan</t>
         </is>
       </c>
       <c r="N252" t="n">
@@ -17064,7 +17064,7 @@
         </is>
       </c>
       <c r="C253" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D253" t="inlineStr">
         <is>
@@ -17073,12 +17073,12 @@
       </c>
       <c r="E253" t="inlineStr">
         <is>
-          <t>sec_grade_7_abu_sufyan_ibn_al_harith_1st_shift_boys</t>
+          <t>sec_grade_7_anas_ibn_malik_2nd_shift_mix</t>
         </is>
       </c>
       <c r="F253" t="inlineStr">
         <is>
-          <t>GRADE 7 - ABU SUFYAN IBN AL-HARITH (1ST SHIFT) BOYS</t>
+          <t>GRADE 7 - ANAS IBN MALIK (2ND SHIFT) - MIX</t>
         </is>
       </c>
       <c r="G253" t="inlineStr">
@@ -17093,27 +17093,27 @@
       </c>
       <c r="I253" t="inlineStr">
         <is>
-          <t>ODL - 1ST SHIFT</t>
+          <t>ODL - 2ND SHIFT</t>
         </is>
       </c>
       <c r="J253" t="inlineStr">
         <is>
-          <t>subj_social_studies</t>
+          <t>subj_gmrc</t>
         </is>
       </c>
       <c r="K253" t="inlineStr">
         <is>
-          <t>Social Studies</t>
+          <t>GMRC</t>
         </is>
       </c>
       <c r="L253" t="inlineStr">
         <is>
-          <t>tchr_shirehan</t>
+          <t>tchr_silfah</t>
         </is>
       </c>
       <c r="M253" t="inlineStr">
         <is>
-          <t>Teacher Shirehan</t>
+          <t>Ustadh Silfah</t>
         </is>
       </c>
       <c r="N253" t="n">
@@ -17130,7 +17130,7 @@
         </is>
       </c>
       <c r="C254" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D254" t="inlineStr">
         <is>
@@ -17139,12 +17139,12 @@
       </c>
       <c r="E254" t="inlineStr">
         <is>
-          <t>sec_grade_7_anas_ibn_malik_2nd_shift_mix</t>
+          <t>sec_grade_7_usama_ibn_zayd_1st_shift_girls</t>
         </is>
       </c>
       <c r="F254" t="inlineStr">
         <is>
-          <t>GRADE 7 - ANAS IBN MALIK (2ND SHIFT) - MIX</t>
+          <t>GRADE 7 - USAMA IBN ZAYD (1ST SHIFT) GIRLS</t>
         </is>
       </c>
       <c r="G254" t="inlineStr">
@@ -17159,27 +17159,27 @@
       </c>
       <c r="I254" t="inlineStr">
         <is>
-          <t>ODL - 2ND SHIFT</t>
+          <t>ODL - 1ST SHIFT</t>
         </is>
       </c>
       <c r="J254" t="inlineStr">
         <is>
-          <t>subj_gmrc</t>
+          <t>subj_science</t>
         </is>
       </c>
       <c r="K254" t="inlineStr">
         <is>
-          <t>GMRC</t>
+          <t>Science</t>
         </is>
       </c>
       <c r="L254" t="inlineStr">
         <is>
-          <t>tchr_silfah</t>
+          <t>tchr_aniah</t>
         </is>
       </c>
       <c r="M254" t="inlineStr">
         <is>
-          <t>Ustadh Silfah</t>
+          <t>Teacher Aniah</t>
         </is>
       </c>
       <c r="N254" t="n">
@@ -17196,7 +17196,7 @@
         </is>
       </c>
       <c r="C255" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D255" t="inlineStr">
         <is>
@@ -17205,12 +17205,12 @@
       </c>
       <c r="E255" t="inlineStr">
         <is>
-          <t>sec_grade_7_usama_ibn_zayd_1st_shift_girls</t>
+          <t>sec_grade_8_mu_adh_ibn_jabal_2nd_shift_boys</t>
         </is>
       </c>
       <c r="F255" t="inlineStr">
         <is>
-          <t>GRADE 7 - USAMA IBN ZAYD (1ST SHIFT) GIRLS</t>
+          <t>GRADE 8 - MU'ADH IBN JABAL (2ND SHIFT) - BOYS</t>
         </is>
       </c>
       <c r="G255" t="inlineStr">
@@ -17220,12 +17220,12 @@
       </c>
       <c r="H255" t="inlineStr">
         <is>
-          <t>Grade 7</t>
+          <t>Grade 8</t>
         </is>
       </c>
       <c r="I255" t="inlineStr">
         <is>
-          <t>ODL - 1ST SHIFT</t>
+          <t>ODL - 2ND SHIFT</t>
         </is>
       </c>
       <c r="J255" t="inlineStr">
@@ -17240,12 +17240,12 @@
       </c>
       <c r="L255" t="inlineStr">
         <is>
-          <t>tchr_aniah</t>
+          <t>tchr_radzmia</t>
         </is>
       </c>
       <c r="M255" t="inlineStr">
         <is>
-          <t>Teacher Aniah</t>
+          <t>Teacher Radzmia</t>
         </is>
       </c>
       <c r="N255" t="n">
@@ -17271,12 +17271,12 @@
       </c>
       <c r="E256" t="inlineStr">
         <is>
-          <t>sec_grade_8_mu_adh_ibn_jabal_2nd_shift_boys</t>
+          <t>sec_grade_8_nuaym_ibn_mas_ud_2nd_shift_mix</t>
         </is>
       </c>
       <c r="F256" t="inlineStr">
         <is>
-          <t>GRADE 8 - MU'ADH IBN JABAL (2ND SHIFT) - BOYS</t>
+          <t>GRADE 8 - NUAYM IBN MAS'UD (2ND SHIFT) MIX</t>
         </is>
       </c>
       <c r="G256" t="inlineStr">
@@ -17296,22 +17296,22 @@
       </c>
       <c r="J256" t="inlineStr">
         <is>
-          <t>subj_science</t>
+          <t>subj_tle</t>
         </is>
       </c>
       <c r="K256" t="inlineStr">
         <is>
-          <t>Science</t>
+          <t>TLE</t>
         </is>
       </c>
       <c r="L256" t="inlineStr">
         <is>
-          <t>tchr_radzmia</t>
+          <t>tchr_halnaisa</t>
         </is>
       </c>
       <c r="M256" t="inlineStr">
         <is>
-          <t>Teacher Radzmia</t>
+          <t>Teacher Halnaisa</t>
         </is>
       </c>
       <c r="N256" t="n">
@@ -17328,7 +17328,7 @@
         </is>
       </c>
       <c r="C257" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D257" t="inlineStr">
         <is>
@@ -17337,12 +17337,12 @@
       </c>
       <c r="E257" t="inlineStr">
         <is>
-          <t>sec_grade_8_nuaym_ibn_mas_ud_2nd_shift_mix</t>
+          <t>sec_grade_8_sa_ad_ibn_mua_dh_1st_shift_girls</t>
         </is>
       </c>
       <c r="F257" t="inlineStr">
         <is>
-          <t>GRADE 8 - NUAYM IBN MAS'UD (2ND SHIFT) MIX</t>
+          <t>GRADE 8 - SA'AD IBN MUA'DH (1ST SHIFT) - GIRLS</t>
         </is>
       </c>
       <c r="G257" t="inlineStr">
@@ -17357,27 +17357,27 @@
       </c>
       <c r="I257" t="inlineStr">
         <is>
-          <t>ODL - 2ND SHIFT</t>
+          <t>ODL - 1ST SHIFT</t>
         </is>
       </c>
       <c r="J257" t="inlineStr">
         <is>
-          <t>subj_tle</t>
+          <t>subj_shaf</t>
         </is>
       </c>
       <c r="K257" t="inlineStr">
         <is>
-          <t>TLE</t>
+          <t>SHAF</t>
         </is>
       </c>
       <c r="L257" t="inlineStr">
         <is>
-          <t>tchr_halnaisa</t>
+          <t>tchr_samsuddin</t>
         </is>
       </c>
       <c r="M257" t="inlineStr">
         <is>
-          <t>Teacher Halnaisa</t>
+          <t>Alim Samsuddin</t>
         </is>
       </c>
       <c r="N257" t="n">
@@ -17394,7 +17394,7 @@
         </is>
       </c>
       <c r="C258" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D258" t="inlineStr">
         <is>
@@ -17403,12 +17403,12 @@
       </c>
       <c r="E258" t="inlineStr">
         <is>
-          <t>sec_grade_8_sa_ad_ibn_mua_dh_1st_shift_girls</t>
+          <t>sec_grade_9_abu_dharr_al_ghifarri_2nd_shift_boys</t>
         </is>
       </c>
       <c r="F258" t="inlineStr">
         <is>
-          <t>GRADE 8 - SA'AD IBN MUA'DH (1ST SHIFT) - GIRLS</t>
+          <t>GRADE 9 - ABU DHARR AL GHIFARRI (2ND SHIFT) BOYS</t>
         </is>
       </c>
       <c r="G258" t="inlineStr">
@@ -17418,32 +17418,32 @@
       </c>
       <c r="H258" t="inlineStr">
         <is>
-          <t>Grade 8</t>
+          <t>Grade 9</t>
         </is>
       </c>
       <c r="I258" t="inlineStr">
         <is>
-          <t>ODL - 1ST SHIFT</t>
+          <t>ODL - 2ND SHIFT</t>
         </is>
       </c>
       <c r="J258" t="inlineStr">
         <is>
-          <t>subj_shaf</t>
+          <t>subj_social_studies</t>
         </is>
       </c>
       <c r="K258" t="inlineStr">
         <is>
-          <t>SHAF</t>
+          <t>Social Science</t>
         </is>
       </c>
       <c r="L258" t="inlineStr">
         <is>
-          <t>tchr_samsuddin</t>
+          <t>tchr_sophia</t>
         </is>
       </c>
       <c r="M258" t="inlineStr">
         <is>
-          <t>Alim Samsuddin</t>
+          <t>Teacher Sophia</t>
         </is>
       </c>
       <c r="N258" t="n">
@@ -17469,12 +17469,12 @@
       </c>
       <c r="E259" t="inlineStr">
         <is>
-          <t>sec_grade_9_abu_dharr_al_ghifarri_2nd_shift_boys</t>
+          <t>sec_grade_9_abu_jandal_ibn_suhayl_2nd_shift_girls</t>
         </is>
       </c>
       <c r="F259" t="inlineStr">
         <is>
-          <t>GRADE 9 - ABU DHARR AL GHIFARRI (2ND SHIFT) BOYS</t>
+          <t>GRADE 9 - ABU JANDAL IBN SUHAYL (2ND SHIFT) GIRLS</t>
         </is>
       </c>
       <c r="G259" t="inlineStr">
@@ -17494,22 +17494,22 @@
       </c>
       <c r="J259" t="inlineStr">
         <is>
-          <t>subj_social_studies</t>
+          <t>subj_tle</t>
         </is>
       </c>
       <c r="K259" t="inlineStr">
         <is>
-          <t>Social Science</t>
+          <t>TLE</t>
         </is>
       </c>
       <c r="L259" t="inlineStr">
         <is>
-          <t>tchr_sophia</t>
+          <t>tchr_angeleni</t>
         </is>
       </c>
       <c r="M259" t="inlineStr">
         <is>
-          <t>Teacher Sophia</t>
+          <t>Teacher Angeleni</t>
         </is>
       </c>
       <c r="N259" t="n">
@@ -17526,21 +17526,21 @@
         </is>
       </c>
       <c r="C260" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D260" t="inlineStr">
         <is>
-          <t>03:10 PM – 04:10 PM</t>
+          <t>04:20 PM – 05:20 PM</t>
         </is>
       </c>
       <c r="E260" t="inlineStr">
         <is>
-          <t>sec_grade_9_abu_jandal_ibn_suhayl_2nd_shift_girls</t>
+          <t>sec_grade_10_abu_ayyub_al_ansari_2nd_shift_boys</t>
         </is>
       </c>
       <c r="F260" t="inlineStr">
         <is>
-          <t>GRADE 9 - ABU JANDAL IBN SUHAYL (2ND SHIFT) GIRLS</t>
+          <t>GRADE 10 - ABU AYYUB AL-ANSARI (2ND SHIFT) BOYS</t>
         </is>
       </c>
       <c r="G260" t="inlineStr">
@@ -17550,7 +17550,7 @@
       </c>
       <c r="H260" t="inlineStr">
         <is>
-          <t>Grade 9</t>
+          <t>Grade 10</t>
         </is>
       </c>
       <c r="I260" t="inlineStr">
@@ -17560,22 +17560,22 @@
       </c>
       <c r="J260" t="inlineStr">
         <is>
-          <t>subj_tle</t>
+          <t>subj_filipino</t>
         </is>
       </c>
       <c r="K260" t="inlineStr">
         <is>
-          <t>TLE</t>
+          <t>Filipino</t>
         </is>
       </c>
       <c r="L260" t="inlineStr">
         <is>
-          <t>tchr_angeleni</t>
+          <t>tchr_nadzra</t>
         </is>
       </c>
       <c r="M260" t="inlineStr">
         <is>
-          <t>Teacher Angeleni</t>
+          <t>Teacher Nadzra</t>
         </is>
       </c>
       <c r="N260" t="n">
@@ -17592,7 +17592,7 @@
         </is>
       </c>
       <c r="C261" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D261" t="inlineStr">
         <is>
@@ -17601,47 +17601,47 @@
       </c>
       <c r="E261" t="inlineStr">
         <is>
-          <t>sec_grade_10_abu_ayyub_al_ansari_2nd_shift_boys</t>
+          <t>sec_grade_11_1st_shift_girls</t>
         </is>
       </c>
       <c r="F261" t="inlineStr">
         <is>
-          <t>GRADE 10 - ABU AYYUB AL-ANSARI (2ND SHIFT) BOYS</t>
+          <t>GRADE 11 (1ST SHIFT GIRLS)</t>
         </is>
       </c>
       <c r="G261" t="inlineStr">
         <is>
-          <t>Junior High School</t>
+          <t>Senior High School</t>
         </is>
       </c>
       <c r="H261" t="inlineStr">
         <is>
-          <t>Grade 10</t>
+          <t>Grade 11</t>
         </is>
       </c>
       <c r="I261" t="inlineStr">
         <is>
-          <t>ODL - 2ND SHIFT</t>
+          <t>ODL - 1ST SHIFT</t>
         </is>
       </c>
       <c r="J261" t="inlineStr">
         <is>
-          <t>subj_filipino</t>
+          <t>subj_gen_bio_1</t>
         </is>
       </c>
       <c r="K261" t="inlineStr">
         <is>
-          <t>Filipino</t>
+          <t>Gen Bio 1</t>
         </is>
       </c>
       <c r="L261" t="inlineStr">
         <is>
-          <t>tchr_nadzra</t>
+          <t>tchr_rowena</t>
         </is>
       </c>
       <c r="M261" t="inlineStr">
         <is>
-          <t>Teacher Nadzra</t>
+          <t>Teacher Rowena</t>
         </is>
       </c>
       <c r="N261" t="n">
@@ -17658,21 +17658,21 @@
         </is>
       </c>
       <c r="C262" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D262" t="inlineStr">
         <is>
-          <t>04:20 PM – 05:20 PM</t>
+          <t>04:20 PM – 06:30 PM</t>
         </is>
       </c>
       <c r="E262" t="inlineStr">
         <is>
-          <t>sec_grade_11_1st_shift_girls</t>
+          <t>sec_grade_11_2nd_shift_boys</t>
         </is>
       </c>
       <c r="F262" t="inlineStr">
         <is>
-          <t>GRADE 11 (1ST SHIFT GIRLS)</t>
+          <t>GRADE 11 (2ND SHIFT BOYS)</t>
         </is>
       </c>
       <c r="G262" t="inlineStr">
@@ -17687,31 +17687,31 @@
       </c>
       <c r="I262" t="inlineStr">
         <is>
-          <t>ODL - 1ST SHIFT</t>
+          <t>ODL - 2ND SHIFT</t>
         </is>
       </c>
       <c r="J262" t="inlineStr">
         <is>
-          <t>subj_gen_bio_1</t>
+          <t>subj_gen_math</t>
         </is>
       </c>
       <c r="K262" t="inlineStr">
         <is>
-          <t>Gen Bio 1</t>
+          <t>Gen Math</t>
         </is>
       </c>
       <c r="L262" t="inlineStr">
         <is>
-          <t>tchr_rowena</t>
+          <t>tchr_jhelyn</t>
         </is>
       </c>
       <c r="M262" t="inlineStr">
         <is>
-          <t>Teacher Rowena</t>
+          <t>Teacher Jhelyn</t>
         </is>
       </c>
       <c r="N262" t="n">
-        <v>60</v>
+        <v>120</v>
       </c>
     </row>
     <row r="263">
@@ -17724,21 +17724,21 @@
         </is>
       </c>
       <c r="C263" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D263" t="inlineStr">
         <is>
-          <t>04:20 PM – 06:30 PM</t>
+          <t>04:20 PM – 05:20 PM</t>
         </is>
       </c>
       <c r="E263" t="inlineStr">
         <is>
-          <t>sec_grade_11_2nd_shift_boys</t>
+          <t>sec_grade_12_abu_musa_al_ashari</t>
         </is>
       </c>
       <c r="F263" t="inlineStr">
         <is>
-          <t>GRADE 11 (2ND SHIFT BOYS)</t>
+          <t>GRADE 12 - ABU MUSA AL-ASHARI</t>
         </is>
       </c>
       <c r="G263" t="inlineStr">
@@ -17748,36 +17748,36 @@
       </c>
       <c r="H263" t="inlineStr">
         <is>
-          <t>Grade 11</t>
+          <t>Grade 12</t>
         </is>
       </c>
       <c r="I263" t="inlineStr">
         <is>
-          <t>ODL - 2ND SHIFT</t>
+          <t>ODL - 1ST SHIFT</t>
         </is>
       </c>
       <c r="J263" t="inlineStr">
         <is>
-          <t>subj_gen_math</t>
+          <t>subj_mil</t>
         </is>
       </c>
       <c r="K263" t="inlineStr">
         <is>
-          <t>Gen Math</t>
+          <t>MIL</t>
         </is>
       </c>
       <c r="L263" t="inlineStr">
         <is>
-          <t>tchr_jhelyn</t>
+          <t>tchr_ethel</t>
         </is>
       </c>
       <c r="M263" t="inlineStr">
         <is>
-          <t>Teacher Jhelyn</t>
+          <t>Teacher Ethel</t>
         </is>
       </c>
       <c r="N263" t="n">
-        <v>120</v>
+        <v>60</v>
       </c>
     </row>
     <row r="264">
@@ -17790,7 +17790,7 @@
         </is>
       </c>
       <c r="C264" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D264" t="inlineStr">
         <is>
@@ -17799,47 +17799,47 @@
       </c>
       <c r="E264" t="inlineStr">
         <is>
-          <t>sec_grade_12_abu_musa_al_ashari</t>
+          <t>sec_grade_2_aasim_ibn_thabit_2nd_shift</t>
         </is>
       </c>
       <c r="F264" t="inlineStr">
         <is>
-          <t>GRADE 12 - ABU MUSA AL-ASHARI</t>
+          <t>GRADE 2 - AASIM IBN THABIT (2ND SHIFT)</t>
         </is>
       </c>
       <c r="G264" t="inlineStr">
         <is>
-          <t>Senior High School</t>
+          <t>Elementary</t>
         </is>
       </c>
       <c r="H264" t="inlineStr">
         <is>
-          <t>Grade 12</t>
+          <t>Grade 2</t>
         </is>
       </c>
       <c r="I264" t="inlineStr">
         <is>
-          <t>ODL - 1ST SHIFT</t>
+          <t>ODL - 2ND SHIFT</t>
         </is>
       </c>
       <c r="J264" t="inlineStr">
         <is>
-          <t>subj_mil</t>
+          <t>subj_makabansa</t>
         </is>
       </c>
       <c r="K264" t="inlineStr">
         <is>
-          <t>MIL</t>
+          <t>Makabansa</t>
         </is>
       </c>
       <c r="L264" t="inlineStr">
         <is>
-          <t>tchr_ethel</t>
+          <t>tchr_monisa</t>
         </is>
       </c>
       <c r="M264" t="inlineStr">
         <is>
-          <t>Teacher Ethel</t>
+          <t>Teacher Monisa</t>
         </is>
       </c>
       <c r="N264" t="n">
@@ -17865,12 +17865,12 @@
       </c>
       <c r="E265" t="inlineStr">
         <is>
-          <t>sec_grade_2_aasim_ibn_thabit_2nd_shift</t>
+          <t>sec_grade_2_saeed_ibn_zayd_2nd_shift</t>
         </is>
       </c>
       <c r="F265" t="inlineStr">
         <is>
-          <t>GRADE 2 - AASIM IBN THABIT (2ND SHIFT)</t>
+          <t>GRADE 2 - SAEED IBN ZAYD (2ND SHIFT)</t>
         </is>
       </c>
       <c r="G265" t="inlineStr">
@@ -17890,22 +17890,22 @@
       </c>
       <c r="J265" t="inlineStr">
         <is>
-          <t>subj_makabansa</t>
+          <t>subj_shaf</t>
         </is>
       </c>
       <c r="K265" t="inlineStr">
         <is>
-          <t>Makabansa</t>
+          <t>SHAF</t>
         </is>
       </c>
       <c r="L265" t="inlineStr">
         <is>
-          <t>tchr_monisa</t>
+          <t>tchr_abdul_karim</t>
         </is>
       </c>
       <c r="M265" t="inlineStr">
         <is>
-          <t>Teacher Monisa</t>
+          <t>Alim Abdul Karim</t>
         </is>
       </c>
       <c r="N265" t="n">
@@ -17931,12 +17931,12 @@
       </c>
       <c r="E266" t="inlineStr">
         <is>
-          <t>sec_grade_2_saeed_ibn_zayd_2nd_shift</t>
+          <t>sec_grade_3_as_ad_ibn_zurarah_2nd_shift_mix</t>
         </is>
       </c>
       <c r="F266" t="inlineStr">
         <is>
-          <t>GRADE 2 - SAEED IBN ZAYD (2ND SHIFT)</t>
+          <t>GRADE 3 - AS'AD IBN ZURARAH (2ND SHIFT) MIX</t>
         </is>
       </c>
       <c r="G266" t="inlineStr">
@@ -17946,7 +17946,7 @@
       </c>
       <c r="H266" t="inlineStr">
         <is>
-          <t>Grade 2</t>
+          <t>Grade 3</t>
         </is>
       </c>
       <c r="I266" t="inlineStr">
@@ -17956,22 +17956,22 @@
       </c>
       <c r="J266" t="inlineStr">
         <is>
-          <t>subj_shaf</t>
+          <t>subj_filipino</t>
         </is>
       </c>
       <c r="K266" t="inlineStr">
         <is>
-          <t>SHAF</t>
+          <t>Filipino</t>
         </is>
       </c>
       <c r="L266" t="inlineStr">
         <is>
-          <t>tchr_abdul_karim</t>
+          <t>tchr_jenny</t>
         </is>
       </c>
       <c r="M266" t="inlineStr">
         <is>
-          <t>Alim Abdul Karim</t>
+          <t>Teacher Jenny</t>
         </is>
       </c>
       <c r="N266" t="n">
@@ -17997,12 +17997,12 @@
       </c>
       <c r="E267" t="inlineStr">
         <is>
-          <t>sec_grade_3_as_ad_ibn_zurarah_2nd_shift_mix</t>
+          <t>sec_grade_3_thabit_ibn_qays_2nd_shift_boys</t>
         </is>
       </c>
       <c r="F267" t="inlineStr">
         <is>
-          <t>GRADE 3 - AS'AD IBN ZURARAH (2ND SHIFT) MIX</t>
+          <t>GRADE 3 - THABIT IBN QAYS (2ND SHIFT) - BOYS</t>
         </is>
       </c>
       <c r="G267" t="inlineStr">
@@ -18022,22 +18022,22 @@
       </c>
       <c r="J267" t="inlineStr">
         <is>
-          <t>subj_filipino</t>
+          <t>subj_arabic</t>
         </is>
       </c>
       <c r="K267" t="inlineStr">
         <is>
-          <t>Filipino</t>
+          <t>Arabic</t>
         </is>
       </c>
       <c r="L267" t="inlineStr">
         <is>
-          <t>tchr_jenny</t>
+          <t>tchr_silfah</t>
         </is>
       </c>
       <c r="M267" t="inlineStr">
         <is>
-          <t>Teacher Jenny</t>
+          <t>Ustadh Silfah</t>
         </is>
       </c>
       <c r="N267" t="n">
@@ -18063,12 +18063,12 @@
       </c>
       <c r="E268" t="inlineStr">
         <is>
-          <t>sec_grade_3_thabit_ibn_qays_2nd_shift_boys</t>
+          <t>sec_grade_4_az_zubair_ibn_al_awwaam_2nd_shift</t>
         </is>
       </c>
       <c r="F268" t="inlineStr">
         <is>
-          <t>GRADE 3 - THABIT IBN QAYS (2ND SHIFT) - BOYS</t>
+          <t>GRADE 4 - AZ ZUBAIR IBN AL AWWAAM (2ND SHIFT)</t>
         </is>
       </c>
       <c r="G268" t="inlineStr">
@@ -18078,7 +18078,7 @@
       </c>
       <c r="H268" t="inlineStr">
         <is>
-          <t>Grade 3</t>
+          <t>Grade 4</t>
         </is>
       </c>
       <c r="I268" t="inlineStr">
@@ -18088,22 +18088,22 @@
       </c>
       <c r="J268" t="inlineStr">
         <is>
-          <t>subj_arabic</t>
+          <t>subj_gmrc</t>
         </is>
       </c>
       <c r="K268" t="inlineStr">
         <is>
-          <t>Arabic</t>
+          <t>GMRC</t>
         </is>
       </c>
       <c r="L268" t="inlineStr">
         <is>
-          <t>tchr_silfah</t>
+          <t>tchr_sahdia</t>
         </is>
       </c>
       <c r="M268" t="inlineStr">
         <is>
-          <t>Ustadh Silfah</t>
+          <t>Teacher Sahdia</t>
         </is>
       </c>
       <c r="N268" t="n">
@@ -18129,12 +18129,12 @@
       </c>
       <c r="E269" t="inlineStr">
         <is>
-          <t>sec_grade_4_az_zubair_ibn_al_awwaam_2nd_shift</t>
+          <t>sec_grade_4_ikrimah_ibn_abi_jahl_2nd_shift</t>
         </is>
       </c>
       <c r="F269" t="inlineStr">
         <is>
-          <t>GRADE 4 - AZ ZUBAIR IBN AL AWWAAM (2ND SHIFT)</t>
+          <t>GRADE 4 - IKRIMAH IBN ABI JAHL (2ND SHIFT)</t>
         </is>
       </c>
       <c r="G269" t="inlineStr">
@@ -18154,22 +18154,22 @@
       </c>
       <c r="J269" t="inlineStr">
         <is>
-          <t>subj_gmrc</t>
+          <t>subj_qur_an</t>
         </is>
       </c>
       <c r="K269" t="inlineStr">
         <is>
-          <t>GMRC</t>
+          <t>Qur'an</t>
         </is>
       </c>
       <c r="L269" t="inlineStr">
         <is>
-          <t>tchr_sahdia</t>
+          <t>tchr_obaydah</t>
         </is>
       </c>
       <c r="M269" t="inlineStr">
         <is>
-          <t>Teacher Sahdia</t>
+          <t>Ustadh Obaydah</t>
         </is>
       </c>
       <c r="N269" t="n">
@@ -18195,12 +18195,12 @@
       </c>
       <c r="E270" t="inlineStr">
         <is>
-          <t>sec_grade_4_ikrimah_ibn_abi_jahl_2nd_shift</t>
+          <t>sec_grade_4_hassan_ibn_thabit_2nd_shift_mix</t>
         </is>
       </c>
       <c r="F270" t="inlineStr">
         <is>
-          <t>GRADE 4 - IKRIMAH IBN ABI JAHL (2ND SHIFT)</t>
+          <t>GRADE 4 -HASSAN IBN THABIT (2ND SHIFT) - MIX</t>
         </is>
       </c>
       <c r="G270" t="inlineStr">
@@ -18220,22 +18220,22 @@
       </c>
       <c r="J270" t="inlineStr">
         <is>
-          <t>subj_qur_an</t>
+          <t>subj_filipino</t>
         </is>
       </c>
       <c r="K270" t="inlineStr">
         <is>
-          <t>Qur'an</t>
+          <t>Filipino</t>
         </is>
       </c>
       <c r="L270" t="inlineStr">
         <is>
-          <t>tchr_obaydah</t>
+          <t>tchr_zuhora</t>
         </is>
       </c>
       <c r="M270" t="inlineStr">
         <is>
-          <t>Ustadh Obaydah</t>
+          <t>Teacher Zuhora</t>
         </is>
       </c>
       <c r="N270" t="n">
@@ -18261,12 +18261,12 @@
       </c>
       <c r="E271" t="inlineStr">
         <is>
-          <t>sec_grade_4_hassan_ibn_thabit_2nd_shift_mix</t>
+          <t>sec_grade_5_al_harith_bin_awf_2nd_shift</t>
         </is>
       </c>
       <c r="F271" t="inlineStr">
         <is>
-          <t>GRADE 4 -HASSAN IBN THABIT (2ND SHIFT) - MIX</t>
+          <t>GRADE 5 - AL HARITH BIN AWF (2ND SHIFT)</t>
         </is>
       </c>
       <c r="G271" t="inlineStr">
@@ -18276,7 +18276,7 @@
       </c>
       <c r="H271" t="inlineStr">
         <is>
-          <t>Grade 4</t>
+          <t>Grade 5</t>
         </is>
       </c>
       <c r="I271" t="inlineStr">
@@ -18286,22 +18286,22 @@
       </c>
       <c r="J271" t="inlineStr">
         <is>
-          <t>subj_filipino</t>
+          <t>subj_arabic</t>
         </is>
       </c>
       <c r="K271" t="inlineStr">
         <is>
-          <t>Filipino</t>
+          <t>Arabic</t>
         </is>
       </c>
       <c r="L271" t="inlineStr">
         <is>
-          <t>tchr_zuhora</t>
+          <t>tchr_ersahad</t>
         </is>
       </c>
       <c r="M271" t="inlineStr">
         <is>
-          <t>Teacher Zuhora</t>
+          <t>Ustadh Ersahad</t>
         </is>
       </c>
       <c r="N271" t="n">
@@ -18327,12 +18327,12 @@
       </c>
       <c r="E272" t="inlineStr">
         <is>
-          <t>sec_grade_5_al_harith_bin_awf_2nd_shift</t>
+          <t>sec_grade_5_ja_far_ibn_abi_talib_2nd_shift_mix</t>
         </is>
       </c>
       <c r="F272" t="inlineStr">
         <is>
-          <t>GRADE 5 - AL HARITH BIN AWF (2ND SHIFT)</t>
+          <t>GRADE 5 - JA'FAR IBN ABI TALIB (2ND SHIFT) - MIX</t>
         </is>
       </c>
       <c r="G272" t="inlineStr">
@@ -18352,22 +18352,22 @@
       </c>
       <c r="J272" t="inlineStr">
         <is>
-          <t>subj_arabic</t>
+          <t>subj_araling_panlipunan</t>
         </is>
       </c>
       <c r="K272" t="inlineStr">
         <is>
-          <t>Arabic</t>
+          <t>Araling Panlipunan</t>
         </is>
       </c>
       <c r="L272" t="inlineStr">
         <is>
-          <t>tchr_ersahad</t>
+          <t>tchr_saimonah</t>
         </is>
       </c>
       <c r="M272" t="inlineStr">
         <is>
-          <t>Ustadh Ersahad</t>
+          <t>Teacher Saimonah</t>
         </is>
       </c>
       <c r="N272" t="n">
@@ -18393,12 +18393,12 @@
       </c>
       <c r="E273" t="inlineStr">
         <is>
-          <t>sec_grade_5_ja_far_ibn_abi_talib_2nd_shift_mix</t>
+          <t>sec_grade_5_mus_ab_ibn_abdul_mutalib_2nd_shift</t>
         </is>
       </c>
       <c r="F273" t="inlineStr">
         <is>
-          <t>GRADE 5 - JA'FAR IBN ABI TALIB (2ND SHIFT) - MIX</t>
+          <t>GRADE 5 - MUS'AB IBN ABDUL MUTALIB (2ND SHIFT)</t>
         </is>
       </c>
       <c r="G273" t="inlineStr">
@@ -18418,22 +18418,22 @@
       </c>
       <c r="J273" t="inlineStr">
         <is>
-          <t>subj_araling_panlipunan</t>
+          <t>subj_mapeh</t>
         </is>
       </c>
       <c r="K273" t="inlineStr">
         <is>
-          <t>Araling Panlipunan</t>
+          <t>MAPEH</t>
         </is>
       </c>
       <c r="L273" t="inlineStr">
         <is>
-          <t>tchr_saimonah</t>
+          <t>tchr_norhydie</t>
         </is>
       </c>
       <c r="M273" t="inlineStr">
         <is>
-          <t>Teacher Saimonah</t>
+          <t>Teacher Norhydie</t>
         </is>
       </c>
       <c r="N273" t="n">
@@ -18459,12 +18459,12 @@
       </c>
       <c r="E274" t="inlineStr">
         <is>
-          <t>sec_grade_5_mus_ab_ibn_abdul_mutalib_2nd_shift</t>
+          <t>sec_grade_6_dihya_ibn_khalifah_2nd_shift_girls</t>
         </is>
       </c>
       <c r="F274" t="inlineStr">
         <is>
-          <t>GRADE 5 - MUS'AB IBN ABDUL MUTALIB (2ND SHIFT)</t>
+          <t>GRADE 6 - DIHYA IBN KHALIFAH (2ND SHIFT) GIRLS</t>
         </is>
       </c>
       <c r="G274" t="inlineStr">
@@ -18474,7 +18474,7 @@
       </c>
       <c r="H274" t="inlineStr">
         <is>
-          <t>Grade 5</t>
+          <t>Grade 6</t>
         </is>
       </c>
       <c r="I274" t="inlineStr">
@@ -18484,22 +18484,22 @@
       </c>
       <c r="J274" t="inlineStr">
         <is>
-          <t>subj_mapeh</t>
+          <t>subj_tle</t>
         </is>
       </c>
       <c r="K274" t="inlineStr">
         <is>
-          <t>MAPEH</t>
+          <t>TLE</t>
         </is>
       </c>
       <c r="L274" t="inlineStr">
         <is>
-          <t>tchr_norhydie</t>
+          <t>tchr_arvin</t>
         </is>
       </c>
       <c r="M274" t="inlineStr">
         <is>
-          <t>Teacher Norhydie</t>
+          <t>Teacher Arvin</t>
         </is>
       </c>
       <c r="N274" t="n">
@@ -18525,12 +18525,12 @@
       </c>
       <c r="E275" t="inlineStr">
         <is>
-          <t>sec_grade_6_dihya_ibn_khalifah_2nd_shift_girls</t>
+          <t>sec_grade_6_khaleed_ibn_waleed_2nd_shift</t>
         </is>
       </c>
       <c r="F275" t="inlineStr">
         <is>
-          <t>GRADE 6 - DIHYA IBN KHALIFAH (2ND SHIFT) GIRLS</t>
+          <t>GRADE 6 - KHALEED IBN WALEED (2ND SHIFT)</t>
         </is>
       </c>
       <c r="G275" t="inlineStr">
@@ -18550,22 +18550,22 @@
       </c>
       <c r="J275" t="inlineStr">
         <is>
-          <t>subj_tle</t>
+          <t>subj_fil</t>
         </is>
       </c>
       <c r="K275" t="inlineStr">
         <is>
-          <t>TLE</t>
+          <t>Fil</t>
         </is>
       </c>
       <c r="L275" t="inlineStr">
         <is>
-          <t>tchr_arvin</t>
+          <t>tchr_normylah</t>
         </is>
       </c>
       <c r="M275" t="inlineStr">
         <is>
-          <t>Teacher Arvin</t>
+          <t>Teacher Normylah</t>
         </is>
       </c>
       <c r="N275" t="n">
@@ -18591,22 +18591,22 @@
       </c>
       <c r="E276" t="inlineStr">
         <is>
-          <t>sec_grade_6_khaleed_ibn_waleed_2nd_shift</t>
+          <t>sec_grade_7_anas_ibn_malik_2nd_shift_mix</t>
         </is>
       </c>
       <c r="F276" t="inlineStr">
         <is>
-          <t>GRADE 6 - KHALEED IBN WALEED (2ND SHIFT)</t>
+          <t>GRADE 7 - ANAS IBN MALIK (2ND SHIFT) - MIX</t>
         </is>
       </c>
       <c r="G276" t="inlineStr">
         <is>
-          <t>Elementary</t>
+          <t>Junior High School</t>
         </is>
       </c>
       <c r="H276" t="inlineStr">
         <is>
-          <t>Grade 6</t>
+          <t>Grade 7</t>
         </is>
       </c>
       <c r="I276" t="inlineStr">
@@ -18616,22 +18616,22 @@
       </c>
       <c r="J276" t="inlineStr">
         <is>
-          <t>subj_fil</t>
+          <t>subj_shaf</t>
         </is>
       </c>
       <c r="K276" t="inlineStr">
         <is>
-          <t>Fil</t>
+          <t>SHAF</t>
         </is>
       </c>
       <c r="L276" t="inlineStr">
         <is>
-          <t>tchr_normylah</t>
+          <t>tchr_samsuddin</t>
         </is>
       </c>
       <c r="M276" t="inlineStr">
         <is>
-          <t>Teacher Normylah</t>
+          <t>Alim Samsuddin</t>
         </is>
       </c>
       <c r="N276" t="n">
@@ -18657,12 +18657,12 @@
       </c>
       <c r="E277" t="inlineStr">
         <is>
-          <t>sec_grade_7_anas_ibn_malik_2nd_shift_mix</t>
+          <t>sec_grade_8_nuaym_ibn_mas_ud_2nd_shift_mix</t>
         </is>
       </c>
       <c r="F277" t="inlineStr">
         <is>
-          <t>GRADE 7 - ANAS IBN MALIK (2ND SHIFT) - MIX</t>
+          <t>GRADE 8 - NUAYM IBN MAS'UD (2ND SHIFT) MIX</t>
         </is>
       </c>
       <c r="G277" t="inlineStr">
@@ -18672,7 +18672,7 @@
       </c>
       <c r="H277" t="inlineStr">
         <is>
-          <t>Grade 7</t>
+          <t>Grade 8</t>
         </is>
       </c>
       <c r="I277" t="inlineStr">
@@ -18682,22 +18682,22 @@
       </c>
       <c r="J277" t="inlineStr">
         <is>
-          <t>subj_shaf</t>
+          <t>subj_arabic</t>
         </is>
       </c>
       <c r="K277" t="inlineStr">
         <is>
-          <t>SHAF</t>
+          <t>Arabic</t>
         </is>
       </c>
       <c r="L277" t="inlineStr">
         <is>
-          <t>tchr_samsuddin</t>
+          <t>tchr_ali</t>
         </is>
       </c>
       <c r="M277" t="inlineStr">
         <is>
-          <t>Alim Samsuddin</t>
+          <t>Ustadh Ali</t>
         </is>
       </c>
       <c r="N277" t="n">
@@ -18723,12 +18723,12 @@
       </c>
       <c r="E278" t="inlineStr">
         <is>
-          <t>sec_grade_8_nuaym_ibn_mas_ud_2nd_shift_mix</t>
+          <t>sec_grade_9_abu_dharr_al_ghifarri_2nd_shift_boys</t>
         </is>
       </c>
       <c r="F278" t="inlineStr">
         <is>
-          <t>GRADE 8 - NUAYM IBN MAS'UD (2ND SHIFT) MIX</t>
+          <t>GRADE 9 - ABU DHARR AL GHIFARRI (2ND SHIFT) BOYS</t>
         </is>
       </c>
       <c r="G278" t="inlineStr">
@@ -18738,7 +18738,7 @@
       </c>
       <c r="H278" t="inlineStr">
         <is>
-          <t>Grade 8</t>
+          <t>Grade 9</t>
         </is>
       </c>
       <c r="I278" t="inlineStr">
@@ -18748,22 +18748,22 @@
       </c>
       <c r="J278" t="inlineStr">
         <is>
-          <t>subj_arabic</t>
+          <t>subj_english</t>
         </is>
       </c>
       <c r="K278" t="inlineStr">
         <is>
-          <t>Arabic</t>
+          <t>English</t>
         </is>
       </c>
       <c r="L278" t="inlineStr">
         <is>
-          <t>tchr_ali</t>
+          <t>tchr_norhaima</t>
         </is>
       </c>
       <c r="M278" t="inlineStr">
         <is>
-          <t>Ustadh Ali</t>
+          <t>Teacher Norhaima</t>
         </is>
       </c>
       <c r="N278" t="n">
@@ -18789,12 +18789,12 @@
       </c>
       <c r="E279" t="inlineStr">
         <is>
-          <t>sec_grade_9_abu_dharr_al_ghifarri_2nd_shift_boys</t>
+          <t>sec_grade_9_abu_jandal_ibn_suhayl_2nd_shift_girls</t>
         </is>
       </c>
       <c r="F279" t="inlineStr">
         <is>
-          <t>GRADE 9 - ABU DHARR AL GHIFARRI (2ND SHIFT) BOYS</t>
+          <t>GRADE 9 - ABU JANDAL IBN SUHAYL (2ND SHIFT) GIRLS</t>
         </is>
       </c>
       <c r="G279" t="inlineStr">
@@ -18814,22 +18814,22 @@
       </c>
       <c r="J279" t="inlineStr">
         <is>
-          <t>subj_english</t>
+          <t>subj_social_studies</t>
         </is>
       </c>
       <c r="K279" t="inlineStr">
         <is>
-          <t>English</t>
+          <t>Social Science</t>
         </is>
       </c>
       <c r="L279" t="inlineStr">
         <is>
-          <t>tchr_norhaima</t>
+          <t>tchr_sophia</t>
         </is>
       </c>
       <c r="M279" t="inlineStr">
         <is>
-          <t>Teacher Norhaima</t>
+          <t>Teacher Sophia</t>
         </is>
       </c>
       <c r="N279" t="n">
@@ -18855,22 +18855,22 @@
       </c>
       <c r="E280" t="inlineStr">
         <is>
-          <t>sec_grade_9_abu_jandal_ibn_suhayl_2nd_shift_girls</t>
+          <t>sec_k1_husain_ibn_ali_2nd_shift</t>
         </is>
       </c>
       <c r="F280" t="inlineStr">
         <is>
-          <t>GRADE 9 - ABU JANDAL IBN SUHAYL (2ND SHIFT) GIRLS</t>
+          <t>K1 - HUSAIN IBN ALI (2ND SHIFT)</t>
         </is>
       </c>
       <c r="G280" t="inlineStr">
         <is>
-          <t>Junior High School</t>
+          <t>Elementary</t>
         </is>
       </c>
       <c r="H280" t="inlineStr">
         <is>
-          <t>Grade 9</t>
+          <t>Kinder 1</t>
         </is>
       </c>
       <c r="I280" t="inlineStr">
@@ -18880,22 +18880,22 @@
       </c>
       <c r="J280" t="inlineStr">
         <is>
-          <t>subj_social_studies</t>
+          <t>subj_hadith</t>
         </is>
       </c>
       <c r="K280" t="inlineStr">
         <is>
-          <t>Social Science</t>
+          <t>Hadith</t>
         </is>
       </c>
       <c r="L280" t="inlineStr">
         <is>
-          <t>tchr_sophia</t>
+          <t>tchr_hainur</t>
         </is>
       </c>
       <c r="M280" t="inlineStr">
         <is>
-          <t>Teacher Sophia</t>
+          <t>Ustadha Hainur</t>
         </is>
       </c>
       <c r="N280" t="n">
@@ -18921,12 +18921,12 @@
       </c>
       <c r="E281" t="inlineStr">
         <is>
-          <t>sec_k1_husain_ibn_ali_2nd_shift</t>
+          <t>sec_k2_abdullah_ibn_mas_ud_2nd_shift</t>
         </is>
       </c>
       <c r="F281" t="inlineStr">
         <is>
-          <t>K1 - HUSAIN IBN ALI (2ND SHIFT)</t>
+          <t>K2 - ABDULLAH IBN MAS'UD (2ND SHIFT)</t>
         </is>
       </c>
       <c r="G281" t="inlineStr">
@@ -18936,7 +18936,7 @@
       </c>
       <c r="H281" t="inlineStr">
         <is>
-          <t>Kinder 1</t>
+          <t>Kinder 2</t>
         </is>
       </c>
       <c r="I281" t="inlineStr">
@@ -18946,22 +18946,22 @@
       </c>
       <c r="J281" t="inlineStr">
         <is>
-          <t>subj_hadith</t>
+          <t>subj_oral_written_exam</t>
         </is>
       </c>
       <c r="K281" t="inlineStr">
         <is>
-          <t>Hadith</t>
+          <t>Oral &amp; Written Exam</t>
         </is>
       </c>
       <c r="L281" t="inlineStr">
         <is>
-          <t>tchr_hainur</t>
+          <t>tchr_ayah</t>
         </is>
       </c>
       <c r="M281" t="inlineStr">
         <is>
-          <t>Ustadha Hainur</t>
+          <t>Teacher Ayah</t>
         </is>
       </c>
       <c r="N281" t="n">
@@ -18987,12 +18987,12 @@
       </c>
       <c r="E282" t="inlineStr">
         <is>
-          <t>sec_k2_abdullah_ibn_mas_ud_2nd_shift</t>
+          <t>sec_kinder_2_khabaab_ibn_arat_2nd_shift</t>
         </is>
       </c>
       <c r="F282" t="inlineStr">
         <is>
-          <t>K2 - ABDULLAH IBN MAS'UD (2ND SHIFT)</t>
+          <t>Kinder 2 KHABAAB IBN ARAT (2ND SHIFT)</t>
         </is>
       </c>
       <c r="G282" t="inlineStr">
@@ -19012,22 +19012,22 @@
       </c>
       <c r="J282" t="inlineStr">
         <is>
-          <t>subj_oral_written_exam</t>
+          <t>subj_hadith</t>
         </is>
       </c>
       <c r="K282" t="inlineStr">
         <is>
-          <t>Oral &amp; Written Exam</t>
+          <t>Hadith</t>
         </is>
       </c>
       <c r="L282" t="inlineStr">
         <is>
-          <t>tchr_ayah</t>
+          <t>tchr_faidh</t>
         </is>
       </c>
       <c r="M282" t="inlineStr">
         <is>
-          <t>Teacher Ayah</t>
+          <t>Ustadh Faidh</t>
         </is>
       </c>
       <c r="N282" t="n">
@@ -19044,21 +19044,21 @@
         </is>
       </c>
       <c r="C283" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D283" t="inlineStr">
         <is>
-          <t>04:20 PM – 05:20 PM</t>
+          <t>05:30 PM – 06:30 PM</t>
         </is>
       </c>
       <c r="E283" t="inlineStr">
         <is>
-          <t>sec_kinder_2_khabaab_ibn_arat_2nd_shift</t>
+          <t>sec_grade_1_sa_ad_ibn_abi_waqqaas_2nd_shift</t>
         </is>
       </c>
       <c r="F283" t="inlineStr">
         <is>
-          <t>Kinder 2 KHABAAB IBN ARAT (2ND SHIFT)</t>
+          <t>GRADE 1 - SA'AD IBN ABI WAQQAAS (2ND SHIFT)</t>
         </is>
       </c>
       <c r="G283" t="inlineStr">
@@ -19068,7 +19068,7 @@
       </c>
       <c r="H283" t="inlineStr">
         <is>
-          <t>Kinder 2</t>
+          <t>Grade 1</t>
         </is>
       </c>
       <c r="I283" t="inlineStr">
@@ -19078,22 +19078,22 @@
       </c>
       <c r="J283" t="inlineStr">
         <is>
-          <t>subj_hadith</t>
+          <t>subj_math</t>
         </is>
       </c>
       <c r="K283" t="inlineStr">
         <is>
-          <t>Hadith</t>
+          <t>Math</t>
         </is>
       </c>
       <c r="L283" t="inlineStr">
         <is>
-          <t>tchr_faidh</t>
+          <t>tchr_joanna</t>
         </is>
       </c>
       <c r="M283" t="inlineStr">
         <is>
-          <t>Ustadh Faidh</t>
+          <t>Teacher Joanna</t>
         </is>
       </c>
       <c r="N283" t="n">
@@ -19119,12 +19119,12 @@
       </c>
       <c r="E284" t="inlineStr">
         <is>
-          <t>sec_grade_1_sa_ad_ibn_abi_waqqaas_2nd_shift</t>
+          <t>sec_grade_1_suhayb_ar_rumi_2nd_shift</t>
         </is>
       </c>
       <c r="F284" t="inlineStr">
         <is>
-          <t>GRADE 1 - SA'AD IBN ABI WAQQAAS (2ND SHIFT)</t>
+          <t>GRADE 1 - SUHAYB AR-RUMI (2ND SHIFT)</t>
         </is>
       </c>
       <c r="G284" t="inlineStr">
@@ -19144,22 +19144,22 @@
       </c>
       <c r="J284" t="inlineStr">
         <is>
-          <t>subj_math</t>
+          <t>subj_reading_literacy</t>
         </is>
       </c>
       <c r="K284" t="inlineStr">
         <is>
-          <t>Math</t>
+          <t>Reading &amp; Literacy</t>
         </is>
       </c>
       <c r="L284" t="inlineStr">
         <is>
-          <t>tchr_joanna</t>
+          <t>tchr_katrina</t>
         </is>
       </c>
       <c r="M284" t="inlineStr">
         <is>
-          <t>Teacher Joanna</t>
+          <t>Teacher Katrina</t>
         </is>
       </c>
       <c r="N284" t="n">
@@ -19185,22 +19185,22 @@
       </c>
       <c r="E285" t="inlineStr">
         <is>
-          <t>sec_grade_1_suhayb_ar_rumi_2nd_shift</t>
+          <t>sec_grade_10_abu_ayyub_al_ansari_2nd_shift_boys</t>
         </is>
       </c>
       <c r="F285" t="inlineStr">
         <is>
-          <t>GRADE 1 - SUHAYB AR-RUMI (2ND SHIFT)</t>
+          <t>GRADE 10 - ABU AYYUB AL-ANSARI (2ND SHIFT) BOYS</t>
         </is>
       </c>
       <c r="G285" t="inlineStr">
         <is>
-          <t>Elementary</t>
+          <t>Junior High School</t>
         </is>
       </c>
       <c r="H285" t="inlineStr">
         <is>
-          <t>Grade 1</t>
+          <t>Grade 10</t>
         </is>
       </c>
       <c r="I285" t="inlineStr">
@@ -19210,22 +19210,22 @@
       </c>
       <c r="J285" t="inlineStr">
         <is>
-          <t>subj_reading_literacy</t>
+          <t>subj_shaf</t>
         </is>
       </c>
       <c r="K285" t="inlineStr">
         <is>
-          <t>Reading &amp; Literacy</t>
+          <t>SHAF</t>
         </is>
       </c>
       <c r="L285" t="inlineStr">
         <is>
-          <t>tchr_katrina</t>
+          <t>tchr_bustamante</t>
         </is>
       </c>
       <c r="M285" t="inlineStr">
         <is>
-          <t>Teacher Katrina</t>
+          <t>Alim Bustamante</t>
         </is>
       </c>
       <c r="N285" t="n">
@@ -19251,22 +19251,22 @@
       </c>
       <c r="E286" t="inlineStr">
         <is>
-          <t>sec_grade_10_abu_ayyub_al_ansari_2nd_shift_boys</t>
+          <t>sec_grade_2_aasim_ibn_thabit_2nd_shift</t>
         </is>
       </c>
       <c r="F286" t="inlineStr">
         <is>
-          <t>GRADE 10 - ABU AYYUB AL-ANSARI (2ND SHIFT) BOYS</t>
+          <t>GRADE 2 - AASIM IBN THABIT (2ND SHIFT)</t>
         </is>
       </c>
       <c r="G286" t="inlineStr">
         <is>
-          <t>Junior High School</t>
+          <t>Elementary</t>
         </is>
       </c>
       <c r="H286" t="inlineStr">
         <is>
-          <t>Grade 10</t>
+          <t>Grade 2</t>
         </is>
       </c>
       <c r="I286" t="inlineStr">
@@ -19276,22 +19276,22 @@
       </c>
       <c r="J286" t="inlineStr">
         <is>
-          <t>subj_shaf</t>
+          <t>subj_arabic</t>
         </is>
       </c>
       <c r="K286" t="inlineStr">
         <is>
-          <t>SHAF</t>
+          <t>Arabic</t>
         </is>
       </c>
       <c r="L286" t="inlineStr">
         <is>
-          <t>tchr_bustamante</t>
+          <t>tchr_hainur</t>
         </is>
       </c>
       <c r="M286" t="inlineStr">
         <is>
-          <t>Alim Bustamante</t>
+          <t>Ustadha Hainur</t>
         </is>
       </c>
       <c r="N286" t="n">
@@ -19317,12 +19317,12 @@
       </c>
       <c r="E287" t="inlineStr">
         <is>
-          <t>sec_grade_2_aasim_ibn_thabit_2nd_shift</t>
+          <t>sec_grade_2_saeed_ibn_zayd_2nd_shift</t>
         </is>
       </c>
       <c r="F287" t="inlineStr">
         <is>
-          <t>GRADE 2 - AASIM IBN THABIT (2ND SHIFT)</t>
+          <t>GRADE 2 - SAEED IBN ZAYD (2ND SHIFT)</t>
         </is>
       </c>
       <c r="G287" t="inlineStr">
@@ -19342,22 +19342,22 @@
       </c>
       <c r="J287" t="inlineStr">
         <is>
-          <t>subj_arabic</t>
+          <t>subj_makabansa</t>
         </is>
       </c>
       <c r="K287" t="inlineStr">
         <is>
-          <t>Arabic</t>
+          <t>Makabansa</t>
         </is>
       </c>
       <c r="L287" t="inlineStr">
         <is>
-          <t>tchr_hainur</t>
+          <t>tchr_monisa</t>
         </is>
       </c>
       <c r="M287" t="inlineStr">
         <is>
-          <t>Ustadha Hainur</t>
+          <t>Teacher Monisa</t>
         </is>
       </c>
       <c r="N287" t="n">
@@ -19383,12 +19383,12 @@
       </c>
       <c r="E288" t="inlineStr">
         <is>
-          <t>sec_grade_2_saeed_ibn_zayd_2nd_shift</t>
+          <t>sec_grade_3_as_ad_ibn_zurarah_2nd_shift_mix</t>
         </is>
       </c>
       <c r="F288" t="inlineStr">
         <is>
-          <t>GRADE 2 - SAEED IBN ZAYD (2ND SHIFT)</t>
+          <t>GRADE 3 - AS'AD IBN ZURARAH (2ND SHIFT) MIX</t>
         </is>
       </c>
       <c r="G288" t="inlineStr">
@@ -19398,7 +19398,7 @@
       </c>
       <c r="H288" t="inlineStr">
         <is>
-          <t>Grade 2</t>
+          <t>Grade 3</t>
         </is>
       </c>
       <c r="I288" t="inlineStr">
@@ -19408,22 +19408,22 @@
       </c>
       <c r="J288" t="inlineStr">
         <is>
-          <t>subj_makabansa</t>
+          <t>subj_science</t>
         </is>
       </c>
       <c r="K288" t="inlineStr">
         <is>
-          <t>Makabansa</t>
+          <t>Science</t>
         </is>
       </c>
       <c r="L288" t="inlineStr">
         <is>
-          <t>tchr_monisa</t>
+          <t>tchr_saimonah</t>
         </is>
       </c>
       <c r="M288" t="inlineStr">
         <is>
-          <t>Teacher Monisa</t>
+          <t>Teacher Saimonah</t>
         </is>
       </c>
       <c r="N288" t="n">
@@ -19449,12 +19449,12 @@
       </c>
       <c r="E289" t="inlineStr">
         <is>
-          <t>sec_grade_3_as_ad_ibn_zurarah_2nd_shift_mix</t>
+          <t>sec_grade_3_thabit_ibn_qays_2nd_shift_boys</t>
         </is>
       </c>
       <c r="F289" t="inlineStr">
         <is>
-          <t>GRADE 3 - AS'AD IBN ZURARAH (2ND SHIFT) MIX</t>
+          <t>GRADE 3 - THABIT IBN QAYS (2ND SHIFT) - BOYS</t>
         </is>
       </c>
       <c r="G289" t="inlineStr">
@@ -19474,22 +19474,22 @@
       </c>
       <c r="J289" t="inlineStr">
         <is>
-          <t>subj_science</t>
+          <t>subj_english</t>
         </is>
       </c>
       <c r="K289" t="inlineStr">
         <is>
-          <t>Science</t>
+          <t>English</t>
         </is>
       </c>
       <c r="L289" t="inlineStr">
         <is>
-          <t>tchr_saimonah</t>
+          <t>tchr_marham</t>
         </is>
       </c>
       <c r="M289" t="inlineStr">
         <is>
-          <t>Teacher Saimonah</t>
+          <t>Teacher Marham</t>
         </is>
       </c>
       <c r="N289" t="n">
@@ -19515,12 +19515,12 @@
       </c>
       <c r="E290" t="inlineStr">
         <is>
-          <t>sec_grade_3_thabit_ibn_qays_2nd_shift_boys</t>
+          <t>sec_grade_3_zayd_ibn_haritha_2nd_shift_girls</t>
         </is>
       </c>
       <c r="F290" t="inlineStr">
         <is>
-          <t>GRADE 3 - THABIT IBN QAYS (2ND SHIFT) - BOYS</t>
+          <t>GRADE 3 - ZAYD IBN HARITHA (2ND SHIFT) - GIRLS</t>
         </is>
       </c>
       <c r="G290" t="inlineStr">
@@ -19540,22 +19540,22 @@
       </c>
       <c r="J290" t="inlineStr">
         <is>
-          <t>subj_english</t>
+          <t>subj_math</t>
         </is>
       </c>
       <c r="K290" t="inlineStr">
         <is>
-          <t>English</t>
+          <t>Math</t>
         </is>
       </c>
       <c r="L290" t="inlineStr">
         <is>
-          <t>tchr_marham</t>
+          <t>tchr_jerlyn</t>
         </is>
       </c>
       <c r="M290" t="inlineStr">
         <is>
-          <t>Teacher Marham</t>
+          <t>Teacher Jerlyn</t>
         </is>
       </c>
       <c r="N290" t="n">
@@ -19581,12 +19581,12 @@
       </c>
       <c r="E291" t="inlineStr">
         <is>
-          <t>sec_grade_3_zayd_ibn_haritha_2nd_shift_girls</t>
+          <t>sec_grade_4_az_zubair_ibn_al_awwaam_2nd_shift</t>
         </is>
       </c>
       <c r="F291" t="inlineStr">
         <is>
-          <t>GRADE 3 - ZAYD IBN HARITHA (2ND SHIFT) - GIRLS</t>
+          <t>GRADE 4 - AZ ZUBAIR IBN AL AWWAAM (2ND SHIFT)</t>
         </is>
       </c>
       <c r="G291" t="inlineStr">
@@ -19596,7 +19596,7 @@
       </c>
       <c r="H291" t="inlineStr">
         <is>
-          <t>Grade 3</t>
+          <t>Grade 4</t>
         </is>
       </c>
       <c r="I291" t="inlineStr">
@@ -19606,22 +19606,22 @@
       </c>
       <c r="J291" t="inlineStr">
         <is>
-          <t>subj_math</t>
+          <t>subj_mapeh</t>
         </is>
       </c>
       <c r="K291" t="inlineStr">
         <is>
-          <t>Math</t>
+          <t>MAPEH</t>
         </is>
       </c>
       <c r="L291" t="inlineStr">
         <is>
-          <t>tchr_jerlyn</t>
+          <t>tchr_halnaisa</t>
         </is>
       </c>
       <c r="M291" t="inlineStr">
         <is>
-          <t>Teacher Jerlyn</t>
+          <t>Teacher Halnaisa</t>
         </is>
       </c>
       <c r="N291" t="n">
@@ -19647,12 +19647,12 @@
       </c>
       <c r="E292" t="inlineStr">
         <is>
-          <t>sec_grade_4_az_zubair_ibn_al_awwaam_2nd_shift</t>
+          <t>sec_grade_4_ikrimah_ibn_abi_jahl_2nd_shift</t>
         </is>
       </c>
       <c r="F292" t="inlineStr">
         <is>
-          <t>GRADE 4 - AZ ZUBAIR IBN AL AWWAAM (2ND SHIFT)</t>
+          <t>GRADE 4 - IKRIMAH IBN ABI JAHL (2ND SHIFT)</t>
         </is>
       </c>
       <c r="G292" t="inlineStr">
@@ -19672,22 +19672,22 @@
       </c>
       <c r="J292" t="inlineStr">
         <is>
-          <t>subj_mapeh</t>
+          <t>subj_gmrc</t>
         </is>
       </c>
       <c r="K292" t="inlineStr">
         <is>
-          <t>MAPEH</t>
+          <t>GMRC</t>
         </is>
       </c>
       <c r="L292" t="inlineStr">
         <is>
-          <t>tchr_halnaisa</t>
+          <t>tchr_sahdia</t>
         </is>
       </c>
       <c r="M292" t="inlineStr">
         <is>
-          <t>Teacher Halnaisa</t>
+          <t>Teacher Sahdia</t>
         </is>
       </c>
       <c r="N292" t="n">
@@ -19713,12 +19713,12 @@
       </c>
       <c r="E293" t="inlineStr">
         <is>
-          <t>sec_grade_4_ikrimah_ibn_abi_jahl_2nd_shift</t>
+          <t>sec_grade_5_al_harith_bin_awf_2nd_shift</t>
         </is>
       </c>
       <c r="F293" t="inlineStr">
         <is>
-          <t>GRADE 4 - IKRIMAH IBN ABI JAHL (2ND SHIFT)</t>
+          <t>GRADE 5 - AL HARITH BIN AWF (2ND SHIFT)</t>
         </is>
       </c>
       <c r="G293" t="inlineStr">
@@ -19728,7 +19728,7 @@
       </c>
       <c r="H293" t="inlineStr">
         <is>
-          <t>Grade 4</t>
+          <t>Grade 5</t>
         </is>
       </c>
       <c r="I293" t="inlineStr">
@@ -19738,22 +19738,22 @@
       </c>
       <c r="J293" t="inlineStr">
         <is>
-          <t>subj_gmrc</t>
+          <t>subj_science</t>
         </is>
       </c>
       <c r="K293" t="inlineStr">
         <is>
-          <t>GMRC</t>
+          <t>Science</t>
         </is>
       </c>
       <c r="L293" t="inlineStr">
         <is>
-          <t>tchr_sahdia</t>
+          <t>tchr_anna</t>
         </is>
       </c>
       <c r="M293" t="inlineStr">
         <is>
-          <t>Teacher Sahdia</t>
+          <t>Teacher Anna</t>
         </is>
       </c>
       <c r="N293" t="n">
@@ -19779,12 +19779,12 @@
       </c>
       <c r="E294" t="inlineStr">
         <is>
-          <t>sec_grade_5_al_harith_bin_awf_2nd_shift</t>
+          <t>sec_grade_5_ja_far_ibn_abi_talib_2nd_shift_mix</t>
         </is>
       </c>
       <c r="F294" t="inlineStr">
         <is>
-          <t>GRADE 5 - AL HARITH BIN AWF (2ND SHIFT)</t>
+          <t>GRADE 5 - JA'FAR IBN ABI TALIB (2ND SHIFT) - MIX</t>
         </is>
       </c>
       <c r="G294" t="inlineStr">
@@ -19804,22 +19804,22 @@
       </c>
       <c r="J294" t="inlineStr">
         <is>
-          <t>subj_science</t>
+          <t>subj_tle</t>
         </is>
       </c>
       <c r="K294" t="inlineStr">
         <is>
-          <t>Science</t>
+          <t>TLE</t>
         </is>
       </c>
       <c r="L294" t="inlineStr">
         <is>
-          <t>tchr_anna</t>
+          <t>tchr_jenny</t>
         </is>
       </c>
       <c r="M294" t="inlineStr">
         <is>
-          <t>Teacher Anna</t>
+          <t>Teacher Jenny</t>
         </is>
       </c>
       <c r="N294" t="n">
@@ -19845,12 +19845,12 @@
       </c>
       <c r="E295" t="inlineStr">
         <is>
-          <t>sec_grade_5_ja_far_ibn_abi_talib_2nd_shift_mix</t>
+          <t>sec_grade_5_mus_ab_ibn_abdul_mutalib_2nd_shift</t>
         </is>
       </c>
       <c r="F295" t="inlineStr">
         <is>
-          <t>GRADE 5 - JA'FAR IBN ABI TALIB (2ND SHIFT) - MIX</t>
+          <t>GRADE 5 - MUS'AB IBN ABDUL MUTALIB (2ND SHIFT)</t>
         </is>
       </c>
       <c r="G295" t="inlineStr">
@@ -19870,22 +19870,22 @@
       </c>
       <c r="J295" t="inlineStr">
         <is>
-          <t>subj_tle</t>
+          <t>subj_english</t>
         </is>
       </c>
       <c r="K295" t="inlineStr">
         <is>
-          <t>TLE</t>
+          <t>English</t>
         </is>
       </c>
       <c r="L295" t="inlineStr">
         <is>
-          <t>tchr_jenny</t>
+          <t>tchr_jessa</t>
         </is>
       </c>
       <c r="M295" t="inlineStr">
         <is>
-          <t>Teacher Jenny</t>
+          <t>Teacher Jessa</t>
         </is>
       </c>
       <c r="N295" t="n">
@@ -19911,12 +19911,12 @@
       </c>
       <c r="E296" t="inlineStr">
         <is>
-          <t>sec_grade_5_mus_ab_ibn_abdul_mutalib_2nd_shift</t>
+          <t>sec_grade_6_dihya_ibn_khalifah_2nd_shift_girls</t>
         </is>
       </c>
       <c r="F296" t="inlineStr">
         <is>
-          <t>GRADE 5 - MUS'AB IBN ABDUL MUTALIB (2ND SHIFT)</t>
+          <t>GRADE 6 - DIHYA IBN KHALIFAH (2ND SHIFT) GIRLS</t>
         </is>
       </c>
       <c r="G296" t="inlineStr">
@@ -19926,7 +19926,7 @@
       </c>
       <c r="H296" t="inlineStr">
         <is>
-          <t>Grade 5</t>
+          <t>Grade 6</t>
         </is>
       </c>
       <c r="I296" t="inlineStr">
@@ -19936,22 +19936,22 @@
       </c>
       <c r="J296" t="inlineStr">
         <is>
-          <t>subj_english</t>
+          <t>subj_filipino</t>
         </is>
       </c>
       <c r="K296" t="inlineStr">
         <is>
-          <t>English</t>
+          <t>Filipino</t>
         </is>
       </c>
       <c r="L296" t="inlineStr">
         <is>
-          <t>tchr_jessa</t>
+          <t>tchr_normylah</t>
         </is>
       </c>
       <c r="M296" t="inlineStr">
         <is>
-          <t>Teacher Jessa</t>
+          <t>Teacher Normylah</t>
         </is>
       </c>
       <c r="N296" t="n">
@@ -19977,12 +19977,12 @@
       </c>
       <c r="E297" t="inlineStr">
         <is>
-          <t>sec_grade_6_dihya_ibn_khalifah_2nd_shift_girls</t>
+          <t>sec_grade_6_khaleed_ibn_waleed_2nd_shift</t>
         </is>
       </c>
       <c r="F297" t="inlineStr">
         <is>
-          <t>GRADE 6 - DIHYA IBN KHALIFAH (2ND SHIFT) GIRLS</t>
+          <t>GRADE 6 - KHALEED IBN WALEED (2ND SHIFT)</t>
         </is>
       </c>
       <c r="G297" t="inlineStr">
@@ -20002,22 +20002,22 @@
       </c>
       <c r="J297" t="inlineStr">
         <is>
-          <t>subj_filipino</t>
+          <t>subj_shaf</t>
         </is>
       </c>
       <c r="K297" t="inlineStr">
         <is>
-          <t>Filipino</t>
+          <t>SHAF</t>
         </is>
       </c>
       <c r="L297" t="inlineStr">
         <is>
-          <t>tchr_normylah</t>
+          <t>tchr_abdiraheem</t>
         </is>
       </c>
       <c r="M297" t="inlineStr">
         <is>
-          <t>Teacher Normylah</t>
+          <t>Ustadh Abdiraheem</t>
         </is>
       </c>
       <c r="N297" t="n">
@@ -20043,22 +20043,22 @@
       </c>
       <c r="E298" t="inlineStr">
         <is>
-          <t>sec_grade_6_khaleed_ibn_waleed_2nd_shift</t>
+          <t>sec_grade_7_anas_ibn_malik_2nd_shift_mix</t>
         </is>
       </c>
       <c r="F298" t="inlineStr">
         <is>
-          <t>GRADE 6 - KHALEED IBN WALEED (2ND SHIFT)</t>
+          <t>GRADE 7 - ANAS IBN MALIK (2ND SHIFT) - MIX</t>
         </is>
       </c>
       <c r="G298" t="inlineStr">
         <is>
-          <t>Elementary</t>
+          <t>Junior High School</t>
         </is>
       </c>
       <c r="H298" t="inlineStr">
         <is>
-          <t>Grade 6</t>
+          <t>Grade 7</t>
         </is>
       </c>
       <c r="I298" t="inlineStr">
@@ -20068,22 +20068,22 @@
       </c>
       <c r="J298" t="inlineStr">
         <is>
-          <t>subj_shaf</t>
+          <t>subj_arabic</t>
         </is>
       </c>
       <c r="K298" t="inlineStr">
         <is>
-          <t>SHAF</t>
+          <t>Arabic</t>
         </is>
       </c>
       <c r="L298" t="inlineStr">
         <is>
-          <t>tchr_abdiraheem</t>
+          <t>tchr_ali</t>
         </is>
       </c>
       <c r="M298" t="inlineStr">
         <is>
-          <t>Ustadh Abdiraheem</t>
+          <t>Ustadh Ali</t>
         </is>
       </c>
       <c r="N298" t="n">
@@ -20109,12 +20109,12 @@
       </c>
       <c r="E299" t="inlineStr">
         <is>
-          <t>sec_grade_7_anas_ibn_malik_2nd_shift_mix</t>
+          <t>sec_grade_8_nuaym_ibn_mas_ud_2nd_shift_mix</t>
         </is>
       </c>
       <c r="F299" t="inlineStr">
         <is>
-          <t>GRADE 7 - ANAS IBN MALIK (2ND SHIFT) - MIX</t>
+          <t>GRADE 8 - NUAYM IBN MAS'UD (2ND SHIFT) MIX</t>
         </is>
       </c>
       <c r="G299" t="inlineStr">
@@ -20124,7 +20124,7 @@
       </c>
       <c r="H299" t="inlineStr">
         <is>
-          <t>Grade 7</t>
+          <t>Grade 8</t>
         </is>
       </c>
       <c r="I299" t="inlineStr">
@@ -20134,22 +20134,22 @@
       </c>
       <c r="J299" t="inlineStr">
         <is>
-          <t>subj_arabic</t>
+          <t>subj_shaf</t>
         </is>
       </c>
       <c r="K299" t="inlineStr">
         <is>
-          <t>Arabic</t>
+          <t>SHAF</t>
         </is>
       </c>
       <c r="L299" t="inlineStr">
         <is>
-          <t>tchr_ali</t>
+          <t>tchr_samsuddin</t>
         </is>
       </c>
       <c r="M299" t="inlineStr">
         <is>
-          <t>Ustadh Ali</t>
+          <t>Alim Samsuddin</t>
         </is>
       </c>
       <c r="N299" t="n">
@@ -20175,12 +20175,12 @@
       </c>
       <c r="E300" t="inlineStr">
         <is>
-          <t>sec_grade_8_nuaym_ibn_mas_ud_2nd_shift_mix</t>
+          <t>sec_grade_9_abu_dharr_al_ghifarri_2nd_shift_boys</t>
         </is>
       </c>
       <c r="F300" t="inlineStr">
         <is>
-          <t>GRADE 8 - NUAYM IBN MAS'UD (2ND SHIFT) MIX</t>
+          <t>GRADE 9 - ABU DHARR AL GHIFARRI (2ND SHIFT) BOYS</t>
         </is>
       </c>
       <c r="G300" t="inlineStr">
@@ -20190,7 +20190,7 @@
       </c>
       <c r="H300" t="inlineStr">
         <is>
-          <t>Grade 8</t>
+          <t>Grade 9</t>
         </is>
       </c>
       <c r="I300" t="inlineStr">
@@ -20200,22 +20200,22 @@
       </c>
       <c r="J300" t="inlineStr">
         <is>
-          <t>subj_shaf</t>
+          <t>subj_science</t>
         </is>
       </c>
       <c r="K300" t="inlineStr">
         <is>
-          <t>SHAF</t>
+          <t>Science</t>
         </is>
       </c>
       <c r="L300" t="inlineStr">
         <is>
-          <t>tchr_samsuddin</t>
+          <t>tchr_rowena</t>
         </is>
       </c>
       <c r="M300" t="inlineStr">
         <is>
-          <t>Alim Samsuddin</t>
+          <t>Teacher Rowena</t>
         </is>
       </c>
       <c r="N300" t="n">
@@ -20241,12 +20241,12 @@
       </c>
       <c r="E301" t="inlineStr">
         <is>
-          <t>sec_grade_9_abu_dharr_al_ghifarri_2nd_shift_boys</t>
+          <t>sec_grade_9_abu_jandal_ibn_suhayl_2nd_shift_girls</t>
         </is>
       </c>
       <c r="F301" t="inlineStr">
         <is>
-          <t>GRADE 9 - ABU DHARR AL GHIFARRI (2ND SHIFT) BOYS</t>
+          <t>GRADE 9 - ABU JANDAL IBN SUHAYL (2ND SHIFT) GIRLS</t>
         </is>
       </c>
       <c r="G301" t="inlineStr">
@@ -20266,22 +20266,22 @@
       </c>
       <c r="J301" t="inlineStr">
         <is>
-          <t>subj_science</t>
+          <t>subj_filipino</t>
         </is>
       </c>
       <c r="K301" t="inlineStr">
         <is>
-          <t>Science</t>
+          <t>Filipino</t>
         </is>
       </c>
       <c r="L301" t="inlineStr">
         <is>
-          <t>tchr_rowena</t>
+          <t>tchr_nadzra</t>
         </is>
       </c>
       <c r="M301" t="inlineStr">
         <is>
-          <t>Teacher Rowena</t>
+          <t>Teacher Nadzra</t>
         </is>
       </c>
       <c r="N301" t="n">
@@ -20290,64 +20290,64 @@
     </row>
     <row r="302">
       <c r="A302" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B302" t="inlineStr">
         <is>
-          <t>Thursday, September 3, 2026</t>
+          <t>Sunday, September 6, 2026</t>
         </is>
       </c>
       <c r="C302" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D302" t="inlineStr">
         <is>
-          <t>05:30 PM – 06:30 PM</t>
+          <t>08:00 AM – 09:00 AM</t>
         </is>
       </c>
       <c r="E302" t="inlineStr">
         <is>
-          <t>sec_grade_9_abu_jandal_ibn_suhayl_2nd_shift_girls</t>
+          <t>sec_grade_1_face_to_face</t>
         </is>
       </c>
       <c r="F302" t="inlineStr">
         <is>
-          <t>GRADE 9 - ABU JANDAL IBN SUHAYL (2ND SHIFT) GIRLS</t>
+          <t>GRADE 1 (FACE TO FACE)</t>
         </is>
       </c>
       <c r="G302" t="inlineStr">
         <is>
-          <t>Junior High School</t>
+          <t>Elementary</t>
         </is>
       </c>
       <c r="H302" t="inlineStr">
         <is>
-          <t>Grade 9</t>
+          <t>Grade 1</t>
         </is>
       </c>
       <c r="I302" t="inlineStr">
         <is>
-          <t>ODL - 2ND SHIFT</t>
+          <t>F2F</t>
         </is>
       </c>
       <c r="J302" t="inlineStr">
         <is>
-          <t>subj_filipino</t>
+          <t>subj_shaf</t>
         </is>
       </c>
       <c r="K302" t="inlineStr">
         <is>
-          <t>Filipino</t>
+          <t>SHAF</t>
         </is>
       </c>
       <c r="L302" t="inlineStr">
         <is>
-          <t>tchr_nadzra</t>
+          <t>tchr_abdiraheem</t>
         </is>
       </c>
       <c r="M302" t="inlineStr">
         <is>
-          <t>Teacher Nadzra</t>
+          <t>Ustadh Abdiraheem</t>
         </is>
       </c>
       <c r="N302" t="n">
@@ -20373,22 +20373,22 @@
       </c>
       <c r="E303" t="inlineStr">
         <is>
-          <t>sec_grade_1_face_to_face</t>
+          <t>sec_grade_11_face_to_face</t>
         </is>
       </c>
       <c r="F303" t="inlineStr">
         <is>
-          <t>GRADE 1 (FACE TO FACE)</t>
+          <t>GRADE 11 (FACE TO FACE)</t>
         </is>
       </c>
       <c r="G303" t="inlineStr">
         <is>
-          <t>Elementary</t>
+          <t>Senior High School</t>
         </is>
       </c>
       <c r="H303" t="inlineStr">
         <is>
-          <t>Grade 1</t>
+          <t>Grade 11</t>
         </is>
       </c>
       <c r="I303" t="inlineStr">
@@ -20398,22 +20398,22 @@
       </c>
       <c r="J303" t="inlineStr">
         <is>
-          <t>subj_shaf</t>
+          <t>subj_gen_bio_1</t>
         </is>
       </c>
       <c r="K303" t="inlineStr">
         <is>
-          <t>SHAF</t>
+          <t>Gen Bio 1</t>
         </is>
       </c>
       <c r="L303" t="inlineStr">
         <is>
-          <t>tchr_abdiraheem</t>
+          <t>tchr_radzmia</t>
         </is>
       </c>
       <c r="M303" t="inlineStr">
         <is>
-          <t>Ustadh Abdiraheem</t>
+          <t>Teacher Radzmia</t>
         </is>
       </c>
       <c r="N303" t="n">
@@ -20434,17 +20434,17 @@
       </c>
       <c r="D304" t="inlineStr">
         <is>
-          <t>08:00 AM – 09:00 AM</t>
+          <t>08:00 AM – 10:00 AM</t>
         </is>
       </c>
       <c r="E304" t="inlineStr">
         <is>
-          <t>sec_grade_11_face_to_face</t>
+          <t>sec_grade_12_suhayb_ar_rumi</t>
         </is>
       </c>
       <c r="F304" t="inlineStr">
         <is>
-          <t>GRADE 11 (FACE TO FACE)</t>
+          <t>GRADE 12 - SUHAYB AR-RUMI</t>
         </is>
       </c>
       <c r="G304" t="inlineStr">
@@ -20454,7 +20454,7 @@
       </c>
       <c r="H304" t="inlineStr">
         <is>
-          <t>Grade 11</t>
+          <t>Grade 12</t>
         </is>
       </c>
       <c r="I304" t="inlineStr">
@@ -20464,26 +20464,26 @@
       </c>
       <c r="J304" t="inlineStr">
         <is>
-          <t>subj_gen_bio_1</t>
+          <t>subj_gen_physics_1</t>
         </is>
       </c>
       <c r="K304" t="inlineStr">
         <is>
-          <t>Gen Bio 1</t>
+          <t>General Physics 1</t>
         </is>
       </c>
       <c r="L304" t="inlineStr">
         <is>
-          <t>tchr_radzmia</t>
+          <t>tchr_aniah</t>
         </is>
       </c>
       <c r="M304" t="inlineStr">
         <is>
-          <t>Teacher Radzmia</t>
+          <t>Teacher Aniah</t>
         </is>
       </c>
       <c r="N304" t="n">
-        <v>60</v>
+        <v>120</v>
       </c>
     </row>
     <row r="305">
@@ -20500,27 +20500,27 @@
       </c>
       <c r="D305" t="inlineStr">
         <is>
-          <t>08:00 AM – 10:00 AM</t>
+          <t>08:00 AM – 09:00 AM</t>
         </is>
       </c>
       <c r="E305" t="inlineStr">
         <is>
-          <t>sec_grade_12_suhayb_ar_rumi</t>
+          <t>sec_grade_2_face_to_face</t>
         </is>
       </c>
       <c r="F305" t="inlineStr">
         <is>
-          <t>GRADE 12 - SUHAYB AR-RUMI</t>
+          <t>GRADE 2 (FACE TO FACE)</t>
         </is>
       </c>
       <c r="G305" t="inlineStr">
         <is>
-          <t>Senior High School</t>
+          <t>Elementary</t>
         </is>
       </c>
       <c r="H305" t="inlineStr">
         <is>
-          <t>Grade 12</t>
+          <t>Grade 2</t>
         </is>
       </c>
       <c r="I305" t="inlineStr">
@@ -20530,26 +20530,26 @@
       </c>
       <c r="J305" t="inlineStr">
         <is>
-          <t>subj_gen_physics_1</t>
+          <t>subj_filipino</t>
         </is>
       </c>
       <c r="K305" t="inlineStr">
         <is>
-          <t>General Physics 1</t>
+          <t>Filipino</t>
         </is>
       </c>
       <c r="L305" t="inlineStr">
         <is>
-          <t>tchr_aniah</t>
+          <t>tchr_sitti_kauzar</t>
         </is>
       </c>
       <c r="M305" t="inlineStr">
         <is>
-          <t>Teacher Aniah</t>
+          <t>Teacher Sitti Kauzar</t>
         </is>
       </c>
       <c r="N305" t="n">
-        <v>120</v>
+        <v>60</v>
       </c>
     </row>
     <row r="306">
@@ -20571,12 +20571,12 @@
       </c>
       <c r="E306" t="inlineStr">
         <is>
-          <t>sec_grade_2_face_to_face</t>
+          <t>sec_grade_3_face_to_face</t>
         </is>
       </c>
       <c r="F306" t="inlineStr">
         <is>
-          <t>GRADE 2 (FACE TO FACE)</t>
+          <t>GRADE 3 (FACE TO FACE)</t>
         </is>
       </c>
       <c r="G306" t="inlineStr">
@@ -20586,7 +20586,7 @@
       </c>
       <c r="H306" t="inlineStr">
         <is>
-          <t>Grade 2</t>
+          <t>Grade 3</t>
         </is>
       </c>
       <c r="I306" t="inlineStr">
@@ -20596,22 +20596,22 @@
       </c>
       <c r="J306" t="inlineStr">
         <is>
-          <t>subj_filipino</t>
+          <t>subj_qur_an</t>
         </is>
       </c>
       <c r="K306" t="inlineStr">
         <is>
-          <t>Filipino</t>
+          <t>Qur'an</t>
         </is>
       </c>
       <c r="L306" t="inlineStr">
         <is>
-          <t>tchr_sitti_kauzar</t>
+          <t>tchr_obaydah</t>
         </is>
       </c>
       <c r="M306" t="inlineStr">
         <is>
-          <t>Teacher Sitti Kauzar</t>
+          <t>Ustadh Obaydah</t>
         </is>
       </c>
       <c r="N306" t="n">
@@ -20637,12 +20637,12 @@
       </c>
       <c r="E307" t="inlineStr">
         <is>
-          <t>sec_grade_3_face_to_face</t>
+          <t>sec_grade_5_face_to_face</t>
         </is>
       </c>
       <c r="F307" t="inlineStr">
         <is>
-          <t>GRADE 3 (FACE TO FACE)</t>
+          <t>GRADE 5 (FACE TO FACE)</t>
         </is>
       </c>
       <c r="G307" t="inlineStr">
@@ -20652,7 +20652,7 @@
       </c>
       <c r="H307" t="inlineStr">
         <is>
-          <t>Grade 3</t>
+          <t>Grade 5</t>
         </is>
       </c>
       <c r="I307" t="inlineStr">
@@ -20662,22 +20662,22 @@
       </c>
       <c r="J307" t="inlineStr">
         <is>
-          <t>subj_qur_an</t>
+          <t>subj_tle</t>
         </is>
       </c>
       <c r="K307" t="inlineStr">
         <is>
-          <t>Qur'an</t>
+          <t>TLE</t>
         </is>
       </c>
       <c r="L307" t="inlineStr">
         <is>
-          <t>tchr_obaydah</t>
+          <t>tchr_halnaisa</t>
         </is>
       </c>
       <c r="M307" t="inlineStr">
         <is>
-          <t>Ustadh Obaydah</t>
+          <t>Teacher Halnaisa</t>
         </is>
       </c>
       <c r="N307" t="n">
@@ -20703,22 +20703,22 @@
       </c>
       <c r="E308" t="inlineStr">
         <is>
-          <t>sec_grade_5_face_to_face</t>
+          <t>sec_grade_7_8_boys_face_to_face</t>
         </is>
       </c>
       <c r="F308" t="inlineStr">
         <is>
-          <t>GRADE 5 (FACE TO FACE)</t>
+          <t>GRADE 7 &amp; 8 BOYS (FACE TO FACE)</t>
         </is>
       </c>
       <c r="G308" t="inlineStr">
         <is>
-          <t>Elementary</t>
+          <t>Junior High School</t>
         </is>
       </c>
       <c r="H308" t="inlineStr">
         <is>
-          <t>Grade 5</t>
+          <t>Grade 7 &amp; 8</t>
         </is>
       </c>
       <c r="I308" t="inlineStr">
@@ -20728,22 +20728,22 @@
       </c>
       <c r="J308" t="inlineStr">
         <is>
-          <t>subj_tle</t>
+          <t>subj_mapeh</t>
         </is>
       </c>
       <c r="K308" t="inlineStr">
         <is>
-          <t>TLE</t>
+          <t>MAPEH</t>
         </is>
       </c>
       <c r="L308" t="inlineStr">
         <is>
-          <t>tchr_halnaisa</t>
+          <t>tchr_franchette</t>
         </is>
       </c>
       <c r="M308" t="inlineStr">
         <is>
-          <t>Teacher Halnaisa</t>
+          <t>Teacher Franchette</t>
         </is>
       </c>
       <c r="N308" t="n">
@@ -20769,12 +20769,12 @@
       </c>
       <c r="E309" t="inlineStr">
         <is>
-          <t>sec_grade_7_8_boys_face_to_face</t>
+          <t>sec_grade_7_8_girls_face_to_face</t>
         </is>
       </c>
       <c r="F309" t="inlineStr">
         <is>
-          <t>GRADE 7 &amp; 8 BOYS (FACE TO FACE)</t>
+          <t>GRADE 7 &amp; 8 GIRLS (FACE TO FACE)</t>
         </is>
       </c>
       <c r="G309" t="inlineStr">
@@ -20794,22 +20794,22 @@
       </c>
       <c r="J309" t="inlineStr">
         <is>
-          <t>subj_mapeh</t>
+          <t>subj_english</t>
         </is>
       </c>
       <c r="K309" t="inlineStr">
         <is>
-          <t>MAPEH</t>
+          <t>English</t>
         </is>
       </c>
       <c r="L309" t="inlineStr">
         <is>
-          <t>tchr_franchette</t>
+          <t>tchr_jairah</t>
         </is>
       </c>
       <c r="M309" t="inlineStr">
         <is>
-          <t>Teacher Franchette</t>
+          <t>Teacher Jairah</t>
         </is>
       </c>
       <c r="N309" t="n">
@@ -20835,12 +20835,12 @@
       </c>
       <c r="E310" t="inlineStr">
         <is>
-          <t>sec_grade_7_8_girls_face_to_face</t>
+          <t>sec_grade_9_10_boys_face_to_face</t>
         </is>
       </c>
       <c r="F310" t="inlineStr">
         <is>
-          <t>GRADE 7 &amp; 8 GIRLS (FACE TO FACE)</t>
+          <t>GRADE 9 &amp; 10 BOYS (FACE TO FACE)</t>
         </is>
       </c>
       <c r="G310" t="inlineStr">
@@ -20850,7 +20850,7 @@
       </c>
       <c r="H310" t="inlineStr">
         <is>
-          <t>Grade 7 &amp; 8</t>
+          <t>Grade 9 &amp; 10</t>
         </is>
       </c>
       <c r="I310" t="inlineStr">
@@ -20860,22 +20860,22 @@
       </c>
       <c r="J310" t="inlineStr">
         <is>
-          <t>subj_english</t>
+          <t>subj_tle</t>
         </is>
       </c>
       <c r="K310" t="inlineStr">
         <is>
-          <t>English</t>
+          <t>TLE</t>
         </is>
       </c>
       <c r="L310" t="inlineStr">
         <is>
-          <t>tchr_jairah</t>
+          <t>tchr_angeleni</t>
         </is>
       </c>
       <c r="M310" t="inlineStr">
         <is>
-          <t>Teacher Jairah</t>
+          <t>Teacher Angeleni</t>
         </is>
       </c>
       <c r="N310" t="n">
@@ -20901,12 +20901,12 @@
       </c>
       <c r="E311" t="inlineStr">
         <is>
-          <t>sec_grade_9_10_boys_face_to_face</t>
+          <t>sec_grade_9_10_girls_face_to_face</t>
         </is>
       </c>
       <c r="F311" t="inlineStr">
         <is>
-          <t>GRADE 9 &amp; 10 BOYS (FACE TO FACE)</t>
+          <t>GRADE 9 &amp; 10 GIRLS (FACE TO FACE)</t>
         </is>
       </c>
       <c r="G311" t="inlineStr">
@@ -20926,22 +20926,22 @@
       </c>
       <c r="J311" t="inlineStr">
         <is>
-          <t>subj_tle</t>
+          <t>subj_filipino</t>
         </is>
       </c>
       <c r="K311" t="inlineStr">
         <is>
-          <t>TLE</t>
+          <t>Filipino</t>
         </is>
       </c>
       <c r="L311" t="inlineStr">
         <is>
-          <t>tchr_angeleni</t>
+          <t>tchr_nadzra</t>
         </is>
       </c>
       <c r="M311" t="inlineStr">
         <is>
-          <t>Teacher Angeleni</t>
+          <t>Teacher Nadzra</t>
         </is>
       </c>
       <c r="N311" t="n">
@@ -20967,22 +20967,22 @@
       </c>
       <c r="E312" t="inlineStr">
         <is>
-          <t>sec_grade_9_10_girls_face_to_face</t>
+          <t>sec_kinder_2_class_schedule_f2f</t>
         </is>
       </c>
       <c r="F312" t="inlineStr">
         <is>
-          <t>GRADE 9 &amp; 10 GIRLS (FACE TO FACE)</t>
+          <t>KINDER 2 CLASS SCHEDULE (F2F)</t>
         </is>
       </c>
       <c r="G312" t="inlineStr">
         <is>
-          <t>Junior High School</t>
+          <t>Elementary</t>
         </is>
       </c>
       <c r="H312" t="inlineStr">
         <is>
-          <t>Grade 9 &amp; 10</t>
+          <t>Kinder 2</t>
         </is>
       </c>
       <c r="I312" t="inlineStr">
@@ -20992,22 +20992,22 @@
       </c>
       <c r="J312" t="inlineStr">
         <is>
-          <t>subj_filipino</t>
+          <t>subj_hadith</t>
         </is>
       </c>
       <c r="K312" t="inlineStr">
         <is>
-          <t>Filipino</t>
+          <t>Hadith</t>
         </is>
       </c>
       <c r="L312" t="inlineStr">
         <is>
-          <t>tchr_nadzra</t>
+          <t>tchr_saliha</t>
         </is>
       </c>
       <c r="M312" t="inlineStr">
         <is>
-          <t>Teacher Nadzra</t>
+          <t>Ustadha Saliha</t>
         </is>
       </c>
       <c r="N312" t="n">
@@ -21024,21 +21024,21 @@
         </is>
       </c>
       <c r="C313" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D313" t="inlineStr">
         <is>
-          <t>08:00 AM – 09:00 AM</t>
+          <t>09:00 AM – 10:00 AM</t>
         </is>
       </c>
       <c r="E313" t="inlineStr">
         <is>
-          <t>sec_kinder_2_class_schedule_f2f</t>
+          <t>sec_grade_6_face_to_face</t>
         </is>
       </c>
       <c r="F313" t="inlineStr">
         <is>
-          <t>KINDER 2 CLASS SCHEDULE (F2F)</t>
+          <t>GRADE  6  FACE TO FACE</t>
         </is>
       </c>
       <c r="G313" t="inlineStr">
@@ -21048,7 +21048,7 @@
       </c>
       <c r="H313" t="inlineStr">
         <is>
-          <t>Kinder 2</t>
+          <t>Grade 6</t>
         </is>
       </c>
       <c r="I313" t="inlineStr">
@@ -21058,22 +21058,22 @@
       </c>
       <c r="J313" t="inlineStr">
         <is>
-          <t>subj_hadith</t>
+          <t>subj_filipino</t>
         </is>
       </c>
       <c r="K313" t="inlineStr">
         <is>
-          <t>Hadith</t>
+          <t>Filipino</t>
         </is>
       </c>
       <c r="L313" t="inlineStr">
         <is>
-          <t>tchr_saliha</t>
+          <t>tchr_normylah</t>
         </is>
       </c>
       <c r="M313" t="inlineStr">
         <is>
-          <t>Ustadha Saliha</t>
+          <t>Teacher Normylah</t>
         </is>
       </c>
       <c r="N313" t="n">
@@ -21099,12 +21099,12 @@
       </c>
       <c r="E314" t="inlineStr">
         <is>
-          <t>sec_grade_6_face_to_face</t>
+          <t>sec_grade_1_face_to_face</t>
         </is>
       </c>
       <c r="F314" t="inlineStr">
         <is>
-          <t>GRADE  6  FACE TO FACE</t>
+          <t>GRADE 1 (FACE TO FACE)</t>
         </is>
       </c>
       <c r="G314" t="inlineStr">
@@ -21114,7 +21114,7 @@
       </c>
       <c r="H314" t="inlineStr">
         <is>
-          <t>Grade 6</t>
+          <t>Grade 1</t>
         </is>
       </c>
       <c r="I314" t="inlineStr">
@@ -21124,22 +21124,22 @@
       </c>
       <c r="J314" t="inlineStr">
         <is>
-          <t>subj_filipino</t>
+          <t>subj_qur_an</t>
         </is>
       </c>
       <c r="K314" t="inlineStr">
         <is>
-          <t>Filipino</t>
+          <t>Qur'an</t>
         </is>
       </c>
       <c r="L314" t="inlineStr">
         <is>
-          <t>tchr_normylah</t>
+          <t>tchr_obaydah</t>
         </is>
       </c>
       <c r="M314" t="inlineStr">
         <is>
-          <t>Teacher Normylah</t>
+          <t>Ustadh Obaydah</t>
         </is>
       </c>
       <c r="N314" t="n">
@@ -21165,22 +21165,22 @@
       </c>
       <c r="E315" t="inlineStr">
         <is>
-          <t>sec_grade_1_face_to_face</t>
+          <t>sec_grade_11_face_to_face</t>
         </is>
       </c>
       <c r="F315" t="inlineStr">
         <is>
-          <t>GRADE 1 (FACE TO FACE)</t>
+          <t>GRADE 11 (FACE TO FACE)</t>
         </is>
       </c>
       <c r="G315" t="inlineStr">
         <is>
-          <t>Elementary</t>
+          <t>Senior High School</t>
         </is>
       </c>
       <c r="H315" t="inlineStr">
         <is>
-          <t>Grade 1</t>
+          <t>Grade 11</t>
         </is>
       </c>
       <c r="I315" t="inlineStr">
@@ -21190,22 +21190,22 @@
       </c>
       <c r="J315" t="inlineStr">
         <is>
-          <t>subj_qur_an</t>
+          <t>subj_mabisang_komunikasyon</t>
         </is>
       </c>
       <c r="K315" t="inlineStr">
         <is>
-          <t>Qur'an</t>
+          <t>Mabisang Komunikasyon</t>
         </is>
       </c>
       <c r="L315" t="inlineStr">
         <is>
-          <t>tchr_obaydah</t>
+          <t>tchr_nadzra</t>
         </is>
       </c>
       <c r="M315" t="inlineStr">
         <is>
-          <t>Ustadh Obaydah</t>
+          <t>Teacher Nadzra</t>
         </is>
       </c>
       <c r="N315" t="n">
@@ -21231,22 +21231,22 @@
       </c>
       <c r="E316" t="inlineStr">
         <is>
-          <t>sec_grade_11_face_to_face</t>
+          <t>sec_grade_2_face_to_face</t>
         </is>
       </c>
       <c r="F316" t="inlineStr">
         <is>
-          <t>GRADE 11 (FACE TO FACE)</t>
+          <t>GRADE 2 (FACE TO FACE)</t>
         </is>
       </c>
       <c r="G316" t="inlineStr">
         <is>
-          <t>Senior High School</t>
+          <t>Elementary</t>
         </is>
       </c>
       <c r="H316" t="inlineStr">
         <is>
-          <t>Grade 11</t>
+          <t>Grade 2</t>
         </is>
       </c>
       <c r="I316" t="inlineStr">
@@ -21256,22 +21256,22 @@
       </c>
       <c r="J316" t="inlineStr">
         <is>
-          <t>subj_mabisang_komunikasyon</t>
+          <t>subj_english</t>
         </is>
       </c>
       <c r="K316" t="inlineStr">
         <is>
-          <t>Mabisang Komunikasyon</t>
+          <t>English</t>
         </is>
       </c>
       <c r="L316" t="inlineStr">
         <is>
-          <t>tchr_nadzra</t>
+          <t>tchr_marham</t>
         </is>
       </c>
       <c r="M316" t="inlineStr">
         <is>
-          <t>Teacher Nadzra</t>
+          <t>Teacher Marham</t>
         </is>
       </c>
       <c r="N316" t="n">
@@ -21297,12 +21297,12 @@
       </c>
       <c r="E317" t="inlineStr">
         <is>
-          <t>sec_grade_2_face_to_face</t>
+          <t>sec_grade_3_face_to_face</t>
         </is>
       </c>
       <c r="F317" t="inlineStr">
         <is>
-          <t>GRADE 2 (FACE TO FACE)</t>
+          <t>GRADE 3 (FACE TO FACE)</t>
         </is>
       </c>
       <c r="G317" t="inlineStr">
@@ -21312,7 +21312,7 @@
       </c>
       <c r="H317" t="inlineStr">
         <is>
-          <t>Grade 2</t>
+          <t>Grade 3</t>
         </is>
       </c>
       <c r="I317" t="inlineStr">
@@ -21322,22 +21322,22 @@
       </c>
       <c r="J317" t="inlineStr">
         <is>
-          <t>subj_english</t>
+          <t>subj_gmrc</t>
         </is>
       </c>
       <c r="K317" t="inlineStr">
         <is>
-          <t>English</t>
+          <t>GMRC</t>
         </is>
       </c>
       <c r="L317" t="inlineStr">
         <is>
-          <t>tchr_marham</t>
+          <t>tchr_saliha</t>
         </is>
       </c>
       <c r="M317" t="inlineStr">
         <is>
-          <t>Teacher Marham</t>
+          <t>Ustadha Saliha</t>
         </is>
       </c>
       <c r="N317" t="n">
@@ -31065,12 +31065,12 @@
       </c>
       <c r="E465" t="inlineStr">
         <is>
-          <t>sec_grade_4_face_to_face</t>
+          <t>sec_grade_3_face_to_face</t>
         </is>
       </c>
       <c r="F465" t="inlineStr">
         <is>
-          <t>GRADE 4 (FACE TO FACE)</t>
+          <t>GRADE 3 (FACE TO FACE)</t>
         </is>
       </c>
       <c r="G465" t="inlineStr">
@@ -31080,7 +31080,7 @@
       </c>
       <c r="H465" t="inlineStr">
         <is>
-          <t>Grade 4</t>
+          <t>Grade 3</t>
         </is>
       </c>
       <c r="I465" t="inlineStr">
@@ -31090,22 +31090,22 @@
       </c>
       <c r="J465" t="inlineStr">
         <is>
-          <t>subj_tle</t>
+          <t>subj_shaf</t>
         </is>
       </c>
       <c r="K465" t="inlineStr">
         <is>
-          <t>TLE</t>
+          <t>SHAF</t>
         </is>
       </c>
       <c r="L465" t="inlineStr">
         <is>
-          <t>tchr_monisa</t>
+          <t>tchr_ersahad</t>
         </is>
       </c>
       <c r="M465" t="inlineStr">
         <is>
-          <t>Teacher Monisa</t>
+          <t>Ustadh Ersahad</t>
         </is>
       </c>
       <c r="N465" t="n">
@@ -31131,12 +31131,12 @@
       </c>
       <c r="E466" t="inlineStr">
         <is>
-          <t>sec_grade_5_face_to_face</t>
+          <t>sec_grade_4_face_to_face</t>
         </is>
       </c>
       <c r="F466" t="inlineStr">
         <is>
-          <t>GRADE 5 (FACE TO FACE)</t>
+          <t>GRADE 4 (FACE TO FACE)</t>
         </is>
       </c>
       <c r="G466" t="inlineStr">
@@ -31146,7 +31146,7 @@
       </c>
       <c r="H466" t="inlineStr">
         <is>
-          <t>Grade 5</t>
+          <t>Grade 4</t>
         </is>
       </c>
       <c r="I466" t="inlineStr">
@@ -31156,22 +31156,22 @@
       </c>
       <c r="J466" t="inlineStr">
         <is>
-          <t>subj_araling_panlipunan</t>
+          <t>subj_tle</t>
         </is>
       </c>
       <c r="K466" t="inlineStr">
         <is>
-          <t>Araling Panlipunan</t>
+          <t>TLE</t>
         </is>
       </c>
       <c r="L466" t="inlineStr">
         <is>
-          <t>tchr_norhydie</t>
+          <t>tchr_monisa</t>
         </is>
       </c>
       <c r="M466" t="inlineStr">
         <is>
-          <t>Teacher Norhydie</t>
+          <t>Teacher Monisa</t>
         </is>
       </c>
       <c r="N466" t="n">
@@ -31192,27 +31192,27 @@
       </c>
       <c r="D467" t="inlineStr">
         <is>
-          <t>09:00 AM – 11:25 AM</t>
+          <t>09:00 AM – 10:00 AM</t>
         </is>
       </c>
       <c r="E467" t="inlineStr">
         <is>
-          <t>sec_grade_7_8_boys_face_to_face</t>
+          <t>sec_grade_5_face_to_face</t>
         </is>
       </c>
       <c r="F467" t="inlineStr">
         <is>
-          <t>GRADE 7 &amp; 8 BOYS (FACE TO FACE)</t>
+          <t>GRADE 5 (FACE TO FACE)</t>
         </is>
       </c>
       <c r="G467" t="inlineStr">
         <is>
-          <t>Junior High School</t>
+          <t>Elementary</t>
         </is>
       </c>
       <c r="H467" t="inlineStr">
         <is>
-          <t>Grade 7 &amp; 8</t>
+          <t>Grade 5</t>
         </is>
       </c>
       <c r="I467" t="inlineStr">
@@ -31222,26 +31222,26 @@
       </c>
       <c r="J467" t="inlineStr">
         <is>
-          <t>subj_math</t>
+          <t>subj_araling_panlipunan</t>
         </is>
       </c>
       <c r="K467" t="inlineStr">
         <is>
-          <t>Math</t>
+          <t>Araling Panlipunan</t>
         </is>
       </c>
       <c r="L467" t="inlineStr">
         <is>
-          <t>tchr_fhairudz</t>
+          <t>tchr_norhydie</t>
         </is>
       </c>
       <c r="M467" t="inlineStr">
         <is>
-          <t>Teacher Fhairudz</t>
+          <t>Teacher Norhydie</t>
         </is>
       </c>
       <c r="N467" t="n">
-        <v>120</v>
+        <v>60</v>
       </c>
     </row>
     <row r="468">
@@ -31258,17 +31258,17 @@
       </c>
       <c r="D468" t="inlineStr">
         <is>
-          <t>09:00 AM – 10:00 AM</t>
+          <t>09:00 AM – 11:25 AM</t>
         </is>
       </c>
       <c r="E468" t="inlineStr">
         <is>
-          <t>sec_grade_7_8_girls_face_to_face</t>
+          <t>sec_grade_7_8_boys_face_to_face</t>
         </is>
       </c>
       <c r="F468" t="inlineStr">
         <is>
-          <t>GRADE 7 &amp; 8 GIRLS (FACE TO FACE)</t>
+          <t>GRADE 7 &amp; 8 BOYS (FACE TO FACE)</t>
         </is>
       </c>
       <c r="G468" t="inlineStr">
@@ -31288,26 +31288,26 @@
       </c>
       <c r="J468" t="inlineStr">
         <is>
-          <t>subj_gmrc</t>
+          <t>subj_math</t>
         </is>
       </c>
       <c r="K468" t="inlineStr">
         <is>
-          <t>GMRC</t>
+          <t>Math</t>
         </is>
       </c>
       <c r="L468" t="inlineStr">
         <is>
-          <t>tchr_silfah</t>
+          <t>tchr_fhairudz</t>
         </is>
       </c>
       <c r="M468" t="inlineStr">
         <is>
-          <t>Ustadh Silfah</t>
+          <t>Teacher Fhairudz</t>
         </is>
       </c>
       <c r="N468" t="n">
-        <v>60</v>
+        <v>120</v>
       </c>
     </row>
     <row r="469">
@@ -31329,12 +31329,12 @@
       </c>
       <c r="E469" t="inlineStr">
         <is>
-          <t>sec_grade_9_10_boys_face_to_face</t>
+          <t>sec_grade_7_8_girls_face_to_face</t>
         </is>
       </c>
       <c r="F469" t="inlineStr">
         <is>
-          <t>GRADE 9 &amp; 10 BOYS (FACE TO FACE)</t>
+          <t>GRADE 7 &amp; 8 GIRLS (FACE TO FACE)</t>
         </is>
       </c>
       <c r="G469" t="inlineStr">
@@ -31344,7 +31344,7 @@
       </c>
       <c r="H469" t="inlineStr">
         <is>
-          <t>Grade 9 &amp; 10</t>
+          <t>Grade 7 &amp; 8</t>
         </is>
       </c>
       <c r="I469" t="inlineStr">
@@ -31354,22 +31354,22 @@
       </c>
       <c r="J469" t="inlineStr">
         <is>
-          <t>subj_mapeh</t>
+          <t>subj_gmrc</t>
         </is>
       </c>
       <c r="K469" t="inlineStr">
         <is>
-          <t>MAPEH</t>
+          <t>GMRC</t>
         </is>
       </c>
       <c r="L469" t="inlineStr">
         <is>
-          <t>tchr_mohaymen</t>
+          <t>tchr_silfah</t>
         </is>
       </c>
       <c r="M469" t="inlineStr">
         <is>
-          <t>Sir Mohaymen</t>
+          <t>Ustadh Silfah</t>
         </is>
       </c>
       <c r="N469" t="n">
@@ -31386,31 +31386,31 @@
         </is>
       </c>
       <c r="C470" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D470" t="inlineStr">
         <is>
-          <t>10:25 AM – 11:25 AM</t>
+          <t>09:00 AM – 10:00 AM</t>
         </is>
       </c>
       <c r="E470" t="inlineStr">
         <is>
-          <t>sec_grade_6_face_to_face</t>
+          <t>sec_grade_9_10_boys_face_to_face</t>
         </is>
       </c>
       <c r="F470" t="inlineStr">
         <is>
-          <t>GRADE  6  FACE TO FACE</t>
+          <t>GRADE 9 &amp; 10 BOYS (FACE TO FACE)</t>
         </is>
       </c>
       <c r="G470" t="inlineStr">
         <is>
-          <t>Elementary</t>
+          <t>Junior High School</t>
         </is>
       </c>
       <c r="H470" t="inlineStr">
         <is>
-          <t>Grade 6</t>
+          <t>Grade 9 &amp; 10</t>
         </is>
       </c>
       <c r="I470" t="inlineStr">
@@ -31420,22 +31420,22 @@
       </c>
       <c r="J470" t="inlineStr">
         <is>
-          <t>subj_araling_panlipunan</t>
+          <t>subj_mapeh</t>
         </is>
       </c>
       <c r="K470" t="inlineStr">
         <is>
-          <t>Araling Panlipunan</t>
+          <t>MAPEH</t>
         </is>
       </c>
       <c r="L470" t="inlineStr">
         <is>
-          <t>tchr_zuhora</t>
+          <t>tchr_mohaymen</t>
         </is>
       </c>
       <c r="M470" t="inlineStr">
         <is>
-          <t>Teacher Zuhora</t>
+          <t>Sir Mohaymen</t>
         </is>
       </c>
       <c r="N470" t="n">
@@ -31461,22 +31461,22 @@
       </c>
       <c r="E471" t="inlineStr">
         <is>
-          <t>sec_grade_11_face_to_face</t>
+          <t>sec_grade_6_face_to_face</t>
         </is>
       </c>
       <c r="F471" t="inlineStr">
         <is>
-          <t>GRADE 11 (FACE TO FACE)</t>
+          <t>GRADE  6  FACE TO FACE</t>
         </is>
       </c>
       <c r="G471" t="inlineStr">
         <is>
-          <t>Senior High School</t>
+          <t>Elementary</t>
         </is>
       </c>
       <c r="H471" t="inlineStr">
         <is>
-          <t>Grade 11</t>
+          <t>Grade 6</t>
         </is>
       </c>
       <c r="I471" t="inlineStr">
@@ -31486,22 +31486,22 @@
       </c>
       <c r="J471" t="inlineStr">
         <is>
-          <t>subj_qur_an</t>
+          <t>subj_araling_panlipunan</t>
         </is>
       </c>
       <c r="K471" t="inlineStr">
         <is>
-          <t>Qur'an</t>
+          <t>Araling Panlipunan</t>
         </is>
       </c>
       <c r="L471" t="inlineStr">
         <is>
-          <t>tchr_dipatuan</t>
+          <t>tchr_zuhora</t>
         </is>
       </c>
       <c r="M471" t="inlineStr">
         <is>
-          <t>Alim Dipatuan</t>
+          <t>Teacher Zuhora</t>
         </is>
       </c>
       <c r="N471" t="n">
@@ -31527,12 +31527,12 @@
       </c>
       <c r="E472" t="inlineStr">
         <is>
-          <t>sec_grade_12_suhayb_ar_rumi</t>
+          <t>sec_grade_11_face_to_face</t>
         </is>
       </c>
       <c r="F472" t="inlineStr">
         <is>
-          <t>GRADE 12 - SUHAYB AR-RUMI</t>
+          <t>GRADE 11 (FACE TO FACE)</t>
         </is>
       </c>
       <c r="G472" t="inlineStr">
@@ -31542,7 +31542,7 @@
       </c>
       <c r="H472" t="inlineStr">
         <is>
-          <t>Grade 12</t>
+          <t>Grade 11</t>
         </is>
       </c>
       <c r="I472" t="inlineStr">
@@ -31552,22 +31552,22 @@
       </c>
       <c r="J472" t="inlineStr">
         <is>
-          <t>subj_arabic</t>
+          <t>subj_qur_an</t>
         </is>
       </c>
       <c r="K472" t="inlineStr">
         <is>
-          <t>Arabic</t>
+          <t>Qur'an</t>
         </is>
       </c>
       <c r="L472" t="inlineStr">
         <is>
-          <t>tchr_mamonas</t>
+          <t>tchr_dipatuan</t>
         </is>
       </c>
       <c r="M472" t="inlineStr">
         <is>
-          <t>Alim Mamonas</t>
+          <t>Alim Dipatuan</t>
         </is>
       </c>
       <c r="N472" t="n">
@@ -31593,22 +31593,22 @@
       </c>
       <c r="E473" t="inlineStr">
         <is>
-          <t>sec_grade_3_face_to_face</t>
+          <t>sec_grade_12_suhayb_ar_rumi</t>
         </is>
       </c>
       <c r="F473" t="inlineStr">
         <is>
-          <t>GRADE 3 (FACE TO FACE)</t>
+          <t>GRADE 12 - SUHAYB AR-RUMI</t>
         </is>
       </c>
       <c r="G473" t="inlineStr">
         <is>
-          <t>Elementary</t>
+          <t>Senior High School</t>
         </is>
       </c>
       <c r="H473" t="inlineStr">
         <is>
-          <t>Grade 3</t>
+          <t>Grade 12</t>
         </is>
       </c>
       <c r="I473" t="inlineStr">
@@ -31618,22 +31618,22 @@
       </c>
       <c r="J473" t="inlineStr">
         <is>
-          <t>subj_shaf</t>
+          <t>subj_arabic</t>
         </is>
       </c>
       <c r="K473" t="inlineStr">
         <is>
-          <t>SHAF</t>
+          <t>Arabic</t>
         </is>
       </c>
       <c r="L473" t="inlineStr">
         <is>
-          <t>tchr_ersahad</t>
+          <t>tchr_mamonas</t>
         </is>
       </c>
       <c r="M473" t="inlineStr">
         <is>
-          <t>Ustadh Ersahad</t>
+          <t>Alim Mamonas</t>
         </is>
       </c>
       <c r="N473" t="n">

--- a/Term_Examination_Schedule_S.Y._2026-2027_Optimized.xlsx
+++ b/Term_Examination_Schedule_S.Y._2026-2027_Optimized.xlsx
@@ -2817,12 +2817,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>sec_grade_6_abbas_ibn_abd_al_muttalib_1st_shift</t>
+          <t>sec_grade_5_muhammad_ibn_maslamah_1st_shift</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>GRADE 6 - ABBAS IBN ABD AL-MUTTALIB (1ST SHIFT)</t>
+          <t>GRADE 5 - MUHAMMAD IBN MASLAMAH (1ST SHIFT)</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
@@ -2832,7 +2832,7 @@
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>Grade 6</t>
+          <t>Grade 5</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
@@ -2842,22 +2842,22 @@
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>subj_gmrc</t>
+          <t>subj_shaf</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>GMRC</t>
+          <t>SHAF</t>
         </is>
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>tchr_silfah</t>
+          <t>tchr_hainur</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>Ustadh Silfah</t>
+          <t>Ustadha Hainur</t>
         </is>
       </c>
       <c r="N37" t="n">
@@ -2874,21 +2874,21 @@
         </is>
       </c>
       <c r="C38" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>12:40 PM – 01:40 PM</t>
+          <t>11:30 AM – 12:30 PM</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>sec_grade_1_ali_ibn_abi_talib_1st_shift</t>
+          <t>sec_grade_6_abbas_ibn_abd_al_muttalib_1st_shift</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>GRADE 1 - ALI IBN ABI TALIB(1ST SHIFT)</t>
+          <t>GRADE 6 - ABBAS IBN ABD AL-MUTTALIB (1ST SHIFT)</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
@@ -2898,7 +2898,7 @@
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>Grade 1</t>
+          <t>Grade 6</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
@@ -2908,22 +2908,22 @@
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>subj_makabansa</t>
+          <t>subj_gmrc</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>Makabansa</t>
+          <t>GMRC</t>
         </is>
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>tchr_norhydie</t>
+          <t>tchr_silfah</t>
         </is>
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>Teacher Norhydie</t>
+          <t>Ustadh Silfah</t>
         </is>
       </c>
       <c r="N38" t="n">
@@ -2949,12 +2949,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>sec_grade_1_hudhayfah_ibn_al_yam_1st_shift</t>
+          <t>sec_grade_1_ali_ibn_abi_talib_1st_shift</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>GRADE 1 - HUDHAYFAH IBN AL-YAM (1ST SHIFT)</t>
+          <t>GRADE 1 - ALI IBN ABI TALIB(1ST SHIFT)</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
@@ -2974,22 +2974,22 @@
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>subj_arabic</t>
+          <t>subj_makabansa</t>
         </is>
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>Arabic</t>
+          <t>Makabansa</t>
         </is>
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>tchr_hainur</t>
+          <t>tchr_norhydie</t>
         </is>
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>Ustadha Hainur</t>
+          <t>Teacher Norhydie</t>
         </is>
       </c>
       <c r="N39" t="n">
@@ -3015,22 +3015,22 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>sec_grade_10_utbah_ibn_ghazwan_1st_shift_girls</t>
+          <t>sec_grade_1_hudhayfah_ibn_al_yam_1st_shift</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>GRADE 10 - UTBAH IBN GHAZWAN (1ST SHIFT) GIRLS</t>
+          <t>GRADE 1 - HUDHAYFAH IBN AL-YAM (1ST SHIFT)</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Junior High School</t>
+          <t>Elementary</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>Grade 10</t>
+          <t>Grade 1</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
@@ -3040,22 +3040,22 @@
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>subj_social_studies</t>
+          <t>subj_arabic</t>
         </is>
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>Social Science</t>
+          <t>Arabic</t>
         </is>
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>tchr_sophia</t>
+          <t>tchr_hainur</t>
         </is>
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>Teacher Sophia</t>
+          <t>Ustadha Hainur</t>
         </is>
       </c>
       <c r="N40" t="n">
@@ -3072,7 +3072,7 @@
         </is>
       </c>
       <c r="C41" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -3081,22 +3081,22 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>sec_grade_11_1st_shift_girls</t>
+          <t>sec_grade_10_utbah_ibn_ghazwan_1st_shift_girls</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>GRADE 11 (1ST SHIFT GIRLS)</t>
+          <t>GRADE 10 - UTBAH IBN GHAZWAN (1ST SHIFT) GIRLS</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Senior High School</t>
+          <t>Junior High School</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>Grade 11</t>
+          <t>Grade 10</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
@@ -3106,22 +3106,22 @@
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>subj_qur_an</t>
+          <t>subj_social_studies</t>
         </is>
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>Qur'an</t>
+          <t>Social Science</t>
         </is>
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>tchr_abdulwahab</t>
+          <t>tchr_sophia</t>
         </is>
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>Alim Abdulwahab</t>
+          <t>Teacher Sophia</t>
         </is>
       </c>
       <c r="N41" t="n">
@@ -3147,12 +3147,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>sec_grade_12_abu_musa_al_ashari</t>
+          <t>sec_grade_11_1st_shift_girls</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>GRADE 12 - ABU MUSA AL-ASHARI</t>
+          <t>GRADE 11 (1ST SHIFT GIRLS)</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
@@ -3162,7 +3162,7 @@
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>Grade 12</t>
+          <t>Grade 11</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
@@ -3172,22 +3172,22 @@
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>subj_pe_12</t>
+          <t>subj_qur_an</t>
         </is>
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>PE 12</t>
+          <t>Qur'an</t>
         </is>
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>tchr_mohaymen</t>
+          <t>tchr_abdulwahab</t>
         </is>
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>Sir Mohaymen</t>
+          <t>Alim Abdulwahab</t>
         </is>
       </c>
       <c r="N42" t="n">
@@ -3204,7 +3204,7 @@
         </is>
       </c>
       <c r="C43" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -3213,22 +3213,22 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>sec_grade_2_amr_ibn_al_jamuh_1st_shift</t>
+          <t>sec_grade_12_abu_musa_al_ashari</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>GRADE 2 - AMR IBN AL-JAMUH (1ST SHIFT)</t>
+          <t>GRADE 12 - ABU MUSA AL-ASHARI</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Elementary</t>
+          <t>Senior High School</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>Grade 2</t>
+          <t>Grade 12</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
@@ -3238,22 +3238,22 @@
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>subj_shaf</t>
+          <t>subj_pe_12</t>
         </is>
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>SHAF</t>
+          <t>PE 12</t>
         </is>
       </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>tchr_abdul_karim</t>
+          <t>tchr_mohaymen</t>
         </is>
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>Alim Abdul Karim</t>
+          <t>Sir Mohaymen</t>
         </is>
       </c>
       <c r="N43" t="n">
@@ -3279,12 +3279,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>sec_grade_2_talha_ibn_ubaydullah_1st_shift</t>
+          <t>sec_grade_2_amr_ibn_al_jamuh_1st_shift</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>GRADE 2 - TALHA IBN UBAYDULLAH (1ST SHIFT)</t>
+          <t>GRADE 2 - AMR IBN AL-JAMUH (1ST SHIFT)</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
@@ -3304,22 +3304,22 @@
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>subj_filipino</t>
+          <t>subj_shaf</t>
         </is>
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>Filipino</t>
+          <t>SHAF</t>
         </is>
       </c>
       <c r="L44" t="inlineStr">
         <is>
-          <t>tchr_sitti_kauzar</t>
+          <t>tchr_abdul_karim</t>
         </is>
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>Teacher Sitti Kauzar</t>
+          <t>Alim Abdul Karim</t>
         </is>
       </c>
       <c r="N44" t="n">
@@ -3345,12 +3345,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>sec_grade_3_ammar_ibn_yasir_1st_shift_boys</t>
+          <t>sec_grade_2_talha_ibn_ubaydullah_1st_shift</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>GRADE 3 -AMMAR IBN YASIR (1ST SHIFT) - BOYS</t>
+          <t>GRADE 2 - TALHA IBN UBAYDULLAH (1ST SHIFT)</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
@@ -3360,7 +3360,7 @@
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>Grade 3</t>
+          <t>Grade 2</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
@@ -3370,22 +3370,22 @@
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>subj_qur_an</t>
+          <t>subj_filipino</t>
         </is>
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>Qur'an</t>
+          <t>Filipino</t>
         </is>
       </c>
       <c r="L45" t="inlineStr">
         <is>
-          <t>tchr_obaydah</t>
+          <t>tchr_sitti_kauzar</t>
         </is>
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>Ustadh Obaydah</t>
+          <t>Teacher Sitti Kauzar</t>
         </is>
       </c>
       <c r="N45" t="n">
@@ -3411,12 +3411,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>sec_grade_4_abdur_rahman_ibn_awf_1st_shift</t>
+          <t>sec_grade_3_ammar_ibn_yasir_1st_shift_boys</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>GRADE 4 - ABDUR RAHMAN IBN AWF (1ST SHIFT)</t>
+          <t>GRADE 3 -AMMAR IBN YASIR (1ST SHIFT) - BOYS</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
@@ -3426,7 +3426,7 @@
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>Grade 4</t>
+          <t>Grade 3</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
@@ -3436,22 +3436,22 @@
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>subj_tle</t>
+          <t>subj_qur_an</t>
         </is>
       </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t>TLE</t>
+          <t>Qur'an</t>
         </is>
       </c>
       <c r="L46" t="inlineStr">
         <is>
-          <t>tchr_monisa</t>
+          <t>tchr_obaydah</t>
         </is>
       </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t>Teacher Monisa</t>
+          <t>Ustadh Obaydah</t>
         </is>
       </c>
       <c r="N46" t="n">
@@ -3477,12 +3477,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>sec_grade_4_hakim_ibn_hazm_1st_shift</t>
+          <t>sec_grade_4_abdur_rahman_ibn_awf_1st_shift</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>GRADE 4 - HAKIM IBN HAZM(1ST SHIFT)</t>
+          <t>GRADE 4 - ABDUR RAHMAN IBN AWF (1ST SHIFT)</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
@@ -3502,22 +3502,22 @@
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>subj_science</t>
+          <t>subj_tle</t>
         </is>
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>Science</t>
+          <t>TLE</t>
         </is>
       </c>
       <c r="L47" t="inlineStr">
         <is>
-          <t>tchr_anna</t>
+          <t>tchr_monisa</t>
         </is>
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t>Teacher Anna</t>
+          <t>Teacher Monisa</t>
         </is>
       </c>
       <c r="N47" t="n">
@@ -3543,12 +3543,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>sec_grade_4_usayd_ibn_hudhayr_1st_shift_mix</t>
+          <t>sec_grade_4_hakim_ibn_hazm_1st_shift</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>GRADE 4 - USAYD IBN HUDHAYR (1ST SHIFT) - MIX</t>
+          <t>GRADE 4 - HAKIM IBN HAZM(1ST SHIFT)</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
@@ -3568,22 +3568,22 @@
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>subj_shaf</t>
+          <t>subj_science</t>
         </is>
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>SHAF</t>
+          <t>Science</t>
         </is>
       </c>
       <c r="L48" t="inlineStr">
         <is>
-          <t>tchr_abdiraheem</t>
+          <t>tchr_anna</t>
         </is>
       </c>
       <c r="M48" t="inlineStr">
         <is>
-          <t>Ustadh Abdiraheem</t>
+          <t>Teacher Anna</t>
         </is>
       </c>
       <c r="N48" t="n">
@@ -3609,12 +3609,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>sec_grade_5_ayyash_ibn_abi_rabi_ah_1st_shift</t>
+          <t>sec_grade_4_usayd_ibn_hudhayr_1st_shift_mix</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>GRADE 5 - AYYASH IBN ABI RABI'AH(1ST SHIFT)</t>
+          <t>GRADE 4 - USAYD IBN HUDHAYR (1ST SHIFT) - MIX</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
@@ -3624,7 +3624,7 @@
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>Grade 5</t>
+          <t>Grade 4</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
@@ -3634,22 +3634,22 @@
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>subj_gmrc</t>
+          <t>subj_shaf</t>
         </is>
       </c>
       <c r="K49" t="inlineStr">
         <is>
-          <t>GMRC</t>
+          <t>SHAF</t>
         </is>
       </c>
       <c r="L49" t="inlineStr">
         <is>
-          <t>tchr_saliha</t>
+          <t>tchr_abdiraheem</t>
         </is>
       </c>
       <c r="M49" t="inlineStr">
         <is>
-          <t>Ustadha Saliha</t>
+          <t>Ustadh Abdiraheem</t>
         </is>
       </c>
       <c r="N49" t="n">
@@ -3675,12 +3675,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>sec_grade_5_muhammad_ibn_maslamah_1st_shift</t>
+          <t>sec_grade_5_ayyash_ibn_abi_rabi_ah_1st_shift</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>GRADE 5 - MUHAMMAD IBN MASLAMAH (1ST SHIFT)</t>
+          <t>GRADE 5 - AYYASH IBN ABI RABI'AH(1ST SHIFT)</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
@@ -3700,22 +3700,22 @@
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>subj_qur_an</t>
+          <t>subj_gmrc</t>
         </is>
       </c>
       <c r="K50" t="inlineStr">
         <is>
-          <t>Qur'an</t>
+          <t>GMRC</t>
         </is>
       </c>
       <c r="L50" t="inlineStr">
         <is>
-          <t>tchr_jaisam</t>
+          <t>tchr_saliha</t>
         </is>
       </c>
       <c r="M50" t="inlineStr">
         <is>
-          <t>Ustadh Jaisam</t>
+          <t>Ustadha Saliha</t>
         </is>
       </c>
       <c r="N50" t="n">
@@ -3741,12 +3741,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>sec_grade_6_abbas_ibn_abd_al_muttalib_1st_shift</t>
+          <t>sec_grade_5_muhammad_ibn_maslamah_1st_shift</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>GRADE 6 - ABBAS IBN ABD AL-MUTTALIB (1ST SHIFT)</t>
+          <t>GRADE 5 - MUHAMMAD IBN MASLAMAH (1ST SHIFT)</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
@@ -3756,7 +3756,7 @@
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>Grade 6</t>
+          <t>Grade 5</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
@@ -3766,22 +3766,22 @@
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>subj_tle</t>
+          <t>subj_qur_an</t>
         </is>
       </c>
       <c r="K51" t="inlineStr">
         <is>
-          <t>TLE</t>
+          <t>Qur'an</t>
         </is>
       </c>
       <c r="L51" t="inlineStr">
         <is>
-          <t>tchr_arvin</t>
+          <t>tchr_jaisam</t>
         </is>
       </c>
       <c r="M51" t="inlineStr">
         <is>
-          <t>Teacher Arvin</t>
+          <t>Ustadh Jaisam</t>
         </is>
       </c>
       <c r="N51" t="n">
@@ -3807,12 +3807,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>sec_grade_6_abdullah_ibn_salaam_1st_shift</t>
+          <t>sec_grade_6_abbas_ibn_abd_al_muttalib_1st_shift</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>GRADE 6 - ABDULLAH IBN SALAAM (1ST SHIFT)</t>
+          <t>GRADE 6 - ABBAS IBN ABD AL-MUTTALIB (1ST SHIFT)</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
@@ -3832,22 +3832,22 @@
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>subj_arabic</t>
+          <t>subj_tle</t>
         </is>
       </c>
       <c r="K52" t="inlineStr">
         <is>
-          <t>Arabic</t>
+          <t>TLE</t>
         </is>
       </c>
       <c r="L52" t="inlineStr">
         <is>
-          <t>tchr_ali</t>
+          <t>tchr_arvin</t>
         </is>
       </c>
       <c r="M52" t="inlineStr">
         <is>
-          <t>Ustadh Ali</t>
+          <t>Teacher Arvin</t>
         </is>
       </c>
       <c r="N52" t="n">
@@ -3873,22 +3873,22 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>sec_grade_7_abu_sufyan_ibn_al_harith_1st_shift_boys</t>
+          <t>sec_grade_6_abdullah_ibn_salaam_1st_shift</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>GRADE 7 - ABU SUFYAN IBN AL-HARITH (1ST SHIFT) BOYS</t>
+          <t>GRADE 6 - ABDULLAH IBN SALAAM (1ST SHIFT)</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Junior High School</t>
+          <t>Elementary</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>Grade 7</t>
+          <t>Grade 6</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
@@ -3898,22 +3898,22 @@
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>subj_gmrc</t>
+          <t>subj_arabic</t>
         </is>
       </c>
       <c r="K53" t="inlineStr">
         <is>
-          <t>GMRC</t>
+          <t>Arabic</t>
         </is>
       </c>
       <c r="L53" t="inlineStr">
         <is>
-          <t>tchr_silfah</t>
+          <t>tchr_ali</t>
         </is>
       </c>
       <c r="M53" t="inlineStr">
         <is>
-          <t>Ustadh Silfah</t>
+          <t>Ustadh Ali</t>
         </is>
       </c>
       <c r="N53" t="n">
@@ -3939,12 +3939,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>sec_grade_7_usama_ibn_zayd_1st_shift_girls</t>
+          <t>sec_grade_7_abu_sufyan_ibn_al_harith_1st_shift_boys</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>GRADE 7 - USAMA IBN ZAYD (1ST SHIFT) GIRLS</t>
+          <t>GRADE 7 - ABU SUFYAN IBN AL-HARITH (1ST SHIFT) BOYS</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
@@ -3964,22 +3964,22 @@
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>subj_tle</t>
+          <t>subj_gmrc</t>
         </is>
       </c>
       <c r="K54" t="inlineStr">
         <is>
-          <t>TLE</t>
+          <t>GMRC</t>
         </is>
       </c>
       <c r="L54" t="inlineStr">
         <is>
-          <t>tchr_halnaisa</t>
+          <t>tchr_silfah</t>
         </is>
       </c>
       <c r="M54" t="inlineStr">
         <is>
-          <t>Teacher Halnaisa</t>
+          <t>Ustadh Silfah</t>
         </is>
       </c>
       <c r="N54" t="n">
@@ -4005,12 +4005,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>sec_grade_8_sa_ad_ibn_mua_dh_1st_shift_girls</t>
+          <t>sec_grade_7_usama_ibn_zayd_1st_shift_girls</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>GRADE 8 - SA'AD IBN MUA'DH (1ST SHIFT) - GIRLS</t>
+          <t>GRADE 7 - USAMA IBN ZAYD (1ST SHIFT) GIRLS</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
@@ -4020,7 +4020,7 @@
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>Grade 8</t>
+          <t>Grade 7</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
@@ -4030,22 +4030,22 @@
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t>subj_social_studies</t>
+          <t>subj_tle</t>
         </is>
       </c>
       <c r="K55" t="inlineStr">
         <is>
-          <t>Social Studies</t>
+          <t>TLE</t>
         </is>
       </c>
       <c r="L55" t="inlineStr">
         <is>
-          <t>tchr_shirehan</t>
+          <t>tchr_halnaisa</t>
         </is>
       </c>
       <c r="M55" t="inlineStr">
         <is>
-          <t>Teacher Shirehan</t>
+          <t>Teacher Halnaisa</t>
         </is>
       </c>
       <c r="N55" t="n">
@@ -4071,12 +4071,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>sec_grade_9_abu_hurayrah_1st_shift_girls</t>
+          <t>sec_grade_8_sa_ad_ibn_mua_dh_1st_shift_girls</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>GRADE 9 - ABU HURAYRAH (1ST SHIFT) GIRLS</t>
+          <t>GRADE 8 - SA'AD IBN MUA'DH (1ST SHIFT) - GIRLS</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
@@ -4086,7 +4086,7 @@
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>Grade 9</t>
+          <t>Grade 8</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
@@ -4096,22 +4096,22 @@
       </c>
       <c r="J56" t="inlineStr">
         <is>
-          <t>subj_english</t>
+          <t>subj_social_studies</t>
         </is>
       </c>
       <c r="K56" t="inlineStr">
         <is>
-          <t>English</t>
+          <t>Social Studies</t>
         </is>
       </c>
       <c r="L56" t="inlineStr">
         <is>
-          <t>tchr_norhaima</t>
+          <t>tchr_shirehan</t>
         </is>
       </c>
       <c r="M56" t="inlineStr">
         <is>
-          <t>Teacher Norhaima</t>
+          <t>Teacher Shirehan</t>
         </is>
       </c>
       <c r="N56" t="n">
@@ -4128,31 +4128,31 @@
         </is>
       </c>
       <c r="C57" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>01:30 PM – 02:30 PM</t>
+          <t>12:40 PM – 01:40 PM</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>sec_kinder_2_abu_bakr_as_sideeq_1st_shift</t>
+          <t>sec_grade_9_abu_hurayrah_1st_shift_girls</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Kinder 2 ABU BAKR AS-SIDEEQ (1ST SHIFT)</t>
+          <t>GRADE 9 - ABU HURAYRAH (1ST SHIFT) GIRLS</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Elementary</t>
+          <t>Junior High School</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>Kinder 2</t>
+          <t>Grade 9</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
@@ -4162,22 +4162,22 @@
       </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t>subj_oral_written_exam</t>
+          <t>subj_english</t>
         </is>
       </c>
       <c r="K57" t="inlineStr">
         <is>
-          <t>Oral &amp; Written Exam</t>
+          <t>English</t>
         </is>
       </c>
       <c r="L57" t="inlineStr">
         <is>
-          <t>tchr_joanna</t>
+          <t>tchr_norhaima</t>
         </is>
       </c>
       <c r="M57" t="inlineStr">
         <is>
-          <t>Teacher Joanna</t>
+          <t>Teacher Norhaima</t>
         </is>
       </c>
       <c r="N57" t="n">
@@ -4203,12 +4203,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>sec_kinder_2_uthman_ibn_affan_1st_shift</t>
+          <t>sec_kinder_2_abu_bakr_as_sideeq_1st_shift</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Kinder 2 UTHMAN IBN AFFAN (1ST SHIFT)</t>
+          <t>Kinder 2 ABU BAKR AS-SIDEEQ (1ST SHIFT)</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
@@ -4238,12 +4238,12 @@
       </c>
       <c r="L58" t="inlineStr">
         <is>
-          <t>tchr_ayah</t>
+          <t>tchr_joanna</t>
         </is>
       </c>
       <c r="M58" t="inlineStr">
         <is>
-          <t>Teacher Ayah</t>
+          <t>Teacher Joanna</t>
         </is>
       </c>
       <c r="N58" t="n">
@@ -4260,21 +4260,21 @@
         </is>
       </c>
       <c r="C59" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>01:50 PM – 02:50 PM</t>
+          <t>01:30 PM – 02:30 PM</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>sec_grade_1_hudhayfah_ibn_al_yam_1st_shift</t>
+          <t>sec_kinder_2_uthman_ibn_affan_1st_shift</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>GRADE 1 - HUDHAYFAH IBN AL-YAM (1ST SHIFT)</t>
+          <t>Kinder 2 UTHMAN IBN AFFAN (1ST SHIFT)</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
@@ -4284,7 +4284,7 @@
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>Grade 1</t>
+          <t>Kinder 2</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
@@ -4294,22 +4294,22 @@
       </c>
       <c r="J59" t="inlineStr">
         <is>
-          <t>subj_makabansa</t>
+          <t>subj_oral_written_exam</t>
         </is>
       </c>
       <c r="K59" t="inlineStr">
         <is>
-          <t>Makabansa</t>
+          <t>Oral &amp; Written Exam</t>
         </is>
       </c>
       <c r="L59" t="inlineStr">
         <is>
-          <t>tchr_norhydie</t>
+          <t>tchr_ayah</t>
         </is>
       </c>
       <c r="M59" t="inlineStr">
         <is>
-          <t>Teacher Norhydie</t>
+          <t>Teacher Ayah</t>
         </is>
       </c>
       <c r="N59" t="n">
@@ -4335,22 +4335,22 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>sec_grade_10_utbah_ibn_ghazwan_1st_shift_girls</t>
+          <t>sec_grade_1_hudhayfah_ibn_al_yam_1st_shift</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>GRADE 10 - UTBAH IBN GHAZWAN (1ST SHIFT) GIRLS</t>
+          <t>GRADE 1 - HUDHAYFAH IBN AL-YAM (1ST SHIFT)</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Junior High School</t>
+          <t>Elementary</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>Grade 10</t>
+          <t>Grade 1</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
@@ -4360,22 +4360,22 @@
       </c>
       <c r="J60" t="inlineStr">
         <is>
-          <t>subj_qur_an</t>
+          <t>subj_makabansa</t>
         </is>
       </c>
       <c r="K60" t="inlineStr">
         <is>
-          <t>Qur'an</t>
+          <t>Makabansa</t>
         </is>
       </c>
       <c r="L60" t="inlineStr">
         <is>
-          <t>tchr_abdulwahab</t>
+          <t>tchr_norhydie</t>
         </is>
       </c>
       <c r="M60" t="inlineStr">
         <is>
-          <t>Alim Abdulwahab</t>
+          <t>Teacher Norhydie</t>
         </is>
       </c>
       <c r="N60" t="n">
@@ -4392,7 +4392,7 @@
         </is>
       </c>
       <c r="C61" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -4401,22 +4401,22 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>sec_grade_11_1st_shift_girls</t>
+          <t>sec_grade_10_utbah_ibn_ghazwan_1st_shift_girls</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>GRADE 11 (1ST SHIFT GIRLS)</t>
+          <t>GRADE 10 - UTBAH IBN GHAZWAN (1ST SHIFT) GIRLS</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Senior High School</t>
+          <t>Junior High School</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>Grade 11</t>
+          <t>Grade 10</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
@@ -4426,22 +4426,22 @@
       </c>
       <c r="J61" t="inlineStr">
         <is>
-          <t>subj_arabic</t>
+          <t>subj_qur_an</t>
         </is>
       </c>
       <c r="K61" t="inlineStr">
         <is>
-          <t>Arabic</t>
+          <t>Qur'an</t>
         </is>
       </c>
       <c r="L61" t="inlineStr">
         <is>
-          <t>tchr_mamonas</t>
+          <t>tchr_abdulwahab</t>
         </is>
       </c>
       <c r="M61" t="inlineStr">
         <is>
-          <t>Alim Mamonas</t>
+          <t>Alim Abdulwahab</t>
         </is>
       </c>
       <c r="N61" t="n">
@@ -4467,12 +4467,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>sec_grade_12_abu_musa_al_ashari</t>
+          <t>sec_grade_11_1st_shift_girls</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>GRADE 12 - ABU MUSA AL-ASHARI</t>
+          <t>GRADE 11 (1ST SHIFT GIRLS)</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
@@ -4482,7 +4482,7 @@
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>Grade 12</t>
+          <t>Grade 11</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
@@ -4492,22 +4492,22 @@
       </c>
       <c r="J62" t="inlineStr">
         <is>
-          <t>subj_gen_bio_1</t>
+          <t>subj_arabic</t>
         </is>
       </c>
       <c r="K62" t="inlineStr">
         <is>
-          <t>Gen Bio 1</t>
+          <t>Arabic</t>
         </is>
       </c>
       <c r="L62" t="inlineStr">
         <is>
-          <t>tchr_radzmia</t>
+          <t>tchr_mamonas</t>
         </is>
       </c>
       <c r="M62" t="inlineStr">
         <is>
-          <t>Teacher Radzmia</t>
+          <t>Alim Mamonas</t>
         </is>
       </c>
       <c r="N62" t="n">
@@ -4524,7 +4524,7 @@
         </is>
       </c>
       <c r="C63" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -4533,22 +4533,22 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>sec_grade_2_amr_ibn_al_jamuh_1st_shift</t>
+          <t>sec_grade_12_abu_musa_al_ashari</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>GRADE 2 - AMR IBN AL-JAMUH (1ST SHIFT)</t>
+          <t>GRADE 12 - ABU MUSA AL-ASHARI</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Elementary</t>
+          <t>Senior High School</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>Grade 2</t>
+          <t>Grade 12</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
@@ -4558,22 +4558,22 @@
       </c>
       <c r="J63" t="inlineStr">
         <is>
-          <t>subj_filipino</t>
+          <t>subj_gen_bio_1</t>
         </is>
       </c>
       <c r="K63" t="inlineStr">
         <is>
-          <t>Filipino</t>
+          <t>Gen Bio 1</t>
         </is>
       </c>
       <c r="L63" t="inlineStr">
         <is>
-          <t>tchr_sitti_kauzar</t>
+          <t>tchr_radzmia</t>
         </is>
       </c>
       <c r="M63" t="inlineStr">
         <is>
-          <t>Teacher Sitti Kauzar</t>
+          <t>Teacher Radzmia</t>
         </is>
       </c>
       <c r="N63" t="n">
@@ -4599,12 +4599,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>sec_grade_2_talha_ibn_ubaydullah_1st_shift</t>
+          <t>sec_grade_2_amr_ibn_al_jamuh_1st_shift</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>GRADE 2 - TALHA IBN UBAYDULLAH (1ST SHIFT)</t>
+          <t>GRADE 2 - AMR IBN AL-JAMUH (1ST SHIFT)</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
@@ -4624,22 +4624,22 @@
       </c>
       <c r="J64" t="inlineStr">
         <is>
-          <t>subj_makabansa</t>
+          <t>subj_filipino</t>
         </is>
       </c>
       <c r="K64" t="inlineStr">
         <is>
-          <t>Makabansa</t>
+          <t>Filipino</t>
         </is>
       </c>
       <c r="L64" t="inlineStr">
         <is>
-          <t>tchr_zuhora</t>
+          <t>tchr_sitti_kauzar</t>
         </is>
       </c>
       <c r="M64" t="inlineStr">
         <is>
-          <t>Teacher Zuhora</t>
+          <t>Teacher Sitti Kauzar</t>
         </is>
       </c>
       <c r="N64" t="n">
@@ -4656,7 +4656,7 @@
         </is>
       </c>
       <c r="C65" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -4665,12 +4665,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>sec_grade_3_as_ad_ibn_zurarah_2nd_shift_mix</t>
+          <t>sec_grade_2_talha_ibn_ubaydullah_1st_shift</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>GRADE 3 - AS'AD IBN ZURARAH (2ND SHIFT) MIX</t>
+          <t>GRADE 2 - TALHA IBN UBAYDULLAH (1ST SHIFT)</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
@@ -4680,32 +4680,32 @@
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>Grade 3</t>
+          <t>Grade 2</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>ODL - 2ND SHIFT</t>
+          <t>ODL - 1ST SHIFT</t>
         </is>
       </c>
       <c r="J65" t="inlineStr">
         <is>
-          <t>subj_gmrc</t>
+          <t>subj_makabansa</t>
         </is>
       </c>
       <c r="K65" t="inlineStr">
         <is>
-          <t>GMRC</t>
+          <t>Makabansa</t>
         </is>
       </c>
       <c r="L65" t="inlineStr">
         <is>
-          <t>tchr_saliha</t>
+          <t>tchr_zuhora</t>
         </is>
       </c>
       <c r="M65" t="inlineStr">
         <is>
-          <t>Ustadha Saliha</t>
+          <t>Teacher Zuhora</t>
         </is>
       </c>
       <c r="N65" t="n">
@@ -4722,7 +4722,7 @@
         </is>
       </c>
       <c r="C66" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -4731,12 +4731,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>sec_grade_3_habib_ibn_zayd_al_ansari_1st_shift_girls</t>
+          <t>sec_grade_3_as_ad_ibn_zurarah_2nd_shift_mix</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Grade 3 - HABIB IBN ZAYD AL-ANSARI (1ST SHIFT) - GIRLS</t>
+          <t>GRADE 3 - AS'AD IBN ZURARAH (2ND SHIFT) MIX</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
@@ -4751,27 +4751,27 @@
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>ODL - 1ST SHIFT</t>
+          <t>ODL - 2ND SHIFT</t>
         </is>
       </c>
       <c r="J66" t="inlineStr">
         <is>
-          <t>subj_filipino</t>
+          <t>subj_gmrc</t>
         </is>
       </c>
       <c r="K66" t="inlineStr">
         <is>
-          <t>Filipino</t>
+          <t>GMRC</t>
         </is>
       </c>
       <c r="L66" t="inlineStr">
         <is>
-          <t>tchr_normylah</t>
+          <t>tchr_saliha</t>
         </is>
       </c>
       <c r="M66" t="inlineStr">
         <is>
-          <t>Teacher Normylah</t>
+          <t>Ustadha Saliha</t>
         </is>
       </c>
       <c r="N66" t="n">
@@ -4797,12 +4797,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>sec_grade_4_abdur_rahman_ibn_awf_1st_shift</t>
+          <t>sec_grade_3_habib_ibn_zayd_al_ansari_1st_shift_girls</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>GRADE 4 - ABDUR RAHMAN IBN AWF (1ST SHIFT)</t>
+          <t>Grade 3 - HABIB IBN ZAYD AL-ANSARI (1ST SHIFT) - GIRLS</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
@@ -4812,7 +4812,7 @@
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>Grade 4</t>
+          <t>Grade 3</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
@@ -4822,22 +4822,22 @@
       </c>
       <c r="J67" t="inlineStr">
         <is>
-          <t>subj_fil</t>
+          <t>subj_filipino</t>
         </is>
       </c>
       <c r="K67" t="inlineStr">
         <is>
-          <t>FIL</t>
+          <t>Filipino</t>
         </is>
       </c>
       <c r="L67" t="inlineStr">
         <is>
-          <t>tchr_monisa</t>
+          <t>tchr_normylah</t>
         </is>
       </c>
       <c r="M67" t="inlineStr">
         <is>
-          <t>Teacher Monisa</t>
+          <t>Teacher Normylah</t>
         </is>
       </c>
       <c r="N67" t="n">
@@ -4863,12 +4863,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>sec_grade_4_hakim_ibn_hazm_1st_shift</t>
+          <t>sec_grade_4_abdur_rahman_ibn_awf_1st_shift</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>GRADE 4 - HAKIM IBN HAZM(1ST SHIFT)</t>
+          <t>GRADE 4 - ABDUR RAHMAN IBN AWF (1ST SHIFT)</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
@@ -4888,22 +4888,22 @@
       </c>
       <c r="J68" t="inlineStr">
         <is>
-          <t>subj_mapeh</t>
+          <t>subj_fil</t>
         </is>
       </c>
       <c r="K68" t="inlineStr">
         <is>
-          <t>MAPEH</t>
+          <t>FIL</t>
         </is>
       </c>
       <c r="L68" t="inlineStr">
         <is>
-          <t>tchr_halnaisa</t>
+          <t>tchr_monisa</t>
         </is>
       </c>
       <c r="M68" t="inlineStr">
         <is>
-          <t>Teacher Halnaisa</t>
+          <t>Teacher Monisa</t>
         </is>
       </c>
       <c r="N68" t="n">
@@ -4929,12 +4929,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>sec_grade_4_usayd_ibn_hudhayr_1st_shift_mix</t>
+          <t>sec_grade_4_hakim_ibn_hazm_1st_shift</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>GRADE 4 - USAYD IBN HUDHAYR (1ST SHIFT) - MIX</t>
+          <t>GRADE 4 - HAKIM IBN HAZM(1ST SHIFT)</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
@@ -4954,22 +4954,22 @@
       </c>
       <c r="J69" t="inlineStr">
         <is>
-          <t>subj_qur_an</t>
+          <t>subj_mapeh</t>
         </is>
       </c>
       <c r="K69" t="inlineStr">
         <is>
-          <t>Qur'an</t>
+          <t>MAPEH</t>
         </is>
       </c>
       <c r="L69" t="inlineStr">
         <is>
-          <t>tchr_faidh</t>
+          <t>tchr_halnaisa</t>
         </is>
       </c>
       <c r="M69" t="inlineStr">
         <is>
-          <t>Ustadh Faidh</t>
+          <t>Teacher Halnaisa</t>
         </is>
       </c>
       <c r="N69" t="n">
@@ -4995,12 +4995,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>sec_grade_5_ayyash_ibn_abi_rabi_ah_1st_shift</t>
+          <t>sec_grade_4_usayd_ibn_hudhayr_1st_shift_mix</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>GRADE 5 - AYYASH IBN ABI RABI'AH(1ST SHIFT)</t>
+          <t>GRADE 4 - USAYD IBN HUDHAYR (1ST SHIFT) - MIX</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
@@ -5010,7 +5010,7 @@
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>Grade 5</t>
+          <t>Grade 4</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
@@ -5030,12 +5030,12 @@
       </c>
       <c r="L70" t="inlineStr">
         <is>
-          <t>tchr_obaydah</t>
+          <t>tchr_faidh</t>
         </is>
       </c>
       <c r="M70" t="inlineStr">
         <is>
-          <t>Ustadh Obaydah</t>
+          <t>Ustadh Faidh</t>
         </is>
       </c>
       <c r="N70" t="n">
@@ -5061,12 +5061,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>sec_grade_5_hamza_ibn_abdul_1st_shift</t>
+          <t>sec_grade_5_ayyash_ibn_abi_rabi_ah_1st_shift</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>GRADE 5 - HAMZA IBN ABDUL (1ST SHIFT)</t>
+          <t>GRADE 5 - AYYASH IBN ABI RABI'AH(1ST SHIFT)</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
@@ -5086,22 +5086,22 @@
       </c>
       <c r="J71" t="inlineStr">
         <is>
-          <t>subj_shaf</t>
+          <t>subj_qur_an</t>
         </is>
       </c>
       <c r="K71" t="inlineStr">
         <is>
-          <t>SHAF</t>
+          <t>Qur'an</t>
         </is>
       </c>
       <c r="L71" t="inlineStr">
         <is>
-          <t>tchr_raslina</t>
+          <t>tchr_obaydah</t>
         </is>
       </c>
       <c r="M71" t="inlineStr">
         <is>
-          <t>Ustadh Raslina</t>
+          <t>Ustadh Obaydah</t>
         </is>
       </c>
       <c r="N71" t="n">
@@ -24597,12 +24597,12 @@
       </c>
       <c r="E367" t="inlineStr">
         <is>
-          <t>sec_grade_5_muhammad_ibn_maslamah_1st_shift</t>
+          <t>sec_grade_6_abbas_ibn_abd_al_muttalib_1st_shift</t>
         </is>
       </c>
       <c r="F367" t="inlineStr">
         <is>
-          <t>GRADE 5 - MUHAMMAD IBN MASLAMAH (1ST SHIFT)</t>
+          <t>GRADE 6 - ABBAS IBN ABD AL-MUTTALIB (1ST SHIFT)</t>
         </is>
       </c>
       <c r="G367" t="inlineStr">
@@ -24612,7 +24612,7 @@
       </c>
       <c r="H367" t="inlineStr">
         <is>
-          <t>Grade 5</t>
+          <t>Grade 6</t>
         </is>
       </c>
       <c r="I367" t="inlineStr">
@@ -24622,22 +24622,22 @@
       </c>
       <c r="J367" t="inlineStr">
         <is>
-          <t>subj_shaf</t>
+          <t>subj_science</t>
         </is>
       </c>
       <c r="K367" t="inlineStr">
         <is>
-          <t>SHAF</t>
+          <t>Science</t>
         </is>
       </c>
       <c r="L367" t="inlineStr">
         <is>
-          <t>tchr_raslina</t>
+          <t>tchr_anna</t>
         </is>
       </c>
       <c r="M367" t="inlineStr">
         <is>
-          <t>Ustadh Raslina</t>
+          <t>Teacher Anna</t>
         </is>
       </c>
       <c r="N367" t="n">
@@ -24663,22 +24663,22 @@
       </c>
       <c r="E368" t="inlineStr">
         <is>
-          <t>sec_grade_6_abbas_ibn_abd_al_muttalib_1st_shift</t>
+          <t>sec_grade_7_abu_sufyan_ibn_al_harith_1st_shift_boys</t>
         </is>
       </c>
       <c r="F368" t="inlineStr">
         <is>
-          <t>GRADE 6 - ABBAS IBN ABD AL-MUTTALIB (1ST SHIFT)</t>
+          <t>GRADE 7 - ABU SUFYAN IBN AL-HARITH (1ST SHIFT) BOYS</t>
         </is>
       </c>
       <c r="G368" t="inlineStr">
         <is>
-          <t>Elementary</t>
+          <t>Junior High School</t>
         </is>
       </c>
       <c r="H368" t="inlineStr">
         <is>
-          <t>Grade 6</t>
+          <t>Grade 7</t>
         </is>
       </c>
       <c r="I368" t="inlineStr">
@@ -24698,12 +24698,12 @@
       </c>
       <c r="L368" t="inlineStr">
         <is>
-          <t>tchr_anna</t>
+          <t>tchr_aniah</t>
         </is>
       </c>
       <c r="M368" t="inlineStr">
         <is>
-          <t>Teacher Anna</t>
+          <t>Teacher Aniah</t>
         </is>
       </c>
       <c r="N368" t="n">
@@ -24720,7 +24720,7 @@
         </is>
       </c>
       <c r="C369" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D369" t="inlineStr">
         <is>
@@ -24729,12 +24729,12 @@
       </c>
       <c r="E369" t="inlineStr">
         <is>
-          <t>sec_grade_7_abu_sufyan_ibn_al_harith_1st_shift_boys</t>
+          <t>sec_grade_7_anas_ibn_malik_2nd_shift_mix</t>
         </is>
       </c>
       <c r="F369" t="inlineStr">
         <is>
-          <t>GRADE 7 - ABU SUFYAN IBN AL-HARITH (1ST SHIFT) BOYS</t>
+          <t>GRADE 7 - ANAS IBN MALIK (2ND SHIFT) - MIX</t>
         </is>
       </c>
       <c r="G369" t="inlineStr">
@@ -24749,27 +24749,27 @@
       </c>
       <c r="I369" t="inlineStr">
         <is>
-          <t>ODL - 1ST SHIFT</t>
+          <t>ODL - 2ND SHIFT</t>
         </is>
       </c>
       <c r="J369" t="inlineStr">
         <is>
-          <t>subj_science</t>
+          <t>subj_mapeh</t>
         </is>
       </c>
       <c r="K369" t="inlineStr">
         <is>
-          <t>Science</t>
+          <t>MAPEH</t>
         </is>
       </c>
       <c r="L369" t="inlineStr">
         <is>
-          <t>tchr_aniah</t>
+          <t>tchr_franchette</t>
         </is>
       </c>
       <c r="M369" t="inlineStr">
         <is>
-          <t>Teacher Aniah</t>
+          <t>Teacher Franchette</t>
         </is>
       </c>
       <c r="N369" t="n">
@@ -24786,7 +24786,7 @@
         </is>
       </c>
       <c r="C370" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D370" t="inlineStr">
         <is>
@@ -24795,12 +24795,12 @@
       </c>
       <c r="E370" t="inlineStr">
         <is>
-          <t>sec_grade_7_anas_ibn_malik_2nd_shift_mix</t>
+          <t>sec_grade_8_sa_ad_ibn_mua_dh_1st_shift_girls</t>
         </is>
       </c>
       <c r="F370" t="inlineStr">
         <is>
-          <t>GRADE 7 - ANAS IBN MALIK (2ND SHIFT) - MIX</t>
+          <t>GRADE 8 - SA'AD IBN MUA'DH (1ST SHIFT) - GIRLS</t>
         </is>
       </c>
       <c r="G370" t="inlineStr">
@@ -24810,32 +24810,32 @@
       </c>
       <c r="H370" t="inlineStr">
         <is>
-          <t>Grade 7</t>
+          <t>Grade 8</t>
         </is>
       </c>
       <c r="I370" t="inlineStr">
         <is>
-          <t>ODL - 2ND SHIFT</t>
+          <t>ODL - 1ST SHIFT</t>
         </is>
       </c>
       <c r="J370" t="inlineStr">
         <is>
-          <t>subj_mapeh</t>
+          <t>subj_arabic</t>
         </is>
       </c>
       <c r="K370" t="inlineStr">
         <is>
-          <t>MAPEH</t>
+          <t>Arabic</t>
         </is>
       </c>
       <c r="L370" t="inlineStr">
         <is>
-          <t>tchr_franchette</t>
+          <t>tchr_ali</t>
         </is>
       </c>
       <c r="M370" t="inlineStr">
         <is>
-          <t>Teacher Franchette</t>
+          <t>Ustadh Ali</t>
         </is>
       </c>
       <c r="N370" t="n">
@@ -24861,12 +24861,12 @@
       </c>
       <c r="E371" t="inlineStr">
         <is>
-          <t>sec_grade_8_sa_ad_ibn_mua_dh_1st_shift_girls</t>
+          <t>sec_grade_9_abu_hurayrah_1st_shift_girls</t>
         </is>
       </c>
       <c r="F371" t="inlineStr">
         <is>
-          <t>GRADE 8 - SA'AD IBN MUA'DH (1ST SHIFT) - GIRLS</t>
+          <t>GRADE 9 - ABU HURAYRAH (1ST SHIFT) GIRLS</t>
         </is>
       </c>
       <c r="G371" t="inlineStr">
@@ -24876,7 +24876,7 @@
       </c>
       <c r="H371" t="inlineStr">
         <is>
-          <t>Grade 8</t>
+          <t>Grade 9</t>
         </is>
       </c>
       <c r="I371" t="inlineStr">
@@ -24886,22 +24886,22 @@
       </c>
       <c r="J371" t="inlineStr">
         <is>
-          <t>subj_arabic</t>
+          <t>subj_shaf</t>
         </is>
       </c>
       <c r="K371" t="inlineStr">
         <is>
-          <t>Arabic</t>
+          <t>SHAF</t>
         </is>
       </c>
       <c r="L371" t="inlineStr">
         <is>
-          <t>tchr_ali</t>
+          <t>tchr_samsuddin</t>
         </is>
       </c>
       <c r="M371" t="inlineStr">
         <is>
-          <t>Ustadh Ali</t>
+          <t>Alim Samsuddin</t>
         </is>
       </c>
       <c r="N371" t="n">
@@ -24918,7 +24918,7 @@
         </is>
       </c>
       <c r="C372" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D372" t="inlineStr">
         <is>
@@ -24927,47 +24927,47 @@
       </c>
       <c r="E372" t="inlineStr">
         <is>
-          <t>sec_grade_9_abu_hurayrah_1st_shift_girls</t>
+          <t>sec_k2_abdullah_ibn_mas_ud_2nd_shift</t>
         </is>
       </c>
       <c r="F372" t="inlineStr">
         <is>
-          <t>GRADE 9 - ABU HURAYRAH (1ST SHIFT) GIRLS</t>
+          <t>K2 - ABDULLAH IBN MAS'UD (2ND SHIFT)</t>
         </is>
       </c>
       <c r="G372" t="inlineStr">
         <is>
-          <t>Junior High School</t>
+          <t>Elementary</t>
         </is>
       </c>
       <c r="H372" t="inlineStr">
         <is>
-          <t>Grade 9</t>
+          <t>Kinder 2</t>
         </is>
       </c>
       <c r="I372" t="inlineStr">
         <is>
-          <t>ODL - 1ST SHIFT</t>
+          <t>ODL - 2ND SHIFT</t>
         </is>
       </c>
       <c r="J372" t="inlineStr">
         <is>
-          <t>subj_shaf</t>
+          <t>subj_hadith</t>
         </is>
       </c>
       <c r="K372" t="inlineStr">
         <is>
-          <t>SHAF</t>
+          <t>Hadith</t>
         </is>
       </c>
       <c r="L372" t="inlineStr">
         <is>
-          <t>tchr_samsuddin</t>
+          <t>tchr_hainur</t>
         </is>
       </c>
       <c r="M372" t="inlineStr">
         <is>
-          <t>Alim Samsuddin</t>
+          <t>Ustadha Hainur</t>
         </is>
       </c>
       <c r="N372" t="n">
@@ -24993,12 +24993,12 @@
       </c>
       <c r="E373" t="inlineStr">
         <is>
-          <t>sec_k2_abdullah_ibn_mas_ud_2nd_shift</t>
+          <t>sec_kinder_2_khabaab_ibn_arat_2nd_shift</t>
         </is>
       </c>
       <c r="F373" t="inlineStr">
         <is>
-          <t>K2 - ABDULLAH IBN MAS'UD (2ND SHIFT)</t>
+          <t>Kinder 2 KHABAAB IBN ARAT (2ND SHIFT)</t>
         </is>
       </c>
       <c r="G373" t="inlineStr">
@@ -25018,22 +25018,22 @@
       </c>
       <c r="J373" t="inlineStr">
         <is>
-          <t>subj_hadith</t>
+          <t>subj_arabic</t>
         </is>
       </c>
       <c r="K373" t="inlineStr">
         <is>
-          <t>Hadith</t>
+          <t>Arabic</t>
         </is>
       </c>
       <c r="L373" t="inlineStr">
         <is>
-          <t>tchr_hainur</t>
+          <t>tchr_faidh</t>
         </is>
       </c>
       <c r="M373" t="inlineStr">
         <is>
-          <t>Ustadha Hainur</t>
+          <t>Ustadh Faidh</t>
         </is>
       </c>
       <c r="N373" t="n">
@@ -25050,21 +25050,21 @@
         </is>
       </c>
       <c r="C374" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D374" t="inlineStr">
         <is>
-          <t>01:50 PM – 02:50 PM</t>
+          <t>02:40 PM – 03:40 PM</t>
         </is>
       </c>
       <c r="E374" t="inlineStr">
         <is>
-          <t>sec_kinder_2_khabaab_ibn_arat_2nd_shift</t>
+          <t>sec_kinder_2_uthman_ibn_affan_1st_shift</t>
         </is>
       </c>
       <c r="F374" t="inlineStr">
         <is>
-          <t>Kinder 2 KHABAAB IBN ARAT (2ND SHIFT)</t>
+          <t>Kinder 2 UTHMAN IBN AFFAN (1ST SHIFT)</t>
         </is>
       </c>
       <c r="G374" t="inlineStr">
@@ -25079,7 +25079,7 @@
       </c>
       <c r="I374" t="inlineStr">
         <is>
-          <t>ODL - 2ND SHIFT</t>
+          <t>ODL - 1ST SHIFT</t>
         </is>
       </c>
       <c r="J374" t="inlineStr">
@@ -25094,12 +25094,12 @@
       </c>
       <c r="L374" t="inlineStr">
         <is>
-          <t>tchr_faidh</t>
+          <t>tchr_silfah</t>
         </is>
       </c>
       <c r="M374" t="inlineStr">
         <is>
-          <t>Ustadh Faidh</t>
+          <t>Ustadh Silfah</t>
         </is>
       </c>
       <c r="N374" t="n">
@@ -25116,21 +25116,21 @@
         </is>
       </c>
       <c r="C375" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D375" t="inlineStr">
         <is>
-          <t>02:40 PM – 03:40 PM</t>
+          <t>03:10 PM – 04:10 PM</t>
         </is>
       </c>
       <c r="E375" t="inlineStr">
         <is>
-          <t>sec_kinder_2_uthman_ibn_affan_1st_shift</t>
+          <t>sec_grade_1_ali_ibn_abi_talib_1st_shift</t>
         </is>
       </c>
       <c r="F375" t="inlineStr">
         <is>
-          <t>Kinder 2 UTHMAN IBN AFFAN (1ST SHIFT)</t>
+          <t>GRADE 1 - ALI IBN ABI TALIB(1ST SHIFT)</t>
         </is>
       </c>
       <c r="G375" t="inlineStr">
@@ -25140,7 +25140,7 @@
       </c>
       <c r="H375" t="inlineStr">
         <is>
-          <t>Kinder 2</t>
+          <t>Grade 1</t>
         </is>
       </c>
       <c r="I375" t="inlineStr">
@@ -25150,22 +25150,22 @@
       </c>
       <c r="J375" t="inlineStr">
         <is>
-          <t>subj_arabic</t>
+          <t>subj_gmrc</t>
         </is>
       </c>
       <c r="K375" t="inlineStr">
         <is>
-          <t>Arabic</t>
+          <t>GMRC</t>
         </is>
       </c>
       <c r="L375" t="inlineStr">
         <is>
-          <t>tchr_silfah</t>
+          <t>tchr_saliha</t>
         </is>
       </c>
       <c r="M375" t="inlineStr">
         <is>
-          <t>Ustadh Silfah</t>
+          <t>Ustadha Saliha</t>
         </is>
       </c>
       <c r="N375" t="n">
@@ -25191,12 +25191,12 @@
       </c>
       <c r="E376" t="inlineStr">
         <is>
-          <t>sec_grade_1_ali_ibn_abi_talib_1st_shift</t>
+          <t>sec_grade_1_hudhayfah_ibn_al_yam_1st_shift</t>
         </is>
       </c>
       <c r="F376" t="inlineStr">
         <is>
-          <t>GRADE 1 - ALI IBN ABI TALIB(1ST SHIFT)</t>
+          <t>GRADE 1 - HUDHAYFAH IBN AL-YAM (1ST SHIFT)</t>
         </is>
       </c>
       <c r="G376" t="inlineStr">
@@ -25226,12 +25226,12 @@
       </c>
       <c r="L376" t="inlineStr">
         <is>
-          <t>tchr_saliha</t>
+          <t>tchr_sahdia</t>
         </is>
       </c>
       <c r="M376" t="inlineStr">
         <is>
-          <t>Ustadha Saliha</t>
+          <t>Teacher Sahdia</t>
         </is>
       </c>
       <c r="N376" t="n">
@@ -25248,7 +25248,7 @@
         </is>
       </c>
       <c r="C377" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D377" t="inlineStr">
         <is>
@@ -25257,12 +25257,12 @@
       </c>
       <c r="E377" t="inlineStr">
         <is>
-          <t>sec_grade_1_hudhayfah_ibn_al_yam_1st_shift</t>
+          <t>sec_grade_1_sa_ad_ibn_abi_waqqaas_2nd_shift</t>
         </is>
       </c>
       <c r="F377" t="inlineStr">
         <is>
-          <t>GRADE 1 - HUDHAYFAH IBN AL-YAM (1ST SHIFT)</t>
+          <t>GRADE 1 - SA'AD IBN ABI WAQQAAS (2ND SHIFT)</t>
         </is>
       </c>
       <c r="G377" t="inlineStr">
@@ -25277,27 +25277,27 @@
       </c>
       <c r="I377" t="inlineStr">
         <is>
-          <t>ODL - 1ST SHIFT</t>
+          <t>ODL - 2ND SHIFT</t>
         </is>
       </c>
       <c r="J377" t="inlineStr">
         <is>
-          <t>subj_gmrc</t>
+          <t>subj_shaf</t>
         </is>
       </c>
       <c r="K377" t="inlineStr">
         <is>
-          <t>GMRC</t>
+          <t>SHAF</t>
         </is>
       </c>
       <c r="L377" t="inlineStr">
         <is>
-          <t>tchr_sahdia</t>
+          <t>tchr_abdul_karim</t>
         </is>
       </c>
       <c r="M377" t="inlineStr">
         <is>
-          <t>Teacher Sahdia</t>
+          <t>Alim Abdul Karim</t>
         </is>
       </c>
       <c r="N377" t="n">
@@ -25323,12 +25323,12 @@
       </c>
       <c r="E378" t="inlineStr">
         <is>
-          <t>sec_grade_1_sa_ad_ibn_abi_waqqaas_2nd_shift</t>
+          <t>sec_grade_1_suhayb_ar_rumi_2nd_shift</t>
         </is>
       </c>
       <c r="F378" t="inlineStr">
         <is>
-          <t>GRADE 1 - SA'AD IBN ABI WAQQAAS (2ND SHIFT)</t>
+          <t>GRADE 1 - SUHAYB AR-RUMI (2ND SHIFT)</t>
         </is>
       </c>
       <c r="G378" t="inlineStr">
@@ -25348,22 +25348,22 @@
       </c>
       <c r="J378" t="inlineStr">
         <is>
-          <t>subj_shaf</t>
+          <t>subj_qur_an</t>
         </is>
       </c>
       <c r="K378" t="inlineStr">
         <is>
-          <t>SHAF</t>
+          <t>Qur'an</t>
         </is>
       </c>
       <c r="L378" t="inlineStr">
         <is>
-          <t>tchr_abdul_karim</t>
+          <t>tchr_hainur</t>
         </is>
       </c>
       <c r="M378" t="inlineStr">
         <is>
-          <t>Alim Abdul Karim</t>
+          <t>Ustadha Hainur</t>
         </is>
       </c>
       <c r="N378" t="n">
@@ -25389,22 +25389,22 @@
       </c>
       <c r="E379" t="inlineStr">
         <is>
-          <t>sec_grade_1_suhayb_ar_rumi_2nd_shift</t>
+          <t>sec_grade_10_abu_ayyub_al_ansari_2nd_shift_boys</t>
         </is>
       </c>
       <c r="F379" t="inlineStr">
         <is>
-          <t>GRADE 1 - SUHAYB AR-RUMI (2ND SHIFT)</t>
+          <t>GRADE 10 - ABU AYYUB AL-ANSARI (2ND SHIFT) BOYS</t>
         </is>
       </c>
       <c r="G379" t="inlineStr">
         <is>
-          <t>Elementary</t>
+          <t>Junior High School</t>
         </is>
       </c>
       <c r="H379" t="inlineStr">
         <is>
-          <t>Grade 1</t>
+          <t>Grade 10</t>
         </is>
       </c>
       <c r="I379" t="inlineStr">
@@ -25414,22 +25414,22 @@
       </c>
       <c r="J379" t="inlineStr">
         <is>
-          <t>subj_qur_an</t>
+          <t>subj_mapeh</t>
         </is>
       </c>
       <c r="K379" t="inlineStr">
         <is>
-          <t>Qur'an</t>
+          <t>MAPEH</t>
         </is>
       </c>
       <c r="L379" t="inlineStr">
         <is>
-          <t>tchr_hainur</t>
+          <t>tchr_mohaymen</t>
         </is>
       </c>
       <c r="M379" t="inlineStr">
         <is>
-          <t>Ustadha Hainur</t>
+          <t>Sir Mohaymen</t>
         </is>
       </c>
       <c r="N379" t="n">
@@ -25446,7 +25446,7 @@
         </is>
       </c>
       <c r="C380" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D380" t="inlineStr">
         <is>
@@ -25455,12 +25455,12 @@
       </c>
       <c r="E380" t="inlineStr">
         <is>
-          <t>sec_grade_10_abu_ayyub_al_ansari_2nd_shift_boys</t>
+          <t>sec_grade_10_utbah_ibn_ghazwan_1st_shift_girls</t>
         </is>
       </c>
       <c r="F380" t="inlineStr">
         <is>
-          <t>GRADE 10 - ABU AYYUB AL-ANSARI (2ND SHIFT) BOYS</t>
+          <t>GRADE 10 - UTBAH IBN GHAZWAN (1ST SHIFT) GIRLS</t>
         </is>
       </c>
       <c r="G380" t="inlineStr">
@@ -25475,27 +25475,27 @@
       </c>
       <c r="I380" t="inlineStr">
         <is>
-          <t>ODL - 2ND SHIFT</t>
+          <t>ODL - 1ST SHIFT</t>
         </is>
       </c>
       <c r="J380" t="inlineStr">
         <is>
-          <t>subj_mapeh</t>
+          <t>subj_arabic</t>
         </is>
       </c>
       <c r="K380" t="inlineStr">
         <is>
-          <t>MAPEH</t>
+          <t>Arabic</t>
         </is>
       </c>
       <c r="L380" t="inlineStr">
         <is>
-          <t>tchr_mohaymen</t>
+          <t>tchr_mamonas</t>
         </is>
       </c>
       <c r="M380" t="inlineStr">
         <is>
-          <t>Sir Mohaymen</t>
+          <t>Alim Mamonas</t>
         </is>
       </c>
       <c r="N380" t="n">
@@ -25512,7 +25512,7 @@
         </is>
       </c>
       <c r="C381" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D381" t="inlineStr">
         <is>
@@ -25521,47 +25521,47 @@
       </c>
       <c r="E381" t="inlineStr">
         <is>
-          <t>sec_grade_10_utbah_ibn_ghazwan_1st_shift_girls</t>
+          <t>sec_grade_2_saeed_ibn_zayd_2nd_shift</t>
         </is>
       </c>
       <c r="F381" t="inlineStr">
         <is>
-          <t>GRADE 10 - UTBAH IBN GHAZWAN (1ST SHIFT) GIRLS</t>
+          <t>GRADE 2 - SAEED IBN ZAYD (2ND SHIFT)</t>
         </is>
       </c>
       <c r="G381" t="inlineStr">
         <is>
-          <t>Junior High School</t>
+          <t>Elementary</t>
         </is>
       </c>
       <c r="H381" t="inlineStr">
         <is>
-          <t>Grade 10</t>
+          <t>Grade 2</t>
         </is>
       </c>
       <c r="I381" t="inlineStr">
         <is>
-          <t>ODL - 1ST SHIFT</t>
+          <t>ODL - 2ND SHIFT</t>
         </is>
       </c>
       <c r="J381" t="inlineStr">
         <is>
-          <t>subj_arabic</t>
+          <t>subj_math</t>
         </is>
       </c>
       <c r="K381" t="inlineStr">
         <is>
-          <t>Arabic</t>
+          <t>Math</t>
         </is>
       </c>
       <c r="L381" t="inlineStr">
         <is>
-          <t>tchr_mamonas</t>
+          <t>tchr_sitti_kauzar</t>
         </is>
       </c>
       <c r="M381" t="inlineStr">
         <is>
-          <t>Alim Mamonas</t>
+          <t>Teacher Sitti Kauzar</t>
         </is>
       </c>
       <c r="N381" t="n">
@@ -25587,12 +25587,12 @@
       </c>
       <c r="E382" t="inlineStr">
         <is>
-          <t>sec_grade_2_saeed_ibn_zayd_2nd_shift</t>
+          <t>sec_grade_3_as_ad_ibn_zurarah_2nd_shift_mix</t>
         </is>
       </c>
       <c r="F382" t="inlineStr">
         <is>
-          <t>GRADE 2 - SAEED IBN ZAYD (2ND SHIFT)</t>
+          <t>GRADE 3 - AS'AD IBN ZURARAH (2ND SHIFT) MIX</t>
         </is>
       </c>
       <c r="G382" t="inlineStr">
@@ -25602,7 +25602,7 @@
       </c>
       <c r="H382" t="inlineStr">
         <is>
-          <t>Grade 2</t>
+          <t>Grade 3</t>
         </is>
       </c>
       <c r="I382" t="inlineStr">
@@ -25612,22 +25612,22 @@
       </c>
       <c r="J382" t="inlineStr">
         <is>
-          <t>subj_math</t>
+          <t>subj_arabic</t>
         </is>
       </c>
       <c r="K382" t="inlineStr">
         <is>
-          <t>Math</t>
+          <t>Arabic</t>
         </is>
       </c>
       <c r="L382" t="inlineStr">
         <is>
-          <t>tchr_sitti_kauzar</t>
+          <t>tchr_faidh</t>
         </is>
       </c>
       <c r="M382" t="inlineStr">
         <is>
-          <t>Teacher Sitti Kauzar</t>
+          <t>Ustadh Faidh</t>
         </is>
       </c>
       <c r="N382" t="n">
@@ -25644,7 +25644,7 @@
         </is>
       </c>
       <c r="C383" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D383" t="inlineStr">
         <is>
@@ -25653,12 +25653,12 @@
       </c>
       <c r="E383" t="inlineStr">
         <is>
-          <t>sec_grade_3_as_ad_ibn_zurarah_2nd_shift_mix</t>
+          <t>sec_grade_3_habib_ibn_zayd_al_ansari_1st_shift_girls</t>
         </is>
       </c>
       <c r="F383" t="inlineStr">
         <is>
-          <t>GRADE 3 - AS'AD IBN ZURARAH (2ND SHIFT) MIX</t>
+          <t>Grade 3 - HABIB IBN ZAYD AL-ANSARI (1ST SHIFT) - GIRLS</t>
         </is>
       </c>
       <c r="G383" t="inlineStr">
@@ -25673,27 +25673,27 @@
       </c>
       <c r="I383" t="inlineStr">
         <is>
-          <t>ODL - 2ND SHIFT</t>
+          <t>ODL - 1ST SHIFT</t>
         </is>
       </c>
       <c r="J383" t="inlineStr">
         <is>
-          <t>subj_arabic</t>
+          <t>subj_makabansa</t>
         </is>
       </c>
       <c r="K383" t="inlineStr">
         <is>
-          <t>Arabic</t>
+          <t>Makabansa</t>
         </is>
       </c>
       <c r="L383" t="inlineStr">
         <is>
-          <t>tchr_faidh</t>
+          <t>tchr_zara</t>
         </is>
       </c>
       <c r="M383" t="inlineStr">
         <is>
-          <t>Ustadh Faidh</t>
+          <t>Teacher Zara</t>
         </is>
       </c>
       <c r="N383" t="n">
@@ -25719,12 +25719,12 @@
       </c>
       <c r="E384" t="inlineStr">
         <is>
-          <t>sec_grade_3_habib_ibn_zayd_al_ansari_1st_shift_girls</t>
+          <t>sec_grade_3_salman_al_farsi_1st_shift_mix</t>
         </is>
       </c>
       <c r="F384" t="inlineStr">
         <is>
-          <t>Grade 3 - HABIB IBN ZAYD AL-ANSARI (1ST SHIFT) - GIRLS</t>
+          <t>GRADE 3 - SALMAN AL FARSI (1ST SHIFT) MIX</t>
         </is>
       </c>
       <c r="G384" t="inlineStr">
@@ -25744,22 +25744,22 @@
       </c>
       <c r="J384" t="inlineStr">
         <is>
-          <t>subj_makabansa</t>
+          <t>subj_english</t>
         </is>
       </c>
       <c r="K384" t="inlineStr">
         <is>
-          <t>Makabansa</t>
+          <t>English</t>
         </is>
       </c>
       <c r="L384" t="inlineStr">
         <is>
-          <t>tchr_zara</t>
+          <t>tchr_jenny</t>
         </is>
       </c>
       <c r="M384" t="inlineStr">
         <is>
-          <t>Teacher Zara</t>
+          <t>Teacher Jenny</t>
         </is>
       </c>
       <c r="N384" t="n">
@@ -25776,7 +25776,7 @@
         </is>
       </c>
       <c r="C385" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D385" t="inlineStr">
         <is>
@@ -25785,12 +25785,12 @@
       </c>
       <c r="E385" t="inlineStr">
         <is>
-          <t>sec_grade_3_salman_al_farsi_1st_shift_mix</t>
+          <t>sec_grade_3_zayd_ibn_haritha_2nd_shift_girls</t>
         </is>
       </c>
       <c r="F385" t="inlineStr">
         <is>
-          <t>GRADE 3 - SALMAN AL FARSI (1ST SHIFT) MIX</t>
+          <t>GRADE 3 - ZAYD IBN HARITHA (2ND SHIFT) - GIRLS</t>
         </is>
       </c>
       <c r="G385" t="inlineStr">
@@ -25805,27 +25805,27 @@
       </c>
       <c r="I385" t="inlineStr">
         <is>
-          <t>ODL - 1ST SHIFT</t>
+          <t>ODL - 2ND SHIFT</t>
         </is>
       </c>
       <c r="J385" t="inlineStr">
         <is>
-          <t>subj_english</t>
+          <t>subj_filipino</t>
         </is>
       </c>
       <c r="K385" t="inlineStr">
         <is>
-          <t>English</t>
+          <t>Filipino</t>
         </is>
       </c>
       <c r="L385" t="inlineStr">
         <is>
-          <t>tchr_jenny</t>
+          <t>tchr_normylah</t>
         </is>
       </c>
       <c r="M385" t="inlineStr">
         <is>
-          <t>Teacher Jenny</t>
+          <t>Teacher Normylah</t>
         </is>
       </c>
       <c r="N385" t="n">
@@ -25842,7 +25842,7 @@
         </is>
       </c>
       <c r="C386" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D386" t="inlineStr">
         <is>
@@ -25851,12 +25851,12 @@
       </c>
       <c r="E386" t="inlineStr">
         <is>
-          <t>sec_grade_3_zayd_ibn_haritha_2nd_shift_girls</t>
+          <t>sec_grade_3_ammar_ibn_yasir_1st_shift_boys</t>
         </is>
       </c>
       <c r="F386" t="inlineStr">
         <is>
-          <t>GRADE 3 - ZAYD IBN HARITHA (2ND SHIFT) - GIRLS</t>
+          <t>GRADE 3 -AMMAR IBN YASIR (1ST SHIFT) - BOYS</t>
         </is>
       </c>
       <c r="G386" t="inlineStr">
@@ -25871,27 +25871,27 @@
       </c>
       <c r="I386" t="inlineStr">
         <is>
-          <t>ODL - 2ND SHIFT</t>
+          <t>ODL - 1ST SHIFT</t>
         </is>
       </c>
       <c r="J386" t="inlineStr">
         <is>
-          <t>subj_filipino</t>
+          <t>subj_english</t>
         </is>
       </c>
       <c r="K386" t="inlineStr">
         <is>
-          <t>Filipino</t>
+          <t>English</t>
         </is>
       </c>
       <c r="L386" t="inlineStr">
         <is>
-          <t>tchr_normylah</t>
+          <t>tchr_marham</t>
         </is>
       </c>
       <c r="M386" t="inlineStr">
         <is>
-          <t>Teacher Normylah</t>
+          <t>Teacher Marham</t>
         </is>
       </c>
       <c r="N386" t="n">
@@ -25917,12 +25917,12 @@
       </c>
       <c r="E387" t="inlineStr">
         <is>
-          <t>sec_grade_3_ammar_ibn_yasir_1st_shift_boys</t>
+          <t>sec_grade_4_abdur_rahman_ibn_awf_1st_shift</t>
         </is>
       </c>
       <c r="F387" t="inlineStr">
         <is>
-          <t>GRADE 3 -AMMAR IBN YASIR (1ST SHIFT) - BOYS</t>
+          <t>GRADE 4 - ABDUR RAHMAN IBN AWF (1ST SHIFT)</t>
         </is>
       </c>
       <c r="G387" t="inlineStr">
@@ -25932,7 +25932,7 @@
       </c>
       <c r="H387" t="inlineStr">
         <is>
-          <t>Grade 3</t>
+          <t>Grade 4</t>
         </is>
       </c>
       <c r="I387" t="inlineStr">
@@ -25942,22 +25942,22 @@
       </c>
       <c r="J387" t="inlineStr">
         <is>
-          <t>subj_english</t>
+          <t>subj_arabic</t>
         </is>
       </c>
       <c r="K387" t="inlineStr">
         <is>
-          <t>English</t>
+          <t>Arabic</t>
         </is>
       </c>
       <c r="L387" t="inlineStr">
         <is>
-          <t>tchr_marham</t>
+          <t>tchr_ali</t>
         </is>
       </c>
       <c r="M387" t="inlineStr">
         <is>
-          <t>Teacher Marham</t>
+          <t>Ustadh Ali</t>
         </is>
       </c>
       <c r="N387" t="n">
@@ -25974,7 +25974,7 @@
         </is>
       </c>
       <c r="C388" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D388" t="inlineStr">
         <is>
@@ -25983,12 +25983,12 @@
       </c>
       <c r="E388" t="inlineStr">
         <is>
-          <t>sec_grade_4_abdur_rahman_ibn_awf_1st_shift</t>
+          <t>sec_grade_4_az_zubair_ibn_al_awwaam_2nd_shift</t>
         </is>
       </c>
       <c r="F388" t="inlineStr">
         <is>
-          <t>GRADE 4 - ABDUR RAHMAN IBN AWF (1ST SHIFT)</t>
+          <t>GRADE 4 - AZ ZUBAIR IBN AL AWWAAM (2ND SHIFT)</t>
         </is>
       </c>
       <c r="G388" t="inlineStr">
@@ -26003,27 +26003,27 @@
       </c>
       <c r="I388" t="inlineStr">
         <is>
-          <t>ODL - 1ST SHIFT</t>
+          <t>ODL - 2ND SHIFT</t>
         </is>
       </c>
       <c r="J388" t="inlineStr">
         <is>
-          <t>subj_arabic</t>
+          <t>subj_araling_panlipunan</t>
         </is>
       </c>
       <c r="K388" t="inlineStr">
         <is>
-          <t>Arabic</t>
+          <t>Araling Panlipunan</t>
         </is>
       </c>
       <c r="L388" t="inlineStr">
         <is>
-          <t>tchr_ali</t>
+          <t>tchr_monisa</t>
         </is>
       </c>
       <c r="M388" t="inlineStr">
         <is>
-          <t>Ustadh Ali</t>
+          <t>Teacher Monisa</t>
         </is>
       </c>
       <c r="N388" t="n">
@@ -26049,12 +26049,12 @@
       </c>
       <c r="E389" t="inlineStr">
         <is>
-          <t>sec_grade_4_az_zubair_ibn_al_awwaam_2nd_shift</t>
+          <t>sec_grade_4_ikrimah_ibn_abi_jahl_2nd_shift</t>
         </is>
       </c>
       <c r="F389" t="inlineStr">
         <is>
-          <t>GRADE 4 - AZ ZUBAIR IBN AL AWWAAM (2ND SHIFT)</t>
+          <t>GRADE 4 - IKRIMAH IBN ABI JAHL (2ND SHIFT)</t>
         </is>
       </c>
       <c r="G389" t="inlineStr">
@@ -26074,22 +26074,22 @@
       </c>
       <c r="J389" t="inlineStr">
         <is>
-          <t>subj_araling_panlipunan</t>
+          <t>subj_filipino</t>
         </is>
       </c>
       <c r="K389" t="inlineStr">
         <is>
-          <t>Araling Panlipunan</t>
+          <t>Filipino</t>
         </is>
       </c>
       <c r="L389" t="inlineStr">
         <is>
-          <t>tchr_monisa</t>
+          <t>tchr_norhydie</t>
         </is>
       </c>
       <c r="M389" t="inlineStr">
         <is>
-          <t>Teacher Monisa</t>
+          <t>Teacher Norhydie</t>
         </is>
       </c>
       <c r="N389" t="n">
@@ -26106,7 +26106,7 @@
         </is>
       </c>
       <c r="C390" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D390" t="inlineStr">
         <is>
@@ -26115,12 +26115,12 @@
       </c>
       <c r="E390" t="inlineStr">
         <is>
-          <t>sec_grade_4_ikrimah_ibn_abi_jahl_2nd_shift</t>
+          <t>sec_grade_4_usayd_ibn_hudhayr_1st_shift_mix</t>
         </is>
       </c>
       <c r="F390" t="inlineStr">
         <is>
-          <t>GRADE 4 - IKRIMAH IBN ABI JAHL (2ND SHIFT)</t>
+          <t>GRADE 4 - USAYD IBN HUDHAYR (1ST SHIFT) - MIX</t>
         </is>
       </c>
       <c r="G390" t="inlineStr">
@@ -26135,27 +26135,27 @@
       </c>
       <c r="I390" t="inlineStr">
         <is>
-          <t>ODL - 2ND SHIFT</t>
+          <t>ODL - 1ST SHIFT</t>
         </is>
       </c>
       <c r="J390" t="inlineStr">
         <is>
-          <t>subj_filipino</t>
+          <t>subj_fil4</t>
         </is>
       </c>
       <c r="K390" t="inlineStr">
         <is>
-          <t>Filipino</t>
+          <t>Fil4</t>
         </is>
       </c>
       <c r="L390" t="inlineStr">
         <is>
-          <t>tchr_norhydie</t>
+          <t>tchr_zuhora</t>
         </is>
       </c>
       <c r="M390" t="inlineStr">
         <is>
-          <t>Teacher Norhydie</t>
+          <t>Teacher Zuhora</t>
         </is>
       </c>
       <c r="N390" t="n">
@@ -26172,7 +26172,7 @@
         </is>
       </c>
       <c r="C391" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D391" t="inlineStr">
         <is>
@@ -26181,12 +26181,12 @@
       </c>
       <c r="E391" t="inlineStr">
         <is>
-          <t>sec_grade_4_usayd_ibn_hudhayr_1st_shift_mix</t>
+          <t>sec_grade_4_hassan_ibn_thabit_2nd_shift_mix</t>
         </is>
       </c>
       <c r="F391" t="inlineStr">
         <is>
-          <t>GRADE 4 - USAYD IBN HUDHAYR (1ST SHIFT) - MIX</t>
+          <t>GRADE 4 -HASSAN IBN THABIT (2ND SHIFT) - MIX</t>
         </is>
       </c>
       <c r="G391" t="inlineStr">
@@ -26201,27 +26201,27 @@
       </c>
       <c r="I391" t="inlineStr">
         <is>
-          <t>ODL - 1ST SHIFT</t>
+          <t>ODL - 2ND SHIFT</t>
         </is>
       </c>
       <c r="J391" t="inlineStr">
         <is>
-          <t>subj_fil4</t>
+          <t>subj_science</t>
         </is>
       </c>
       <c r="K391" t="inlineStr">
         <is>
-          <t>Fil4</t>
+          <t>Science</t>
         </is>
       </c>
       <c r="L391" t="inlineStr">
         <is>
-          <t>tchr_zuhora</t>
+          <t>tchr_saimonah</t>
         </is>
       </c>
       <c r="M391" t="inlineStr">
         <is>
-          <t>Teacher Zuhora</t>
+          <t>Teacher Saimonah</t>
         </is>
       </c>
       <c r="N391" t="n">
@@ -26247,12 +26247,12 @@
       </c>
       <c r="E392" t="inlineStr">
         <is>
-          <t>sec_grade_4_hassan_ibn_thabit_2nd_shift_mix</t>
+          <t>sec_grade_5_al_harith_bin_awf_2nd_shift</t>
         </is>
       </c>
       <c r="F392" t="inlineStr">
         <is>
-          <t>GRADE 4 -HASSAN IBN THABIT (2ND SHIFT) - MIX</t>
+          <t>GRADE 5 - AL HARITH BIN AWF (2ND SHIFT)</t>
         </is>
       </c>
       <c r="G392" t="inlineStr">
@@ -26262,7 +26262,7 @@
       </c>
       <c r="H392" t="inlineStr">
         <is>
-          <t>Grade 4</t>
+          <t>Grade 5</t>
         </is>
       </c>
       <c r="I392" t="inlineStr">
@@ -26272,22 +26272,22 @@
       </c>
       <c r="J392" t="inlineStr">
         <is>
-          <t>subj_science</t>
+          <t>subj_math</t>
         </is>
       </c>
       <c r="K392" t="inlineStr">
         <is>
-          <t>Science</t>
+          <t>Math</t>
         </is>
       </c>
       <c r="L392" t="inlineStr">
         <is>
-          <t>tchr_saimonah</t>
+          <t>tchr_fhairudz</t>
         </is>
       </c>
       <c r="M392" t="inlineStr">
         <is>
-          <t>Teacher Saimonah</t>
+          <t>Teacher Fhairudz</t>
         </is>
       </c>
       <c r="N392" t="n">
@@ -26304,7 +26304,7 @@
         </is>
       </c>
       <c r="C393" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D393" t="inlineStr">
         <is>
@@ -26313,12 +26313,12 @@
       </c>
       <c r="E393" t="inlineStr">
         <is>
-          <t>sec_grade_5_al_harith_bin_awf_2nd_shift</t>
+          <t>sec_grade_5_hamza_ibn_abdul_1st_shift</t>
         </is>
       </c>
       <c r="F393" t="inlineStr">
         <is>
-          <t>GRADE 5 - AL HARITH BIN AWF (2ND SHIFT)</t>
+          <t>GRADE 5 - HAMZA IBN ABDUL (1ST SHIFT)</t>
         </is>
       </c>
       <c r="G393" t="inlineStr">
@@ -26333,27 +26333,27 @@
       </c>
       <c r="I393" t="inlineStr">
         <is>
-          <t>ODL - 2ND SHIFT</t>
+          <t>ODL - 1ST SHIFT</t>
         </is>
       </c>
       <c r="J393" t="inlineStr">
         <is>
-          <t>subj_math</t>
+          <t>subj_english</t>
         </is>
       </c>
       <c r="K393" t="inlineStr">
         <is>
-          <t>Math</t>
+          <t>English</t>
         </is>
       </c>
       <c r="L393" t="inlineStr">
         <is>
-          <t>tchr_fhairudz</t>
+          <t>tchr_jessa</t>
         </is>
       </c>
       <c r="M393" t="inlineStr">
         <is>
-          <t>Teacher Fhairudz</t>
+          <t>Teacher Jessa</t>
         </is>
       </c>
       <c r="N393" t="n">
@@ -26370,7 +26370,7 @@
         </is>
       </c>
       <c r="C394" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D394" t="inlineStr">
         <is>
@@ -26379,12 +26379,12 @@
       </c>
       <c r="E394" t="inlineStr">
         <is>
-          <t>sec_grade_5_hamza_ibn_abdul_1st_shift</t>
+          <t>sec_grade_5_ja_far_ibn_abi_talib_2nd_shift_mix</t>
         </is>
       </c>
       <c r="F394" t="inlineStr">
         <is>
-          <t>GRADE 5 - HAMZA IBN ABDUL (1ST SHIFT)</t>
+          <t>GRADE 5 - JA'FAR IBN ABI TALIB (2ND SHIFT) - MIX</t>
         </is>
       </c>
       <c r="G394" t="inlineStr">
@@ -26399,27 +26399,27 @@
       </c>
       <c r="I394" t="inlineStr">
         <is>
-          <t>ODL - 1ST SHIFT</t>
+          <t>ODL - 2ND SHIFT</t>
         </is>
       </c>
       <c r="J394" t="inlineStr">
         <is>
-          <t>subj_english</t>
+          <t>subj_qur_an</t>
         </is>
       </c>
       <c r="K394" t="inlineStr">
         <is>
-          <t>English</t>
+          <t>Qur'an</t>
         </is>
       </c>
       <c r="L394" t="inlineStr">
         <is>
-          <t>tchr_jessa</t>
+          <t>tchr_obaydah</t>
         </is>
       </c>
       <c r="M394" t="inlineStr">
         <is>
-          <t>Teacher Jessa</t>
+          <t>Ustadh Obaydah</t>
         </is>
       </c>
       <c r="N394" t="n">
@@ -26436,7 +26436,7 @@
         </is>
       </c>
       <c r="C395" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D395" t="inlineStr">
         <is>
@@ -26445,12 +26445,12 @@
       </c>
       <c r="E395" t="inlineStr">
         <is>
-          <t>sec_grade_5_ja_far_ibn_abi_talib_2nd_shift_mix</t>
+          <t>sec_grade_5_muhammad_ibn_maslamah_1st_shift</t>
         </is>
       </c>
       <c r="F395" t="inlineStr">
         <is>
-          <t>GRADE 5 - JA'FAR IBN ABI TALIB (2ND SHIFT) - MIX</t>
+          <t>GRADE 5 - MUHAMMAD IBN MASLAMAH (1ST SHIFT)</t>
         </is>
       </c>
       <c r="G395" t="inlineStr">
@@ -26465,27 +26465,27 @@
       </c>
       <c r="I395" t="inlineStr">
         <is>
-          <t>ODL - 2ND SHIFT</t>
+          <t>ODL - 1ST SHIFT</t>
         </is>
       </c>
       <c r="J395" t="inlineStr">
         <is>
-          <t>subj_qur_an</t>
+          <t>subj_mapeh</t>
         </is>
       </c>
       <c r="K395" t="inlineStr">
         <is>
-          <t>Qur'an</t>
+          <t>MAPEH</t>
         </is>
       </c>
       <c r="L395" t="inlineStr">
         <is>
-          <t>tchr_obaydah</t>
+          <t>tchr_keychell</t>
         </is>
       </c>
       <c r="M395" t="inlineStr">
         <is>
-          <t>Ustadh Obaydah</t>
+          <t>Teacher Keychell</t>
         </is>
       </c>
       <c r="N395" t="n">
@@ -26502,7 +26502,7 @@
         </is>
       </c>
       <c r="C396" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D396" t="inlineStr">
         <is>
@@ -26511,12 +26511,12 @@
       </c>
       <c r="E396" t="inlineStr">
         <is>
-          <t>sec_grade_5_muhammad_ibn_maslamah_1st_shift</t>
+          <t>sec_grade_5_mus_ab_ibn_abdul_mutalib_2nd_shift</t>
         </is>
       </c>
       <c r="F396" t="inlineStr">
         <is>
-          <t>GRADE 5 - MUHAMMAD IBN MASLAMAH (1ST SHIFT)</t>
+          <t>GRADE 5 - MUS'AB IBN ABDUL MUTALIB (2ND SHIFT)</t>
         </is>
       </c>
       <c r="G396" t="inlineStr">
@@ -26531,27 +26531,27 @@
       </c>
       <c r="I396" t="inlineStr">
         <is>
-          <t>ODL - 1ST SHIFT</t>
+          <t>ODL - 2ND SHIFT</t>
         </is>
       </c>
       <c r="J396" t="inlineStr">
         <is>
-          <t>subj_mapeh</t>
+          <t>subj_arabic</t>
         </is>
       </c>
       <c r="K396" t="inlineStr">
         <is>
-          <t>MAPEH</t>
+          <t>Arabic</t>
         </is>
       </c>
       <c r="L396" t="inlineStr">
         <is>
-          <t>tchr_keychell</t>
+          <t>tchr_ersahad</t>
         </is>
       </c>
       <c r="M396" t="inlineStr">
         <is>
-          <t>Teacher Keychell</t>
+          <t>Ustadh Ersahad</t>
         </is>
       </c>
       <c r="N396" t="n">
@@ -26568,7 +26568,7 @@
         </is>
       </c>
       <c r="C397" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D397" t="inlineStr">
         <is>
@@ -26577,12 +26577,12 @@
       </c>
       <c r="E397" t="inlineStr">
         <is>
-          <t>sec_grade_5_mus_ab_ibn_abdul_mutalib_2nd_shift</t>
+          <t>sec_grade_6_abdullah_ibn_salaam_1st_shift</t>
         </is>
       </c>
       <c r="F397" t="inlineStr">
         <is>
-          <t>GRADE 5 - MUS'AB IBN ABDUL MUTALIB (2ND SHIFT)</t>
+          <t>GRADE 6 - ABDULLAH IBN SALAAM (1ST SHIFT)</t>
         </is>
       </c>
       <c r="G397" t="inlineStr">
@@ -26592,32 +26592,32 @@
       </c>
       <c r="H397" t="inlineStr">
         <is>
-          <t>Grade 5</t>
+          <t>Grade 6</t>
         </is>
       </c>
       <c r="I397" t="inlineStr">
         <is>
-          <t>ODL - 2ND SHIFT</t>
+          <t>ODL - 1ST SHIFT</t>
         </is>
       </c>
       <c r="J397" t="inlineStr">
         <is>
-          <t>subj_arabic</t>
+          <t>subj_shaf</t>
         </is>
       </c>
       <c r="K397" t="inlineStr">
         <is>
-          <t>Arabic</t>
+          <t>SHAF</t>
         </is>
       </c>
       <c r="L397" t="inlineStr">
         <is>
-          <t>tchr_ersahad</t>
+          <t>tchr_abdiraheem</t>
         </is>
       </c>
       <c r="M397" t="inlineStr">
         <is>
-          <t>Ustadh Ersahad</t>
+          <t>Ustadh Abdiraheem</t>
         </is>
       </c>
       <c r="N397" t="n">
@@ -26634,7 +26634,7 @@
         </is>
       </c>
       <c r="C398" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D398" t="inlineStr">
         <is>
@@ -26643,12 +26643,12 @@
       </c>
       <c r="E398" t="inlineStr">
         <is>
-          <t>sec_grade_6_abdullah_ibn_salaam_1st_shift</t>
+          <t>sec_grade_6_khaleed_ibn_waleed_2nd_shift</t>
         </is>
       </c>
       <c r="F398" t="inlineStr">
         <is>
-          <t>GRADE 6 - ABDULLAH IBN SALAAM (1ST SHIFT)</t>
+          <t>GRADE 6 - KHALEED IBN WALEED (2ND SHIFT)</t>
         </is>
       </c>
       <c r="G398" t="inlineStr">
@@ -26663,27 +26663,27 @@
       </c>
       <c r="I398" t="inlineStr">
         <is>
-          <t>ODL - 1ST SHIFT</t>
+          <t>ODL - 2ND SHIFT</t>
         </is>
       </c>
       <c r="J398" t="inlineStr">
         <is>
-          <t>subj_shaf</t>
+          <t>subj_tle</t>
         </is>
       </c>
       <c r="K398" t="inlineStr">
         <is>
-          <t>SHAF</t>
+          <t>TLE</t>
         </is>
       </c>
       <c r="L398" t="inlineStr">
         <is>
-          <t>tchr_abdiraheem</t>
+          <t>tchr_arvin</t>
         </is>
       </c>
       <c r="M398" t="inlineStr">
         <is>
-          <t>Ustadh Abdiraheem</t>
+          <t>Teacher Arvin</t>
         </is>
       </c>
       <c r="N398" t="n">
@@ -26700,7 +26700,7 @@
         </is>
       </c>
       <c r="C399" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D399" t="inlineStr">
         <is>
@@ -26709,47 +26709,47 @@
       </c>
       <c r="E399" t="inlineStr">
         <is>
-          <t>sec_grade_6_khaleed_ibn_waleed_2nd_shift</t>
+          <t>sec_grade_7_abu_sufyan_ibn_al_harith_1st_shift_boys</t>
         </is>
       </c>
       <c r="F399" t="inlineStr">
         <is>
-          <t>GRADE 6 - KHALEED IBN WALEED (2ND SHIFT)</t>
+          <t>GRADE 7 - ABU SUFYAN IBN AL-HARITH (1ST SHIFT) BOYS</t>
         </is>
       </c>
       <c r="G399" t="inlineStr">
         <is>
-          <t>Elementary</t>
+          <t>Junior High School</t>
         </is>
       </c>
       <c r="H399" t="inlineStr">
         <is>
-          <t>Grade 6</t>
+          <t>Grade 7</t>
         </is>
       </c>
       <c r="I399" t="inlineStr">
         <is>
-          <t>ODL - 2ND SHIFT</t>
+          <t>ODL - 1ST SHIFT</t>
         </is>
       </c>
       <c r="J399" t="inlineStr">
         <is>
-          <t>subj_tle</t>
+          <t>subj_shaf</t>
         </is>
       </c>
       <c r="K399" t="inlineStr">
         <is>
-          <t>TLE</t>
+          <t>SHAF</t>
         </is>
       </c>
       <c r="L399" t="inlineStr">
         <is>
-          <t>tchr_arvin</t>
+          <t>tchr_samsuddin</t>
         </is>
       </c>
       <c r="M399" t="inlineStr">
         <is>
-          <t>Teacher Arvin</t>
+          <t>Alim Samsuddin</t>
         </is>
       </c>
       <c r="N399" t="n">
@@ -26766,21 +26766,21 @@
         </is>
       </c>
       <c r="C400" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D400" t="inlineStr">
         <is>
-          <t>03:10 PM – 04:10 PM</t>
+          <t>03:10 PM – 05:20 PM</t>
         </is>
       </c>
       <c r="E400" t="inlineStr">
         <is>
-          <t>sec_grade_7_abu_sufyan_ibn_al_harith_1st_shift_boys</t>
+          <t>sec_grade_7_anas_ibn_malik_2nd_shift_mix</t>
         </is>
       </c>
       <c r="F400" t="inlineStr">
         <is>
-          <t>GRADE 7 - ABU SUFYAN IBN AL-HARITH (1ST SHIFT) BOYS</t>
+          <t>GRADE 7 - ANAS IBN MALIK (2ND SHIFT) - MIX</t>
         </is>
       </c>
       <c r="G400" t="inlineStr">
@@ -26795,31 +26795,31 @@
       </c>
       <c r="I400" t="inlineStr">
         <is>
-          <t>ODL - 1ST SHIFT</t>
+          <t>ODL - 2ND SHIFT</t>
         </is>
       </c>
       <c r="J400" t="inlineStr">
         <is>
-          <t>subj_shaf</t>
+          <t>subj_math</t>
         </is>
       </c>
       <c r="K400" t="inlineStr">
         <is>
-          <t>SHAF</t>
+          <t>Math</t>
         </is>
       </c>
       <c r="L400" t="inlineStr">
         <is>
-          <t>tchr_samsuddin</t>
+          <t>tchr_ethel</t>
         </is>
       </c>
       <c r="M400" t="inlineStr">
         <is>
-          <t>Alim Samsuddin</t>
+          <t>Teacher Ethel</t>
         </is>
       </c>
       <c r="N400" t="n">
-        <v>60</v>
+        <v>120</v>
       </c>
     </row>
     <row r="401">
@@ -26832,21 +26832,21 @@
         </is>
       </c>
       <c r="C401" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D401" t="inlineStr">
         <is>
-          <t>03:10 PM – 05:20 PM</t>
+          <t>03:10 PM – 04:10 PM</t>
         </is>
       </c>
       <c r="E401" t="inlineStr">
         <is>
-          <t>sec_grade_7_anas_ibn_malik_2nd_shift_mix</t>
+          <t>sec_grade_7_usama_ibn_zayd_1st_shift_girls</t>
         </is>
       </c>
       <c r="F401" t="inlineStr">
         <is>
-          <t>GRADE 7 - ANAS IBN MALIK (2ND SHIFT) - MIX</t>
+          <t>GRADE 7 - USAMA IBN ZAYD (1ST SHIFT) GIRLS</t>
         </is>
       </c>
       <c r="G401" t="inlineStr">
@@ -26861,31 +26861,31 @@
       </c>
       <c r="I401" t="inlineStr">
         <is>
-          <t>ODL - 2ND SHIFT</t>
+          <t>ODL - 1ST SHIFT</t>
         </is>
       </c>
       <c r="J401" t="inlineStr">
         <is>
-          <t>subj_math</t>
+          <t>subj_english</t>
         </is>
       </c>
       <c r="K401" t="inlineStr">
         <is>
-          <t>Math</t>
+          <t>English</t>
         </is>
       </c>
       <c r="L401" t="inlineStr">
         <is>
-          <t>tchr_ethel</t>
+          <t>tchr_jairah</t>
         </is>
       </c>
       <c r="M401" t="inlineStr">
         <is>
-          <t>Teacher Ethel</t>
+          <t>Teacher Jairah</t>
         </is>
       </c>
       <c r="N401" t="n">
-        <v>120</v>
+        <v>60</v>
       </c>
     </row>
     <row r="402">
@@ -26898,7 +26898,7 @@
         </is>
       </c>
       <c r="C402" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D402" t="inlineStr">
         <is>
@@ -26907,12 +26907,12 @@
       </c>
       <c r="E402" t="inlineStr">
         <is>
-          <t>sec_grade_7_usama_ibn_zayd_1st_shift_girls</t>
+          <t>sec_grade_8_mu_adh_ibn_jabal_2nd_shift_boys</t>
         </is>
       </c>
       <c r="F402" t="inlineStr">
         <is>
-          <t>GRADE 7 - USAMA IBN ZAYD (1ST SHIFT) GIRLS</t>
+          <t>GRADE 8 - MU'ADH IBN JABAL (2ND SHIFT) - BOYS</t>
         </is>
       </c>
       <c r="G402" t="inlineStr">
@@ -26922,32 +26922,32 @@
       </c>
       <c r="H402" t="inlineStr">
         <is>
-          <t>Grade 7</t>
+          <t>Grade 8</t>
         </is>
       </c>
       <c r="I402" t="inlineStr">
         <is>
-          <t>ODL - 1ST SHIFT</t>
+          <t>ODL - 2ND SHIFT</t>
         </is>
       </c>
       <c r="J402" t="inlineStr">
         <is>
-          <t>subj_english</t>
+          <t>subj_qur_an</t>
         </is>
       </c>
       <c r="K402" t="inlineStr">
         <is>
-          <t>English</t>
+          <t>Qur'an</t>
         </is>
       </c>
       <c r="L402" t="inlineStr">
         <is>
-          <t>tchr_jairah</t>
+          <t>tchr_jaisam</t>
         </is>
       </c>
       <c r="M402" t="inlineStr">
         <is>
-          <t>Teacher Jairah</t>
+          <t>Ustadh Jaisam</t>
         </is>
       </c>
       <c r="N402" t="n">
@@ -26973,12 +26973,12 @@
       </c>
       <c r="E403" t="inlineStr">
         <is>
-          <t>sec_grade_8_mu_adh_ibn_jabal_2nd_shift_boys</t>
+          <t>sec_grade_8_nuaym_ibn_mas_ud_2nd_shift_mix</t>
         </is>
       </c>
       <c r="F403" t="inlineStr">
         <is>
-          <t>GRADE 8 - MU'ADH IBN JABAL (2ND SHIFT) - BOYS</t>
+          <t>GRADE 8 - NUAYM IBN MAS'UD (2ND SHIFT) MIX</t>
         </is>
       </c>
       <c r="G403" t="inlineStr">
@@ -26998,22 +26998,22 @@
       </c>
       <c r="J403" t="inlineStr">
         <is>
-          <t>subj_qur_an</t>
+          <t>subj_values_ed</t>
         </is>
       </c>
       <c r="K403" t="inlineStr">
         <is>
-          <t>Qur'an</t>
+          <t>Values Ed</t>
         </is>
       </c>
       <c r="L403" t="inlineStr">
         <is>
-          <t>tchr_jaisam</t>
+          <t>tchr_wardah</t>
         </is>
       </c>
       <c r="M403" t="inlineStr">
         <is>
-          <t>Ustadh Jaisam</t>
+          <t>Teacher Wardah</t>
         </is>
       </c>
       <c r="N403" t="n">
@@ -27030,7 +27030,7 @@
         </is>
       </c>
       <c r="C404" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D404" t="inlineStr">
         <is>
@@ -27039,12 +27039,12 @@
       </c>
       <c r="E404" t="inlineStr">
         <is>
-          <t>sec_grade_8_nuaym_ibn_mas_ud_2nd_shift_mix</t>
+          <t>sec_grade_8_sa_ad_ibn_mua_dh_1st_shift_girls</t>
         </is>
       </c>
       <c r="F404" t="inlineStr">
         <is>
-          <t>GRADE 8 - NUAYM IBN MAS'UD (2ND SHIFT) MIX</t>
+          <t>GRADE 8 - SA'AD IBN MUA'DH (1ST SHIFT) - GIRLS</t>
         </is>
       </c>
       <c r="G404" t="inlineStr">
@@ -27059,27 +27059,27 @@
       </c>
       <c r="I404" t="inlineStr">
         <is>
-          <t>ODL - 2ND SHIFT</t>
+          <t>ODL - 1ST SHIFT</t>
         </is>
       </c>
       <c r="J404" t="inlineStr">
         <is>
-          <t>subj_values_ed</t>
+          <t>subj_science</t>
         </is>
       </c>
       <c r="K404" t="inlineStr">
         <is>
-          <t>Values Ed</t>
+          <t>Science</t>
         </is>
       </c>
       <c r="L404" t="inlineStr">
         <is>
-          <t>tchr_wardah</t>
+          <t>tchr_radzmia</t>
         </is>
       </c>
       <c r="M404" t="inlineStr">
         <is>
-          <t>Teacher Wardah</t>
+          <t>Teacher Radzmia</t>
         </is>
       </c>
       <c r="N404" t="n">
@@ -27096,21 +27096,21 @@
         </is>
       </c>
       <c r="C405" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D405" t="inlineStr">
         <is>
-          <t>03:10 PM – 04:10 PM</t>
+          <t>03:10 PM – 05:20 PM</t>
         </is>
       </c>
       <c r="E405" t="inlineStr">
         <is>
-          <t>sec_grade_8_sa_ad_ibn_mua_dh_1st_shift_girls</t>
+          <t>sec_grade_9_abu_dharr_al_ghifarri_2nd_shift_boys</t>
         </is>
       </c>
       <c r="F405" t="inlineStr">
         <is>
-          <t>GRADE 8 - SA'AD IBN MUA'DH (1ST SHIFT) - GIRLS</t>
+          <t>GRADE 9 - ABU DHARR AL GHIFARRI (2ND SHIFT) BOYS</t>
         </is>
       </c>
       <c r="G405" t="inlineStr">
@@ -27120,36 +27120,36 @@
       </c>
       <c r="H405" t="inlineStr">
         <is>
-          <t>Grade 8</t>
+          <t>Grade 9</t>
         </is>
       </c>
       <c r="I405" t="inlineStr">
         <is>
-          <t>ODL - 1ST SHIFT</t>
+          <t>ODL - 2ND SHIFT</t>
         </is>
       </c>
       <c r="J405" t="inlineStr">
         <is>
-          <t>subj_science</t>
+          <t>subj_math</t>
         </is>
       </c>
       <c r="K405" t="inlineStr">
         <is>
-          <t>Science</t>
+          <t>Math</t>
         </is>
       </c>
       <c r="L405" t="inlineStr">
         <is>
-          <t>tchr_radzmia</t>
+          <t>tchr_jhelyn</t>
         </is>
       </c>
       <c r="M405" t="inlineStr">
         <is>
-          <t>Teacher Radzmia</t>
+          <t>Teacher Jhelyn</t>
         </is>
       </c>
       <c r="N405" t="n">
-        <v>60</v>
+        <v>120</v>
       </c>
     </row>
     <row r="406">
@@ -27162,21 +27162,21 @@
         </is>
       </c>
       <c r="C406" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D406" t="inlineStr">
         <is>
-          <t>03:10 PM – 05:20 PM</t>
+          <t>03:10 PM – 04:10 PM</t>
         </is>
       </c>
       <c r="E406" t="inlineStr">
         <is>
-          <t>sec_grade_9_abu_dharr_al_ghifarri_2nd_shift_boys</t>
+          <t>sec_grade_9_abu_hurayrah_1st_shift_girls</t>
         </is>
       </c>
       <c r="F406" t="inlineStr">
         <is>
-          <t>GRADE 9 - ABU DHARR AL GHIFARRI (2ND SHIFT) BOYS</t>
+          <t>GRADE 9 - ABU HURAYRAH (1ST SHIFT) GIRLS</t>
         </is>
       </c>
       <c r="G406" t="inlineStr">
@@ -27191,31 +27191,31 @@
       </c>
       <c r="I406" t="inlineStr">
         <is>
-          <t>ODL - 2ND SHIFT</t>
+          <t>ODL - 1ST SHIFT</t>
         </is>
       </c>
       <c r="J406" t="inlineStr">
         <is>
-          <t>subj_math</t>
+          <t>subj_qur_an</t>
         </is>
       </c>
       <c r="K406" t="inlineStr">
         <is>
-          <t>Math</t>
+          <t>Qur'an</t>
         </is>
       </c>
       <c r="L406" t="inlineStr">
         <is>
-          <t>tchr_jhelyn</t>
+          <t>tchr_abdulwahab</t>
         </is>
       </c>
       <c r="M406" t="inlineStr">
         <is>
-          <t>Teacher Jhelyn</t>
+          <t>Alim Abdulwahab</t>
         </is>
       </c>
       <c r="N406" t="n">
-        <v>120</v>
+        <v>60</v>
       </c>
     </row>
     <row r="407">
@@ -27228,7 +27228,7 @@
         </is>
       </c>
       <c r="C407" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D407" t="inlineStr">
         <is>
@@ -27237,12 +27237,12 @@
       </c>
       <c r="E407" t="inlineStr">
         <is>
-          <t>sec_grade_9_abu_hurayrah_1st_shift_girls</t>
+          <t>sec_grade_9_abu_jandal_ibn_suhayl_2nd_shift_girls</t>
         </is>
       </c>
       <c r="F407" t="inlineStr">
         <is>
-          <t>GRADE 9 - ABU HURAYRAH (1ST SHIFT) GIRLS</t>
+          <t>GRADE 9 - ABU JANDAL IBN SUHAYL (2ND SHIFT) GIRLS</t>
         </is>
       </c>
       <c r="G407" t="inlineStr">
@@ -27257,27 +27257,27 @@
       </c>
       <c r="I407" t="inlineStr">
         <is>
-          <t>ODL - 1ST SHIFT</t>
+          <t>ODL - 2ND SHIFT</t>
         </is>
       </c>
       <c r="J407" t="inlineStr">
         <is>
-          <t>subj_qur_an</t>
+          <t>subj_english</t>
         </is>
       </c>
       <c r="K407" t="inlineStr">
         <is>
-          <t>Qur'an</t>
+          <t>English</t>
         </is>
       </c>
       <c r="L407" t="inlineStr">
         <is>
-          <t>tchr_abdulwahab</t>
+          <t>tchr_norhaima</t>
         </is>
       </c>
       <c r="M407" t="inlineStr">
         <is>
-          <t>Alim Abdulwahab</t>
+          <t>Teacher Norhaima</t>
         </is>
       </c>
       <c r="N407" t="n">
@@ -27294,31 +27294,31 @@
         </is>
       </c>
       <c r="C408" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D408" t="inlineStr">
         <is>
-          <t>03:10 PM – 04:10 PM</t>
+          <t>04:20 PM – 05:20 PM</t>
         </is>
       </c>
       <c r="E408" t="inlineStr">
         <is>
-          <t>sec_grade_9_abu_jandal_ibn_suhayl_2nd_shift_girls</t>
+          <t>sec_grade_1_sa_ad_ibn_abi_waqqaas_2nd_shift</t>
         </is>
       </c>
       <c r="F408" t="inlineStr">
         <is>
-          <t>GRADE 9 - ABU JANDAL IBN SUHAYL (2ND SHIFT) GIRLS</t>
+          <t>GRADE 1 - SA'AD IBN ABI WAQQAAS (2ND SHIFT)</t>
         </is>
       </c>
       <c r="G408" t="inlineStr">
         <is>
-          <t>Junior High School</t>
+          <t>Elementary</t>
         </is>
       </c>
       <c r="H408" t="inlineStr">
         <is>
-          <t>Grade 9</t>
+          <t>Grade 1</t>
         </is>
       </c>
       <c r="I408" t="inlineStr">
@@ -27328,22 +27328,22 @@
       </c>
       <c r="J408" t="inlineStr">
         <is>
-          <t>subj_english</t>
+          <t>subj_language</t>
         </is>
       </c>
       <c r="K408" t="inlineStr">
         <is>
-          <t>English</t>
+          <t>Language</t>
         </is>
       </c>
       <c r="L408" t="inlineStr">
         <is>
-          <t>tchr_norhaima</t>
+          <t>tchr_sahdia</t>
         </is>
       </c>
       <c r="M408" t="inlineStr">
         <is>
-          <t>Teacher Norhaima</t>
+          <t>Teacher Sahdia</t>
         </is>
       </c>
       <c r="N408" t="n">
@@ -27369,12 +27369,12 @@
       </c>
       <c r="E409" t="inlineStr">
         <is>
-          <t>sec_grade_1_sa_ad_ibn_abi_waqqaas_2nd_shift</t>
+          <t>sec_grade_1_suhayb_ar_rumi_2nd_shift</t>
         </is>
       </c>
       <c r="F409" t="inlineStr">
         <is>
-          <t>GRADE 1 - SA'AD IBN ABI WAQQAAS (2ND SHIFT)</t>
+          <t>GRADE 1 - SUHAYB AR-RUMI (2ND SHIFT)</t>
         </is>
       </c>
       <c r="G409" t="inlineStr">
@@ -27394,22 +27394,22 @@
       </c>
       <c r="J409" t="inlineStr">
         <is>
-          <t>subj_language</t>
+          <t>subj_arabic</t>
         </is>
       </c>
       <c r="K409" t="inlineStr">
         <is>
-          <t>Language</t>
+          <t>Arabic</t>
         </is>
       </c>
       <c r="L409" t="inlineStr">
         <is>
-          <t>tchr_sahdia</t>
+          <t>tchr_hainur</t>
         </is>
       </c>
       <c r="M409" t="inlineStr">
         <is>
-          <t>Teacher Sahdia</t>
+          <t>Ustadha Hainur</t>
         </is>
       </c>
       <c r="N409" t="n">
@@ -27435,22 +27435,22 @@
       </c>
       <c r="E410" t="inlineStr">
         <is>
-          <t>sec_grade_1_suhayb_ar_rumi_2nd_shift</t>
+          <t>sec_grade_10_abu_ayyub_al_ansari_2nd_shift_boys</t>
         </is>
       </c>
       <c r="F410" t="inlineStr">
         <is>
-          <t>GRADE 1 - SUHAYB AR-RUMI (2ND SHIFT)</t>
+          <t>GRADE 10 - ABU AYYUB AL-ANSARI (2ND SHIFT) BOYS</t>
         </is>
       </c>
       <c r="G410" t="inlineStr">
         <is>
-          <t>Elementary</t>
+          <t>Junior High School</t>
         </is>
       </c>
       <c r="H410" t="inlineStr">
         <is>
-          <t>Grade 1</t>
+          <t>Grade 10</t>
         </is>
       </c>
       <c r="I410" t="inlineStr">
@@ -27460,22 +27460,22 @@
       </c>
       <c r="J410" t="inlineStr">
         <is>
-          <t>subj_arabic</t>
+          <t>subj_tle</t>
         </is>
       </c>
       <c r="K410" t="inlineStr">
         <is>
-          <t>Arabic</t>
+          <t>TLE</t>
         </is>
       </c>
       <c r="L410" t="inlineStr">
         <is>
-          <t>tchr_hainur</t>
+          <t>tchr_angeleni</t>
         </is>
       </c>
       <c r="M410" t="inlineStr">
         <is>
-          <t>Ustadha Hainur</t>
+          <t>Teacher Angeleni</t>
         </is>
       </c>
       <c r="N410" t="n">
@@ -27492,7 +27492,7 @@
         </is>
       </c>
       <c r="C411" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D411" t="inlineStr">
         <is>
@@ -27501,47 +27501,47 @@
       </c>
       <c r="E411" t="inlineStr">
         <is>
-          <t>sec_grade_10_abu_ayyub_al_ansari_2nd_shift_boys</t>
+          <t>sec_grade_11_1st_shift_girls</t>
         </is>
       </c>
       <c r="F411" t="inlineStr">
         <is>
-          <t>GRADE 10 - ABU AYYUB AL-ANSARI (2ND SHIFT) BOYS</t>
+          <t>GRADE 11 (1ST SHIFT GIRLS)</t>
         </is>
       </c>
       <c r="G411" t="inlineStr">
         <is>
-          <t>Junior High School</t>
+          <t>Senior High School</t>
         </is>
       </c>
       <c r="H411" t="inlineStr">
         <is>
-          <t>Grade 10</t>
+          <t>Grade 11</t>
         </is>
       </c>
       <c r="I411" t="inlineStr">
         <is>
-          <t>ODL - 2ND SHIFT</t>
+          <t>ODL - 1ST SHIFT</t>
         </is>
       </c>
       <c r="J411" t="inlineStr">
         <is>
-          <t>subj_tle</t>
+          <t>subj_shaf</t>
         </is>
       </c>
       <c r="K411" t="inlineStr">
         <is>
-          <t>TLE</t>
+          <t>SHAF</t>
         </is>
       </c>
       <c r="L411" t="inlineStr">
         <is>
-          <t>tchr_angeleni</t>
+          <t>tchr_samsuddin</t>
         </is>
       </c>
       <c r="M411" t="inlineStr">
         <is>
-          <t>Teacher Angeleni</t>
+          <t>Alim Samsuddin</t>
         </is>
       </c>
       <c r="N411" t="n">
@@ -27558,7 +27558,7 @@
         </is>
       </c>
       <c r="C412" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D412" t="inlineStr">
         <is>
@@ -27567,12 +27567,12 @@
       </c>
       <c r="E412" t="inlineStr">
         <is>
-          <t>sec_grade_11_1st_shift_girls</t>
+          <t>sec_grade_11_2nd_shift_boys</t>
         </is>
       </c>
       <c r="F412" t="inlineStr">
         <is>
-          <t>GRADE 11 (1ST SHIFT GIRLS)</t>
+          <t>GRADE 11 (2ND SHIFT BOYS)</t>
         </is>
       </c>
       <c r="G412" t="inlineStr">
@@ -27587,27 +27587,27 @@
       </c>
       <c r="I412" t="inlineStr">
         <is>
-          <t>ODL - 1ST SHIFT</t>
+          <t>ODL - 2ND SHIFT</t>
         </is>
       </c>
       <c r="J412" t="inlineStr">
         <is>
-          <t>subj_shaf</t>
+          <t>subj_ec</t>
         </is>
       </c>
       <c r="K412" t="inlineStr">
         <is>
-          <t>SHAF</t>
+          <t>EC</t>
         </is>
       </c>
       <c r="L412" t="inlineStr">
         <is>
-          <t>tchr_samsuddin</t>
+          <t>tchr_nadzra</t>
         </is>
       </c>
       <c r="M412" t="inlineStr">
         <is>
-          <t>Alim Samsuddin</t>
+          <t>Teacher Nadzra</t>
         </is>
       </c>
       <c r="N412" t="n">
@@ -27624,7 +27624,7 @@
         </is>
       </c>
       <c r="C413" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D413" t="inlineStr">
         <is>
@@ -27633,12 +27633,12 @@
       </c>
       <c r="E413" t="inlineStr">
         <is>
-          <t>sec_grade_11_2nd_shift_boys</t>
+          <t>sec_grade_12_abu_musa_al_ashari</t>
         </is>
       </c>
       <c r="F413" t="inlineStr">
         <is>
-          <t>GRADE 11 (2ND SHIFT BOYS)</t>
+          <t>GRADE 12 - ABU MUSA AL-ASHARI</t>
         </is>
       </c>
       <c r="G413" t="inlineStr">
@@ -27648,32 +27648,32 @@
       </c>
       <c r="H413" t="inlineStr">
         <is>
-          <t>Grade 11</t>
+          <t>Grade 12</t>
         </is>
       </c>
       <c r="I413" t="inlineStr">
         <is>
-          <t>ODL - 2ND SHIFT</t>
+          <t>ODL - 1ST SHIFT</t>
         </is>
       </c>
       <c r="J413" t="inlineStr">
         <is>
-          <t>subj_ec</t>
+          <t>subj_prac_res_2</t>
         </is>
       </c>
       <c r="K413" t="inlineStr">
         <is>
-          <t>EC</t>
+          <t>Prac. Res. 2</t>
         </is>
       </c>
       <c r="L413" t="inlineStr">
         <is>
-          <t>tchr_nadzra</t>
+          <t>tchr_aniah</t>
         </is>
       </c>
       <c r="M413" t="inlineStr">
         <is>
-          <t>Teacher Nadzra</t>
+          <t>Teacher Aniah</t>
         </is>
       </c>
       <c r="N413" t="n">
@@ -27690,7 +27690,7 @@
         </is>
       </c>
       <c r="C414" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D414" t="inlineStr">
         <is>
@@ -27699,47 +27699,47 @@
       </c>
       <c r="E414" t="inlineStr">
         <is>
-          <t>sec_grade_12_abu_musa_al_ashari</t>
+          <t>sec_grade_2_aasim_ibn_thabit_2nd_shift</t>
         </is>
       </c>
       <c r="F414" t="inlineStr">
         <is>
-          <t>GRADE 12 - ABU MUSA AL-ASHARI</t>
+          <t>GRADE 2 - AASIM IBN THABIT (2ND SHIFT)</t>
         </is>
       </c>
       <c r="G414" t="inlineStr">
         <is>
-          <t>Senior High School</t>
+          <t>Elementary</t>
         </is>
       </c>
       <c r="H414" t="inlineStr">
         <is>
-          <t>Grade 12</t>
+          <t>Grade 2</t>
         </is>
       </c>
       <c r="I414" t="inlineStr">
         <is>
-          <t>ODL - 1ST SHIFT</t>
+          <t>ODL - 2ND SHIFT</t>
         </is>
       </c>
       <c r="J414" t="inlineStr">
         <is>
-          <t>subj_prac_res_2</t>
+          <t>subj_shaf</t>
         </is>
       </c>
       <c r="K414" t="inlineStr">
         <is>
-          <t>Prac. Res. 2</t>
+          <t>SHAF</t>
         </is>
       </c>
       <c r="L414" t="inlineStr">
         <is>
-          <t>tchr_aniah</t>
+          <t>tchr_abdul_karim</t>
         </is>
       </c>
       <c r="M414" t="inlineStr">
         <is>
-          <t>Teacher Aniah</t>
+          <t>Alim Abdul Karim</t>
         </is>
       </c>
       <c r="N414" t="n">
@@ -27765,12 +27765,12 @@
       </c>
       <c r="E415" t="inlineStr">
         <is>
-          <t>sec_grade_2_aasim_ibn_thabit_2nd_shift</t>
+          <t>sec_grade_3_as_ad_ibn_zurarah_2nd_shift_mix</t>
         </is>
       </c>
       <c r="F415" t="inlineStr">
         <is>
-          <t>GRADE 2 - AASIM IBN THABIT (2ND SHIFT)</t>
+          <t>GRADE 3 - AS'AD IBN ZURARAH (2ND SHIFT) MIX</t>
         </is>
       </c>
       <c r="G415" t="inlineStr">
@@ -27780,7 +27780,7 @@
       </c>
       <c r="H415" t="inlineStr">
         <is>
-          <t>Grade 2</t>
+          <t>Grade 3</t>
         </is>
       </c>
       <c r="I415" t="inlineStr">
@@ -27800,12 +27800,12 @@
       </c>
       <c r="L415" t="inlineStr">
         <is>
-          <t>tchr_abdul_karim</t>
+          <t>tchr_faidh</t>
         </is>
       </c>
       <c r="M415" t="inlineStr">
         <is>
-          <t>Alim Abdul Karim</t>
+          <t>Ustadh Faidh</t>
         </is>
       </c>
       <c r="N415" t="n">
@@ -27831,12 +27831,12 @@
       </c>
       <c r="E416" t="inlineStr">
         <is>
-          <t>sec_grade_3_as_ad_ibn_zurarah_2nd_shift_mix</t>
+          <t>sec_grade_3_thabit_ibn_qays_2nd_shift_boys</t>
         </is>
       </c>
       <c r="F416" t="inlineStr">
         <is>
-          <t>GRADE 3 - AS'AD IBN ZURARAH (2ND SHIFT) MIX</t>
+          <t>GRADE 3 - THABIT IBN QAYS (2ND SHIFT) - BOYS</t>
         </is>
       </c>
       <c r="G416" t="inlineStr">
@@ -27866,12 +27866,12 @@
       </c>
       <c r="L416" t="inlineStr">
         <is>
-          <t>tchr_faidh</t>
+          <t>tchr_ersahad</t>
         </is>
       </c>
       <c r="M416" t="inlineStr">
         <is>
-          <t>Ustadh Faidh</t>
+          <t>Ustadh Ersahad</t>
         </is>
       </c>
       <c r="N416" t="n">
@@ -27897,12 +27897,12 @@
       </c>
       <c r="E417" t="inlineStr">
         <is>
-          <t>sec_grade_3_thabit_ibn_qays_2nd_shift_boys</t>
+          <t>sec_grade_3_zayd_ibn_haritha_2nd_shift_girls</t>
         </is>
       </c>
       <c r="F417" t="inlineStr">
         <is>
-          <t>GRADE 3 - THABIT IBN QAYS (2ND SHIFT) - BOYS</t>
+          <t>GRADE 3 - ZAYD IBN HARITHA (2ND SHIFT) - GIRLS</t>
         </is>
       </c>
       <c r="G417" t="inlineStr">
@@ -27922,22 +27922,22 @@
       </c>
       <c r="J417" t="inlineStr">
         <is>
-          <t>subj_shaf</t>
+          <t>subj_qur_an</t>
         </is>
       </c>
       <c r="K417" t="inlineStr">
         <is>
-          <t>SHAF</t>
+          <t>Qur'an</t>
         </is>
       </c>
       <c r="L417" t="inlineStr">
         <is>
-          <t>tchr_ersahad</t>
+          <t>tchr_obaydah</t>
         </is>
       </c>
       <c r="M417" t="inlineStr">
         <is>
-          <t>Ustadh Ersahad</t>
+          <t>Ustadh Obaydah</t>
         </is>
       </c>
       <c r="N417" t="n">
@@ -27963,12 +27963,12 @@
       </c>
       <c r="E418" t="inlineStr">
         <is>
-          <t>sec_grade_3_zayd_ibn_haritha_2nd_shift_girls</t>
+          <t>sec_grade_4_az_zubair_ibn_al_awwaam_2nd_shift</t>
         </is>
       </c>
       <c r="F418" t="inlineStr">
         <is>
-          <t>GRADE 3 - ZAYD IBN HARITHA (2ND SHIFT) - GIRLS</t>
+          <t>GRADE 4 - AZ ZUBAIR IBN AL AWWAAM (2ND SHIFT)</t>
         </is>
       </c>
       <c r="G418" t="inlineStr">
@@ -27978,7 +27978,7 @@
       </c>
       <c r="H418" t="inlineStr">
         <is>
-          <t>Grade 3</t>
+          <t>Grade 4</t>
         </is>
       </c>
       <c r="I418" t="inlineStr">
@@ -27988,22 +27988,22 @@
       </c>
       <c r="J418" t="inlineStr">
         <is>
-          <t>subj_qur_an</t>
+          <t>subj_tle</t>
         </is>
       </c>
       <c r="K418" t="inlineStr">
         <is>
-          <t>Qur'an</t>
+          <t>TLE</t>
         </is>
       </c>
       <c r="L418" t="inlineStr">
         <is>
-          <t>tchr_obaydah</t>
+          <t>tchr_monisa</t>
         </is>
       </c>
       <c r="M418" t="inlineStr">
         <is>
-          <t>Ustadh Obaydah</t>
+          <t>Teacher Monisa</t>
         </is>
       </c>
       <c r="N418" t="n">
@@ -28029,12 +28029,12 @@
       </c>
       <c r="E419" t="inlineStr">
         <is>
-          <t>sec_grade_4_az_zubair_ibn_al_awwaam_2nd_shift</t>
+          <t>sec_grade_4_ikrimah_ibn_abi_jahl_2nd_shift</t>
         </is>
       </c>
       <c r="F419" t="inlineStr">
         <is>
-          <t>GRADE 4 - AZ ZUBAIR IBN AL AWWAAM (2ND SHIFT)</t>
+          <t>GRADE 4 - IKRIMAH IBN ABI JAHL (2ND SHIFT)</t>
         </is>
       </c>
       <c r="G419" t="inlineStr">
@@ -28054,22 +28054,22 @@
       </c>
       <c r="J419" t="inlineStr">
         <is>
-          <t>subj_tle</t>
+          <t>subj_mapeh</t>
         </is>
       </c>
       <c r="K419" t="inlineStr">
         <is>
-          <t>TLE</t>
+          <t>MAPEH</t>
         </is>
       </c>
       <c r="L419" t="inlineStr">
         <is>
-          <t>tchr_monisa</t>
+          <t>tchr_halnaisa</t>
         </is>
       </c>
       <c r="M419" t="inlineStr">
         <is>
-          <t>Teacher Monisa</t>
+          <t>Teacher Halnaisa</t>
         </is>
       </c>
       <c r="N419" t="n">
@@ -28095,12 +28095,12 @@
       </c>
       <c r="E420" t="inlineStr">
         <is>
-          <t>sec_grade_4_ikrimah_ibn_abi_jahl_2nd_shift</t>
+          <t>sec_grade_4_hassan_ibn_thabit_2nd_shift_mix</t>
         </is>
       </c>
       <c r="F420" t="inlineStr">
         <is>
-          <t>GRADE 4 - IKRIMAH IBN ABI JAHL (2ND SHIFT)</t>
+          <t>GRADE 4 -HASSAN IBN THABIT (2ND SHIFT) - MIX</t>
         </is>
       </c>
       <c r="G420" t="inlineStr">
@@ -28120,22 +28120,22 @@
       </c>
       <c r="J420" t="inlineStr">
         <is>
-          <t>subj_mapeh</t>
+          <t>subj_shaf</t>
         </is>
       </c>
       <c r="K420" t="inlineStr">
         <is>
-          <t>MAPEH</t>
+          <t>SHAF</t>
         </is>
       </c>
       <c r="L420" t="inlineStr">
         <is>
-          <t>tchr_halnaisa</t>
+          <t>tchr_abdiraheem</t>
         </is>
       </c>
       <c r="M420" t="inlineStr">
         <is>
-          <t>Teacher Halnaisa</t>
+          <t>Ustadh Abdiraheem</t>
         </is>
       </c>
       <c r="N420" t="n">
@@ -28161,12 +28161,12 @@
       </c>
       <c r="E421" t="inlineStr">
         <is>
-          <t>sec_grade_4_hassan_ibn_thabit_2nd_shift_mix</t>
+          <t>sec_grade_5_al_harith_bin_awf_2nd_shift</t>
         </is>
       </c>
       <c r="F421" t="inlineStr">
         <is>
-          <t>GRADE 4 -HASSAN IBN THABIT (2ND SHIFT) - MIX</t>
+          <t>GRADE 5 - AL HARITH BIN AWF (2ND SHIFT)</t>
         </is>
       </c>
       <c r="G421" t="inlineStr">
@@ -28176,7 +28176,7 @@
       </c>
       <c r="H421" t="inlineStr">
         <is>
-          <t>Grade 4</t>
+          <t>Grade 5</t>
         </is>
       </c>
       <c r="I421" t="inlineStr">
@@ -28186,22 +28186,22 @@
       </c>
       <c r="J421" t="inlineStr">
         <is>
-          <t>subj_shaf</t>
+          <t>subj_mapeh</t>
         </is>
       </c>
       <c r="K421" t="inlineStr">
         <is>
-          <t>SHAF</t>
+          <t>MAPEH</t>
         </is>
       </c>
       <c r="L421" t="inlineStr">
         <is>
-          <t>tchr_abdiraheem</t>
+          <t>tchr_norhydie</t>
         </is>
       </c>
       <c r="M421" t="inlineStr">
         <is>
-          <t>Ustadh Abdiraheem</t>
+          <t>Teacher Norhydie</t>
         </is>
       </c>
       <c r="N421" t="n">
@@ -28227,12 +28227,12 @@
       </c>
       <c r="E422" t="inlineStr">
         <is>
-          <t>sec_grade_5_al_harith_bin_awf_2nd_shift</t>
+          <t>sec_grade_5_ja_far_ibn_abi_talib_2nd_shift_mix</t>
         </is>
       </c>
       <c r="F422" t="inlineStr">
         <is>
-          <t>GRADE 5 - AL HARITH BIN AWF (2ND SHIFT)</t>
+          <t>GRADE 5 - JA'FAR IBN ABI TALIB (2ND SHIFT) - MIX</t>
         </is>
       </c>
       <c r="G422" t="inlineStr">
@@ -28252,22 +28252,22 @@
       </c>
       <c r="J422" t="inlineStr">
         <is>
-          <t>subj_mapeh</t>
+          <t>subj_filipino</t>
         </is>
       </c>
       <c r="K422" t="inlineStr">
         <is>
-          <t>MAPEH</t>
+          <t>Filipino</t>
         </is>
       </c>
       <c r="L422" t="inlineStr">
         <is>
-          <t>tchr_norhydie</t>
+          <t>tchr_jenny</t>
         </is>
       </c>
       <c r="M422" t="inlineStr">
         <is>
-          <t>Teacher Norhydie</t>
+          <t>Teacher Jenny</t>
         </is>
       </c>
       <c r="N422" t="n">
@@ -28293,12 +28293,12 @@
       </c>
       <c r="E423" t="inlineStr">
         <is>
-          <t>sec_grade_5_ja_far_ibn_abi_talib_2nd_shift_mix</t>
+          <t>sec_grade_5_mus_ab_ibn_abdul_mutalib_2nd_shift</t>
         </is>
       </c>
       <c r="F423" t="inlineStr">
         <is>
-          <t>GRADE 5 - JA'FAR IBN ABI TALIB (2ND SHIFT) - MIX</t>
+          <t>GRADE 5 - MUS'AB IBN ABDUL MUTALIB (2ND SHIFT)</t>
         </is>
       </c>
       <c r="G423" t="inlineStr">
@@ -28318,22 +28318,22 @@
       </c>
       <c r="J423" t="inlineStr">
         <is>
-          <t>subj_filipino</t>
+          <t>subj_science</t>
         </is>
       </c>
       <c r="K423" t="inlineStr">
         <is>
-          <t>Filipino</t>
+          <t>Science</t>
         </is>
       </c>
       <c r="L423" t="inlineStr">
         <is>
-          <t>tchr_jenny</t>
+          <t>tchr_anna</t>
         </is>
       </c>
       <c r="M423" t="inlineStr">
         <is>
-          <t>Teacher Jenny</t>
+          <t>Teacher Anna</t>
         </is>
       </c>
       <c r="N423" t="n">
@@ -28354,17 +28354,17 @@
       </c>
       <c r="D424" t="inlineStr">
         <is>
-          <t>04:20 PM – 05:20 PM</t>
+          <t>04:20 PM – 06:30 PM</t>
         </is>
       </c>
       <c r="E424" t="inlineStr">
         <is>
-          <t>sec_grade_5_mus_ab_ibn_abdul_mutalib_2nd_shift</t>
+          <t>sec_grade_6_dihya_ibn_khalifah_2nd_shift_girls</t>
         </is>
       </c>
       <c r="F424" t="inlineStr">
         <is>
-          <t>GRADE 5 - MUS'AB IBN ABDUL MUTALIB (2ND SHIFT)</t>
+          <t>GRADE 6 - DIHYA IBN KHALIFAH (2ND SHIFT) GIRLS</t>
         </is>
       </c>
       <c r="G424" t="inlineStr">
@@ -28374,7 +28374,7 @@
       </c>
       <c r="H424" t="inlineStr">
         <is>
-          <t>Grade 5</t>
+          <t>Grade 6</t>
         </is>
       </c>
       <c r="I424" t="inlineStr">
@@ -28384,26 +28384,26 @@
       </c>
       <c r="J424" t="inlineStr">
         <is>
-          <t>subj_science</t>
+          <t>subj_math</t>
         </is>
       </c>
       <c r="K424" t="inlineStr">
         <is>
-          <t>Science</t>
+          <t>Math</t>
         </is>
       </c>
       <c r="L424" t="inlineStr">
         <is>
-          <t>tchr_anna</t>
+          <t>tchr_saimonah</t>
         </is>
       </c>
       <c r="M424" t="inlineStr">
         <is>
-          <t>Teacher Anna</t>
+          <t>Teacher Saimonah</t>
         </is>
       </c>
       <c r="N424" t="n">
-        <v>60</v>
+        <v>120</v>
       </c>
     </row>
     <row r="425">
@@ -28425,12 +28425,12 @@
       </c>
       <c r="E425" t="inlineStr">
         <is>
-          <t>sec_grade_6_dihya_ibn_khalifah_2nd_shift_girls</t>
+          <t>sec_grade_6_khaleed_ibn_waleed_2nd_shift</t>
         </is>
       </c>
       <c r="F425" t="inlineStr">
         <is>
-          <t>GRADE 6 - DIHYA IBN KHALIFAH (2ND SHIFT) GIRLS</t>
+          <t>GRADE 6 - KHALEED IBN WALEED (2ND SHIFT)</t>
         </is>
       </c>
       <c r="G425" t="inlineStr">
@@ -28460,12 +28460,12 @@
       </c>
       <c r="L425" t="inlineStr">
         <is>
-          <t>tchr_saimonah</t>
+          <t>tchr_katrina</t>
         </is>
       </c>
       <c r="M425" t="inlineStr">
         <is>
-          <t>Teacher Saimonah</t>
+          <t>Teacher Katrina</t>
         </is>
       </c>
       <c r="N425" t="n">
@@ -28486,27 +28486,27 @@
       </c>
       <c r="D426" t="inlineStr">
         <is>
-          <t>04:20 PM – 06:30 PM</t>
+          <t>04:20 PM – 05:20 PM</t>
         </is>
       </c>
       <c r="E426" t="inlineStr">
         <is>
-          <t>sec_grade_6_khaleed_ibn_waleed_2nd_shift</t>
+          <t>sec_grade_8_mu_adh_ibn_jabal_2nd_shift_boys</t>
         </is>
       </c>
       <c r="F426" t="inlineStr">
         <is>
-          <t>GRADE 6 - KHALEED IBN WALEED (2ND SHIFT)</t>
+          <t>GRADE 8 - MU'ADH IBN JABAL (2ND SHIFT) - BOYS</t>
         </is>
       </c>
       <c r="G426" t="inlineStr">
         <is>
-          <t>Elementary</t>
+          <t>Junior High School</t>
         </is>
       </c>
       <c r="H426" t="inlineStr">
         <is>
-          <t>Grade 6</t>
+          <t>Grade 8</t>
         </is>
       </c>
       <c r="I426" t="inlineStr">
@@ -28516,26 +28516,26 @@
       </c>
       <c r="J426" t="inlineStr">
         <is>
-          <t>subj_math</t>
+          <t>subj_filipino</t>
         </is>
       </c>
       <c r="K426" t="inlineStr">
         <is>
-          <t>Math</t>
+          <t>Filipino</t>
         </is>
       </c>
       <c r="L426" t="inlineStr">
         <is>
-          <t>tchr_katrina</t>
+          <t>tchr_sophia</t>
         </is>
       </c>
       <c r="M426" t="inlineStr">
         <is>
-          <t>Teacher Katrina</t>
+          <t>Teacher Sophia</t>
         </is>
       </c>
       <c r="N426" t="n">
-        <v>120</v>
+        <v>60</v>
       </c>
     </row>
     <row r="427">
@@ -28552,17 +28552,17 @@
       </c>
       <c r="D427" t="inlineStr">
         <is>
-          <t>04:20 PM – 05:20 PM</t>
+          <t>04:20 PM – 06:30 PM</t>
         </is>
       </c>
       <c r="E427" t="inlineStr">
         <is>
-          <t>sec_grade_8_mu_adh_ibn_jabal_2nd_shift_boys</t>
+          <t>sec_grade_8_nuaym_ibn_mas_ud_2nd_shift_mix</t>
         </is>
       </c>
       <c r="F427" t="inlineStr">
         <is>
-          <t>GRADE 8 - MU'ADH IBN JABAL (2ND SHIFT) - BOYS</t>
+          <t>GRADE 8 - NUAYM IBN MAS'UD (2ND SHIFT) MIX</t>
         </is>
       </c>
       <c r="G427" t="inlineStr">
@@ -28582,26 +28582,26 @@
       </c>
       <c r="J427" t="inlineStr">
         <is>
-          <t>subj_filipino</t>
+          <t>subj_math</t>
         </is>
       </c>
       <c r="K427" t="inlineStr">
         <is>
-          <t>Filipino</t>
+          <t>Math</t>
         </is>
       </c>
       <c r="L427" t="inlineStr">
         <is>
-          <t>tchr_sophia</t>
+          <t>tchr_fhairudz</t>
         </is>
       </c>
       <c r="M427" t="inlineStr">
         <is>
-          <t>Teacher Sophia</t>
+          <t>Teacher Fhairudz</t>
         </is>
       </c>
       <c r="N427" t="n">
-        <v>60</v>
+        <v>120</v>
       </c>
     </row>
     <row r="428">
@@ -28618,17 +28618,17 @@
       </c>
       <c r="D428" t="inlineStr">
         <is>
-          <t>04:20 PM – 06:30 PM</t>
+          <t>04:20 PM – 05:20 PM</t>
         </is>
       </c>
       <c r="E428" t="inlineStr">
         <is>
-          <t>sec_grade_8_nuaym_ibn_mas_ud_2nd_shift_mix</t>
+          <t>sec_grade_9_abu_jandal_ibn_suhayl_2nd_shift_girls</t>
         </is>
       </c>
       <c r="F428" t="inlineStr">
         <is>
-          <t>GRADE 8 - NUAYM IBN MAS'UD (2ND SHIFT) MIX</t>
+          <t>GRADE 9 - ABU JANDAL IBN SUHAYL (2ND SHIFT) GIRLS</t>
         </is>
       </c>
       <c r="G428" t="inlineStr">
@@ -28638,7 +28638,7 @@
       </c>
       <c r="H428" t="inlineStr">
         <is>
-          <t>Grade 8</t>
+          <t>Grade 9</t>
         </is>
       </c>
       <c r="I428" t="inlineStr">
@@ -28648,26 +28648,26 @@
       </c>
       <c r="J428" t="inlineStr">
         <is>
-          <t>subj_math</t>
+          <t>subj_mapeh</t>
         </is>
       </c>
       <c r="K428" t="inlineStr">
         <is>
-          <t>Math</t>
+          <t>MAPEH</t>
         </is>
       </c>
       <c r="L428" t="inlineStr">
         <is>
-          <t>tchr_fhairudz</t>
+          <t>tchr_mohaymen</t>
         </is>
       </c>
       <c r="M428" t="inlineStr">
         <is>
-          <t>Teacher Fhairudz</t>
+          <t>Sir Mohaymen</t>
         </is>
       </c>
       <c r="N428" t="n">
-        <v>120</v>
+        <v>60</v>
       </c>
     </row>
     <row r="429">
@@ -28689,22 +28689,22 @@
       </c>
       <c r="E429" t="inlineStr">
         <is>
-          <t>sec_grade_9_abu_jandal_ibn_suhayl_2nd_shift_girls</t>
+          <t>sec_k1_husain_ibn_ali_2nd_shift</t>
         </is>
       </c>
       <c r="F429" t="inlineStr">
         <is>
-          <t>GRADE 9 - ABU JANDAL IBN SUHAYL (2ND SHIFT) GIRLS</t>
+          <t>K1 - HUSAIN IBN ALI (2ND SHIFT)</t>
         </is>
       </c>
       <c r="G429" t="inlineStr">
         <is>
-          <t>Junior High School</t>
+          <t>Elementary</t>
         </is>
       </c>
       <c r="H429" t="inlineStr">
         <is>
-          <t>Grade 9</t>
+          <t>Kinder 1</t>
         </is>
       </c>
       <c r="I429" t="inlineStr">
@@ -28714,22 +28714,22 @@
       </c>
       <c r="J429" t="inlineStr">
         <is>
-          <t>subj_mapeh</t>
+          <t>subj_arabic</t>
         </is>
       </c>
       <c r="K429" t="inlineStr">
         <is>
-          <t>MAPEH</t>
+          <t>Arabic</t>
         </is>
       </c>
       <c r="L429" t="inlineStr">
         <is>
-          <t>tchr_mohaymen</t>
+          <t>tchr_bustamante</t>
         </is>
       </c>
       <c r="M429" t="inlineStr">
         <is>
-          <t>Sir Mohaymen</t>
+          <t>Alim Bustamante</t>
         </is>
       </c>
       <c r="N429" t="n">
@@ -28755,12 +28755,12 @@
       </c>
       <c r="E430" t="inlineStr">
         <is>
-          <t>sec_k1_husain_ibn_ali_2nd_shift</t>
+          <t>sec_k2_umar_ibn_al_khattab_2nd_shift</t>
         </is>
       </c>
       <c r="F430" t="inlineStr">
         <is>
-          <t>K1 - HUSAIN IBN ALI (2ND SHIFT)</t>
+          <t>K2 - UMAR IBN AL-KHATTAB (2ND SHIFT)</t>
         </is>
       </c>
       <c r="G430" t="inlineStr">
@@ -28770,7 +28770,7 @@
       </c>
       <c r="H430" t="inlineStr">
         <is>
-          <t>Kinder 1</t>
+          <t>Kinder 2</t>
         </is>
       </c>
       <c r="I430" t="inlineStr">
@@ -28790,12 +28790,12 @@
       </c>
       <c r="L430" t="inlineStr">
         <is>
-          <t>tchr_bustamante</t>
+          <t>tchr_silfah</t>
         </is>
       </c>
       <c r="M430" t="inlineStr">
         <is>
-          <t>Alim Bustamante</t>
+          <t>Ustadh Silfah</t>
         </is>
       </c>
       <c r="N430" t="n">
@@ -28812,21 +28812,21 @@
         </is>
       </c>
       <c r="C431" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D431" t="inlineStr">
         <is>
-          <t>04:20 PM – 05:20 PM</t>
+          <t>05:30 PM – 06:30 PM</t>
         </is>
       </c>
       <c r="E431" t="inlineStr">
         <is>
-          <t>sec_k2_umar_ibn_al_khattab_2nd_shift</t>
+          <t>sec_grade_1_suhayb_ar_rumi_2nd_shift</t>
         </is>
       </c>
       <c r="F431" t="inlineStr">
         <is>
-          <t>K2 - UMAR IBN AL-KHATTAB (2ND SHIFT)</t>
+          <t>GRADE 1 - SUHAYB AR-RUMI (2ND SHIFT)</t>
         </is>
       </c>
       <c r="G431" t="inlineStr">
@@ -28836,7 +28836,7 @@
       </c>
       <c r="H431" t="inlineStr">
         <is>
-          <t>Kinder 2</t>
+          <t>Grade 1</t>
         </is>
       </c>
       <c r="I431" t="inlineStr">
@@ -28846,22 +28846,22 @@
       </c>
       <c r="J431" t="inlineStr">
         <is>
-          <t>subj_arabic</t>
+          <t>subj_gmrc</t>
         </is>
       </c>
       <c r="K431" t="inlineStr">
         <is>
-          <t>Arabic</t>
+          <t>GMRC</t>
         </is>
       </c>
       <c r="L431" t="inlineStr">
         <is>
-          <t>tchr_silfah</t>
+          <t>tchr_sahdia</t>
         </is>
       </c>
       <c r="M431" t="inlineStr">
         <is>
-          <t>Ustadh Silfah</t>
+          <t>Teacher Sahdia</t>
         </is>
       </c>
       <c r="N431" t="n">
@@ -28887,22 +28887,22 @@
       </c>
       <c r="E432" t="inlineStr">
         <is>
-          <t>sec_grade_1_suhayb_ar_rumi_2nd_shift</t>
+          <t>sec_grade_10_abu_ayyub_al_ansari_2nd_shift_boys</t>
         </is>
       </c>
       <c r="F432" t="inlineStr">
         <is>
-          <t>GRADE 1 - SUHAYB AR-RUMI (2ND SHIFT)</t>
+          <t>GRADE 10 - ABU AYYUB AL-ANSARI (2ND SHIFT) BOYS</t>
         </is>
       </c>
       <c r="G432" t="inlineStr">
         <is>
-          <t>Elementary</t>
+          <t>Junior High School</t>
         </is>
       </c>
       <c r="H432" t="inlineStr">
         <is>
-          <t>Grade 1</t>
+          <t>Grade 10</t>
         </is>
       </c>
       <c r="I432" t="inlineStr">
@@ -28912,22 +28912,22 @@
       </c>
       <c r="J432" t="inlineStr">
         <is>
-          <t>subj_gmrc</t>
+          <t>subj_social_studies</t>
         </is>
       </c>
       <c r="K432" t="inlineStr">
         <is>
-          <t>GMRC</t>
+          <t>Social Science</t>
         </is>
       </c>
       <c r="L432" t="inlineStr">
         <is>
-          <t>tchr_sahdia</t>
+          <t>tchr_sophia</t>
         </is>
       </c>
       <c r="M432" t="inlineStr">
         <is>
-          <t>Teacher Sahdia</t>
+          <t>Teacher Sophia</t>
         </is>
       </c>
       <c r="N432" t="n">
@@ -28953,22 +28953,22 @@
       </c>
       <c r="E433" t="inlineStr">
         <is>
-          <t>sec_grade_10_abu_ayyub_al_ansari_2nd_shift_boys</t>
+          <t>sec_grade_11_2nd_shift_boys</t>
         </is>
       </c>
       <c r="F433" t="inlineStr">
         <is>
-          <t>GRADE 10 - ABU AYYUB AL-ANSARI (2ND SHIFT) BOYS</t>
+          <t>GRADE 11 (2ND SHIFT BOYS)</t>
         </is>
       </c>
       <c r="G433" t="inlineStr">
         <is>
-          <t>Junior High School</t>
+          <t>Senior High School</t>
         </is>
       </c>
       <c r="H433" t="inlineStr">
         <is>
-          <t>Grade 10</t>
+          <t>Grade 11</t>
         </is>
       </c>
       <c r="I433" t="inlineStr">
@@ -28978,22 +28978,22 @@
       </c>
       <c r="J433" t="inlineStr">
         <is>
-          <t>subj_social_studies</t>
+          <t>subj_lcs</t>
         </is>
       </c>
       <c r="K433" t="inlineStr">
         <is>
-          <t>Social Science</t>
+          <t>LCS</t>
         </is>
       </c>
       <c r="L433" t="inlineStr">
         <is>
-          <t>tchr_sophia</t>
+          <t>tchr_norhaima</t>
         </is>
       </c>
       <c r="M433" t="inlineStr">
         <is>
-          <t>Teacher Sophia</t>
+          <t>Teacher Norhaima</t>
         </is>
       </c>
       <c r="N433" t="n">
@@ -29019,22 +29019,22 @@
       </c>
       <c r="E434" t="inlineStr">
         <is>
-          <t>sec_grade_11_2nd_shift_boys</t>
+          <t>sec_grade_2_aasim_ibn_thabit_2nd_shift</t>
         </is>
       </c>
       <c r="F434" t="inlineStr">
         <is>
-          <t>GRADE 11 (2ND SHIFT BOYS)</t>
+          <t>GRADE 2 - AASIM IBN THABIT (2ND SHIFT)</t>
         </is>
       </c>
       <c r="G434" t="inlineStr">
         <is>
-          <t>Senior High School</t>
+          <t>Elementary</t>
         </is>
       </c>
       <c r="H434" t="inlineStr">
         <is>
-          <t>Grade 11</t>
+          <t>Grade 2</t>
         </is>
       </c>
       <c r="I434" t="inlineStr">
@@ -29044,22 +29044,22 @@
       </c>
       <c r="J434" t="inlineStr">
         <is>
-          <t>subj_lcs</t>
+          <t>subj_qur_an</t>
         </is>
       </c>
       <c r="K434" t="inlineStr">
         <is>
-          <t>LCS</t>
+          <t>Qur'an</t>
         </is>
       </c>
       <c r="L434" t="inlineStr">
         <is>
-          <t>tchr_norhaima</t>
+          <t>tchr_obaydah</t>
         </is>
       </c>
       <c r="M434" t="inlineStr">
         <is>
-          <t>Teacher Norhaima</t>
+          <t>Ustadh Obaydah</t>
         </is>
       </c>
       <c r="N434" t="n">
@@ -29085,12 +29085,12 @@
       </c>
       <c r="E435" t="inlineStr">
         <is>
-          <t>sec_grade_2_aasim_ibn_thabit_2nd_shift</t>
+          <t>sec_grade_2_saeed_ibn_zayd_2nd_shift</t>
         </is>
       </c>
       <c r="F435" t="inlineStr">
         <is>
-          <t>GRADE 2 - AASIM IBN THABIT (2ND SHIFT)</t>
+          <t>GRADE 2 - SAEED IBN ZAYD (2ND SHIFT)</t>
         </is>
       </c>
       <c r="G435" t="inlineStr">
@@ -29110,22 +29110,22 @@
       </c>
       <c r="J435" t="inlineStr">
         <is>
-          <t>subj_qur_an</t>
+          <t>subj_arabic</t>
         </is>
       </c>
       <c r="K435" t="inlineStr">
         <is>
-          <t>Qur'an</t>
+          <t>Arabic</t>
         </is>
       </c>
       <c r="L435" t="inlineStr">
         <is>
-          <t>tchr_obaydah</t>
+          <t>tchr_hainur</t>
         </is>
       </c>
       <c r="M435" t="inlineStr">
         <is>
-          <t>Ustadh Obaydah</t>
+          <t>Ustadha Hainur</t>
         </is>
       </c>
       <c r="N435" t="n">
@@ -29151,12 +29151,12 @@
       </c>
       <c r="E436" t="inlineStr">
         <is>
-          <t>sec_grade_2_saeed_ibn_zayd_2nd_shift</t>
+          <t>sec_grade_3_as_ad_ibn_zurarah_2nd_shift_mix</t>
         </is>
       </c>
       <c r="F436" t="inlineStr">
         <is>
-          <t>GRADE 2 - SAEED IBN ZAYD (2ND SHIFT)</t>
+          <t>GRADE 3 - AS'AD IBN ZURARAH (2ND SHIFT) MIX</t>
         </is>
       </c>
       <c r="G436" t="inlineStr">
@@ -29166,7 +29166,7 @@
       </c>
       <c r="H436" t="inlineStr">
         <is>
-          <t>Grade 2</t>
+          <t>Grade 3</t>
         </is>
       </c>
       <c r="I436" t="inlineStr">
@@ -29176,22 +29176,22 @@
       </c>
       <c r="J436" t="inlineStr">
         <is>
-          <t>subj_arabic</t>
+          <t>subj_filipino</t>
         </is>
       </c>
       <c r="K436" t="inlineStr">
         <is>
-          <t>Arabic</t>
+          <t>Filipino</t>
         </is>
       </c>
       <c r="L436" t="inlineStr">
         <is>
-          <t>tchr_hainur</t>
+          <t>tchr_jenny</t>
         </is>
       </c>
       <c r="M436" t="inlineStr">
         <is>
-          <t>Ustadha Hainur</t>
+          <t>Teacher Jenny</t>
         </is>
       </c>
       <c r="N436" t="n">
@@ -29217,12 +29217,12 @@
       </c>
       <c r="E437" t="inlineStr">
         <is>
-          <t>sec_grade_3_as_ad_ibn_zurarah_2nd_shift_mix</t>
+          <t>sec_grade_3_thabit_ibn_qays_2nd_shift_boys</t>
         </is>
       </c>
       <c r="F437" t="inlineStr">
         <is>
-          <t>GRADE 3 - AS'AD IBN ZURARAH (2ND SHIFT) MIX</t>
+          <t>GRADE 3 - THABIT IBN QAYS (2ND SHIFT) - BOYS</t>
         </is>
       </c>
       <c r="G437" t="inlineStr">
@@ -29252,12 +29252,12 @@
       </c>
       <c r="L437" t="inlineStr">
         <is>
-          <t>tchr_jenny</t>
+          <t>tchr_normylah</t>
         </is>
       </c>
       <c r="M437" t="inlineStr">
         <is>
-          <t>Teacher Jenny</t>
+          <t>Teacher Normylah</t>
         </is>
       </c>
       <c r="N437" t="n">
@@ -29283,12 +29283,12 @@
       </c>
       <c r="E438" t="inlineStr">
         <is>
-          <t>sec_grade_3_thabit_ibn_qays_2nd_shift_boys</t>
+          <t>sec_grade_3_zayd_ibn_haritha_2nd_shift_girls</t>
         </is>
       </c>
       <c r="F438" t="inlineStr">
         <is>
-          <t>GRADE 3 - THABIT IBN QAYS (2ND SHIFT) - BOYS</t>
+          <t>GRADE 3 - ZAYD IBN HARITHA (2ND SHIFT) - GIRLS</t>
         </is>
       </c>
       <c r="G438" t="inlineStr">
@@ -29308,22 +29308,22 @@
       </c>
       <c r="J438" t="inlineStr">
         <is>
-          <t>subj_filipino</t>
+          <t>subj_science</t>
         </is>
       </c>
       <c r="K438" t="inlineStr">
         <is>
-          <t>Filipino</t>
+          <t>Science</t>
         </is>
       </c>
       <c r="L438" t="inlineStr">
         <is>
-          <t>tchr_normylah</t>
+          <t>tchr_jerlyn</t>
         </is>
       </c>
       <c r="M438" t="inlineStr">
         <is>
-          <t>Teacher Normylah</t>
+          <t>Teacher Jerlyn</t>
         </is>
       </c>
       <c r="N438" t="n">
@@ -29349,12 +29349,12 @@
       </c>
       <c r="E439" t="inlineStr">
         <is>
-          <t>sec_grade_3_zayd_ibn_haritha_2nd_shift_girls</t>
+          <t>sec_grade_4_az_zubair_ibn_al_awwaam_2nd_shift</t>
         </is>
       </c>
       <c r="F439" t="inlineStr">
         <is>
-          <t>GRADE 3 - ZAYD IBN HARITHA (2ND SHIFT) - GIRLS</t>
+          <t>GRADE 4 - AZ ZUBAIR IBN AL AWWAAM (2ND SHIFT)</t>
         </is>
       </c>
       <c r="G439" t="inlineStr">
@@ -29364,7 +29364,7 @@
       </c>
       <c r="H439" t="inlineStr">
         <is>
-          <t>Grade 3</t>
+          <t>Grade 4</t>
         </is>
       </c>
       <c r="I439" t="inlineStr">
@@ -29384,12 +29384,12 @@
       </c>
       <c r="L439" t="inlineStr">
         <is>
-          <t>tchr_jerlyn</t>
+          <t>tchr_anna</t>
         </is>
       </c>
       <c r="M439" t="inlineStr">
         <is>
-          <t>Teacher Jerlyn</t>
+          <t>Teacher Anna</t>
         </is>
       </c>
       <c r="N439" t="n">
@@ -29415,12 +29415,12 @@
       </c>
       <c r="E440" t="inlineStr">
         <is>
-          <t>sec_grade_4_az_zubair_ibn_al_awwaam_2nd_shift</t>
+          <t>sec_grade_4_ikrimah_ibn_abi_jahl_2nd_shift</t>
         </is>
       </c>
       <c r="F440" t="inlineStr">
         <is>
-          <t>GRADE 4 - AZ ZUBAIR IBN AL AWWAAM (2ND SHIFT)</t>
+          <t>GRADE 4 - IKRIMAH IBN ABI JAHL (2ND SHIFT)</t>
         </is>
       </c>
       <c r="G440" t="inlineStr">
@@ -29440,22 +29440,22 @@
       </c>
       <c r="J440" t="inlineStr">
         <is>
-          <t>subj_science</t>
+          <t>subj_math</t>
         </is>
       </c>
       <c r="K440" t="inlineStr">
         <is>
-          <t>Science</t>
+          <t>Math</t>
         </is>
       </c>
       <c r="L440" t="inlineStr">
         <is>
-          <t>tchr_anna</t>
+          <t>tchr_arvin</t>
         </is>
       </c>
       <c r="M440" t="inlineStr">
         <is>
-          <t>Teacher Anna</t>
+          <t>Teacher Arvin</t>
         </is>
       </c>
       <c r="N440" t="n">
@@ -29481,12 +29481,12 @@
       </c>
       <c r="E441" t="inlineStr">
         <is>
-          <t>sec_grade_4_ikrimah_ibn_abi_jahl_2nd_shift</t>
+          <t>sec_grade_4_hassan_ibn_thabit_2nd_shift_mix</t>
         </is>
       </c>
       <c r="F441" t="inlineStr">
         <is>
-          <t>GRADE 4 - IKRIMAH IBN ABI JAHL (2ND SHIFT)</t>
+          <t>GRADE 4 -HASSAN IBN THABIT (2ND SHIFT) - MIX</t>
         </is>
       </c>
       <c r="G441" t="inlineStr">
@@ -29506,22 +29506,22 @@
       </c>
       <c r="J441" t="inlineStr">
         <is>
-          <t>subj_math</t>
+          <t>subj_araling_panlipunan</t>
         </is>
       </c>
       <c r="K441" t="inlineStr">
         <is>
-          <t>Math</t>
+          <t>Araling Panlipunan</t>
         </is>
       </c>
       <c r="L441" t="inlineStr">
         <is>
-          <t>tchr_arvin</t>
+          <t>tchr_monisa</t>
         </is>
       </c>
       <c r="M441" t="inlineStr">
         <is>
-          <t>Teacher Arvin</t>
+          <t>Teacher Monisa</t>
         </is>
       </c>
       <c r="N441" t="n">
@@ -29547,12 +29547,12 @@
       </c>
       <c r="E442" t="inlineStr">
         <is>
-          <t>sec_grade_4_hassan_ibn_thabit_2nd_shift_mix</t>
+          <t>sec_grade_5_al_harith_bin_awf_2nd_shift</t>
         </is>
       </c>
       <c r="F442" t="inlineStr">
         <is>
-          <t>GRADE 4 -HASSAN IBN THABIT (2ND SHIFT) - MIX</t>
+          <t>GRADE 5 - AL HARITH BIN AWF (2ND SHIFT)</t>
         </is>
       </c>
       <c r="G442" t="inlineStr">
@@ -29562,7 +29562,7 @@
       </c>
       <c r="H442" t="inlineStr">
         <is>
-          <t>Grade 4</t>
+          <t>Grade 5</t>
         </is>
       </c>
       <c r="I442" t="inlineStr">
@@ -29572,22 +29572,22 @@
       </c>
       <c r="J442" t="inlineStr">
         <is>
-          <t>subj_araling_panlipunan</t>
+          <t>subj_filipino</t>
         </is>
       </c>
       <c r="K442" t="inlineStr">
         <is>
-          <t>Araling Panlipunan</t>
+          <t>Filipino</t>
         </is>
       </c>
       <c r="L442" t="inlineStr">
         <is>
-          <t>tchr_monisa</t>
+          <t>tchr_joanna</t>
         </is>
       </c>
       <c r="M442" t="inlineStr">
         <is>
-          <t>Teacher Monisa</t>
+          <t>Teacher Joanna</t>
         </is>
       </c>
       <c r="N442" t="n">
@@ -29613,12 +29613,12 @@
       </c>
       <c r="E443" t="inlineStr">
         <is>
-          <t>sec_grade_5_al_harith_bin_awf_2nd_shift</t>
+          <t>sec_grade_5_ja_far_ibn_abi_talib_2nd_shift_mix</t>
         </is>
       </c>
       <c r="F443" t="inlineStr">
         <is>
-          <t>GRADE 5 - AL HARITH BIN AWF (2ND SHIFT)</t>
+          <t>GRADE 5 - JA'FAR IBN ABI TALIB (2ND SHIFT) - MIX</t>
         </is>
       </c>
       <c r="G443" t="inlineStr">
@@ -29638,22 +29638,22 @@
       </c>
       <c r="J443" t="inlineStr">
         <is>
-          <t>subj_filipino</t>
+          <t>subj_shaf</t>
         </is>
       </c>
       <c r="K443" t="inlineStr">
         <is>
-          <t>Filipino</t>
+          <t>SHAF</t>
         </is>
       </c>
       <c r="L443" t="inlineStr">
         <is>
-          <t>tchr_joanna</t>
+          <t>tchr_faidh</t>
         </is>
       </c>
       <c r="M443" t="inlineStr">
         <is>
-          <t>Teacher Joanna</t>
+          <t>Ustadh Faidh</t>
         </is>
       </c>
       <c r="N443" t="n">
@@ -29679,12 +29679,12 @@
       </c>
       <c r="E444" t="inlineStr">
         <is>
-          <t>sec_grade_5_ja_far_ibn_abi_talib_2nd_shift_mix</t>
+          <t>sec_grade_5_mus_ab_ibn_abdul_mutalib_2nd_shift</t>
         </is>
       </c>
       <c r="F444" t="inlineStr">
         <is>
-          <t>GRADE 5 - JA'FAR IBN ABI TALIB (2ND SHIFT) - MIX</t>
+          <t>GRADE 5 - MUS'AB IBN ABDUL MUTALIB (2ND SHIFT)</t>
         </is>
       </c>
       <c r="G444" t="inlineStr">
@@ -29704,22 +29704,22 @@
       </c>
       <c r="J444" t="inlineStr">
         <is>
-          <t>subj_shaf</t>
+          <t>subj_gmrc</t>
         </is>
       </c>
       <c r="K444" t="inlineStr">
         <is>
-          <t>SHAF</t>
+          <t>GMRC</t>
         </is>
       </c>
       <c r="L444" t="inlineStr">
         <is>
-          <t>tchr_faidh</t>
+          <t>tchr_jairah</t>
         </is>
       </c>
       <c r="M444" t="inlineStr">
         <is>
-          <t>Ustadh Faidh</t>
+          <t>Teacher Jairah</t>
         </is>
       </c>
       <c r="N444" t="n">
@@ -29745,22 +29745,22 @@
       </c>
       <c r="E445" t="inlineStr">
         <is>
-          <t>sec_grade_5_mus_ab_ibn_abdul_mutalib_2nd_shift</t>
+          <t>sec_grade_8_mu_adh_ibn_jabal_2nd_shift_boys</t>
         </is>
       </c>
       <c r="F445" t="inlineStr">
         <is>
-          <t>GRADE 5 - MUS'AB IBN ABDUL MUTALIB (2ND SHIFT)</t>
+          <t>GRADE 8 - MU'ADH IBN JABAL (2ND SHIFT) - BOYS</t>
         </is>
       </c>
       <c r="G445" t="inlineStr">
         <is>
-          <t>Elementary</t>
+          <t>Junior High School</t>
         </is>
       </c>
       <c r="H445" t="inlineStr">
         <is>
-          <t>Grade 5</t>
+          <t>Grade 8</t>
         </is>
       </c>
       <c r="I445" t="inlineStr">
@@ -29770,22 +29770,22 @@
       </c>
       <c r="J445" t="inlineStr">
         <is>
-          <t>subj_gmrc</t>
+          <t>subj_tle</t>
         </is>
       </c>
       <c r="K445" t="inlineStr">
         <is>
-          <t>GMRC</t>
+          <t>TLE</t>
         </is>
       </c>
       <c r="L445" t="inlineStr">
         <is>
-          <t>tchr_jairah</t>
+          <t>tchr_halnaisa</t>
         </is>
       </c>
       <c r="M445" t="inlineStr">
         <is>
-          <t>Teacher Jairah</t>
+          <t>Teacher Halnaisa</t>
         </is>
       </c>
       <c r="N445" t="n">
@@ -29811,12 +29811,12 @@
       </c>
       <c r="E446" t="inlineStr">
         <is>
-          <t>sec_grade_8_mu_adh_ibn_jabal_2nd_shift_boys</t>
+          <t>sec_grade_9_abu_dharr_al_ghifarri_2nd_shift_boys</t>
         </is>
       </c>
       <c r="F446" t="inlineStr">
         <is>
-          <t>GRADE 8 - MU'ADH IBN JABAL (2ND SHIFT) - BOYS</t>
+          <t>GRADE 9 - ABU DHARR AL GHIFARRI (2ND SHIFT) BOYS</t>
         </is>
       </c>
       <c r="G446" t="inlineStr">
@@ -29826,7 +29826,7 @@
       </c>
       <c r="H446" t="inlineStr">
         <is>
-          <t>Grade 8</t>
+          <t>Grade 9</t>
         </is>
       </c>
       <c r="I446" t="inlineStr">
@@ -29836,22 +29836,22 @@
       </c>
       <c r="J446" t="inlineStr">
         <is>
-          <t>subj_tle</t>
+          <t>subj_shaf</t>
         </is>
       </c>
       <c r="K446" t="inlineStr">
         <is>
-          <t>TLE</t>
+          <t>SHAF</t>
         </is>
       </c>
       <c r="L446" t="inlineStr">
         <is>
-          <t>tchr_halnaisa</t>
+          <t>tchr_samsuddin</t>
         </is>
       </c>
       <c r="M446" t="inlineStr">
         <is>
-          <t>Teacher Halnaisa</t>
+          <t>Alim Samsuddin</t>
         </is>
       </c>
       <c r="N446" t="n">
@@ -29877,12 +29877,12 @@
       </c>
       <c r="E447" t="inlineStr">
         <is>
-          <t>sec_grade_9_abu_dharr_al_ghifarri_2nd_shift_boys</t>
+          <t>sec_grade_9_abu_jandal_ibn_suhayl_2nd_shift_girls</t>
         </is>
       </c>
       <c r="F447" t="inlineStr">
         <is>
-          <t>GRADE 9 - ABU DHARR AL GHIFARRI (2ND SHIFT) BOYS</t>
+          <t>GRADE 9 - ABU JANDAL IBN SUHAYL (2ND SHIFT) GIRLS</t>
         </is>
       </c>
       <c r="G447" t="inlineStr">
@@ -29902,22 +29902,22 @@
       </c>
       <c r="J447" t="inlineStr">
         <is>
-          <t>subj_shaf</t>
+          <t>subj_arabic</t>
         </is>
       </c>
       <c r="K447" t="inlineStr">
         <is>
-          <t>SHAF</t>
+          <t>Arabic</t>
         </is>
       </c>
       <c r="L447" t="inlineStr">
         <is>
-          <t>tchr_samsuddin</t>
+          <t>tchr_ali</t>
         </is>
       </c>
       <c r="M447" t="inlineStr">
         <is>
-          <t>Alim Samsuddin</t>
+          <t>Ustadh Ali</t>
         </is>
       </c>
       <c r="N447" t="n">
@@ -29926,64 +29926,64 @@
     </row>
     <row r="448">
       <c r="A448" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B448" t="inlineStr">
         <is>
-          <t>Sunday, September 6, 2026</t>
+          <t>Monday, September 7, 2026</t>
         </is>
       </c>
       <c r="C448" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D448" t="inlineStr">
         <is>
-          <t>05:30 PM – 06:30 PM</t>
+          <t>08:00 AM – 09:00 AM</t>
         </is>
       </c>
       <c r="E448" t="inlineStr">
         <is>
-          <t>sec_grade_9_abu_jandal_ibn_suhayl_2nd_shift_girls</t>
+          <t>sec_grade_6_face_to_face</t>
         </is>
       </c>
       <c r="F448" t="inlineStr">
         <is>
-          <t>GRADE 9 - ABU JANDAL IBN SUHAYL (2ND SHIFT) GIRLS</t>
+          <t>GRADE  6  FACE TO FACE</t>
         </is>
       </c>
       <c r="G448" t="inlineStr">
         <is>
-          <t>Junior High School</t>
+          <t>Elementary</t>
         </is>
       </c>
       <c r="H448" t="inlineStr">
         <is>
-          <t>Grade 9</t>
+          <t>Grade 6</t>
         </is>
       </c>
       <c r="I448" t="inlineStr">
         <is>
-          <t>ODL - 2ND SHIFT</t>
+          <t>F2F</t>
         </is>
       </c>
       <c r="J448" t="inlineStr">
         <is>
-          <t>subj_arabic</t>
+          <t>subj_qur_an</t>
         </is>
       </c>
       <c r="K448" t="inlineStr">
         <is>
-          <t>Arabic</t>
+          <t>Qur'an</t>
         </is>
       </c>
       <c r="L448" t="inlineStr">
         <is>
-          <t>tchr_ali</t>
+          <t>tchr_faidh</t>
         </is>
       </c>
       <c r="M448" t="inlineStr">
         <is>
-          <t>Ustadh Ali</t>
+          <t>Ustadh Faidh</t>
         </is>
       </c>
       <c r="N448" t="n">
@@ -30009,12 +30009,12 @@
       </c>
       <c r="E449" t="inlineStr">
         <is>
-          <t>sec_grade_6_face_to_face</t>
+          <t>sec_grade_1_face_to_face</t>
         </is>
       </c>
       <c r="F449" t="inlineStr">
         <is>
-          <t>GRADE  6  FACE TO FACE</t>
+          <t>GRADE 1 (FACE TO FACE)</t>
         </is>
       </c>
       <c r="G449" t="inlineStr">
@@ -30024,7 +30024,7 @@
       </c>
       <c r="H449" t="inlineStr">
         <is>
-          <t>Grade 6</t>
+          <t>Grade 1</t>
         </is>
       </c>
       <c r="I449" t="inlineStr">
@@ -30034,22 +30034,22 @@
       </c>
       <c r="J449" t="inlineStr">
         <is>
-          <t>subj_qur_an</t>
+          <t>subj_math</t>
         </is>
       </c>
       <c r="K449" t="inlineStr">
         <is>
-          <t>Qur'an</t>
+          <t>Math</t>
         </is>
       </c>
       <c r="L449" t="inlineStr">
         <is>
-          <t>tchr_faidh</t>
+          <t>tchr_wendy</t>
         </is>
       </c>
       <c r="M449" t="inlineStr">
         <is>
-          <t>Ustadh Faidh</t>
+          <t>Teacher Wendy</t>
         </is>
       </c>
       <c r="N449" t="n">
@@ -30075,22 +30075,22 @@
       </c>
       <c r="E450" t="inlineStr">
         <is>
-          <t>sec_grade_1_face_to_face</t>
+          <t>sec_grade_11_face_to_face</t>
         </is>
       </c>
       <c r="F450" t="inlineStr">
         <is>
-          <t>GRADE 1 (FACE TO FACE)</t>
+          <t>GRADE 11 (FACE TO FACE)</t>
         </is>
       </c>
       <c r="G450" t="inlineStr">
         <is>
-          <t>Elementary</t>
+          <t>Senior High School</t>
         </is>
       </c>
       <c r="H450" t="inlineStr">
         <is>
-          <t>Grade 1</t>
+          <t>Grade 11</t>
         </is>
       </c>
       <c r="I450" t="inlineStr">
@@ -30100,22 +30100,22 @@
       </c>
       <c r="J450" t="inlineStr">
         <is>
-          <t>subj_math</t>
+          <t>subj_shaf</t>
         </is>
       </c>
       <c r="K450" t="inlineStr">
         <is>
-          <t>Math</t>
+          <t>SHAF</t>
         </is>
       </c>
       <c r="L450" t="inlineStr">
         <is>
-          <t>tchr_wendy</t>
+          <t>tchr_samsuddin</t>
         </is>
       </c>
       <c r="M450" t="inlineStr">
         <is>
-          <t>Teacher Wendy</t>
+          <t>Alim Samsuddin</t>
         </is>
       </c>
       <c r="N450" t="n">
@@ -30141,22 +30141,22 @@
       </c>
       <c r="E451" t="inlineStr">
         <is>
-          <t>sec_grade_11_face_to_face</t>
+          <t>sec_grade_2_face_to_face</t>
         </is>
       </c>
       <c r="F451" t="inlineStr">
         <is>
-          <t>GRADE 11 (FACE TO FACE)</t>
+          <t>GRADE 2 (FACE TO FACE)</t>
         </is>
       </c>
       <c r="G451" t="inlineStr">
         <is>
-          <t>Senior High School</t>
+          <t>Elementary</t>
         </is>
       </c>
       <c r="H451" t="inlineStr">
         <is>
-          <t>Grade 11</t>
+          <t>Grade 2</t>
         </is>
       </c>
       <c r="I451" t="inlineStr">
@@ -30166,22 +30166,22 @@
       </c>
       <c r="J451" t="inlineStr">
         <is>
-          <t>subj_shaf</t>
+          <t>subj_arabic</t>
         </is>
       </c>
       <c r="K451" t="inlineStr">
         <is>
-          <t>SHAF</t>
+          <t>Arabic</t>
         </is>
       </c>
       <c r="L451" t="inlineStr">
         <is>
-          <t>tchr_samsuddin</t>
+          <t>tchr_obaydah</t>
         </is>
       </c>
       <c r="M451" t="inlineStr">
         <is>
-          <t>Alim Samsuddin</t>
+          <t>Ustadh Obaydah</t>
         </is>
       </c>
       <c r="N451" t="n">
@@ -30207,12 +30207,12 @@
       </c>
       <c r="E452" t="inlineStr">
         <is>
-          <t>sec_grade_2_face_to_face</t>
+          <t>sec_grade_3_face_to_face</t>
         </is>
       </c>
       <c r="F452" t="inlineStr">
         <is>
-          <t>GRADE 2 (FACE TO FACE)</t>
+          <t>GRADE 3 (FACE TO FACE)</t>
         </is>
       </c>
       <c r="G452" t="inlineStr">
@@ -30222,7 +30222,7 @@
       </c>
       <c r="H452" t="inlineStr">
         <is>
-          <t>Grade 2</t>
+          <t>Grade 3</t>
         </is>
       </c>
       <c r="I452" t="inlineStr">
@@ -30232,22 +30232,22 @@
       </c>
       <c r="J452" t="inlineStr">
         <is>
-          <t>subj_arabic</t>
+          <t>subj_science</t>
         </is>
       </c>
       <c r="K452" t="inlineStr">
         <is>
-          <t>Arabic</t>
+          <t>Science</t>
         </is>
       </c>
       <c r="L452" t="inlineStr">
         <is>
-          <t>tchr_obaydah</t>
+          <t>tchr_jerlyn</t>
         </is>
       </c>
       <c r="M452" t="inlineStr">
         <is>
-          <t>Ustadh Obaydah</t>
+          <t>Teacher Jerlyn</t>
         </is>
       </c>
       <c r="N452" t="n">
@@ -30273,12 +30273,12 @@
       </c>
       <c r="E453" t="inlineStr">
         <is>
-          <t>sec_grade_3_face_to_face</t>
+          <t>sec_grade_4_face_to_face</t>
         </is>
       </c>
       <c r="F453" t="inlineStr">
         <is>
-          <t>GRADE 3 (FACE TO FACE)</t>
+          <t>GRADE 4 (FACE TO FACE)</t>
         </is>
       </c>
       <c r="G453" t="inlineStr">
@@ -30288,7 +30288,7 @@
       </c>
       <c r="H453" t="inlineStr">
         <is>
-          <t>Grade 3</t>
+          <t>Grade 4</t>
         </is>
       </c>
       <c r="I453" t="inlineStr">
@@ -30298,22 +30298,22 @@
       </c>
       <c r="J453" t="inlineStr">
         <is>
-          <t>subj_science</t>
+          <t>subj_gmrc</t>
         </is>
       </c>
       <c r="K453" t="inlineStr">
         <is>
-          <t>Science</t>
+          <t>GMRC</t>
         </is>
       </c>
       <c r="L453" t="inlineStr">
         <is>
-          <t>tchr_jerlyn</t>
+          <t>tchr_sahdia</t>
         </is>
       </c>
       <c r="M453" t="inlineStr">
         <is>
-          <t>Teacher Jerlyn</t>
+          <t>Teacher Sahdia</t>
         </is>
       </c>
       <c r="N453" t="n">
@@ -30339,22 +30339,22 @@
       </c>
       <c r="E454" t="inlineStr">
         <is>
-          <t>sec_grade_4_face_to_face</t>
+          <t>sec_grade_7_8_boys_face_to_face</t>
         </is>
       </c>
       <c r="F454" t="inlineStr">
         <is>
-          <t>GRADE 4 (FACE TO FACE)</t>
+          <t>GRADE 7 &amp; 8 BOYS (FACE TO FACE)</t>
         </is>
       </c>
       <c r="G454" t="inlineStr">
         <is>
-          <t>Elementary</t>
+          <t>Junior High School</t>
         </is>
       </c>
       <c r="H454" t="inlineStr">
         <is>
-          <t>Grade 4</t>
+          <t>Grade 7 &amp; 8</t>
         </is>
       </c>
       <c r="I454" t="inlineStr">
@@ -30374,12 +30374,12 @@
       </c>
       <c r="L454" t="inlineStr">
         <is>
-          <t>tchr_sahdia</t>
+          <t>tchr_silfah</t>
         </is>
       </c>
       <c r="M454" t="inlineStr">
         <is>
-          <t>Teacher Sahdia</t>
+          <t>Ustadh Silfah</t>
         </is>
       </c>
       <c r="N454" t="n">
@@ -30405,12 +30405,12 @@
       </c>
       <c r="E455" t="inlineStr">
         <is>
-          <t>sec_grade_7_8_boys_face_to_face</t>
+          <t>sec_grade_7_8_girls_face_to_face</t>
         </is>
       </c>
       <c r="F455" t="inlineStr">
         <is>
-          <t>GRADE 7 &amp; 8 BOYS (FACE TO FACE)</t>
+          <t>GRADE 7 &amp; 8 GIRLS (FACE TO FACE)</t>
         </is>
       </c>
       <c r="G455" t="inlineStr">
@@ -30430,22 +30430,22 @@
       </c>
       <c r="J455" t="inlineStr">
         <is>
-          <t>subj_gmrc</t>
+          <t>subj_arabic</t>
         </is>
       </c>
       <c r="K455" t="inlineStr">
         <is>
-          <t>GMRC</t>
+          <t>Arabic</t>
         </is>
       </c>
       <c r="L455" t="inlineStr">
         <is>
-          <t>tchr_silfah</t>
+          <t>tchr_ali</t>
         </is>
       </c>
       <c r="M455" t="inlineStr">
         <is>
-          <t>Ustadh Silfah</t>
+          <t>Ustadh Ali</t>
         </is>
       </c>
       <c r="N455" t="n">
@@ -30471,12 +30471,12 @@
       </c>
       <c r="E456" t="inlineStr">
         <is>
-          <t>sec_grade_7_8_girls_face_to_face</t>
+          <t>sec_grade_9_10_boys_face_to_face</t>
         </is>
       </c>
       <c r="F456" t="inlineStr">
         <is>
-          <t>GRADE 7 &amp; 8 GIRLS (FACE TO FACE)</t>
+          <t>GRADE 9 &amp; 10 BOYS (FACE TO FACE)</t>
         </is>
       </c>
       <c r="G456" t="inlineStr">
@@ -30486,7 +30486,7 @@
       </c>
       <c r="H456" t="inlineStr">
         <is>
-          <t>Grade 7 &amp; 8</t>
+          <t>Grade 9 &amp; 10</t>
         </is>
       </c>
       <c r="I456" t="inlineStr">
@@ -30506,12 +30506,12 @@
       </c>
       <c r="L456" t="inlineStr">
         <is>
-          <t>tchr_ali</t>
+          <t>tchr_mamonas</t>
         </is>
       </c>
       <c r="M456" t="inlineStr">
         <is>
-          <t>Ustadh Ali</t>
+          <t>Alim Mamonas</t>
         </is>
       </c>
       <c r="N456" t="n">
@@ -30532,17 +30532,17 @@
       </c>
       <c r="D457" t="inlineStr">
         <is>
-          <t>08:00 AM – 09:00 AM</t>
+          <t>08:00 AM – 10:00 AM</t>
         </is>
       </c>
       <c r="E457" t="inlineStr">
         <is>
-          <t>sec_grade_9_10_boys_face_to_face</t>
+          <t>sec_grade_9_10_girls_face_to_face</t>
         </is>
       </c>
       <c r="F457" t="inlineStr">
         <is>
-          <t>GRADE 9 &amp; 10 BOYS (FACE TO FACE)</t>
+          <t>GRADE 9 &amp; 10 GIRLS (FACE TO FACE)</t>
         </is>
       </c>
       <c r="G457" t="inlineStr">
@@ -30562,26 +30562,26 @@
       </c>
       <c r="J457" t="inlineStr">
         <is>
-          <t>subj_arabic</t>
+          <t>subj_math</t>
         </is>
       </c>
       <c r="K457" t="inlineStr">
         <is>
-          <t>Arabic</t>
+          <t>Math</t>
         </is>
       </c>
       <c r="L457" t="inlineStr">
         <is>
-          <t>tchr_mamonas</t>
+          <t>tchr_jhelyn</t>
         </is>
       </c>
       <c r="M457" t="inlineStr">
         <is>
-          <t>Alim Mamonas</t>
+          <t>Teacher Jhelyn</t>
         </is>
       </c>
       <c r="N457" t="n">
-        <v>60</v>
+        <v>120</v>
       </c>
     </row>
     <row r="458">
@@ -30598,27 +30598,27 @@
       </c>
       <c r="D458" t="inlineStr">
         <is>
-          <t>08:00 AM – 10:00 AM</t>
+          <t>08:00 AM – 09:00 AM</t>
         </is>
       </c>
       <c r="E458" t="inlineStr">
         <is>
-          <t>sec_grade_9_10_girls_face_to_face</t>
+          <t>sec_kinder_2_class_schedule_f2f</t>
         </is>
       </c>
       <c r="F458" t="inlineStr">
         <is>
-          <t>GRADE 9 &amp; 10 GIRLS (FACE TO FACE)</t>
+          <t>KINDER 2 CLASS SCHEDULE (F2F)</t>
         </is>
       </c>
       <c r="G458" t="inlineStr">
         <is>
-          <t>Junior High School</t>
+          <t>Elementary</t>
         </is>
       </c>
       <c r="H458" t="inlineStr">
         <is>
-          <t>Grade 9 &amp; 10</t>
+          <t>Kinder 2</t>
         </is>
       </c>
       <c r="I458" t="inlineStr">
@@ -30628,26 +30628,26 @@
       </c>
       <c r="J458" t="inlineStr">
         <is>
-          <t>subj_math</t>
+          <t>subj_oral_written_exam</t>
         </is>
       </c>
       <c r="K458" t="inlineStr">
         <is>
-          <t>Math</t>
+          <t>Oral &amp; Written Exam</t>
         </is>
       </c>
       <c r="L458" t="inlineStr">
         <is>
-          <t>tchr_jhelyn</t>
+          <t>tchr_keychell</t>
         </is>
       </c>
       <c r="M458" t="inlineStr">
         <is>
-          <t>Teacher Jhelyn</t>
+          <t>Teacher Keychell</t>
         </is>
       </c>
       <c r="N458" t="n">
-        <v>120</v>
+        <v>60</v>
       </c>
     </row>
     <row r="459">
@@ -30660,21 +30660,21 @@
         </is>
       </c>
       <c r="C459" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D459" t="inlineStr">
         <is>
-          <t>08:00 AM – 09:00 AM</t>
+          <t>09:00 AM – 10:00 AM</t>
         </is>
       </c>
       <c r="E459" t="inlineStr">
         <is>
-          <t>sec_kinder_2_class_schedule_f2f</t>
+          <t>sec_grade_6_face_to_face</t>
         </is>
       </c>
       <c r="F459" t="inlineStr">
         <is>
-          <t>KINDER 2 CLASS SCHEDULE (F2F)</t>
+          <t>GRADE  6  FACE TO FACE</t>
         </is>
       </c>
       <c r="G459" t="inlineStr">
@@ -30684,7 +30684,7 @@
       </c>
       <c r="H459" t="inlineStr">
         <is>
-          <t>Kinder 2</t>
+          <t>Grade 6</t>
         </is>
       </c>
       <c r="I459" t="inlineStr">
@@ -30694,22 +30694,22 @@
       </c>
       <c r="J459" t="inlineStr">
         <is>
-          <t>subj_oral_written_exam</t>
+          <t>subj_shaf</t>
         </is>
       </c>
       <c r="K459" t="inlineStr">
         <is>
-          <t>Oral &amp; Written Exam</t>
+          <t>SHAF</t>
         </is>
       </c>
       <c r="L459" t="inlineStr">
         <is>
-          <t>tchr_keychell</t>
+          <t>tchr_abdiraheem</t>
         </is>
       </c>
       <c r="M459" t="inlineStr">
         <is>
-          <t>Teacher Keychell</t>
+          <t>Ustadh Abdiraheem</t>
         </is>
       </c>
       <c r="N459" t="n">
@@ -30735,12 +30735,12 @@
       </c>
       <c r="E460" t="inlineStr">
         <is>
-          <t>sec_grade_6_face_to_face</t>
+          <t>sec_grade_1_face_to_face</t>
         </is>
       </c>
       <c r="F460" t="inlineStr">
         <is>
-          <t>GRADE  6  FACE TO FACE</t>
+          <t>GRADE 1 (FACE TO FACE)</t>
         </is>
       </c>
       <c r="G460" t="inlineStr">
@@ -30750,7 +30750,7 @@
       </c>
       <c r="H460" t="inlineStr">
         <is>
-          <t>Grade 6</t>
+          <t>Grade 1</t>
         </is>
       </c>
       <c r="I460" t="inlineStr">
@@ -30760,22 +30760,22 @@
       </c>
       <c r="J460" t="inlineStr">
         <is>
-          <t>subj_shaf</t>
+          <t>subj_arabic</t>
         </is>
       </c>
       <c r="K460" t="inlineStr">
         <is>
-          <t>SHAF</t>
+          <t>Arabic</t>
         </is>
       </c>
       <c r="L460" t="inlineStr">
         <is>
-          <t>tchr_abdiraheem</t>
+          <t>tchr_sahdia</t>
         </is>
       </c>
       <c r="M460" t="inlineStr">
         <is>
-          <t>Ustadh Abdiraheem</t>
+          <t>Teacher Sahdia</t>
         </is>
       </c>
       <c r="N460" t="n">
@@ -30801,22 +30801,22 @@
       </c>
       <c r="E461" t="inlineStr">
         <is>
-          <t>sec_grade_1_face_to_face</t>
+          <t>sec_grade_11_face_to_face</t>
         </is>
       </c>
       <c r="F461" t="inlineStr">
         <is>
-          <t>GRADE 1 (FACE TO FACE)</t>
+          <t>GRADE 11 (FACE TO FACE)</t>
         </is>
       </c>
       <c r="G461" t="inlineStr">
         <is>
-          <t>Elementary</t>
+          <t>Senior High School</t>
         </is>
       </c>
       <c r="H461" t="inlineStr">
         <is>
-          <t>Grade 1</t>
+          <t>Grade 11</t>
         </is>
       </c>
       <c r="I461" t="inlineStr">
@@ -30826,22 +30826,22 @@
       </c>
       <c r="J461" t="inlineStr">
         <is>
-          <t>subj_arabic</t>
+          <t>subj_ec</t>
         </is>
       </c>
       <c r="K461" t="inlineStr">
         <is>
-          <t>Arabic</t>
+          <t>EC</t>
         </is>
       </c>
       <c r="L461" t="inlineStr">
         <is>
-          <t>tchr_sahdia</t>
+          <t>tchr_nadzra</t>
         </is>
       </c>
       <c r="M461" t="inlineStr">
         <is>
-          <t>Teacher Sahdia</t>
+          <t>Teacher Nadzra</t>
         </is>
       </c>
       <c r="N461" t="n">
@@ -30867,12 +30867,12 @@
       </c>
       <c r="E462" t="inlineStr">
         <is>
-          <t>sec_grade_11_face_to_face</t>
+          <t>sec_grade_12_suhayb_ar_rumi</t>
         </is>
       </c>
       <c r="F462" t="inlineStr">
         <is>
-          <t>GRADE 11 (FACE TO FACE)</t>
+          <t>GRADE 12 - SUHAYB AR-RUMI</t>
         </is>
       </c>
       <c r="G462" t="inlineStr">
@@ -30882,7 +30882,7 @@
       </c>
       <c r="H462" t="inlineStr">
         <is>
-          <t>Grade 11</t>
+          <t>Grade 12</t>
         </is>
       </c>
       <c r="I462" t="inlineStr">
@@ -30892,22 +30892,22 @@
       </c>
       <c r="J462" t="inlineStr">
         <is>
-          <t>subj_ec</t>
+          <t>subj_qur_an</t>
         </is>
       </c>
       <c r="K462" t="inlineStr">
         <is>
-          <t>EC</t>
+          <t>Qur'an</t>
         </is>
       </c>
       <c r="L462" t="inlineStr">
         <is>
-          <t>tchr_nadzra</t>
+          <t>tchr_dipatuan</t>
         </is>
       </c>
       <c r="M462" t="inlineStr">
         <is>
-          <t>Teacher Nadzra</t>
+          <t>Alim Dipatuan</t>
         </is>
       </c>
       <c r="N462" t="n">
@@ -30933,22 +30933,22 @@
       </c>
       <c r="E463" t="inlineStr">
         <is>
-          <t>sec_grade_12_suhayb_ar_rumi</t>
+          <t>sec_grade_2_face_to_face</t>
         </is>
       </c>
       <c r="F463" t="inlineStr">
         <is>
-          <t>GRADE 12 - SUHAYB AR-RUMI</t>
+          <t>GRADE 2 (FACE TO FACE)</t>
         </is>
       </c>
       <c r="G463" t="inlineStr">
         <is>
-          <t>Senior High School</t>
+          <t>Elementary</t>
         </is>
       </c>
       <c r="H463" t="inlineStr">
         <is>
-          <t>Grade 12</t>
+          <t>Grade 2</t>
         </is>
       </c>
       <c r="I463" t="inlineStr">
@@ -30958,22 +30958,22 @@
       </c>
       <c r="J463" t="inlineStr">
         <is>
-          <t>subj_qur_an</t>
+          <t>subj_gmrc</t>
         </is>
       </c>
       <c r="K463" t="inlineStr">
         <is>
-          <t>Qur'an</t>
+          <t>GMRC</t>
         </is>
       </c>
       <c r="L463" t="inlineStr">
         <is>
-          <t>tchr_dipatuan</t>
+          <t>tchr_saliha</t>
         </is>
       </c>
       <c r="M463" t="inlineStr">
         <is>
-          <t>Alim Dipatuan</t>
+          <t>Ustadha Saliha</t>
         </is>
       </c>
       <c r="N463" t="n">
@@ -30999,12 +30999,12 @@
       </c>
       <c r="E464" t="inlineStr">
         <is>
-          <t>sec_grade_2_face_to_face</t>
+          <t>sec_grade_3_face_to_face</t>
         </is>
       </c>
       <c r="F464" t="inlineStr">
         <is>
-          <t>GRADE 2 (FACE TO FACE)</t>
+          <t>GRADE 3 (FACE TO FACE)</t>
         </is>
       </c>
       <c r="G464" t="inlineStr">
@@ -31014,7 +31014,7 @@
       </c>
       <c r="H464" t="inlineStr">
         <is>
-          <t>Grade 2</t>
+          <t>Grade 3</t>
         </is>
       </c>
       <c r="I464" t="inlineStr">
@@ -31024,22 +31024,22 @@
       </c>
       <c r="J464" t="inlineStr">
         <is>
-          <t>subj_gmrc</t>
+          <t>subj_shaf</t>
         </is>
       </c>
       <c r="K464" t="inlineStr">
         <is>
-          <t>GMRC</t>
+          <t>SHAF</t>
         </is>
       </c>
       <c r="L464" t="inlineStr">
         <is>
-          <t>tchr_saliha</t>
+          <t>tchr_ersahad</t>
         </is>
       </c>
       <c r="M464" t="inlineStr">
         <is>
-          <t>Ustadha Saliha</t>
+          <t>Ustadh Ersahad</t>
         </is>
       </c>
       <c r="N464" t="n">
@@ -31065,12 +31065,12 @@
       </c>
       <c r="E465" t="inlineStr">
         <is>
-          <t>sec_grade_3_face_to_face</t>
+          <t>sec_grade_4_face_to_face</t>
         </is>
       </c>
       <c r="F465" t="inlineStr">
         <is>
-          <t>GRADE 3 (FACE TO FACE)</t>
+          <t>GRADE 4 (FACE TO FACE)</t>
         </is>
       </c>
       <c r="G465" t="inlineStr">
@@ -31080,7 +31080,7 @@
       </c>
       <c r="H465" t="inlineStr">
         <is>
-          <t>Grade 3</t>
+          <t>Grade 4</t>
         </is>
       </c>
       <c r="I465" t="inlineStr">
@@ -31090,22 +31090,22 @@
       </c>
       <c r="J465" t="inlineStr">
         <is>
-          <t>subj_shaf</t>
+          <t>subj_tle</t>
         </is>
       </c>
       <c r="K465" t="inlineStr">
         <is>
-          <t>SHAF</t>
+          <t>TLE</t>
         </is>
       </c>
       <c r="L465" t="inlineStr">
         <is>
-          <t>tchr_ersahad</t>
+          <t>tchr_monisa</t>
         </is>
       </c>
       <c r="M465" t="inlineStr">
         <is>
-          <t>Ustadh Ersahad</t>
+          <t>Teacher Monisa</t>
         </is>
       </c>
       <c r="N465" t="n">
@@ -31131,12 +31131,12 @@
       </c>
       <c r="E466" t="inlineStr">
         <is>
-          <t>sec_grade_4_face_to_face</t>
+          <t>sec_grade_5_face_to_face</t>
         </is>
       </c>
       <c r="F466" t="inlineStr">
         <is>
-          <t>GRADE 4 (FACE TO FACE)</t>
+          <t>GRADE 5 (FACE TO FACE)</t>
         </is>
       </c>
       <c r="G466" t="inlineStr">
@@ -31146,7 +31146,7 @@
       </c>
       <c r="H466" t="inlineStr">
         <is>
-          <t>Grade 4</t>
+          <t>Grade 5</t>
         </is>
       </c>
       <c r="I466" t="inlineStr">
@@ -31156,22 +31156,22 @@
       </c>
       <c r="J466" t="inlineStr">
         <is>
-          <t>subj_tle</t>
+          <t>subj_araling_panlipunan</t>
         </is>
       </c>
       <c r="K466" t="inlineStr">
         <is>
-          <t>TLE</t>
+          <t>Araling Panlipunan</t>
         </is>
       </c>
       <c r="L466" t="inlineStr">
         <is>
-          <t>tchr_monisa</t>
+          <t>tchr_norhydie</t>
         </is>
       </c>
       <c r="M466" t="inlineStr">
         <is>
-          <t>Teacher Monisa</t>
+          <t>Teacher Norhydie</t>
         </is>
       </c>
       <c r="N466" t="n">
@@ -31192,27 +31192,27 @@
       </c>
       <c r="D467" t="inlineStr">
         <is>
-          <t>09:00 AM – 10:00 AM</t>
+          <t>09:00 AM – 11:25 AM</t>
         </is>
       </c>
       <c r="E467" t="inlineStr">
         <is>
-          <t>sec_grade_5_face_to_face</t>
+          <t>sec_grade_7_8_boys_face_to_face</t>
         </is>
       </c>
       <c r="F467" t="inlineStr">
         <is>
-          <t>GRADE 5 (FACE TO FACE)</t>
+          <t>GRADE 7 &amp; 8 BOYS (FACE TO FACE)</t>
         </is>
       </c>
       <c r="G467" t="inlineStr">
         <is>
-          <t>Elementary</t>
+          <t>Junior High School</t>
         </is>
       </c>
       <c r="H467" t="inlineStr">
         <is>
-          <t>Grade 5</t>
+          <t>Grade 7 &amp; 8</t>
         </is>
       </c>
       <c r="I467" t="inlineStr">
@@ -31222,26 +31222,26 @@
       </c>
       <c r="J467" t="inlineStr">
         <is>
-          <t>subj_araling_panlipunan</t>
+          <t>subj_math</t>
         </is>
       </c>
       <c r="K467" t="inlineStr">
         <is>
-          <t>Araling Panlipunan</t>
+          <t>Math</t>
         </is>
       </c>
       <c r="L467" t="inlineStr">
         <is>
-          <t>tchr_norhydie</t>
+          <t>tchr_fhairudz</t>
         </is>
       </c>
       <c r="M467" t="inlineStr">
         <is>
-          <t>Teacher Norhydie</t>
+          <t>Teacher Fhairudz</t>
         </is>
       </c>
       <c r="N467" t="n">
-        <v>60</v>
+        <v>120</v>
       </c>
     </row>
     <row r="468">
@@ -31258,17 +31258,17 @@
       </c>
       <c r="D468" t="inlineStr">
         <is>
-          <t>09:00 AM – 11:25 AM</t>
+          <t>09:00 AM – 10:00 AM</t>
         </is>
       </c>
       <c r="E468" t="inlineStr">
         <is>
-          <t>sec_grade_7_8_boys_face_to_face</t>
+          <t>sec_grade_7_8_girls_face_to_face</t>
         </is>
       </c>
       <c r="F468" t="inlineStr">
         <is>
-          <t>GRADE 7 &amp; 8 BOYS (FACE TO FACE)</t>
+          <t>GRADE 7 &amp; 8 GIRLS (FACE TO FACE)</t>
         </is>
       </c>
       <c r="G468" t="inlineStr">
@@ -31288,26 +31288,26 @@
       </c>
       <c r="J468" t="inlineStr">
         <is>
-          <t>subj_math</t>
+          <t>subj_gmrc</t>
         </is>
       </c>
       <c r="K468" t="inlineStr">
         <is>
-          <t>Math</t>
+          <t>GMRC</t>
         </is>
       </c>
       <c r="L468" t="inlineStr">
         <is>
-          <t>tchr_fhairudz</t>
+          <t>tchr_silfah</t>
         </is>
       </c>
       <c r="M468" t="inlineStr">
         <is>
-          <t>Teacher Fhairudz</t>
+          <t>Ustadh Silfah</t>
         </is>
       </c>
       <c r="N468" t="n">
-        <v>120</v>
+        <v>60</v>
       </c>
     </row>
     <row r="469">
@@ -31329,12 +31329,12 @@
       </c>
       <c r="E469" t="inlineStr">
         <is>
-          <t>sec_grade_7_8_girls_face_to_face</t>
+          <t>sec_grade_9_10_boys_face_to_face</t>
         </is>
       </c>
       <c r="F469" t="inlineStr">
         <is>
-          <t>GRADE 7 &amp; 8 GIRLS (FACE TO FACE)</t>
+          <t>GRADE 9 &amp; 10 BOYS (FACE TO FACE)</t>
         </is>
       </c>
       <c r="G469" t="inlineStr">
@@ -31344,7 +31344,7 @@
       </c>
       <c r="H469" t="inlineStr">
         <is>
-          <t>Grade 7 &amp; 8</t>
+          <t>Grade 9 &amp; 10</t>
         </is>
       </c>
       <c r="I469" t="inlineStr">
@@ -31354,22 +31354,22 @@
       </c>
       <c r="J469" t="inlineStr">
         <is>
-          <t>subj_gmrc</t>
+          <t>subj_mapeh</t>
         </is>
       </c>
       <c r="K469" t="inlineStr">
         <is>
-          <t>GMRC</t>
+          <t>MAPEH</t>
         </is>
       </c>
       <c r="L469" t="inlineStr">
         <is>
-          <t>tchr_silfah</t>
+          <t>tchr_mohaymen</t>
         </is>
       </c>
       <c r="M469" t="inlineStr">
         <is>
-          <t>Ustadh Silfah</t>
+          <t>Sir Mohaymen</t>
         </is>
       </c>
       <c r="N469" t="n">
@@ -31386,31 +31386,31 @@
         </is>
       </c>
       <c r="C470" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D470" t="inlineStr">
         <is>
-          <t>09:00 AM – 10:00 AM</t>
+          <t>10:25 AM – 11:25 AM</t>
         </is>
       </c>
       <c r="E470" t="inlineStr">
         <is>
-          <t>sec_grade_9_10_boys_face_to_face</t>
+          <t>sec_grade_6_face_to_face</t>
         </is>
       </c>
       <c r="F470" t="inlineStr">
         <is>
-          <t>GRADE 9 &amp; 10 BOYS (FACE TO FACE)</t>
+          <t>GRADE  6  FACE TO FACE</t>
         </is>
       </c>
       <c r="G470" t="inlineStr">
         <is>
-          <t>Junior High School</t>
+          <t>Elementary</t>
         </is>
       </c>
       <c r="H470" t="inlineStr">
         <is>
-          <t>Grade 9 &amp; 10</t>
+          <t>Grade 6</t>
         </is>
       </c>
       <c r="I470" t="inlineStr">
@@ -31420,22 +31420,22 @@
       </c>
       <c r="J470" t="inlineStr">
         <is>
-          <t>subj_mapeh</t>
+          <t>subj_araling_panlipunan</t>
         </is>
       </c>
       <c r="K470" t="inlineStr">
         <is>
-          <t>MAPEH</t>
+          <t>Araling Panlipunan</t>
         </is>
       </c>
       <c r="L470" t="inlineStr">
         <is>
-          <t>tchr_mohaymen</t>
+          <t>tchr_zuhora</t>
         </is>
       </c>
       <c r="M470" t="inlineStr">
         <is>
-          <t>Sir Mohaymen</t>
+          <t>Teacher Zuhora</t>
         </is>
       </c>
       <c r="N470" t="n">
@@ -31461,22 +31461,22 @@
       </c>
       <c r="E471" t="inlineStr">
         <is>
-          <t>sec_grade_6_face_to_face</t>
+          <t>sec_grade_11_face_to_face</t>
         </is>
       </c>
       <c r="F471" t="inlineStr">
         <is>
-          <t>GRADE  6  FACE TO FACE</t>
+          <t>GRADE 11 (FACE TO FACE)</t>
         </is>
       </c>
       <c r="G471" t="inlineStr">
         <is>
-          <t>Elementary</t>
+          <t>Senior High School</t>
         </is>
       </c>
       <c r="H471" t="inlineStr">
         <is>
-          <t>Grade 6</t>
+          <t>Grade 11</t>
         </is>
       </c>
       <c r="I471" t="inlineStr">
@@ -31486,22 +31486,22 @@
       </c>
       <c r="J471" t="inlineStr">
         <is>
-          <t>subj_araling_panlipunan</t>
+          <t>subj_qur_an</t>
         </is>
       </c>
       <c r="K471" t="inlineStr">
         <is>
-          <t>Araling Panlipunan</t>
+          <t>Qur'an</t>
         </is>
       </c>
       <c r="L471" t="inlineStr">
         <is>
-          <t>tchr_zuhora</t>
+          <t>tchr_dipatuan</t>
         </is>
       </c>
       <c r="M471" t="inlineStr">
         <is>
-          <t>Teacher Zuhora</t>
+          <t>Alim Dipatuan</t>
         </is>
       </c>
       <c r="N471" t="n">
@@ -31527,12 +31527,12 @@
       </c>
       <c r="E472" t="inlineStr">
         <is>
-          <t>sec_grade_11_face_to_face</t>
+          <t>sec_grade_12_suhayb_ar_rumi</t>
         </is>
       </c>
       <c r="F472" t="inlineStr">
         <is>
-          <t>GRADE 11 (FACE TO FACE)</t>
+          <t>GRADE 12 - SUHAYB AR-RUMI</t>
         </is>
       </c>
       <c r="G472" t="inlineStr">
@@ -31542,7 +31542,7 @@
       </c>
       <c r="H472" t="inlineStr">
         <is>
-          <t>Grade 11</t>
+          <t>Grade 12</t>
         </is>
       </c>
       <c r="I472" t="inlineStr">
@@ -31552,22 +31552,22 @@
       </c>
       <c r="J472" t="inlineStr">
         <is>
-          <t>subj_qur_an</t>
+          <t>subj_arabic</t>
         </is>
       </c>
       <c r="K472" t="inlineStr">
         <is>
-          <t>Qur'an</t>
+          <t>Arabic</t>
         </is>
       </c>
       <c r="L472" t="inlineStr">
         <is>
-          <t>tchr_dipatuan</t>
+          <t>tchr_mamonas</t>
         </is>
       </c>
       <c r="M472" t="inlineStr">
         <is>
-          <t>Alim Dipatuan</t>
+          <t>Alim Mamonas</t>
         </is>
       </c>
       <c r="N472" t="n">
@@ -31593,22 +31593,22 @@
       </c>
       <c r="E473" t="inlineStr">
         <is>
-          <t>sec_grade_12_suhayb_ar_rumi</t>
+          <t>sec_grade_4_face_to_face</t>
         </is>
       </c>
       <c r="F473" t="inlineStr">
         <is>
-          <t>GRADE 12 - SUHAYB AR-RUMI</t>
+          <t>GRADE 4 (FACE TO FACE)</t>
         </is>
       </c>
       <c r="G473" t="inlineStr">
         <is>
-          <t>Senior High School</t>
+          <t>Elementary</t>
         </is>
       </c>
       <c r="H473" t="inlineStr">
         <is>
-          <t>Grade 12</t>
+          <t>Grade 4</t>
         </is>
       </c>
       <c r="I473" t="inlineStr">
@@ -31618,22 +31618,22 @@
       </c>
       <c r="J473" t="inlineStr">
         <is>
-          <t>subj_arabic</t>
+          <t>subj_qur_an</t>
         </is>
       </c>
       <c r="K473" t="inlineStr">
         <is>
-          <t>Arabic</t>
+          <t>Qur'an</t>
         </is>
       </c>
       <c r="L473" t="inlineStr">
         <is>
-          <t>tchr_mamonas</t>
+          <t>tchr_obaydah</t>
         </is>
       </c>
       <c r="M473" t="inlineStr">
         <is>
-          <t>Alim Mamonas</t>
+          <t>Ustadh Obaydah</t>
         </is>
       </c>
       <c r="N473" t="n">
@@ -31659,12 +31659,12 @@
       </c>
       <c r="E474" t="inlineStr">
         <is>
-          <t>sec_grade_4_face_to_face</t>
+          <t>sec_grade_5_face_to_face</t>
         </is>
       </c>
       <c r="F474" t="inlineStr">
         <is>
-          <t>GRADE 4 (FACE TO FACE)</t>
+          <t>GRADE 5 (FACE TO FACE)</t>
         </is>
       </c>
       <c r="G474" t="inlineStr">
@@ -31674,7 +31674,7 @@
       </c>
       <c r="H474" t="inlineStr">
         <is>
-          <t>Grade 4</t>
+          <t>Grade 5</t>
         </is>
       </c>
       <c r="I474" t="inlineStr">
@@ -31684,22 +31684,22 @@
       </c>
       <c r="J474" t="inlineStr">
         <is>
-          <t>subj_qur_an</t>
+          <t>subj_gmrc</t>
         </is>
       </c>
       <c r="K474" t="inlineStr">
         <is>
-          <t>Qur'an</t>
+          <t>GMRC</t>
         </is>
       </c>
       <c r="L474" t="inlineStr">
         <is>
-          <t>tchr_obaydah</t>
+          <t>tchr_jairah</t>
         </is>
       </c>
       <c r="M474" t="inlineStr">
         <is>
-          <t>Ustadh Obaydah</t>
+          <t>Teacher Jairah</t>
         </is>
       </c>
       <c r="N474" t="n">
@@ -31725,22 +31725,22 @@
       </c>
       <c r="E475" t="inlineStr">
         <is>
-          <t>sec_grade_5_face_to_face</t>
+          <t>sec_grade_7_8_girls_face_to_face</t>
         </is>
       </c>
       <c r="F475" t="inlineStr">
         <is>
-          <t>GRADE 5 (FACE TO FACE)</t>
+          <t>GRADE 7 &amp; 8 GIRLS (FACE TO FACE)</t>
         </is>
       </c>
       <c r="G475" t="inlineStr">
         <is>
-          <t>Elementary</t>
+          <t>Junior High School</t>
         </is>
       </c>
       <c r="H475" t="inlineStr">
         <is>
-          <t>Grade 5</t>
+          <t>Grade 7 &amp; 8</t>
         </is>
       </c>
       <c r="I475" t="inlineStr">
@@ -31750,22 +31750,22 @@
       </c>
       <c r="J475" t="inlineStr">
         <is>
-          <t>subj_gmrc</t>
+          <t>subj_tle</t>
         </is>
       </c>
       <c r="K475" t="inlineStr">
         <is>
-          <t>GMRC</t>
+          <t>TLE</t>
         </is>
       </c>
       <c r="L475" t="inlineStr">
         <is>
-          <t>tchr_jairah</t>
+          <t>tchr_halnaisa</t>
         </is>
       </c>
       <c r="M475" t="inlineStr">
         <is>
-          <t>Teacher Jairah</t>
+          <t>Teacher Halnaisa</t>
         </is>
       </c>
       <c r="N475" t="n">
@@ -31791,12 +31791,12 @@
       </c>
       <c r="E476" t="inlineStr">
         <is>
-          <t>sec_grade_7_8_girls_face_to_face</t>
+          <t>sec_grade_9_10_boys_face_to_face</t>
         </is>
       </c>
       <c r="F476" t="inlineStr">
         <is>
-          <t>GRADE 7 &amp; 8 GIRLS (FACE TO FACE)</t>
+          <t>GRADE 9 &amp; 10 BOYS (FACE TO FACE)</t>
         </is>
       </c>
       <c r="G476" t="inlineStr">
@@ -31806,7 +31806,7 @@
       </c>
       <c r="H476" t="inlineStr">
         <is>
-          <t>Grade 7 &amp; 8</t>
+          <t>Grade 9 &amp; 10</t>
         </is>
       </c>
       <c r="I476" t="inlineStr">
@@ -31816,22 +31816,22 @@
       </c>
       <c r="J476" t="inlineStr">
         <is>
-          <t>subj_tle</t>
+          <t>subj_english</t>
         </is>
       </c>
       <c r="K476" t="inlineStr">
         <is>
-          <t>TLE</t>
+          <t>English</t>
         </is>
       </c>
       <c r="L476" t="inlineStr">
         <is>
-          <t>tchr_halnaisa</t>
+          <t>tchr_norhaima</t>
         </is>
       </c>
       <c r="M476" t="inlineStr">
         <is>
-          <t>Teacher Halnaisa</t>
+          <t>Teacher Norhaima</t>
         </is>
       </c>
       <c r="N476" t="n">
@@ -31857,12 +31857,12 @@
       </c>
       <c r="E477" t="inlineStr">
         <is>
-          <t>sec_grade_9_10_boys_face_to_face</t>
+          <t>sec_grade_9_10_girls_face_to_face</t>
         </is>
       </c>
       <c r="F477" t="inlineStr">
         <is>
-          <t>GRADE 9 &amp; 10 BOYS (FACE TO FACE)</t>
+          <t>GRADE 9 &amp; 10 GIRLS (FACE TO FACE)</t>
         </is>
       </c>
       <c r="G477" t="inlineStr">
@@ -31882,22 +31882,22 @@
       </c>
       <c r="J477" t="inlineStr">
         <is>
-          <t>subj_english</t>
+          <t>subj_tle</t>
         </is>
       </c>
       <c r="K477" t="inlineStr">
         <is>
-          <t>English</t>
+          <t>TLE</t>
         </is>
       </c>
       <c r="L477" t="inlineStr">
         <is>
-          <t>tchr_norhaima</t>
+          <t>tchr_angeleni</t>
         </is>
       </c>
       <c r="M477" t="inlineStr">
         <is>
-          <t>Teacher Norhaima</t>
+          <t>Teacher Angeleni</t>
         </is>
       </c>
       <c r="N477" t="n">
@@ -31914,56 +31914,56 @@
         </is>
       </c>
       <c r="C478" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D478" t="inlineStr">
         <is>
-          <t>10:25 AM – 11:25 AM</t>
+          <t>11:30 AM – 12:30 PM</t>
         </is>
       </c>
       <c r="E478" t="inlineStr">
         <is>
-          <t>sec_grade_9_10_girls_face_to_face</t>
+          <t>sec_grade_2_talha_ibn_ubaydullah_1st_shift</t>
         </is>
       </c>
       <c r="F478" t="inlineStr">
         <is>
-          <t>GRADE 9 &amp; 10 GIRLS (FACE TO FACE)</t>
+          <t>GRADE 2 - TALHA IBN UBAYDULLAH (1ST SHIFT)</t>
         </is>
       </c>
       <c r="G478" t="inlineStr">
         <is>
-          <t>Junior High School</t>
+          <t>Elementary</t>
         </is>
       </c>
       <c r="H478" t="inlineStr">
         <is>
-          <t>Grade 9 &amp; 10</t>
+          <t>Grade 2</t>
         </is>
       </c>
       <c r="I478" t="inlineStr">
         <is>
-          <t>F2F</t>
+          <t>ODL - 1ST SHIFT</t>
         </is>
       </c>
       <c r="J478" t="inlineStr">
         <is>
-          <t>subj_tle</t>
+          <t>subj_qur_an</t>
         </is>
       </c>
       <c r="K478" t="inlineStr">
         <is>
-          <t>TLE</t>
+          <t>Qur'an</t>
         </is>
       </c>
       <c r="L478" t="inlineStr">
         <is>
-          <t>tchr_angeleni</t>
+          <t>tchr_obaydah</t>
         </is>
       </c>
       <c r="M478" t="inlineStr">
         <is>
-          <t>Teacher Angeleni</t>
+          <t>Ustadh Obaydah</t>
         </is>
       </c>
       <c r="N478" t="n">
@@ -31989,12 +31989,12 @@
       </c>
       <c r="E479" t="inlineStr">
         <is>
-          <t>sec_grade_2_talha_ibn_ubaydullah_1st_shift</t>
+          <t>sec_grade_3_habib_ibn_zayd_al_ansari_1st_shift_girls</t>
         </is>
       </c>
       <c r="F479" t="inlineStr">
         <is>
-          <t>GRADE 2 - TALHA IBN UBAYDULLAH (1ST SHIFT)</t>
+          <t>Grade 3 - HABIB IBN ZAYD AL-ANSARI (1ST SHIFT) - GIRLS</t>
         </is>
       </c>
       <c r="G479" t="inlineStr">
@@ -32004,7 +32004,7 @@
       </c>
       <c r="H479" t="inlineStr">
         <is>
-          <t>Grade 2</t>
+          <t>Grade 3</t>
         </is>
       </c>
       <c r="I479" t="inlineStr">
@@ -32014,22 +32014,22 @@
       </c>
       <c r="J479" t="inlineStr">
         <is>
-          <t>subj_qur_an</t>
+          <t>subj_arabic</t>
         </is>
       </c>
       <c r="K479" t="inlineStr">
         <is>
-          <t>Qur'an</t>
+          <t>Arabic</t>
         </is>
       </c>
       <c r="L479" t="inlineStr">
         <is>
-          <t>tchr_obaydah</t>
+          <t>tchr_silfah</t>
         </is>
       </c>
       <c r="M479" t="inlineStr">
         <is>
-          <t>Ustadh Obaydah</t>
+          <t>Ustadh Silfah</t>
         </is>
       </c>
       <c r="N479" t="n">
@@ -32055,12 +32055,12 @@
       </c>
       <c r="E480" t="inlineStr">
         <is>
-          <t>sec_grade_3_habib_ibn_zayd_al_ansari_1st_shift_girls</t>
+          <t>sec_grade_5_hamza_ibn_abdul_1st_shift</t>
         </is>
       </c>
       <c r="F480" t="inlineStr">
         <is>
-          <t>Grade 3 - HABIB IBN ZAYD AL-ANSARI (1ST SHIFT) - GIRLS</t>
+          <t>GRADE 5 - HAMZA IBN ABDUL (1ST SHIFT)</t>
         </is>
       </c>
       <c r="G480" t="inlineStr">
@@ -32070,7 +32070,7 @@
       </c>
       <c r="H480" t="inlineStr">
         <is>
-          <t>Grade 3</t>
+          <t>Grade 5</t>
         </is>
       </c>
       <c r="I480" t="inlineStr">
@@ -32080,22 +32080,22 @@
       </c>
       <c r="J480" t="inlineStr">
         <is>
-          <t>subj_arabic</t>
+          <t>subj_shaf</t>
         </is>
       </c>
       <c r="K480" t="inlineStr">
         <is>
-          <t>Arabic</t>
+          <t>SHAF</t>
         </is>
       </c>
       <c r="L480" t="inlineStr">
         <is>
-          <t>tchr_silfah</t>
+          <t>tchr_hainur</t>
         </is>
       </c>
       <c r="M480" t="inlineStr">
         <is>
-          <t>Ustadh Silfah</t>
+          <t>Ustadha Hainur</t>
         </is>
       </c>
       <c r="N480" t="n">

--- a/Term_Examination_Schedule_S.Y._2026-2027_Optimized.xlsx
+++ b/Term_Examination_Schedule_S.Y._2026-2027_Optimized.xlsx
@@ -15942,7 +15942,7 @@
         </is>
       </c>
       <c r="C236" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D236" t="inlineStr">
         <is>
@@ -15951,47 +15951,47 @@
       </c>
       <c r="E236" t="inlineStr">
         <is>
-          <t>sec_grade_2_saeed_ibn_zayd_2nd_shift</t>
+          <t>sec_grade_12_abu_musa_al_ashari</t>
         </is>
       </c>
       <c r="F236" t="inlineStr">
         <is>
-          <t>GRADE 2 - SAEED IBN ZAYD (2ND SHIFT)</t>
+          <t>GRADE 12 - ABU MUSA AL-ASHARI</t>
         </is>
       </c>
       <c r="G236" t="inlineStr">
         <is>
-          <t>Elementary</t>
+          <t>Senior High School</t>
         </is>
       </c>
       <c r="H236" t="inlineStr">
         <is>
-          <t>Grade 2</t>
+          <t>Grade 12</t>
         </is>
       </c>
       <c r="I236" t="inlineStr">
         <is>
-          <t>ODL - 2ND SHIFT</t>
+          <t>ODL - 1ST SHIFT</t>
         </is>
       </c>
       <c r="J236" t="inlineStr">
         <is>
-          <t>subj_filipino</t>
+          <t>subj_mil</t>
         </is>
       </c>
       <c r="K236" t="inlineStr">
         <is>
-          <t>Filipino</t>
+          <t>MIL</t>
         </is>
       </c>
       <c r="L236" t="inlineStr">
         <is>
-          <t>tchr_zuhora</t>
+          <t>tchr_ethel</t>
         </is>
       </c>
       <c r="M236" t="inlineStr">
         <is>
-          <t>Teacher Zuhora</t>
+          <t>Teacher Ethel</t>
         </is>
       </c>
       <c r="N236" t="n">
@@ -16008,7 +16008,7 @@
         </is>
       </c>
       <c r="C237" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D237" t="inlineStr">
         <is>
@@ -16017,12 +16017,12 @@
       </c>
       <c r="E237" t="inlineStr">
         <is>
-          <t>sec_grade_3_salman_al_farsi_1st_shift_mix</t>
+          <t>sec_grade_2_saeed_ibn_zayd_2nd_shift</t>
         </is>
       </c>
       <c r="F237" t="inlineStr">
         <is>
-          <t>GRADE 3 - SALMAN AL FARSI (1ST SHIFT) MIX</t>
+          <t>GRADE 2 - SAEED IBN ZAYD (2ND SHIFT)</t>
         </is>
       </c>
       <c r="G237" t="inlineStr">
@@ -16032,32 +16032,32 @@
       </c>
       <c r="H237" t="inlineStr">
         <is>
-          <t>Grade 3</t>
+          <t>Grade 2</t>
         </is>
       </c>
       <c r="I237" t="inlineStr">
         <is>
-          <t>ODL - 1ST SHIFT</t>
+          <t>ODL - 2ND SHIFT</t>
         </is>
       </c>
       <c r="J237" t="inlineStr">
         <is>
-          <t>subj_fil3</t>
+          <t>subj_filipino</t>
         </is>
       </c>
       <c r="K237" t="inlineStr">
         <is>
-          <t>Fil3</t>
+          <t>Filipino</t>
         </is>
       </c>
       <c r="L237" t="inlineStr">
         <is>
-          <t>tchr_jenny</t>
+          <t>tchr_zuhora</t>
         </is>
       </c>
       <c r="M237" t="inlineStr">
         <is>
-          <t>Teacher Jenny</t>
+          <t>Teacher Zuhora</t>
         </is>
       </c>
       <c r="N237" t="n">
@@ -16074,7 +16074,7 @@
         </is>
       </c>
       <c r="C238" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D238" t="inlineStr">
         <is>
@@ -16083,12 +16083,12 @@
       </c>
       <c r="E238" t="inlineStr">
         <is>
-          <t>sec_grade_3_thabit_ibn_qays_2nd_shift_boys</t>
+          <t>sec_grade_3_salman_al_farsi_1st_shift_mix</t>
         </is>
       </c>
       <c r="F238" t="inlineStr">
         <is>
-          <t>GRADE 3 - THABIT IBN QAYS (2ND SHIFT) - BOYS</t>
+          <t>GRADE 3 - SALMAN AL FARSI (1ST SHIFT) MIX</t>
         </is>
       </c>
       <c r="G238" t="inlineStr">
@@ -16103,27 +16103,27 @@
       </c>
       <c r="I238" t="inlineStr">
         <is>
-          <t>ODL - 2ND SHIFT</t>
+          <t>ODL - 1ST SHIFT</t>
         </is>
       </c>
       <c r="J238" t="inlineStr">
         <is>
-          <t>subj_math</t>
+          <t>subj_fil3</t>
         </is>
       </c>
       <c r="K238" t="inlineStr">
         <is>
-          <t>Math</t>
+          <t>Fil3</t>
         </is>
       </c>
       <c r="L238" t="inlineStr">
         <is>
-          <t>tchr_jerlyn</t>
+          <t>tchr_jenny</t>
         </is>
       </c>
       <c r="M238" t="inlineStr">
         <is>
-          <t>Teacher Jerlyn</t>
+          <t>Teacher Jenny</t>
         </is>
       </c>
       <c r="N238" t="n">
@@ -16149,12 +16149,12 @@
       </c>
       <c r="E239" t="inlineStr">
         <is>
-          <t>sec_grade_3_zayd_ibn_haritha_2nd_shift_girls</t>
+          <t>sec_grade_3_thabit_ibn_qays_2nd_shift_boys</t>
         </is>
       </c>
       <c r="F239" t="inlineStr">
         <is>
-          <t>GRADE 3 - ZAYD IBN HARITHA (2ND SHIFT) - GIRLS</t>
+          <t>GRADE 3 - THABIT IBN QAYS (2ND SHIFT) - BOYS</t>
         </is>
       </c>
       <c r="G239" t="inlineStr">
@@ -16174,22 +16174,22 @@
       </c>
       <c r="J239" t="inlineStr">
         <is>
-          <t>subj_english</t>
+          <t>subj_math</t>
         </is>
       </c>
       <c r="K239" t="inlineStr">
         <is>
-          <t>English</t>
+          <t>Math</t>
         </is>
       </c>
       <c r="L239" t="inlineStr">
         <is>
-          <t>tchr_marham</t>
+          <t>tchr_jerlyn</t>
         </is>
       </c>
       <c r="M239" t="inlineStr">
         <is>
-          <t>Teacher Marham</t>
+          <t>Teacher Jerlyn</t>
         </is>
       </c>
       <c r="N239" t="n">
@@ -16206,7 +16206,7 @@
         </is>
       </c>
       <c r="C240" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D240" t="inlineStr">
         <is>
@@ -16215,12 +16215,12 @@
       </c>
       <c r="E240" t="inlineStr">
         <is>
-          <t>sec_grade_3_ammar_ibn_yasir_1st_shift_boys</t>
+          <t>sec_grade_3_zayd_ibn_haritha_2nd_shift_girls</t>
         </is>
       </c>
       <c r="F240" t="inlineStr">
         <is>
-          <t>GRADE 3 -AMMAR IBN YASIR (1ST SHIFT) - BOYS</t>
+          <t>GRADE 3 - ZAYD IBN HARITHA (2ND SHIFT) - GIRLS</t>
         </is>
       </c>
       <c r="G240" t="inlineStr">
@@ -16235,27 +16235,27 @@
       </c>
       <c r="I240" t="inlineStr">
         <is>
-          <t>ODL - 1ST SHIFT</t>
+          <t>ODL - 2ND SHIFT</t>
         </is>
       </c>
       <c r="J240" t="inlineStr">
         <is>
-          <t>subj_shaf</t>
+          <t>subj_english</t>
         </is>
       </c>
       <c r="K240" t="inlineStr">
         <is>
-          <t>SHAF</t>
+          <t>English</t>
         </is>
       </c>
       <c r="L240" t="inlineStr">
         <is>
-          <t>tchr_ersahad</t>
+          <t>tchr_marham</t>
         </is>
       </c>
       <c r="M240" t="inlineStr">
         <is>
-          <t>Ustadh Ersahad</t>
+          <t>Teacher Marham</t>
         </is>
       </c>
       <c r="N240" t="n">
@@ -16272,7 +16272,7 @@
         </is>
       </c>
       <c r="C241" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D241" t="inlineStr">
         <is>
@@ -16281,12 +16281,12 @@
       </c>
       <c r="E241" t="inlineStr">
         <is>
-          <t>sec_grade_4_az_zubair_ibn_al_awwaam_2nd_shift</t>
+          <t>sec_grade_3_ammar_ibn_yasir_1st_shift_boys</t>
         </is>
       </c>
       <c r="F241" t="inlineStr">
         <is>
-          <t>GRADE 4 - AZ ZUBAIR IBN AL AWWAAM (2ND SHIFT)</t>
+          <t>GRADE 3 -AMMAR IBN YASIR (1ST SHIFT) - BOYS</t>
         </is>
       </c>
       <c r="G241" t="inlineStr">
@@ -16296,32 +16296,32 @@
       </c>
       <c r="H241" t="inlineStr">
         <is>
-          <t>Grade 4</t>
+          <t>Grade 3</t>
         </is>
       </c>
       <c r="I241" t="inlineStr">
         <is>
-          <t>ODL - 2ND SHIFT</t>
+          <t>ODL - 1ST SHIFT</t>
         </is>
       </c>
       <c r="J241" t="inlineStr">
         <is>
-          <t>subj_filipino</t>
+          <t>subj_shaf</t>
         </is>
       </c>
       <c r="K241" t="inlineStr">
         <is>
-          <t>Filipino</t>
+          <t>SHAF</t>
         </is>
       </c>
       <c r="L241" t="inlineStr">
         <is>
-          <t>tchr_norhydie</t>
+          <t>tchr_ersahad</t>
         </is>
       </c>
       <c r="M241" t="inlineStr">
         <is>
-          <t>Teacher Norhydie</t>
+          <t>Ustadh Ersahad</t>
         </is>
       </c>
       <c r="N241" t="n">
@@ -16338,7 +16338,7 @@
         </is>
       </c>
       <c r="C242" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D242" t="inlineStr">
         <is>
@@ -16347,12 +16347,12 @@
       </c>
       <c r="E242" t="inlineStr">
         <is>
-          <t>sec_grade_4_hakim_ibn_hazm_1st_shift</t>
+          <t>sec_grade_4_az_zubair_ibn_al_awwaam_2nd_shift</t>
         </is>
       </c>
       <c r="F242" t="inlineStr">
         <is>
-          <t>GRADE 4 - HAKIM IBN HAZM(1ST SHIFT)</t>
+          <t>GRADE 4 - AZ ZUBAIR IBN AL AWWAAM (2ND SHIFT)</t>
         </is>
       </c>
       <c r="G242" t="inlineStr">
@@ -16367,27 +16367,27 @@
       </c>
       <c r="I242" t="inlineStr">
         <is>
-          <t>ODL - 1ST SHIFT</t>
+          <t>ODL - 2ND SHIFT</t>
         </is>
       </c>
       <c r="J242" t="inlineStr">
         <is>
-          <t>subj_math</t>
+          <t>subj_filipino</t>
         </is>
       </c>
       <c r="K242" t="inlineStr">
         <is>
-          <t>Math</t>
+          <t>Filipino</t>
         </is>
       </c>
       <c r="L242" t="inlineStr">
         <is>
-          <t>tchr_arvin</t>
+          <t>tchr_norhydie</t>
         </is>
       </c>
       <c r="M242" t="inlineStr">
         <is>
-          <t>Teacher Arvin</t>
+          <t>Teacher Norhydie</t>
         </is>
       </c>
       <c r="N242" t="n">
@@ -16404,7 +16404,7 @@
         </is>
       </c>
       <c r="C243" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D243" t="inlineStr">
         <is>
@@ -16413,12 +16413,12 @@
       </c>
       <c r="E243" t="inlineStr">
         <is>
-          <t>sec_grade_4_ikrimah_ibn_abi_jahl_2nd_shift</t>
+          <t>sec_grade_4_hakim_ibn_hazm_1st_shift</t>
         </is>
       </c>
       <c r="F243" t="inlineStr">
         <is>
-          <t>GRADE 4 - IKRIMAH IBN ABI JAHL (2ND SHIFT)</t>
+          <t>GRADE 4 - HAKIM IBN HAZM(1ST SHIFT)</t>
         </is>
       </c>
       <c r="G243" t="inlineStr">
@@ -16433,27 +16433,27 @@
       </c>
       <c r="I243" t="inlineStr">
         <is>
-          <t>ODL - 2ND SHIFT</t>
+          <t>ODL - 1ST SHIFT</t>
         </is>
       </c>
       <c r="J243" t="inlineStr">
         <is>
-          <t>subj_tle</t>
+          <t>subj_math</t>
         </is>
       </c>
       <c r="K243" t="inlineStr">
         <is>
-          <t>TLE</t>
+          <t>Math</t>
         </is>
       </c>
       <c r="L243" t="inlineStr">
         <is>
-          <t>tchr_monisa</t>
+          <t>tchr_arvin</t>
         </is>
       </c>
       <c r="M243" t="inlineStr">
         <is>
-          <t>Teacher Monisa</t>
+          <t>Teacher Arvin</t>
         </is>
       </c>
       <c r="N243" t="n">
@@ -16479,12 +16479,12 @@
       </c>
       <c r="E244" t="inlineStr">
         <is>
-          <t>sec_grade_4_hassan_ibn_thabit_2nd_shift_mix</t>
+          <t>sec_grade_4_ikrimah_ibn_abi_jahl_2nd_shift</t>
         </is>
       </c>
       <c r="F244" t="inlineStr">
         <is>
-          <t>GRADE 4 -HASSAN IBN THABIT (2ND SHIFT) - MIX</t>
+          <t>GRADE 4 - IKRIMAH IBN ABI JAHL (2ND SHIFT)</t>
         </is>
       </c>
       <c r="G244" t="inlineStr">
@@ -16504,22 +16504,22 @@
       </c>
       <c r="J244" t="inlineStr">
         <is>
-          <t>subj_math</t>
+          <t>subj_tle</t>
         </is>
       </c>
       <c r="K244" t="inlineStr">
         <is>
-          <t>Math</t>
+          <t>TLE</t>
         </is>
       </c>
       <c r="L244" t="inlineStr">
         <is>
-          <t>tchr_saimonah</t>
+          <t>tchr_monisa</t>
         </is>
       </c>
       <c r="M244" t="inlineStr">
         <is>
-          <t>Teacher Saimonah</t>
+          <t>Teacher Monisa</t>
         </is>
       </c>
       <c r="N244" t="n">
@@ -16536,7 +16536,7 @@
         </is>
       </c>
       <c r="C245" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D245" t="inlineStr">
         <is>
@@ -16545,12 +16545,12 @@
       </c>
       <c r="E245" t="inlineStr">
         <is>
-          <t>sec_grade_5_ayyash_ibn_abi_rabi_ah_1st_shift</t>
+          <t>sec_grade_4_hassan_ibn_thabit_2nd_shift_mix</t>
         </is>
       </c>
       <c r="F245" t="inlineStr">
         <is>
-          <t>GRADE 5 - AYYASH IBN ABI RABI'AH(1ST SHIFT)</t>
+          <t>GRADE 4 -HASSAN IBN THABIT (2ND SHIFT) - MIX</t>
         </is>
       </c>
       <c r="G245" t="inlineStr">
@@ -16560,32 +16560,32 @@
       </c>
       <c r="H245" t="inlineStr">
         <is>
-          <t>Grade 5</t>
+          <t>Grade 4</t>
         </is>
       </c>
       <c r="I245" t="inlineStr">
         <is>
-          <t>ODL - 1ST SHIFT</t>
+          <t>ODL - 2ND SHIFT</t>
         </is>
       </c>
       <c r="J245" t="inlineStr">
         <is>
-          <t>subj_shaf</t>
+          <t>subj_math</t>
         </is>
       </c>
       <c r="K245" t="inlineStr">
         <is>
-          <t>SHAF</t>
+          <t>Math</t>
         </is>
       </c>
       <c r="L245" t="inlineStr">
         <is>
-          <t>tchr_faidh</t>
+          <t>tchr_saimonah</t>
         </is>
       </c>
       <c r="M245" t="inlineStr">
         <is>
-          <t>Ustadh Faidh</t>
+          <t>Teacher Saimonah</t>
         </is>
       </c>
       <c r="N245" t="n">
@@ -16611,12 +16611,12 @@
       </c>
       <c r="E246" t="inlineStr">
         <is>
-          <t>sec_grade_5_hamza_ibn_abdul_1st_shift</t>
+          <t>sec_grade_5_ayyash_ibn_abi_rabi_ah_1st_shift</t>
         </is>
       </c>
       <c r="F246" t="inlineStr">
         <is>
-          <t>GRADE 5 - HAMZA IBN ABDUL (1ST SHIFT)</t>
+          <t>GRADE 5 - AYYASH IBN ABI RABI'AH(1ST SHIFT)</t>
         </is>
       </c>
       <c r="G246" t="inlineStr">
@@ -16636,22 +16636,22 @@
       </c>
       <c r="J246" t="inlineStr">
         <is>
-          <t>subj_gmrc</t>
+          <t>subj_shaf</t>
         </is>
       </c>
       <c r="K246" t="inlineStr">
         <is>
-          <t>GMRC</t>
+          <t>SHAF</t>
         </is>
       </c>
       <c r="L246" t="inlineStr">
         <is>
-          <t>tchr_jairah</t>
+          <t>tchr_faidh</t>
         </is>
       </c>
       <c r="M246" t="inlineStr">
         <is>
-          <t>Teacher Jairah</t>
+          <t>Ustadh Faidh</t>
         </is>
       </c>
       <c r="N246" t="n">
@@ -16677,12 +16677,12 @@
       </c>
       <c r="E247" t="inlineStr">
         <is>
-          <t>sec_grade_5_muhammad_ibn_maslamah_1st_shift</t>
+          <t>sec_grade_5_hamza_ibn_abdul_1st_shift</t>
         </is>
       </c>
       <c r="F247" t="inlineStr">
         <is>
-          <t>GRADE 5 - MUHAMMAD IBN MASLAMAH (1ST SHIFT)</t>
+          <t>GRADE 5 - HAMZA IBN ABDUL (1ST SHIFT)</t>
         </is>
       </c>
       <c r="G247" t="inlineStr">
@@ -16702,22 +16702,22 @@
       </c>
       <c r="J247" t="inlineStr">
         <is>
-          <t>subj_araling_panlipunan</t>
+          <t>subj_gmrc</t>
         </is>
       </c>
       <c r="K247" t="inlineStr">
         <is>
-          <t>Araling Panlipunan</t>
+          <t>GMRC</t>
         </is>
       </c>
       <c r="L247" t="inlineStr">
         <is>
-          <t>tchr_keychell</t>
+          <t>tchr_jairah</t>
         </is>
       </c>
       <c r="M247" t="inlineStr">
         <is>
-          <t>Teacher Keychell</t>
+          <t>Teacher Jairah</t>
         </is>
       </c>
       <c r="N247" t="n">
@@ -16734,7 +16734,7 @@
         </is>
       </c>
       <c r="C248" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D248" t="inlineStr">
         <is>
@@ -16743,12 +16743,12 @@
       </c>
       <c r="E248" t="inlineStr">
         <is>
-          <t>sec_grade_5_mus_ab_ibn_abdul_mutalib_2nd_shift</t>
+          <t>sec_grade_5_muhammad_ibn_maslamah_1st_shift</t>
         </is>
       </c>
       <c r="F248" t="inlineStr">
         <is>
-          <t>GRADE 5 - MUS'AB IBN ABDUL MUTALIB (2ND SHIFT)</t>
+          <t>GRADE 5 - MUHAMMAD IBN MASLAMAH (1ST SHIFT)</t>
         </is>
       </c>
       <c r="G248" t="inlineStr">
@@ -16763,27 +16763,27 @@
       </c>
       <c r="I248" t="inlineStr">
         <is>
-          <t>ODL - 2ND SHIFT</t>
+          <t>ODL - 1ST SHIFT</t>
         </is>
       </c>
       <c r="J248" t="inlineStr">
         <is>
-          <t>subj_qur_an</t>
+          <t>subj_araling_panlipunan</t>
         </is>
       </c>
       <c r="K248" t="inlineStr">
         <is>
-          <t>Qur'an</t>
+          <t>Araling Panlipunan</t>
         </is>
       </c>
       <c r="L248" t="inlineStr">
         <is>
-          <t>tchr_jaisam</t>
+          <t>tchr_keychell</t>
         </is>
       </c>
       <c r="M248" t="inlineStr">
         <is>
-          <t>Ustadh Jaisam</t>
+          <t>Teacher Keychell</t>
         </is>
       </c>
       <c r="N248" t="n">
@@ -16800,7 +16800,7 @@
         </is>
       </c>
       <c r="C249" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D249" t="inlineStr">
         <is>
@@ -16809,12 +16809,12 @@
       </c>
       <c r="E249" t="inlineStr">
         <is>
-          <t>sec_grade_6_abbas_ibn_abd_al_muttalib_1st_shift</t>
+          <t>sec_grade_5_mus_ab_ibn_abdul_mutalib_2nd_shift</t>
         </is>
       </c>
       <c r="F249" t="inlineStr">
         <is>
-          <t>GRADE 6 - ABBAS IBN ABD AL-MUTTALIB (1ST SHIFT)</t>
+          <t>GRADE 5 - MUS'AB IBN ABDUL MUTALIB (2ND SHIFT)</t>
         </is>
       </c>
       <c r="G249" t="inlineStr">
@@ -16824,32 +16824,32 @@
       </c>
       <c r="H249" t="inlineStr">
         <is>
-          <t>Grade 6</t>
+          <t>Grade 5</t>
         </is>
       </c>
       <c r="I249" t="inlineStr">
         <is>
-          <t>ODL - 1ST SHIFT</t>
+          <t>ODL - 2ND SHIFT</t>
         </is>
       </c>
       <c r="J249" t="inlineStr">
         <is>
-          <t>subj_english</t>
+          <t>subj_qur_an</t>
         </is>
       </c>
       <c r="K249" t="inlineStr">
         <is>
-          <t>English</t>
+          <t>Qur'an</t>
         </is>
       </c>
       <c r="L249" t="inlineStr">
         <is>
-          <t>tchr_jessa</t>
+          <t>tchr_jaisam</t>
         </is>
       </c>
       <c r="M249" t="inlineStr">
         <is>
-          <t>Teacher Jessa</t>
+          <t>Ustadh Jaisam</t>
         </is>
       </c>
       <c r="N249" t="n">
@@ -16866,7 +16866,7 @@
         </is>
       </c>
       <c r="C250" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D250" t="inlineStr">
         <is>
@@ -16875,12 +16875,12 @@
       </c>
       <c r="E250" t="inlineStr">
         <is>
-          <t>sec_grade_6_dihya_ibn_khalifah_2nd_shift_girls</t>
+          <t>sec_grade_6_abbas_ibn_abd_al_muttalib_1st_shift</t>
         </is>
       </c>
       <c r="F250" t="inlineStr">
         <is>
-          <t>GRADE 6 - DIHYA IBN KHALIFAH (2ND SHIFT) GIRLS</t>
+          <t>GRADE 6 - ABBAS IBN ABD AL-MUTTALIB (1ST SHIFT)</t>
         </is>
       </c>
       <c r="G250" t="inlineStr">
@@ -16895,27 +16895,27 @@
       </c>
       <c r="I250" t="inlineStr">
         <is>
-          <t>ODL - 2ND SHIFT</t>
+          <t>ODL - 1ST SHIFT</t>
         </is>
       </c>
       <c r="J250" t="inlineStr">
         <is>
-          <t>subj_qur_an</t>
+          <t>subj_english</t>
         </is>
       </c>
       <c r="K250" t="inlineStr">
         <is>
-          <t>Qur'an</t>
+          <t>English</t>
         </is>
       </c>
       <c r="L250" t="inlineStr">
         <is>
-          <t>tchr_obaydah</t>
+          <t>tchr_jessa</t>
         </is>
       </c>
       <c r="M250" t="inlineStr">
         <is>
-          <t>Ustadh Obaydah</t>
+          <t>Teacher Jessa</t>
         </is>
       </c>
       <c r="N250" t="n">
@@ -16941,12 +16941,12 @@
       </c>
       <c r="E251" t="inlineStr">
         <is>
-          <t>sec_grade_6_khaleed_ibn_waleed_2nd_shift</t>
+          <t>sec_grade_6_dihya_ibn_khalifah_2nd_shift_girls</t>
         </is>
       </c>
       <c r="F251" t="inlineStr">
         <is>
-          <t>GRADE 6 - KHALEED IBN WALEED (2ND SHIFT)</t>
+          <t>GRADE 6 - DIHYA IBN KHALIFAH (2ND SHIFT) GIRLS</t>
         </is>
       </c>
       <c r="G251" t="inlineStr">
@@ -16966,22 +16966,22 @@
       </c>
       <c r="J251" t="inlineStr">
         <is>
-          <t>subj_arabic</t>
+          <t>subj_qur_an</t>
         </is>
       </c>
       <c r="K251" t="inlineStr">
         <is>
-          <t>Arabic</t>
+          <t>Qur'an</t>
         </is>
       </c>
       <c r="L251" t="inlineStr">
         <is>
-          <t>tchr_ali</t>
+          <t>tchr_obaydah</t>
         </is>
       </c>
       <c r="M251" t="inlineStr">
         <is>
-          <t>Ustadh Ali</t>
+          <t>Ustadh Obaydah</t>
         </is>
       </c>
       <c r="N251" t="n">
@@ -16998,7 +16998,7 @@
         </is>
       </c>
       <c r="C252" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D252" t="inlineStr">
         <is>
@@ -17007,47 +17007,47 @@
       </c>
       <c r="E252" t="inlineStr">
         <is>
-          <t>sec_grade_7_abu_sufyan_ibn_al_harith_1st_shift_boys</t>
+          <t>sec_grade_6_khaleed_ibn_waleed_2nd_shift</t>
         </is>
       </c>
       <c r="F252" t="inlineStr">
         <is>
-          <t>GRADE 7 - ABU SUFYAN IBN AL-HARITH (1ST SHIFT) BOYS</t>
+          <t>GRADE 6 - KHALEED IBN WALEED (2ND SHIFT)</t>
         </is>
       </c>
       <c r="G252" t="inlineStr">
         <is>
-          <t>Junior High School</t>
+          <t>Elementary</t>
         </is>
       </c>
       <c r="H252" t="inlineStr">
         <is>
-          <t>Grade 7</t>
+          <t>Grade 6</t>
         </is>
       </c>
       <c r="I252" t="inlineStr">
         <is>
-          <t>ODL - 1ST SHIFT</t>
+          <t>ODL - 2ND SHIFT</t>
         </is>
       </c>
       <c r="J252" t="inlineStr">
         <is>
-          <t>subj_social_studies</t>
+          <t>subj_arabic</t>
         </is>
       </c>
       <c r="K252" t="inlineStr">
         <is>
-          <t>Social Studies</t>
+          <t>Arabic</t>
         </is>
       </c>
       <c r="L252" t="inlineStr">
         <is>
-          <t>tchr_shirehan</t>
+          <t>tchr_ali</t>
         </is>
       </c>
       <c r="M252" t="inlineStr">
         <is>
-          <t>Teacher Shirehan</t>
+          <t>Ustadh Ali</t>
         </is>
       </c>
       <c r="N252" t="n">
@@ -17064,7 +17064,7 @@
         </is>
       </c>
       <c r="C253" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D253" t="inlineStr">
         <is>
@@ -17073,12 +17073,12 @@
       </c>
       <c r="E253" t="inlineStr">
         <is>
-          <t>sec_grade_7_anas_ibn_malik_2nd_shift_mix</t>
+          <t>sec_grade_7_abu_sufyan_ibn_al_harith_1st_shift_boys</t>
         </is>
       </c>
       <c r="F253" t="inlineStr">
         <is>
-          <t>GRADE 7 - ANAS IBN MALIK (2ND SHIFT) - MIX</t>
+          <t>GRADE 7 - ABU SUFYAN IBN AL-HARITH (1ST SHIFT) BOYS</t>
         </is>
       </c>
       <c r="G253" t="inlineStr">
@@ -17093,27 +17093,27 @@
       </c>
       <c r="I253" t="inlineStr">
         <is>
-          <t>ODL - 2ND SHIFT</t>
+          <t>ODL - 1ST SHIFT</t>
         </is>
       </c>
       <c r="J253" t="inlineStr">
         <is>
-          <t>subj_gmrc</t>
+          <t>subj_social_studies</t>
         </is>
       </c>
       <c r="K253" t="inlineStr">
         <is>
-          <t>GMRC</t>
+          <t>Social Studies</t>
         </is>
       </c>
       <c r="L253" t="inlineStr">
         <is>
-          <t>tchr_silfah</t>
+          <t>tchr_shirehan</t>
         </is>
       </c>
       <c r="M253" t="inlineStr">
         <is>
-          <t>Ustadh Silfah</t>
+          <t>Teacher Shirehan</t>
         </is>
       </c>
       <c r="N253" t="n">
@@ -17130,7 +17130,7 @@
         </is>
       </c>
       <c r="C254" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D254" t="inlineStr">
         <is>
@@ -17139,12 +17139,12 @@
       </c>
       <c r="E254" t="inlineStr">
         <is>
-          <t>sec_grade_7_usama_ibn_zayd_1st_shift_girls</t>
+          <t>sec_grade_7_anas_ibn_malik_2nd_shift_mix</t>
         </is>
       </c>
       <c r="F254" t="inlineStr">
         <is>
-          <t>GRADE 7 - USAMA IBN ZAYD (1ST SHIFT) GIRLS</t>
+          <t>GRADE 7 - ANAS IBN MALIK (2ND SHIFT) - MIX</t>
         </is>
       </c>
       <c r="G254" t="inlineStr">
@@ -17159,27 +17159,27 @@
       </c>
       <c r="I254" t="inlineStr">
         <is>
-          <t>ODL - 1ST SHIFT</t>
+          <t>ODL - 2ND SHIFT</t>
         </is>
       </c>
       <c r="J254" t="inlineStr">
         <is>
-          <t>subj_science</t>
+          <t>subj_gmrc</t>
         </is>
       </c>
       <c r="K254" t="inlineStr">
         <is>
-          <t>Science</t>
+          <t>GMRC</t>
         </is>
       </c>
       <c r="L254" t="inlineStr">
         <is>
-          <t>tchr_aniah</t>
+          <t>tchr_silfah</t>
         </is>
       </c>
       <c r="M254" t="inlineStr">
         <is>
-          <t>Teacher Aniah</t>
+          <t>Ustadh Silfah</t>
         </is>
       </c>
       <c r="N254" t="n">
@@ -17196,7 +17196,7 @@
         </is>
       </c>
       <c r="C255" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D255" t="inlineStr">
         <is>
@@ -17205,12 +17205,12 @@
       </c>
       <c r="E255" t="inlineStr">
         <is>
-          <t>sec_grade_8_mu_adh_ibn_jabal_2nd_shift_boys</t>
+          <t>sec_grade_7_usama_ibn_zayd_1st_shift_girls</t>
         </is>
       </c>
       <c r="F255" t="inlineStr">
         <is>
-          <t>GRADE 8 - MU'ADH IBN JABAL (2ND SHIFT) - BOYS</t>
+          <t>GRADE 7 - USAMA IBN ZAYD (1ST SHIFT) GIRLS</t>
         </is>
       </c>
       <c r="G255" t="inlineStr">
@@ -17220,12 +17220,12 @@
       </c>
       <c r="H255" t="inlineStr">
         <is>
-          <t>Grade 8</t>
+          <t>Grade 7</t>
         </is>
       </c>
       <c r="I255" t="inlineStr">
         <is>
-          <t>ODL - 2ND SHIFT</t>
+          <t>ODL - 1ST SHIFT</t>
         </is>
       </c>
       <c r="J255" t="inlineStr">
@@ -17240,12 +17240,12 @@
       </c>
       <c r="L255" t="inlineStr">
         <is>
-          <t>tchr_radzmia</t>
+          <t>tchr_aniah</t>
         </is>
       </c>
       <c r="M255" t="inlineStr">
         <is>
-          <t>Teacher Radzmia</t>
+          <t>Teacher Aniah</t>
         </is>
       </c>
       <c r="N255" t="n">
@@ -17271,12 +17271,12 @@
       </c>
       <c r="E256" t="inlineStr">
         <is>
-          <t>sec_grade_8_nuaym_ibn_mas_ud_2nd_shift_mix</t>
+          <t>sec_grade_8_mu_adh_ibn_jabal_2nd_shift_boys</t>
         </is>
       </c>
       <c r="F256" t="inlineStr">
         <is>
-          <t>GRADE 8 - NUAYM IBN MAS'UD (2ND SHIFT) MIX</t>
+          <t>GRADE 8 - MU'ADH IBN JABAL (2ND SHIFT) - BOYS</t>
         </is>
       </c>
       <c r="G256" t="inlineStr">
@@ -17296,22 +17296,22 @@
       </c>
       <c r="J256" t="inlineStr">
         <is>
-          <t>subj_tle</t>
+          <t>subj_science</t>
         </is>
       </c>
       <c r="K256" t="inlineStr">
         <is>
-          <t>TLE</t>
+          <t>Science</t>
         </is>
       </c>
       <c r="L256" t="inlineStr">
         <is>
-          <t>tchr_halnaisa</t>
+          <t>tchr_radzmia</t>
         </is>
       </c>
       <c r="M256" t="inlineStr">
         <is>
-          <t>Teacher Halnaisa</t>
+          <t>Teacher Radzmia</t>
         </is>
       </c>
       <c r="N256" t="n">
@@ -17328,7 +17328,7 @@
         </is>
       </c>
       <c r="C257" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D257" t="inlineStr">
         <is>
@@ -17337,12 +17337,12 @@
       </c>
       <c r="E257" t="inlineStr">
         <is>
-          <t>sec_grade_8_sa_ad_ibn_mua_dh_1st_shift_girls</t>
+          <t>sec_grade_8_nuaym_ibn_mas_ud_2nd_shift_mix</t>
         </is>
       </c>
       <c r="F257" t="inlineStr">
         <is>
-          <t>GRADE 8 - SA'AD IBN MUA'DH (1ST SHIFT) - GIRLS</t>
+          <t>GRADE 8 - NUAYM IBN MAS'UD (2ND SHIFT) MIX</t>
         </is>
       </c>
       <c r="G257" t="inlineStr">
@@ -17357,27 +17357,27 @@
       </c>
       <c r="I257" t="inlineStr">
         <is>
-          <t>ODL - 1ST SHIFT</t>
+          <t>ODL - 2ND SHIFT</t>
         </is>
       </c>
       <c r="J257" t="inlineStr">
         <is>
-          <t>subj_shaf</t>
+          <t>subj_tle</t>
         </is>
       </c>
       <c r="K257" t="inlineStr">
         <is>
-          <t>SHAF</t>
+          <t>TLE</t>
         </is>
       </c>
       <c r="L257" t="inlineStr">
         <is>
-          <t>tchr_samsuddin</t>
+          <t>tchr_halnaisa</t>
         </is>
       </c>
       <c r="M257" t="inlineStr">
         <is>
-          <t>Alim Samsuddin</t>
+          <t>Teacher Halnaisa</t>
         </is>
       </c>
       <c r="N257" t="n">
@@ -17394,7 +17394,7 @@
         </is>
       </c>
       <c r="C258" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D258" t="inlineStr">
         <is>
@@ -17403,12 +17403,12 @@
       </c>
       <c r="E258" t="inlineStr">
         <is>
-          <t>sec_grade_9_abu_dharr_al_ghifarri_2nd_shift_boys</t>
+          <t>sec_grade_8_sa_ad_ibn_mua_dh_1st_shift_girls</t>
         </is>
       </c>
       <c r="F258" t="inlineStr">
         <is>
-          <t>GRADE 9 - ABU DHARR AL GHIFARRI (2ND SHIFT) BOYS</t>
+          <t>GRADE 8 - SA'AD IBN MUA'DH (1ST SHIFT) - GIRLS</t>
         </is>
       </c>
       <c r="G258" t="inlineStr">
@@ -17418,32 +17418,32 @@
       </c>
       <c r="H258" t="inlineStr">
         <is>
-          <t>Grade 9</t>
+          <t>Grade 8</t>
         </is>
       </c>
       <c r="I258" t="inlineStr">
         <is>
-          <t>ODL - 2ND SHIFT</t>
+          <t>ODL - 1ST SHIFT</t>
         </is>
       </c>
       <c r="J258" t="inlineStr">
         <is>
-          <t>subj_social_studies</t>
+          <t>subj_shaf</t>
         </is>
       </c>
       <c r="K258" t="inlineStr">
         <is>
-          <t>Social Science</t>
+          <t>SHAF</t>
         </is>
       </c>
       <c r="L258" t="inlineStr">
         <is>
-          <t>tchr_sophia</t>
+          <t>tchr_samsuddin</t>
         </is>
       </c>
       <c r="M258" t="inlineStr">
         <is>
-          <t>Teacher Sophia</t>
+          <t>Alim Samsuddin</t>
         </is>
       </c>
       <c r="N258" t="n">
@@ -17469,12 +17469,12 @@
       </c>
       <c r="E259" t="inlineStr">
         <is>
-          <t>sec_grade_9_abu_jandal_ibn_suhayl_2nd_shift_girls</t>
+          <t>sec_grade_9_abu_dharr_al_ghifarri_2nd_shift_boys</t>
         </is>
       </c>
       <c r="F259" t="inlineStr">
         <is>
-          <t>GRADE 9 - ABU JANDAL IBN SUHAYL (2ND SHIFT) GIRLS</t>
+          <t>GRADE 9 - ABU DHARR AL GHIFARRI (2ND SHIFT) BOYS</t>
         </is>
       </c>
       <c r="G259" t="inlineStr">
@@ -17494,22 +17494,22 @@
       </c>
       <c r="J259" t="inlineStr">
         <is>
-          <t>subj_tle</t>
+          <t>subj_social_studies</t>
         </is>
       </c>
       <c r="K259" t="inlineStr">
         <is>
-          <t>TLE</t>
+          <t>Social Science</t>
         </is>
       </c>
       <c r="L259" t="inlineStr">
         <is>
-          <t>tchr_angeleni</t>
+          <t>tchr_sophia</t>
         </is>
       </c>
       <c r="M259" t="inlineStr">
         <is>
-          <t>Teacher Angeleni</t>
+          <t>Teacher Sophia</t>
         </is>
       </c>
       <c r="N259" t="n">
@@ -17526,21 +17526,21 @@
         </is>
       </c>
       <c r="C260" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D260" t="inlineStr">
         <is>
-          <t>04:20 PM – 05:20 PM</t>
+          <t>03:10 PM – 04:10 PM</t>
         </is>
       </c>
       <c r="E260" t="inlineStr">
         <is>
-          <t>sec_grade_10_abu_ayyub_al_ansari_2nd_shift_boys</t>
+          <t>sec_grade_9_abu_jandal_ibn_suhayl_2nd_shift_girls</t>
         </is>
       </c>
       <c r="F260" t="inlineStr">
         <is>
-          <t>GRADE 10 - ABU AYYUB AL-ANSARI (2ND SHIFT) BOYS</t>
+          <t>GRADE 9 - ABU JANDAL IBN SUHAYL (2ND SHIFT) GIRLS</t>
         </is>
       </c>
       <c r="G260" t="inlineStr">
@@ -17550,7 +17550,7 @@
       </c>
       <c r="H260" t="inlineStr">
         <is>
-          <t>Grade 10</t>
+          <t>Grade 9</t>
         </is>
       </c>
       <c r="I260" t="inlineStr">
@@ -17560,22 +17560,22 @@
       </c>
       <c r="J260" t="inlineStr">
         <is>
-          <t>subj_filipino</t>
+          <t>subj_tle</t>
         </is>
       </c>
       <c r="K260" t="inlineStr">
         <is>
-          <t>Filipino</t>
+          <t>TLE</t>
         </is>
       </c>
       <c r="L260" t="inlineStr">
         <is>
-          <t>tchr_nadzra</t>
+          <t>tchr_angeleni</t>
         </is>
       </c>
       <c r="M260" t="inlineStr">
         <is>
-          <t>Teacher Nadzra</t>
+          <t>Teacher Angeleni</t>
         </is>
       </c>
       <c r="N260" t="n">
@@ -17592,7 +17592,7 @@
         </is>
       </c>
       <c r="C261" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D261" t="inlineStr">
         <is>
@@ -17601,47 +17601,47 @@
       </c>
       <c r="E261" t="inlineStr">
         <is>
-          <t>sec_grade_11_1st_shift_girls</t>
+          <t>sec_grade_10_abu_ayyub_al_ansari_2nd_shift_boys</t>
         </is>
       </c>
       <c r="F261" t="inlineStr">
         <is>
-          <t>GRADE 11 (1ST SHIFT GIRLS)</t>
+          <t>GRADE 10 - ABU AYYUB AL-ANSARI (2ND SHIFT) BOYS</t>
         </is>
       </c>
       <c r="G261" t="inlineStr">
         <is>
-          <t>Senior High School</t>
+          <t>Junior High School</t>
         </is>
       </c>
       <c r="H261" t="inlineStr">
         <is>
-          <t>Grade 11</t>
+          <t>Grade 10</t>
         </is>
       </c>
       <c r="I261" t="inlineStr">
         <is>
-          <t>ODL - 1ST SHIFT</t>
+          <t>ODL - 2ND SHIFT</t>
         </is>
       </c>
       <c r="J261" t="inlineStr">
         <is>
-          <t>subj_gen_bio_1</t>
+          <t>subj_filipino</t>
         </is>
       </c>
       <c r="K261" t="inlineStr">
         <is>
-          <t>Gen Bio 1</t>
+          <t>Filipino</t>
         </is>
       </c>
       <c r="L261" t="inlineStr">
         <is>
-          <t>tchr_rowena</t>
+          <t>tchr_nadzra</t>
         </is>
       </c>
       <c r="M261" t="inlineStr">
         <is>
-          <t>Teacher Rowena</t>
+          <t>Teacher Nadzra</t>
         </is>
       </c>
       <c r="N261" t="n">
@@ -17658,21 +17658,21 @@
         </is>
       </c>
       <c r="C262" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D262" t="inlineStr">
         <is>
-          <t>04:20 PM – 06:30 PM</t>
+          <t>04:20 PM – 05:20 PM</t>
         </is>
       </c>
       <c r="E262" t="inlineStr">
         <is>
-          <t>sec_grade_11_2nd_shift_boys</t>
+          <t>sec_grade_11_1st_shift_girls</t>
         </is>
       </c>
       <c r="F262" t="inlineStr">
         <is>
-          <t>GRADE 11 (2ND SHIFT BOYS)</t>
+          <t>GRADE 11 (1ST SHIFT GIRLS)</t>
         </is>
       </c>
       <c r="G262" t="inlineStr">
@@ -17687,31 +17687,31 @@
       </c>
       <c r="I262" t="inlineStr">
         <is>
-          <t>ODL - 2ND SHIFT</t>
+          <t>ODL - 1ST SHIFT</t>
         </is>
       </c>
       <c r="J262" t="inlineStr">
         <is>
-          <t>subj_gen_math</t>
+          <t>subj_gen_bio_1</t>
         </is>
       </c>
       <c r="K262" t="inlineStr">
         <is>
-          <t>Gen Math</t>
+          <t>Gen Bio 1</t>
         </is>
       </c>
       <c r="L262" t="inlineStr">
         <is>
-          <t>tchr_jhelyn</t>
+          <t>tchr_rowena</t>
         </is>
       </c>
       <c r="M262" t="inlineStr">
         <is>
-          <t>Teacher Jhelyn</t>
+          <t>Teacher Rowena</t>
         </is>
       </c>
       <c r="N262" t="n">
-        <v>120</v>
+        <v>60</v>
       </c>
     </row>
     <row r="263">
@@ -17724,21 +17724,21 @@
         </is>
       </c>
       <c r="C263" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D263" t="inlineStr">
         <is>
-          <t>04:20 PM – 05:20 PM</t>
+          <t>04:20 PM – 06:30 PM</t>
         </is>
       </c>
       <c r="E263" t="inlineStr">
         <is>
-          <t>sec_grade_12_abu_musa_al_ashari</t>
+          <t>sec_grade_11_2nd_shift_boys</t>
         </is>
       </c>
       <c r="F263" t="inlineStr">
         <is>
-          <t>GRADE 12 - ABU MUSA AL-ASHARI</t>
+          <t>GRADE 11 (2ND SHIFT BOYS)</t>
         </is>
       </c>
       <c r="G263" t="inlineStr">
@@ -17748,36 +17748,36 @@
       </c>
       <c r="H263" t="inlineStr">
         <is>
-          <t>Grade 12</t>
+          <t>Grade 11</t>
         </is>
       </c>
       <c r="I263" t="inlineStr">
         <is>
-          <t>ODL - 1ST SHIFT</t>
+          <t>ODL - 2ND SHIFT</t>
         </is>
       </c>
       <c r="J263" t="inlineStr">
         <is>
-          <t>subj_mil</t>
+          <t>subj_gen_math</t>
         </is>
       </c>
       <c r="K263" t="inlineStr">
         <is>
-          <t>MIL</t>
+          <t>Gen Math</t>
         </is>
       </c>
       <c r="L263" t="inlineStr">
         <is>
-          <t>tchr_ethel</t>
+          <t>tchr_jhelyn</t>
         </is>
       </c>
       <c r="M263" t="inlineStr">
         <is>
-          <t>Teacher Ethel</t>
+          <t>Teacher Jhelyn</t>
         </is>
       </c>
       <c r="N263" t="n">
-        <v>60</v>
+        <v>120</v>
       </c>
     </row>
     <row r="264">
@@ -25512,7 +25512,7 @@
         </is>
       </c>
       <c r="C381" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D381" t="inlineStr">
         <is>
@@ -25521,47 +25521,47 @@
       </c>
       <c r="E381" t="inlineStr">
         <is>
-          <t>sec_grade_2_saeed_ibn_zayd_2nd_shift</t>
+          <t>sec_grade_12_abu_musa_al_ashari</t>
         </is>
       </c>
       <c r="F381" t="inlineStr">
         <is>
-          <t>GRADE 2 - SAEED IBN ZAYD (2ND SHIFT)</t>
+          <t>GRADE 12 - ABU MUSA AL-ASHARI</t>
         </is>
       </c>
       <c r="G381" t="inlineStr">
         <is>
-          <t>Elementary</t>
+          <t>Senior High School</t>
         </is>
       </c>
       <c r="H381" t="inlineStr">
         <is>
-          <t>Grade 2</t>
+          <t>Grade 12</t>
         </is>
       </c>
       <c r="I381" t="inlineStr">
         <is>
-          <t>ODL - 2ND SHIFT</t>
+          <t>ODL - 1ST SHIFT</t>
         </is>
       </c>
       <c r="J381" t="inlineStr">
         <is>
-          <t>subj_math</t>
+          <t>subj_prac_res_2</t>
         </is>
       </c>
       <c r="K381" t="inlineStr">
         <is>
-          <t>Math</t>
+          <t>Prac. Res. 2</t>
         </is>
       </c>
       <c r="L381" t="inlineStr">
         <is>
-          <t>tchr_sitti_kauzar</t>
+          <t>tchr_aniah</t>
         </is>
       </c>
       <c r="M381" t="inlineStr">
         <is>
-          <t>Teacher Sitti Kauzar</t>
+          <t>Teacher Aniah</t>
         </is>
       </c>
       <c r="N381" t="n">
@@ -25587,12 +25587,12 @@
       </c>
       <c r="E382" t="inlineStr">
         <is>
-          <t>sec_grade_3_as_ad_ibn_zurarah_2nd_shift_mix</t>
+          <t>sec_grade_2_saeed_ibn_zayd_2nd_shift</t>
         </is>
       </c>
       <c r="F382" t="inlineStr">
         <is>
-          <t>GRADE 3 - AS'AD IBN ZURARAH (2ND SHIFT) MIX</t>
+          <t>GRADE 2 - SAEED IBN ZAYD (2ND SHIFT)</t>
         </is>
       </c>
       <c r="G382" t="inlineStr">
@@ -25602,7 +25602,7 @@
       </c>
       <c r="H382" t="inlineStr">
         <is>
-          <t>Grade 3</t>
+          <t>Grade 2</t>
         </is>
       </c>
       <c r="I382" t="inlineStr">
@@ -25612,22 +25612,22 @@
       </c>
       <c r="J382" t="inlineStr">
         <is>
-          <t>subj_arabic</t>
+          <t>subj_math</t>
         </is>
       </c>
       <c r="K382" t="inlineStr">
         <is>
-          <t>Arabic</t>
+          <t>Math</t>
         </is>
       </c>
       <c r="L382" t="inlineStr">
         <is>
-          <t>tchr_faidh</t>
+          <t>tchr_sitti_kauzar</t>
         </is>
       </c>
       <c r="M382" t="inlineStr">
         <is>
-          <t>Ustadh Faidh</t>
+          <t>Teacher Sitti Kauzar</t>
         </is>
       </c>
       <c r="N382" t="n">
@@ -25644,7 +25644,7 @@
         </is>
       </c>
       <c r="C383" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D383" t="inlineStr">
         <is>
@@ -25653,12 +25653,12 @@
       </c>
       <c r="E383" t="inlineStr">
         <is>
-          <t>sec_grade_3_habib_ibn_zayd_al_ansari_1st_shift_girls</t>
+          <t>sec_grade_3_as_ad_ibn_zurarah_2nd_shift_mix</t>
         </is>
       </c>
       <c r="F383" t="inlineStr">
         <is>
-          <t>Grade 3 - HABIB IBN ZAYD AL-ANSARI (1ST SHIFT) - GIRLS</t>
+          <t>GRADE 3 - AS'AD IBN ZURARAH (2ND SHIFT) MIX</t>
         </is>
       </c>
       <c r="G383" t="inlineStr">
@@ -25673,27 +25673,27 @@
       </c>
       <c r="I383" t="inlineStr">
         <is>
-          <t>ODL - 1ST SHIFT</t>
+          <t>ODL - 2ND SHIFT</t>
         </is>
       </c>
       <c r="J383" t="inlineStr">
         <is>
-          <t>subj_makabansa</t>
+          <t>subj_arabic</t>
         </is>
       </c>
       <c r="K383" t="inlineStr">
         <is>
-          <t>Makabansa</t>
+          <t>Arabic</t>
         </is>
       </c>
       <c r="L383" t="inlineStr">
         <is>
-          <t>tchr_zara</t>
+          <t>tchr_faidh</t>
         </is>
       </c>
       <c r="M383" t="inlineStr">
         <is>
-          <t>Teacher Zara</t>
+          <t>Ustadh Faidh</t>
         </is>
       </c>
       <c r="N383" t="n">
@@ -25719,12 +25719,12 @@
       </c>
       <c r="E384" t="inlineStr">
         <is>
-          <t>sec_grade_3_salman_al_farsi_1st_shift_mix</t>
+          <t>sec_grade_3_habib_ibn_zayd_al_ansari_1st_shift_girls</t>
         </is>
       </c>
       <c r="F384" t="inlineStr">
         <is>
-          <t>GRADE 3 - SALMAN AL FARSI (1ST SHIFT) MIX</t>
+          <t>Grade 3 - HABIB IBN ZAYD AL-ANSARI (1ST SHIFT) - GIRLS</t>
         </is>
       </c>
       <c r="G384" t="inlineStr">
@@ -25744,22 +25744,22 @@
       </c>
       <c r="J384" t="inlineStr">
         <is>
-          <t>subj_english</t>
+          <t>subj_makabansa</t>
         </is>
       </c>
       <c r="K384" t="inlineStr">
         <is>
-          <t>English</t>
+          <t>Makabansa</t>
         </is>
       </c>
       <c r="L384" t="inlineStr">
         <is>
-          <t>tchr_jenny</t>
+          <t>tchr_zara</t>
         </is>
       </c>
       <c r="M384" t="inlineStr">
         <is>
-          <t>Teacher Jenny</t>
+          <t>Teacher Zara</t>
         </is>
       </c>
       <c r="N384" t="n">
@@ -25776,7 +25776,7 @@
         </is>
       </c>
       <c r="C385" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D385" t="inlineStr">
         <is>
@@ -25785,12 +25785,12 @@
       </c>
       <c r="E385" t="inlineStr">
         <is>
-          <t>sec_grade_3_zayd_ibn_haritha_2nd_shift_girls</t>
+          <t>sec_grade_3_salman_al_farsi_1st_shift_mix</t>
         </is>
       </c>
       <c r="F385" t="inlineStr">
         <is>
-          <t>GRADE 3 - ZAYD IBN HARITHA (2ND SHIFT) - GIRLS</t>
+          <t>GRADE 3 - SALMAN AL FARSI (1ST SHIFT) MIX</t>
         </is>
       </c>
       <c r="G385" t="inlineStr">
@@ -25805,27 +25805,27 @@
       </c>
       <c r="I385" t="inlineStr">
         <is>
-          <t>ODL - 2ND SHIFT</t>
+          <t>ODL - 1ST SHIFT</t>
         </is>
       </c>
       <c r="J385" t="inlineStr">
         <is>
-          <t>subj_filipino</t>
+          <t>subj_english</t>
         </is>
       </c>
       <c r="K385" t="inlineStr">
         <is>
-          <t>Filipino</t>
+          <t>English</t>
         </is>
       </c>
       <c r="L385" t="inlineStr">
         <is>
-          <t>tchr_normylah</t>
+          <t>tchr_jenny</t>
         </is>
       </c>
       <c r="M385" t="inlineStr">
         <is>
-          <t>Teacher Normylah</t>
+          <t>Teacher Jenny</t>
         </is>
       </c>
       <c r="N385" t="n">
@@ -25842,7 +25842,7 @@
         </is>
       </c>
       <c r="C386" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D386" t="inlineStr">
         <is>
@@ -25851,12 +25851,12 @@
       </c>
       <c r="E386" t="inlineStr">
         <is>
-          <t>sec_grade_3_ammar_ibn_yasir_1st_shift_boys</t>
+          <t>sec_grade_3_zayd_ibn_haritha_2nd_shift_girls</t>
         </is>
       </c>
       <c r="F386" t="inlineStr">
         <is>
-          <t>GRADE 3 -AMMAR IBN YASIR (1ST SHIFT) - BOYS</t>
+          <t>GRADE 3 - ZAYD IBN HARITHA (2ND SHIFT) - GIRLS</t>
         </is>
       </c>
       <c r="G386" t="inlineStr">
@@ -25871,27 +25871,27 @@
       </c>
       <c r="I386" t="inlineStr">
         <is>
-          <t>ODL - 1ST SHIFT</t>
+          <t>ODL - 2ND SHIFT</t>
         </is>
       </c>
       <c r="J386" t="inlineStr">
         <is>
-          <t>subj_english</t>
+          <t>subj_filipino</t>
         </is>
       </c>
       <c r="K386" t="inlineStr">
         <is>
-          <t>English</t>
+          <t>Filipino</t>
         </is>
       </c>
       <c r="L386" t="inlineStr">
         <is>
-          <t>tchr_marham</t>
+          <t>tchr_normylah</t>
         </is>
       </c>
       <c r="M386" t="inlineStr">
         <is>
-          <t>Teacher Marham</t>
+          <t>Teacher Normylah</t>
         </is>
       </c>
       <c r="N386" t="n">
@@ -25917,12 +25917,12 @@
       </c>
       <c r="E387" t="inlineStr">
         <is>
-          <t>sec_grade_4_abdur_rahman_ibn_awf_1st_shift</t>
+          <t>sec_grade_3_ammar_ibn_yasir_1st_shift_boys</t>
         </is>
       </c>
       <c r="F387" t="inlineStr">
         <is>
-          <t>GRADE 4 - ABDUR RAHMAN IBN AWF (1ST SHIFT)</t>
+          <t>GRADE 3 -AMMAR IBN YASIR (1ST SHIFT) - BOYS</t>
         </is>
       </c>
       <c r="G387" t="inlineStr">
@@ -25932,7 +25932,7 @@
       </c>
       <c r="H387" t="inlineStr">
         <is>
-          <t>Grade 4</t>
+          <t>Grade 3</t>
         </is>
       </c>
       <c r="I387" t="inlineStr">
@@ -25942,22 +25942,22 @@
       </c>
       <c r="J387" t="inlineStr">
         <is>
-          <t>subj_arabic</t>
+          <t>subj_english</t>
         </is>
       </c>
       <c r="K387" t="inlineStr">
         <is>
-          <t>Arabic</t>
+          <t>English</t>
         </is>
       </c>
       <c r="L387" t="inlineStr">
         <is>
-          <t>tchr_ali</t>
+          <t>tchr_marham</t>
         </is>
       </c>
       <c r="M387" t="inlineStr">
         <is>
-          <t>Ustadh Ali</t>
+          <t>Teacher Marham</t>
         </is>
       </c>
       <c r="N387" t="n">
@@ -25974,7 +25974,7 @@
         </is>
       </c>
       <c r="C388" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D388" t="inlineStr">
         <is>
@@ -25983,12 +25983,12 @@
       </c>
       <c r="E388" t="inlineStr">
         <is>
-          <t>sec_grade_4_az_zubair_ibn_al_awwaam_2nd_shift</t>
+          <t>sec_grade_4_abdur_rahman_ibn_awf_1st_shift</t>
         </is>
       </c>
       <c r="F388" t="inlineStr">
         <is>
-          <t>GRADE 4 - AZ ZUBAIR IBN AL AWWAAM (2ND SHIFT)</t>
+          <t>GRADE 4 - ABDUR RAHMAN IBN AWF (1ST SHIFT)</t>
         </is>
       </c>
       <c r="G388" t="inlineStr">
@@ -26003,27 +26003,27 @@
       </c>
       <c r="I388" t="inlineStr">
         <is>
-          <t>ODL - 2ND SHIFT</t>
+          <t>ODL - 1ST SHIFT</t>
         </is>
       </c>
       <c r="J388" t="inlineStr">
         <is>
-          <t>subj_araling_panlipunan</t>
+          <t>subj_arabic</t>
         </is>
       </c>
       <c r="K388" t="inlineStr">
         <is>
-          <t>Araling Panlipunan</t>
+          <t>Arabic</t>
         </is>
       </c>
       <c r="L388" t="inlineStr">
         <is>
-          <t>tchr_monisa</t>
+          <t>tchr_ali</t>
         </is>
       </c>
       <c r="M388" t="inlineStr">
         <is>
-          <t>Teacher Monisa</t>
+          <t>Ustadh Ali</t>
         </is>
       </c>
       <c r="N388" t="n">
@@ -26049,12 +26049,12 @@
       </c>
       <c r="E389" t="inlineStr">
         <is>
-          <t>sec_grade_4_ikrimah_ibn_abi_jahl_2nd_shift</t>
+          <t>sec_grade_4_az_zubair_ibn_al_awwaam_2nd_shift</t>
         </is>
       </c>
       <c r="F389" t="inlineStr">
         <is>
-          <t>GRADE 4 - IKRIMAH IBN ABI JAHL (2ND SHIFT)</t>
+          <t>GRADE 4 - AZ ZUBAIR IBN AL AWWAAM (2ND SHIFT)</t>
         </is>
       </c>
       <c r="G389" t="inlineStr">
@@ -26074,22 +26074,22 @@
       </c>
       <c r="J389" t="inlineStr">
         <is>
-          <t>subj_filipino</t>
+          <t>subj_araling_panlipunan</t>
         </is>
       </c>
       <c r="K389" t="inlineStr">
         <is>
-          <t>Filipino</t>
+          <t>Araling Panlipunan</t>
         </is>
       </c>
       <c r="L389" t="inlineStr">
         <is>
-          <t>tchr_norhydie</t>
+          <t>tchr_monisa</t>
         </is>
       </c>
       <c r="M389" t="inlineStr">
         <is>
-          <t>Teacher Norhydie</t>
+          <t>Teacher Monisa</t>
         </is>
       </c>
       <c r="N389" t="n">
@@ -26106,7 +26106,7 @@
         </is>
       </c>
       <c r="C390" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D390" t="inlineStr">
         <is>
@@ -26115,12 +26115,12 @@
       </c>
       <c r="E390" t="inlineStr">
         <is>
-          <t>sec_grade_4_usayd_ibn_hudhayr_1st_shift_mix</t>
+          <t>sec_grade_4_ikrimah_ibn_abi_jahl_2nd_shift</t>
         </is>
       </c>
       <c r="F390" t="inlineStr">
         <is>
-          <t>GRADE 4 - USAYD IBN HUDHAYR (1ST SHIFT) - MIX</t>
+          <t>GRADE 4 - IKRIMAH IBN ABI JAHL (2ND SHIFT)</t>
         </is>
       </c>
       <c r="G390" t="inlineStr">
@@ -26135,27 +26135,27 @@
       </c>
       <c r="I390" t="inlineStr">
         <is>
-          <t>ODL - 1ST SHIFT</t>
+          <t>ODL - 2ND SHIFT</t>
         </is>
       </c>
       <c r="J390" t="inlineStr">
         <is>
-          <t>subj_fil4</t>
+          <t>subj_filipino</t>
         </is>
       </c>
       <c r="K390" t="inlineStr">
         <is>
-          <t>Fil4</t>
+          <t>Filipino</t>
         </is>
       </c>
       <c r="L390" t="inlineStr">
         <is>
-          <t>tchr_zuhora</t>
+          <t>tchr_norhydie</t>
         </is>
       </c>
       <c r="M390" t="inlineStr">
         <is>
-          <t>Teacher Zuhora</t>
+          <t>Teacher Norhydie</t>
         </is>
       </c>
       <c r="N390" t="n">
@@ -26172,7 +26172,7 @@
         </is>
       </c>
       <c r="C391" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D391" t="inlineStr">
         <is>
@@ -26181,12 +26181,12 @@
       </c>
       <c r="E391" t="inlineStr">
         <is>
-          <t>sec_grade_4_hassan_ibn_thabit_2nd_shift_mix</t>
+          <t>sec_grade_4_usayd_ibn_hudhayr_1st_shift_mix</t>
         </is>
       </c>
       <c r="F391" t="inlineStr">
         <is>
-          <t>GRADE 4 -HASSAN IBN THABIT (2ND SHIFT) - MIX</t>
+          <t>GRADE 4 - USAYD IBN HUDHAYR (1ST SHIFT) - MIX</t>
         </is>
       </c>
       <c r="G391" t="inlineStr">
@@ -26201,27 +26201,27 @@
       </c>
       <c r="I391" t="inlineStr">
         <is>
-          <t>ODL - 2ND SHIFT</t>
+          <t>ODL - 1ST SHIFT</t>
         </is>
       </c>
       <c r="J391" t="inlineStr">
         <is>
-          <t>subj_science</t>
+          <t>subj_fil4</t>
         </is>
       </c>
       <c r="K391" t="inlineStr">
         <is>
-          <t>Science</t>
+          <t>Fil4</t>
         </is>
       </c>
       <c r="L391" t="inlineStr">
         <is>
-          <t>tchr_saimonah</t>
+          <t>tchr_zuhora</t>
         </is>
       </c>
       <c r="M391" t="inlineStr">
         <is>
-          <t>Teacher Saimonah</t>
+          <t>Teacher Zuhora</t>
         </is>
       </c>
       <c r="N391" t="n">
@@ -26247,12 +26247,12 @@
       </c>
       <c r="E392" t="inlineStr">
         <is>
-          <t>sec_grade_5_al_harith_bin_awf_2nd_shift</t>
+          <t>sec_grade_4_hassan_ibn_thabit_2nd_shift_mix</t>
         </is>
       </c>
       <c r="F392" t="inlineStr">
         <is>
-          <t>GRADE 5 - AL HARITH BIN AWF (2ND SHIFT)</t>
+          <t>GRADE 4 -HASSAN IBN THABIT (2ND SHIFT) - MIX</t>
         </is>
       </c>
       <c r="G392" t="inlineStr">
@@ -26262,7 +26262,7 @@
       </c>
       <c r="H392" t="inlineStr">
         <is>
-          <t>Grade 5</t>
+          <t>Grade 4</t>
         </is>
       </c>
       <c r="I392" t="inlineStr">
@@ -26272,22 +26272,22 @@
       </c>
       <c r="J392" t="inlineStr">
         <is>
-          <t>subj_math</t>
+          <t>subj_science</t>
         </is>
       </c>
       <c r="K392" t="inlineStr">
         <is>
-          <t>Math</t>
+          <t>Science</t>
         </is>
       </c>
       <c r="L392" t="inlineStr">
         <is>
-          <t>tchr_fhairudz</t>
+          <t>tchr_saimonah</t>
         </is>
       </c>
       <c r="M392" t="inlineStr">
         <is>
-          <t>Teacher Fhairudz</t>
+          <t>Teacher Saimonah</t>
         </is>
       </c>
       <c r="N392" t="n">
@@ -26304,7 +26304,7 @@
         </is>
       </c>
       <c r="C393" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D393" t="inlineStr">
         <is>
@@ -26313,12 +26313,12 @@
       </c>
       <c r="E393" t="inlineStr">
         <is>
-          <t>sec_grade_5_hamza_ibn_abdul_1st_shift</t>
+          <t>sec_grade_5_al_harith_bin_awf_2nd_shift</t>
         </is>
       </c>
       <c r="F393" t="inlineStr">
         <is>
-          <t>GRADE 5 - HAMZA IBN ABDUL (1ST SHIFT)</t>
+          <t>GRADE 5 - AL HARITH BIN AWF (2ND SHIFT)</t>
         </is>
       </c>
       <c r="G393" t="inlineStr">
@@ -26333,27 +26333,27 @@
       </c>
       <c r="I393" t="inlineStr">
         <is>
-          <t>ODL - 1ST SHIFT</t>
+          <t>ODL - 2ND SHIFT</t>
         </is>
       </c>
       <c r="J393" t="inlineStr">
         <is>
-          <t>subj_english</t>
+          <t>subj_math</t>
         </is>
       </c>
       <c r="K393" t="inlineStr">
         <is>
-          <t>English</t>
+          <t>Math</t>
         </is>
       </c>
       <c r="L393" t="inlineStr">
         <is>
-          <t>tchr_jessa</t>
+          <t>tchr_fhairudz</t>
         </is>
       </c>
       <c r="M393" t="inlineStr">
         <is>
-          <t>Teacher Jessa</t>
+          <t>Teacher Fhairudz</t>
         </is>
       </c>
       <c r="N393" t="n">
@@ -26370,7 +26370,7 @@
         </is>
       </c>
       <c r="C394" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D394" t="inlineStr">
         <is>
@@ -26379,12 +26379,12 @@
       </c>
       <c r="E394" t="inlineStr">
         <is>
-          <t>sec_grade_5_ja_far_ibn_abi_talib_2nd_shift_mix</t>
+          <t>sec_grade_5_hamza_ibn_abdul_1st_shift</t>
         </is>
       </c>
       <c r="F394" t="inlineStr">
         <is>
-          <t>GRADE 5 - JA'FAR IBN ABI TALIB (2ND SHIFT) - MIX</t>
+          <t>GRADE 5 - HAMZA IBN ABDUL (1ST SHIFT)</t>
         </is>
       </c>
       <c r="G394" t="inlineStr">
@@ -26399,27 +26399,27 @@
       </c>
       <c r="I394" t="inlineStr">
         <is>
-          <t>ODL - 2ND SHIFT</t>
+          <t>ODL - 1ST SHIFT</t>
         </is>
       </c>
       <c r="J394" t="inlineStr">
         <is>
-          <t>subj_qur_an</t>
+          <t>subj_english</t>
         </is>
       </c>
       <c r="K394" t="inlineStr">
         <is>
-          <t>Qur'an</t>
+          <t>English</t>
         </is>
       </c>
       <c r="L394" t="inlineStr">
         <is>
-          <t>tchr_obaydah</t>
+          <t>tchr_jessa</t>
         </is>
       </c>
       <c r="M394" t="inlineStr">
         <is>
-          <t>Ustadh Obaydah</t>
+          <t>Teacher Jessa</t>
         </is>
       </c>
       <c r="N394" t="n">
@@ -26436,7 +26436,7 @@
         </is>
       </c>
       <c r="C395" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D395" t="inlineStr">
         <is>
@@ -26445,12 +26445,12 @@
       </c>
       <c r="E395" t="inlineStr">
         <is>
-          <t>sec_grade_5_muhammad_ibn_maslamah_1st_shift</t>
+          <t>sec_grade_5_ja_far_ibn_abi_talib_2nd_shift_mix</t>
         </is>
       </c>
       <c r="F395" t="inlineStr">
         <is>
-          <t>GRADE 5 - MUHAMMAD IBN MASLAMAH (1ST SHIFT)</t>
+          <t>GRADE 5 - JA'FAR IBN ABI TALIB (2ND SHIFT) - MIX</t>
         </is>
       </c>
       <c r="G395" t="inlineStr">
@@ -26465,27 +26465,27 @@
       </c>
       <c r="I395" t="inlineStr">
         <is>
-          <t>ODL - 1ST SHIFT</t>
+          <t>ODL - 2ND SHIFT</t>
         </is>
       </c>
       <c r="J395" t="inlineStr">
         <is>
-          <t>subj_mapeh</t>
+          <t>subj_qur_an</t>
         </is>
       </c>
       <c r="K395" t="inlineStr">
         <is>
-          <t>MAPEH</t>
+          <t>Qur'an</t>
         </is>
       </c>
       <c r="L395" t="inlineStr">
         <is>
-          <t>tchr_keychell</t>
+          <t>tchr_obaydah</t>
         </is>
       </c>
       <c r="M395" t="inlineStr">
         <is>
-          <t>Teacher Keychell</t>
+          <t>Ustadh Obaydah</t>
         </is>
       </c>
       <c r="N395" t="n">
@@ -26502,7 +26502,7 @@
         </is>
       </c>
       <c r="C396" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D396" t="inlineStr">
         <is>
@@ -26511,12 +26511,12 @@
       </c>
       <c r="E396" t="inlineStr">
         <is>
-          <t>sec_grade_5_mus_ab_ibn_abdul_mutalib_2nd_shift</t>
+          <t>sec_grade_5_muhammad_ibn_maslamah_1st_shift</t>
         </is>
       </c>
       <c r="F396" t="inlineStr">
         <is>
-          <t>GRADE 5 - MUS'AB IBN ABDUL MUTALIB (2ND SHIFT)</t>
+          <t>GRADE 5 - MUHAMMAD IBN MASLAMAH (1ST SHIFT)</t>
         </is>
       </c>
       <c r="G396" t="inlineStr">
@@ -26531,27 +26531,27 @@
       </c>
       <c r="I396" t="inlineStr">
         <is>
-          <t>ODL - 2ND SHIFT</t>
+          <t>ODL - 1ST SHIFT</t>
         </is>
       </c>
       <c r="J396" t="inlineStr">
         <is>
-          <t>subj_arabic</t>
+          <t>subj_mapeh</t>
         </is>
       </c>
       <c r="K396" t="inlineStr">
         <is>
-          <t>Arabic</t>
+          <t>MAPEH</t>
         </is>
       </c>
       <c r="L396" t="inlineStr">
         <is>
-          <t>tchr_ersahad</t>
+          <t>tchr_keychell</t>
         </is>
       </c>
       <c r="M396" t="inlineStr">
         <is>
-          <t>Ustadh Ersahad</t>
+          <t>Teacher Keychell</t>
         </is>
       </c>
       <c r="N396" t="n">
@@ -26568,7 +26568,7 @@
         </is>
       </c>
       <c r="C397" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D397" t="inlineStr">
         <is>
@@ -26577,12 +26577,12 @@
       </c>
       <c r="E397" t="inlineStr">
         <is>
-          <t>sec_grade_6_abdullah_ibn_salaam_1st_shift</t>
+          <t>sec_grade_5_mus_ab_ibn_abdul_mutalib_2nd_shift</t>
         </is>
       </c>
       <c r="F397" t="inlineStr">
         <is>
-          <t>GRADE 6 - ABDULLAH IBN SALAAM (1ST SHIFT)</t>
+          <t>GRADE 5 - MUS'AB IBN ABDUL MUTALIB (2ND SHIFT)</t>
         </is>
       </c>
       <c r="G397" t="inlineStr">
@@ -26592,32 +26592,32 @@
       </c>
       <c r="H397" t="inlineStr">
         <is>
-          <t>Grade 6</t>
+          <t>Grade 5</t>
         </is>
       </c>
       <c r="I397" t="inlineStr">
         <is>
-          <t>ODL - 1ST SHIFT</t>
+          <t>ODL - 2ND SHIFT</t>
         </is>
       </c>
       <c r="J397" t="inlineStr">
         <is>
-          <t>subj_shaf</t>
+          <t>subj_arabic</t>
         </is>
       </c>
       <c r="K397" t="inlineStr">
         <is>
-          <t>SHAF</t>
+          <t>Arabic</t>
         </is>
       </c>
       <c r="L397" t="inlineStr">
         <is>
-          <t>tchr_abdiraheem</t>
+          <t>tchr_ersahad</t>
         </is>
       </c>
       <c r="M397" t="inlineStr">
         <is>
-          <t>Ustadh Abdiraheem</t>
+          <t>Ustadh Ersahad</t>
         </is>
       </c>
       <c r="N397" t="n">
@@ -26634,7 +26634,7 @@
         </is>
       </c>
       <c r="C398" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D398" t="inlineStr">
         <is>
@@ -26643,12 +26643,12 @@
       </c>
       <c r="E398" t="inlineStr">
         <is>
-          <t>sec_grade_6_khaleed_ibn_waleed_2nd_shift</t>
+          <t>sec_grade_6_abdullah_ibn_salaam_1st_shift</t>
         </is>
       </c>
       <c r="F398" t="inlineStr">
         <is>
-          <t>GRADE 6 - KHALEED IBN WALEED (2ND SHIFT)</t>
+          <t>GRADE 6 - ABDULLAH IBN SALAAM (1ST SHIFT)</t>
         </is>
       </c>
       <c r="G398" t="inlineStr">
@@ -26663,27 +26663,27 @@
       </c>
       <c r="I398" t="inlineStr">
         <is>
-          <t>ODL - 2ND SHIFT</t>
+          <t>ODL - 1ST SHIFT</t>
         </is>
       </c>
       <c r="J398" t="inlineStr">
         <is>
-          <t>subj_tle</t>
+          <t>subj_shaf</t>
         </is>
       </c>
       <c r="K398" t="inlineStr">
         <is>
-          <t>TLE</t>
+          <t>SHAF</t>
         </is>
       </c>
       <c r="L398" t="inlineStr">
         <is>
-          <t>tchr_arvin</t>
+          <t>tchr_abdiraheem</t>
         </is>
       </c>
       <c r="M398" t="inlineStr">
         <is>
-          <t>Teacher Arvin</t>
+          <t>Ustadh Abdiraheem</t>
         </is>
       </c>
       <c r="N398" t="n">
@@ -26700,7 +26700,7 @@
         </is>
       </c>
       <c r="C399" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D399" t="inlineStr">
         <is>
@@ -26709,47 +26709,47 @@
       </c>
       <c r="E399" t="inlineStr">
         <is>
-          <t>sec_grade_7_abu_sufyan_ibn_al_harith_1st_shift_boys</t>
+          <t>sec_grade_6_khaleed_ibn_waleed_2nd_shift</t>
         </is>
       </c>
       <c r="F399" t="inlineStr">
         <is>
-          <t>GRADE 7 - ABU SUFYAN IBN AL-HARITH (1ST SHIFT) BOYS</t>
+          <t>GRADE 6 - KHALEED IBN WALEED (2ND SHIFT)</t>
         </is>
       </c>
       <c r="G399" t="inlineStr">
         <is>
-          <t>Junior High School</t>
+          <t>Elementary</t>
         </is>
       </c>
       <c r="H399" t="inlineStr">
         <is>
-          <t>Grade 7</t>
+          <t>Grade 6</t>
         </is>
       </c>
       <c r="I399" t="inlineStr">
         <is>
-          <t>ODL - 1ST SHIFT</t>
+          <t>ODL - 2ND SHIFT</t>
         </is>
       </c>
       <c r="J399" t="inlineStr">
         <is>
-          <t>subj_shaf</t>
+          <t>subj_tle</t>
         </is>
       </c>
       <c r="K399" t="inlineStr">
         <is>
-          <t>SHAF</t>
+          <t>TLE</t>
         </is>
       </c>
       <c r="L399" t="inlineStr">
         <is>
-          <t>tchr_samsuddin</t>
+          <t>tchr_arvin</t>
         </is>
       </c>
       <c r="M399" t="inlineStr">
         <is>
-          <t>Alim Samsuddin</t>
+          <t>Teacher Arvin</t>
         </is>
       </c>
       <c r="N399" t="n">
@@ -26766,21 +26766,21 @@
         </is>
       </c>
       <c r="C400" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D400" t="inlineStr">
         <is>
-          <t>03:10 PM – 05:20 PM</t>
+          <t>03:10 PM – 04:10 PM</t>
         </is>
       </c>
       <c r="E400" t="inlineStr">
         <is>
-          <t>sec_grade_7_anas_ibn_malik_2nd_shift_mix</t>
+          <t>sec_grade_7_abu_sufyan_ibn_al_harith_1st_shift_boys</t>
         </is>
       </c>
       <c r="F400" t="inlineStr">
         <is>
-          <t>GRADE 7 - ANAS IBN MALIK (2ND SHIFT) - MIX</t>
+          <t>GRADE 7 - ABU SUFYAN IBN AL-HARITH (1ST SHIFT) BOYS</t>
         </is>
       </c>
       <c r="G400" t="inlineStr">
@@ -26795,31 +26795,31 @@
       </c>
       <c r="I400" t="inlineStr">
         <is>
-          <t>ODL - 2ND SHIFT</t>
+          <t>ODL - 1ST SHIFT</t>
         </is>
       </c>
       <c r="J400" t="inlineStr">
         <is>
-          <t>subj_math</t>
+          <t>subj_shaf</t>
         </is>
       </c>
       <c r="K400" t="inlineStr">
         <is>
-          <t>Math</t>
+          <t>SHAF</t>
         </is>
       </c>
       <c r="L400" t="inlineStr">
         <is>
-          <t>tchr_ethel</t>
+          <t>tchr_samsuddin</t>
         </is>
       </c>
       <c r="M400" t="inlineStr">
         <is>
-          <t>Teacher Ethel</t>
+          <t>Alim Samsuddin</t>
         </is>
       </c>
       <c r="N400" t="n">
-        <v>120</v>
+        <v>60</v>
       </c>
     </row>
     <row r="401">
@@ -26832,21 +26832,21 @@
         </is>
       </c>
       <c r="C401" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D401" t="inlineStr">
         <is>
-          <t>03:10 PM – 04:10 PM</t>
+          <t>03:10 PM – 05:20 PM</t>
         </is>
       </c>
       <c r="E401" t="inlineStr">
         <is>
-          <t>sec_grade_7_usama_ibn_zayd_1st_shift_girls</t>
+          <t>sec_grade_7_anas_ibn_malik_2nd_shift_mix</t>
         </is>
       </c>
       <c r="F401" t="inlineStr">
         <is>
-          <t>GRADE 7 - USAMA IBN ZAYD (1ST SHIFT) GIRLS</t>
+          <t>GRADE 7 - ANAS IBN MALIK (2ND SHIFT) - MIX</t>
         </is>
       </c>
       <c r="G401" t="inlineStr">
@@ -26861,31 +26861,31 @@
       </c>
       <c r="I401" t="inlineStr">
         <is>
-          <t>ODL - 1ST SHIFT</t>
+          <t>ODL - 2ND SHIFT</t>
         </is>
       </c>
       <c r="J401" t="inlineStr">
         <is>
-          <t>subj_english</t>
+          <t>subj_math</t>
         </is>
       </c>
       <c r="K401" t="inlineStr">
         <is>
-          <t>English</t>
+          <t>Math</t>
         </is>
       </c>
       <c r="L401" t="inlineStr">
         <is>
-          <t>tchr_jairah</t>
+          <t>tchr_ethel</t>
         </is>
       </c>
       <c r="M401" t="inlineStr">
         <is>
-          <t>Teacher Jairah</t>
+          <t>Teacher Ethel</t>
         </is>
       </c>
       <c r="N401" t="n">
-        <v>60</v>
+        <v>120</v>
       </c>
     </row>
     <row r="402">
@@ -26898,7 +26898,7 @@
         </is>
       </c>
       <c r="C402" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D402" t="inlineStr">
         <is>
@@ -26907,12 +26907,12 @@
       </c>
       <c r="E402" t="inlineStr">
         <is>
-          <t>sec_grade_8_mu_adh_ibn_jabal_2nd_shift_boys</t>
+          <t>sec_grade_7_usama_ibn_zayd_1st_shift_girls</t>
         </is>
       </c>
       <c r="F402" t="inlineStr">
         <is>
-          <t>GRADE 8 - MU'ADH IBN JABAL (2ND SHIFT) - BOYS</t>
+          <t>GRADE 7 - USAMA IBN ZAYD (1ST SHIFT) GIRLS</t>
         </is>
       </c>
       <c r="G402" t="inlineStr">
@@ -26922,32 +26922,32 @@
       </c>
       <c r="H402" t="inlineStr">
         <is>
-          <t>Grade 8</t>
+          <t>Grade 7</t>
         </is>
       </c>
       <c r="I402" t="inlineStr">
         <is>
-          <t>ODL - 2ND SHIFT</t>
+          <t>ODL - 1ST SHIFT</t>
         </is>
       </c>
       <c r="J402" t="inlineStr">
         <is>
-          <t>subj_qur_an</t>
+          <t>subj_english</t>
         </is>
       </c>
       <c r="K402" t="inlineStr">
         <is>
-          <t>Qur'an</t>
+          <t>English</t>
         </is>
       </c>
       <c r="L402" t="inlineStr">
         <is>
-          <t>tchr_jaisam</t>
+          <t>tchr_jairah</t>
         </is>
       </c>
       <c r="M402" t="inlineStr">
         <is>
-          <t>Ustadh Jaisam</t>
+          <t>Teacher Jairah</t>
         </is>
       </c>
       <c r="N402" t="n">
@@ -26973,12 +26973,12 @@
       </c>
       <c r="E403" t="inlineStr">
         <is>
-          <t>sec_grade_8_nuaym_ibn_mas_ud_2nd_shift_mix</t>
+          <t>sec_grade_8_mu_adh_ibn_jabal_2nd_shift_boys</t>
         </is>
       </c>
       <c r="F403" t="inlineStr">
         <is>
-          <t>GRADE 8 - NUAYM IBN MAS'UD (2ND SHIFT) MIX</t>
+          <t>GRADE 8 - MU'ADH IBN JABAL (2ND SHIFT) - BOYS</t>
         </is>
       </c>
       <c r="G403" t="inlineStr">
@@ -26998,22 +26998,22 @@
       </c>
       <c r="J403" t="inlineStr">
         <is>
-          <t>subj_values_ed</t>
+          <t>subj_qur_an</t>
         </is>
       </c>
       <c r="K403" t="inlineStr">
         <is>
-          <t>Values Ed</t>
+          <t>Qur'an</t>
         </is>
       </c>
       <c r="L403" t="inlineStr">
         <is>
-          <t>tchr_wardah</t>
+          <t>tchr_jaisam</t>
         </is>
       </c>
       <c r="M403" t="inlineStr">
         <is>
-          <t>Teacher Wardah</t>
+          <t>Ustadh Jaisam</t>
         </is>
       </c>
       <c r="N403" t="n">
@@ -27030,7 +27030,7 @@
         </is>
       </c>
       <c r="C404" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D404" t="inlineStr">
         <is>
@@ -27039,12 +27039,12 @@
       </c>
       <c r="E404" t="inlineStr">
         <is>
-          <t>sec_grade_8_sa_ad_ibn_mua_dh_1st_shift_girls</t>
+          <t>sec_grade_8_nuaym_ibn_mas_ud_2nd_shift_mix</t>
         </is>
       </c>
       <c r="F404" t="inlineStr">
         <is>
-          <t>GRADE 8 - SA'AD IBN MUA'DH (1ST SHIFT) - GIRLS</t>
+          <t>GRADE 8 - NUAYM IBN MAS'UD (2ND SHIFT) MIX</t>
         </is>
       </c>
       <c r="G404" t="inlineStr">
@@ -27059,27 +27059,27 @@
       </c>
       <c r="I404" t="inlineStr">
         <is>
-          <t>ODL - 1ST SHIFT</t>
+          <t>ODL - 2ND SHIFT</t>
         </is>
       </c>
       <c r="J404" t="inlineStr">
         <is>
-          <t>subj_science</t>
+          <t>subj_values_ed</t>
         </is>
       </c>
       <c r="K404" t="inlineStr">
         <is>
-          <t>Science</t>
+          <t>Values Ed</t>
         </is>
       </c>
       <c r="L404" t="inlineStr">
         <is>
-          <t>tchr_radzmia</t>
+          <t>tchr_wardah</t>
         </is>
       </c>
       <c r="M404" t="inlineStr">
         <is>
-          <t>Teacher Radzmia</t>
+          <t>Teacher Wardah</t>
         </is>
       </c>
       <c r="N404" t="n">
@@ -27096,21 +27096,21 @@
         </is>
       </c>
       <c r="C405" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D405" t="inlineStr">
         <is>
-          <t>03:10 PM – 05:20 PM</t>
+          <t>03:10 PM – 04:10 PM</t>
         </is>
       </c>
       <c r="E405" t="inlineStr">
         <is>
-          <t>sec_grade_9_abu_dharr_al_ghifarri_2nd_shift_boys</t>
+          <t>sec_grade_8_sa_ad_ibn_mua_dh_1st_shift_girls</t>
         </is>
       </c>
       <c r="F405" t="inlineStr">
         <is>
-          <t>GRADE 9 - ABU DHARR AL GHIFARRI (2ND SHIFT) BOYS</t>
+          <t>GRADE 8 - SA'AD IBN MUA'DH (1ST SHIFT) - GIRLS</t>
         </is>
       </c>
       <c r="G405" t="inlineStr">
@@ -27120,36 +27120,36 @@
       </c>
       <c r="H405" t="inlineStr">
         <is>
-          <t>Grade 9</t>
+          <t>Grade 8</t>
         </is>
       </c>
       <c r="I405" t="inlineStr">
         <is>
-          <t>ODL - 2ND SHIFT</t>
+          <t>ODL - 1ST SHIFT</t>
         </is>
       </c>
       <c r="J405" t="inlineStr">
         <is>
-          <t>subj_math</t>
+          <t>subj_science</t>
         </is>
       </c>
       <c r="K405" t="inlineStr">
         <is>
-          <t>Math</t>
+          <t>Science</t>
         </is>
       </c>
       <c r="L405" t="inlineStr">
         <is>
-          <t>tchr_jhelyn</t>
+          <t>tchr_radzmia</t>
         </is>
       </c>
       <c r="M405" t="inlineStr">
         <is>
-          <t>Teacher Jhelyn</t>
+          <t>Teacher Radzmia</t>
         </is>
       </c>
       <c r="N405" t="n">
-        <v>120</v>
+        <v>60</v>
       </c>
     </row>
     <row r="406">
@@ -27162,21 +27162,21 @@
         </is>
       </c>
       <c r="C406" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D406" t="inlineStr">
         <is>
-          <t>03:10 PM – 04:10 PM</t>
+          <t>03:10 PM – 05:20 PM</t>
         </is>
       </c>
       <c r="E406" t="inlineStr">
         <is>
-          <t>sec_grade_9_abu_hurayrah_1st_shift_girls</t>
+          <t>sec_grade_9_abu_dharr_al_ghifarri_2nd_shift_boys</t>
         </is>
       </c>
       <c r="F406" t="inlineStr">
         <is>
-          <t>GRADE 9 - ABU HURAYRAH (1ST SHIFT) GIRLS</t>
+          <t>GRADE 9 - ABU DHARR AL GHIFARRI (2ND SHIFT) BOYS</t>
         </is>
       </c>
       <c r="G406" t="inlineStr">
@@ -27191,31 +27191,31 @@
       </c>
       <c r="I406" t="inlineStr">
         <is>
-          <t>ODL - 1ST SHIFT</t>
+          <t>ODL - 2ND SHIFT</t>
         </is>
       </c>
       <c r="J406" t="inlineStr">
         <is>
-          <t>subj_qur_an</t>
+          <t>subj_math</t>
         </is>
       </c>
       <c r="K406" t="inlineStr">
         <is>
-          <t>Qur'an</t>
+          <t>Math</t>
         </is>
       </c>
       <c r="L406" t="inlineStr">
         <is>
-          <t>tchr_abdulwahab</t>
+          <t>tchr_jhelyn</t>
         </is>
       </c>
       <c r="M406" t="inlineStr">
         <is>
-          <t>Alim Abdulwahab</t>
+          <t>Teacher Jhelyn</t>
         </is>
       </c>
       <c r="N406" t="n">
-        <v>60</v>
+        <v>120</v>
       </c>
     </row>
     <row r="407">
@@ -27228,7 +27228,7 @@
         </is>
       </c>
       <c r="C407" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D407" t="inlineStr">
         <is>
@@ -27237,12 +27237,12 @@
       </c>
       <c r="E407" t="inlineStr">
         <is>
-          <t>sec_grade_9_abu_jandal_ibn_suhayl_2nd_shift_girls</t>
+          <t>sec_grade_9_abu_hurayrah_1st_shift_girls</t>
         </is>
       </c>
       <c r="F407" t="inlineStr">
         <is>
-          <t>GRADE 9 - ABU JANDAL IBN SUHAYL (2ND SHIFT) GIRLS</t>
+          <t>GRADE 9 - ABU HURAYRAH (1ST SHIFT) GIRLS</t>
         </is>
       </c>
       <c r="G407" t="inlineStr">
@@ -27257,27 +27257,27 @@
       </c>
       <c r="I407" t="inlineStr">
         <is>
-          <t>ODL - 2ND SHIFT</t>
+          <t>ODL - 1ST SHIFT</t>
         </is>
       </c>
       <c r="J407" t="inlineStr">
         <is>
-          <t>subj_english</t>
+          <t>subj_qur_an</t>
         </is>
       </c>
       <c r="K407" t="inlineStr">
         <is>
-          <t>English</t>
+          <t>Qur'an</t>
         </is>
       </c>
       <c r="L407" t="inlineStr">
         <is>
-          <t>tchr_norhaima</t>
+          <t>tchr_abdulwahab</t>
         </is>
       </c>
       <c r="M407" t="inlineStr">
         <is>
-          <t>Teacher Norhaima</t>
+          <t>Alim Abdulwahab</t>
         </is>
       </c>
       <c r="N407" t="n">
@@ -27294,31 +27294,31 @@
         </is>
       </c>
       <c r="C408" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D408" t="inlineStr">
         <is>
-          <t>04:20 PM – 05:20 PM</t>
+          <t>03:10 PM – 04:10 PM</t>
         </is>
       </c>
       <c r="E408" t="inlineStr">
         <is>
-          <t>sec_grade_1_sa_ad_ibn_abi_waqqaas_2nd_shift</t>
+          <t>sec_grade_9_abu_jandal_ibn_suhayl_2nd_shift_girls</t>
         </is>
       </c>
       <c r="F408" t="inlineStr">
         <is>
-          <t>GRADE 1 - SA'AD IBN ABI WAQQAAS (2ND SHIFT)</t>
+          <t>GRADE 9 - ABU JANDAL IBN SUHAYL (2ND SHIFT) GIRLS</t>
         </is>
       </c>
       <c r="G408" t="inlineStr">
         <is>
-          <t>Elementary</t>
+          <t>Junior High School</t>
         </is>
       </c>
       <c r="H408" t="inlineStr">
         <is>
-          <t>Grade 1</t>
+          <t>Grade 9</t>
         </is>
       </c>
       <c r="I408" t="inlineStr">
@@ -27328,22 +27328,22 @@
       </c>
       <c r="J408" t="inlineStr">
         <is>
-          <t>subj_language</t>
+          <t>subj_english</t>
         </is>
       </c>
       <c r="K408" t="inlineStr">
         <is>
-          <t>Language</t>
+          <t>English</t>
         </is>
       </c>
       <c r="L408" t="inlineStr">
         <is>
-          <t>tchr_sahdia</t>
+          <t>tchr_norhaima</t>
         </is>
       </c>
       <c r="M408" t="inlineStr">
         <is>
-          <t>Teacher Sahdia</t>
+          <t>Teacher Norhaima</t>
         </is>
       </c>
       <c r="N408" t="n">
@@ -27369,12 +27369,12 @@
       </c>
       <c r="E409" t="inlineStr">
         <is>
-          <t>sec_grade_1_suhayb_ar_rumi_2nd_shift</t>
+          <t>sec_grade_1_sa_ad_ibn_abi_waqqaas_2nd_shift</t>
         </is>
       </c>
       <c r="F409" t="inlineStr">
         <is>
-          <t>GRADE 1 - SUHAYB AR-RUMI (2ND SHIFT)</t>
+          <t>GRADE 1 - SA'AD IBN ABI WAQQAAS (2ND SHIFT)</t>
         </is>
       </c>
       <c r="G409" t="inlineStr">
@@ -27394,22 +27394,22 @@
       </c>
       <c r="J409" t="inlineStr">
         <is>
-          <t>subj_arabic</t>
+          <t>subj_language</t>
         </is>
       </c>
       <c r="K409" t="inlineStr">
         <is>
-          <t>Arabic</t>
+          <t>Language</t>
         </is>
       </c>
       <c r="L409" t="inlineStr">
         <is>
-          <t>tchr_hainur</t>
+          <t>tchr_sahdia</t>
         </is>
       </c>
       <c r="M409" t="inlineStr">
         <is>
-          <t>Ustadha Hainur</t>
+          <t>Teacher Sahdia</t>
         </is>
       </c>
       <c r="N409" t="n">
@@ -27435,22 +27435,22 @@
       </c>
       <c r="E410" t="inlineStr">
         <is>
-          <t>sec_grade_10_abu_ayyub_al_ansari_2nd_shift_boys</t>
+          <t>sec_grade_1_suhayb_ar_rumi_2nd_shift</t>
         </is>
       </c>
       <c r="F410" t="inlineStr">
         <is>
-          <t>GRADE 10 - ABU AYYUB AL-ANSARI (2ND SHIFT) BOYS</t>
+          <t>GRADE 1 - SUHAYB AR-RUMI (2ND SHIFT)</t>
         </is>
       </c>
       <c r="G410" t="inlineStr">
         <is>
-          <t>Junior High School</t>
+          <t>Elementary</t>
         </is>
       </c>
       <c r="H410" t="inlineStr">
         <is>
-          <t>Grade 10</t>
+          <t>Grade 1</t>
         </is>
       </c>
       <c r="I410" t="inlineStr">
@@ -27460,22 +27460,22 @@
       </c>
       <c r="J410" t="inlineStr">
         <is>
-          <t>subj_tle</t>
+          <t>subj_arabic</t>
         </is>
       </c>
       <c r="K410" t="inlineStr">
         <is>
-          <t>TLE</t>
+          <t>Arabic</t>
         </is>
       </c>
       <c r="L410" t="inlineStr">
         <is>
-          <t>tchr_angeleni</t>
+          <t>tchr_hainur</t>
         </is>
       </c>
       <c r="M410" t="inlineStr">
         <is>
-          <t>Teacher Angeleni</t>
+          <t>Ustadha Hainur</t>
         </is>
       </c>
       <c r="N410" t="n">
@@ -27492,7 +27492,7 @@
         </is>
       </c>
       <c r="C411" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D411" t="inlineStr">
         <is>
@@ -27501,47 +27501,47 @@
       </c>
       <c r="E411" t="inlineStr">
         <is>
-          <t>sec_grade_11_1st_shift_girls</t>
+          <t>sec_grade_10_abu_ayyub_al_ansari_2nd_shift_boys</t>
         </is>
       </c>
       <c r="F411" t="inlineStr">
         <is>
-          <t>GRADE 11 (1ST SHIFT GIRLS)</t>
+          <t>GRADE 10 - ABU AYYUB AL-ANSARI (2ND SHIFT) BOYS</t>
         </is>
       </c>
       <c r="G411" t="inlineStr">
         <is>
-          <t>Senior High School</t>
+          <t>Junior High School</t>
         </is>
       </c>
       <c r="H411" t="inlineStr">
         <is>
-          <t>Grade 11</t>
+          <t>Grade 10</t>
         </is>
       </c>
       <c r="I411" t="inlineStr">
         <is>
-          <t>ODL - 1ST SHIFT</t>
+          <t>ODL - 2ND SHIFT</t>
         </is>
       </c>
       <c r="J411" t="inlineStr">
         <is>
-          <t>subj_shaf</t>
+          <t>subj_tle</t>
         </is>
       </c>
       <c r="K411" t="inlineStr">
         <is>
-          <t>SHAF</t>
+          <t>TLE</t>
         </is>
       </c>
       <c r="L411" t="inlineStr">
         <is>
-          <t>tchr_samsuddin</t>
+          <t>tchr_angeleni</t>
         </is>
       </c>
       <c r="M411" t="inlineStr">
         <is>
-          <t>Alim Samsuddin</t>
+          <t>Teacher Angeleni</t>
         </is>
       </c>
       <c r="N411" t="n">
@@ -27558,7 +27558,7 @@
         </is>
       </c>
       <c r="C412" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D412" t="inlineStr">
         <is>
@@ -27567,12 +27567,12 @@
       </c>
       <c r="E412" t="inlineStr">
         <is>
-          <t>sec_grade_11_2nd_shift_boys</t>
+          <t>sec_grade_11_1st_shift_girls</t>
         </is>
       </c>
       <c r="F412" t="inlineStr">
         <is>
-          <t>GRADE 11 (2ND SHIFT BOYS)</t>
+          <t>GRADE 11 (1ST SHIFT GIRLS)</t>
         </is>
       </c>
       <c r="G412" t="inlineStr">
@@ -27587,27 +27587,27 @@
       </c>
       <c r="I412" t="inlineStr">
         <is>
-          <t>ODL - 2ND SHIFT</t>
+          <t>ODL - 1ST SHIFT</t>
         </is>
       </c>
       <c r="J412" t="inlineStr">
         <is>
-          <t>subj_ec</t>
+          <t>subj_shaf</t>
         </is>
       </c>
       <c r="K412" t="inlineStr">
         <is>
-          <t>EC</t>
+          <t>SHAF</t>
         </is>
       </c>
       <c r="L412" t="inlineStr">
         <is>
-          <t>tchr_nadzra</t>
+          <t>tchr_samsuddin</t>
         </is>
       </c>
       <c r="M412" t="inlineStr">
         <is>
-          <t>Teacher Nadzra</t>
+          <t>Alim Samsuddin</t>
         </is>
       </c>
       <c r="N412" t="n">
@@ -27624,7 +27624,7 @@
         </is>
       </c>
       <c r="C413" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D413" t="inlineStr">
         <is>
@@ -27633,12 +27633,12 @@
       </c>
       <c r="E413" t="inlineStr">
         <is>
-          <t>sec_grade_12_abu_musa_al_ashari</t>
+          <t>sec_grade_11_2nd_shift_boys</t>
         </is>
       </c>
       <c r="F413" t="inlineStr">
         <is>
-          <t>GRADE 12 - ABU MUSA AL-ASHARI</t>
+          <t>GRADE 11 (2ND SHIFT BOYS)</t>
         </is>
       </c>
       <c r="G413" t="inlineStr">
@@ -27648,32 +27648,32 @@
       </c>
       <c r="H413" t="inlineStr">
         <is>
-          <t>Grade 12</t>
+          <t>Grade 11</t>
         </is>
       </c>
       <c r="I413" t="inlineStr">
         <is>
-          <t>ODL - 1ST SHIFT</t>
+          <t>ODL - 2ND SHIFT</t>
         </is>
       </c>
       <c r="J413" t="inlineStr">
         <is>
-          <t>subj_prac_res_2</t>
+          <t>subj_ec</t>
         </is>
       </c>
       <c r="K413" t="inlineStr">
         <is>
-          <t>Prac. Res. 2</t>
+          <t>EC</t>
         </is>
       </c>
       <c r="L413" t="inlineStr">
         <is>
-          <t>tchr_aniah</t>
+          <t>tchr_nadzra</t>
         </is>
       </c>
       <c r="M413" t="inlineStr">
         <is>
-          <t>Teacher Aniah</t>
+          <t>Teacher Nadzra</t>
         </is>
       </c>
       <c r="N413" t="n">

--- a/Term_Examination_Schedule_S.Y._2026-2027_Optimized.xlsx
+++ b/Term_Examination_Schedule_S.Y._2026-2027_Optimized.xlsx
@@ -2395,7 +2395,7 @@
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>Teacher Keychell</t>
+          <t>Teacher Keychelle</t>
         </is>
       </c>
       <c r="N30" t="n">
@@ -9325,7 +9325,7 @@
       </c>
       <c r="M135" t="inlineStr">
         <is>
-          <t>Teacher Keychell</t>
+          <t>Teacher Keychelle</t>
         </is>
       </c>
       <c r="N135" t="n">
@@ -13615,7 +13615,7 @@
       </c>
       <c r="M200" t="inlineStr">
         <is>
-          <t>Teacher Keychell</t>
+          <t>Teacher Keychelle</t>
         </is>
       </c>
       <c r="N200" t="n">
@@ -16783,7 +16783,7 @@
       </c>
       <c r="M248" t="inlineStr">
         <is>
-          <t>Teacher Keychell</t>
+          <t>Teacher Keychelle</t>
         </is>
       </c>
       <c r="N248" t="n">
@@ -26551,7 +26551,7 @@
       </c>
       <c r="M396" t="inlineStr">
         <is>
-          <t>Teacher Keychell</t>
+          <t>Teacher Keychelle</t>
         </is>
       </c>
       <c r="N396" t="n">
@@ -30643,7 +30643,7 @@
       </c>
       <c r="M458" t="inlineStr">
         <is>
-          <t>Teacher Keychell</t>
+          <t>Teacher Keychelle</t>
         </is>
       </c>
       <c r="N458" t="n">

--- a/Term_Examination_Schedule_S.Y._2026-2027_Optimized.xlsx
+++ b/Term_Examination_Schedule_S.Y._2026-2027_Optimized.xlsx
@@ -22419,12 +22419,12 @@
       </c>
       <c r="E334" t="inlineStr">
         <is>
-          <t>sec_grade_12_abu_musa_al_ashari</t>
+          <t>sec_grade_11_1st_shift_girls</t>
         </is>
       </c>
       <c r="F334" t="inlineStr">
         <is>
-          <t>GRADE 12 - ABU MUSA AL-ASHARI</t>
+          <t>GRADE 11 (1ST SHIFT GIRLS)</t>
         </is>
       </c>
       <c r="G334" t="inlineStr">
@@ -22434,7 +22434,7 @@
       </c>
       <c r="H334" t="inlineStr">
         <is>
-          <t>Grade 12</t>
+          <t>Grade 11</t>
         </is>
       </c>
       <c r="I334" t="inlineStr">
@@ -22444,22 +22444,22 @@
       </c>
       <c r="J334" t="inlineStr">
         <is>
-          <t>subj_shaf</t>
+          <t>subj_mabisang_komunikasyon</t>
         </is>
       </c>
       <c r="K334" t="inlineStr">
         <is>
-          <t>SHAF</t>
+          <t>Mabisang Komunikasyon</t>
         </is>
       </c>
       <c r="L334" t="inlineStr">
         <is>
-          <t>tchr_samsuddin</t>
+          <t>tchr_nadzra</t>
         </is>
       </c>
       <c r="M334" t="inlineStr">
         <is>
-          <t>Alim Samsuddin</t>
+          <t>Teacher Nadzra</t>
         </is>
       </c>
       <c r="N334" t="n">
@@ -22485,22 +22485,22 @@
       </c>
       <c r="E335" t="inlineStr">
         <is>
-          <t>sec_grade_2_amr_ibn_al_jamuh_1st_shift</t>
+          <t>sec_grade_12_abu_musa_al_ashari</t>
         </is>
       </c>
       <c r="F335" t="inlineStr">
         <is>
-          <t>GRADE 2 - AMR IBN AL-JAMUH (1ST SHIFT)</t>
+          <t>GRADE 12 - ABU MUSA AL-ASHARI</t>
         </is>
       </c>
       <c r="G335" t="inlineStr">
         <is>
-          <t>Elementary</t>
+          <t>Senior High School</t>
         </is>
       </c>
       <c r="H335" t="inlineStr">
         <is>
-          <t>Grade 2</t>
+          <t>Grade 12</t>
         </is>
       </c>
       <c r="I335" t="inlineStr">
@@ -22510,22 +22510,22 @@
       </c>
       <c r="J335" t="inlineStr">
         <is>
-          <t>subj_math</t>
+          <t>subj_shaf</t>
         </is>
       </c>
       <c r="K335" t="inlineStr">
         <is>
-          <t>Math</t>
+          <t>SHAF</t>
         </is>
       </c>
       <c r="L335" t="inlineStr">
         <is>
-          <t>tchr_sitti_kauzar</t>
+          <t>tchr_samsuddin</t>
         </is>
       </c>
       <c r="M335" t="inlineStr">
         <is>
-          <t>Teacher Sitti Kauzar</t>
+          <t>Alim Samsuddin</t>
         </is>
       </c>
       <c r="N335" t="n">
@@ -22551,12 +22551,12 @@
       </c>
       <c r="E336" t="inlineStr">
         <is>
-          <t>sec_grade_2_talha_ibn_ubaydullah_1st_shift</t>
+          <t>sec_grade_2_amr_ibn_al_jamuh_1st_shift</t>
         </is>
       </c>
       <c r="F336" t="inlineStr">
         <is>
-          <t>GRADE 2 - TALHA IBN UBAYDULLAH (1ST SHIFT)</t>
+          <t>GRADE 2 - AMR IBN AL-JAMUH (1ST SHIFT)</t>
         </is>
       </c>
       <c r="G336" t="inlineStr">
@@ -22576,22 +22576,22 @@
       </c>
       <c r="J336" t="inlineStr">
         <is>
-          <t>subj_qur_an</t>
+          <t>subj_math</t>
         </is>
       </c>
       <c r="K336" t="inlineStr">
         <is>
-          <t>Qur'an</t>
+          <t>Math</t>
         </is>
       </c>
       <c r="L336" t="inlineStr">
         <is>
-          <t>tchr_obaydah</t>
+          <t>tchr_sitti_kauzar</t>
         </is>
       </c>
       <c r="M336" t="inlineStr">
         <is>
-          <t>Ustadh Obaydah</t>
+          <t>Teacher Sitti Kauzar</t>
         </is>
       </c>
       <c r="N336" t="n">
@@ -22617,12 +22617,12 @@
       </c>
       <c r="E337" t="inlineStr">
         <is>
-          <t>sec_grade_3_habib_ibn_zayd_al_ansari_1st_shift_girls</t>
+          <t>sec_grade_2_talha_ibn_ubaydullah_1st_shift</t>
         </is>
       </c>
       <c r="F337" t="inlineStr">
         <is>
-          <t>Grade 3 - HABIB IBN ZAYD AL-ANSARI (1ST SHIFT) - GIRLS</t>
+          <t>GRADE 2 - TALHA IBN UBAYDULLAH (1ST SHIFT)</t>
         </is>
       </c>
       <c r="G337" t="inlineStr">
@@ -22632,7 +22632,7 @@
       </c>
       <c r="H337" t="inlineStr">
         <is>
-          <t>Grade 3</t>
+          <t>Grade 2</t>
         </is>
       </c>
       <c r="I337" t="inlineStr">
@@ -22642,22 +22642,22 @@
       </c>
       <c r="J337" t="inlineStr">
         <is>
-          <t>subj_arabic</t>
+          <t>subj_qur_an</t>
         </is>
       </c>
       <c r="K337" t="inlineStr">
         <is>
-          <t>Arabic</t>
+          <t>Qur'an</t>
         </is>
       </c>
       <c r="L337" t="inlineStr">
         <is>
-          <t>tchr_silfah</t>
+          <t>tchr_obaydah</t>
         </is>
       </c>
       <c r="M337" t="inlineStr">
         <is>
-          <t>Ustadh Silfah</t>
+          <t>Ustadh Obaydah</t>
         </is>
       </c>
       <c r="N337" t="n">
@@ -22683,12 +22683,12 @@
       </c>
       <c r="E338" t="inlineStr">
         <is>
-          <t>sec_grade_3_salman_al_farsi_1st_shift_mix</t>
+          <t>sec_grade_3_habib_ibn_zayd_al_ansari_1st_shift_girls</t>
         </is>
       </c>
       <c r="F338" t="inlineStr">
         <is>
-          <t>GRADE 3 - SALMAN AL FARSI (1ST SHIFT) MIX</t>
+          <t>Grade 3 - HABIB IBN ZAYD AL-ANSARI (1ST SHIFT) - GIRLS</t>
         </is>
       </c>
       <c r="G338" t="inlineStr">
@@ -22708,22 +22708,22 @@
       </c>
       <c r="J338" t="inlineStr">
         <is>
-          <t>subj_math</t>
+          <t>subj_arabic</t>
         </is>
       </c>
       <c r="K338" t="inlineStr">
         <is>
-          <t>Math</t>
+          <t>Arabic</t>
         </is>
       </c>
       <c r="L338" t="inlineStr">
         <is>
-          <t>tchr_jerlyn</t>
+          <t>tchr_silfah</t>
         </is>
       </c>
       <c r="M338" t="inlineStr">
         <is>
-          <t>Teacher Jerlyn</t>
+          <t>Ustadh Silfah</t>
         </is>
       </c>
       <c r="N338" t="n">
@@ -22749,12 +22749,12 @@
       </c>
       <c r="E339" t="inlineStr">
         <is>
-          <t>sec_grade_3_ammar_ibn_yasir_1st_shift_boys</t>
+          <t>sec_grade_3_salman_al_farsi_1st_shift_mix</t>
         </is>
       </c>
       <c r="F339" t="inlineStr">
         <is>
-          <t>GRADE 3 -AMMAR IBN YASIR (1ST SHIFT) - BOYS</t>
+          <t>GRADE 3 - SALMAN AL FARSI (1ST SHIFT) MIX</t>
         </is>
       </c>
       <c r="G339" t="inlineStr">
@@ -22774,22 +22774,22 @@
       </c>
       <c r="J339" t="inlineStr">
         <is>
-          <t>subj_filipino</t>
+          <t>subj_math</t>
         </is>
       </c>
       <c r="K339" t="inlineStr">
         <is>
-          <t>Filipino</t>
+          <t>Math</t>
         </is>
       </c>
       <c r="L339" t="inlineStr">
         <is>
-          <t>tchr_normylah</t>
+          <t>tchr_jerlyn</t>
         </is>
       </c>
       <c r="M339" t="inlineStr">
         <is>
-          <t>Teacher Normylah</t>
+          <t>Teacher Jerlyn</t>
         </is>
       </c>
       <c r="N339" t="n">
@@ -22815,12 +22815,12 @@
       </c>
       <c r="E340" t="inlineStr">
         <is>
-          <t>sec_grade_4_abdur_rahman_ibn_awf_1st_shift</t>
+          <t>sec_grade_3_ammar_ibn_yasir_1st_shift_boys</t>
         </is>
       </c>
       <c r="F340" t="inlineStr">
         <is>
-          <t>GRADE 4 - ABDUR RAHMAN IBN AWF (1ST SHIFT)</t>
+          <t>GRADE 3 -AMMAR IBN YASIR (1ST SHIFT) - BOYS</t>
         </is>
       </c>
       <c r="G340" t="inlineStr">
@@ -22830,7 +22830,7 @@
       </c>
       <c r="H340" t="inlineStr">
         <is>
-          <t>Grade 4</t>
+          <t>Grade 3</t>
         </is>
       </c>
       <c r="I340" t="inlineStr">
@@ -22840,22 +22840,22 @@
       </c>
       <c r="J340" t="inlineStr">
         <is>
-          <t>subj_araling_panlipunan</t>
+          <t>subj_filipino</t>
         </is>
       </c>
       <c r="K340" t="inlineStr">
         <is>
-          <t>Araling Panlipunan</t>
+          <t>Filipino</t>
         </is>
       </c>
       <c r="L340" t="inlineStr">
         <is>
-          <t>tchr_monisa</t>
+          <t>tchr_normylah</t>
         </is>
       </c>
       <c r="M340" t="inlineStr">
         <is>
-          <t>Teacher Monisa</t>
+          <t>Teacher Normylah</t>
         </is>
       </c>
       <c r="N340" t="n">
@@ -22881,12 +22881,12 @@
       </c>
       <c r="E341" t="inlineStr">
         <is>
-          <t>sec_grade_4_hakim_ibn_hazm_1st_shift</t>
+          <t>sec_grade_4_abdur_rahman_ibn_awf_1st_shift</t>
         </is>
       </c>
       <c r="F341" t="inlineStr">
         <is>
-          <t>GRADE 4 - HAKIM IBN HAZM(1ST SHIFT)</t>
+          <t>GRADE 4 - ABDUR RAHMAN IBN AWF (1ST SHIFT)</t>
         </is>
       </c>
       <c r="G341" t="inlineStr">
@@ -22906,22 +22906,22 @@
       </c>
       <c r="J341" t="inlineStr">
         <is>
-          <t>subj_english</t>
+          <t>subj_araling_panlipunan</t>
         </is>
       </c>
       <c r="K341" t="inlineStr">
         <is>
-          <t>English</t>
+          <t>Araling Panlipunan</t>
         </is>
       </c>
       <c r="L341" t="inlineStr">
         <is>
-          <t>tchr_arvin</t>
+          <t>tchr_monisa</t>
         </is>
       </c>
       <c r="M341" t="inlineStr">
         <is>
-          <t>Teacher Arvin</t>
+          <t>Teacher Monisa</t>
         </is>
       </c>
       <c r="N341" t="n">
@@ -22947,12 +22947,12 @@
       </c>
       <c r="E342" t="inlineStr">
         <is>
-          <t>sec_grade_4_usayd_ibn_hudhayr_1st_shift_mix</t>
+          <t>sec_grade_4_hakim_ibn_hazm_1st_shift</t>
         </is>
       </c>
       <c r="F342" t="inlineStr">
         <is>
-          <t>GRADE 4 - USAYD IBN HUDHAYR (1ST SHIFT) - MIX</t>
+          <t>GRADE 4 - HAKIM IBN HAZM(1ST SHIFT)</t>
         </is>
       </c>
       <c r="G342" t="inlineStr">
@@ -22972,22 +22972,22 @@
       </c>
       <c r="J342" t="inlineStr">
         <is>
-          <t>subj_gmrc</t>
+          <t>subj_english</t>
         </is>
       </c>
       <c r="K342" t="inlineStr">
         <is>
-          <t>GMRC</t>
+          <t>English</t>
         </is>
       </c>
       <c r="L342" t="inlineStr">
         <is>
-          <t>tchr_sahdia</t>
+          <t>tchr_arvin</t>
         </is>
       </c>
       <c r="M342" t="inlineStr">
         <is>
-          <t>Teacher Sahdia</t>
+          <t>Teacher Arvin</t>
         </is>
       </c>
       <c r="N342" t="n">
@@ -23013,12 +23013,12 @@
       </c>
       <c r="E343" t="inlineStr">
         <is>
-          <t>sec_grade_5_ayyash_ibn_abi_rabi_ah_1st_shift</t>
+          <t>sec_grade_4_usayd_ibn_hudhayr_1st_shift_mix</t>
         </is>
       </c>
       <c r="F343" t="inlineStr">
         <is>
-          <t>GRADE 5 - AYYASH IBN ABI RABI'AH(1ST SHIFT)</t>
+          <t>GRADE 4 - USAYD IBN HUDHAYR (1ST SHIFT) - MIX</t>
         </is>
       </c>
       <c r="G343" t="inlineStr">
@@ -23028,7 +23028,7 @@
       </c>
       <c r="H343" t="inlineStr">
         <is>
-          <t>Grade 5</t>
+          <t>Grade 4</t>
         </is>
       </c>
       <c r="I343" t="inlineStr">
@@ -23038,22 +23038,22 @@
       </c>
       <c r="J343" t="inlineStr">
         <is>
-          <t>subj_araling_panlipunan</t>
+          <t>subj_gmrc</t>
         </is>
       </c>
       <c r="K343" t="inlineStr">
         <is>
-          <t>Araling Panlipunan</t>
+          <t>GMRC</t>
         </is>
       </c>
       <c r="L343" t="inlineStr">
         <is>
-          <t>tchr_saimonah</t>
+          <t>tchr_sahdia</t>
         </is>
       </c>
       <c r="M343" t="inlineStr">
         <is>
-          <t>Teacher Saimonah</t>
+          <t>Teacher Sahdia</t>
         </is>
       </c>
       <c r="N343" t="n">
@@ -23079,12 +23079,12 @@
       </c>
       <c r="E344" t="inlineStr">
         <is>
-          <t>sec_grade_5_hamza_ibn_abdul_1st_shift</t>
+          <t>sec_grade_5_ayyash_ibn_abi_rabi_ah_1st_shift</t>
         </is>
       </c>
       <c r="F344" t="inlineStr">
         <is>
-          <t>GRADE 5 - HAMZA IBN ABDUL (1ST SHIFT)</t>
+          <t>GRADE 5 - AYYASH IBN ABI RABI'AH(1ST SHIFT)</t>
         </is>
       </c>
       <c r="G344" t="inlineStr">
@@ -23104,22 +23104,22 @@
       </c>
       <c r="J344" t="inlineStr">
         <is>
-          <t>subj_tle</t>
+          <t>subj_araling_panlipunan</t>
         </is>
       </c>
       <c r="K344" t="inlineStr">
         <is>
-          <t>TLE</t>
+          <t>Araling Panlipunan</t>
         </is>
       </c>
       <c r="L344" t="inlineStr">
         <is>
-          <t>tchr_anna</t>
+          <t>tchr_saimonah</t>
         </is>
       </c>
       <c r="M344" t="inlineStr">
         <is>
-          <t>Teacher Anna</t>
+          <t>Teacher Saimonah</t>
         </is>
       </c>
       <c r="N344" t="n">
@@ -23145,12 +23145,12 @@
       </c>
       <c r="E345" t="inlineStr">
         <is>
-          <t>sec_grade_5_muhammad_ibn_maslamah_1st_shift</t>
+          <t>sec_grade_5_hamza_ibn_abdul_1st_shift</t>
         </is>
       </c>
       <c r="F345" t="inlineStr">
         <is>
-          <t>GRADE 5 - MUHAMMAD IBN MASLAMAH (1ST SHIFT)</t>
+          <t>GRADE 5 - HAMZA IBN ABDUL (1ST SHIFT)</t>
         </is>
       </c>
       <c r="G345" t="inlineStr">
@@ -23170,22 +23170,22 @@
       </c>
       <c r="J345" t="inlineStr">
         <is>
-          <t>subj_filipino</t>
+          <t>subj_tle</t>
         </is>
       </c>
       <c r="K345" t="inlineStr">
         <is>
-          <t>Filipino</t>
+          <t>TLE</t>
         </is>
       </c>
       <c r="L345" t="inlineStr">
         <is>
-          <t>tchr_joanna</t>
+          <t>tchr_anna</t>
         </is>
       </c>
       <c r="M345" t="inlineStr">
         <is>
-          <t>Teacher Joanna</t>
+          <t>Teacher Anna</t>
         </is>
       </c>
       <c r="N345" t="n">
@@ -23211,12 +23211,12 @@
       </c>
       <c r="E346" t="inlineStr">
         <is>
-          <t>sec_grade_6_abbas_ibn_abd_al_muttalib_1st_shift</t>
+          <t>sec_grade_5_muhammad_ibn_maslamah_1st_shift</t>
         </is>
       </c>
       <c r="F346" t="inlineStr">
         <is>
-          <t>GRADE 6 - ABBAS IBN ABD AL-MUTTALIB (1ST SHIFT)</t>
+          <t>GRADE 5 - MUHAMMAD IBN MASLAMAH (1ST SHIFT)</t>
         </is>
       </c>
       <c r="G346" t="inlineStr">
@@ -23226,7 +23226,7 @@
       </c>
       <c r="H346" t="inlineStr">
         <is>
-          <t>Grade 6</t>
+          <t>Grade 5</t>
         </is>
       </c>
       <c r="I346" t="inlineStr">
@@ -23236,22 +23236,22 @@
       </c>
       <c r="J346" t="inlineStr">
         <is>
-          <t>subj_shaf</t>
+          <t>subj_filipino</t>
         </is>
       </c>
       <c r="K346" t="inlineStr">
         <is>
-          <t>SHAF</t>
+          <t>Filipino</t>
         </is>
       </c>
       <c r="L346" t="inlineStr">
         <is>
-          <t>tchr_abdiraheem</t>
+          <t>tchr_joanna</t>
         </is>
       </c>
       <c r="M346" t="inlineStr">
         <is>
-          <t>Ustadh Abdiraheem</t>
+          <t>Teacher Joanna</t>
         </is>
       </c>
       <c r="N346" t="n">
@@ -23277,12 +23277,12 @@
       </c>
       <c r="E347" t="inlineStr">
         <is>
-          <t>sec_grade_6_abdullah_ibn_salaam_1st_shift</t>
+          <t>sec_grade_6_abbas_ibn_abd_al_muttalib_1st_shift</t>
         </is>
       </c>
       <c r="F347" t="inlineStr">
         <is>
-          <t>GRADE 6 - ABDULLAH IBN SALAAM (1ST SHIFT)</t>
+          <t>GRADE 6 - ABBAS IBN ABD AL-MUTTALIB (1ST SHIFT)</t>
         </is>
       </c>
       <c r="G347" t="inlineStr">
@@ -23302,22 +23302,22 @@
       </c>
       <c r="J347" t="inlineStr">
         <is>
-          <t>subj_english</t>
+          <t>subj_shaf</t>
         </is>
       </c>
       <c r="K347" t="inlineStr">
         <is>
-          <t>English</t>
+          <t>SHAF</t>
         </is>
       </c>
       <c r="L347" t="inlineStr">
         <is>
-          <t>tchr_jessa</t>
+          <t>tchr_abdiraheem</t>
         </is>
       </c>
       <c r="M347" t="inlineStr">
         <is>
-          <t>Teacher Jessa</t>
+          <t>Ustadh Abdiraheem</t>
         </is>
       </c>
       <c r="N347" t="n">
@@ -23343,22 +23343,22 @@
       </c>
       <c r="E348" t="inlineStr">
         <is>
-          <t>sec_grade_7_abu_sufyan_ibn_al_harith_1st_shift_boys</t>
+          <t>sec_grade_6_abdullah_ibn_salaam_1st_shift</t>
         </is>
       </c>
       <c r="F348" t="inlineStr">
         <is>
-          <t>GRADE 7 - ABU SUFYAN IBN AL-HARITH (1ST SHIFT) BOYS</t>
+          <t>GRADE 6 - ABDULLAH IBN SALAAM (1ST SHIFT)</t>
         </is>
       </c>
       <c r="G348" t="inlineStr">
         <is>
-          <t>Junior High School</t>
+          <t>Elementary</t>
         </is>
       </c>
       <c r="H348" t="inlineStr">
         <is>
-          <t>Grade 7</t>
+          <t>Grade 6</t>
         </is>
       </c>
       <c r="I348" t="inlineStr">
@@ -23368,22 +23368,22 @@
       </c>
       <c r="J348" t="inlineStr">
         <is>
-          <t>subj_arabic</t>
+          <t>subj_english</t>
         </is>
       </c>
       <c r="K348" t="inlineStr">
         <is>
-          <t>Arabic</t>
+          <t>English</t>
         </is>
       </c>
       <c r="L348" t="inlineStr">
         <is>
-          <t>tchr_ali</t>
+          <t>tchr_jessa</t>
         </is>
       </c>
       <c r="M348" t="inlineStr">
         <is>
-          <t>Ustadh Ali</t>
+          <t>Teacher Jessa</t>
         </is>
       </c>
       <c r="N348" t="n">
@@ -23404,17 +23404,17 @@
       </c>
       <c r="D349" t="inlineStr">
         <is>
-          <t>12:40 PM – 02:50 PM</t>
+          <t>12:40 PM – 01:40 PM</t>
         </is>
       </c>
       <c r="E349" t="inlineStr">
         <is>
-          <t>sec_grade_7_usama_ibn_zayd_1st_shift_girls</t>
+          <t>sec_grade_7_abu_sufyan_ibn_al_harith_1st_shift_boys</t>
         </is>
       </c>
       <c r="F349" t="inlineStr">
         <is>
-          <t>GRADE 7 - USAMA IBN ZAYD (1ST SHIFT) GIRLS</t>
+          <t>GRADE 7 - ABU SUFYAN IBN AL-HARITH (1ST SHIFT) BOYS</t>
         </is>
       </c>
       <c r="G349" t="inlineStr">
@@ -23434,26 +23434,26 @@
       </c>
       <c r="J349" t="inlineStr">
         <is>
-          <t>subj_math</t>
+          <t>subj_arabic</t>
         </is>
       </c>
       <c r="K349" t="inlineStr">
         <is>
-          <t>Math</t>
+          <t>Arabic</t>
         </is>
       </c>
       <c r="L349" t="inlineStr">
         <is>
-          <t>tchr_ethel</t>
+          <t>tchr_ali</t>
         </is>
       </c>
       <c r="M349" t="inlineStr">
         <is>
-          <t>Teacher Ethel</t>
+          <t>Ustadh Ali</t>
         </is>
       </c>
       <c r="N349" t="n">
-        <v>120</v>
+        <v>60</v>
       </c>
     </row>
     <row r="350">
@@ -23470,17 +23470,17 @@
       </c>
       <c r="D350" t="inlineStr">
         <is>
-          <t>12:40 PM – 01:40 PM</t>
+          <t>12:40 PM – 02:50 PM</t>
         </is>
       </c>
       <c r="E350" t="inlineStr">
         <is>
-          <t>sec_grade_8_sa_ad_ibn_mua_dh_1st_shift_girls</t>
+          <t>sec_grade_7_usama_ibn_zayd_1st_shift_girls</t>
         </is>
       </c>
       <c r="F350" t="inlineStr">
         <is>
-          <t>GRADE 8 - SA'AD IBN MUA'DH (1ST SHIFT) - GIRLS</t>
+          <t>GRADE 7 - USAMA IBN ZAYD (1ST SHIFT) GIRLS</t>
         </is>
       </c>
       <c r="G350" t="inlineStr">
@@ -23490,7 +23490,7 @@
       </c>
       <c r="H350" t="inlineStr">
         <is>
-          <t>Grade 8</t>
+          <t>Grade 7</t>
         </is>
       </c>
       <c r="I350" t="inlineStr">
@@ -23500,26 +23500,26 @@
       </c>
       <c r="J350" t="inlineStr">
         <is>
-          <t>subj_filipino</t>
+          <t>subj_math</t>
         </is>
       </c>
       <c r="K350" t="inlineStr">
         <is>
-          <t>Filipino</t>
+          <t>Math</t>
         </is>
       </c>
       <c r="L350" t="inlineStr">
         <is>
-          <t>tchr_sophia</t>
+          <t>tchr_ethel</t>
         </is>
       </c>
       <c r="M350" t="inlineStr">
         <is>
-          <t>Teacher Sophia</t>
+          <t>Teacher Ethel</t>
         </is>
       </c>
       <c r="N350" t="n">
-        <v>60</v>
+        <v>120</v>
       </c>
     </row>
     <row r="351">
@@ -23541,12 +23541,12 @@
       </c>
       <c r="E351" t="inlineStr">
         <is>
-          <t>sec_grade_9_abu_hurayrah_1st_shift_girls</t>
+          <t>sec_grade_8_sa_ad_ibn_mua_dh_1st_shift_girls</t>
         </is>
       </c>
       <c r="F351" t="inlineStr">
         <is>
-          <t>GRADE 9 - ABU HURAYRAH (1ST SHIFT) GIRLS</t>
+          <t>GRADE 8 - SA'AD IBN MUA'DH (1ST SHIFT) - GIRLS</t>
         </is>
       </c>
       <c r="G351" t="inlineStr">
@@ -23556,7 +23556,7 @@
       </c>
       <c r="H351" t="inlineStr">
         <is>
-          <t>Grade 9</t>
+          <t>Grade 8</t>
         </is>
       </c>
       <c r="I351" t="inlineStr">
@@ -23566,22 +23566,22 @@
       </c>
       <c r="J351" t="inlineStr">
         <is>
-          <t>subj_arabic</t>
+          <t>subj_filipino</t>
         </is>
       </c>
       <c r="K351" t="inlineStr">
         <is>
-          <t>Arabic</t>
+          <t>Filipino</t>
         </is>
       </c>
       <c r="L351" t="inlineStr">
         <is>
-          <t>tchr_raslina</t>
+          <t>tchr_sophia</t>
         </is>
       </c>
       <c r="M351" t="inlineStr">
         <is>
-          <t>Ustadh Raslina</t>
+          <t>Teacher Sophia</t>
         </is>
       </c>
       <c r="N351" t="n">
@@ -23602,27 +23602,27 @@
       </c>
       <c r="D352" t="inlineStr">
         <is>
-          <t>01:30 PM – 02:30 PM</t>
+          <t>12:40 PM – 01:40 PM</t>
         </is>
       </c>
       <c r="E352" t="inlineStr">
         <is>
-          <t>sec_kinder_2_abu_bakr_as_sideeq_1st_shift</t>
+          <t>sec_grade_9_abu_hurayrah_1st_shift_girls</t>
         </is>
       </c>
       <c r="F352" t="inlineStr">
         <is>
-          <t>Kinder 2 ABU BAKR AS-SIDEEQ (1ST SHIFT)</t>
+          <t>GRADE 9 - ABU HURAYRAH (1ST SHIFT) GIRLS</t>
         </is>
       </c>
       <c r="G352" t="inlineStr">
         <is>
-          <t>Elementary</t>
+          <t>Junior High School</t>
         </is>
       </c>
       <c r="H352" t="inlineStr">
         <is>
-          <t>Kinder 2</t>
+          <t>Grade 9</t>
         </is>
       </c>
       <c r="I352" t="inlineStr">
@@ -23632,22 +23632,22 @@
       </c>
       <c r="J352" t="inlineStr">
         <is>
-          <t>subj_hadith</t>
+          <t>subj_arabic</t>
         </is>
       </c>
       <c r="K352" t="inlineStr">
         <is>
-          <t>Hadith</t>
+          <t>Arabic</t>
         </is>
       </c>
       <c r="L352" t="inlineStr">
         <is>
-          <t>tchr_saliha</t>
+          <t>tchr_raslina</t>
         </is>
       </c>
       <c r="M352" t="inlineStr">
         <is>
-          <t>Ustadha Saliha</t>
+          <t>Ustadh Raslina</t>
         </is>
       </c>
       <c r="N352" t="n">
@@ -23673,12 +23673,12 @@
       </c>
       <c r="E353" t="inlineStr">
         <is>
-          <t>sec_kinder_2_uthman_ibn_affan_1st_shift</t>
+          <t>sec_kinder_2_abu_bakr_as_sideeq_1st_shift</t>
         </is>
       </c>
       <c r="F353" t="inlineStr">
         <is>
-          <t>Kinder 2 UTHMAN IBN AFFAN (1ST SHIFT)</t>
+          <t>Kinder 2 ABU BAKR AS-SIDEEQ (1ST SHIFT)</t>
         </is>
       </c>
       <c r="G353" t="inlineStr">
@@ -23698,22 +23698,22 @@
       </c>
       <c r="J353" t="inlineStr">
         <is>
-          <t>subj_arabic</t>
+          <t>subj_hadith</t>
         </is>
       </c>
       <c r="K353" t="inlineStr">
         <is>
-          <t>Arabic</t>
+          <t>Hadith</t>
         </is>
       </c>
       <c r="L353" t="inlineStr">
         <is>
-          <t>tchr_abdul_karim</t>
+          <t>tchr_saliha</t>
         </is>
       </c>
       <c r="M353" t="inlineStr">
         <is>
-          <t>Alim Abdul Karim</t>
+          <t>Ustadha Saliha</t>
         </is>
       </c>
       <c r="N353" t="n">
@@ -23730,21 +23730,21 @@
         </is>
       </c>
       <c r="C354" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D354" t="inlineStr">
         <is>
-          <t>01:50 PM – 02:50 PM</t>
+          <t>01:30 PM – 02:30 PM</t>
         </is>
       </c>
       <c r="E354" t="inlineStr">
         <is>
-          <t>sec_grade_1_hudhayfah_ibn_al_yam_1st_shift</t>
+          <t>sec_kinder_2_uthman_ibn_affan_1st_shift</t>
         </is>
       </c>
       <c r="F354" t="inlineStr">
         <is>
-          <t>GRADE 1 - HUDHAYFAH IBN AL-YAM (1ST SHIFT)</t>
+          <t>Kinder 2 UTHMAN IBN AFFAN (1ST SHIFT)</t>
         </is>
       </c>
       <c r="G354" t="inlineStr">
@@ -23754,7 +23754,7 @@
       </c>
       <c r="H354" t="inlineStr">
         <is>
-          <t>Grade 1</t>
+          <t>Kinder 2</t>
         </is>
       </c>
       <c r="I354" t="inlineStr">
@@ -23764,22 +23764,22 @@
       </c>
       <c r="J354" t="inlineStr">
         <is>
-          <t>subj_language</t>
+          <t>subj_arabic</t>
         </is>
       </c>
       <c r="K354" t="inlineStr">
         <is>
-          <t>Language</t>
+          <t>Arabic</t>
         </is>
       </c>
       <c r="L354" t="inlineStr">
         <is>
-          <t>tchr_sahdia</t>
+          <t>tchr_abdul_karim</t>
         </is>
       </c>
       <c r="M354" t="inlineStr">
         <is>
-          <t>Teacher Sahdia</t>
+          <t>Alim Abdul Karim</t>
         </is>
       </c>
       <c r="N354" t="n">
@@ -23805,22 +23805,22 @@
       </c>
       <c r="E355" t="inlineStr">
         <is>
-          <t>sec_grade_11_1st_shift_girls</t>
+          <t>sec_grade_1_hudhayfah_ibn_al_yam_1st_shift</t>
         </is>
       </c>
       <c r="F355" t="inlineStr">
         <is>
-          <t>GRADE 11 (1ST SHIFT GIRLS)</t>
+          <t>GRADE 1 - HUDHAYFAH IBN AL-YAM (1ST SHIFT)</t>
         </is>
       </c>
       <c r="G355" t="inlineStr">
         <is>
-          <t>Senior High School</t>
+          <t>Elementary</t>
         </is>
       </c>
       <c r="H355" t="inlineStr">
         <is>
-          <t>Grade 11</t>
+          <t>Grade 1</t>
         </is>
       </c>
       <c r="I355" t="inlineStr">
@@ -23830,22 +23830,22 @@
       </c>
       <c r="J355" t="inlineStr">
         <is>
-          <t>subj_gen_science</t>
+          <t>subj_language</t>
         </is>
       </c>
       <c r="K355" t="inlineStr">
         <is>
-          <t>Gen Science</t>
+          <t>Language</t>
         </is>
       </c>
       <c r="L355" t="inlineStr">
         <is>
-          <t>tchr_rowena</t>
+          <t>tchr_sahdia</t>
         </is>
       </c>
       <c r="M355" t="inlineStr">
         <is>
-          <t>Teacher Rowena</t>
+          <t>Teacher Sahdia</t>
         </is>
       </c>
       <c r="N355" t="n">
@@ -23871,12 +23871,12 @@
       </c>
       <c r="E356" t="inlineStr">
         <is>
-          <t>sec_grade_12_abu_musa_al_ashari</t>
+          <t>sec_grade_11_1st_shift_girls</t>
         </is>
       </c>
       <c r="F356" t="inlineStr">
         <is>
-          <t>GRADE 12 - ABU MUSA AL-ASHARI</t>
+          <t>GRADE 11 (1ST SHIFT GIRLS)</t>
         </is>
       </c>
       <c r="G356" t="inlineStr">
@@ -23886,7 +23886,7 @@
       </c>
       <c r="H356" t="inlineStr">
         <is>
-          <t>Grade 12</t>
+          <t>Grade 11</t>
         </is>
       </c>
       <c r="I356" t="inlineStr">
@@ -23896,22 +23896,22 @@
       </c>
       <c r="J356" t="inlineStr">
         <is>
-          <t>subj_arabic</t>
+          <t>subj_gen_science</t>
         </is>
       </c>
       <c r="K356" t="inlineStr">
         <is>
-          <t>Arabic</t>
+          <t>Gen Science</t>
         </is>
       </c>
       <c r="L356" t="inlineStr">
         <is>
-          <t>tchr_mamonas</t>
+          <t>tchr_rowena</t>
         </is>
       </c>
       <c r="M356" t="inlineStr">
         <is>
-          <t>Alim Mamonas</t>
+          <t>Teacher Rowena</t>
         </is>
       </c>
       <c r="N356" t="n">
@@ -23937,22 +23937,22 @@
       </c>
       <c r="E357" t="inlineStr">
         <is>
-          <t>sec_grade_2_amr_ibn_al_jamuh_1st_shift</t>
+          <t>sec_grade_12_abu_musa_al_ashari</t>
         </is>
       </c>
       <c r="F357" t="inlineStr">
         <is>
-          <t>GRADE 2 - AMR IBN AL-JAMUH (1ST SHIFT)</t>
+          <t>GRADE 12 - ABU MUSA AL-ASHARI</t>
         </is>
       </c>
       <c r="G357" t="inlineStr">
         <is>
-          <t>Elementary</t>
+          <t>Senior High School</t>
         </is>
       </c>
       <c r="H357" t="inlineStr">
         <is>
-          <t>Grade 2</t>
+          <t>Grade 12</t>
         </is>
       </c>
       <c r="I357" t="inlineStr">
@@ -23962,22 +23962,22 @@
       </c>
       <c r="J357" t="inlineStr">
         <is>
-          <t>subj_makabansa</t>
+          <t>subj_arabic</t>
         </is>
       </c>
       <c r="K357" t="inlineStr">
         <is>
-          <t>Makabansa</t>
+          <t>Arabic</t>
         </is>
       </c>
       <c r="L357" t="inlineStr">
         <is>
-          <t>tchr_monisa</t>
+          <t>tchr_mamonas</t>
         </is>
       </c>
       <c r="M357" t="inlineStr">
         <is>
-          <t>Teacher Monisa</t>
+          <t>Alim Mamonas</t>
         </is>
       </c>
       <c r="N357" t="n">
@@ -24003,12 +24003,12 @@
       </c>
       <c r="E358" t="inlineStr">
         <is>
-          <t>sec_grade_3_habib_ibn_zayd_al_ansari_1st_shift_girls</t>
+          <t>sec_grade_2_amr_ibn_al_jamuh_1st_shift</t>
         </is>
       </c>
       <c r="F358" t="inlineStr">
         <is>
-          <t>Grade 3 - HABIB IBN ZAYD AL-ANSARI (1ST SHIFT) - GIRLS</t>
+          <t>GRADE 2 - AMR IBN AL-JAMUH (1ST SHIFT)</t>
         </is>
       </c>
       <c r="G358" t="inlineStr">
@@ -24018,7 +24018,7 @@
       </c>
       <c r="H358" t="inlineStr">
         <is>
-          <t>Grade 3</t>
+          <t>Grade 2</t>
         </is>
       </c>
       <c r="I358" t="inlineStr">
@@ -24028,22 +24028,22 @@
       </c>
       <c r="J358" t="inlineStr">
         <is>
-          <t>subj_math</t>
+          <t>subj_makabansa</t>
         </is>
       </c>
       <c r="K358" t="inlineStr">
         <is>
-          <t>Math</t>
+          <t>Makabansa</t>
         </is>
       </c>
       <c r="L358" t="inlineStr">
         <is>
-          <t>tchr_jerlyn</t>
+          <t>tchr_monisa</t>
         </is>
       </c>
       <c r="M358" t="inlineStr">
         <is>
-          <t>Teacher Jerlyn</t>
+          <t>Teacher Monisa</t>
         </is>
       </c>
       <c r="N358" t="n">
@@ -24069,12 +24069,12 @@
       </c>
       <c r="E359" t="inlineStr">
         <is>
-          <t>sec_grade_3_salman_al_farsi_1st_shift_mix</t>
+          <t>sec_grade_3_habib_ibn_zayd_al_ansari_1st_shift_girls</t>
         </is>
       </c>
       <c r="F359" t="inlineStr">
         <is>
-          <t>GRADE 3 - SALMAN AL FARSI (1ST SHIFT) MIX</t>
+          <t>Grade 3 - HABIB IBN ZAYD AL-ANSARI (1ST SHIFT) - GIRLS</t>
         </is>
       </c>
       <c r="G359" t="inlineStr">
@@ -24094,22 +24094,22 @@
       </c>
       <c r="J359" t="inlineStr">
         <is>
-          <t>subj_science</t>
+          <t>subj_math</t>
         </is>
       </c>
       <c r="K359" t="inlineStr">
         <is>
-          <t>Science</t>
+          <t>Math</t>
         </is>
       </c>
       <c r="L359" t="inlineStr">
         <is>
-          <t>tchr_saimonah</t>
+          <t>tchr_jerlyn</t>
         </is>
       </c>
       <c r="M359" t="inlineStr">
         <is>
-          <t>Teacher Saimonah</t>
+          <t>Teacher Jerlyn</t>
         </is>
       </c>
       <c r="N359" t="n">
@@ -24135,12 +24135,12 @@
       </c>
       <c r="E360" t="inlineStr">
         <is>
-          <t>sec_grade_3_ammar_ibn_yasir_1st_shift_boys</t>
+          <t>sec_grade_3_salman_al_farsi_1st_shift_mix</t>
         </is>
       </c>
       <c r="F360" t="inlineStr">
         <is>
-          <t>GRADE 3 -AMMAR IBN YASIR (1ST SHIFT) - BOYS</t>
+          <t>GRADE 3 - SALMAN AL FARSI (1ST SHIFT) MIX</t>
         </is>
       </c>
       <c r="G360" t="inlineStr">
@@ -24160,22 +24160,22 @@
       </c>
       <c r="J360" t="inlineStr">
         <is>
-          <t>subj_gmrc</t>
+          <t>subj_science</t>
         </is>
       </c>
       <c r="K360" t="inlineStr">
         <is>
-          <t>GMRC</t>
+          <t>Science</t>
         </is>
       </c>
       <c r="L360" t="inlineStr">
         <is>
-          <t>tchr_silfah</t>
+          <t>tchr_saimonah</t>
         </is>
       </c>
       <c r="M360" t="inlineStr">
         <is>
-          <t>Ustadh Silfah</t>
+          <t>Teacher Saimonah</t>
         </is>
       </c>
       <c r="N360" t="n">
@@ -24201,12 +24201,12 @@
       </c>
       <c r="E361" t="inlineStr">
         <is>
-          <t>sec_grade_4_abdur_rahman_ibn_awf_1st_shift</t>
+          <t>sec_grade_3_ammar_ibn_yasir_1st_shift_boys</t>
         </is>
       </c>
       <c r="F361" t="inlineStr">
         <is>
-          <t>GRADE 4 - ABDUR RAHMAN IBN AWF (1ST SHIFT)</t>
+          <t>GRADE 3 -AMMAR IBN YASIR (1ST SHIFT) - BOYS</t>
         </is>
       </c>
       <c r="G361" t="inlineStr">
@@ -24216,7 +24216,7 @@
       </c>
       <c r="H361" t="inlineStr">
         <is>
-          <t>Grade 4</t>
+          <t>Grade 3</t>
         </is>
       </c>
       <c r="I361" t="inlineStr">
@@ -24226,22 +24226,22 @@
       </c>
       <c r="J361" t="inlineStr">
         <is>
-          <t>subj_qur_an</t>
+          <t>subj_gmrc</t>
         </is>
       </c>
       <c r="K361" t="inlineStr">
         <is>
-          <t>Qur'an</t>
+          <t>GMRC</t>
         </is>
       </c>
       <c r="L361" t="inlineStr">
         <is>
-          <t>tchr_obaydah</t>
+          <t>tchr_silfah</t>
         </is>
       </c>
       <c r="M361" t="inlineStr">
         <is>
-          <t>Ustadh Obaydah</t>
+          <t>Ustadh Silfah</t>
         </is>
       </c>
       <c r="N361" t="n">
@@ -24267,12 +24267,12 @@
       </c>
       <c r="E362" t="inlineStr">
         <is>
-          <t>sec_grade_4_hakim_ibn_hazm_1st_shift</t>
+          <t>sec_grade_4_abdur_rahman_ibn_awf_1st_shift</t>
         </is>
       </c>
       <c r="F362" t="inlineStr">
         <is>
-          <t>GRADE 4 - HAKIM IBN HAZM(1ST SHIFT)</t>
+          <t>GRADE 4 - ABDUR RAHMAN IBN AWF (1ST SHIFT)</t>
         </is>
       </c>
       <c r="G362" t="inlineStr">
@@ -24292,22 +24292,22 @@
       </c>
       <c r="J362" t="inlineStr">
         <is>
-          <t>subj_shaf</t>
+          <t>subj_qur_an</t>
         </is>
       </c>
       <c r="K362" t="inlineStr">
         <is>
-          <t>SHAF</t>
+          <t>Qur'an</t>
         </is>
       </c>
       <c r="L362" t="inlineStr">
         <is>
-          <t>tchr_abdiraheem</t>
+          <t>tchr_obaydah</t>
         </is>
       </c>
       <c r="M362" t="inlineStr">
         <is>
-          <t>Ustadh Abdiraheem</t>
+          <t>Ustadh Obaydah</t>
         </is>
       </c>
       <c r="N362" t="n">
@@ -24333,12 +24333,12 @@
       </c>
       <c r="E363" t="inlineStr">
         <is>
-          <t>sec_grade_4_usayd_ibn_hudhayr_1st_shift_mix</t>
+          <t>sec_grade_4_hakim_ibn_hazm_1st_shift</t>
         </is>
       </c>
       <c r="F363" t="inlineStr">
         <is>
-          <t>GRADE 4 - USAYD IBN HUDHAYR (1ST SHIFT) - MIX</t>
+          <t>GRADE 4 - HAKIM IBN HAZM(1ST SHIFT)</t>
         </is>
       </c>
       <c r="G363" t="inlineStr">
@@ -24358,22 +24358,22 @@
       </c>
       <c r="J363" t="inlineStr">
         <is>
-          <t>subj_english</t>
+          <t>subj_shaf</t>
         </is>
       </c>
       <c r="K363" t="inlineStr">
         <is>
-          <t>English</t>
+          <t>SHAF</t>
         </is>
       </c>
       <c r="L363" t="inlineStr">
         <is>
-          <t>tchr_jenny</t>
+          <t>tchr_abdiraheem</t>
         </is>
       </c>
       <c r="M363" t="inlineStr">
         <is>
-          <t>Teacher Jenny</t>
+          <t>Ustadh Abdiraheem</t>
         </is>
       </c>
       <c r="N363" t="n">
@@ -24399,12 +24399,12 @@
       </c>
       <c r="E364" t="inlineStr">
         <is>
-          <t>sec_grade_5_ayyash_ibn_abi_rabi_ah_1st_shift</t>
+          <t>sec_grade_4_usayd_ibn_hudhayr_1st_shift_mix</t>
         </is>
       </c>
       <c r="F364" t="inlineStr">
         <is>
-          <t>GRADE 5 - AYYASH IBN ABI RABI'AH(1ST SHIFT)</t>
+          <t>GRADE 4 - USAYD IBN HUDHAYR (1ST SHIFT) - MIX</t>
         </is>
       </c>
       <c r="G364" t="inlineStr">
@@ -24414,7 +24414,7 @@
       </c>
       <c r="H364" t="inlineStr">
         <is>
-          <t>Grade 5</t>
+          <t>Grade 4</t>
         </is>
       </c>
       <c r="I364" t="inlineStr">
@@ -24424,22 +24424,22 @@
       </c>
       <c r="J364" t="inlineStr">
         <is>
-          <t>subj_shaf</t>
+          <t>subj_english</t>
         </is>
       </c>
       <c r="K364" t="inlineStr">
         <is>
-          <t>SHAF</t>
+          <t>English</t>
         </is>
       </c>
       <c r="L364" t="inlineStr">
         <is>
-          <t>tchr_faidh</t>
+          <t>tchr_jenny</t>
         </is>
       </c>
       <c r="M364" t="inlineStr">
         <is>
-          <t>Ustadh Faidh</t>
+          <t>Teacher Jenny</t>
         </is>
       </c>
       <c r="N364" t="n">
@@ -24465,12 +24465,12 @@
       </c>
       <c r="E365" t="inlineStr">
         <is>
-          <t>sec_grade_5_hamza_ibn_abdul_1st_shift</t>
+          <t>sec_grade_5_ayyash_ibn_abi_rabi_ah_1st_shift</t>
         </is>
       </c>
       <c r="F365" t="inlineStr">
         <is>
-          <t>GRADE 5 - HAMZA IBN ABDUL (1ST SHIFT)</t>
+          <t>GRADE 5 - AYYASH IBN ABI RABI'AH(1ST SHIFT)</t>
         </is>
       </c>
       <c r="G365" t="inlineStr">
@@ -24490,22 +24490,22 @@
       </c>
       <c r="J365" t="inlineStr">
         <is>
-          <t>subj_qur_an</t>
+          <t>subj_shaf</t>
         </is>
       </c>
       <c r="K365" t="inlineStr">
         <is>
-          <t>Qur'an</t>
+          <t>SHAF</t>
         </is>
       </c>
       <c r="L365" t="inlineStr">
         <is>
-          <t>tchr_jaisam</t>
+          <t>tchr_faidh</t>
         </is>
       </c>
       <c r="M365" t="inlineStr">
         <is>
-          <t>Ustadh Jaisam</t>
+          <t>Ustadh Faidh</t>
         </is>
       </c>
       <c r="N365" t="n">
@@ -24531,12 +24531,12 @@
       </c>
       <c r="E366" t="inlineStr">
         <is>
-          <t>sec_grade_5_muhammad_ibn_maslamah_1st_shift</t>
+          <t>sec_grade_5_hamza_ibn_abdul_1st_shift</t>
         </is>
       </c>
       <c r="F366" t="inlineStr">
         <is>
-          <t>GRADE 5 - MUHAMMAD IBN MASLAMAH (1ST SHIFT)</t>
+          <t>GRADE 5 - HAMZA IBN ABDUL (1ST SHIFT)</t>
         </is>
       </c>
       <c r="G366" t="inlineStr">
@@ -24556,22 +24556,22 @@
       </c>
       <c r="J366" t="inlineStr">
         <is>
-          <t>subj_shaf</t>
+          <t>subj_qur_an</t>
         </is>
       </c>
       <c r="K366" t="inlineStr">
         <is>
-          <t>SHAF</t>
+          <t>Qur'an</t>
         </is>
       </c>
       <c r="L366" t="inlineStr">
         <is>
-          <t>tchr_hainur</t>
+          <t>tchr_jaisam</t>
         </is>
       </c>
       <c r="M366" t="inlineStr">
         <is>
-          <t>Ustadha Hainur</t>
+          <t>Ustadh Jaisam</t>
         </is>
       </c>
       <c r="N366" t="n">
@@ -24597,12 +24597,12 @@
       </c>
       <c r="E367" t="inlineStr">
         <is>
-          <t>sec_grade_6_abbas_ibn_abd_al_muttalib_1st_shift</t>
+          <t>sec_grade_5_muhammad_ibn_maslamah_1st_shift</t>
         </is>
       </c>
       <c r="F367" t="inlineStr">
         <is>
-          <t>GRADE 6 - ABBAS IBN ABD AL-MUTTALIB (1ST SHIFT)</t>
+          <t>GRADE 5 - MUHAMMAD IBN MASLAMAH (1ST SHIFT)</t>
         </is>
       </c>
       <c r="G367" t="inlineStr">
@@ -24612,7 +24612,7 @@
       </c>
       <c r="H367" t="inlineStr">
         <is>
-          <t>Grade 6</t>
+          <t>Grade 5</t>
         </is>
       </c>
       <c r="I367" t="inlineStr">
@@ -24622,22 +24622,22 @@
       </c>
       <c r="J367" t="inlineStr">
         <is>
-          <t>subj_science</t>
+          <t>subj_shaf</t>
         </is>
       </c>
       <c r="K367" t="inlineStr">
         <is>
-          <t>Science</t>
+          <t>SHAF</t>
         </is>
       </c>
       <c r="L367" t="inlineStr">
         <is>
-          <t>tchr_anna</t>
+          <t>tchr_hainur</t>
         </is>
       </c>
       <c r="M367" t="inlineStr">
         <is>
-          <t>Teacher Anna</t>
+          <t>Ustadha Hainur</t>
         </is>
       </c>
       <c r="N367" t="n">
@@ -24663,22 +24663,22 @@
       </c>
       <c r="E368" t="inlineStr">
         <is>
-          <t>sec_grade_7_abu_sufyan_ibn_al_harith_1st_shift_boys</t>
+          <t>sec_grade_6_abbas_ibn_abd_al_muttalib_1st_shift</t>
         </is>
       </c>
       <c r="F368" t="inlineStr">
         <is>
-          <t>GRADE 7 - ABU SUFYAN IBN AL-HARITH (1ST SHIFT) BOYS</t>
+          <t>GRADE 6 - ABBAS IBN ABD AL-MUTTALIB (1ST SHIFT)</t>
         </is>
       </c>
       <c r="G368" t="inlineStr">
         <is>
-          <t>Junior High School</t>
+          <t>Elementary</t>
         </is>
       </c>
       <c r="H368" t="inlineStr">
         <is>
-          <t>Grade 7</t>
+          <t>Grade 6</t>
         </is>
       </c>
       <c r="I368" t="inlineStr">
@@ -24698,12 +24698,12 @@
       </c>
       <c r="L368" t="inlineStr">
         <is>
-          <t>tchr_aniah</t>
+          <t>tchr_anna</t>
         </is>
       </c>
       <c r="M368" t="inlineStr">
         <is>
-          <t>Teacher Aniah</t>
+          <t>Teacher Anna</t>
         </is>
       </c>
       <c r="N368" t="n">
@@ -24729,12 +24729,12 @@
       </c>
       <c r="E369" t="inlineStr">
         <is>
-          <t>sec_grade_8_sa_ad_ibn_mua_dh_1st_shift_girls</t>
+          <t>sec_grade_7_abu_sufyan_ibn_al_harith_1st_shift_boys</t>
         </is>
       </c>
       <c r="F369" t="inlineStr">
         <is>
-          <t>GRADE 8 - SA'AD IBN MUA'DH (1ST SHIFT) - GIRLS</t>
+          <t>GRADE 7 - ABU SUFYAN IBN AL-HARITH (1ST SHIFT) BOYS</t>
         </is>
       </c>
       <c r="G369" t="inlineStr">
@@ -24744,7 +24744,7 @@
       </c>
       <c r="H369" t="inlineStr">
         <is>
-          <t>Grade 8</t>
+          <t>Grade 7</t>
         </is>
       </c>
       <c r="I369" t="inlineStr">
@@ -24754,22 +24754,22 @@
       </c>
       <c r="J369" t="inlineStr">
         <is>
-          <t>subj_arabic</t>
+          <t>subj_science</t>
         </is>
       </c>
       <c r="K369" t="inlineStr">
         <is>
-          <t>Arabic</t>
+          <t>Science</t>
         </is>
       </c>
       <c r="L369" t="inlineStr">
         <is>
-          <t>tchr_ali</t>
+          <t>tchr_aniah</t>
         </is>
       </c>
       <c r="M369" t="inlineStr">
         <is>
-          <t>Ustadh Ali</t>
+          <t>Teacher Aniah</t>
         </is>
       </c>
       <c r="N369" t="n">
@@ -24795,12 +24795,12 @@
       </c>
       <c r="E370" t="inlineStr">
         <is>
-          <t>sec_grade_9_abu_hurayrah_1st_shift_girls</t>
+          <t>sec_grade_8_sa_ad_ibn_mua_dh_1st_shift_girls</t>
         </is>
       </c>
       <c r="F370" t="inlineStr">
         <is>
-          <t>GRADE 9 - ABU HURAYRAH (1ST SHIFT) GIRLS</t>
+          <t>GRADE 8 - SA'AD IBN MUA'DH (1ST SHIFT) - GIRLS</t>
         </is>
       </c>
       <c r="G370" t="inlineStr">
@@ -24810,7 +24810,7 @@
       </c>
       <c r="H370" t="inlineStr">
         <is>
-          <t>Grade 9</t>
+          <t>Grade 8</t>
         </is>
       </c>
       <c r="I370" t="inlineStr">
@@ -24820,22 +24820,22 @@
       </c>
       <c r="J370" t="inlineStr">
         <is>
-          <t>subj_shaf</t>
+          <t>subj_arabic</t>
         </is>
       </c>
       <c r="K370" t="inlineStr">
         <is>
-          <t>SHAF</t>
+          <t>Arabic</t>
         </is>
       </c>
       <c r="L370" t="inlineStr">
         <is>
-          <t>tchr_samsuddin</t>
+          <t>tchr_ali</t>
         </is>
       </c>
       <c r="M370" t="inlineStr">
         <is>
-          <t>Alim Samsuddin</t>
+          <t>Ustadh Ali</t>
         </is>
       </c>
       <c r="N370" t="n">
@@ -24852,31 +24852,31 @@
         </is>
       </c>
       <c r="C371" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D371" t="inlineStr">
         <is>
-          <t>03:10 PM – 04:10 PM</t>
+          <t>01:50 PM – 02:50 PM</t>
         </is>
       </c>
       <c r="E371" t="inlineStr">
         <is>
-          <t>sec_grade_1_hudhayfah_ibn_al_yam_1st_shift</t>
+          <t>sec_grade_9_abu_hurayrah_1st_shift_girls</t>
         </is>
       </c>
       <c r="F371" t="inlineStr">
         <is>
-          <t>GRADE 1 - HUDHAYFAH IBN AL-YAM (1ST SHIFT)</t>
+          <t>GRADE 9 - ABU HURAYRAH (1ST SHIFT) GIRLS</t>
         </is>
       </c>
       <c r="G371" t="inlineStr">
         <is>
-          <t>Elementary</t>
+          <t>Junior High School</t>
         </is>
       </c>
       <c r="H371" t="inlineStr">
         <is>
-          <t>Grade 1</t>
+          <t>Grade 9</t>
         </is>
       </c>
       <c r="I371" t="inlineStr">
@@ -24886,22 +24886,22 @@
       </c>
       <c r="J371" t="inlineStr">
         <is>
-          <t>subj_gmrc</t>
+          <t>subj_shaf</t>
         </is>
       </c>
       <c r="K371" t="inlineStr">
         <is>
-          <t>GMRC</t>
+          <t>SHAF</t>
         </is>
       </c>
       <c r="L371" t="inlineStr">
         <is>
-          <t>tchr_sahdia</t>
+          <t>tchr_samsuddin</t>
         </is>
       </c>
       <c r="M371" t="inlineStr">
         <is>
-          <t>Teacher Sahdia</t>
+          <t>Alim Samsuddin</t>
         </is>
       </c>
       <c r="N371" t="n">
@@ -24918,7 +24918,7 @@
         </is>
       </c>
       <c r="C372" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D372" t="inlineStr">
         <is>
@@ -24927,12 +24927,12 @@
       </c>
       <c r="E372" t="inlineStr">
         <is>
-          <t>sec_grade_1_sa_ad_ibn_abi_waqqaas_2nd_shift</t>
+          <t>sec_grade_1_hudhayfah_ibn_al_yam_1st_shift</t>
         </is>
       </c>
       <c r="F372" t="inlineStr">
         <is>
-          <t>GRADE 1 - SA'AD IBN ABI WAQQAAS (2ND SHIFT)</t>
+          <t>GRADE 1 - HUDHAYFAH IBN AL-YAM (1ST SHIFT)</t>
         </is>
       </c>
       <c r="G372" t="inlineStr">
@@ -24947,27 +24947,27 @@
       </c>
       <c r="I372" t="inlineStr">
         <is>
-          <t>ODL - 2ND SHIFT</t>
+          <t>ODL - 1ST SHIFT</t>
         </is>
       </c>
       <c r="J372" t="inlineStr">
         <is>
-          <t>subj_shaf</t>
+          <t>subj_gmrc</t>
         </is>
       </c>
       <c r="K372" t="inlineStr">
         <is>
-          <t>SHAF</t>
+          <t>GMRC</t>
         </is>
       </c>
       <c r="L372" t="inlineStr">
         <is>
-          <t>tchr_abdul_karim</t>
+          <t>tchr_sahdia</t>
         </is>
       </c>
       <c r="M372" t="inlineStr">
         <is>
-          <t>Alim Abdul Karim</t>
+          <t>Teacher Sahdia</t>
         </is>
       </c>
       <c r="N372" t="n">
@@ -24993,22 +24993,22 @@
       </c>
       <c r="E373" t="inlineStr">
         <is>
-          <t>sec_grade_10_abu_ayyub_al_ansari_2nd_shift_boys</t>
+          <t>sec_grade_1_sa_ad_ibn_abi_waqqaas_2nd_shift</t>
         </is>
       </c>
       <c r="F373" t="inlineStr">
         <is>
-          <t>GRADE 10 - ABU AYYUB AL-ANSARI (2ND SHIFT) BOYS</t>
+          <t>GRADE 1 - SA'AD IBN ABI WAQQAAS (2ND SHIFT)</t>
         </is>
       </c>
       <c r="G373" t="inlineStr">
         <is>
-          <t>Junior High School</t>
+          <t>Elementary</t>
         </is>
       </c>
       <c r="H373" t="inlineStr">
         <is>
-          <t>Grade 10</t>
+          <t>Grade 1</t>
         </is>
       </c>
       <c r="I373" t="inlineStr">
@@ -25018,22 +25018,22 @@
       </c>
       <c r="J373" t="inlineStr">
         <is>
-          <t>subj_mapeh</t>
+          <t>subj_shaf</t>
         </is>
       </c>
       <c r="K373" t="inlineStr">
         <is>
-          <t>MAPEH</t>
+          <t>SHAF</t>
         </is>
       </c>
       <c r="L373" t="inlineStr">
         <is>
-          <t>tchr_mohaymen</t>
+          <t>tchr_abdul_karim</t>
         </is>
       </c>
       <c r="M373" t="inlineStr">
         <is>
-          <t>Sir Mohaymen</t>
+          <t>Alim Abdul Karim</t>
         </is>
       </c>
       <c r="N373" t="n">
@@ -25050,7 +25050,7 @@
         </is>
       </c>
       <c r="C374" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D374" t="inlineStr">
         <is>
@@ -25059,12 +25059,12 @@
       </c>
       <c r="E374" t="inlineStr">
         <is>
-          <t>sec_grade_10_utbah_ibn_ghazwan_1st_shift_girls</t>
+          <t>sec_grade_10_abu_ayyub_al_ansari_2nd_shift_boys</t>
         </is>
       </c>
       <c r="F374" t="inlineStr">
         <is>
-          <t>GRADE 10 - UTBAH IBN GHAZWAN (1ST SHIFT) GIRLS</t>
+          <t>GRADE 10 - ABU AYYUB AL-ANSARI (2ND SHIFT) BOYS</t>
         </is>
       </c>
       <c r="G374" t="inlineStr">
@@ -25079,27 +25079,27 @@
       </c>
       <c r="I374" t="inlineStr">
         <is>
-          <t>ODL - 1ST SHIFT</t>
+          <t>ODL - 2ND SHIFT</t>
         </is>
       </c>
       <c r="J374" t="inlineStr">
         <is>
-          <t>subj_arabic</t>
+          <t>subj_mapeh</t>
         </is>
       </c>
       <c r="K374" t="inlineStr">
         <is>
-          <t>Arabic</t>
+          <t>MAPEH</t>
         </is>
       </c>
       <c r="L374" t="inlineStr">
         <is>
-          <t>tchr_mamonas</t>
+          <t>tchr_mohaymen</t>
         </is>
       </c>
       <c r="M374" t="inlineStr">
         <is>
-          <t>Alim Mamonas</t>
+          <t>Sir Mohaymen</t>
         </is>
       </c>
       <c r="N374" t="n">
@@ -25125,22 +25125,22 @@
       </c>
       <c r="E375" t="inlineStr">
         <is>
-          <t>sec_grade_11_1st_shift_girls</t>
+          <t>sec_grade_10_utbah_ibn_ghazwan_1st_shift_girls</t>
         </is>
       </c>
       <c r="F375" t="inlineStr">
         <is>
-          <t>GRADE 11 (1ST SHIFT GIRLS)</t>
+          <t>GRADE 10 - UTBAH IBN GHAZWAN (1ST SHIFT) GIRLS</t>
         </is>
       </c>
       <c r="G375" t="inlineStr">
         <is>
-          <t>Senior High School</t>
+          <t>Junior High School</t>
         </is>
       </c>
       <c r="H375" t="inlineStr">
         <is>
-          <t>Grade 11</t>
+          <t>Grade 10</t>
         </is>
       </c>
       <c r="I375" t="inlineStr">
@@ -25150,22 +25150,22 @@
       </c>
       <c r="J375" t="inlineStr">
         <is>
-          <t>subj_mabisang_komunikasyon</t>
+          <t>subj_arabic</t>
         </is>
       </c>
       <c r="K375" t="inlineStr">
         <is>
-          <t>Mabisang Komunikasyon</t>
+          <t>Arabic</t>
         </is>
       </c>
       <c r="L375" t="inlineStr">
         <is>
-          <t>tchr_nadzra</t>
+          <t>tchr_mamonas</t>
         </is>
       </c>
       <c r="M375" t="inlineStr">
         <is>
-          <t>Teacher Nadzra</t>
+          <t>Alim Mamonas</t>
         </is>
       </c>
       <c r="N375" t="n">

--- a/Term_Examination_Schedule_S.Y._2026-2027_Optimized.xlsx
+++ b/Term_Examination_Schedule_S.Y._2026-2027_Optimized.xlsx
@@ -22322,12 +22322,12 @@
       </c>
       <c r="L332" t="inlineStr">
         <is>
-          <t>tchr_hainur</t>
+          <t>tchr_mamonas</t>
         </is>
       </c>
       <c r="M332" t="inlineStr">
         <is>
-          <t>Ustadha Hainur</t>
+          <t>Alim Mamonas</t>
         </is>
       </c>
       <c r="N332" t="n">
@@ -23642,12 +23642,12 @@
       </c>
       <c r="L352" t="inlineStr">
         <is>
-          <t>tchr_raslina</t>
+          <t>tchr_hainur</t>
         </is>
       </c>
       <c r="M352" t="inlineStr">
         <is>
-          <t>Ustadh Raslina</t>
+          <t>Ustadha Hainur</t>
         </is>
       </c>
       <c r="N352" t="n">

--- a/Term_Examination_Schedule_S.Y._2026-2027_Optimized.xlsx
+++ b/Term_Examination_Schedule_S.Y._2026-2027_Optimized.xlsx
@@ -8990,12 +8990,12 @@
       </c>
       <c r="L130" t="inlineStr">
         <is>
-          <t>tchr_keychell</t>
+          <t>tchr_sitti_kauzar</t>
         </is>
       </c>
       <c r="M130" t="inlineStr">
         <is>
-          <t>Teacher Keychelle</t>
+          <t>Teacher Sitti Kauzar</t>
         </is>
       </c>
       <c r="N130" t="n">

--- a/Term_Examination_Schedule_S.Y._2026-2027_Optimized.xlsx
+++ b/Term_Examination_Schedule_S.Y._2026-2027_Optimized.xlsx
@@ -6229,12 +6229,12 @@
       </c>
       <c r="P64" t="inlineStr">
         <is>
-          <t>tchr_franchette</t>
+          <t>tchr_wardah</t>
         </is>
       </c>
       <c r="Q64" t="inlineStr">
         <is>
-          <t>Teacher Franchette</t>
+          <t>Teacher Wardah</t>
         </is>
       </c>
       <c r="R64" t="inlineStr">
@@ -39899,12 +39899,12 @@
       </c>
       <c r="P434" t="inlineStr">
         <is>
-          <t>tchr_ayah</t>
+          <t>tchr_wardah</t>
         </is>
       </c>
       <c r="Q434" t="inlineStr">
         <is>
-          <t>Teacher Ayah</t>
+          <t>Teacher Wardah</t>
         </is>
       </c>
       <c r="R434" t="inlineStr">
@@ -45086,12 +45086,12 @@
       </c>
       <c r="P491" t="inlineStr">
         <is>
-          <t>tchr_zara</t>
+          <t>tchr_wardah</t>
         </is>
       </c>
       <c r="Q491" t="inlineStr">
         <is>
-          <t>Teacher Zara</t>
+          <t>Teacher Wardah</t>
         </is>
       </c>
       <c r="R491" t="inlineStr">

--- a/Term_Examination_Schedule_S.Y._2026-2027_Optimized.xlsx
+++ b/Term_Examination_Schedule_S.Y._2026-2027_Optimized.xlsx
@@ -6229,12 +6229,12 @@
       </c>
       <c r="P64" t="inlineStr">
         <is>
-          <t>tchr_wardah</t>
+          <t>tchr_franchette</t>
         </is>
       </c>
       <c r="Q64" t="inlineStr">
         <is>
-          <t>Teacher Wardah</t>
+          <t>Teacher Franchette</t>
         </is>
       </c>
       <c r="R64" t="inlineStr">
@@ -39899,12 +39899,12 @@
       </c>
       <c r="P434" t="inlineStr">
         <is>
-          <t>tchr_wardah</t>
+          <t>tchr_ayah</t>
         </is>
       </c>
       <c r="Q434" t="inlineStr">
         <is>
-          <t>Teacher Wardah</t>
+          <t>Teacher Ayah</t>
         </is>
       </c>
       <c r="R434" t="inlineStr">
@@ -45086,12 +45086,12 @@
       </c>
       <c r="P491" t="inlineStr">
         <is>
-          <t>tchr_wardah</t>
+          <t>tchr_zara</t>
         </is>
       </c>
       <c r="Q491" t="inlineStr">
         <is>
-          <t>Teacher Wardah</t>
+          <t>Teacher Zara</t>
         </is>
       </c>
       <c r="R491" t="inlineStr">

--- a/Term_Examination_Schedule_S.Y._2026-2027_Optimized.xlsx
+++ b/Term_Examination_Schedule_S.Y._2026-2027_Optimized.xlsx
@@ -9505,12 +9505,12 @@
       </c>
       <c r="P100" t="inlineStr">
         <is>
-          <t>tchr_junaisah</t>
+          <t>tchr_ayah</t>
         </is>
       </c>
       <c r="Q100" t="inlineStr">
         <is>
-          <t>Teacher Junaisah</t>
+          <t>Teacher Ayah</t>
         </is>
       </c>
       <c r="R100" t="inlineStr">
@@ -25157,12 +25157,12 @@
       </c>
       <c r="P272" t="inlineStr">
         <is>
-          <t>tchr_junaisah</t>
+          <t>tchr_franchette</t>
         </is>
       </c>
       <c r="Q272" t="inlineStr">
         <is>
-          <t>Teacher Junaisah</t>
+          <t>Teacher Franchette</t>
         </is>
       </c>
       <c r="R272" t="inlineStr">
@@ -27250,12 +27250,12 @@
       </c>
       <c r="P295" t="inlineStr">
         <is>
-          <t>tchr_ayah</t>
+          <t>tchr_junaisah</t>
         </is>
       </c>
       <c r="Q295" t="inlineStr">
         <is>
-          <t>Teacher Ayah</t>
+          <t>Teacher Junaisah</t>
         </is>
       </c>
       <c r="R295" t="inlineStr">
@@ -28797,12 +28797,12 @@
       </c>
       <c r="P312" t="inlineStr">
         <is>
-          <t>tchr_ayah</t>
+          <t>tchr_zuhora</t>
         </is>
       </c>
       <c r="Q312" t="inlineStr">
         <is>
-          <t>Teacher Ayah</t>
+          <t>Teacher Zuhora</t>
         </is>
       </c>
       <c r="R312" t="inlineStr">
@@ -39899,12 +39899,12 @@
       </c>
       <c r="P434" t="inlineStr">
         <is>
-          <t>tchr_ayah</t>
+          <t>tchr_mohaymen</t>
         </is>
       </c>
       <c r="Q434" t="inlineStr">
         <is>
-          <t>Teacher Ayah</t>
+          <t>Sir Mohaymen</t>
         </is>
       </c>
       <c r="R434" t="inlineStr">
@@ -51638,12 +51638,12 @@
       </c>
       <c r="P563" t="inlineStr">
         <is>
-          <t>tchr_junaisah</t>
+          <t>tchr_mohaymen</t>
         </is>
       </c>
       <c r="Q563" t="inlineStr">
         <is>
-          <t>Teacher Junaisah</t>
+          <t>Sir Mohaymen</t>
         </is>
       </c>
       <c r="R563" t="inlineStr">
@@ -53640,12 +53640,12 @@
       </c>
       <c r="P585" t="inlineStr">
         <is>
-          <t>tchr_keychell</t>
+          <t>tchr_zuhora</t>
         </is>
       </c>
       <c r="Q585" t="inlineStr">
         <is>
-          <t>Teacher Keychelle</t>
+          <t>Teacher Zuhora</t>
         </is>
       </c>
       <c r="R585" t="inlineStr">

--- a/Term_Examination_Schedule_S.Y._2026-2027_Optimized.xlsx
+++ b/Term_Examination_Schedule_S.Y._2026-2027_Optimized.xlsx
@@ -1042,12 +1042,12 @@
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>tchr_ayah</t>
+          <t>tchr_wardah</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>Teacher Ayah</t>
+          <t>Teacher Wardah</t>
         </is>
       </c>
       <c r="R7" t="inlineStr">
@@ -9505,12 +9505,12 @@
       </c>
       <c r="P100" t="inlineStr">
         <is>
-          <t>tchr_ayah</t>
+          <t>tchr_wardah</t>
         </is>
       </c>
       <c r="Q100" t="inlineStr">
         <is>
-          <t>Teacher Ayah</t>
+          <t>Teacher Wardah</t>
         </is>
       </c>
       <c r="R100" t="inlineStr">

--- a/Term_Examination_Schedule_S.Y._2026-2027_Optimized.xlsx
+++ b/Term_Examination_Schedule_S.Y._2026-2027_Optimized.xlsx
@@ -6229,12 +6229,12 @@
       </c>
       <c r="P64" t="inlineStr">
         <is>
-          <t>tchr_franchette</t>
+          <t>tchr_rowena</t>
         </is>
       </c>
       <c r="Q64" t="inlineStr">
         <is>
-          <t>Teacher Franchette</t>
+          <t>Teacher Rowena</t>
         </is>
       </c>
       <c r="R64" t="inlineStr">
@@ -15769,7 +15769,7 @@
       </c>
       <c r="M169" t="inlineStr">
         <is>
-          <t>Teacher Franchette</t>
+          <t>Teacher Franchette Zarah M. Ranain</t>
         </is>
       </c>
       <c r="N169" t="inlineStr">
@@ -15789,7 +15789,7 @@
       </c>
       <c r="Q169" t="inlineStr">
         <is>
-          <t>Teacher Franchette</t>
+          <t>Teacher Franchette Zarah M. Ranain</t>
         </is>
       </c>
       <c r="R169" t="inlineStr">
@@ -18590,7 +18590,7 @@
       </c>
       <c r="M200" t="inlineStr">
         <is>
-          <t>Teacher Franchette</t>
+          <t>Teacher Franchette Zarah M. Ranain</t>
         </is>
       </c>
       <c r="N200" t="inlineStr">
@@ -18610,7 +18610,7 @@
       </c>
       <c r="Q200" t="inlineStr">
         <is>
-          <t>Teacher Franchette</t>
+          <t>Teacher Franchette Zarah M. Ranain</t>
         </is>
       </c>
       <c r="R200" t="inlineStr">
@@ -19591,7 +19591,7 @@
       </c>
       <c r="M211" t="inlineStr">
         <is>
-          <t>Teacher Zara</t>
+          <t>Teacher Franchette Zarah M. Ranain</t>
         </is>
       </c>
       <c r="N211" t="inlineStr">
@@ -19606,12 +19606,12 @@
       </c>
       <c r="P211" t="inlineStr">
         <is>
-          <t>tchr_zara</t>
+          <t>tchr_keychell</t>
         </is>
       </c>
       <c r="Q211" t="inlineStr">
         <is>
-          <t>Teacher Zara</t>
+          <t>Teacher Keychelle</t>
         </is>
       </c>
       <c r="R211" t="inlineStr">
@@ -20592,7 +20592,7 @@
       </c>
       <c r="M222" t="inlineStr">
         <is>
-          <t>Teacher Franchette</t>
+          <t>Teacher Franchette Zarah M. Ranain</t>
         </is>
       </c>
       <c r="N222" t="inlineStr">
@@ -20612,7 +20612,7 @@
       </c>
       <c r="Q222" t="inlineStr">
         <is>
-          <t>Teacher Franchette</t>
+          <t>Teacher Franchette Zarah M. Ranain</t>
         </is>
       </c>
       <c r="R222" t="inlineStr">
@@ -25157,12 +25157,12 @@
       </c>
       <c r="P272" t="inlineStr">
         <is>
-          <t>tchr_franchette</t>
+          <t>tchr_junaisah</t>
         </is>
       </c>
       <c r="Q272" t="inlineStr">
         <is>
-          <t>Teacher Franchette</t>
+          <t>Teacher Junaisah</t>
         </is>
       </c>
       <c r="R272" t="inlineStr">
@@ -28327,7 +28327,7 @@
       </c>
       <c r="M307" t="inlineStr">
         <is>
-          <t>Teacher Franchette</t>
+          <t>Teacher Franchette Zarah M. Ranain</t>
         </is>
       </c>
       <c r="N307" t="inlineStr">
@@ -28347,7 +28347,7 @@
       </c>
       <c r="Q307" t="inlineStr">
         <is>
-          <t>Teacher Franchette</t>
+          <t>Teacher Franchette Zarah M. Ranain</t>
         </is>
       </c>
       <c r="R307" t="inlineStr">
@@ -31345,12 +31345,12 @@
       </c>
       <c r="P340" t="inlineStr">
         <is>
-          <t>tchr_zara</t>
+          <t>tchr_rowena</t>
         </is>
       </c>
       <c r="Q340" t="inlineStr">
         <is>
-          <t>Teacher Zara</t>
+          <t>Teacher Rowena</t>
         </is>
       </c>
       <c r="R340" t="inlineStr">
@@ -34879,7 +34879,7 @@
       </c>
       <c r="M379" t="inlineStr">
         <is>
-          <t>Teacher Zara</t>
+          <t>Teacher Franchette Zarah M. Ranain</t>
         </is>
       </c>
       <c r="N379" t="inlineStr">
@@ -34894,12 +34894,12 @@
       </c>
       <c r="P379" t="inlineStr">
         <is>
-          <t>tchr_zara</t>
+          <t>tchr_franchette</t>
         </is>
       </c>
       <c r="Q379" t="inlineStr">
         <is>
-          <t>Teacher Zara</t>
+          <t>Teacher Franchette Zarah M. Ranain</t>
         </is>
       </c>
       <c r="R379" t="inlineStr">
@@ -35076,12 +35076,12 @@
       </c>
       <c r="P381" t="inlineStr">
         <is>
-          <t>tchr_junaisah</t>
+          <t>tchr_wendy</t>
         </is>
       </c>
       <c r="Q381" t="inlineStr">
         <is>
-          <t>Teacher Junaisah</t>
+          <t>Teacher Wendy</t>
         </is>
       </c>
       <c r="R381" t="inlineStr">
@@ -40521,7 +40521,7 @@
       </c>
       <c r="M441" t="inlineStr">
         <is>
-          <t>Teacher Franchette</t>
+          <t>Teacher Franchette Zarah M. Ranain</t>
         </is>
       </c>
       <c r="N441" t="inlineStr">
@@ -40541,7 +40541,7 @@
       </c>
       <c r="Q441" t="inlineStr">
         <is>
-          <t>Teacher Franchette</t>
+          <t>Teacher Franchette Zarah M. Ranain</t>
         </is>
       </c>
       <c r="R441" t="inlineStr">
@@ -45086,12 +45086,12 @@
       </c>
       <c r="P491" t="inlineStr">
         <is>
-          <t>tchr_zara</t>
+          <t>tchr_norhaima</t>
         </is>
       </c>
       <c r="Q491" t="inlineStr">
         <is>
-          <t>Teacher Zara</t>
+          <t>Teacher Norhaima</t>
         </is>
       </c>
       <c r="R491" t="inlineStr">
@@ -48347,7 +48347,7 @@
       </c>
       <c r="M527" t="inlineStr">
         <is>
-          <t>Teacher Zara</t>
+          <t>Teacher Franchette Zarah M. Ranain</t>
         </is>
       </c>
       <c r="N527" t="inlineStr">
@@ -48362,12 +48362,12 @@
       </c>
       <c r="P527" t="inlineStr">
         <is>
-          <t>tchr_zara</t>
+          <t>tchr_ayah</t>
         </is>
       </c>
       <c r="Q527" t="inlineStr">
         <is>
-          <t>Teacher Zara</t>
+          <t>Teacher Ayah</t>
         </is>
       </c>
       <c r="R527" t="inlineStr">
@@ -49621,7 +49621,7 @@
       </c>
       <c r="M541" t="inlineStr">
         <is>
-          <t>Teacher Franchette</t>
+          <t>Teacher Franchette Zarah M. Ranain</t>
         </is>
       </c>
       <c r="N541" t="inlineStr">
@@ -49641,7 +49641,7 @@
       </c>
       <c r="Q541" t="inlineStr">
         <is>
-          <t>Teacher Franchette</t>
+          <t>Teacher Franchette Zarah M. Ranain</t>
         </is>
       </c>
       <c r="R541" t="inlineStr">
@@ -51896,7 +51896,7 @@
       </c>
       <c r="M566" t="inlineStr">
         <is>
-          <t>Teacher Franchette</t>
+          <t>Teacher Franchette Zarah M. Ranain</t>
         </is>
       </c>
       <c r="N566" t="inlineStr">
@@ -51916,7 +51916,7 @@
       </c>
       <c r="Q566" t="inlineStr">
         <is>
-          <t>Teacher Franchette</t>
+          <t>Teacher Franchette Zarah M. Ranain</t>
         </is>
       </c>
       <c r="R566" t="inlineStr">
@@ -52988,7 +52988,7 @@
       </c>
       <c r="M578" t="inlineStr">
         <is>
-          <t>Teacher Zara</t>
+          <t>Teacher Franchette Zarah M. Ranain</t>
         </is>
       </c>
       <c r="N578" t="inlineStr">
@@ -53003,12 +53003,12 @@
       </c>
       <c r="P578" t="inlineStr">
         <is>
-          <t>tchr_zara</t>
+          <t>tchr_junaisah</t>
         </is>
       </c>
       <c r="Q578" t="inlineStr">
         <is>
-          <t>Teacher Zara</t>
+          <t>Teacher Junaisah</t>
         </is>
       </c>
       <c r="R578" t="inlineStr">
@@ -53898,7 +53898,7 @@
       </c>
       <c r="M588" t="inlineStr">
         <is>
-          <t>Teacher Franchette</t>
+          <t>Teacher Franchette Zarah M. Ranain</t>
         </is>
       </c>
       <c r="N588" t="inlineStr">
@@ -53918,7 +53918,7 @@
       </c>
       <c r="Q588" t="inlineStr">
         <is>
-          <t>Teacher Franchette</t>
+          <t>Teacher Franchette Zarah M. Ranain</t>
         </is>
       </c>
       <c r="R588" t="inlineStr">

--- a/Term_Examination_Schedule_S.Y._2026-2027_Optimized.xlsx
+++ b/Term_Examination_Schedule_S.Y._2026-2027_Optimized.xlsx
@@ -19606,12 +19606,12 @@
       </c>
       <c r="P211" t="inlineStr">
         <is>
-          <t>tchr_keychell</t>
+          <t>tchr_junaisah</t>
         </is>
       </c>
       <c r="Q211" t="inlineStr">
         <is>
-          <t>Teacher Keychelle</t>
+          <t>Teacher Junaisah</t>
         </is>
       </c>
       <c r="R211" t="inlineStr">
@@ -48362,12 +48362,12 @@
       </c>
       <c r="P527" t="inlineStr">
         <is>
-          <t>tchr_ayah</t>
+          <t>tchr_junaisah</t>
         </is>
       </c>
       <c r="Q527" t="inlineStr">
         <is>
-          <t>Teacher Ayah</t>
+          <t>Teacher Junaisah</t>
         </is>
       </c>
       <c r="R527" t="inlineStr">

--- a/Term_Examination_Schedule_S.Y._2026-2027_Optimized.xlsx
+++ b/Term_Examination_Schedule_S.Y._2026-2027_Optimized.xlsx
@@ -25157,12 +25157,12 @@
       </c>
       <c r="P272" t="inlineStr">
         <is>
-          <t>tchr_junaisah</t>
+          <t>tchr_franchette</t>
         </is>
       </c>
       <c r="Q272" t="inlineStr">
         <is>
-          <t>Teacher Junaisah</t>
+          <t>Teacher Franchette Zarah M. Ranain</t>
         </is>
       </c>
       <c r="R272" t="inlineStr">
@@ -27250,12 +27250,12 @@
       </c>
       <c r="P295" t="inlineStr">
         <is>
-          <t>tchr_junaisah</t>
+          <t>tchr_franchette</t>
         </is>
       </c>
       <c r="Q295" t="inlineStr">
         <is>
-          <t>Teacher Junaisah</t>
+          <t>Teacher Franchette Zarah M. Ranain</t>
         </is>
       </c>
       <c r="R295" t="inlineStr">
@@ -39899,12 +39899,12 @@
       </c>
       <c r="P434" t="inlineStr">
         <is>
-          <t>tchr_mohaymen</t>
+          <t>tchr_junaisah</t>
         </is>
       </c>
       <c r="Q434" t="inlineStr">
         <is>
-          <t>Sir Mohaymen</t>
+          <t>Teacher Junaisah</t>
         </is>
       </c>
       <c r="R434" t="inlineStr">
@@ -51638,12 +51638,12 @@
       </c>
       <c r="P563" t="inlineStr">
         <is>
-          <t>tchr_mohaymen</t>
+          <t>tchr_junaisah</t>
         </is>
       </c>
       <c r="Q563" t="inlineStr">
         <is>
-          <t>Sir Mohaymen</t>
+          <t>Teacher Junaisah</t>
         </is>
       </c>
       <c r="R563" t="inlineStr">

--- a/Term_Examination_Schedule_S.Y._2026-2027_Optimized.xlsx
+++ b/Term_Examination_Schedule_S.Y._2026-2027_Optimized.xlsx
@@ -1042,12 +1042,12 @@
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>tchr_wardah</t>
+          <t>tchr_zuhora</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>Teacher Wardah</t>
+          <t>Teacher Zuhora</t>
         </is>
       </c>
       <c r="R7" t="inlineStr">
@@ -6229,12 +6229,12 @@
       </c>
       <c r="P64" t="inlineStr">
         <is>
-          <t>tchr_rowena</t>
+          <t>tchr_wardah</t>
         </is>
       </c>
       <c r="Q64" t="inlineStr">
         <is>
-          <t>Teacher Rowena</t>
+          <t>Teacher Wardah</t>
         </is>
       </c>
       <c r="R64" t="inlineStr">
@@ -9505,12 +9505,12 @@
       </c>
       <c r="P100" t="inlineStr">
         <is>
-          <t>tchr_wardah</t>
+          <t>tchr_junaisah</t>
         </is>
       </c>
       <c r="Q100" t="inlineStr">
         <is>
-          <t>Teacher Wardah</t>
+          <t>Teacher Junaisah</t>
         </is>
       </c>
       <c r="R100" t="inlineStr">
@@ -31345,12 +31345,12 @@
       </c>
       <c r="P340" t="inlineStr">
         <is>
-          <t>tchr_rowena</t>
+          <t>tchr_wardah</t>
         </is>
       </c>
       <c r="Q340" t="inlineStr">
         <is>
-          <t>Teacher Rowena</t>
+          <t>Teacher Wardah</t>
         </is>
       </c>
       <c r="R340" t="inlineStr">
@@ -35076,12 +35076,12 @@
       </c>
       <c r="P381" t="inlineStr">
         <is>
-          <t>tchr_wendy</t>
+          <t>tchr_junaisah</t>
         </is>
       </c>
       <c r="Q381" t="inlineStr">
         <is>
-          <t>Teacher Wendy</t>
+          <t>Teacher Junaisah</t>
         </is>
       </c>
       <c r="R381" t="inlineStr">
@@ -39899,12 +39899,12 @@
       </c>
       <c r="P434" t="inlineStr">
         <is>
-          <t>tchr_junaisah</t>
+          <t>tchr_shirehan</t>
         </is>
       </c>
       <c r="Q434" t="inlineStr">
         <is>
-          <t>Teacher Junaisah</t>
+          <t>Teacher Shirehan</t>
         </is>
       </c>
       <c r="R434" t="inlineStr">
@@ -45086,12 +45086,12 @@
       </c>
       <c r="P491" t="inlineStr">
         <is>
-          <t>tchr_norhaima</t>
+          <t>tchr_shirehan</t>
         </is>
       </c>
       <c r="Q491" t="inlineStr">
         <is>
-          <t>Teacher Norhaima</t>
+          <t>Teacher Shirehan</t>
         </is>
       </c>
       <c r="R491" t="inlineStr">
@@ -51638,12 +51638,12 @@
       </c>
       <c r="P563" t="inlineStr">
         <is>
-          <t>tchr_junaisah</t>
+          <t>tchr_mohaymen</t>
         </is>
       </c>
       <c r="Q563" t="inlineStr">
         <is>
-          <t>Teacher Junaisah</t>
+          <t>Sir Mohaymen</t>
         </is>
       </c>
       <c r="R563" t="inlineStr">
@@ -53640,12 +53640,12 @@
       </c>
       <c r="P585" t="inlineStr">
         <is>
-          <t>tchr_zuhora</t>
+          <t>tchr_mohaymen</t>
         </is>
       </c>
       <c r="Q585" t="inlineStr">
         <is>
-          <t>Teacher Zuhora</t>
+          <t>Sir Mohaymen</t>
         </is>
       </c>
       <c r="R585" t="inlineStr">

--- a/Term_Examination_Schedule_S.Y._2026-2027_Optimized.xlsx
+++ b/Term_Examination_Schedule_S.Y._2026-2027_Optimized.xlsx
@@ -6290,12 +6290,12 @@
       </c>
       <c r="J65" t="inlineStr">
         <is>
-          <t>subj_fil</t>
+          <t>subj_filipino</t>
         </is>
       </c>
       <c r="K65" t="inlineStr">
         <is>
-          <t>FIL</t>
+          <t>Filipino</t>
         </is>
       </c>
       <c r="L65" t="inlineStr">
@@ -9384,12 +9384,12 @@
       </c>
       <c r="J99" t="inlineStr">
         <is>
-          <t>subj_fil</t>
+          <t>subj_filipino</t>
         </is>
       </c>
       <c r="K99" t="inlineStr">
         <is>
-          <t>Fil</t>
+          <t>Filipino</t>
         </is>
       </c>
       <c r="L99" t="inlineStr">
@@ -17847,12 +17847,12 @@
       </c>
       <c r="J192" t="inlineStr">
         <is>
-          <t>subj_fil</t>
+          <t>subj_filipino</t>
         </is>
       </c>
       <c r="K192" t="inlineStr">
         <is>
-          <t>FIL</t>
+          <t>Filipino</t>
         </is>
       </c>
       <c r="L192" t="inlineStr">
@@ -19940,12 +19940,12 @@
       </c>
       <c r="J215" t="inlineStr">
         <is>
-          <t>subj_fil5</t>
+          <t>subj_filipino</t>
         </is>
       </c>
       <c r="K215" t="inlineStr">
         <is>
-          <t>Fil5</t>
+          <t>Filipino</t>
         </is>
       </c>
       <c r="L215" t="inlineStr">
@@ -21760,12 +21760,12 @@
       </c>
       <c r="J235" t="inlineStr">
         <is>
-          <t>subj_fil3</t>
+          <t>subj_filipino</t>
         </is>
       </c>
       <c r="K235" t="inlineStr">
         <is>
-          <t>Fil3</t>
+          <t>Filipino</t>
         </is>
       </c>
       <c r="L235" t="inlineStr">
@@ -25127,12 +25127,12 @@
       </c>
       <c r="J272" t="inlineStr">
         <is>
-          <t>subj_fil</t>
+          <t>subj_filipino</t>
         </is>
       </c>
       <c r="K272" t="inlineStr">
         <is>
-          <t>Fil</t>
+          <t>Filipino</t>
         </is>
       </c>
       <c r="L272" t="inlineStr">
@@ -35501,12 +35501,12 @@
       </c>
       <c r="J386" t="inlineStr">
         <is>
-          <t>subj_fil4</t>
+          <t>subj_filipino</t>
         </is>
       </c>
       <c r="K386" t="inlineStr">
         <is>
-          <t>Fil4</t>
+          <t>Filipino</t>
         </is>
       </c>
       <c r="L386" t="inlineStr">
@@ -46876,12 +46876,12 @@
       </c>
       <c r="J511" t="inlineStr">
         <is>
-          <t>subj_fil</t>
+          <t>subj_filipino</t>
         </is>
       </c>
       <c r="K511" t="inlineStr">
         <is>
-          <t>Fil</t>
+          <t>Filipino</t>
         </is>
       </c>
       <c r="L511" t="inlineStr">

--- a/Term_Examination_Schedule_S.Y._2026-2027_Optimized.xlsx
+++ b/Term_Examination_Schedule_S.Y._2026-2027_Optimized.xlsx
@@ -19606,12 +19606,12 @@
       </c>
       <c r="P211" t="inlineStr">
         <is>
-          <t>tchr_junaisah</t>
+          <t>tchr_keychell</t>
         </is>
       </c>
       <c r="Q211" t="inlineStr">
         <is>
-          <t>Teacher Junaisah</t>
+          <t>Teacher Keychelle</t>
         </is>
       </c>
       <c r="R211" t="inlineStr">
@@ -48362,12 +48362,12 @@
       </c>
       <c r="P527" t="inlineStr">
         <is>
-          <t>tchr_junaisah</t>
+          <t>tchr_wendy</t>
         </is>
       </c>
       <c r="Q527" t="inlineStr">
         <is>
-          <t>Teacher Junaisah</t>
+          <t>Teacher Wendy</t>
         </is>
       </c>
       <c r="R527" t="inlineStr">
@@ -53003,12 +53003,12 @@
       </c>
       <c r="P578" t="inlineStr">
         <is>
-          <t>tchr_junaisah</t>
+          <t>tchr_ethel</t>
         </is>
       </c>
       <c r="Q578" t="inlineStr">
         <is>
-          <t>Teacher Junaisah</t>
+          <t>Teacher Ethel</t>
         </is>
       </c>
       <c r="R578" t="inlineStr">

--- a/Term_Examination_Schedule_S.Y._2026-2027_Optimized.xlsx
+++ b/Term_Examination_Schedule_S.Y._2026-2027_Optimized.xlsx
@@ -4296,34 +4296,30 @@
           <t>Makabansa</t>
         </is>
       </c>
-      <c r="L43" t="inlineStr">
-        <is>
-          <t>tchr_franchette</t>
-        </is>
-      </c>
+      <c r="L43" t="inlineStr"/>
       <c r="M43" t="inlineStr">
         <is>
-          <t>Teacher Franchette Zarah M. Ranain</t>
+          <t>Unassigned</t>
         </is>
       </c>
       <c r="N43" t="inlineStr">
         <is>
-          <t>ACTIVE_VERIFIED</t>
+          <t>VACANT_REPLACEMENT_REQUIRED</t>
         </is>
       </c>
       <c r="O43" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>YES</t>
         </is>
       </c>
       <c r="P43" t="inlineStr">
         <is>
-          <t>tchr_franchette</t>
+          <t>tchr_ethel</t>
         </is>
       </c>
       <c r="Q43" t="inlineStr">
         <is>
-          <t>Teacher Franchette Zarah M. Ranain</t>
+          <t>Teacher Ethel</t>
         </is>
       </c>
       <c r="R43" t="inlineStr">
@@ -9756,34 +9752,30 @@
           <t>MAPEH</t>
         </is>
       </c>
-      <c r="L103" t="inlineStr">
-        <is>
-          <t>tchr_franchette</t>
-        </is>
-      </c>
+      <c r="L103" t="inlineStr"/>
       <c r="M103" t="inlineStr">
         <is>
-          <t>Teacher Franchette Zarah M. Ranain</t>
+          <t>Unassigned</t>
         </is>
       </c>
       <c r="N103" t="inlineStr">
         <is>
-          <t>ACTIVE_VERIFIED</t>
+          <t>VACANT_REPLACEMENT_REQUIRED</t>
         </is>
       </c>
       <c r="O103" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>YES</t>
         </is>
       </c>
       <c r="P103" t="inlineStr">
         <is>
-          <t>tchr_franchette</t>
+          <t>tchr_ethel</t>
         </is>
       </c>
       <c r="Q103" t="inlineStr">
         <is>
-          <t>Teacher Franchette Zarah M. Ranain</t>
+          <t>Teacher Ethel</t>
         </is>
       </c>
       <c r="R103" t="inlineStr">
@@ -11121,24 +11113,20 @@
           <t>Makabansa</t>
         </is>
       </c>
-      <c r="L118" t="inlineStr">
-        <is>
-          <t>tchr_franchette</t>
-        </is>
-      </c>
+      <c r="L118" t="inlineStr"/>
       <c r="M118" t="inlineStr">
         <is>
-          <t>Teacher Franchette Zarah M. Ranain</t>
+          <t>Unassigned</t>
         </is>
       </c>
       <c r="N118" t="inlineStr">
         <is>
-          <t>ACTIVE_VERIFIED</t>
+          <t>VACANT_REPLACEMENT_REQUIRED</t>
         </is>
       </c>
       <c r="O118" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>YES</t>
         </is>
       </c>
       <c r="P118" t="inlineStr">
@@ -19857,24 +19845,20 @@
           <t>Makabansa</t>
         </is>
       </c>
-      <c r="L214" t="inlineStr">
-        <is>
-          <t>tchr_franchette</t>
-        </is>
-      </c>
+      <c r="L214" t="inlineStr"/>
       <c r="M214" t="inlineStr">
         <is>
-          <t>Teacher Franchette Zarah M. Ranain</t>
+          <t>Unassigned</t>
         </is>
       </c>
       <c r="N214" t="inlineStr">
         <is>
-          <t>ACTIVE_VERIFIED</t>
+          <t>VACANT_REPLACEMENT_REQUIRED</t>
         </is>
       </c>
       <c r="O214" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>YES</t>
         </is>
       </c>
       <c r="P214" t="inlineStr">
@@ -30140,34 +30124,30 @@
           <t>MAPEH</t>
         </is>
       </c>
-      <c r="L327" t="inlineStr">
-        <is>
-          <t>tchr_franchette</t>
-        </is>
-      </c>
+      <c r="L327" t="inlineStr"/>
       <c r="M327" t="inlineStr">
         <is>
-          <t>Teacher Franchette Zarah M. Ranain</t>
+          <t>Unassigned</t>
         </is>
       </c>
       <c r="N327" t="inlineStr">
         <is>
-          <t>ACTIVE_VERIFIED</t>
+          <t>VACANT_REPLACEMENT_REQUIRED</t>
         </is>
       </c>
       <c r="O327" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>YES</t>
         </is>
       </c>
       <c r="P327" t="inlineStr">
         <is>
-          <t>tchr_franchette</t>
+          <t>tchr_radzmia</t>
         </is>
       </c>
       <c r="Q327" t="inlineStr">
         <is>
-          <t>Teacher Franchette Zarah M. Ranain</t>
+          <t>Teacher Radzmia</t>
         </is>
       </c>
       <c r="R327" t="inlineStr">
@@ -34326,34 +34306,30 @@
           <t>MAPEH</t>
         </is>
       </c>
-      <c r="L373" t="inlineStr">
-        <is>
-          <t>tchr_franchette</t>
-        </is>
-      </c>
+      <c r="L373" t="inlineStr"/>
       <c r="M373" t="inlineStr">
         <is>
-          <t>Teacher Franchette Zarah M. Ranain</t>
+          <t>Unassigned</t>
         </is>
       </c>
       <c r="N373" t="inlineStr">
         <is>
-          <t>ACTIVE_VERIFIED</t>
+          <t>VACANT_REPLACEMENT_REQUIRED</t>
         </is>
       </c>
       <c r="O373" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>YES</t>
         </is>
       </c>
       <c r="P373" t="inlineStr">
         <is>
-          <t>tchr_franchette</t>
+          <t>tchr_mohaymen</t>
         </is>
       </c>
       <c r="Q373" t="inlineStr">
         <is>
-          <t>Teacher Franchette Zarah M. Ranain</t>
+          <t>Sir Mohaymen</t>
         </is>
       </c>
       <c r="R373" t="inlineStr">
@@ -36510,34 +36486,30 @@
           <t>MAPEH</t>
         </is>
       </c>
-      <c r="L397" t="inlineStr">
-        <is>
-          <t>tchr_franchette</t>
-        </is>
-      </c>
+      <c r="L397" t="inlineStr"/>
       <c r="M397" t="inlineStr">
         <is>
-          <t>Teacher Franchette Zarah M. Ranain</t>
+          <t>Unassigned</t>
         </is>
       </c>
       <c r="N397" t="inlineStr">
         <is>
-          <t>ACTIVE_VERIFIED</t>
+          <t>VACANT_REPLACEMENT_REQUIRED</t>
         </is>
       </c>
       <c r="O397" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>YES</t>
         </is>
       </c>
       <c r="P397" t="inlineStr">
         <is>
-          <t>tchr_franchette</t>
+          <t>tchr_wendy</t>
         </is>
       </c>
       <c r="Q397" t="inlineStr">
         <is>
-          <t>Teacher Franchette Zarah M. Ranain</t>
+          <t>Teacher Wendy</t>
         </is>
       </c>
       <c r="R397" t="inlineStr">
@@ -48795,24 +48767,20 @@
           <t>Makabansa</t>
         </is>
       </c>
-      <c r="L532" t="inlineStr">
-        <is>
-          <t>tchr_franchette</t>
-        </is>
-      </c>
+      <c r="L532" t="inlineStr"/>
       <c r="M532" t="inlineStr">
         <is>
-          <t>Teacher Franchette Zarah M. Ranain</t>
+          <t>Unassigned</t>
         </is>
       </c>
       <c r="N532" t="inlineStr">
         <is>
-          <t>ACTIVE_VERIFIED</t>
+          <t>VACANT_REPLACEMENT_REQUIRED</t>
         </is>
       </c>
       <c r="O532" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>YES</t>
         </is>
       </c>
       <c r="P532" t="inlineStr">

--- a/Term_Examination_Schedule_S.Y._2026-2027_Optimized.xlsx
+++ b/Term_Examination_Schedule_S.Y._2026-2027_Optimized.xlsx
@@ -12383,34 +12383,30 @@
           <t>Qur'an</t>
         </is>
       </c>
-      <c r="L132" t="inlineStr">
-        <is>
-          <t>tchr_hainur</t>
-        </is>
-      </c>
+      <c r="L132" t="inlineStr"/>
       <c r="M132" t="inlineStr">
         <is>
-          <t>Ustadha Hainur</t>
+          <t>Unassigned</t>
         </is>
       </c>
       <c r="N132" t="inlineStr">
         <is>
-          <t>ACTIVE_VERIFIED</t>
+          <t>VACANT_REPLACEMENT_REQUIRED</t>
         </is>
       </c>
       <c r="O132" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>YES</t>
         </is>
       </c>
       <c r="P132" t="inlineStr">
         <is>
-          <t>tchr_hainur</t>
+          <t>tchr_junaisah</t>
         </is>
       </c>
       <c r="Q132" t="inlineStr">
         <is>
-          <t>Ustadha Hainur</t>
+          <t>Teacher Junaisah</t>
         </is>
       </c>
       <c r="R132" t="inlineStr">

--- a/Term_Examination_Schedule_S.Y._2026-2027_Optimized.xlsx
+++ b/Term_Examination_Schedule_S.Y._2026-2027_Optimized.xlsx
@@ -11920,22 +11920,22 @@
       </c>
       <c r="J127" t="inlineStr">
         <is>
-          <t>subj_social_studies</t>
+          <t>subj_filipino</t>
         </is>
       </c>
       <c r="K127" t="inlineStr">
         <is>
-          <t>Social Studies</t>
+          <t>Filipino</t>
         </is>
       </c>
       <c r="L127" t="inlineStr">
         <is>
-          <t>tchr_shirehan</t>
+          <t>tchr_sophia</t>
         </is>
       </c>
       <c r="M127" t="inlineStr">
         <is>
-          <t>Teacher Shirehan</t>
+          <t>Teacher Sophia</t>
         </is>
       </c>
       <c r="N127" t="inlineStr">
@@ -11950,12 +11950,12 @@
       </c>
       <c r="P127" t="inlineStr">
         <is>
-          <t>tchr_shirehan</t>
+          <t>tchr_sophia</t>
         </is>
       </c>
       <c r="Q127" t="inlineStr">
         <is>
-          <t>Teacher Shirehan</t>
+          <t>Teacher Sophia</t>
         </is>
       </c>
       <c r="R127" t="inlineStr">
@@ -13645,22 +13645,22 @@
       </c>
       <c r="J146" t="inlineStr">
         <is>
-          <t>subj_filipino</t>
+          <t>subj_social_studies</t>
         </is>
       </c>
       <c r="K146" t="inlineStr">
         <is>
-          <t>Filipino</t>
+          <t>Social Studies</t>
         </is>
       </c>
       <c r="L146" t="inlineStr">
         <is>
-          <t>tchr_sophia</t>
+          <t>tchr_shirehan</t>
         </is>
       </c>
       <c r="M146" t="inlineStr">
         <is>
-          <t>Teacher Sophia</t>
+          <t>Teacher Shirehan</t>
         </is>
       </c>
       <c r="N146" t="inlineStr">
@@ -13675,12 +13675,12 @@
       </c>
       <c r="P146" t="inlineStr">
         <is>
-          <t>tchr_sophia</t>
+          <t>tchr_keychell</t>
         </is>
       </c>
       <c r="Q146" t="inlineStr">
         <is>
-          <t>Teacher Sophia</t>
+          <t>Teacher Keychelle</t>
         </is>
       </c>
       <c r="R146" t="inlineStr">

--- a/Term_Examination_Schedule_S.Y._2026-2027_Optimized.xlsx
+++ b/Term_Examination_Schedule_S.Y._2026-2027_Optimized.xlsx
@@ -9770,12 +9770,12 @@
       </c>
       <c r="P103" t="inlineStr">
         <is>
-          <t>tchr_ethel</t>
+          <t>tchr_keychell</t>
         </is>
       </c>
       <c r="Q103" t="inlineStr">
         <is>
-          <t>Teacher Ethel</t>
+          <t>Teacher Keychelle</t>
         </is>
       </c>
       <c r="R103" t="inlineStr">
@@ -25410,12 +25410,12 @@
       </c>
       <c r="P275" t="inlineStr">
         <is>
-          <t>tchr_franchette</t>
+          <t>tchr_ethel</t>
         </is>
       </c>
       <c r="Q275" t="inlineStr">
         <is>
-          <t>Teacher Franchette Zarah M. Ranain</t>
+          <t>Teacher Ethel</t>
         </is>
       </c>
       <c r="R275" t="inlineStr">
@@ -27503,12 +27503,12 @@
       </c>
       <c r="P298" t="inlineStr">
         <is>
-          <t>tchr_franchette</t>
+          <t>tchr_ethel</t>
         </is>
       </c>
       <c r="Q298" t="inlineStr">
         <is>
-          <t>Teacher Franchette Zarah M. Ranain</t>
+          <t>Teacher Ethel</t>
         </is>
       </c>
       <c r="R298" t="inlineStr">
@@ -30138,12 +30138,12 @@
       </c>
       <c r="P327" t="inlineStr">
         <is>
-          <t>tchr_radzmia</t>
+          <t>tchr_franchette</t>
         </is>
       </c>
       <c r="Q327" t="inlineStr">
         <is>
-          <t>Teacher Radzmia</t>
+          <t>Teacher Franchette Zarah M. Ranain</t>
         </is>
       </c>
       <c r="R327" t="inlineStr">

--- a/Term_Examination_Schedule_S.Y._2026-2027_Optimized.xlsx
+++ b/Term_Examination_Schedule_S.Y._2026-2027_Optimized.xlsx
@@ -2756,7 +2756,7 @@
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>Teacher Wendy</t>
+          <t>Teacher Wendelyn</t>
         </is>
       </c>
       <c r="N26" t="inlineStr">
@@ -2776,7 +2776,7 @@
       </c>
       <c r="Q26" t="inlineStr">
         <is>
-          <t>Teacher Wendy</t>
+          <t>Teacher Wendelyn</t>
         </is>
       </c>
       <c r="R26" t="inlineStr">
@@ -14206,7 +14206,7 @@
       </c>
       <c r="M152" t="inlineStr">
         <is>
-          <t>Teacher Wendy</t>
+          <t>Teacher Wendelyn</t>
         </is>
       </c>
       <c r="N152" t="inlineStr">
@@ -14226,7 +14226,7 @@
       </c>
       <c r="Q152" t="inlineStr">
         <is>
-          <t>Teacher Wendy</t>
+          <t>Teacher Wendelyn</t>
         </is>
       </c>
       <c r="R152" t="inlineStr">
@@ -15662,7 +15662,7 @@
       </c>
       <c r="M168" t="inlineStr">
         <is>
-          <t>Teacher Wendy</t>
+          <t>Teacher Wendelyn</t>
         </is>
       </c>
       <c r="N168" t="inlineStr">
@@ -15682,7 +15682,7 @@
       </c>
       <c r="Q168" t="inlineStr">
         <is>
-          <t>Teacher Wendy</t>
+          <t>Teacher Wendelyn</t>
         </is>
       </c>
       <c r="R168" t="inlineStr">
@@ -35392,22 +35392,22 @@
       </c>
       <c r="L385" t="inlineStr">
         <is>
-          <t>tchr_normylah</t>
+          <t>tchr_wendy</t>
         </is>
       </c>
       <c r="M385" t="inlineStr">
         <is>
-          <t>Teacher Normylah</t>
+          <t>Teacher Wendelyn</t>
         </is>
       </c>
       <c r="N385" t="inlineStr">
         <is>
-          <t>RESIGNED_INACTIVE</t>
+          <t>ACTIVE_VERIFIED</t>
         </is>
       </c>
       <c r="O385" t="inlineStr">
         <is>
-          <t>YES</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="P385" t="inlineStr">
@@ -36500,12 +36500,12 @@
       </c>
       <c r="P397" t="inlineStr">
         <is>
-          <t>tchr_wendy</t>
+          <t>tchr_katrina</t>
         </is>
       </c>
       <c r="Q397" t="inlineStr">
         <is>
-          <t>Teacher Wendy</t>
+          <t>Teacher Katrina</t>
         </is>
       </c>
       <c r="R397" t="inlineStr">
@@ -41399,7 +41399,7 @@
       </c>
       <c r="M451" t="inlineStr">
         <is>
-          <t>Teacher Wendy</t>
+          <t>Teacher Wendelyn</t>
         </is>
       </c>
       <c r="N451" t="inlineStr">
@@ -41419,7 +41419,7 @@
       </c>
       <c r="Q451" t="inlineStr">
         <is>
-          <t>Teacher Wendy</t>
+          <t>Teacher Wendelyn</t>
         </is>
       </c>
       <c r="R451" t="inlineStr">
@@ -48786,7 +48786,7 @@
       </c>
       <c r="Q532" t="inlineStr">
         <is>
-          <t>Teacher Wendy</t>
+          <t>Teacher Wendelyn</t>
         </is>
       </c>
       <c r="R532" t="inlineStr">
@@ -52588,7 +52588,7 @@
       </c>
       <c r="M574" t="inlineStr">
         <is>
-          <t>Teacher Wendy</t>
+          <t>Teacher Wendelyn</t>
         </is>
       </c>
       <c r="N574" t="inlineStr">
@@ -52608,7 +52608,7 @@
       </c>
       <c r="Q574" t="inlineStr">
         <is>
-          <t>Teacher Wendy</t>
+          <t>Teacher Wendelyn</t>
         </is>
       </c>
       <c r="R574" t="inlineStr">

--- a/Term_Examination_Schedule_S.Y._2026-2027_Optimized.xlsx
+++ b/Term_Examination_Schedule_S.Y._2026-2027_Optimized.xlsx
@@ -35412,12 +35412,12 @@
       </c>
       <c r="P385" t="inlineStr">
         <is>
-          <t>tchr_junaisah</t>
+          <t>tchr_ethel</t>
         </is>
       </c>
       <c r="Q385" t="inlineStr">
         <is>
-          <t>Teacher Junaisah</t>
+          <t>Teacher Ethel</t>
         </is>
       </c>
       <c r="R385" t="inlineStr">
@@ -36955,12 +36955,12 @@
       </c>
       <c r="P402" t="inlineStr">
         <is>
-          <t>tchr_ethel</t>
+          <t>tchr_nof</t>
         </is>
       </c>
       <c r="Q402" t="inlineStr">
         <is>
-          <t>Teacher Ethel</t>
+          <t>Teacher Nof</t>
         </is>
       </c>
       <c r="R402" t="inlineStr">

--- a/Term_Examination_Schedule_S.Y._2026-2027_Optimized.xlsx
+++ b/Term_Examination_Schedule_S.Y._2026-2027_Optimized.xlsx
@@ -9768,19 +9768,11 @@
           <t>YES</t>
         </is>
       </c>
-      <c r="P103" t="inlineStr">
-        <is>
-          <t>tchr_keychell</t>
-        </is>
-      </c>
-      <c r="Q103" t="inlineStr">
-        <is>
-          <t>Teacher Keychelle</t>
-        </is>
-      </c>
+      <c r="P103" t="inlineStr"/>
+      <c r="Q103" t="inlineStr"/>
       <c r="R103" t="inlineStr">
         <is>
-          <t>ACTIVE_ASSIGNED</t>
+          <t>NOT_ASSIGNED</t>
         </is>
       </c>
       <c r="S103" t="n">
@@ -30136,19 +30128,11 @@
           <t>YES</t>
         </is>
       </c>
-      <c r="P327" t="inlineStr">
-        <is>
-          <t>tchr_franchette</t>
-        </is>
-      </c>
-      <c r="Q327" t="inlineStr">
-        <is>
-          <t>Teacher Franchette Zarah M. Ranain</t>
-        </is>
-      </c>
+      <c r="P327" t="inlineStr"/>
+      <c r="Q327" t="inlineStr"/>
       <c r="R327" t="inlineStr">
         <is>
-          <t>ACTIVE_ASSIGNED</t>
+          <t>NOT_ASSIGNED</t>
         </is>
       </c>
       <c r="S327" t="n">
@@ -34318,19 +34302,11 @@
           <t>YES</t>
         </is>
       </c>
-      <c r="P373" t="inlineStr">
-        <is>
-          <t>tchr_mohaymen</t>
-        </is>
-      </c>
-      <c r="Q373" t="inlineStr">
-        <is>
-          <t>Sir Mohaymen</t>
-        </is>
-      </c>
+      <c r="P373" t="inlineStr"/>
+      <c r="Q373" t="inlineStr"/>
       <c r="R373" t="inlineStr">
         <is>
-          <t>ACTIVE_ASSIGNED</t>
+          <t>NOT_ASSIGNED</t>
         </is>
       </c>
       <c r="S373" t="n">
@@ -36498,19 +36474,11 @@
           <t>YES</t>
         </is>
       </c>
-      <c r="P397" t="inlineStr">
-        <is>
-          <t>tchr_katrina</t>
-        </is>
-      </c>
-      <c r="Q397" t="inlineStr">
-        <is>
-          <t>Teacher Katrina</t>
-        </is>
-      </c>
+      <c r="P397" t="inlineStr"/>
+      <c r="Q397" t="inlineStr"/>
       <c r="R397" t="inlineStr">
         <is>
-          <t>ACTIVE_ASSIGNED</t>
+          <t>NOT_ASSIGNED</t>
         </is>
       </c>
       <c r="S397" t="n">
@@ -54239,19 +54207,11 @@
           <t>NO</t>
         </is>
       </c>
-      <c r="P592" t="inlineStr">
-        <is>
-          <t>tchr_franchette</t>
-        </is>
-      </c>
-      <c r="Q592" t="inlineStr">
-        <is>
-          <t>Teacher Franchette Zarah M. Ranain</t>
-        </is>
-      </c>
+      <c r="P592" t="inlineStr"/>
+      <c r="Q592" t="inlineStr"/>
       <c r="R592" t="inlineStr">
         <is>
-          <t>ACTIVE_ASSIGNED</t>
+          <t>NOT_ASSIGNED</t>
         </is>
       </c>
       <c r="S592" t="n">

--- a/Term_Examination_Schedule_S.Y._2026-2027_Optimized.xlsx
+++ b/Term_Examination_Schedule_S.Y._2026-2027_Optimized.xlsx
@@ -27495,12 +27495,12 @@
       </c>
       <c r="P298" t="inlineStr">
         <is>
-          <t>tchr_ethel</t>
+          <t>tchr_wendy</t>
         </is>
       </c>
       <c r="Q298" t="inlineStr">
         <is>
-          <t>Teacher Ethel</t>
+          <t>Teacher Wendelyn</t>
         </is>
       </c>
       <c r="R298" t="inlineStr">

--- a/Term_Examination_Schedule_S.Y._2026-2027_Optimized.xlsx
+++ b/Term_Examination_Schedule_S.Y._2026-2027_Optimized.xlsx
@@ -6316,12 +6316,12 @@
       </c>
       <c r="P65" t="inlineStr">
         <is>
-          <t>tchr_wardah</t>
+          <t>tchr_rowena</t>
         </is>
       </c>
       <c r="Q65" t="inlineStr">
         <is>
-          <t>Teacher Wardah</t>
+          <t>Teacher Rowena</t>
         </is>
       </c>
       <c r="R65" t="inlineStr">
@@ -9592,12 +9592,12 @@
       </c>
       <c r="P101" t="inlineStr">
         <is>
-          <t>tchr_junaisah</t>
+          <t>tchr_wendy</t>
         </is>
       </c>
       <c r="Q101" t="inlineStr">
         <is>
-          <t>Teacher Junaisah</t>
+          <t>Teacher Wendelyn</t>
         </is>
       </c>
       <c r="R101" t="inlineStr">
@@ -12393,12 +12393,12 @@
       </c>
       <c r="P132" t="inlineStr">
         <is>
-          <t>tchr_junaisah</t>
+          <t>tchr_rowena</t>
         </is>
       </c>
       <c r="Q132" t="inlineStr">
         <is>
-          <t>Teacher Junaisah</t>
+          <t>Teacher Rowena</t>
         </is>
       </c>
       <c r="R132" t="inlineStr">

--- a/Term_Examination_Schedule_S.Y._2026-2027_Optimized.xlsx
+++ b/Term_Examination_Schedule_S.Y._2026-2027_Optimized.xlsx
@@ -6316,12 +6316,12 @@
       </c>
       <c r="P65" t="inlineStr">
         <is>
-          <t>tchr_rowena</t>
+          <t>tchr_franchette</t>
         </is>
       </c>
       <c r="Q65" t="inlineStr">
         <is>
-          <t>Teacher Rowena</t>
+          <t>Teacher Franchette Zarah M. Ranain</t>
         </is>
       </c>
       <c r="R65" t="inlineStr">

--- a/Term_Examination_Schedule_S.Y._2026-2027_Optimized.xlsx
+++ b/Term_Examination_Schedule_S.Y._2026-2027_Optimized.xlsx
@@ -12393,12 +12393,12 @@
       </c>
       <c r="P132" t="inlineStr">
         <is>
-          <t>tchr_rowena</t>
+          <t>tchr_junaisah</t>
         </is>
       </c>
       <c r="Q132" t="inlineStr">
         <is>
-          <t>Teacher Rowena</t>
+          <t>Teacher Junaisah</t>
         </is>
       </c>
       <c r="R132" t="inlineStr">

--- a/Term_Examination_Schedule_S.Y._2026-2027_Optimized.xlsx
+++ b/Term_Examination_Schedule_S.Y._2026-2027_Optimized.xlsx
@@ -12391,19 +12391,11 @@
           <t>YES</t>
         </is>
       </c>
-      <c r="P132" t="inlineStr">
-        <is>
-          <t>tchr_junaisah</t>
-        </is>
-      </c>
-      <c r="Q132" t="inlineStr">
-        <is>
-          <t>Teacher Junaisah</t>
-        </is>
-      </c>
+      <c r="P132" t="inlineStr"/>
+      <c r="Q132" t="inlineStr"/>
       <c r="R132" t="inlineStr">
         <is>
-          <t>ACTIVE_ASSIGNED</t>
+          <t>NOT_ASSIGNED</t>
         </is>
       </c>
       <c r="S132" t="n">

--- a/Term_Examination_Schedule_S.Y._2026-2027_Optimized.xlsx
+++ b/Term_Examination_Schedule_S.Y._2026-2027_Optimized.xlsx
@@ -4296,30 +4296,34 @@
           <t>Makabansa</t>
         </is>
       </c>
-      <c r="L43" t="inlineStr"/>
+      <c r="L43" t="inlineStr">
+        <is>
+          <t>tchr_franchette</t>
+        </is>
+      </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>Unassigned</t>
+          <t>Teacher Franchette Zarah M. Ranain</t>
         </is>
       </c>
       <c r="N43" t="inlineStr">
         <is>
-          <t>VACANT_REPLACEMENT_REQUIRED</t>
+          <t>ACTIVE_VERIFIED</t>
         </is>
       </c>
       <c r="O43" t="inlineStr">
         <is>
-          <t>YES</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="P43" t="inlineStr">
         <is>
-          <t>tchr_ethel</t>
+          <t>tchr_franchette</t>
         </is>
       </c>
       <c r="Q43" t="inlineStr">
         <is>
-          <t>Teacher Ethel</t>
+          <t>Teacher Franchette Zarah M. Ranain</t>
         </is>
       </c>
       <c r="R43" t="inlineStr">
@@ -8527,7 +8531,7 @@
         </is>
       </c>
       <c r="C90" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -8536,12 +8540,12 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>sec_grade_4_az_zubair_ibn_al_awwaam_2nd_shift</t>
+          <t>sec_grade_3_ammar_ibn_yasir_1st_shift_boys</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>GRADE 4 - AZ ZUBAIR IBN AL AWWAAM (2ND SHIFT)</t>
+          <t>GRADE 3 -AMMAR IBN YASIR (1ST SHIFT) - BOYS</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
@@ -8551,32 +8555,32 @@
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>Grade 4</t>
+          <t>Grade 3</t>
         </is>
       </c>
       <c r="I90" t="inlineStr">
         <is>
-          <t>ODL - 2ND SHIFT</t>
+          <t>ODL - 1ST SHIFT</t>
         </is>
       </c>
       <c r="J90" t="inlineStr">
         <is>
-          <t>subj_math</t>
+          <t>subj_makabansa</t>
         </is>
       </c>
       <c r="K90" t="inlineStr">
         <is>
-          <t>Math</t>
+          <t>Makabansa</t>
         </is>
       </c>
       <c r="L90" t="inlineStr">
         <is>
-          <t>tchr_arvin</t>
+          <t>tchr_franchette</t>
         </is>
       </c>
       <c r="M90" t="inlineStr">
         <is>
-          <t>Teacher Arvin</t>
+          <t>Teacher Franchette Zarah M. Ranain</t>
         </is>
       </c>
       <c r="N90" t="inlineStr">
@@ -8591,12 +8595,12 @@
       </c>
       <c r="P90" t="inlineStr">
         <is>
-          <t>tchr_arvin</t>
+          <t>tchr_franchette</t>
         </is>
       </c>
       <c r="Q90" t="inlineStr">
         <is>
-          <t>Teacher Arvin</t>
+          <t>Teacher Franchette Zarah M. Ranain</t>
         </is>
       </c>
       <c r="R90" t="inlineStr">
@@ -8618,7 +8622,7 @@
         </is>
       </c>
       <c r="C91" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -8627,12 +8631,12 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>sec_grade_4_hakim_ibn_hazm_1st_shift</t>
+          <t>sec_grade_4_az_zubair_ibn_al_awwaam_2nd_shift</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>GRADE 4 - HAKIM IBN HAZM(1ST SHIFT)</t>
+          <t>GRADE 4 - AZ ZUBAIR IBN AL AWWAAM (2ND SHIFT)</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
@@ -8647,27 +8651,27 @@
       </c>
       <c r="I91" t="inlineStr">
         <is>
-          <t>ODL - 1ST SHIFT</t>
+          <t>ODL - 2ND SHIFT</t>
         </is>
       </c>
       <c r="J91" t="inlineStr">
         <is>
-          <t>subj_araling_panlipunan</t>
+          <t>subj_math</t>
         </is>
       </c>
       <c r="K91" t="inlineStr">
         <is>
-          <t>Araling Panlipunan</t>
+          <t>Math</t>
         </is>
       </c>
       <c r="L91" t="inlineStr">
         <is>
-          <t>tchr_monisa</t>
+          <t>tchr_arvin</t>
         </is>
       </c>
       <c r="M91" t="inlineStr">
         <is>
-          <t>Teacher Monisa</t>
+          <t>Teacher Arvin</t>
         </is>
       </c>
       <c r="N91" t="inlineStr">
@@ -8682,12 +8686,12 @@
       </c>
       <c r="P91" t="inlineStr">
         <is>
-          <t>tchr_monisa</t>
+          <t>tchr_arvin</t>
         </is>
       </c>
       <c r="Q91" t="inlineStr">
         <is>
-          <t>Teacher Monisa</t>
+          <t>Teacher Arvin</t>
         </is>
       </c>
       <c r="R91" t="inlineStr">
@@ -8709,7 +8713,7 @@
         </is>
       </c>
       <c r="C92" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -8718,12 +8722,12 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>sec_grade_4_ikrimah_ibn_abi_jahl_2nd_shift</t>
+          <t>sec_grade_4_hakim_ibn_hazm_1st_shift</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>GRADE 4 - IKRIMAH IBN ABI JAHL (2ND SHIFT)</t>
+          <t>GRADE 4 - HAKIM IBN HAZM(1ST SHIFT)</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
@@ -8738,27 +8742,27 @@
       </c>
       <c r="I92" t="inlineStr">
         <is>
-          <t>ODL - 2ND SHIFT</t>
+          <t>ODL - 1ST SHIFT</t>
         </is>
       </c>
       <c r="J92" t="inlineStr">
         <is>
-          <t>subj_shaf</t>
+          <t>subj_araling_panlipunan</t>
         </is>
       </c>
       <c r="K92" t="inlineStr">
         <is>
-          <t>SHAF</t>
+          <t>Araling Panlipunan</t>
         </is>
       </c>
       <c r="L92" t="inlineStr">
         <is>
-          <t>tchr_abdiraheem</t>
+          <t>tchr_monisa</t>
         </is>
       </c>
       <c r="M92" t="inlineStr">
         <is>
-          <t>Ustadh Abdiraheem</t>
+          <t>Teacher Monisa</t>
         </is>
       </c>
       <c r="N92" t="inlineStr">
@@ -8773,12 +8777,12 @@
       </c>
       <c r="P92" t="inlineStr">
         <is>
-          <t>tchr_abdiraheem</t>
+          <t>tchr_monisa</t>
         </is>
       </c>
       <c r="Q92" t="inlineStr">
         <is>
-          <t>Ustadh Abdiraheem</t>
+          <t>Teacher Monisa</t>
         </is>
       </c>
       <c r="R92" t="inlineStr">
@@ -8800,7 +8804,7 @@
         </is>
       </c>
       <c r="C93" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -8809,12 +8813,12 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>sec_grade_4_usayd_ibn_hudhayr_1st_shift_mix</t>
+          <t>sec_grade_4_ikrimah_ibn_abi_jahl_2nd_shift</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>GRADE 4 - USAYD IBN HUDHAYR (1ST SHIFT) - MIX</t>
+          <t>GRADE 4 - IKRIMAH IBN ABI JAHL (2ND SHIFT)</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
@@ -8829,27 +8833,27 @@
       </c>
       <c r="I93" t="inlineStr">
         <is>
-          <t>ODL - 1ST SHIFT</t>
+          <t>ODL - 2ND SHIFT</t>
         </is>
       </c>
       <c r="J93" t="inlineStr">
         <is>
-          <t>subj_math</t>
+          <t>subj_shaf</t>
         </is>
       </c>
       <c r="K93" t="inlineStr">
         <is>
-          <t>Math</t>
+          <t>SHAF</t>
         </is>
       </c>
       <c r="L93" t="inlineStr">
         <is>
-          <t>tchr_saimonah</t>
+          <t>tchr_abdiraheem</t>
         </is>
       </c>
       <c r="M93" t="inlineStr">
         <is>
-          <t>Teacher Saimonah</t>
+          <t>Ustadh Abdiraheem</t>
         </is>
       </c>
       <c r="N93" t="inlineStr">
@@ -8864,12 +8868,12 @@
       </c>
       <c r="P93" t="inlineStr">
         <is>
-          <t>tchr_saimonah</t>
+          <t>tchr_abdiraheem</t>
         </is>
       </c>
       <c r="Q93" t="inlineStr">
         <is>
-          <t>Teacher Saimonah</t>
+          <t>Ustadh Abdiraheem</t>
         </is>
       </c>
       <c r="R93" t="inlineStr">
@@ -8891,7 +8895,7 @@
         </is>
       </c>
       <c r="C94" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -8900,12 +8904,12 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>sec_grade_4_hassan_ibn_thabit_2nd_shift_mix</t>
+          <t>sec_grade_4_usayd_ibn_hudhayr_1st_shift_mix</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>GRADE 4 -HASSAN IBN THABIT (2ND SHIFT) - MIX</t>
+          <t>GRADE 4 - USAYD IBN HUDHAYR (1ST SHIFT) - MIX</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
@@ -8920,27 +8924,27 @@
       </c>
       <c r="I94" t="inlineStr">
         <is>
-          <t>ODL - 2ND SHIFT</t>
+          <t>ODL - 1ST SHIFT</t>
         </is>
       </c>
       <c r="J94" t="inlineStr">
         <is>
-          <t>subj_arabic</t>
+          <t>subj_math</t>
         </is>
       </c>
       <c r="K94" t="inlineStr">
         <is>
-          <t>Arabic</t>
+          <t>Math</t>
         </is>
       </c>
       <c r="L94" t="inlineStr">
         <is>
-          <t>tchr_ali</t>
+          <t>tchr_saimonah</t>
         </is>
       </c>
       <c r="M94" t="inlineStr">
         <is>
-          <t>Ustadh Ali</t>
+          <t>Teacher Saimonah</t>
         </is>
       </c>
       <c r="N94" t="inlineStr">
@@ -8955,12 +8959,12 @@
       </c>
       <c r="P94" t="inlineStr">
         <is>
-          <t>tchr_ali</t>
+          <t>tchr_saimonah</t>
         </is>
       </c>
       <c r="Q94" t="inlineStr">
         <is>
-          <t>Ustadh Ali</t>
+          <t>Teacher Saimonah</t>
         </is>
       </c>
       <c r="R94" t="inlineStr">
@@ -8991,12 +8995,12 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>sec_grade_5_al_harith_bin_awf_2nd_shift</t>
+          <t>sec_grade_4_hassan_ibn_thabit_2nd_shift_mix</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>GRADE 5 - AL HARITH BIN AWF (2ND SHIFT)</t>
+          <t>GRADE 4 -HASSAN IBN THABIT (2ND SHIFT) - MIX</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
@@ -9006,7 +9010,7 @@
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>Grade 5</t>
+          <t>Grade 4</t>
         </is>
       </c>
       <c r="I95" t="inlineStr">
@@ -9016,22 +9020,22 @@
       </c>
       <c r="J95" t="inlineStr">
         <is>
-          <t>subj_shaf</t>
+          <t>subj_arabic</t>
         </is>
       </c>
       <c r="K95" t="inlineStr">
         <is>
-          <t>SHAF</t>
+          <t>Arabic</t>
         </is>
       </c>
       <c r="L95" t="inlineStr">
         <is>
-          <t>tchr_ersahad</t>
+          <t>tchr_ali</t>
         </is>
       </c>
       <c r="M95" t="inlineStr">
         <is>
-          <t>Ustadh Ersahad</t>
+          <t>Ustadh Ali</t>
         </is>
       </c>
       <c r="N95" t="inlineStr">
@@ -9046,12 +9050,12 @@
       </c>
       <c r="P95" t="inlineStr">
         <is>
-          <t>tchr_ersahad</t>
+          <t>tchr_ali</t>
         </is>
       </c>
       <c r="Q95" t="inlineStr">
         <is>
-          <t>Ustadh Ersahad</t>
+          <t>Ustadh Ali</t>
         </is>
       </c>
       <c r="R95" t="inlineStr">
@@ -9073,7 +9077,7 @@
         </is>
       </c>
       <c r="C96" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -9082,12 +9086,12 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>sec_grade_5_ayyash_ibn_abi_rabi_ah_1st_shift</t>
+          <t>sec_grade_5_al_harith_bin_awf_2nd_shift</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>GRADE 5 - AYYASH IBN ABI RABI'AH(1ST SHIFT)</t>
+          <t>GRADE 5 - AL HARITH BIN AWF (2ND SHIFT)</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
@@ -9102,27 +9106,27 @@
       </c>
       <c r="I96" t="inlineStr">
         <is>
-          <t>ODL - 1ST SHIFT</t>
+          <t>ODL - 2ND SHIFT</t>
         </is>
       </c>
       <c r="J96" t="inlineStr">
         <is>
-          <t>subj_arabic</t>
+          <t>subj_shaf</t>
         </is>
       </c>
       <c r="K96" t="inlineStr">
         <is>
-          <t>Arabic</t>
+          <t>SHAF</t>
         </is>
       </c>
       <c r="L96" t="inlineStr">
         <is>
-          <t>tchr_faidh</t>
+          <t>tchr_ersahad</t>
         </is>
       </c>
       <c r="M96" t="inlineStr">
         <is>
-          <t>Ustadh Faidh</t>
+          <t>Ustadh Ersahad</t>
         </is>
       </c>
       <c r="N96" t="inlineStr">
@@ -9137,12 +9141,12 @@
       </c>
       <c r="P96" t="inlineStr">
         <is>
-          <t>tchr_faidh</t>
+          <t>tchr_ersahad</t>
         </is>
       </c>
       <c r="Q96" t="inlineStr">
         <is>
-          <t>Ustadh Faidh</t>
+          <t>Ustadh Ersahad</t>
         </is>
       </c>
       <c r="R96" t="inlineStr">
@@ -9173,12 +9177,12 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>sec_grade_5_hamza_ibn_abdul_1st_shift</t>
+          <t>sec_grade_5_ayyash_ibn_abi_rabi_ah_1st_shift</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>GRADE 5 - HAMZA IBN ABDUL (1ST SHIFT)</t>
+          <t>GRADE 5 - AYYASH IBN ABI RABI'AH(1ST SHIFT)</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
@@ -9198,22 +9202,22 @@
       </c>
       <c r="J97" t="inlineStr">
         <is>
-          <t>subj_filipino</t>
+          <t>subj_arabic</t>
         </is>
       </c>
       <c r="K97" t="inlineStr">
         <is>
-          <t>Filipino</t>
+          <t>Arabic</t>
         </is>
       </c>
       <c r="L97" t="inlineStr">
         <is>
-          <t>tchr_joanna</t>
+          <t>tchr_faidh</t>
         </is>
       </c>
       <c r="M97" t="inlineStr">
         <is>
-          <t>Teacher Joanna</t>
+          <t>Ustadh Faidh</t>
         </is>
       </c>
       <c r="N97" t="inlineStr">
@@ -9228,12 +9232,12 @@
       </c>
       <c r="P97" t="inlineStr">
         <is>
-          <t>tchr_joanna</t>
+          <t>tchr_faidh</t>
         </is>
       </c>
       <c r="Q97" t="inlineStr">
         <is>
-          <t>Teacher Joanna</t>
+          <t>Ustadh Faidh</t>
         </is>
       </c>
       <c r="R97" t="inlineStr">
@@ -9255,7 +9259,7 @@
         </is>
       </c>
       <c r="C98" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -9264,12 +9268,12 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>sec_grade_5_ja_far_ibn_abi_talib_2nd_shift_mix</t>
+          <t>sec_grade_5_hamza_ibn_abdul_1st_shift</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>GRADE 5 - JA'FAR IBN ABI TALIB (2ND SHIFT) - MIX</t>
+          <t>GRADE 5 - HAMZA IBN ABDUL (1ST SHIFT)</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
@@ -9284,27 +9288,27 @@
       </c>
       <c r="I98" t="inlineStr">
         <is>
-          <t>ODL - 2ND SHIFT</t>
+          <t>ODL - 1ST SHIFT</t>
         </is>
       </c>
       <c r="J98" t="inlineStr">
         <is>
-          <t>subj_gmrc</t>
+          <t>subj_filipino</t>
         </is>
       </c>
       <c r="K98" t="inlineStr">
         <is>
-          <t>GMRC</t>
+          <t>Filipino</t>
         </is>
       </c>
       <c r="L98" t="inlineStr">
         <is>
-          <t>tchr_saliha</t>
+          <t>tchr_joanna</t>
         </is>
       </c>
       <c r="M98" t="inlineStr">
         <is>
-          <t>Ustadha Saliha</t>
+          <t>Teacher Joanna</t>
         </is>
       </c>
       <c r="N98" t="inlineStr">
@@ -9319,12 +9323,12 @@
       </c>
       <c r="P98" t="inlineStr">
         <is>
-          <t>tchr_saliha</t>
+          <t>tchr_joanna</t>
         </is>
       </c>
       <c r="Q98" t="inlineStr">
         <is>
-          <t>Ustadha Saliha</t>
+          <t>Teacher Joanna</t>
         </is>
       </c>
       <c r="R98" t="inlineStr">
@@ -9346,7 +9350,7 @@
         </is>
       </c>
       <c r="C99" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -9355,12 +9359,12 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>sec_grade_5_muhammad_ibn_maslamah_1st_shift</t>
+          <t>sec_grade_5_ja_far_ibn_abi_talib_2nd_shift_mix</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>GRADE 5 - MUHAMMAD IBN MASLAMAH (1ST SHIFT)</t>
+          <t>GRADE 5 - JA'FAR IBN ABI TALIB (2ND SHIFT) - MIX</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
@@ -9375,27 +9379,27 @@
       </c>
       <c r="I99" t="inlineStr">
         <is>
-          <t>ODL - 1ST SHIFT</t>
+          <t>ODL - 2ND SHIFT</t>
         </is>
       </c>
       <c r="J99" t="inlineStr">
         <is>
-          <t>subj_tle</t>
+          <t>subj_gmrc</t>
         </is>
       </c>
       <c r="K99" t="inlineStr">
         <is>
-          <t>TLE</t>
+          <t>GMRC</t>
         </is>
       </c>
       <c r="L99" t="inlineStr">
         <is>
-          <t>tchr_anna</t>
+          <t>tchr_saliha</t>
         </is>
       </c>
       <c r="M99" t="inlineStr">
         <is>
-          <t>Teacher Anna</t>
+          <t>Ustadha Saliha</t>
         </is>
       </c>
       <c r="N99" t="inlineStr">
@@ -9410,12 +9414,12 @@
       </c>
       <c r="P99" t="inlineStr">
         <is>
-          <t>tchr_anna</t>
+          <t>tchr_saliha</t>
         </is>
       </c>
       <c r="Q99" t="inlineStr">
         <is>
-          <t>Teacher Anna</t>
+          <t>Ustadha Saliha</t>
         </is>
       </c>
       <c r="R99" t="inlineStr">
@@ -9446,12 +9450,12 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>sec_grade_6_abbas_ibn_abd_al_muttalib_1st_shift</t>
+          <t>sec_grade_5_muhammad_ibn_maslamah_1st_shift</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>GRADE 6 - ABBAS IBN ABD AL-MUTTALIB (1ST SHIFT)</t>
+          <t>GRADE 5 - MUHAMMAD IBN MASLAMAH (1ST SHIFT)</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
@@ -9461,7 +9465,7 @@
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>Grade 6</t>
+          <t>Grade 5</t>
         </is>
       </c>
       <c r="I100" t="inlineStr">
@@ -9471,22 +9475,22 @@
       </c>
       <c r="J100" t="inlineStr">
         <is>
-          <t>subj_filipino</t>
+          <t>subj_tle</t>
         </is>
       </c>
       <c r="K100" t="inlineStr">
         <is>
-          <t>Filipino</t>
+          <t>TLE</t>
         </is>
       </c>
       <c r="L100" t="inlineStr">
         <is>
-          <t>tchr_zuhora</t>
+          <t>tchr_anna</t>
         </is>
       </c>
       <c r="M100" t="inlineStr">
         <is>
-          <t>Teacher Zuhora</t>
+          <t>Teacher Anna</t>
         </is>
       </c>
       <c r="N100" t="inlineStr">
@@ -9501,12 +9505,12 @@
       </c>
       <c r="P100" t="inlineStr">
         <is>
-          <t>tchr_zuhora</t>
+          <t>tchr_anna</t>
         </is>
       </c>
       <c r="Q100" t="inlineStr">
         <is>
-          <t>Teacher Zuhora</t>
+          <t>Teacher Anna</t>
         </is>
       </c>
       <c r="R100" t="inlineStr">
@@ -9537,12 +9541,12 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>sec_grade_6_abdullah_ibn_salaam_1st_shift</t>
+          <t>sec_grade_6_abbas_ibn_abd_al_muttalib_1st_shift</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>GRADE 6 - ABDULLAH IBN SALAAM (1ST SHIFT)</t>
+          <t>GRADE 6 - ABBAS IBN ABD AL-MUTTALIB (1ST SHIFT)</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
@@ -9562,42 +9566,42 @@
       </c>
       <c r="J101" t="inlineStr">
         <is>
-          <t>subj_araling_panlipunan</t>
+          <t>subj_filipino</t>
         </is>
       </c>
       <c r="K101" t="inlineStr">
         <is>
-          <t>Araling Panlipunan</t>
+          <t>Filipino</t>
         </is>
       </c>
       <c r="L101" t="inlineStr">
         <is>
-          <t>tchr_normylah</t>
+          <t>tchr_zuhora</t>
         </is>
       </c>
       <c r="M101" t="inlineStr">
         <is>
-          <t>Teacher Normylah</t>
+          <t>Teacher Zuhora</t>
         </is>
       </c>
       <c r="N101" t="inlineStr">
         <is>
-          <t>RESIGNED_INACTIVE</t>
+          <t>ACTIVE_VERIFIED</t>
         </is>
       </c>
       <c r="O101" t="inlineStr">
         <is>
-          <t>YES</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="P101" t="inlineStr">
         <is>
-          <t>tchr_wendy</t>
+          <t>tchr_zuhora</t>
         </is>
       </c>
       <c r="Q101" t="inlineStr">
         <is>
-          <t>Teacher Wendelyn</t>
+          <t>Teacher Zuhora</t>
         </is>
       </c>
       <c r="R101" t="inlineStr">
@@ -9619,7 +9623,7 @@
         </is>
       </c>
       <c r="C102" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -9628,12 +9632,12 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>sec_grade_6_dihya_ibn_khalifah_2nd_shift_girls</t>
+          <t>sec_grade_6_abdullah_ibn_salaam_1st_shift</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>GRADE 6 - DIHYA IBN KHALIFAH (2ND SHIFT) GIRLS</t>
+          <t>GRADE 6 - ABDULLAH IBN SALAAM (1ST SHIFT)</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
@@ -9648,47 +9652,47 @@
       </c>
       <c r="I102" t="inlineStr">
         <is>
-          <t>ODL - 2ND SHIFT</t>
+          <t>ODL - 1ST SHIFT</t>
         </is>
       </c>
       <c r="J102" t="inlineStr">
         <is>
-          <t>subj_science</t>
+          <t>subj_araling_panlipunan</t>
         </is>
       </c>
       <c r="K102" t="inlineStr">
         <is>
-          <t>Science</t>
+          <t>Araling Panlipunan</t>
         </is>
       </c>
       <c r="L102" t="inlineStr">
         <is>
-          <t>tchr_fhairudz</t>
+          <t>tchr_normylah</t>
         </is>
       </c>
       <c r="M102" t="inlineStr">
         <is>
-          <t>Teacher Fhairudz</t>
+          <t>Teacher Normylah</t>
         </is>
       </c>
       <c r="N102" t="inlineStr">
         <is>
-          <t>ACTIVE_VERIFIED</t>
+          <t>RESIGNED_INACTIVE</t>
         </is>
       </c>
       <c r="O102" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>YES</t>
         </is>
       </c>
       <c r="P102" t="inlineStr">
         <is>
-          <t>tchr_fhairudz</t>
+          <t>tchr_wendy</t>
         </is>
       </c>
       <c r="Q102" t="inlineStr">
         <is>
-          <t>Teacher Fhairudz</t>
+          <t>Teacher Wendelyn</t>
         </is>
       </c>
       <c r="R102" t="inlineStr">
@@ -9719,12 +9723,12 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>sec_grade_6_khaleed_ibn_waleed_2nd_shift</t>
+          <t>sec_grade_6_dihya_ibn_khalifah_2nd_shift_girls</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>GRADE 6 - KHALEED IBN WALEED (2ND SHIFT)</t>
+          <t>GRADE 6 - DIHYA IBN KHALIFAH (2ND SHIFT) GIRLS</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
@@ -9744,35 +9748,47 @@
       </c>
       <c r="J103" t="inlineStr">
         <is>
-          <t>subj_mapeh</t>
+          <t>subj_science</t>
         </is>
       </c>
       <c r="K103" t="inlineStr">
         <is>
-          <t>MAPEH</t>
-        </is>
-      </c>
-      <c r="L103" t="inlineStr"/>
+          <t>Science</t>
+        </is>
+      </c>
+      <c r="L103" t="inlineStr">
+        <is>
+          <t>tchr_fhairudz</t>
+        </is>
+      </c>
       <c r="M103" t="inlineStr">
         <is>
-          <t>Unassigned</t>
+          <t>Teacher Fhairudz</t>
         </is>
       </c>
       <c r="N103" t="inlineStr">
         <is>
-          <t>VACANT_REPLACEMENT_REQUIRED</t>
+          <t>ACTIVE_VERIFIED</t>
         </is>
       </c>
       <c r="O103" t="inlineStr">
         <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="P103" t="inlineStr"/>
-      <c r="Q103" t="inlineStr"/>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="P103" t="inlineStr">
+        <is>
+          <t>tchr_fhairudz</t>
+        </is>
+      </c>
+      <c r="Q103" t="inlineStr">
+        <is>
+          <t>Teacher Fhairudz</t>
+        </is>
+      </c>
       <c r="R103" t="inlineStr">
         <is>
-          <t>NOT_ASSIGNED</t>
+          <t>ACTIVE_ASSIGNED</t>
         </is>
       </c>
       <c r="S103" t="n">
@@ -9789,7 +9805,7 @@
         </is>
       </c>
       <c r="C104" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -9798,72 +9814,60 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>sec_grade_7_abu_sufyan_ibn_al_harith_1st_shift_boys</t>
+          <t>sec_grade_6_khaleed_ibn_waleed_2nd_shift</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>GRADE 7 - ABU SUFYAN IBN AL-HARITH (1ST SHIFT) BOYS</t>
+          <t>GRADE 6 - KHALEED IBN WALEED (2ND SHIFT)</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Junior High School</t>
+          <t>Elementary</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>Grade 7</t>
+          <t>Grade 6</t>
         </is>
       </c>
       <c r="I104" t="inlineStr">
         <is>
-          <t>ODL - 1ST SHIFT</t>
+          <t>ODL - 2ND SHIFT</t>
         </is>
       </c>
       <c r="J104" t="inlineStr">
         <is>
-          <t>subj_qur_an</t>
+          <t>subj_mapeh</t>
         </is>
       </c>
       <c r="K104" t="inlineStr">
         <is>
-          <t>Qur'an</t>
-        </is>
-      </c>
-      <c r="L104" t="inlineStr">
-        <is>
-          <t>tchr_jaisam</t>
-        </is>
-      </c>
+          <t>MAPEH</t>
+        </is>
+      </c>
+      <c r="L104" t="inlineStr"/>
       <c r="M104" t="inlineStr">
         <is>
-          <t>Ustadh Jaisam</t>
+          <t>Unassigned</t>
         </is>
       </c>
       <c r="N104" t="inlineStr">
         <is>
-          <t>ACTIVE_VERIFIED</t>
+          <t>VACANT_REPLACEMENT_REQUIRED</t>
         </is>
       </c>
       <c r="O104" t="inlineStr">
         <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="P104" t="inlineStr">
-        <is>
-          <t>tchr_jaisam</t>
-        </is>
-      </c>
-      <c r="Q104" t="inlineStr">
-        <is>
-          <t>Ustadh Jaisam</t>
-        </is>
-      </c>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="P104" t="inlineStr"/>
+      <c r="Q104" t="inlineStr"/>
       <c r="R104" t="inlineStr">
         <is>
-          <t>ACTIVE_ASSIGNED</t>
+          <t>NOT_ASSIGNED</t>
         </is>
       </c>
       <c r="S104" t="n">
@@ -9880,7 +9884,7 @@
         </is>
       </c>
       <c r="C105" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -9889,12 +9893,12 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>sec_grade_7_anas_ibn_malik_2nd_shift_mix</t>
+          <t>sec_grade_7_abu_sufyan_ibn_al_harith_1st_shift_boys</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>GRADE 7 - ANAS IBN MALIK (2ND SHIFT) - MIX</t>
+          <t>GRADE 7 - ABU SUFYAN IBN AL-HARITH (1ST SHIFT) BOYS</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
@@ -9909,27 +9913,27 @@
       </c>
       <c r="I105" t="inlineStr">
         <is>
-          <t>ODL - 2ND SHIFT</t>
+          <t>ODL - 1ST SHIFT</t>
         </is>
       </c>
       <c r="J105" t="inlineStr">
         <is>
-          <t>subj_science</t>
+          <t>subj_qur_an</t>
         </is>
       </c>
       <c r="K105" t="inlineStr">
         <is>
-          <t>Science</t>
+          <t>Qur'an</t>
         </is>
       </c>
       <c r="L105" t="inlineStr">
         <is>
-          <t>tchr_aniah</t>
+          <t>tchr_jaisam</t>
         </is>
       </c>
       <c r="M105" t="inlineStr">
         <is>
-          <t>Teacher Aniah</t>
+          <t>Ustadh Jaisam</t>
         </is>
       </c>
       <c r="N105" t="inlineStr">
@@ -9944,12 +9948,12 @@
       </c>
       <c r="P105" t="inlineStr">
         <is>
-          <t>tchr_aniah</t>
+          <t>tchr_jaisam</t>
         </is>
       </c>
       <c r="Q105" t="inlineStr">
         <is>
-          <t>Teacher Aniah</t>
+          <t>Ustadh Jaisam</t>
         </is>
       </c>
       <c r="R105" t="inlineStr">
@@ -9971,7 +9975,7 @@
         </is>
       </c>
       <c r="C106" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -9980,12 +9984,12 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>sec_grade_7_usama_ibn_zayd_1st_shift_girls</t>
+          <t>sec_grade_7_anas_ibn_malik_2nd_shift_mix</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>GRADE 7 - USAMA IBN ZAYD (1ST SHIFT) GIRLS</t>
+          <t>GRADE 7 - ANAS IBN MALIK (2ND SHIFT) - MIX</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
@@ -10000,27 +10004,27 @@
       </c>
       <c r="I106" t="inlineStr">
         <is>
-          <t>ODL - 1ST SHIFT</t>
+          <t>ODL - 2ND SHIFT</t>
         </is>
       </c>
       <c r="J106" t="inlineStr">
         <is>
-          <t>subj_social_studies</t>
+          <t>subj_science</t>
         </is>
       </c>
       <c r="K106" t="inlineStr">
         <is>
-          <t>Social Studies</t>
+          <t>Science</t>
         </is>
       </c>
       <c r="L106" t="inlineStr">
         <is>
-          <t>tchr_shirehan</t>
+          <t>tchr_aniah</t>
         </is>
       </c>
       <c r="M106" t="inlineStr">
         <is>
-          <t>Teacher Shirehan</t>
+          <t>Teacher Aniah</t>
         </is>
       </c>
       <c r="N106" t="inlineStr">
@@ -10035,12 +10039,12 @@
       </c>
       <c r="P106" t="inlineStr">
         <is>
-          <t>tchr_shirehan</t>
+          <t>tchr_aniah</t>
         </is>
       </c>
       <c r="Q106" t="inlineStr">
         <is>
-          <t>Teacher Shirehan</t>
+          <t>Teacher Aniah</t>
         </is>
       </c>
       <c r="R106" t="inlineStr">
@@ -10062,7 +10066,7 @@
         </is>
       </c>
       <c r="C107" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -10071,12 +10075,12 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>sec_grade_8_mu_adh_ibn_jabal_2nd_shift_boys</t>
+          <t>sec_grade_7_usama_ibn_zayd_1st_shift_girls</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>GRADE 8 - MU'ADH IBN JABAL (2ND SHIFT) - BOYS</t>
+          <t>GRADE 7 - USAMA IBN ZAYD (1ST SHIFT) GIRLS</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
@@ -10086,32 +10090,32 @@
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>Grade 8</t>
+          <t>Grade 7</t>
         </is>
       </c>
       <c r="I107" t="inlineStr">
         <is>
-          <t>ODL - 2ND SHIFT</t>
+          <t>ODL - 1ST SHIFT</t>
         </is>
       </c>
       <c r="J107" t="inlineStr">
         <is>
-          <t>subj_english</t>
+          <t>subj_social_studies</t>
         </is>
       </c>
       <c r="K107" t="inlineStr">
         <is>
-          <t>English</t>
+          <t>Social Studies</t>
         </is>
       </c>
       <c r="L107" t="inlineStr">
         <is>
-          <t>tchr_jairah</t>
+          <t>tchr_shirehan</t>
         </is>
       </c>
       <c r="M107" t="inlineStr">
         <is>
-          <t>Teacher Jairah</t>
+          <t>Teacher Shirehan</t>
         </is>
       </c>
       <c r="N107" t="inlineStr">
@@ -10126,12 +10130,12 @@
       </c>
       <c r="P107" t="inlineStr">
         <is>
-          <t>tchr_jairah</t>
+          <t>tchr_shirehan</t>
         </is>
       </c>
       <c r="Q107" t="inlineStr">
         <is>
-          <t>Teacher Jairah</t>
+          <t>Teacher Shirehan</t>
         </is>
       </c>
       <c r="R107" t="inlineStr">
@@ -10162,12 +10166,12 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>sec_grade_8_nuaym_ibn_mas_ud_2nd_shift_mix</t>
+          <t>sec_grade_8_mu_adh_ibn_jabal_2nd_shift_boys</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>GRADE 8 - NUAYM IBN MAS'UD (2ND SHIFT) MIX</t>
+          <t>GRADE 8 - MU'ADH IBN JABAL (2ND SHIFT) - BOYS</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
@@ -10187,22 +10191,22 @@
       </c>
       <c r="J108" t="inlineStr">
         <is>
-          <t>subj_filipino</t>
+          <t>subj_english</t>
         </is>
       </c>
       <c r="K108" t="inlineStr">
         <is>
-          <t>Filipino</t>
+          <t>English</t>
         </is>
       </c>
       <c r="L108" t="inlineStr">
         <is>
-          <t>tchr_sophia</t>
+          <t>tchr_jairah</t>
         </is>
       </c>
       <c r="M108" t="inlineStr">
         <is>
-          <t>Teacher Sophia</t>
+          <t>Teacher Jairah</t>
         </is>
       </c>
       <c r="N108" t="inlineStr">
@@ -10217,12 +10221,12 @@
       </c>
       <c r="P108" t="inlineStr">
         <is>
-          <t>tchr_sophia</t>
+          <t>tchr_jairah</t>
         </is>
       </c>
       <c r="Q108" t="inlineStr">
         <is>
-          <t>Teacher Sophia</t>
+          <t>Teacher Jairah</t>
         </is>
       </c>
       <c r="R108" t="inlineStr">
@@ -10244,7 +10248,7 @@
         </is>
       </c>
       <c r="C109" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -10253,12 +10257,12 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>sec_grade_8_sa_ad_ibn_mua_dh_1st_shift_girls</t>
+          <t>sec_grade_8_nuaym_ibn_mas_ud_2nd_shift_mix</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>GRADE 8 - SA'AD IBN MUA'DH (1ST SHIFT) - GIRLS</t>
+          <t>GRADE 8 - NUAYM IBN MAS'UD (2ND SHIFT) MIX</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
@@ -10273,27 +10277,27 @@
       </c>
       <c r="I109" t="inlineStr">
         <is>
-          <t>ODL - 1ST SHIFT</t>
+          <t>ODL - 2ND SHIFT</t>
         </is>
       </c>
       <c r="J109" t="inlineStr">
         <is>
-          <t>subj_tle</t>
+          <t>subj_filipino</t>
         </is>
       </c>
       <c r="K109" t="inlineStr">
         <is>
-          <t>TLE</t>
+          <t>Filipino</t>
         </is>
       </c>
       <c r="L109" t="inlineStr">
         <is>
-          <t>tchr_halnaisa</t>
+          <t>tchr_sophia</t>
         </is>
       </c>
       <c r="M109" t="inlineStr">
         <is>
-          <t>Teacher Halnaisa</t>
+          <t>Teacher Sophia</t>
         </is>
       </c>
       <c r="N109" t="inlineStr">
@@ -10308,12 +10312,12 @@
       </c>
       <c r="P109" t="inlineStr">
         <is>
-          <t>tchr_halnaisa</t>
+          <t>tchr_sophia</t>
         </is>
       </c>
       <c r="Q109" t="inlineStr">
         <is>
-          <t>Teacher Halnaisa</t>
+          <t>Teacher Sophia</t>
         </is>
       </c>
       <c r="R109" t="inlineStr">
@@ -10335,7 +10339,7 @@
         </is>
       </c>
       <c r="C110" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -10344,12 +10348,12 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>sec_grade_9_abu_dharr_al_ghifarri_2nd_shift_boys</t>
+          <t>sec_grade_8_sa_ad_ibn_mua_dh_1st_shift_girls</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>GRADE 9 - ABU DHARR AL GHIFARRI (2ND SHIFT) BOYS</t>
+          <t>GRADE 8 - SA'AD IBN MUA'DH (1ST SHIFT) - GIRLS</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
@@ -10359,32 +10363,32 @@
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>Grade 9</t>
+          <t>Grade 8</t>
         </is>
       </c>
       <c r="I110" t="inlineStr">
         <is>
-          <t>ODL - 2ND SHIFT</t>
+          <t>ODL - 1ST SHIFT</t>
         </is>
       </c>
       <c r="J110" t="inlineStr">
         <is>
-          <t>subj_qur_an</t>
+          <t>subj_tle</t>
         </is>
       </c>
       <c r="K110" t="inlineStr">
         <is>
-          <t>Qur'an</t>
+          <t>TLE</t>
         </is>
       </c>
       <c r="L110" t="inlineStr">
         <is>
-          <t>tchr_abdulwahab</t>
+          <t>tchr_halnaisa</t>
         </is>
       </c>
       <c r="M110" t="inlineStr">
         <is>
-          <t>Alim Abdulwahab</t>
+          <t>Teacher Halnaisa</t>
         </is>
       </c>
       <c r="N110" t="inlineStr">
@@ -10399,12 +10403,12 @@
       </c>
       <c r="P110" t="inlineStr">
         <is>
-          <t>tchr_abdulwahab</t>
+          <t>tchr_halnaisa</t>
         </is>
       </c>
       <c r="Q110" t="inlineStr">
         <is>
-          <t>Alim Abdulwahab</t>
+          <t>Teacher Halnaisa</t>
         </is>
       </c>
       <c r="R110" t="inlineStr">
@@ -10426,7 +10430,7 @@
         </is>
       </c>
       <c r="C111" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -10435,12 +10439,12 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>sec_grade_9_abu_hurayrah_1st_shift_girls</t>
+          <t>sec_grade_9_abu_dharr_al_ghifarri_2nd_shift_boys</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>GRADE 9 - ABU HURAYRAH (1ST SHIFT) GIRLS</t>
+          <t>GRADE 9 - ABU DHARR AL GHIFARRI (2ND SHIFT) BOYS</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
@@ -10455,27 +10459,27 @@
       </c>
       <c r="I111" t="inlineStr">
         <is>
-          <t>ODL - 1ST SHIFT</t>
+          <t>ODL - 2ND SHIFT</t>
         </is>
       </c>
       <c r="J111" t="inlineStr">
         <is>
-          <t>subj_tle</t>
+          <t>subj_qur_an</t>
         </is>
       </c>
       <c r="K111" t="inlineStr">
         <is>
-          <t>TLE</t>
+          <t>Qur'an</t>
         </is>
       </c>
       <c r="L111" t="inlineStr">
         <is>
-          <t>tchr_angeleni</t>
+          <t>tchr_abdulwahab</t>
         </is>
       </c>
       <c r="M111" t="inlineStr">
         <is>
-          <t>Teacher Angeleni</t>
+          <t>Alim Abdulwahab</t>
         </is>
       </c>
       <c r="N111" t="inlineStr">
@@ -10490,12 +10494,12 @@
       </c>
       <c r="P111" t="inlineStr">
         <is>
-          <t>tchr_angeleni</t>
+          <t>tchr_abdulwahab</t>
         </is>
       </c>
       <c r="Q111" t="inlineStr">
         <is>
-          <t>Teacher Angeleni</t>
+          <t>Alim Abdulwahab</t>
         </is>
       </c>
       <c r="R111" t="inlineStr">
@@ -10517,7 +10521,7 @@
         </is>
       </c>
       <c r="C112" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -10526,12 +10530,12 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>sec_grade_9_abu_jandal_ibn_suhayl_2nd_shift_girls</t>
+          <t>sec_grade_9_abu_hurayrah_1st_shift_girls</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>GRADE 9 - ABU JANDAL IBN SUHAYL (2ND SHIFT) GIRLS</t>
+          <t>GRADE 9 - ABU HURAYRAH (1ST SHIFT) GIRLS</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
@@ -10546,27 +10550,27 @@
       </c>
       <c r="I112" t="inlineStr">
         <is>
-          <t>ODL - 2ND SHIFT</t>
+          <t>ODL - 1ST SHIFT</t>
         </is>
       </c>
       <c r="J112" t="inlineStr">
         <is>
-          <t>subj_values_ed</t>
+          <t>subj_tle</t>
         </is>
       </c>
       <c r="K112" t="inlineStr">
         <is>
-          <t>Values Ed</t>
+          <t>TLE</t>
         </is>
       </c>
       <c r="L112" t="inlineStr">
         <is>
-          <t>tchr_nof</t>
+          <t>tchr_angeleni</t>
         </is>
       </c>
       <c r="M112" t="inlineStr">
         <is>
-          <t>Teacher Nof</t>
+          <t>Teacher Angeleni</t>
         </is>
       </c>
       <c r="N112" t="inlineStr">
@@ -10581,12 +10585,12 @@
       </c>
       <c r="P112" t="inlineStr">
         <is>
-          <t>tchr_nof</t>
+          <t>tchr_angeleni</t>
         </is>
       </c>
       <c r="Q112" t="inlineStr">
         <is>
-          <t>Teacher Nof</t>
+          <t>Teacher Angeleni</t>
         </is>
       </c>
       <c r="R112" t="inlineStr">
@@ -10617,22 +10621,22 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>sec_k2_abdullah_ibn_mas_ud_2nd_shift</t>
+          <t>sec_grade_9_abu_jandal_ibn_suhayl_2nd_shift_girls</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>K2 - ABDULLAH IBN MAS'UD (2ND SHIFT)</t>
+          <t>GRADE 9 - ABU JANDAL IBN SUHAYL (2ND SHIFT) GIRLS</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Elementary</t>
+          <t>Junior High School</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>Kinder 2</t>
+          <t>Grade 9</t>
         </is>
       </c>
       <c r="I113" t="inlineStr">
@@ -10642,22 +10646,22 @@
       </c>
       <c r="J113" t="inlineStr">
         <is>
-          <t>subj_qur_an</t>
+          <t>subj_values_ed</t>
         </is>
       </c>
       <c r="K113" t="inlineStr">
         <is>
-          <t>Qur'an</t>
+          <t>Values Ed</t>
         </is>
       </c>
       <c r="L113" t="inlineStr">
         <is>
-          <t>tchr_hainur</t>
+          <t>tchr_nof</t>
         </is>
       </c>
       <c r="M113" t="inlineStr">
         <is>
-          <t>Ustadha Hainur</t>
+          <t>Teacher Nof</t>
         </is>
       </c>
       <c r="N113" t="inlineStr">
@@ -10672,12 +10676,12 @@
       </c>
       <c r="P113" t="inlineStr">
         <is>
-          <t>tchr_hainur</t>
+          <t>tchr_nof</t>
         </is>
       </c>
       <c r="Q113" t="inlineStr">
         <is>
-          <t>Ustadha Hainur</t>
+          <t>Teacher Nof</t>
         </is>
       </c>
       <c r="R113" t="inlineStr">
@@ -10699,21 +10703,21 @@
         </is>
       </c>
       <c r="C114" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>04:20 PM – 05:20 PM</t>
+          <t>03:10 PM – 04:10 PM</t>
         </is>
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>sec_grade_1_suhayb_ar_rumi_2nd_shift</t>
+          <t>sec_k2_abdullah_ibn_mas_ud_2nd_shift</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>GRADE 1 - SUHAYB AR-RUMI (2ND SHIFT)</t>
+          <t>K2 - ABDULLAH IBN MAS'UD (2ND SHIFT)</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
@@ -10723,7 +10727,7 @@
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>Grade 1</t>
+          <t>Kinder 2</t>
         </is>
       </c>
       <c r="I114" t="inlineStr">
@@ -10733,22 +10737,22 @@
       </c>
       <c r="J114" t="inlineStr">
         <is>
-          <t>subj_math</t>
+          <t>subj_qur_an</t>
         </is>
       </c>
       <c r="K114" t="inlineStr">
         <is>
-          <t>Math</t>
+          <t>Qur'an</t>
         </is>
       </c>
       <c r="L114" t="inlineStr">
         <is>
-          <t>tchr_joanna</t>
+          <t>tchr_hainur</t>
         </is>
       </c>
       <c r="M114" t="inlineStr">
         <is>
-          <t>Teacher Joanna</t>
+          <t>Ustadha Hainur</t>
         </is>
       </c>
       <c r="N114" t="inlineStr">
@@ -10763,12 +10767,12 @@
       </c>
       <c r="P114" t="inlineStr">
         <is>
-          <t>tchr_joanna</t>
+          <t>tchr_hainur</t>
         </is>
       </c>
       <c r="Q114" t="inlineStr">
         <is>
-          <t>Teacher Joanna</t>
+          <t>Ustadha Hainur</t>
         </is>
       </c>
       <c r="R114" t="inlineStr">
@@ -10799,22 +10803,22 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>sec_grade_11_2nd_shift_boys</t>
+          <t>sec_grade_1_suhayb_ar_rumi_2nd_shift</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>GRADE 11 (2ND SHIFT BOYS)</t>
+          <t>GRADE 1 - SUHAYB AR-RUMI (2ND SHIFT)</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Senior High School</t>
+          <t>Elementary</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>Grade 11</t>
+          <t>Grade 1</t>
         </is>
       </c>
       <c r="I115" t="inlineStr">
@@ -10824,22 +10828,22 @@
       </c>
       <c r="J115" t="inlineStr">
         <is>
-          <t>subj_qur_an</t>
+          <t>subj_math</t>
         </is>
       </c>
       <c r="K115" t="inlineStr">
         <is>
-          <t>Qur'an</t>
+          <t>Math</t>
         </is>
       </c>
       <c r="L115" t="inlineStr">
         <is>
-          <t>tchr_abdulwahab</t>
+          <t>tchr_joanna</t>
         </is>
       </c>
       <c r="M115" t="inlineStr">
         <is>
-          <t>Alim Abdulwahab</t>
+          <t>Teacher Joanna</t>
         </is>
       </c>
       <c r="N115" t="inlineStr">
@@ -10854,12 +10858,12 @@
       </c>
       <c r="P115" t="inlineStr">
         <is>
-          <t>tchr_abdulwahab</t>
+          <t>tchr_joanna</t>
         </is>
       </c>
       <c r="Q115" t="inlineStr">
         <is>
-          <t>Alim Abdulwahab</t>
+          <t>Teacher Joanna</t>
         </is>
       </c>
       <c r="R115" t="inlineStr">
@@ -10890,22 +10894,22 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>sec_grade_2_saeed_ibn_zayd_2nd_shift</t>
+          <t>sec_grade_11_2nd_shift_boys</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>GRADE 2 - SAEED IBN ZAYD (2ND SHIFT)</t>
+          <t>GRADE 11 (2ND SHIFT BOYS)</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Elementary</t>
+          <t>Senior High School</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>Grade 2</t>
+          <t>Grade 11</t>
         </is>
       </c>
       <c r="I116" t="inlineStr">
@@ -10925,12 +10929,12 @@
       </c>
       <c r="L116" t="inlineStr">
         <is>
-          <t>tchr_obaydah</t>
+          <t>tchr_abdulwahab</t>
         </is>
       </c>
       <c r="M116" t="inlineStr">
         <is>
-          <t>Ustadh Obaydah</t>
+          <t>Alim Abdulwahab</t>
         </is>
       </c>
       <c r="N116" t="inlineStr">
@@ -10945,12 +10949,12 @@
       </c>
       <c r="P116" t="inlineStr">
         <is>
-          <t>tchr_obaydah</t>
+          <t>tchr_abdulwahab</t>
         </is>
       </c>
       <c r="Q116" t="inlineStr">
         <is>
-          <t>Ustadh Obaydah</t>
+          <t>Alim Abdulwahab</t>
         </is>
       </c>
       <c r="R116" t="inlineStr">
@@ -10981,12 +10985,12 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>sec_grade_3_thabit_ibn_qays_2nd_shift_boys</t>
+          <t>sec_grade_2_saeed_ibn_zayd_2nd_shift</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>GRADE 3 - THABIT IBN QAYS (2ND SHIFT) - BOYS</t>
+          <t>GRADE 2 - SAEED IBN ZAYD (2ND SHIFT)</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
@@ -10996,7 +11000,7 @@
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>Grade 3</t>
+          <t>Grade 2</t>
         </is>
       </c>
       <c r="I117" t="inlineStr">
@@ -11006,22 +11010,22 @@
       </c>
       <c r="J117" t="inlineStr">
         <is>
-          <t>subj_gmrc</t>
+          <t>subj_qur_an</t>
         </is>
       </c>
       <c r="K117" t="inlineStr">
         <is>
-          <t>GMRC</t>
+          <t>Qur'an</t>
         </is>
       </c>
       <c r="L117" t="inlineStr">
         <is>
-          <t>tchr_silfah</t>
+          <t>tchr_obaydah</t>
         </is>
       </c>
       <c r="M117" t="inlineStr">
         <is>
-          <t>Ustadh Silfah</t>
+          <t>Ustadh Obaydah</t>
         </is>
       </c>
       <c r="N117" t="inlineStr">
@@ -11036,12 +11040,12 @@
       </c>
       <c r="P117" t="inlineStr">
         <is>
-          <t>tchr_silfah</t>
+          <t>tchr_obaydah</t>
         </is>
       </c>
       <c r="Q117" t="inlineStr">
         <is>
-          <t>Ustadh Silfah</t>
+          <t>Ustadh Obaydah</t>
         </is>
       </c>
       <c r="R117" t="inlineStr">
@@ -11072,12 +11076,12 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>sec_grade_3_zayd_ibn_haritha_2nd_shift_girls</t>
+          <t>sec_grade_3_thabit_ibn_qays_2nd_shift_boys</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>GRADE 3 - ZAYD IBN HARITHA (2ND SHIFT) - GIRLS</t>
+          <t>GRADE 3 - THABIT IBN QAYS (2ND SHIFT) - BOYS</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
@@ -11097,38 +11101,42 @@
       </c>
       <c r="J118" t="inlineStr">
         <is>
-          <t>subj_makabansa</t>
+          <t>subj_gmrc</t>
         </is>
       </c>
       <c r="K118" t="inlineStr">
         <is>
-          <t>Makabansa</t>
-        </is>
-      </c>
-      <c r="L118" t="inlineStr"/>
+          <t>GMRC</t>
+        </is>
+      </c>
+      <c r="L118" t="inlineStr">
+        <is>
+          <t>tchr_silfah</t>
+        </is>
+      </c>
       <c r="M118" t="inlineStr">
         <is>
-          <t>Unassigned</t>
+          <t>Ustadh Silfah</t>
         </is>
       </c>
       <c r="N118" t="inlineStr">
         <is>
-          <t>VACANT_REPLACEMENT_REQUIRED</t>
+          <t>ACTIVE_VERIFIED</t>
         </is>
       </c>
       <c r="O118" t="inlineStr">
         <is>
-          <t>YES</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="P118" t="inlineStr">
         <is>
-          <t>tchr_ethel</t>
+          <t>tchr_silfah</t>
         </is>
       </c>
       <c r="Q118" t="inlineStr">
         <is>
-          <t>Teacher Ethel</t>
+          <t>Ustadh Silfah</t>
         </is>
       </c>
       <c r="R118" t="inlineStr">
@@ -11159,12 +11167,12 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>sec_grade_4_az_zubair_ibn_al_awwaam_2nd_shift</t>
+          <t>sec_grade_3_zayd_ibn_haritha_2nd_shift_girls</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>GRADE 4 - AZ ZUBAIR IBN AL AWWAAM (2ND SHIFT)</t>
+          <t>GRADE 3 - ZAYD IBN HARITHA (2ND SHIFT) - GIRLS</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
@@ -11174,7 +11182,7 @@
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>Grade 4</t>
+          <t>Grade 3</t>
         </is>
       </c>
       <c r="I119" t="inlineStr">
@@ -11184,22 +11192,22 @@
       </c>
       <c r="J119" t="inlineStr">
         <is>
-          <t>subj_english</t>
+          <t>subj_makabansa</t>
         </is>
       </c>
       <c r="K119" t="inlineStr">
         <is>
-          <t>English</t>
+          <t>Makabansa</t>
         </is>
       </c>
       <c r="L119" t="inlineStr">
         <is>
-          <t>tchr_arvin</t>
+          <t>tchr_franchette</t>
         </is>
       </c>
       <c r="M119" t="inlineStr">
         <is>
-          <t>Teacher Arvin</t>
+          <t>Teacher Franchette Zarah M. Ranain</t>
         </is>
       </c>
       <c r="N119" t="inlineStr">
@@ -11214,12 +11222,12 @@
       </c>
       <c r="P119" t="inlineStr">
         <is>
-          <t>tchr_arvin</t>
+          <t>tchr_franchette</t>
         </is>
       </c>
       <c r="Q119" t="inlineStr">
         <is>
-          <t>Teacher Arvin</t>
+          <t>Teacher Franchette Zarah M. Ranain</t>
         </is>
       </c>
       <c r="R119" t="inlineStr">
@@ -11250,12 +11258,12 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>sec_grade_4_ikrimah_ibn_abi_jahl_2nd_shift</t>
+          <t>sec_grade_4_az_zubair_ibn_al_awwaam_2nd_shift</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>GRADE 4 - IKRIMAH IBN ABI JAHL (2ND SHIFT)</t>
+          <t>GRADE 4 - AZ ZUBAIR IBN AL AWWAAM (2ND SHIFT)</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
@@ -11275,22 +11283,22 @@
       </c>
       <c r="J120" t="inlineStr">
         <is>
-          <t>subj_science</t>
+          <t>subj_english</t>
         </is>
       </c>
       <c r="K120" t="inlineStr">
         <is>
-          <t>Science</t>
+          <t>English</t>
         </is>
       </c>
       <c r="L120" t="inlineStr">
         <is>
-          <t>tchr_anna</t>
+          <t>tchr_arvin</t>
         </is>
       </c>
       <c r="M120" t="inlineStr">
         <is>
-          <t>Teacher Anna</t>
+          <t>Teacher Arvin</t>
         </is>
       </c>
       <c r="N120" t="inlineStr">
@@ -11305,12 +11313,12 @@
       </c>
       <c r="P120" t="inlineStr">
         <is>
-          <t>tchr_anna</t>
+          <t>tchr_arvin</t>
         </is>
       </c>
       <c r="Q120" t="inlineStr">
         <is>
-          <t>Teacher Anna</t>
+          <t>Teacher Arvin</t>
         </is>
       </c>
       <c r="R120" t="inlineStr">
@@ -11341,12 +11349,12 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>sec_grade_4_hassan_ibn_thabit_2nd_shift_mix</t>
+          <t>sec_grade_4_ikrimah_ibn_abi_jahl_2nd_shift</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>GRADE 4 -HASSAN IBN THABIT (2ND SHIFT) - MIX</t>
+          <t>GRADE 4 - IKRIMAH IBN ABI JAHL (2ND SHIFT)</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
@@ -11366,22 +11374,22 @@
       </c>
       <c r="J121" t="inlineStr">
         <is>
-          <t>subj_gmrc</t>
+          <t>subj_science</t>
         </is>
       </c>
       <c r="K121" t="inlineStr">
         <is>
-          <t>GMRC</t>
+          <t>Science</t>
         </is>
       </c>
       <c r="L121" t="inlineStr">
         <is>
-          <t>tchr_sahdia</t>
+          <t>tchr_anna</t>
         </is>
       </c>
       <c r="M121" t="inlineStr">
         <is>
-          <t>Teacher Sahdia</t>
+          <t>Teacher Anna</t>
         </is>
       </c>
       <c r="N121" t="inlineStr">
@@ -11396,12 +11404,12 @@
       </c>
       <c r="P121" t="inlineStr">
         <is>
-          <t>tchr_sahdia</t>
+          <t>tchr_anna</t>
         </is>
       </c>
       <c r="Q121" t="inlineStr">
         <is>
-          <t>Teacher Sahdia</t>
+          <t>Teacher Anna</t>
         </is>
       </c>
       <c r="R121" t="inlineStr">
@@ -11432,12 +11440,12 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>sec_grade_5_al_harith_bin_awf_2nd_shift</t>
+          <t>sec_grade_4_hassan_ibn_thabit_2nd_shift_mix</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>GRADE 5 - AL HARITH BIN AWF (2ND SHIFT)</t>
+          <t>GRADE 4 -HASSAN IBN THABIT (2ND SHIFT) - MIX</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
@@ -11447,7 +11455,7 @@
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>Grade 5</t>
+          <t>Grade 4</t>
         </is>
       </c>
       <c r="I122" t="inlineStr">
@@ -11457,22 +11465,22 @@
       </c>
       <c r="J122" t="inlineStr">
         <is>
-          <t>subj_english</t>
+          <t>subj_gmrc</t>
         </is>
       </c>
       <c r="K122" t="inlineStr">
         <is>
-          <t>English</t>
+          <t>GMRC</t>
         </is>
       </c>
       <c r="L122" t="inlineStr">
         <is>
-          <t>tchr_jessa</t>
+          <t>tchr_sahdia</t>
         </is>
       </c>
       <c r="M122" t="inlineStr">
         <is>
-          <t>Teacher Jessa</t>
+          <t>Teacher Sahdia</t>
         </is>
       </c>
       <c r="N122" t="inlineStr">
@@ -11487,12 +11495,12 @@
       </c>
       <c r="P122" t="inlineStr">
         <is>
-          <t>tchr_jessa</t>
+          <t>tchr_sahdia</t>
         </is>
       </c>
       <c r="Q122" t="inlineStr">
         <is>
-          <t>Teacher Jessa</t>
+          <t>Teacher Sahdia</t>
         </is>
       </c>
       <c r="R122" t="inlineStr">
@@ -11523,12 +11531,12 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>sec_grade_5_ja_far_ibn_abi_talib_2nd_shift_mix</t>
+          <t>sec_grade_5_al_harith_bin_awf_2nd_shift</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>GRADE 5 - JA'FAR IBN ABI TALIB (2ND SHIFT) - MIX</t>
+          <t>GRADE 5 - AL HARITH BIN AWF (2ND SHIFT)</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
@@ -11548,22 +11556,22 @@
       </c>
       <c r="J123" t="inlineStr">
         <is>
-          <t>subj_math</t>
+          <t>subj_english</t>
         </is>
       </c>
       <c r="K123" t="inlineStr">
         <is>
-          <t>Math</t>
+          <t>English</t>
         </is>
       </c>
       <c r="L123" t="inlineStr">
         <is>
-          <t>tchr_saimonah</t>
+          <t>tchr_jessa</t>
         </is>
       </c>
       <c r="M123" t="inlineStr">
         <is>
-          <t>Teacher Saimonah</t>
+          <t>Teacher Jessa</t>
         </is>
       </c>
       <c r="N123" t="inlineStr">
@@ -11578,12 +11586,12 @@
       </c>
       <c r="P123" t="inlineStr">
         <is>
-          <t>tchr_saimonah</t>
+          <t>tchr_jessa</t>
         </is>
       </c>
       <c r="Q123" t="inlineStr">
         <is>
-          <t>Teacher Saimonah</t>
+          <t>Teacher Jessa</t>
         </is>
       </c>
       <c r="R123" t="inlineStr">
@@ -11614,12 +11622,12 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>sec_grade_5_mus_ab_ibn_abdul_mutalib_2nd_shift</t>
+          <t>sec_grade_5_ja_far_ibn_abi_talib_2nd_shift_mix</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>GRADE 5 - MUS'AB IBN ABDUL MUTALIB (2ND SHIFT)</t>
+          <t>GRADE 5 - JA'FAR IBN ABI TALIB (2ND SHIFT) - MIX</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
@@ -11639,22 +11647,22 @@
       </c>
       <c r="J124" t="inlineStr">
         <is>
-          <t>subj_araling_panlipunan</t>
+          <t>subj_math</t>
         </is>
       </c>
       <c r="K124" t="inlineStr">
         <is>
-          <t>Araling Panlipunan</t>
+          <t>Math</t>
         </is>
       </c>
       <c r="L124" t="inlineStr">
         <is>
-          <t>tchr_monisa</t>
+          <t>tchr_saimonah</t>
         </is>
       </c>
       <c r="M124" t="inlineStr">
         <is>
-          <t>Teacher Monisa</t>
+          <t>Teacher Saimonah</t>
         </is>
       </c>
       <c r="N124" t="inlineStr">
@@ -11669,12 +11677,12 @@
       </c>
       <c r="P124" t="inlineStr">
         <is>
-          <t>tchr_monisa</t>
+          <t>tchr_saimonah</t>
         </is>
       </c>
       <c r="Q124" t="inlineStr">
         <is>
-          <t>Teacher Monisa</t>
+          <t>Teacher Saimonah</t>
         </is>
       </c>
       <c r="R124" t="inlineStr">
@@ -11705,12 +11713,12 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>sec_grade_6_dihya_ibn_khalifah_2nd_shift_girls</t>
+          <t>sec_grade_5_mus_ab_ibn_abdul_mutalib_2nd_shift</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>GRADE 6 - DIHYA IBN KHALIFAH (2ND SHIFT) GIRLS</t>
+          <t>GRADE 5 - MUS'AB IBN ABDUL MUTALIB (2ND SHIFT)</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
@@ -11720,7 +11728,7 @@
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>Grade 6</t>
+          <t>Grade 5</t>
         </is>
       </c>
       <c r="I125" t="inlineStr">
@@ -11730,22 +11738,22 @@
       </c>
       <c r="J125" t="inlineStr">
         <is>
-          <t>subj_shaf</t>
+          <t>subj_araling_panlipunan</t>
         </is>
       </c>
       <c r="K125" t="inlineStr">
         <is>
-          <t>SHAF</t>
+          <t>Araling Panlipunan</t>
         </is>
       </c>
       <c r="L125" t="inlineStr">
         <is>
-          <t>tchr_faidh</t>
+          <t>tchr_monisa</t>
         </is>
       </c>
       <c r="M125" t="inlineStr">
         <is>
-          <t>Ustadh Faidh</t>
+          <t>Teacher Monisa</t>
         </is>
       </c>
       <c r="N125" t="inlineStr">
@@ -11760,12 +11768,12 @@
       </c>
       <c r="P125" t="inlineStr">
         <is>
-          <t>tchr_faidh</t>
+          <t>tchr_monisa</t>
         </is>
       </c>
       <c r="Q125" t="inlineStr">
         <is>
-          <t>Ustadh Faidh</t>
+          <t>Teacher Monisa</t>
         </is>
       </c>
       <c r="R125" t="inlineStr">
@@ -11796,12 +11804,12 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>sec_grade_6_khaleed_ibn_waleed_2nd_shift</t>
+          <t>sec_grade_6_dihya_ibn_khalifah_2nd_shift_girls</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>GRADE 6 - KHALEED IBN WALEED (2ND SHIFT)</t>
+          <t>GRADE 6 - DIHYA IBN KHALIFAH (2ND SHIFT) GIRLS</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
@@ -11821,22 +11829,22 @@
       </c>
       <c r="J126" t="inlineStr">
         <is>
-          <t>subj_qur_an</t>
+          <t>subj_shaf</t>
         </is>
       </c>
       <c r="K126" t="inlineStr">
         <is>
-          <t>Qur'an</t>
+          <t>SHAF</t>
         </is>
       </c>
       <c r="L126" t="inlineStr">
         <is>
-          <t>tchr_jaisam</t>
+          <t>tchr_faidh</t>
         </is>
       </c>
       <c r="M126" t="inlineStr">
         <is>
-          <t>Ustadh Jaisam</t>
+          <t>Ustadh Faidh</t>
         </is>
       </c>
       <c r="N126" t="inlineStr">
@@ -11851,12 +11859,12 @@
       </c>
       <c r="P126" t="inlineStr">
         <is>
-          <t>tchr_jaisam</t>
+          <t>tchr_faidh</t>
         </is>
       </c>
       <c r="Q126" t="inlineStr">
         <is>
-          <t>Ustadh Jaisam</t>
+          <t>Ustadh Faidh</t>
         </is>
       </c>
       <c r="R126" t="inlineStr">
@@ -11887,22 +11895,22 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>sec_grade_7_anas_ibn_malik_2nd_shift_mix</t>
+          <t>sec_grade_6_khaleed_ibn_waleed_2nd_shift</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>GRADE 7 - ANAS IBN MALIK (2ND SHIFT) - MIX</t>
+          <t>GRADE 6 - KHALEED IBN WALEED (2ND SHIFT)</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>Junior High School</t>
+          <t>Elementary</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>Grade 7</t>
+          <t>Grade 6</t>
         </is>
       </c>
       <c r="I127" t="inlineStr">
@@ -11912,22 +11920,22 @@
       </c>
       <c r="J127" t="inlineStr">
         <is>
-          <t>subj_filipino</t>
+          <t>subj_qur_an</t>
         </is>
       </c>
       <c r="K127" t="inlineStr">
         <is>
-          <t>Filipino</t>
+          <t>Qur'an</t>
         </is>
       </c>
       <c r="L127" t="inlineStr">
         <is>
-          <t>tchr_sophia</t>
+          <t>tchr_jaisam</t>
         </is>
       </c>
       <c r="M127" t="inlineStr">
         <is>
-          <t>Teacher Sophia</t>
+          <t>Ustadh Jaisam</t>
         </is>
       </c>
       <c r="N127" t="inlineStr">
@@ -11942,12 +11950,12 @@
       </c>
       <c r="P127" t="inlineStr">
         <is>
-          <t>tchr_sophia</t>
+          <t>tchr_jaisam</t>
         </is>
       </c>
       <c r="Q127" t="inlineStr">
         <is>
-          <t>Teacher Sophia</t>
+          <t>Ustadh Jaisam</t>
         </is>
       </c>
       <c r="R127" t="inlineStr">
@@ -11978,12 +11986,12 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>sec_grade_8_mu_adh_ibn_jabal_2nd_shift_boys</t>
+          <t>sec_grade_7_anas_ibn_malik_2nd_shift_mix</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>GRADE 8 - MU'ADH IBN JABAL (2ND SHIFT) - BOYS</t>
+          <t>GRADE 7 - ANAS IBN MALIK (2ND SHIFT) - MIX</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
@@ -11993,7 +12001,7 @@
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>Grade 8</t>
+          <t>Grade 7</t>
         </is>
       </c>
       <c r="I128" t="inlineStr">
@@ -12003,22 +12011,22 @@
       </c>
       <c r="J128" t="inlineStr">
         <is>
-          <t>subj_arabic</t>
+          <t>subj_filipino</t>
         </is>
       </c>
       <c r="K128" t="inlineStr">
         <is>
-          <t>Arabic</t>
+          <t>Filipino</t>
         </is>
       </c>
       <c r="L128" t="inlineStr">
         <is>
-          <t>tchr_ali</t>
+          <t>tchr_sophia</t>
         </is>
       </c>
       <c r="M128" t="inlineStr">
         <is>
-          <t>Ustadh Ali</t>
+          <t>Teacher Sophia</t>
         </is>
       </c>
       <c r="N128" t="inlineStr">
@@ -12033,12 +12041,12 @@
       </c>
       <c r="P128" t="inlineStr">
         <is>
-          <t>tchr_ali</t>
+          <t>tchr_sophia</t>
         </is>
       </c>
       <c r="Q128" t="inlineStr">
         <is>
-          <t>Ustadh Ali</t>
+          <t>Teacher Sophia</t>
         </is>
       </c>
       <c r="R128" t="inlineStr">
@@ -12069,12 +12077,12 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>sec_grade_8_nuaym_ibn_mas_ud_2nd_shift_mix</t>
+          <t>sec_grade_8_mu_adh_ibn_jabal_2nd_shift_boys</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>GRADE 8 - NUAYM IBN MAS'UD (2ND SHIFT) MIX</t>
+          <t>GRADE 8 - MU'ADH IBN JABAL (2ND SHIFT) - BOYS</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
@@ -12094,22 +12102,22 @@
       </c>
       <c r="J129" t="inlineStr">
         <is>
-          <t>subj_english</t>
+          <t>subj_arabic</t>
         </is>
       </c>
       <c r="K129" t="inlineStr">
         <is>
-          <t>English</t>
+          <t>Arabic</t>
         </is>
       </c>
       <c r="L129" t="inlineStr">
         <is>
-          <t>tchr_jairah</t>
+          <t>tchr_ali</t>
         </is>
       </c>
       <c r="M129" t="inlineStr">
         <is>
-          <t>Teacher Jairah</t>
+          <t>Ustadh Ali</t>
         </is>
       </c>
       <c r="N129" t="inlineStr">
@@ -12124,12 +12132,12 @@
       </c>
       <c r="P129" t="inlineStr">
         <is>
-          <t>tchr_jairah</t>
+          <t>tchr_ali</t>
         </is>
       </c>
       <c r="Q129" t="inlineStr">
         <is>
-          <t>Teacher Jairah</t>
+          <t>Ustadh Ali</t>
         </is>
       </c>
       <c r="R129" t="inlineStr">
@@ -12160,12 +12168,12 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>sec_grade_9_abu_dharr_al_ghifarri_2nd_shift_boys</t>
+          <t>sec_grade_8_nuaym_ibn_mas_ud_2nd_shift_mix</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>GRADE 9 - ABU DHARR AL GHIFARRI (2ND SHIFT) BOYS</t>
+          <t>GRADE 8 - NUAYM IBN MAS'UD (2ND SHIFT) MIX</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
@@ -12175,7 +12183,7 @@
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>Grade 9</t>
+          <t>Grade 8</t>
         </is>
       </c>
       <c r="I130" t="inlineStr">
@@ -12185,22 +12193,22 @@
       </c>
       <c r="J130" t="inlineStr">
         <is>
-          <t>subj_values_ed</t>
+          <t>subj_english</t>
         </is>
       </c>
       <c r="K130" t="inlineStr">
         <is>
-          <t>Values Ed</t>
+          <t>English</t>
         </is>
       </c>
       <c r="L130" t="inlineStr">
         <is>
-          <t>tchr_nof</t>
+          <t>tchr_jairah</t>
         </is>
       </c>
       <c r="M130" t="inlineStr">
         <is>
-          <t>Teacher Nof</t>
+          <t>Teacher Jairah</t>
         </is>
       </c>
       <c r="N130" t="inlineStr">
@@ -12215,12 +12223,12 @@
       </c>
       <c r="P130" t="inlineStr">
         <is>
-          <t>tchr_nof</t>
+          <t>tchr_jairah</t>
         </is>
       </c>
       <c r="Q130" t="inlineStr">
         <is>
-          <t>Teacher Nof</t>
+          <t>Teacher Jairah</t>
         </is>
       </c>
       <c r="R130" t="inlineStr">
@@ -12251,12 +12259,12 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>sec_grade_9_abu_jandal_ibn_suhayl_2nd_shift_girls</t>
+          <t>sec_grade_9_abu_dharr_al_ghifarri_2nd_shift_boys</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>GRADE 9 - ABU JANDAL IBN SUHAYL (2ND SHIFT) GIRLS</t>
+          <t>GRADE 9 - ABU DHARR AL GHIFARRI (2ND SHIFT) BOYS</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
@@ -12276,22 +12284,22 @@
       </c>
       <c r="J131" t="inlineStr">
         <is>
-          <t>subj_shaf</t>
+          <t>subj_values_ed</t>
         </is>
       </c>
       <c r="K131" t="inlineStr">
         <is>
-          <t>SHAF</t>
+          <t>Values Ed</t>
         </is>
       </c>
       <c r="L131" t="inlineStr">
         <is>
-          <t>tchr_samsuddin</t>
+          <t>tchr_nof</t>
         </is>
       </c>
       <c r="M131" t="inlineStr">
         <is>
-          <t>Alim Samsuddin</t>
+          <t>Teacher Nof</t>
         </is>
       </c>
       <c r="N131" t="inlineStr">
@@ -12306,12 +12314,12 @@
       </c>
       <c r="P131" t="inlineStr">
         <is>
-          <t>tchr_samsuddin</t>
+          <t>tchr_nof</t>
         </is>
       </c>
       <c r="Q131" t="inlineStr">
         <is>
-          <t>Alim Samsuddin</t>
+          <t>Teacher Nof</t>
         </is>
       </c>
       <c r="R131" t="inlineStr">
@@ -12342,22 +12350,22 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>sec_k1_husain_ibn_ali_2nd_shift</t>
+          <t>sec_grade_9_abu_jandal_ibn_suhayl_2nd_shift_girls</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>K1 - HUSAIN IBN ALI (2ND SHIFT)</t>
+          <t>GRADE 9 - ABU JANDAL IBN SUHAYL (2ND SHIFT) GIRLS</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>Elementary</t>
+          <t>Junior High School</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>Kinder 1</t>
+          <t>Grade 9</t>
         </is>
       </c>
       <c r="I132" t="inlineStr">
@@ -12367,35 +12375,47 @@
       </c>
       <c r="J132" t="inlineStr">
         <is>
-          <t>subj_qur_an</t>
+          <t>subj_shaf</t>
         </is>
       </c>
       <c r="K132" t="inlineStr">
         <is>
-          <t>Qur'an</t>
-        </is>
-      </c>
-      <c r="L132" t="inlineStr"/>
+          <t>SHAF</t>
+        </is>
+      </c>
+      <c r="L132" t="inlineStr">
+        <is>
+          <t>tchr_samsuddin</t>
+        </is>
+      </c>
       <c r="M132" t="inlineStr">
         <is>
-          <t>Unassigned</t>
+          <t>Alim Samsuddin</t>
         </is>
       </c>
       <c r="N132" t="inlineStr">
         <is>
-          <t>VACANT_REPLACEMENT_REQUIRED</t>
+          <t>ACTIVE_VERIFIED</t>
         </is>
       </c>
       <c r="O132" t="inlineStr">
         <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="P132" t="inlineStr"/>
-      <c r="Q132" t="inlineStr"/>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="P132" t="inlineStr">
+        <is>
+          <t>tchr_samsuddin</t>
+        </is>
+      </c>
+      <c r="Q132" t="inlineStr">
+        <is>
+          <t>Alim Samsuddin</t>
+        </is>
+      </c>
       <c r="R132" t="inlineStr">
         <is>
-          <t>NOT_ASSIGNED</t>
+          <t>ACTIVE_ASSIGNED</t>
         </is>
       </c>
       <c r="S132" t="n">
@@ -12421,12 +12441,12 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>sec_kinder_2_khabaab_ibn_arat_2nd_shift</t>
+          <t>sec_k1_husain_ibn_ali_2nd_shift</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Kinder 2 KHABAAB IBN ARAT (2ND SHIFT)</t>
+          <t>K1 - HUSAIN IBN ALI (2ND SHIFT)</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
@@ -12436,7 +12456,7 @@
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>Kinder 2</t>
+          <t>Kinder 1</t>
         </is>
       </c>
       <c r="I133" t="inlineStr">
@@ -12446,47 +12466,35 @@
       </c>
       <c r="J133" t="inlineStr">
         <is>
-          <t>subj_oral_written_exam</t>
+          <t>subj_qur_an</t>
         </is>
       </c>
       <c r="K133" t="inlineStr">
         <is>
-          <t>Oral &amp; Written Exam</t>
-        </is>
-      </c>
-      <c r="L133" t="inlineStr">
-        <is>
-          <t>tchr_sitti_kauzar</t>
-        </is>
-      </c>
+          <t>Qur'an</t>
+        </is>
+      </c>
+      <c r="L133" t="inlineStr"/>
       <c r="M133" t="inlineStr">
         <is>
-          <t>Teacher Sitti Kauzar</t>
+          <t>Unassigned</t>
         </is>
       </c>
       <c r="N133" t="inlineStr">
         <is>
-          <t>ACTIVE_VERIFIED</t>
+          <t>VACANT_REPLACEMENT_REQUIRED</t>
         </is>
       </c>
       <c r="O133" t="inlineStr">
         <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="P133" t="inlineStr">
-        <is>
-          <t>tchr_sitti_kauzar</t>
-        </is>
-      </c>
-      <c r="Q133" t="inlineStr">
-        <is>
-          <t>Teacher Sitti Kauzar</t>
-        </is>
-      </c>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="P133" t="inlineStr"/>
+      <c r="Q133" t="inlineStr"/>
       <c r="R133" t="inlineStr">
         <is>
-          <t>ACTIVE_ASSIGNED</t>
+          <t>NOT_ASSIGNED</t>
         </is>
       </c>
       <c r="S133" t="n">
@@ -12503,21 +12511,21 @@
         </is>
       </c>
       <c r="C134" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>05:30 PM – 06:30 PM</t>
+          <t>04:20 PM – 05:20 PM</t>
         </is>
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>sec_grade_1_sa_ad_ibn_abi_waqqaas_2nd_shift</t>
+          <t>sec_kinder_2_khabaab_ibn_arat_2nd_shift</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>GRADE 1 - SA'AD IBN ABI WAQQAAS (2ND SHIFT)</t>
+          <t>Kinder 2 KHABAAB IBN ARAT (2ND SHIFT)</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
@@ -12527,7 +12535,7 @@
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>Grade 1</t>
+          <t>Kinder 2</t>
         </is>
       </c>
       <c r="I134" t="inlineStr">
@@ -12537,22 +12545,22 @@
       </c>
       <c r="J134" t="inlineStr">
         <is>
-          <t>subj_qur_an</t>
+          <t>subj_oral_written_exam</t>
         </is>
       </c>
       <c r="K134" t="inlineStr">
         <is>
-          <t>Qur'an</t>
+          <t>Oral &amp; Written Exam</t>
         </is>
       </c>
       <c r="L134" t="inlineStr">
         <is>
-          <t>tchr_hainur</t>
+          <t>tchr_sitti_kauzar</t>
         </is>
       </c>
       <c r="M134" t="inlineStr">
         <is>
-          <t>Ustadha Hainur</t>
+          <t>Teacher Sitti Kauzar</t>
         </is>
       </c>
       <c r="N134" t="inlineStr">
@@ -12567,12 +12575,12 @@
       </c>
       <c r="P134" t="inlineStr">
         <is>
-          <t>tchr_hainur</t>
+          <t>tchr_sitti_kauzar</t>
         </is>
       </c>
       <c r="Q134" t="inlineStr">
         <is>
-          <t>Ustadha Hainur</t>
+          <t>Teacher Sitti Kauzar</t>
         </is>
       </c>
       <c r="R134" t="inlineStr">
@@ -12603,22 +12611,22 @@
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>sec_grade_10_abu_ayyub_al_ansari_2nd_shift_boys</t>
+          <t>sec_grade_1_sa_ad_ibn_abi_waqqaas_2nd_shift</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>GRADE 10 - ABU AYYUB AL-ANSARI (2ND SHIFT) BOYS</t>
+          <t>GRADE 1 - SA'AD IBN ABI WAQQAAS (2ND SHIFT)</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>Junior High School</t>
+          <t>Elementary</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>Grade 10</t>
+          <t>Grade 1</t>
         </is>
       </c>
       <c r="I135" t="inlineStr">
@@ -12628,22 +12636,22 @@
       </c>
       <c r="J135" t="inlineStr">
         <is>
-          <t>subj_values_ed</t>
+          <t>subj_qur_an</t>
         </is>
       </c>
       <c r="K135" t="inlineStr">
         <is>
-          <t>Values Ed</t>
+          <t>Qur'an</t>
         </is>
       </c>
       <c r="L135" t="inlineStr">
         <is>
-          <t>tchr_nof</t>
+          <t>tchr_hainur</t>
         </is>
       </c>
       <c r="M135" t="inlineStr">
         <is>
-          <t>Teacher Nof</t>
+          <t>Ustadha Hainur</t>
         </is>
       </c>
       <c r="N135" t="inlineStr">
@@ -12658,12 +12666,12 @@
       </c>
       <c r="P135" t="inlineStr">
         <is>
-          <t>tchr_nof</t>
+          <t>tchr_hainur</t>
         </is>
       </c>
       <c r="Q135" t="inlineStr">
         <is>
-          <t>Teacher Nof</t>
+          <t>Ustadha Hainur</t>
         </is>
       </c>
       <c r="R135" t="inlineStr">
@@ -12694,22 +12702,22 @@
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>sec_grade_11_2nd_shift_boys</t>
+          <t>sec_grade_10_abu_ayyub_al_ansari_2nd_shift_boys</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>GRADE 11 (2ND SHIFT BOYS)</t>
+          <t>GRADE 10 - ABU AYYUB AL-ANSARI (2ND SHIFT) BOYS</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>Senior High School</t>
+          <t>Junior High School</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>Grade 11</t>
+          <t>Grade 10</t>
         </is>
       </c>
       <c r="I136" t="inlineStr">
@@ -12719,22 +12727,22 @@
       </c>
       <c r="J136" t="inlineStr">
         <is>
-          <t>subj_gen_science</t>
+          <t>subj_values_ed</t>
         </is>
       </c>
       <c r="K136" t="inlineStr">
         <is>
-          <t>Gen Science</t>
+          <t>Values Ed</t>
         </is>
       </c>
       <c r="L136" t="inlineStr">
         <is>
-          <t>tchr_rowena</t>
+          <t>tchr_nof</t>
         </is>
       </c>
       <c r="M136" t="inlineStr">
         <is>
-          <t>Teacher Rowena</t>
+          <t>Teacher Nof</t>
         </is>
       </c>
       <c r="N136" t="inlineStr">
@@ -12749,12 +12757,12 @@
       </c>
       <c r="P136" t="inlineStr">
         <is>
-          <t>tchr_rowena</t>
+          <t>tchr_nof</t>
         </is>
       </c>
       <c r="Q136" t="inlineStr">
         <is>
-          <t>Teacher Rowena</t>
+          <t>Teacher Nof</t>
         </is>
       </c>
       <c r="R136" t="inlineStr">
@@ -12785,22 +12793,22 @@
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>sec_grade_2_aasim_ibn_thabit_2nd_shift</t>
+          <t>sec_grade_11_2nd_shift_boys</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>GRADE 2 - AASIM IBN THABIT (2ND SHIFT)</t>
+          <t>GRADE 11 (2ND SHIFT BOYS)</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>Elementary</t>
+          <t>Senior High School</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>Grade 2</t>
+          <t>Grade 11</t>
         </is>
       </c>
       <c r="I137" t="inlineStr">
@@ -12810,22 +12818,22 @@
       </c>
       <c r="J137" t="inlineStr">
         <is>
-          <t>subj_english</t>
+          <t>subj_gen_science</t>
         </is>
       </c>
       <c r="K137" t="inlineStr">
         <is>
-          <t>English</t>
+          <t>Gen Science</t>
         </is>
       </c>
       <c r="L137" t="inlineStr">
         <is>
-          <t>tchr_marham</t>
+          <t>tchr_rowena</t>
         </is>
       </c>
       <c r="M137" t="inlineStr">
         <is>
-          <t>Teacher Marham</t>
+          <t>Teacher Rowena</t>
         </is>
       </c>
       <c r="N137" t="inlineStr">
@@ -12840,12 +12848,12 @@
       </c>
       <c r="P137" t="inlineStr">
         <is>
-          <t>tchr_marham</t>
+          <t>tchr_rowena</t>
         </is>
       </c>
       <c r="Q137" t="inlineStr">
         <is>
-          <t>Teacher Marham</t>
+          <t>Teacher Rowena</t>
         </is>
       </c>
       <c r="R137" t="inlineStr">
@@ -12876,12 +12884,12 @@
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>sec_grade_3_as_ad_ibn_zurarah_2nd_shift_mix</t>
+          <t>sec_grade_2_aasim_ibn_thabit_2nd_shift</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>GRADE 3 - AS'AD IBN ZURARAH (2ND SHIFT) MIX</t>
+          <t>GRADE 2 - AASIM IBN THABIT (2ND SHIFT)</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
@@ -12891,7 +12899,7 @@
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>Grade 3</t>
+          <t>Grade 2</t>
         </is>
       </c>
       <c r="I138" t="inlineStr">
@@ -12901,22 +12909,22 @@
       </c>
       <c r="J138" t="inlineStr">
         <is>
-          <t>subj_makabansa</t>
+          <t>subj_english</t>
         </is>
       </c>
       <c r="K138" t="inlineStr">
         <is>
-          <t>Makabansa</t>
+          <t>English</t>
         </is>
       </c>
       <c r="L138" t="inlineStr">
         <is>
-          <t>tchr_jenny</t>
+          <t>tchr_marham</t>
         </is>
       </c>
       <c r="M138" t="inlineStr">
         <is>
-          <t>Teacher Jenny</t>
+          <t>Teacher Marham</t>
         </is>
       </c>
       <c r="N138" t="inlineStr">
@@ -12931,12 +12939,12 @@
       </c>
       <c r="P138" t="inlineStr">
         <is>
-          <t>tchr_jenny</t>
+          <t>tchr_marham</t>
         </is>
       </c>
       <c r="Q138" t="inlineStr">
         <is>
-          <t>Teacher Jenny</t>
+          <t>Teacher Marham</t>
         </is>
       </c>
       <c r="R138" t="inlineStr">
@@ -12967,12 +12975,12 @@
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>sec_grade_4_az_zubair_ibn_al_awwaam_2nd_shift</t>
+          <t>sec_grade_3_as_ad_ibn_zurarah_2nd_shift_mix</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>GRADE 4 - AZ ZUBAIR IBN AL AWWAAM (2ND SHIFT)</t>
+          <t>GRADE 3 - AS'AD IBN ZURARAH (2ND SHIFT) MIX</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
@@ -12982,7 +12990,7 @@
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>Grade 4</t>
+          <t>Grade 3</t>
         </is>
       </c>
       <c r="I139" t="inlineStr">
@@ -12992,22 +13000,22 @@
       </c>
       <c r="J139" t="inlineStr">
         <is>
-          <t>subj_qur_an</t>
+          <t>subj_makabansa</t>
         </is>
       </c>
       <c r="K139" t="inlineStr">
         <is>
-          <t>Qur'an</t>
+          <t>Makabansa</t>
         </is>
       </c>
       <c r="L139" t="inlineStr">
         <is>
-          <t>tchr_obaydah</t>
+          <t>tchr_jenny</t>
         </is>
       </c>
       <c r="M139" t="inlineStr">
         <is>
-          <t>Ustadh Obaydah</t>
+          <t>Teacher Jenny</t>
         </is>
       </c>
       <c r="N139" t="inlineStr">
@@ -13022,12 +13030,12 @@
       </c>
       <c r="P139" t="inlineStr">
         <is>
-          <t>tchr_obaydah</t>
+          <t>tchr_jenny</t>
         </is>
       </c>
       <c r="Q139" t="inlineStr">
         <is>
-          <t>Ustadh Obaydah</t>
+          <t>Teacher Jenny</t>
         </is>
       </c>
       <c r="R139" t="inlineStr">
@@ -13058,12 +13066,12 @@
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>sec_grade_4_ikrimah_ibn_abi_jahl_2nd_shift</t>
+          <t>sec_grade_4_az_zubair_ibn_al_awwaam_2nd_shift</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>GRADE 4 - IKRIMAH IBN ABI JAHL (2ND SHIFT)</t>
+          <t>GRADE 4 - AZ ZUBAIR IBN AL AWWAAM (2ND SHIFT)</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
@@ -13083,22 +13091,22 @@
       </c>
       <c r="J140" t="inlineStr">
         <is>
-          <t>subj_english</t>
+          <t>subj_qur_an</t>
         </is>
       </c>
       <c r="K140" t="inlineStr">
         <is>
-          <t>English</t>
+          <t>Qur'an</t>
         </is>
       </c>
       <c r="L140" t="inlineStr">
         <is>
-          <t>tchr_arvin</t>
+          <t>tchr_obaydah</t>
         </is>
       </c>
       <c r="M140" t="inlineStr">
         <is>
-          <t>Teacher Arvin</t>
+          <t>Ustadh Obaydah</t>
         </is>
       </c>
       <c r="N140" t="inlineStr">
@@ -13113,12 +13121,12 @@
       </c>
       <c r="P140" t="inlineStr">
         <is>
-          <t>tchr_arvin</t>
+          <t>tchr_obaydah</t>
         </is>
       </c>
       <c r="Q140" t="inlineStr">
         <is>
-          <t>Teacher Arvin</t>
+          <t>Ustadh Obaydah</t>
         </is>
       </c>
       <c r="R140" t="inlineStr">
@@ -13149,12 +13157,12 @@
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>sec_grade_4_hassan_ibn_thabit_2nd_shift_mix</t>
+          <t>sec_grade_4_ikrimah_ibn_abi_jahl_2nd_shift</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>GRADE 4 -HASSAN IBN THABIT (2ND SHIFT) - MIX</t>
+          <t>GRADE 4 - IKRIMAH IBN ABI JAHL (2ND SHIFT)</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
@@ -13174,22 +13182,22 @@
       </c>
       <c r="J141" t="inlineStr">
         <is>
-          <t>subj_qur_an</t>
+          <t>subj_english</t>
         </is>
       </c>
       <c r="K141" t="inlineStr">
         <is>
-          <t>Qur'an</t>
+          <t>English</t>
         </is>
       </c>
       <c r="L141" t="inlineStr">
         <is>
-          <t>tchr_faidh</t>
+          <t>tchr_arvin</t>
         </is>
       </c>
       <c r="M141" t="inlineStr">
         <is>
-          <t>Ustadh Faidh</t>
+          <t>Teacher Arvin</t>
         </is>
       </c>
       <c r="N141" t="inlineStr">
@@ -13204,12 +13212,12 @@
       </c>
       <c r="P141" t="inlineStr">
         <is>
-          <t>tchr_faidh</t>
+          <t>tchr_arvin</t>
         </is>
       </c>
       <c r="Q141" t="inlineStr">
         <is>
-          <t>Ustadh Faidh</t>
+          <t>Teacher Arvin</t>
         </is>
       </c>
       <c r="R141" t="inlineStr">
@@ -13240,12 +13248,12 @@
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>sec_grade_5_al_harith_bin_awf_2nd_shift</t>
+          <t>sec_grade_4_hassan_ibn_thabit_2nd_shift_mix</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>GRADE 5 - AL HARITH BIN AWF (2ND SHIFT)</t>
+          <t>GRADE 4 -HASSAN IBN THABIT (2ND SHIFT) - MIX</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
@@ -13255,7 +13263,7 @@
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>Grade 5</t>
+          <t>Grade 4</t>
         </is>
       </c>
       <c r="I142" t="inlineStr">
@@ -13265,22 +13273,22 @@
       </c>
       <c r="J142" t="inlineStr">
         <is>
-          <t>subj_gmrc</t>
+          <t>subj_qur_an</t>
         </is>
       </c>
       <c r="K142" t="inlineStr">
         <is>
-          <t>GMRC</t>
+          <t>Qur'an</t>
         </is>
       </c>
       <c r="L142" t="inlineStr">
         <is>
-          <t>tchr_jairah</t>
+          <t>tchr_faidh</t>
         </is>
       </c>
       <c r="M142" t="inlineStr">
         <is>
-          <t>Teacher Jairah</t>
+          <t>Ustadh Faidh</t>
         </is>
       </c>
       <c r="N142" t="inlineStr">
@@ -13295,12 +13303,12 @@
       </c>
       <c r="P142" t="inlineStr">
         <is>
-          <t>tchr_jairah</t>
+          <t>tchr_faidh</t>
         </is>
       </c>
       <c r="Q142" t="inlineStr">
         <is>
-          <t>Teacher Jairah</t>
+          <t>Ustadh Faidh</t>
         </is>
       </c>
       <c r="R142" t="inlineStr">
@@ -13331,12 +13339,12 @@
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>sec_grade_5_mus_ab_ibn_abdul_mutalib_2nd_shift</t>
+          <t>sec_grade_5_al_harith_bin_awf_2nd_shift</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>GRADE 5 - MUS'AB IBN ABDUL MUTALIB (2ND SHIFT)</t>
+          <t>GRADE 5 - AL HARITH BIN AWF (2ND SHIFT)</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
@@ -13356,22 +13364,22 @@
       </c>
       <c r="J143" t="inlineStr">
         <is>
-          <t>subj_tle</t>
+          <t>subj_gmrc</t>
         </is>
       </c>
       <c r="K143" t="inlineStr">
         <is>
-          <t>TLE</t>
+          <t>GMRC</t>
         </is>
       </c>
       <c r="L143" t="inlineStr">
         <is>
-          <t>tchr_anna</t>
+          <t>tchr_jairah</t>
         </is>
       </c>
       <c r="M143" t="inlineStr">
         <is>
-          <t>Teacher Anna</t>
+          <t>Teacher Jairah</t>
         </is>
       </c>
       <c r="N143" t="inlineStr">
@@ -13386,12 +13394,12 @@
       </c>
       <c r="P143" t="inlineStr">
         <is>
-          <t>tchr_anna</t>
+          <t>tchr_jairah</t>
         </is>
       </c>
       <c r="Q143" t="inlineStr">
         <is>
-          <t>Teacher Anna</t>
+          <t>Teacher Jairah</t>
         </is>
       </c>
       <c r="R143" t="inlineStr">
@@ -13422,12 +13430,12 @@
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>sec_grade_6_dihya_ibn_khalifah_2nd_shift_girls</t>
+          <t>sec_grade_5_mus_ab_ibn_abdul_mutalib_2nd_shift</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>GRADE 6 - DIHYA IBN KHALIFAH (2ND SHIFT) GIRLS</t>
+          <t>GRADE 5 - MUS'AB IBN ABDUL MUTALIB (2ND SHIFT)</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
@@ -13437,7 +13445,7 @@
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t>Grade 6</t>
+          <t>Grade 5</t>
         </is>
       </c>
       <c r="I144" t="inlineStr">
@@ -13447,22 +13455,22 @@
       </c>
       <c r="J144" t="inlineStr">
         <is>
-          <t>subj_english</t>
+          <t>subj_tle</t>
         </is>
       </c>
       <c r="K144" t="inlineStr">
         <is>
-          <t>English</t>
+          <t>TLE</t>
         </is>
       </c>
       <c r="L144" t="inlineStr">
         <is>
-          <t>tchr_jessa</t>
+          <t>tchr_anna</t>
         </is>
       </c>
       <c r="M144" t="inlineStr">
         <is>
-          <t>Teacher Jessa</t>
+          <t>Teacher Anna</t>
         </is>
       </c>
       <c r="N144" t="inlineStr">
@@ -13477,12 +13485,12 @@
       </c>
       <c r="P144" t="inlineStr">
         <is>
-          <t>tchr_jessa</t>
+          <t>tchr_anna</t>
         </is>
       </c>
       <c r="Q144" t="inlineStr">
         <is>
-          <t>Teacher Jessa</t>
+          <t>Teacher Anna</t>
         </is>
       </c>
       <c r="R144" t="inlineStr">
@@ -13513,12 +13521,12 @@
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>sec_grade_6_khaleed_ibn_waleed_2nd_shift</t>
+          <t>sec_grade_6_dihya_ibn_khalifah_2nd_shift_girls</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>GRADE 6 - KHALEED IBN WALEED (2ND SHIFT)</t>
+          <t>GRADE 6 - DIHYA IBN KHALIFAH (2ND SHIFT) GIRLS</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
@@ -13538,22 +13546,22 @@
       </c>
       <c r="J145" t="inlineStr">
         <is>
-          <t>subj_gmrc</t>
+          <t>subj_english</t>
         </is>
       </c>
       <c r="K145" t="inlineStr">
         <is>
-          <t>GMRC</t>
+          <t>English</t>
         </is>
       </c>
       <c r="L145" t="inlineStr">
         <is>
-          <t>tchr_zuhora</t>
+          <t>tchr_jessa</t>
         </is>
       </c>
       <c r="M145" t="inlineStr">
         <is>
-          <t>Teacher Zuhora</t>
+          <t>Teacher Jessa</t>
         </is>
       </c>
       <c r="N145" t="inlineStr">
@@ -13568,12 +13576,12 @@
       </c>
       <c r="P145" t="inlineStr">
         <is>
-          <t>tchr_zuhora</t>
+          <t>tchr_jessa</t>
         </is>
       </c>
       <c r="Q145" t="inlineStr">
         <is>
-          <t>Teacher Zuhora</t>
+          <t>Teacher Jessa</t>
         </is>
       </c>
       <c r="R145" t="inlineStr">
@@ -13604,22 +13612,22 @@
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>sec_grade_7_anas_ibn_malik_2nd_shift_mix</t>
+          <t>sec_grade_6_khaleed_ibn_waleed_2nd_shift</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>GRADE 7 - ANAS IBN MALIK (2ND SHIFT) - MIX</t>
+          <t>GRADE 6 - KHALEED IBN WALEED (2ND SHIFT)</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>Junior High School</t>
+          <t>Elementary</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t>Grade 7</t>
+          <t>Grade 6</t>
         </is>
       </c>
       <c r="I146" t="inlineStr">
@@ -13629,22 +13637,22 @@
       </c>
       <c r="J146" t="inlineStr">
         <is>
-          <t>subj_social_studies</t>
+          <t>subj_gmrc</t>
         </is>
       </c>
       <c r="K146" t="inlineStr">
         <is>
-          <t>Social Studies</t>
+          <t>GMRC</t>
         </is>
       </c>
       <c r="L146" t="inlineStr">
         <is>
-          <t>tchr_shirehan</t>
+          <t>tchr_zuhora</t>
         </is>
       </c>
       <c r="M146" t="inlineStr">
         <is>
-          <t>Teacher Shirehan</t>
+          <t>Teacher Zuhora</t>
         </is>
       </c>
       <c r="N146" t="inlineStr">
@@ -13659,12 +13667,12 @@
       </c>
       <c r="P146" t="inlineStr">
         <is>
-          <t>tchr_keychell</t>
+          <t>tchr_zuhora</t>
         </is>
       </c>
       <c r="Q146" t="inlineStr">
         <is>
-          <t>Teacher Keychelle</t>
+          <t>Teacher Zuhora</t>
         </is>
       </c>
       <c r="R146" t="inlineStr">
@@ -13695,12 +13703,12 @@
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>sec_grade_8_mu_adh_ibn_jabal_2nd_shift_boys</t>
+          <t>sec_grade_7_anas_ibn_malik_2nd_shift_mix</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>GRADE 8 - MU'ADH IBN JABAL (2ND SHIFT) - BOYS</t>
+          <t>GRADE 7 - ANAS IBN MALIK (2ND SHIFT) - MIX</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
@@ -13710,7 +13718,7 @@
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t>Grade 8</t>
+          <t>Grade 7</t>
         </is>
       </c>
       <c r="I147" t="inlineStr">
@@ -13720,22 +13728,22 @@
       </c>
       <c r="J147" t="inlineStr">
         <is>
-          <t>subj_shaf</t>
+          <t>subj_social_studies</t>
         </is>
       </c>
       <c r="K147" t="inlineStr">
         <is>
-          <t>SHAF</t>
+          <t>Social Studies</t>
         </is>
       </c>
       <c r="L147" t="inlineStr">
         <is>
-          <t>tchr_samsuddin</t>
+          <t>tchr_shirehan</t>
         </is>
       </c>
       <c r="M147" t="inlineStr">
         <is>
-          <t>Alim Samsuddin</t>
+          <t>Teacher Shirehan</t>
         </is>
       </c>
       <c r="N147" t="inlineStr">
@@ -13750,12 +13758,12 @@
       </c>
       <c r="P147" t="inlineStr">
         <is>
-          <t>tchr_samsuddin</t>
+          <t>tchr_keychell</t>
         </is>
       </c>
       <c r="Q147" t="inlineStr">
         <is>
-          <t>Alim Samsuddin</t>
+          <t>Teacher Keychelle</t>
         </is>
       </c>
       <c r="R147" t="inlineStr">
@@ -13786,12 +13794,12 @@
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>sec_grade_8_nuaym_ibn_mas_ud_2nd_shift_mix</t>
+          <t>sec_grade_8_mu_adh_ibn_jabal_2nd_shift_boys</t>
         </is>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>GRADE 8 - NUAYM IBN MAS'UD (2ND SHIFT) MIX</t>
+          <t>GRADE 8 - MU'ADH IBN JABAL (2ND SHIFT) - BOYS</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
@@ -13811,22 +13819,22 @@
       </c>
       <c r="J148" t="inlineStr">
         <is>
-          <t>subj_qur_an</t>
+          <t>subj_shaf</t>
         </is>
       </c>
       <c r="K148" t="inlineStr">
         <is>
-          <t>Qur'an</t>
+          <t>SHAF</t>
         </is>
       </c>
       <c r="L148" t="inlineStr">
         <is>
-          <t>tchr_jaisam</t>
+          <t>tchr_samsuddin</t>
         </is>
       </c>
       <c r="M148" t="inlineStr">
         <is>
-          <t>Ustadh Jaisam</t>
+          <t>Alim Samsuddin</t>
         </is>
       </c>
       <c r="N148" t="inlineStr">
@@ -13841,12 +13849,12 @@
       </c>
       <c r="P148" t="inlineStr">
         <is>
-          <t>tchr_jaisam</t>
+          <t>tchr_samsuddin</t>
         </is>
       </c>
       <c r="Q148" t="inlineStr">
         <is>
-          <t>Ustadh Jaisam</t>
+          <t>Alim Samsuddin</t>
         </is>
       </c>
       <c r="R148" t="inlineStr">
@@ -13877,12 +13885,12 @@
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>sec_grade_9_abu_dharr_al_ghifarri_2nd_shift_boys</t>
+          <t>sec_grade_8_nuaym_ibn_mas_ud_2nd_shift_mix</t>
         </is>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>GRADE 9 - ABU DHARR AL GHIFARRI (2ND SHIFT) BOYS</t>
+          <t>GRADE 8 - NUAYM IBN MAS'UD (2ND SHIFT) MIX</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
@@ -13892,7 +13900,7 @@
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t>Grade 9</t>
+          <t>Grade 8</t>
         </is>
       </c>
       <c r="I149" t="inlineStr">
@@ -13902,22 +13910,22 @@
       </c>
       <c r="J149" t="inlineStr">
         <is>
-          <t>subj_arabic</t>
+          <t>subj_qur_an</t>
         </is>
       </c>
       <c r="K149" t="inlineStr">
         <is>
-          <t>Arabic</t>
+          <t>Qur'an</t>
         </is>
       </c>
       <c r="L149" t="inlineStr">
         <is>
-          <t>tchr_ali</t>
+          <t>tchr_jaisam</t>
         </is>
       </c>
       <c r="M149" t="inlineStr">
         <is>
-          <t>Ustadh Ali</t>
+          <t>Ustadh Jaisam</t>
         </is>
       </c>
       <c r="N149" t="inlineStr">
@@ -13932,12 +13940,12 @@
       </c>
       <c r="P149" t="inlineStr">
         <is>
-          <t>tchr_ali</t>
+          <t>tchr_jaisam</t>
         </is>
       </c>
       <c r="Q149" t="inlineStr">
         <is>
-          <t>Ustadh Ali</t>
+          <t>Ustadh Jaisam</t>
         </is>
       </c>
       <c r="R149" t="inlineStr">
@@ -13968,12 +13976,12 @@
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>sec_grade_9_abu_jandal_ibn_suhayl_2nd_shift_girls</t>
+          <t>sec_grade_9_abu_dharr_al_ghifarri_2nd_shift_boys</t>
         </is>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>GRADE 9 - ABU JANDAL IBN SUHAYL (2ND SHIFT) GIRLS</t>
+          <t>GRADE 9 - ABU DHARR AL GHIFARRI (2ND SHIFT) BOYS</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
@@ -13993,22 +14001,22 @@
       </c>
       <c r="J150" t="inlineStr">
         <is>
-          <t>subj_qur_an</t>
+          <t>subj_arabic</t>
         </is>
       </c>
       <c r="K150" t="inlineStr">
         <is>
-          <t>Qur'an</t>
+          <t>Arabic</t>
         </is>
       </c>
       <c r="L150" t="inlineStr">
         <is>
-          <t>tchr_abdulwahab</t>
+          <t>tchr_ali</t>
         </is>
       </c>
       <c r="M150" t="inlineStr">
         <is>
-          <t>Alim Abdulwahab</t>
+          <t>Ustadh Ali</t>
         </is>
       </c>
       <c r="N150" t="inlineStr">
@@ -14023,12 +14031,12 @@
       </c>
       <c r="P150" t="inlineStr">
         <is>
-          <t>tchr_abdulwahab</t>
+          <t>tchr_ali</t>
         </is>
       </c>
       <c r="Q150" t="inlineStr">
         <is>
-          <t>Alim Abdulwahab</t>
+          <t>Ustadh Ali</t>
         </is>
       </c>
       <c r="R150" t="inlineStr">
@@ -14059,22 +14067,22 @@
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>sec_k2_umar_ibn_al_khattab_2nd_shift</t>
+          <t>sec_grade_9_abu_jandal_ibn_suhayl_2nd_shift_girls</t>
         </is>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>K2 - UMAR IBN AL-KHATTAB (2ND SHIFT)</t>
+          <t>GRADE 9 - ABU JANDAL IBN SUHAYL (2ND SHIFT) GIRLS</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>Elementary</t>
+          <t>Junior High School</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t>Kinder 2</t>
+          <t>Grade 9</t>
         </is>
       </c>
       <c r="I151" t="inlineStr">
@@ -14084,22 +14092,22 @@
       </c>
       <c r="J151" t="inlineStr">
         <is>
-          <t>subj_oral_written_exam</t>
+          <t>subj_qur_an</t>
         </is>
       </c>
       <c r="K151" t="inlineStr">
         <is>
-          <t>Oral &amp; Written Exam</t>
+          <t>Qur'an</t>
         </is>
       </c>
       <c r="L151" t="inlineStr">
         <is>
-          <t>tchr_joanna</t>
+          <t>tchr_abdulwahab</t>
         </is>
       </c>
       <c r="M151" t="inlineStr">
         <is>
-          <t>Teacher Joanna</t>
+          <t>Alim Abdulwahab</t>
         </is>
       </c>
       <c r="N151" t="inlineStr">
@@ -14114,12 +14122,12 @@
       </c>
       <c r="P151" t="inlineStr">
         <is>
-          <t>tchr_joanna</t>
+          <t>tchr_abdulwahab</t>
         </is>
       </c>
       <c r="Q151" t="inlineStr">
         <is>
-          <t>Teacher Joanna</t>
+          <t>Alim Abdulwahab</t>
         </is>
       </c>
       <c r="R151" t="inlineStr">
@@ -14133,29 +14141,29 @@
     </row>
     <row r="152">
       <c r="A152" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>Thursday, September 3, 2026</t>
+          <t>Wednesday, September 2, 2026</t>
         </is>
       </c>
       <c r="C152" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>08:00 AM – 09:00 AM</t>
+          <t>05:30 PM – 06:30 PM</t>
         </is>
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>sec_grade_6_face_to_face</t>
+          <t>sec_k2_umar_ibn_al_khattab_2nd_shift</t>
         </is>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>GRADE  6  FACE TO FACE</t>
+          <t>K2 - UMAR IBN AL-KHATTAB (2ND SHIFT)</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
@@ -14165,32 +14173,32 @@
       </c>
       <c r="H152" t="inlineStr">
         <is>
-          <t>Grade 6</t>
+          <t>Kinder 2</t>
         </is>
       </c>
       <c r="I152" t="inlineStr">
         <is>
-          <t>F2F</t>
+          <t>ODL - 2ND SHIFT</t>
         </is>
       </c>
       <c r="J152" t="inlineStr">
         <is>
-          <t>subj_science</t>
+          <t>subj_oral_written_exam</t>
         </is>
       </c>
       <c r="K152" t="inlineStr">
         <is>
-          <t>Science</t>
+          <t>Oral &amp; Written Exam</t>
         </is>
       </c>
       <c r="L152" t="inlineStr">
         <is>
-          <t>tchr_wendy</t>
+          <t>tchr_joanna</t>
         </is>
       </c>
       <c r="M152" t="inlineStr">
         <is>
-          <t>Teacher Wendelyn</t>
+          <t>Teacher Joanna</t>
         </is>
       </c>
       <c r="N152" t="inlineStr">
@@ -14205,12 +14213,12 @@
       </c>
       <c r="P152" t="inlineStr">
         <is>
-          <t>tchr_wendy</t>
+          <t>tchr_joanna</t>
         </is>
       </c>
       <c r="Q152" t="inlineStr">
         <is>
-          <t>Teacher Wendelyn</t>
+          <t>Teacher Joanna</t>
         </is>
       </c>
       <c r="R152" t="inlineStr">
@@ -14241,12 +14249,12 @@
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>sec_grade_1_face_to_face</t>
+          <t>sec_grade_6_face_to_face</t>
         </is>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>GRADE 1 (FACE TO FACE)</t>
+          <t>GRADE  6  FACE TO FACE</t>
         </is>
       </c>
       <c r="G153" t="inlineStr">
@@ -14256,7 +14264,7 @@
       </c>
       <c r="H153" t="inlineStr">
         <is>
-          <t>Grade 1</t>
+          <t>Grade 6</t>
         </is>
       </c>
       <c r="I153" t="inlineStr">
@@ -14266,22 +14274,22 @@
       </c>
       <c r="J153" t="inlineStr">
         <is>
-          <t>subj_gmrc</t>
+          <t>subj_science</t>
         </is>
       </c>
       <c r="K153" t="inlineStr">
         <is>
-          <t>GMRC</t>
+          <t>Science</t>
         </is>
       </c>
       <c r="L153" t="inlineStr">
         <is>
-          <t>tchr_saliha</t>
+          <t>tchr_wendy</t>
         </is>
       </c>
       <c r="M153" t="inlineStr">
         <is>
-          <t>Ustadha Saliha</t>
+          <t>Teacher Wendelyn</t>
         </is>
       </c>
       <c r="N153" t="inlineStr">
@@ -14296,12 +14304,12 @@
       </c>
       <c r="P153" t="inlineStr">
         <is>
-          <t>tchr_saliha</t>
+          <t>tchr_wendy</t>
         </is>
       </c>
       <c r="Q153" t="inlineStr">
         <is>
-          <t>Ustadha Saliha</t>
+          <t>Teacher Wendelyn</t>
         </is>
       </c>
       <c r="R153" t="inlineStr">
@@ -14327,27 +14335,27 @@
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>08:00 AM – 10:00 AM</t>
+          <t>08:00 AM – 09:00 AM</t>
         </is>
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>sec_grade_11_face_to_face</t>
+          <t>sec_grade_1_face_to_face</t>
         </is>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>GRADE 11 (FACE TO FACE)</t>
+          <t>GRADE 1 (FACE TO FACE)</t>
         </is>
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>Senior High School</t>
+          <t>Elementary</t>
         </is>
       </c>
       <c r="H154" t="inlineStr">
         <is>
-          <t>Grade 11</t>
+          <t>Grade 1</t>
         </is>
       </c>
       <c r="I154" t="inlineStr">
@@ -14357,22 +14365,22 @@
       </c>
       <c r="J154" t="inlineStr">
         <is>
-          <t>subj_gen_math_hr</t>
+          <t>subj_gmrc</t>
         </is>
       </c>
       <c r="K154" t="inlineStr">
         <is>
-          <t>Gen Math</t>
+          <t>GMRC</t>
         </is>
       </c>
       <c r="L154" t="inlineStr">
         <is>
-          <t>tchr_jhelyn</t>
+          <t>tchr_saliha</t>
         </is>
       </c>
       <c r="M154" t="inlineStr">
         <is>
-          <t>Teacher Jhelyn</t>
+          <t>Ustadha Saliha</t>
         </is>
       </c>
       <c r="N154" t="inlineStr">
@@ -14387,12 +14395,12 @@
       </c>
       <c r="P154" t="inlineStr">
         <is>
-          <t>tchr_jhelyn</t>
+          <t>tchr_saliha</t>
         </is>
       </c>
       <c r="Q154" t="inlineStr">
         <is>
-          <t>Teacher Jhelyn</t>
+          <t>Ustadha Saliha</t>
         </is>
       </c>
       <c r="R154" t="inlineStr">
@@ -14401,7 +14409,7 @@
         </is>
       </c>
       <c r="S154" t="n">
-        <v>120</v>
+        <v>60</v>
       </c>
     </row>
     <row r="155">
@@ -14418,17 +14426,17 @@
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>08:00 AM – 09:00 AM</t>
+          <t>08:00 AM – 10:00 AM</t>
         </is>
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>sec_grade_12_suhayb_ar_rumi</t>
+          <t>sec_grade_11_face_to_face</t>
         </is>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>GRADE 12 - SUHAYB AR-RUMI</t>
+          <t>GRADE 11 (FACE TO FACE)</t>
         </is>
       </c>
       <c r="G155" t="inlineStr">
@@ -14438,7 +14446,7 @@
       </c>
       <c r="H155" t="inlineStr">
         <is>
-          <t>Grade 12</t>
+          <t>Grade 11</t>
         </is>
       </c>
       <c r="I155" t="inlineStr">
@@ -14448,22 +14456,22 @@
       </c>
       <c r="J155" t="inlineStr">
         <is>
-          <t>subj_pe_12</t>
+          <t>subj_gen_math_hr</t>
         </is>
       </c>
       <c r="K155" t="inlineStr">
         <is>
-          <t>PE 12</t>
+          <t>Gen Math</t>
         </is>
       </c>
       <c r="L155" t="inlineStr">
         <is>
-          <t>tchr_mohaymen</t>
+          <t>tchr_jhelyn</t>
         </is>
       </c>
       <c r="M155" t="inlineStr">
         <is>
-          <t>Sir Mohaymen</t>
+          <t>Teacher Jhelyn</t>
         </is>
       </c>
       <c r="N155" t="inlineStr">
@@ -14478,12 +14486,12 @@
       </c>
       <c r="P155" t="inlineStr">
         <is>
-          <t>tchr_mohaymen</t>
+          <t>tchr_jhelyn</t>
         </is>
       </c>
       <c r="Q155" t="inlineStr">
         <is>
-          <t>Sir Mohaymen</t>
+          <t>Teacher Jhelyn</t>
         </is>
       </c>
       <c r="R155" t="inlineStr">
@@ -14492,7 +14500,7 @@
         </is>
       </c>
       <c r="S155" t="n">
-        <v>60</v>
+        <v>120</v>
       </c>
     </row>
     <row r="156">
@@ -14514,22 +14522,22 @@
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>sec_grade_2_face_to_face</t>
+          <t>sec_grade_12_suhayb_ar_rumi</t>
         </is>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>GRADE 2 (FACE TO FACE)</t>
+          <t>GRADE 12 - SUHAYB AR-RUMI</t>
         </is>
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>Elementary</t>
+          <t>Senior High School</t>
         </is>
       </c>
       <c r="H156" t="inlineStr">
         <is>
-          <t>Grade 2</t>
+          <t>Grade 12</t>
         </is>
       </c>
       <c r="I156" t="inlineStr">
@@ -14539,22 +14547,22 @@
       </c>
       <c r="J156" t="inlineStr">
         <is>
-          <t>subj_makabansa</t>
+          <t>subj_pe_12</t>
         </is>
       </c>
       <c r="K156" t="inlineStr">
         <is>
-          <t>Makabansa</t>
+          <t>PE 12</t>
         </is>
       </c>
       <c r="L156" t="inlineStr">
         <is>
-          <t>tchr_monisa</t>
+          <t>tchr_mohaymen</t>
         </is>
       </c>
       <c r="M156" t="inlineStr">
         <is>
-          <t>Teacher Monisa</t>
+          <t>Sir Mohaymen</t>
         </is>
       </c>
       <c r="N156" t="inlineStr">
@@ -14569,12 +14577,12 @@
       </c>
       <c r="P156" t="inlineStr">
         <is>
-          <t>tchr_monisa</t>
+          <t>tchr_mohaymen</t>
         </is>
       </c>
       <c r="Q156" t="inlineStr">
         <is>
-          <t>Teacher Monisa</t>
+          <t>Sir Mohaymen</t>
         </is>
       </c>
       <c r="R156" t="inlineStr">
@@ -14605,12 +14613,12 @@
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>sec_grade_3_face_to_face</t>
+          <t>sec_grade_2_face_to_face</t>
         </is>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>GRADE 3 (FACE TO FACE)</t>
+          <t>GRADE 2 (FACE TO FACE)</t>
         </is>
       </c>
       <c r="G157" t="inlineStr">
@@ -14620,7 +14628,7 @@
       </c>
       <c r="H157" t="inlineStr">
         <is>
-          <t>Grade 3</t>
+          <t>Grade 2</t>
         </is>
       </c>
       <c r="I157" t="inlineStr">
@@ -14630,22 +14638,22 @@
       </c>
       <c r="J157" t="inlineStr">
         <is>
-          <t>subj_english</t>
+          <t>subj_makabansa</t>
         </is>
       </c>
       <c r="K157" t="inlineStr">
         <is>
-          <t>English</t>
+          <t>Makabansa</t>
         </is>
       </c>
       <c r="L157" t="inlineStr">
         <is>
-          <t>tchr_marham</t>
+          <t>tchr_monisa</t>
         </is>
       </c>
       <c r="M157" t="inlineStr">
         <is>
-          <t>Teacher Marham</t>
+          <t>Teacher Monisa</t>
         </is>
       </c>
       <c r="N157" t="inlineStr">
@@ -14660,12 +14668,12 @@
       </c>
       <c r="P157" t="inlineStr">
         <is>
-          <t>tchr_marham</t>
+          <t>tchr_monisa</t>
         </is>
       </c>
       <c r="Q157" t="inlineStr">
         <is>
-          <t>Teacher Marham</t>
+          <t>Teacher Monisa</t>
         </is>
       </c>
       <c r="R157" t="inlineStr">
@@ -14696,12 +14704,12 @@
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>sec_grade_4_face_to_face</t>
+          <t>sec_grade_3_face_to_face</t>
         </is>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>GRADE 4 (FACE TO FACE)</t>
+          <t>GRADE 3 (FACE TO FACE)</t>
         </is>
       </c>
       <c r="G158" t="inlineStr">
@@ -14711,7 +14719,7 @@
       </c>
       <c r="H158" t="inlineStr">
         <is>
-          <t>Grade 4</t>
+          <t>Grade 3</t>
         </is>
       </c>
       <c r="I158" t="inlineStr">
@@ -14721,22 +14729,22 @@
       </c>
       <c r="J158" t="inlineStr">
         <is>
-          <t>subj_shaf</t>
+          <t>subj_english</t>
         </is>
       </c>
       <c r="K158" t="inlineStr">
         <is>
-          <t>SHAF</t>
+          <t>English</t>
         </is>
       </c>
       <c r="L158" t="inlineStr">
         <is>
-          <t>tchr_abdiraheem</t>
+          <t>tchr_marham</t>
         </is>
       </c>
       <c r="M158" t="inlineStr">
         <is>
-          <t>Ustadh Abdiraheem</t>
+          <t>Teacher Marham</t>
         </is>
       </c>
       <c r="N158" t="inlineStr">
@@ -14751,12 +14759,12 @@
       </c>
       <c r="P158" t="inlineStr">
         <is>
-          <t>tchr_abdiraheem</t>
+          <t>tchr_marham</t>
         </is>
       </c>
       <c r="Q158" t="inlineStr">
         <is>
-          <t>Ustadh Abdiraheem</t>
+          <t>Teacher Marham</t>
         </is>
       </c>
       <c r="R158" t="inlineStr">
@@ -14787,12 +14795,12 @@
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>sec_grade_5_face_to_face</t>
+          <t>sec_grade_4_face_to_face</t>
         </is>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>GRADE 5 (FACE TO FACE)</t>
+          <t>GRADE 4 (FACE TO FACE)</t>
         </is>
       </c>
       <c r="G159" t="inlineStr">
@@ -14802,7 +14810,7 @@
       </c>
       <c r="H159" t="inlineStr">
         <is>
-          <t>Grade 5</t>
+          <t>Grade 4</t>
         </is>
       </c>
       <c r="I159" t="inlineStr">
@@ -14812,22 +14820,22 @@
       </c>
       <c r="J159" t="inlineStr">
         <is>
-          <t>subj_math</t>
+          <t>subj_shaf</t>
         </is>
       </c>
       <c r="K159" t="inlineStr">
         <is>
-          <t>Math</t>
+          <t>SHAF</t>
         </is>
       </c>
       <c r="L159" t="inlineStr">
         <is>
-          <t>tchr_fhairudz</t>
+          <t>tchr_abdiraheem</t>
         </is>
       </c>
       <c r="M159" t="inlineStr">
         <is>
-          <t>Teacher Fhairudz</t>
+          <t>Ustadh Abdiraheem</t>
         </is>
       </c>
       <c r="N159" t="inlineStr">
@@ -14842,12 +14850,12 @@
       </c>
       <c r="P159" t="inlineStr">
         <is>
-          <t>tchr_fhairudz</t>
+          <t>tchr_abdiraheem</t>
         </is>
       </c>
       <c r="Q159" t="inlineStr">
         <is>
-          <t>Teacher Fhairudz</t>
+          <t>Ustadh Abdiraheem</t>
         </is>
       </c>
       <c r="R159" t="inlineStr">
@@ -14878,22 +14886,22 @@
       </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t>sec_grade_7_8_boys_face_to_face</t>
+          <t>sec_grade_5_face_to_face</t>
         </is>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>GRADE 7 &amp; 8 BOYS (FACE TO FACE)</t>
+          <t>GRADE 5 (FACE TO FACE)</t>
         </is>
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>Junior High School</t>
+          <t>Elementary</t>
         </is>
       </c>
       <c r="H160" t="inlineStr">
         <is>
-          <t>Grade 7 &amp; 8</t>
+          <t>Grade 5</t>
         </is>
       </c>
       <c r="I160" t="inlineStr">
@@ -14903,22 +14911,22 @@
       </c>
       <c r="J160" t="inlineStr">
         <is>
-          <t>subj_qur_an</t>
+          <t>subj_math</t>
         </is>
       </c>
       <c r="K160" t="inlineStr">
         <is>
-          <t>Qur'an</t>
+          <t>Math</t>
         </is>
       </c>
       <c r="L160" t="inlineStr">
         <is>
-          <t>tchr_jaisam</t>
+          <t>tchr_fhairudz</t>
         </is>
       </c>
       <c r="M160" t="inlineStr">
         <is>
-          <t>Ustadh Jaisam</t>
+          <t>Teacher Fhairudz</t>
         </is>
       </c>
       <c r="N160" t="inlineStr">
@@ -14933,12 +14941,12 @@
       </c>
       <c r="P160" t="inlineStr">
         <is>
-          <t>tchr_jaisam</t>
+          <t>tchr_fhairudz</t>
         </is>
       </c>
       <c r="Q160" t="inlineStr">
         <is>
-          <t>Ustadh Jaisam</t>
+          <t>Teacher Fhairudz</t>
         </is>
       </c>
       <c r="R160" t="inlineStr">
@@ -14969,12 +14977,12 @@
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>sec_grade_7_8_girls_face_to_face</t>
+          <t>sec_grade_7_8_boys_face_to_face</t>
         </is>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>GRADE 7 &amp; 8 GIRLS (FACE TO FACE)</t>
+          <t>GRADE 7 &amp; 8 BOYS (FACE TO FACE)</t>
         </is>
       </c>
       <c r="G161" t="inlineStr">
@@ -14994,22 +15002,22 @@
       </c>
       <c r="J161" t="inlineStr">
         <is>
-          <t>subj_social_studies</t>
+          <t>subj_qur_an</t>
         </is>
       </c>
       <c r="K161" t="inlineStr">
         <is>
-          <t>Social Studies</t>
+          <t>Qur'an</t>
         </is>
       </c>
       <c r="L161" t="inlineStr">
         <is>
-          <t>tchr_shirehan</t>
+          <t>tchr_jaisam</t>
         </is>
       </c>
       <c r="M161" t="inlineStr">
         <is>
-          <t>Teacher Shirehan</t>
+          <t>Ustadh Jaisam</t>
         </is>
       </c>
       <c r="N161" t="inlineStr">
@@ -15024,12 +15032,12 @@
       </c>
       <c r="P161" t="inlineStr">
         <is>
-          <t>tchr_shirehan</t>
+          <t>tchr_jaisam</t>
         </is>
       </c>
       <c r="Q161" t="inlineStr">
         <is>
-          <t>Teacher Shirehan</t>
+          <t>Ustadh Jaisam</t>
         </is>
       </c>
       <c r="R161" t="inlineStr">
@@ -15060,12 +15068,12 @@
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t>sec_grade_9_10_boys_face_to_face</t>
+          <t>sec_grade_7_8_girls_face_to_face</t>
         </is>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>GRADE 9 &amp; 10 BOYS (FACE TO FACE)</t>
+          <t>GRADE 7 &amp; 8 GIRLS (FACE TO FACE)</t>
         </is>
       </c>
       <c r="G162" t="inlineStr">
@@ -15075,7 +15083,7 @@
       </c>
       <c r="H162" t="inlineStr">
         <is>
-          <t>Grade 9 &amp; 10</t>
+          <t>Grade 7 &amp; 8</t>
         </is>
       </c>
       <c r="I162" t="inlineStr">
@@ -15085,22 +15093,22 @@
       </c>
       <c r="J162" t="inlineStr">
         <is>
-          <t>subj_qur_an</t>
+          <t>subj_social_studies</t>
         </is>
       </c>
       <c r="K162" t="inlineStr">
         <is>
-          <t>Qur'an</t>
+          <t>Social Studies</t>
         </is>
       </c>
       <c r="L162" t="inlineStr">
         <is>
-          <t>tchr_abdulwahab</t>
+          <t>tchr_shirehan</t>
         </is>
       </c>
       <c r="M162" t="inlineStr">
         <is>
-          <t>Alim Abdulwahab</t>
+          <t>Teacher Shirehan</t>
         </is>
       </c>
       <c r="N162" t="inlineStr">
@@ -15115,12 +15123,12 @@
       </c>
       <c r="P162" t="inlineStr">
         <is>
-          <t>tchr_abdulwahab</t>
+          <t>tchr_shirehan</t>
         </is>
       </c>
       <c r="Q162" t="inlineStr">
         <is>
-          <t>Alim Abdulwahab</t>
+          <t>Teacher Shirehan</t>
         </is>
       </c>
       <c r="R162" t="inlineStr">
@@ -15151,12 +15159,12 @@
       </c>
       <c r="E163" t="inlineStr">
         <is>
-          <t>sec_grade_9_10_girls_face_to_face</t>
+          <t>sec_grade_9_10_boys_face_to_face</t>
         </is>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>GRADE 9 &amp; 10 GIRLS (FACE TO FACE)</t>
+          <t>GRADE 9 &amp; 10 BOYS (FACE TO FACE)</t>
         </is>
       </c>
       <c r="G163" t="inlineStr">
@@ -15176,22 +15184,22 @@
       </c>
       <c r="J163" t="inlineStr">
         <is>
-          <t>subj_social_studies</t>
+          <t>subj_qur_an</t>
         </is>
       </c>
       <c r="K163" t="inlineStr">
         <is>
-          <t>Social Science</t>
+          <t>Qur'an</t>
         </is>
       </c>
       <c r="L163" t="inlineStr">
         <is>
-          <t>tchr_sophia</t>
+          <t>tchr_abdulwahab</t>
         </is>
       </c>
       <c r="M163" t="inlineStr">
         <is>
-          <t>Teacher Sophia</t>
+          <t>Alim Abdulwahab</t>
         </is>
       </c>
       <c r="N163" t="inlineStr">
@@ -15206,12 +15214,12 @@
       </c>
       <c r="P163" t="inlineStr">
         <is>
-          <t>tchr_sophia</t>
+          <t>tchr_abdulwahab</t>
         </is>
       </c>
       <c r="Q163" t="inlineStr">
         <is>
-          <t>Teacher Sophia</t>
+          <t>Alim Abdulwahab</t>
         </is>
       </c>
       <c r="R163" t="inlineStr">
@@ -15233,31 +15241,31 @@
         </is>
       </c>
       <c r="C164" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>09:00 AM – 10:00 AM</t>
+          <t>08:00 AM – 09:00 AM</t>
         </is>
       </c>
       <c r="E164" t="inlineStr">
         <is>
-          <t>sec_grade_6_face_to_face</t>
+          <t>sec_grade_9_10_girls_face_to_face</t>
         </is>
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>GRADE  6  FACE TO FACE</t>
+          <t>GRADE 9 &amp; 10 GIRLS (FACE TO FACE)</t>
         </is>
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t>Elementary</t>
+          <t>Junior High School</t>
         </is>
       </c>
       <c r="H164" t="inlineStr">
         <is>
-          <t>Grade 6</t>
+          <t>Grade 9 &amp; 10</t>
         </is>
       </c>
       <c r="I164" t="inlineStr">
@@ -15267,22 +15275,22 @@
       </c>
       <c r="J164" t="inlineStr">
         <is>
-          <t>subj_arabic</t>
+          <t>subj_social_studies</t>
         </is>
       </c>
       <c r="K164" t="inlineStr">
         <is>
-          <t>Arabic</t>
+          <t>Social Science</t>
         </is>
       </c>
       <c r="L164" t="inlineStr">
         <is>
-          <t>tchr_ali</t>
+          <t>tchr_sophia</t>
         </is>
       </c>
       <c r="M164" t="inlineStr">
         <is>
-          <t>Ustadh Ali</t>
+          <t>Teacher Sophia</t>
         </is>
       </c>
       <c r="N164" t="inlineStr">
@@ -15297,12 +15305,12 @@
       </c>
       <c r="P164" t="inlineStr">
         <is>
-          <t>tchr_ali</t>
+          <t>tchr_sophia</t>
         </is>
       </c>
       <c r="Q164" t="inlineStr">
         <is>
-          <t>Ustadh Ali</t>
+          <t>Teacher Sophia</t>
         </is>
       </c>
       <c r="R164" t="inlineStr">
@@ -15333,12 +15341,12 @@
       </c>
       <c r="E165" t="inlineStr">
         <is>
-          <t>sec_grade_1_face_to_face</t>
+          <t>sec_grade_6_face_to_face</t>
         </is>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>GRADE 1 (FACE TO FACE)</t>
+          <t>GRADE  6  FACE TO FACE</t>
         </is>
       </c>
       <c r="G165" t="inlineStr">
@@ -15348,7 +15356,7 @@
       </c>
       <c r="H165" t="inlineStr">
         <is>
-          <t>Grade 1</t>
+          <t>Grade 6</t>
         </is>
       </c>
       <c r="I165" t="inlineStr">
@@ -15358,22 +15366,22 @@
       </c>
       <c r="J165" t="inlineStr">
         <is>
-          <t>subj_language</t>
+          <t>subj_arabic</t>
         </is>
       </c>
       <c r="K165" t="inlineStr">
         <is>
-          <t>Language</t>
+          <t>Arabic</t>
         </is>
       </c>
       <c r="L165" t="inlineStr">
         <is>
-          <t>tchr_sahdia</t>
+          <t>tchr_ali</t>
         </is>
       </c>
       <c r="M165" t="inlineStr">
         <is>
-          <t>Teacher Sahdia</t>
+          <t>Ustadh Ali</t>
         </is>
       </c>
       <c r="N165" t="inlineStr">
@@ -15388,12 +15396,12 @@
       </c>
       <c r="P165" t="inlineStr">
         <is>
-          <t>tchr_sahdia</t>
+          <t>tchr_ali</t>
         </is>
       </c>
       <c r="Q165" t="inlineStr">
         <is>
-          <t>Teacher Sahdia</t>
+          <t>Ustadh Ali</t>
         </is>
       </c>
       <c r="R165" t="inlineStr">
@@ -15424,22 +15432,22 @@
       </c>
       <c r="E166" t="inlineStr">
         <is>
-          <t>sec_grade_12_suhayb_ar_rumi</t>
+          <t>sec_grade_1_face_to_face</t>
         </is>
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>GRADE 12 - SUHAYB AR-RUMI</t>
+          <t>GRADE 1 (FACE TO FACE)</t>
         </is>
       </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t>Senior High School</t>
+          <t>Elementary</t>
         </is>
       </c>
       <c r="H166" t="inlineStr">
         <is>
-          <t>Grade 12</t>
+          <t>Grade 1</t>
         </is>
       </c>
       <c r="I166" t="inlineStr">
@@ -15449,22 +15457,22 @@
       </c>
       <c r="J166" t="inlineStr">
         <is>
-          <t>subj_mil</t>
+          <t>subj_language</t>
         </is>
       </c>
       <c r="K166" t="inlineStr">
         <is>
-          <t>MIL</t>
+          <t>Language</t>
         </is>
       </c>
       <c r="L166" t="inlineStr">
         <is>
-          <t>tchr_ethel</t>
+          <t>tchr_sahdia</t>
         </is>
       </c>
       <c r="M166" t="inlineStr">
         <is>
-          <t>Teacher Ethel</t>
+          <t>Teacher Sahdia</t>
         </is>
       </c>
       <c r="N166" t="inlineStr">
@@ -15479,12 +15487,12 @@
       </c>
       <c r="P166" t="inlineStr">
         <is>
-          <t>tchr_ethel</t>
+          <t>tchr_sahdia</t>
         </is>
       </c>
       <c r="Q166" t="inlineStr">
         <is>
-          <t>Teacher Ethel</t>
+          <t>Teacher Sahdia</t>
         </is>
       </c>
       <c r="R166" t="inlineStr">
@@ -15515,22 +15523,22 @@
       </c>
       <c r="E167" t="inlineStr">
         <is>
-          <t>sec_grade_2_face_to_face</t>
+          <t>sec_grade_12_suhayb_ar_rumi</t>
         </is>
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>GRADE 2 (FACE TO FACE)</t>
+          <t>GRADE 12 - SUHAYB AR-RUMI</t>
         </is>
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t>Elementary</t>
+          <t>Senior High School</t>
         </is>
       </c>
       <c r="H167" t="inlineStr">
         <is>
-          <t>Grade 2</t>
+          <t>Grade 12</t>
         </is>
       </c>
       <c r="I167" t="inlineStr">
@@ -15540,22 +15548,22 @@
       </c>
       <c r="J167" t="inlineStr">
         <is>
-          <t>subj_qur_an</t>
+          <t>subj_mil</t>
         </is>
       </c>
       <c r="K167" t="inlineStr">
         <is>
-          <t>Qur'an</t>
+          <t>MIL</t>
         </is>
       </c>
       <c r="L167" t="inlineStr">
         <is>
-          <t>tchr_obaydah</t>
+          <t>tchr_ethel</t>
         </is>
       </c>
       <c r="M167" t="inlineStr">
         <is>
-          <t>Ustadh Obaydah</t>
+          <t>Teacher Ethel</t>
         </is>
       </c>
       <c r="N167" t="inlineStr">
@@ -15570,12 +15578,12 @@
       </c>
       <c r="P167" t="inlineStr">
         <is>
-          <t>tchr_obaydah</t>
+          <t>tchr_ethel</t>
         </is>
       </c>
       <c r="Q167" t="inlineStr">
         <is>
-          <t>Ustadh Obaydah</t>
+          <t>Teacher Ethel</t>
         </is>
       </c>
       <c r="R167" t="inlineStr">
@@ -15606,12 +15614,12 @@
       </c>
       <c r="E168" t="inlineStr">
         <is>
-          <t>sec_grade_3_face_to_face</t>
+          <t>sec_grade_2_face_to_face</t>
         </is>
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>GRADE 3 (FACE TO FACE)</t>
+          <t>GRADE 2 (FACE TO FACE)</t>
         </is>
       </c>
       <c r="G168" t="inlineStr">
@@ -15621,7 +15629,7 @@
       </c>
       <c r="H168" t="inlineStr">
         <is>
-          <t>Grade 3</t>
+          <t>Grade 2</t>
         </is>
       </c>
       <c r="I168" t="inlineStr">
@@ -15631,22 +15639,22 @@
       </c>
       <c r="J168" t="inlineStr">
         <is>
-          <t>subj_makabansa</t>
+          <t>subj_qur_an</t>
         </is>
       </c>
       <c r="K168" t="inlineStr">
         <is>
-          <t>Makabansa</t>
+          <t>Qur'an</t>
         </is>
       </c>
       <c r="L168" t="inlineStr">
         <is>
-          <t>tchr_wendy</t>
+          <t>tchr_obaydah</t>
         </is>
       </c>
       <c r="M168" t="inlineStr">
         <is>
-          <t>Teacher Wendelyn</t>
+          <t>Ustadh Obaydah</t>
         </is>
       </c>
       <c r="N168" t="inlineStr">
@@ -15661,12 +15669,12 @@
       </c>
       <c r="P168" t="inlineStr">
         <is>
-          <t>tchr_wendy</t>
+          <t>tchr_obaydah</t>
         </is>
       </c>
       <c r="Q168" t="inlineStr">
         <is>
-          <t>Teacher Wendelyn</t>
+          <t>Ustadh Obaydah</t>
         </is>
       </c>
       <c r="R168" t="inlineStr">
@@ -15697,12 +15705,12 @@
       </c>
       <c r="E169" t="inlineStr">
         <is>
-          <t>sec_grade_4_face_to_face</t>
+          <t>sec_grade_3_face_to_face</t>
         </is>
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>GRADE 4 (FACE TO FACE)</t>
+          <t>GRADE 3 (FACE TO FACE)</t>
         </is>
       </c>
       <c r="G169" t="inlineStr">
@@ -15712,7 +15720,7 @@
       </c>
       <c r="H169" t="inlineStr">
         <is>
-          <t>Grade 4</t>
+          <t>Grade 3</t>
         </is>
       </c>
       <c r="I169" t="inlineStr">
@@ -15722,22 +15730,22 @@
       </c>
       <c r="J169" t="inlineStr">
         <is>
-          <t>subj_math</t>
+          <t>subj_makabansa</t>
         </is>
       </c>
       <c r="K169" t="inlineStr">
         <is>
-          <t>Math</t>
+          <t>Makabansa</t>
         </is>
       </c>
       <c r="L169" t="inlineStr">
         <is>
-          <t>tchr_arvin</t>
+          <t>tchr_wendy</t>
         </is>
       </c>
       <c r="M169" t="inlineStr">
         <is>
-          <t>Teacher Arvin</t>
+          <t>Teacher Wendelyn</t>
         </is>
       </c>
       <c r="N169" t="inlineStr">
@@ -15752,12 +15760,12 @@
       </c>
       <c r="P169" t="inlineStr">
         <is>
-          <t>tchr_arvin</t>
+          <t>tchr_wendy</t>
         </is>
       </c>
       <c r="Q169" t="inlineStr">
         <is>
-          <t>Teacher Arvin</t>
+          <t>Teacher Wendelyn</t>
         </is>
       </c>
       <c r="R169" t="inlineStr">
@@ -15788,12 +15796,12 @@
       </c>
       <c r="E170" t="inlineStr">
         <is>
-          <t>sec_grade_5_face_to_face</t>
+          <t>sec_grade_4_face_to_face</t>
         </is>
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>GRADE 5 (FACE TO FACE)</t>
+          <t>GRADE 4 (FACE TO FACE)</t>
         </is>
       </c>
       <c r="G170" t="inlineStr">
@@ -15803,7 +15811,7 @@
       </c>
       <c r="H170" t="inlineStr">
         <is>
-          <t>Grade 5</t>
+          <t>Grade 4</t>
         </is>
       </c>
       <c r="I170" t="inlineStr">
@@ -15813,22 +15821,22 @@
       </c>
       <c r="J170" t="inlineStr">
         <is>
-          <t>subj_english</t>
+          <t>subj_math</t>
         </is>
       </c>
       <c r="K170" t="inlineStr">
         <is>
-          <t>English</t>
+          <t>Math</t>
         </is>
       </c>
       <c r="L170" t="inlineStr">
         <is>
-          <t>tchr_jessa</t>
+          <t>tchr_arvin</t>
         </is>
       </c>
       <c r="M170" t="inlineStr">
         <is>
-          <t>Teacher Jessa</t>
+          <t>Teacher Arvin</t>
         </is>
       </c>
       <c r="N170" t="inlineStr">
@@ -15843,12 +15851,12 @@
       </c>
       <c r="P170" t="inlineStr">
         <is>
-          <t>tchr_jessa</t>
+          <t>tchr_arvin</t>
         </is>
       </c>
       <c r="Q170" t="inlineStr">
         <is>
-          <t>Teacher Jessa</t>
+          <t>Teacher Arvin</t>
         </is>
       </c>
       <c r="R170" t="inlineStr">
@@ -15879,22 +15887,22 @@
       </c>
       <c r="E171" t="inlineStr">
         <is>
-          <t>sec_grade_7_8_boys_face_to_face</t>
+          <